--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-06-12.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-06-12.xlsx
@@ -1080,7 +1080,7 @@
       </c>
       <c r="CB2" t="inlineStr">
         <is>
-          <t>2026-06-10 00:58:03</t>
+          <t>2026-06-10 03:05:10</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-06-12.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-06-12.xlsx
@@ -1080,7 +1080,7 @@
       </c>
       <c r="CB2" t="inlineStr">
         <is>
-          <t>2026-06-10 03:05:10</t>
+          <t>2026-06-10 05:12:42</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-06-12.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-06-12.xlsx
@@ -1080,7 +1080,7 @@
       </c>
       <c r="CB2" t="inlineStr">
         <is>
-          <t>2026-06-10 05:12:42</t>
+          <t>2026-06-10 07:20:08</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-06-12.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-06-12.xlsx
@@ -1080,7 +1080,7 @@
       </c>
       <c r="CB2" t="inlineStr">
         <is>
-          <t>2026-06-10 07:20:08</t>
+          <t>2026-06-10 09:31:04</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-06-12.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-06-12.xlsx
@@ -1080,7 +1080,7 @@
       </c>
       <c r="CB2" t="inlineStr">
         <is>
-          <t>2026-06-10 09:31:04</t>
+          <t>2026-06-10 11:40:19</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-06-12.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-06-12.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:CB2"/>
+  <dimension ref="A1:CB12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -833,254 +833,2794 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
+          <t>Georgian Umaglesi Liga</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>2026-06-12</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>12:00:00</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>FC Iberia 1999</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>FC Spaeri</t>
+        </is>
+      </c>
+      <c r="F2" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="G2" t="n">
+        <v>1000</v>
+      </c>
+      <c r="H2" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="I2" t="n">
+        <v>1000</v>
+      </c>
+      <c r="J2" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="K2" t="n">
+        <v>1000</v>
+      </c>
+      <c r="L2" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="M2" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="N2" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="O2" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="P2" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="Q2" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="R2" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="S2" t="n">
+        <v>2.74</v>
+      </c>
+      <c r="T2" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="U2" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="V2" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="W2" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="X2" t="n">
+        <v>1000</v>
+      </c>
+      <c r="Y2" t="n">
+        <v>1000</v>
+      </c>
+      <c r="Z2" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AA2" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AB2" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AC2" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AD2" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AE2" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AF2" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AG2" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AH2" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AI2" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AJ2" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AK2" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AL2" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AM2" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AN2" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AO2" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AP2" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AQ2" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AR2" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AS2" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AT2" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AU2" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AV2" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AW2" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AX2" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AY2" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AZ2" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BA2" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BB2" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BC2" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BD2" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BE2" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BF2" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BG2" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BH2" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BI2" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="BJ2" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BK2" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="BL2" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BM2" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="BN2" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BO2" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="BP2" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BQ2" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="BR2" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BS2" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="BT2" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BU2" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="BV2" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BW2" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="BX2" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BY2" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="BZ2" t="n">
+        <v>1000</v>
+      </c>
+      <c r="CA2" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="CB2" t="inlineStr">
+        <is>
+          <t>2026-06-10 13:52:15</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>Latvian Virsliga</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>2026-06-12</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>12:00:00</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>FK Tukums 2000</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>BFC Daugavpils</t>
+        </is>
+      </c>
+      <c r="F3" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="G3" t="n">
+        <v>1000</v>
+      </c>
+      <c r="H3" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="I3" t="n">
+        <v>1000</v>
+      </c>
+      <c r="J3" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="K3" t="n">
+        <v>1000</v>
+      </c>
+      <c r="L3" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="M3" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="N3" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="O3" t="n">
+        <v>1.23</v>
+      </c>
+      <c r="P3" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="Q3" t="n">
+        <v>1.23</v>
+      </c>
+      <c r="R3" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="S3" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="T3" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="U3" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="V3" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="W3" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="X3" t="n">
+        <v>1000</v>
+      </c>
+      <c r="Y3" t="n">
+        <v>1000</v>
+      </c>
+      <c r="Z3" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AA3" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AB3" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AC3" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AD3" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AE3" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AF3" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AG3" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AH3" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AI3" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AJ3" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AK3" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AL3" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AM3" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AN3" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AO3" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AP3" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AQ3" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AR3" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AS3" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AT3" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AU3" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AV3" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AW3" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AX3" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AY3" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AZ3" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BA3" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BB3" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BC3" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BD3" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BE3" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BF3" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BG3" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BH3" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BI3" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="BJ3" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BK3" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="BL3" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BM3" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="BN3" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BO3" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="BP3" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BQ3" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="BR3" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BS3" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="BT3" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BU3" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="BV3" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BW3" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="BX3" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BY3" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="BZ3" t="n">
+        <v>1000</v>
+      </c>
+      <c r="CA3" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="CB3" t="inlineStr">
+        <is>
+          <t>2026-06-10 13:52:15</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>Moroccan Botola Pro 1</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>2026-06-12</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>12:00:00</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>FUS Rabat</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>MAS Maghrib A Fes</t>
+        </is>
+      </c>
+      <c r="F4" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="G4" t="n">
+        <v>1000</v>
+      </c>
+      <c r="H4" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="I4" t="n">
+        <v>1000</v>
+      </c>
+      <c r="J4" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="K4" t="n">
+        <v>1000</v>
+      </c>
+      <c r="L4" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="M4" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="N4" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="O4" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="P4" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="Q4" t="n">
+        <v>1.49</v>
+      </c>
+      <c r="R4" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="S4" t="n">
+        <v>1.49</v>
+      </c>
+      <c r="T4" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="U4" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="V4" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="W4" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="X4" t="n">
+        <v>1000</v>
+      </c>
+      <c r="Y4" t="n">
+        <v>1000</v>
+      </c>
+      <c r="Z4" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AA4" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AB4" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AC4" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AD4" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AE4" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AF4" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AG4" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AH4" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AI4" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AJ4" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AK4" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AL4" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AM4" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AN4" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AO4" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AP4" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AQ4" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AR4" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AS4" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AT4" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AU4" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AV4" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AW4" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AX4" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AY4" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AZ4" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BA4" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BB4" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BC4" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BD4" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BE4" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BF4" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BG4" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BH4" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BI4" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="BJ4" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BK4" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="BL4" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BM4" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="BN4" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BO4" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="BP4" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BQ4" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="BR4" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BS4" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="BT4" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BU4" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="BV4" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BW4" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="BX4" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BY4" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="BZ4" t="n">
+        <v>1000</v>
+      </c>
+      <c r="CA4" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="CB4" t="inlineStr">
+        <is>
+          <t>2026-06-10 13:52:15</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>Moroccan Botola Pro 1</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>2026-06-12</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>12:00:00</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>Olympic Safi</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>Kawkab Marrakech</t>
+        </is>
+      </c>
+      <c r="F5" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="G5" t="n">
+        <v>1000</v>
+      </c>
+      <c r="H5" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="I5" t="n">
+        <v>1000</v>
+      </c>
+      <c r="J5" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="K5" t="n">
+        <v>950</v>
+      </c>
+      <c r="L5" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="M5" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="N5" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="O5" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="P5" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="Q5" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="R5" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="S5" t="n">
+        <v>1.54</v>
+      </c>
+      <c r="T5" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="U5" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="V5" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="W5" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="X5" t="n">
+        <v>1000</v>
+      </c>
+      <c r="Y5" t="n">
+        <v>1000</v>
+      </c>
+      <c r="Z5" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AA5" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AB5" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AC5" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AD5" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AE5" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AF5" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AG5" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AH5" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AI5" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AJ5" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AK5" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AL5" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AM5" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AN5" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AO5" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AP5" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AQ5" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AR5" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AS5" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AT5" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AU5" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AV5" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AW5" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AX5" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AY5" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AZ5" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BA5" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BB5" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BC5" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BD5" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BE5" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BF5" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BG5" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BH5" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BI5" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="BJ5" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BK5" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="BL5" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BM5" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="BN5" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BO5" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="BP5" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BQ5" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="BR5" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BS5" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="BT5" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BU5" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="BV5" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BW5" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="BX5" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BY5" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="BZ5" t="n">
+        <v>1000</v>
+      </c>
+      <c r="CA5" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="CB5" t="inlineStr">
+        <is>
+          <t>2026-06-10 13:52:15</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>Lithuanian A Lyga</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>2026-06-12</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>12:30:00</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>Panevezys</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>TransINVEST Vilnius</t>
+        </is>
+      </c>
+      <c r="F6" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="G6" t="n">
+        <v>1000</v>
+      </c>
+      <c r="H6" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="I6" t="n">
+        <v>1000</v>
+      </c>
+      <c r="J6" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="K6" t="n">
+        <v>1000</v>
+      </c>
+      <c r="L6" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="M6" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="N6" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="O6" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="P6" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="Q6" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="R6" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="S6" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="T6" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="U6" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="V6" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="W6" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="X6" t="n">
+        <v>1000</v>
+      </c>
+      <c r="Y6" t="n">
+        <v>1000</v>
+      </c>
+      <c r="Z6" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AA6" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AB6" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AC6" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AD6" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AE6" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AF6" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AG6" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AH6" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AI6" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AJ6" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AK6" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AL6" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AM6" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AN6" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AO6" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AP6" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AQ6" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AR6" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AS6" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AT6" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AU6" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AV6" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AW6" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AX6" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AY6" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AZ6" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BA6" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BB6" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BC6" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BD6" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BE6" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BF6" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BG6" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BH6" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BI6" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BJ6" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BK6" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BL6" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BM6" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BN6" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BO6" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BP6" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BQ6" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BR6" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BS6" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BT6" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BU6" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BV6" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BW6" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BX6" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BY6" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BZ6" t="n">
+        <v>1000</v>
+      </c>
+      <c r="CA6" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="CB6" t="inlineStr">
+        <is>
+          <t>2026-06-10 13:52:15</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>Lithuanian A Lyga</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>2026-06-12</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>13:00:00</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>FC Dziugas</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>Fk Siauliai</t>
+        </is>
+      </c>
+      <c r="F7" t="n">
+        <v>0</v>
+      </c>
+      <c r="G7" t="n">
+        <v>0</v>
+      </c>
+      <c r="H7" t="n">
+        <v>0</v>
+      </c>
+      <c r="I7" t="n">
+        <v>0</v>
+      </c>
+      <c r="J7" t="n">
+        <v>0</v>
+      </c>
+      <c r="K7" t="n">
+        <v>0</v>
+      </c>
+      <c r="L7" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="M7" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="N7" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="O7" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="P7" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="Q7" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="R7" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="S7" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="T7" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="U7" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="V7" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="W7" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="X7" t="n">
+        <v>1000</v>
+      </c>
+      <c r="Y7" t="n">
+        <v>1000</v>
+      </c>
+      <c r="Z7" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AA7" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AB7" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AC7" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AD7" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AE7" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AF7" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AG7" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AH7" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AI7" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AJ7" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AK7" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AL7" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AM7" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AN7" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AO7" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AP7" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AQ7" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AR7" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AS7" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AT7" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AU7" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AV7" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AW7" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AX7" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AY7" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AZ7" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BA7" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BB7" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BC7" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BD7" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BE7" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BF7" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BG7" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BH7" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BI7" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BJ7" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BK7" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BL7" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BM7" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BN7" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BO7" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BP7" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BQ7" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BR7" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BS7" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BT7" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BU7" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BV7" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BW7" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BX7" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BY7" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BZ7" t="n">
+        <v>1000</v>
+      </c>
+      <c r="CA7" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="CB7" t="inlineStr">
+        <is>
+          <t>2026-06-10 13:52:15</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>Georgian Umaglesi Liga</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>2026-06-12</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>14:00:00</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>Dinamo Batumi</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>Dila Gori</t>
+        </is>
+      </c>
+      <c r="F8" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="G8" t="n">
+        <v>1000</v>
+      </c>
+      <c r="H8" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="I8" t="n">
+        <v>1000</v>
+      </c>
+      <c r="J8" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="K8" t="n">
+        <v>1000</v>
+      </c>
+      <c r="L8" t="n">
+        <v>0</v>
+      </c>
+      <c r="M8" t="n">
+        <v>0</v>
+      </c>
+      <c r="N8" t="n">
+        <v>0</v>
+      </c>
+      <c r="O8" t="n">
+        <v>0</v>
+      </c>
+      <c r="P8" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="Q8" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="R8" t="n">
+        <v>0</v>
+      </c>
+      <c r="S8" t="n">
+        <v>0</v>
+      </c>
+      <c r="T8" t="n">
+        <v>0</v>
+      </c>
+      <c r="U8" t="n">
+        <v>0</v>
+      </c>
+      <c r="V8" t="n">
+        <v>0</v>
+      </c>
+      <c r="W8" t="n">
+        <v>0</v>
+      </c>
+      <c r="X8" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y8" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ8" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA8" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB8" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC8" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD8" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE8" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF8" t="n">
+        <v>0</v>
+      </c>
+      <c r="BG8" t="n">
+        <v>0</v>
+      </c>
+      <c r="BH8" t="n">
+        <v>0</v>
+      </c>
+      <c r="BI8" t="n">
+        <v>0</v>
+      </c>
+      <c r="BJ8" t="n">
+        <v>0</v>
+      </c>
+      <c r="BK8" t="n">
+        <v>0</v>
+      </c>
+      <c r="BL8" t="n">
+        <v>0</v>
+      </c>
+      <c r="BM8" t="n">
+        <v>0</v>
+      </c>
+      <c r="BN8" t="n">
+        <v>0</v>
+      </c>
+      <c r="BO8" t="n">
+        <v>0</v>
+      </c>
+      <c r="BP8" t="n">
+        <v>0</v>
+      </c>
+      <c r="BQ8" t="n">
+        <v>0</v>
+      </c>
+      <c r="BR8" t="n">
+        <v>0</v>
+      </c>
+      <c r="BS8" t="n">
+        <v>0</v>
+      </c>
+      <c r="BT8" t="n">
+        <v>0</v>
+      </c>
+      <c r="BU8" t="n">
+        <v>0</v>
+      </c>
+      <c r="BV8" t="n">
+        <v>0</v>
+      </c>
+      <c r="BW8" t="n">
+        <v>0</v>
+      </c>
+      <c r="BX8" t="n">
+        <v>0</v>
+      </c>
+      <c r="BY8" t="n">
+        <v>0</v>
+      </c>
+      <c r="BZ8" t="n">
+        <v>0</v>
+      </c>
+      <c r="CA8" t="n">
+        <v>0</v>
+      </c>
+      <c r="CB8" t="inlineStr">
+        <is>
+          <t>2026-06-10 13:52:15</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>Lithuanian A Lyga</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>2026-06-12</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>14:00:00</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>VMFD Zalgiris</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>Riteriai</t>
+        </is>
+      </c>
+      <c r="F9" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="G9" t="n">
+        <v>1000</v>
+      </c>
+      <c r="H9" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="I9" t="n">
+        <v>1000</v>
+      </c>
+      <c r="J9" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="K9" t="n">
+        <v>1000</v>
+      </c>
+      <c r="L9" t="n">
+        <v>0</v>
+      </c>
+      <c r="M9" t="n">
+        <v>0</v>
+      </c>
+      <c r="N9" t="n">
+        <v>0</v>
+      </c>
+      <c r="O9" t="n">
+        <v>0</v>
+      </c>
+      <c r="P9" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="Q9" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="R9" t="n">
+        <v>0</v>
+      </c>
+      <c r="S9" t="n">
+        <v>0</v>
+      </c>
+      <c r="T9" t="n">
+        <v>0</v>
+      </c>
+      <c r="U9" t="n">
+        <v>0</v>
+      </c>
+      <c r="V9" t="n">
+        <v>0</v>
+      </c>
+      <c r="W9" t="n">
+        <v>0</v>
+      </c>
+      <c r="X9" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y9" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ9" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA9" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB9" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC9" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD9" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE9" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF9" t="n">
+        <v>0</v>
+      </c>
+      <c r="BG9" t="n">
+        <v>0</v>
+      </c>
+      <c r="BH9" t="n">
+        <v>0</v>
+      </c>
+      <c r="BI9" t="n">
+        <v>0</v>
+      </c>
+      <c r="BJ9" t="n">
+        <v>0</v>
+      </c>
+      <c r="BK9" t="n">
+        <v>0</v>
+      </c>
+      <c r="BL9" t="n">
+        <v>0</v>
+      </c>
+      <c r="BM9" t="n">
+        <v>0</v>
+      </c>
+      <c r="BN9" t="n">
+        <v>0</v>
+      </c>
+      <c r="BO9" t="n">
+        <v>0</v>
+      </c>
+      <c r="BP9" t="n">
+        <v>0</v>
+      </c>
+      <c r="BQ9" t="n">
+        <v>0</v>
+      </c>
+      <c r="BR9" t="n">
+        <v>0</v>
+      </c>
+      <c r="BS9" t="n">
+        <v>0</v>
+      </c>
+      <c r="BT9" t="n">
+        <v>0</v>
+      </c>
+      <c r="BU9" t="n">
+        <v>0</v>
+      </c>
+      <c r="BV9" t="n">
+        <v>0</v>
+      </c>
+      <c r="BW9" t="n">
+        <v>0</v>
+      </c>
+      <c r="BX9" t="n">
+        <v>0</v>
+      </c>
+      <c r="BY9" t="n">
+        <v>0</v>
+      </c>
+      <c r="BZ9" t="n">
+        <v>0</v>
+      </c>
+      <c r="CA9" t="n">
+        <v>0</v>
+      </c>
+      <c r="CB9" t="inlineStr">
+        <is>
+          <t>2026-06-10 13:52:15</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>Moroccan Botola Pro 1</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>2026-06-12</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>14:00:00</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>CODM Meknes</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>Club R Zemamra</t>
+        </is>
+      </c>
+      <c r="F10" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="G10" t="n">
+        <v>1000</v>
+      </c>
+      <c r="H10" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="I10" t="n">
+        <v>1000</v>
+      </c>
+      <c r="J10" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="K10" t="n">
+        <v>1000</v>
+      </c>
+      <c r="L10" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="M10" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="N10" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="O10" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="P10" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="Q10" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="R10" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="S10" t="n">
+        <v>1.52</v>
+      </c>
+      <c r="T10" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="U10" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="V10" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="W10" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="X10" t="n">
+        <v>1000</v>
+      </c>
+      <c r="Y10" t="n">
+        <v>1000</v>
+      </c>
+      <c r="Z10" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AA10" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AB10" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AC10" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AD10" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AE10" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AF10" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AG10" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AH10" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AI10" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AJ10" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AK10" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AL10" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AM10" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AN10" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AO10" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AP10" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AQ10" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AR10" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AS10" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AT10" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AU10" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AV10" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AW10" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AX10" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AY10" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AZ10" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BA10" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BB10" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BC10" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BD10" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BE10" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BF10" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BG10" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BH10" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BI10" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="BJ10" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BK10" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="BL10" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BM10" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="BN10" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BO10" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="BP10" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BQ10" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="BR10" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BS10" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="BT10" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BU10" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="BV10" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BW10" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="BX10" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BY10" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="BZ10" t="n">
+        <v>1000</v>
+      </c>
+      <c r="CA10" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="CB10" t="inlineStr">
+        <is>
+          <t>2026-06-10 13:52:15</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>Moroccan Botola Pro 1</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>2026-06-12</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>14:00:00</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>DHJ El Jadida</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>Olympique Dcheira</t>
+        </is>
+      </c>
+      <c r="F11" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="G11" t="n">
+        <v>1000</v>
+      </c>
+      <c r="H11" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="I11" t="n">
+        <v>1000</v>
+      </c>
+      <c r="J11" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="K11" t="n">
+        <v>950</v>
+      </c>
+      <c r="L11" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="M11" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="N11" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="O11" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="P11" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="Q11" t="n">
+        <v>1.86</v>
+      </c>
+      <c r="R11" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="S11" t="n">
+        <v>2.96</v>
+      </c>
+      <c r="T11" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="U11" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="V11" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="W11" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="X11" t="n">
+        <v>1000</v>
+      </c>
+      <c r="Y11" t="n">
+        <v>1000</v>
+      </c>
+      <c r="Z11" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AA11" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AB11" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AC11" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AD11" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AE11" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AF11" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AG11" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AH11" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AI11" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AJ11" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AK11" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AL11" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AM11" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AN11" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AO11" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AP11" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AQ11" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AR11" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AS11" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AT11" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AU11" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AV11" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AW11" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AX11" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AY11" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AZ11" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BA11" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BB11" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BC11" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BD11" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BE11" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BF11" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BG11" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BH11" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BI11" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="BJ11" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BK11" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="BL11" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BM11" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="BN11" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BO11" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="BP11" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BQ11" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="BR11" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BS11" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="BT11" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BU11" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="BV11" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BW11" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="BX11" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BY11" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="BZ11" t="n">
+        <v>1000</v>
+      </c>
+      <c r="CA11" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="CB11" t="inlineStr">
+        <is>
+          <t>2026-06-10 13:52:15</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
           <t>Brazilian Serie B</t>
         </is>
       </c>
-      <c r="B2" t="inlineStr">
+      <c r="B12" t="inlineStr">
         <is>
           <t>2026-06-12</t>
         </is>
       </c>
-      <c r="C2" t="inlineStr">
+      <c r="C12" t="inlineStr">
         <is>
           <t>19:00:00</t>
         </is>
       </c>
-      <c r="D2" t="inlineStr">
+      <c r="D12" t="inlineStr">
         <is>
           <t>Atletico GO</t>
         </is>
       </c>
-      <c r="E2" t="inlineStr">
+      <c r="E12" t="inlineStr">
         <is>
           <t>CRB</t>
         </is>
       </c>
-      <c r="F2" t="n">
-        <v>0</v>
-      </c>
-      <c r="G2" t="n">
-        <v>0</v>
-      </c>
-      <c r="H2" t="n">
-        <v>0</v>
-      </c>
-      <c r="I2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J2" t="n">
-        <v>0</v>
-      </c>
-      <c r="K2" t="n">
-        <v>0</v>
-      </c>
-      <c r="L2" t="n">
-        <v>0</v>
-      </c>
-      <c r="M2" t="n">
-        <v>0</v>
-      </c>
-      <c r="N2" t="n">
-        <v>0</v>
-      </c>
-      <c r="O2" t="n">
-        <v>0</v>
-      </c>
-      <c r="P2" t="n">
+      <c r="F12" t="n">
+        <v>0</v>
+      </c>
+      <c r="G12" t="n">
+        <v>0</v>
+      </c>
+      <c r="H12" t="n">
+        <v>0</v>
+      </c>
+      <c r="I12" t="n">
+        <v>0</v>
+      </c>
+      <c r="J12" t="n">
+        <v>0</v>
+      </c>
+      <c r="K12" t="n">
+        <v>0</v>
+      </c>
+      <c r="L12" t="n">
+        <v>0</v>
+      </c>
+      <c r="M12" t="n">
+        <v>0</v>
+      </c>
+      <c r="N12" t="n">
+        <v>0</v>
+      </c>
+      <c r="O12" t="n">
+        <v>0</v>
+      </c>
+      <c r="P12" t="n">
         <v>1.25</v>
       </c>
-      <c r="Q2" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="R2" t="n">
-        <v>0</v>
-      </c>
-      <c r="S2" t="n">
-        <v>0</v>
-      </c>
-      <c r="T2" t="n">
-        <v>0</v>
-      </c>
-      <c r="U2" t="n">
-        <v>0</v>
-      </c>
-      <c r="V2" t="n">
-        <v>0</v>
-      </c>
-      <c r="W2" t="n">
-        <v>0</v>
-      </c>
-      <c r="X2" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y2" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AN2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AO2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AQ2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AR2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AS2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AT2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AU2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AV2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AW2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AX2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AY2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AZ2" t="n">
-        <v>0</v>
-      </c>
-      <c r="BA2" t="n">
-        <v>0</v>
-      </c>
-      <c r="BB2" t="n">
-        <v>0</v>
-      </c>
-      <c r="BC2" t="n">
-        <v>0</v>
-      </c>
-      <c r="BD2" t="n">
-        <v>0</v>
-      </c>
-      <c r="BE2" t="n">
-        <v>0</v>
-      </c>
-      <c r="BF2" t="n">
-        <v>0</v>
-      </c>
-      <c r="BG2" t="n">
-        <v>0</v>
-      </c>
-      <c r="BH2" t="n">
-        <v>0</v>
-      </c>
-      <c r="BI2" t="n">
-        <v>0</v>
-      </c>
-      <c r="BJ2" t="n">
-        <v>0</v>
-      </c>
-      <c r="BK2" t="n">
-        <v>0</v>
-      </c>
-      <c r="BL2" t="n">
-        <v>0</v>
-      </c>
-      <c r="BM2" t="n">
-        <v>0</v>
-      </c>
-      <c r="BN2" t="n">
-        <v>0</v>
-      </c>
-      <c r="BO2" t="n">
-        <v>0</v>
-      </c>
-      <c r="BP2" t="n">
-        <v>0</v>
-      </c>
-      <c r="BQ2" t="n">
-        <v>0</v>
-      </c>
-      <c r="BR2" t="n">
-        <v>0</v>
-      </c>
-      <c r="BS2" t="n">
-        <v>0</v>
-      </c>
-      <c r="BT2" t="n">
-        <v>0</v>
-      </c>
-      <c r="BU2" t="n">
-        <v>0</v>
-      </c>
-      <c r="BV2" t="n">
-        <v>0</v>
-      </c>
-      <c r="BW2" t="n">
-        <v>0</v>
-      </c>
-      <c r="BX2" t="n">
-        <v>0</v>
-      </c>
-      <c r="BY2" t="n">
-        <v>0</v>
-      </c>
-      <c r="BZ2" t="n">
-        <v>0</v>
-      </c>
-      <c r="CA2" t="n">
-        <v>0</v>
-      </c>
-      <c r="CB2" t="inlineStr">
-        <is>
-          <t>2026-06-10 11:40:19</t>
+      <c r="Q12" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="R12" t="n">
+        <v>0</v>
+      </c>
+      <c r="S12" t="n">
+        <v>0</v>
+      </c>
+      <c r="T12" t="n">
+        <v>0</v>
+      </c>
+      <c r="U12" t="n">
+        <v>0</v>
+      </c>
+      <c r="V12" t="n">
+        <v>0</v>
+      </c>
+      <c r="W12" t="n">
+        <v>0</v>
+      </c>
+      <c r="X12" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y12" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ12" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA12" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB12" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC12" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD12" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE12" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF12" t="n">
+        <v>0</v>
+      </c>
+      <c r="BG12" t="n">
+        <v>0</v>
+      </c>
+      <c r="BH12" t="n">
+        <v>0</v>
+      </c>
+      <c r="BI12" t="n">
+        <v>0</v>
+      </c>
+      <c r="BJ12" t="n">
+        <v>0</v>
+      </c>
+      <c r="BK12" t="n">
+        <v>0</v>
+      </c>
+      <c r="BL12" t="n">
+        <v>0</v>
+      </c>
+      <c r="BM12" t="n">
+        <v>0</v>
+      </c>
+      <c r="BN12" t="n">
+        <v>0</v>
+      </c>
+      <c r="BO12" t="n">
+        <v>0</v>
+      </c>
+      <c r="BP12" t="n">
+        <v>0</v>
+      </c>
+      <c r="BQ12" t="n">
+        <v>0</v>
+      </c>
+      <c r="BR12" t="n">
+        <v>0</v>
+      </c>
+      <c r="BS12" t="n">
+        <v>0</v>
+      </c>
+      <c r="BT12" t="n">
+        <v>0</v>
+      </c>
+      <c r="BU12" t="n">
+        <v>0</v>
+      </c>
+      <c r="BV12" t="n">
+        <v>0</v>
+      </c>
+      <c r="BW12" t="n">
+        <v>0</v>
+      </c>
+      <c r="BX12" t="n">
+        <v>0</v>
+      </c>
+      <c r="BY12" t="n">
+        <v>0</v>
+      </c>
+      <c r="BZ12" t="n">
+        <v>0</v>
+      </c>
+      <c r="CA12" t="n">
+        <v>0</v>
+      </c>
+      <c r="CB12" t="inlineStr">
+        <is>
+          <t>2026-06-10 13:52:15</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-06-12.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-06-12.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:CB12"/>
+  <dimension ref="A1:CB23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -869,7 +869,7 @@
         <v>1000</v>
       </c>
       <c r="J2" t="n">
-        <v>1.04</v>
+        <v>1.08</v>
       </c>
       <c r="K2" t="n">
         <v>1000</v>
@@ -881,13 +881,13 @@
         <v>1.01</v>
       </c>
       <c r="N2" t="n">
-        <v>1.26</v>
+        <v>1.28</v>
       </c>
       <c r="O2" t="n">
         <v>1.3</v>
       </c>
       <c r="P2" t="n">
-        <v>1.26</v>
+        <v>1.28</v>
       </c>
       <c r="Q2" t="n">
         <v>1.8</v>
@@ -896,7 +896,7 @@
         <v>1.18</v>
       </c>
       <c r="S2" t="n">
-        <v>2.74</v>
+        <v>2.6</v>
       </c>
       <c r="T2" t="n">
         <v>1.01</v>
@@ -908,7 +908,7 @@
         <v>1.01</v>
       </c>
       <c r="W2" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="X2" t="n">
         <v>1000</v>
@@ -1080,7 +1080,7 @@
       </c>
       <c r="CB2" t="inlineStr">
         <is>
-          <t>2026-06-10 13:52:15</t>
+          <t>2026-06-10 16:02:38</t>
         </is>
       </c>
     </row>
@@ -1117,13 +1117,13 @@
         <v>1000</v>
       </c>
       <c r="H3" t="n">
-        <v>1.04</v>
+        <v>1.09</v>
       </c>
       <c r="I3" t="n">
         <v>1000</v>
       </c>
       <c r="J3" t="n">
-        <v>1.1</v>
+        <v>1.12</v>
       </c>
       <c r="K3" t="n">
         <v>1000</v>
@@ -1135,13 +1135,13 @@
         <v>1.01</v>
       </c>
       <c r="N3" t="n">
-        <v>1.3</v>
+        <v>1.32</v>
       </c>
       <c r="O3" t="n">
-        <v>1.23</v>
+        <v>1.22</v>
       </c>
       <c r="P3" t="n">
-        <v>1.3</v>
+        <v>1.32</v>
       </c>
       <c r="Q3" t="n">
         <v>1.23</v>
@@ -1150,7 +1150,7 @@
         <v>1.18</v>
       </c>
       <c r="S3" t="n">
-        <v>2.5</v>
+        <v>2.46</v>
       </c>
       <c r="T3" t="n">
         <v>1.11</v>
@@ -1162,7 +1162,7 @@
         <v>1.01</v>
       </c>
       <c r="W3" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="X3" t="n">
         <v>1000</v>
@@ -1334,7 +1334,7 @@
       </c>
       <c r="CB3" t="inlineStr">
         <is>
-          <t>2026-06-10 13:52:15</t>
+          <t>2026-06-10 16:02:38</t>
         </is>
       </c>
     </row>
@@ -1377,7 +1377,7 @@
         <v>1000</v>
       </c>
       <c r="J4" t="n">
-        <v>1.04</v>
+        <v>1.08</v>
       </c>
       <c r="K4" t="n">
         <v>1000</v>
@@ -1392,7 +1392,7 @@
         <v>1.24</v>
       </c>
       <c r="O4" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="P4" t="n">
         <v>1.24</v>
@@ -1413,10 +1413,10 @@
         <v>1.11</v>
       </c>
       <c r="V4" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="W4" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="X4" t="n">
         <v>1000</v>
@@ -1588,7 +1588,7 @@
       </c>
       <c r="CB4" t="inlineStr">
         <is>
-          <t>2026-06-10 13:52:15</t>
+          <t>2026-06-10 16:02:38</t>
         </is>
       </c>
     </row>
@@ -1631,10 +1631,10 @@
         <v>1000</v>
       </c>
       <c r="J5" t="n">
-        <v>1.02</v>
+        <v>1.04</v>
       </c>
       <c r="K5" t="n">
-        <v>950</v>
+        <v>1000</v>
       </c>
       <c r="L5" t="n">
         <v>1.01</v>
@@ -1646,7 +1646,7 @@
         <v>1.25</v>
       </c>
       <c r="O5" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="P5" t="n">
         <v>1.24</v>
@@ -1658,7 +1658,7 @@
         <v>1.18</v>
       </c>
       <c r="S5" t="n">
-        <v>1.54</v>
+        <v>1.53</v>
       </c>
       <c r="T5" t="n">
         <v>1.11</v>
@@ -1667,10 +1667,10 @@
         <v>1.11</v>
       </c>
       <c r="V5" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="W5" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="X5" t="n">
         <v>1000</v>
@@ -1842,7 +1842,7 @@
       </c>
       <c r="CB5" t="inlineStr">
         <is>
-          <t>2026-06-10 13:52:15</t>
+          <t>2026-06-10 16:02:38</t>
         </is>
       </c>
     </row>
@@ -1885,7 +1885,7 @@
         <v>1000</v>
       </c>
       <c r="J6" t="n">
-        <v>1.04</v>
+        <v>1.08</v>
       </c>
       <c r="K6" t="n">
         <v>1000</v>
@@ -1897,7 +1897,7 @@
         <v>1.01</v>
       </c>
       <c r="N6" t="n">
-        <v>1.24</v>
+        <v>1.25</v>
       </c>
       <c r="O6" t="n">
         <v>1.22</v>
@@ -1906,7 +1906,7 @@
         <v>1.24</v>
       </c>
       <c r="Q6" t="n">
-        <v>1.22</v>
+        <v>1.21</v>
       </c>
       <c r="R6" t="n">
         <v>1.18</v>
@@ -1915,16 +1915,16 @@
         <v>1.22</v>
       </c>
       <c r="T6" t="n">
-        <v>1.01</v>
+        <v>1.11</v>
       </c>
       <c r="U6" t="n">
-        <v>1.01</v>
+        <v>1.11</v>
       </c>
       <c r="V6" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="W6" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="X6" t="n">
         <v>1000</v>
@@ -1981,52 +1981,52 @@
         <v>1000</v>
       </c>
       <c r="AP6" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AQ6" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AR6" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AS6" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AT6" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AU6" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AV6" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AW6" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AX6" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AY6" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AZ6" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BA6" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BB6" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BC6" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BD6" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BE6" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BF6" t="n">
         <v>1.01</v>
@@ -2038,65 +2038,65 @@
         <v>1000</v>
       </c>
       <c r="BI6" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BJ6" t="n">
         <v>1000</v>
       </c>
       <c r="BK6" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BL6" t="n">
         <v>1000</v>
       </c>
       <c r="BM6" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BN6" t="n">
         <v>1000</v>
       </c>
       <c r="BO6" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BP6" t="n">
         <v>1000</v>
       </c>
       <c r="BQ6" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BR6" t="n">
         <v>1000</v>
       </c>
       <c r="BS6" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BT6" t="n">
         <v>1000</v>
       </c>
       <c r="BU6" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BV6" t="n">
         <v>1000</v>
       </c>
       <c r="BW6" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BX6" t="n">
         <v>1000</v>
       </c>
       <c r="BY6" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BZ6" t="n">
         <v>1000</v>
       </c>
       <c r="CA6" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="CB6" t="inlineStr">
         <is>
-          <t>2026-06-10 13:52:15</t>
+          <t>2026-06-10 16:02:38</t>
         </is>
       </c>
     </row>
@@ -2127,22 +2127,22 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="G7" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="H7" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="I7" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="J7" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="K7" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="L7" t="n">
         <v>1.01</v>
@@ -2151,13 +2151,13 @@
         <v>1.01</v>
       </c>
       <c r="N7" t="n">
-        <v>1.24</v>
+        <v>1.28</v>
       </c>
       <c r="O7" t="n">
         <v>1.27</v>
       </c>
       <c r="P7" t="n">
-        <v>1.24</v>
+        <v>1.28</v>
       </c>
       <c r="Q7" t="n">
         <v>1.27</v>
@@ -2166,19 +2166,19 @@
         <v>1.18</v>
       </c>
       <c r="S7" t="n">
-        <v>1.27</v>
+        <v>2.44</v>
       </c>
       <c r="T7" t="n">
-        <v>1.01</v>
+        <v>1.11</v>
       </c>
       <c r="U7" t="n">
-        <v>1.01</v>
+        <v>1.11</v>
       </c>
       <c r="V7" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="W7" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="X7" t="n">
         <v>1000</v>
@@ -2235,52 +2235,52 @@
         <v>1000</v>
       </c>
       <c r="AP7" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AQ7" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AR7" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AS7" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AT7" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AU7" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AV7" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AW7" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AX7" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AY7" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AZ7" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BA7" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BB7" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BC7" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BD7" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BE7" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BF7" t="n">
         <v>1.01</v>
@@ -2292,72 +2292,72 @@
         <v>1000</v>
       </c>
       <c r="BI7" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BJ7" t="n">
         <v>1000</v>
       </c>
       <c r="BK7" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BL7" t="n">
         <v>1000</v>
       </c>
       <c r="BM7" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BN7" t="n">
         <v>1000</v>
       </c>
       <c r="BO7" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BP7" t="n">
         <v>1000</v>
       </c>
       <c r="BQ7" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BR7" t="n">
         <v>1000</v>
       </c>
       <c r="BS7" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BT7" t="n">
         <v>1000</v>
       </c>
       <c r="BU7" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BV7" t="n">
         <v>1000</v>
       </c>
       <c r="BW7" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BX7" t="n">
         <v>1000</v>
       </c>
       <c r="BY7" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BZ7" t="n">
         <v>1000</v>
       </c>
       <c r="CA7" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="CB7" t="inlineStr">
         <is>
-          <t>2026-06-10 13:52:15</t>
+          <t>2026-06-10 16:02:38</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Georgian Umaglesi Liga</t>
+          <t>Swedish Division 1</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -2372,12 +2372,12 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>Dinamo Batumi</t>
+          <t>Lunds BK</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Dila Gori</t>
+          <t>Ariana FC</t>
         </is>
       </c>
       <c r="F8" t="n">
@@ -2393,225 +2393,225 @@
         <v>1000</v>
       </c>
       <c r="J8" t="n">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="K8" t="n">
         <v>1000</v>
       </c>
       <c r="L8" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="M8" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="N8" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="O8" t="n">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="P8" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="Q8" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="R8" t="n">
         <v>1.24</v>
       </c>
-      <c r="Q8" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="R8" t="n">
-        <v>0</v>
-      </c>
       <c r="S8" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="T8" t="n">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="U8" t="n">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="V8" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="W8" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="X8" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Y8" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Z8" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AA8" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AB8" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AC8" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AD8" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AE8" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AF8" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AG8" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AH8" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AI8" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AJ8" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AK8" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AL8" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AM8" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AN8" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AO8" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AP8" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AQ8" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AR8" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AS8" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AT8" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AU8" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AV8" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AW8" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AX8" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AY8" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AZ8" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BA8" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BB8" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BC8" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BD8" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BE8" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BF8" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BG8" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BH8" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BI8" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BJ8" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BK8" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BL8" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BM8" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BN8" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BO8" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BP8" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BQ8" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BR8" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BS8" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BT8" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BU8" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BV8" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BW8" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BX8" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BY8" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BZ8" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="CA8" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="CB8" t="inlineStr">
         <is>
-          <t>2026-06-10 13:52:15</t>
+          <t>2026-06-10 16:02:38</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Lithuanian A Lyga</t>
+          <t>Moroccan Botola Pro 1</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -2626,12 +2626,12 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>VMFD Zalgiris</t>
+          <t>DHJ El Jadida</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Riteriai</t>
+          <t>Olympique Dcheira</t>
         </is>
       </c>
       <c r="F9" t="n">
@@ -2647,225 +2647,225 @@
         <v>1000</v>
       </c>
       <c r="J9" t="n">
-        <v>1.03</v>
+        <v>1.06</v>
       </c>
       <c r="K9" t="n">
         <v>1000</v>
       </c>
       <c r="L9" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="M9" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="N9" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="O9" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="P9" t="n">
         <v>1.24</v>
       </c>
       <c r="Q9" t="n">
-        <v>1.01</v>
+        <v>1.43</v>
       </c>
       <c r="R9" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="S9" t="n">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="T9" t="n">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="U9" t="n">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="V9" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="W9" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="X9" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Y9" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Z9" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AA9" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AB9" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AC9" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AD9" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AE9" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AF9" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AG9" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AH9" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AI9" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AJ9" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AK9" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AL9" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AM9" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AN9" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AO9" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AP9" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AQ9" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AR9" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AS9" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AT9" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AU9" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AV9" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AW9" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AX9" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AY9" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AZ9" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BA9" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BB9" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BC9" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BD9" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BE9" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BF9" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BG9" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BH9" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BI9" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="BJ9" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BK9" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="BL9" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BM9" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="BN9" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BO9" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="BP9" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BQ9" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="BR9" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BS9" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="BT9" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BU9" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="BV9" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BW9" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="BX9" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BY9" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="BZ9" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="CA9" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="CB9" t="inlineStr">
         <is>
-          <t>2026-06-10 13:52:15</t>
+          <t>2026-06-10 16:02:38</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Moroccan Botola Pro 1</t>
+          <t>Swedish Division 1</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -2880,12 +2880,12 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>CODM Meknes</t>
+          <t>Umea FC</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Club R Zemamra</t>
+          <t>Pitea</t>
         </is>
       </c>
       <c r="F10" t="n">
@@ -2913,22 +2913,22 @@
         <v>1.01</v>
       </c>
       <c r="N10" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="O10" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="P10" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="Q10" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="R10" t="n">
         <v>1.24</v>
       </c>
-      <c r="O10" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="P10" t="n">
-        <v>1.24</v>
-      </c>
-      <c r="Q10" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="R10" t="n">
-        <v>1.18</v>
-      </c>
       <c r="S10" t="n">
-        <v>1.52</v>
+        <v>1.15</v>
       </c>
       <c r="T10" t="n">
         <v>1.11</v>
@@ -3054,72 +3054,72 @@
         <v>1000</v>
       </c>
       <c r="BI10" t="n">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="BJ10" t="n">
         <v>1000</v>
       </c>
       <c r="BK10" t="n">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="BL10" t="n">
         <v>1000</v>
       </c>
       <c r="BM10" t="n">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="BN10" t="n">
         <v>1000</v>
       </c>
       <c r="BO10" t="n">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="BP10" t="n">
         <v>1000</v>
       </c>
       <c r="BQ10" t="n">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="BR10" t="n">
         <v>1000</v>
       </c>
       <c r="BS10" t="n">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="BT10" t="n">
         <v>1000</v>
       </c>
       <c r="BU10" t="n">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="BV10" t="n">
         <v>1000</v>
       </c>
       <c r="BW10" t="n">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="BX10" t="n">
         <v>1000</v>
       </c>
       <c r="BY10" t="n">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="BZ10" t="n">
         <v>1000</v>
       </c>
       <c r="CA10" t="n">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="CB10" t="inlineStr">
         <is>
-          <t>2026-06-10 13:52:15</t>
+          <t>2026-06-10 16:02:38</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Moroccan Botola Pro 1</t>
+          <t>Lithuanian A Lyga</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -3134,55 +3134,55 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>DHJ El Jadida</t>
+          <t>VMFD Zalgiris</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Olympique Dcheira</t>
+          <t>Riteriai</t>
         </is>
       </c>
       <c r="F11" t="n">
-        <v>1.41</v>
+        <v>1.04</v>
       </c>
       <c r="G11" t="n">
         <v>1000</v>
       </c>
       <c r="H11" t="n">
-        <v>1.41</v>
+        <v>1.04</v>
       </c>
       <c r="I11" t="n">
         <v>1000</v>
       </c>
       <c r="J11" t="n">
-        <v>1.04</v>
+        <v>1.06</v>
       </c>
       <c r="K11" t="n">
-        <v>950</v>
+        <v>1000</v>
       </c>
       <c r="L11" t="n">
         <v>1.01</v>
       </c>
       <c r="M11" t="n">
-        <v>1.09</v>
+        <v>1.01</v>
       </c>
       <c r="N11" t="n">
-        <v>1.25</v>
+        <v>1.26</v>
       </c>
       <c r="O11" t="n">
-        <v>1.4</v>
+        <v>1.12</v>
       </c>
       <c r="P11" t="n">
-        <v>1.24</v>
+        <v>1.26</v>
       </c>
       <c r="Q11" t="n">
-        <v>1.86</v>
+        <v>1.11</v>
       </c>
       <c r="R11" t="n">
         <v>1.18</v>
       </c>
       <c r="S11" t="n">
-        <v>2.96</v>
+        <v>1.12</v>
       </c>
       <c r="T11" t="n">
         <v>1.11</v>
@@ -3251,52 +3251,52 @@
         <v>1000</v>
       </c>
       <c r="AP11" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AQ11" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AR11" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AS11" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AT11" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AU11" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AV11" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AW11" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AX11" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AY11" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AZ11" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BA11" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BB11" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BC11" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BD11" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BE11" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BF11" t="n">
         <v>1.01</v>
@@ -3308,319 +3308,3113 @@
         <v>1000</v>
       </c>
       <c r="BI11" t="n">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="BJ11" t="n">
         <v>1000</v>
       </c>
       <c r="BK11" t="n">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="BL11" t="n">
         <v>1000</v>
       </c>
       <c r="BM11" t="n">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="BN11" t="n">
         <v>1000</v>
       </c>
       <c r="BO11" t="n">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="BP11" t="n">
         <v>1000</v>
       </c>
       <c r="BQ11" t="n">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="BR11" t="n">
         <v>1000</v>
       </c>
       <c r="BS11" t="n">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="BT11" t="n">
         <v>1000</v>
       </c>
       <c r="BU11" t="n">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="BV11" t="n">
         <v>1000</v>
       </c>
       <c r="BW11" t="n">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="BX11" t="n">
         <v>1000</v>
       </c>
       <c r="BY11" t="n">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="BZ11" t="n">
         <v>1000</v>
       </c>
       <c r="CA11" t="n">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="CB11" t="inlineStr">
         <is>
-          <t>2026-06-10 13:52:15</t>
+          <t>2026-06-10 16:02:38</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
+          <t>Georgian Umaglesi Liga</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>2026-06-12</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>14:00:00</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>Dinamo Batumi</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>Dila Gori</t>
+        </is>
+      </c>
+      <c r="F12" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="G12" t="n">
+        <v>1000</v>
+      </c>
+      <c r="H12" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="I12" t="n">
+        <v>1000</v>
+      </c>
+      <c r="J12" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="K12" t="n">
+        <v>1000</v>
+      </c>
+      <c r="L12" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="M12" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="N12" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="O12" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="P12" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="Q12" t="n">
+        <v>1.87</v>
+      </c>
+      <c r="R12" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="S12" t="n">
+        <v>2.84</v>
+      </c>
+      <c r="T12" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="U12" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="V12" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="W12" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="X12" t="n">
+        <v>1000</v>
+      </c>
+      <c r="Y12" t="n">
+        <v>1000</v>
+      </c>
+      <c r="Z12" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AA12" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AB12" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AC12" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AD12" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AE12" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AF12" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AG12" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AH12" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AI12" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AJ12" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AK12" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AL12" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AM12" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AN12" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AO12" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AP12" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AQ12" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AR12" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AS12" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AT12" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AU12" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AV12" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AW12" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AX12" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AY12" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AZ12" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BA12" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BB12" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BC12" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BD12" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BE12" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BF12" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BG12" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BH12" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BI12" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BJ12" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BK12" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BL12" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BM12" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BN12" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BO12" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BP12" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BQ12" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BR12" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BS12" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BT12" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BU12" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BV12" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BW12" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BX12" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BY12" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BZ12" t="n">
+        <v>1000</v>
+      </c>
+      <c r="CA12" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="CB12" t="inlineStr">
+        <is>
+          <t>2026-06-10 16:02:38</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>Moroccan Botola Pro 1</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>2026-06-12</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>14:00:00</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>CODM Meknes</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>Club R Zemamra</t>
+        </is>
+      </c>
+      <c r="F13" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="G13" t="n">
+        <v>1000</v>
+      </c>
+      <c r="H13" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="I13" t="n">
+        <v>1000</v>
+      </c>
+      <c r="J13" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="K13" t="n">
+        <v>1000</v>
+      </c>
+      <c r="L13" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="M13" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="N13" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="O13" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="P13" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="Q13" t="n">
+        <v>1.51</v>
+      </c>
+      <c r="R13" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="S13" t="n">
+        <v>1.52</v>
+      </c>
+      <c r="T13" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="U13" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="V13" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="W13" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="X13" t="n">
+        <v>1000</v>
+      </c>
+      <c r="Y13" t="n">
+        <v>1000</v>
+      </c>
+      <c r="Z13" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AA13" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AB13" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AC13" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AD13" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AE13" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AF13" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AG13" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AH13" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AI13" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AJ13" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AK13" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AL13" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AM13" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AN13" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AO13" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AP13" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AQ13" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AR13" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AS13" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AT13" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AU13" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AV13" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AW13" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AX13" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AY13" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AZ13" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BA13" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BB13" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BC13" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BD13" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BE13" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BF13" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BG13" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BH13" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BI13" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="BJ13" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BK13" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="BL13" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BM13" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="BN13" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BO13" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="BP13" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BQ13" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="BR13" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BS13" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="BT13" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BU13" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="BV13" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BW13" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="BX13" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BY13" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="BZ13" t="n">
+        <v>1000</v>
+      </c>
+      <c r="CA13" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="CB13" t="inlineStr">
+        <is>
+          <t>2026-06-10 16:02:38</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>Irish Division 1</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>2026-06-12</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>15:45:00</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>Finn Harps</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>UCD</t>
+        </is>
+      </c>
+      <c r="F14" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="G14" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="H14" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="I14" t="n">
+        <v>2.08</v>
+      </c>
+      <c r="J14" t="n">
+        <v>3.65</v>
+      </c>
+      <c r="K14" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="L14" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="M14" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="N14" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="O14" t="n">
+        <v>1.23</v>
+      </c>
+      <c r="P14" t="n">
+        <v>2.08</v>
+      </c>
+      <c r="Q14" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="R14" t="n">
+        <v>1.34</v>
+      </c>
+      <c r="S14" t="n">
+        <v>2.56</v>
+      </c>
+      <c r="T14" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="U14" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="V14" t="n">
+        <v>1.92</v>
+      </c>
+      <c r="W14" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="X14" t="n">
+        <v>1000</v>
+      </c>
+      <c r="Y14" t="n">
+        <v>1000</v>
+      </c>
+      <c r="Z14" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AA14" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AB14" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AC14" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AD14" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AE14" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AF14" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AG14" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AH14" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AI14" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AJ14" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AK14" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AL14" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AM14" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AN14" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AO14" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AP14" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AQ14" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AR14" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AS14" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AT14" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AU14" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AV14" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AW14" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AX14" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AY14" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AZ14" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BA14" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BB14" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BC14" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BD14" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BE14" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BF14" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BG14" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BH14" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BI14" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BJ14" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BK14" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BL14" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BM14" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BN14" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BO14" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BP14" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BQ14" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BR14" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BS14" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BT14" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BU14" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BV14" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BW14" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BX14" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BY14" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BZ14" t="n">
+        <v>1000</v>
+      </c>
+      <c r="CA14" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="CB14" t="inlineStr">
+        <is>
+          <t>2026-06-10 16:02:38</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>Irish Division 1</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>2026-06-12</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>15:45:00</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>Kerry FC</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>Athlone Town</t>
+        </is>
+      </c>
+      <c r="F15" t="n">
+        <v>2.28</v>
+      </c>
+      <c r="G15" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="H15" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="I15" t="n">
+        <v>3.65</v>
+      </c>
+      <c r="J15" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="K15" t="n">
+        <v>3.65</v>
+      </c>
+      <c r="L15" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="M15" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="N15" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="O15" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="P15" t="n">
+        <v>1.81</v>
+      </c>
+      <c r="Q15" t="n">
+        <v>2.04</v>
+      </c>
+      <c r="R15" t="n">
+        <v>1.21</v>
+      </c>
+      <c r="S15" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="T15" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="U15" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="V15" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="W15" t="n">
+        <v>1.66</v>
+      </c>
+      <c r="X15" t="n">
+        <v>1000</v>
+      </c>
+      <c r="Y15" t="n">
+        <v>1000</v>
+      </c>
+      <c r="Z15" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AA15" t="n">
+        <v>65</v>
+      </c>
+      <c r="AB15" t="n">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="AC15" t="n">
+        <v>8</v>
+      </c>
+      <c r="AD15" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AE15" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AF15" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AG15" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AH15" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AI15" t="n">
+        <v>55</v>
+      </c>
+      <c r="AJ15" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AK15" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AL15" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AM15" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AN15" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AO15" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AP15" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="AQ15" t="n">
+        <v>9</v>
+      </c>
+      <c r="AR15" t="n">
+        <v>17</v>
+      </c>
+      <c r="AS15" t="n">
+        <v>44</v>
+      </c>
+      <c r="AT15" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="AU15" t="n">
+        <v>5.8</v>
+      </c>
+      <c r="AV15" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AW15" t="n">
+        <v>30</v>
+      </c>
+      <c r="AX15" t="n">
+        <v>11</v>
+      </c>
+      <c r="AY15" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="AZ15" t="n">
+        <v>13</v>
+      </c>
+      <c r="BA15" t="n">
+        <v>38</v>
+      </c>
+      <c r="BB15" t="n">
+        <v>23</v>
+      </c>
+      <c r="BC15" t="n">
+        <v>19.5</v>
+      </c>
+      <c r="BD15" t="n">
+        <v>30</v>
+      </c>
+      <c r="BE15" t="n">
+        <v>70</v>
+      </c>
+      <c r="BF15" t="n">
+        <v>16</v>
+      </c>
+      <c r="BG15" t="n">
+        <v>30</v>
+      </c>
+      <c r="BH15" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="BI15" t="n">
+        <v>2.94</v>
+      </c>
+      <c r="BJ15" t="n">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="BK15" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="BL15" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BM15" t="n">
+        <v>22</v>
+      </c>
+      <c r="BN15" t="n">
+        <v>5.3</v>
+      </c>
+      <c r="BO15" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="BP15" t="n">
+        <v>18.5</v>
+      </c>
+      <c r="BQ15" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="BR15" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BS15" t="n">
+        <v>28</v>
+      </c>
+      <c r="BT15" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="BU15" t="n">
+        <v>5.7</v>
+      </c>
+      <c r="BV15" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BW15" t="n">
+        <v>24</v>
+      </c>
+      <c r="BX15" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BY15" t="n">
+        <v>34</v>
+      </c>
+      <c r="BZ15" t="n">
+        <v>1000</v>
+      </c>
+      <c r="CA15" t="n">
+        <v>25</v>
+      </c>
+      <c r="CB15" t="inlineStr">
+        <is>
+          <t>2026-06-10 16:02:38</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>Irish Division 1</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>2026-06-12</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>15:45:00</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>Treaty United</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>Bray Wanderers</t>
+        </is>
+      </c>
+      <c r="F16" t="n">
+        <v>4</v>
+      </c>
+      <c r="G16" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="H16" t="n">
+        <v>1.84</v>
+      </c>
+      <c r="I16" t="n">
+        <v>2.04</v>
+      </c>
+      <c r="J16" t="n">
+        <v>3.65</v>
+      </c>
+      <c r="K16" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="L16" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="M16" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="N16" t="n">
+        <v>2.04</v>
+      </c>
+      <c r="O16" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="P16" t="n">
+        <v>2.04</v>
+      </c>
+      <c r="Q16" t="n">
+        <v>1.77</v>
+      </c>
+      <c r="R16" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="S16" t="n">
+        <v>2.68</v>
+      </c>
+      <c r="T16" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="U16" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="V16" t="n">
+        <v>1.96</v>
+      </c>
+      <c r="W16" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="X16" t="n">
+        <v>1000</v>
+      </c>
+      <c r="Y16" t="n">
+        <v>1000</v>
+      </c>
+      <c r="Z16" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AA16" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AB16" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AC16" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AD16" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AE16" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AF16" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AG16" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AH16" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AI16" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AJ16" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AK16" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AL16" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AM16" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AN16" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AO16" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AP16" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AQ16" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AR16" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AS16" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AT16" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AU16" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AV16" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AW16" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AX16" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AY16" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AZ16" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BA16" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BB16" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BC16" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BD16" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BE16" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BF16" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BG16" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BH16" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="BI16" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="BJ16" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="BK16" t="n">
+        <v>5.9</v>
+      </c>
+      <c r="BL16" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BM16" t="n">
+        <v>21</v>
+      </c>
+      <c r="BN16" t="n">
+        <v>11</v>
+      </c>
+      <c r="BO16" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="BP16" t="n">
+        <v>50</v>
+      </c>
+      <c r="BQ16" t="n">
+        <v>20</v>
+      </c>
+      <c r="BR16" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BS16" t="n">
+        <v>21</v>
+      </c>
+      <c r="BT16" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="BU16" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="BV16" t="n">
+        <v>18.5</v>
+      </c>
+      <c r="BW16" t="n">
+        <v>8</v>
+      </c>
+      <c r="BX16" t="n">
+        <v>38</v>
+      </c>
+      <c r="BY16" t="n">
+        <v>15</v>
+      </c>
+      <c r="BZ16" t="n">
+        <v>30</v>
+      </c>
+      <c r="CA16" t="n">
+        <v>12</v>
+      </c>
+      <c r="CB16" t="inlineStr">
+        <is>
+          <t>2026-06-10 16:02:38</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>Irish Division 1</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>2026-06-12</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>15:45:00</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>Wexford F.C</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>Cork City</t>
+        </is>
+      </c>
+      <c r="F17" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="G17" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="H17" t="n">
+        <v>1.82</v>
+      </c>
+      <c r="I17" t="n">
+        <v>2.02</v>
+      </c>
+      <c r="J17" t="n">
+        <v>3.55</v>
+      </c>
+      <c r="K17" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="L17" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="M17" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="N17" t="n">
+        <v>3.55</v>
+      </c>
+      <c r="O17" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="P17" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="Q17" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="R17" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="S17" t="n">
+        <v>2.96</v>
+      </c>
+      <c r="T17" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="U17" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="V17" t="n">
+        <v>1.98</v>
+      </c>
+      <c r="W17" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="X17" t="n">
+        <v>1000</v>
+      </c>
+      <c r="Y17" t="n">
+        <v>1000</v>
+      </c>
+      <c r="Z17" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AA17" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AB17" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AC17" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AD17" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AE17" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AF17" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AG17" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AH17" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AI17" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AJ17" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AK17" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AL17" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AM17" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AN17" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AO17" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AP17" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AQ17" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AR17" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AS17" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AT17" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AU17" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AV17" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AW17" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AX17" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AY17" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AZ17" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BA17" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BB17" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BC17" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BD17" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BE17" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BF17" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BG17" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BH17" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="BI17" t="n">
+        <v>2.72</v>
+      </c>
+      <c r="BJ17" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="BK17" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="BL17" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BM17" t="n">
+        <v>21</v>
+      </c>
+      <c r="BN17" t="n">
+        <v>11</v>
+      </c>
+      <c r="BO17" t="n">
+        <v>5.3</v>
+      </c>
+      <c r="BP17" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BQ17" t="n">
+        <v>21</v>
+      </c>
+      <c r="BR17" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BS17" t="n">
+        <v>21</v>
+      </c>
+      <c r="BT17" t="n">
+        <v>6</v>
+      </c>
+      <c r="BU17" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="BV17" t="n">
+        <v>18</v>
+      </c>
+      <c r="BW17" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="BX17" t="n">
+        <v>38</v>
+      </c>
+      <c r="BY17" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="BZ17" t="n">
+        <v>32</v>
+      </c>
+      <c r="CA17" t="n">
+        <v>15</v>
+      </c>
+      <c r="CB17" t="inlineStr">
+        <is>
+          <t>2026-06-10 16:02:38</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>Irish Premier Division</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>2026-06-12</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>15:45:00</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>Derry City</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>Bohemians</t>
+        </is>
+      </c>
+      <c r="F18" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="G18" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="H18" t="n">
+        <v>2.42</v>
+      </c>
+      <c r="I18" t="n">
+        <v>2.64</v>
+      </c>
+      <c r="J18" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="K18" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="L18" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="M18" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="N18" t="n">
+        <v>3</v>
+      </c>
+      <c r="O18" t="n">
+        <v>1.39</v>
+      </c>
+      <c r="P18" t="n">
+        <v>1.71</v>
+      </c>
+      <c r="Q18" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="R18" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="S18" t="n">
+        <v>3.55</v>
+      </c>
+      <c r="T18" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="U18" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="V18" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="W18" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="X18" t="n">
+        <v>15</v>
+      </c>
+      <c r="Y18" t="n">
+        <v>12</v>
+      </c>
+      <c r="Z18" t="n">
+        <v>21</v>
+      </c>
+      <c r="AA18" t="n">
+        <v>50</v>
+      </c>
+      <c r="AB18" t="n">
+        <v>15</v>
+      </c>
+      <c r="AC18" t="n">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="AD18" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="AE18" t="n">
+        <v>36</v>
+      </c>
+      <c r="AF18" t="n">
+        <v>30</v>
+      </c>
+      <c r="AG18" t="n">
+        <v>19</v>
+      </c>
+      <c r="AH18" t="n">
+        <v>25</v>
+      </c>
+      <c r="AI18" t="n">
+        <v>55</v>
+      </c>
+      <c r="AJ18" t="n">
+        <v>80</v>
+      </c>
+      <c r="AK18" t="n">
+        <v>55</v>
+      </c>
+      <c r="AL18" t="n">
+        <v>75</v>
+      </c>
+      <c r="AM18" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AN18" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AO18" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AP18" t="n">
+        <v>2.52</v>
+      </c>
+      <c r="AQ18" t="n">
+        <v>2.42</v>
+      </c>
+      <c r="AR18" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AS18" t="n">
+        <v>26</v>
+      </c>
+      <c r="AT18" t="n">
+        <v>2.52</v>
+      </c>
+      <c r="AU18" t="n">
+        <v>2.32</v>
+      </c>
+      <c r="AV18" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="AW18" t="n">
+        <v>20</v>
+      </c>
+      <c r="AX18" t="n">
+        <v>16</v>
+      </c>
+      <c r="AY18" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AZ18" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="BA18" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="BB18" t="n">
+        <v>2.92</v>
+      </c>
+      <c r="BC18" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="BD18" t="n">
+        <v>2.92</v>
+      </c>
+      <c r="BE18" t="n">
+        <v>3</v>
+      </c>
+      <c r="BF18" t="n">
+        <v>3</v>
+      </c>
+      <c r="BG18" t="n">
+        <v>3</v>
+      </c>
+      <c r="BH18" t="n">
+        <v>3.55</v>
+      </c>
+      <c r="BI18" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="BJ18" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="BK18" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="BL18" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BM18" t="n">
+        <v>21</v>
+      </c>
+      <c r="BN18" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="BO18" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="BP18" t="n">
+        <v>38</v>
+      </c>
+      <c r="BQ18" t="n">
+        <v>17.5</v>
+      </c>
+      <c r="BR18" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BS18" t="n">
+        <v>21</v>
+      </c>
+      <c r="BT18" t="n">
+        <v>7</v>
+      </c>
+      <c r="BU18" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="BV18" t="n">
+        <v>28</v>
+      </c>
+      <c r="BW18" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="BX18" t="n">
+        <v>50</v>
+      </c>
+      <c r="BY18" t="n">
+        <v>21</v>
+      </c>
+      <c r="BZ18" t="n">
+        <v>48</v>
+      </c>
+      <c r="CA18" t="n">
+        <v>21</v>
+      </c>
+      <c r="CB18" t="inlineStr">
+        <is>
+          <t>2026-06-10 16:02:38</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>Irish Premier Division</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>2026-06-12</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>15:45:00</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>Waterford</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>Sligo Rovers</t>
+        </is>
+      </c>
+      <c r="F19" t="n">
+        <v>2.24</v>
+      </c>
+      <c r="G19" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="H19" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="I19" t="n">
+        <v>3.55</v>
+      </c>
+      <c r="J19" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="K19" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="L19" t="n">
+        <v>1.34</v>
+      </c>
+      <c r="M19" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="N19" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="O19" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="P19" t="n">
+        <v>2.02</v>
+      </c>
+      <c r="Q19" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="R19" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="S19" t="n">
+        <v>2.72</v>
+      </c>
+      <c r="T19" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="U19" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="V19" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="W19" t="n">
+        <v>1.71</v>
+      </c>
+      <c r="X19" t="n">
+        <v>22</v>
+      </c>
+      <c r="Y19" t="n">
+        <v>19.5</v>
+      </c>
+      <c r="Z19" t="n">
+        <v>34</v>
+      </c>
+      <c r="AA19" t="n">
+        <v>80</v>
+      </c>
+      <c r="AB19" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="AC19" t="n">
+        <v>12</v>
+      </c>
+      <c r="AD19" t="n">
+        <v>20</v>
+      </c>
+      <c r="AE19" t="n">
+        <v>50</v>
+      </c>
+      <c r="AF19" t="n">
+        <v>22</v>
+      </c>
+      <c r="AG19" t="n">
+        <v>16</v>
+      </c>
+      <c r="AH19" t="n">
+        <v>23</v>
+      </c>
+      <c r="AI19" t="n">
+        <v>60</v>
+      </c>
+      <c r="AJ19" t="n">
+        <v>42</v>
+      </c>
+      <c r="AK19" t="n">
+        <v>32</v>
+      </c>
+      <c r="AL19" t="n">
+        <v>50</v>
+      </c>
+      <c r="AM19" t="n">
+        <v>100</v>
+      </c>
+      <c r="AN19" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AO19" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AP19" t="n">
+        <v>2.28</v>
+      </c>
+      <c r="AQ19" t="n">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="AR19" t="n">
+        <v>17</v>
+      </c>
+      <c r="AS19" t="n">
+        <v>2.48</v>
+      </c>
+      <c r="AT19" t="n">
+        <v>9</v>
+      </c>
+      <c r="AU19" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="AV19" t="n">
+        <v>10</v>
+      </c>
+      <c r="AW19" t="n">
+        <v>24</v>
+      </c>
+      <c r="AX19" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AY19" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="AZ19" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="BA19" t="n">
+        <v>2.44</v>
+      </c>
+      <c r="BB19" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="BC19" t="n">
+        <v>2.36</v>
+      </c>
+      <c r="BD19" t="n">
+        <v>2.42</v>
+      </c>
+      <c r="BE19" t="n">
+        <v>2.48</v>
+      </c>
+      <c r="BF19" t="n">
+        <v>2.56</v>
+      </c>
+      <c r="BG19" t="n">
+        <v>2.56</v>
+      </c>
+      <c r="BH19" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="BI19" t="n">
+        <v>2.84</v>
+      </c>
+      <c r="BJ19" t="n">
+        <v>13</v>
+      </c>
+      <c r="BK19" t="n">
+        <v>5.6</v>
+      </c>
+      <c r="BL19" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BM19" t="n">
+        <v>21</v>
+      </c>
+      <c r="BN19" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="BO19" t="n">
+        <v>3.45</v>
+      </c>
+      <c r="BP19" t="n">
+        <v>23</v>
+      </c>
+      <c r="BQ19" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="BR19" t="n">
+        <v>40</v>
+      </c>
+      <c r="BS19" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="BT19" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="BU19" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="BV19" t="n">
+        <v>38</v>
+      </c>
+      <c r="BW19" t="n">
+        <v>15</v>
+      </c>
+      <c r="BX19" t="n">
+        <v>50</v>
+      </c>
+      <c r="BY19" t="n">
+        <v>20</v>
+      </c>
+      <c r="BZ19" t="n">
+        <v>34</v>
+      </c>
+      <c r="CA19" t="n">
+        <v>14</v>
+      </c>
+      <c r="CB19" t="inlineStr">
+        <is>
+          <t>2026-06-10 16:02:38</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>Irish Premier Division</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>2026-06-12</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>15:45:00</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>St Patricks</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>Drogheda</t>
+        </is>
+      </c>
+      <c r="F20" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="G20" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="H20" t="n">
+        <v>11</v>
+      </c>
+      <c r="I20" t="n">
+        <v>15</v>
+      </c>
+      <c r="J20" t="n">
+        <v>5</v>
+      </c>
+      <c r="K20" t="n">
+        <v>5.6</v>
+      </c>
+      <c r="L20" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="M20" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="N20" t="n">
+        <v>2.06</v>
+      </c>
+      <c r="O20" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="P20" t="n">
+        <v>2.06</v>
+      </c>
+      <c r="Q20" t="n">
+        <v>1.84</v>
+      </c>
+      <c r="R20" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="S20" t="n">
+        <v>3</v>
+      </c>
+      <c r="T20" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="U20" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="V20" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="W20" t="n">
+        <v>3.45</v>
+      </c>
+      <c r="X20" t="n">
+        <v>22</v>
+      </c>
+      <c r="Y20" t="n">
+        <v>40</v>
+      </c>
+      <c r="Z20" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AA20" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AB20" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="AC20" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AD20" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AE20" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AF20" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="AG20" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AH20" t="n">
+        <v>42</v>
+      </c>
+      <c r="AI20" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AJ20" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AK20" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AL20" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AM20" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AN20" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AO20" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AP20" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="AQ20" t="n">
+        <v>21</v>
+      </c>
+      <c r="AR20" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="AS20" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="AT20" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AU20" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="AV20" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="AW20" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="AX20" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AY20" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="AZ20" t="n">
+        <v>1.39</v>
+      </c>
+      <c r="BA20" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="BB20" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="BC20" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="BD20" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="BE20" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="BF20" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="BG20" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="BH20" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BI20" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BJ20" t="n">
+        <v>18.5</v>
+      </c>
+      <c r="BK20" t="n">
+        <v>8</v>
+      </c>
+      <c r="BL20" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BM20" t="n">
+        <v>21</v>
+      </c>
+      <c r="BN20" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="BO20" t="n">
+        <v>2.54</v>
+      </c>
+      <c r="BP20" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="BQ20" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="BR20" t="n">
+        <v>40</v>
+      </c>
+      <c r="BS20" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="BT20" t="n">
+        <v>20</v>
+      </c>
+      <c r="BU20" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="BV20" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BW20" t="n">
+        <v>21</v>
+      </c>
+      <c r="BX20" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BY20" t="n">
+        <v>21</v>
+      </c>
+      <c r="BZ20" t="n">
+        <v>22</v>
+      </c>
+      <c r="CA20" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="CB20" t="inlineStr">
+        <is>
+          <t>2026-06-10 16:02:38</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>Irish Premier Division</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>2026-06-12</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>15:45:00</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>Galway Utd</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>Dundalk</t>
+        </is>
+      </c>
+      <c r="F21" t="n">
+        <v>2.82</v>
+      </c>
+      <c r="G21" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="H21" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="I21" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="J21" t="n">
+        <v>3.65</v>
+      </c>
+      <c r="K21" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="L21" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="M21" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="N21" t="n">
+        <v>2.36</v>
+      </c>
+      <c r="O21" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="P21" t="n">
+        <v>2.36</v>
+      </c>
+      <c r="Q21" t="n">
+        <v>1.56</v>
+      </c>
+      <c r="R21" t="n">
+        <v>1.21</v>
+      </c>
+      <c r="S21" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="T21" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="U21" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="V21" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="W21" t="n">
+        <v>1.47</v>
+      </c>
+      <c r="X21" t="n">
+        <v>1000</v>
+      </c>
+      <c r="Y21" t="n">
+        <v>1000</v>
+      </c>
+      <c r="Z21" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AA21" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AB21" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AC21" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AD21" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AE21" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AF21" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AG21" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AH21" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AI21" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AJ21" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AK21" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AL21" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AM21" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AN21" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AO21" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AP21" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AQ21" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AR21" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AS21" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AT21" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AU21" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AV21" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AW21" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AX21" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AY21" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AZ21" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BA21" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BB21" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BC21" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BD21" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BE21" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BF21" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BG21" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BH21" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BI21" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BJ21" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BK21" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BL21" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BM21" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BN21" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BO21" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BP21" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BQ21" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BR21" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BS21" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BT21" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BU21" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BV21" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BW21" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BX21" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BY21" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BZ21" t="n">
+        <v>1000</v>
+      </c>
+      <c r="CA21" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="CB21" t="inlineStr">
+        <is>
+          <t>2026-06-10 16:02:38</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>Irish Premier Division</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>2026-06-12</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>16:00:00</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>Shelbourne</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>Shamrock Rovers</t>
+        </is>
+      </c>
+      <c r="F22" t="n">
+        <v>2.78</v>
+      </c>
+      <c r="G22" t="n">
+        <v>3</v>
+      </c>
+      <c r="H22" t="n">
+        <v>2.68</v>
+      </c>
+      <c r="I22" t="n">
+        <v>2.92</v>
+      </c>
+      <c r="J22" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="K22" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="L22" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="M22" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="N22" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="O22" t="n">
+        <v>1.37</v>
+      </c>
+      <c r="P22" t="n">
+        <v>1.78</v>
+      </c>
+      <c r="Q22" t="n">
+        <v>2.12</v>
+      </c>
+      <c r="R22" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="S22" t="n">
+        <v>3.85</v>
+      </c>
+      <c r="T22" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="U22" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="V22" t="n">
+        <v>1.52</v>
+      </c>
+      <c r="W22" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="X22" t="n">
+        <v>1000</v>
+      </c>
+      <c r="Y22" t="n">
+        <v>1000</v>
+      </c>
+      <c r="Z22" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AA22" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AB22" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AC22" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AD22" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AE22" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AF22" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AG22" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AH22" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AI22" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AJ22" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AK22" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AL22" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AM22" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AN22" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AO22" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AP22" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="AQ22" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="AR22" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="AS22" t="n">
+        <v>27</v>
+      </c>
+      <c r="AT22" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="AU22" t="n">
+        <v>6</v>
+      </c>
+      <c r="AV22" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="AW22" t="n">
+        <v>22</v>
+      </c>
+      <c r="AX22" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="AY22" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="AZ22" t="n">
+        <v>16</v>
+      </c>
+      <c r="BA22" t="n">
+        <v>34</v>
+      </c>
+      <c r="BB22" t="n">
+        <v>28</v>
+      </c>
+      <c r="BC22" t="n">
+        <v>24</v>
+      </c>
+      <c r="BD22" t="n">
+        <v>36</v>
+      </c>
+      <c r="BE22" t="n">
+        <v>40</v>
+      </c>
+      <c r="BF22" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BG22" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BH22" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BI22" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BJ22" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BK22" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BL22" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BM22" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BN22" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BO22" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BP22" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BQ22" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BR22" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BS22" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BT22" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BU22" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BV22" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BW22" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BX22" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BY22" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BZ22" t="n">
+        <v>1000</v>
+      </c>
+      <c r="CA22" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="CB22" t="inlineStr">
+        <is>
+          <t>2026-06-10 16:02:38</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
           <t>Brazilian Serie B</t>
         </is>
       </c>
-      <c r="B12" t="inlineStr">
+      <c r="B23" t="inlineStr">
         <is>
           <t>2026-06-12</t>
         </is>
       </c>
-      <c r="C12" t="inlineStr">
+      <c r="C23" t="inlineStr">
         <is>
           <t>19:00:00</t>
         </is>
       </c>
-      <c r="D12" t="inlineStr">
+      <c r="D23" t="inlineStr">
         <is>
           <t>Atletico GO</t>
         </is>
       </c>
-      <c r="E12" t="inlineStr">
+      <c r="E23" t="inlineStr">
         <is>
           <t>CRB</t>
         </is>
       </c>
-      <c r="F12" t="n">
-        <v>0</v>
-      </c>
-      <c r="G12" t="n">
-        <v>0</v>
-      </c>
-      <c r="H12" t="n">
-        <v>0</v>
-      </c>
-      <c r="I12" t="n">
-        <v>0</v>
-      </c>
-      <c r="J12" t="n">
-        <v>0</v>
-      </c>
-      <c r="K12" t="n">
-        <v>0</v>
-      </c>
-      <c r="L12" t="n">
-        <v>0</v>
-      </c>
-      <c r="M12" t="n">
-        <v>0</v>
-      </c>
-      <c r="N12" t="n">
-        <v>0</v>
-      </c>
-      <c r="O12" t="n">
-        <v>0</v>
-      </c>
-      <c r="P12" t="n">
+      <c r="F23" t="n">
+        <v>0</v>
+      </c>
+      <c r="G23" t="n">
+        <v>0</v>
+      </c>
+      <c r="H23" t="n">
+        <v>0</v>
+      </c>
+      <c r="I23" t="n">
+        <v>0</v>
+      </c>
+      <c r="J23" t="n">
+        <v>0</v>
+      </c>
+      <c r="K23" t="n">
+        <v>0</v>
+      </c>
+      <c r="L23" t="n">
+        <v>0</v>
+      </c>
+      <c r="M23" t="n">
+        <v>0</v>
+      </c>
+      <c r="N23" t="n">
+        <v>0</v>
+      </c>
+      <c r="O23" t="n">
+        <v>0</v>
+      </c>
+      <c r="P23" t="n">
         <v>1.25</v>
       </c>
-      <c r="Q12" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="R12" t="n">
-        <v>0</v>
-      </c>
-      <c r="S12" t="n">
-        <v>0</v>
-      </c>
-      <c r="T12" t="n">
-        <v>0</v>
-      </c>
-      <c r="U12" t="n">
-        <v>0</v>
-      </c>
-      <c r="V12" t="n">
-        <v>0</v>
-      </c>
-      <c r="W12" t="n">
-        <v>0</v>
-      </c>
-      <c r="X12" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y12" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AN12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AO12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AQ12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AR12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AS12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AT12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AU12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AV12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AW12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AX12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AY12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AZ12" t="n">
-        <v>0</v>
-      </c>
-      <c r="BA12" t="n">
-        <v>0</v>
-      </c>
-      <c r="BB12" t="n">
-        <v>0</v>
-      </c>
-      <c r="BC12" t="n">
-        <v>0</v>
-      </c>
-      <c r="BD12" t="n">
-        <v>0</v>
-      </c>
-      <c r="BE12" t="n">
-        <v>0</v>
-      </c>
-      <c r="BF12" t="n">
-        <v>0</v>
-      </c>
-      <c r="BG12" t="n">
-        <v>0</v>
-      </c>
-      <c r="BH12" t="n">
-        <v>0</v>
-      </c>
-      <c r="BI12" t="n">
-        <v>0</v>
-      </c>
-      <c r="BJ12" t="n">
-        <v>0</v>
-      </c>
-      <c r="BK12" t="n">
-        <v>0</v>
-      </c>
-      <c r="BL12" t="n">
-        <v>0</v>
-      </c>
-      <c r="BM12" t="n">
-        <v>0</v>
-      </c>
-      <c r="BN12" t="n">
-        <v>0</v>
-      </c>
-      <c r="BO12" t="n">
-        <v>0</v>
-      </c>
-      <c r="BP12" t="n">
-        <v>0</v>
-      </c>
-      <c r="BQ12" t="n">
-        <v>0</v>
-      </c>
-      <c r="BR12" t="n">
-        <v>0</v>
-      </c>
-      <c r="BS12" t="n">
-        <v>0</v>
-      </c>
-      <c r="BT12" t="n">
-        <v>0</v>
-      </c>
-      <c r="BU12" t="n">
-        <v>0</v>
-      </c>
-      <c r="BV12" t="n">
-        <v>0</v>
-      </c>
-      <c r="BW12" t="n">
-        <v>0</v>
-      </c>
-      <c r="BX12" t="n">
-        <v>0</v>
-      </c>
-      <c r="BY12" t="n">
-        <v>0</v>
-      </c>
-      <c r="BZ12" t="n">
-        <v>0</v>
-      </c>
-      <c r="CA12" t="n">
-        <v>0</v>
-      </c>
-      <c r="CB12" t="inlineStr">
-        <is>
-          <t>2026-06-10 13:52:15</t>
+      <c r="Q23" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="R23" t="n">
+        <v>0</v>
+      </c>
+      <c r="S23" t="n">
+        <v>0</v>
+      </c>
+      <c r="T23" t="n">
+        <v>0</v>
+      </c>
+      <c r="U23" t="n">
+        <v>0</v>
+      </c>
+      <c r="V23" t="n">
+        <v>0</v>
+      </c>
+      <c r="W23" t="n">
+        <v>0</v>
+      </c>
+      <c r="X23" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y23" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z23" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA23" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB23" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC23" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD23" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE23" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF23" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG23" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH23" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI23" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ23" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK23" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL23" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM23" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN23" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO23" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP23" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ23" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR23" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS23" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT23" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU23" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV23" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW23" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX23" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY23" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ23" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA23" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB23" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC23" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD23" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE23" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF23" t="n">
+        <v>0</v>
+      </c>
+      <c r="BG23" t="n">
+        <v>0</v>
+      </c>
+      <c r="BH23" t="n">
+        <v>0</v>
+      </c>
+      <c r="BI23" t="n">
+        <v>0</v>
+      </c>
+      <c r="BJ23" t="n">
+        <v>0</v>
+      </c>
+      <c r="BK23" t="n">
+        <v>0</v>
+      </c>
+      <c r="BL23" t="n">
+        <v>0</v>
+      </c>
+      <c r="BM23" t="n">
+        <v>0</v>
+      </c>
+      <c r="BN23" t="n">
+        <v>0</v>
+      </c>
+      <c r="BO23" t="n">
+        <v>0</v>
+      </c>
+      <c r="BP23" t="n">
+        <v>0</v>
+      </c>
+      <c r="BQ23" t="n">
+        <v>0</v>
+      </c>
+      <c r="BR23" t="n">
+        <v>0</v>
+      </c>
+      <c r="BS23" t="n">
+        <v>0</v>
+      </c>
+      <c r="BT23" t="n">
+        <v>0</v>
+      </c>
+      <c r="BU23" t="n">
+        <v>0</v>
+      </c>
+      <c r="BV23" t="n">
+        <v>0</v>
+      </c>
+      <c r="BW23" t="n">
+        <v>0</v>
+      </c>
+      <c r="BX23" t="n">
+        <v>0</v>
+      </c>
+      <c r="BY23" t="n">
+        <v>0</v>
+      </c>
+      <c r="BZ23" t="n">
+        <v>0</v>
+      </c>
+      <c r="CA23" t="n">
+        <v>0</v>
+      </c>
+      <c r="CB23" t="inlineStr">
+        <is>
+          <t>2026-06-10 16:02:38</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-06-12.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-06-12.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:CB23"/>
+  <dimension ref="A1:CB25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -869,7 +869,7 @@
         <v>1000</v>
       </c>
       <c r="J2" t="n">
-        <v>1.08</v>
+        <v>1.1</v>
       </c>
       <c r="K2" t="n">
         <v>1000</v>
@@ -881,13 +881,13 @@
         <v>1.01</v>
       </c>
       <c r="N2" t="n">
-        <v>1.28</v>
+        <v>1.3</v>
       </c>
       <c r="O2" t="n">
         <v>1.3</v>
       </c>
       <c r="P2" t="n">
-        <v>1.28</v>
+        <v>1.31</v>
       </c>
       <c r="Q2" t="n">
         <v>1.8</v>
@@ -896,7 +896,7 @@
         <v>1.18</v>
       </c>
       <c r="S2" t="n">
-        <v>2.6</v>
+        <v>1.3</v>
       </c>
       <c r="T2" t="n">
         <v>1.01</v>
@@ -908,7 +908,7 @@
         <v>1.01</v>
       </c>
       <c r="W2" t="n">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="X2" t="n">
         <v>1000</v>
@@ -1080,7 +1080,7 @@
       </c>
       <c r="CB2" t="inlineStr">
         <is>
-          <t>2026-06-10 16:02:38</t>
+          <t>2026-06-10 18:12:00</t>
         </is>
       </c>
     </row>
@@ -1111,7 +1111,7 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>1.04</v>
+        <v>1.09</v>
       </c>
       <c r="G3" t="n">
         <v>1000</v>
@@ -1123,7 +1123,7 @@
         <v>1000</v>
       </c>
       <c r="J3" t="n">
-        <v>1.12</v>
+        <v>1.1</v>
       </c>
       <c r="K3" t="n">
         <v>1000</v>
@@ -1162,7 +1162,7 @@
         <v>1.01</v>
       </c>
       <c r="W3" t="n">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="X3" t="n">
         <v>1000</v>
@@ -1334,7 +1334,7 @@
       </c>
       <c r="CB3" t="inlineStr">
         <is>
-          <t>2026-06-10 16:02:38</t>
+          <t>2026-06-10 18:12:00</t>
         </is>
       </c>
     </row>
@@ -1377,7 +1377,7 @@
         <v>1000</v>
       </c>
       <c r="J4" t="n">
-        <v>1.08</v>
+        <v>1.1</v>
       </c>
       <c r="K4" t="n">
         <v>1000</v>
@@ -1398,13 +1398,13 @@
         <v>1.24</v>
       </c>
       <c r="Q4" t="n">
-        <v>1.49</v>
+        <v>1.48</v>
       </c>
       <c r="R4" t="n">
         <v>1.18</v>
       </c>
       <c r="S4" t="n">
-        <v>1.49</v>
+        <v>1.48</v>
       </c>
       <c r="T4" t="n">
         <v>1.11</v>
@@ -1588,7 +1588,7 @@
       </c>
       <c r="CB4" t="inlineStr">
         <is>
-          <t>2026-06-10 16:02:38</t>
+          <t>2026-06-10 18:12:00</t>
         </is>
       </c>
     </row>
@@ -1646,7 +1646,7 @@
         <v>1.25</v>
       </c>
       <c r="O5" t="n">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="P5" t="n">
         <v>1.24</v>
@@ -1658,7 +1658,7 @@
         <v>1.18</v>
       </c>
       <c r="S5" t="n">
-        <v>1.53</v>
+        <v>1.54</v>
       </c>
       <c r="T5" t="n">
         <v>1.11</v>
@@ -1842,7 +1842,7 @@
       </c>
       <c r="CB5" t="inlineStr">
         <is>
-          <t>2026-06-10 16:02:38</t>
+          <t>2026-06-10 18:12:00</t>
         </is>
       </c>
     </row>
@@ -1885,7 +1885,7 @@
         <v>1000</v>
       </c>
       <c r="J6" t="n">
-        <v>1.08</v>
+        <v>1.1</v>
       </c>
       <c r="K6" t="n">
         <v>1000</v>
@@ -1897,13 +1897,13 @@
         <v>1.01</v>
       </c>
       <c r="N6" t="n">
-        <v>1.25</v>
+        <v>1.35</v>
       </c>
       <c r="O6" t="n">
         <v>1.22</v>
       </c>
       <c r="P6" t="n">
-        <v>1.24</v>
+        <v>1.34</v>
       </c>
       <c r="Q6" t="n">
         <v>1.21</v>
@@ -2096,7 +2096,7 @@
       </c>
       <c r="CB6" t="inlineStr">
         <is>
-          <t>2026-06-10 16:02:38</t>
+          <t>2026-06-10 18:12:00</t>
         </is>
       </c>
     </row>
@@ -2139,7 +2139,7 @@
         <v>1000</v>
       </c>
       <c r="J7" t="n">
-        <v>1.06</v>
+        <v>1.09</v>
       </c>
       <c r="K7" t="n">
         <v>1000</v>
@@ -2151,13 +2151,13 @@
         <v>1.01</v>
       </c>
       <c r="N7" t="n">
-        <v>1.28</v>
+        <v>1.3</v>
       </c>
       <c r="O7" t="n">
         <v>1.27</v>
       </c>
       <c r="P7" t="n">
-        <v>1.28</v>
+        <v>1.3</v>
       </c>
       <c r="Q7" t="n">
         <v>1.27</v>
@@ -2350,7 +2350,7 @@
       </c>
       <c r="CB7" t="inlineStr">
         <is>
-          <t>2026-06-10 16:02:38</t>
+          <t>2026-06-10 18:12:00</t>
         </is>
       </c>
     </row>
@@ -2372,12 +2372,12 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>Lunds BK</t>
+          <t>Umea FC</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Ariana FC</t>
+          <t>Pitea</t>
         </is>
       </c>
       <c r="F8" t="n">
@@ -2393,7 +2393,7 @@
         <v>1000</v>
       </c>
       <c r="J8" t="n">
-        <v>1.04</v>
+        <v>1.06</v>
       </c>
       <c r="K8" t="n">
         <v>1000</v>
@@ -2405,22 +2405,22 @@
         <v>1.01</v>
       </c>
       <c r="N8" t="n">
-        <v>1.25</v>
+        <v>1.28</v>
       </c>
       <c r="O8" t="n">
-        <v>1.24</v>
+        <v>1.15</v>
       </c>
       <c r="P8" t="n">
-        <v>1.25</v>
+        <v>1.28</v>
       </c>
       <c r="Q8" t="n">
-        <v>1.25</v>
+        <v>1.15</v>
       </c>
       <c r="R8" t="n">
         <v>1.24</v>
       </c>
       <c r="S8" t="n">
-        <v>1.25</v>
+        <v>1.15</v>
       </c>
       <c r="T8" t="n">
         <v>1.11</v>
@@ -2429,7 +2429,7 @@
         <v>1.11</v>
       </c>
       <c r="V8" t="n">
-        <v>1.06</v>
+        <v>1.01</v>
       </c>
       <c r="W8" t="n">
         <v>1.01</v>
@@ -2489,52 +2489,52 @@
         <v>1000</v>
       </c>
       <c r="AP8" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AQ8" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AR8" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AS8" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AT8" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AU8" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AV8" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AW8" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AX8" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AY8" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AZ8" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BA8" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BB8" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BC8" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BD8" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BE8" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BF8" t="n">
         <v>1.01</v>
@@ -2546,65 +2546,65 @@
         <v>1000</v>
       </c>
       <c r="BI8" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BJ8" t="n">
         <v>1000</v>
       </c>
       <c r="BK8" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BL8" t="n">
         <v>1000</v>
       </c>
       <c r="BM8" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BN8" t="n">
         <v>1000</v>
       </c>
       <c r="BO8" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BP8" t="n">
         <v>1000</v>
       </c>
       <c r="BQ8" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BR8" t="n">
         <v>1000</v>
       </c>
       <c r="BS8" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BT8" t="n">
         <v>1000</v>
       </c>
       <c r="BU8" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BV8" t="n">
         <v>1000</v>
       </c>
       <c r="BW8" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BX8" t="n">
         <v>1000</v>
       </c>
       <c r="BY8" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BZ8" t="n">
         <v>1000</v>
       </c>
       <c r="CA8" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="CB8" t="inlineStr">
         <is>
-          <t>2026-06-10 16:02:38</t>
+          <t>2026-06-10 18:12:00</t>
         </is>
       </c>
     </row>
@@ -2647,7 +2647,7 @@
         <v>1000</v>
       </c>
       <c r="J9" t="n">
-        <v>1.06</v>
+        <v>1.08</v>
       </c>
       <c r="K9" t="n">
         <v>1000</v>
@@ -2858,7 +2858,7 @@
       </c>
       <c r="CB9" t="inlineStr">
         <is>
-          <t>2026-06-10 16:02:38</t>
+          <t>2026-06-10 18:12:00</t>
         </is>
       </c>
     </row>
@@ -2880,12 +2880,12 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>Umea FC</t>
+          <t>Lunds BK</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Pitea</t>
+          <t>Ariana FC</t>
         </is>
       </c>
       <c r="F10" t="n">
@@ -2901,7 +2901,7 @@
         <v>1000</v>
       </c>
       <c r="J10" t="n">
-        <v>1.04</v>
+        <v>1.1</v>
       </c>
       <c r="K10" t="n">
         <v>1000</v>
@@ -2913,22 +2913,22 @@
         <v>1.01</v>
       </c>
       <c r="N10" t="n">
-        <v>1.27</v>
+        <v>1.3</v>
       </c>
       <c r="O10" t="n">
-        <v>1.15</v>
+        <v>1.24</v>
       </c>
       <c r="P10" t="n">
-        <v>1.27</v>
+        <v>1.29</v>
       </c>
       <c r="Q10" t="n">
-        <v>1.15</v>
+        <v>1.24</v>
       </c>
       <c r="R10" t="n">
         <v>1.24</v>
       </c>
       <c r="S10" t="n">
-        <v>1.15</v>
+        <v>1.25</v>
       </c>
       <c r="T10" t="n">
         <v>1.11</v>
@@ -2997,52 +2997,52 @@
         <v>1000</v>
       </c>
       <c r="AP10" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AQ10" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AR10" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AS10" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AT10" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AU10" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AV10" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AW10" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AX10" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AY10" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AZ10" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BA10" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BB10" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BC10" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BD10" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BE10" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BF10" t="n">
         <v>1.01</v>
@@ -3054,65 +3054,65 @@
         <v>1000</v>
       </c>
       <c r="BI10" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BJ10" t="n">
         <v>1000</v>
       </c>
       <c r="BK10" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BL10" t="n">
         <v>1000</v>
       </c>
       <c r="BM10" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BN10" t="n">
         <v>1000</v>
       </c>
       <c r="BO10" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BP10" t="n">
         <v>1000</v>
       </c>
       <c r="BQ10" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BR10" t="n">
         <v>1000</v>
       </c>
       <c r="BS10" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BT10" t="n">
         <v>1000</v>
       </c>
       <c r="BU10" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BV10" t="n">
         <v>1000</v>
       </c>
       <c r="BW10" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BX10" t="n">
         <v>1000</v>
       </c>
       <c r="BY10" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BZ10" t="n">
         <v>1000</v>
       </c>
       <c r="CA10" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="CB10" t="inlineStr">
         <is>
-          <t>2026-06-10 16:02:38</t>
+          <t>2026-06-10 18:12:00</t>
         </is>
       </c>
     </row>
@@ -3167,13 +3167,13 @@
         <v>1.01</v>
       </c>
       <c r="N11" t="n">
-        <v>1.26</v>
+        <v>1.28</v>
       </c>
       <c r="O11" t="n">
         <v>1.12</v>
       </c>
       <c r="P11" t="n">
-        <v>1.26</v>
+        <v>1.28</v>
       </c>
       <c r="Q11" t="n">
         <v>1.11</v>
@@ -3191,10 +3191,10 @@
         <v>1.11</v>
       </c>
       <c r="V11" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="W11" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="X11" t="n">
         <v>1000</v>
@@ -3251,52 +3251,52 @@
         <v>1000</v>
       </c>
       <c r="AP11" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AQ11" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AR11" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AS11" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AT11" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AU11" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AV11" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AW11" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AX11" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AY11" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AZ11" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BA11" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BB11" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BC11" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BD11" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BE11" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BF11" t="n">
         <v>1.01</v>
@@ -3308,65 +3308,65 @@
         <v>1000</v>
       </c>
       <c r="BI11" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BJ11" t="n">
         <v>1000</v>
       </c>
       <c r="BK11" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BL11" t="n">
         <v>1000</v>
       </c>
       <c r="BM11" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BN11" t="n">
         <v>1000</v>
       </c>
       <c r="BO11" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BP11" t="n">
         <v>1000</v>
       </c>
       <c r="BQ11" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BR11" t="n">
         <v>1000</v>
       </c>
       <c r="BS11" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BT11" t="n">
         <v>1000</v>
       </c>
       <c r="BU11" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BV11" t="n">
         <v>1000</v>
       </c>
       <c r="BW11" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BX11" t="n">
         <v>1000</v>
       </c>
       <c r="BY11" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BZ11" t="n">
         <v>1000</v>
       </c>
       <c r="CA11" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="CB11" t="inlineStr">
         <is>
-          <t>2026-06-10 16:02:38</t>
+          <t>2026-06-10 18:12:00</t>
         </is>
       </c>
     </row>
@@ -3409,7 +3409,7 @@
         <v>1000</v>
       </c>
       <c r="J12" t="n">
-        <v>1.04</v>
+        <v>1.06</v>
       </c>
       <c r="K12" t="n">
         <v>1000</v>
@@ -3421,13 +3421,13 @@
         <v>1.01</v>
       </c>
       <c r="N12" t="n">
-        <v>1.26</v>
+        <v>1.28</v>
       </c>
       <c r="O12" t="n">
         <v>1.33</v>
       </c>
       <c r="P12" t="n">
-        <v>1.26</v>
+        <v>1.29</v>
       </c>
       <c r="Q12" t="n">
         <v>1.87</v>
@@ -3436,19 +3436,19 @@
         <v>1.18</v>
       </c>
       <c r="S12" t="n">
-        <v>2.84</v>
+        <v>2.78</v>
       </c>
       <c r="T12" t="n">
-        <v>1.01</v>
+        <v>1.11</v>
       </c>
       <c r="U12" t="n">
-        <v>1.01</v>
+        <v>1.11</v>
       </c>
       <c r="V12" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="W12" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="X12" t="n">
         <v>1000</v>
@@ -3505,52 +3505,52 @@
         <v>1000</v>
       </c>
       <c r="AP12" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AQ12" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AR12" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AS12" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AT12" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AU12" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AV12" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AW12" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AX12" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AY12" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AZ12" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BA12" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BB12" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BC12" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BD12" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BE12" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BF12" t="n">
         <v>1.01</v>
@@ -3562,65 +3562,65 @@
         <v>1000</v>
       </c>
       <c r="BI12" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BJ12" t="n">
         <v>1000</v>
       </c>
       <c r="BK12" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BL12" t="n">
         <v>1000</v>
       </c>
       <c r="BM12" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BN12" t="n">
         <v>1000</v>
       </c>
       <c r="BO12" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BP12" t="n">
         <v>1000</v>
       </c>
       <c r="BQ12" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BR12" t="n">
         <v>1000</v>
       </c>
       <c r="BS12" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BT12" t="n">
         <v>1000</v>
       </c>
       <c r="BU12" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BV12" t="n">
         <v>1000</v>
       </c>
       <c r="BW12" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BX12" t="n">
         <v>1000</v>
       </c>
       <c r="BY12" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BZ12" t="n">
         <v>1000</v>
       </c>
       <c r="CA12" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="CB12" t="inlineStr">
         <is>
-          <t>2026-06-10 16:02:38</t>
+          <t>2026-06-10 18:12:00</t>
         </is>
       </c>
     </row>
@@ -3663,7 +3663,7 @@
         <v>1000</v>
       </c>
       <c r="J13" t="n">
-        <v>1.08</v>
+        <v>1.09</v>
       </c>
       <c r="K13" t="n">
         <v>1000</v>
@@ -3678,13 +3678,13 @@
         <v>1.25</v>
       </c>
       <c r="O13" t="n">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="P13" t="n">
         <v>1.24</v>
       </c>
       <c r="Q13" t="n">
-        <v>1.51</v>
+        <v>1.05</v>
       </c>
       <c r="R13" t="n">
         <v>1.18</v>
@@ -3874,7 +3874,7 @@
       </c>
       <c r="CB13" t="inlineStr">
         <is>
-          <t>2026-06-10 16:02:38</t>
+          <t>2026-06-10 18:12:00</t>
         </is>
       </c>
     </row>
@@ -3905,28 +3905,28 @@
         </is>
       </c>
       <c r="F14" t="n">
-        <v>3.9</v>
+        <v>3.7</v>
       </c>
       <c r="G14" t="n">
-        <v>4.5</v>
+        <v>5.4</v>
       </c>
       <c r="H14" t="n">
-        <v>1.9</v>
+        <v>1.75</v>
       </c>
       <c r="I14" t="n">
-        <v>2.08</v>
+        <v>2.28</v>
       </c>
       <c r="J14" t="n">
-        <v>3.65</v>
+        <v>3.25</v>
       </c>
       <c r="K14" t="n">
-        <v>4.2</v>
+        <v>5</v>
       </c>
       <c r="L14" t="n">
         <v>1.01</v>
       </c>
       <c r="M14" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="N14" t="n">
         <v>4.1</v>
@@ -3938,197 +3938,197 @@
         <v>2.08</v>
       </c>
       <c r="Q14" t="n">
-        <v>1.75</v>
+        <v>1.77</v>
       </c>
       <c r="R14" t="n">
-        <v>1.34</v>
+        <v>1.33</v>
       </c>
       <c r="S14" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="T14" t="n">
+        <v>1.37</v>
+      </c>
+      <c r="U14" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="V14" t="n">
+        <v>1.78</v>
+      </c>
+      <c r="W14" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="X14" t="n">
+        <v>1000</v>
+      </c>
+      <c r="Y14" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="Z14" t="n">
+        <v>18</v>
+      </c>
+      <c r="AA14" t="n">
+        <v>30</v>
+      </c>
+      <c r="AB14" t="n">
+        <v>24</v>
+      </c>
+      <c r="AC14" t="n">
+        <v>11</v>
+      </c>
+      <c r="AD14" t="n">
+        <v>15</v>
+      </c>
+      <c r="AE14" t="n">
+        <v>28</v>
+      </c>
+      <c r="AF14" t="n">
+        <v>46</v>
+      </c>
+      <c r="AG14" t="n">
+        <v>24</v>
+      </c>
+      <c r="AH14" t="n">
+        <v>24</v>
+      </c>
+      <c r="AI14" t="n">
+        <v>46</v>
+      </c>
+      <c r="AJ14" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AK14" t="n">
+        <v>70</v>
+      </c>
+      <c r="AL14" t="n">
+        <v>70</v>
+      </c>
+      <c r="AM14" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AN14" t="n">
+        <v>65</v>
+      </c>
+      <c r="AO14" t="n">
+        <v>16</v>
+      </c>
+      <c r="AP14" t="n">
+        <v>2.66</v>
+      </c>
+      <c r="AQ14" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="AR14" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="AS14" t="n">
+        <v>16</v>
+      </c>
+      <c r="AT14" t="n">
+        <v>12</v>
+      </c>
+      <c r="AU14" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="AV14" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="AW14" t="n">
+        <v>14</v>
+      </c>
+      <c r="AX14" t="n">
+        <v>2.52</v>
+      </c>
+      <c r="AY14" t="n">
+        <v>12</v>
+      </c>
+      <c r="AZ14" t="n">
+        <v>12</v>
+      </c>
+      <c r="BA14" t="n">
+        <v>2.52</v>
+      </c>
+      <c r="BB14" t="n">
+        <v>2.68</v>
+      </c>
+      <c r="BC14" t="n">
+        <v>2.58</v>
+      </c>
+      <c r="BD14" t="n">
+        <v>2.58</v>
+      </c>
+      <c r="BE14" t="n">
+        <v>2.68</v>
+      </c>
+      <c r="BF14" t="n">
         <v>2.56</v>
       </c>
-      <c r="T14" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="U14" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="V14" t="n">
-        <v>1.92</v>
-      </c>
-      <c r="W14" t="n">
-        <v>1.28</v>
-      </c>
-      <c r="X14" t="n">
-        <v>1000</v>
-      </c>
-      <c r="Y14" t="n">
-        <v>1000</v>
-      </c>
-      <c r="Z14" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AA14" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AB14" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AC14" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AD14" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AE14" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AF14" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AG14" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AH14" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AI14" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AJ14" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AK14" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AL14" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AM14" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AN14" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AO14" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AP14" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="AQ14" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="AR14" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="AS14" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="AT14" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="AU14" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="AV14" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="AW14" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="AX14" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="AY14" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="AZ14" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BA14" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BB14" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BC14" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BD14" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BE14" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BF14" t="n">
-        <v>1.01</v>
-      </c>
       <c r="BG14" t="n">
-        <v>1.01</v>
+        <v>8.4</v>
       </c>
       <c r="BH14" t="n">
         <v>1000</v>
       </c>
       <c r="BI14" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BJ14" t="n">
         <v>1000</v>
       </c>
       <c r="BK14" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BL14" t="n">
         <v>1000</v>
       </c>
       <c r="BM14" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BN14" t="n">
         <v>1000</v>
       </c>
       <c r="BO14" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BP14" t="n">
         <v>1000</v>
       </c>
       <c r="BQ14" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BR14" t="n">
         <v>1000</v>
       </c>
       <c r="BS14" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BT14" t="n">
         <v>1000</v>
       </c>
       <c r="BU14" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BV14" t="n">
         <v>1000</v>
       </c>
       <c r="BW14" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BX14" t="n">
         <v>1000</v>
       </c>
       <c r="BY14" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BZ14" t="n">
         <v>1000</v>
       </c>
       <c r="CA14" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="CB14" t="inlineStr">
         <is>
-          <t>2026-06-10 16:02:38</t>
+          <t>2026-06-10 18:12:00</t>
         </is>
       </c>
     </row>
@@ -4159,58 +4159,58 @@
         </is>
       </c>
       <c r="F15" t="n">
-        <v>2.28</v>
+        <v>2.26</v>
       </c>
       <c r="G15" t="n">
-        <v>2.5</v>
+        <v>2.54</v>
       </c>
       <c r="H15" t="n">
-        <v>3.25</v>
+        <v>3.15</v>
       </c>
       <c r="I15" t="n">
-        <v>3.65</v>
+        <v>4.2</v>
       </c>
       <c r="J15" t="n">
-        <v>3.25</v>
+        <v>2.68</v>
       </c>
       <c r="K15" t="n">
-        <v>3.65</v>
+        <v>950</v>
       </c>
       <c r="L15" t="n">
         <v>1.36</v>
       </c>
       <c r="M15" t="n">
-        <v>1.01</v>
+        <v>1.07</v>
       </c>
       <c r="N15" t="n">
-        <v>1.01</v>
+        <v>3.15</v>
       </c>
       <c r="O15" t="n">
         <v>1.36</v>
       </c>
       <c r="P15" t="n">
-        <v>1.81</v>
+        <v>1.74</v>
       </c>
       <c r="Q15" t="n">
         <v>2.04</v>
       </c>
       <c r="R15" t="n">
-        <v>1.21</v>
+        <v>1.27</v>
       </c>
       <c r="S15" t="n">
-        <v>1.02</v>
+        <v>3.7</v>
       </c>
       <c r="T15" t="n">
-        <v>1.01</v>
+        <v>1.11</v>
       </c>
       <c r="U15" t="n">
-        <v>1.01</v>
+        <v>2.06</v>
       </c>
       <c r="V15" t="n">
         <v>1.38</v>
       </c>
       <c r="W15" t="n">
-        <v>1.66</v>
+        <v>1.67</v>
       </c>
       <c r="X15" t="n">
         <v>1000</v>
@@ -4246,7 +4246,7 @@
         <v>1000</v>
       </c>
       <c r="AI15" t="n">
-        <v>55</v>
+        <v>1000</v>
       </c>
       <c r="AJ15" t="n">
         <v>1000</v>
@@ -4276,7 +4276,7 @@
         <v>17</v>
       </c>
       <c r="AS15" t="n">
-        <v>44</v>
+        <v>1.3</v>
       </c>
       <c r="AT15" t="n">
         <v>7.2</v>
@@ -4288,7 +4288,7 @@
         <v>10.5</v>
       </c>
       <c r="AW15" t="n">
-        <v>30</v>
+        <v>1.33</v>
       </c>
       <c r="AX15" t="n">
         <v>11</v>
@@ -4300,89 +4300,89 @@
         <v>13</v>
       </c>
       <c r="BA15" t="n">
-        <v>38</v>
+        <v>1.33</v>
       </c>
       <c r="BB15" t="n">
-        <v>23</v>
+        <v>1.33</v>
       </c>
       <c r="BC15" t="n">
         <v>19.5</v>
       </c>
       <c r="BD15" t="n">
-        <v>30</v>
+        <v>1.33</v>
       </c>
       <c r="BE15" t="n">
-        <v>70</v>
+        <v>1.33</v>
       </c>
       <c r="BF15" t="n">
         <v>16</v>
       </c>
       <c r="BG15" t="n">
-        <v>30</v>
+        <v>1.33</v>
       </c>
       <c r="BH15" t="n">
         <v>3.3</v>
       </c>
       <c r="BI15" t="n">
-        <v>2.94</v>
+        <v>2.66</v>
       </c>
       <c r="BJ15" t="n">
         <v>9.800000000000001</v>
       </c>
       <c r="BK15" t="n">
-        <v>8.4</v>
+        <v>5.7</v>
       </c>
       <c r="BL15" t="n">
         <v>1000</v>
       </c>
       <c r="BM15" t="n">
-        <v>22</v>
+        <v>12.5</v>
       </c>
       <c r="BN15" t="n">
         <v>5.3</v>
       </c>
       <c r="BO15" t="n">
-        <v>4.6</v>
+        <v>4</v>
       </c>
       <c r="BP15" t="n">
         <v>18.5</v>
       </c>
       <c r="BQ15" t="n">
-        <v>15.5</v>
+        <v>8</v>
       </c>
       <c r="BR15" t="n">
         <v>1000</v>
       </c>
       <c r="BS15" t="n">
-        <v>28</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BT15" t="n">
         <v>6.6</v>
       </c>
       <c r="BU15" t="n">
-        <v>5.7</v>
+        <v>5</v>
       </c>
       <c r="BV15" t="n">
         <v>1000</v>
       </c>
       <c r="BW15" t="n">
-        <v>24</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BX15" t="n">
         <v>1000</v>
       </c>
       <c r="BY15" t="n">
-        <v>34</v>
+        <v>10.5</v>
       </c>
       <c r="BZ15" t="n">
         <v>1000</v>
       </c>
       <c r="CA15" t="n">
-        <v>25</v>
+        <v>9.6</v>
       </c>
       <c r="CB15" t="inlineStr">
         <is>
-          <t>2026-06-10 16:02:38</t>
+          <t>2026-06-10 18:12:00</t>
         </is>
       </c>
     </row>
@@ -4425,22 +4425,22 @@
         <v>2.04</v>
       </c>
       <c r="J16" t="n">
-        <v>3.65</v>
+        <v>3.6</v>
       </c>
       <c r="K16" t="n">
         <v>4.3</v>
       </c>
       <c r="L16" t="n">
-        <v>1.01</v>
+        <v>1.29</v>
       </c>
       <c r="M16" t="n">
-        <v>1.01</v>
+        <v>1.05</v>
       </c>
       <c r="N16" t="n">
-        <v>2.04</v>
+        <v>4</v>
       </c>
       <c r="O16" t="n">
-        <v>1.24</v>
+        <v>1.25</v>
       </c>
       <c r="P16" t="n">
         <v>2.04</v>
@@ -4449,16 +4449,16 @@
         <v>1.77</v>
       </c>
       <c r="R16" t="n">
-        <v>1.35</v>
+        <v>1.4</v>
       </c>
       <c r="S16" t="n">
-        <v>2.68</v>
+        <v>2.96</v>
       </c>
       <c r="T16" t="n">
-        <v>1.01</v>
+        <v>1.72</v>
       </c>
       <c r="U16" t="n">
-        <v>1.01</v>
+        <v>2.12</v>
       </c>
       <c r="V16" t="n">
         <v>1.96</v>
@@ -4470,173 +4470,173 @@
         <v>1000</v>
       </c>
       <c r="Y16" t="n">
-        <v>1000</v>
+        <v>10.5</v>
       </c>
       <c r="Z16" t="n">
-        <v>1000</v>
+        <v>13.5</v>
       </c>
       <c r="AA16" t="n">
-        <v>1000</v>
+        <v>23</v>
       </c>
       <c r="AB16" t="n">
-        <v>1000</v>
+        <v>18</v>
       </c>
       <c r="AC16" t="n">
-        <v>1000</v>
+        <v>9.4</v>
       </c>
       <c r="AD16" t="n">
-        <v>1000</v>
+        <v>11</v>
       </c>
       <c r="AE16" t="n">
-        <v>1000</v>
+        <v>21</v>
       </c>
       <c r="AF16" t="n">
-        <v>1000</v>
+        <v>36</v>
       </c>
       <c r="AG16" t="n">
-        <v>1000</v>
+        <v>18.5</v>
       </c>
       <c r="AH16" t="n">
-        <v>1000</v>
+        <v>18.5</v>
       </c>
       <c r="AI16" t="n">
-        <v>1000</v>
+        <v>34</v>
       </c>
       <c r="AJ16" t="n">
         <v>1000</v>
       </c>
       <c r="AK16" t="n">
-        <v>1000</v>
+        <v>75</v>
       </c>
       <c r="AL16" t="n">
-        <v>1000</v>
+        <v>60</v>
       </c>
       <c r="AM16" t="n">
         <v>1000</v>
       </c>
       <c r="AN16" t="n">
-        <v>1000</v>
+        <v>55</v>
       </c>
       <c r="AO16" t="n">
-        <v>1000</v>
+        <v>12.5</v>
       </c>
       <c r="AP16" t="n">
-        <v>1.01</v>
+        <v>12.5</v>
       </c>
       <c r="AQ16" t="n">
-        <v>1.01</v>
+        <v>8.6</v>
       </c>
       <c r="AR16" t="n">
-        <v>1.01</v>
+        <v>10.5</v>
       </c>
       <c r="AS16" t="n">
-        <v>1.01</v>
+        <v>18</v>
       </c>
       <c r="AT16" t="n">
-        <v>1.01</v>
+        <v>14.5</v>
       </c>
       <c r="AU16" t="n">
-        <v>1.01</v>
+        <v>7.6</v>
       </c>
       <c r="AV16" t="n">
-        <v>1.01</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AW16" t="n">
-        <v>1.01</v>
+        <v>16.5</v>
       </c>
       <c r="AX16" t="n">
-        <v>1.01</v>
+        <v>23</v>
       </c>
       <c r="AY16" t="n">
-        <v>1.01</v>
+        <v>14.5</v>
       </c>
       <c r="AZ16" t="n">
-        <v>1.01</v>
+        <v>15</v>
       </c>
       <c r="BA16" t="n">
-        <v>1.01</v>
+        <v>23</v>
       </c>
       <c r="BB16" t="n">
-        <v>1.01</v>
+        <v>5.3</v>
       </c>
       <c r="BC16" t="n">
-        <v>1.01</v>
+        <v>36</v>
       </c>
       <c r="BD16" t="n">
-        <v>1.01</v>
+        <v>4.9</v>
       </c>
       <c r="BE16" t="n">
-        <v>1.01</v>
+        <v>5.3</v>
       </c>
       <c r="BF16" t="n">
-        <v>1.01</v>
+        <v>32</v>
       </c>
       <c r="BG16" t="n">
-        <v>1.01</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BH16" t="n">
-        <v>4.6</v>
+        <v>1000</v>
       </c>
       <c r="BI16" t="n">
-        <v>2.88</v>
+        <v>1.87</v>
       </c>
       <c r="BJ16" t="n">
         <v>13.5</v>
       </c>
       <c r="BK16" t="n">
-        <v>5.9</v>
+        <v>1.65</v>
       </c>
       <c r="BL16" t="n">
         <v>1000</v>
       </c>
       <c r="BM16" t="n">
-        <v>21</v>
+        <v>1.87</v>
       </c>
       <c r="BN16" t="n">
         <v>11</v>
       </c>
       <c r="BO16" t="n">
-        <v>4.9</v>
+        <v>1.6</v>
       </c>
       <c r="BP16" t="n">
         <v>50</v>
       </c>
       <c r="BQ16" t="n">
-        <v>20</v>
+        <v>1.81</v>
       </c>
       <c r="BR16" t="n">
         <v>1000</v>
       </c>
       <c r="BS16" t="n">
-        <v>21</v>
+        <v>1.82</v>
       </c>
       <c r="BT16" t="n">
         <v>6.6</v>
       </c>
       <c r="BU16" t="n">
-        <v>3.2</v>
+        <v>3.55</v>
       </c>
       <c r="BV16" t="n">
         <v>18.5</v>
       </c>
       <c r="BW16" t="n">
-        <v>8</v>
+        <v>1.7</v>
       </c>
       <c r="BX16" t="n">
         <v>38</v>
       </c>
       <c r="BY16" t="n">
-        <v>15</v>
+        <v>1.79</v>
       </c>
       <c r="BZ16" t="n">
         <v>30</v>
       </c>
       <c r="CA16" t="n">
-        <v>12</v>
+        <v>1.77</v>
       </c>
       <c r="CB16" t="inlineStr">
         <is>
-          <t>2026-06-10 16:02:38</t>
+          <t>2026-06-10 18:12:00</t>
         </is>
       </c>
     </row>
@@ -4667,52 +4667,52 @@
         </is>
       </c>
       <c r="F17" t="n">
-        <v>4.3</v>
+        <v>3.9</v>
       </c>
       <c r="G17" t="n">
-        <v>5.2</v>
+        <v>5.8</v>
       </c>
       <c r="H17" t="n">
-        <v>1.82</v>
+        <v>1.84</v>
       </c>
       <c r="I17" t="n">
-        <v>2.02</v>
+        <v>2.04</v>
       </c>
       <c r="J17" t="n">
-        <v>3.55</v>
+        <v>3.2</v>
       </c>
       <c r="K17" t="n">
-        <v>4.2</v>
+        <v>4.4</v>
       </c>
       <c r="L17" t="n">
         <v>1.01</v>
       </c>
       <c r="M17" t="n">
-        <v>1.01</v>
+        <v>1.06</v>
       </c>
       <c r="N17" t="n">
-        <v>3.55</v>
+        <v>2.8</v>
       </c>
       <c r="O17" t="n">
         <v>1.28</v>
       </c>
       <c r="P17" t="n">
-        <v>1.9</v>
+        <v>1.83</v>
       </c>
       <c r="Q17" t="n">
         <v>1.9</v>
       </c>
       <c r="R17" t="n">
-        <v>1.3</v>
+        <v>1.34</v>
       </c>
       <c r="S17" t="n">
-        <v>2.96</v>
+        <v>3.3</v>
       </c>
       <c r="T17" t="n">
-        <v>1.01</v>
+        <v>1.11</v>
       </c>
       <c r="U17" t="n">
-        <v>1.01</v>
+        <v>1.11</v>
       </c>
       <c r="V17" t="n">
         <v>1.98</v>
@@ -4724,37 +4724,37 @@
         <v>1000</v>
       </c>
       <c r="Y17" t="n">
-        <v>1000</v>
+        <v>11</v>
       </c>
       <c r="Z17" t="n">
-        <v>1000</v>
+        <v>15</v>
       </c>
       <c r="AA17" t="n">
-        <v>1000</v>
+        <v>28</v>
       </c>
       <c r="AB17" t="n">
-        <v>1000</v>
+        <v>21</v>
       </c>
       <c r="AC17" t="n">
-        <v>1000</v>
+        <v>10.5</v>
       </c>
       <c r="AD17" t="n">
-        <v>1000</v>
+        <v>13</v>
       </c>
       <c r="AE17" t="n">
-        <v>1000</v>
+        <v>26</v>
       </c>
       <c r="AF17" t="n">
-        <v>1000</v>
+        <v>100</v>
       </c>
       <c r="AG17" t="n">
-        <v>1000</v>
+        <v>24</v>
       </c>
       <c r="AH17" t="n">
-        <v>1000</v>
+        <v>24</v>
       </c>
       <c r="AI17" t="n">
-        <v>1000</v>
+        <v>100</v>
       </c>
       <c r="AJ17" t="n">
         <v>1000</v>
@@ -4772,125 +4772,125 @@
         <v>1000</v>
       </c>
       <c r="AO17" t="n">
-        <v>1000</v>
+        <v>17</v>
       </c>
       <c r="AP17" t="n">
-        <v>1.01</v>
+        <v>2.58</v>
       </c>
       <c r="AQ17" t="n">
-        <v>1.01</v>
+        <v>6.4</v>
       </c>
       <c r="AR17" t="n">
-        <v>1.01</v>
+        <v>8.4</v>
       </c>
       <c r="AS17" t="n">
-        <v>1.01</v>
+        <v>15</v>
       </c>
       <c r="AT17" t="n">
-        <v>1.01</v>
+        <v>11.5</v>
       </c>
       <c r="AU17" t="n">
-        <v>1.01</v>
+        <v>2.08</v>
       </c>
       <c r="AV17" t="n">
-        <v>1.01</v>
+        <v>7.4</v>
       </c>
       <c r="AW17" t="n">
-        <v>1.01</v>
+        <v>14</v>
       </c>
       <c r="AX17" t="n">
-        <v>1.01</v>
+        <v>24</v>
       </c>
       <c r="AY17" t="n">
-        <v>1.01</v>
+        <v>13</v>
       </c>
       <c r="AZ17" t="n">
-        <v>1.01</v>
+        <v>13.5</v>
       </c>
       <c r="BA17" t="n">
-        <v>1.01</v>
+        <v>25</v>
       </c>
       <c r="BB17" t="n">
-        <v>1.01</v>
+        <v>2.58</v>
       </c>
       <c r="BC17" t="n">
-        <v>1.01</v>
+        <v>2.58</v>
       </c>
       <c r="BD17" t="n">
-        <v>1.01</v>
+        <v>2.58</v>
       </c>
       <c r="BE17" t="n">
-        <v>1.01</v>
+        <v>2.58</v>
       </c>
       <c r="BF17" t="n">
-        <v>1.01</v>
+        <v>2.58</v>
       </c>
       <c r="BG17" t="n">
-        <v>1.01</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BH17" t="n">
-        <v>4.2</v>
+        <v>4.1</v>
       </c>
       <c r="BI17" t="n">
-        <v>2.72</v>
+        <v>2.76</v>
       </c>
       <c r="BJ17" t="n">
         <v>13.5</v>
       </c>
       <c r="BK17" t="n">
-        <v>6.4</v>
+        <v>2.84</v>
       </c>
       <c r="BL17" t="n">
         <v>1000</v>
       </c>
       <c r="BM17" t="n">
-        <v>21</v>
+        <v>3.6</v>
       </c>
       <c r="BN17" t="n">
         <v>11</v>
       </c>
       <c r="BO17" t="n">
-        <v>5.3</v>
+        <v>2.7</v>
       </c>
       <c r="BP17" t="n">
         <v>1000</v>
       </c>
       <c r="BQ17" t="n">
-        <v>21</v>
+        <v>3.35</v>
       </c>
       <c r="BR17" t="n">
         <v>1000</v>
       </c>
       <c r="BS17" t="n">
-        <v>21</v>
+        <v>3.4</v>
       </c>
       <c r="BT17" t="n">
         <v>6</v>
       </c>
       <c r="BU17" t="n">
-        <v>3.2</v>
+        <v>3.4</v>
       </c>
       <c r="BV17" t="n">
         <v>18</v>
       </c>
       <c r="BW17" t="n">
-        <v>8.4</v>
+        <v>3</v>
       </c>
       <c r="BX17" t="n">
         <v>38</v>
       </c>
       <c r="BY17" t="n">
-        <v>16.5</v>
+        <v>3.25</v>
       </c>
       <c r="BZ17" t="n">
         <v>32</v>
       </c>
       <c r="CA17" t="n">
-        <v>15</v>
+        <v>3.2</v>
       </c>
       <c r="CB17" t="inlineStr">
         <is>
-          <t>2026-06-10 16:02:38</t>
+          <t>2026-06-10 18:12:00</t>
         </is>
       </c>
     </row>
@@ -4921,7 +4921,7 @@
         </is>
       </c>
       <c r="F18" t="n">
-        <v>3.1</v>
+        <v>3</v>
       </c>
       <c r="G18" t="n">
         <v>3.5</v>
@@ -4930,85 +4930,85 @@
         <v>2.42</v>
       </c>
       <c r="I18" t="n">
-        <v>2.64</v>
+        <v>2.68</v>
       </c>
       <c r="J18" t="n">
         <v>3.25</v>
       </c>
       <c r="K18" t="n">
-        <v>3.5</v>
+        <v>3.95</v>
       </c>
       <c r="L18" t="n">
-        <v>1.44</v>
+        <v>1.01</v>
       </c>
       <c r="M18" t="n">
-        <v>1.01</v>
+        <v>1.09</v>
       </c>
       <c r="N18" t="n">
-        <v>3</v>
+        <v>3.05</v>
       </c>
       <c r="O18" t="n">
         <v>1.39</v>
       </c>
       <c r="P18" t="n">
-        <v>1.71</v>
+        <v>1.69</v>
       </c>
       <c r="Q18" t="n">
-        <v>2.2</v>
+        <v>2.16</v>
       </c>
       <c r="R18" t="n">
-        <v>1.22</v>
+        <v>1.26</v>
       </c>
       <c r="S18" t="n">
-        <v>3.55</v>
+        <v>4.1</v>
       </c>
       <c r="T18" t="n">
-        <v>1.01</v>
+        <v>1.84</v>
       </c>
       <c r="U18" t="n">
-        <v>1.01</v>
+        <v>1.92</v>
       </c>
       <c r="V18" t="n">
-        <v>1.6</v>
+        <v>1.59</v>
       </c>
       <c r="W18" t="n">
         <v>1.4</v>
       </c>
       <c r="X18" t="n">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="Y18" t="n">
-        <v>12</v>
+        <v>9.6</v>
       </c>
       <c r="Z18" t="n">
-        <v>21</v>
+        <v>16.5</v>
       </c>
       <c r="AA18" t="n">
         <v>50</v>
       </c>
       <c r="AB18" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="AC18" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="AD18" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="AE18" t="n">
+        <v>34</v>
+      </c>
+      <c r="AF18" t="n">
+        <v>23</v>
+      </c>
+      <c r="AG18" t="n">
         <v>15</v>
       </c>
-      <c r="AC18" t="n">
-        <v>9.800000000000001</v>
-      </c>
-      <c r="AD18" t="n">
-        <v>14.5</v>
-      </c>
-      <c r="AE18" t="n">
-        <v>36</v>
-      </c>
-      <c r="AF18" t="n">
-        <v>30</v>
-      </c>
-      <c r="AG18" t="n">
-        <v>19</v>
-      </c>
       <c r="AH18" t="n">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="AI18" t="n">
-        <v>55</v>
+        <v>70</v>
       </c>
       <c r="AJ18" t="n">
         <v>80</v>
@@ -5017,134 +5017,134 @@
         <v>55</v>
       </c>
       <c r="AL18" t="n">
-        <v>75</v>
+        <v>80</v>
       </c>
       <c r="AM18" t="n">
         <v>1000</v>
       </c>
       <c r="AN18" t="n">
-        <v>1000</v>
+        <v>70</v>
       </c>
       <c r="AO18" t="n">
-        <v>1000</v>
+        <v>38</v>
       </c>
       <c r="AP18" t="n">
-        <v>2.52</v>
+        <v>9.6</v>
       </c>
       <c r="AQ18" t="n">
-        <v>2.42</v>
+        <v>7.8</v>
       </c>
       <c r="AR18" t="n">
-        <v>10.5</v>
+        <v>12</v>
       </c>
       <c r="AS18" t="n">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="AT18" t="n">
-        <v>2.52</v>
+        <v>9.4</v>
       </c>
       <c r="AU18" t="n">
-        <v>2.32</v>
+        <v>6.6</v>
       </c>
       <c r="AV18" t="n">
-        <v>2.5</v>
+        <v>10</v>
       </c>
       <c r="AW18" t="n">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="AX18" t="n">
+        <v>18.5</v>
+      </c>
+      <c r="AY18" t="n">
+        <v>12</v>
+      </c>
+      <c r="AZ18" t="n">
         <v>16</v>
       </c>
-      <c r="AY18" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="AZ18" t="n">
-        <v>2.7</v>
-      </c>
       <c r="BA18" t="n">
-        <v>2.88</v>
+        <v>32</v>
       </c>
       <c r="BB18" t="n">
-        <v>2.92</v>
+        <v>40</v>
       </c>
       <c r="BC18" t="n">
-        <v>2.88</v>
+        <v>29</v>
       </c>
       <c r="BD18" t="n">
-        <v>2.92</v>
+        <v>38</v>
       </c>
       <c r="BE18" t="n">
-        <v>3</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BF18" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="BG18" t="n">
-        <v>3</v>
+        <v>6.4</v>
       </c>
       <c r="BH18" t="n">
-        <v>3.55</v>
+        <v>1000</v>
       </c>
       <c r="BI18" t="n">
-        <v>2.5</v>
+        <v>1.83</v>
       </c>
       <c r="BJ18" t="n">
         <v>13.5</v>
       </c>
       <c r="BK18" t="n">
-        <v>6.6</v>
+        <v>1.61</v>
       </c>
       <c r="BL18" t="n">
         <v>1000</v>
       </c>
       <c r="BM18" t="n">
-        <v>21</v>
+        <v>1.83</v>
       </c>
       <c r="BN18" t="n">
         <v>8.6</v>
       </c>
       <c r="BO18" t="n">
-        <v>4.3</v>
+        <v>4.6</v>
       </c>
       <c r="BP18" t="n">
         <v>38</v>
       </c>
       <c r="BQ18" t="n">
-        <v>17.5</v>
+        <v>1.74</v>
       </c>
       <c r="BR18" t="n">
         <v>1000</v>
       </c>
       <c r="BS18" t="n">
-        <v>21</v>
+        <v>1.77</v>
       </c>
       <c r="BT18" t="n">
         <v>7</v>
       </c>
       <c r="BU18" t="n">
-        <v>3.6</v>
+        <v>3.85</v>
       </c>
       <c r="BV18" t="n">
         <v>28</v>
       </c>
       <c r="BW18" t="n">
-        <v>12.5</v>
+        <v>1.72</v>
       </c>
       <c r="BX18" t="n">
         <v>50</v>
       </c>
       <c r="BY18" t="n">
-        <v>21</v>
+        <v>1.76</v>
       </c>
       <c r="BZ18" t="n">
         <v>48</v>
       </c>
       <c r="CA18" t="n">
-        <v>21</v>
+        <v>1.76</v>
       </c>
       <c r="CB18" t="inlineStr">
         <is>
-          <t>2026-06-10 16:02:38</t>
+          <t>2026-06-10 18:12:00</t>
         </is>
       </c>
     </row>
@@ -5175,230 +5175,230 @@
         </is>
       </c>
       <c r="F19" t="n">
-        <v>2.24</v>
+        <v>2.26</v>
       </c>
       <c r="G19" t="n">
-        <v>2.4</v>
+        <v>2.42</v>
       </c>
       <c r="H19" t="n">
         <v>3.2</v>
       </c>
       <c r="I19" t="n">
-        <v>3.55</v>
+        <v>3.75</v>
       </c>
       <c r="J19" t="n">
-        <v>3.5</v>
+        <v>3.1</v>
       </c>
       <c r="K19" t="n">
-        <v>3.8</v>
+        <v>4.7</v>
       </c>
       <c r="L19" t="n">
-        <v>1.34</v>
+        <v>1.12</v>
       </c>
       <c r="M19" t="n">
         <v>1.01</v>
       </c>
       <c r="N19" t="n">
-        <v>3.4</v>
+        <v>3.95</v>
       </c>
       <c r="O19" t="n">
         <v>1.27</v>
       </c>
       <c r="P19" t="n">
-        <v>2.02</v>
+        <v>1.86</v>
       </c>
       <c r="Q19" t="n">
         <v>1.83</v>
       </c>
       <c r="R19" t="n">
-        <v>1.32</v>
+        <v>1.33</v>
       </c>
       <c r="S19" t="n">
-        <v>2.72</v>
+        <v>3.1</v>
       </c>
       <c r="T19" t="n">
-        <v>1.01</v>
+        <v>1.38</v>
       </c>
       <c r="U19" t="n">
-        <v>1.01</v>
+        <v>1.72</v>
       </c>
       <c r="V19" t="n">
         <v>1.4</v>
       </c>
       <c r="W19" t="n">
-        <v>1.71</v>
+        <v>1.7</v>
       </c>
       <c r="X19" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="Y19" t="n">
-        <v>19.5</v>
+        <v>20</v>
       </c>
       <c r="Z19" t="n">
+        <v>36</v>
+      </c>
+      <c r="AA19" t="n">
+        <v>85</v>
+      </c>
+      <c r="AB19" t="n">
+        <v>16</v>
+      </c>
+      <c r="AC19" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="AD19" t="n">
+        <v>21</v>
+      </c>
+      <c r="AE19" t="n">
+        <v>55</v>
+      </c>
+      <c r="AF19" t="n">
+        <v>23</v>
+      </c>
+      <c r="AG19" t="n">
+        <v>17</v>
+      </c>
+      <c r="AH19" t="n">
+        <v>24</v>
+      </c>
+      <c r="AI19" t="n">
+        <v>65</v>
+      </c>
+      <c r="AJ19" t="n">
+        <v>46</v>
+      </c>
+      <c r="AK19" t="n">
         <v>34</v>
-      </c>
-      <c r="AA19" t="n">
-        <v>80</v>
-      </c>
-      <c r="AB19" t="n">
-        <v>15.5</v>
-      </c>
-      <c r="AC19" t="n">
-        <v>12</v>
-      </c>
-      <c r="AD19" t="n">
-        <v>20</v>
-      </c>
-      <c r="AE19" t="n">
-        <v>50</v>
-      </c>
-      <c r="AF19" t="n">
-        <v>22</v>
-      </c>
-      <c r="AG19" t="n">
-        <v>16</v>
-      </c>
-      <c r="AH19" t="n">
-        <v>23</v>
-      </c>
-      <c r="AI19" t="n">
-        <v>60</v>
-      </c>
-      <c r="AJ19" t="n">
-        <v>42</v>
-      </c>
-      <c r="AK19" t="n">
-        <v>32</v>
       </c>
       <c r="AL19" t="n">
         <v>50</v>
       </c>
       <c r="AM19" t="n">
-        <v>100</v>
+        <v>1000</v>
       </c>
       <c r="AN19" t="n">
-        <v>1000</v>
+        <v>25</v>
       </c>
       <c r="AO19" t="n">
-        <v>1000</v>
+        <v>48</v>
       </c>
       <c r="AP19" t="n">
-        <v>2.28</v>
+        <v>13.5</v>
       </c>
       <c r="AQ19" t="n">
-        <v>9.800000000000001</v>
+        <v>12</v>
       </c>
       <c r="AR19" t="n">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="AS19" t="n">
-        <v>2.48</v>
+        <v>2.62</v>
       </c>
       <c r="AT19" t="n">
-        <v>9</v>
+        <v>9.4</v>
       </c>
       <c r="AU19" t="n">
-        <v>2.1</v>
+        <v>7.2</v>
       </c>
       <c r="AV19" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="AW19" t="n">
-        <v>24</v>
+        <v>2.58</v>
       </c>
       <c r="AX19" t="n">
-        <v>10.5</v>
+        <v>13</v>
       </c>
       <c r="AY19" t="n">
-        <v>2.2</v>
+        <v>9.6</v>
       </c>
       <c r="AZ19" t="n">
-        <v>2.3</v>
+        <v>14</v>
       </c>
       <c r="BA19" t="n">
-        <v>2.44</v>
+        <v>36</v>
       </c>
       <c r="BB19" t="n">
-        <v>2.4</v>
+        <v>2.56</v>
       </c>
       <c r="BC19" t="n">
-        <v>2.36</v>
+        <v>20</v>
       </c>
       <c r="BD19" t="n">
-        <v>2.42</v>
+        <v>2.58</v>
       </c>
       <c r="BE19" t="n">
-        <v>2.48</v>
+        <v>2.72</v>
       </c>
       <c r="BF19" t="n">
-        <v>2.56</v>
+        <v>12</v>
       </c>
       <c r="BG19" t="n">
         <v>2.56</v>
       </c>
       <c r="BH19" t="n">
-        <v>4.4</v>
+        <v>1000</v>
       </c>
       <c r="BI19" t="n">
-        <v>2.84</v>
+        <v>1.84</v>
       </c>
       <c r="BJ19" t="n">
         <v>13</v>
       </c>
       <c r="BK19" t="n">
-        <v>5.6</v>
+        <v>1.61</v>
       </c>
       <c r="BL19" t="n">
         <v>1000</v>
       </c>
       <c r="BM19" t="n">
-        <v>21</v>
+        <v>1.84</v>
       </c>
       <c r="BN19" t="n">
         <v>7.6</v>
       </c>
       <c r="BO19" t="n">
-        <v>3.45</v>
+        <v>3.95</v>
       </c>
       <c r="BP19" t="n">
         <v>23</v>
       </c>
       <c r="BQ19" t="n">
-        <v>9.6</v>
+        <v>1.71</v>
       </c>
       <c r="BR19" t="n">
         <v>40</v>
       </c>
       <c r="BS19" t="n">
-        <v>16.5</v>
+        <v>1.76</v>
       </c>
       <c r="BT19" t="n">
         <v>9.6</v>
       </c>
       <c r="BU19" t="n">
-        <v>4.3</v>
+        <v>4.9</v>
       </c>
       <c r="BV19" t="n">
         <v>38</v>
       </c>
       <c r="BW19" t="n">
-        <v>15</v>
+        <v>1.76</v>
       </c>
       <c r="BX19" t="n">
         <v>50</v>
       </c>
       <c r="BY19" t="n">
-        <v>20</v>
+        <v>1.78</v>
       </c>
       <c r="BZ19" t="n">
         <v>34</v>
       </c>
       <c r="CA19" t="n">
-        <v>14</v>
+        <v>1.75</v>
       </c>
       <c r="CB19" t="inlineStr">
         <is>
-          <t>2026-06-10 16:02:38</t>
+          <t>2026-06-10 18:12:00</t>
         </is>
       </c>
     </row>
@@ -5429,7 +5429,7 @@
         </is>
       </c>
       <c r="F20" t="n">
-        <v>1.35</v>
+        <v>1.36</v>
       </c>
       <c r="G20" t="n">
         <v>1.4</v>
@@ -5450,10 +5450,10 @@
         <v>1.33</v>
       </c>
       <c r="M20" t="n">
-        <v>1.01</v>
+        <v>1.06</v>
       </c>
       <c r="N20" t="n">
-        <v>2.06</v>
+        <v>3.7</v>
       </c>
       <c r="O20" t="n">
         <v>1.26</v>
@@ -5468,13 +5468,13 @@
         <v>1.38</v>
       </c>
       <c r="S20" t="n">
-        <v>3</v>
+        <v>3.15</v>
       </c>
       <c r="T20" t="n">
-        <v>1.01</v>
+        <v>2.18</v>
       </c>
       <c r="U20" t="n">
-        <v>1.01</v>
+        <v>1.66</v>
       </c>
       <c r="V20" t="n">
         <v>1.07</v>
@@ -5483,10 +5483,10 @@
         <v>3.45</v>
       </c>
       <c r="X20" t="n">
-        <v>22</v>
+        <v>1000</v>
       </c>
       <c r="Y20" t="n">
-        <v>40</v>
+        <v>1000</v>
       </c>
       <c r="Z20" t="n">
         <v>1000</v>
@@ -5495,164 +5495,164 @@
         <v>1000</v>
       </c>
       <c r="AB20" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="AC20" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AD20" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AE20" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AF20" t="n">
+        <v>8</v>
+      </c>
+      <c r="AG20" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AH20" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AI20" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AJ20" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AK20" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AL20" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AM20" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AN20" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="AO20" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AP20" t="n">
+        <v>14</v>
+      </c>
+      <c r="AQ20" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="AR20" t="n">
+        <v>1.66</v>
+      </c>
+      <c r="AS20" t="n">
+        <v>1.66</v>
+      </c>
+      <c r="AT20" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="AU20" t="n">
+        <v>10</v>
+      </c>
+      <c r="AV20" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="AW20" t="n">
+        <v>1.66</v>
+      </c>
+      <c r="AX20" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="AY20" t="n">
+        <v>9</v>
+      </c>
+      <c r="AZ20" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="BA20" t="n">
+        <v>1.66</v>
+      </c>
+      <c r="BB20" t="n">
         <v>9.199999999999999</v>
       </c>
-      <c r="AC20" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AD20" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AE20" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AF20" t="n">
-        <v>9.4</v>
-      </c>
-      <c r="AG20" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AH20" t="n">
-        <v>42</v>
-      </c>
-      <c r="AI20" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AJ20" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AK20" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AL20" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AM20" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AN20" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AO20" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AP20" t="n">
-        <v>1.35</v>
-      </c>
-      <c r="AQ20" t="n">
-        <v>21</v>
-      </c>
-      <c r="AR20" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="AS20" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="AT20" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="AU20" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="AV20" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="AW20" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="AX20" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="AY20" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="AZ20" t="n">
-        <v>1.39</v>
-      </c>
-      <c r="BA20" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="BB20" t="n">
-        <v>1.44</v>
-      </c>
       <c r="BC20" t="n">
-        <v>1.44</v>
+        <v>13.5</v>
       </c>
       <c r="BD20" t="n">
-        <v>1.44</v>
+        <v>1.66</v>
       </c>
       <c r="BE20" t="n">
-        <v>1.44</v>
+        <v>1.66</v>
       </c>
       <c r="BF20" t="n">
-        <v>1.44</v>
+        <v>5.1</v>
       </c>
       <c r="BG20" t="n">
-        <v>1.44</v>
+        <v>1.66</v>
       </c>
       <c r="BH20" t="n">
         <v>1000</v>
       </c>
       <c r="BI20" t="n">
-        <v>1.01</v>
+        <v>1.88</v>
       </c>
       <c r="BJ20" t="n">
         <v>18.5</v>
       </c>
       <c r="BK20" t="n">
-        <v>8</v>
+        <v>1.71</v>
       </c>
       <c r="BL20" t="n">
         <v>1000</v>
       </c>
       <c r="BM20" t="n">
-        <v>21</v>
+        <v>1.88</v>
       </c>
       <c r="BN20" t="n">
         <v>4.9</v>
       </c>
       <c r="BO20" t="n">
-        <v>2.54</v>
+        <v>2.8</v>
       </c>
       <c r="BP20" t="n">
         <v>11.5</v>
       </c>
       <c r="BQ20" t="n">
-        <v>5.1</v>
+        <v>1.61</v>
       </c>
       <c r="BR20" t="n">
         <v>40</v>
       </c>
       <c r="BS20" t="n">
-        <v>16.5</v>
+        <v>1.8</v>
       </c>
       <c r="BT20" t="n">
         <v>20</v>
       </c>
       <c r="BU20" t="n">
-        <v>8.4</v>
+        <v>1.72</v>
       </c>
       <c r="BV20" t="n">
         <v>1000</v>
       </c>
       <c r="BW20" t="n">
-        <v>21</v>
+        <v>1.88</v>
       </c>
       <c r="BX20" t="n">
         <v>1000</v>
       </c>
       <c r="BY20" t="n">
-        <v>21</v>
+        <v>1.88</v>
       </c>
       <c r="BZ20" t="n">
         <v>22</v>
       </c>
       <c r="CA20" t="n">
-        <v>9.199999999999999</v>
+        <v>1.73</v>
       </c>
       <c r="CB20" t="inlineStr">
         <is>
-          <t>2026-06-10 16:02:38</t>
+          <t>2026-06-10 18:12:00</t>
         </is>
       </c>
     </row>
@@ -5683,31 +5683,31 @@
         </is>
       </c>
       <c r="F21" t="n">
-        <v>2.82</v>
+        <v>2.68</v>
       </c>
       <c r="G21" t="n">
-        <v>3.1</v>
+        <v>3.2</v>
       </c>
       <c r="H21" t="n">
-        <v>2.38</v>
+        <v>2.3</v>
       </c>
       <c r="I21" t="n">
-        <v>2.6</v>
+        <v>2.8</v>
       </c>
       <c r="J21" t="n">
-        <v>3.65</v>
+        <v>2.64</v>
       </c>
       <c r="K21" t="n">
-        <v>4.1</v>
+        <v>1000</v>
       </c>
       <c r="L21" t="n">
-        <v>1.28</v>
+        <v>1.01</v>
       </c>
       <c r="M21" t="n">
         <v>1.01</v>
       </c>
       <c r="N21" t="n">
-        <v>2.36</v>
+        <v>3.95</v>
       </c>
       <c r="O21" t="n">
         <v>1.2</v>
@@ -5716,25 +5716,25 @@
         <v>2.36</v>
       </c>
       <c r="Q21" t="n">
-        <v>1.56</v>
+        <v>1.4</v>
       </c>
       <c r="R21" t="n">
-        <v>1.21</v>
+        <v>1.39</v>
       </c>
       <c r="S21" t="n">
-        <v>1.67</v>
+        <v>2.24</v>
       </c>
       <c r="T21" t="n">
-        <v>1.01</v>
+        <v>1.3</v>
       </c>
       <c r="U21" t="n">
-        <v>1.01</v>
+        <v>1.9</v>
       </c>
       <c r="V21" t="n">
-        <v>1.65</v>
+        <v>1.55</v>
       </c>
       <c r="W21" t="n">
-        <v>1.47</v>
+        <v>1.45</v>
       </c>
       <c r="X21" t="n">
         <v>1000</v>
@@ -5752,10 +5752,10 @@
         <v>1000</v>
       </c>
       <c r="AC21" t="n">
-        <v>1000</v>
+        <v>18</v>
       </c>
       <c r="AD21" t="n">
-        <v>1000</v>
+        <v>22</v>
       </c>
       <c r="AE21" t="n">
         <v>1000</v>
@@ -5791,129 +5791,129 @@
         <v>1000</v>
       </c>
       <c r="AP21" t="n">
-        <v>1.01</v>
+        <v>1.11</v>
       </c>
       <c r="AQ21" t="n">
-        <v>1.01</v>
+        <v>1.11</v>
       </c>
       <c r="AR21" t="n">
-        <v>1.01</v>
+        <v>1.11</v>
       </c>
       <c r="AS21" t="n">
-        <v>1.01</v>
+        <v>1.11</v>
       </c>
       <c r="AT21" t="n">
-        <v>1.01</v>
+        <v>1.11</v>
       </c>
       <c r="AU21" t="n">
-        <v>1.01</v>
+        <v>1.05</v>
       </c>
       <c r="AV21" t="n">
-        <v>1.01</v>
+        <v>1.06</v>
       </c>
       <c r="AW21" t="n">
-        <v>1.01</v>
+        <v>1.11</v>
       </c>
       <c r="AX21" t="n">
-        <v>1.01</v>
+        <v>1.11</v>
       </c>
       <c r="AY21" t="n">
-        <v>1.01</v>
+        <v>1.11</v>
       </c>
       <c r="AZ21" t="n">
-        <v>1.01</v>
+        <v>1.11</v>
       </c>
       <c r="BA21" t="n">
-        <v>1.01</v>
+        <v>1.11</v>
       </c>
       <c r="BB21" t="n">
-        <v>1.01</v>
+        <v>1.11</v>
       </c>
       <c r="BC21" t="n">
-        <v>1.01</v>
+        <v>1.11</v>
       </c>
       <c r="BD21" t="n">
-        <v>1.01</v>
+        <v>1.11</v>
       </c>
       <c r="BE21" t="n">
-        <v>1.01</v>
+        <v>1.11</v>
       </c>
       <c r="BF21" t="n">
-        <v>1.01</v>
+        <v>1.11</v>
       </c>
       <c r="BG21" t="n">
-        <v>1.01</v>
+        <v>1.11</v>
       </c>
       <c r="BH21" t="n">
         <v>1000</v>
       </c>
       <c r="BI21" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BJ21" t="n">
         <v>1000</v>
       </c>
       <c r="BK21" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BL21" t="n">
         <v>1000</v>
       </c>
       <c r="BM21" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BN21" t="n">
         <v>1000</v>
       </c>
       <c r="BO21" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BP21" t="n">
         <v>1000</v>
       </c>
       <c r="BQ21" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BR21" t="n">
         <v>1000</v>
       </c>
       <c r="BS21" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BT21" t="n">
         <v>1000</v>
       </c>
       <c r="BU21" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BV21" t="n">
         <v>1000</v>
       </c>
       <c r="BW21" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BX21" t="n">
         <v>1000</v>
       </c>
       <c r="BY21" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BZ21" t="n">
         <v>1000</v>
       </c>
       <c r="CA21" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="CB21" t="inlineStr">
         <is>
-          <t>2026-06-10 16:02:38</t>
+          <t>2026-06-10 18:12:00</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Irish Premier Division</t>
+          <t>Bolivian Liga de Futbol Profesional</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -5928,31 +5928,31 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>Shelbourne</t>
+          <t>San Antonio Bulo Bulo</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Shamrock Rovers</t>
+          <t>Academia de Balompie Boli</t>
         </is>
       </c>
       <c r="F22" t="n">
-        <v>2.78</v>
+        <v>1.6</v>
       </c>
       <c r="G22" t="n">
-        <v>3</v>
+        <v>1.62</v>
       </c>
       <c r="H22" t="n">
-        <v>2.68</v>
+        <v>4.8</v>
       </c>
       <c r="I22" t="n">
-        <v>2.92</v>
+        <v>870</v>
       </c>
       <c r="J22" t="n">
-        <v>3.2</v>
+        <v>4.5</v>
       </c>
       <c r="K22" t="n">
-        <v>3.5</v>
+        <v>500</v>
       </c>
       <c r="L22" t="n">
         <v>1.01</v>
@@ -5961,34 +5961,34 @@
         <v>1.01</v>
       </c>
       <c r="N22" t="n">
-        <v>3.25</v>
+        <v>1.25</v>
       </c>
       <c r="O22" t="n">
-        <v>1.37</v>
+        <v>1.1</v>
       </c>
       <c r="P22" t="n">
-        <v>1.78</v>
+        <v>1.24</v>
       </c>
       <c r="Q22" t="n">
-        <v>2.12</v>
+        <v>1.1</v>
       </c>
       <c r="R22" t="n">
-        <v>1.2</v>
+        <v>1.18</v>
       </c>
       <c r="S22" t="n">
-        <v>3.85</v>
+        <v>1.1</v>
       </c>
       <c r="T22" t="n">
-        <v>1.01</v>
+        <v>1.11</v>
       </c>
       <c r="U22" t="n">
-        <v>1.01</v>
+        <v>1.11</v>
       </c>
       <c r="V22" t="n">
-        <v>1.52</v>
+        <v>1.18</v>
       </c>
       <c r="W22" t="n">
-        <v>1.5</v>
+        <v>2.6</v>
       </c>
       <c r="X22" t="n">
         <v>1000</v>
@@ -6045,52 +6045,52 @@
         <v>1000</v>
       </c>
       <c r="AP22" t="n">
-        <v>9.6</v>
+        <v>1.01</v>
       </c>
       <c r="AQ22" t="n">
-        <v>8.199999999999999</v>
+        <v>1.01</v>
       </c>
       <c r="AR22" t="n">
-        <v>11.5</v>
+        <v>1.01</v>
       </c>
       <c r="AS22" t="n">
-        <v>27</v>
+        <v>1.01</v>
       </c>
       <c r="AT22" t="n">
-        <v>8.6</v>
+        <v>1.01</v>
       </c>
       <c r="AU22" t="n">
-        <v>6</v>
+        <v>1.01</v>
       </c>
       <c r="AV22" t="n">
-        <v>9.6</v>
+        <v>1.01</v>
       </c>
       <c r="AW22" t="n">
-        <v>22</v>
+        <v>1.01</v>
       </c>
       <c r="AX22" t="n">
-        <v>12.5</v>
+        <v>1.01</v>
       </c>
       <c r="AY22" t="n">
-        <v>9.6</v>
+        <v>1.01</v>
       </c>
       <c r="AZ22" t="n">
-        <v>16</v>
+        <v>1.01</v>
       </c>
       <c r="BA22" t="n">
-        <v>34</v>
+        <v>1.01</v>
       </c>
       <c r="BB22" t="n">
-        <v>28</v>
+        <v>1.01</v>
       </c>
       <c r="BC22" t="n">
-        <v>24</v>
+        <v>1.01</v>
       </c>
       <c r="BD22" t="n">
-        <v>36</v>
+        <v>1.01</v>
       </c>
       <c r="BE22" t="n">
-        <v>40</v>
+        <v>1.01</v>
       </c>
       <c r="BF22" t="n">
         <v>1.01</v>
@@ -6102,319 +6102,827 @@
         <v>1000</v>
       </c>
       <c r="BI22" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BJ22" t="n">
         <v>1000</v>
       </c>
       <c r="BK22" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BL22" t="n">
         <v>1000</v>
       </c>
       <c r="BM22" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BN22" t="n">
         <v>1000</v>
       </c>
       <c r="BO22" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BP22" t="n">
         <v>1000</v>
       </c>
       <c r="BQ22" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BR22" t="n">
         <v>1000</v>
       </c>
       <c r="BS22" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BT22" t="n">
         <v>1000</v>
       </c>
       <c r="BU22" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BV22" t="n">
         <v>1000</v>
       </c>
       <c r="BW22" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BX22" t="n">
         <v>1000</v>
       </c>
       <c r="BY22" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BZ22" t="n">
         <v>1000</v>
       </c>
       <c r="CA22" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="CB22" t="inlineStr">
         <is>
-          <t>2026-06-10 16:02:38</t>
+          <t>2026-06-10 18:12:00</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
+          <t>Irish Premier Division</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>2026-06-12</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>16:00:00</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>Shelbourne</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>Shamrock Rovers</t>
+        </is>
+      </c>
+      <c r="F23" t="n">
+        <v>2.78</v>
+      </c>
+      <c r="G23" t="n">
+        <v>3.05</v>
+      </c>
+      <c r="H23" t="n">
+        <v>2.68</v>
+      </c>
+      <c r="I23" t="n">
+        <v>2.92</v>
+      </c>
+      <c r="J23" t="n">
+        <v>3</v>
+      </c>
+      <c r="K23" t="n">
+        <v>3.55</v>
+      </c>
+      <c r="L23" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="M23" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="N23" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="O23" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="P23" t="n">
+        <v>1.78</v>
+      </c>
+      <c r="Q23" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="R23" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="S23" t="n">
+        <v>3.85</v>
+      </c>
+      <c r="T23" t="n">
+        <v>1.81</v>
+      </c>
+      <c r="U23" t="n">
+        <v>2.04</v>
+      </c>
+      <c r="V23" t="n">
+        <v>1.52</v>
+      </c>
+      <c r="W23" t="n">
+        <v>1.49</v>
+      </c>
+      <c r="X23" t="n">
+        <v>1000</v>
+      </c>
+      <c r="Y23" t="n">
+        <v>1000</v>
+      </c>
+      <c r="Z23" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AA23" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AB23" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AC23" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AD23" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AE23" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AF23" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AG23" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AH23" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AI23" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AJ23" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AK23" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AL23" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AM23" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AN23" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AO23" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AP23" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AQ23" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="AR23" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="AS23" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AT23" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="AU23" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="AV23" t="n">
+        <v>11</v>
+      </c>
+      <c r="AW23" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AX23" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="AY23" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="AZ23" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BA23" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BB23" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BC23" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BD23" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BE23" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BF23" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="BG23" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="BH23" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BI23" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BJ23" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="BK23" t="n">
+        <v>1.59</v>
+      </c>
+      <c r="BL23" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BM23" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BN23" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="BO23" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="BP23" t="n">
+        <v>34</v>
+      </c>
+      <c r="BQ23" t="n">
+        <v>1.71</v>
+      </c>
+      <c r="BR23" t="n">
+        <v>50</v>
+      </c>
+      <c r="BS23" t="n">
+        <v>1.74</v>
+      </c>
+      <c r="BT23" t="n">
+        <v>8</v>
+      </c>
+      <c r="BU23" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="BV23" t="n">
+        <v>30</v>
+      </c>
+      <c r="BW23" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="BX23" t="n">
+        <v>50</v>
+      </c>
+      <c r="BY23" t="n">
+        <v>1.74</v>
+      </c>
+      <c r="BZ23" t="n">
+        <v>46</v>
+      </c>
+      <c r="CA23" t="n">
+        <v>1.74</v>
+      </c>
+      <c r="CB23" t="inlineStr">
+        <is>
+          <t>2026-06-10 18:12:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
           <t>Brazilian Serie B</t>
         </is>
       </c>
-      <c r="B23" t="inlineStr">
+      <c r="B24" t="inlineStr">
         <is>
           <t>2026-06-12</t>
         </is>
       </c>
-      <c r="C23" t="inlineStr">
+      <c r="C24" t="inlineStr">
         <is>
           <t>19:00:00</t>
         </is>
       </c>
-      <c r="D23" t="inlineStr">
+      <c r="D24" t="inlineStr">
         <is>
           <t>Atletico GO</t>
         </is>
       </c>
-      <c r="E23" t="inlineStr">
+      <c r="E24" t="inlineStr">
         <is>
           <t>CRB</t>
         </is>
       </c>
-      <c r="F23" t="n">
+      <c r="F24" t="n">
+        <v>2.18</v>
+      </c>
+      <c r="G24" t="n">
+        <v>2.58</v>
+      </c>
+      <c r="H24" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="I24" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="J24" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="K24" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="L24" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="M24" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="N24" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="O24" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="P24" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="Q24" t="n">
+        <v>2.18</v>
+      </c>
+      <c r="R24" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="S24" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="T24" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="U24" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="V24" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="W24" t="n">
+        <v>1.64</v>
+      </c>
+      <c r="X24" t="n">
+        <v>1000</v>
+      </c>
+      <c r="Y24" t="n">
+        <v>1000</v>
+      </c>
+      <c r="Z24" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AA24" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AB24" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AC24" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AD24" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AE24" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AF24" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AG24" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AH24" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AI24" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AJ24" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AK24" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AL24" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AM24" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AN24" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AO24" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AP24" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AQ24" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AR24" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AS24" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AT24" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AU24" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AV24" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AW24" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AX24" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AY24" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AZ24" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BA24" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BB24" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BC24" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BD24" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BE24" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BF24" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BG24" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BH24" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BI24" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BJ24" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BK24" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BL24" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BM24" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BN24" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BO24" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BP24" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BQ24" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BR24" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BS24" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BT24" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BU24" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BV24" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BW24" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BX24" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BY24" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BZ24" t="n">
+        <v>1000</v>
+      </c>
+      <c r="CA24" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="CB24" t="inlineStr">
+        <is>
+          <t>2026-06-10 18:12:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>Bolivian Liga de Futbol Profesional</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>2026-06-12</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>20:00:00</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>Nacional Potosi</t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>CDT Real Oruro</t>
+        </is>
+      </c>
+      <c r="F25" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="G25" t="n">
+        <v>1000</v>
+      </c>
+      <c r="H25" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="I25" t="n">
+        <v>1000</v>
+      </c>
+      <c r="J25" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="K25" t="n">
+        <v>1000</v>
+      </c>
+      <c r="L25" t="n">
         <v>0</v>
       </c>
-      <c r="G23" t="n">
+      <c r="M25" t="n">
         <v>0</v>
       </c>
-      <c r="H23" t="n">
+      <c r="N25" t="n">
         <v>0</v>
       </c>
-      <c r="I23" t="n">
+      <c r="O25" t="n">
         <v>0</v>
       </c>
-      <c r="J23" t="n">
+      <c r="P25" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="Q25" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="R25" t="n">
         <v>0</v>
       </c>
-      <c r="K23" t="n">
+      <c r="S25" t="n">
         <v>0</v>
       </c>
-      <c r="L23" t="n">
+      <c r="T25" t="n">
         <v>0</v>
       </c>
-      <c r="M23" t="n">
+      <c r="U25" t="n">
         <v>0</v>
       </c>
-      <c r="N23" t="n">
+      <c r="V25" t="n">
         <v>0</v>
       </c>
-      <c r="O23" t="n">
+      <c r="W25" t="n">
         <v>0</v>
       </c>
-      <c r="P23" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="Q23" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="R23" t="n">
+      <c r="X25" t="n">
         <v>0</v>
       </c>
-      <c r="S23" t="n">
+      <c r="Y25" t="n">
         <v>0</v>
       </c>
-      <c r="T23" t="n">
+      <c r="Z25" t="n">
         <v>0</v>
       </c>
-      <c r="U23" t="n">
+      <c r="AA25" t="n">
         <v>0</v>
       </c>
-      <c r="V23" t="n">
+      <c r="AB25" t="n">
         <v>0</v>
       </c>
-      <c r="W23" t="n">
+      <c r="AC25" t="n">
         <v>0</v>
       </c>
-      <c r="X23" t="n">
+      <c r="AD25" t="n">
         <v>0</v>
       </c>
-      <c r="Y23" t="n">
+      <c r="AE25" t="n">
         <v>0</v>
       </c>
-      <c r="Z23" t="n">
+      <c r="AF25" t="n">
         <v>0</v>
       </c>
-      <c r="AA23" t="n">
+      <c r="AG25" t="n">
         <v>0</v>
       </c>
-      <c r="AB23" t="n">
+      <c r="AH25" t="n">
         <v>0</v>
       </c>
-      <c r="AC23" t="n">
+      <c r="AI25" t="n">
         <v>0</v>
       </c>
-      <c r="AD23" t="n">
+      <c r="AJ25" t="n">
         <v>0</v>
       </c>
-      <c r="AE23" t="n">
+      <c r="AK25" t="n">
         <v>0</v>
       </c>
-      <c r="AF23" t="n">
+      <c r="AL25" t="n">
         <v>0</v>
       </c>
-      <c r="AG23" t="n">
+      <c r="AM25" t="n">
         <v>0</v>
       </c>
-      <c r="AH23" t="n">
+      <c r="AN25" t="n">
         <v>0</v>
       </c>
-      <c r="AI23" t="n">
+      <c r="AO25" t="n">
         <v>0</v>
       </c>
-      <c r="AJ23" t="n">
+      <c r="AP25" t="n">
         <v>0</v>
       </c>
-      <c r="AK23" t="n">
+      <c r="AQ25" t="n">
         <v>0</v>
       </c>
-      <c r="AL23" t="n">
+      <c r="AR25" t="n">
         <v>0</v>
       </c>
-      <c r="AM23" t="n">
+      <c r="AS25" t="n">
         <v>0</v>
       </c>
-      <c r="AN23" t="n">
+      <c r="AT25" t="n">
         <v>0</v>
       </c>
-      <c r="AO23" t="n">
+      <c r="AU25" t="n">
         <v>0</v>
       </c>
-      <c r="AP23" t="n">
+      <c r="AV25" t="n">
         <v>0</v>
       </c>
-      <c r="AQ23" t="n">
+      <c r="AW25" t="n">
         <v>0</v>
       </c>
-      <c r="AR23" t="n">
+      <c r="AX25" t="n">
         <v>0</v>
       </c>
-      <c r="AS23" t="n">
+      <c r="AY25" t="n">
         <v>0</v>
       </c>
-      <c r="AT23" t="n">
+      <c r="AZ25" t="n">
         <v>0</v>
       </c>
-      <c r="AU23" t="n">
+      <c r="BA25" t="n">
         <v>0</v>
       </c>
-      <c r="AV23" t="n">
+      <c r="BB25" t="n">
         <v>0</v>
       </c>
-      <c r="AW23" t="n">
+      <c r="BC25" t="n">
         <v>0</v>
       </c>
-      <c r="AX23" t="n">
+      <c r="BD25" t="n">
         <v>0</v>
       </c>
-      <c r="AY23" t="n">
+      <c r="BE25" t="n">
         <v>0</v>
       </c>
-      <c r="AZ23" t="n">
+      <c r="BF25" t="n">
         <v>0</v>
       </c>
-      <c r="BA23" t="n">
+      <c r="BG25" t="n">
         <v>0</v>
       </c>
-      <c r="BB23" t="n">
+      <c r="BH25" t="n">
         <v>0</v>
       </c>
-      <c r="BC23" t="n">
+      <c r="BI25" t="n">
         <v>0</v>
       </c>
-      <c r="BD23" t="n">
+      <c r="BJ25" t="n">
         <v>0</v>
       </c>
-      <c r="BE23" t="n">
+      <c r="BK25" t="n">
         <v>0</v>
       </c>
-      <c r="BF23" t="n">
+      <c r="BL25" t="n">
         <v>0</v>
       </c>
-      <c r="BG23" t="n">
+      <c r="BM25" t="n">
         <v>0</v>
       </c>
-      <c r="BH23" t="n">
+      <c r="BN25" t="n">
         <v>0</v>
       </c>
-      <c r="BI23" t="n">
+      <c r="BO25" t="n">
         <v>0</v>
       </c>
-      <c r="BJ23" t="n">
+      <c r="BP25" t="n">
         <v>0</v>
       </c>
-      <c r="BK23" t="n">
+      <c r="BQ25" t="n">
         <v>0</v>
       </c>
-      <c r="BL23" t="n">
+      <c r="BR25" t="n">
         <v>0</v>
       </c>
-      <c r="BM23" t="n">
+      <c r="BS25" t="n">
         <v>0</v>
       </c>
-      <c r="BN23" t="n">
+      <c r="BT25" t="n">
         <v>0</v>
       </c>
-      <c r="BO23" t="n">
+      <c r="BU25" t="n">
         <v>0</v>
       </c>
-      <c r="BP23" t="n">
+      <c r="BV25" t="n">
         <v>0</v>
       </c>
-      <c r="BQ23" t="n">
+      <c r="BW25" t="n">
         <v>0</v>
       </c>
-      <c r="BR23" t="n">
+      <c r="BX25" t="n">
         <v>0</v>
       </c>
-      <c r="BS23" t="n">
+      <c r="BY25" t="n">
         <v>0</v>
       </c>
-      <c r="BT23" t="n">
+      <c r="BZ25" t="n">
         <v>0</v>
       </c>
-      <c r="BU23" t="n">
+      <c r="CA25" t="n">
         <v>0</v>
       </c>
-      <c r="BV23" t="n">
-        <v>0</v>
-      </c>
-      <c r="BW23" t="n">
-        <v>0</v>
-      </c>
-      <c r="BX23" t="n">
-        <v>0</v>
-      </c>
-      <c r="BY23" t="n">
-        <v>0</v>
-      </c>
-      <c r="BZ23" t="n">
-        <v>0</v>
-      </c>
-      <c r="CA23" t="n">
-        <v>0</v>
-      </c>
-      <c r="CB23" t="inlineStr">
-        <is>
-          <t>2026-06-10 16:02:38</t>
+      <c r="CB25" t="inlineStr">
+        <is>
+          <t>2026-06-10 18:12:00</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-06-12.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-06-12.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:CB25"/>
+  <dimension ref="A1:CB27"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -857,7 +857,7 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>1.04</v>
+        <v>1.08</v>
       </c>
       <c r="G2" t="n">
         <v>1000</v>
@@ -881,16 +881,16 @@
         <v>1.01</v>
       </c>
       <c r="N2" t="n">
-        <v>1.3</v>
+        <v>1.25</v>
       </c>
       <c r="O2" t="n">
         <v>1.3</v>
       </c>
       <c r="P2" t="n">
-        <v>1.31</v>
+        <v>1.24</v>
       </c>
       <c r="Q2" t="n">
-        <v>1.8</v>
+        <v>1.3</v>
       </c>
       <c r="R2" t="n">
         <v>1.18</v>
@@ -1080,7 +1080,7 @@
       </c>
       <c r="CB2" t="inlineStr">
         <is>
-          <t>2026-06-10 18:12:00</t>
+          <t>2026-06-10 20:21:14</t>
         </is>
       </c>
     </row>
@@ -1111,13 +1111,13 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>1.09</v>
+        <v>1.04</v>
       </c>
       <c r="G3" t="n">
         <v>1000</v>
       </c>
       <c r="H3" t="n">
-        <v>1.09</v>
+        <v>1.04</v>
       </c>
       <c r="I3" t="n">
         <v>1000</v>
@@ -1150,7 +1150,7 @@
         <v>1.18</v>
       </c>
       <c r="S3" t="n">
-        <v>2.46</v>
+        <v>1.23</v>
       </c>
       <c r="T3" t="n">
         <v>1.11</v>
@@ -1162,7 +1162,7 @@
         <v>1.01</v>
       </c>
       <c r="W3" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="X3" t="n">
         <v>1000</v>
@@ -1334,7 +1334,7 @@
       </c>
       <c r="CB3" t="inlineStr">
         <is>
-          <t>2026-06-10 18:12:00</t>
+          <t>2026-06-10 20:21:14</t>
         </is>
       </c>
     </row>
@@ -1365,13 +1365,13 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>1.04</v>
+        <v>1.09</v>
       </c>
       <c r="G4" t="n">
         <v>1000</v>
       </c>
       <c r="H4" t="n">
-        <v>1.04</v>
+        <v>1.09</v>
       </c>
       <c r="I4" t="n">
         <v>1000</v>
@@ -1413,7 +1413,7 @@
         <v>1.11</v>
       </c>
       <c r="V4" t="n">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="W4" t="n">
         <v>1.02</v>
@@ -1588,7 +1588,7 @@
       </c>
       <c r="CB4" t="inlineStr">
         <is>
-          <t>2026-06-10 18:12:00</t>
+          <t>2026-06-10 20:21:14</t>
         </is>
       </c>
     </row>
@@ -1646,7 +1646,7 @@
         <v>1.25</v>
       </c>
       <c r="O5" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="P5" t="n">
         <v>1.24</v>
@@ -1658,7 +1658,7 @@
         <v>1.18</v>
       </c>
       <c r="S5" t="n">
-        <v>1.54</v>
+        <v>1.05</v>
       </c>
       <c r="T5" t="n">
         <v>1.11</v>
@@ -1667,7 +1667,7 @@
         <v>1.11</v>
       </c>
       <c r="V5" t="n">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="W5" t="n">
         <v>1.02</v>
@@ -1842,7 +1842,7 @@
       </c>
       <c r="CB5" t="inlineStr">
         <is>
-          <t>2026-06-10 18:12:00</t>
+          <t>2026-06-10 20:21:14</t>
         </is>
       </c>
     </row>
@@ -1873,13 +1873,13 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>1.04</v>
+        <v>1.08</v>
       </c>
       <c r="G6" t="n">
         <v>1000</v>
       </c>
       <c r="H6" t="n">
-        <v>1.04</v>
+        <v>1.09</v>
       </c>
       <c r="I6" t="n">
         <v>1000</v>
@@ -1897,16 +1897,16 @@
         <v>1.01</v>
       </c>
       <c r="N6" t="n">
-        <v>1.35</v>
+        <v>1.36</v>
       </c>
       <c r="O6" t="n">
         <v>1.22</v>
       </c>
       <c r="P6" t="n">
-        <v>1.34</v>
+        <v>1.36</v>
       </c>
       <c r="Q6" t="n">
-        <v>1.21</v>
+        <v>1.22</v>
       </c>
       <c r="R6" t="n">
         <v>1.18</v>
@@ -2096,7 +2096,7 @@
       </c>
       <c r="CB6" t="inlineStr">
         <is>
-          <t>2026-06-10 18:12:00</t>
+          <t>2026-06-10 20:21:14</t>
         </is>
       </c>
     </row>
@@ -2127,19 +2127,19 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>1.04</v>
+        <v>1.08</v>
       </c>
       <c r="G7" t="n">
         <v>1000</v>
       </c>
       <c r="H7" t="n">
-        <v>1.04</v>
+        <v>1.08</v>
       </c>
       <c r="I7" t="n">
         <v>1000</v>
       </c>
       <c r="J7" t="n">
-        <v>1.09</v>
+        <v>1.1</v>
       </c>
       <c r="K7" t="n">
         <v>1000</v>
@@ -2151,13 +2151,13 @@
         <v>1.01</v>
       </c>
       <c r="N7" t="n">
-        <v>1.3</v>
+        <v>1.25</v>
       </c>
       <c r="O7" t="n">
         <v>1.27</v>
       </c>
       <c r="P7" t="n">
-        <v>1.3</v>
+        <v>1.24</v>
       </c>
       <c r="Q7" t="n">
         <v>1.27</v>
@@ -2166,7 +2166,7 @@
         <v>1.18</v>
       </c>
       <c r="S7" t="n">
-        <v>2.44</v>
+        <v>1.27</v>
       </c>
       <c r="T7" t="n">
         <v>1.11</v>
@@ -2350,14 +2350,14 @@
       </c>
       <c r="CB7" t="inlineStr">
         <is>
-          <t>2026-06-10 18:12:00</t>
+          <t>2026-06-10 20:21:14</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Swedish Division 1</t>
+          <t>Georgian Umaglesi Liga</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -2372,12 +2372,12 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>Umea FC</t>
+          <t>Dinamo Batumi</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Pitea</t>
+          <t>Dila Gori</t>
         </is>
       </c>
       <c r="F8" t="n">
@@ -2393,7 +2393,7 @@
         <v>1000</v>
       </c>
       <c r="J8" t="n">
-        <v>1.06</v>
+        <v>1.09</v>
       </c>
       <c r="K8" t="n">
         <v>1000</v>
@@ -2405,22 +2405,22 @@
         <v>1.01</v>
       </c>
       <c r="N8" t="n">
-        <v>1.28</v>
+        <v>1.25</v>
       </c>
       <c r="O8" t="n">
-        <v>1.15</v>
+        <v>1.33</v>
       </c>
       <c r="P8" t="n">
-        <v>1.28</v>
+        <v>1.24</v>
       </c>
       <c r="Q8" t="n">
-        <v>1.15</v>
+        <v>1.33</v>
       </c>
       <c r="R8" t="n">
-        <v>1.24</v>
+        <v>1.18</v>
       </c>
       <c r="S8" t="n">
-        <v>1.15</v>
+        <v>1.33</v>
       </c>
       <c r="T8" t="n">
         <v>1.11</v>
@@ -2429,10 +2429,10 @@
         <v>1.11</v>
       </c>
       <c r="V8" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="W8" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="X8" t="n">
         <v>1000</v>
@@ -2604,14 +2604,14 @@
       </c>
       <c r="CB8" t="inlineStr">
         <is>
-          <t>2026-06-10 18:12:00</t>
+          <t>2026-06-10 20:21:14</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Moroccan Botola Pro 1</t>
+          <t>Lithuanian A Lyga</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -2626,12 +2626,12 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>DHJ El Jadida</t>
+          <t>VMFD Zalgiris</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Olympique Dcheira</t>
+          <t>Riteriai</t>
         </is>
       </c>
       <c r="F9" t="n">
@@ -2647,7 +2647,7 @@
         <v>1000</v>
       </c>
       <c r="J9" t="n">
-        <v>1.08</v>
+        <v>1.09</v>
       </c>
       <c r="K9" t="n">
         <v>1000</v>
@@ -2659,22 +2659,22 @@
         <v>1.01</v>
       </c>
       <c r="N9" t="n">
-        <v>1.25</v>
+        <v>1.3</v>
       </c>
       <c r="O9" t="n">
-        <v>1.02</v>
+        <v>1.12</v>
       </c>
       <c r="P9" t="n">
-        <v>1.24</v>
+        <v>1.3</v>
       </c>
       <c r="Q9" t="n">
-        <v>1.43</v>
+        <v>1.11</v>
       </c>
       <c r="R9" t="n">
         <v>1.18</v>
       </c>
       <c r="S9" t="n">
-        <v>1.43</v>
+        <v>1.12</v>
       </c>
       <c r="T9" t="n">
         <v>1.11</v>
@@ -2683,7 +2683,7 @@
         <v>1.11</v>
       </c>
       <c r="V9" t="n">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="W9" t="n">
         <v>1.02</v>
@@ -2858,14 +2858,14 @@
       </c>
       <c r="CB9" t="inlineStr">
         <is>
-          <t>2026-06-10 18:12:00</t>
+          <t>2026-06-10 20:21:14</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Swedish Division 1</t>
+          <t>Moroccan Botola Pro 1</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -2880,16 +2880,16 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>Lunds BK</t>
+          <t>CODM Meknes</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Ariana FC</t>
+          <t>Club R Zemamra</t>
         </is>
       </c>
       <c r="F10" t="n">
-        <v>1.04</v>
+        <v>1.07</v>
       </c>
       <c r="G10" t="n">
         <v>1000</v>
@@ -2913,22 +2913,22 @@
         <v>1.01</v>
       </c>
       <c r="N10" t="n">
-        <v>1.3</v>
+        <v>1.25</v>
       </c>
       <c r="O10" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="P10" t="n">
         <v>1.24</v>
       </c>
-      <c r="P10" t="n">
-        <v>1.29</v>
-      </c>
       <c r="Q10" t="n">
-        <v>1.24</v>
+        <v>1.05</v>
       </c>
       <c r="R10" t="n">
-        <v>1.24</v>
+        <v>1.18</v>
       </c>
       <c r="S10" t="n">
-        <v>1.25</v>
+        <v>1.52</v>
       </c>
       <c r="T10" t="n">
         <v>1.11</v>
@@ -2940,7 +2940,7 @@
         <v>1.01</v>
       </c>
       <c r="W10" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="X10" t="n">
         <v>1000</v>
@@ -2997,52 +2997,52 @@
         <v>1000</v>
       </c>
       <c r="AP10" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AQ10" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AR10" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AS10" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AT10" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AU10" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AV10" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AW10" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AX10" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AY10" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AZ10" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BA10" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BB10" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BC10" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BD10" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BE10" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BF10" t="n">
         <v>1.01</v>
@@ -3112,14 +3112,14 @@
       </c>
       <c r="CB10" t="inlineStr">
         <is>
-          <t>2026-06-10 18:12:00</t>
+          <t>2026-06-10 20:21:14</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Lithuanian A Lyga</t>
+          <t>Moroccan Botola Pro 1</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -3134,12 +3134,12 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>VMFD Zalgiris</t>
+          <t>DHJ El Jadida</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Riteriai</t>
+          <t>Olympique Dcheira</t>
         </is>
       </c>
       <c r="F11" t="n">
@@ -3155,7 +3155,7 @@
         <v>1000</v>
       </c>
       <c r="J11" t="n">
-        <v>1.06</v>
+        <v>1.11</v>
       </c>
       <c r="K11" t="n">
         <v>1000</v>
@@ -3167,22 +3167,22 @@
         <v>1.01</v>
       </c>
       <c r="N11" t="n">
-        <v>1.28</v>
+        <v>1.25</v>
       </c>
       <c r="O11" t="n">
-        <v>1.12</v>
+        <v>1.02</v>
       </c>
       <c r="P11" t="n">
-        <v>1.28</v>
+        <v>1.24</v>
       </c>
       <c r="Q11" t="n">
-        <v>1.11</v>
+        <v>1.43</v>
       </c>
       <c r="R11" t="n">
         <v>1.18</v>
       </c>
       <c r="S11" t="n">
-        <v>1.12</v>
+        <v>1.43</v>
       </c>
       <c r="T11" t="n">
         <v>1.11</v>
@@ -3366,14 +3366,14 @@
       </c>
       <c r="CB11" t="inlineStr">
         <is>
-          <t>2026-06-10 18:12:00</t>
+          <t>2026-06-10 20:21:14</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Georgian Umaglesi Liga</t>
+          <t>Swedish Division 1</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -3388,12 +3388,12 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>Dinamo Batumi</t>
+          <t>Umea FC</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Dila Gori</t>
+          <t>Pitea</t>
         </is>
       </c>
       <c r="F12" t="n">
@@ -3409,7 +3409,7 @@
         <v>1000</v>
       </c>
       <c r="J12" t="n">
-        <v>1.06</v>
+        <v>1.1</v>
       </c>
       <c r="K12" t="n">
         <v>1000</v>
@@ -3421,22 +3421,22 @@
         <v>1.01</v>
       </c>
       <c r="N12" t="n">
-        <v>1.28</v>
+        <v>1.3</v>
       </c>
       <c r="O12" t="n">
-        <v>1.33</v>
+        <v>1.15</v>
       </c>
       <c r="P12" t="n">
-        <v>1.29</v>
+        <v>1.3</v>
       </c>
       <c r="Q12" t="n">
-        <v>1.87</v>
+        <v>1.15</v>
       </c>
       <c r="R12" t="n">
-        <v>1.18</v>
+        <v>1.24</v>
       </c>
       <c r="S12" t="n">
-        <v>2.78</v>
+        <v>1.14</v>
       </c>
       <c r="T12" t="n">
         <v>1.11</v>
@@ -3445,10 +3445,10 @@
         <v>1.11</v>
       </c>
       <c r="V12" t="n">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="W12" t="n">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="X12" t="n">
         <v>1000</v>
@@ -3620,14 +3620,14 @@
       </c>
       <c r="CB12" t="inlineStr">
         <is>
-          <t>2026-06-10 18:12:00</t>
+          <t>2026-06-10 20:21:14</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Moroccan Botola Pro 1</t>
+          <t>Swedish Division 1</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -3642,12 +3642,12 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>CODM Meknes</t>
+          <t>Lunds BK</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Club R Zemamra</t>
+          <t>Ariana FC</t>
         </is>
       </c>
       <c r="F13" t="n">
@@ -3663,7 +3663,7 @@
         <v>1000</v>
       </c>
       <c r="J13" t="n">
-        <v>1.09</v>
+        <v>1.11</v>
       </c>
       <c r="K13" t="n">
         <v>1000</v>
@@ -3681,16 +3681,16 @@
         <v>1.01</v>
       </c>
       <c r="P13" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="Q13" t="n">
         <v>1.24</v>
       </c>
-      <c r="Q13" t="n">
-        <v>1.05</v>
-      </c>
       <c r="R13" t="n">
-        <v>1.18</v>
+        <v>1.24</v>
       </c>
       <c r="S13" t="n">
-        <v>1.52</v>
+        <v>1.25</v>
       </c>
       <c r="T13" t="n">
         <v>1.11</v>
@@ -3699,10 +3699,10 @@
         <v>1.11</v>
       </c>
       <c r="V13" t="n">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="W13" t="n">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="X13" t="n">
         <v>1000</v>
@@ -3759,52 +3759,52 @@
         <v>1000</v>
       </c>
       <c r="AP13" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AQ13" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AR13" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AS13" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AT13" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AU13" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AV13" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AW13" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AX13" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AY13" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AZ13" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BA13" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BB13" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BC13" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BD13" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BE13" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BF13" t="n">
         <v>1.01</v>
@@ -3874,14 +3874,14 @@
       </c>
       <c r="CB13" t="inlineStr">
         <is>
-          <t>2026-06-10 18:12:00</t>
+          <t>2026-06-10 20:21:14</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Irish Division 1</t>
+          <t>Argentinian Primera C</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -3891,244 +3891,244 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>15:45:00</t>
+          <t>15:30:00</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>Finn Harps</t>
+          <t>CD Cambaceres</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>UCD</t>
+          <t>AD Berazategui</t>
         </is>
       </c>
       <c r="F14" t="n">
-        <v>3.7</v>
+        <v>1.01</v>
       </c>
       <c r="G14" t="n">
-        <v>5.4</v>
+        <v>1000</v>
       </c>
       <c r="H14" t="n">
-        <v>1.75</v>
+        <v>1.01</v>
       </c>
       <c r="I14" t="n">
-        <v>2.28</v>
+        <v>1000</v>
       </c>
       <c r="J14" t="n">
-        <v>3.25</v>
+        <v>1.02</v>
       </c>
       <c r="K14" t="n">
-        <v>5</v>
+        <v>950</v>
       </c>
       <c r="L14" t="n">
         <v>1.01</v>
       </c>
       <c r="M14" t="n">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="N14" t="n">
-        <v>4.1</v>
+        <v>1.24</v>
       </c>
       <c r="O14" t="n">
-        <v>1.23</v>
+        <v>1.01</v>
       </c>
       <c r="P14" t="n">
-        <v>2.08</v>
+        <v>1.24</v>
       </c>
       <c r="Q14" t="n">
-        <v>1.77</v>
+        <v>1.01</v>
       </c>
       <c r="R14" t="n">
-        <v>1.33</v>
+        <v>1.12</v>
       </c>
       <c r="S14" t="n">
-        <v>2.3</v>
+        <v>1.01</v>
       </c>
       <c r="T14" t="n">
-        <v>1.37</v>
+        <v>1.01</v>
       </c>
       <c r="U14" t="n">
-        <v>1.73</v>
+        <v>1.01</v>
       </c>
       <c r="V14" t="n">
-        <v>1.78</v>
+        <v>1.01</v>
       </c>
       <c r="W14" t="n">
-        <v>1.22</v>
+        <v>1.01</v>
       </c>
       <c r="X14" t="n">
         <v>1000</v>
       </c>
       <c r="Y14" t="n">
-        <v>14.5</v>
+        <v>1000</v>
       </c>
       <c r="Z14" t="n">
-        <v>18</v>
+        <v>1000</v>
       </c>
       <c r="AA14" t="n">
-        <v>30</v>
+        <v>1000</v>
       </c>
       <c r="AB14" t="n">
-        <v>24</v>
+        <v>1000</v>
       </c>
       <c r="AC14" t="n">
-        <v>11</v>
+        <v>1000</v>
       </c>
       <c r="AD14" t="n">
-        <v>15</v>
+        <v>1000</v>
       </c>
       <c r="AE14" t="n">
-        <v>28</v>
+        <v>1000</v>
       </c>
       <c r="AF14" t="n">
-        <v>46</v>
+        <v>1000</v>
       </c>
       <c r="AG14" t="n">
-        <v>24</v>
+        <v>1000</v>
       </c>
       <c r="AH14" t="n">
-        <v>24</v>
+        <v>1000</v>
       </c>
       <c r="AI14" t="n">
-        <v>46</v>
+        <v>1000</v>
       </c>
       <c r="AJ14" t="n">
         <v>1000</v>
       </c>
       <c r="AK14" t="n">
-        <v>70</v>
+        <v>1000</v>
       </c>
       <c r="AL14" t="n">
-        <v>70</v>
+        <v>1000</v>
       </c>
       <c r="AM14" t="n">
         <v>1000</v>
       </c>
       <c r="AN14" t="n">
-        <v>65</v>
+        <v>1000</v>
       </c>
       <c r="AO14" t="n">
-        <v>16</v>
+        <v>1000</v>
       </c>
       <c r="AP14" t="n">
-        <v>2.66</v>
+        <v>1.03</v>
       </c>
       <c r="AQ14" t="n">
-        <v>7.4</v>
+        <v>1.03</v>
       </c>
       <c r="AR14" t="n">
-        <v>9.199999999999999</v>
+        <v>1.03</v>
       </c>
       <c r="AS14" t="n">
-        <v>16</v>
+        <v>1.03</v>
       </c>
       <c r="AT14" t="n">
-        <v>12</v>
+        <v>1.03</v>
       </c>
       <c r="AU14" t="n">
-        <v>6.4</v>
+        <v>1.03</v>
       </c>
       <c r="AV14" t="n">
-        <v>7.6</v>
+        <v>1.03</v>
       </c>
       <c r="AW14" t="n">
-        <v>14</v>
+        <v>1.03</v>
       </c>
       <c r="AX14" t="n">
-        <v>2.52</v>
+        <v>1.03</v>
       </c>
       <c r="AY14" t="n">
-        <v>12</v>
+        <v>1.03</v>
       </c>
       <c r="AZ14" t="n">
-        <v>12</v>
+        <v>1.03</v>
       </c>
       <c r="BA14" t="n">
-        <v>2.52</v>
+        <v>1.03</v>
       </c>
       <c r="BB14" t="n">
-        <v>2.68</v>
+        <v>1.03</v>
       </c>
       <c r="BC14" t="n">
-        <v>2.58</v>
+        <v>1.03</v>
       </c>
       <c r="BD14" t="n">
-        <v>2.58</v>
+        <v>1.03</v>
       </c>
       <c r="BE14" t="n">
-        <v>2.68</v>
+        <v>1.03</v>
       </c>
       <c r="BF14" t="n">
-        <v>2.56</v>
+        <v>1.01</v>
       </c>
       <c r="BG14" t="n">
-        <v>8.4</v>
+        <v>1.01</v>
       </c>
       <c r="BH14" t="n">
         <v>1000</v>
       </c>
       <c r="BI14" t="n">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="BJ14" t="n">
         <v>1000</v>
       </c>
       <c r="BK14" t="n">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="BL14" t="n">
         <v>1000</v>
       </c>
       <c r="BM14" t="n">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="BN14" t="n">
         <v>1000</v>
       </c>
       <c r="BO14" t="n">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="BP14" t="n">
         <v>1000</v>
       </c>
       <c r="BQ14" t="n">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="BR14" t="n">
         <v>1000</v>
       </c>
       <c r="BS14" t="n">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="BT14" t="n">
         <v>1000</v>
       </c>
       <c r="BU14" t="n">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="BV14" t="n">
         <v>1000</v>
       </c>
       <c r="BW14" t="n">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="BX14" t="n">
         <v>1000</v>
       </c>
       <c r="BY14" t="n">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="BZ14" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="CA14" t="n">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="CB14" t="inlineStr">
         <is>
-          <t>2026-06-10 18:12:00</t>
+          <t>2026-06-10 20:21:14</t>
         </is>
       </c>
     </row>
@@ -4150,239 +4150,239 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>Kerry FC</t>
+          <t>Finn Harps</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Athlone Town</t>
+          <t>UCD</t>
         </is>
       </c>
       <c r="F15" t="n">
-        <v>2.26</v>
+        <v>3.7</v>
       </c>
       <c r="G15" t="n">
-        <v>2.54</v>
+        <v>5.4</v>
       </c>
       <c r="H15" t="n">
-        <v>3.15</v>
+        <v>1.75</v>
       </c>
       <c r="I15" t="n">
-        <v>4.2</v>
+        <v>2.28</v>
       </c>
       <c r="J15" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="K15" t="n">
+        <v>5</v>
+      </c>
+      <c r="L15" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="M15" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="N15" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="O15" t="n">
+        <v>1.23</v>
+      </c>
+      <c r="P15" t="n">
+        <v>2.08</v>
+      </c>
+      <c r="Q15" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="R15" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="S15" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="T15" t="n">
+        <v>1.37</v>
+      </c>
+      <c r="U15" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="V15" t="n">
+        <v>1.79</v>
+      </c>
+      <c r="W15" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="X15" t="n">
+        <v>1000</v>
+      </c>
+      <c r="Y15" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="Z15" t="n">
+        <v>18</v>
+      </c>
+      <c r="AA15" t="n">
+        <v>30</v>
+      </c>
+      <c r="AB15" t="n">
+        <v>24</v>
+      </c>
+      <c r="AC15" t="n">
+        <v>11</v>
+      </c>
+      <c r="AD15" t="n">
+        <v>15</v>
+      </c>
+      <c r="AE15" t="n">
+        <v>28</v>
+      </c>
+      <c r="AF15" t="n">
+        <v>46</v>
+      </c>
+      <c r="AG15" t="n">
+        <v>24</v>
+      </c>
+      <c r="AH15" t="n">
+        <v>24</v>
+      </c>
+      <c r="AI15" t="n">
+        <v>46</v>
+      </c>
+      <c r="AJ15" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AK15" t="n">
+        <v>70</v>
+      </c>
+      <c r="AL15" t="n">
+        <v>70</v>
+      </c>
+      <c r="AM15" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AN15" t="n">
+        <v>65</v>
+      </c>
+      <c r="AO15" t="n">
+        <v>16</v>
+      </c>
+      <c r="AP15" t="n">
+        <v>2.66</v>
+      </c>
+      <c r="AQ15" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="AR15" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="AS15" t="n">
+        <v>16</v>
+      </c>
+      <c r="AT15" t="n">
+        <v>12</v>
+      </c>
+      <c r="AU15" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="AV15" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="AW15" t="n">
+        <v>14</v>
+      </c>
+      <c r="AX15" t="n">
+        <v>2.52</v>
+      </c>
+      <c r="AY15" t="n">
+        <v>12</v>
+      </c>
+      <c r="AZ15" t="n">
+        <v>12</v>
+      </c>
+      <c r="BA15" t="n">
+        <v>2.52</v>
+      </c>
+      <c r="BB15" t="n">
         <v>2.68</v>
       </c>
-      <c r="K15" t="n">
-        <v>950</v>
-      </c>
-      <c r="L15" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="M15" t="n">
-        <v>1.07</v>
-      </c>
-      <c r="N15" t="n">
-        <v>3.15</v>
-      </c>
-      <c r="O15" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="P15" t="n">
-        <v>1.74</v>
-      </c>
-      <c r="Q15" t="n">
-        <v>2.04</v>
-      </c>
-      <c r="R15" t="n">
-        <v>1.27</v>
-      </c>
-      <c r="S15" t="n">
-        <v>3.7</v>
-      </c>
-      <c r="T15" t="n">
-        <v>1.11</v>
-      </c>
-      <c r="U15" t="n">
-        <v>2.06</v>
-      </c>
-      <c r="V15" t="n">
-        <v>1.38</v>
-      </c>
-      <c r="W15" t="n">
-        <v>1.67</v>
-      </c>
-      <c r="X15" t="n">
-        <v>1000</v>
-      </c>
-      <c r="Y15" t="n">
-        <v>1000</v>
-      </c>
-      <c r="Z15" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AA15" t="n">
-        <v>65</v>
-      </c>
-      <c r="AB15" t="n">
-        <v>9.800000000000001</v>
-      </c>
-      <c r="AC15" t="n">
-        <v>8</v>
-      </c>
-      <c r="AD15" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AE15" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AF15" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AG15" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AH15" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AI15" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AJ15" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AK15" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AL15" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AM15" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AN15" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AO15" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AP15" t="n">
-        <v>9.4</v>
-      </c>
-      <c r="AQ15" t="n">
-        <v>9</v>
-      </c>
-      <c r="AR15" t="n">
-        <v>17</v>
-      </c>
-      <c r="AS15" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="AT15" t="n">
-        <v>7.2</v>
-      </c>
-      <c r="AU15" t="n">
-        <v>5.8</v>
-      </c>
-      <c r="AV15" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="AW15" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="AX15" t="n">
-        <v>11</v>
-      </c>
-      <c r="AY15" t="n">
-        <v>8.4</v>
-      </c>
-      <c r="AZ15" t="n">
-        <v>13</v>
-      </c>
-      <c r="BA15" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="BB15" t="n">
-        <v>1.33</v>
-      </c>
       <c r="BC15" t="n">
-        <v>19.5</v>
+        <v>2.58</v>
       </c>
       <c r="BD15" t="n">
-        <v>1.33</v>
+        <v>2.58</v>
       </c>
       <c r="BE15" t="n">
-        <v>1.33</v>
+        <v>2.68</v>
       </c>
       <c r="BF15" t="n">
-        <v>16</v>
+        <v>2.56</v>
       </c>
       <c r="BG15" t="n">
-        <v>1.33</v>
+        <v>7.6</v>
       </c>
       <c r="BH15" t="n">
-        <v>3.3</v>
+        <v>1000</v>
       </c>
       <c r="BI15" t="n">
-        <v>2.66</v>
+        <v>1.04</v>
       </c>
       <c r="BJ15" t="n">
-        <v>9.800000000000001</v>
+        <v>1000</v>
       </c>
       <c r="BK15" t="n">
-        <v>5.7</v>
+        <v>1.04</v>
       </c>
       <c r="BL15" t="n">
         <v>1000</v>
       </c>
       <c r="BM15" t="n">
-        <v>12.5</v>
+        <v>1.04</v>
       </c>
       <c r="BN15" t="n">
-        <v>5.3</v>
+        <v>1000</v>
       </c>
       <c r="BO15" t="n">
-        <v>4</v>
+        <v>1.04</v>
       </c>
       <c r="BP15" t="n">
-        <v>18.5</v>
+        <v>1000</v>
       </c>
       <c r="BQ15" t="n">
-        <v>8</v>
+        <v>1.04</v>
       </c>
       <c r="BR15" t="n">
         <v>1000</v>
       </c>
       <c r="BS15" t="n">
-        <v>9.800000000000001</v>
+        <v>1.04</v>
       </c>
       <c r="BT15" t="n">
-        <v>6.6</v>
+        <v>1000</v>
       </c>
       <c r="BU15" t="n">
-        <v>5</v>
+        <v>1.04</v>
       </c>
       <c r="BV15" t="n">
         <v>1000</v>
       </c>
       <c r="BW15" t="n">
-        <v>9.199999999999999</v>
+        <v>1.04</v>
       </c>
       <c r="BX15" t="n">
         <v>1000</v>
       </c>
       <c r="BY15" t="n">
-        <v>10.5</v>
+        <v>1.04</v>
       </c>
       <c r="BZ15" t="n">
         <v>1000</v>
       </c>
       <c r="CA15" t="n">
-        <v>9.6</v>
+        <v>1.04</v>
       </c>
       <c r="CB15" t="inlineStr">
         <is>
-          <t>2026-06-10 18:12:00</t>
+          <t>2026-06-10 20:21:14</t>
         </is>
       </c>
     </row>
@@ -4404,239 +4404,239 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>Treaty United</t>
+          <t>Kerry FC</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Bray Wanderers</t>
+          <t>Athlone Town</t>
         </is>
       </c>
       <c r="F16" t="n">
+        <v>2.28</v>
+      </c>
+      <c r="G16" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="H16" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="I16" t="n">
+        <v>3.65</v>
+      </c>
+      <c r="J16" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="K16" t="n">
+        <v>3.65</v>
+      </c>
+      <c r="L16" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="M16" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="N16" t="n">
+        <v>3.35</v>
+      </c>
+      <c r="O16" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="P16" t="n">
+        <v>1.81</v>
+      </c>
+      <c r="Q16" t="n">
+        <v>2.04</v>
+      </c>
+      <c r="R16" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="S16" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="T16" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="U16" t="n">
+        <v>2.06</v>
+      </c>
+      <c r="V16" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="W16" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="X16" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="Y16" t="n">
+        <v>15</v>
+      </c>
+      <c r="Z16" t="n">
+        <v>29</v>
+      </c>
+      <c r="AA16" t="n">
+        <v>65</v>
+      </c>
+      <c r="AB16" t="n">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="AC16" t="n">
+        <v>8</v>
+      </c>
+      <c r="AD16" t="n">
+        <v>17.5</v>
+      </c>
+      <c r="AE16" t="n">
+        <v>55</v>
+      </c>
+      <c r="AF16" t="n">
+        <v>18.5</v>
+      </c>
+      <c r="AG16" t="n">
+        <v>14</v>
+      </c>
+      <c r="AH16" t="n">
+        <v>22</v>
+      </c>
+      <c r="AI16" t="n">
+        <v>65</v>
+      </c>
+      <c r="AJ16" t="n">
+        <v>40</v>
+      </c>
+      <c r="AK16" t="n">
+        <v>34</v>
+      </c>
+      <c r="AL16" t="n">
+        <v>55</v>
+      </c>
+      <c r="AM16" t="n">
+        <v>130</v>
+      </c>
+      <c r="AN16" t="n">
+        <v>27</v>
+      </c>
+      <c r="AO16" t="n">
+        <v>55</v>
+      </c>
+      <c r="AP16" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="AQ16" t="n">
+        <v>9</v>
+      </c>
+      <c r="AR16" t="n">
+        <v>17</v>
+      </c>
+      <c r="AS16" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="AT16" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="AU16" t="n">
+        <v>5.8</v>
+      </c>
+      <c r="AV16" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AW16" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="AX16" t="n">
+        <v>11</v>
+      </c>
+      <c r="AY16" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="AZ16" t="n">
+        <v>13</v>
+      </c>
+      <c r="BA16" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="BB16" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="BC16" t="n">
+        <v>19.5</v>
+      </c>
+      <c r="BD16" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="BE16" t="n">
+        <v>5</v>
+      </c>
+      <c r="BF16" t="n">
+        <v>16</v>
+      </c>
+      <c r="BG16" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="BH16" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="BI16" t="n">
+        <v>2.66</v>
+      </c>
+      <c r="BJ16" t="n">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="BK16" t="n">
+        <v>5.7</v>
+      </c>
+      <c r="BL16" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BM16" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="BN16" t="n">
+        <v>5.3</v>
+      </c>
+      <c r="BO16" t="n">
         <v>4</v>
       </c>
-      <c r="G16" t="n">
-        <v>4.8</v>
-      </c>
-      <c r="H16" t="n">
-        <v>1.84</v>
-      </c>
-      <c r="I16" t="n">
-        <v>2.04</v>
-      </c>
-      <c r="J16" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="K16" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="L16" t="n">
-        <v>1.29</v>
-      </c>
-      <c r="M16" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="N16" t="n">
-        <v>4</v>
-      </c>
-      <c r="O16" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="P16" t="n">
-        <v>2.04</v>
-      </c>
-      <c r="Q16" t="n">
-        <v>1.77</v>
-      </c>
-      <c r="R16" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="S16" t="n">
-        <v>2.96</v>
-      </c>
-      <c r="T16" t="n">
-        <v>1.72</v>
-      </c>
-      <c r="U16" t="n">
-        <v>2.12</v>
-      </c>
-      <c r="V16" t="n">
-        <v>1.96</v>
-      </c>
-      <c r="W16" t="n">
-        <v>1.26</v>
-      </c>
-      <c r="X16" t="n">
-        <v>1000</v>
-      </c>
-      <c r="Y16" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="Z16" t="n">
-        <v>13.5</v>
-      </c>
-      <c r="AA16" t="n">
-        <v>23</v>
-      </c>
-      <c r="AB16" t="n">
-        <v>18</v>
-      </c>
-      <c r="AC16" t="n">
-        <v>9.4</v>
-      </c>
-      <c r="AD16" t="n">
-        <v>11</v>
-      </c>
-      <c r="AE16" t="n">
-        <v>21</v>
-      </c>
-      <c r="AF16" t="n">
-        <v>36</v>
-      </c>
-      <c r="AG16" t="n">
+      <c r="BP16" t="n">
         <v>18.5</v>
       </c>
-      <c r="AH16" t="n">
-        <v>18.5</v>
-      </c>
-      <c r="AI16" t="n">
-        <v>34</v>
-      </c>
-      <c r="AJ16" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AK16" t="n">
-        <v>75</v>
-      </c>
-      <c r="AL16" t="n">
-        <v>60</v>
-      </c>
-      <c r="AM16" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AN16" t="n">
-        <v>55</v>
-      </c>
-      <c r="AO16" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="AP16" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="AQ16" t="n">
-        <v>8.6</v>
-      </c>
-      <c r="AR16" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="AS16" t="n">
-        <v>18</v>
-      </c>
-      <c r="AT16" t="n">
-        <v>14.5</v>
-      </c>
-      <c r="AU16" t="n">
-        <v>7.6</v>
-      </c>
-      <c r="AV16" t="n">
-        <v>8.800000000000001</v>
-      </c>
-      <c r="AW16" t="n">
-        <v>16.5</v>
-      </c>
-      <c r="AX16" t="n">
-        <v>23</v>
-      </c>
-      <c r="AY16" t="n">
-        <v>14.5</v>
-      </c>
-      <c r="AZ16" t="n">
-        <v>15</v>
-      </c>
-      <c r="BA16" t="n">
-        <v>23</v>
-      </c>
-      <c r="BB16" t="n">
-        <v>5.3</v>
-      </c>
-      <c r="BC16" t="n">
-        <v>36</v>
-      </c>
-      <c r="BD16" t="n">
-        <v>4.9</v>
-      </c>
-      <c r="BE16" t="n">
-        <v>5.3</v>
-      </c>
-      <c r="BF16" t="n">
-        <v>32</v>
-      </c>
-      <c r="BG16" t="n">
+      <c r="BQ16" t="n">
+        <v>8</v>
+      </c>
+      <c r="BR16" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BS16" t="n">
         <v>9.800000000000001</v>
-      </c>
-      <c r="BH16" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BI16" t="n">
-        <v>1.87</v>
-      </c>
-      <c r="BJ16" t="n">
-        <v>13.5</v>
-      </c>
-      <c r="BK16" t="n">
-        <v>1.65</v>
-      </c>
-      <c r="BL16" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BM16" t="n">
-        <v>1.87</v>
-      </c>
-      <c r="BN16" t="n">
-        <v>11</v>
-      </c>
-      <c r="BO16" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="BP16" t="n">
-        <v>50</v>
-      </c>
-      <c r="BQ16" t="n">
-        <v>1.81</v>
-      </c>
-      <c r="BR16" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BS16" t="n">
-        <v>1.82</v>
       </c>
       <c r="BT16" t="n">
         <v>6.6</v>
       </c>
       <c r="BU16" t="n">
-        <v>3.55</v>
+        <v>4.9</v>
       </c>
       <c r="BV16" t="n">
-        <v>18.5</v>
+        <v>1000</v>
       </c>
       <c r="BW16" t="n">
-        <v>1.7</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BX16" t="n">
-        <v>38</v>
+        <v>1000</v>
       </c>
       <c r="BY16" t="n">
-        <v>1.79</v>
+        <v>10.5</v>
       </c>
       <c r="BZ16" t="n">
-        <v>30</v>
+        <v>1000</v>
       </c>
       <c r="CA16" t="n">
-        <v>1.77</v>
+        <v>9.6</v>
       </c>
       <c r="CB16" t="inlineStr">
         <is>
-          <t>2026-06-10 18:12:00</t>
+          <t>2026-06-10 20:21:14</t>
         </is>
       </c>
     </row>
@@ -4658,19 +4658,19 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>Wexford F.C</t>
+          <t>Treaty United</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Cork City</t>
+          <t>Bray Wanderers</t>
         </is>
       </c>
       <c r="F17" t="n">
-        <v>3.9</v>
+        <v>3.85</v>
       </c>
       <c r="G17" t="n">
-        <v>5.8</v>
+        <v>4.6</v>
       </c>
       <c r="H17" t="n">
         <v>1.84</v>
@@ -4679,225 +4679,225 @@
         <v>2.04</v>
       </c>
       <c r="J17" t="n">
-        <v>3.2</v>
+        <v>3.85</v>
       </c>
       <c r="K17" t="n">
-        <v>4.4</v>
+        <v>4.5</v>
       </c>
       <c r="L17" t="n">
-        <v>1.01</v>
+        <v>1.24</v>
       </c>
       <c r="M17" t="n">
-        <v>1.06</v>
+        <v>1.03</v>
       </c>
       <c r="N17" t="n">
-        <v>2.8</v>
+        <v>5</v>
       </c>
       <c r="O17" t="n">
-        <v>1.28</v>
+        <v>1.21</v>
       </c>
       <c r="P17" t="n">
-        <v>1.83</v>
+        <v>2.44</v>
       </c>
       <c r="Q17" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="R17" t="n">
+        <v>1.59</v>
+      </c>
+      <c r="S17" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="T17" t="n">
+        <v>1.56</v>
+      </c>
+      <c r="U17" t="n">
+        <v>2.44</v>
+      </c>
+      <c r="V17" t="n">
+        <v>1.96</v>
+      </c>
+      <c r="W17" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="X17" t="n">
+        <v>29</v>
+      </c>
+      <c r="Y17" t="n">
+        <v>15</v>
+      </c>
+      <c r="Z17" t="n">
+        <v>17.5</v>
+      </c>
+      <c r="AA17" t="n">
+        <v>30</v>
+      </c>
+      <c r="AB17" t="n">
+        <v>22</v>
+      </c>
+      <c r="AC17" t="n">
+        <v>12</v>
+      </c>
+      <c r="AD17" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="AE17" t="n">
+        <v>17.5</v>
+      </c>
+      <c r="AF17" t="n">
+        <v>38</v>
+      </c>
+      <c r="AG17" t="n">
+        <v>23</v>
+      </c>
+      <c r="AH17" t="n">
+        <v>17.5</v>
+      </c>
+      <c r="AI17" t="n">
+        <v>32</v>
+      </c>
+      <c r="AJ17" t="n">
+        <v>110</v>
+      </c>
+      <c r="AK17" t="n">
+        <v>42</v>
+      </c>
+      <c r="AL17" t="n">
+        <v>50</v>
+      </c>
+      <c r="AM17" t="n">
+        <v>70</v>
+      </c>
+      <c r="AN17" t="n">
+        <v>34</v>
+      </c>
+      <c r="AO17" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AP17" t="n">
+        <v>17</v>
+      </c>
+      <c r="AQ17" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="AR17" t="n">
+        <v>11</v>
+      </c>
+      <c r="AS17" t="n">
+        <v>18</v>
+      </c>
+      <c r="AT17" t="n">
+        <v>15</v>
+      </c>
+      <c r="AU17" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="AV17" t="n">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="AW17" t="n">
+        <v>12</v>
+      </c>
+      <c r="AX17" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="AY17" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="AZ17" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="BA17" t="n">
+        <v>18.5</v>
+      </c>
+      <c r="BB17" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="BC17" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="BD17" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="BE17" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="BF17" t="n">
+        <v>23</v>
+      </c>
+      <c r="BG17" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="BH17" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BI17" t="n">
         <v>1.9</v>
-      </c>
-      <c r="R17" t="n">
-        <v>1.34</v>
-      </c>
-      <c r="S17" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="T17" t="n">
-        <v>1.11</v>
-      </c>
-      <c r="U17" t="n">
-        <v>1.11</v>
-      </c>
-      <c r="V17" t="n">
-        <v>1.98</v>
-      </c>
-      <c r="W17" t="n">
-        <v>1.24</v>
-      </c>
-      <c r="X17" t="n">
-        <v>1000</v>
-      </c>
-      <c r="Y17" t="n">
-        <v>11</v>
-      </c>
-      <c r="Z17" t="n">
-        <v>15</v>
-      </c>
-      <c r="AA17" t="n">
-        <v>28</v>
-      </c>
-      <c r="AB17" t="n">
-        <v>21</v>
-      </c>
-      <c r="AC17" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="AD17" t="n">
-        <v>13</v>
-      </c>
-      <c r="AE17" t="n">
-        <v>26</v>
-      </c>
-      <c r="AF17" t="n">
-        <v>100</v>
-      </c>
-      <c r="AG17" t="n">
-        <v>24</v>
-      </c>
-      <c r="AH17" t="n">
-        <v>24</v>
-      </c>
-      <c r="AI17" t="n">
-        <v>100</v>
-      </c>
-      <c r="AJ17" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AK17" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AL17" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AM17" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AN17" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AO17" t="n">
-        <v>17</v>
-      </c>
-      <c r="AP17" t="n">
-        <v>2.58</v>
-      </c>
-      <c r="AQ17" t="n">
-        <v>6.4</v>
-      </c>
-      <c r="AR17" t="n">
-        <v>8.4</v>
-      </c>
-      <c r="AS17" t="n">
-        <v>15</v>
-      </c>
-      <c r="AT17" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="AU17" t="n">
-        <v>2.08</v>
-      </c>
-      <c r="AV17" t="n">
-        <v>7.4</v>
-      </c>
-      <c r="AW17" t="n">
-        <v>14</v>
-      </c>
-      <c r="AX17" t="n">
-        <v>24</v>
-      </c>
-      <c r="AY17" t="n">
-        <v>13</v>
-      </c>
-      <c r="AZ17" t="n">
-        <v>13.5</v>
-      </c>
-      <c r="BA17" t="n">
-        <v>25</v>
-      </c>
-      <c r="BB17" t="n">
-        <v>2.58</v>
-      </c>
-      <c r="BC17" t="n">
-        <v>2.58</v>
-      </c>
-      <c r="BD17" t="n">
-        <v>2.58</v>
-      </c>
-      <c r="BE17" t="n">
-        <v>2.58</v>
-      </c>
-      <c r="BF17" t="n">
-        <v>2.58</v>
-      </c>
-      <c r="BG17" t="n">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="BH17" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="BI17" t="n">
-        <v>2.76</v>
       </c>
       <c r="BJ17" t="n">
         <v>13.5</v>
       </c>
       <c r="BK17" t="n">
-        <v>2.84</v>
+        <v>1.67</v>
       </c>
       <c r="BL17" t="n">
         <v>1000</v>
       </c>
       <c r="BM17" t="n">
-        <v>3.6</v>
+        <v>1.9</v>
       </c>
       <c r="BN17" t="n">
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="BO17" t="n">
-        <v>2.7</v>
+        <v>4.9</v>
       </c>
       <c r="BP17" t="n">
-        <v>1000</v>
+        <v>44</v>
       </c>
       <c r="BQ17" t="n">
-        <v>3.35</v>
+        <v>1.83</v>
       </c>
       <c r="BR17" t="n">
         <v>1000</v>
       </c>
       <c r="BS17" t="n">
-        <v>3.4</v>
+        <v>1.84</v>
       </c>
       <c r="BT17" t="n">
-        <v>6</v>
+        <v>6.8</v>
       </c>
       <c r="BU17" t="n">
-        <v>3.4</v>
+        <v>3.3</v>
       </c>
       <c r="BV17" t="n">
         <v>18</v>
       </c>
       <c r="BW17" t="n">
-        <v>3</v>
+        <v>1.72</v>
       </c>
       <c r="BX17" t="n">
         <v>38</v>
       </c>
       <c r="BY17" t="n">
-        <v>3.25</v>
+        <v>1.81</v>
       </c>
       <c r="BZ17" t="n">
-        <v>32</v>
+        <v>23</v>
       </c>
       <c r="CA17" t="n">
-        <v>3.2</v>
+        <v>1.76</v>
       </c>
       <c r="CB17" t="inlineStr">
         <is>
-          <t>2026-06-10 18:12:00</t>
+          <t>2026-06-10 20:21:14</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Irish Premier Division</t>
+          <t>Irish Division 1</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -4912,239 +4912,239 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>Derry City</t>
+          <t>Wexford F.C</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Bohemians</t>
+          <t>Cork City</t>
         </is>
       </c>
       <c r="F18" t="n">
-        <v>3</v>
+        <v>4.3</v>
       </c>
       <c r="G18" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="H18" t="n">
+        <v>1.84</v>
+      </c>
+      <c r="I18" t="n">
+        <v>2</v>
+      </c>
+      <c r="J18" t="n">
         <v>3.5</v>
       </c>
-      <c r="H18" t="n">
-        <v>2.42</v>
-      </c>
-      <c r="I18" t="n">
-        <v>2.68</v>
-      </c>
-      <c r="J18" t="n">
-        <v>3.25</v>
-      </c>
       <c r="K18" t="n">
-        <v>3.95</v>
+        <v>4.2</v>
       </c>
       <c r="L18" t="n">
         <v>1.01</v>
       </c>
       <c r="M18" t="n">
-        <v>1.09</v>
+        <v>1.07</v>
       </c>
       <c r="N18" t="n">
-        <v>3.05</v>
+        <v>3.6</v>
       </c>
       <c r="O18" t="n">
-        <v>1.39</v>
+        <v>1.3</v>
       </c>
       <c r="P18" t="n">
-        <v>1.69</v>
+        <v>1.9</v>
       </c>
       <c r="Q18" t="n">
-        <v>2.16</v>
+        <v>1.9</v>
       </c>
       <c r="R18" t="n">
-        <v>1.26</v>
+        <v>1.34</v>
       </c>
       <c r="S18" t="n">
-        <v>4.1</v>
+        <v>3.3</v>
       </c>
       <c r="T18" t="n">
-        <v>1.84</v>
+        <v>1.79</v>
       </c>
       <c r="U18" t="n">
-        <v>1.92</v>
+        <v>2</v>
       </c>
       <c r="V18" t="n">
-        <v>1.59</v>
+        <v>2</v>
       </c>
       <c r="W18" t="n">
-        <v>1.4</v>
+        <v>1.24</v>
       </c>
       <c r="X18" t="n">
-        <v>12</v>
+        <v>17</v>
       </c>
       <c r="Y18" t="n">
-        <v>9.6</v>
+        <v>9.4</v>
       </c>
       <c r="Z18" t="n">
-        <v>16.5</v>
+        <v>12.5</v>
       </c>
       <c r="AA18" t="n">
-        <v>50</v>
+        <v>23</v>
       </c>
       <c r="AB18" t="n">
-        <v>11.5</v>
+        <v>17</v>
       </c>
       <c r="AC18" t="n">
-        <v>7.8</v>
+        <v>9</v>
       </c>
       <c r="AD18" t="n">
-        <v>12.5</v>
+        <v>11</v>
       </c>
       <c r="AE18" t="n">
-        <v>34</v>
+        <v>22</v>
       </c>
       <c r="AF18" t="n">
-        <v>23</v>
+        <v>38</v>
       </c>
       <c r="AG18" t="n">
-        <v>15</v>
+        <v>19.5</v>
       </c>
       <c r="AH18" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AI18" t="n">
+        <v>38</v>
+      </c>
+      <c r="AJ18" t="n">
+        <v>130</v>
+      </c>
+      <c r="AK18" t="n">
+        <v>75</v>
+      </c>
+      <c r="AL18" t="n">
         <v>70</v>
       </c>
-      <c r="AJ18" t="n">
-        <v>80</v>
-      </c>
-      <c r="AK18" t="n">
-        <v>55</v>
-      </c>
-      <c r="AL18" t="n">
-        <v>80</v>
-      </c>
       <c r="AM18" t="n">
-        <v>1000</v>
+        <v>130</v>
       </c>
       <c r="AN18" t="n">
-        <v>70</v>
+        <v>75</v>
       </c>
       <c r="AO18" t="n">
-        <v>38</v>
+        <v>14</v>
       </c>
       <c r="AP18" t="n">
-        <v>9.6</v>
+        <v>11</v>
       </c>
       <c r="AQ18" t="n">
-        <v>7.8</v>
+        <v>7.6</v>
       </c>
       <c r="AR18" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="AS18" t="n">
-        <v>30</v>
+        <v>18</v>
       </c>
       <c r="AT18" t="n">
-        <v>9.4</v>
+        <v>13.5</v>
       </c>
       <c r="AU18" t="n">
-        <v>6.6</v>
+        <v>7.2</v>
       </c>
       <c r="AV18" t="n">
-        <v>10</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AW18" t="n">
+        <v>17</v>
+      </c>
+      <c r="AX18" t="n">
         <v>24</v>
       </c>
-      <c r="AX18" t="n">
-        <v>18.5</v>
-      </c>
       <c r="AY18" t="n">
-        <v>12</v>
+        <v>15.5</v>
       </c>
       <c r="AZ18" t="n">
         <v>16</v>
       </c>
       <c r="BA18" t="n">
-        <v>32</v>
+        <v>25</v>
       </c>
       <c r="BB18" t="n">
-        <v>40</v>
+        <v>7.6</v>
       </c>
       <c r="BC18" t="n">
-        <v>29</v>
+        <v>7.2</v>
       </c>
       <c r="BD18" t="n">
-        <v>38</v>
+        <v>7.2</v>
       </c>
       <c r="BE18" t="n">
-        <v>8.199999999999999</v>
+        <v>7.6</v>
       </c>
       <c r="BF18" t="n">
-        <v>7</v>
+        <v>7.2</v>
       </c>
       <c r="BG18" t="n">
-        <v>6.4</v>
+        <v>11</v>
       </c>
       <c r="BH18" t="n">
-        <v>1000</v>
+        <v>4.1</v>
       </c>
       <c r="BI18" t="n">
-        <v>1.83</v>
+        <v>2.76</v>
       </c>
       <c r="BJ18" t="n">
         <v>13.5</v>
       </c>
       <c r="BK18" t="n">
-        <v>1.61</v>
+        <v>2.84</v>
       </c>
       <c r="BL18" t="n">
         <v>1000</v>
       </c>
       <c r="BM18" t="n">
-        <v>1.83</v>
+        <v>3.6</v>
       </c>
       <c r="BN18" t="n">
-        <v>8.6</v>
+        <v>11</v>
       </c>
       <c r="BO18" t="n">
-        <v>4.6</v>
+        <v>2.7</v>
       </c>
       <c r="BP18" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BQ18" t="n">
+        <v>3.35</v>
+      </c>
+      <c r="BR18" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BS18" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="BT18" t="n">
+        <v>6</v>
+      </c>
+      <c r="BU18" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="BV18" t="n">
+        <v>18</v>
+      </c>
+      <c r="BW18" t="n">
+        <v>3</v>
+      </c>
+      <c r="BX18" t="n">
         <v>38</v>
       </c>
-      <c r="BQ18" t="n">
-        <v>1.74</v>
-      </c>
-      <c r="BR18" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BS18" t="n">
-        <v>1.77</v>
-      </c>
-      <c r="BT18" t="n">
-        <v>7</v>
-      </c>
-      <c r="BU18" t="n">
-        <v>3.85</v>
-      </c>
-      <c r="BV18" t="n">
-        <v>28</v>
-      </c>
-      <c r="BW18" t="n">
-        <v>1.72</v>
-      </c>
-      <c r="BX18" t="n">
-        <v>50</v>
-      </c>
       <c r="BY18" t="n">
-        <v>1.76</v>
+        <v>3.25</v>
       </c>
       <c r="BZ18" t="n">
-        <v>48</v>
+        <v>32</v>
       </c>
       <c r="CA18" t="n">
-        <v>1.76</v>
+        <v>3.2</v>
       </c>
       <c r="CB18" t="inlineStr">
         <is>
-          <t>2026-06-10 18:12:00</t>
+          <t>2026-06-10 20:21:14</t>
         </is>
       </c>
     </row>
@@ -5166,184 +5166,184 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>Waterford</t>
+          <t>Derry City</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Sligo Rovers</t>
+          <t>Bohemians</t>
         </is>
       </c>
       <c r="F19" t="n">
-        <v>2.26</v>
+        <v>3.1</v>
       </c>
       <c r="G19" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="H19" t="n">
         <v>2.42</v>
       </c>
-      <c r="H19" t="n">
-        <v>3.2</v>
-      </c>
       <c r="I19" t="n">
-        <v>3.75</v>
+        <v>2.64</v>
       </c>
       <c r="J19" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="K19" t="n">
+        <v>3.55</v>
+      </c>
+      <c r="L19" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="M19" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="N19" t="n">
         <v>3.1</v>
       </c>
-      <c r="K19" t="n">
-        <v>4.7</v>
-      </c>
-      <c r="L19" t="n">
-        <v>1.12</v>
-      </c>
-      <c r="M19" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="N19" t="n">
-        <v>3.95</v>
-      </c>
       <c r="O19" t="n">
-        <v>1.27</v>
+        <v>1.41</v>
       </c>
       <c r="P19" t="n">
-        <v>1.86</v>
+        <v>1.71</v>
       </c>
       <c r="Q19" t="n">
-        <v>1.83</v>
+        <v>2.2</v>
       </c>
       <c r="R19" t="n">
-        <v>1.33</v>
+        <v>1.26</v>
       </c>
       <c r="S19" t="n">
-        <v>3.1</v>
+        <v>4.3</v>
       </c>
       <c r="T19" t="n">
-        <v>1.38</v>
+        <v>1.88</v>
       </c>
       <c r="U19" t="n">
-        <v>1.72</v>
+        <v>1.96</v>
       </c>
       <c r="V19" t="n">
+        <v>1.61</v>
+      </c>
+      <c r="W19" t="n">
         <v>1.4</v>
       </c>
-      <c r="W19" t="n">
-        <v>1.7</v>
-      </c>
       <c r="X19" t="n">
-        <v>23</v>
+        <v>12</v>
       </c>
       <c r="Y19" t="n">
-        <v>20</v>
+        <v>9.6</v>
       </c>
       <c r="Z19" t="n">
-        <v>36</v>
+        <v>16.5</v>
       </c>
       <c r="AA19" t="n">
-        <v>85</v>
+        <v>50</v>
       </c>
       <c r="AB19" t="n">
-        <v>16</v>
+        <v>11.5</v>
       </c>
       <c r="AC19" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="AD19" t="n">
         <v>12.5</v>
       </c>
-      <c r="AD19" t="n">
-        <v>21</v>
-      </c>
       <c r="AE19" t="n">
-        <v>55</v>
+        <v>34</v>
       </c>
       <c r="AF19" t="n">
         <v>23</v>
       </c>
       <c r="AG19" t="n">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="AH19" t="n">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="AI19" t="n">
-        <v>65</v>
+        <v>70</v>
       </c>
       <c r="AJ19" t="n">
-        <v>46</v>
+        <v>80</v>
       </c>
       <c r="AK19" t="n">
-        <v>34</v>
+        <v>55</v>
       </c>
       <c r="AL19" t="n">
-        <v>50</v>
+        <v>80</v>
       </c>
       <c r="AM19" t="n">
-        <v>1000</v>
+        <v>150</v>
       </c>
       <c r="AN19" t="n">
-        <v>25</v>
+        <v>70</v>
       </c>
       <c r="AO19" t="n">
-        <v>48</v>
+        <v>38</v>
       </c>
       <c r="AP19" t="n">
-        <v>13.5</v>
+        <v>9.6</v>
       </c>
       <c r="AQ19" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="AR19" t="n">
         <v>12</v>
       </c>
-      <c r="AR19" t="n">
-        <v>20</v>
-      </c>
       <c r="AS19" t="n">
-        <v>2.62</v>
+        <v>7.2</v>
       </c>
       <c r="AT19" t="n">
         <v>9.4</v>
       </c>
       <c r="AU19" t="n">
-        <v>7.2</v>
+        <v>6.6</v>
       </c>
       <c r="AV19" t="n">
+        <v>10</v>
+      </c>
+      <c r="AW19" t="n">
+        <v>24</v>
+      </c>
+      <c r="AX19" t="n">
+        <v>18.5</v>
+      </c>
+      <c r="AY19" t="n">
         <v>12</v>
       </c>
-      <c r="AW19" t="n">
-        <v>2.58</v>
-      </c>
-      <c r="AX19" t="n">
-        <v>13</v>
-      </c>
-      <c r="AY19" t="n">
-        <v>9.6</v>
-      </c>
       <c r="AZ19" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="BA19" t="n">
-        <v>36</v>
+        <v>32</v>
       </c>
       <c r="BB19" t="n">
-        <v>2.56</v>
+        <v>40</v>
       </c>
       <c r="BC19" t="n">
-        <v>20</v>
+        <v>29</v>
       </c>
       <c r="BD19" t="n">
-        <v>2.58</v>
+        <v>38</v>
       </c>
       <c r="BE19" t="n">
-        <v>2.72</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BF19" t="n">
-        <v>12</v>
+        <v>7.4</v>
       </c>
       <c r="BG19" t="n">
-        <v>2.56</v>
+        <v>6.8</v>
       </c>
       <c r="BH19" t="n">
         <v>1000</v>
       </c>
       <c r="BI19" t="n">
-        <v>1.84</v>
+        <v>1.83</v>
       </c>
       <c r="BJ19" t="n">
-        <v>13</v>
+        <v>13.5</v>
       </c>
       <c r="BK19" t="n">
         <v>1.61</v>
@@ -5352,53 +5352,53 @@
         <v>1000</v>
       </c>
       <c r="BM19" t="n">
-        <v>1.84</v>
+        <v>1.83</v>
       </c>
       <c r="BN19" t="n">
-        <v>7.6</v>
+        <v>8.6</v>
       </c>
       <c r="BO19" t="n">
-        <v>3.95</v>
+        <v>4.6</v>
       </c>
       <c r="BP19" t="n">
-        <v>23</v>
+        <v>38</v>
       </c>
       <c r="BQ19" t="n">
-        <v>1.71</v>
+        <v>1.74</v>
       </c>
       <c r="BR19" t="n">
-        <v>40</v>
+        <v>1000</v>
       </c>
       <c r="BS19" t="n">
-        <v>1.76</v>
+        <v>1.77</v>
       </c>
       <c r="BT19" t="n">
-        <v>9.6</v>
+        <v>7</v>
       </c>
       <c r="BU19" t="n">
-        <v>4.9</v>
+        <v>3.85</v>
       </c>
       <c r="BV19" t="n">
-        <v>38</v>
+        <v>28</v>
       </c>
       <c r="BW19" t="n">
-        <v>1.76</v>
+        <v>1.72</v>
       </c>
       <c r="BX19" t="n">
         <v>50</v>
       </c>
       <c r="BY19" t="n">
-        <v>1.78</v>
+        <v>1.76</v>
       </c>
       <c r="BZ19" t="n">
-        <v>34</v>
+        <v>48</v>
       </c>
       <c r="CA19" t="n">
-        <v>1.75</v>
+        <v>1.76</v>
       </c>
       <c r="CB19" t="inlineStr">
         <is>
-          <t>2026-06-10 18:12:00</t>
+          <t>2026-06-10 20:21:14</t>
         </is>
       </c>
     </row>
@@ -5420,239 +5420,239 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>St Patricks</t>
+          <t>Waterford</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Drogheda</t>
+          <t>Sligo Rovers</t>
         </is>
       </c>
       <c r="F20" t="n">
-        <v>1.36</v>
+        <v>2.26</v>
       </c>
       <c r="G20" t="n">
-        <v>1.4</v>
+        <v>2.42</v>
       </c>
       <c r="H20" t="n">
-        <v>11</v>
+        <v>3.2</v>
       </c>
       <c r="I20" t="n">
-        <v>15</v>
+        <v>3.55</v>
       </c>
       <c r="J20" t="n">
-        <v>5</v>
+        <v>3.5</v>
       </c>
       <c r="K20" t="n">
-        <v>5.6</v>
+        <v>3.9</v>
       </c>
       <c r="L20" t="n">
-        <v>1.33</v>
+        <v>1.12</v>
       </c>
       <c r="M20" t="n">
         <v>1.06</v>
       </c>
       <c r="N20" t="n">
-        <v>3.7</v>
+        <v>3.95</v>
       </c>
       <c r="O20" t="n">
-        <v>1.26</v>
+        <v>1.28</v>
       </c>
       <c r="P20" t="n">
-        <v>2.06</v>
+        <v>2.02</v>
       </c>
       <c r="Q20" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="R20" t="n">
+        <v>1.39</v>
+      </c>
+      <c r="S20" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="T20" t="n">
+        <v>1.69</v>
+      </c>
+      <c r="U20" t="n">
+        <v>2.22</v>
+      </c>
+      <c r="V20" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="W20" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="X20" t="n">
+        <v>17</v>
+      </c>
+      <c r="Y20" t="n">
+        <v>15</v>
+      </c>
+      <c r="Z20" t="n">
+        <v>26</v>
+      </c>
+      <c r="AA20" t="n">
+        <v>85</v>
+      </c>
+      <c r="AB20" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="AC20" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="AD20" t="n">
+        <v>15</v>
+      </c>
+      <c r="AE20" t="n">
+        <v>55</v>
+      </c>
+      <c r="AF20" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="AG20" t="n">
+        <v>12</v>
+      </c>
+      <c r="AH20" t="n">
+        <v>17.5</v>
+      </c>
+      <c r="AI20" t="n">
+        <v>65</v>
+      </c>
+      <c r="AJ20" t="n">
+        <v>46</v>
+      </c>
+      <c r="AK20" t="n">
+        <v>25</v>
+      </c>
+      <c r="AL20" t="n">
+        <v>50</v>
+      </c>
+      <c r="AM20" t="n">
+        <v>100</v>
+      </c>
+      <c r="AN20" t="n">
+        <v>17.5</v>
+      </c>
+      <c r="AO20" t="n">
+        <v>48</v>
+      </c>
+      <c r="AP20" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="AQ20" t="n">
+        <v>12</v>
+      </c>
+      <c r="AR20" t="n">
+        <v>20</v>
+      </c>
+      <c r="AS20" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="AT20" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="AU20" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="AV20" t="n">
+        <v>12</v>
+      </c>
+      <c r="AW20" t="n">
+        <v>30</v>
+      </c>
+      <c r="AX20" t="n">
+        <v>13</v>
+      </c>
+      <c r="AY20" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="AZ20" t="n">
+        <v>14</v>
+      </c>
+      <c r="BA20" t="n">
+        <v>36</v>
+      </c>
+      <c r="BB20" t="n">
+        <v>7</v>
+      </c>
+      <c r="BC20" t="n">
+        <v>20</v>
+      </c>
+      <c r="BD20" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="BE20" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="BF20" t="n">
+        <v>12</v>
+      </c>
+      <c r="BG20" t="n">
+        <v>7</v>
+      </c>
+      <c r="BH20" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BI20" t="n">
         <v>1.84</v>
       </c>
-      <c r="R20" t="n">
-        <v>1.38</v>
-      </c>
-      <c r="S20" t="n">
-        <v>3.15</v>
-      </c>
-      <c r="T20" t="n">
-        <v>2.18</v>
-      </c>
-      <c r="U20" t="n">
-        <v>1.66</v>
-      </c>
-      <c r="V20" t="n">
-        <v>1.07</v>
-      </c>
-      <c r="W20" t="n">
+      <c r="BJ20" t="n">
+        <v>13</v>
+      </c>
+      <c r="BK20" t="n">
+        <v>1.61</v>
+      </c>
+      <c r="BL20" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BM20" t="n">
+        <v>1.84</v>
+      </c>
+      <c r="BN20" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="BO20" t="n">
         <v>3.45</v>
       </c>
-      <c r="X20" t="n">
-        <v>1000</v>
-      </c>
-      <c r="Y20" t="n">
-        <v>1000</v>
-      </c>
-      <c r="Z20" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AA20" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AB20" t="n">
-        <v>7.8</v>
-      </c>
-      <c r="AC20" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AD20" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AE20" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AF20" t="n">
-        <v>8</v>
-      </c>
-      <c r="AG20" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AH20" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AI20" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AJ20" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AK20" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AL20" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AM20" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AN20" t="n">
-        <v>7.2</v>
-      </c>
-      <c r="AO20" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AP20" t="n">
-        <v>14</v>
-      </c>
-      <c r="AQ20" t="n">
-        <v>1.65</v>
-      </c>
-      <c r="AR20" t="n">
-        <v>1.66</v>
-      </c>
-      <c r="AS20" t="n">
-        <v>1.66</v>
-      </c>
-      <c r="AT20" t="n">
-        <v>6.4</v>
-      </c>
-      <c r="AU20" t="n">
-        <v>10</v>
-      </c>
-      <c r="AV20" t="n">
-        <v>1.65</v>
-      </c>
-      <c r="AW20" t="n">
-        <v>1.66</v>
-      </c>
-      <c r="AX20" t="n">
-        <v>6.4</v>
-      </c>
-      <c r="AY20" t="n">
-        <v>9</v>
-      </c>
-      <c r="AZ20" t="n">
-        <v>1.65</v>
-      </c>
-      <c r="BA20" t="n">
-        <v>1.66</v>
-      </c>
-      <c r="BB20" t="n">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="BC20" t="n">
-        <v>13.5</v>
-      </c>
-      <c r="BD20" t="n">
-        <v>1.66</v>
-      </c>
-      <c r="BE20" t="n">
-        <v>1.66</v>
-      </c>
-      <c r="BF20" t="n">
-        <v>5.1</v>
-      </c>
-      <c r="BG20" t="n">
-        <v>1.66</v>
-      </c>
-      <c r="BH20" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BI20" t="n">
-        <v>1.88</v>
-      </c>
-      <c r="BJ20" t="n">
-        <v>18.5</v>
-      </c>
-      <c r="BK20" t="n">
+      <c r="BP20" t="n">
+        <v>23</v>
+      </c>
+      <c r="BQ20" t="n">
         <v>1.71</v>
-      </c>
-      <c r="BL20" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BM20" t="n">
-        <v>1.88</v>
-      </c>
-      <c r="BN20" t="n">
-        <v>4.9</v>
-      </c>
-      <c r="BO20" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="BP20" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="BQ20" t="n">
-        <v>1.61</v>
       </c>
       <c r="BR20" t="n">
         <v>40</v>
       </c>
       <c r="BS20" t="n">
-        <v>1.8</v>
+        <v>1.76</v>
       </c>
       <c r="BT20" t="n">
-        <v>20</v>
+        <v>9.6</v>
       </c>
       <c r="BU20" t="n">
-        <v>1.72</v>
+        <v>4.3</v>
       </c>
       <c r="BV20" t="n">
-        <v>1000</v>
+        <v>38</v>
       </c>
       <c r="BW20" t="n">
-        <v>1.88</v>
+        <v>1.76</v>
       </c>
       <c r="BX20" t="n">
-        <v>1000</v>
+        <v>50</v>
       </c>
       <c r="BY20" t="n">
-        <v>1.88</v>
+        <v>1.78</v>
       </c>
       <c r="BZ20" t="n">
-        <v>22</v>
+        <v>34</v>
       </c>
       <c r="CA20" t="n">
-        <v>1.73</v>
+        <v>1.75</v>
       </c>
       <c r="CB20" t="inlineStr">
         <is>
-          <t>2026-06-10 18:12:00</t>
+          <t>2026-06-10 20:21:14</t>
         </is>
       </c>
     </row>
@@ -5674,246 +5674,246 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>Galway Utd</t>
+          <t>St Patricks</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Dundalk</t>
+          <t>Drogheda</t>
         </is>
       </c>
       <c r="F21" t="n">
-        <v>2.68</v>
+        <v>1.36</v>
       </c>
       <c r="G21" t="n">
-        <v>3.2</v>
+        <v>1.42</v>
       </c>
       <c r="H21" t="n">
-        <v>2.3</v>
+        <v>10.5</v>
       </c>
       <c r="I21" t="n">
-        <v>2.8</v>
+        <v>13</v>
       </c>
       <c r="J21" t="n">
-        <v>2.64</v>
+        <v>4.9</v>
       </c>
       <c r="K21" t="n">
-        <v>1000</v>
+        <v>5.6</v>
       </c>
       <c r="L21" t="n">
         <v>1.01</v>
       </c>
       <c r="M21" t="n">
-        <v>1.01</v>
+        <v>1.06</v>
       </c>
       <c r="N21" t="n">
-        <v>3.95</v>
+        <v>3.9</v>
       </c>
       <c r="O21" t="n">
-        <v>1.2</v>
+        <v>1.28</v>
       </c>
       <c r="P21" t="n">
-        <v>2.36</v>
+        <v>2.06</v>
       </c>
       <c r="Q21" t="n">
-        <v>1.4</v>
+        <v>1.84</v>
       </c>
       <c r="R21" t="n">
-        <v>1.39</v>
+        <v>1.38</v>
       </c>
       <c r="S21" t="n">
-        <v>2.24</v>
+        <v>3.15</v>
       </c>
       <c r="T21" t="n">
-        <v>1.3</v>
+        <v>2.2</v>
       </c>
       <c r="U21" t="n">
-        <v>1.9</v>
+        <v>1.67</v>
       </c>
       <c r="V21" t="n">
-        <v>1.55</v>
+        <v>1.08</v>
       </c>
       <c r="W21" t="n">
-        <v>1.45</v>
+        <v>3.4</v>
       </c>
       <c r="X21" t="n">
-        <v>1000</v>
+        <v>21</v>
       </c>
       <c r="Y21" t="n">
-        <v>1000</v>
+        <v>38</v>
       </c>
       <c r="Z21" t="n">
-        <v>1000</v>
+        <v>130</v>
       </c>
       <c r="AA21" t="n">
-        <v>1000</v>
+        <v>630</v>
       </c>
       <c r="AB21" t="n">
-        <v>1000</v>
+        <v>7.6</v>
       </c>
       <c r="AC21" t="n">
-        <v>18</v>
+        <v>14.5</v>
       </c>
       <c r="AD21" t="n">
+        <v>55</v>
+      </c>
+      <c r="AE21" t="n">
+        <v>280</v>
+      </c>
+      <c r="AF21" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="AG21" t="n">
+        <v>13</v>
+      </c>
+      <c r="AH21" t="n">
+        <v>40</v>
+      </c>
+      <c r="AI21" t="n">
+        <v>220</v>
+      </c>
+      <c r="AJ21" t="n">
+        <v>13</v>
+      </c>
+      <c r="AK21" t="n">
+        <v>19.5</v>
+      </c>
+      <c r="AL21" t="n">
+        <v>60</v>
+      </c>
+      <c r="AM21" t="n">
+        <v>270</v>
+      </c>
+      <c r="AN21" t="n">
+        <v>7</v>
+      </c>
+      <c r="AO21" t="n">
+        <v>460</v>
+      </c>
+      <c r="AP21" t="n">
+        <v>14</v>
+      </c>
+      <c r="AQ21" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="AR21" t="n">
+        <v>5.7</v>
+      </c>
+      <c r="AS21" t="n">
+        <v>5.9</v>
+      </c>
+      <c r="AT21" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="AU21" t="n">
+        <v>10</v>
+      </c>
+      <c r="AV21" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="AW21" t="n">
+        <v>5.8</v>
+      </c>
+      <c r="AX21" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="AY21" t="n">
+        <v>9</v>
+      </c>
+      <c r="AZ21" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="BA21" t="n">
+        <v>5.8</v>
+      </c>
+      <c r="BB21" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="BC21" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="BD21" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="BE21" t="n">
+        <v>5.8</v>
+      </c>
+      <c r="BF21" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="BG21" t="n">
+        <v>5.9</v>
+      </c>
+      <c r="BH21" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BI21" t="n">
+        <v>1.88</v>
+      </c>
+      <c r="BJ21" t="n">
+        <v>18.5</v>
+      </c>
+      <c r="BK21" t="n">
+        <v>1.71</v>
+      </c>
+      <c r="BL21" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BM21" t="n">
+        <v>1.88</v>
+      </c>
+      <c r="BN21" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="BO21" t="n">
+        <v>2.54</v>
+      </c>
+      <c r="BP21" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="BQ21" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="BR21" t="n">
+        <v>40</v>
+      </c>
+      <c r="BS21" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BT21" t="n">
+        <v>20</v>
+      </c>
+      <c r="BU21" t="n">
+        <v>1.72</v>
+      </c>
+      <c r="BV21" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BW21" t="n">
+        <v>1.88</v>
+      </c>
+      <c r="BX21" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BY21" t="n">
+        <v>1.88</v>
+      </c>
+      <c r="BZ21" t="n">
         <v>22</v>
       </c>
-      <c r="AE21" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AF21" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AG21" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AH21" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AI21" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AJ21" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AK21" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AL21" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AM21" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AN21" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AO21" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AP21" t="n">
-        <v>1.11</v>
-      </c>
-      <c r="AQ21" t="n">
-        <v>1.11</v>
-      </c>
-      <c r="AR21" t="n">
-        <v>1.11</v>
-      </c>
-      <c r="AS21" t="n">
-        <v>1.11</v>
-      </c>
-      <c r="AT21" t="n">
-        <v>1.11</v>
-      </c>
-      <c r="AU21" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="AV21" t="n">
-        <v>1.06</v>
-      </c>
-      <c r="AW21" t="n">
-        <v>1.11</v>
-      </c>
-      <c r="AX21" t="n">
-        <v>1.11</v>
-      </c>
-      <c r="AY21" t="n">
-        <v>1.11</v>
-      </c>
-      <c r="AZ21" t="n">
-        <v>1.11</v>
-      </c>
-      <c r="BA21" t="n">
-        <v>1.11</v>
-      </c>
-      <c r="BB21" t="n">
-        <v>1.11</v>
-      </c>
-      <c r="BC21" t="n">
-        <v>1.11</v>
-      </c>
-      <c r="BD21" t="n">
-        <v>1.11</v>
-      </c>
-      <c r="BE21" t="n">
-        <v>1.11</v>
-      </c>
-      <c r="BF21" t="n">
-        <v>1.11</v>
-      </c>
-      <c r="BG21" t="n">
-        <v>1.11</v>
-      </c>
-      <c r="BH21" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BI21" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="BJ21" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BK21" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="BL21" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BM21" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="BN21" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BO21" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="BP21" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BQ21" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="BR21" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BS21" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="BT21" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BU21" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="BV21" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BW21" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="BX21" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BY21" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="BZ21" t="n">
-        <v>1000</v>
-      </c>
       <c r="CA21" t="n">
-        <v>1.04</v>
+        <v>1.73</v>
       </c>
       <c r="CB21" t="inlineStr">
         <is>
-          <t>2026-06-10 18:12:00</t>
+          <t>2026-06-10 20:21:14</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Bolivian Liga de Futbol Profesional</t>
+          <t>Irish Premier Division</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -5923,36 +5923,36 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>16:00:00</t>
+          <t>15:45:00</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>San Antonio Bulo Bulo</t>
+          <t>Galway Utd</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Academia de Balompie Boli</t>
+          <t>Dundalk</t>
         </is>
       </c>
       <c r="F22" t="n">
-        <v>1.6</v>
+        <v>2.54</v>
       </c>
       <c r="G22" t="n">
-        <v>1.62</v>
+        <v>3.6</v>
       </c>
       <c r="H22" t="n">
-        <v>4.8</v>
+        <v>2.18</v>
       </c>
       <c r="I22" t="n">
-        <v>870</v>
+        <v>2.88</v>
       </c>
       <c r="J22" t="n">
-        <v>4.5</v>
+        <v>2.66</v>
       </c>
       <c r="K22" t="n">
-        <v>500</v>
+        <v>1000</v>
       </c>
       <c r="L22" t="n">
         <v>1.01</v>
@@ -5961,142 +5961,142 @@
         <v>1.01</v>
       </c>
       <c r="N22" t="n">
-        <v>1.25</v>
+        <v>2.44</v>
       </c>
       <c r="O22" t="n">
-        <v>1.1</v>
+        <v>1.2</v>
       </c>
       <c r="P22" t="n">
+        <v>2.36</v>
+      </c>
+      <c r="Q22" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="R22" t="n">
+        <v>1.39</v>
+      </c>
+      <c r="S22" t="n">
+        <v>2.16</v>
+      </c>
+      <c r="T22" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="U22" t="n">
+        <v>1.92</v>
+      </c>
+      <c r="V22" t="n">
+        <v>1.52</v>
+      </c>
+      <c r="W22" t="n">
+        <v>1.39</v>
+      </c>
+      <c r="X22" t="n">
+        <v>1000</v>
+      </c>
+      <c r="Y22" t="n">
+        <v>1000</v>
+      </c>
+      <c r="Z22" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AA22" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AB22" t="n">
+        <v>950</v>
+      </c>
+      <c r="AC22" t="n">
+        <v>18</v>
+      </c>
+      <c r="AD22" t="n">
+        <v>22</v>
+      </c>
+      <c r="AE22" t="n">
+        <v>48</v>
+      </c>
+      <c r="AF22" t="n">
+        <v>48</v>
+      </c>
+      <c r="AG22" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AH22" t="n">
+        <v>950</v>
+      </c>
+      <c r="AI22" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AJ22" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AK22" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AL22" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AM22" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AN22" t="n">
+        <v>48</v>
+      </c>
+      <c r="AO22" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AP22" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="AQ22" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="AR22" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="AS22" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="AT22" t="n">
         <v>1.24</v>
       </c>
-      <c r="Q22" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="R22" t="n">
-        <v>1.18</v>
-      </c>
-      <c r="S22" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="T22" t="n">
-        <v>1.11</v>
-      </c>
-      <c r="U22" t="n">
-        <v>1.11</v>
-      </c>
-      <c r="V22" t="n">
-        <v>1.18</v>
-      </c>
-      <c r="W22" t="n">
-        <v>2.6</v>
-      </c>
-      <c r="X22" t="n">
-        <v>1000</v>
-      </c>
-      <c r="Y22" t="n">
-        <v>1000</v>
-      </c>
-      <c r="Z22" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AA22" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AB22" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AC22" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AD22" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AE22" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AF22" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AG22" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AH22" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AI22" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AJ22" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AK22" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AL22" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AM22" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AN22" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AO22" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AP22" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="AQ22" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="AR22" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="AS22" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="AT22" t="n">
-        <v>1.01</v>
-      </c>
       <c r="AU22" t="n">
-        <v>1.01</v>
+        <v>1.21</v>
       </c>
       <c r="AV22" t="n">
-        <v>1.01</v>
+        <v>1.22</v>
       </c>
       <c r="AW22" t="n">
-        <v>1.01</v>
+        <v>1.26</v>
       </c>
       <c r="AX22" t="n">
-        <v>1.01</v>
+        <v>1.26</v>
       </c>
       <c r="AY22" t="n">
-        <v>1.01</v>
+        <v>1.29</v>
       </c>
       <c r="AZ22" t="n">
-        <v>1.01</v>
+        <v>1.24</v>
       </c>
       <c r="BA22" t="n">
-        <v>1.01</v>
+        <v>1.29</v>
       </c>
       <c r="BB22" t="n">
-        <v>1.01</v>
+        <v>1.29</v>
       </c>
       <c r="BC22" t="n">
-        <v>1.01</v>
+        <v>1.29</v>
       </c>
       <c r="BD22" t="n">
-        <v>1.01</v>
+        <v>1.29</v>
       </c>
       <c r="BE22" t="n">
-        <v>1.01</v>
+        <v>1.29</v>
       </c>
       <c r="BF22" t="n">
-        <v>1.01</v>
+        <v>10.5</v>
       </c>
       <c r="BG22" t="n">
-        <v>1.01</v>
+        <v>1.29</v>
       </c>
       <c r="BH22" t="n">
         <v>1000</v>
@@ -6160,14 +6160,14 @@
       </c>
       <c r="CB22" t="inlineStr">
         <is>
-          <t>2026-06-10 18:12:00</t>
+          <t>2026-06-10 20:21:14</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Irish Premier Division</t>
+          <t>Bolivian Liga de Futbol Profesional</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -6182,67 +6182,67 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>Shelbourne</t>
+          <t>San Antonio Bulo Bulo</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Shamrock Rovers</t>
+          <t>Academia de Balompie Boli</t>
         </is>
       </c>
       <c r="F23" t="n">
-        <v>2.78</v>
+        <v>1.42</v>
       </c>
       <c r="G23" t="n">
-        <v>3.05</v>
+        <v>1.66</v>
       </c>
       <c r="H23" t="n">
-        <v>2.68</v>
+        <v>4.8</v>
       </c>
       <c r="I23" t="n">
-        <v>2.92</v>
+        <v>1000</v>
       </c>
       <c r="J23" t="n">
-        <v>3</v>
+        <v>4.5</v>
       </c>
       <c r="K23" t="n">
-        <v>3.55</v>
+        <v>1000</v>
       </c>
       <c r="L23" t="n">
         <v>1.01</v>
       </c>
       <c r="M23" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="N23" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="O23" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="P23" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="Q23" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="R23" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="S23" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="T23" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="U23" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="V23" t="n">
         <v>1.08</v>
       </c>
-      <c r="N23" t="n">
-        <v>3.25</v>
-      </c>
-      <c r="O23" t="n">
-        <v>1.38</v>
-      </c>
-      <c r="P23" t="n">
-        <v>1.78</v>
-      </c>
-      <c r="Q23" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="R23" t="n">
-        <v>1.29</v>
-      </c>
-      <c r="S23" t="n">
-        <v>3.85</v>
-      </c>
-      <c r="T23" t="n">
-        <v>1.81</v>
-      </c>
-      <c r="U23" t="n">
-        <v>2.04</v>
-      </c>
-      <c r="V23" t="n">
-        <v>1.52</v>
-      </c>
       <c r="W23" t="n">
-        <v>1.49</v>
+        <v>2.5</v>
       </c>
       <c r="X23" t="n">
         <v>1000</v>
@@ -6299,34 +6299,34 @@
         <v>1000</v>
       </c>
       <c r="AP23" t="n">
-        <v>10.5</v>
+        <v>1.01</v>
       </c>
       <c r="AQ23" t="n">
-        <v>9.199999999999999</v>
+        <v>1.01</v>
       </c>
       <c r="AR23" t="n">
-        <v>1.05</v>
+        <v>1.01</v>
       </c>
       <c r="AS23" t="n">
         <v>1.01</v>
       </c>
       <c r="AT23" t="n">
-        <v>9.4</v>
+        <v>1.01</v>
       </c>
       <c r="AU23" t="n">
-        <v>6.6</v>
+        <v>1.01</v>
       </c>
       <c r="AV23" t="n">
-        <v>11</v>
+        <v>1.01</v>
       </c>
       <c r="AW23" t="n">
         <v>1.01</v>
       </c>
       <c r="AX23" t="n">
-        <v>16.5</v>
+        <v>1.01</v>
       </c>
       <c r="AY23" t="n">
-        <v>11.5</v>
+        <v>1.01</v>
       </c>
       <c r="AZ23" t="n">
         <v>1.01</v>
@@ -6338,7 +6338,7 @@
         <v>1.01</v>
       </c>
       <c r="BC23" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BD23" t="n">
         <v>1.01</v>
@@ -6347,81 +6347,81 @@
         <v>1.01</v>
       </c>
       <c r="BF23" t="n">
-        <v>1.05</v>
+        <v>1.01</v>
       </c>
       <c r="BG23" t="n">
-        <v>1.05</v>
+        <v>1.01</v>
       </c>
       <c r="BH23" t="n">
         <v>1000</v>
       </c>
       <c r="BI23" t="n">
-        <v>1.8</v>
+        <v>1.04</v>
       </c>
       <c r="BJ23" t="n">
-        <v>13.5</v>
+        <v>1000</v>
       </c>
       <c r="BK23" t="n">
-        <v>1.59</v>
+        <v>1.04</v>
       </c>
       <c r="BL23" t="n">
         <v>1000</v>
       </c>
       <c r="BM23" t="n">
-        <v>1.8</v>
+        <v>1.04</v>
       </c>
       <c r="BN23" t="n">
-        <v>8.199999999999999</v>
+        <v>1000</v>
       </c>
       <c r="BO23" t="n">
-        <v>4.5</v>
+        <v>1.04</v>
       </c>
       <c r="BP23" t="n">
-        <v>34</v>
+        <v>1000</v>
       </c>
       <c r="BQ23" t="n">
-        <v>1.71</v>
+        <v>1.04</v>
       </c>
       <c r="BR23" t="n">
-        <v>50</v>
+        <v>1000</v>
       </c>
       <c r="BS23" t="n">
-        <v>1.74</v>
+        <v>1.04</v>
       </c>
       <c r="BT23" t="n">
-        <v>8</v>
+        <v>1000</v>
       </c>
       <c r="BU23" t="n">
-        <v>4.4</v>
+        <v>1.04</v>
       </c>
       <c r="BV23" t="n">
-        <v>30</v>
+        <v>1000</v>
       </c>
       <c r="BW23" t="n">
-        <v>1.7</v>
+        <v>1.04</v>
       </c>
       <c r="BX23" t="n">
-        <v>50</v>
+        <v>1000</v>
       </c>
       <c r="BY23" t="n">
-        <v>1.74</v>
+        <v>1.04</v>
       </c>
       <c r="BZ23" t="n">
-        <v>46</v>
+        <v>1000</v>
       </c>
       <c r="CA23" t="n">
-        <v>1.74</v>
+        <v>1.04</v>
       </c>
       <c r="CB23" t="inlineStr">
         <is>
-          <t>2026-06-10 18:12:00</t>
+          <t>2026-06-10 20:21:14</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Brazilian Serie B</t>
+          <t>Irish Premier Division</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -6431,498 +6431,1006 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>19:00:00</t>
+          <t>16:00:00</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>Atletico GO</t>
+          <t>Shelbourne</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>CRB</t>
+          <t>Shamrock Rovers</t>
         </is>
       </c>
       <c r="F24" t="n">
-        <v>2.18</v>
+        <v>2.78</v>
       </c>
       <c r="G24" t="n">
-        <v>2.58</v>
+        <v>3.05</v>
       </c>
       <c r="H24" t="n">
-        <v>3.5</v>
+        <v>2.68</v>
       </c>
       <c r="I24" t="n">
-        <v>4.7</v>
+        <v>2.9</v>
       </c>
       <c r="J24" t="n">
-        <v>2.5</v>
+        <v>3.25</v>
       </c>
       <c r="K24" t="n">
+        <v>3.55</v>
+      </c>
+      <c r="L24" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="M24" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="N24" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="O24" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="P24" t="n">
+        <v>1.78</v>
+      </c>
+      <c r="Q24" t="n">
+        <v>2.12</v>
+      </c>
+      <c r="R24" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="S24" t="n">
         <v>3.9</v>
       </c>
-      <c r="L24" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="M24" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="N24" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="O24" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="P24" t="n">
-        <v>1.65</v>
-      </c>
-      <c r="Q24" t="n">
-        <v>2.18</v>
-      </c>
-      <c r="R24" t="n">
-        <v>1.17</v>
-      </c>
-      <c r="S24" t="n">
-        <v>3.75</v>
-      </c>
       <c r="T24" t="n">
-        <v>1.01</v>
+        <v>1.83</v>
       </c>
       <c r="U24" t="n">
-        <v>1.01</v>
+        <v>2.06</v>
       </c>
       <c r="V24" t="n">
-        <v>1.27</v>
+        <v>1.52</v>
       </c>
       <c r="W24" t="n">
-        <v>1.64</v>
+        <v>1.49</v>
       </c>
       <c r="X24" t="n">
-        <v>1000</v>
+        <v>15</v>
       </c>
       <c r="Y24" t="n">
-        <v>1000</v>
+        <v>12.5</v>
       </c>
       <c r="Z24" t="n">
-        <v>1000</v>
+        <v>22</v>
       </c>
       <c r="AA24" t="n">
-        <v>1000</v>
+        <v>55</v>
       </c>
       <c r="AB24" t="n">
-        <v>1000</v>
+        <v>13</v>
       </c>
       <c r="AC24" t="n">
-        <v>1000</v>
+        <v>9</v>
       </c>
       <c r="AD24" t="n">
-        <v>1000</v>
+        <v>15.5</v>
       </c>
       <c r="AE24" t="n">
-        <v>1000</v>
+        <v>42</v>
       </c>
       <c r="AF24" t="n">
-        <v>1000</v>
+        <v>23</v>
       </c>
       <c r="AG24" t="n">
-        <v>1000</v>
+        <v>16</v>
       </c>
       <c r="AH24" t="n">
-        <v>1000</v>
+        <v>22</v>
       </c>
       <c r="AI24" t="n">
-        <v>1000</v>
+        <v>60</v>
       </c>
       <c r="AJ24" t="n">
-        <v>1000</v>
+        <v>60</v>
       </c>
       <c r="AK24" t="n">
-        <v>1000</v>
+        <v>44</v>
       </c>
       <c r="AL24" t="n">
-        <v>1000</v>
+        <v>60</v>
       </c>
       <c r="AM24" t="n">
-        <v>1000</v>
+        <v>130</v>
       </c>
       <c r="AN24" t="n">
-        <v>1000</v>
+        <v>42</v>
       </c>
       <c r="AO24" t="n">
-        <v>1000</v>
+        <v>38</v>
       </c>
       <c r="AP24" t="n">
-        <v>1.01</v>
+        <v>10.5</v>
       </c>
       <c r="AQ24" t="n">
-        <v>1.01</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AR24" t="n">
-        <v>1.01</v>
+        <v>3.6</v>
       </c>
       <c r="AS24" t="n">
-        <v>1.01</v>
+        <v>4</v>
       </c>
       <c r="AT24" t="n">
-        <v>1.01</v>
+        <v>9.4</v>
       </c>
       <c r="AU24" t="n">
-        <v>1.01</v>
+        <v>6.6</v>
       </c>
       <c r="AV24" t="n">
-        <v>1.01</v>
+        <v>11</v>
       </c>
       <c r="AW24" t="n">
-        <v>1.01</v>
+        <v>3.9</v>
       </c>
       <c r="AX24" t="n">
-        <v>1.01</v>
+        <v>16.5</v>
       </c>
       <c r="AY24" t="n">
-        <v>1.01</v>
+        <v>11.5</v>
       </c>
       <c r="AZ24" t="n">
-        <v>1.01</v>
+        <v>3.6</v>
       </c>
       <c r="BA24" t="n">
-        <v>1.01</v>
+        <v>4</v>
       </c>
       <c r="BB24" t="n">
-        <v>1.01</v>
+        <v>4</v>
       </c>
       <c r="BC24" t="n">
-        <v>1.01</v>
+        <v>3.9</v>
       </c>
       <c r="BD24" t="n">
-        <v>1.01</v>
+        <v>4</v>
       </c>
       <c r="BE24" t="n">
-        <v>1.01</v>
+        <v>4.1</v>
       </c>
       <c r="BF24" t="n">
-        <v>1.01</v>
+        <v>3.9</v>
       </c>
       <c r="BG24" t="n">
-        <v>1.01</v>
+        <v>3.85</v>
       </c>
       <c r="BH24" t="n">
         <v>1000</v>
       </c>
       <c r="BI24" t="n">
-        <v>1.01</v>
+        <v>1.8</v>
       </c>
       <c r="BJ24" t="n">
-        <v>1000</v>
+        <v>13.5</v>
       </c>
       <c r="BK24" t="n">
-        <v>1.01</v>
+        <v>1.59</v>
       </c>
       <c r="BL24" t="n">
         <v>1000</v>
       </c>
       <c r="BM24" t="n">
-        <v>1.01</v>
+        <v>1.8</v>
       </c>
       <c r="BN24" t="n">
-        <v>1000</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BO24" t="n">
-        <v>1.01</v>
+        <v>4.5</v>
       </c>
       <c r="BP24" t="n">
-        <v>1000</v>
+        <v>34</v>
       </c>
       <c r="BQ24" t="n">
-        <v>1.01</v>
+        <v>1.71</v>
       </c>
       <c r="BR24" t="n">
-        <v>1000</v>
+        <v>50</v>
       </c>
       <c r="BS24" t="n">
-        <v>1.01</v>
+        <v>1.74</v>
       </c>
       <c r="BT24" t="n">
-        <v>1000</v>
+        <v>8</v>
       </c>
       <c r="BU24" t="n">
-        <v>1.01</v>
+        <v>4.4</v>
       </c>
       <c r="BV24" t="n">
-        <v>1000</v>
+        <v>30</v>
       </c>
       <c r="BW24" t="n">
-        <v>1.01</v>
+        <v>1.7</v>
       </c>
       <c r="BX24" t="n">
-        <v>1000</v>
+        <v>50</v>
       </c>
       <c r="BY24" t="n">
-        <v>1.01</v>
+        <v>1.74</v>
       </c>
       <c r="BZ24" t="n">
-        <v>1000</v>
+        <v>46</v>
       </c>
       <c r="CA24" t="n">
-        <v>1.01</v>
+        <v>1.74</v>
       </c>
       <c r="CB24" t="inlineStr">
         <is>
-          <t>2026-06-10 18:12:00</t>
+          <t>2026-06-10 20:21:14</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
+          <t>Icelandic 1 Deild</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>2026-06-12</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>16:15:00</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>Throttur</t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>HK Kopavogur</t>
+        </is>
+      </c>
+      <c r="F25" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="G25" t="n">
+        <v>1000</v>
+      </c>
+      <c r="H25" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="I25" t="n">
+        <v>1000</v>
+      </c>
+      <c r="J25" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="K25" t="n">
+        <v>950</v>
+      </c>
+      <c r="L25" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="M25" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="N25" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="O25" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="P25" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="Q25" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="R25" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="S25" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="T25" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="U25" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="V25" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="W25" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="X25" t="n">
+        <v>1000</v>
+      </c>
+      <c r="Y25" t="n">
+        <v>1000</v>
+      </c>
+      <c r="Z25" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AA25" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AB25" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AC25" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AD25" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AE25" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AF25" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AG25" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AH25" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AI25" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AJ25" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AK25" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AL25" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AM25" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AN25" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AO25" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AP25" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AQ25" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AR25" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AS25" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AT25" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AU25" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AV25" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AW25" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AX25" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AY25" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AZ25" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BA25" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BB25" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BC25" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BD25" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BE25" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BF25" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BG25" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BH25" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BI25" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BJ25" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BK25" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BL25" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BM25" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BN25" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BO25" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BP25" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BQ25" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BR25" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BS25" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BT25" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BU25" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BV25" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BW25" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BX25" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BY25" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BZ25" t="n">
+        <v>1000</v>
+      </c>
+      <c r="CA25" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="CB25" t="inlineStr">
+        <is>
+          <t>2026-06-10 20:21:14</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>Brazilian Serie B</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>2026-06-12</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>19:00:00</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>Atletico GO</t>
+        </is>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>CRB</t>
+        </is>
+      </c>
+      <c r="F26" t="n">
+        <v>2.18</v>
+      </c>
+      <c r="G26" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="H26" t="n">
+        <v>3.15</v>
+      </c>
+      <c r="I26" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="J26" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="K26" t="n">
+        <v>3.45</v>
+      </c>
+      <c r="L26" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="M26" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="N26" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="O26" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="P26" t="n">
+        <v>1.64</v>
+      </c>
+      <c r="Q26" t="n">
+        <v>1.92</v>
+      </c>
+      <c r="R26" t="n">
+        <v>1.19</v>
+      </c>
+      <c r="S26" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="T26" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="U26" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="V26" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="W26" t="n">
+        <v>1.58</v>
+      </c>
+      <c r="X26" t="n">
+        <v>1000</v>
+      </c>
+      <c r="Y26" t="n">
+        <v>1000</v>
+      </c>
+      <c r="Z26" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AA26" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AB26" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AC26" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AD26" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AE26" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AF26" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AG26" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AH26" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AI26" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AJ26" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AK26" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AL26" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AM26" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AN26" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AO26" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AP26" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AQ26" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AR26" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AS26" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AT26" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AU26" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AV26" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AW26" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AX26" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AY26" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AZ26" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BA26" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BB26" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BC26" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BD26" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BE26" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BF26" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BG26" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BH26" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BI26" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="BJ26" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BK26" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="BL26" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BM26" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="BN26" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BO26" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="BP26" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BQ26" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="BR26" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BS26" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="BT26" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BU26" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="BV26" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BW26" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="BX26" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BY26" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="BZ26" t="n">
+        <v>1000</v>
+      </c>
+      <c r="CA26" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="CB26" t="inlineStr">
+        <is>
+          <t>2026-06-10 20:21:14</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
           <t>Bolivian Liga de Futbol Profesional</t>
         </is>
       </c>
-      <c r="B25" t="inlineStr">
+      <c r="B27" t="inlineStr">
         <is>
           <t>2026-06-12</t>
         </is>
       </c>
-      <c r="C25" t="inlineStr">
+      <c r="C27" t="inlineStr">
         <is>
           <t>20:00:00</t>
         </is>
       </c>
-      <c r="D25" t="inlineStr">
+      <c r="D27" t="inlineStr">
         <is>
           <t>Nacional Potosi</t>
         </is>
       </c>
-      <c r="E25" t="inlineStr">
+      <c r="E27" t="inlineStr">
         <is>
           <t>CDT Real Oruro</t>
         </is>
       </c>
-      <c r="F25" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="G25" t="n">
-        <v>1000</v>
-      </c>
-      <c r="H25" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="I25" t="n">
-        <v>1000</v>
-      </c>
-      <c r="J25" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="K25" t="n">
-        <v>1000</v>
-      </c>
-      <c r="L25" t="n">
-        <v>0</v>
-      </c>
-      <c r="M25" t="n">
-        <v>0</v>
-      </c>
-      <c r="N25" t="n">
-        <v>0</v>
-      </c>
-      <c r="O25" t="n">
-        <v>0</v>
-      </c>
-      <c r="P25" t="n">
+      <c r="F27" t="n">
+        <v>1.37</v>
+      </c>
+      <c r="G27" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="H27" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="I27" t="n">
+        <v>1000</v>
+      </c>
+      <c r="J27" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="K27" t="n">
+        <v>1000</v>
+      </c>
+      <c r="L27" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="M27" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="N27" t="n">
         <v>1.24</v>
       </c>
-      <c r="Q25" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="R25" t="n">
-        <v>0</v>
-      </c>
-      <c r="S25" t="n">
-        <v>0</v>
-      </c>
-      <c r="T25" t="n">
-        <v>0</v>
-      </c>
-      <c r="U25" t="n">
-        <v>0</v>
-      </c>
-      <c r="V25" t="n">
-        <v>0</v>
-      </c>
-      <c r="W25" t="n">
-        <v>0</v>
-      </c>
-      <c r="X25" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y25" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z25" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA25" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB25" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC25" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD25" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE25" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF25" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG25" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH25" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI25" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ25" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK25" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL25" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM25" t="n">
-        <v>0</v>
-      </c>
-      <c r="AN25" t="n">
-        <v>0</v>
-      </c>
-      <c r="AO25" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP25" t="n">
-        <v>0</v>
-      </c>
-      <c r="AQ25" t="n">
-        <v>0</v>
-      </c>
-      <c r="AR25" t="n">
-        <v>0</v>
-      </c>
-      <c r="AS25" t="n">
-        <v>0</v>
-      </c>
-      <c r="AT25" t="n">
-        <v>0</v>
-      </c>
-      <c r="AU25" t="n">
-        <v>0</v>
-      </c>
-      <c r="AV25" t="n">
-        <v>0</v>
-      </c>
-      <c r="AW25" t="n">
-        <v>0</v>
-      </c>
-      <c r="AX25" t="n">
-        <v>0</v>
-      </c>
-      <c r="AY25" t="n">
-        <v>0</v>
-      </c>
-      <c r="AZ25" t="n">
-        <v>0</v>
-      </c>
-      <c r="BA25" t="n">
-        <v>0</v>
-      </c>
-      <c r="BB25" t="n">
-        <v>0</v>
-      </c>
-      <c r="BC25" t="n">
-        <v>0</v>
-      </c>
-      <c r="BD25" t="n">
-        <v>0</v>
-      </c>
-      <c r="BE25" t="n">
-        <v>0</v>
-      </c>
-      <c r="BF25" t="n">
-        <v>0</v>
-      </c>
-      <c r="BG25" t="n">
-        <v>0</v>
-      </c>
-      <c r="BH25" t="n">
-        <v>0</v>
-      </c>
-      <c r="BI25" t="n">
-        <v>0</v>
-      </c>
-      <c r="BJ25" t="n">
-        <v>0</v>
-      </c>
-      <c r="BK25" t="n">
-        <v>0</v>
-      </c>
-      <c r="BL25" t="n">
-        <v>0</v>
-      </c>
-      <c r="BM25" t="n">
-        <v>0</v>
-      </c>
-      <c r="BN25" t="n">
-        <v>0</v>
-      </c>
-      <c r="BO25" t="n">
-        <v>0</v>
-      </c>
-      <c r="BP25" t="n">
-        <v>0</v>
-      </c>
-      <c r="BQ25" t="n">
-        <v>0</v>
-      </c>
-      <c r="BR25" t="n">
-        <v>0</v>
-      </c>
-      <c r="BS25" t="n">
-        <v>0</v>
-      </c>
-      <c r="BT25" t="n">
-        <v>0</v>
-      </c>
-      <c r="BU25" t="n">
-        <v>0</v>
-      </c>
-      <c r="BV25" t="n">
-        <v>0</v>
-      </c>
-      <c r="BW25" t="n">
-        <v>0</v>
-      </c>
-      <c r="BX25" t="n">
-        <v>0</v>
-      </c>
-      <c r="BY25" t="n">
-        <v>0</v>
-      </c>
-      <c r="BZ25" t="n">
-        <v>0</v>
-      </c>
-      <c r="CA25" t="n">
-        <v>0</v>
-      </c>
-      <c r="CB25" t="inlineStr">
-        <is>
-          <t>2026-06-10 18:12:00</t>
+      <c r="O27" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="P27" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="Q27" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="R27" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="S27" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="T27" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="U27" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="V27" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="W27" t="n">
+        <v>2.62</v>
+      </c>
+      <c r="X27" t="n">
+        <v>1000</v>
+      </c>
+      <c r="Y27" t="n">
+        <v>1000</v>
+      </c>
+      <c r="Z27" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AA27" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AB27" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AC27" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AD27" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AE27" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AF27" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AG27" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AH27" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AI27" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AJ27" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AK27" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AL27" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AM27" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AN27" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AO27" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AP27" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AQ27" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AR27" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AS27" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AT27" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AU27" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AV27" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AW27" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AX27" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AY27" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AZ27" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BA27" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BB27" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BC27" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BD27" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BE27" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BF27" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BG27" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BH27" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BI27" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BJ27" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BK27" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BL27" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BM27" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BN27" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BO27" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BP27" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BQ27" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BR27" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BS27" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BT27" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BU27" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BV27" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BW27" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BX27" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BY27" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BZ27" t="n">
+        <v>1000</v>
+      </c>
+      <c r="CA27" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="CB27" t="inlineStr">
+        <is>
+          <t>2026-06-10 20:21:14</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-06-12.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-06-12.xlsx
@@ -857,13 +857,13 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>1.08</v>
+        <v>1.11</v>
       </c>
       <c r="G2" t="n">
         <v>1000</v>
       </c>
       <c r="H2" t="n">
-        <v>1.04</v>
+        <v>1.11</v>
       </c>
       <c r="I2" t="n">
         <v>1000</v>
@@ -908,7 +908,7 @@
         <v>1.01</v>
       </c>
       <c r="W2" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="X2" t="n">
         <v>1000</v>
@@ -1080,7 +1080,7 @@
       </c>
       <c r="CB2" t="inlineStr">
         <is>
-          <t>2026-06-10 20:21:14</t>
+          <t>2026-06-10 22:29:58</t>
         </is>
       </c>
     </row>
@@ -1334,7 +1334,7 @@
       </c>
       <c r="CB3" t="inlineStr">
         <is>
-          <t>2026-06-10 20:21:14</t>
+          <t>2026-06-10 22:29:58</t>
         </is>
       </c>
     </row>
@@ -1365,13 +1365,13 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>1.09</v>
+        <v>1.11</v>
       </c>
       <c r="G4" t="n">
         <v>1000</v>
       </c>
       <c r="H4" t="n">
-        <v>1.09</v>
+        <v>1.11</v>
       </c>
       <c r="I4" t="n">
         <v>1000</v>
@@ -1413,7 +1413,7 @@
         <v>1.11</v>
       </c>
       <c r="V4" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="W4" t="n">
         <v>1.02</v>
@@ -1588,7 +1588,7 @@
       </c>
       <c r="CB4" t="inlineStr">
         <is>
-          <t>2026-06-10 20:21:14</t>
+          <t>2026-06-10 22:29:58</t>
         </is>
       </c>
     </row>
@@ -1631,10 +1631,10 @@
         <v>1000</v>
       </c>
       <c r="J5" t="n">
-        <v>1.04</v>
+        <v>1.09</v>
       </c>
       <c r="K5" t="n">
-        <v>1000</v>
+        <v>3</v>
       </c>
       <c r="L5" t="n">
         <v>1.01</v>
@@ -1652,7 +1652,7 @@
         <v>1.24</v>
       </c>
       <c r="Q5" t="n">
-        <v>1.02</v>
+        <v>1.55</v>
       </c>
       <c r="R5" t="n">
         <v>1.18</v>
@@ -1667,7 +1667,7 @@
         <v>1.11</v>
       </c>
       <c r="V5" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="W5" t="n">
         <v>1.02</v>
@@ -1842,7 +1842,7 @@
       </c>
       <c r="CB5" t="inlineStr">
         <is>
-          <t>2026-06-10 20:21:14</t>
+          <t>2026-06-10 22:29:58</t>
         </is>
       </c>
     </row>
@@ -1873,13 +1873,13 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>1.08</v>
+        <v>1.11</v>
       </c>
       <c r="G6" t="n">
         <v>1000</v>
       </c>
       <c r="H6" t="n">
-        <v>1.09</v>
+        <v>1.11</v>
       </c>
       <c r="I6" t="n">
         <v>1000</v>
@@ -1921,7 +1921,7 @@
         <v>1.11</v>
       </c>
       <c r="V6" t="n">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="W6" t="n">
         <v>1.02</v>
@@ -2096,7 +2096,7 @@
       </c>
       <c r="CB6" t="inlineStr">
         <is>
-          <t>2026-06-10 20:21:14</t>
+          <t>2026-06-10 22:29:58</t>
         </is>
       </c>
     </row>
@@ -2127,13 +2127,13 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>1.08</v>
+        <v>1.1</v>
       </c>
       <c r="G7" t="n">
         <v>1000</v>
       </c>
       <c r="H7" t="n">
-        <v>1.08</v>
+        <v>1.1</v>
       </c>
       <c r="I7" t="n">
         <v>1000</v>
@@ -2175,7 +2175,7 @@
         <v>1.11</v>
       </c>
       <c r="V7" t="n">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="W7" t="n">
         <v>1.02</v>
@@ -2350,7 +2350,7 @@
       </c>
       <c r="CB7" t="inlineStr">
         <is>
-          <t>2026-06-10 20:21:14</t>
+          <t>2026-06-10 22:29:58</t>
         </is>
       </c>
     </row>
@@ -2381,19 +2381,19 @@
         </is>
       </c>
       <c r="F8" t="n">
-        <v>1.04</v>
+        <v>1.09</v>
       </c>
       <c r="G8" t="n">
         <v>1000</v>
       </c>
       <c r="H8" t="n">
-        <v>1.04</v>
+        <v>1.09</v>
       </c>
       <c r="I8" t="n">
         <v>1000</v>
       </c>
       <c r="J8" t="n">
-        <v>1.09</v>
+        <v>1.1</v>
       </c>
       <c r="K8" t="n">
         <v>1000</v>
@@ -2604,7 +2604,7 @@
       </c>
       <c r="CB8" t="inlineStr">
         <is>
-          <t>2026-06-10 20:21:14</t>
+          <t>2026-06-10 22:29:58</t>
         </is>
       </c>
     </row>
@@ -2635,7 +2635,7 @@
         </is>
       </c>
       <c r="F9" t="n">
-        <v>1.04</v>
+        <v>1.09</v>
       </c>
       <c r="G9" t="n">
         <v>1000</v>
@@ -2647,7 +2647,7 @@
         <v>1000</v>
       </c>
       <c r="J9" t="n">
-        <v>1.09</v>
+        <v>1.1</v>
       </c>
       <c r="K9" t="n">
         <v>1000</v>
@@ -2659,13 +2659,13 @@
         <v>1.01</v>
       </c>
       <c r="N9" t="n">
-        <v>1.3</v>
+        <v>1.32</v>
       </c>
       <c r="O9" t="n">
         <v>1.12</v>
       </c>
       <c r="P9" t="n">
-        <v>1.3</v>
+        <v>1.32</v>
       </c>
       <c r="Q9" t="n">
         <v>1.11</v>
@@ -2858,7 +2858,7 @@
       </c>
       <c r="CB9" t="inlineStr">
         <is>
-          <t>2026-06-10 20:21:14</t>
+          <t>2026-06-10 22:29:58</t>
         </is>
       </c>
     </row>
@@ -2889,13 +2889,13 @@
         </is>
       </c>
       <c r="F10" t="n">
-        <v>1.07</v>
+        <v>1.09</v>
       </c>
       <c r="G10" t="n">
         <v>1000</v>
       </c>
       <c r="H10" t="n">
-        <v>1.04</v>
+        <v>1.11</v>
       </c>
       <c r="I10" t="n">
         <v>1000</v>
@@ -2922,13 +2922,13 @@
         <v>1.24</v>
       </c>
       <c r="Q10" t="n">
-        <v>1.05</v>
+        <v>1.56</v>
       </c>
       <c r="R10" t="n">
         <v>1.18</v>
       </c>
       <c r="S10" t="n">
-        <v>1.52</v>
+        <v>1.56</v>
       </c>
       <c r="T10" t="n">
         <v>1.11</v>
@@ -2937,10 +2937,10 @@
         <v>1.11</v>
       </c>
       <c r="V10" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="W10" t="n">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="X10" t="n">
         <v>1000</v>
@@ -3112,7 +3112,7 @@
       </c>
       <c r="CB10" t="inlineStr">
         <is>
-          <t>2026-06-10 20:21:14</t>
+          <t>2026-06-10 22:29:58</t>
         </is>
       </c>
     </row>
@@ -3143,19 +3143,19 @@
         </is>
       </c>
       <c r="F11" t="n">
-        <v>1.04</v>
+        <v>1.09</v>
       </c>
       <c r="G11" t="n">
         <v>1000</v>
       </c>
       <c r="H11" t="n">
-        <v>1.04</v>
+        <v>1.09</v>
       </c>
       <c r="I11" t="n">
         <v>1000</v>
       </c>
       <c r="J11" t="n">
-        <v>1.11</v>
+        <v>1.1</v>
       </c>
       <c r="K11" t="n">
         <v>1000</v>
@@ -3170,7 +3170,7 @@
         <v>1.25</v>
       </c>
       <c r="O11" t="n">
-        <v>1.02</v>
+        <v>1.43</v>
       </c>
       <c r="P11" t="n">
         <v>1.24</v>
@@ -3366,7 +3366,7 @@
       </c>
       <c r="CB11" t="inlineStr">
         <is>
-          <t>2026-06-10 20:21:14</t>
+          <t>2026-06-10 22:29:58</t>
         </is>
       </c>
     </row>
@@ -3421,7 +3421,7 @@
         <v>1.01</v>
       </c>
       <c r="N12" t="n">
-        <v>1.3</v>
+        <v>1.31</v>
       </c>
       <c r="O12" t="n">
         <v>1.15</v>
@@ -3620,7 +3620,7 @@
       </c>
       <c r="CB12" t="inlineStr">
         <is>
-          <t>2026-06-10 20:21:14</t>
+          <t>2026-06-10 22:29:58</t>
         </is>
       </c>
     </row>
@@ -3663,7 +3663,7 @@
         <v>1000</v>
       </c>
       <c r="J13" t="n">
-        <v>1.11</v>
+        <v>1.13</v>
       </c>
       <c r="K13" t="n">
         <v>1000</v>
@@ -3675,10 +3675,10 @@
         <v>1.01</v>
       </c>
       <c r="N13" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="O13" t="n">
         <v>1.25</v>
-      </c>
-      <c r="O13" t="n">
-        <v>1.01</v>
       </c>
       <c r="P13" t="n">
         <v>1.25</v>
@@ -3874,7 +3874,7 @@
       </c>
       <c r="CB13" t="inlineStr">
         <is>
-          <t>2026-06-10 20:21:14</t>
+          <t>2026-06-10 22:29:58</t>
         </is>
       </c>
     </row>
@@ -3905,22 +3905,22 @@
         </is>
       </c>
       <c r="F14" t="n">
-        <v>1.01</v>
+        <v>1.53</v>
       </c>
       <c r="G14" t="n">
-        <v>1000</v>
+        <v>990</v>
       </c>
       <c r="H14" t="n">
-        <v>1.01</v>
+        <v>1.46</v>
       </c>
       <c r="I14" t="n">
         <v>1000</v>
       </c>
       <c r="J14" t="n">
-        <v>1.02</v>
+        <v>1.04</v>
       </c>
       <c r="K14" t="n">
-        <v>950</v>
+        <v>3.25</v>
       </c>
       <c r="L14" t="n">
         <v>1.01</v>
@@ -3944,13 +3944,13 @@
         <v>1.12</v>
       </c>
       <c r="S14" t="n">
-        <v>1.01</v>
+        <v>1.52</v>
       </c>
       <c r="T14" t="n">
-        <v>1.01</v>
+        <v>1.11</v>
       </c>
       <c r="U14" t="n">
-        <v>1.01</v>
+        <v>1.11</v>
       </c>
       <c r="V14" t="n">
         <v>1.01</v>
@@ -4013,52 +4013,52 @@
         <v>1000</v>
       </c>
       <c r="AP14" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AQ14" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AR14" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AS14" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AT14" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AU14" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AV14" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AW14" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AX14" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AY14" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AZ14" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BA14" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BB14" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BC14" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BD14" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BE14" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BF14" t="n">
         <v>1.01</v>
@@ -4070,55 +4070,55 @@
         <v>1000</v>
       </c>
       <c r="BI14" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BJ14" t="n">
         <v>1000</v>
       </c>
       <c r="BK14" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BL14" t="n">
         <v>1000</v>
       </c>
       <c r="BM14" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BN14" t="n">
         <v>1000</v>
       </c>
       <c r="BO14" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BP14" t="n">
         <v>1000</v>
       </c>
       <c r="BQ14" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BR14" t="n">
         <v>1000</v>
       </c>
       <c r="BS14" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BT14" t="n">
         <v>1000</v>
       </c>
       <c r="BU14" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BV14" t="n">
         <v>1000</v>
       </c>
       <c r="BW14" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BX14" t="n">
         <v>1000</v>
       </c>
       <c r="BY14" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BZ14" t="n">
         <v>0</v>
@@ -4128,7 +4128,7 @@
       </c>
       <c r="CB14" t="inlineStr">
         <is>
-          <t>2026-06-10 20:21:14</t>
+          <t>2026-06-10 22:29:58</t>
         </is>
       </c>
     </row>
@@ -4168,7 +4168,7 @@
         <v>1.75</v>
       </c>
       <c r="I15" t="n">
-        <v>2.28</v>
+        <v>2.22</v>
       </c>
       <c r="J15" t="n">
         <v>3.25</v>
@@ -4207,7 +4207,7 @@
         <v>1.73</v>
       </c>
       <c r="V15" t="n">
-        <v>1.79</v>
+        <v>1.83</v>
       </c>
       <c r="W15" t="n">
         <v>1.22</v>
@@ -4382,7 +4382,7 @@
       </c>
       <c r="CB15" t="inlineStr">
         <is>
-          <t>2026-06-10 20:21:14</t>
+          <t>2026-06-10 22:29:58</t>
         </is>
       </c>
     </row>
@@ -4419,7 +4419,7 @@
         <v>2.5</v>
       </c>
       <c r="H16" t="n">
-        <v>3.25</v>
+        <v>3.2</v>
       </c>
       <c r="I16" t="n">
         <v>3.65</v>
@@ -4431,7 +4431,7 @@
         <v>3.65</v>
       </c>
       <c r="L16" t="n">
-        <v>1.43</v>
+        <v>1.36</v>
       </c>
       <c r="M16" t="n">
         <v>1.08</v>
@@ -4636,7 +4636,7 @@
       </c>
       <c r="CB16" t="inlineStr">
         <is>
-          <t>2026-06-10 20:21:14</t>
+          <t>2026-06-10 22:29:58</t>
         </is>
       </c>
     </row>
@@ -4694,10 +4694,10 @@
         <v>5</v>
       </c>
       <c r="O17" t="n">
-        <v>1.21</v>
+        <v>1.2</v>
       </c>
       <c r="P17" t="n">
-        <v>2.44</v>
+        <v>2.42</v>
       </c>
       <c r="Q17" t="n">
         <v>1.6</v>
@@ -4718,7 +4718,7 @@
         <v>1.96</v>
       </c>
       <c r="W17" t="n">
-        <v>1.27</v>
+        <v>1.28</v>
       </c>
       <c r="X17" t="n">
         <v>29</v>
@@ -4890,7 +4890,7 @@
       </c>
       <c r="CB17" t="inlineStr">
         <is>
-          <t>2026-06-10 20:21:14</t>
+          <t>2026-06-10 22:29:58</t>
         </is>
       </c>
     </row>
@@ -5017,7 +5017,7 @@
         <v>75</v>
       </c>
       <c r="AL18" t="n">
-        <v>70</v>
+        <v>75</v>
       </c>
       <c r="AM18" t="n">
         <v>130</v>
@@ -5144,7 +5144,7 @@
       </c>
       <c r="CB18" t="inlineStr">
         <is>
-          <t>2026-06-10 20:21:14</t>
+          <t>2026-06-10 22:29:58</t>
         </is>
       </c>
     </row>
@@ -5181,7 +5181,7 @@
         <v>3.5</v>
       </c>
       <c r="H19" t="n">
-        <v>2.42</v>
+        <v>2.44</v>
       </c>
       <c r="I19" t="n">
         <v>2.64</v>
@@ -5292,7 +5292,7 @@
         <v>12</v>
       </c>
       <c r="AS19" t="n">
-        <v>7.2</v>
+        <v>30</v>
       </c>
       <c r="AT19" t="n">
         <v>9.4</v>
@@ -5398,7 +5398,7 @@
       </c>
       <c r="CB19" t="inlineStr">
         <is>
-          <t>2026-06-10 20:21:14</t>
+          <t>2026-06-10 22:29:58</t>
         </is>
       </c>
     </row>
@@ -5438,7 +5438,7 @@
         <v>3.2</v>
       </c>
       <c r="I20" t="n">
-        <v>3.55</v>
+        <v>3.5</v>
       </c>
       <c r="J20" t="n">
         <v>3.5</v>
@@ -5447,7 +5447,7 @@
         <v>3.9</v>
       </c>
       <c r="L20" t="n">
-        <v>1.12</v>
+        <v>1.34</v>
       </c>
       <c r="M20" t="n">
         <v>1.06</v>
@@ -5489,7 +5489,7 @@
         <v>15</v>
       </c>
       <c r="Z20" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="AA20" t="n">
         <v>85</v>
@@ -5546,7 +5546,7 @@
         <v>20</v>
       </c>
       <c r="AS20" t="n">
-        <v>7.8</v>
+        <v>8</v>
       </c>
       <c r="AT20" t="n">
         <v>9.4</v>
@@ -5573,22 +5573,22 @@
         <v>36</v>
       </c>
       <c r="BB20" t="n">
-        <v>7</v>
+        <v>7.2</v>
       </c>
       <c r="BC20" t="n">
         <v>20</v>
       </c>
       <c r="BD20" t="n">
-        <v>7.2</v>
+        <v>7.4</v>
       </c>
       <c r="BE20" t="n">
-        <v>8.199999999999999</v>
+        <v>8.4</v>
       </c>
       <c r="BF20" t="n">
         <v>12</v>
       </c>
       <c r="BG20" t="n">
-        <v>7</v>
+        <v>7.2</v>
       </c>
       <c r="BH20" t="n">
         <v>1000</v>
@@ -5652,7 +5652,7 @@
       </c>
       <c r="CB20" t="inlineStr">
         <is>
-          <t>2026-06-10 20:21:14</t>
+          <t>2026-06-10 22:29:58</t>
         </is>
       </c>
     </row>
@@ -5683,7 +5683,7 @@
         </is>
       </c>
       <c r="F21" t="n">
-        <v>1.36</v>
+        <v>1.35</v>
       </c>
       <c r="G21" t="n">
         <v>1.42</v>
@@ -5906,7 +5906,7 @@
       </c>
       <c r="CB21" t="inlineStr">
         <is>
-          <t>2026-06-10 20:21:14</t>
+          <t>2026-06-10 22:29:58</t>
         </is>
       </c>
     </row>
@@ -5940,13 +5940,13 @@
         <v>2.54</v>
       </c>
       <c r="G22" t="n">
-        <v>3.6</v>
+        <v>3.55</v>
       </c>
       <c r="H22" t="n">
         <v>2.18</v>
       </c>
       <c r="I22" t="n">
-        <v>2.88</v>
+        <v>2.92</v>
       </c>
       <c r="J22" t="n">
         <v>2.66</v>
@@ -5982,7 +5982,7 @@
         <v>1.3</v>
       </c>
       <c r="U22" t="n">
-        <v>1.92</v>
+        <v>1.94</v>
       </c>
       <c r="V22" t="n">
         <v>1.52</v>
@@ -5994,7 +5994,7 @@
         <v>1000</v>
       </c>
       <c r="Y22" t="n">
-        <v>1000</v>
+        <v>950</v>
       </c>
       <c r="Z22" t="n">
         <v>1000</v>
@@ -6018,7 +6018,7 @@
         <v>48</v>
       </c>
       <c r="AG22" t="n">
-        <v>1000</v>
+        <v>26</v>
       </c>
       <c r="AH22" t="n">
         <v>950</v>
@@ -6042,61 +6042,61 @@
         <v>48</v>
       </c>
       <c r="AO22" t="n">
-        <v>1000</v>
+        <v>30</v>
       </c>
       <c r="AP22" t="n">
-        <v>1.29</v>
+        <v>1.49</v>
       </c>
       <c r="AQ22" t="n">
-        <v>1.29</v>
+        <v>1.42</v>
       </c>
       <c r="AR22" t="n">
-        <v>1.29</v>
+        <v>1.5</v>
       </c>
       <c r="AS22" t="n">
-        <v>1.29</v>
+        <v>1.5</v>
       </c>
       <c r="AT22" t="n">
-        <v>1.24</v>
+        <v>1.43</v>
       </c>
       <c r="AU22" t="n">
-        <v>1.21</v>
+        <v>1.38</v>
       </c>
       <c r="AV22" t="n">
-        <v>1.22</v>
+        <v>1.4</v>
       </c>
       <c r="AW22" t="n">
-        <v>1.26</v>
+        <v>1.45</v>
       </c>
       <c r="AX22" t="n">
-        <v>1.26</v>
+        <v>1.45</v>
       </c>
       <c r="AY22" t="n">
-        <v>1.29</v>
+        <v>1.41</v>
       </c>
       <c r="AZ22" t="n">
-        <v>1.24</v>
+        <v>1.43</v>
       </c>
       <c r="BA22" t="n">
-        <v>1.29</v>
+        <v>1.5</v>
       </c>
       <c r="BB22" t="n">
-        <v>1.29</v>
+        <v>1.5</v>
       </c>
       <c r="BC22" t="n">
-        <v>1.29</v>
+        <v>1.5</v>
       </c>
       <c r="BD22" t="n">
-        <v>1.29</v>
+        <v>1.5</v>
       </c>
       <c r="BE22" t="n">
-        <v>1.29</v>
+        <v>1.5</v>
       </c>
       <c r="BF22" t="n">
         <v>10.5</v>
       </c>
       <c r="BG22" t="n">
-        <v>1.29</v>
+        <v>7.8</v>
       </c>
       <c r="BH22" t="n">
         <v>1000</v>
@@ -6160,7 +6160,7 @@
       </c>
       <c r="CB22" t="inlineStr">
         <is>
-          <t>2026-06-10 20:21:14</t>
+          <t>2026-06-10 22:29:58</t>
         </is>
       </c>
     </row>
@@ -6239,7 +6239,7 @@
         <v>1.11</v>
       </c>
       <c r="V23" t="n">
-        <v>1.08</v>
+        <v>1.09</v>
       </c>
       <c r="W23" t="n">
         <v>2.5</v>
@@ -6414,7 +6414,7 @@
       </c>
       <c r="CB23" t="inlineStr">
         <is>
-          <t>2026-06-10 20:21:14</t>
+          <t>2026-06-10 22:29:58</t>
         </is>
       </c>
     </row>
@@ -6668,7 +6668,7 @@
       </c>
       <c r="CB24" t="inlineStr">
         <is>
-          <t>2026-06-10 20:21:14</t>
+          <t>2026-06-10 22:29:58</t>
         </is>
       </c>
     </row>
@@ -6702,16 +6702,16 @@
         <v>1.04</v>
       </c>
       <c r="G25" t="n">
-        <v>1000</v>
+        <v>990</v>
       </c>
       <c r="H25" t="n">
         <v>1.04</v>
       </c>
       <c r="I25" t="n">
-        <v>1000</v>
+        <v>990</v>
       </c>
       <c r="J25" t="n">
-        <v>1.02</v>
+        <v>1.06</v>
       </c>
       <c r="K25" t="n">
         <v>950</v>
@@ -6723,13 +6723,13 @@
         <v>1.01</v>
       </c>
       <c r="N25" t="n">
-        <v>1.25</v>
+        <v>1.26</v>
       </c>
       <c r="O25" t="n">
         <v>1.12</v>
       </c>
       <c r="P25" t="n">
-        <v>1.25</v>
+        <v>1.26</v>
       </c>
       <c r="Q25" t="n">
         <v>1.12</v>
@@ -6741,16 +6741,16 @@
         <v>1.12</v>
       </c>
       <c r="T25" t="n">
-        <v>1.01</v>
+        <v>1.11</v>
       </c>
       <c r="U25" t="n">
-        <v>1.01</v>
+        <v>1.11</v>
       </c>
       <c r="V25" t="n">
         <v>1.01</v>
       </c>
       <c r="W25" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="X25" t="n">
         <v>1000</v>
@@ -6807,52 +6807,52 @@
         <v>1000</v>
       </c>
       <c r="AP25" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AQ25" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AR25" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AS25" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AT25" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AU25" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AV25" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AW25" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AX25" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AY25" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AZ25" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BA25" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BB25" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BC25" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BD25" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BE25" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BF25" t="n">
         <v>1.01</v>
@@ -6864,65 +6864,65 @@
         <v>1000</v>
       </c>
       <c r="BI25" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BJ25" t="n">
         <v>1000</v>
       </c>
       <c r="BK25" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BL25" t="n">
         <v>1000</v>
       </c>
       <c r="BM25" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BN25" t="n">
         <v>1000</v>
       </c>
       <c r="BO25" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BP25" t="n">
         <v>1000</v>
       </c>
       <c r="BQ25" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BR25" t="n">
         <v>1000</v>
       </c>
       <c r="BS25" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BT25" t="n">
         <v>1000</v>
       </c>
       <c r="BU25" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BV25" t="n">
         <v>1000</v>
       </c>
       <c r="BW25" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BX25" t="n">
         <v>1000</v>
       </c>
       <c r="BY25" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BZ25" t="n">
         <v>1000</v>
       </c>
       <c r="CA25" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="CB25" t="inlineStr">
         <is>
-          <t>2026-06-10 20:21:14</t>
+          <t>2026-06-10 22:29:58</t>
         </is>
       </c>
     </row>
@@ -6953,10 +6953,10 @@
         </is>
       </c>
       <c r="F26" t="n">
-        <v>2.18</v>
+        <v>2.08</v>
       </c>
       <c r="G26" t="n">
-        <v>2.7</v>
+        <v>2.68</v>
       </c>
       <c r="H26" t="n">
         <v>3.15</v>
@@ -6965,7 +6965,7 @@
         <v>4.7</v>
       </c>
       <c r="J26" t="n">
-        <v>2.38</v>
+        <v>2.44</v>
       </c>
       <c r="K26" t="n">
         <v>3.45</v>
@@ -6974,16 +6974,16 @@
         <v>1.01</v>
       </c>
       <c r="M26" t="n">
-        <v>1.01</v>
+        <v>1.09</v>
       </c>
       <c r="N26" t="n">
-        <v>1.1</v>
+        <v>2.4</v>
       </c>
       <c r="O26" t="n">
-        <v>1.05</v>
+        <v>1.44</v>
       </c>
       <c r="P26" t="n">
-        <v>1.64</v>
+        <v>1.53</v>
       </c>
       <c r="Q26" t="n">
         <v>1.92</v>
@@ -7004,7 +7004,7 @@
         <v>1.27</v>
       </c>
       <c r="W26" t="n">
-        <v>1.58</v>
+        <v>1.59</v>
       </c>
       <c r="X26" t="n">
         <v>1000</v>
@@ -7176,7 +7176,7 @@
       </c>
       <c r="CB26" t="inlineStr">
         <is>
-          <t>2026-06-10 20:21:14</t>
+          <t>2026-06-10 22:29:58</t>
         </is>
       </c>
     </row>
@@ -7210,7 +7210,7 @@
         <v>1.37</v>
       </c>
       <c r="G27" t="n">
-        <v>1.5</v>
+        <v>1.49</v>
       </c>
       <c r="H27" t="n">
         <v>2.7</v>
@@ -7222,16 +7222,16 @@
         <v>2.7</v>
       </c>
       <c r="K27" t="n">
-        <v>1000</v>
+        <v>950</v>
       </c>
       <c r="L27" t="n">
-        <v>1.17</v>
+        <v>1.01</v>
       </c>
       <c r="M27" t="n">
         <v>1.01</v>
       </c>
       <c r="N27" t="n">
-        <v>1.24</v>
+        <v>1.25</v>
       </c>
       <c r="O27" t="n">
         <v>1.09</v>
@@ -7243,22 +7243,22 @@
         <v>1.09</v>
       </c>
       <c r="R27" t="n">
-        <v>1.08</v>
+        <v>1.18</v>
       </c>
       <c r="S27" t="n">
         <v>1.09</v>
       </c>
       <c r="T27" t="n">
-        <v>1.01</v>
+        <v>1.11</v>
       </c>
       <c r="U27" t="n">
-        <v>1.01</v>
+        <v>1.11</v>
       </c>
       <c r="V27" t="n">
         <v>1.08</v>
       </c>
       <c r="W27" t="n">
-        <v>2.62</v>
+        <v>2.7</v>
       </c>
       <c r="X27" t="n">
         <v>1000</v>
@@ -7315,52 +7315,52 @@
         <v>1000</v>
       </c>
       <c r="AP27" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AQ27" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AR27" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AS27" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AT27" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AU27" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AV27" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AW27" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AX27" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AY27" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AZ27" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BA27" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BB27" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BC27" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BD27" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BE27" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BF27" t="n">
         <v>1.01</v>
@@ -7372,65 +7372,65 @@
         <v>1000</v>
       </c>
       <c r="BI27" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BJ27" t="n">
         <v>1000</v>
       </c>
       <c r="BK27" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BL27" t="n">
         <v>1000</v>
       </c>
       <c r="BM27" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BN27" t="n">
         <v>1000</v>
       </c>
       <c r="BO27" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BP27" t="n">
         <v>1000</v>
       </c>
       <c r="BQ27" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BR27" t="n">
         <v>1000</v>
       </c>
       <c r="BS27" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BT27" t="n">
         <v>1000</v>
       </c>
       <c r="BU27" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BV27" t="n">
         <v>1000</v>
       </c>
       <c r="BW27" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BX27" t="n">
         <v>1000</v>
       </c>
       <c r="BY27" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BZ27" t="n">
         <v>1000</v>
       </c>
       <c r="CA27" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="CB27" t="inlineStr">
         <is>
-          <t>2026-06-10 20:21:14</t>
+          <t>2026-06-10 22:29:58</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-06-12.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-06-12.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:CB27"/>
+  <dimension ref="A1:CB28"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -857,13 +857,13 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>1.11</v>
+        <v>1.13</v>
       </c>
       <c r="G2" t="n">
         <v>1000</v>
       </c>
       <c r="H2" t="n">
-        <v>1.11</v>
+        <v>1.13</v>
       </c>
       <c r="I2" t="n">
         <v>1000</v>
@@ -1080,7 +1080,7 @@
       </c>
       <c r="CB2" t="inlineStr">
         <is>
-          <t>2026-06-10 22:29:58</t>
+          <t>2026-06-11 00:39:13</t>
         </is>
       </c>
     </row>
@@ -1334,7 +1334,7 @@
       </c>
       <c r="CB3" t="inlineStr">
         <is>
-          <t>2026-06-10 22:29:58</t>
+          <t>2026-06-11 00:39:13</t>
         </is>
       </c>
     </row>
@@ -1365,13 +1365,13 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>1.11</v>
+        <v>1.13</v>
       </c>
       <c r="G4" t="n">
         <v>1000</v>
       </c>
       <c r="H4" t="n">
-        <v>1.11</v>
+        <v>1.13</v>
       </c>
       <c r="I4" t="n">
         <v>1000</v>
@@ -1413,10 +1413,10 @@
         <v>1.11</v>
       </c>
       <c r="V4" t="n">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="W4" t="n">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="X4" t="n">
         <v>1000</v>
@@ -1588,7 +1588,7 @@
       </c>
       <c r="CB4" t="inlineStr">
         <is>
-          <t>2026-06-10 22:29:58</t>
+          <t>2026-06-11 00:39:13</t>
         </is>
       </c>
     </row>
@@ -1619,13 +1619,13 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>1.04</v>
+        <v>1.54</v>
       </c>
       <c r="G5" t="n">
         <v>1000</v>
       </c>
       <c r="H5" t="n">
-        <v>1.04</v>
+        <v>1.54</v>
       </c>
       <c r="I5" t="n">
         <v>1000</v>
@@ -1643,13 +1643,13 @@
         <v>1.01</v>
       </c>
       <c r="N5" t="n">
-        <v>1.25</v>
+        <v>1.26</v>
       </c>
       <c r="O5" t="n">
         <v>1.02</v>
       </c>
       <c r="P5" t="n">
-        <v>1.24</v>
+        <v>1.26</v>
       </c>
       <c r="Q5" t="n">
         <v>1.55</v>
@@ -1658,7 +1658,7 @@
         <v>1.18</v>
       </c>
       <c r="S5" t="n">
-        <v>1.05</v>
+        <v>1.55</v>
       </c>
       <c r="T5" t="n">
         <v>1.11</v>
@@ -1842,7 +1842,7 @@
       </c>
       <c r="CB5" t="inlineStr">
         <is>
-          <t>2026-06-10 22:29:58</t>
+          <t>2026-06-11 00:39:13</t>
         </is>
       </c>
     </row>
@@ -1873,13 +1873,13 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>1.11</v>
+        <v>1.13</v>
       </c>
       <c r="G6" t="n">
         <v>1000</v>
       </c>
       <c r="H6" t="n">
-        <v>1.11</v>
+        <v>1.13</v>
       </c>
       <c r="I6" t="n">
         <v>1000</v>
@@ -2096,7 +2096,7 @@
       </c>
       <c r="CB6" t="inlineStr">
         <is>
-          <t>2026-06-10 22:29:58</t>
+          <t>2026-06-11 00:39:13</t>
         </is>
       </c>
     </row>
@@ -2127,13 +2127,13 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>1.1</v>
+        <v>1.12</v>
       </c>
       <c r="G7" t="n">
         <v>1000</v>
       </c>
       <c r="H7" t="n">
-        <v>1.1</v>
+        <v>1.12</v>
       </c>
       <c r="I7" t="n">
         <v>1000</v>
@@ -2175,7 +2175,7 @@
         <v>1.11</v>
       </c>
       <c r="V7" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="W7" t="n">
         <v>1.02</v>
@@ -2350,14 +2350,14 @@
       </c>
       <c r="CB7" t="inlineStr">
         <is>
-          <t>2026-06-10 22:29:58</t>
+          <t>2026-06-11 00:39:13</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Georgian Umaglesi Liga</t>
+          <t>Swedish Division 1</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -2372,22 +2372,22 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>Dinamo Batumi</t>
+          <t>Lunds BK</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Dila Gori</t>
+          <t>Ariana FC</t>
         </is>
       </c>
       <c r="F8" t="n">
-        <v>1.09</v>
+        <v>1.04</v>
       </c>
       <c r="G8" t="n">
         <v>1000</v>
       </c>
       <c r="H8" t="n">
-        <v>1.09</v>
+        <v>1.04</v>
       </c>
       <c r="I8" t="n">
         <v>1000</v>
@@ -2405,22 +2405,22 @@
         <v>1.01</v>
       </c>
       <c r="N8" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="O8" t="n">
         <v>1.25</v>
       </c>
-      <c r="O8" t="n">
-        <v>1.33</v>
-      </c>
       <c r="P8" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="Q8" t="n">
         <v>1.24</v>
       </c>
-      <c r="Q8" t="n">
-        <v>1.33</v>
-      </c>
       <c r="R8" t="n">
-        <v>1.18</v>
+        <v>1.24</v>
       </c>
       <c r="S8" t="n">
-        <v>1.33</v>
+        <v>1.25</v>
       </c>
       <c r="T8" t="n">
         <v>1.11</v>
@@ -2429,10 +2429,10 @@
         <v>1.11</v>
       </c>
       <c r="V8" t="n">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="W8" t="n">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="X8" t="n">
         <v>1000</v>
@@ -2604,14 +2604,14 @@
       </c>
       <c r="CB8" t="inlineStr">
         <is>
-          <t>2026-06-10 22:29:58</t>
+          <t>2026-06-11 00:39:13</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Lithuanian A Lyga</t>
+          <t>Swedish Division 1</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -2626,16 +2626,16 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>VMFD Zalgiris</t>
+          <t>Umea FC</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Riteriai</t>
+          <t>Pitea</t>
         </is>
       </c>
       <c r="F9" t="n">
-        <v>1.09</v>
+        <v>1.04</v>
       </c>
       <c r="G9" t="n">
         <v>1000</v>
@@ -2659,22 +2659,22 @@
         <v>1.01</v>
       </c>
       <c r="N9" t="n">
-        <v>1.32</v>
+        <v>1.31</v>
       </c>
       <c r="O9" t="n">
-        <v>1.12</v>
+        <v>1.15</v>
       </c>
       <c r="P9" t="n">
-        <v>1.32</v>
+        <v>1.3</v>
       </c>
       <c r="Q9" t="n">
-        <v>1.11</v>
+        <v>1.15</v>
       </c>
       <c r="R9" t="n">
-        <v>1.18</v>
+        <v>1.24</v>
       </c>
       <c r="S9" t="n">
-        <v>1.12</v>
+        <v>1.14</v>
       </c>
       <c r="T9" t="n">
         <v>1.11</v>
@@ -2686,7 +2686,7 @@
         <v>1.01</v>
       </c>
       <c r="W9" t="n">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="X9" t="n">
         <v>1000</v>
@@ -2858,7 +2858,7 @@
       </c>
       <c r="CB9" t="inlineStr">
         <is>
-          <t>2026-06-10 22:29:58</t>
+          <t>2026-06-11 00:39:13</t>
         </is>
       </c>
     </row>
@@ -2880,16 +2880,16 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>CODM Meknes</t>
+          <t>DHJ El Jadida</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Club R Zemamra</t>
+          <t>Olympique Dcheira</t>
         </is>
       </c>
       <c r="F10" t="n">
-        <v>1.09</v>
+        <v>1.11</v>
       </c>
       <c r="G10" t="n">
         <v>1000</v>
@@ -2916,19 +2916,19 @@
         <v>1.25</v>
       </c>
       <c r="O10" t="n">
-        <v>1.02</v>
+        <v>1.43</v>
       </c>
       <c r="P10" t="n">
         <v>1.24</v>
       </c>
       <c r="Q10" t="n">
-        <v>1.56</v>
+        <v>1.43</v>
       </c>
       <c r="R10" t="n">
         <v>1.18</v>
       </c>
       <c r="S10" t="n">
-        <v>1.56</v>
+        <v>1.43</v>
       </c>
       <c r="T10" t="n">
         <v>1.11</v>
@@ -2940,7 +2940,7 @@
         <v>1.02</v>
       </c>
       <c r="W10" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="X10" t="n">
         <v>1000</v>
@@ -2997,52 +2997,52 @@
         <v>1000</v>
       </c>
       <c r="AP10" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AQ10" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AR10" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AS10" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AT10" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AU10" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AV10" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AW10" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AX10" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AY10" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AZ10" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BA10" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BB10" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BC10" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BD10" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BE10" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BF10" t="n">
         <v>1.01</v>
@@ -3112,7 +3112,7 @@
       </c>
       <c r="CB10" t="inlineStr">
         <is>
-          <t>2026-06-10 22:29:58</t>
+          <t>2026-06-11 00:39:13</t>
         </is>
       </c>
     </row>
@@ -3134,22 +3134,22 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>DHJ El Jadida</t>
+          <t>CODM Meknes</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Olympique Dcheira</t>
+          <t>Club R Zemamra</t>
         </is>
       </c>
       <c r="F11" t="n">
-        <v>1.09</v>
+        <v>1.11</v>
       </c>
       <c r="G11" t="n">
         <v>1000</v>
       </c>
       <c r="H11" t="n">
-        <v>1.09</v>
+        <v>1.13</v>
       </c>
       <c r="I11" t="n">
         <v>1000</v>
@@ -3167,22 +3167,22 @@
         <v>1.01</v>
       </c>
       <c r="N11" t="n">
-        <v>1.25</v>
+        <v>1.28</v>
       </c>
       <c r="O11" t="n">
-        <v>1.43</v>
+        <v>1.02</v>
       </c>
       <c r="P11" t="n">
-        <v>1.24</v>
+        <v>1.28</v>
       </c>
       <c r="Q11" t="n">
-        <v>1.43</v>
+        <v>1.56</v>
       </c>
       <c r="R11" t="n">
         <v>1.18</v>
       </c>
       <c r="S11" t="n">
-        <v>1.43</v>
+        <v>1.56</v>
       </c>
       <c r="T11" t="n">
         <v>1.11</v>
@@ -3251,52 +3251,52 @@
         <v>1000</v>
       </c>
       <c r="AP11" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AQ11" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AR11" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AS11" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AT11" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AU11" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AV11" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AW11" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AX11" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AY11" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AZ11" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BA11" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BB11" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BC11" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BD11" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BE11" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BF11" t="n">
         <v>1.01</v>
@@ -3366,14 +3366,14 @@
       </c>
       <c r="CB11" t="inlineStr">
         <is>
-          <t>2026-06-10 22:29:58</t>
+          <t>2026-06-11 00:39:13</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Swedish Division 1</t>
+          <t>Lithuanian A Lyga</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -3388,12 +3388,12 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>Umea FC</t>
+          <t>VMFD Zalgiris</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Pitea</t>
+          <t>Riteriai</t>
         </is>
       </c>
       <c r="F12" t="n">
@@ -3421,22 +3421,22 @@
         <v>1.01</v>
       </c>
       <c r="N12" t="n">
-        <v>1.31</v>
+        <v>1.32</v>
       </c>
       <c r="O12" t="n">
-        <v>1.15</v>
+        <v>1.12</v>
       </c>
       <c r="P12" t="n">
-        <v>1.3</v>
+        <v>1.32</v>
       </c>
       <c r="Q12" t="n">
-        <v>1.15</v>
+        <v>1.11</v>
       </c>
       <c r="R12" t="n">
-        <v>1.24</v>
+        <v>1.18</v>
       </c>
       <c r="S12" t="n">
-        <v>1.14</v>
+        <v>1.12</v>
       </c>
       <c r="T12" t="n">
         <v>1.11</v>
@@ -3448,7 +3448,7 @@
         <v>1.01</v>
       </c>
       <c r="W12" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="X12" t="n">
         <v>1000</v>
@@ -3620,14 +3620,14 @@
       </c>
       <c r="CB12" t="inlineStr">
         <is>
-          <t>2026-06-10 22:29:58</t>
+          <t>2026-06-11 00:39:13</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Swedish Division 1</t>
+          <t>Georgian Umaglesi Liga</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -3642,28 +3642,28 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>Lunds BK</t>
+          <t>Dinamo Batumi</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Ariana FC</t>
+          <t>Dila Gori</t>
         </is>
       </c>
       <c r="F13" t="n">
-        <v>1.04</v>
+        <v>1.1</v>
       </c>
       <c r="G13" t="n">
         <v>1000</v>
       </c>
       <c r="H13" t="n">
-        <v>1.04</v>
+        <v>1.1</v>
       </c>
       <c r="I13" t="n">
         <v>1000</v>
       </c>
       <c r="J13" t="n">
-        <v>1.13</v>
+        <v>1.1</v>
       </c>
       <c r="K13" t="n">
         <v>1000</v>
@@ -3675,22 +3675,22 @@
         <v>1.01</v>
       </c>
       <c r="N13" t="n">
-        <v>1.26</v>
+        <v>1.25</v>
       </c>
       <c r="O13" t="n">
-        <v>1.25</v>
+        <v>1.33</v>
       </c>
       <c r="P13" t="n">
-        <v>1.25</v>
+        <v>1.24</v>
       </c>
       <c r="Q13" t="n">
-        <v>1.24</v>
+        <v>1.33</v>
       </c>
       <c r="R13" t="n">
-        <v>1.24</v>
+        <v>1.18</v>
       </c>
       <c r="S13" t="n">
-        <v>1.25</v>
+        <v>1.33</v>
       </c>
       <c r="T13" t="n">
         <v>1.11</v>
@@ -3699,10 +3699,10 @@
         <v>1.11</v>
       </c>
       <c r="V13" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="W13" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="X13" t="n">
         <v>1000</v>
@@ -3874,7 +3874,7 @@
       </c>
       <c r="CB13" t="inlineStr">
         <is>
-          <t>2026-06-10 22:29:58</t>
+          <t>2026-06-11 00:39:13</t>
         </is>
       </c>
     </row>
@@ -3905,10 +3905,10 @@
         </is>
       </c>
       <c r="F14" t="n">
-        <v>1.53</v>
+        <v>1.46</v>
       </c>
       <c r="G14" t="n">
-        <v>990</v>
+        <v>1000</v>
       </c>
       <c r="H14" t="n">
         <v>1.46</v>
@@ -3917,7 +3917,7 @@
         <v>1000</v>
       </c>
       <c r="J14" t="n">
-        <v>1.04</v>
+        <v>1.08</v>
       </c>
       <c r="K14" t="n">
         <v>3.25</v>
@@ -4128,14 +4128,14 @@
       </c>
       <c r="CB14" t="inlineStr">
         <is>
-          <t>2026-06-10 22:29:58</t>
+          <t>2026-06-11 00:39:13</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Irish Division 1</t>
+          <t>Irish Premier Division</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -4150,175 +4150,175 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>Finn Harps</t>
+          <t>Galway Utd</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>UCD</t>
+          <t>Dundalk</t>
         </is>
       </c>
       <c r="F15" t="n">
-        <v>3.7</v>
+        <v>2.8</v>
       </c>
       <c r="G15" t="n">
-        <v>5.4</v>
+        <v>3.4</v>
       </c>
       <c r="H15" t="n">
-        <v>1.75</v>
+        <v>1.99</v>
       </c>
       <c r="I15" t="n">
-        <v>2.22</v>
+        <v>2.82</v>
       </c>
       <c r="J15" t="n">
-        <v>3.25</v>
+        <v>3.3</v>
       </c>
       <c r="K15" t="n">
-        <v>5</v>
+        <v>950</v>
       </c>
       <c r="L15" t="n">
         <v>1.01</v>
       </c>
       <c r="M15" t="n">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="N15" t="n">
-        <v>4.1</v>
+        <v>2.44</v>
       </c>
       <c r="O15" t="n">
-        <v>1.23</v>
+        <v>1.2</v>
       </c>
       <c r="P15" t="n">
-        <v>2.08</v>
+        <v>2.36</v>
       </c>
       <c r="Q15" t="n">
-        <v>1.75</v>
+        <v>1.4</v>
       </c>
       <c r="R15" t="n">
-        <v>1.32</v>
+        <v>1.39</v>
       </c>
       <c r="S15" t="n">
-        <v>2.3</v>
+        <v>2.16</v>
       </c>
       <c r="T15" t="n">
-        <v>1.37</v>
+        <v>1.3</v>
       </c>
       <c r="U15" t="n">
-        <v>1.73</v>
+        <v>1.96</v>
       </c>
       <c r="V15" t="n">
-        <v>1.83</v>
+        <v>1.54</v>
       </c>
       <c r="W15" t="n">
-        <v>1.22</v>
+        <v>1.42</v>
       </c>
       <c r="X15" t="n">
         <v>1000</v>
       </c>
       <c r="Y15" t="n">
-        <v>14.5</v>
+        <v>1000</v>
       </c>
       <c r="Z15" t="n">
-        <v>18</v>
+        <v>1000</v>
       </c>
       <c r="AA15" t="n">
-        <v>30</v>
+        <v>1000</v>
       </c>
       <c r="AB15" t="n">
-        <v>24</v>
+        <v>1000</v>
       </c>
       <c r="AC15" t="n">
-        <v>11</v>
+        <v>1000</v>
       </c>
       <c r="AD15" t="n">
-        <v>15</v>
+        <v>1000</v>
       </c>
       <c r="AE15" t="n">
-        <v>28</v>
+        <v>1000</v>
       </c>
       <c r="AF15" t="n">
-        <v>46</v>
+        <v>1000</v>
       </c>
       <c r="AG15" t="n">
-        <v>24</v>
+        <v>1000</v>
       </c>
       <c r="AH15" t="n">
-        <v>24</v>
+        <v>1000</v>
       </c>
       <c r="AI15" t="n">
-        <v>46</v>
+        <v>1000</v>
       </c>
       <c r="AJ15" t="n">
         <v>1000</v>
       </c>
       <c r="AK15" t="n">
-        <v>70</v>
+        <v>1000</v>
       </c>
       <c r="AL15" t="n">
-        <v>70</v>
+        <v>1000</v>
       </c>
       <c r="AM15" t="n">
         <v>1000</v>
       </c>
       <c r="AN15" t="n">
-        <v>65</v>
+        <v>1000</v>
       </c>
       <c r="AO15" t="n">
-        <v>16</v>
+        <v>1000</v>
       </c>
       <c r="AP15" t="n">
-        <v>2.66</v>
+        <v>1.01</v>
       </c>
       <c r="AQ15" t="n">
-        <v>7.4</v>
+        <v>1.01</v>
       </c>
       <c r="AR15" t="n">
-        <v>9.199999999999999</v>
+        <v>1.01</v>
       </c>
       <c r="AS15" t="n">
-        <v>16</v>
+        <v>1.01</v>
       </c>
       <c r="AT15" t="n">
-        <v>12</v>
+        <v>1.01</v>
       </c>
       <c r="AU15" t="n">
-        <v>6.4</v>
+        <v>1.01</v>
       </c>
       <c r="AV15" t="n">
-        <v>7.6</v>
+        <v>1.01</v>
       </c>
       <c r="AW15" t="n">
-        <v>14</v>
+        <v>1.01</v>
       </c>
       <c r="AX15" t="n">
-        <v>2.52</v>
+        <v>1.01</v>
       </c>
       <c r="AY15" t="n">
-        <v>12</v>
+        <v>1.01</v>
       </c>
       <c r="AZ15" t="n">
-        <v>12</v>
+        <v>1.01</v>
       </c>
       <c r="BA15" t="n">
-        <v>2.52</v>
+        <v>1.01</v>
       </c>
       <c r="BB15" t="n">
-        <v>2.68</v>
+        <v>1.01</v>
       </c>
       <c r="BC15" t="n">
-        <v>2.58</v>
+        <v>1.01</v>
       </c>
       <c r="BD15" t="n">
-        <v>2.58</v>
+        <v>1.01</v>
       </c>
       <c r="BE15" t="n">
-        <v>2.68</v>
+        <v>1.01</v>
       </c>
       <c r="BF15" t="n">
-        <v>2.56</v>
+        <v>1.01</v>
       </c>
       <c r="BG15" t="n">
-        <v>7.6</v>
+        <v>1.01</v>
       </c>
       <c r="BH15" t="n">
         <v>1000</v>
@@ -4382,14 +4382,14 @@
       </c>
       <c r="CB15" t="inlineStr">
         <is>
-          <t>2026-06-10 22:29:58</t>
+          <t>2026-06-11 00:39:13</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Irish Division 1</t>
+          <t>Irish Premier Division</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -4404,246 +4404,246 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>Kerry FC</t>
+          <t>St Patricks</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Athlone Town</t>
+          <t>Drogheda</t>
         </is>
       </c>
       <c r="F16" t="n">
-        <v>2.28</v>
+        <v>1.35</v>
       </c>
       <c r="G16" t="n">
-        <v>2.5</v>
+        <v>1.42</v>
       </c>
       <c r="H16" t="n">
-        <v>3.2</v>
+        <v>10.5</v>
       </c>
       <c r="I16" t="n">
-        <v>3.65</v>
+        <v>13</v>
       </c>
       <c r="J16" t="n">
-        <v>3.25</v>
+        <v>4.9</v>
       </c>
       <c r="K16" t="n">
-        <v>3.65</v>
+        <v>5.6</v>
       </c>
       <c r="L16" t="n">
-        <v>1.36</v>
+        <v>1.01</v>
       </c>
       <c r="M16" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="N16" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="O16" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="P16" t="n">
+        <v>2.06</v>
+      </c>
+      <c r="Q16" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="R16" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="S16" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="T16" t="n">
+        <v>2.18</v>
+      </c>
+      <c r="U16" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="V16" t="n">
         <v>1.08</v>
       </c>
-      <c r="N16" t="n">
+      <c r="W16" t="n">
         <v>3.35</v>
       </c>
-      <c r="O16" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="P16" t="n">
-        <v>1.81</v>
-      </c>
-      <c r="Q16" t="n">
-        <v>2.04</v>
-      </c>
-      <c r="R16" t="n">
-        <v>1.31</v>
-      </c>
-      <c r="S16" t="n">
-        <v>3.7</v>
-      </c>
-      <c r="T16" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="U16" t="n">
-        <v>2.06</v>
-      </c>
-      <c r="V16" t="n">
-        <v>1.38</v>
-      </c>
-      <c r="W16" t="n">
-        <v>1.67</v>
-      </c>
       <c r="X16" t="n">
-        <v>15.5</v>
+        <v>21</v>
       </c>
       <c r="Y16" t="n">
-        <v>15</v>
+        <v>38</v>
       </c>
       <c r="Z16" t="n">
-        <v>29</v>
+        <v>130</v>
       </c>
       <c r="AA16" t="n">
-        <v>65</v>
+        <v>630</v>
       </c>
       <c r="AB16" t="n">
-        <v>9.800000000000001</v>
+        <v>9</v>
       </c>
       <c r="AC16" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="AD16" t="n">
+        <v>55</v>
+      </c>
+      <c r="AE16" t="n">
+        <v>280</v>
+      </c>
+      <c r="AF16" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="AG16" t="n">
+        <v>13</v>
+      </c>
+      <c r="AH16" t="n">
+        <v>40</v>
+      </c>
+      <c r="AI16" t="n">
+        <v>220</v>
+      </c>
+      <c r="AJ16" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="AK16" t="n">
+        <v>20</v>
+      </c>
+      <c r="AL16" t="n">
+        <v>60</v>
+      </c>
+      <c r="AM16" t="n">
+        <v>270</v>
+      </c>
+      <c r="AN16" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="AO16" t="n">
+        <v>460</v>
+      </c>
+      <c r="AP16" t="n">
+        <v>12</v>
+      </c>
+      <c r="AQ16" t="n">
+        <v>3.85</v>
+      </c>
+      <c r="AR16" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="AS16" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="AT16" t="n">
+        <v>5.6</v>
+      </c>
+      <c r="AU16" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="AV16" t="n">
+        <v>4</v>
+      </c>
+      <c r="AW16" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="AX16" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="AY16" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="AZ16" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="BA16" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="BB16" t="n">
         <v>8</v>
       </c>
-      <c r="AD16" t="n">
-        <v>17.5</v>
-      </c>
-      <c r="AE16" t="n">
-        <v>55</v>
-      </c>
-      <c r="AF16" t="n">
-        <v>18.5</v>
-      </c>
-      <c r="AG16" t="n">
-        <v>14</v>
-      </c>
-      <c r="AH16" t="n">
-        <v>22</v>
-      </c>
-      <c r="AI16" t="n">
-        <v>65</v>
-      </c>
-      <c r="AJ16" t="n">
-        <v>40</v>
-      </c>
-      <c r="AK16" t="n">
-        <v>34</v>
-      </c>
-      <c r="AL16" t="n">
-        <v>55</v>
-      </c>
-      <c r="AM16" t="n">
-        <v>130</v>
-      </c>
-      <c r="AN16" t="n">
-        <v>27</v>
-      </c>
-      <c r="AO16" t="n">
-        <v>55</v>
-      </c>
-      <c r="AP16" t="n">
-        <v>9.4</v>
-      </c>
-      <c r="AQ16" t="n">
-        <v>9</v>
-      </c>
-      <c r="AR16" t="n">
-        <v>17</v>
-      </c>
-      <c r="AS16" t="n">
-        <v>4.8</v>
-      </c>
-      <c r="AT16" t="n">
-        <v>7.2</v>
-      </c>
-      <c r="AU16" t="n">
+      <c r="BC16" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="BD16" t="n">
+        <v>4</v>
+      </c>
+      <c r="BE16" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="BF16" t="n">
         <v>5.8</v>
       </c>
-      <c r="AV16" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="AW16" t="n">
-        <v>4.7</v>
-      </c>
-      <c r="AX16" t="n">
-        <v>11</v>
-      </c>
-      <c r="AY16" t="n">
-        <v>8.4</v>
-      </c>
-      <c r="AZ16" t="n">
-        <v>13</v>
-      </c>
-      <c r="BA16" t="n">
-        <v>4.7</v>
-      </c>
-      <c r="BB16" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="BC16" t="n">
-        <v>19.5</v>
-      </c>
-      <c r="BD16" t="n">
-        <v>4.7</v>
-      </c>
-      <c r="BE16" t="n">
-        <v>5</v>
-      </c>
-      <c r="BF16" t="n">
-        <v>16</v>
-      </c>
       <c r="BG16" t="n">
-        <v>4.7</v>
+        <v>4.2</v>
       </c>
       <c r="BH16" t="n">
-        <v>3.3</v>
+        <v>1000</v>
       </c>
       <c r="BI16" t="n">
-        <v>2.66</v>
+        <v>1.04</v>
       </c>
       <c r="BJ16" t="n">
-        <v>9.800000000000001</v>
+        <v>1000</v>
       </c>
       <c r="BK16" t="n">
-        <v>5.7</v>
+        <v>1.58</v>
       </c>
       <c r="BL16" t="n">
         <v>1000</v>
       </c>
       <c r="BM16" t="n">
-        <v>12.5</v>
+        <v>1.72</v>
       </c>
       <c r="BN16" t="n">
-        <v>5.3</v>
+        <v>1000</v>
       </c>
       <c r="BO16" t="n">
-        <v>4</v>
+        <v>1.3</v>
       </c>
       <c r="BP16" t="n">
-        <v>18.5</v>
+        <v>1000</v>
       </c>
       <c r="BQ16" t="n">
-        <v>8</v>
+        <v>1.5</v>
       </c>
       <c r="BR16" t="n">
         <v>1000</v>
       </c>
       <c r="BS16" t="n">
-        <v>9.800000000000001</v>
+        <v>1.65</v>
       </c>
       <c r="BT16" t="n">
-        <v>6.6</v>
+        <v>1000</v>
       </c>
       <c r="BU16" t="n">
-        <v>4.9</v>
+        <v>1.59</v>
       </c>
       <c r="BV16" t="n">
         <v>1000</v>
       </c>
       <c r="BW16" t="n">
-        <v>9.199999999999999</v>
+        <v>1.72</v>
       </c>
       <c r="BX16" t="n">
         <v>1000</v>
       </c>
       <c r="BY16" t="n">
-        <v>10.5</v>
+        <v>1.72</v>
       </c>
       <c r="BZ16" t="n">
         <v>1000</v>
       </c>
       <c r="CA16" t="n">
-        <v>9.6</v>
+        <v>1.6</v>
       </c>
       <c r="CB16" t="inlineStr">
         <is>
-          <t>2026-06-10 22:29:58</t>
+          <t>2026-06-11 00:39:13</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Irish Division 1</t>
+          <t>Irish Premier Division</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -4658,246 +4658,246 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>Treaty United</t>
+          <t>Waterford</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Bray Wanderers</t>
+          <t>Sligo Rovers</t>
         </is>
       </c>
       <c r="F17" t="n">
-        <v>3.85</v>
+        <v>2.26</v>
       </c>
       <c r="G17" t="n">
-        <v>4.6</v>
+        <v>2.44</v>
       </c>
       <c r="H17" t="n">
-        <v>1.84</v>
+        <v>3.2</v>
       </c>
       <c r="I17" t="n">
-        <v>2.04</v>
+        <v>3.5</v>
       </c>
       <c r="J17" t="n">
-        <v>3.85</v>
+        <v>3.5</v>
       </c>
       <c r="K17" t="n">
-        <v>4.5</v>
+        <v>3.9</v>
       </c>
       <c r="L17" t="n">
-        <v>1.24</v>
+        <v>1.12</v>
       </c>
       <c r="M17" t="n">
-        <v>1.03</v>
+        <v>1.06</v>
       </c>
       <c r="N17" t="n">
-        <v>5</v>
+        <v>3.95</v>
       </c>
       <c r="O17" t="n">
-        <v>1.2</v>
+        <v>1.28</v>
       </c>
       <c r="P17" t="n">
-        <v>2.42</v>
+        <v>2.02</v>
       </c>
       <c r="Q17" t="n">
-        <v>1.6</v>
+        <v>1.83</v>
       </c>
       <c r="R17" t="n">
-        <v>1.59</v>
+        <v>1.39</v>
       </c>
       <c r="S17" t="n">
-        <v>2.3</v>
+        <v>3.1</v>
       </c>
       <c r="T17" t="n">
-        <v>1.56</v>
+        <v>1.69</v>
       </c>
       <c r="U17" t="n">
-        <v>2.44</v>
+        <v>2.22</v>
       </c>
       <c r="V17" t="n">
-        <v>1.96</v>
+        <v>1.4</v>
       </c>
       <c r="W17" t="n">
-        <v>1.28</v>
+        <v>1.69</v>
       </c>
       <c r="X17" t="n">
-        <v>29</v>
+        <v>17</v>
       </c>
       <c r="Y17" t="n">
         <v>15</v>
       </c>
       <c r="Z17" t="n">
-        <v>17.5</v>
+        <v>25</v>
       </c>
       <c r="AA17" t="n">
-        <v>30</v>
+        <v>85</v>
       </c>
       <c r="AB17" t="n">
-        <v>22</v>
+        <v>12</v>
       </c>
       <c r="AC17" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="AD17" t="n">
+        <v>15</v>
+      </c>
+      <c r="AE17" t="n">
+        <v>50</v>
+      </c>
+      <c r="AF17" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="AG17" t="n">
         <v>12</v>
-      </c>
-      <c r="AD17" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="AE17" t="n">
-        <v>17.5</v>
-      </c>
-      <c r="AF17" t="n">
-        <v>38</v>
-      </c>
-      <c r="AG17" t="n">
-        <v>23</v>
       </c>
       <c r="AH17" t="n">
         <v>17.5</v>
       </c>
       <c r="AI17" t="n">
-        <v>32</v>
+        <v>60</v>
       </c>
       <c r="AJ17" t="n">
-        <v>110</v>
+        <v>34</v>
       </c>
       <c r="AK17" t="n">
-        <v>42</v>
+        <v>26</v>
       </c>
       <c r="AL17" t="n">
         <v>50</v>
       </c>
       <c r="AM17" t="n">
-        <v>70</v>
+        <v>100</v>
       </c>
       <c r="AN17" t="n">
-        <v>34</v>
+        <v>18</v>
       </c>
       <c r="AO17" t="n">
-        <v>10.5</v>
+        <v>44</v>
       </c>
       <c r="AP17" t="n">
-        <v>17</v>
+        <v>11.5</v>
       </c>
       <c r="AQ17" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="AR17" t="n">
+        <v>20</v>
+      </c>
+      <c r="AS17" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="AT17" t="n">
         <v>9.4</v>
       </c>
-      <c r="AR17" t="n">
-        <v>11</v>
-      </c>
-      <c r="AS17" t="n">
-        <v>18</v>
-      </c>
-      <c r="AT17" t="n">
-        <v>15</v>
-      </c>
       <c r="AU17" t="n">
-        <v>8.800000000000001</v>
+        <v>7.2</v>
       </c>
       <c r="AV17" t="n">
-        <v>9.800000000000001</v>
+        <v>12</v>
       </c>
       <c r="AW17" t="n">
-        <v>12</v>
+        <v>24</v>
       </c>
       <c r="AX17" t="n">
-        <v>4.7</v>
+        <v>13.5</v>
       </c>
       <c r="AY17" t="n">
-        <v>13.5</v>
+        <v>9.6</v>
       </c>
       <c r="AZ17" t="n">
-        <v>10.5</v>
+        <v>14</v>
       </c>
       <c r="BA17" t="n">
-        <v>18.5</v>
+        <v>30</v>
       </c>
       <c r="BB17" t="n">
-        <v>5.1</v>
+        <v>23</v>
       </c>
       <c r="BC17" t="n">
-        <v>4.7</v>
+        <v>20</v>
       </c>
       <c r="BD17" t="n">
-        <v>4.8</v>
+        <v>25</v>
       </c>
       <c r="BE17" t="n">
-        <v>4.9</v>
+        <v>7.8</v>
       </c>
       <c r="BF17" t="n">
-        <v>23</v>
+        <v>14.5</v>
       </c>
       <c r="BG17" t="n">
-        <v>7.2</v>
+        <v>19</v>
       </c>
       <c r="BH17" t="n">
         <v>1000</v>
       </c>
       <c r="BI17" t="n">
-        <v>1.9</v>
+        <v>1.04</v>
       </c>
       <c r="BJ17" t="n">
-        <v>13.5</v>
+        <v>1000</v>
       </c>
       <c r="BK17" t="n">
-        <v>1.67</v>
+        <v>1.5</v>
       </c>
       <c r="BL17" t="n">
         <v>1000</v>
       </c>
       <c r="BM17" t="n">
-        <v>1.9</v>
+        <v>1.69</v>
       </c>
       <c r="BN17" t="n">
-        <v>11.5</v>
+        <v>1000</v>
       </c>
       <c r="BO17" t="n">
-        <v>4.9</v>
+        <v>1.39</v>
       </c>
       <c r="BP17" t="n">
-        <v>44</v>
+        <v>1000</v>
       </c>
       <c r="BQ17" t="n">
-        <v>1.83</v>
+        <v>1.58</v>
       </c>
       <c r="BR17" t="n">
         <v>1000</v>
       </c>
       <c r="BS17" t="n">
-        <v>1.84</v>
+        <v>1.04</v>
       </c>
       <c r="BT17" t="n">
-        <v>6.8</v>
+        <v>1000</v>
       </c>
       <c r="BU17" t="n">
-        <v>3.3</v>
+        <v>1.44</v>
       </c>
       <c r="BV17" t="n">
-        <v>18</v>
+        <v>1000</v>
       </c>
       <c r="BW17" t="n">
-        <v>1.72</v>
+        <v>1.62</v>
       </c>
       <c r="BX17" t="n">
-        <v>38</v>
+        <v>1000</v>
       </c>
       <c r="BY17" t="n">
-        <v>1.81</v>
+        <v>1.04</v>
       </c>
       <c r="BZ17" t="n">
-        <v>23</v>
+        <v>1000</v>
       </c>
       <c r="CA17" t="n">
-        <v>1.76</v>
+        <v>1.61</v>
       </c>
       <c r="CB17" t="inlineStr">
         <is>
-          <t>2026-06-10 22:29:58</t>
+          <t>2026-06-11 00:39:13</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Irish Division 1</t>
+          <t>Irish Premier Division</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -4912,246 +4912,246 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>Wexford F.C</t>
+          <t>Derry City</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Cork City</t>
+          <t>Bohemians</t>
         </is>
       </c>
       <c r="F18" t="n">
-        <v>4.3</v>
+        <v>3.1</v>
       </c>
       <c r="G18" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="H18" t="n">
+        <v>2.42</v>
+      </c>
+      <c r="I18" t="n">
+        <v>2.64</v>
+      </c>
+      <c r="J18" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="K18" t="n">
+        <v>3.55</v>
+      </c>
+      <c r="L18" t="n">
+        <v>1.46</v>
+      </c>
+      <c r="M18" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="N18" t="n">
+        <v>3</v>
+      </c>
+      <c r="O18" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="P18" t="n">
+        <v>1.71</v>
+      </c>
+      <c r="Q18" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="R18" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="S18" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="T18" t="n">
+        <v>1.87</v>
+      </c>
+      <c r="U18" t="n">
+        <v>1.96</v>
+      </c>
+      <c r="V18" t="n">
+        <v>1.61</v>
+      </c>
+      <c r="W18" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="X18" t="n">
+        <v>12</v>
+      </c>
+      <c r="Y18" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="Z18" t="n">
+        <v>18</v>
+      </c>
+      <c r="AA18" t="n">
+        <v>44</v>
+      </c>
+      <c r="AB18" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="AC18" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="AD18" t="n">
+        <v>14</v>
+      </c>
+      <c r="AE18" t="n">
+        <v>36</v>
+      </c>
+      <c r="AF18" t="n">
+        <v>23</v>
+      </c>
+      <c r="AG18" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="AH18" t="n">
+        <v>21</v>
+      </c>
+      <c r="AI18" t="n">
+        <v>60</v>
+      </c>
+      <c r="AJ18" t="n">
+        <v>70</v>
+      </c>
+      <c r="AK18" t="n">
+        <v>50</v>
+      </c>
+      <c r="AL18" t="n">
+        <v>70</v>
+      </c>
+      <c r="AM18" t="n">
+        <v>150</v>
+      </c>
+      <c r="AN18" t="n">
+        <v>55</v>
+      </c>
+      <c r="AO18" t="n">
+        <v>34</v>
+      </c>
+      <c r="AP18" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="AQ18" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="AR18" t="n">
+        <v>13</v>
+      </c>
+      <c r="AS18" t="n">
+        <v>28</v>
+      </c>
+      <c r="AT18" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="AU18" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="AV18" t="n">
+        <v>10</v>
+      </c>
+      <c r="AW18" t="n">
+        <v>24</v>
+      </c>
+      <c r="AX18" t="n">
+        <v>18.5</v>
+      </c>
+      <c r="AY18" t="n">
+        <v>12</v>
+      </c>
+      <c r="AZ18" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="BA18" t="n">
+        <v>38</v>
+      </c>
+      <c r="BB18" t="n">
+        <v>5.6</v>
+      </c>
+      <c r="BC18" t="n">
+        <v>34</v>
+      </c>
+      <c r="BD18" t="n">
+        <v>5.6</v>
+      </c>
+      <c r="BE18" t="n">
+        <v>5.9</v>
+      </c>
+      <c r="BF18" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="BG18" t="n">
+        <v>21</v>
+      </c>
+      <c r="BH18" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="BI18" t="n">
+        <v>2.74</v>
+      </c>
+      <c r="BJ18" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="BK18" t="n">
         <v>5.2</v>
       </c>
-      <c r="H18" t="n">
-        <v>1.84</v>
-      </c>
-      <c r="I18" t="n">
-        <v>2</v>
-      </c>
-      <c r="J18" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="K18" t="n">
+      <c r="BL18" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BM18" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="BN18" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="BO18" t="n">
+        <v>5</v>
+      </c>
+      <c r="BP18" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BQ18" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="BR18" t="n">
+        <v>46</v>
+      </c>
+      <c r="BS18" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="BT18" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="BU18" t="n">
         <v>4.2</v>
       </c>
-      <c r="L18" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="M18" t="n">
-        <v>1.07</v>
-      </c>
-      <c r="N18" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="O18" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="P18" t="n">
-        <v>1.9</v>
-      </c>
-      <c r="Q18" t="n">
-        <v>1.9</v>
-      </c>
-      <c r="R18" t="n">
-        <v>1.34</v>
-      </c>
-      <c r="S18" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="T18" t="n">
-        <v>1.79</v>
-      </c>
-      <c r="U18" t="n">
-        <v>2</v>
-      </c>
-      <c r="V18" t="n">
-        <v>2</v>
-      </c>
-      <c r="W18" t="n">
-        <v>1.24</v>
-      </c>
-      <c r="X18" t="n">
-        <v>17</v>
-      </c>
-      <c r="Y18" t="n">
-        <v>9.4</v>
-      </c>
-      <c r="Z18" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="AA18" t="n">
-        <v>23</v>
-      </c>
-      <c r="AB18" t="n">
-        <v>17</v>
-      </c>
-      <c r="AC18" t="n">
-        <v>9</v>
-      </c>
-      <c r="AD18" t="n">
-        <v>11</v>
-      </c>
-      <c r="AE18" t="n">
-        <v>22</v>
-      </c>
-      <c r="AF18" t="n">
+      <c r="BV18" t="n">
+        <v>21</v>
+      </c>
+      <c r="BW18" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="BX18" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BY18" t="n">
+        <v>8</v>
+      </c>
+      <c r="BZ18" t="n">
         <v>38</v>
       </c>
-      <c r="AG18" t="n">
-        <v>19.5</v>
-      </c>
-      <c r="AH18" t="n">
-        <v>20</v>
-      </c>
-      <c r="AI18" t="n">
-        <v>38</v>
-      </c>
-      <c r="AJ18" t="n">
-        <v>130</v>
-      </c>
-      <c r="AK18" t="n">
-        <v>75</v>
-      </c>
-      <c r="AL18" t="n">
-        <v>75</v>
-      </c>
-      <c r="AM18" t="n">
-        <v>130</v>
-      </c>
-      <c r="AN18" t="n">
-        <v>75</v>
-      </c>
-      <c r="AO18" t="n">
-        <v>14</v>
-      </c>
-      <c r="AP18" t="n">
-        <v>11</v>
-      </c>
-      <c r="AQ18" t="n">
-        <v>7.6</v>
-      </c>
-      <c r="AR18" t="n">
-        <v>10</v>
-      </c>
-      <c r="AS18" t="n">
-        <v>18</v>
-      </c>
-      <c r="AT18" t="n">
-        <v>13.5</v>
-      </c>
-      <c r="AU18" t="n">
-        <v>7.2</v>
-      </c>
-      <c r="AV18" t="n">
-        <v>8.800000000000001</v>
-      </c>
-      <c r="AW18" t="n">
-        <v>17</v>
-      </c>
-      <c r="AX18" t="n">
-        <v>24</v>
-      </c>
-      <c r="AY18" t="n">
-        <v>15.5</v>
-      </c>
-      <c r="AZ18" t="n">
-        <v>16</v>
-      </c>
-      <c r="BA18" t="n">
-        <v>25</v>
-      </c>
-      <c r="BB18" t="n">
-        <v>7.6</v>
-      </c>
-      <c r="BC18" t="n">
-        <v>7.2</v>
-      </c>
-      <c r="BD18" t="n">
-        <v>7.2</v>
-      </c>
-      <c r="BE18" t="n">
-        <v>7.6</v>
-      </c>
-      <c r="BF18" t="n">
-        <v>7.2</v>
-      </c>
-      <c r="BG18" t="n">
-        <v>11</v>
-      </c>
-      <c r="BH18" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="BI18" t="n">
-        <v>2.76</v>
-      </c>
-      <c r="BJ18" t="n">
-        <v>13.5</v>
-      </c>
-      <c r="BK18" t="n">
-        <v>2.84</v>
-      </c>
-      <c r="BL18" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BM18" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="BN18" t="n">
-        <v>11</v>
-      </c>
-      <c r="BO18" t="n">
-        <v>2.7</v>
-      </c>
-      <c r="BP18" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BQ18" t="n">
-        <v>3.35</v>
-      </c>
-      <c r="BR18" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BS18" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="BT18" t="n">
-        <v>6</v>
-      </c>
-      <c r="BU18" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="BV18" t="n">
-        <v>18</v>
-      </c>
-      <c r="BW18" t="n">
-        <v>3</v>
-      </c>
-      <c r="BX18" t="n">
-        <v>38</v>
-      </c>
-      <c r="BY18" t="n">
-        <v>3.25</v>
-      </c>
-      <c r="BZ18" t="n">
-        <v>32</v>
-      </c>
       <c r="CA18" t="n">
-        <v>3.2</v>
+        <v>8</v>
       </c>
       <c r="CB18" t="inlineStr">
         <is>
-          <t>2026-06-10 22:29:58</t>
+          <t>2026-06-11 00:39:13</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Irish Premier Division</t>
+          <t>Irish Division 1</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -5166,246 +5166,246 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>Derry City</t>
+          <t>Finn Harps</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Bohemians</t>
+          <t>UCD</t>
         </is>
       </c>
       <c r="F19" t="n">
-        <v>3.1</v>
+        <v>3.7</v>
       </c>
       <c r="G19" t="n">
-        <v>3.5</v>
+        <v>5.4</v>
       </c>
       <c r="H19" t="n">
-        <v>2.44</v>
+        <v>1.75</v>
       </c>
       <c r="I19" t="n">
-        <v>2.64</v>
+        <v>2.18</v>
       </c>
       <c r="J19" t="n">
         <v>3.25</v>
       </c>
       <c r="K19" t="n">
-        <v>3.55</v>
+        <v>6.4</v>
       </c>
       <c r="L19" t="n">
         <v>1.01</v>
       </c>
       <c r="M19" t="n">
-        <v>1.09</v>
+        <v>1.03</v>
       </c>
       <c r="N19" t="n">
-        <v>3.1</v>
+        <v>4.1</v>
       </c>
       <c r="O19" t="n">
-        <v>1.41</v>
+        <v>1.23</v>
       </c>
       <c r="P19" t="n">
-        <v>1.71</v>
+        <v>1.94</v>
       </c>
       <c r="Q19" t="n">
-        <v>2.2</v>
+        <v>1.61</v>
       </c>
       <c r="R19" t="n">
-        <v>1.26</v>
+        <v>1.31</v>
       </c>
       <c r="S19" t="n">
-        <v>4.3</v>
+        <v>2.3</v>
       </c>
       <c r="T19" t="n">
-        <v>1.88</v>
+        <v>1.37</v>
       </c>
       <c r="U19" t="n">
-        <v>1.96</v>
+        <v>1.73</v>
       </c>
       <c r="V19" t="n">
-        <v>1.61</v>
+        <v>1.85</v>
       </c>
       <c r="W19" t="n">
-        <v>1.4</v>
+        <v>1.22</v>
       </c>
       <c r="X19" t="n">
-        <v>12</v>
+        <v>1000</v>
       </c>
       <c r="Y19" t="n">
-        <v>9.6</v>
+        <v>1000</v>
       </c>
       <c r="Z19" t="n">
-        <v>16.5</v>
+        <v>1000</v>
       </c>
       <c r="AA19" t="n">
-        <v>50</v>
+        <v>1000</v>
       </c>
       <c r="AB19" t="n">
-        <v>11.5</v>
+        <v>1000</v>
       </c>
       <c r="AC19" t="n">
-        <v>7.8</v>
+        <v>1000</v>
       </c>
       <c r="AD19" t="n">
-        <v>12.5</v>
+        <v>1000</v>
       </c>
       <c r="AE19" t="n">
-        <v>34</v>
+        <v>1000</v>
       </c>
       <c r="AF19" t="n">
-        <v>23</v>
+        <v>1000</v>
       </c>
       <c r="AG19" t="n">
-        <v>15</v>
+        <v>1000</v>
       </c>
       <c r="AH19" t="n">
-        <v>21</v>
+        <v>1000</v>
       </c>
       <c r="AI19" t="n">
-        <v>70</v>
+        <v>1000</v>
       </c>
       <c r="AJ19" t="n">
-        <v>80</v>
+        <v>1000</v>
       </c>
       <c r="AK19" t="n">
-        <v>55</v>
+        <v>1000</v>
       </c>
       <c r="AL19" t="n">
-        <v>80</v>
+        <v>1000</v>
       </c>
       <c r="AM19" t="n">
-        <v>150</v>
+        <v>1000</v>
       </c>
       <c r="AN19" t="n">
-        <v>70</v>
+        <v>1000</v>
       </c>
       <c r="AO19" t="n">
-        <v>38</v>
+        <v>1000</v>
       </c>
       <c r="AP19" t="n">
-        <v>9.6</v>
+        <v>1.01</v>
       </c>
       <c r="AQ19" t="n">
-        <v>7.8</v>
+        <v>1.01</v>
       </c>
       <c r="AR19" t="n">
-        <v>12</v>
+        <v>1.01</v>
       </c>
       <c r="AS19" t="n">
-        <v>30</v>
+        <v>1.01</v>
       </c>
       <c r="AT19" t="n">
-        <v>9.4</v>
+        <v>1.01</v>
       </c>
       <c r="AU19" t="n">
-        <v>6.6</v>
+        <v>1.01</v>
       </c>
       <c r="AV19" t="n">
-        <v>10</v>
+        <v>1.01</v>
       </c>
       <c r="AW19" t="n">
-        <v>24</v>
+        <v>1.01</v>
       </c>
       <c r="AX19" t="n">
-        <v>18.5</v>
+        <v>1.01</v>
       </c>
       <c r="AY19" t="n">
-        <v>12</v>
+        <v>1.01</v>
       </c>
       <c r="AZ19" t="n">
-        <v>16</v>
+        <v>1.01</v>
       </c>
       <c r="BA19" t="n">
-        <v>32</v>
+        <v>1.01</v>
       </c>
       <c r="BB19" t="n">
-        <v>40</v>
+        <v>1.01</v>
       </c>
       <c r="BC19" t="n">
-        <v>29</v>
+        <v>1.01</v>
       </c>
       <c r="BD19" t="n">
-        <v>38</v>
+        <v>1.01</v>
       </c>
       <c r="BE19" t="n">
-        <v>8.199999999999999</v>
+        <v>1.01</v>
       </c>
       <c r="BF19" t="n">
-        <v>7.4</v>
+        <v>1.01</v>
       </c>
       <c r="BG19" t="n">
-        <v>6.8</v>
+        <v>1.01</v>
       </c>
       <c r="BH19" t="n">
         <v>1000</v>
       </c>
       <c r="BI19" t="n">
-        <v>1.83</v>
+        <v>1.04</v>
       </c>
       <c r="BJ19" t="n">
-        <v>13.5</v>
+        <v>1000</v>
       </c>
       <c r="BK19" t="n">
-        <v>1.61</v>
+        <v>1.04</v>
       </c>
       <c r="BL19" t="n">
         <v>1000</v>
       </c>
       <c r="BM19" t="n">
-        <v>1.83</v>
+        <v>1.04</v>
       </c>
       <c r="BN19" t="n">
-        <v>8.6</v>
+        <v>1000</v>
       </c>
       <c r="BO19" t="n">
-        <v>4.6</v>
+        <v>1.04</v>
       </c>
       <c r="BP19" t="n">
-        <v>38</v>
+        <v>1000</v>
       </c>
       <c r="BQ19" t="n">
-        <v>1.74</v>
+        <v>1.04</v>
       </c>
       <c r="BR19" t="n">
         <v>1000</v>
       </c>
       <c r="BS19" t="n">
-        <v>1.77</v>
+        <v>1.04</v>
       </c>
       <c r="BT19" t="n">
-        <v>7</v>
+        <v>1000</v>
       </c>
       <c r="BU19" t="n">
-        <v>3.85</v>
+        <v>1.04</v>
       </c>
       <c r="BV19" t="n">
-        <v>28</v>
+        <v>1000</v>
       </c>
       <c r="BW19" t="n">
-        <v>1.72</v>
+        <v>1.04</v>
       </c>
       <c r="BX19" t="n">
-        <v>50</v>
+        <v>1000</v>
       </c>
       <c r="BY19" t="n">
-        <v>1.76</v>
+        <v>1.04</v>
       </c>
       <c r="BZ19" t="n">
-        <v>48</v>
+        <v>1000</v>
       </c>
       <c r="CA19" t="n">
-        <v>1.76</v>
+        <v>1.04</v>
       </c>
       <c r="CB19" t="inlineStr">
         <is>
-          <t>2026-06-10 22:29:58</t>
+          <t>2026-06-11 00:39:13</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Irish Premier Division</t>
+          <t>Irish Division 1</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -5420,172 +5420,172 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>Waterford</t>
+          <t>Treaty United</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Sligo Rovers</t>
+          <t>Bray Wanderers</t>
         </is>
       </c>
       <c r="F20" t="n">
-        <v>2.26</v>
+        <v>3.85</v>
       </c>
       <c r="G20" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="H20" t="n">
+        <v>1.86</v>
+      </c>
+      <c r="I20" t="n">
+        <v>2.04</v>
+      </c>
+      <c r="J20" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="K20" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="L20" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="M20" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="N20" t="n">
+        <v>5</v>
+      </c>
+      <c r="O20" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="P20" t="n">
         <v>2.42</v>
       </c>
-      <c r="H20" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="I20" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="J20" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="K20" t="n">
-        <v>3.9</v>
-      </c>
-      <c r="L20" t="n">
-        <v>1.34</v>
-      </c>
-      <c r="M20" t="n">
-        <v>1.06</v>
-      </c>
-      <c r="N20" t="n">
-        <v>3.95</v>
-      </c>
-      <c r="O20" t="n">
-        <v>1.28</v>
-      </c>
-      <c r="P20" t="n">
-        <v>2.02</v>
-      </c>
       <c r="Q20" t="n">
-        <v>1.83</v>
+        <v>1.6</v>
       </c>
       <c r="R20" t="n">
-        <v>1.39</v>
+        <v>1.59</v>
       </c>
       <c r="S20" t="n">
-        <v>3.1</v>
+        <v>2.3</v>
       </c>
       <c r="T20" t="n">
-        <v>1.69</v>
+        <v>1.56</v>
       </c>
       <c r="U20" t="n">
-        <v>2.22</v>
+        <v>2.44</v>
       </c>
       <c r="V20" t="n">
-        <v>1.4</v>
+        <v>1.96</v>
       </c>
       <c r="W20" t="n">
-        <v>1.7</v>
+        <v>1.29</v>
       </c>
       <c r="X20" t="n">
-        <v>17</v>
+        <v>28</v>
       </c>
       <c r="Y20" t="n">
         <v>15</v>
       </c>
       <c r="Z20" t="n">
-        <v>25</v>
+        <v>17.5</v>
       </c>
       <c r="AA20" t="n">
-        <v>85</v>
+        <v>30</v>
       </c>
       <c r="AB20" t="n">
-        <v>11.5</v>
+        <v>22</v>
       </c>
       <c r="AC20" t="n">
-        <v>8.800000000000001</v>
+        <v>11</v>
       </c>
       <c r="AD20" t="n">
-        <v>15</v>
+        <v>12.5</v>
       </c>
       <c r="AE20" t="n">
-        <v>55</v>
+        <v>17.5</v>
       </c>
       <c r="AF20" t="n">
-        <v>16.5</v>
+        <v>38</v>
       </c>
       <c r="AG20" t="n">
-        <v>12</v>
+        <v>23</v>
       </c>
       <c r="AH20" t="n">
         <v>17.5</v>
       </c>
       <c r="AI20" t="n">
-        <v>65</v>
+        <v>32</v>
       </c>
       <c r="AJ20" t="n">
-        <v>46</v>
+        <v>110</v>
       </c>
       <c r="AK20" t="n">
-        <v>25</v>
+        <v>42</v>
       </c>
       <c r="AL20" t="n">
         <v>50</v>
       </c>
       <c r="AM20" t="n">
-        <v>100</v>
+        <v>70</v>
       </c>
       <c r="AN20" t="n">
-        <v>17.5</v>
+        <v>34</v>
       </c>
       <c r="AO20" t="n">
-        <v>48</v>
+        <v>10.5</v>
       </c>
       <c r="AP20" t="n">
+        <v>17</v>
+      </c>
+      <c r="AQ20" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="AR20" t="n">
+        <v>11</v>
+      </c>
+      <c r="AS20" t="n">
+        <v>18</v>
+      </c>
+      <c r="AT20" t="n">
+        <v>15</v>
+      </c>
+      <c r="AU20" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="AV20" t="n">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="AW20" t="n">
+        <v>12</v>
+      </c>
+      <c r="AX20" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="AY20" t="n">
         <v>13.5</v>
       </c>
-      <c r="AQ20" t="n">
-        <v>12</v>
-      </c>
-      <c r="AR20" t="n">
-        <v>20</v>
-      </c>
-      <c r="AS20" t="n">
-        <v>8</v>
-      </c>
-      <c r="AT20" t="n">
-        <v>9.4</v>
-      </c>
-      <c r="AU20" t="n">
-        <v>7.2</v>
-      </c>
-      <c r="AV20" t="n">
-        <v>12</v>
-      </c>
-      <c r="AW20" t="n">
-        <v>30</v>
-      </c>
-      <c r="AX20" t="n">
-        <v>13</v>
-      </c>
-      <c r="AY20" t="n">
-        <v>9.6</v>
-      </c>
       <c r="AZ20" t="n">
-        <v>14</v>
+        <v>10.5</v>
       </c>
       <c r="BA20" t="n">
-        <v>36</v>
+        <v>18.5</v>
       </c>
       <c r="BB20" t="n">
-        <v>7.2</v>
+        <v>5.3</v>
       </c>
       <c r="BC20" t="n">
-        <v>20</v>
+        <v>4.9</v>
       </c>
       <c r="BD20" t="n">
-        <v>7.4</v>
+        <v>5</v>
       </c>
       <c r="BE20" t="n">
-        <v>8.4</v>
+        <v>5.1</v>
       </c>
       <c r="BF20" t="n">
-        <v>12</v>
+        <v>23</v>
       </c>
       <c r="BG20" t="n">
         <v>7.2</v>
@@ -5594,72 +5594,72 @@
         <v>1000</v>
       </c>
       <c r="BI20" t="n">
-        <v>1.84</v>
+        <v>1.89</v>
       </c>
       <c r="BJ20" t="n">
-        <v>13</v>
+        <v>13.5</v>
       </c>
       <c r="BK20" t="n">
-        <v>1.61</v>
+        <v>1.66</v>
       </c>
       <c r="BL20" t="n">
         <v>1000</v>
       </c>
       <c r="BM20" t="n">
-        <v>1.84</v>
+        <v>1.89</v>
       </c>
       <c r="BN20" t="n">
-        <v>7.6</v>
+        <v>11</v>
       </c>
       <c r="BO20" t="n">
-        <v>3.45</v>
+        <v>4.9</v>
       </c>
       <c r="BP20" t="n">
-        <v>23</v>
+        <v>44</v>
       </c>
       <c r="BQ20" t="n">
-        <v>1.71</v>
+        <v>1.82</v>
       </c>
       <c r="BR20" t="n">
-        <v>40</v>
+        <v>1000</v>
       </c>
       <c r="BS20" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="BT20" t="n">
+        <v>7</v>
+      </c>
+      <c r="BU20" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="BV20" t="n">
+        <v>18</v>
+      </c>
+      <c r="BW20" t="n">
+        <v>1.72</v>
+      </c>
+      <c r="BX20" t="n">
+        <v>38</v>
+      </c>
+      <c r="BY20" t="n">
+        <v>1.81</v>
+      </c>
+      <c r="BZ20" t="n">
+        <v>24</v>
+      </c>
+      <c r="CA20" t="n">
         <v>1.76</v>
       </c>
-      <c r="BT20" t="n">
-        <v>9.6</v>
-      </c>
-      <c r="BU20" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="BV20" t="n">
-        <v>38</v>
-      </c>
-      <c r="BW20" t="n">
-        <v>1.76</v>
-      </c>
-      <c r="BX20" t="n">
-        <v>50</v>
-      </c>
-      <c r="BY20" t="n">
-        <v>1.78</v>
-      </c>
-      <c r="BZ20" t="n">
-        <v>34</v>
-      </c>
-      <c r="CA20" t="n">
-        <v>1.75</v>
-      </c>
       <c r="CB20" t="inlineStr">
         <is>
-          <t>2026-06-10 22:29:58</t>
+          <t>2026-06-11 00:39:13</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Irish Premier Division</t>
+          <t>Irish Division 1</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -5674,246 +5674,246 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>St Patricks</t>
+          <t>Kerry FC</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Drogheda</t>
+          <t>Athlone Town</t>
         </is>
       </c>
       <c r="F21" t="n">
-        <v>1.35</v>
+        <v>2.28</v>
       </c>
       <c r="G21" t="n">
-        <v>1.42</v>
+        <v>2.5</v>
       </c>
       <c r="H21" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="I21" t="n">
+        <v>3.65</v>
+      </c>
+      <c r="J21" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="K21" t="n">
+        <v>3.65</v>
+      </c>
+      <c r="L21" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="M21" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="N21" t="n">
+        <v>3.35</v>
+      </c>
+      <c r="O21" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="P21" t="n">
+        <v>1.81</v>
+      </c>
+      <c r="Q21" t="n">
+        <v>2.04</v>
+      </c>
+      <c r="R21" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="S21" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="T21" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="U21" t="n">
+        <v>2.06</v>
+      </c>
+      <c r="V21" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="W21" t="n">
+        <v>1.66</v>
+      </c>
+      <c r="X21" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="Y21" t="n">
+        <v>15</v>
+      </c>
+      <c r="Z21" t="n">
+        <v>29</v>
+      </c>
+      <c r="AA21" t="n">
+        <v>80</v>
+      </c>
+      <c r="AB21" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="AC21" t="n">
+        <v>8</v>
+      </c>
+      <c r="AD21" t="n">
+        <v>17.5</v>
+      </c>
+      <c r="AE21" t="n">
+        <v>55</v>
+      </c>
+      <c r="AF21" t="n">
+        <v>18.5</v>
+      </c>
+      <c r="AG21" t="n">
+        <v>14</v>
+      </c>
+      <c r="AH21" t="n">
+        <v>22</v>
+      </c>
+      <c r="AI21" t="n">
+        <v>65</v>
+      </c>
+      <c r="AJ21" t="n">
+        <v>40</v>
+      </c>
+      <c r="AK21" t="n">
+        <v>34</v>
+      </c>
+      <c r="AL21" t="n">
+        <v>55</v>
+      </c>
+      <c r="AM21" t="n">
+        <v>130</v>
+      </c>
+      <c r="AN21" t="n">
+        <v>27</v>
+      </c>
+      <c r="AO21" t="n">
+        <v>55</v>
+      </c>
+      <c r="AP21" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="AQ21" t="n">
+        <v>9</v>
+      </c>
+      <c r="AR21" t="n">
+        <v>17</v>
+      </c>
+      <c r="AS21" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="AT21" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="AU21" t="n">
+        <v>5.8</v>
+      </c>
+      <c r="AV21" t="n">
         <v>10.5</v>
       </c>
-      <c r="I21" t="n">
+      <c r="AW21" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="AX21" t="n">
+        <v>11</v>
+      </c>
+      <c r="AY21" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="AZ21" t="n">
         <v>13</v>
       </c>
-      <c r="J21" t="n">
+      <c r="BA21" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="BB21" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="BC21" t="n">
+        <v>19.5</v>
+      </c>
+      <c r="BD21" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="BE21" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="BF21" t="n">
+        <v>16</v>
+      </c>
+      <c r="BG21" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="BH21" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="BI21" t="n">
+        <v>2.66</v>
+      </c>
+      <c r="BJ21" t="n">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="BK21" t="n">
+        <v>5.7</v>
+      </c>
+      <c r="BL21" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BM21" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="BN21" t="n">
+        <v>5.3</v>
+      </c>
+      <c r="BO21" t="n">
+        <v>4</v>
+      </c>
+      <c r="BP21" t="n">
+        <v>18.5</v>
+      </c>
+      <c r="BQ21" t="n">
+        <v>8</v>
+      </c>
+      <c r="BR21" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BS21" t="n">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="BT21" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="BU21" t="n">
         <v>4.9</v>
       </c>
-      <c r="K21" t="n">
-        <v>5.6</v>
-      </c>
-      <c r="L21" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="M21" t="n">
-        <v>1.06</v>
-      </c>
-      <c r="N21" t="n">
-        <v>3.9</v>
-      </c>
-      <c r="O21" t="n">
-        <v>1.28</v>
-      </c>
-      <c r="P21" t="n">
-        <v>2.06</v>
-      </c>
-      <c r="Q21" t="n">
-        <v>1.84</v>
-      </c>
-      <c r="R21" t="n">
-        <v>1.38</v>
-      </c>
-      <c r="S21" t="n">
-        <v>3.15</v>
-      </c>
-      <c r="T21" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="U21" t="n">
-        <v>1.67</v>
-      </c>
-      <c r="V21" t="n">
-        <v>1.08</v>
-      </c>
-      <c r="W21" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="X21" t="n">
-        <v>21</v>
-      </c>
-      <c r="Y21" t="n">
-        <v>38</v>
-      </c>
-      <c r="Z21" t="n">
-        <v>130</v>
-      </c>
-      <c r="AA21" t="n">
-        <v>630</v>
-      </c>
-      <c r="AB21" t="n">
-        <v>7.6</v>
-      </c>
-      <c r="AC21" t="n">
-        <v>14.5</v>
-      </c>
-      <c r="AD21" t="n">
-        <v>55</v>
-      </c>
-      <c r="AE21" t="n">
-        <v>280</v>
-      </c>
-      <c r="AF21" t="n">
-        <v>7.8</v>
-      </c>
-      <c r="AG21" t="n">
-        <v>13</v>
-      </c>
-      <c r="AH21" t="n">
-        <v>40</v>
-      </c>
-      <c r="AI21" t="n">
-        <v>220</v>
-      </c>
-      <c r="AJ21" t="n">
-        <v>13</v>
-      </c>
-      <c r="AK21" t="n">
-        <v>19.5</v>
-      </c>
-      <c r="AL21" t="n">
-        <v>60</v>
-      </c>
-      <c r="AM21" t="n">
-        <v>270</v>
-      </c>
-      <c r="AN21" t="n">
-        <v>7</v>
-      </c>
-      <c r="AO21" t="n">
-        <v>460</v>
-      </c>
-      <c r="AP21" t="n">
-        <v>14</v>
-      </c>
-      <c r="AQ21" t="n">
-        <v>5.1</v>
-      </c>
-      <c r="AR21" t="n">
-        <v>5.7</v>
-      </c>
-      <c r="AS21" t="n">
-        <v>5.9</v>
-      </c>
-      <c r="AT21" t="n">
-        <v>6.4</v>
-      </c>
-      <c r="AU21" t="n">
-        <v>10</v>
-      </c>
-      <c r="AV21" t="n">
-        <v>5.4</v>
-      </c>
-      <c r="AW21" t="n">
-        <v>5.8</v>
-      </c>
-      <c r="AX21" t="n">
-        <v>6.4</v>
-      </c>
-      <c r="AY21" t="n">
-        <v>9</v>
-      </c>
-      <c r="AZ21" t="n">
-        <v>5.2</v>
-      </c>
-      <c r="BA21" t="n">
-        <v>5.8</v>
-      </c>
-      <c r="BB21" t="n">
+      <c r="BV21" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BW21" t="n">
         <v>9.199999999999999</v>
       </c>
-      <c r="BC21" t="n">
-        <v>13.5</v>
-      </c>
-      <c r="BD21" t="n">
-        <v>5.4</v>
-      </c>
-      <c r="BE21" t="n">
-        <v>5.8</v>
-      </c>
-      <c r="BF21" t="n">
-        <v>5.1</v>
-      </c>
-      <c r="BG21" t="n">
-        <v>5.9</v>
-      </c>
-      <c r="BH21" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BI21" t="n">
-        <v>1.88</v>
-      </c>
-      <c r="BJ21" t="n">
-        <v>18.5</v>
-      </c>
-      <c r="BK21" t="n">
-        <v>1.71</v>
-      </c>
-      <c r="BL21" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BM21" t="n">
-        <v>1.88</v>
-      </c>
-      <c r="BN21" t="n">
-        <v>4.9</v>
-      </c>
-      <c r="BO21" t="n">
-        <v>2.54</v>
-      </c>
-      <c r="BP21" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="BQ21" t="n">
-        <v>5.1</v>
-      </c>
-      <c r="BR21" t="n">
-        <v>40</v>
-      </c>
-      <c r="BS21" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="BT21" t="n">
-        <v>20</v>
-      </c>
-      <c r="BU21" t="n">
-        <v>1.72</v>
-      </c>
-      <c r="BV21" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BW21" t="n">
-        <v>1.88</v>
-      </c>
       <c r="BX21" t="n">
         <v>1000</v>
       </c>
       <c r="BY21" t="n">
-        <v>1.88</v>
+        <v>10.5</v>
       </c>
       <c r="BZ21" t="n">
-        <v>22</v>
+        <v>1000</v>
       </c>
       <c r="CA21" t="n">
-        <v>1.73</v>
+        <v>9.6</v>
       </c>
       <c r="CB21" t="inlineStr">
         <is>
-          <t>2026-06-10 22:29:58</t>
+          <t>2026-06-11 00:39:13</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Irish Premier Division</t>
+          <t>Irish Division 1</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -5928,175 +5928,175 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>Galway Utd</t>
+          <t>Wexford F.C</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Dundalk</t>
+          <t>Cork City</t>
         </is>
       </c>
       <c r="F22" t="n">
-        <v>2.54</v>
+        <v>4.3</v>
       </c>
       <c r="G22" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="H22" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="I22" t="n">
+        <v>2</v>
+      </c>
+      <c r="J22" t="n">
         <v>3.55</v>
       </c>
-      <c r="H22" t="n">
-        <v>2.18</v>
-      </c>
-      <c r="I22" t="n">
-        <v>2.92</v>
-      </c>
-      <c r="J22" t="n">
-        <v>2.66</v>
-      </c>
       <c r="K22" t="n">
-        <v>1000</v>
+        <v>4.2</v>
       </c>
       <c r="L22" t="n">
-        <v>1.01</v>
+        <v>1.31</v>
       </c>
       <c r="M22" t="n">
-        <v>1.01</v>
+        <v>1.07</v>
       </c>
       <c r="N22" t="n">
-        <v>2.44</v>
+        <v>3.6</v>
       </c>
       <c r="O22" t="n">
-        <v>1.2</v>
+        <v>1.3</v>
       </c>
       <c r="P22" t="n">
-        <v>2.36</v>
+        <v>1.9</v>
       </c>
       <c r="Q22" t="n">
-        <v>1.4</v>
+        <v>1.9</v>
       </c>
       <c r="R22" t="n">
-        <v>1.39</v>
+        <v>1.34</v>
       </c>
       <c r="S22" t="n">
-        <v>2.16</v>
+        <v>3.3</v>
       </c>
       <c r="T22" t="n">
-        <v>1.3</v>
+        <v>1.79</v>
       </c>
       <c r="U22" t="n">
-        <v>1.94</v>
+        <v>2</v>
       </c>
       <c r="V22" t="n">
-        <v>1.52</v>
+        <v>2</v>
       </c>
       <c r="W22" t="n">
-        <v>1.39</v>
+        <v>1.24</v>
       </c>
       <c r="X22" t="n">
-        <v>1000</v>
+        <v>17</v>
       </c>
       <c r="Y22" t="n">
-        <v>950</v>
+        <v>9.4</v>
       </c>
       <c r="Z22" t="n">
-        <v>1000</v>
+        <v>12.5</v>
       </c>
       <c r="AA22" t="n">
-        <v>1000</v>
+        <v>23</v>
       </c>
       <c r="AB22" t="n">
-        <v>950</v>
+        <v>17</v>
       </c>
       <c r="AC22" t="n">
+        <v>9</v>
+      </c>
+      <c r="AD22" t="n">
+        <v>11</v>
+      </c>
+      <c r="AE22" t="n">
+        <v>22</v>
+      </c>
+      <c r="AF22" t="n">
+        <v>38</v>
+      </c>
+      <c r="AG22" t="n">
+        <v>19.5</v>
+      </c>
+      <c r="AH22" t="n">
+        <v>20</v>
+      </c>
+      <c r="AI22" t="n">
+        <v>38</v>
+      </c>
+      <c r="AJ22" t="n">
+        <v>130</v>
+      </c>
+      <c r="AK22" t="n">
+        <v>90</v>
+      </c>
+      <c r="AL22" t="n">
+        <v>70</v>
+      </c>
+      <c r="AM22" t="n">
+        <v>130</v>
+      </c>
+      <c r="AN22" t="n">
+        <v>95</v>
+      </c>
+      <c r="AO22" t="n">
+        <v>14</v>
+      </c>
+      <c r="AP22" t="n">
+        <v>11</v>
+      </c>
+      <c r="AQ22" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="AR22" t="n">
+        <v>10</v>
+      </c>
+      <c r="AS22" t="n">
         <v>18</v>
       </c>
-      <c r="AD22" t="n">
-        <v>22</v>
-      </c>
-      <c r="AE22" t="n">
-        <v>48</v>
-      </c>
-      <c r="AF22" t="n">
-        <v>48</v>
-      </c>
-      <c r="AG22" t="n">
-        <v>26</v>
-      </c>
-      <c r="AH22" t="n">
-        <v>950</v>
-      </c>
-      <c r="AI22" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AJ22" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AK22" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AL22" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AM22" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AN22" t="n">
-        <v>48</v>
-      </c>
-      <c r="AO22" t="n">
-        <v>30</v>
-      </c>
-      <c r="AP22" t="n">
-        <v>1.49</v>
-      </c>
-      <c r="AQ22" t="n">
-        <v>1.42</v>
-      </c>
-      <c r="AR22" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="AS22" t="n">
-        <v>1.5</v>
-      </c>
       <c r="AT22" t="n">
-        <v>1.43</v>
+        <v>13.5</v>
       </c>
       <c r="AU22" t="n">
-        <v>1.38</v>
+        <v>7.2</v>
       </c>
       <c r="AV22" t="n">
-        <v>1.4</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AW22" t="n">
-        <v>1.45</v>
+        <v>17</v>
       </c>
       <c r="AX22" t="n">
-        <v>1.45</v>
+        <v>23</v>
       </c>
       <c r="AY22" t="n">
-        <v>1.41</v>
+        <v>15.5</v>
       </c>
       <c r="AZ22" t="n">
-        <v>1.43</v>
+        <v>16</v>
       </c>
       <c r="BA22" t="n">
-        <v>1.5</v>
+        <v>23</v>
       </c>
       <c r="BB22" t="n">
-        <v>1.5</v>
+        <v>7.6</v>
       </c>
       <c r="BC22" t="n">
-        <v>1.5</v>
+        <v>7.2</v>
       </c>
       <c r="BD22" t="n">
-        <v>1.5</v>
+        <v>7.2</v>
       </c>
       <c r="BE22" t="n">
-        <v>1.5</v>
+        <v>7.6</v>
       </c>
       <c r="BF22" t="n">
-        <v>10.5</v>
+        <v>7.4</v>
       </c>
       <c r="BG22" t="n">
-        <v>7.8</v>
+        <v>11</v>
       </c>
       <c r="BH22" t="n">
         <v>1000</v>
@@ -6108,7 +6108,7 @@
         <v>1000</v>
       </c>
       <c r="BK22" t="n">
-        <v>1.04</v>
+        <v>2.5</v>
       </c>
       <c r="BL22" t="n">
         <v>1000</v>
@@ -6120,47 +6120,47 @@
         <v>1000</v>
       </c>
       <c r="BO22" t="n">
-        <v>1.04</v>
+        <v>2.38</v>
       </c>
       <c r="BP22" t="n">
         <v>1000</v>
       </c>
       <c r="BQ22" t="n">
-        <v>1.04</v>
+        <v>2.84</v>
       </c>
       <c r="BR22" t="n">
         <v>1000</v>
       </c>
       <c r="BS22" t="n">
-        <v>1.04</v>
+        <v>2.8</v>
       </c>
       <c r="BT22" t="n">
         <v>1000</v>
       </c>
       <c r="BU22" t="n">
-        <v>1.04</v>
+        <v>2.02</v>
       </c>
       <c r="BV22" t="n">
         <v>1000</v>
       </c>
       <c r="BW22" t="n">
-        <v>1.04</v>
+        <v>2.64</v>
       </c>
       <c r="BX22" t="n">
         <v>1000</v>
       </c>
       <c r="BY22" t="n">
-        <v>1.04</v>
+        <v>2.8</v>
       </c>
       <c r="BZ22" t="n">
         <v>1000</v>
       </c>
       <c r="CA22" t="n">
-        <v>1.04</v>
+        <v>2.8</v>
       </c>
       <c r="CB22" t="inlineStr">
         <is>
-          <t>2026-06-10 22:29:58</t>
+          <t>2026-06-11 00:39:13</t>
         </is>
       </c>
     </row>
@@ -6414,7 +6414,7 @@
       </c>
       <c r="CB23" t="inlineStr">
         <is>
-          <t>2026-06-10 22:29:58</t>
+          <t>2026-06-11 00:39:13</t>
         </is>
       </c>
     </row>
@@ -6493,10 +6493,10 @@
         <v>2.06</v>
       </c>
       <c r="V24" t="n">
-        <v>1.52</v>
+        <v>1.53</v>
       </c>
       <c r="W24" t="n">
-        <v>1.49</v>
+        <v>1.5</v>
       </c>
       <c r="X24" t="n">
         <v>15</v>
@@ -6628,7 +6628,7 @@
         <v>8.199999999999999</v>
       </c>
       <c r="BO24" t="n">
-        <v>4.5</v>
+        <v>3.8</v>
       </c>
       <c r="BP24" t="n">
         <v>34</v>
@@ -6646,7 +6646,7 @@
         <v>8</v>
       </c>
       <c r="BU24" t="n">
-        <v>4.4</v>
+        <v>3.7</v>
       </c>
       <c r="BV24" t="n">
         <v>30</v>
@@ -6668,7 +6668,7 @@
       </c>
       <c r="CB24" t="inlineStr">
         <is>
-          <t>2026-06-10 22:29:58</t>
+          <t>2026-06-11 00:39:13</t>
         </is>
       </c>
     </row>
@@ -6711,7 +6711,7 @@
         <v>990</v>
       </c>
       <c r="J25" t="n">
-        <v>1.06</v>
+        <v>1.09</v>
       </c>
       <c r="K25" t="n">
         <v>950</v>
@@ -6723,13 +6723,13 @@
         <v>1.01</v>
       </c>
       <c r="N25" t="n">
-        <v>1.26</v>
+        <v>1.3</v>
       </c>
       <c r="O25" t="n">
         <v>1.12</v>
       </c>
       <c r="P25" t="n">
-        <v>1.26</v>
+        <v>1.3</v>
       </c>
       <c r="Q25" t="n">
         <v>1.12</v>
@@ -6747,7 +6747,7 @@
         <v>1.11</v>
       </c>
       <c r="V25" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="W25" t="n">
         <v>1.02</v>
@@ -6922,7 +6922,7 @@
       </c>
       <c r="CB25" t="inlineStr">
         <is>
-          <t>2026-06-10 22:29:58</t>
+          <t>2026-06-11 00:39:13</t>
         </is>
       </c>
     </row>
@@ -6953,19 +6953,19 @@
         </is>
       </c>
       <c r="F26" t="n">
-        <v>2.08</v>
+        <v>2.18</v>
       </c>
       <c r="G26" t="n">
-        <v>2.68</v>
+        <v>2.38</v>
       </c>
       <c r="H26" t="n">
-        <v>3.15</v>
+        <v>3.6</v>
       </c>
       <c r="I26" t="n">
-        <v>4.7</v>
+        <v>4.2</v>
       </c>
       <c r="J26" t="n">
-        <v>2.44</v>
+        <v>3.35</v>
       </c>
       <c r="K26" t="n">
         <v>3.45</v>
@@ -6983,10 +6983,10 @@
         <v>1.44</v>
       </c>
       <c r="P26" t="n">
-        <v>1.53</v>
+        <v>1.25</v>
       </c>
       <c r="Q26" t="n">
-        <v>1.92</v>
+        <v>1.9</v>
       </c>
       <c r="R26" t="n">
         <v>1.19</v>
@@ -7001,10 +7001,10 @@
         <v>1.11</v>
       </c>
       <c r="V26" t="n">
-        <v>1.27</v>
+        <v>1.32</v>
       </c>
       <c r="W26" t="n">
-        <v>1.59</v>
+        <v>1.73</v>
       </c>
       <c r="X26" t="n">
         <v>1000</v>
@@ -7176,7 +7176,7 @@
       </c>
       <c r="CB26" t="inlineStr">
         <is>
-          <t>2026-06-10 22:29:58</t>
+          <t>2026-06-11 00:39:13</t>
         </is>
       </c>
     </row>
@@ -7213,7 +7213,7 @@
         <v>1.49</v>
       </c>
       <c r="H27" t="n">
-        <v>2.7</v>
+        <v>3.6</v>
       </c>
       <c r="I27" t="n">
         <v>1000</v>
@@ -7222,7 +7222,7 @@
         <v>2.7</v>
       </c>
       <c r="K27" t="n">
-        <v>950</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="L27" t="n">
         <v>1.01</v>
@@ -7430,7 +7430,261 @@
       </c>
       <c r="CB27" t="inlineStr">
         <is>
-          <t>2026-06-10 22:29:58</t>
+          <t>2026-06-11 00:39:13</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>Chilean Primera Division</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>2026-06-12</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>21:00:00</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>Audax Italiano</t>
+        </is>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>La Serena</t>
+        </is>
+      </c>
+      <c r="F28" t="n">
+        <v>1.99</v>
+      </c>
+      <c r="G28" t="n">
+        <v>2.14</v>
+      </c>
+      <c r="H28" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="I28" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="J28" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="K28" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="L28" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="M28" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="N28" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="O28" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="P28" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="Q28" t="n">
+        <v>1.77</v>
+      </c>
+      <c r="R28" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="S28" t="n">
+        <v>2.94</v>
+      </c>
+      <c r="T28" t="n">
+        <v>1.69</v>
+      </c>
+      <c r="U28" t="n">
+        <v>2.26</v>
+      </c>
+      <c r="V28" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="W28" t="n">
+        <v>1.88</v>
+      </c>
+      <c r="X28" t="n">
+        <v>22</v>
+      </c>
+      <c r="Y28" t="n">
+        <v>19.5</v>
+      </c>
+      <c r="Z28" t="n">
+        <v>36</v>
+      </c>
+      <c r="AA28" t="n">
+        <v>90</v>
+      </c>
+      <c r="AB28" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="AC28" t="n">
+        <v>10</v>
+      </c>
+      <c r="AD28" t="n">
+        <v>19.5</v>
+      </c>
+      <c r="AE28" t="n">
+        <v>55</v>
+      </c>
+      <c r="AF28" t="n">
+        <v>17</v>
+      </c>
+      <c r="AG28" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="AH28" t="n">
+        <v>19.5</v>
+      </c>
+      <c r="AI28" t="n">
+        <v>60</v>
+      </c>
+      <c r="AJ28" t="n">
+        <v>30</v>
+      </c>
+      <c r="AK28" t="n">
+        <v>24</v>
+      </c>
+      <c r="AL28" t="n">
+        <v>40</v>
+      </c>
+      <c r="AM28" t="n">
+        <v>100</v>
+      </c>
+      <c r="AN28" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="AO28" t="n">
+        <v>48</v>
+      </c>
+      <c r="AP28" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="AQ28" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="AR28" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="AS28" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="AT28" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="AU28" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="AV28" t="n">
+        <v>14</v>
+      </c>
+      <c r="AW28" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="AX28" t="n">
+        <v>12</v>
+      </c>
+      <c r="AY28" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="AZ28" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="BA28" t="n">
+        <v>40</v>
+      </c>
+      <c r="BB28" t="n">
+        <v>21</v>
+      </c>
+      <c r="BC28" t="n">
+        <v>18</v>
+      </c>
+      <c r="BD28" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="BE28" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="BF28" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="BG28" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="BH28" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="BI28" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="BJ28" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="BK28" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BL28" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BM28" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BN28" t="n">
+        <v>5</v>
+      </c>
+      <c r="BO28" t="n">
+        <v>3.85</v>
+      </c>
+      <c r="BP28" t="n">
+        <v>14</v>
+      </c>
+      <c r="BQ28" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BR28" t="n">
+        <v>26</v>
+      </c>
+      <c r="BS28" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BT28" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="BU28" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="BV28" t="n">
+        <v>30</v>
+      </c>
+      <c r="BW28" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BX28" t="n">
+        <v>38</v>
+      </c>
+      <c r="BY28" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BZ28" t="n">
+        <v>21</v>
+      </c>
+      <c r="CA28" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="CB28" t="inlineStr">
+        <is>
+          <t>2026-06-11 00:39:13</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-06-12.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-06-12.xlsx
@@ -857,13 +857,13 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>1.13</v>
+        <v>1.15</v>
       </c>
       <c r="G2" t="n">
         <v>1000</v>
       </c>
       <c r="H2" t="n">
-        <v>1.13</v>
+        <v>1.15</v>
       </c>
       <c r="I2" t="n">
         <v>1000</v>
@@ -1080,7 +1080,7 @@
       </c>
       <c r="CB2" t="inlineStr">
         <is>
-          <t>2026-06-11 00:39:13</t>
+          <t>2026-06-11 02:48:02</t>
         </is>
       </c>
     </row>
@@ -1334,7 +1334,7 @@
       </c>
       <c r="CB3" t="inlineStr">
         <is>
-          <t>2026-06-11 00:39:13</t>
+          <t>2026-06-11 02:48:02</t>
         </is>
       </c>
     </row>
@@ -1365,13 +1365,13 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>1.13</v>
+        <v>1.15</v>
       </c>
       <c r="G4" t="n">
         <v>1000</v>
       </c>
       <c r="H4" t="n">
-        <v>1.13</v>
+        <v>1.15</v>
       </c>
       <c r="I4" t="n">
         <v>1000</v>
@@ -1398,13 +1398,13 @@
         <v>1.24</v>
       </c>
       <c r="Q4" t="n">
-        <v>1.48</v>
+        <v>1.53</v>
       </c>
       <c r="R4" t="n">
         <v>1.18</v>
       </c>
       <c r="S4" t="n">
-        <v>1.48</v>
+        <v>1.53</v>
       </c>
       <c r="T4" t="n">
         <v>1.11</v>
@@ -1413,10 +1413,10 @@
         <v>1.11</v>
       </c>
       <c r="V4" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="W4" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="X4" t="n">
         <v>1000</v>
@@ -1588,7 +1588,7 @@
       </c>
       <c r="CB4" t="inlineStr">
         <is>
-          <t>2026-06-11 00:39:13</t>
+          <t>2026-06-11 02:48:02</t>
         </is>
       </c>
     </row>
@@ -1619,13 +1619,13 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>1.54</v>
+        <v>1.55</v>
       </c>
       <c r="G5" t="n">
         <v>1000</v>
       </c>
       <c r="H5" t="n">
-        <v>1.54</v>
+        <v>1.55</v>
       </c>
       <c r="I5" t="n">
         <v>1000</v>
@@ -1634,7 +1634,7 @@
         <v>1.09</v>
       </c>
       <c r="K5" t="n">
-        <v>3</v>
+        <v>2.96</v>
       </c>
       <c r="L5" t="n">
         <v>1.01</v>
@@ -1643,13 +1643,13 @@
         <v>1.01</v>
       </c>
       <c r="N5" t="n">
-        <v>1.26</v>
+        <v>1.28</v>
       </c>
       <c r="O5" t="n">
         <v>1.02</v>
       </c>
       <c r="P5" t="n">
-        <v>1.26</v>
+        <v>1.28</v>
       </c>
       <c r="Q5" t="n">
         <v>1.55</v>
@@ -1842,7 +1842,7 @@
       </c>
       <c r="CB5" t="inlineStr">
         <is>
-          <t>2026-06-11 00:39:13</t>
+          <t>2026-06-11 02:48:02</t>
         </is>
       </c>
     </row>
@@ -1873,13 +1873,13 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>1.13</v>
+        <v>1.15</v>
       </c>
       <c r="G6" t="n">
         <v>1000</v>
       </c>
       <c r="H6" t="n">
-        <v>1.13</v>
+        <v>1.15</v>
       </c>
       <c r="I6" t="n">
         <v>1000</v>
@@ -2096,7 +2096,7 @@
       </c>
       <c r="CB6" t="inlineStr">
         <is>
-          <t>2026-06-11 00:39:13</t>
+          <t>2026-06-11 02:48:02</t>
         </is>
       </c>
     </row>
@@ -2127,13 +2127,13 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>1.12</v>
+        <v>1.14</v>
       </c>
       <c r="G7" t="n">
         <v>1000</v>
       </c>
       <c r="H7" t="n">
-        <v>1.12</v>
+        <v>1.14</v>
       </c>
       <c r="I7" t="n">
         <v>1000</v>
@@ -2350,7 +2350,7 @@
       </c>
       <c r="CB7" t="inlineStr">
         <is>
-          <t>2026-06-11 00:39:13</t>
+          <t>2026-06-11 02:48:02</t>
         </is>
       </c>
     </row>
@@ -2604,7 +2604,7 @@
       </c>
       <c r="CB8" t="inlineStr">
         <is>
-          <t>2026-06-11 00:39:13</t>
+          <t>2026-06-11 02:48:02</t>
         </is>
       </c>
     </row>
@@ -2858,7 +2858,7 @@
       </c>
       <c r="CB9" t="inlineStr">
         <is>
-          <t>2026-06-11 00:39:13</t>
+          <t>2026-06-11 02:48:02</t>
         </is>
       </c>
     </row>
@@ -2889,13 +2889,13 @@
         </is>
       </c>
       <c r="F10" t="n">
-        <v>1.11</v>
+        <v>1.13</v>
       </c>
       <c r="G10" t="n">
         <v>1000</v>
       </c>
       <c r="H10" t="n">
-        <v>1.11</v>
+        <v>1.13</v>
       </c>
       <c r="I10" t="n">
         <v>1000</v>
@@ -2916,19 +2916,19 @@
         <v>1.25</v>
       </c>
       <c r="O10" t="n">
-        <v>1.43</v>
+        <v>1.05</v>
       </c>
       <c r="P10" t="n">
         <v>1.24</v>
       </c>
       <c r="Q10" t="n">
-        <v>1.43</v>
+        <v>1.44</v>
       </c>
       <c r="R10" t="n">
         <v>1.18</v>
       </c>
       <c r="S10" t="n">
-        <v>1.43</v>
+        <v>1.44</v>
       </c>
       <c r="T10" t="n">
         <v>1.11</v>
@@ -3112,7 +3112,7 @@
       </c>
       <c r="CB10" t="inlineStr">
         <is>
-          <t>2026-06-11 00:39:13</t>
+          <t>2026-06-11 02:48:02</t>
         </is>
       </c>
     </row>
@@ -3143,13 +3143,13 @@
         </is>
       </c>
       <c r="F11" t="n">
-        <v>1.11</v>
+        <v>1.13</v>
       </c>
       <c r="G11" t="n">
         <v>1000</v>
       </c>
       <c r="H11" t="n">
-        <v>1.13</v>
+        <v>1.15</v>
       </c>
       <c r="I11" t="n">
         <v>1000</v>
@@ -3167,13 +3167,13 @@
         <v>1.01</v>
       </c>
       <c r="N11" t="n">
-        <v>1.28</v>
+        <v>1.3</v>
       </c>
       <c r="O11" t="n">
         <v>1.02</v>
       </c>
       <c r="P11" t="n">
-        <v>1.28</v>
+        <v>1.3</v>
       </c>
       <c r="Q11" t="n">
         <v>1.56</v>
@@ -3366,7 +3366,7 @@
       </c>
       <c r="CB11" t="inlineStr">
         <is>
-          <t>2026-06-11 00:39:13</t>
+          <t>2026-06-11 02:48:02</t>
         </is>
       </c>
     </row>
@@ -3409,7 +3409,7 @@
         <v>1000</v>
       </c>
       <c r="J12" t="n">
-        <v>1.1</v>
+        <v>1.12</v>
       </c>
       <c r="K12" t="n">
         <v>1000</v>
@@ -3620,7 +3620,7 @@
       </c>
       <c r="CB12" t="inlineStr">
         <is>
-          <t>2026-06-11 00:39:13</t>
+          <t>2026-06-11 02:48:02</t>
         </is>
       </c>
     </row>
@@ -3651,13 +3651,13 @@
         </is>
       </c>
       <c r="F13" t="n">
-        <v>1.1</v>
+        <v>1.12</v>
       </c>
       <c r="G13" t="n">
         <v>1000</v>
       </c>
       <c r="H13" t="n">
-        <v>1.1</v>
+        <v>1.12</v>
       </c>
       <c r="I13" t="n">
         <v>1000</v>
@@ -3874,7 +3874,7 @@
       </c>
       <c r="CB13" t="inlineStr">
         <is>
-          <t>2026-06-11 00:39:13</t>
+          <t>2026-06-11 02:48:02</t>
         </is>
       </c>
     </row>
@@ -3908,7 +3908,7 @@
         <v>1.46</v>
       </c>
       <c r="G14" t="n">
-        <v>1000</v>
+        <v>990</v>
       </c>
       <c r="H14" t="n">
         <v>1.46</v>
@@ -3917,7 +3917,7 @@
         <v>1000</v>
       </c>
       <c r="J14" t="n">
-        <v>1.08</v>
+        <v>1.1</v>
       </c>
       <c r="K14" t="n">
         <v>3.25</v>
@@ -4128,7 +4128,7 @@
       </c>
       <c r="CB14" t="inlineStr">
         <is>
-          <t>2026-06-11 00:39:13</t>
+          <t>2026-06-11 02:48:02</t>
         </is>
       </c>
     </row>
@@ -4159,22 +4159,22 @@
         </is>
       </c>
       <c r="F15" t="n">
-        <v>2.8</v>
+        <v>2.76</v>
       </c>
       <c r="G15" t="n">
-        <v>3.4</v>
+        <v>3.3</v>
       </c>
       <c r="H15" t="n">
-        <v>1.99</v>
+        <v>2</v>
       </c>
       <c r="I15" t="n">
-        <v>2.82</v>
+        <v>2.92</v>
       </c>
       <c r="J15" t="n">
         <v>3.3</v>
       </c>
       <c r="K15" t="n">
-        <v>950</v>
+        <v>1000</v>
       </c>
       <c r="L15" t="n">
         <v>1.01</v>
@@ -4192,7 +4192,7 @@
         <v>2.36</v>
       </c>
       <c r="Q15" t="n">
-        <v>1.4</v>
+        <v>1.2</v>
       </c>
       <c r="R15" t="n">
         <v>1.39</v>
@@ -4204,13 +4204,13 @@
         <v>1.3</v>
       </c>
       <c r="U15" t="n">
-        <v>1.96</v>
+        <v>1.98</v>
       </c>
       <c r="V15" t="n">
-        <v>1.54</v>
+        <v>1.52</v>
       </c>
       <c r="W15" t="n">
-        <v>1.42</v>
+        <v>1.44</v>
       </c>
       <c r="X15" t="n">
         <v>1000</v>
@@ -4382,7 +4382,7 @@
       </c>
       <c r="CB15" t="inlineStr">
         <is>
-          <t>2026-06-11 00:39:13</t>
+          <t>2026-06-11 02:48:02</t>
         </is>
       </c>
     </row>
@@ -4455,7 +4455,7 @@
         <v>3.1</v>
       </c>
       <c r="T16" t="n">
-        <v>2.18</v>
+        <v>2.22</v>
       </c>
       <c r="U16" t="n">
         <v>1.67</v>
@@ -4476,7 +4476,7 @@
         <v>130</v>
       </c>
       <c r="AA16" t="n">
-        <v>630</v>
+        <v>620</v>
       </c>
       <c r="AB16" t="n">
         <v>9</v>
@@ -4488,13 +4488,13 @@
         <v>55</v>
       </c>
       <c r="AE16" t="n">
-        <v>280</v>
+        <v>270</v>
       </c>
       <c r="AF16" t="n">
         <v>9.199999999999999</v>
       </c>
       <c r="AG16" t="n">
-        <v>13</v>
+        <v>11.5</v>
       </c>
       <c r="AH16" t="n">
         <v>40</v>
@@ -4506,31 +4506,31 @@
         <v>13.5</v>
       </c>
       <c r="AK16" t="n">
-        <v>20</v>
+        <v>19.5</v>
       </c>
       <c r="AL16" t="n">
         <v>60</v>
       </c>
       <c r="AM16" t="n">
-        <v>270</v>
+        <v>260</v>
       </c>
       <c r="AN16" t="n">
         <v>8.199999999999999</v>
       </c>
       <c r="AO16" t="n">
-        <v>460</v>
+        <v>450</v>
       </c>
       <c r="AP16" t="n">
         <v>12</v>
       </c>
       <c r="AQ16" t="n">
-        <v>3.85</v>
+        <v>4</v>
       </c>
       <c r="AR16" t="n">
-        <v>4.1</v>
+        <v>4.4</v>
       </c>
       <c r="AS16" t="n">
-        <v>4.2</v>
+        <v>4.5</v>
       </c>
       <c r="AT16" t="n">
         <v>5.6</v>
@@ -4539,40 +4539,40 @@
         <v>8.800000000000001</v>
       </c>
       <c r="AV16" t="n">
-        <v>4</v>
+        <v>30</v>
       </c>
       <c r="AW16" t="n">
-        <v>4.2</v>
+        <v>4.4</v>
       </c>
       <c r="AX16" t="n">
-        <v>6.4</v>
+        <v>6.6</v>
       </c>
       <c r="AY16" t="n">
         <v>7.8</v>
       </c>
       <c r="AZ16" t="n">
-        <v>3.9</v>
+        <v>4</v>
       </c>
       <c r="BA16" t="n">
-        <v>4.2</v>
+        <v>4.4</v>
       </c>
       <c r="BB16" t="n">
-        <v>8</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BC16" t="n">
         <v>11.5</v>
       </c>
       <c r="BD16" t="n">
-        <v>4</v>
+        <v>4.2</v>
       </c>
       <c r="BE16" t="n">
-        <v>4.2</v>
+        <v>4.4</v>
       </c>
       <c r="BF16" t="n">
-        <v>5.8</v>
+        <v>5.1</v>
       </c>
       <c r="BG16" t="n">
-        <v>4.2</v>
+        <v>4.5</v>
       </c>
       <c r="BH16" t="n">
         <v>1000</v>
@@ -4584,7 +4584,7 @@
         <v>1000</v>
       </c>
       <c r="BK16" t="n">
-        <v>1.58</v>
+        <v>1.04</v>
       </c>
       <c r="BL16" t="n">
         <v>1000</v>
@@ -4596,13 +4596,13 @@
         <v>1000</v>
       </c>
       <c r="BO16" t="n">
-        <v>1.3</v>
+        <v>1.04</v>
       </c>
       <c r="BP16" t="n">
         <v>1000</v>
       </c>
       <c r="BQ16" t="n">
-        <v>1.5</v>
+        <v>1.04</v>
       </c>
       <c r="BR16" t="n">
         <v>1000</v>
@@ -4636,7 +4636,7 @@
       </c>
       <c r="CB16" t="inlineStr">
         <is>
-          <t>2026-06-11 00:39:13</t>
+          <t>2026-06-11 02:48:02</t>
         </is>
       </c>
     </row>
@@ -4775,7 +4775,7 @@
         <v>44</v>
       </c>
       <c r="AP17" t="n">
-        <v>11.5</v>
+        <v>13.5</v>
       </c>
       <c r="AQ17" t="n">
         <v>11.5</v>
@@ -4890,7 +4890,7 @@
       </c>
       <c r="CB17" t="inlineStr">
         <is>
-          <t>2026-06-11 00:39:13</t>
+          <t>2026-06-11 02:48:02</t>
         </is>
       </c>
     </row>
@@ -4939,7 +4939,7 @@
         <v>3.55</v>
       </c>
       <c r="L18" t="n">
-        <v>1.46</v>
+        <v>1.41</v>
       </c>
       <c r="M18" t="n">
         <v>1.09</v>
@@ -4978,7 +4978,7 @@
         <v>12</v>
       </c>
       <c r="Y18" t="n">
-        <v>10.5</v>
+        <v>9.6</v>
       </c>
       <c r="Z18" t="n">
         <v>18</v>
@@ -4996,7 +4996,7 @@
         <v>14</v>
       </c>
       <c r="AE18" t="n">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="AF18" t="n">
         <v>23</v>
@@ -5065,34 +5065,34 @@
         <v>38</v>
       </c>
       <c r="BB18" t="n">
-        <v>5.6</v>
+        <v>6</v>
       </c>
       <c r="BC18" t="n">
         <v>34</v>
       </c>
       <c r="BD18" t="n">
-        <v>5.6</v>
+        <v>6</v>
       </c>
       <c r="BE18" t="n">
-        <v>5.9</v>
+        <v>6.2</v>
       </c>
       <c r="BF18" t="n">
-        <v>5.4</v>
+        <v>5.8</v>
       </c>
       <c r="BG18" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="BH18" t="n">
         <v>3.2</v>
       </c>
       <c r="BI18" t="n">
-        <v>2.74</v>
+        <v>2.56</v>
       </c>
       <c r="BJ18" t="n">
         <v>10.5</v>
       </c>
       <c r="BK18" t="n">
-        <v>5.2</v>
+        <v>7.8</v>
       </c>
       <c r="BL18" t="n">
         <v>1000</v>
@@ -5104,7 +5104,7 @@
         <v>6.6</v>
       </c>
       <c r="BO18" t="n">
-        <v>5</v>
+        <v>5.4</v>
       </c>
       <c r="BP18" t="n">
         <v>1000</v>
@@ -5122,7 +5122,7 @@
         <v>5.5</v>
       </c>
       <c r="BU18" t="n">
-        <v>4.2</v>
+        <v>4.5</v>
       </c>
       <c r="BV18" t="n">
         <v>21</v>
@@ -5137,14 +5137,14 @@
         <v>8</v>
       </c>
       <c r="BZ18" t="n">
-        <v>38</v>
+        <v>1000</v>
       </c>
       <c r="CA18" t="n">
         <v>8</v>
       </c>
       <c r="CB18" t="inlineStr">
         <is>
-          <t>2026-06-11 00:39:13</t>
+          <t>2026-06-11 02:48:02</t>
         </is>
       </c>
     </row>
@@ -5211,7 +5211,7 @@
         <v>1.61</v>
       </c>
       <c r="R19" t="n">
-        <v>1.31</v>
+        <v>1.26</v>
       </c>
       <c r="S19" t="n">
         <v>2.3</v>
@@ -5398,7 +5398,7 @@
       </c>
       <c r="CB19" t="inlineStr">
         <is>
-          <t>2026-06-11 00:39:13</t>
+          <t>2026-06-11 02:48:02</t>
         </is>
       </c>
     </row>
@@ -5429,85 +5429,85 @@
         </is>
       </c>
       <c r="F20" t="n">
-        <v>3.85</v>
+        <v>3.9</v>
       </c>
       <c r="G20" t="n">
-        <v>4.5</v>
+        <v>4.6</v>
       </c>
       <c r="H20" t="n">
         <v>1.86</v>
       </c>
       <c r="I20" t="n">
-        <v>2.04</v>
+        <v>2.06</v>
       </c>
       <c r="J20" t="n">
-        <v>3.8</v>
+        <v>3.7</v>
       </c>
       <c r="K20" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="L20" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="M20" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="N20" t="n">
         <v>4.5</v>
       </c>
-      <c r="L20" t="n">
-        <v>1.24</v>
-      </c>
-      <c r="M20" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="N20" t="n">
-        <v>5</v>
-      </c>
       <c r="O20" t="n">
-        <v>1.2</v>
+        <v>1.22</v>
       </c>
       <c r="P20" t="n">
-        <v>2.42</v>
+        <v>2.24</v>
       </c>
       <c r="Q20" t="n">
-        <v>1.6</v>
+        <v>1.66</v>
       </c>
       <c r="R20" t="n">
-        <v>1.59</v>
+        <v>1.53</v>
       </c>
       <c r="S20" t="n">
+        <v>2.48</v>
+      </c>
+      <c r="T20" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="U20" t="n">
         <v>2.3</v>
       </c>
-      <c r="T20" t="n">
-        <v>1.56</v>
-      </c>
-      <c r="U20" t="n">
-        <v>2.44</v>
-      </c>
       <c r="V20" t="n">
-        <v>1.96</v>
+        <v>1.95</v>
       </c>
       <c r="W20" t="n">
-        <v>1.29</v>
+        <v>1.28</v>
       </c>
       <c r="X20" t="n">
-        <v>28</v>
+        <v>21</v>
       </c>
       <c r="Y20" t="n">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="Z20" t="n">
-        <v>17.5</v>
+        <v>14.5</v>
       </c>
       <c r="AA20" t="n">
-        <v>30</v>
+        <v>26</v>
       </c>
       <c r="AB20" t="n">
-        <v>22</v>
+        <v>19.5</v>
       </c>
       <c r="AC20" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="AD20" t="n">
-        <v>12.5</v>
+        <v>12</v>
       </c>
       <c r="AE20" t="n">
-        <v>17.5</v>
+        <v>18</v>
       </c>
       <c r="AF20" t="n">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="AG20" t="n">
         <v>23</v>
@@ -5522,16 +5522,16 @@
         <v>110</v>
       </c>
       <c r="AK20" t="n">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="AL20" t="n">
         <v>50</v>
       </c>
       <c r="AM20" t="n">
-        <v>70</v>
+        <v>85</v>
       </c>
       <c r="AN20" t="n">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="AO20" t="n">
         <v>10.5</v>
@@ -5552,7 +5552,7 @@
         <v>15</v>
       </c>
       <c r="AU20" t="n">
-        <v>8.800000000000001</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AV20" t="n">
         <v>9.800000000000001</v>
@@ -5561,7 +5561,7 @@
         <v>12</v>
       </c>
       <c r="AX20" t="n">
-        <v>4.9</v>
+        <v>6.4</v>
       </c>
       <c r="AY20" t="n">
         <v>13.5</v>
@@ -5573,16 +5573,16 @@
         <v>18.5</v>
       </c>
       <c r="BB20" t="n">
-        <v>5.3</v>
+        <v>7.4</v>
       </c>
       <c r="BC20" t="n">
-        <v>4.9</v>
+        <v>28</v>
       </c>
       <c r="BD20" t="n">
-        <v>5</v>
+        <v>29</v>
       </c>
       <c r="BE20" t="n">
-        <v>5.1</v>
+        <v>42</v>
       </c>
       <c r="BF20" t="n">
         <v>23</v>
@@ -5594,65 +5594,65 @@
         <v>1000</v>
       </c>
       <c r="BI20" t="n">
-        <v>1.89</v>
+        <v>1.93</v>
       </c>
       <c r="BJ20" t="n">
         <v>13.5</v>
       </c>
       <c r="BK20" t="n">
-        <v>1.66</v>
+        <v>1.69</v>
       </c>
       <c r="BL20" t="n">
         <v>1000</v>
       </c>
       <c r="BM20" t="n">
-        <v>1.89</v>
+        <v>1.93</v>
       </c>
       <c r="BN20" t="n">
         <v>11</v>
       </c>
       <c r="BO20" t="n">
-        <v>4.9</v>
+        <v>1.65</v>
       </c>
       <c r="BP20" t="n">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="BQ20" t="n">
-        <v>1.82</v>
+        <v>1.86</v>
       </c>
       <c r="BR20" t="n">
-        <v>1000</v>
+        <v>50</v>
       </c>
       <c r="BS20" t="n">
-        <v>1.83</v>
+        <v>1.87</v>
       </c>
       <c r="BT20" t="n">
-        <v>7</v>
+        <v>6.6</v>
       </c>
       <c r="BU20" t="n">
-        <v>3.3</v>
+        <v>3.6</v>
       </c>
       <c r="BV20" t="n">
         <v>18</v>
       </c>
       <c r="BW20" t="n">
-        <v>1.72</v>
+        <v>1.75</v>
       </c>
       <c r="BX20" t="n">
-        <v>38</v>
+        <v>34</v>
       </c>
       <c r="BY20" t="n">
-        <v>1.81</v>
+        <v>1.83</v>
       </c>
       <c r="BZ20" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="CA20" t="n">
-        <v>1.76</v>
+        <v>1.8</v>
       </c>
       <c r="CB20" t="inlineStr">
         <is>
-          <t>2026-06-11 00:39:13</t>
+          <t>2026-06-11 02:48:02</t>
         </is>
       </c>
     </row>
@@ -5683,13 +5683,13 @@
         </is>
       </c>
       <c r="F21" t="n">
-        <v>2.28</v>
+        <v>2.26</v>
       </c>
       <c r="G21" t="n">
-        <v>2.5</v>
+        <v>2.48</v>
       </c>
       <c r="H21" t="n">
-        <v>3.2</v>
+        <v>3.25</v>
       </c>
       <c r="I21" t="n">
         <v>3.65</v>
@@ -5698,7 +5698,7 @@
         <v>3.25</v>
       </c>
       <c r="K21" t="n">
-        <v>3.65</v>
+        <v>3.7</v>
       </c>
       <c r="L21" t="n">
         <v>1.43</v>
@@ -5707,25 +5707,25 @@
         <v>1.08</v>
       </c>
       <c r="N21" t="n">
-        <v>3.35</v>
+        <v>3.4</v>
       </c>
       <c r="O21" t="n">
         <v>1.36</v>
       </c>
       <c r="P21" t="n">
-        <v>1.81</v>
+        <v>1.82</v>
       </c>
       <c r="Q21" t="n">
-        <v>2.04</v>
+        <v>2.02</v>
       </c>
       <c r="R21" t="n">
         <v>1.31</v>
       </c>
       <c r="S21" t="n">
-        <v>3.7</v>
+        <v>3.65</v>
       </c>
       <c r="T21" t="n">
-        <v>1.8</v>
+        <v>1.79</v>
       </c>
       <c r="U21" t="n">
         <v>2.06</v>
@@ -5734,10 +5734,10 @@
         <v>1.38</v>
       </c>
       <c r="W21" t="n">
-        <v>1.66</v>
+        <v>1.67</v>
       </c>
       <c r="X21" t="n">
-        <v>15.5</v>
+        <v>16</v>
       </c>
       <c r="Y21" t="n">
         <v>15</v>
@@ -5749,13 +5749,13 @@
         <v>80</v>
       </c>
       <c r="AB21" t="n">
-        <v>11.5</v>
+        <v>12</v>
       </c>
       <c r="AC21" t="n">
-        <v>8</v>
+        <v>9.4</v>
       </c>
       <c r="AD21" t="n">
-        <v>17.5</v>
+        <v>18</v>
       </c>
       <c r="AE21" t="n">
         <v>55</v>
@@ -5779,7 +5779,7 @@
         <v>34</v>
       </c>
       <c r="AL21" t="n">
-        <v>55</v>
+        <v>50</v>
       </c>
       <c r="AM21" t="n">
         <v>130</v>
@@ -5791,28 +5791,28 @@
         <v>55</v>
       </c>
       <c r="AP21" t="n">
-        <v>9.4</v>
+        <v>9.6</v>
       </c>
       <c r="AQ21" t="n">
-        <v>9</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AR21" t="n">
         <v>17</v>
       </c>
       <c r="AS21" t="n">
-        <v>4.4</v>
+        <v>4</v>
       </c>
       <c r="AT21" t="n">
         <v>7.2</v>
       </c>
       <c r="AU21" t="n">
-        <v>5.8</v>
+        <v>5.9</v>
       </c>
       <c r="AV21" t="n">
         <v>10.5</v>
       </c>
       <c r="AW21" t="n">
-        <v>4.3</v>
+        <v>3.9</v>
       </c>
       <c r="AX21" t="n">
         <v>11</v>
@@ -5824,25 +5824,25 @@
         <v>13</v>
       </c>
       <c r="BA21" t="n">
-        <v>4.3</v>
+        <v>3.95</v>
       </c>
       <c r="BB21" t="n">
-        <v>4.2</v>
+        <v>3.8</v>
       </c>
       <c r="BC21" t="n">
-        <v>19.5</v>
+        <v>19</v>
       </c>
       <c r="BD21" t="n">
-        <v>4.3</v>
+        <v>3.85</v>
       </c>
       <c r="BE21" t="n">
-        <v>4.5</v>
+        <v>4</v>
       </c>
       <c r="BF21" t="n">
-        <v>16</v>
+        <v>18.5</v>
       </c>
       <c r="BG21" t="n">
-        <v>4.3</v>
+        <v>3.9</v>
       </c>
       <c r="BH21" t="n">
         <v>3.3</v>
@@ -5866,19 +5866,19 @@
         <v>5.3</v>
       </c>
       <c r="BO21" t="n">
-        <v>4</v>
+        <v>3.95</v>
       </c>
       <c r="BP21" t="n">
-        <v>18.5</v>
+        <v>1000</v>
       </c>
       <c r="BQ21" t="n">
-        <v>8</v>
+        <v>7.8</v>
       </c>
       <c r="BR21" t="n">
         <v>1000</v>
       </c>
       <c r="BS21" t="n">
-        <v>9.800000000000001</v>
+        <v>10</v>
       </c>
       <c r="BT21" t="n">
         <v>6.6</v>
@@ -5890,7 +5890,7 @@
         <v>1000</v>
       </c>
       <c r="BW21" t="n">
-        <v>9.199999999999999</v>
+        <v>9.4</v>
       </c>
       <c r="BX21" t="n">
         <v>1000</v>
@@ -5906,7 +5906,7 @@
       </c>
       <c r="CB21" t="inlineStr">
         <is>
-          <t>2026-06-11 00:39:13</t>
+          <t>2026-06-11 02:48:02</t>
         </is>
       </c>
     </row>
@@ -5937,16 +5937,16 @@
         </is>
       </c>
       <c r="F22" t="n">
-        <v>4.3</v>
+        <v>4.2</v>
       </c>
       <c r="G22" t="n">
-        <v>5.2</v>
+        <v>4.9</v>
       </c>
       <c r="H22" t="n">
-        <v>1.85</v>
+        <v>1.86</v>
       </c>
       <c r="I22" t="n">
-        <v>2</v>
+        <v>2.04</v>
       </c>
       <c r="J22" t="n">
         <v>3.55</v>
@@ -5955,16 +5955,16 @@
         <v>4.2</v>
       </c>
       <c r="L22" t="n">
-        <v>1.31</v>
+        <v>1.38</v>
       </c>
       <c r="M22" t="n">
-        <v>1.07</v>
+        <v>1.06</v>
       </c>
       <c r="N22" t="n">
         <v>3.6</v>
       </c>
       <c r="O22" t="n">
-        <v>1.3</v>
+        <v>1.28</v>
       </c>
       <c r="P22" t="n">
         <v>1.9</v>
@@ -5976,19 +5976,19 @@
         <v>1.34</v>
       </c>
       <c r="S22" t="n">
-        <v>3.3</v>
+        <v>3.25</v>
       </c>
       <c r="T22" t="n">
-        <v>1.79</v>
+        <v>1.78</v>
       </c>
       <c r="U22" t="n">
-        <v>2</v>
+        <v>2.02</v>
       </c>
       <c r="V22" t="n">
-        <v>2</v>
+        <v>1.98</v>
       </c>
       <c r="W22" t="n">
-        <v>1.24</v>
+        <v>1.25</v>
       </c>
       <c r="X22" t="n">
         <v>17</v>
@@ -6015,19 +6015,19 @@
         <v>22</v>
       </c>
       <c r="AF22" t="n">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="AG22" t="n">
+        <v>18.5</v>
+      </c>
+      <c r="AH22" t="n">
         <v>19.5</v>
-      </c>
-      <c r="AH22" t="n">
-        <v>20</v>
       </c>
       <c r="AI22" t="n">
         <v>38</v>
       </c>
       <c r="AJ22" t="n">
-        <v>130</v>
+        <v>110</v>
       </c>
       <c r="AK22" t="n">
         <v>90</v>
@@ -6036,10 +6036,10 @@
         <v>70</v>
       </c>
       <c r="AM22" t="n">
-        <v>130</v>
+        <v>120</v>
       </c>
       <c r="AN22" t="n">
-        <v>95</v>
+        <v>80</v>
       </c>
       <c r="AO22" t="n">
         <v>14</v>
@@ -6081,86 +6081,86 @@
         <v>23</v>
       </c>
       <c r="BB22" t="n">
-        <v>7.6</v>
+        <v>8</v>
       </c>
       <c r="BC22" t="n">
-        <v>7.2</v>
+        <v>40</v>
       </c>
       <c r="BD22" t="n">
-        <v>7.2</v>
+        <v>7.8</v>
       </c>
       <c r="BE22" t="n">
-        <v>7.6</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BF22" t="n">
-        <v>7.4</v>
+        <v>7.8</v>
       </c>
       <c r="BG22" t="n">
         <v>11</v>
       </c>
       <c r="BH22" t="n">
-        <v>1000</v>
+        <v>3.55</v>
       </c>
       <c r="BI22" t="n">
-        <v>1.04</v>
+        <v>2.84</v>
       </c>
       <c r="BJ22" t="n">
-        <v>1000</v>
+        <v>10.5</v>
       </c>
       <c r="BK22" t="n">
-        <v>2.5</v>
+        <v>5.2</v>
       </c>
       <c r="BL22" t="n">
         <v>1000</v>
       </c>
       <c r="BM22" t="n">
-        <v>1.04</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BN22" t="n">
-        <v>1000</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BO22" t="n">
-        <v>2.38</v>
+        <v>4.6</v>
       </c>
       <c r="BP22" t="n">
-        <v>1000</v>
+        <v>40</v>
       </c>
       <c r="BQ22" t="n">
-        <v>2.84</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BR22" t="n">
-        <v>1000</v>
+        <v>50</v>
       </c>
       <c r="BS22" t="n">
-        <v>2.8</v>
+        <v>8.6</v>
       </c>
       <c r="BT22" t="n">
-        <v>1000</v>
+        <v>4.8</v>
       </c>
       <c r="BU22" t="n">
-        <v>2.02</v>
+        <v>4</v>
       </c>
       <c r="BV22" t="n">
-        <v>1000</v>
+        <v>14</v>
       </c>
       <c r="BW22" t="n">
-        <v>2.64</v>
+        <v>6</v>
       </c>
       <c r="BX22" t="n">
-        <v>1000</v>
+        <v>29</v>
       </c>
       <c r="BY22" t="n">
-        <v>2.8</v>
+        <v>7.6</v>
       </c>
       <c r="BZ22" t="n">
-        <v>1000</v>
+        <v>25</v>
       </c>
       <c r="CA22" t="n">
-        <v>2.8</v>
+        <v>7.4</v>
       </c>
       <c r="CB22" t="inlineStr">
         <is>
-          <t>2026-06-11 00:39:13</t>
+          <t>2026-06-11 02:48:02</t>
         </is>
       </c>
     </row>
@@ -6215,13 +6215,13 @@
         <v>1.01</v>
       </c>
       <c r="N23" t="n">
-        <v>1.26</v>
+        <v>1.99</v>
       </c>
       <c r="O23" t="n">
         <v>1.1</v>
       </c>
       <c r="P23" t="n">
-        <v>1.25</v>
+        <v>1.98</v>
       </c>
       <c r="Q23" t="n">
         <v>1.1</v>
@@ -6414,7 +6414,7 @@
       </c>
       <c r="CB23" t="inlineStr">
         <is>
-          <t>2026-06-11 00:39:13</t>
+          <t>2026-06-11 02:48:02</t>
         </is>
       </c>
     </row>
@@ -6668,7 +6668,7 @@
       </c>
       <c r="CB24" t="inlineStr">
         <is>
-          <t>2026-06-11 00:39:13</t>
+          <t>2026-06-11 02:48:02</t>
         </is>
       </c>
     </row>
@@ -6723,13 +6723,13 @@
         <v>1.01</v>
       </c>
       <c r="N25" t="n">
-        <v>1.3</v>
+        <v>1.31</v>
       </c>
       <c r="O25" t="n">
         <v>1.12</v>
       </c>
       <c r="P25" t="n">
-        <v>1.3</v>
+        <v>1.31</v>
       </c>
       <c r="Q25" t="n">
         <v>1.12</v>
@@ -6922,7 +6922,7 @@
       </c>
       <c r="CB25" t="inlineStr">
         <is>
-          <t>2026-06-11 00:39:13</t>
+          <t>2026-06-11 02:48:02</t>
         </is>
       </c>
     </row>
@@ -6956,13 +6956,13 @@
         <v>2.18</v>
       </c>
       <c r="G26" t="n">
-        <v>2.38</v>
+        <v>2.34</v>
       </c>
       <c r="H26" t="n">
         <v>3.6</v>
       </c>
       <c r="I26" t="n">
-        <v>4.2</v>
+        <v>4.1</v>
       </c>
       <c r="J26" t="n">
         <v>3.35</v>
@@ -6971,212 +6971,212 @@
         <v>3.45</v>
       </c>
       <c r="L26" t="n">
-        <v>1.01</v>
+        <v>1.43</v>
       </c>
       <c r="M26" t="n">
-        <v>1.09</v>
+        <v>1.1</v>
       </c>
       <c r="N26" t="n">
-        <v>2.4</v>
+        <v>3</v>
       </c>
       <c r="O26" t="n">
         <v>1.44</v>
       </c>
       <c r="P26" t="n">
-        <v>1.25</v>
+        <v>1.65</v>
       </c>
       <c r="Q26" t="n">
+        <v>2.28</v>
+      </c>
+      <c r="R26" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="S26" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="T26" t="n">
         <v>1.9</v>
       </c>
-      <c r="R26" t="n">
-        <v>1.19</v>
-      </c>
-      <c r="S26" t="n">
-        <v>3.75</v>
-      </c>
-      <c r="T26" t="n">
-        <v>1.11</v>
-      </c>
       <c r="U26" t="n">
-        <v>1.11</v>
+        <v>1.87</v>
       </c>
       <c r="V26" t="n">
-        <v>1.32</v>
+        <v>1.33</v>
       </c>
       <c r="W26" t="n">
-        <v>1.73</v>
+        <v>1.74</v>
       </c>
       <c r="X26" t="n">
-        <v>1000</v>
+        <v>12.5</v>
       </c>
       <c r="Y26" t="n">
-        <v>1000</v>
+        <v>970</v>
       </c>
       <c r="Z26" t="n">
-        <v>1000</v>
+        <v>28</v>
       </c>
       <c r="AA26" t="n">
-        <v>1000</v>
+        <v>100</v>
       </c>
       <c r="AB26" t="n">
-        <v>1000</v>
+        <v>8.6</v>
       </c>
       <c r="AC26" t="n">
-        <v>1000</v>
+        <v>970</v>
       </c>
       <c r="AD26" t="n">
-        <v>1000</v>
+        <v>970</v>
       </c>
       <c r="AE26" t="n">
-        <v>1000</v>
+        <v>60</v>
       </c>
       <c r="AF26" t="n">
-        <v>1000</v>
+        <v>970</v>
       </c>
       <c r="AG26" t="n">
-        <v>1000</v>
+        <v>970</v>
       </c>
       <c r="AH26" t="n">
-        <v>1000</v>
+        <v>950</v>
       </c>
       <c r="AI26" t="n">
-        <v>1000</v>
+        <v>75</v>
       </c>
       <c r="AJ26" t="n">
-        <v>1000</v>
+        <v>32</v>
       </c>
       <c r="AK26" t="n">
-        <v>1000</v>
+        <v>29</v>
       </c>
       <c r="AL26" t="n">
-        <v>1000</v>
+        <v>50</v>
       </c>
       <c r="AM26" t="n">
-        <v>1000</v>
+        <v>160</v>
       </c>
       <c r="AN26" t="n">
-        <v>1000</v>
+        <v>26</v>
       </c>
       <c r="AO26" t="n">
-        <v>1000</v>
+        <v>75</v>
       </c>
       <c r="AP26" t="n">
-        <v>1.01</v>
+        <v>5</v>
       </c>
       <c r="AQ26" t="n">
-        <v>1.01</v>
+        <v>5</v>
       </c>
       <c r="AR26" t="n">
-        <v>1.01</v>
+        <v>6.4</v>
       </c>
       <c r="AS26" t="n">
-        <v>1.01</v>
+        <v>7.8</v>
       </c>
       <c r="AT26" t="n">
-        <v>1.01</v>
+        <v>4.2</v>
       </c>
       <c r="AU26" t="n">
-        <v>1.01</v>
+        <v>6.4</v>
       </c>
       <c r="AV26" t="n">
-        <v>1.01</v>
+        <v>5.6</v>
       </c>
       <c r="AW26" t="n">
-        <v>1.01</v>
+        <v>7.4</v>
       </c>
       <c r="AX26" t="n">
-        <v>1.01</v>
+        <v>5.3</v>
       </c>
       <c r="AY26" t="n">
-        <v>1.01</v>
+        <v>4.9</v>
       </c>
       <c r="AZ26" t="n">
-        <v>1.01</v>
+        <v>6</v>
       </c>
       <c r="BA26" t="n">
-        <v>1.01</v>
+        <v>7.6</v>
       </c>
       <c r="BB26" t="n">
-        <v>1.01</v>
+        <v>6.6</v>
       </c>
       <c r="BC26" t="n">
-        <v>1.01</v>
+        <v>6.6</v>
       </c>
       <c r="BD26" t="n">
-        <v>1.01</v>
+        <v>7.2</v>
       </c>
       <c r="BE26" t="n">
-        <v>1.01</v>
+        <v>8</v>
       </c>
       <c r="BF26" t="n">
-        <v>1.01</v>
+        <v>6.4</v>
       </c>
       <c r="BG26" t="n">
-        <v>1.01</v>
+        <v>7.6</v>
       </c>
       <c r="BH26" t="n">
-        <v>1000</v>
+        <v>3.1</v>
       </c>
       <c r="BI26" t="n">
-        <v>1.04</v>
+        <v>2.5</v>
       </c>
       <c r="BJ26" t="n">
-        <v>1000</v>
+        <v>11</v>
       </c>
       <c r="BK26" t="n">
-        <v>1.04</v>
+        <v>5.4</v>
       </c>
       <c r="BL26" t="n">
         <v>1000</v>
       </c>
       <c r="BM26" t="n">
-        <v>1.04</v>
+        <v>10</v>
       </c>
       <c r="BN26" t="n">
-        <v>1000</v>
+        <v>5.1</v>
       </c>
       <c r="BO26" t="n">
-        <v>1.04</v>
+        <v>3.9</v>
       </c>
       <c r="BP26" t="n">
         <v>1000</v>
       </c>
       <c r="BQ26" t="n">
-        <v>1.04</v>
+        <v>6.6</v>
       </c>
       <c r="BR26" t="n">
         <v>1000</v>
       </c>
       <c r="BS26" t="n">
-        <v>1.04</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BT26" t="n">
-        <v>1000</v>
+        <v>7.2</v>
       </c>
       <c r="BU26" t="n">
-        <v>1.04</v>
+        <v>5.4</v>
       </c>
       <c r="BV26" t="n">
         <v>1000</v>
       </c>
       <c r="BW26" t="n">
-        <v>1.04</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BX26" t="n">
         <v>1000</v>
       </c>
       <c r="BY26" t="n">
-        <v>1.04</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BZ26" t="n">
         <v>1000</v>
       </c>
       <c r="CA26" t="n">
-        <v>1.04</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="CB26" t="inlineStr">
         <is>
-          <t>2026-06-11 00:39:13</t>
+          <t>2026-06-11 02:48:02</t>
         </is>
       </c>
     </row>
@@ -7430,7 +7430,7 @@
       </c>
       <c r="CB27" t="inlineStr">
         <is>
-          <t>2026-06-11 00:39:13</t>
+          <t>2026-06-11 02:48:02</t>
         </is>
       </c>
     </row>
@@ -7626,19 +7626,19 @@
         <v>3.75</v>
       </c>
       <c r="BI28" t="n">
-        <v>3.4</v>
+        <v>3</v>
       </c>
       <c r="BJ28" t="n">
         <v>9.199999999999999</v>
       </c>
       <c r="BK28" t="n">
-        <v>1.01</v>
+        <v>5.8</v>
       </c>
       <c r="BL28" t="n">
         <v>1000</v>
       </c>
       <c r="BM28" t="n">
-        <v>1.01</v>
+        <v>13.5</v>
       </c>
       <c r="BN28" t="n">
         <v>5</v>
@@ -7650,13 +7650,13 @@
         <v>14</v>
       </c>
       <c r="BQ28" t="n">
-        <v>1.01</v>
+        <v>7.4</v>
       </c>
       <c r="BR28" t="n">
         <v>26</v>
       </c>
       <c r="BS28" t="n">
-        <v>1.01</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BT28" t="n">
         <v>7.4</v>
@@ -7668,23 +7668,23 @@
         <v>30</v>
       </c>
       <c r="BW28" t="n">
-        <v>1.01</v>
+        <v>10</v>
       </c>
       <c r="BX28" t="n">
         <v>38</v>
       </c>
       <c r="BY28" t="n">
-        <v>1.01</v>
+        <v>11</v>
       </c>
       <c r="BZ28" t="n">
         <v>21</v>
       </c>
       <c r="CA28" t="n">
-        <v>1.01</v>
+        <v>9</v>
       </c>
       <c r="CB28" t="inlineStr">
         <is>
-          <t>2026-06-11 00:39:13</t>
+          <t>2026-06-11 02:48:02</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-06-12.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-06-12.xlsx
@@ -857,13 +857,13 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>1.15</v>
+        <v>1.18</v>
       </c>
       <c r="G2" t="n">
         <v>1000</v>
       </c>
       <c r="H2" t="n">
-        <v>1.15</v>
+        <v>1.18</v>
       </c>
       <c r="I2" t="n">
         <v>1000</v>
@@ -1080,7 +1080,7 @@
       </c>
       <c r="CB2" t="inlineStr">
         <is>
-          <t>2026-06-11 02:48:02</t>
+          <t>2026-06-11 04:56:51</t>
         </is>
       </c>
     </row>
@@ -1135,10 +1135,10 @@
         <v>1.01</v>
       </c>
       <c r="N3" t="n">
-        <v>1.32</v>
+        <v>1.1</v>
       </c>
       <c r="O3" t="n">
-        <v>1.22</v>
+        <v>1.21</v>
       </c>
       <c r="P3" t="n">
         <v>1.32</v>
@@ -1334,7 +1334,7 @@
       </c>
       <c r="CB3" t="inlineStr">
         <is>
-          <t>2026-06-11 02:48:02</t>
+          <t>2026-06-11 04:56:51</t>
         </is>
       </c>
     </row>
@@ -1365,13 +1365,13 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>1.15</v>
+        <v>1.18</v>
       </c>
       <c r="G4" t="n">
         <v>1000</v>
       </c>
       <c r="H4" t="n">
-        <v>1.15</v>
+        <v>1.18</v>
       </c>
       <c r="I4" t="n">
         <v>1000</v>
@@ -1389,7 +1389,7 @@
         <v>1.01</v>
       </c>
       <c r="N4" t="n">
-        <v>1.24</v>
+        <v>1.29</v>
       </c>
       <c r="O4" t="n">
         <v>1.02</v>
@@ -1398,13 +1398,13 @@
         <v>1.24</v>
       </c>
       <c r="Q4" t="n">
-        <v>1.53</v>
+        <v>1.52</v>
       </c>
       <c r="R4" t="n">
         <v>1.18</v>
       </c>
       <c r="S4" t="n">
-        <v>1.53</v>
+        <v>1.52</v>
       </c>
       <c r="T4" t="n">
         <v>1.11</v>
@@ -1413,7 +1413,7 @@
         <v>1.11</v>
       </c>
       <c r="V4" t="n">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="W4" t="n">
         <v>1.02</v>
@@ -1588,7 +1588,7 @@
       </c>
       <c r="CB4" t="inlineStr">
         <is>
-          <t>2026-06-11 02:48:02</t>
+          <t>2026-06-11 04:56:51</t>
         </is>
       </c>
     </row>
@@ -1643,22 +1643,22 @@
         <v>1.01</v>
       </c>
       <c r="N5" t="n">
-        <v>1.28</v>
+        <v>1.3</v>
       </c>
       <c r="O5" t="n">
         <v>1.02</v>
       </c>
       <c r="P5" t="n">
-        <v>1.28</v>
+        <v>1.3</v>
       </c>
       <c r="Q5" t="n">
-        <v>1.55</v>
+        <v>1.51</v>
       </c>
       <c r="R5" t="n">
         <v>1.18</v>
       </c>
       <c r="S5" t="n">
-        <v>1.55</v>
+        <v>1.51</v>
       </c>
       <c r="T5" t="n">
         <v>1.11</v>
@@ -1842,7 +1842,7 @@
       </c>
       <c r="CB5" t="inlineStr">
         <is>
-          <t>2026-06-11 02:48:02</t>
+          <t>2026-06-11 04:56:51</t>
         </is>
       </c>
     </row>
@@ -1873,13 +1873,13 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>1.15</v>
+        <v>1.18</v>
       </c>
       <c r="G6" t="n">
         <v>1000</v>
       </c>
       <c r="H6" t="n">
-        <v>1.15</v>
+        <v>1.18</v>
       </c>
       <c r="I6" t="n">
         <v>1000</v>
@@ -1903,7 +1903,7 @@
         <v>1.22</v>
       </c>
       <c r="P6" t="n">
-        <v>1.36</v>
+        <v>1.25</v>
       </c>
       <c r="Q6" t="n">
         <v>1.22</v>
@@ -2096,7 +2096,7 @@
       </c>
       <c r="CB6" t="inlineStr">
         <is>
-          <t>2026-06-11 02:48:02</t>
+          <t>2026-06-11 04:56:51</t>
         </is>
       </c>
     </row>
@@ -2127,13 +2127,13 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>1.14</v>
+        <v>1.17</v>
       </c>
       <c r="G7" t="n">
         <v>1000</v>
       </c>
       <c r="H7" t="n">
-        <v>1.14</v>
+        <v>1.17</v>
       </c>
       <c r="I7" t="n">
         <v>1000</v>
@@ -2350,7 +2350,7 @@
       </c>
       <c r="CB7" t="inlineStr">
         <is>
-          <t>2026-06-11 02:48:02</t>
+          <t>2026-06-11 04:56:51</t>
         </is>
       </c>
     </row>
@@ -2381,19 +2381,19 @@
         </is>
       </c>
       <c r="F8" t="n">
-        <v>1.04</v>
+        <v>1.23</v>
       </c>
       <c r="G8" t="n">
         <v>1000</v>
       </c>
       <c r="H8" t="n">
-        <v>1.04</v>
+        <v>1.17</v>
       </c>
       <c r="I8" t="n">
         <v>1000</v>
       </c>
       <c r="J8" t="n">
-        <v>1.1</v>
+        <v>1.37</v>
       </c>
       <c r="K8" t="n">
         <v>1000</v>
@@ -2604,7 +2604,7 @@
       </c>
       <c r="CB8" t="inlineStr">
         <is>
-          <t>2026-06-11 02:48:02</t>
+          <t>2026-06-11 04:56:51</t>
         </is>
       </c>
     </row>
@@ -2858,7 +2858,7 @@
       </c>
       <c r="CB9" t="inlineStr">
         <is>
-          <t>2026-06-11 02:48:02</t>
+          <t>2026-06-11 04:56:51</t>
         </is>
       </c>
     </row>
@@ -2889,22 +2889,22 @@
         </is>
       </c>
       <c r="F10" t="n">
-        <v>1.13</v>
+        <v>2.12</v>
       </c>
       <c r="G10" t="n">
-        <v>1000</v>
+        <v>2.62</v>
       </c>
       <c r="H10" t="n">
-        <v>1.13</v>
+        <v>3.3</v>
       </c>
       <c r="I10" t="n">
-        <v>1000</v>
+        <v>4.8</v>
       </c>
       <c r="J10" t="n">
-        <v>1.1</v>
+        <v>2.78</v>
       </c>
       <c r="K10" t="n">
-        <v>1000</v>
+        <v>4.4</v>
       </c>
       <c r="L10" t="n">
         <v>1.01</v>
@@ -2913,22 +2913,22 @@
         <v>1.01</v>
       </c>
       <c r="N10" t="n">
-        <v>1.25</v>
+        <v>2.28</v>
       </c>
       <c r="O10" t="n">
-        <v>1.05</v>
+        <v>1.46</v>
       </c>
       <c r="P10" t="n">
-        <v>1.24</v>
+        <v>1.43</v>
       </c>
       <c r="Q10" t="n">
-        <v>1.44</v>
+        <v>2.48</v>
       </c>
       <c r="R10" t="n">
         <v>1.18</v>
       </c>
       <c r="S10" t="n">
-        <v>1.44</v>
+        <v>3</v>
       </c>
       <c r="T10" t="n">
         <v>1.11</v>
@@ -2937,10 +2937,10 @@
         <v>1.11</v>
       </c>
       <c r="V10" t="n">
-        <v>1.02</v>
+        <v>1.26</v>
       </c>
       <c r="W10" t="n">
-        <v>1.02</v>
+        <v>1.61</v>
       </c>
       <c r="X10" t="n">
         <v>1000</v>
@@ -3051,7 +3051,7 @@
         <v>1.01</v>
       </c>
       <c r="BH10" t="n">
-        <v>1000</v>
+        <v>3.2</v>
       </c>
       <c r="BI10" t="n">
         <v>1.04</v>
@@ -3060,59 +3060,59 @@
         <v>1000</v>
       </c>
       <c r="BK10" t="n">
-        <v>1.04</v>
+        <v>1.47</v>
       </c>
       <c r="BL10" t="n">
         <v>1000</v>
       </c>
       <c r="BM10" t="n">
-        <v>1.04</v>
+        <v>1.47</v>
       </c>
       <c r="BN10" t="n">
         <v>1000</v>
       </c>
       <c r="BO10" t="n">
-        <v>1.04</v>
+        <v>1.47</v>
       </c>
       <c r="BP10" t="n">
         <v>1000</v>
       </c>
       <c r="BQ10" t="n">
-        <v>1.04</v>
+        <v>1.47</v>
       </c>
       <c r="BR10" t="n">
         <v>1000</v>
       </c>
       <c r="BS10" t="n">
-        <v>1.04</v>
+        <v>1.47</v>
       </c>
       <c r="BT10" t="n">
         <v>1000</v>
       </c>
       <c r="BU10" t="n">
-        <v>1.04</v>
+        <v>1.47</v>
       </c>
       <c r="BV10" t="n">
         <v>1000</v>
       </c>
       <c r="BW10" t="n">
-        <v>1.04</v>
+        <v>1.47</v>
       </c>
       <c r="BX10" t="n">
         <v>1000</v>
       </c>
       <c r="BY10" t="n">
-        <v>1.04</v>
+        <v>1.47</v>
       </c>
       <c r="BZ10" t="n">
         <v>1000</v>
       </c>
       <c r="CA10" t="n">
-        <v>1.04</v>
+        <v>1.47</v>
       </c>
       <c r="CB10" t="inlineStr">
         <is>
-          <t>2026-06-11 02:48:02</t>
+          <t>2026-06-11 04:56:51</t>
         </is>
       </c>
     </row>
@@ -3143,13 +3143,13 @@
         </is>
       </c>
       <c r="F11" t="n">
-        <v>1.13</v>
+        <v>1.16</v>
       </c>
       <c r="G11" t="n">
         <v>1000</v>
       </c>
       <c r="H11" t="n">
-        <v>1.15</v>
+        <v>1.18</v>
       </c>
       <c r="I11" t="n">
         <v>1000</v>
@@ -3167,13 +3167,13 @@
         <v>1.01</v>
       </c>
       <c r="N11" t="n">
-        <v>1.3</v>
+        <v>1.32</v>
       </c>
       <c r="O11" t="n">
         <v>1.02</v>
       </c>
       <c r="P11" t="n">
-        <v>1.3</v>
+        <v>1.32</v>
       </c>
       <c r="Q11" t="n">
         <v>1.56</v>
@@ -3191,7 +3191,7 @@
         <v>1.11</v>
       </c>
       <c r="V11" t="n">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="W11" t="n">
         <v>1.02</v>
@@ -3366,7 +3366,7 @@
       </c>
       <c r="CB11" t="inlineStr">
         <is>
-          <t>2026-06-11 02:48:02</t>
+          <t>2026-06-11 04:56:51</t>
         </is>
       </c>
     </row>
@@ -3409,7 +3409,7 @@
         <v>1000</v>
       </c>
       <c r="J12" t="n">
-        <v>1.12</v>
+        <v>1.15</v>
       </c>
       <c r="K12" t="n">
         <v>1000</v>
@@ -3620,7 +3620,7 @@
       </c>
       <c r="CB12" t="inlineStr">
         <is>
-          <t>2026-06-11 02:48:02</t>
+          <t>2026-06-11 04:56:51</t>
         </is>
       </c>
     </row>
@@ -3651,13 +3651,13 @@
         </is>
       </c>
       <c r="F13" t="n">
-        <v>1.12</v>
+        <v>1.15</v>
       </c>
       <c r="G13" t="n">
         <v>1000</v>
       </c>
       <c r="H13" t="n">
-        <v>1.12</v>
+        <v>1.15</v>
       </c>
       <c r="I13" t="n">
         <v>1000</v>
@@ -3874,7 +3874,7 @@
       </c>
       <c r="CB13" t="inlineStr">
         <is>
-          <t>2026-06-11 02:48:02</t>
+          <t>2026-06-11 04:56:51</t>
         </is>
       </c>
     </row>
@@ -3908,7 +3908,7 @@
         <v>1.46</v>
       </c>
       <c r="G14" t="n">
-        <v>990</v>
+        <v>1000</v>
       </c>
       <c r="H14" t="n">
         <v>1.46</v>
@@ -4128,7 +4128,7 @@
       </c>
       <c r="CB14" t="inlineStr">
         <is>
-          <t>2026-06-11 02:48:02</t>
+          <t>2026-06-11 04:56:51</t>
         </is>
       </c>
     </row>
@@ -4159,31 +4159,31 @@
         </is>
       </c>
       <c r="F15" t="n">
-        <v>2.76</v>
+        <v>2.74</v>
       </c>
       <c r="G15" t="n">
-        <v>3.3</v>
+        <v>3.4</v>
       </c>
       <c r="H15" t="n">
-        <v>2</v>
+        <v>2.36</v>
       </c>
       <c r="I15" t="n">
-        <v>2.92</v>
+        <v>2.88</v>
       </c>
       <c r="J15" t="n">
         <v>3.3</v>
       </c>
       <c r="K15" t="n">
-        <v>1000</v>
+        <v>4.7</v>
       </c>
       <c r="L15" t="n">
         <v>1.01</v>
       </c>
       <c r="M15" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="N15" t="n">
-        <v>2.44</v>
+        <v>2.46</v>
       </c>
       <c r="O15" t="n">
         <v>1.2</v>
@@ -4192,7 +4192,7 @@
         <v>2.36</v>
       </c>
       <c r="Q15" t="n">
-        <v>1.2</v>
+        <v>1.39</v>
       </c>
       <c r="R15" t="n">
         <v>1.39</v>
@@ -4201,16 +4201,16 @@
         <v>2.16</v>
       </c>
       <c r="T15" t="n">
-        <v>1.3</v>
+        <v>1.48</v>
       </c>
       <c r="U15" t="n">
-        <v>1.98</v>
+        <v>2.28</v>
       </c>
       <c r="V15" t="n">
-        <v>1.52</v>
+        <v>1.53</v>
       </c>
       <c r="W15" t="n">
-        <v>1.44</v>
+        <v>1.42</v>
       </c>
       <c r="X15" t="n">
         <v>1000</v>
@@ -4382,7 +4382,7 @@
       </c>
       <c r="CB15" t="inlineStr">
         <is>
-          <t>2026-06-11 02:48:02</t>
+          <t>2026-06-11 04:56:51</t>
         </is>
       </c>
     </row>
@@ -4413,7 +4413,7 @@
         </is>
       </c>
       <c r="F16" t="n">
-        <v>1.35</v>
+        <v>1.36</v>
       </c>
       <c r="G16" t="n">
         <v>1.42</v>
@@ -4422,13 +4422,13 @@
         <v>10.5</v>
       </c>
       <c r="I16" t="n">
-        <v>13</v>
+        <v>12.5</v>
       </c>
       <c r="J16" t="n">
         <v>4.9</v>
       </c>
       <c r="K16" t="n">
-        <v>5.6</v>
+        <v>5.5</v>
       </c>
       <c r="L16" t="n">
         <v>1.01</v>
@@ -4446,19 +4446,19 @@
         <v>2.06</v>
       </c>
       <c r="Q16" t="n">
-        <v>1.83</v>
+        <v>1.84</v>
       </c>
       <c r="R16" t="n">
         <v>1.38</v>
       </c>
       <c r="S16" t="n">
-        <v>3.1</v>
+        <v>3.15</v>
       </c>
       <c r="T16" t="n">
-        <v>2.22</v>
+        <v>2.2</v>
       </c>
       <c r="U16" t="n">
-        <v>1.67</v>
+        <v>1.73</v>
       </c>
       <c r="V16" t="n">
         <v>1.08</v>
@@ -4470,37 +4470,37 @@
         <v>21</v>
       </c>
       <c r="Y16" t="n">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="Z16" t="n">
         <v>130</v>
       </c>
       <c r="AA16" t="n">
-        <v>620</v>
+        <v>570</v>
       </c>
       <c r="AB16" t="n">
-        <v>9</v>
+        <v>7.8</v>
       </c>
       <c r="AC16" t="n">
-        <v>14.5</v>
+        <v>14</v>
       </c>
       <c r="AD16" t="n">
-        <v>55</v>
+        <v>50</v>
       </c>
       <c r="AE16" t="n">
-        <v>270</v>
+        <v>250</v>
       </c>
       <c r="AF16" t="n">
         <v>9.199999999999999</v>
       </c>
       <c r="AG16" t="n">
-        <v>11.5</v>
+        <v>13</v>
       </c>
       <c r="AH16" t="n">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="AI16" t="n">
-        <v>220</v>
+        <v>210</v>
       </c>
       <c r="AJ16" t="n">
         <v>13.5</v>
@@ -4509,70 +4509,70 @@
         <v>19.5</v>
       </c>
       <c r="AL16" t="n">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="AM16" t="n">
-        <v>260</v>
+        <v>250</v>
       </c>
       <c r="AN16" t="n">
-        <v>8.199999999999999</v>
+        <v>7.4</v>
       </c>
       <c r="AO16" t="n">
-        <v>450</v>
+        <v>410</v>
       </c>
       <c r="AP16" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="AQ16" t="n">
-        <v>4</v>
+        <v>21</v>
       </c>
       <c r="AR16" t="n">
-        <v>4.4</v>
+        <v>5</v>
       </c>
       <c r="AS16" t="n">
-        <v>4.5</v>
+        <v>5.2</v>
       </c>
       <c r="AT16" t="n">
-        <v>5.6</v>
+        <v>6.4</v>
       </c>
       <c r="AU16" t="n">
-        <v>8.800000000000001</v>
+        <v>10</v>
       </c>
       <c r="AV16" t="n">
-        <v>30</v>
+        <v>4.7</v>
       </c>
       <c r="AW16" t="n">
-        <v>4.4</v>
+        <v>5.1</v>
       </c>
       <c r="AX16" t="n">
         <v>6.6</v>
       </c>
       <c r="AY16" t="n">
-        <v>7.8</v>
+        <v>9</v>
       </c>
       <c r="AZ16" t="n">
-        <v>4</v>
+        <v>4.6</v>
       </c>
       <c r="BA16" t="n">
-        <v>4.4</v>
+        <v>5.1</v>
       </c>
       <c r="BB16" t="n">
-        <v>9.199999999999999</v>
+        <v>9.4</v>
       </c>
       <c r="BC16" t="n">
-        <v>11.5</v>
+        <v>12</v>
       </c>
       <c r="BD16" t="n">
-        <v>4.2</v>
+        <v>4.8</v>
       </c>
       <c r="BE16" t="n">
-        <v>4.4</v>
+        <v>5.1</v>
       </c>
       <c r="BF16" t="n">
-        <v>5.1</v>
+        <v>6</v>
       </c>
       <c r="BG16" t="n">
-        <v>4.5</v>
+        <v>5.2</v>
       </c>
       <c r="BH16" t="n">
         <v>1000</v>
@@ -4584,7 +4584,7 @@
         <v>1000</v>
       </c>
       <c r="BK16" t="n">
-        <v>1.04</v>
+        <v>1.58</v>
       </c>
       <c r="BL16" t="n">
         <v>1000</v>
@@ -4596,13 +4596,13 @@
         <v>1000</v>
       </c>
       <c r="BO16" t="n">
-        <v>1.04</v>
+        <v>1.3</v>
       </c>
       <c r="BP16" t="n">
         <v>1000</v>
       </c>
       <c r="BQ16" t="n">
-        <v>1.04</v>
+        <v>1.5</v>
       </c>
       <c r="BR16" t="n">
         <v>1000</v>
@@ -4636,7 +4636,7 @@
       </c>
       <c r="CB16" t="inlineStr">
         <is>
-          <t>2026-06-11 02:48:02</t>
+          <t>2026-06-11 04:56:51</t>
         </is>
       </c>
     </row>
@@ -4667,19 +4667,19 @@
         </is>
       </c>
       <c r="F17" t="n">
-        <v>2.26</v>
+        <v>2.2</v>
       </c>
       <c r="G17" t="n">
-        <v>2.44</v>
+        <v>2.42</v>
       </c>
       <c r="H17" t="n">
-        <v>3.2</v>
+        <v>3.25</v>
       </c>
       <c r="I17" t="n">
-        <v>3.5</v>
+        <v>3.6</v>
       </c>
       <c r="J17" t="n">
-        <v>3.5</v>
+        <v>3.55</v>
       </c>
       <c r="K17" t="n">
         <v>3.9</v>
@@ -4691,7 +4691,7 @@
         <v>1.06</v>
       </c>
       <c r="N17" t="n">
-        <v>3.95</v>
+        <v>3.9</v>
       </c>
       <c r="O17" t="n">
         <v>1.28</v>
@@ -4700,7 +4700,7 @@
         <v>2.02</v>
       </c>
       <c r="Q17" t="n">
-        <v>1.83</v>
+        <v>1.84</v>
       </c>
       <c r="R17" t="n">
         <v>1.39</v>
@@ -4709,82 +4709,82 @@
         <v>3.1</v>
       </c>
       <c r="T17" t="n">
-        <v>1.69</v>
+        <v>1.67</v>
       </c>
       <c r="U17" t="n">
-        <v>2.22</v>
+        <v>2.2</v>
       </c>
       <c r="V17" t="n">
-        <v>1.4</v>
+        <v>1.39</v>
       </c>
       <c r="W17" t="n">
-        <v>1.69</v>
+        <v>1.72</v>
       </c>
       <c r="X17" t="n">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="Y17" t="n">
         <v>15</v>
       </c>
       <c r="Z17" t="n">
-        <v>25</v>
+        <v>32</v>
       </c>
       <c r="AA17" t="n">
-        <v>85</v>
+        <v>65</v>
       </c>
       <c r="AB17" t="n">
-        <v>12</v>
+        <v>11.5</v>
       </c>
       <c r="AC17" t="n">
-        <v>8.800000000000001</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AD17" t="n">
-        <v>15</v>
+        <v>15.5</v>
       </c>
       <c r="AE17" t="n">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="AF17" t="n">
-        <v>16.5</v>
+        <v>18.5</v>
       </c>
       <c r="AG17" t="n">
         <v>12</v>
       </c>
       <c r="AH17" t="n">
-        <v>17.5</v>
+        <v>21</v>
       </c>
       <c r="AI17" t="n">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="AJ17" t="n">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="AK17" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="AL17" t="n">
-        <v>50</v>
+        <v>42</v>
       </c>
       <c r="AM17" t="n">
-        <v>100</v>
+        <v>95</v>
       </c>
       <c r="AN17" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="AO17" t="n">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="AP17" t="n">
         <v>13.5</v>
       </c>
       <c r="AQ17" t="n">
-        <v>11.5</v>
+        <v>12</v>
       </c>
       <c r="AR17" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AS17" t="n">
-        <v>7.4</v>
+        <v>40</v>
       </c>
       <c r="AT17" t="n">
         <v>9.4</v>
@@ -4796,37 +4796,37 @@
         <v>12</v>
       </c>
       <c r="AW17" t="n">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="AX17" t="n">
-        <v>13.5</v>
+        <v>13</v>
       </c>
       <c r="AY17" t="n">
-        <v>9.6</v>
+        <v>9.4</v>
       </c>
       <c r="AZ17" t="n">
         <v>14</v>
       </c>
       <c r="BA17" t="n">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="BB17" t="n">
         <v>23</v>
       </c>
       <c r="BC17" t="n">
-        <v>20</v>
+        <v>19.5</v>
       </c>
       <c r="BD17" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="BE17" t="n">
-        <v>7.8</v>
+        <v>5.9</v>
       </c>
       <c r="BF17" t="n">
-        <v>14.5</v>
+        <v>13.5</v>
       </c>
       <c r="BG17" t="n">
-        <v>19</v>
+        <v>24</v>
       </c>
       <c r="BH17" t="n">
         <v>1000</v>
@@ -4838,7 +4838,7 @@
         <v>1000</v>
       </c>
       <c r="BK17" t="n">
-        <v>1.5</v>
+        <v>1.52</v>
       </c>
       <c r="BL17" t="n">
         <v>1000</v>
@@ -4850,13 +4850,13 @@
         <v>1000</v>
       </c>
       <c r="BO17" t="n">
-        <v>1.39</v>
+        <v>1.41</v>
       </c>
       <c r="BP17" t="n">
         <v>1000</v>
       </c>
       <c r="BQ17" t="n">
-        <v>1.58</v>
+        <v>1.6</v>
       </c>
       <c r="BR17" t="n">
         <v>1000</v>
@@ -4868,7 +4868,7 @@
         <v>1000</v>
       </c>
       <c r="BU17" t="n">
-        <v>1.44</v>
+        <v>1.46</v>
       </c>
       <c r="BV17" t="n">
         <v>1000</v>
@@ -4890,7 +4890,7 @@
       </c>
       <c r="CB17" t="inlineStr">
         <is>
-          <t>2026-06-11 02:48:02</t>
+          <t>2026-06-11 04:56:51</t>
         </is>
       </c>
     </row>
@@ -4945,7 +4945,7 @@
         <v>1.09</v>
       </c>
       <c r="N18" t="n">
-        <v>3</v>
+        <v>3.1</v>
       </c>
       <c r="O18" t="n">
         <v>1.4</v>
@@ -4957,19 +4957,19 @@
         <v>2.2</v>
       </c>
       <c r="R18" t="n">
-        <v>1.26</v>
+        <v>1.27</v>
       </c>
       <c r="S18" t="n">
         <v>4.1</v>
       </c>
       <c r="T18" t="n">
-        <v>1.87</v>
+        <v>1.86</v>
       </c>
       <c r="U18" t="n">
         <v>1.96</v>
       </c>
       <c r="V18" t="n">
-        <v>1.61</v>
+        <v>1.6</v>
       </c>
       <c r="W18" t="n">
         <v>1.4</v>
@@ -4978,58 +4978,58 @@
         <v>12</v>
       </c>
       <c r="Y18" t="n">
-        <v>9.6</v>
+        <v>9.4</v>
       </c>
       <c r="Z18" t="n">
-        <v>18</v>
+        <v>16.5</v>
       </c>
       <c r="AA18" t="n">
-        <v>44</v>
+        <v>40</v>
       </c>
       <c r="AB18" t="n">
         <v>11.5</v>
       </c>
       <c r="AC18" t="n">
-        <v>8.6</v>
+        <v>8</v>
       </c>
       <c r="AD18" t="n">
-        <v>14</v>
+        <v>12.5</v>
       </c>
       <c r="AE18" t="n">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="AF18" t="n">
         <v>23</v>
       </c>
       <c r="AG18" t="n">
-        <v>16.5</v>
+        <v>15</v>
       </c>
       <c r="AH18" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AI18" t="n">
+        <v>50</v>
+      </c>
+      <c r="AJ18" t="n">
+        <v>65</v>
+      </c>
+      <c r="AK18" t="n">
+        <v>44</v>
+      </c>
+      <c r="AL18" t="n">
         <v>60</v>
       </c>
-      <c r="AJ18" t="n">
-        <v>70</v>
-      </c>
-      <c r="AK18" t="n">
-        <v>50</v>
-      </c>
-      <c r="AL18" t="n">
-        <v>70</v>
-      </c>
       <c r="AM18" t="n">
-        <v>150</v>
+        <v>140</v>
       </c>
       <c r="AN18" t="n">
-        <v>55</v>
+        <v>48</v>
       </c>
       <c r="AO18" t="n">
-        <v>34</v>
+        <v>30</v>
       </c>
       <c r="AP18" t="n">
-        <v>9.6</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AQ18" t="n">
         <v>7.8</v>
@@ -5038,10 +5038,10 @@
         <v>13</v>
       </c>
       <c r="AS18" t="n">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="AT18" t="n">
-        <v>9.199999999999999</v>
+        <v>9.4</v>
       </c>
       <c r="AU18" t="n">
         <v>6.4</v>
@@ -5050,37 +5050,37 @@
         <v>10</v>
       </c>
       <c r="AW18" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="AX18" t="n">
-        <v>18.5</v>
+        <v>18</v>
       </c>
       <c r="AY18" t="n">
-        <v>12</v>
+        <v>11.5</v>
       </c>
       <c r="AZ18" t="n">
-        <v>16.5</v>
+        <v>16</v>
       </c>
       <c r="BA18" t="n">
-        <v>38</v>
+        <v>7.8</v>
       </c>
       <c r="BB18" t="n">
-        <v>6</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BC18" t="n">
-        <v>34</v>
+        <v>7.8</v>
       </c>
       <c r="BD18" t="n">
-        <v>6</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BE18" t="n">
-        <v>6.2</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BF18" t="n">
-        <v>5.8</v>
+        <v>7.8</v>
       </c>
       <c r="BG18" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="BH18" t="n">
         <v>3.2</v>
@@ -5098,7 +5098,7 @@
         <v>1000</v>
       </c>
       <c r="BM18" t="n">
-        <v>9.6</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BN18" t="n">
         <v>6.6</v>
@@ -5113,10 +5113,10 @@
         <v>7.6</v>
       </c>
       <c r="BR18" t="n">
-        <v>46</v>
+        <v>1000</v>
       </c>
       <c r="BS18" t="n">
-        <v>8.4</v>
+        <v>8.6</v>
       </c>
       <c r="BT18" t="n">
         <v>5.5</v>
@@ -5128,13 +5128,13 @@
         <v>21</v>
       </c>
       <c r="BW18" t="n">
-        <v>6.8</v>
+        <v>7</v>
       </c>
       <c r="BX18" t="n">
         <v>1000</v>
       </c>
       <c r="BY18" t="n">
-        <v>8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BZ18" t="n">
         <v>1000</v>
@@ -5144,7 +5144,7 @@
       </c>
       <c r="CB18" t="inlineStr">
         <is>
-          <t>2026-06-11 02:48:02</t>
+          <t>2026-06-11 04:56:51</t>
         </is>
       </c>
     </row>
@@ -5175,28 +5175,28 @@
         </is>
       </c>
       <c r="F19" t="n">
-        <v>3.7</v>
+        <v>3.4</v>
       </c>
       <c r="G19" t="n">
-        <v>5.4</v>
+        <v>5.6</v>
       </c>
       <c r="H19" t="n">
         <v>1.75</v>
       </c>
       <c r="I19" t="n">
-        <v>2.18</v>
+        <v>2.26</v>
       </c>
       <c r="J19" t="n">
-        <v>3.25</v>
+        <v>3.3</v>
       </c>
       <c r="K19" t="n">
-        <v>6.4</v>
+        <v>7.2</v>
       </c>
       <c r="L19" t="n">
         <v>1.01</v>
       </c>
       <c r="M19" t="n">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="N19" t="n">
         <v>4.1</v>
@@ -5208,13 +5208,13 @@
         <v>1.94</v>
       </c>
       <c r="Q19" t="n">
-        <v>1.61</v>
+        <v>1.63</v>
       </c>
       <c r="R19" t="n">
-        <v>1.26</v>
+        <v>1.32</v>
       </c>
       <c r="S19" t="n">
-        <v>2.3</v>
+        <v>2.32</v>
       </c>
       <c r="T19" t="n">
         <v>1.37</v>
@@ -5223,10 +5223,10 @@
         <v>1.73</v>
       </c>
       <c r="V19" t="n">
-        <v>1.85</v>
+        <v>1.79</v>
       </c>
       <c r="W19" t="n">
-        <v>1.22</v>
+        <v>1.21</v>
       </c>
       <c r="X19" t="n">
         <v>1000</v>
@@ -5398,7 +5398,7 @@
       </c>
       <c r="CB19" t="inlineStr">
         <is>
-          <t>2026-06-11 02:48:02</t>
+          <t>2026-06-11 04:56:51</t>
         </is>
       </c>
     </row>
@@ -5435,7 +5435,7 @@
         <v>4.6</v>
       </c>
       <c r="H20" t="n">
-        <v>1.86</v>
+        <v>1.88</v>
       </c>
       <c r="I20" t="n">
         <v>2.06</v>
@@ -5444,10 +5444,10 @@
         <v>3.7</v>
       </c>
       <c r="K20" t="n">
-        <v>4.4</v>
+        <v>4.2</v>
       </c>
       <c r="L20" t="n">
-        <v>1.25</v>
+        <v>1.23</v>
       </c>
       <c r="M20" t="n">
         <v>1.05</v>
@@ -5456,25 +5456,25 @@
         <v>4.5</v>
       </c>
       <c r="O20" t="n">
-        <v>1.22</v>
+        <v>1.23</v>
       </c>
       <c r="P20" t="n">
         <v>2.24</v>
       </c>
       <c r="Q20" t="n">
-        <v>1.66</v>
+        <v>1.68</v>
       </c>
       <c r="R20" t="n">
         <v>1.53</v>
       </c>
       <c r="S20" t="n">
-        <v>2.48</v>
+        <v>2.52</v>
       </c>
       <c r="T20" t="n">
-        <v>1.62</v>
+        <v>1.63</v>
       </c>
       <c r="U20" t="n">
-        <v>2.3</v>
+        <v>2.32</v>
       </c>
       <c r="V20" t="n">
         <v>1.95</v>
@@ -5510,7 +5510,7 @@
         <v>36</v>
       </c>
       <c r="AG20" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AH20" t="n">
         <v>17.5</v>
@@ -5522,13 +5522,13 @@
         <v>110</v>
       </c>
       <c r="AK20" t="n">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="AL20" t="n">
         <v>50</v>
       </c>
       <c r="AM20" t="n">
-        <v>85</v>
+        <v>70</v>
       </c>
       <c r="AN20" t="n">
         <v>38</v>
@@ -5540,7 +5540,7 @@
         <v>17</v>
       </c>
       <c r="AQ20" t="n">
-        <v>9.4</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AR20" t="n">
         <v>11</v>
@@ -5549,7 +5549,7 @@
         <v>18</v>
       </c>
       <c r="AT20" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AU20" t="n">
         <v>8.199999999999999</v>
@@ -5561,7 +5561,7 @@
         <v>12</v>
       </c>
       <c r="AX20" t="n">
-        <v>6.4</v>
+        <v>6.6</v>
       </c>
       <c r="AY20" t="n">
         <v>13.5</v>
@@ -5570,22 +5570,22 @@
         <v>10.5</v>
       </c>
       <c r="BA20" t="n">
-        <v>18.5</v>
+        <v>6.6</v>
       </c>
       <c r="BB20" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="BC20" t="n">
+        <v>34</v>
+      </c>
+      <c r="BD20" t="n">
+        <v>7</v>
+      </c>
+      <c r="BE20" t="n">
         <v>7.4</v>
       </c>
-      <c r="BC20" t="n">
-        <v>28</v>
-      </c>
-      <c r="BD20" t="n">
-        <v>29</v>
-      </c>
-      <c r="BE20" t="n">
-        <v>42</v>
-      </c>
       <c r="BF20" t="n">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="BG20" t="n">
         <v>7.2</v>
@@ -5597,10 +5597,10 @@
         <v>1.93</v>
       </c>
       <c r="BJ20" t="n">
-        <v>13.5</v>
+        <v>13</v>
       </c>
       <c r="BK20" t="n">
-        <v>1.69</v>
+        <v>1.68</v>
       </c>
       <c r="BL20" t="n">
         <v>1000</v>
@@ -5612,19 +5612,19 @@
         <v>11</v>
       </c>
       <c r="BO20" t="n">
-        <v>1.65</v>
+        <v>4.9</v>
       </c>
       <c r="BP20" t="n">
         <v>46</v>
       </c>
       <c r="BQ20" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="BR20" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BS20" t="n">
         <v>1.86</v>
-      </c>
-      <c r="BR20" t="n">
-        <v>50</v>
-      </c>
-      <c r="BS20" t="n">
-        <v>1.87</v>
       </c>
       <c r="BT20" t="n">
         <v>6.6</v>
@@ -5633,7 +5633,7 @@
         <v>3.6</v>
       </c>
       <c r="BV20" t="n">
-        <v>18</v>
+        <v>18.5</v>
       </c>
       <c r="BW20" t="n">
         <v>1.75</v>
@@ -5645,14 +5645,14 @@
         <v>1.83</v>
       </c>
       <c r="BZ20" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="CA20" t="n">
         <v>1.8</v>
       </c>
       <c r="CB20" t="inlineStr">
         <is>
-          <t>2026-06-11 02:48:02</t>
+          <t>2026-06-11 04:56:51</t>
         </is>
       </c>
     </row>
@@ -5683,178 +5683,178 @@
         </is>
       </c>
       <c r="F21" t="n">
-        <v>2.26</v>
+        <v>2.28</v>
       </c>
       <c r="G21" t="n">
-        <v>2.48</v>
+        <v>2.5</v>
       </c>
       <c r="H21" t="n">
-        <v>3.25</v>
+        <v>3.35</v>
       </c>
       <c r="I21" t="n">
-        <v>3.65</v>
+        <v>3.75</v>
       </c>
       <c r="J21" t="n">
-        <v>3.25</v>
+        <v>3.2</v>
       </c>
       <c r="K21" t="n">
-        <v>3.7</v>
+        <v>3.5</v>
       </c>
       <c r="L21" t="n">
-        <v>1.43</v>
+        <v>1.39</v>
       </c>
       <c r="M21" t="n">
-        <v>1.08</v>
+        <v>1.09</v>
       </c>
       <c r="N21" t="n">
-        <v>3.4</v>
+        <v>3.15</v>
       </c>
       <c r="O21" t="n">
-        <v>1.36</v>
+        <v>1.4</v>
       </c>
       <c r="P21" t="n">
-        <v>1.82</v>
+        <v>1.75</v>
       </c>
       <c r="Q21" t="n">
-        <v>2.02</v>
+        <v>2.16</v>
       </c>
       <c r="R21" t="n">
-        <v>1.31</v>
+        <v>1.27</v>
       </c>
       <c r="S21" t="n">
-        <v>3.65</v>
+        <v>4</v>
       </c>
       <c r="T21" t="n">
-        <v>1.79</v>
+        <v>1.87</v>
       </c>
       <c r="U21" t="n">
-        <v>2.06</v>
+        <v>1.99</v>
       </c>
       <c r="V21" t="n">
-        <v>1.38</v>
+        <v>1.37</v>
       </c>
       <c r="W21" t="n">
-        <v>1.67</v>
+        <v>1.66</v>
       </c>
       <c r="X21" t="n">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="Y21" t="n">
-        <v>15</v>
+        <v>14.5</v>
       </c>
       <c r="Z21" t="n">
         <v>29</v>
       </c>
       <c r="AA21" t="n">
-        <v>80</v>
+        <v>85</v>
       </c>
       <c r="AB21" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="AC21" t="n">
-        <v>9.4</v>
+        <v>9</v>
       </c>
       <c r="AD21" t="n">
         <v>18</v>
       </c>
       <c r="AE21" t="n">
-        <v>55</v>
+        <v>60</v>
       </c>
       <c r="AF21" t="n">
-        <v>18.5</v>
+        <v>18</v>
       </c>
       <c r="AG21" t="n">
         <v>14</v>
       </c>
       <c r="AH21" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="AI21" t="n">
+        <v>75</v>
+      </c>
+      <c r="AJ21" t="n">
+        <v>42</v>
+      </c>
+      <c r="AK21" t="n">
+        <v>36</v>
+      </c>
+      <c r="AL21" t="n">
+        <v>55</v>
+      </c>
+      <c r="AM21" t="n">
+        <v>150</v>
+      </c>
+      <c r="AN21" t="n">
+        <v>32</v>
+      </c>
+      <c r="AO21" t="n">
         <v>65</v>
       </c>
-      <c r="AJ21" t="n">
-        <v>40</v>
-      </c>
-      <c r="AK21" t="n">
-        <v>34</v>
-      </c>
-      <c r="AL21" t="n">
-        <v>50</v>
-      </c>
-      <c r="AM21" t="n">
-        <v>130</v>
-      </c>
-      <c r="AN21" t="n">
-        <v>27</v>
-      </c>
-      <c r="AO21" t="n">
-        <v>55</v>
-      </c>
       <c r="AP21" t="n">
-        <v>9.6</v>
+        <v>8.6</v>
       </c>
       <c r="AQ21" t="n">
-        <v>9.199999999999999</v>
+        <v>8.6</v>
       </c>
       <c r="AR21" t="n">
-        <v>17</v>
+        <v>17.5</v>
       </c>
       <c r="AS21" t="n">
         <v>4</v>
       </c>
       <c r="AT21" t="n">
-        <v>7.2</v>
+        <v>7.8</v>
       </c>
       <c r="AU21" t="n">
-        <v>5.9</v>
+        <v>6.6</v>
       </c>
       <c r="AV21" t="n">
+        <v>11</v>
+      </c>
+      <c r="AW21" t="n">
+        <v>32</v>
+      </c>
+      <c r="AX21" t="n">
         <v>10.5</v>
-      </c>
-      <c r="AW21" t="n">
-        <v>3.9</v>
-      </c>
-      <c r="AX21" t="n">
-        <v>11</v>
       </c>
       <c r="AY21" t="n">
         <v>8.4</v>
       </c>
       <c r="AZ21" t="n">
-        <v>13</v>
+        <v>13.5</v>
       </c>
       <c r="BA21" t="n">
+        <v>4</v>
+      </c>
+      <c r="BB21" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="BC21" t="n">
+        <v>20</v>
+      </c>
+      <c r="BD21" t="n">
         <v>3.95</v>
       </c>
-      <c r="BB21" t="n">
-        <v>3.8</v>
-      </c>
-      <c r="BC21" t="n">
-        <v>19</v>
-      </c>
-      <c r="BD21" t="n">
-        <v>3.85</v>
-      </c>
       <c r="BE21" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="BF21" t="n">
+        <v>21</v>
+      </c>
+      <c r="BG21" t="n">
         <v>4</v>
       </c>
-      <c r="BF21" t="n">
-        <v>18.5</v>
-      </c>
-      <c r="BG21" t="n">
-        <v>3.9</v>
-      </c>
       <c r="BH21" t="n">
-        <v>3.3</v>
+        <v>3.15</v>
       </c>
       <c r="BI21" t="n">
-        <v>2.66</v>
+        <v>2.56</v>
       </c>
       <c r="BJ21" t="n">
-        <v>9.800000000000001</v>
+        <v>10.5</v>
       </c>
       <c r="BK21" t="n">
-        <v>5.7</v>
+        <v>5.9</v>
       </c>
       <c r="BL21" t="n">
         <v>1000</v>
@@ -5863,16 +5863,16 @@
         <v>12.5</v>
       </c>
       <c r="BN21" t="n">
-        <v>5.3</v>
+        <v>5.2</v>
       </c>
       <c r="BO21" t="n">
         <v>3.95</v>
       </c>
       <c r="BP21" t="n">
-        <v>1000</v>
+        <v>970</v>
       </c>
       <c r="BQ21" t="n">
-        <v>7.8</v>
+        <v>8</v>
       </c>
       <c r="BR21" t="n">
         <v>1000</v>
@@ -5902,11 +5902,11 @@
         <v>1000</v>
       </c>
       <c r="CA21" t="n">
-        <v>9.6</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="CB21" t="inlineStr">
         <is>
-          <t>2026-06-11 02:48:02</t>
+          <t>2026-06-11 04:56:51</t>
         </is>
       </c>
     </row>
@@ -5937,25 +5937,25 @@
         </is>
       </c>
       <c r="F22" t="n">
-        <v>4.2</v>
+        <v>4.3</v>
       </c>
       <c r="G22" t="n">
-        <v>4.9</v>
+        <v>5</v>
       </c>
       <c r="H22" t="n">
-        <v>1.86</v>
+        <v>1.85</v>
       </c>
       <c r="I22" t="n">
-        <v>2.04</v>
+        <v>2.02</v>
       </c>
       <c r="J22" t="n">
         <v>3.55</v>
       </c>
       <c r="K22" t="n">
-        <v>4.2</v>
+        <v>4</v>
       </c>
       <c r="L22" t="n">
-        <v>1.38</v>
+        <v>1.39</v>
       </c>
       <c r="M22" t="n">
         <v>1.06</v>
@@ -5964,10 +5964,10 @@
         <v>3.6</v>
       </c>
       <c r="O22" t="n">
-        <v>1.28</v>
+        <v>1.3</v>
       </c>
       <c r="P22" t="n">
-        <v>1.9</v>
+        <v>1.91</v>
       </c>
       <c r="Q22" t="n">
         <v>1.9</v>
@@ -5976,13 +5976,13 @@
         <v>1.34</v>
       </c>
       <c r="S22" t="n">
-        <v>3.25</v>
+        <v>3.3</v>
       </c>
       <c r="T22" t="n">
-        <v>1.78</v>
+        <v>1.79</v>
       </c>
       <c r="U22" t="n">
-        <v>2.02</v>
+        <v>2.04</v>
       </c>
       <c r="V22" t="n">
         <v>1.98</v>
@@ -6000,13 +6000,13 @@
         <v>12.5</v>
       </c>
       <c r="AA22" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="AB22" t="n">
-        <v>17</v>
+        <v>16.5</v>
       </c>
       <c r="AC22" t="n">
-        <v>9</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AD22" t="n">
         <v>11</v>
@@ -6030,34 +6030,34 @@
         <v>110</v>
       </c>
       <c r="AK22" t="n">
-        <v>90</v>
+        <v>60</v>
       </c>
       <c r="AL22" t="n">
-        <v>70</v>
+        <v>65</v>
       </c>
       <c r="AM22" t="n">
         <v>120</v>
       </c>
       <c r="AN22" t="n">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="AO22" t="n">
-        <v>14</v>
+        <v>14.5</v>
       </c>
       <c r="AP22" t="n">
         <v>11</v>
       </c>
       <c r="AQ22" t="n">
-        <v>7.6</v>
+        <v>7.8</v>
       </c>
       <c r="AR22" t="n">
         <v>10</v>
       </c>
       <c r="AS22" t="n">
-        <v>18</v>
+        <v>18.5</v>
       </c>
       <c r="AT22" t="n">
-        <v>13.5</v>
+        <v>13</v>
       </c>
       <c r="AU22" t="n">
         <v>7.2</v>
@@ -6066,43 +6066,43 @@
         <v>8.800000000000001</v>
       </c>
       <c r="AW22" t="n">
-        <v>17</v>
+        <v>17.5</v>
       </c>
       <c r="AX22" t="n">
-        <v>23</v>
+        <v>7.2</v>
       </c>
       <c r="AY22" t="n">
+        <v>15</v>
+      </c>
+      <c r="AZ22" t="n">
         <v>15.5</v>
       </c>
-      <c r="AZ22" t="n">
-        <v>16</v>
-      </c>
       <c r="BA22" t="n">
-        <v>23</v>
+        <v>7.2</v>
       </c>
       <c r="BB22" t="n">
-        <v>8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BC22" t="n">
-        <v>40</v>
+        <v>7.8</v>
       </c>
       <c r="BD22" t="n">
         <v>7.8</v>
       </c>
       <c r="BE22" t="n">
-        <v>8.199999999999999</v>
+        <v>8.4</v>
       </c>
       <c r="BF22" t="n">
-        <v>7.8</v>
+        <v>8</v>
       </c>
       <c r="BG22" t="n">
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="BH22" t="n">
         <v>3.55</v>
       </c>
       <c r="BI22" t="n">
-        <v>2.84</v>
+        <v>3.05</v>
       </c>
       <c r="BJ22" t="n">
         <v>10.5</v>
@@ -6138,7 +6138,7 @@
         <v>4.8</v>
       </c>
       <c r="BU22" t="n">
-        <v>4</v>
+        <v>3.7</v>
       </c>
       <c r="BV22" t="n">
         <v>14</v>
@@ -6160,7 +6160,7 @@
       </c>
       <c r="CB22" t="inlineStr">
         <is>
-          <t>2026-06-11 02:48:02</t>
+          <t>2026-06-11 04:56:51</t>
         </is>
       </c>
     </row>
@@ -6194,7 +6194,7 @@
         <v>1.42</v>
       </c>
       <c r="G23" t="n">
-        <v>1.66</v>
+        <v>1.62</v>
       </c>
       <c r="H23" t="n">
         <v>4.8</v>
@@ -6242,7 +6242,7 @@
         <v>1.09</v>
       </c>
       <c r="W23" t="n">
-        <v>2.5</v>
+        <v>2.58</v>
       </c>
       <c r="X23" t="n">
         <v>1000</v>
@@ -6414,7 +6414,7 @@
       </c>
       <c r="CB23" t="inlineStr">
         <is>
-          <t>2026-06-11 02:48:02</t>
+          <t>2026-06-11 04:56:51</t>
         </is>
       </c>
     </row>
@@ -6448,58 +6448,58 @@
         <v>2.78</v>
       </c>
       <c r="G24" t="n">
-        <v>3.05</v>
+        <v>3</v>
       </c>
       <c r="H24" t="n">
         <v>2.68</v>
       </c>
       <c r="I24" t="n">
-        <v>2.9</v>
+        <v>2.92</v>
       </c>
       <c r="J24" t="n">
-        <v>3.25</v>
+        <v>3.2</v>
       </c>
       <c r="K24" t="n">
-        <v>3.55</v>
+        <v>3.5</v>
       </c>
       <c r="L24" t="n">
-        <v>1.01</v>
+        <v>1.41</v>
       </c>
       <c r="M24" t="n">
         <v>1.09</v>
       </c>
       <c r="N24" t="n">
-        <v>3.3</v>
+        <v>3.2</v>
       </c>
       <c r="O24" t="n">
-        <v>1.38</v>
+        <v>1.39</v>
       </c>
       <c r="P24" t="n">
-        <v>1.78</v>
+        <v>1.76</v>
       </c>
       <c r="Q24" t="n">
-        <v>2.12</v>
+        <v>2.16</v>
       </c>
       <c r="R24" t="n">
-        <v>1.3</v>
+        <v>1.28</v>
       </c>
       <c r="S24" t="n">
         <v>3.9</v>
       </c>
       <c r="T24" t="n">
-        <v>1.83</v>
+        <v>1.85</v>
       </c>
       <c r="U24" t="n">
         <v>2.06</v>
       </c>
       <c r="V24" t="n">
-        <v>1.53</v>
+        <v>1.52</v>
       </c>
       <c r="W24" t="n">
         <v>1.5</v>
       </c>
       <c r="X24" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="Y24" t="n">
         <v>12.5</v>
@@ -6511,7 +6511,7 @@
         <v>55</v>
       </c>
       <c r="AB24" t="n">
-        <v>13</v>
+        <v>12.5</v>
       </c>
       <c r="AC24" t="n">
         <v>9</v>
@@ -6559,10 +6559,10 @@
         <v>9.199999999999999</v>
       </c>
       <c r="AR24" t="n">
-        <v>3.6</v>
+        <v>3.7</v>
       </c>
       <c r="AS24" t="n">
-        <v>4</v>
+        <v>4.1</v>
       </c>
       <c r="AT24" t="n">
         <v>9.4</v>
@@ -6574,7 +6574,7 @@
         <v>11</v>
       </c>
       <c r="AW24" t="n">
-        <v>3.9</v>
+        <v>4</v>
       </c>
       <c r="AX24" t="n">
         <v>16.5</v>
@@ -6583,92 +6583,92 @@
         <v>11.5</v>
       </c>
       <c r="AZ24" t="n">
-        <v>3.6</v>
+        <v>3.7</v>
       </c>
       <c r="BA24" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="BB24" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="BC24" t="n">
         <v>4</v>
       </c>
-      <c r="BB24" t="n">
+      <c r="BD24" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="BE24" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="BF24" t="n">
         <v>4</v>
       </c>
-      <c r="BC24" t="n">
-        <v>3.9</v>
-      </c>
-      <c r="BD24" t="n">
+      <c r="BG24" t="n">
         <v>4</v>
       </c>
-      <c r="BE24" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="BF24" t="n">
-        <v>3.9</v>
-      </c>
-      <c r="BG24" t="n">
-        <v>3.85</v>
-      </c>
       <c r="BH24" t="n">
         <v>1000</v>
       </c>
       <c r="BI24" t="n">
-        <v>1.8</v>
+        <v>1.78</v>
       </c>
       <c r="BJ24" t="n">
         <v>13.5</v>
       </c>
       <c r="BK24" t="n">
-        <v>1.59</v>
+        <v>1.57</v>
       </c>
       <c r="BL24" t="n">
         <v>1000</v>
       </c>
       <c r="BM24" t="n">
-        <v>1.8</v>
+        <v>1.78</v>
       </c>
       <c r="BN24" t="n">
         <v>8.199999999999999</v>
       </c>
       <c r="BO24" t="n">
-        <v>3.8</v>
+        <v>4.5</v>
       </c>
       <c r="BP24" t="n">
         <v>34</v>
       </c>
       <c r="BQ24" t="n">
-        <v>1.71</v>
+        <v>1.69</v>
       </c>
       <c r="BR24" t="n">
-        <v>50</v>
+        <v>1000</v>
       </c>
       <c r="BS24" t="n">
-        <v>1.74</v>
+        <v>1.73</v>
       </c>
       <c r="BT24" t="n">
         <v>8</v>
       </c>
       <c r="BU24" t="n">
-        <v>3.7</v>
+        <v>4.4</v>
       </c>
       <c r="BV24" t="n">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="BW24" t="n">
-        <v>1.7</v>
+        <v>1.69</v>
       </c>
       <c r="BX24" t="n">
-        <v>50</v>
+        <v>1000</v>
       </c>
       <c r="BY24" t="n">
-        <v>1.74</v>
+        <v>1.73</v>
       </c>
       <c r="BZ24" t="n">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="CA24" t="n">
-        <v>1.74</v>
+        <v>1.72</v>
       </c>
       <c r="CB24" t="inlineStr">
         <is>
-          <t>2026-06-11 02:48:02</t>
+          <t>2026-06-11 04:56:51</t>
         </is>
       </c>
     </row>
@@ -6702,19 +6702,19 @@
         <v>1.04</v>
       </c>
       <c r="G25" t="n">
-        <v>990</v>
+        <v>1000</v>
       </c>
       <c r="H25" t="n">
         <v>1.04</v>
       </c>
       <c r="I25" t="n">
-        <v>990</v>
+        <v>1000</v>
       </c>
       <c r="J25" t="n">
         <v>1.09</v>
       </c>
       <c r="K25" t="n">
-        <v>950</v>
+        <v>1000</v>
       </c>
       <c r="L25" t="n">
         <v>1.01</v>
@@ -6723,13 +6723,13 @@
         <v>1.01</v>
       </c>
       <c r="N25" t="n">
-        <v>1.31</v>
+        <v>1.33</v>
       </c>
       <c r="O25" t="n">
         <v>1.12</v>
       </c>
       <c r="P25" t="n">
-        <v>1.31</v>
+        <v>1.33</v>
       </c>
       <c r="Q25" t="n">
         <v>1.12</v>
@@ -6922,7 +6922,7 @@
       </c>
       <c r="CB25" t="inlineStr">
         <is>
-          <t>2026-06-11 02:48:02</t>
+          <t>2026-06-11 04:56:51</t>
         </is>
       </c>
     </row>
@@ -6953,7 +6953,7 @@
         </is>
       </c>
       <c r="F26" t="n">
-        <v>2.18</v>
+        <v>2.2</v>
       </c>
       <c r="G26" t="n">
         <v>2.34</v>
@@ -6968,7 +6968,7 @@
         <v>3.35</v>
       </c>
       <c r="K26" t="n">
-        <v>3.45</v>
+        <v>3.4</v>
       </c>
       <c r="L26" t="n">
         <v>1.43</v>
@@ -6995,7 +6995,7 @@
         <v>4.4</v>
       </c>
       <c r="T26" t="n">
-        <v>1.9</v>
+        <v>1.92</v>
       </c>
       <c r="U26" t="n">
         <v>1.87</v>
@@ -7007,7 +7007,7 @@
         <v>1.74</v>
       </c>
       <c r="X26" t="n">
-        <v>12.5</v>
+        <v>12</v>
       </c>
       <c r="Y26" t="n">
         <v>970</v>
@@ -7016,7 +7016,7 @@
         <v>28</v>
       </c>
       <c r="AA26" t="n">
-        <v>100</v>
+        <v>95</v>
       </c>
       <c r="AB26" t="n">
         <v>8.6</v>
@@ -7064,73 +7064,73 @@
         <v>5</v>
       </c>
       <c r="AQ26" t="n">
-        <v>5</v>
+        <v>5.1</v>
       </c>
       <c r="AR26" t="n">
-        <v>6.4</v>
+        <v>6.6</v>
       </c>
       <c r="AS26" t="n">
-        <v>7.8</v>
+        <v>8</v>
       </c>
       <c r="AT26" t="n">
-        <v>4.2</v>
+        <v>4.3</v>
       </c>
       <c r="AU26" t="n">
         <v>6.4</v>
       </c>
       <c r="AV26" t="n">
-        <v>5.6</v>
+        <v>5.8</v>
       </c>
       <c r="AW26" t="n">
-        <v>7.4</v>
+        <v>7.6</v>
       </c>
       <c r="AX26" t="n">
-        <v>5.3</v>
+        <v>5.4</v>
       </c>
       <c r="AY26" t="n">
-        <v>4.9</v>
+        <v>5</v>
       </c>
       <c r="AZ26" t="n">
-        <v>6</v>
+        <v>6.2</v>
       </c>
       <c r="BA26" t="n">
-        <v>7.6</v>
+        <v>7.8</v>
       </c>
       <c r="BB26" t="n">
-        <v>6.6</v>
+        <v>6.8</v>
       </c>
       <c r="BC26" t="n">
         <v>6.6</v>
       </c>
       <c r="BD26" t="n">
-        <v>7.2</v>
+        <v>7.4</v>
       </c>
       <c r="BE26" t="n">
-        <v>8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BF26" t="n">
         <v>6.4</v>
       </c>
       <c r="BG26" t="n">
-        <v>7.6</v>
+        <v>7.8</v>
       </c>
       <c r="BH26" t="n">
         <v>3.1</v>
       </c>
       <c r="BI26" t="n">
-        <v>2.5</v>
+        <v>2.48</v>
       </c>
       <c r="BJ26" t="n">
         <v>11</v>
       </c>
       <c r="BK26" t="n">
-        <v>5.4</v>
+        <v>5.3</v>
       </c>
       <c r="BL26" t="n">
         <v>1000</v>
       </c>
       <c r="BM26" t="n">
-        <v>10</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BN26" t="n">
         <v>5.1</v>
@@ -7160,7 +7160,7 @@
         <v>1000</v>
       </c>
       <c r="BW26" t="n">
-        <v>8.199999999999999</v>
+        <v>8</v>
       </c>
       <c r="BX26" t="n">
         <v>1000</v>
@@ -7176,7 +7176,7 @@
       </c>
       <c r="CB26" t="inlineStr">
         <is>
-          <t>2026-06-11 02:48:02</t>
+          <t>2026-06-11 04:56:51</t>
         </is>
       </c>
     </row>
@@ -7430,7 +7430,7 @@
       </c>
       <c r="CB27" t="inlineStr">
         <is>
-          <t>2026-06-11 02:48:02</t>
+          <t>2026-06-11 04:56:51</t>
         </is>
       </c>
     </row>
@@ -7461,10 +7461,10 @@
         </is>
       </c>
       <c r="F28" t="n">
-        <v>1.99</v>
+        <v>2</v>
       </c>
       <c r="G28" t="n">
-        <v>2.14</v>
+        <v>2.12</v>
       </c>
       <c r="H28" t="n">
         <v>3.7</v>
@@ -7512,7 +7512,7 @@
         <v>1.32</v>
       </c>
       <c r="W28" t="n">
-        <v>1.88</v>
+        <v>1.9</v>
       </c>
       <c r="X28" t="n">
         <v>22</v>
@@ -7521,10 +7521,10 @@
         <v>19.5</v>
       </c>
       <c r="Z28" t="n">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="AA28" t="n">
-        <v>90</v>
+        <v>75</v>
       </c>
       <c r="AB28" t="n">
         <v>12.5</v>
@@ -7533,13 +7533,13 @@
         <v>10</v>
       </c>
       <c r="AD28" t="n">
-        <v>19.5</v>
+        <v>19</v>
       </c>
       <c r="AE28" t="n">
         <v>55</v>
       </c>
       <c r="AF28" t="n">
-        <v>17</v>
+        <v>16.5</v>
       </c>
       <c r="AG28" t="n">
         <v>12.5</v>
@@ -7560,25 +7560,25 @@
         <v>40</v>
       </c>
       <c r="AM28" t="n">
-        <v>100</v>
+        <v>85</v>
       </c>
       <c r="AN28" t="n">
         <v>15.5</v>
       </c>
       <c r="AO28" t="n">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="AP28" t="n">
         <v>15.5</v>
       </c>
       <c r="AQ28" t="n">
-        <v>14.5</v>
+        <v>14</v>
       </c>
       <c r="AR28" t="n">
-        <v>4.2</v>
+        <v>4.4</v>
       </c>
       <c r="AS28" t="n">
-        <v>4.5</v>
+        <v>4.7</v>
       </c>
       <c r="AT28" t="n">
         <v>9.6</v>
@@ -7590,7 +7590,7 @@
         <v>14</v>
       </c>
       <c r="AW28" t="n">
-        <v>4.4</v>
+        <v>36</v>
       </c>
       <c r="AX28" t="n">
         <v>12</v>
@@ -7602,7 +7602,7 @@
         <v>14.5</v>
       </c>
       <c r="BA28" t="n">
-        <v>40</v>
+        <v>4.6</v>
       </c>
       <c r="BB28" t="n">
         <v>21</v>
@@ -7611,16 +7611,16 @@
         <v>18</v>
       </c>
       <c r="BD28" t="n">
-        <v>4.2</v>
+        <v>4.4</v>
       </c>
       <c r="BE28" t="n">
-        <v>4.6</v>
+        <v>4.7</v>
       </c>
       <c r="BF28" t="n">
-        <v>9.4</v>
+        <v>9.6</v>
       </c>
       <c r="BG28" t="n">
-        <v>4.4</v>
+        <v>4.5</v>
       </c>
       <c r="BH28" t="n">
         <v>3.75</v>
@@ -7684,7 +7684,7 @@
       </c>
       <c r="CB28" t="inlineStr">
         <is>
-          <t>2026-06-11 02:48:02</t>
+          <t>2026-06-11 04:56:51</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-06-12.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-06-12.xlsx
@@ -857,19 +857,19 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>1.18</v>
+        <v>1.22</v>
       </c>
       <c r="G2" t="n">
         <v>1000</v>
       </c>
       <c r="H2" t="n">
-        <v>1.18</v>
+        <v>1.09</v>
       </c>
       <c r="I2" t="n">
         <v>1000</v>
       </c>
       <c r="J2" t="n">
-        <v>1.1</v>
+        <v>1.09</v>
       </c>
       <c r="K2" t="n">
         <v>1000</v>
@@ -905,7 +905,7 @@
         <v>1.01</v>
       </c>
       <c r="V2" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="W2" t="n">
         <v>1.02</v>
@@ -1080,7 +1080,7 @@
       </c>
       <c r="CB2" t="inlineStr">
         <is>
-          <t>2026-06-11 04:56:51</t>
+          <t>2026-06-11 07:05:44</t>
         </is>
       </c>
     </row>
@@ -1111,19 +1111,19 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>1.04</v>
+        <v>1.09</v>
       </c>
       <c r="G3" t="n">
         <v>1000</v>
       </c>
       <c r="H3" t="n">
-        <v>1.04</v>
+        <v>1.09</v>
       </c>
       <c r="I3" t="n">
         <v>1000</v>
       </c>
       <c r="J3" t="n">
-        <v>1.1</v>
+        <v>1.09</v>
       </c>
       <c r="K3" t="n">
         <v>1000</v>
@@ -1135,7 +1135,7 @@
         <v>1.01</v>
       </c>
       <c r="N3" t="n">
-        <v>1.1</v>
+        <v>4.4</v>
       </c>
       <c r="O3" t="n">
         <v>1.21</v>
@@ -1159,7 +1159,7 @@
         <v>1.11</v>
       </c>
       <c r="V3" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="W3" t="n">
         <v>1.02</v>
@@ -1334,7 +1334,7 @@
       </c>
       <c r="CB3" t="inlineStr">
         <is>
-          <t>2026-06-11 04:56:51</t>
+          <t>2026-06-11 07:05:44</t>
         </is>
       </c>
     </row>
@@ -1365,100 +1365,100 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>1.18</v>
+        <v>2.56</v>
       </c>
       <c r="G4" t="n">
-        <v>1000</v>
+        <v>3.3</v>
       </c>
       <c r="H4" t="n">
-        <v>1.18</v>
+        <v>2.78</v>
       </c>
       <c r="I4" t="n">
-        <v>1000</v>
+        <v>3.5</v>
       </c>
       <c r="J4" t="n">
-        <v>1.1</v>
+        <v>2.54</v>
       </c>
       <c r="K4" t="n">
-        <v>1000</v>
+        <v>3.55</v>
       </c>
       <c r="L4" t="n">
         <v>1.01</v>
       </c>
       <c r="M4" t="n">
-        <v>1.01</v>
+        <v>1.14</v>
       </c>
       <c r="N4" t="n">
-        <v>1.29</v>
+        <v>2.42</v>
       </c>
       <c r="O4" t="n">
-        <v>1.02</v>
+        <v>1.59</v>
       </c>
       <c r="P4" t="n">
-        <v>1.24</v>
+        <v>1.5</v>
       </c>
       <c r="Q4" t="n">
-        <v>1.52</v>
+        <v>2.5</v>
       </c>
       <c r="R4" t="n">
-        <v>1.18</v>
+        <v>1.19</v>
       </c>
       <c r="S4" t="n">
-        <v>1.52</v>
+        <v>3.95</v>
       </c>
       <c r="T4" t="n">
-        <v>1.11</v>
+        <v>2.14</v>
       </c>
       <c r="U4" t="n">
-        <v>1.11</v>
+        <v>1.68</v>
       </c>
       <c r="V4" t="n">
-        <v>1.01</v>
+        <v>1.41</v>
       </c>
       <c r="W4" t="n">
-        <v>1.02</v>
+        <v>1.45</v>
       </c>
       <c r="X4" t="n">
-        <v>1000</v>
+        <v>970</v>
       </c>
       <c r="Y4" t="n">
-        <v>1000</v>
+        <v>970</v>
       </c>
       <c r="Z4" t="n">
-        <v>1000</v>
+        <v>22</v>
       </c>
       <c r="AA4" t="n">
-        <v>1000</v>
+        <v>75</v>
       </c>
       <c r="AB4" t="n">
-        <v>1000</v>
+        <v>970</v>
       </c>
       <c r="AC4" t="n">
-        <v>1000</v>
+        <v>970</v>
       </c>
       <c r="AD4" t="n">
-        <v>1000</v>
+        <v>970</v>
       </c>
       <c r="AE4" t="n">
-        <v>1000</v>
+        <v>60</v>
       </c>
       <c r="AF4" t="n">
-        <v>1000</v>
+        <v>21</v>
       </c>
       <c r="AG4" t="n">
-        <v>1000</v>
+        <v>970</v>
       </c>
       <c r="AH4" t="n">
-        <v>1000</v>
+        <v>29</v>
       </c>
       <c r="AI4" t="n">
         <v>1000</v>
       </c>
       <c r="AJ4" t="n">
-        <v>1000</v>
+        <v>65</v>
       </c>
       <c r="AK4" t="n">
-        <v>1000</v>
+        <v>60</v>
       </c>
       <c r="AL4" t="n">
         <v>1000</v>
@@ -1467,43 +1467,43 @@
         <v>1000</v>
       </c>
       <c r="AN4" t="n">
-        <v>1000</v>
+        <v>75</v>
       </c>
       <c r="AO4" t="n">
         <v>1000</v>
       </c>
       <c r="AP4" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AQ4" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AR4" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AS4" t="n">
         <v>1.03</v>
       </c>
       <c r="AT4" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AU4" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AV4" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AW4" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AX4" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AY4" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AZ4" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BA4" t="n">
         <v>1.03</v>
@@ -1512,7 +1512,7 @@
         <v>1.03</v>
       </c>
       <c r="BC4" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BD4" t="n">
         <v>1.03</v>
@@ -1527,7 +1527,7 @@
         <v>1.01</v>
       </c>
       <c r="BH4" t="n">
-        <v>1000</v>
+        <v>2.84</v>
       </c>
       <c r="BI4" t="n">
         <v>1.04</v>
@@ -1536,59 +1536,59 @@
         <v>1000</v>
       </c>
       <c r="BK4" t="n">
-        <v>1.04</v>
+        <v>1.56</v>
       </c>
       <c r="BL4" t="n">
         <v>1000</v>
       </c>
       <c r="BM4" t="n">
-        <v>1.04</v>
+        <v>1.56</v>
       </c>
       <c r="BN4" t="n">
         <v>1000</v>
       </c>
       <c r="BO4" t="n">
-        <v>1.04</v>
+        <v>1.56</v>
       </c>
       <c r="BP4" t="n">
         <v>1000</v>
       </c>
       <c r="BQ4" t="n">
-        <v>1.04</v>
+        <v>1.56</v>
       </c>
       <c r="BR4" t="n">
         <v>1000</v>
       </c>
       <c r="BS4" t="n">
-        <v>1.04</v>
+        <v>1.56</v>
       </c>
       <c r="BT4" t="n">
         <v>1000</v>
       </c>
       <c r="BU4" t="n">
-        <v>1.04</v>
+        <v>1.56</v>
       </c>
       <c r="BV4" t="n">
         <v>1000</v>
       </c>
       <c r="BW4" t="n">
-        <v>1.04</v>
+        <v>1.56</v>
       </c>
       <c r="BX4" t="n">
         <v>1000</v>
       </c>
       <c r="BY4" t="n">
-        <v>1.04</v>
+        <v>1.56</v>
       </c>
       <c r="BZ4" t="n">
         <v>1000</v>
       </c>
       <c r="CA4" t="n">
-        <v>1.04</v>
+        <v>1.56</v>
       </c>
       <c r="CB4" t="inlineStr">
         <is>
-          <t>2026-06-11 04:56:51</t>
+          <t>2026-06-11 07:05:44</t>
         </is>
       </c>
     </row>
@@ -1619,46 +1619,46 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>1.55</v>
+        <v>2.14</v>
       </c>
       <c r="G5" t="n">
-        <v>1000</v>
+        <v>2.38</v>
       </c>
       <c r="H5" t="n">
-        <v>1.55</v>
+        <v>3.7</v>
       </c>
       <c r="I5" t="n">
-        <v>1000</v>
+        <v>4.5</v>
       </c>
       <c r="J5" t="n">
-        <v>1.09</v>
+        <v>2.9</v>
       </c>
       <c r="K5" t="n">
-        <v>2.96</v>
+        <v>3.25</v>
       </c>
       <c r="L5" t="n">
-        <v>1.01</v>
+        <v>1.52</v>
       </c>
       <c r="M5" t="n">
         <v>1.01</v>
       </c>
       <c r="N5" t="n">
-        <v>1.3</v>
+        <v>2.52</v>
       </c>
       <c r="O5" t="n">
-        <v>1.02</v>
+        <v>1.5</v>
       </c>
       <c r="P5" t="n">
-        <v>1.3</v>
+        <v>1.43</v>
       </c>
       <c r="Q5" t="n">
-        <v>1.51</v>
+        <v>2.48</v>
       </c>
       <c r="R5" t="n">
         <v>1.18</v>
       </c>
       <c r="S5" t="n">
-        <v>1.51</v>
+        <v>3.05</v>
       </c>
       <c r="T5" t="n">
         <v>1.11</v>
@@ -1667,10 +1667,10 @@
         <v>1.11</v>
       </c>
       <c r="V5" t="n">
-        <v>1.02</v>
+        <v>1.28</v>
       </c>
       <c r="W5" t="n">
-        <v>1.02</v>
+        <v>1.72</v>
       </c>
       <c r="X5" t="n">
         <v>1000</v>
@@ -1842,7 +1842,7 @@
       </c>
       <c r="CB5" t="inlineStr">
         <is>
-          <t>2026-06-11 04:56:51</t>
+          <t>2026-06-11 07:05:44</t>
         </is>
       </c>
     </row>
@@ -1873,46 +1873,46 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>1.18</v>
+        <v>3.35</v>
       </c>
       <c r="G6" t="n">
-        <v>1000</v>
+        <v>4.7</v>
       </c>
       <c r="H6" t="n">
-        <v>1.18</v>
+        <v>1.96</v>
       </c>
       <c r="I6" t="n">
-        <v>1000</v>
+        <v>2.28</v>
       </c>
       <c r="J6" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="K6" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="L6" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="M6" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="N6" t="n">
         <v>1.1</v>
       </c>
-      <c r="K6" t="n">
-        <v>1000</v>
-      </c>
-      <c r="L6" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="M6" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="N6" t="n">
-        <v>1.36</v>
-      </c>
       <c r="O6" t="n">
-        <v>1.22</v>
+        <v>1.24</v>
       </c>
       <c r="P6" t="n">
-        <v>1.25</v>
+        <v>2.04</v>
       </c>
       <c r="Q6" t="n">
-        <v>1.22</v>
+        <v>1.81</v>
       </c>
       <c r="R6" t="n">
-        <v>1.18</v>
+        <v>1.31</v>
       </c>
       <c r="S6" t="n">
-        <v>1.22</v>
+        <v>2.82</v>
       </c>
       <c r="T6" t="n">
         <v>1.11</v>
@@ -1921,10 +1921,10 @@
         <v>1.11</v>
       </c>
       <c r="V6" t="n">
-        <v>1.01</v>
+        <v>1.78</v>
       </c>
       <c r="W6" t="n">
-        <v>1.02</v>
+        <v>1.27</v>
       </c>
       <c r="X6" t="n">
         <v>1000</v>
@@ -2096,7 +2096,7 @@
       </c>
       <c r="CB6" t="inlineStr">
         <is>
-          <t>2026-06-11 04:56:51</t>
+          <t>2026-06-11 07:05:44</t>
         </is>
       </c>
     </row>
@@ -2127,19 +2127,19 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>1.17</v>
+        <v>1.21</v>
       </c>
       <c r="G7" t="n">
         <v>1000</v>
       </c>
       <c r="H7" t="n">
-        <v>1.17</v>
+        <v>1.22</v>
       </c>
       <c r="I7" t="n">
         <v>1000</v>
       </c>
       <c r="J7" t="n">
-        <v>1.1</v>
+        <v>1.4</v>
       </c>
       <c r="K7" t="n">
         <v>1000</v>
@@ -2154,19 +2154,19 @@
         <v>1.25</v>
       </c>
       <c r="O7" t="n">
-        <v>1.27</v>
+        <v>1.28</v>
       </c>
       <c r="P7" t="n">
         <v>1.24</v>
       </c>
       <c r="Q7" t="n">
-        <v>1.27</v>
+        <v>1.28</v>
       </c>
       <c r="R7" t="n">
         <v>1.18</v>
       </c>
       <c r="S7" t="n">
-        <v>1.27</v>
+        <v>1.28</v>
       </c>
       <c r="T7" t="n">
         <v>1.11</v>
@@ -2350,7 +2350,7 @@
       </c>
       <c r="CB7" t="inlineStr">
         <is>
-          <t>2026-06-11 04:56:51</t>
+          <t>2026-06-11 07:05:44</t>
         </is>
       </c>
     </row>
@@ -2381,22 +2381,22 @@
         </is>
       </c>
       <c r="F8" t="n">
-        <v>1.23</v>
+        <v>1.34</v>
       </c>
       <c r="G8" t="n">
-        <v>1000</v>
+        <v>95</v>
       </c>
       <c r="H8" t="n">
-        <v>1.17</v>
+        <v>1.21</v>
       </c>
       <c r="I8" t="n">
-        <v>1000</v>
+        <v>95</v>
       </c>
       <c r="J8" t="n">
-        <v>1.37</v>
+        <v>1.43</v>
       </c>
       <c r="K8" t="n">
-        <v>1000</v>
+        <v>32</v>
       </c>
       <c r="L8" t="n">
         <v>1.01</v>
@@ -2429,10 +2429,10 @@
         <v>1.11</v>
       </c>
       <c r="V8" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="W8" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="X8" t="n">
         <v>1000</v>
@@ -2604,7 +2604,7 @@
       </c>
       <c r="CB8" t="inlineStr">
         <is>
-          <t>2026-06-11 04:56:51</t>
+          <t>2026-06-11 07:05:44</t>
         </is>
       </c>
     </row>
@@ -2635,7 +2635,7 @@
         </is>
       </c>
       <c r="F9" t="n">
-        <v>1.04</v>
+        <v>1.09</v>
       </c>
       <c r="G9" t="n">
         <v>1000</v>
@@ -2647,7 +2647,7 @@
         <v>1000</v>
       </c>
       <c r="J9" t="n">
-        <v>1.1</v>
+        <v>1.09</v>
       </c>
       <c r="K9" t="n">
         <v>1000</v>
@@ -2659,7 +2659,7 @@
         <v>1.01</v>
       </c>
       <c r="N9" t="n">
-        <v>1.31</v>
+        <v>1.32</v>
       </c>
       <c r="O9" t="n">
         <v>1.15</v>
@@ -2683,10 +2683,10 @@
         <v>1.11</v>
       </c>
       <c r="V9" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="W9" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="X9" t="n">
         <v>1000</v>
@@ -2858,7 +2858,7 @@
       </c>
       <c r="CB9" t="inlineStr">
         <is>
-          <t>2026-06-11 04:56:51</t>
+          <t>2026-06-11 07:05:44</t>
         </is>
       </c>
     </row>
@@ -2892,7 +2892,7 @@
         <v>2.12</v>
       </c>
       <c r="G10" t="n">
-        <v>2.62</v>
+        <v>2.6</v>
       </c>
       <c r="H10" t="n">
         <v>3.3</v>
@@ -2940,7 +2940,7 @@
         <v>1.26</v>
       </c>
       <c r="W10" t="n">
-        <v>1.61</v>
+        <v>1.62</v>
       </c>
       <c r="X10" t="n">
         <v>1000</v>
@@ -3112,7 +3112,7 @@
       </c>
       <c r="CB10" t="inlineStr">
         <is>
-          <t>2026-06-11 04:56:51</t>
+          <t>2026-06-11 07:05:44</t>
         </is>
       </c>
     </row>
@@ -3143,13 +3143,13 @@
         </is>
       </c>
       <c r="F11" t="n">
-        <v>1.16</v>
+        <v>1.2</v>
       </c>
       <c r="G11" t="n">
         <v>1000</v>
       </c>
       <c r="H11" t="n">
-        <v>1.18</v>
+        <v>1.22</v>
       </c>
       <c r="I11" t="n">
         <v>1000</v>
@@ -3167,13 +3167,13 @@
         <v>1.01</v>
       </c>
       <c r="N11" t="n">
-        <v>1.32</v>
+        <v>1.36</v>
       </c>
       <c r="O11" t="n">
         <v>1.02</v>
       </c>
       <c r="P11" t="n">
-        <v>1.32</v>
+        <v>1.36</v>
       </c>
       <c r="Q11" t="n">
         <v>1.56</v>
@@ -3191,7 +3191,7 @@
         <v>1.11</v>
       </c>
       <c r="V11" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="W11" t="n">
         <v>1.02</v>
@@ -3366,7 +3366,7 @@
       </c>
       <c r="CB11" t="inlineStr">
         <is>
-          <t>2026-06-11 04:56:51</t>
+          <t>2026-06-11 07:05:44</t>
         </is>
       </c>
     </row>
@@ -3397,7 +3397,7 @@
         </is>
       </c>
       <c r="F12" t="n">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="G12" t="n">
         <v>1000</v>
@@ -3409,7 +3409,7 @@
         <v>1000</v>
       </c>
       <c r="J12" t="n">
-        <v>1.15</v>
+        <v>1.09</v>
       </c>
       <c r="K12" t="n">
         <v>1000</v>
@@ -3421,22 +3421,22 @@
         <v>1.01</v>
       </c>
       <c r="N12" t="n">
-        <v>1.32</v>
+        <v>5.7</v>
       </c>
       <c r="O12" t="n">
         <v>1.12</v>
       </c>
       <c r="P12" t="n">
-        <v>1.32</v>
+        <v>1.25</v>
       </c>
       <c r="Q12" t="n">
-        <v>1.11</v>
+        <v>1.13</v>
       </c>
       <c r="R12" t="n">
         <v>1.18</v>
       </c>
       <c r="S12" t="n">
-        <v>1.12</v>
+        <v>1.13</v>
       </c>
       <c r="T12" t="n">
         <v>1.11</v>
@@ -3620,7 +3620,7 @@
       </c>
       <c r="CB12" t="inlineStr">
         <is>
-          <t>2026-06-11 04:56:51</t>
+          <t>2026-06-11 07:05:44</t>
         </is>
       </c>
     </row>
@@ -3651,19 +3651,19 @@
         </is>
       </c>
       <c r="F13" t="n">
-        <v>1.15</v>
+        <v>1.19</v>
       </c>
       <c r="G13" t="n">
         <v>1000</v>
       </c>
       <c r="H13" t="n">
-        <v>1.15</v>
+        <v>1.19</v>
       </c>
       <c r="I13" t="n">
         <v>1000</v>
       </c>
       <c r="J13" t="n">
-        <v>1.1</v>
+        <v>3.25</v>
       </c>
       <c r="K13" t="n">
         <v>1000</v>
@@ -3675,13 +3675,13 @@
         <v>1.01</v>
       </c>
       <c r="N13" t="n">
-        <v>1.25</v>
+        <v>3.5</v>
       </c>
       <c r="O13" t="n">
-        <v>1.33</v>
+        <v>1.32</v>
       </c>
       <c r="P13" t="n">
-        <v>1.24</v>
+        <v>1.31</v>
       </c>
       <c r="Q13" t="n">
         <v>1.33</v>
@@ -3690,7 +3690,7 @@
         <v>1.18</v>
       </c>
       <c r="S13" t="n">
-        <v>1.33</v>
+        <v>1.32</v>
       </c>
       <c r="T13" t="n">
         <v>1.11</v>
@@ -3874,7 +3874,7 @@
       </c>
       <c r="CB13" t="inlineStr">
         <is>
-          <t>2026-06-11 04:56:51</t>
+          <t>2026-06-11 07:05:44</t>
         </is>
       </c>
     </row>
@@ -3905,19 +3905,19 @@
         </is>
       </c>
       <c r="F14" t="n">
-        <v>1.46</v>
+        <v>1.01</v>
       </c>
       <c r="G14" t="n">
         <v>1000</v>
       </c>
       <c r="H14" t="n">
-        <v>1.46</v>
+        <v>1.49</v>
       </c>
       <c r="I14" t="n">
         <v>1000</v>
       </c>
       <c r="J14" t="n">
-        <v>1.1</v>
+        <v>1.11</v>
       </c>
       <c r="K14" t="n">
         <v>3.25</v>
@@ -3929,13 +3929,13 @@
         <v>1.01</v>
       </c>
       <c r="N14" t="n">
-        <v>1.24</v>
+        <v>1.28</v>
       </c>
       <c r="O14" t="n">
-        <v>1.01</v>
+        <v>1.43</v>
       </c>
       <c r="P14" t="n">
-        <v>1.24</v>
+        <v>1.28</v>
       </c>
       <c r="Q14" t="n">
         <v>1.01</v>
@@ -3944,7 +3944,7 @@
         <v>1.12</v>
       </c>
       <c r="S14" t="n">
-        <v>1.52</v>
+        <v>1.05</v>
       </c>
       <c r="T14" t="n">
         <v>1.11</v>
@@ -3953,10 +3953,10 @@
         <v>1.11</v>
       </c>
       <c r="V14" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="W14" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="X14" t="n">
         <v>1000</v>
@@ -4128,7 +4128,7 @@
       </c>
       <c r="CB14" t="inlineStr">
         <is>
-          <t>2026-06-11 04:56:51</t>
+          <t>2026-06-11 07:05:44</t>
         </is>
       </c>
     </row>
@@ -4162,19 +4162,19 @@
         <v>2.74</v>
       </c>
       <c r="G15" t="n">
-        <v>3.4</v>
+        <v>3.25</v>
       </c>
       <c r="H15" t="n">
-        <v>2.36</v>
+        <v>2.12</v>
       </c>
       <c r="I15" t="n">
-        <v>2.88</v>
+        <v>2.9</v>
       </c>
       <c r="J15" t="n">
         <v>3.3</v>
       </c>
       <c r="K15" t="n">
-        <v>4.7</v>
+        <v>5.6</v>
       </c>
       <c r="L15" t="n">
         <v>1.01</v>
@@ -4183,7 +4183,7 @@
         <v>1.04</v>
       </c>
       <c r="N15" t="n">
-        <v>2.46</v>
+        <v>5</v>
       </c>
       <c r="O15" t="n">
         <v>1.2</v>
@@ -4192,7 +4192,7 @@
         <v>2.36</v>
       </c>
       <c r="Q15" t="n">
-        <v>1.39</v>
+        <v>1.63</v>
       </c>
       <c r="R15" t="n">
         <v>1.39</v>
@@ -4201,16 +4201,16 @@
         <v>2.16</v>
       </c>
       <c r="T15" t="n">
-        <v>1.48</v>
+        <v>1.5</v>
       </c>
       <c r="U15" t="n">
-        <v>2.28</v>
+        <v>2.3</v>
       </c>
       <c r="V15" t="n">
         <v>1.53</v>
       </c>
       <c r="W15" t="n">
-        <v>1.42</v>
+        <v>1.44</v>
       </c>
       <c r="X15" t="n">
         <v>1000</v>
@@ -4382,7 +4382,7 @@
       </c>
       <c r="CB15" t="inlineStr">
         <is>
-          <t>2026-06-11 04:56:51</t>
+          <t>2026-06-11 07:05:44</t>
         </is>
       </c>
     </row>
@@ -4413,7 +4413,7 @@
         </is>
       </c>
       <c r="F16" t="n">
-        <v>1.36</v>
+        <v>1.37</v>
       </c>
       <c r="G16" t="n">
         <v>1.42</v>
@@ -4437,7 +4437,7 @@
         <v>1.06</v>
       </c>
       <c r="N16" t="n">
-        <v>3.9</v>
+        <v>3.95</v>
       </c>
       <c r="O16" t="n">
         <v>1.28</v>
@@ -4449,7 +4449,7 @@
         <v>1.84</v>
       </c>
       <c r="R16" t="n">
-        <v>1.38</v>
+        <v>1.39</v>
       </c>
       <c r="S16" t="n">
         <v>3.15</v>
@@ -4473,19 +4473,19 @@
         <v>36</v>
       </c>
       <c r="Z16" t="n">
-        <v>130</v>
+        <v>120</v>
       </c>
       <c r="AA16" t="n">
-        <v>570</v>
+        <v>560</v>
       </c>
       <c r="AB16" t="n">
-        <v>7.8</v>
+        <v>8</v>
       </c>
       <c r="AC16" t="n">
         <v>14</v>
       </c>
       <c r="AD16" t="n">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="AE16" t="n">
         <v>250</v>
@@ -4500,7 +4500,7 @@
         <v>38</v>
       </c>
       <c r="AI16" t="n">
-        <v>210</v>
+        <v>200</v>
       </c>
       <c r="AJ16" t="n">
         <v>13.5</v>
@@ -4515,10 +4515,10 @@
         <v>250</v>
       </c>
       <c r="AN16" t="n">
-        <v>7.4</v>
+        <v>8</v>
       </c>
       <c r="AO16" t="n">
-        <v>410</v>
+        <v>400</v>
       </c>
       <c r="AP16" t="n">
         <v>14</v>
@@ -4527,10 +4527,10 @@
         <v>21</v>
       </c>
       <c r="AR16" t="n">
-        <v>5</v>
+        <v>4.7</v>
       </c>
       <c r="AS16" t="n">
-        <v>5.2</v>
+        <v>4.9</v>
       </c>
       <c r="AT16" t="n">
         <v>6.4</v>
@@ -4539,10 +4539,10 @@
         <v>10</v>
       </c>
       <c r="AV16" t="n">
-        <v>4.7</v>
+        <v>4.5</v>
       </c>
       <c r="AW16" t="n">
-        <v>5.1</v>
+        <v>4.8</v>
       </c>
       <c r="AX16" t="n">
         <v>6.6</v>
@@ -4551,10 +4551,10 @@
         <v>9</v>
       </c>
       <c r="AZ16" t="n">
-        <v>4.6</v>
+        <v>4.3</v>
       </c>
       <c r="BA16" t="n">
-        <v>5.1</v>
+        <v>4.8</v>
       </c>
       <c r="BB16" t="n">
         <v>9.4</v>
@@ -4563,16 +4563,16 @@
         <v>12</v>
       </c>
       <c r="BD16" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="BE16" t="n">
         <v>4.8</v>
-      </c>
-      <c r="BE16" t="n">
-        <v>5.1</v>
       </c>
       <c r="BF16" t="n">
         <v>6</v>
       </c>
       <c r="BG16" t="n">
-        <v>5.2</v>
+        <v>4.9</v>
       </c>
       <c r="BH16" t="n">
         <v>1000</v>
@@ -4636,7 +4636,7 @@
       </c>
       <c r="CB16" t="inlineStr">
         <is>
-          <t>2026-06-11 04:56:51</t>
+          <t>2026-06-11 07:05:44</t>
         </is>
       </c>
     </row>
@@ -4667,10 +4667,10 @@
         </is>
       </c>
       <c r="F17" t="n">
-        <v>2.2</v>
+        <v>2.22</v>
       </c>
       <c r="G17" t="n">
-        <v>2.42</v>
+        <v>2.38</v>
       </c>
       <c r="H17" t="n">
         <v>3.25</v>
@@ -4709,7 +4709,7 @@
         <v>3.1</v>
       </c>
       <c r="T17" t="n">
-        <v>1.67</v>
+        <v>1.7</v>
       </c>
       <c r="U17" t="n">
         <v>2.2</v>
@@ -4721,7 +4721,7 @@
         <v>1.72</v>
       </c>
       <c r="X17" t="n">
-        <v>20</v>
+        <v>19.5</v>
       </c>
       <c r="Y17" t="n">
         <v>15</v>
@@ -4730,7 +4730,7 @@
         <v>32</v>
       </c>
       <c r="AA17" t="n">
-        <v>65</v>
+        <v>60</v>
       </c>
       <c r="AB17" t="n">
         <v>11.5</v>
@@ -4739,7 +4739,7 @@
         <v>9.800000000000001</v>
       </c>
       <c r="AD17" t="n">
-        <v>15.5</v>
+        <v>15</v>
       </c>
       <c r="AE17" t="n">
         <v>46</v>
@@ -4820,7 +4820,7 @@
         <v>26</v>
       </c>
       <c r="BE17" t="n">
-        <v>5.9</v>
+        <v>6</v>
       </c>
       <c r="BF17" t="n">
         <v>13.5</v>
@@ -4838,7 +4838,7 @@
         <v>1000</v>
       </c>
       <c r="BK17" t="n">
-        <v>1.52</v>
+        <v>1.54</v>
       </c>
       <c r="BL17" t="n">
         <v>1000</v>
@@ -4850,13 +4850,13 @@
         <v>1000</v>
       </c>
       <c r="BO17" t="n">
-        <v>1.41</v>
+        <v>1.43</v>
       </c>
       <c r="BP17" t="n">
         <v>1000</v>
       </c>
       <c r="BQ17" t="n">
-        <v>1.6</v>
+        <v>1.62</v>
       </c>
       <c r="BR17" t="n">
         <v>1000</v>
@@ -4868,7 +4868,7 @@
         <v>1000</v>
       </c>
       <c r="BU17" t="n">
-        <v>1.46</v>
+        <v>1.48</v>
       </c>
       <c r="BV17" t="n">
         <v>1000</v>
@@ -4890,7 +4890,7 @@
       </c>
       <c r="CB17" t="inlineStr">
         <is>
-          <t>2026-06-11 04:56:51</t>
+          <t>2026-06-11 07:05:44</t>
         </is>
       </c>
     </row>
@@ -4924,7 +4924,7 @@
         <v>3.1</v>
       </c>
       <c r="G18" t="n">
-        <v>3.5</v>
+        <v>3.45</v>
       </c>
       <c r="H18" t="n">
         <v>2.42</v>
@@ -4939,7 +4939,7 @@
         <v>3.55</v>
       </c>
       <c r="L18" t="n">
-        <v>1.41</v>
+        <v>1.46</v>
       </c>
       <c r="M18" t="n">
         <v>1.09</v>
@@ -4954,7 +4954,7 @@
         <v>1.71</v>
       </c>
       <c r="Q18" t="n">
-        <v>2.2</v>
+        <v>2.18</v>
       </c>
       <c r="R18" t="n">
         <v>1.27</v>
@@ -4969,7 +4969,7 @@
         <v>1.96</v>
       </c>
       <c r="V18" t="n">
-        <v>1.6</v>
+        <v>1.61</v>
       </c>
       <c r="W18" t="n">
         <v>1.4</v>
@@ -5077,13 +5077,13 @@
         <v>8.800000000000001</v>
       </c>
       <c r="BF18" t="n">
-        <v>7.8</v>
+        <v>38</v>
       </c>
       <c r="BG18" t="n">
         <v>23</v>
       </c>
       <c r="BH18" t="n">
-        <v>3.2</v>
+        <v>3.15</v>
       </c>
       <c r="BI18" t="n">
         <v>2.56</v>
@@ -5098,7 +5098,7 @@
         <v>1000</v>
       </c>
       <c r="BM18" t="n">
-        <v>9.800000000000001</v>
+        <v>10</v>
       </c>
       <c r="BN18" t="n">
         <v>6.6</v>
@@ -5110,13 +5110,13 @@
         <v>1000</v>
       </c>
       <c r="BQ18" t="n">
-        <v>7.6</v>
+        <v>7.8</v>
       </c>
       <c r="BR18" t="n">
-        <v>1000</v>
+        <v>46</v>
       </c>
       <c r="BS18" t="n">
-        <v>8.6</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BT18" t="n">
         <v>5.5</v>
@@ -5128,23 +5128,23 @@
         <v>21</v>
       </c>
       <c r="BW18" t="n">
-        <v>7</v>
+        <v>7.2</v>
       </c>
       <c r="BX18" t="n">
         <v>1000</v>
       </c>
       <c r="BY18" t="n">
-        <v>8.199999999999999</v>
+        <v>8.4</v>
       </c>
       <c r="BZ18" t="n">
-        <v>1000</v>
+        <v>38</v>
       </c>
       <c r="CA18" t="n">
-        <v>8</v>
+        <v>8.4</v>
       </c>
       <c r="CB18" t="inlineStr">
         <is>
-          <t>2026-06-11 04:56:51</t>
+          <t>2026-06-11 07:05:44</t>
         </is>
       </c>
     </row>
@@ -5181,16 +5181,16 @@
         <v>5.6</v>
       </c>
       <c r="H19" t="n">
-        <v>1.75</v>
+        <v>1.85</v>
       </c>
       <c r="I19" t="n">
-        <v>2.26</v>
+        <v>2.22</v>
       </c>
       <c r="J19" t="n">
         <v>3.3</v>
       </c>
       <c r="K19" t="n">
-        <v>7.2</v>
+        <v>6</v>
       </c>
       <c r="L19" t="n">
         <v>1.01</v>
@@ -5223,10 +5223,10 @@
         <v>1.73</v>
       </c>
       <c r="V19" t="n">
-        <v>1.79</v>
+        <v>1.81</v>
       </c>
       <c r="W19" t="n">
-        <v>1.21</v>
+        <v>1.22</v>
       </c>
       <c r="X19" t="n">
         <v>1000</v>
@@ -5398,7 +5398,7 @@
       </c>
       <c r="CB19" t="inlineStr">
         <is>
-          <t>2026-06-11 04:56:51</t>
+          <t>2026-06-11 07:05:44</t>
         </is>
       </c>
     </row>
@@ -5438,7 +5438,7 @@
         <v>1.88</v>
       </c>
       <c r="I20" t="n">
-        <v>2.06</v>
+        <v>2.04</v>
       </c>
       <c r="J20" t="n">
         <v>3.7</v>
@@ -5453,13 +5453,13 @@
         <v>1.05</v>
       </c>
       <c r="N20" t="n">
-        <v>4.5</v>
+        <v>4.6</v>
       </c>
       <c r="O20" t="n">
         <v>1.23</v>
       </c>
       <c r="P20" t="n">
-        <v>2.24</v>
+        <v>2.2</v>
       </c>
       <c r="Q20" t="n">
         <v>1.68</v>
@@ -5468,7 +5468,7 @@
         <v>1.53</v>
       </c>
       <c r="S20" t="n">
-        <v>2.52</v>
+        <v>2.54</v>
       </c>
       <c r="T20" t="n">
         <v>1.63</v>
@@ -5477,7 +5477,7 @@
         <v>2.32</v>
       </c>
       <c r="V20" t="n">
-        <v>1.95</v>
+        <v>1.96</v>
       </c>
       <c r="W20" t="n">
         <v>1.28</v>
@@ -5495,7 +5495,7 @@
         <v>26</v>
       </c>
       <c r="AB20" t="n">
-        <v>19.5</v>
+        <v>19</v>
       </c>
       <c r="AC20" t="n">
         <v>10</v>
@@ -5522,7 +5522,7 @@
         <v>110</v>
       </c>
       <c r="AK20" t="n">
-        <v>42</v>
+        <v>46</v>
       </c>
       <c r="AL20" t="n">
         <v>50</v>
@@ -5567,10 +5567,10 @@
         <v>13.5</v>
       </c>
       <c r="AZ20" t="n">
-        <v>10.5</v>
+        <v>13</v>
       </c>
       <c r="BA20" t="n">
-        <v>6.6</v>
+        <v>6.4</v>
       </c>
       <c r="BB20" t="n">
         <v>7.6</v>
@@ -5579,10 +5579,10 @@
         <v>34</v>
       </c>
       <c r="BD20" t="n">
-        <v>7</v>
+        <v>36</v>
       </c>
       <c r="BE20" t="n">
-        <v>7.4</v>
+        <v>7.2</v>
       </c>
       <c r="BF20" t="n">
         <v>26</v>
@@ -5652,7 +5652,7 @@
       </c>
       <c r="CB20" t="inlineStr">
         <is>
-          <t>2026-06-11 04:56:51</t>
+          <t>2026-06-11 07:05:44</t>
         </is>
       </c>
     </row>
@@ -5686,88 +5686,88 @@
         <v>2.28</v>
       </c>
       <c r="G21" t="n">
-        <v>2.5</v>
+        <v>2.48</v>
       </c>
       <c r="H21" t="n">
-        <v>3.35</v>
+        <v>3.4</v>
       </c>
       <c r="I21" t="n">
         <v>3.75</v>
       </c>
       <c r="J21" t="n">
-        <v>3.2</v>
+        <v>3.15</v>
       </c>
       <c r="K21" t="n">
         <v>3.5</v>
       </c>
       <c r="L21" t="n">
-        <v>1.39</v>
+        <v>1.48</v>
       </c>
       <c r="M21" t="n">
         <v>1.09</v>
       </c>
       <c r="N21" t="n">
-        <v>3.15</v>
+        <v>3.05</v>
       </c>
       <c r="O21" t="n">
-        <v>1.4</v>
+        <v>1.41</v>
       </c>
       <c r="P21" t="n">
-        <v>1.75</v>
+        <v>1.7</v>
       </c>
       <c r="Q21" t="n">
-        <v>2.16</v>
+        <v>2.2</v>
       </c>
       <c r="R21" t="n">
-        <v>1.27</v>
+        <v>1.26</v>
       </c>
       <c r="S21" t="n">
-        <v>4</v>
+        <v>4.2</v>
       </c>
       <c r="T21" t="n">
-        <v>1.87</v>
+        <v>1.89</v>
       </c>
       <c r="U21" t="n">
-        <v>1.99</v>
+        <v>1.96</v>
       </c>
       <c r="V21" t="n">
         <v>1.37</v>
       </c>
       <c r="W21" t="n">
-        <v>1.66</v>
+        <v>1.67</v>
       </c>
       <c r="X21" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="Y21" t="n">
         <v>14</v>
       </c>
-      <c r="Y21" t="n">
-        <v>14.5</v>
-      </c>
       <c r="Z21" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="AA21" t="n">
         <v>85</v>
       </c>
       <c r="AB21" t="n">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="AC21" t="n">
         <v>9</v>
       </c>
       <c r="AD21" t="n">
-        <v>18</v>
+        <v>18.5</v>
       </c>
       <c r="AE21" t="n">
         <v>60</v>
       </c>
       <c r="AF21" t="n">
-        <v>18</v>
+        <v>17.5</v>
       </c>
       <c r="AG21" t="n">
         <v>14</v>
       </c>
       <c r="AH21" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="AI21" t="n">
         <v>75</v>
@@ -5779,7 +5779,7 @@
         <v>36</v>
       </c>
       <c r="AL21" t="n">
-        <v>55</v>
+        <v>60</v>
       </c>
       <c r="AM21" t="n">
         <v>150</v>
@@ -5788,10 +5788,10 @@
         <v>32</v>
       </c>
       <c r="AO21" t="n">
-        <v>65</v>
+        <v>70</v>
       </c>
       <c r="AP21" t="n">
-        <v>8.6</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AQ21" t="n">
         <v>8.6</v>
@@ -5800,52 +5800,52 @@
         <v>17.5</v>
       </c>
       <c r="AS21" t="n">
-        <v>4</v>
+        <v>4.1</v>
       </c>
       <c r="AT21" t="n">
-        <v>7.8</v>
+        <v>6.4</v>
       </c>
       <c r="AU21" t="n">
-        <v>6.6</v>
+        <v>5.6</v>
       </c>
       <c r="AV21" t="n">
         <v>11</v>
       </c>
       <c r="AW21" t="n">
-        <v>32</v>
+        <v>4</v>
       </c>
       <c r="AX21" t="n">
         <v>10.5</v>
       </c>
       <c r="AY21" t="n">
-        <v>8.4</v>
+        <v>8.6</v>
       </c>
       <c r="AZ21" t="n">
-        <v>13.5</v>
+        <v>14</v>
       </c>
       <c r="BA21" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="BB21" t="n">
+        <v>3.95</v>
+      </c>
+      <c r="BC21" t="n">
+        <v>21</v>
+      </c>
+      <c r="BD21" t="n">
         <v>4</v>
       </c>
-      <c r="BB21" t="n">
-        <v>3.9</v>
-      </c>
-      <c r="BC21" t="n">
-        <v>20</v>
-      </c>
-      <c r="BD21" t="n">
-        <v>3.95</v>
-      </c>
       <c r="BE21" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="BF21" t="n">
+        <v>18.5</v>
+      </c>
+      <c r="BG21" t="n">
         <v>4.1</v>
       </c>
-      <c r="BF21" t="n">
-        <v>21</v>
-      </c>
-      <c r="BG21" t="n">
-        <v>4</v>
-      </c>
       <c r="BH21" t="n">
-        <v>3.15</v>
+        <v>3.1</v>
       </c>
       <c r="BI21" t="n">
         <v>2.56</v>
@@ -5854,59 +5854,59 @@
         <v>10.5</v>
       </c>
       <c r="BK21" t="n">
-        <v>5.9</v>
+        <v>6</v>
       </c>
       <c r="BL21" t="n">
         <v>1000</v>
       </c>
       <c r="BM21" t="n">
-        <v>12.5</v>
+        <v>13.5</v>
       </c>
       <c r="BN21" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="BO21" t="n">
-        <v>3.95</v>
+        <v>3.9</v>
       </c>
       <c r="BP21" t="n">
-        <v>970</v>
+        <v>1000</v>
       </c>
       <c r="BQ21" t="n">
-        <v>8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BR21" t="n">
         <v>1000</v>
       </c>
       <c r="BS21" t="n">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="BT21" t="n">
         <v>6.6</v>
       </c>
       <c r="BU21" t="n">
-        <v>4.9</v>
+        <v>5</v>
       </c>
       <c r="BV21" t="n">
         <v>1000</v>
       </c>
       <c r="BW21" t="n">
-        <v>9.4</v>
+        <v>10</v>
       </c>
       <c r="BX21" t="n">
         <v>1000</v>
       </c>
       <c r="BY21" t="n">
+        <v>11</v>
+      </c>
+      <c r="BZ21" t="n">
+        <v>1000</v>
+      </c>
+      <c r="CA21" t="n">
         <v>10.5</v>
       </c>
-      <c r="BZ21" t="n">
-        <v>1000</v>
-      </c>
-      <c r="CA21" t="n">
-        <v>9.800000000000001</v>
-      </c>
       <c r="CB21" t="inlineStr">
         <is>
-          <t>2026-06-11 04:56:51</t>
+          <t>2026-06-11 07:05:44</t>
         </is>
       </c>
     </row>
@@ -5937,13 +5937,13 @@
         </is>
       </c>
       <c r="F22" t="n">
-        <v>4.3</v>
+        <v>4.2</v>
       </c>
       <c r="G22" t="n">
         <v>5</v>
       </c>
       <c r="H22" t="n">
-        <v>1.85</v>
+        <v>1.86</v>
       </c>
       <c r="I22" t="n">
         <v>2.02</v>
@@ -5952,10 +5952,10 @@
         <v>3.55</v>
       </c>
       <c r="K22" t="n">
-        <v>4</v>
+        <v>3.95</v>
       </c>
       <c r="L22" t="n">
-        <v>1.39</v>
+        <v>1.35</v>
       </c>
       <c r="M22" t="n">
         <v>1.06</v>
@@ -5967,13 +5967,13 @@
         <v>1.3</v>
       </c>
       <c r="P22" t="n">
-        <v>1.91</v>
+        <v>1.94</v>
       </c>
       <c r="Q22" t="n">
-        <v>1.9</v>
+        <v>1.89</v>
       </c>
       <c r="R22" t="n">
-        <v>1.34</v>
+        <v>1.35</v>
       </c>
       <c r="S22" t="n">
         <v>3.3</v>
@@ -6120,7 +6120,7 @@
         <v>8.199999999999999</v>
       </c>
       <c r="BO22" t="n">
-        <v>4.6</v>
+        <v>6</v>
       </c>
       <c r="BP22" t="n">
         <v>40</v>
@@ -6160,7 +6160,7 @@
       </c>
       <c r="CB22" t="inlineStr">
         <is>
-          <t>2026-06-11 04:56:51</t>
+          <t>2026-06-11 07:05:44</t>
         </is>
       </c>
     </row>
@@ -6194,7 +6194,7 @@
         <v>1.42</v>
       </c>
       <c r="G23" t="n">
-        <v>1.62</v>
+        <v>1.63</v>
       </c>
       <c r="H23" t="n">
         <v>4.8</v>
@@ -6414,7 +6414,7 @@
       </c>
       <c r="CB23" t="inlineStr">
         <is>
-          <t>2026-06-11 04:56:51</t>
+          <t>2026-06-11 07:05:44</t>
         </is>
       </c>
     </row>
@@ -6448,13 +6448,13 @@
         <v>2.78</v>
       </c>
       <c r="G24" t="n">
-        <v>3</v>
+        <v>2.98</v>
       </c>
       <c r="H24" t="n">
         <v>2.68</v>
       </c>
       <c r="I24" t="n">
-        <v>2.92</v>
+        <v>2.9</v>
       </c>
       <c r="J24" t="n">
         <v>3.2</v>
@@ -6484,7 +6484,7 @@
         <v>1.28</v>
       </c>
       <c r="S24" t="n">
-        <v>3.9</v>
+        <v>4</v>
       </c>
       <c r="T24" t="n">
         <v>1.85</v>
@@ -6493,7 +6493,7 @@
         <v>2.06</v>
       </c>
       <c r="V24" t="n">
-        <v>1.52</v>
+        <v>1.53</v>
       </c>
       <c r="W24" t="n">
         <v>1.5</v>
@@ -6514,7 +6514,7 @@
         <v>12.5</v>
       </c>
       <c r="AC24" t="n">
-        <v>9</v>
+        <v>7.6</v>
       </c>
       <c r="AD24" t="n">
         <v>15.5</v>
@@ -6559,10 +6559,10 @@
         <v>9.199999999999999</v>
       </c>
       <c r="AR24" t="n">
-        <v>3.7</v>
+        <v>4</v>
       </c>
       <c r="AS24" t="n">
-        <v>4.1</v>
+        <v>4.5</v>
       </c>
       <c r="AT24" t="n">
         <v>9.4</v>
@@ -6574,7 +6574,7 @@
         <v>11</v>
       </c>
       <c r="AW24" t="n">
-        <v>4</v>
+        <v>4.4</v>
       </c>
       <c r="AX24" t="n">
         <v>16.5</v>
@@ -6583,28 +6583,28 @@
         <v>11.5</v>
       </c>
       <c r="AZ24" t="n">
-        <v>3.7</v>
+        <v>4</v>
       </c>
       <c r="BA24" t="n">
-        <v>4.1</v>
+        <v>4.5</v>
       </c>
       <c r="BB24" t="n">
-        <v>4.1</v>
+        <v>4.5</v>
       </c>
       <c r="BC24" t="n">
-        <v>4</v>
+        <v>4.4</v>
       </c>
       <c r="BD24" t="n">
-        <v>4.1</v>
+        <v>4.5</v>
       </c>
       <c r="BE24" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="BF24" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="BG24" t="n">
         <v>4.3</v>
-      </c>
-      <c r="BF24" t="n">
-        <v>4</v>
-      </c>
-      <c r="BG24" t="n">
-        <v>4</v>
       </c>
       <c r="BH24" t="n">
         <v>1000</v>
@@ -6668,7 +6668,7 @@
       </c>
       <c r="CB24" t="inlineStr">
         <is>
-          <t>2026-06-11 04:56:51</t>
+          <t>2026-06-11 07:05:44</t>
         </is>
       </c>
     </row>
@@ -6699,19 +6699,19 @@
         </is>
       </c>
       <c r="F25" t="n">
-        <v>1.04</v>
+        <v>1.09</v>
       </c>
       <c r="G25" t="n">
         <v>1000</v>
       </c>
       <c r="H25" t="n">
-        <v>1.04</v>
+        <v>1.09</v>
       </c>
       <c r="I25" t="n">
         <v>1000</v>
       </c>
       <c r="J25" t="n">
-        <v>1.09</v>
+        <v>1.1</v>
       </c>
       <c r="K25" t="n">
         <v>1000</v>
@@ -6723,22 +6723,22 @@
         <v>1.01</v>
       </c>
       <c r="N25" t="n">
-        <v>1.33</v>
+        <v>2</v>
       </c>
       <c r="O25" t="n">
-        <v>1.12</v>
+        <v>1.11</v>
       </c>
       <c r="P25" t="n">
-        <v>1.33</v>
+        <v>2</v>
       </c>
       <c r="Q25" t="n">
-        <v>1.12</v>
+        <v>1.11</v>
       </c>
       <c r="R25" t="n">
         <v>1.24</v>
       </c>
       <c r="S25" t="n">
-        <v>1.12</v>
+        <v>1.11</v>
       </c>
       <c r="T25" t="n">
         <v>1.11</v>
@@ -6922,7 +6922,7 @@
       </c>
       <c r="CB25" t="inlineStr">
         <is>
-          <t>2026-06-11 04:56:51</t>
+          <t>2026-06-11 07:05:44</t>
         </is>
       </c>
     </row>
@@ -6953,7 +6953,7 @@
         </is>
       </c>
       <c r="F26" t="n">
-        <v>2.2</v>
+        <v>2.18</v>
       </c>
       <c r="G26" t="n">
         <v>2.34</v>
@@ -6983,16 +6983,16 @@
         <v>1.44</v>
       </c>
       <c r="P26" t="n">
-        <v>1.65</v>
+        <v>1.67</v>
       </c>
       <c r="Q26" t="n">
-        <v>2.28</v>
+        <v>2.3</v>
       </c>
       <c r="R26" t="n">
-        <v>1.24</v>
+        <v>1.27</v>
       </c>
       <c r="S26" t="n">
-        <v>4.4</v>
+        <v>4.5</v>
       </c>
       <c r="T26" t="n">
         <v>1.92</v>
@@ -7019,7 +7019,7 @@
         <v>95</v>
       </c>
       <c r="AB26" t="n">
-        <v>8.6</v>
+        <v>970</v>
       </c>
       <c r="AC26" t="n">
         <v>970</v>
@@ -7061,16 +7061,16 @@
         <v>75</v>
       </c>
       <c r="AP26" t="n">
-        <v>5</v>
+        <v>5.1</v>
       </c>
       <c r="AQ26" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="AR26" t="n">
-        <v>6.6</v>
+        <v>6.8</v>
       </c>
       <c r="AS26" t="n">
-        <v>8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AT26" t="n">
         <v>4.3</v>
@@ -7079,40 +7079,40 @@
         <v>6.4</v>
       </c>
       <c r="AV26" t="n">
-        <v>5.8</v>
+        <v>5.9</v>
       </c>
       <c r="AW26" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="AX26" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="AY26" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="AZ26" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="BA26" t="n">
+        <v>8</v>
+      </c>
+      <c r="BB26" t="n">
+        <v>7</v>
+      </c>
+      <c r="BC26" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="BD26" t="n">
         <v>7.6</v>
       </c>
-      <c r="AX26" t="n">
-        <v>5.4</v>
-      </c>
-      <c r="AY26" t="n">
-        <v>5</v>
-      </c>
-      <c r="AZ26" t="n">
-        <v>6.2</v>
-      </c>
-      <c r="BA26" t="n">
-        <v>7.8</v>
-      </c>
-      <c r="BB26" t="n">
-        <v>6.8</v>
-      </c>
-      <c r="BC26" t="n">
-        <v>6.6</v>
-      </c>
-      <c r="BD26" t="n">
-        <v>7.4</v>
-      </c>
       <c r="BE26" t="n">
-        <v>8.199999999999999</v>
+        <v>8.4</v>
       </c>
       <c r="BF26" t="n">
-        <v>6.4</v>
+        <v>18.5</v>
       </c>
       <c r="BG26" t="n">
-        <v>7.8</v>
+        <v>8</v>
       </c>
       <c r="BH26" t="n">
         <v>3.1</v>
@@ -7176,7 +7176,7 @@
       </c>
       <c r="CB26" t="inlineStr">
         <is>
-          <t>2026-06-11 04:56:51</t>
+          <t>2026-06-11 07:05:44</t>
         </is>
       </c>
     </row>
@@ -7219,7 +7219,7 @@
         <v>1000</v>
       </c>
       <c r="J27" t="n">
-        <v>2.7</v>
+        <v>4.4</v>
       </c>
       <c r="K27" t="n">
         <v>9.800000000000001</v>
@@ -7255,10 +7255,10 @@
         <v>1.11</v>
       </c>
       <c r="V27" t="n">
-        <v>1.08</v>
+        <v>1.09</v>
       </c>
       <c r="W27" t="n">
-        <v>2.7</v>
+        <v>2.8</v>
       </c>
       <c r="X27" t="n">
         <v>1000</v>
@@ -7430,7 +7430,7 @@
       </c>
       <c r="CB27" t="inlineStr">
         <is>
-          <t>2026-06-11 04:56:51</t>
+          <t>2026-06-11 07:05:44</t>
         </is>
       </c>
     </row>
@@ -7461,7 +7461,7 @@
         </is>
       </c>
       <c r="F28" t="n">
-        <v>2</v>
+        <v>1.99</v>
       </c>
       <c r="G28" t="n">
         <v>2.12</v>
@@ -7626,7 +7626,7 @@
         <v>3.75</v>
       </c>
       <c r="BI28" t="n">
-        <v>3</v>
+        <v>3.4</v>
       </c>
       <c r="BJ28" t="n">
         <v>9.199999999999999</v>
@@ -7684,7 +7684,7 @@
       </c>
       <c r="CB28" t="inlineStr">
         <is>
-          <t>2026-06-11 04:56:51</t>
+          <t>2026-06-11 07:05:44</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-06-12.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-06-12.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:CB28"/>
+  <dimension ref="A1:CB30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -857,19 +857,19 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>1.22</v>
+        <v>1.24</v>
       </c>
       <c r="G2" t="n">
-        <v>1000</v>
+        <v>600</v>
       </c>
       <c r="H2" t="n">
-        <v>1.09</v>
+        <v>1.04</v>
       </c>
       <c r="I2" t="n">
         <v>1000</v>
       </c>
       <c r="J2" t="n">
-        <v>1.09</v>
+        <v>1.1</v>
       </c>
       <c r="K2" t="n">
         <v>1000</v>
@@ -881,13 +881,13 @@
         <v>1.01</v>
       </c>
       <c r="N2" t="n">
-        <v>1.25</v>
+        <v>1.35</v>
       </c>
       <c r="O2" t="n">
         <v>1.3</v>
       </c>
       <c r="P2" t="n">
-        <v>1.24</v>
+        <v>1.34</v>
       </c>
       <c r="Q2" t="n">
         <v>1.3</v>
@@ -908,7 +908,7 @@
         <v>1.02</v>
       </c>
       <c r="W2" t="n">
-        <v>1.02</v>
+        <v>1.14</v>
       </c>
       <c r="X2" t="n">
         <v>1000</v>
@@ -1080,7 +1080,7 @@
       </c>
       <c r="CB2" t="inlineStr">
         <is>
-          <t>2026-06-11 07:05:44</t>
+          <t>2026-06-11 09:18:50</t>
         </is>
       </c>
     </row>
@@ -1123,7 +1123,7 @@
         <v>1000</v>
       </c>
       <c r="J3" t="n">
-        <v>1.09</v>
+        <v>1.1</v>
       </c>
       <c r="K3" t="n">
         <v>1000</v>
@@ -1135,7 +1135,7 @@
         <v>1.01</v>
       </c>
       <c r="N3" t="n">
-        <v>4.4</v>
+        <v>1.1</v>
       </c>
       <c r="O3" t="n">
         <v>1.21</v>
@@ -1334,7 +1334,7 @@
       </c>
       <c r="CB3" t="inlineStr">
         <is>
-          <t>2026-06-11 07:05:44</t>
+          <t>2026-06-11 09:18:50</t>
         </is>
       </c>
     </row>
@@ -1365,19 +1365,19 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>2.56</v>
+        <v>2.66</v>
       </c>
       <c r="G4" t="n">
-        <v>3.3</v>
+        <v>3.2</v>
       </c>
       <c r="H4" t="n">
-        <v>2.78</v>
+        <v>2.8</v>
       </c>
       <c r="I4" t="n">
         <v>3.5</v>
       </c>
       <c r="J4" t="n">
-        <v>2.54</v>
+        <v>2.56</v>
       </c>
       <c r="K4" t="n">
         <v>3.55</v>
@@ -1389,22 +1389,22 @@
         <v>1.14</v>
       </c>
       <c r="N4" t="n">
-        <v>2.42</v>
+        <v>2.38</v>
       </c>
       <c r="O4" t="n">
-        <v>1.59</v>
+        <v>1.58</v>
       </c>
       <c r="P4" t="n">
         <v>1.5</v>
       </c>
       <c r="Q4" t="n">
-        <v>2.5</v>
+        <v>2.52</v>
       </c>
       <c r="R4" t="n">
-        <v>1.19</v>
+        <v>1.18</v>
       </c>
       <c r="S4" t="n">
-        <v>3.95</v>
+        <v>4.7</v>
       </c>
       <c r="T4" t="n">
         <v>2.14</v>
@@ -1416,7 +1416,7 @@
         <v>1.41</v>
       </c>
       <c r="W4" t="n">
-        <v>1.45</v>
+        <v>1.46</v>
       </c>
       <c r="X4" t="n">
         <v>970</v>
@@ -1425,7 +1425,7 @@
         <v>970</v>
       </c>
       <c r="Z4" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="AA4" t="n">
         <v>75</v>
@@ -1443,7 +1443,7 @@
         <v>60</v>
       </c>
       <c r="AF4" t="n">
-        <v>21</v>
+        <v>970</v>
       </c>
       <c r="AG4" t="n">
         <v>970</v>
@@ -1473,61 +1473,61 @@
         <v>1000</v>
       </c>
       <c r="AP4" t="n">
-        <v>1.01</v>
+        <v>3.7</v>
       </c>
       <c r="AQ4" t="n">
-        <v>1.01</v>
+        <v>3.75</v>
       </c>
       <c r="AR4" t="n">
-        <v>1.01</v>
+        <v>2.34</v>
       </c>
       <c r="AS4" t="n">
-        <v>1.03</v>
+        <v>2.34</v>
       </c>
       <c r="AT4" t="n">
-        <v>1.01</v>
+        <v>3.65</v>
       </c>
       <c r="AU4" t="n">
-        <v>1.01</v>
+        <v>3.45</v>
       </c>
       <c r="AV4" t="n">
-        <v>1.01</v>
+        <v>2.26</v>
       </c>
       <c r="AW4" t="n">
-        <v>1.01</v>
+        <v>2.32</v>
       </c>
       <c r="AX4" t="n">
-        <v>1.01</v>
+        <v>2.28</v>
       </c>
       <c r="AY4" t="n">
-        <v>1.01</v>
+        <v>2.22</v>
       </c>
       <c r="AZ4" t="n">
-        <v>1.01</v>
+        <v>2.38</v>
       </c>
       <c r="BA4" t="n">
-        <v>1.03</v>
+        <v>2.36</v>
       </c>
       <c r="BB4" t="n">
-        <v>1.03</v>
+        <v>2.32</v>
       </c>
       <c r="BC4" t="n">
-        <v>1.01</v>
+        <v>5.9</v>
       </c>
       <c r="BD4" t="n">
-        <v>1.03</v>
+        <v>2.34</v>
       </c>
       <c r="BE4" t="n">
-        <v>1.03</v>
+        <v>2.38</v>
       </c>
       <c r="BF4" t="n">
-        <v>1.01</v>
+        <v>2.34</v>
       </c>
       <c r="BG4" t="n">
-        <v>1.01</v>
+        <v>2.34</v>
       </c>
       <c r="BH4" t="n">
-        <v>2.84</v>
+        <v>2.94</v>
       </c>
       <c r="BI4" t="n">
         <v>1.04</v>
@@ -1536,59 +1536,59 @@
         <v>1000</v>
       </c>
       <c r="BK4" t="n">
-        <v>1.56</v>
+        <v>1.53</v>
       </c>
       <c r="BL4" t="n">
         <v>1000</v>
       </c>
       <c r="BM4" t="n">
-        <v>1.56</v>
+        <v>1.53</v>
       </c>
       <c r="BN4" t="n">
         <v>1000</v>
       </c>
       <c r="BO4" t="n">
-        <v>1.56</v>
+        <v>1.53</v>
       </c>
       <c r="BP4" t="n">
         <v>1000</v>
       </c>
       <c r="BQ4" t="n">
-        <v>1.56</v>
+        <v>1.53</v>
       </c>
       <c r="BR4" t="n">
         <v>1000</v>
       </c>
       <c r="BS4" t="n">
-        <v>1.56</v>
+        <v>1.53</v>
       </c>
       <c r="BT4" t="n">
         <v>1000</v>
       </c>
       <c r="BU4" t="n">
-        <v>1.56</v>
+        <v>1.53</v>
       </c>
       <c r="BV4" t="n">
         <v>1000</v>
       </c>
       <c r="BW4" t="n">
-        <v>1.56</v>
+        <v>1.53</v>
       </c>
       <c r="BX4" t="n">
         <v>1000</v>
       </c>
       <c r="BY4" t="n">
-        <v>1.56</v>
+        <v>1.53</v>
       </c>
       <c r="BZ4" t="n">
         <v>1000</v>
       </c>
       <c r="CA4" t="n">
-        <v>1.56</v>
+        <v>1.53</v>
       </c>
       <c r="CB4" t="inlineStr">
         <is>
-          <t>2026-06-11 07:05:44</t>
+          <t>2026-06-11 09:18:50</t>
         </is>
       </c>
     </row>
@@ -1619,10 +1619,10 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>2.14</v>
+        <v>2.18</v>
       </c>
       <c r="G5" t="n">
-        <v>2.38</v>
+        <v>2.42</v>
       </c>
       <c r="H5" t="n">
         <v>3.7</v>
@@ -1631,160 +1631,160 @@
         <v>4.5</v>
       </c>
       <c r="J5" t="n">
-        <v>2.9</v>
+        <v>2.96</v>
       </c>
       <c r="K5" t="n">
-        <v>3.25</v>
+        <v>3.3</v>
       </c>
       <c r="L5" t="n">
-        <v>1.52</v>
+        <v>1.01</v>
       </c>
       <c r="M5" t="n">
-        <v>1.01</v>
+        <v>1.13</v>
       </c>
       <c r="N5" t="n">
-        <v>2.52</v>
+        <v>2.46</v>
       </c>
       <c r="O5" t="n">
-        <v>1.5</v>
+        <v>1.56</v>
       </c>
       <c r="P5" t="n">
-        <v>1.43</v>
+        <v>1.49</v>
       </c>
       <c r="Q5" t="n">
-        <v>2.48</v>
+        <v>2.68</v>
       </c>
       <c r="R5" t="n">
         <v>1.18</v>
       </c>
       <c r="S5" t="n">
-        <v>3.05</v>
+        <v>5.5</v>
       </c>
       <c r="T5" t="n">
-        <v>1.11</v>
+        <v>2.16</v>
       </c>
       <c r="U5" t="n">
-        <v>1.11</v>
+        <v>1.71</v>
       </c>
       <c r="V5" t="n">
-        <v>1.28</v>
+        <v>1.29</v>
       </c>
       <c r="W5" t="n">
-        <v>1.72</v>
+        <v>1.71</v>
       </c>
       <c r="X5" t="n">
-        <v>1000</v>
+        <v>9.4</v>
       </c>
       <c r="Y5" t="n">
-        <v>1000</v>
+        <v>12.5</v>
       </c>
       <c r="Z5" t="n">
-        <v>1000</v>
+        <v>36</v>
       </c>
       <c r="AA5" t="n">
-        <v>1000</v>
+        <v>130</v>
       </c>
       <c r="AB5" t="n">
-        <v>1000</v>
+        <v>7</v>
       </c>
       <c r="AC5" t="n">
-        <v>1000</v>
+        <v>7.6</v>
       </c>
       <c r="AD5" t="n">
-        <v>1000</v>
+        <v>22</v>
       </c>
       <c r="AE5" t="n">
-        <v>1000</v>
+        <v>90</v>
       </c>
       <c r="AF5" t="n">
-        <v>1000</v>
+        <v>14.5</v>
       </c>
       <c r="AG5" t="n">
-        <v>1000</v>
+        <v>14</v>
       </c>
       <c r="AH5" t="n">
-        <v>1000</v>
+        <v>29</v>
       </c>
       <c r="AI5" t="n">
-        <v>1000</v>
+        <v>120</v>
       </c>
       <c r="AJ5" t="n">
-        <v>1000</v>
+        <v>34</v>
       </c>
       <c r="AK5" t="n">
-        <v>1000</v>
+        <v>40</v>
       </c>
       <c r="AL5" t="n">
-        <v>1000</v>
+        <v>80</v>
       </c>
       <c r="AM5" t="n">
-        <v>1000</v>
+        <v>250</v>
       </c>
       <c r="AN5" t="n">
-        <v>1000</v>
+        <v>36</v>
       </c>
       <c r="AO5" t="n">
-        <v>1000</v>
+        <v>140</v>
       </c>
       <c r="AP5" t="n">
-        <v>1.01</v>
+        <v>3.9</v>
       </c>
       <c r="AQ5" t="n">
-        <v>1.01</v>
+        <v>4.3</v>
       </c>
       <c r="AR5" t="n">
-        <v>1.01</v>
+        <v>5.5</v>
       </c>
       <c r="AS5" t="n">
-        <v>1.01</v>
+        <v>6.4</v>
       </c>
       <c r="AT5" t="n">
-        <v>1.01</v>
+        <v>3.45</v>
       </c>
       <c r="AU5" t="n">
-        <v>1.01</v>
+        <v>3.55</v>
       </c>
       <c r="AV5" t="n">
-        <v>1.01</v>
+        <v>5.1</v>
       </c>
       <c r="AW5" t="n">
-        <v>1.01</v>
+        <v>6.2</v>
       </c>
       <c r="AX5" t="n">
-        <v>1.01</v>
+        <v>4.6</v>
       </c>
       <c r="AY5" t="n">
-        <v>1.01</v>
+        <v>4.5</v>
       </c>
       <c r="AZ5" t="n">
-        <v>1.01</v>
+        <v>5.4</v>
       </c>
       <c r="BA5" t="n">
-        <v>1.01</v>
+        <v>6.2</v>
       </c>
       <c r="BB5" t="n">
-        <v>1.01</v>
+        <v>5.6</v>
       </c>
       <c r="BC5" t="n">
-        <v>1.01</v>
+        <v>5.6</v>
       </c>
       <c r="BD5" t="n">
-        <v>1.01</v>
+        <v>6.2</v>
       </c>
       <c r="BE5" t="n">
-        <v>1.01</v>
+        <v>6.4</v>
       </c>
       <c r="BF5" t="n">
-        <v>1.01</v>
+        <v>5.6</v>
       </c>
       <c r="BG5" t="n">
-        <v>1.01</v>
+        <v>6.4</v>
       </c>
       <c r="BH5" t="n">
         <v>1000</v>
       </c>
       <c r="BI5" t="n">
-        <v>1.04</v>
+        <v>2.12</v>
       </c>
       <c r="BJ5" t="n">
         <v>1000</v>
@@ -1842,7 +1842,7 @@
       </c>
       <c r="CB5" t="inlineStr">
         <is>
-          <t>2026-06-11 07:05:44</t>
+          <t>2026-06-11 09:18:50</t>
         </is>
       </c>
     </row>
@@ -1873,46 +1873,46 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>3.35</v>
+        <v>2.96</v>
       </c>
       <c r="G6" t="n">
-        <v>4.7</v>
+        <v>4.1</v>
       </c>
       <c r="H6" t="n">
-        <v>1.96</v>
+        <v>2</v>
       </c>
       <c r="I6" t="n">
-        <v>2.28</v>
+        <v>2.44</v>
       </c>
       <c r="J6" t="n">
-        <v>3.3</v>
+        <v>3.25</v>
       </c>
       <c r="K6" t="n">
-        <v>5.2</v>
+        <v>6.2</v>
       </c>
       <c r="L6" t="n">
-        <v>1.28</v>
+        <v>1.3</v>
       </c>
       <c r="M6" t="n">
         <v>1.01</v>
       </c>
       <c r="N6" t="n">
-        <v>1.1</v>
+        <v>0</v>
       </c>
       <c r="O6" t="n">
-        <v>1.24</v>
+        <v>0</v>
       </c>
       <c r="P6" t="n">
-        <v>2.04</v>
+        <v>1.91</v>
       </c>
       <c r="Q6" t="n">
-        <v>1.81</v>
+        <v>1.84</v>
       </c>
       <c r="R6" t="n">
-        <v>1.31</v>
+        <v>1.32</v>
       </c>
       <c r="S6" t="n">
-        <v>2.82</v>
+        <v>2.74</v>
       </c>
       <c r="T6" t="n">
         <v>1.11</v>
@@ -1921,10 +1921,10 @@
         <v>1.11</v>
       </c>
       <c r="V6" t="n">
-        <v>1.78</v>
+        <v>1.7</v>
       </c>
       <c r="W6" t="n">
-        <v>1.27</v>
+        <v>1.32</v>
       </c>
       <c r="X6" t="n">
         <v>1000</v>
@@ -2096,14 +2096,14 @@
       </c>
       <c r="CB6" t="inlineStr">
         <is>
-          <t>2026-06-11 07:05:44</t>
+          <t>2026-06-11 09:18:50</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Lithuanian A Lyga</t>
+          <t>Latvian Virsliga</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -2118,61 +2118,61 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>FC Dziugas</t>
+          <t>Liepajas Metalurgs</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Fk Siauliai</t>
+          <t>SK Super Nova</t>
         </is>
       </c>
       <c r="F7" t="n">
-        <v>1.21</v>
+        <v>1.06</v>
       </c>
       <c r="G7" t="n">
         <v>1000</v>
       </c>
       <c r="H7" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="I7" t="n">
+        <v>1000</v>
+      </c>
+      <c r="J7" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="K7" t="n">
+        <v>1000</v>
+      </c>
+      <c r="L7" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="M7" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="N7" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="O7" t="n">
         <v>1.22</v>
       </c>
-      <c r="I7" t="n">
-        <v>1000</v>
-      </c>
-      <c r="J7" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="K7" t="n">
-        <v>1000</v>
-      </c>
-      <c r="L7" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="M7" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="N7" t="n">
+      <c r="P7" t="n">
         <v>1.25</v>
       </c>
-      <c r="O7" t="n">
-        <v>1.28</v>
-      </c>
-      <c r="P7" t="n">
-        <v>1.24</v>
-      </c>
       <c r="Q7" t="n">
-        <v>1.28</v>
+        <v>1.22</v>
       </c>
       <c r="R7" t="n">
         <v>1.18</v>
       </c>
       <c r="S7" t="n">
-        <v>1.28</v>
+        <v>1.22</v>
       </c>
       <c r="T7" t="n">
-        <v>1.11</v>
+        <v>1.01</v>
       </c>
       <c r="U7" t="n">
-        <v>1.11</v>
+        <v>1.01</v>
       </c>
       <c r="V7" t="n">
         <v>1.02</v>
@@ -2292,72 +2292,72 @@
         <v>1000</v>
       </c>
       <c r="BI7" t="n">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="BJ7" t="n">
         <v>1000</v>
       </c>
       <c r="BK7" t="n">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="BL7" t="n">
         <v>1000</v>
       </c>
       <c r="BM7" t="n">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="BN7" t="n">
         <v>1000</v>
       </c>
       <c r="BO7" t="n">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="BP7" t="n">
         <v>1000</v>
       </c>
       <c r="BQ7" t="n">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="BR7" t="n">
         <v>1000</v>
       </c>
       <c r="BS7" t="n">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="BT7" t="n">
         <v>1000</v>
       </c>
       <c r="BU7" t="n">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="BV7" t="n">
         <v>1000</v>
       </c>
       <c r="BW7" t="n">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="BX7" t="n">
         <v>1000</v>
       </c>
       <c r="BY7" t="n">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="BZ7" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="CA7" t="n">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="CB7" t="inlineStr">
         <is>
-          <t>2026-06-11 07:05:44</t>
+          <t>2026-06-11 09:18:50</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Swedish Division 1</t>
+          <t>Lithuanian A Lyga</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -2367,36 +2367,36 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>14:00:00</t>
+          <t>13:00:00</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>Lunds BK</t>
+          <t>FC Dziugas</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Ariana FC</t>
+          <t>Fk Siauliai</t>
         </is>
       </c>
       <c r="F8" t="n">
-        <v>1.34</v>
+        <v>1.09</v>
       </c>
       <c r="G8" t="n">
-        <v>95</v>
+        <v>1000</v>
       </c>
       <c r="H8" t="n">
-        <v>1.21</v>
+        <v>1.09</v>
       </c>
       <c r="I8" t="n">
-        <v>95</v>
+        <v>1000</v>
       </c>
       <c r="J8" t="n">
-        <v>1.43</v>
+        <v>1.46</v>
       </c>
       <c r="K8" t="n">
-        <v>32</v>
+        <v>950</v>
       </c>
       <c r="L8" t="n">
         <v>1.01</v>
@@ -2405,22 +2405,22 @@
         <v>1.01</v>
       </c>
       <c r="N8" t="n">
-        <v>1.26</v>
+        <v>1.25</v>
       </c>
       <c r="O8" t="n">
-        <v>1.25</v>
+        <v>1.28</v>
       </c>
       <c r="P8" t="n">
-        <v>1.25</v>
+        <v>1.24</v>
       </c>
       <c r="Q8" t="n">
-        <v>1.24</v>
+        <v>1.28</v>
       </c>
       <c r="R8" t="n">
-        <v>1.24</v>
+        <v>1.18</v>
       </c>
       <c r="S8" t="n">
-        <v>1.25</v>
+        <v>1.28</v>
       </c>
       <c r="T8" t="n">
         <v>1.11</v>
@@ -2432,7 +2432,7 @@
         <v>1.02</v>
       </c>
       <c r="W8" t="n">
-        <v>1.02</v>
+        <v>1.05</v>
       </c>
       <c r="X8" t="n">
         <v>1000</v>
@@ -2604,14 +2604,14 @@
       </c>
       <c r="CB8" t="inlineStr">
         <is>
-          <t>2026-06-11 07:05:44</t>
+          <t>2026-06-11 09:18:50</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Swedish Division 1</t>
+          <t>Norwegian 2nd Division</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -2621,33 +2621,33 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>14:00:00</t>
+          <t>13:00:00</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>Umea FC</t>
+          <t>Follo</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Pitea</t>
+          <t>Kjelsas</t>
         </is>
       </c>
       <c r="F9" t="n">
-        <v>1.09</v>
+        <v>1.06</v>
       </c>
       <c r="G9" t="n">
         <v>1000</v>
       </c>
       <c r="H9" t="n">
-        <v>1.04</v>
+        <v>1.06</v>
       </c>
       <c r="I9" t="n">
         <v>1000</v>
       </c>
       <c r="J9" t="n">
-        <v>1.09</v>
+        <v>1.04</v>
       </c>
       <c r="K9" t="n">
         <v>1000</v>
@@ -2659,28 +2659,28 @@
         <v>1.01</v>
       </c>
       <c r="N9" t="n">
-        <v>1.32</v>
+        <v>1.25</v>
       </c>
       <c r="O9" t="n">
-        <v>1.15</v>
+        <v>1.01</v>
       </c>
       <c r="P9" t="n">
-        <v>1.3</v>
+        <v>1.25</v>
       </c>
       <c r="Q9" t="n">
-        <v>1.15</v>
+        <v>1.01</v>
       </c>
       <c r="R9" t="n">
         <v>1.24</v>
       </c>
       <c r="S9" t="n">
-        <v>1.14</v>
+        <v>1.01</v>
       </c>
       <c r="T9" t="n">
-        <v>1.11</v>
+        <v>1.01</v>
       </c>
       <c r="U9" t="n">
-        <v>1.11</v>
+        <v>1.01</v>
       </c>
       <c r="V9" t="n">
         <v>1.02</v>
@@ -2800,72 +2800,72 @@
         <v>1000</v>
       </c>
       <c r="BI9" t="n">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="BJ9" t="n">
         <v>1000</v>
       </c>
       <c r="BK9" t="n">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="BL9" t="n">
         <v>1000</v>
       </c>
       <c r="BM9" t="n">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="BN9" t="n">
         <v>1000</v>
       </c>
       <c r="BO9" t="n">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="BP9" t="n">
         <v>1000</v>
       </c>
       <c r="BQ9" t="n">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="BR9" t="n">
         <v>1000</v>
       </c>
       <c r="BS9" t="n">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="BT9" t="n">
         <v>1000</v>
       </c>
       <c r="BU9" t="n">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="BV9" t="n">
         <v>1000</v>
       </c>
       <c r="BW9" t="n">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="BX9" t="n">
         <v>1000</v>
       </c>
       <c r="BY9" t="n">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="BZ9" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="CA9" t="n">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="CB9" t="inlineStr">
         <is>
-          <t>2026-06-11 07:05:44</t>
+          <t>2026-06-11 09:18:50</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Moroccan Botola Pro 1</t>
+          <t>Georgian Umaglesi Liga</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -2880,31 +2880,31 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>DHJ El Jadida</t>
+          <t>Dinamo Batumi</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Olympique Dcheira</t>
+          <t>Dila Gori</t>
         </is>
       </c>
       <c r="F10" t="n">
-        <v>2.12</v>
+        <v>2</v>
       </c>
       <c r="G10" t="n">
-        <v>2.6</v>
+        <v>1000</v>
       </c>
       <c r="H10" t="n">
-        <v>3.3</v>
+        <v>1.23</v>
       </c>
       <c r="I10" t="n">
-        <v>4.8</v>
+        <v>1000</v>
       </c>
       <c r="J10" t="n">
-        <v>2.78</v>
+        <v>1.52</v>
       </c>
       <c r="K10" t="n">
-        <v>4.4</v>
+        <v>100</v>
       </c>
       <c r="L10" t="n">
         <v>1.01</v>
@@ -2913,22 +2913,22 @@
         <v>1.01</v>
       </c>
       <c r="N10" t="n">
-        <v>2.28</v>
+        <v>1.33</v>
       </c>
       <c r="O10" t="n">
-        <v>1.46</v>
+        <v>1.32</v>
       </c>
       <c r="P10" t="n">
-        <v>1.43</v>
+        <v>1.33</v>
       </c>
       <c r="Q10" t="n">
-        <v>2.48</v>
+        <v>1.32</v>
       </c>
       <c r="R10" t="n">
         <v>1.18</v>
       </c>
       <c r="S10" t="n">
-        <v>3</v>
+        <v>1.06</v>
       </c>
       <c r="T10" t="n">
         <v>1.11</v>
@@ -2937,10 +2937,10 @@
         <v>1.11</v>
       </c>
       <c r="V10" t="n">
-        <v>1.26</v>
+        <v>1.02</v>
       </c>
       <c r="W10" t="n">
-        <v>1.62</v>
+        <v>1.02</v>
       </c>
       <c r="X10" t="n">
         <v>1000</v>
@@ -3051,7 +3051,7 @@
         <v>1.01</v>
       </c>
       <c r="BH10" t="n">
-        <v>3.2</v>
+        <v>1000</v>
       </c>
       <c r="BI10" t="n">
         <v>1.04</v>
@@ -3060,66 +3060,66 @@
         <v>1000</v>
       </c>
       <c r="BK10" t="n">
-        <v>1.47</v>
+        <v>1.04</v>
       </c>
       <c r="BL10" t="n">
         <v>1000</v>
       </c>
       <c r="BM10" t="n">
-        <v>1.47</v>
+        <v>1.04</v>
       </c>
       <c r="BN10" t="n">
         <v>1000</v>
       </c>
       <c r="BO10" t="n">
-        <v>1.47</v>
+        <v>1.04</v>
       </c>
       <c r="BP10" t="n">
         <v>1000</v>
       </c>
       <c r="BQ10" t="n">
-        <v>1.47</v>
+        <v>1.04</v>
       </c>
       <c r="BR10" t="n">
         <v>1000</v>
       </c>
       <c r="BS10" t="n">
-        <v>1.47</v>
+        <v>1.04</v>
       </c>
       <c r="BT10" t="n">
         <v>1000</v>
       </c>
       <c r="BU10" t="n">
-        <v>1.47</v>
+        <v>1.04</v>
       </c>
       <c r="BV10" t="n">
         <v>1000</v>
       </c>
       <c r="BW10" t="n">
-        <v>1.47</v>
+        <v>1.04</v>
       </c>
       <c r="BX10" t="n">
         <v>1000</v>
       </c>
       <c r="BY10" t="n">
-        <v>1.47</v>
+        <v>1.04</v>
       </c>
       <c r="BZ10" t="n">
         <v>1000</v>
       </c>
       <c r="CA10" t="n">
-        <v>1.47</v>
+        <v>1.04</v>
       </c>
       <c r="CB10" t="inlineStr">
         <is>
-          <t>2026-06-11 07:05:44</t>
+          <t>2026-06-11 09:18:50</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Moroccan Botola Pro 1</t>
+          <t>Lithuanian A Lyga</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -3134,73 +3134,73 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>CODM Meknes</t>
+          <t>VMFD Zalgiris</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Club R Zemamra</t>
+          <t>Riteriai</t>
         </is>
       </c>
       <c r="F11" t="n">
-        <v>1.2</v>
+        <v>1.12</v>
       </c>
       <c r="G11" t="n">
-        <v>1000</v>
+        <v>1.16</v>
       </c>
       <c r="H11" t="n">
-        <v>1.22</v>
+        <v>1.09</v>
       </c>
       <c r="I11" t="n">
-        <v>1000</v>
+        <v>55</v>
       </c>
       <c r="J11" t="n">
-        <v>1.1</v>
+        <v>10.5</v>
       </c>
       <c r="K11" t="n">
-        <v>1000</v>
+        <v>32</v>
       </c>
       <c r="L11" t="n">
-        <v>1.01</v>
+        <v>1.19</v>
       </c>
       <c r="M11" t="n">
         <v>1.01</v>
       </c>
       <c r="N11" t="n">
-        <v>1.36</v>
+        <v>3.45</v>
       </c>
       <c r="O11" t="n">
-        <v>1.02</v>
+        <v>1.12</v>
       </c>
       <c r="P11" t="n">
-        <v>1.36</v>
+        <v>2.92</v>
       </c>
       <c r="Q11" t="n">
-        <v>1.56</v>
+        <v>1.37</v>
       </c>
       <c r="R11" t="n">
-        <v>1.18</v>
+        <v>1.88</v>
       </c>
       <c r="S11" t="n">
-        <v>1.56</v>
+        <v>1.94</v>
       </c>
       <c r="T11" t="n">
-        <v>1.11</v>
+        <v>2.4</v>
       </c>
       <c r="U11" t="n">
-        <v>1.11</v>
+        <v>1.57</v>
       </c>
       <c r="V11" t="n">
         <v>1.02</v>
       </c>
       <c r="W11" t="n">
-        <v>1.02</v>
+        <v>7.2</v>
       </c>
       <c r="X11" t="n">
-        <v>1000</v>
+        <v>950</v>
       </c>
       <c r="Y11" t="n">
-        <v>1000</v>
+        <v>950</v>
       </c>
       <c r="Z11" t="n">
         <v>1000</v>
@@ -3209,10 +3209,10 @@
         <v>1000</v>
       </c>
       <c r="AB11" t="n">
-        <v>1000</v>
+        <v>970</v>
       </c>
       <c r="AC11" t="n">
-        <v>1000</v>
+        <v>950</v>
       </c>
       <c r="AD11" t="n">
         <v>1000</v>
@@ -3221,159 +3221,159 @@
         <v>1000</v>
       </c>
       <c r="AF11" t="n">
-        <v>1000</v>
+        <v>970</v>
       </c>
       <c r="AG11" t="n">
-        <v>1000</v>
+        <v>970</v>
       </c>
       <c r="AH11" t="n">
-        <v>1000</v>
+        <v>950</v>
       </c>
       <c r="AI11" t="n">
         <v>1000</v>
       </c>
       <c r="AJ11" t="n">
-        <v>1000</v>
+        <v>970</v>
       </c>
       <c r="AK11" t="n">
-        <v>1000</v>
+        <v>970</v>
       </c>
       <c r="AL11" t="n">
-        <v>1000</v>
+        <v>65</v>
       </c>
       <c r="AM11" t="n">
         <v>1000</v>
       </c>
       <c r="AN11" t="n">
-        <v>1000</v>
+        <v>2.88</v>
       </c>
       <c r="AO11" t="n">
         <v>1000</v>
       </c>
       <c r="AP11" t="n">
-        <v>1.03</v>
+        <v>4.4</v>
       </c>
       <c r="AQ11" t="n">
-        <v>1.03</v>
+        <v>1.79</v>
       </c>
       <c r="AR11" t="n">
-        <v>1.03</v>
+        <v>1.81</v>
       </c>
       <c r="AS11" t="n">
-        <v>1.03</v>
+        <v>1.82</v>
       </c>
       <c r="AT11" t="n">
-        <v>1.03</v>
+        <v>4.9</v>
       </c>
       <c r="AU11" t="n">
-        <v>1.03</v>
+        <v>4.2</v>
       </c>
       <c r="AV11" t="n">
-        <v>1.03</v>
+        <v>1.8</v>
       </c>
       <c r="AW11" t="n">
-        <v>1.03</v>
+        <v>1.82</v>
       </c>
       <c r="AX11" t="n">
-        <v>1.03</v>
+        <v>4</v>
       </c>
       <c r="AY11" t="n">
-        <v>1.03</v>
+        <v>4.8</v>
       </c>
       <c r="AZ11" t="n">
-        <v>1.03</v>
+        <v>4.5</v>
       </c>
       <c r="BA11" t="n">
-        <v>1.03</v>
+        <v>1.82</v>
       </c>
       <c r="BB11" t="n">
-        <v>1.03</v>
+        <v>4.1</v>
       </c>
       <c r="BC11" t="n">
-        <v>1.03</v>
+        <v>3.85</v>
       </c>
       <c r="BD11" t="n">
-        <v>1.03</v>
+        <v>4.5</v>
       </c>
       <c r="BE11" t="n">
-        <v>1.03</v>
+        <v>1.81</v>
       </c>
       <c r="BF11" t="n">
-        <v>1.01</v>
+        <v>2.36</v>
       </c>
       <c r="BG11" t="n">
-        <v>1.01</v>
+        <v>1.82</v>
       </c>
       <c r="BH11" t="n">
         <v>1000</v>
       </c>
       <c r="BI11" t="n">
-        <v>1.04</v>
+        <v>3.65</v>
       </c>
       <c r="BJ11" t="n">
         <v>1000</v>
       </c>
       <c r="BK11" t="n">
-        <v>1.04</v>
+        <v>1.7</v>
       </c>
       <c r="BL11" t="n">
         <v>1000</v>
       </c>
       <c r="BM11" t="n">
-        <v>1.04</v>
+        <v>1.31</v>
       </c>
       <c r="BN11" t="n">
-        <v>1000</v>
+        <v>3.9</v>
       </c>
       <c r="BO11" t="n">
-        <v>1.04</v>
+        <v>2.8</v>
       </c>
       <c r="BP11" t="n">
         <v>1000</v>
       </c>
       <c r="BQ11" t="n">
-        <v>1.04</v>
+        <v>3.65</v>
       </c>
       <c r="BR11" t="n">
         <v>1000</v>
       </c>
       <c r="BS11" t="n">
-        <v>1.04</v>
+        <v>1.25</v>
       </c>
       <c r="BT11" t="n">
         <v>1000</v>
       </c>
       <c r="BU11" t="n">
-        <v>1.04</v>
+        <v>1.26</v>
       </c>
       <c r="BV11" t="n">
         <v>1000</v>
       </c>
       <c r="BW11" t="n">
-        <v>1.04</v>
+        <v>1.31</v>
       </c>
       <c r="BX11" t="n">
         <v>1000</v>
       </c>
       <c r="BY11" t="n">
-        <v>1.04</v>
+        <v>1.31</v>
       </c>
       <c r="BZ11" t="n">
         <v>1000</v>
       </c>
       <c r="CA11" t="n">
-        <v>1.04</v>
+        <v>4</v>
       </c>
       <c r="CB11" t="inlineStr">
         <is>
-          <t>2026-06-11 07:05:44</t>
+          <t>2026-06-11 09:18:50</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Lithuanian A Lyga</t>
+          <t>Moroccan Botola Pro 1</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -3388,121 +3388,121 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>VMFD Zalgiris</t>
+          <t>CODM Meknes</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Riteriai</t>
+          <t>Club R Zemamra</t>
         </is>
       </c>
       <c r="F12" t="n">
-        <v>1.05</v>
+        <v>2.38</v>
       </c>
       <c r="G12" t="n">
-        <v>1000</v>
+        <v>2.7</v>
       </c>
       <c r="H12" t="n">
-        <v>1.04</v>
+        <v>3.2</v>
       </c>
       <c r="I12" t="n">
-        <v>1000</v>
+        <v>4</v>
       </c>
       <c r="J12" t="n">
-        <v>1.09</v>
+        <v>2.8</v>
       </c>
       <c r="K12" t="n">
-        <v>1000</v>
+        <v>3.25</v>
       </c>
       <c r="L12" t="n">
-        <v>1.01</v>
+        <v>1.51</v>
       </c>
       <c r="M12" t="n">
-        <v>1.01</v>
+        <v>1.13</v>
       </c>
       <c r="N12" t="n">
-        <v>5.7</v>
+        <v>2.38</v>
       </c>
       <c r="O12" t="n">
-        <v>1.12</v>
+        <v>1.57</v>
       </c>
       <c r="P12" t="n">
-        <v>1.25</v>
+        <v>1.46</v>
       </c>
       <c r="Q12" t="n">
-        <v>1.13</v>
+        <v>2.66</v>
       </c>
       <c r="R12" t="n">
         <v>1.18</v>
       </c>
       <c r="S12" t="n">
-        <v>1.13</v>
+        <v>4.5</v>
       </c>
       <c r="T12" t="n">
-        <v>1.11</v>
+        <v>2.16</v>
       </c>
       <c r="U12" t="n">
-        <v>1.11</v>
+        <v>1.72</v>
       </c>
       <c r="V12" t="n">
-        <v>1.01</v>
+        <v>1.33</v>
       </c>
       <c r="W12" t="n">
-        <v>1.02</v>
+        <v>1.58</v>
       </c>
       <c r="X12" t="n">
-        <v>1000</v>
+        <v>9.4</v>
       </c>
       <c r="Y12" t="n">
-        <v>1000</v>
+        <v>11.5</v>
       </c>
       <c r="Z12" t="n">
-        <v>1000</v>
+        <v>29</v>
       </c>
       <c r="AA12" t="n">
-        <v>1000</v>
+        <v>100</v>
       </c>
       <c r="AB12" t="n">
-        <v>1000</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AC12" t="n">
-        <v>1000</v>
+        <v>8.4</v>
       </c>
       <c r="AD12" t="n">
-        <v>1000</v>
+        <v>21</v>
       </c>
       <c r="AE12" t="n">
-        <v>1000</v>
+        <v>80</v>
       </c>
       <c r="AF12" t="n">
-        <v>1000</v>
+        <v>17.5</v>
       </c>
       <c r="AG12" t="n">
-        <v>1000</v>
+        <v>15.5</v>
       </c>
       <c r="AH12" t="n">
-        <v>1000</v>
+        <v>30</v>
       </c>
       <c r="AI12" t="n">
-        <v>1000</v>
+        <v>120</v>
       </c>
       <c r="AJ12" t="n">
-        <v>1000</v>
+        <v>50</v>
       </c>
       <c r="AK12" t="n">
-        <v>1000</v>
+        <v>48</v>
       </c>
       <c r="AL12" t="n">
-        <v>1000</v>
+        <v>85</v>
       </c>
       <c r="AM12" t="n">
-        <v>1000</v>
+        <v>260</v>
       </c>
       <c r="AN12" t="n">
-        <v>1000</v>
+        <v>55</v>
       </c>
       <c r="AO12" t="n">
-        <v>1000</v>
+        <v>120</v>
       </c>
       <c r="AP12" t="n">
         <v>1.01</v>
@@ -3514,7 +3514,7 @@
         <v>1.01</v>
       </c>
       <c r="AS12" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AT12" t="n">
         <v>1.01</v>
@@ -3526,7 +3526,7 @@
         <v>1.01</v>
       </c>
       <c r="AW12" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AX12" t="n">
         <v>1.01</v>
@@ -3538,7 +3538,7 @@
         <v>1.01</v>
       </c>
       <c r="BA12" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BB12" t="n">
         <v>1.01</v>
@@ -3547,10 +3547,10 @@
         <v>1.01</v>
       </c>
       <c r="BD12" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BE12" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BF12" t="n">
         <v>1.01</v>
@@ -3559,75 +3559,75 @@
         <v>1.01</v>
       </c>
       <c r="BH12" t="n">
-        <v>1000</v>
+        <v>2.68</v>
       </c>
       <c r="BI12" t="n">
-        <v>1.04</v>
+        <v>2.18</v>
       </c>
       <c r="BJ12" t="n">
-        <v>1000</v>
+        <v>12</v>
       </c>
       <c r="BK12" t="n">
-        <v>1.04</v>
+        <v>5.9</v>
       </c>
       <c r="BL12" t="n">
         <v>1000</v>
       </c>
       <c r="BM12" t="n">
-        <v>1.04</v>
+        <v>2.16</v>
       </c>
       <c r="BN12" t="n">
-        <v>1000</v>
+        <v>5.3</v>
       </c>
       <c r="BO12" t="n">
-        <v>1.04</v>
+        <v>4</v>
       </c>
       <c r="BP12" t="n">
-        <v>1000</v>
+        <v>24</v>
       </c>
       <c r="BQ12" t="n">
-        <v>1.04</v>
+        <v>2</v>
       </c>
       <c r="BR12" t="n">
         <v>1000</v>
       </c>
       <c r="BS12" t="n">
-        <v>1.04</v>
+        <v>2.1</v>
       </c>
       <c r="BT12" t="n">
-        <v>1000</v>
+        <v>6.8</v>
       </c>
       <c r="BU12" t="n">
-        <v>1.04</v>
+        <v>4.3</v>
       </c>
       <c r="BV12" t="n">
         <v>1000</v>
       </c>
       <c r="BW12" t="n">
-        <v>1.04</v>
+        <v>2.06</v>
       </c>
       <c r="BX12" t="n">
         <v>1000</v>
       </c>
       <c r="BY12" t="n">
-        <v>1.04</v>
+        <v>2.12</v>
       </c>
       <c r="BZ12" t="n">
         <v>1000</v>
       </c>
       <c r="CA12" t="n">
-        <v>1.04</v>
+        <v>2.1</v>
       </c>
       <c r="CB12" t="inlineStr">
         <is>
-          <t>2026-06-11 07:05:44</t>
+          <t>2026-06-11 09:18:50</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Georgian Umaglesi Liga</t>
+          <t>Moroccan Botola Pro 1</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -3642,55 +3642,55 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>Dinamo Batumi</t>
+          <t>DHJ El Jadida</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Dila Gori</t>
+          <t>Olympique Dcheira</t>
         </is>
       </c>
       <c r="F13" t="n">
-        <v>1.19</v>
+        <v>2.3</v>
       </c>
       <c r="G13" t="n">
-        <v>1000</v>
+        <v>2.74</v>
       </c>
       <c r="H13" t="n">
-        <v>1.19</v>
+        <v>3.6</v>
       </c>
       <c r="I13" t="n">
-        <v>1000</v>
+        <v>4.9</v>
       </c>
       <c r="J13" t="n">
-        <v>3.25</v>
+        <v>2.52</v>
       </c>
       <c r="K13" t="n">
-        <v>1000</v>
+        <v>2.88</v>
       </c>
       <c r="L13" t="n">
-        <v>1.01</v>
+        <v>1.46</v>
       </c>
       <c r="M13" t="n">
         <v>1.01</v>
       </c>
       <c r="N13" t="n">
-        <v>3.5</v>
+        <v>2.4</v>
       </c>
       <c r="O13" t="n">
-        <v>1.32</v>
+        <v>1.52</v>
       </c>
       <c r="P13" t="n">
-        <v>1.31</v>
+        <v>1.36</v>
       </c>
       <c r="Q13" t="n">
-        <v>1.33</v>
+        <v>2.68</v>
       </c>
       <c r="R13" t="n">
         <v>1.18</v>
       </c>
       <c r="S13" t="n">
-        <v>1.32</v>
+        <v>5.3</v>
       </c>
       <c r="T13" t="n">
         <v>1.11</v>
@@ -3699,10 +3699,10 @@
         <v>1.11</v>
       </c>
       <c r="V13" t="n">
-        <v>1.02</v>
+        <v>1.26</v>
       </c>
       <c r="W13" t="n">
-        <v>1.02</v>
+        <v>1.57</v>
       </c>
       <c r="X13" t="n">
         <v>1000</v>
@@ -3874,14 +3874,14 @@
       </c>
       <c r="CB13" t="inlineStr">
         <is>
-          <t>2026-06-11 07:05:44</t>
+          <t>2026-06-11 09:18:50</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Argentinian Primera C</t>
+          <t>Swedish Division 1</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -3891,36 +3891,36 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>15:30:00</t>
+          <t>14:00:00</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>CD Cambaceres</t>
+          <t>Umea FC</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>AD Berazategui</t>
+          <t>Pitea</t>
         </is>
       </c>
       <c r="F14" t="n">
-        <v>1.01</v>
+        <v>1.09</v>
       </c>
       <c r="G14" t="n">
         <v>1000</v>
       </c>
       <c r="H14" t="n">
-        <v>1.49</v>
+        <v>1.04</v>
       </c>
       <c r="I14" t="n">
         <v>1000</v>
       </c>
       <c r="J14" t="n">
-        <v>1.11</v>
+        <v>1.09</v>
       </c>
       <c r="K14" t="n">
-        <v>3.25</v>
+        <v>950</v>
       </c>
       <c r="L14" t="n">
         <v>1.01</v>
@@ -3929,22 +3929,22 @@
         <v>1.01</v>
       </c>
       <c r="N14" t="n">
-        <v>1.28</v>
+        <v>1.32</v>
       </c>
       <c r="O14" t="n">
-        <v>1.43</v>
+        <v>1.15</v>
       </c>
       <c r="P14" t="n">
-        <v>1.28</v>
+        <v>1.3</v>
       </c>
       <c r="Q14" t="n">
-        <v>1.01</v>
+        <v>1.15</v>
       </c>
       <c r="R14" t="n">
-        <v>1.12</v>
+        <v>1.24</v>
       </c>
       <c r="S14" t="n">
-        <v>1.05</v>
+        <v>1.14</v>
       </c>
       <c r="T14" t="n">
         <v>1.11</v>
@@ -4121,21 +4121,21 @@
         <v>1.04</v>
       </c>
       <c r="BZ14" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="CA14" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="CB14" t="inlineStr">
         <is>
-          <t>2026-06-11 07:05:44</t>
+          <t>2026-06-11 09:18:50</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Irish Premier Division</t>
+          <t>Swedish Division 1</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -4145,72 +4145,72 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>15:45:00</t>
+          <t>14:00:00</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>Galway Utd</t>
+          <t>Lunds BK</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Dundalk</t>
+          <t>Ariana FC</t>
         </is>
       </c>
       <c r="F15" t="n">
-        <v>2.74</v>
+        <v>1.34</v>
       </c>
       <c r="G15" t="n">
-        <v>3.25</v>
+        <v>95</v>
       </c>
       <c r="H15" t="n">
-        <v>2.12</v>
+        <v>1.47</v>
       </c>
       <c r="I15" t="n">
-        <v>2.9</v>
+        <v>55</v>
       </c>
       <c r="J15" t="n">
-        <v>3.3</v>
+        <v>1.76</v>
       </c>
       <c r="K15" t="n">
-        <v>5.6</v>
+        <v>32</v>
       </c>
       <c r="L15" t="n">
         <v>1.01</v>
       </c>
       <c r="M15" t="n">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="N15" t="n">
-        <v>5</v>
+        <v>3.9</v>
       </c>
       <c r="O15" t="n">
-        <v>1.2</v>
+        <v>1.02</v>
       </c>
       <c r="P15" t="n">
-        <v>2.36</v>
+        <v>1.39</v>
       </c>
       <c r="Q15" t="n">
-        <v>1.63</v>
+        <v>1.27</v>
       </c>
       <c r="R15" t="n">
-        <v>1.39</v>
+        <v>1.24</v>
       </c>
       <c r="S15" t="n">
-        <v>2.16</v>
+        <v>1.27</v>
       </c>
       <c r="T15" t="n">
-        <v>1.5</v>
+        <v>1.11</v>
       </c>
       <c r="U15" t="n">
-        <v>2.3</v>
+        <v>1.11</v>
       </c>
       <c r="V15" t="n">
-        <v>1.53</v>
+        <v>1.19</v>
       </c>
       <c r="W15" t="n">
-        <v>1.44</v>
+        <v>1.17</v>
       </c>
       <c r="X15" t="n">
         <v>1000</v>
@@ -4382,14 +4382,14 @@
       </c>
       <c r="CB15" t="inlineStr">
         <is>
-          <t>2026-06-11 07:05:44</t>
+          <t>2026-06-11 09:18:50</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Irish Premier Division</t>
+          <t>Argentinian Primera C</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -4399,180 +4399,180 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>15:45:00</t>
+          <t>15:30:00</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>St Patricks</t>
+          <t>CD Cambaceres</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Drogheda</t>
+          <t>AD Berazategui</t>
         </is>
       </c>
       <c r="F16" t="n">
-        <v>1.37</v>
+        <v>1.09</v>
       </c>
       <c r="G16" t="n">
-        <v>1.42</v>
+        <v>1000</v>
       </c>
       <c r="H16" t="n">
-        <v>10.5</v>
+        <v>1.49</v>
       </c>
       <c r="I16" t="n">
-        <v>12.5</v>
+        <v>1000</v>
       </c>
       <c r="J16" t="n">
-        <v>4.9</v>
+        <v>1.24</v>
       </c>
       <c r="K16" t="n">
-        <v>5.5</v>
+        <v>3.25</v>
       </c>
       <c r="L16" t="n">
         <v>1.01</v>
       </c>
       <c r="M16" t="n">
-        <v>1.06</v>
+        <v>1.01</v>
       </c>
       <c r="N16" t="n">
-        <v>3.95</v>
+        <v>1.24</v>
       </c>
       <c r="O16" t="n">
-        <v>1.28</v>
+        <v>1.01</v>
       </c>
       <c r="P16" t="n">
-        <v>2.06</v>
+        <v>1.24</v>
       </c>
       <c r="Q16" t="n">
-        <v>1.84</v>
+        <v>1.01</v>
       </c>
       <c r="R16" t="n">
-        <v>1.39</v>
+        <v>1.12</v>
       </c>
       <c r="S16" t="n">
-        <v>3.15</v>
+        <v>1.05</v>
       </c>
       <c r="T16" t="n">
-        <v>2.2</v>
+        <v>1.11</v>
       </c>
       <c r="U16" t="n">
-        <v>1.73</v>
+        <v>1.11</v>
       </c>
       <c r="V16" t="n">
-        <v>1.08</v>
+        <v>1.02</v>
       </c>
       <c r="W16" t="n">
-        <v>3.35</v>
+        <v>1.02</v>
       </c>
       <c r="X16" t="n">
-        <v>21</v>
+        <v>1000</v>
       </c>
       <c r="Y16" t="n">
-        <v>36</v>
+        <v>1000</v>
       </c>
       <c r="Z16" t="n">
-        <v>120</v>
+        <v>1000</v>
       </c>
       <c r="AA16" t="n">
-        <v>560</v>
+        <v>1000</v>
       </c>
       <c r="AB16" t="n">
-        <v>8</v>
+        <v>1000</v>
       </c>
       <c r="AC16" t="n">
-        <v>14</v>
+        <v>1000</v>
       </c>
       <c r="AD16" t="n">
-        <v>48</v>
+        <v>1000</v>
       </c>
       <c r="AE16" t="n">
-        <v>250</v>
+        <v>1000</v>
       </c>
       <c r="AF16" t="n">
-        <v>9.199999999999999</v>
+        <v>1000</v>
       </c>
       <c r="AG16" t="n">
-        <v>13</v>
+        <v>1000</v>
       </c>
       <c r="AH16" t="n">
-        <v>38</v>
+        <v>1000</v>
       </c>
       <c r="AI16" t="n">
-        <v>200</v>
+        <v>1000</v>
       </c>
       <c r="AJ16" t="n">
-        <v>13.5</v>
+        <v>1000</v>
       </c>
       <c r="AK16" t="n">
-        <v>19.5</v>
+        <v>1000</v>
       </c>
       <c r="AL16" t="n">
-        <v>55</v>
+        <v>1000</v>
       </c>
       <c r="AM16" t="n">
-        <v>250</v>
+        <v>1000</v>
       </c>
       <c r="AN16" t="n">
-        <v>8</v>
+        <v>1000</v>
       </c>
       <c r="AO16" t="n">
-        <v>400</v>
+        <v>1000</v>
       </c>
       <c r="AP16" t="n">
-        <v>14</v>
+        <v>1.01</v>
       </c>
       <c r="AQ16" t="n">
-        <v>21</v>
+        <v>1.01</v>
       </c>
       <c r="AR16" t="n">
-        <v>4.7</v>
+        <v>1.01</v>
       </c>
       <c r="AS16" t="n">
-        <v>4.9</v>
+        <v>1.01</v>
       </c>
       <c r="AT16" t="n">
-        <v>6.4</v>
+        <v>1.01</v>
       </c>
       <c r="AU16" t="n">
-        <v>10</v>
+        <v>1.01</v>
       </c>
       <c r="AV16" t="n">
-        <v>4.5</v>
+        <v>1.01</v>
       </c>
       <c r="AW16" t="n">
-        <v>4.8</v>
+        <v>1.01</v>
       </c>
       <c r="AX16" t="n">
-        <v>6.6</v>
+        <v>1.01</v>
       </c>
       <c r="AY16" t="n">
-        <v>9</v>
+        <v>1.01</v>
       </c>
       <c r="AZ16" t="n">
-        <v>4.3</v>
+        <v>1.01</v>
       </c>
       <c r="BA16" t="n">
-        <v>4.8</v>
+        <v>1.01</v>
       </c>
       <c r="BB16" t="n">
-        <v>9.4</v>
+        <v>1.01</v>
       </c>
       <c r="BC16" t="n">
-        <v>12</v>
+        <v>1.01</v>
       </c>
       <c r="BD16" t="n">
-        <v>4.5</v>
+        <v>1.01</v>
       </c>
       <c r="BE16" t="n">
-        <v>4.8</v>
+        <v>1.01</v>
       </c>
       <c r="BF16" t="n">
-        <v>6</v>
+        <v>1.01</v>
       </c>
       <c r="BG16" t="n">
-        <v>4.9</v>
+        <v>1.01</v>
       </c>
       <c r="BH16" t="n">
         <v>1000</v>
@@ -4584,66 +4584,66 @@
         <v>1000</v>
       </c>
       <c r="BK16" t="n">
-        <v>1.58</v>
+        <v>1.04</v>
       </c>
       <c r="BL16" t="n">
         <v>1000</v>
       </c>
       <c r="BM16" t="n">
-        <v>1.72</v>
+        <v>1.04</v>
       </c>
       <c r="BN16" t="n">
         <v>1000</v>
       </c>
       <c r="BO16" t="n">
-        <v>1.3</v>
+        <v>1.04</v>
       </c>
       <c r="BP16" t="n">
         <v>1000</v>
       </c>
       <c r="BQ16" t="n">
-        <v>1.5</v>
+        <v>1.04</v>
       </c>
       <c r="BR16" t="n">
         <v>1000</v>
       </c>
       <c r="BS16" t="n">
-        <v>1.65</v>
+        <v>1.04</v>
       </c>
       <c r="BT16" t="n">
         <v>1000</v>
       </c>
       <c r="BU16" t="n">
-        <v>1.59</v>
+        <v>1.04</v>
       </c>
       <c r="BV16" t="n">
         <v>1000</v>
       </c>
       <c r="BW16" t="n">
-        <v>1.72</v>
+        <v>1.04</v>
       </c>
       <c r="BX16" t="n">
         <v>1000</v>
       </c>
       <c r="BY16" t="n">
-        <v>1.72</v>
+        <v>1.04</v>
       </c>
       <c r="BZ16" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="CA16" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="CB16" t="inlineStr">
         <is>
-          <t>2026-06-11 07:05:44</t>
+          <t>2026-06-11 09:18:50</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Irish Premier Division</t>
+          <t>Irish Division 1</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -4658,175 +4658,175 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>Waterford</t>
+          <t>Finn Harps</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Sligo Rovers</t>
+          <t>UCD</t>
         </is>
       </c>
       <c r="F17" t="n">
-        <v>2.22</v>
+        <v>3.5</v>
       </c>
       <c r="G17" t="n">
-        <v>2.38</v>
+        <v>5.4</v>
       </c>
       <c r="H17" t="n">
-        <v>3.25</v>
+        <v>1.85</v>
       </c>
       <c r="I17" t="n">
-        <v>3.6</v>
+        <v>2.14</v>
       </c>
       <c r="J17" t="n">
-        <v>3.55</v>
+        <v>3.3</v>
       </c>
       <c r="K17" t="n">
-        <v>3.9</v>
+        <v>5.8</v>
       </c>
       <c r="L17" t="n">
-        <v>1.12</v>
+        <v>1.01</v>
       </c>
       <c r="M17" t="n">
-        <v>1.06</v>
+        <v>1.02</v>
       </c>
       <c r="N17" t="n">
-        <v>3.9</v>
+        <v>3.7</v>
       </c>
       <c r="O17" t="n">
-        <v>1.28</v>
+        <v>1.23</v>
       </c>
       <c r="P17" t="n">
-        <v>2.02</v>
+        <v>1.94</v>
       </c>
       <c r="Q17" t="n">
-        <v>1.84</v>
+        <v>1.62</v>
       </c>
       <c r="R17" t="n">
-        <v>1.39</v>
+        <v>1.32</v>
       </c>
       <c r="S17" t="n">
-        <v>3.1</v>
+        <v>2.3</v>
       </c>
       <c r="T17" t="n">
-        <v>1.7</v>
+        <v>1.37</v>
       </c>
       <c r="U17" t="n">
-        <v>2.2</v>
+        <v>1.73</v>
       </c>
       <c r="V17" t="n">
-        <v>1.39</v>
+        <v>1.87</v>
       </c>
       <c r="W17" t="n">
-        <v>1.72</v>
+        <v>1.22</v>
       </c>
       <c r="X17" t="n">
-        <v>19.5</v>
+        <v>1000</v>
       </c>
       <c r="Y17" t="n">
-        <v>15</v>
+        <v>1000</v>
       </c>
       <c r="Z17" t="n">
-        <v>32</v>
+        <v>1000</v>
       </c>
       <c r="AA17" t="n">
-        <v>60</v>
+        <v>1000</v>
       </c>
       <c r="AB17" t="n">
-        <v>11.5</v>
+        <v>1000</v>
       </c>
       <c r="AC17" t="n">
-        <v>9.800000000000001</v>
+        <v>1000</v>
       </c>
       <c r="AD17" t="n">
-        <v>15</v>
+        <v>1000</v>
       </c>
       <c r="AE17" t="n">
-        <v>46</v>
+        <v>1000</v>
       </c>
       <c r="AF17" t="n">
-        <v>18.5</v>
+        <v>1000</v>
       </c>
       <c r="AG17" t="n">
-        <v>12</v>
+        <v>1000</v>
       </c>
       <c r="AH17" t="n">
-        <v>21</v>
+        <v>1000</v>
       </c>
       <c r="AI17" t="n">
-        <v>55</v>
+        <v>1000</v>
       </c>
       <c r="AJ17" t="n">
-        <v>32</v>
+        <v>1000</v>
       </c>
       <c r="AK17" t="n">
-        <v>25</v>
+        <v>1000</v>
       </c>
       <c r="AL17" t="n">
-        <v>42</v>
+        <v>1000</v>
       </c>
       <c r="AM17" t="n">
-        <v>95</v>
+        <v>1000</v>
       </c>
       <c r="AN17" t="n">
-        <v>17</v>
+        <v>1000</v>
       </c>
       <c r="AO17" t="n">
-        <v>42</v>
+        <v>1000</v>
       </c>
       <c r="AP17" t="n">
-        <v>13.5</v>
+        <v>1.01</v>
       </c>
       <c r="AQ17" t="n">
-        <v>12</v>
+        <v>1.01</v>
       </c>
       <c r="AR17" t="n">
-        <v>21</v>
+        <v>1.01</v>
       </c>
       <c r="AS17" t="n">
-        <v>40</v>
+        <v>1.01</v>
       </c>
       <c r="AT17" t="n">
-        <v>9.4</v>
+        <v>1.01</v>
       </c>
       <c r="AU17" t="n">
-        <v>7.2</v>
+        <v>1.01</v>
       </c>
       <c r="AV17" t="n">
-        <v>12</v>
+        <v>1.01</v>
       </c>
       <c r="AW17" t="n">
-        <v>26</v>
+        <v>1.01</v>
       </c>
       <c r="AX17" t="n">
-        <v>13</v>
+        <v>1.01</v>
       </c>
       <c r="AY17" t="n">
-        <v>9.4</v>
+        <v>1.01</v>
       </c>
       <c r="AZ17" t="n">
-        <v>14</v>
+        <v>1.01</v>
       </c>
       <c r="BA17" t="n">
-        <v>32</v>
+        <v>1.01</v>
       </c>
       <c r="BB17" t="n">
-        <v>23</v>
+        <v>1.01</v>
       </c>
       <c r="BC17" t="n">
-        <v>19.5</v>
+        <v>1.01</v>
       </c>
       <c r="BD17" t="n">
-        <v>26</v>
+        <v>1.01</v>
       </c>
       <c r="BE17" t="n">
-        <v>6</v>
+        <v>1.01</v>
       </c>
       <c r="BF17" t="n">
-        <v>13.5</v>
+        <v>1.01</v>
       </c>
       <c r="BG17" t="n">
-        <v>24</v>
+        <v>1.01</v>
       </c>
       <c r="BH17" t="n">
         <v>1000</v>
@@ -4838,25 +4838,25 @@
         <v>1000</v>
       </c>
       <c r="BK17" t="n">
-        <v>1.54</v>
+        <v>1.04</v>
       </c>
       <c r="BL17" t="n">
         <v>1000</v>
       </c>
       <c r="BM17" t="n">
-        <v>1.69</v>
+        <v>1.04</v>
       </c>
       <c r="BN17" t="n">
         <v>1000</v>
       </c>
       <c r="BO17" t="n">
-        <v>1.43</v>
+        <v>1.04</v>
       </c>
       <c r="BP17" t="n">
         <v>1000</v>
       </c>
       <c r="BQ17" t="n">
-        <v>1.62</v>
+        <v>1.04</v>
       </c>
       <c r="BR17" t="n">
         <v>1000</v>
@@ -4868,13 +4868,13 @@
         <v>1000</v>
       </c>
       <c r="BU17" t="n">
-        <v>1.48</v>
+        <v>1.04</v>
       </c>
       <c r="BV17" t="n">
         <v>1000</v>
       </c>
       <c r="BW17" t="n">
-        <v>1.62</v>
+        <v>1.04</v>
       </c>
       <c r="BX17" t="n">
         <v>1000</v>
@@ -4886,18 +4886,18 @@
         <v>1000</v>
       </c>
       <c r="CA17" t="n">
-        <v>1.61</v>
+        <v>1.04</v>
       </c>
       <c r="CB17" t="inlineStr">
         <is>
-          <t>2026-06-11 07:05:44</t>
+          <t>2026-06-11 09:18:50</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Irish Premier Division</t>
+          <t>Irish Division 1</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -4912,178 +4912,178 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>Derry City</t>
+          <t>Kerry FC</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Bohemians</t>
+          <t>Athlone Town</t>
         </is>
       </c>
       <c r="F18" t="n">
-        <v>3.1</v>
+        <v>2.28</v>
       </c>
       <c r="G18" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="H18" t="n">
+        <v>3.35</v>
+      </c>
+      <c r="I18" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="J18" t="n">
+        <v>3.15</v>
+      </c>
+      <c r="K18" t="n">
         <v>3.45</v>
       </c>
-      <c r="H18" t="n">
-        <v>2.42</v>
-      </c>
-      <c r="I18" t="n">
-        <v>2.64</v>
-      </c>
-      <c r="J18" t="n">
-        <v>3.25</v>
-      </c>
-      <c r="K18" t="n">
-        <v>3.55</v>
-      </c>
       <c r="L18" t="n">
-        <v>1.46</v>
+        <v>1.4</v>
       </c>
       <c r="M18" t="n">
         <v>1.09</v>
       </c>
       <c r="N18" t="n">
-        <v>3.1</v>
+        <v>3.05</v>
       </c>
       <c r="O18" t="n">
-        <v>1.4</v>
+        <v>1.41</v>
       </c>
       <c r="P18" t="n">
-        <v>1.71</v>
+        <v>1.7</v>
       </c>
       <c r="Q18" t="n">
-        <v>2.18</v>
+        <v>2.2</v>
       </c>
       <c r="R18" t="n">
-        <v>1.27</v>
+        <v>1.26</v>
       </c>
       <c r="S18" t="n">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="T18" t="n">
-        <v>1.86</v>
+        <v>1.89</v>
       </c>
       <c r="U18" t="n">
         <v>1.96</v>
       </c>
       <c r="V18" t="n">
-        <v>1.61</v>
+        <v>0</v>
       </c>
       <c r="W18" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="X18" t="n">
-        <v>12</v>
+        <v>13.5</v>
       </c>
       <c r="Y18" t="n">
-        <v>9.4</v>
+        <v>14</v>
       </c>
       <c r="Z18" t="n">
-        <v>16.5</v>
+        <v>30</v>
       </c>
       <c r="AA18" t="n">
-        <v>40</v>
+        <v>85</v>
       </c>
       <c r="AB18" t="n">
-        <v>11.5</v>
+        <v>10.5</v>
       </c>
       <c r="AC18" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AD18" t="n">
-        <v>12.5</v>
+        <v>18.5</v>
       </c>
       <c r="AE18" t="n">
-        <v>32</v>
+        <v>60</v>
       </c>
       <c r="AF18" t="n">
-        <v>23</v>
+        <v>17.5</v>
       </c>
       <c r="AG18" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="AH18" t="n">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="AI18" t="n">
-        <v>50</v>
+        <v>75</v>
       </c>
       <c r="AJ18" t="n">
-        <v>65</v>
+        <v>42</v>
       </c>
       <c r="AK18" t="n">
-        <v>44</v>
+        <v>36</v>
       </c>
       <c r="AL18" t="n">
         <v>60</v>
       </c>
       <c r="AM18" t="n">
-        <v>140</v>
+        <v>150</v>
       </c>
       <c r="AN18" t="n">
-        <v>48</v>
+        <v>32</v>
       </c>
       <c r="AO18" t="n">
-        <v>30</v>
+        <v>70</v>
       </c>
       <c r="AP18" t="n">
-        <v>9.800000000000001</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AQ18" t="n">
-        <v>7.8</v>
+        <v>8.6</v>
       </c>
       <c r="AR18" t="n">
-        <v>13</v>
+        <v>17.5</v>
       </c>
       <c r="AS18" t="n">
-        <v>30</v>
+        <v>4.1</v>
       </c>
       <c r="AT18" t="n">
-        <v>9.4</v>
+        <v>7.2</v>
       </c>
       <c r="AU18" t="n">
-        <v>6.4</v>
+        <v>5.6</v>
       </c>
       <c r="AV18" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AW18" t="n">
-        <v>25</v>
+        <v>4</v>
       </c>
       <c r="AX18" t="n">
-        <v>18</v>
+        <v>10.5</v>
       </c>
       <c r="AY18" t="n">
-        <v>11.5</v>
+        <v>8.6</v>
       </c>
       <c r="AZ18" t="n">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="BA18" t="n">
-        <v>7.8</v>
+        <v>4.1</v>
       </c>
       <c r="BB18" t="n">
-        <v>8.199999999999999</v>
+        <v>3.95</v>
       </c>
       <c r="BC18" t="n">
-        <v>7.8</v>
+        <v>21</v>
       </c>
       <c r="BD18" t="n">
-        <v>8.199999999999999</v>
+        <v>4</v>
       </c>
       <c r="BE18" t="n">
-        <v>8.800000000000001</v>
+        <v>4.2</v>
       </c>
       <c r="BF18" t="n">
-        <v>38</v>
+        <v>18.5</v>
       </c>
       <c r="BG18" t="n">
-        <v>23</v>
+        <v>4.1</v>
       </c>
       <c r="BH18" t="n">
-        <v>3.15</v>
+        <v>3.1</v>
       </c>
       <c r="BI18" t="n">
         <v>2.56</v>
@@ -5092,59 +5092,59 @@
         <v>10.5</v>
       </c>
       <c r="BK18" t="n">
-        <v>7.8</v>
+        <v>6</v>
       </c>
       <c r="BL18" t="n">
         <v>1000</v>
       </c>
       <c r="BM18" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="BN18" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="BO18" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="BP18" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BQ18" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="BR18" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BS18" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="BT18" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="BU18" t="n">
+        <v>5</v>
+      </c>
+      <c r="BV18" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BW18" t="n">
         <v>10</v>
       </c>
-      <c r="BN18" t="n">
-        <v>6.6</v>
-      </c>
-      <c r="BO18" t="n">
-        <v>5.4</v>
-      </c>
-      <c r="BP18" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BQ18" t="n">
-        <v>7.8</v>
-      </c>
-      <c r="BR18" t="n">
-        <v>46</v>
-      </c>
-      <c r="BS18" t="n">
-        <v>8.800000000000001</v>
-      </c>
-      <c r="BT18" t="n">
-        <v>5.5</v>
-      </c>
-      <c r="BU18" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="BV18" t="n">
-        <v>21</v>
-      </c>
-      <c r="BW18" t="n">
-        <v>7.2</v>
-      </c>
       <c r="BX18" t="n">
         <v>1000</v>
       </c>
       <c r="BY18" t="n">
-        <v>8.4</v>
+        <v>11</v>
       </c>
       <c r="BZ18" t="n">
-        <v>38</v>
+        <v>1000</v>
       </c>
       <c r="CA18" t="n">
-        <v>8.4</v>
+        <v>10.5</v>
       </c>
       <c r="CB18" t="inlineStr">
         <is>
-          <t>2026-06-11 07:05:44</t>
+          <t>2026-06-11 09:18:50</t>
         </is>
       </c>
     </row>
@@ -5166,175 +5166,175 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>Finn Harps</t>
+          <t>Treaty United</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>UCD</t>
+          <t>Bray Wanderers</t>
         </is>
       </c>
       <c r="F19" t="n">
-        <v>3.4</v>
+        <v>3.9</v>
       </c>
       <c r="G19" t="n">
-        <v>5.6</v>
+        <v>4.6</v>
       </c>
       <c r="H19" t="n">
-        <v>1.85</v>
+        <v>1.88</v>
       </c>
       <c r="I19" t="n">
-        <v>2.22</v>
+        <v>2.04</v>
       </c>
       <c r="J19" t="n">
-        <v>3.3</v>
+        <v>3.65</v>
       </c>
       <c r="K19" t="n">
-        <v>6</v>
+        <v>4.2</v>
       </c>
       <c r="L19" t="n">
         <v>1.01</v>
       </c>
       <c r="M19" t="n">
-        <v>1.02</v>
+        <v>1.05</v>
       </c>
       <c r="N19" t="n">
-        <v>4.1</v>
+        <v>4.4</v>
       </c>
       <c r="O19" t="n">
         <v>1.23</v>
       </c>
       <c r="P19" t="n">
-        <v>1.94</v>
+        <v>2.18</v>
       </c>
       <c r="Q19" t="n">
-        <v>1.63</v>
+        <v>1.72</v>
       </c>
       <c r="R19" t="n">
-        <v>1.32</v>
+        <v>1.52</v>
       </c>
       <c r="S19" t="n">
-        <v>2.32</v>
+        <v>2.56</v>
       </c>
       <c r="T19" t="n">
-        <v>1.37</v>
+        <v>1.64</v>
       </c>
       <c r="U19" t="n">
-        <v>1.73</v>
+        <v>2.28</v>
       </c>
       <c r="V19" t="n">
-        <v>1.81</v>
+        <v>1.96</v>
       </c>
       <c r="W19" t="n">
-        <v>1.22</v>
+        <v>1.28</v>
       </c>
       <c r="X19" t="n">
-        <v>1000</v>
+        <v>20</v>
       </c>
       <c r="Y19" t="n">
-        <v>1000</v>
+        <v>12</v>
       </c>
       <c r="Z19" t="n">
-        <v>1000</v>
+        <v>14.5</v>
       </c>
       <c r="AA19" t="n">
-        <v>1000</v>
+        <v>32</v>
       </c>
       <c r="AB19" t="n">
-        <v>1000</v>
+        <v>19</v>
       </c>
       <c r="AC19" t="n">
-        <v>1000</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AD19" t="n">
-        <v>1000</v>
+        <v>14.5</v>
       </c>
       <c r="AE19" t="n">
-        <v>1000</v>
+        <v>18.5</v>
       </c>
       <c r="AF19" t="n">
-        <v>1000</v>
+        <v>34</v>
       </c>
       <c r="AG19" t="n">
-        <v>1000</v>
+        <v>23</v>
       </c>
       <c r="AH19" t="n">
-        <v>1000</v>
+        <v>16.5</v>
       </c>
       <c r="AI19" t="n">
-        <v>1000</v>
+        <v>30</v>
       </c>
       <c r="AJ19" t="n">
-        <v>1000</v>
+        <v>120</v>
       </c>
       <c r="AK19" t="n">
-        <v>1000</v>
+        <v>44</v>
       </c>
       <c r="AL19" t="n">
-        <v>1000</v>
+        <v>48</v>
       </c>
       <c r="AM19" t="n">
-        <v>1000</v>
+        <v>95</v>
       </c>
       <c r="AN19" t="n">
-        <v>1000</v>
+        <v>40</v>
       </c>
       <c r="AO19" t="n">
-        <v>1000</v>
+        <v>10.5</v>
       </c>
       <c r="AP19" t="n">
-        <v>1.01</v>
+        <v>14</v>
       </c>
       <c r="AQ19" t="n">
-        <v>1.01</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AR19" t="n">
-        <v>1.01</v>
+        <v>10</v>
       </c>
       <c r="AS19" t="n">
-        <v>1.01</v>
+        <v>18.5</v>
       </c>
       <c r="AT19" t="n">
-        <v>1.01</v>
+        <v>13</v>
       </c>
       <c r="AU19" t="n">
-        <v>1.01</v>
+        <v>7</v>
       </c>
       <c r="AV19" t="n">
-        <v>1.01</v>
+        <v>8.6</v>
       </c>
       <c r="AW19" t="n">
-        <v>1.01</v>
+        <v>12.5</v>
       </c>
       <c r="AX19" t="n">
-        <v>1.01</v>
+        <v>6</v>
       </c>
       <c r="AY19" t="n">
-        <v>1.01</v>
+        <v>13.5</v>
       </c>
       <c r="AZ19" t="n">
-        <v>1.01</v>
+        <v>11.5</v>
       </c>
       <c r="BA19" t="n">
-        <v>1.01</v>
+        <v>20</v>
       </c>
       <c r="BB19" t="n">
-        <v>1.01</v>
+        <v>6.8</v>
       </c>
       <c r="BC19" t="n">
-        <v>1.01</v>
+        <v>6.2</v>
       </c>
       <c r="BD19" t="n">
-        <v>1.01</v>
+        <v>6.2</v>
       </c>
       <c r="BE19" t="n">
-        <v>1.01</v>
+        <v>6.6</v>
       </c>
       <c r="BF19" t="n">
-        <v>1.01</v>
+        <v>6</v>
       </c>
       <c r="BG19" t="n">
-        <v>1.01</v>
+        <v>7.2</v>
       </c>
       <c r="BH19" t="n">
         <v>1000</v>
@@ -5398,7 +5398,7 @@
       </c>
       <c r="CB19" t="inlineStr">
         <is>
-          <t>2026-06-11 07:05:44</t>
+          <t>2026-06-11 09:18:50</t>
         </is>
       </c>
     </row>
@@ -5420,246 +5420,246 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>Treaty United</t>
+          <t>Wexford F.C</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Bray Wanderers</t>
+          <t>Cork City</t>
         </is>
       </c>
       <c r="F20" t="n">
-        <v>3.9</v>
+        <v>4.2</v>
       </c>
       <c r="G20" t="n">
-        <v>4.6</v>
+        <v>5</v>
       </c>
       <c r="H20" t="n">
-        <v>1.88</v>
+        <v>1.85</v>
       </c>
       <c r="I20" t="n">
-        <v>2.04</v>
+        <v>2.02</v>
       </c>
       <c r="J20" t="n">
-        <v>3.7</v>
+        <v>3.5</v>
       </c>
       <c r="K20" t="n">
-        <v>4.2</v>
+        <v>3.95</v>
       </c>
       <c r="L20" t="n">
-        <v>1.23</v>
+        <v>1.01</v>
       </c>
       <c r="M20" t="n">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="N20" t="n">
-        <v>4.6</v>
+        <v>3.6</v>
       </c>
       <c r="O20" t="n">
-        <v>1.23</v>
+        <v>1.3</v>
       </c>
       <c r="P20" t="n">
-        <v>2.2</v>
+        <v>1.9</v>
       </c>
       <c r="Q20" t="n">
-        <v>1.68</v>
+        <v>1.89</v>
       </c>
       <c r="R20" t="n">
-        <v>1.53</v>
+        <v>1.35</v>
       </c>
       <c r="S20" t="n">
-        <v>2.54</v>
+        <v>3.3</v>
       </c>
       <c r="T20" t="n">
-        <v>1.63</v>
+        <v>1.79</v>
       </c>
       <c r="U20" t="n">
-        <v>2.32</v>
+        <v>2.02</v>
       </c>
       <c r="V20" t="n">
-        <v>1.96</v>
+        <v>1.98</v>
       </c>
       <c r="W20" t="n">
-        <v>1.28</v>
+        <v>1.25</v>
       </c>
       <c r="X20" t="n">
-        <v>21</v>
+        <v>15.5</v>
       </c>
       <c r="Y20" t="n">
-        <v>12</v>
+        <v>9.4</v>
       </c>
       <c r="Z20" t="n">
-        <v>14.5</v>
+        <v>12.5</v>
       </c>
       <c r="AA20" t="n">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="AB20" t="n">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="AC20" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AD20" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="AE20" t="n">
-        <v>18</v>
+        <v>22</v>
       </c>
       <c r="AF20" t="n">
         <v>36</v>
       </c>
       <c r="AG20" t="n">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="AH20" t="n">
-        <v>17.5</v>
+        <v>20</v>
       </c>
       <c r="AI20" t="n">
-        <v>32</v>
+        <v>38</v>
       </c>
       <c r="AJ20" t="n">
-        <v>110</v>
+        <v>120</v>
       </c>
       <c r="AK20" t="n">
-        <v>46</v>
+        <v>65</v>
       </c>
       <c r="AL20" t="n">
-        <v>50</v>
+        <v>70</v>
       </c>
       <c r="AM20" t="n">
-        <v>70</v>
+        <v>120</v>
       </c>
       <c r="AN20" t="n">
+        <v>90</v>
+      </c>
+      <c r="AO20" t="n">
+        <v>14</v>
+      </c>
+      <c r="AP20" t="n">
+        <v>11</v>
+      </c>
+      <c r="AQ20" t="n">
+        <v>7</v>
+      </c>
+      <c r="AR20" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="AS20" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="AT20" t="n">
+        <v>12</v>
+      </c>
+      <c r="AU20" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="AV20" t="n">
+        <v>8</v>
+      </c>
+      <c r="AW20" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="AX20" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="AY20" t="n">
+        <v>14</v>
+      </c>
+      <c r="AZ20" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="BA20" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="BB20" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="BC20" t="n">
         <v>38</v>
       </c>
-      <c r="AO20" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="AP20" t="n">
-        <v>17</v>
-      </c>
-      <c r="AQ20" t="n">
-        <v>9.800000000000001</v>
-      </c>
-      <c r="AR20" t="n">
-        <v>11</v>
-      </c>
-      <c r="AS20" t="n">
-        <v>18</v>
-      </c>
-      <c r="AT20" t="n">
-        <v>16</v>
-      </c>
-      <c r="AU20" t="n">
-        <v>8.199999999999999</v>
-      </c>
-      <c r="AV20" t="n">
-        <v>9.800000000000001</v>
-      </c>
-      <c r="AW20" t="n">
-        <v>12</v>
-      </c>
-      <c r="AX20" t="n">
-        <v>6.6</v>
-      </c>
-      <c r="AY20" t="n">
-        <v>13.5</v>
-      </c>
-      <c r="AZ20" t="n">
-        <v>13</v>
-      </c>
-      <c r="BA20" t="n">
-        <v>6.4</v>
-      </c>
-      <c r="BB20" t="n">
-        <v>7.6</v>
-      </c>
-      <c r="BC20" t="n">
-        <v>34</v>
-      </c>
       <c r="BD20" t="n">
-        <v>36</v>
+        <v>8</v>
       </c>
       <c r="BE20" t="n">
-        <v>7.2</v>
+        <v>8.4</v>
       </c>
       <c r="BF20" t="n">
-        <v>26</v>
+        <v>42</v>
       </c>
       <c r="BG20" t="n">
-        <v>7.2</v>
+        <v>10</v>
       </c>
       <c r="BH20" t="n">
         <v>1000</v>
       </c>
       <c r="BI20" t="n">
-        <v>1.93</v>
+        <v>1.04</v>
       </c>
       <c r="BJ20" t="n">
-        <v>13</v>
+        <v>1000</v>
       </c>
       <c r="BK20" t="n">
-        <v>1.68</v>
+        <v>1.04</v>
       </c>
       <c r="BL20" t="n">
         <v>1000</v>
       </c>
       <c r="BM20" t="n">
-        <v>1.93</v>
+        <v>1.04</v>
       </c>
       <c r="BN20" t="n">
-        <v>11</v>
+        <v>1000</v>
       </c>
       <c r="BO20" t="n">
-        <v>4.9</v>
+        <v>1.04</v>
       </c>
       <c r="BP20" t="n">
-        <v>46</v>
+        <v>1000</v>
       </c>
       <c r="BQ20" t="n">
-        <v>1.85</v>
+        <v>1.04</v>
       </c>
       <c r="BR20" t="n">
         <v>1000</v>
       </c>
       <c r="BS20" t="n">
-        <v>1.86</v>
+        <v>1.04</v>
       </c>
       <c r="BT20" t="n">
-        <v>6.6</v>
+        <v>1000</v>
       </c>
       <c r="BU20" t="n">
-        <v>3.6</v>
+        <v>1.04</v>
       </c>
       <c r="BV20" t="n">
-        <v>18.5</v>
+        <v>1000</v>
       </c>
       <c r="BW20" t="n">
-        <v>1.75</v>
+        <v>1.04</v>
       </c>
       <c r="BX20" t="n">
-        <v>34</v>
+        <v>1000</v>
       </c>
       <c r="BY20" t="n">
-        <v>1.83</v>
+        <v>1.04</v>
       </c>
       <c r="BZ20" t="n">
-        <v>26</v>
+        <v>1000</v>
       </c>
       <c r="CA20" t="n">
-        <v>1.8</v>
+        <v>1.04</v>
       </c>
       <c r="CB20" t="inlineStr">
         <is>
-          <t>2026-06-11 07:05:44</t>
+          <t>2026-06-11 09:18:50</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Irish Division 1</t>
+          <t>Irish Premier Division</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -5674,46 +5674,46 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>Kerry FC</t>
+          <t>Derry City</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Athlone Town</t>
+          <t>Bohemians</t>
         </is>
       </c>
       <c r="F21" t="n">
-        <v>2.28</v>
+        <v>3.1</v>
       </c>
       <c r="G21" t="n">
-        <v>2.48</v>
+        <v>3.45</v>
       </c>
       <c r="H21" t="n">
-        <v>3.4</v>
+        <v>2.42</v>
       </c>
       <c r="I21" t="n">
-        <v>3.75</v>
+        <v>2.64</v>
       </c>
       <c r="J21" t="n">
-        <v>3.15</v>
+        <v>3.25</v>
       </c>
       <c r="K21" t="n">
-        <v>3.5</v>
+        <v>3.55</v>
       </c>
       <c r="L21" t="n">
-        <v>1.48</v>
+        <v>1.46</v>
       </c>
       <c r="M21" t="n">
         <v>1.09</v>
       </c>
       <c r="N21" t="n">
-        <v>3.05</v>
+        <v>3.1</v>
       </c>
       <c r="O21" t="n">
-        <v>1.41</v>
+        <v>1.4</v>
       </c>
       <c r="P21" t="n">
-        <v>1.7</v>
+        <v>1.71</v>
       </c>
       <c r="Q21" t="n">
         <v>2.2</v>
@@ -5725,127 +5725,127 @@
         <v>4.2</v>
       </c>
       <c r="T21" t="n">
-        <v>1.89</v>
+        <v>1.87</v>
       </c>
       <c r="U21" t="n">
         <v>1.96</v>
       </c>
       <c r="V21" t="n">
-        <v>1.37</v>
+        <v>1.6</v>
       </c>
       <c r="W21" t="n">
-        <v>1.67</v>
+        <v>1.4</v>
       </c>
       <c r="X21" t="n">
-        <v>13.5</v>
+        <v>12</v>
       </c>
       <c r="Y21" t="n">
-        <v>14</v>
+        <v>9.6</v>
       </c>
       <c r="Z21" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="AA21" t="n">
+        <v>50</v>
+      </c>
+      <c r="AB21" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="AC21" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="AD21" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="AE21" t="n">
+        <v>42</v>
+      </c>
+      <c r="AF21" t="n">
+        <v>23</v>
+      </c>
+      <c r="AG21" t="n">
+        <v>15</v>
+      </c>
+      <c r="AH21" t="n">
+        <v>21</v>
+      </c>
+      <c r="AI21" t="n">
+        <v>70</v>
+      </c>
+      <c r="AJ21" t="n">
+        <v>80</v>
+      </c>
+      <c r="AK21" t="n">
+        <v>55</v>
+      </c>
+      <c r="AL21" t="n">
+        <v>80</v>
+      </c>
+      <c r="AM21" t="n">
+        <v>140</v>
+      </c>
+      <c r="AN21" t="n">
+        <v>60</v>
+      </c>
+      <c r="AO21" t="n">
+        <v>38</v>
+      </c>
+      <c r="AP21" t="n">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="AQ21" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="AR21" t="n">
+        <v>13</v>
+      </c>
+      <c r="AS21" t="n">
         <v>30</v>
       </c>
-      <c r="AA21" t="n">
-        <v>85</v>
-      </c>
-      <c r="AB21" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="AC21" t="n">
-        <v>9</v>
-      </c>
-      <c r="AD21" t="n">
+      <c r="AT21" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="AU21" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="AV21" t="n">
+        <v>10</v>
+      </c>
+      <c r="AW21" t="n">
+        <v>7</v>
+      </c>
+      <c r="AX21" t="n">
         <v>18.5</v>
       </c>
-      <c r="AE21" t="n">
-        <v>60</v>
-      </c>
-      <c r="AF21" t="n">
-        <v>17.5</v>
-      </c>
-      <c r="AG21" t="n">
-        <v>14</v>
-      </c>
-      <c r="AH21" t="n">
-        <v>24</v>
-      </c>
-      <c r="AI21" t="n">
-        <v>75</v>
-      </c>
-      <c r="AJ21" t="n">
-        <v>42</v>
-      </c>
-      <c r="AK21" t="n">
+      <c r="AY21" t="n">
+        <v>12</v>
+      </c>
+      <c r="AZ21" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="BA21" t="n">
+        <v>32</v>
+      </c>
+      <c r="BB21" t="n">
+        <v>8</v>
+      </c>
+      <c r="BC21" t="n">
+        <v>28</v>
+      </c>
+      <c r="BD21" t="n">
         <v>36</v>
       </c>
-      <c r="AL21" t="n">
-        <v>60</v>
-      </c>
-      <c r="AM21" t="n">
-        <v>150</v>
-      </c>
-      <c r="AN21" t="n">
-        <v>32</v>
-      </c>
-      <c r="AO21" t="n">
-        <v>70</v>
-      </c>
-      <c r="AP21" t="n">
-        <v>8.199999999999999</v>
-      </c>
-      <c r="AQ21" t="n">
+      <c r="BE21" t="n">
         <v>8.6</v>
       </c>
-      <c r="AR21" t="n">
-        <v>17.5</v>
-      </c>
-      <c r="AS21" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="AT21" t="n">
-        <v>6.4</v>
-      </c>
-      <c r="AU21" t="n">
-        <v>5.6</v>
-      </c>
-      <c r="AV21" t="n">
-        <v>11</v>
-      </c>
-      <c r="AW21" t="n">
-        <v>4</v>
-      </c>
-      <c r="AX21" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="AY21" t="n">
-        <v>8.6</v>
-      </c>
-      <c r="AZ21" t="n">
-        <v>14</v>
-      </c>
-      <c r="BA21" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="BB21" t="n">
-        <v>3.95</v>
-      </c>
-      <c r="BC21" t="n">
-        <v>21</v>
-      </c>
-      <c r="BD21" t="n">
-        <v>4</v>
-      </c>
-      <c r="BE21" t="n">
-        <v>4.2</v>
-      </c>
       <c r="BF21" t="n">
-        <v>18.5</v>
+        <v>34</v>
       </c>
       <c r="BG21" t="n">
-        <v>4.1</v>
+        <v>22</v>
       </c>
       <c r="BH21" t="n">
-        <v>3.1</v>
+        <v>3.15</v>
       </c>
       <c r="BI21" t="n">
         <v>2.56</v>
@@ -5854,66 +5854,66 @@
         <v>10.5</v>
       </c>
       <c r="BK21" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="BL21" t="n">
         <v>1000</v>
       </c>
       <c r="BM21" t="n">
-        <v>13.5</v>
+        <v>10</v>
       </c>
       <c r="BN21" t="n">
-        <v>5.1</v>
+        <v>6.6</v>
       </c>
       <c r="BO21" t="n">
-        <v>3.9</v>
+        <v>5.4</v>
       </c>
       <c r="BP21" t="n">
         <v>1000</v>
       </c>
       <c r="BQ21" t="n">
-        <v>8.199999999999999</v>
+        <v>7.8</v>
       </c>
       <c r="BR21" t="n">
         <v>1000</v>
       </c>
       <c r="BS21" t="n">
-        <v>10.5</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BT21" t="n">
-        <v>6.6</v>
+        <v>5.5</v>
       </c>
       <c r="BU21" t="n">
-        <v>5</v>
+        <v>4.5</v>
       </c>
       <c r="BV21" t="n">
-        <v>1000</v>
+        <v>21</v>
       </c>
       <c r="BW21" t="n">
-        <v>10</v>
+        <v>7.2</v>
       </c>
       <c r="BX21" t="n">
         <v>1000</v>
       </c>
       <c r="BY21" t="n">
-        <v>11</v>
+        <v>8.4</v>
       </c>
       <c r="BZ21" t="n">
         <v>1000</v>
       </c>
       <c r="CA21" t="n">
-        <v>10.5</v>
+        <v>8.4</v>
       </c>
       <c r="CB21" t="inlineStr">
         <is>
-          <t>2026-06-11 07:05:44</t>
+          <t>2026-06-11 09:18:50</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Irish Division 1</t>
+          <t>Irish Premier Division</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -5928,246 +5928,246 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>Wexford F.C</t>
+          <t>Waterford</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Cork City</t>
+          <t>Sligo Rovers</t>
         </is>
       </c>
       <c r="F22" t="n">
-        <v>4.2</v>
+        <v>2.2</v>
       </c>
       <c r="G22" t="n">
-        <v>5</v>
+        <v>2.36</v>
       </c>
       <c r="H22" t="n">
-        <v>1.86</v>
+        <v>3.2</v>
       </c>
       <c r="I22" t="n">
-        <v>2.02</v>
+        <v>3.6</v>
       </c>
       <c r="J22" t="n">
-        <v>3.55</v>
+        <v>3.5</v>
       </c>
       <c r="K22" t="n">
-        <v>3.95</v>
+        <v>3.85</v>
       </c>
       <c r="L22" t="n">
-        <v>1.35</v>
+        <v>1.12</v>
       </c>
       <c r="M22" t="n">
         <v>1.06</v>
       </c>
       <c r="N22" t="n">
-        <v>3.6</v>
+        <v>3.95</v>
       </c>
       <c r="O22" t="n">
-        <v>1.3</v>
+        <v>1.28</v>
       </c>
       <c r="P22" t="n">
-        <v>1.94</v>
+        <v>2.02</v>
       </c>
       <c r="Q22" t="n">
-        <v>1.89</v>
+        <v>1.81</v>
       </c>
       <c r="R22" t="n">
-        <v>1.35</v>
+        <v>1.39</v>
       </c>
       <c r="S22" t="n">
-        <v>3.3</v>
+        <v>3.1</v>
       </c>
       <c r="T22" t="n">
-        <v>1.79</v>
+        <v>1.69</v>
       </c>
       <c r="U22" t="n">
-        <v>2.04</v>
+        <v>2.22</v>
       </c>
       <c r="V22" t="n">
-        <v>1.98</v>
+        <v>1.39</v>
       </c>
       <c r="W22" t="n">
-        <v>1.25</v>
+        <v>1.73</v>
       </c>
       <c r="X22" t="n">
         <v>17</v>
       </c>
       <c r="Y22" t="n">
-        <v>9.4</v>
+        <v>17</v>
       </c>
       <c r="Z22" t="n">
-        <v>12.5</v>
+        <v>36</v>
       </c>
       <c r="AA22" t="n">
-        <v>24</v>
+        <v>70</v>
       </c>
       <c r="AB22" t="n">
-        <v>16.5</v>
+        <v>11.5</v>
       </c>
       <c r="AC22" t="n">
         <v>8.800000000000001</v>
       </c>
       <c r="AD22" t="n">
-        <v>11</v>
+        <v>15.5</v>
       </c>
       <c r="AE22" t="n">
-        <v>22</v>
+        <v>50</v>
       </c>
       <c r="AF22" t="n">
-        <v>36</v>
+        <v>16</v>
       </c>
       <c r="AG22" t="n">
-        <v>18.5</v>
+        <v>12</v>
       </c>
       <c r="AH22" t="n">
+        <v>17.5</v>
+      </c>
+      <c r="AI22" t="n">
+        <v>60</v>
+      </c>
+      <c r="AJ22" t="n">
+        <v>32</v>
+      </c>
+      <c r="AK22" t="n">
+        <v>25</v>
+      </c>
+      <c r="AL22" t="n">
+        <v>50</v>
+      </c>
+      <c r="AM22" t="n">
+        <v>100</v>
+      </c>
+      <c r="AN22" t="n">
         <v>19.5</v>
       </c>
-      <c r="AI22" t="n">
-        <v>38</v>
-      </c>
-      <c r="AJ22" t="n">
-        <v>110</v>
-      </c>
-      <c r="AK22" t="n">
-        <v>60</v>
-      </c>
-      <c r="AL22" t="n">
-        <v>65</v>
-      </c>
-      <c r="AM22" t="n">
-        <v>120</v>
-      </c>
-      <c r="AN22" t="n">
-        <v>75</v>
-      </c>
       <c r="AO22" t="n">
-        <v>14.5</v>
+        <v>48</v>
       </c>
       <c r="AP22" t="n">
-        <v>11</v>
+        <v>13.5</v>
       </c>
       <c r="AQ22" t="n">
-        <v>7.8</v>
+        <v>12</v>
       </c>
       <c r="AR22" t="n">
-        <v>10</v>
+        <v>21</v>
       </c>
       <c r="AS22" t="n">
-        <v>18.5</v>
+        <v>6.8</v>
       </c>
       <c r="AT22" t="n">
-        <v>13</v>
+        <v>9.4</v>
       </c>
       <c r="AU22" t="n">
         <v>7.2</v>
       </c>
       <c r="AV22" t="n">
-        <v>8.800000000000001</v>
+        <v>12</v>
       </c>
       <c r="AW22" t="n">
-        <v>17.5</v>
+        <v>24</v>
       </c>
       <c r="AX22" t="n">
+        <v>13</v>
+      </c>
+      <c r="AY22" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="AZ22" t="n">
+        <v>14</v>
+      </c>
+      <c r="BA22" t="n">
+        <v>30</v>
+      </c>
+      <c r="BB22" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="BC22" t="n">
+        <v>19.5</v>
+      </c>
+      <c r="BD22" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="BE22" t="n">
         <v>7.2</v>
       </c>
-      <c r="AY22" t="n">
-        <v>15</v>
-      </c>
-      <c r="AZ22" t="n">
-        <v>15.5</v>
-      </c>
-      <c r="BA22" t="n">
-        <v>7.2</v>
-      </c>
-      <c r="BB22" t="n">
-        <v>8.199999999999999</v>
-      </c>
-      <c r="BC22" t="n">
-        <v>7.8</v>
-      </c>
-      <c r="BD22" t="n">
-        <v>7.8</v>
-      </c>
-      <c r="BE22" t="n">
-        <v>8.4</v>
-      </c>
       <c r="BF22" t="n">
-        <v>8</v>
+        <v>11.5</v>
       </c>
       <c r="BG22" t="n">
-        <v>11.5</v>
+        <v>6.4</v>
       </c>
       <c r="BH22" t="n">
-        <v>3.55</v>
+        <v>1000</v>
       </c>
       <c r="BI22" t="n">
-        <v>3.05</v>
+        <v>1.04</v>
       </c>
       <c r="BJ22" t="n">
-        <v>10.5</v>
+        <v>1000</v>
       </c>
       <c r="BK22" t="n">
-        <v>5.2</v>
+        <v>1.04</v>
       </c>
       <c r="BL22" t="n">
         <v>1000</v>
       </c>
       <c r="BM22" t="n">
-        <v>9.800000000000001</v>
+        <v>1.04</v>
       </c>
       <c r="BN22" t="n">
-        <v>8.199999999999999</v>
+        <v>1000</v>
       </c>
       <c r="BO22" t="n">
-        <v>6</v>
+        <v>1.04</v>
       </c>
       <c r="BP22" t="n">
-        <v>40</v>
+        <v>1000</v>
       </c>
       <c r="BQ22" t="n">
-        <v>8.199999999999999</v>
+        <v>1.04</v>
       </c>
       <c r="BR22" t="n">
-        <v>50</v>
+        <v>1000</v>
       </c>
       <c r="BS22" t="n">
-        <v>8.6</v>
+        <v>1.04</v>
       </c>
       <c r="BT22" t="n">
-        <v>4.8</v>
+        <v>1000</v>
       </c>
       <c r="BU22" t="n">
-        <v>3.7</v>
+        <v>1.04</v>
       </c>
       <c r="BV22" t="n">
-        <v>14</v>
+        <v>1000</v>
       </c>
       <c r="BW22" t="n">
-        <v>6</v>
+        <v>1.04</v>
       </c>
       <c r="BX22" t="n">
-        <v>29</v>
+        <v>1000</v>
       </c>
       <c r="BY22" t="n">
-        <v>7.6</v>
+        <v>1.04</v>
       </c>
       <c r="BZ22" t="n">
-        <v>25</v>
+        <v>1000</v>
       </c>
       <c r="CA22" t="n">
-        <v>7.4</v>
+        <v>1.04</v>
       </c>
       <c r="CB22" t="inlineStr">
         <is>
-          <t>2026-06-11 07:05:44</t>
+          <t>2026-06-11 09:18:50</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Bolivian Liga de Futbol Profesional</t>
+          <t>Irish Premier Division</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -6177,180 +6177,180 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>16:00:00</t>
+          <t>15:45:00</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>San Antonio Bulo Bulo</t>
+          <t>St Patricks</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Academia de Balompie Boli</t>
+          <t>Drogheda</t>
         </is>
       </c>
       <c r="F23" t="n">
-        <v>1.42</v>
+        <v>1.36</v>
       </c>
       <c r="G23" t="n">
-        <v>1.63</v>
+        <v>1.4</v>
       </c>
       <c r="H23" t="n">
-        <v>4.8</v>
+        <v>10.5</v>
       </c>
       <c r="I23" t="n">
-        <v>1000</v>
+        <v>13</v>
       </c>
       <c r="J23" t="n">
-        <v>4.5</v>
+        <v>4.9</v>
       </c>
       <c r="K23" t="n">
-        <v>1000</v>
+        <v>5.5</v>
       </c>
       <c r="L23" t="n">
         <v>1.01</v>
       </c>
       <c r="M23" t="n">
-        <v>1.01</v>
+        <v>1.06</v>
       </c>
       <c r="N23" t="n">
-        <v>1.99</v>
+        <v>3.95</v>
       </c>
       <c r="O23" t="n">
-        <v>1.1</v>
+        <v>1.28</v>
       </c>
       <c r="P23" t="n">
-        <v>1.98</v>
+        <v>2.06</v>
       </c>
       <c r="Q23" t="n">
-        <v>1.1</v>
+        <v>1.83</v>
       </c>
       <c r="R23" t="n">
-        <v>1.18</v>
+        <v>1.39</v>
       </c>
       <c r="S23" t="n">
-        <v>1.1</v>
+        <v>3.1</v>
       </c>
       <c r="T23" t="n">
-        <v>1.11</v>
+        <v>2.18</v>
       </c>
       <c r="U23" t="n">
-        <v>1.11</v>
+        <v>1.73</v>
       </c>
       <c r="V23" t="n">
-        <v>1.09</v>
+        <v>1.08</v>
       </c>
       <c r="W23" t="n">
-        <v>2.58</v>
+        <v>3.4</v>
       </c>
       <c r="X23" t="n">
-        <v>1000</v>
+        <v>21</v>
       </c>
       <c r="Y23" t="n">
-        <v>1000</v>
+        <v>38</v>
       </c>
       <c r="Z23" t="n">
-        <v>1000</v>
+        <v>130</v>
       </c>
       <c r="AA23" t="n">
-        <v>1000</v>
+        <v>610</v>
       </c>
       <c r="AB23" t="n">
-        <v>1000</v>
+        <v>7.8</v>
       </c>
       <c r="AC23" t="n">
-        <v>1000</v>
+        <v>14.5</v>
       </c>
       <c r="AD23" t="n">
-        <v>1000</v>
+        <v>55</v>
       </c>
       <c r="AE23" t="n">
-        <v>1000</v>
+        <v>270</v>
       </c>
       <c r="AF23" t="n">
-        <v>1000</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AG23" t="n">
-        <v>1000</v>
+        <v>13</v>
       </c>
       <c r="AH23" t="n">
-        <v>1000</v>
+        <v>40</v>
       </c>
       <c r="AI23" t="n">
-        <v>1000</v>
+        <v>210</v>
       </c>
       <c r="AJ23" t="n">
-        <v>1000</v>
+        <v>13.5</v>
       </c>
       <c r="AK23" t="n">
-        <v>1000</v>
+        <v>19.5</v>
       </c>
       <c r="AL23" t="n">
-        <v>1000</v>
+        <v>55</v>
       </c>
       <c r="AM23" t="n">
-        <v>1000</v>
+        <v>260</v>
       </c>
       <c r="AN23" t="n">
-        <v>1000</v>
+        <v>8</v>
       </c>
       <c r="AO23" t="n">
-        <v>1000</v>
+        <v>440</v>
       </c>
       <c r="AP23" t="n">
-        <v>1.01</v>
+        <v>14.5</v>
       </c>
       <c r="AQ23" t="n">
-        <v>1.01</v>
+        <v>4.2</v>
       </c>
       <c r="AR23" t="n">
-        <v>1.01</v>
+        <v>4.6</v>
       </c>
       <c r="AS23" t="n">
-        <v>1.01</v>
+        <v>4.7</v>
       </c>
       <c r="AT23" t="n">
-        <v>1.01</v>
+        <v>6.4</v>
       </c>
       <c r="AU23" t="n">
-        <v>1.01</v>
+        <v>10</v>
       </c>
       <c r="AV23" t="n">
-        <v>1.01</v>
+        <v>4.4</v>
       </c>
       <c r="AW23" t="n">
-        <v>1.01</v>
+        <v>4.7</v>
       </c>
       <c r="AX23" t="n">
-        <v>1.01</v>
+        <v>6.6</v>
       </c>
       <c r="AY23" t="n">
-        <v>1.01</v>
+        <v>9</v>
       </c>
       <c r="AZ23" t="n">
-        <v>1.01</v>
+        <v>4.2</v>
       </c>
       <c r="BA23" t="n">
-        <v>1.01</v>
+        <v>4.7</v>
       </c>
       <c r="BB23" t="n">
-        <v>1.01</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BC23" t="n">
-        <v>1.01</v>
+        <v>13.5</v>
       </c>
       <c r="BD23" t="n">
-        <v>1.01</v>
+        <v>4.4</v>
       </c>
       <c r="BE23" t="n">
-        <v>1.01</v>
+        <v>4.7</v>
       </c>
       <c r="BF23" t="n">
-        <v>1.01</v>
+        <v>5.1</v>
       </c>
       <c r="BG23" t="n">
-        <v>1.01</v>
+        <v>4.7</v>
       </c>
       <c r="BH23" t="n">
         <v>1000</v>
@@ -6414,7 +6414,7 @@
       </c>
       <c r="CB23" t="inlineStr">
         <is>
-          <t>2026-06-11 07:05:44</t>
+          <t>2026-06-11 09:18:50</t>
         </is>
       </c>
     </row>
@@ -6431,251 +6431,251 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>16:00:00</t>
+          <t>15:45:00</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>Shelbourne</t>
+          <t>Galway Utd</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Shamrock Rovers</t>
+          <t>Dundalk</t>
         </is>
       </c>
       <c r="F24" t="n">
         <v>2.78</v>
       </c>
       <c r="G24" t="n">
-        <v>2.98</v>
+        <v>3.05</v>
       </c>
       <c r="H24" t="n">
-        <v>2.68</v>
+        <v>2.38</v>
       </c>
       <c r="I24" t="n">
-        <v>2.9</v>
+        <v>2.6</v>
       </c>
       <c r="J24" t="n">
-        <v>3.2</v>
+        <v>3.65</v>
       </c>
       <c r="K24" t="n">
-        <v>3.5</v>
+        <v>4.1</v>
       </c>
       <c r="L24" t="n">
-        <v>1.41</v>
+        <v>1.01</v>
       </c>
       <c r="M24" t="n">
-        <v>1.09</v>
+        <v>1.04</v>
       </c>
       <c r="N24" t="n">
-        <v>3.2</v>
+        <v>5</v>
       </c>
       <c r="O24" t="n">
-        <v>1.39</v>
+        <v>1.2</v>
       </c>
       <c r="P24" t="n">
-        <v>1.76</v>
+        <v>2.36</v>
       </c>
       <c r="Q24" t="n">
-        <v>2.16</v>
+        <v>1.64</v>
       </c>
       <c r="R24" t="n">
-        <v>1.28</v>
+        <v>1.38</v>
       </c>
       <c r="S24" t="n">
-        <v>4</v>
+        <v>2.32</v>
       </c>
       <c r="T24" t="n">
-        <v>1.85</v>
+        <v>1.58</v>
       </c>
       <c r="U24" t="n">
-        <v>2.06</v>
+        <v>2.44</v>
       </c>
       <c r="V24" t="n">
-        <v>1.53</v>
+        <v>1.62</v>
       </c>
       <c r="W24" t="n">
-        <v>1.5</v>
+        <v>1.48</v>
       </c>
       <c r="X24" t="n">
-        <v>14</v>
+        <v>1000</v>
       </c>
       <c r="Y24" t="n">
-        <v>12.5</v>
+        <v>1000</v>
       </c>
       <c r="Z24" t="n">
-        <v>22</v>
+        <v>1000</v>
       </c>
       <c r="AA24" t="n">
-        <v>55</v>
+        <v>1000</v>
       </c>
       <c r="AB24" t="n">
-        <v>12.5</v>
+        <v>1000</v>
       </c>
       <c r="AC24" t="n">
-        <v>7.6</v>
+        <v>1000</v>
       </c>
       <c r="AD24" t="n">
-        <v>15.5</v>
+        <v>1000</v>
       </c>
       <c r="AE24" t="n">
-        <v>42</v>
+        <v>1000</v>
       </c>
       <c r="AF24" t="n">
-        <v>23</v>
+        <v>1000</v>
       </c>
       <c r="AG24" t="n">
-        <v>16</v>
+        <v>1000</v>
       </c>
       <c r="AH24" t="n">
-        <v>22</v>
+        <v>1000</v>
       </c>
       <c r="AI24" t="n">
-        <v>60</v>
+        <v>1000</v>
       </c>
       <c r="AJ24" t="n">
-        <v>60</v>
+        <v>1000</v>
       </c>
       <c r="AK24" t="n">
-        <v>44</v>
+        <v>1000</v>
       </c>
       <c r="AL24" t="n">
-        <v>60</v>
+        <v>1000</v>
       </c>
       <c r="AM24" t="n">
-        <v>130</v>
+        <v>1000</v>
       </c>
       <c r="AN24" t="n">
-        <v>42</v>
+        <v>1000</v>
       </c>
       <c r="AO24" t="n">
-        <v>38</v>
+        <v>1000</v>
       </c>
       <c r="AP24" t="n">
-        <v>10.5</v>
+        <v>1.01</v>
       </c>
       <c r="AQ24" t="n">
-        <v>9.199999999999999</v>
+        <v>1.01</v>
       </c>
       <c r="AR24" t="n">
-        <v>4</v>
+        <v>1.01</v>
       </c>
       <c r="AS24" t="n">
-        <v>4.5</v>
+        <v>1.01</v>
       </c>
       <c r="AT24" t="n">
-        <v>9.4</v>
+        <v>1.01</v>
       </c>
       <c r="AU24" t="n">
-        <v>6.6</v>
+        <v>1.01</v>
       </c>
       <c r="AV24" t="n">
-        <v>11</v>
+        <v>1.01</v>
       </c>
       <c r="AW24" t="n">
-        <v>4.4</v>
+        <v>1.01</v>
       </c>
       <c r="AX24" t="n">
-        <v>16.5</v>
+        <v>1.01</v>
       </c>
       <c r="AY24" t="n">
-        <v>11.5</v>
+        <v>1.01</v>
       </c>
       <c r="AZ24" t="n">
-        <v>4</v>
+        <v>1.01</v>
       </c>
       <c r="BA24" t="n">
-        <v>4.5</v>
+        <v>1.01</v>
       </c>
       <c r="BB24" t="n">
-        <v>4.5</v>
+        <v>1.01</v>
       </c>
       <c r="BC24" t="n">
-        <v>4.4</v>
+        <v>1.01</v>
       </c>
       <c r="BD24" t="n">
-        <v>4.5</v>
+        <v>1.01</v>
       </c>
       <c r="BE24" t="n">
-        <v>4.7</v>
+        <v>1.01</v>
       </c>
       <c r="BF24" t="n">
-        <v>4.4</v>
+        <v>1.01</v>
       </c>
       <c r="BG24" t="n">
-        <v>4.3</v>
+        <v>1.01</v>
       </c>
       <c r="BH24" t="n">
         <v>1000</v>
       </c>
       <c r="BI24" t="n">
-        <v>1.78</v>
+        <v>1.04</v>
       </c>
       <c r="BJ24" t="n">
-        <v>13.5</v>
+        <v>1000</v>
       </c>
       <c r="BK24" t="n">
-        <v>1.57</v>
+        <v>1.04</v>
       </c>
       <c r="BL24" t="n">
         <v>1000</v>
       </c>
       <c r="BM24" t="n">
-        <v>1.78</v>
+        <v>1.04</v>
       </c>
       <c r="BN24" t="n">
-        <v>8.199999999999999</v>
+        <v>1000</v>
       </c>
       <c r="BO24" t="n">
-        <v>4.5</v>
+        <v>1.04</v>
       </c>
       <c r="BP24" t="n">
-        <v>34</v>
+        <v>1000</v>
       </c>
       <c r="BQ24" t="n">
-        <v>1.69</v>
+        <v>1.04</v>
       </c>
       <c r="BR24" t="n">
         <v>1000</v>
       </c>
       <c r="BS24" t="n">
-        <v>1.73</v>
+        <v>1.04</v>
       </c>
       <c r="BT24" t="n">
-        <v>8</v>
+        <v>1000</v>
       </c>
       <c r="BU24" t="n">
-        <v>4.4</v>
+        <v>1.04</v>
       </c>
       <c r="BV24" t="n">
-        <v>32</v>
+        <v>1000</v>
       </c>
       <c r="BW24" t="n">
-        <v>1.69</v>
+        <v>1.04</v>
       </c>
       <c r="BX24" t="n">
         <v>1000</v>
       </c>
       <c r="BY24" t="n">
-        <v>1.73</v>
+        <v>1.04</v>
       </c>
       <c r="BZ24" t="n">
-        <v>48</v>
+        <v>1000</v>
       </c>
       <c r="CA24" t="n">
-        <v>1.72</v>
+        <v>1.04</v>
       </c>
       <c r="CB24" t="inlineStr">
         <is>
-          <t>2026-06-11 07:05:44</t>
+          <t>2026-06-11 09:18:50</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Icelandic 1 Deild</t>
+          <t>Bolivian Liga de Futbol Profesional</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -6685,60 +6685,60 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>16:15:00</t>
+          <t>16:00:00</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>Throttur</t>
+          <t>San Antonio Bulo Bulo</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>HK Kopavogur</t>
+          <t>Academia de Balompie Boli</t>
         </is>
       </c>
       <c r="F25" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="G25" t="n">
+        <v>1.63</v>
+      </c>
+      <c r="H25" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="I25" t="n">
+        <v>14</v>
+      </c>
+      <c r="J25" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="K25" t="n">
+        <v>1000</v>
+      </c>
+      <c r="L25" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="M25" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="N25" t="n">
+        <v>1.99</v>
+      </c>
+      <c r="O25" t="n">
         <v>1.09</v>
       </c>
-      <c r="G25" t="n">
-        <v>1000</v>
-      </c>
-      <c r="H25" t="n">
+      <c r="P25" t="n">
+        <v>1.98</v>
+      </c>
+      <c r="Q25" t="n">
         <v>1.09</v>
       </c>
-      <c r="I25" t="n">
-        <v>1000</v>
-      </c>
-      <c r="J25" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="K25" t="n">
-        <v>1000</v>
-      </c>
-      <c r="L25" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="M25" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="N25" t="n">
-        <v>2</v>
-      </c>
-      <c r="O25" t="n">
-        <v>1.11</v>
-      </c>
-      <c r="P25" t="n">
-        <v>2</v>
-      </c>
-      <c r="Q25" t="n">
-        <v>1.11</v>
-      </c>
       <c r="R25" t="n">
-        <v>1.24</v>
+        <v>1.18</v>
       </c>
       <c r="S25" t="n">
-        <v>1.11</v>
+        <v>1.09</v>
       </c>
       <c r="T25" t="n">
         <v>1.11</v>
@@ -6747,10 +6747,10 @@
         <v>1.11</v>
       </c>
       <c r="V25" t="n">
-        <v>1.02</v>
+        <v>1.1</v>
       </c>
       <c r="W25" t="n">
-        <v>1.02</v>
+        <v>2.58</v>
       </c>
       <c r="X25" t="n">
         <v>1000</v>
@@ -6922,14 +6922,14 @@
       </c>
       <c r="CB25" t="inlineStr">
         <is>
-          <t>2026-06-11 07:05:44</t>
+          <t>2026-06-11 09:18:50</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Brazilian Serie B</t>
+          <t>Irish Premier Division</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -6939,251 +6939,251 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>19:00:00</t>
+          <t>16:00:00</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>Atletico GO</t>
+          <t>Shelbourne</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>CRB</t>
+          <t>Shamrock Rovers</t>
         </is>
       </c>
       <c r="F26" t="n">
-        <v>2.18</v>
+        <v>2.78</v>
       </c>
       <c r="G26" t="n">
-        <v>2.34</v>
+        <v>3.05</v>
       </c>
       <c r="H26" t="n">
-        <v>3.6</v>
+        <v>2.68</v>
       </c>
       <c r="I26" t="n">
-        <v>4.1</v>
+        <v>2.94</v>
       </c>
       <c r="J26" t="n">
-        <v>3.35</v>
+        <v>3.2</v>
       </c>
       <c r="K26" t="n">
-        <v>3.4</v>
+        <v>3.45</v>
       </c>
       <c r="L26" t="n">
-        <v>1.43</v>
+        <v>1.01</v>
       </c>
       <c r="M26" t="n">
-        <v>1.1</v>
+        <v>1.08</v>
       </c>
       <c r="N26" t="n">
-        <v>3</v>
+        <v>3.1</v>
       </c>
       <c r="O26" t="n">
-        <v>1.44</v>
+        <v>1.36</v>
       </c>
       <c r="P26" t="n">
-        <v>1.67</v>
+        <v>1.75</v>
       </c>
       <c r="Q26" t="n">
-        <v>2.3</v>
+        <v>2.16</v>
       </c>
       <c r="R26" t="n">
-        <v>1.27</v>
+        <v>1.25</v>
       </c>
       <c r="S26" t="n">
-        <v>4.5</v>
+        <v>3.5</v>
       </c>
       <c r="T26" t="n">
-        <v>1.92</v>
+        <v>1.53</v>
       </c>
       <c r="U26" t="n">
-        <v>1.87</v>
+        <v>1.55</v>
       </c>
       <c r="V26" t="n">
-        <v>1.33</v>
+        <v>1.52</v>
       </c>
       <c r="W26" t="n">
-        <v>1.74</v>
+        <v>1.49</v>
       </c>
       <c r="X26" t="n">
-        <v>12</v>
+        <v>1000</v>
       </c>
       <c r="Y26" t="n">
-        <v>970</v>
+        <v>1000</v>
       </c>
       <c r="Z26" t="n">
-        <v>28</v>
+        <v>1000</v>
       </c>
       <c r="AA26" t="n">
-        <v>95</v>
+        <v>1000</v>
       </c>
       <c r="AB26" t="n">
-        <v>970</v>
+        <v>1000</v>
       </c>
       <c r="AC26" t="n">
-        <v>970</v>
+        <v>1000</v>
       </c>
       <c r="AD26" t="n">
-        <v>970</v>
+        <v>1000</v>
       </c>
       <c r="AE26" t="n">
-        <v>60</v>
+        <v>1000</v>
       </c>
       <c r="AF26" t="n">
-        <v>970</v>
+        <v>1000</v>
       </c>
       <c r="AG26" t="n">
-        <v>970</v>
+        <v>1000</v>
       </c>
       <c r="AH26" t="n">
-        <v>950</v>
+        <v>1000</v>
       </c>
       <c r="AI26" t="n">
-        <v>75</v>
+        <v>1000</v>
       </c>
       <c r="AJ26" t="n">
-        <v>32</v>
+        <v>1000</v>
       </c>
       <c r="AK26" t="n">
-        <v>29</v>
+        <v>1000</v>
       </c>
       <c r="AL26" t="n">
-        <v>50</v>
+        <v>1000</v>
       </c>
       <c r="AM26" t="n">
-        <v>160</v>
+        <v>1000</v>
       </c>
       <c r="AN26" t="n">
-        <v>26</v>
+        <v>1000</v>
       </c>
       <c r="AO26" t="n">
-        <v>75</v>
+        <v>1000</v>
       </c>
       <c r="AP26" t="n">
-        <v>5.1</v>
+        <v>1.01</v>
       </c>
       <c r="AQ26" t="n">
-        <v>5.2</v>
+        <v>1.01</v>
       </c>
       <c r="AR26" t="n">
-        <v>6.8</v>
+        <v>1.01</v>
       </c>
       <c r="AS26" t="n">
-        <v>8.199999999999999</v>
+        <v>1.01</v>
       </c>
       <c r="AT26" t="n">
-        <v>4.3</v>
+        <v>1.01</v>
       </c>
       <c r="AU26" t="n">
-        <v>6.4</v>
+        <v>1.01</v>
       </c>
       <c r="AV26" t="n">
-        <v>5.9</v>
+        <v>1.01</v>
       </c>
       <c r="AW26" t="n">
-        <v>7.8</v>
+        <v>1.01</v>
       </c>
       <c r="AX26" t="n">
-        <v>5.5</v>
+        <v>1.01</v>
       </c>
       <c r="AY26" t="n">
-        <v>5.1</v>
+        <v>1.01</v>
       </c>
       <c r="AZ26" t="n">
-        <v>6.4</v>
+        <v>1.01</v>
       </c>
       <c r="BA26" t="n">
-        <v>8</v>
+        <v>1.01</v>
       </c>
       <c r="BB26" t="n">
-        <v>7</v>
+        <v>1.01</v>
       </c>
       <c r="BC26" t="n">
-        <v>6.8</v>
+        <v>1.01</v>
       </c>
       <c r="BD26" t="n">
-        <v>7.6</v>
+        <v>1.01</v>
       </c>
       <c r="BE26" t="n">
-        <v>8.4</v>
+        <v>1.01</v>
       </c>
       <c r="BF26" t="n">
-        <v>18.5</v>
+        <v>1.01</v>
       </c>
       <c r="BG26" t="n">
-        <v>8</v>
+        <v>1.01</v>
       </c>
       <c r="BH26" t="n">
-        <v>3.1</v>
+        <v>1000</v>
       </c>
       <c r="BI26" t="n">
-        <v>2.48</v>
+        <v>1.04</v>
       </c>
       <c r="BJ26" t="n">
-        <v>11</v>
+        <v>1000</v>
       </c>
       <c r="BK26" t="n">
-        <v>5.3</v>
+        <v>1.48</v>
       </c>
       <c r="BL26" t="n">
         <v>1000</v>
       </c>
       <c r="BM26" t="n">
-        <v>9.800000000000001</v>
+        <v>1.65</v>
       </c>
       <c r="BN26" t="n">
-        <v>5.1</v>
+        <v>1000</v>
       </c>
       <c r="BO26" t="n">
-        <v>3.9</v>
+        <v>1.39</v>
       </c>
       <c r="BP26" t="n">
         <v>1000</v>
       </c>
       <c r="BQ26" t="n">
-        <v>6.6</v>
+        <v>1.58</v>
       </c>
       <c r="BR26" t="n">
         <v>1000</v>
       </c>
       <c r="BS26" t="n">
-        <v>8.199999999999999</v>
+        <v>1.04</v>
       </c>
       <c r="BT26" t="n">
-        <v>7.2</v>
+        <v>1000</v>
       </c>
       <c r="BU26" t="n">
-        <v>5.4</v>
+        <v>1.39</v>
       </c>
       <c r="BV26" t="n">
         <v>1000</v>
       </c>
       <c r="BW26" t="n">
-        <v>8</v>
+        <v>1.57</v>
       </c>
       <c r="BX26" t="n">
         <v>1000</v>
       </c>
       <c r="BY26" t="n">
-        <v>8.800000000000001</v>
+        <v>1.04</v>
       </c>
       <c r="BZ26" t="n">
         <v>1000</v>
       </c>
       <c r="CA26" t="n">
-        <v>8.199999999999999</v>
+        <v>1.04</v>
       </c>
       <c r="CB26" t="inlineStr">
         <is>
-          <t>2026-06-11 07:05:44</t>
+          <t>2026-06-11 09:18:50</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Bolivian Liga de Futbol Profesional</t>
+          <t>Icelandic 1 Deild</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -7193,251 +7193,251 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>20:00:00</t>
+          <t>16:15:00</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>Nacional Potosi</t>
+          <t>Throttur</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>CDT Real Oruro</t>
+          <t>HK Kopavogur</t>
         </is>
       </c>
       <c r="F27" t="n">
+        <v>1.69</v>
+      </c>
+      <c r="G27" t="n">
+        <v>1.84</v>
+      </c>
+      <c r="H27" t="n">
+        <v>4</v>
+      </c>
+      <c r="I27" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="J27" t="n">
+        <v>4</v>
+      </c>
+      <c r="K27" t="n">
+        <v>5.3</v>
+      </c>
+      <c r="L27" t="n">
+        <v>1.21</v>
+      </c>
+      <c r="M27" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="N27" t="n">
+        <v>3.45</v>
+      </c>
+      <c r="O27" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="P27" t="n">
+        <v>3</v>
+      </c>
+      <c r="Q27" t="n">
         <v>1.37</v>
       </c>
-      <c r="G27" t="n">
-        <v>1.49</v>
-      </c>
-      <c r="H27" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="I27" t="n">
-        <v>1000</v>
-      </c>
-      <c r="J27" t="n">
+      <c r="R27" t="n">
+        <v>1.88</v>
+      </c>
+      <c r="S27" t="n">
+        <v>1.92</v>
+      </c>
+      <c r="T27" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="U27" t="n">
+        <v>2.78</v>
+      </c>
+      <c r="V27" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="W27" t="n">
+        <v>2.18</v>
+      </c>
+      <c r="X27" t="n">
+        <v>48</v>
+      </c>
+      <c r="Y27" t="n">
+        <v>38</v>
+      </c>
+      <c r="Z27" t="n">
+        <v>55</v>
+      </c>
+      <c r="AA27" t="n">
+        <v>110</v>
+      </c>
+      <c r="AB27" t="n">
+        <v>22</v>
+      </c>
+      <c r="AC27" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="AD27" t="n">
+        <v>24</v>
+      </c>
+      <c r="AE27" t="n">
+        <v>50</v>
+      </c>
+      <c r="AF27" t="n">
+        <v>20</v>
+      </c>
+      <c r="AG27" t="n">
+        <v>14</v>
+      </c>
+      <c r="AH27" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="AI27" t="n">
+        <v>46</v>
+      </c>
+      <c r="AJ27" t="n">
+        <v>25</v>
+      </c>
+      <c r="AK27" t="n">
+        <v>19.5</v>
+      </c>
+      <c r="AL27" t="n">
+        <v>27</v>
+      </c>
+      <c r="AM27" t="n">
+        <v>60</v>
+      </c>
+      <c r="AN27" t="n">
+        <v>5.9</v>
+      </c>
+      <c r="AO27" t="n">
+        <v>29</v>
+      </c>
+      <c r="AP27" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="AQ27" t="n">
         <v>4.4</v>
       </c>
-      <c r="K27" t="n">
-        <v>9.800000000000001</v>
-      </c>
-      <c r="L27" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="M27" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="N27" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="O27" t="n">
-        <v>1.09</v>
-      </c>
-      <c r="P27" t="n">
-        <v>1.24</v>
-      </c>
-      <c r="Q27" t="n">
-        <v>1.09</v>
-      </c>
-      <c r="R27" t="n">
-        <v>1.18</v>
-      </c>
-      <c r="S27" t="n">
-        <v>1.09</v>
-      </c>
-      <c r="T27" t="n">
-        <v>1.11</v>
-      </c>
-      <c r="U27" t="n">
-        <v>1.11</v>
-      </c>
-      <c r="V27" t="n">
-        <v>1.09</v>
-      </c>
-      <c r="W27" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="X27" t="n">
-        <v>1000</v>
-      </c>
-      <c r="Y27" t="n">
-        <v>1000</v>
-      </c>
-      <c r="Z27" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AA27" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AB27" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AC27" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AD27" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AE27" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AF27" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AG27" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AH27" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AI27" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AJ27" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AK27" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AL27" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AM27" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AN27" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AO27" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AP27" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="AQ27" t="n">
-        <v>1.01</v>
-      </c>
       <c r="AR27" t="n">
-        <v>1.01</v>
+        <v>4.6</v>
       </c>
       <c r="AS27" t="n">
-        <v>1.01</v>
+        <v>4.8</v>
       </c>
       <c r="AT27" t="n">
-        <v>1.01</v>
+        <v>4.1</v>
       </c>
       <c r="AU27" t="n">
-        <v>1.01</v>
+        <v>3.8</v>
       </c>
       <c r="AV27" t="n">
-        <v>1.01</v>
+        <v>4.1</v>
       </c>
       <c r="AW27" t="n">
-        <v>1.01</v>
+        <v>4.5</v>
       </c>
       <c r="AX27" t="n">
-        <v>1.01</v>
+        <v>4</v>
       </c>
       <c r="AY27" t="n">
-        <v>1.01</v>
+        <v>3.7</v>
       </c>
       <c r="AZ27" t="n">
-        <v>1.01</v>
+        <v>3.85</v>
       </c>
       <c r="BA27" t="n">
-        <v>1.01</v>
+        <v>4.5</v>
       </c>
       <c r="BB27" t="n">
-        <v>1.01</v>
+        <v>4.2</v>
       </c>
       <c r="BC27" t="n">
-        <v>1.01</v>
+        <v>4</v>
       </c>
       <c r="BD27" t="n">
-        <v>1.01</v>
+        <v>4.2</v>
       </c>
       <c r="BE27" t="n">
-        <v>1.01</v>
+        <v>4.6</v>
       </c>
       <c r="BF27" t="n">
-        <v>1.01</v>
+        <v>2.72</v>
       </c>
       <c r="BG27" t="n">
-        <v>1.01</v>
+        <v>4.3</v>
       </c>
       <c r="BH27" t="n">
-        <v>1000</v>
+        <v>5.6</v>
       </c>
       <c r="BI27" t="n">
-        <v>1.04</v>
+        <v>3.65</v>
       </c>
       <c r="BJ27" t="n">
-        <v>1000</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BK27" t="n">
-        <v>1.04</v>
+        <v>4.8</v>
       </c>
       <c r="BL27" t="n">
         <v>1000</v>
       </c>
       <c r="BM27" t="n">
-        <v>1.04</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BN27" t="n">
-        <v>1000</v>
+        <v>5.5</v>
       </c>
       <c r="BO27" t="n">
-        <v>1.04</v>
+        <v>3.65</v>
       </c>
       <c r="BP27" t="n">
-        <v>1000</v>
+        <v>11</v>
       </c>
       <c r="BQ27" t="n">
-        <v>1.04</v>
+        <v>5.4</v>
       </c>
       <c r="BR27" t="n">
-        <v>1000</v>
+        <v>18</v>
       </c>
       <c r="BS27" t="n">
-        <v>1.04</v>
+        <v>6.6</v>
       </c>
       <c r="BT27" t="n">
-        <v>1000</v>
+        <v>9</v>
       </c>
       <c r="BU27" t="n">
-        <v>1.04</v>
+        <v>4.9</v>
       </c>
       <c r="BV27" t="n">
         <v>1000</v>
       </c>
       <c r="BW27" t="n">
-        <v>1.04</v>
+        <v>7.8</v>
       </c>
       <c r="BX27" t="n">
         <v>1000</v>
       </c>
       <c r="BY27" t="n">
-        <v>1.04</v>
+        <v>7.8</v>
       </c>
       <c r="BZ27" t="n">
-        <v>1000</v>
+        <v>11</v>
       </c>
       <c r="CA27" t="n">
-        <v>1.04</v>
+        <v>5.4</v>
       </c>
       <c r="CB27" t="inlineStr">
         <is>
-          <t>2026-06-11 07:05:44</t>
+          <t>2026-06-11 09:18:50</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Chilean Primera Division</t>
+          <t>Brazilian Serie B</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -7447,244 +7447,752 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>21:00:00</t>
+          <t>19:00:00</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>Audax Italiano</t>
+          <t>Atletico GO</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>La Serena</t>
+          <t>CRB</t>
         </is>
       </c>
       <c r="F28" t="n">
-        <v>1.99</v>
+        <v>2.2</v>
       </c>
       <c r="G28" t="n">
-        <v>2.12</v>
+        <v>2.38</v>
       </c>
       <c r="H28" t="n">
-        <v>3.7</v>
+        <v>3.6</v>
       </c>
       <c r="I28" t="n">
         <v>4.1</v>
       </c>
       <c r="J28" t="n">
-        <v>3.7</v>
+        <v>3.2</v>
       </c>
       <c r="K28" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="L28" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="M28" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="N28" t="n">
+        <v>2.98</v>
+      </c>
+      <c r="O28" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="P28" t="n">
+        <v>1.66</v>
+      </c>
+      <c r="Q28" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="R28" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="S28" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="T28" t="n">
+        <v>1.97</v>
+      </c>
+      <c r="U28" t="n">
+        <v>1.89</v>
+      </c>
+      <c r="V28" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="W28" t="n">
+        <v>1.72</v>
+      </c>
+      <c r="X28" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="Y28" t="n">
+        <v>970</v>
+      </c>
+      <c r="Z28" t="n">
+        <v>28</v>
+      </c>
+      <c r="AA28" t="n">
+        <v>95</v>
+      </c>
+      <c r="AB28" t="n">
+        <v>970</v>
+      </c>
+      <c r="AC28" t="n">
+        <v>8</v>
+      </c>
+      <c r="AD28" t="n">
+        <v>970</v>
+      </c>
+      <c r="AE28" t="n">
+        <v>60</v>
+      </c>
+      <c r="AF28" t="n">
+        <v>970</v>
+      </c>
+      <c r="AG28" t="n">
+        <v>970</v>
+      </c>
+      <c r="AH28" t="n">
+        <v>950</v>
+      </c>
+      <c r="AI28" t="n">
+        <v>80</v>
+      </c>
+      <c r="AJ28" t="n">
+        <v>38</v>
+      </c>
+      <c r="AK28" t="n">
+        <v>30</v>
+      </c>
+      <c r="AL28" t="n">
+        <v>60</v>
+      </c>
+      <c r="AM28" t="n">
+        <v>170</v>
+      </c>
+      <c r="AN28" t="n">
+        <v>27</v>
+      </c>
+      <c r="AO28" t="n">
+        <v>80</v>
+      </c>
+      <c r="AP28" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="AQ28" t="n">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="AR28" t="n">
+        <v>6</v>
+      </c>
+      <c r="AS28" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="AT28" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="AU28" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="AV28" t="n">
+        <v>5.3</v>
+      </c>
+      <c r="AW28" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="AX28" t="n">
+        <v>5</v>
+      </c>
+      <c r="AY28" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="AZ28" t="n">
+        <v>5.8</v>
+      </c>
+      <c r="BA28" t="n">
+        <v>7</v>
+      </c>
+      <c r="BB28" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="BC28" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="BD28" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="BE28" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="BF28" t="n">
+        <v>6</v>
+      </c>
+      <c r="BG28" t="n">
+        <v>7</v>
+      </c>
+      <c r="BH28" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BI28" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="BJ28" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BK28" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="BL28" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BM28" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="BN28" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BO28" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="BP28" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BQ28" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="BR28" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BS28" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="BT28" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BU28" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="BV28" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BW28" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="BX28" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BY28" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="BZ28" t="n">
+        <v>1000</v>
+      </c>
+      <c r="CA28" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="CB28" t="inlineStr">
+        <is>
+          <t>2026-06-11 09:18:50</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>Bolivian Liga de Futbol Profesional</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>2026-06-12</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>20:00:00</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>Nacional Potosi</t>
+        </is>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>CDT Real Oruro</t>
+        </is>
+      </c>
+      <c r="F29" t="n">
+        <v>1.37</v>
+      </c>
+      <c r="G29" t="n">
+        <v>1.49</v>
+      </c>
+      <c r="H29" t="n">
+        <v>3.65</v>
+      </c>
+      <c r="I29" t="n">
+        <v>100</v>
+      </c>
+      <c r="J29" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="K29" t="n">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="L29" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="M29" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="N29" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="O29" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="P29" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="Q29" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="R29" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="S29" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="T29" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="U29" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="V29" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="W29" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="X29" t="n">
+        <v>1000</v>
+      </c>
+      <c r="Y29" t="n">
+        <v>1000</v>
+      </c>
+      <c r="Z29" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AA29" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AB29" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AC29" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AD29" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AE29" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AF29" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AG29" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AH29" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AI29" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AJ29" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AK29" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AL29" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AM29" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AN29" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AO29" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AP29" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AQ29" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AR29" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AS29" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AT29" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AU29" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AV29" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AW29" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AX29" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AY29" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AZ29" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BA29" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BB29" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BC29" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BD29" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BE29" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BF29" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BG29" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BH29" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BI29" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="BJ29" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BK29" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="BL29" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BM29" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="BN29" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BO29" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="BP29" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BQ29" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="BR29" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BS29" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="BT29" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BU29" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="BV29" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BW29" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="BX29" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BY29" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="BZ29" t="n">
+        <v>1000</v>
+      </c>
+      <c r="CA29" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="CB29" t="inlineStr">
+        <is>
+          <t>2026-06-11 09:18:50</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>Chilean Primera Division</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>2026-06-12</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>21:00:00</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>Audax Italiano</t>
+        </is>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>La Serena</t>
+        </is>
+      </c>
+      <c r="F30" t="n">
+        <v>1.97</v>
+      </c>
+      <c r="G30" t="n">
+        <v>2.08</v>
+      </c>
+      <c r="H30" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="I30" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="J30" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="K30" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="L30" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="M30" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="N30" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="O30" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="P30" t="n">
+        <v>2.12</v>
+      </c>
+      <c r="Q30" t="n">
+        <v>1.77</v>
+      </c>
+      <c r="R30" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="S30" t="n">
+        <v>2.96</v>
+      </c>
+      <c r="T30" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="U30" t="n">
+        <v>2.24</v>
+      </c>
+      <c r="V30" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="W30" t="n">
+        <v>1.93</v>
+      </c>
+      <c r="X30" t="n">
+        <v>22</v>
+      </c>
+      <c r="Y30" t="n">
+        <v>19.5</v>
+      </c>
+      <c r="Z30" t="n">
+        <v>36</v>
+      </c>
+      <c r="AA30" t="n">
+        <v>90</v>
+      </c>
+      <c r="AB30" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="AC30" t="n">
+        <v>11</v>
+      </c>
+      <c r="AD30" t="n">
+        <v>19.5</v>
+      </c>
+      <c r="AE30" t="n">
+        <v>55</v>
+      </c>
+      <c r="AF30" t="n">
+        <v>16</v>
+      </c>
+      <c r="AG30" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="AH30" t="n">
+        <v>21</v>
+      </c>
+      <c r="AI30" t="n">
+        <v>60</v>
+      </c>
+      <c r="AJ30" t="n">
+        <v>30</v>
+      </c>
+      <c r="AK30" t="n">
+        <v>24</v>
+      </c>
+      <c r="AL30" t="n">
+        <v>40</v>
+      </c>
+      <c r="AM30" t="n">
+        <v>100</v>
+      </c>
+      <c r="AN30" t="n">
+        <v>15</v>
+      </c>
+      <c r="AO30" t="n">
+        <v>48</v>
+      </c>
+      <c r="AP30" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="AQ30" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="AR30" t="n">
         <v>4.1</v>
       </c>
-      <c r="L28" t="n">
-        <v>1.29</v>
-      </c>
-      <c r="M28" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="N28" t="n">
+      <c r="AS30" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="AT30" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="AU30" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="AV30" t="n">
+        <v>14</v>
+      </c>
+      <c r="AW30" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="AX30" t="n">
+        <v>12</v>
+      </c>
+      <c r="AY30" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="AZ30" t="n">
+        <v>15</v>
+      </c>
+      <c r="BA30" t="n">
+        <v>40</v>
+      </c>
+      <c r="BB30" t="n">
+        <v>21</v>
+      </c>
+      <c r="BC30" t="n">
+        <v>17.5</v>
+      </c>
+      <c r="BD30" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="BE30" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="BF30" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="BG30" t="n">
         <v>4.2</v>
       </c>
-      <c r="O28" t="n">
-        <v>1.26</v>
-      </c>
-      <c r="P28" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="Q28" t="n">
-        <v>1.77</v>
-      </c>
-      <c r="R28" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="S28" t="n">
-        <v>2.94</v>
-      </c>
-      <c r="T28" t="n">
-        <v>1.69</v>
-      </c>
-      <c r="U28" t="n">
-        <v>2.26</v>
-      </c>
-      <c r="V28" t="n">
-        <v>1.32</v>
-      </c>
-      <c r="W28" t="n">
-        <v>1.9</v>
-      </c>
-      <c r="X28" t="n">
-        <v>22</v>
-      </c>
-      <c r="Y28" t="n">
-        <v>19.5</v>
-      </c>
-      <c r="Z28" t="n">
-        <v>34</v>
-      </c>
-      <c r="AA28" t="n">
-        <v>75</v>
-      </c>
-      <c r="AB28" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="AC28" t="n">
+      <c r="BH30" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="BI30" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="BJ30" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="BK30" t="n">
+        <v>5.8</v>
+      </c>
+      <c r="BL30" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BM30" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="BN30" t="n">
+        <v>5</v>
+      </c>
+      <c r="BO30" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="BP30" t="n">
+        <v>14</v>
+      </c>
+      <c r="BQ30" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="BR30" t="n">
+        <v>26</v>
+      </c>
+      <c r="BS30" t="n">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="BT30" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="BU30" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="BV30" t="n">
+        <v>30</v>
+      </c>
+      <c r="BW30" t="n">
         <v>10</v>
       </c>
-      <c r="AD28" t="n">
-        <v>19</v>
-      </c>
-      <c r="AE28" t="n">
-        <v>55</v>
-      </c>
-      <c r="AF28" t="n">
-        <v>16.5</v>
-      </c>
-      <c r="AG28" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="AH28" t="n">
-        <v>19.5</v>
-      </c>
-      <c r="AI28" t="n">
-        <v>60</v>
-      </c>
-      <c r="AJ28" t="n">
-        <v>30</v>
-      </c>
-      <c r="AK28" t="n">
-        <v>24</v>
-      </c>
-      <c r="AL28" t="n">
-        <v>40</v>
-      </c>
-      <c r="AM28" t="n">
-        <v>85</v>
-      </c>
-      <c r="AN28" t="n">
-        <v>15.5</v>
-      </c>
-      <c r="AO28" t="n">
-        <v>46</v>
-      </c>
-      <c r="AP28" t="n">
-        <v>15.5</v>
-      </c>
-      <c r="AQ28" t="n">
-        <v>14</v>
-      </c>
-      <c r="AR28" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="AS28" t="n">
-        <v>4.7</v>
-      </c>
-      <c r="AT28" t="n">
-        <v>9.6</v>
-      </c>
-      <c r="AU28" t="n">
-        <v>7.8</v>
-      </c>
-      <c r="AV28" t="n">
-        <v>14</v>
-      </c>
-      <c r="AW28" t="n">
-        <v>36</v>
-      </c>
-      <c r="AX28" t="n">
-        <v>12</v>
-      </c>
-      <c r="AY28" t="n">
-        <v>9.4</v>
-      </c>
-      <c r="AZ28" t="n">
-        <v>14.5</v>
-      </c>
-      <c r="BA28" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="BB28" t="n">
+      <c r="BX30" t="n">
+        <v>38</v>
+      </c>
+      <c r="BY30" t="n">
+        <v>11</v>
+      </c>
+      <c r="BZ30" t="n">
         <v>21</v>
       </c>
-      <c r="BC28" t="n">
-        <v>18</v>
-      </c>
-      <c r="BD28" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="BE28" t="n">
-        <v>4.7</v>
-      </c>
-      <c r="BF28" t="n">
-        <v>9.6</v>
-      </c>
-      <c r="BG28" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="BH28" t="n">
-        <v>3.75</v>
-      </c>
-      <c r="BI28" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="BJ28" t="n">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="BK28" t="n">
-        <v>5.8</v>
-      </c>
-      <c r="BL28" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BM28" t="n">
-        <v>13.5</v>
-      </c>
-      <c r="BN28" t="n">
-        <v>5</v>
-      </c>
-      <c r="BO28" t="n">
-        <v>3.85</v>
-      </c>
-      <c r="BP28" t="n">
-        <v>14</v>
-      </c>
-      <c r="BQ28" t="n">
-        <v>7.4</v>
-      </c>
-      <c r="BR28" t="n">
-        <v>26</v>
-      </c>
-      <c r="BS28" t="n">
-        <v>9.800000000000001</v>
-      </c>
-      <c r="BT28" t="n">
-        <v>7.4</v>
-      </c>
-      <c r="BU28" t="n">
-        <v>5.5</v>
-      </c>
-      <c r="BV28" t="n">
-        <v>30</v>
-      </c>
-      <c r="BW28" t="n">
-        <v>10</v>
-      </c>
-      <c r="BX28" t="n">
-        <v>38</v>
-      </c>
-      <c r="BY28" t="n">
-        <v>11</v>
-      </c>
-      <c r="BZ28" t="n">
-        <v>21</v>
-      </c>
-      <c r="CA28" t="n">
+      <c r="CA30" t="n">
         <v>9</v>
       </c>
-      <c r="CB28" t="inlineStr">
-        <is>
-          <t>2026-06-11 07:05:44</t>
+      <c r="CB30" t="inlineStr">
+        <is>
+          <t>2026-06-11 09:18:50</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-06-12.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-06-12.xlsx
@@ -857,166 +857,166 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>1.24</v>
+        <v>1.5</v>
       </c>
       <c r="G2" t="n">
-        <v>600</v>
+        <v>1.66</v>
       </c>
       <c r="H2" t="n">
-        <v>1.04</v>
+        <v>5.7</v>
       </c>
       <c r="I2" t="n">
-        <v>1000</v>
+        <v>9.4</v>
       </c>
       <c r="J2" t="n">
-        <v>1.1</v>
+        <v>3.6</v>
       </c>
       <c r="K2" t="n">
-        <v>1000</v>
+        <v>32</v>
       </c>
       <c r="L2" t="n">
         <v>1.01</v>
       </c>
       <c r="M2" t="n">
-        <v>1.01</v>
+        <v>1.06</v>
       </c>
       <c r="N2" t="n">
-        <v>1.35</v>
+        <v>3.55</v>
       </c>
       <c r="O2" t="n">
         <v>1.3</v>
       </c>
       <c r="P2" t="n">
+        <v>1.89</v>
+      </c>
+      <c r="Q2" t="n">
+        <v>1.86</v>
+      </c>
+      <c r="R2" t="n">
         <v>1.34</v>
       </c>
-      <c r="Q2" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="R2" t="n">
-        <v>1.18</v>
-      </c>
       <c r="S2" t="n">
-        <v>1.3</v>
+        <v>2.96</v>
       </c>
       <c r="T2" t="n">
-        <v>1.01</v>
+        <v>1.94</v>
       </c>
       <c r="U2" t="n">
-        <v>1.01</v>
+        <v>1.81</v>
       </c>
       <c r="V2" t="n">
-        <v>1.02</v>
+        <v>1.13</v>
       </c>
       <c r="W2" t="n">
-        <v>1.14</v>
+        <v>2.5</v>
       </c>
       <c r="X2" t="n">
-        <v>1000</v>
+        <v>970</v>
       </c>
       <c r="Y2" t="n">
-        <v>1000</v>
+        <v>950</v>
       </c>
       <c r="Z2" t="n">
-        <v>1000</v>
+        <v>75</v>
       </c>
       <c r="AA2" t="n">
         <v>1000</v>
       </c>
       <c r="AB2" t="n">
-        <v>1000</v>
+        <v>970</v>
       </c>
       <c r="AC2" t="n">
-        <v>1000</v>
+        <v>970</v>
       </c>
       <c r="AD2" t="n">
-        <v>1000</v>
+        <v>950</v>
       </c>
       <c r="AE2" t="n">
         <v>1000</v>
       </c>
       <c r="AF2" t="n">
-        <v>1000</v>
+        <v>970</v>
       </c>
       <c r="AG2" t="n">
-        <v>1000</v>
+        <v>970</v>
       </c>
       <c r="AH2" t="n">
-        <v>1000</v>
+        <v>950</v>
       </c>
       <c r="AI2" t="n">
         <v>1000</v>
       </c>
       <c r="AJ2" t="n">
-        <v>1000</v>
+        <v>970</v>
       </c>
       <c r="AK2" t="n">
-        <v>1000</v>
+        <v>21</v>
       </c>
       <c r="AL2" t="n">
-        <v>1000</v>
+        <v>48</v>
       </c>
       <c r="AM2" t="n">
         <v>1000</v>
       </c>
       <c r="AN2" t="n">
-        <v>1000</v>
+        <v>970</v>
       </c>
       <c r="AO2" t="n">
         <v>1000</v>
       </c>
       <c r="AP2" t="n">
-        <v>1.01</v>
+        <v>3.7</v>
       </c>
       <c r="AQ2" t="n">
-        <v>1.01</v>
+        <v>3.95</v>
       </c>
       <c r="AR2" t="n">
-        <v>1.01</v>
+        <v>4.3</v>
       </c>
       <c r="AS2" t="n">
-        <v>1.01</v>
+        <v>4.5</v>
       </c>
       <c r="AT2" t="n">
-        <v>1.01</v>
+        <v>2.98</v>
       </c>
       <c r="AU2" t="n">
-        <v>1.01</v>
+        <v>3.35</v>
       </c>
       <c r="AV2" t="n">
-        <v>1.01</v>
+        <v>4</v>
       </c>
       <c r="AW2" t="n">
-        <v>1.01</v>
+        <v>4.5</v>
       </c>
       <c r="AX2" t="n">
-        <v>1.01</v>
+        <v>3.25</v>
       </c>
       <c r="AY2" t="n">
-        <v>1.01</v>
+        <v>3.35</v>
       </c>
       <c r="AZ2" t="n">
-        <v>1.01</v>
+        <v>4</v>
       </c>
       <c r="BA2" t="n">
-        <v>1.01</v>
+        <v>4.4</v>
       </c>
       <c r="BB2" t="n">
-        <v>1.01</v>
+        <v>3.65</v>
       </c>
       <c r="BC2" t="n">
-        <v>1.01</v>
+        <v>3.8</v>
       </c>
       <c r="BD2" t="n">
-        <v>1.01</v>
+        <v>4.2</v>
       </c>
       <c r="BE2" t="n">
-        <v>1.01</v>
+        <v>4.5</v>
       </c>
       <c r="BF2" t="n">
-        <v>1.01</v>
+        <v>3.3</v>
       </c>
       <c r="BG2" t="n">
-        <v>1.01</v>
+        <v>4.5</v>
       </c>
       <c r="BH2" t="n">
         <v>1000</v>
@@ -1080,7 +1080,7 @@
       </c>
       <c r="CB2" t="inlineStr">
         <is>
-          <t>2026-06-11 09:18:50</t>
+          <t>2026-06-11 11:32:36</t>
         </is>
       </c>
     </row>
@@ -1138,19 +1138,19 @@
         <v>1.1</v>
       </c>
       <c r="O3" t="n">
-        <v>1.21</v>
+        <v>1.22</v>
       </c>
       <c r="P3" t="n">
         <v>1.32</v>
       </c>
       <c r="Q3" t="n">
-        <v>1.23</v>
+        <v>1.22</v>
       </c>
       <c r="R3" t="n">
         <v>1.18</v>
       </c>
       <c r="S3" t="n">
-        <v>1.23</v>
+        <v>1.22</v>
       </c>
       <c r="T3" t="n">
         <v>1.11</v>
@@ -1334,7 +1334,7 @@
       </c>
       <c r="CB3" t="inlineStr">
         <is>
-          <t>2026-06-11 09:18:50</t>
+          <t>2026-06-11 11:32:36</t>
         </is>
       </c>
     </row>
@@ -1365,19 +1365,19 @@
         </is>
       </c>
       <c r="F4" t="n">
+        <v>2.26</v>
+      </c>
+      <c r="G4" t="n">
+        <v>3.45</v>
+      </c>
+      <c r="H4" t="n">
         <v>2.66</v>
       </c>
-      <c r="G4" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="H4" t="n">
-        <v>2.8</v>
-      </c>
       <c r="I4" t="n">
-        <v>3.5</v>
+        <v>3.65</v>
       </c>
       <c r="J4" t="n">
-        <v>2.56</v>
+        <v>2.54</v>
       </c>
       <c r="K4" t="n">
         <v>3.55</v>
@@ -1386,10 +1386,10 @@
         <v>1.01</v>
       </c>
       <c r="M4" t="n">
-        <v>1.14</v>
+        <v>1.01</v>
       </c>
       <c r="N4" t="n">
-        <v>2.38</v>
+        <v>2.42</v>
       </c>
       <c r="O4" t="n">
         <v>1.58</v>
@@ -1404,19 +1404,19 @@
         <v>1.18</v>
       </c>
       <c r="S4" t="n">
-        <v>4.7</v>
+        <v>2.5</v>
       </c>
       <c r="T4" t="n">
-        <v>2.14</v>
+        <v>1.7</v>
       </c>
       <c r="U4" t="n">
-        <v>1.68</v>
+        <v>1.41</v>
       </c>
       <c r="V4" t="n">
         <v>1.41</v>
       </c>
       <c r="W4" t="n">
-        <v>1.46</v>
+        <v>1.45</v>
       </c>
       <c r="X4" t="n">
         <v>970</v>
@@ -1473,64 +1473,64 @@
         <v>1000</v>
       </c>
       <c r="AP4" t="n">
-        <v>3.7</v>
+        <v>3.65</v>
       </c>
       <c r="AQ4" t="n">
-        <v>3.75</v>
+        <v>3.65</v>
       </c>
       <c r="AR4" t="n">
-        <v>2.34</v>
+        <v>2.3</v>
       </c>
       <c r="AS4" t="n">
-        <v>2.34</v>
+        <v>2.44</v>
       </c>
       <c r="AT4" t="n">
         <v>3.65</v>
       </c>
       <c r="AU4" t="n">
-        <v>3.45</v>
+        <v>3.4</v>
       </c>
       <c r="AV4" t="n">
-        <v>2.26</v>
+        <v>2.24</v>
       </c>
       <c r="AW4" t="n">
-        <v>2.32</v>
+        <v>2.42</v>
       </c>
       <c r="AX4" t="n">
         <v>2.28</v>
       </c>
       <c r="AY4" t="n">
-        <v>2.22</v>
+        <v>2.2</v>
       </c>
       <c r="AZ4" t="n">
-        <v>2.38</v>
+        <v>2.36</v>
       </c>
       <c r="BA4" t="n">
-        <v>2.36</v>
+        <v>2.46</v>
       </c>
       <c r="BB4" t="n">
-        <v>2.32</v>
+        <v>2.42</v>
       </c>
       <c r="BC4" t="n">
-        <v>5.9</v>
+        <v>3.4</v>
       </c>
       <c r="BD4" t="n">
-        <v>2.34</v>
+        <v>2.46</v>
       </c>
       <c r="BE4" t="n">
-        <v>2.38</v>
+        <v>2.5</v>
       </c>
       <c r="BF4" t="n">
-        <v>2.34</v>
+        <v>2.44</v>
       </c>
       <c r="BG4" t="n">
-        <v>2.34</v>
+        <v>2.46</v>
       </c>
       <c r="BH4" t="n">
         <v>2.94</v>
       </c>
       <c r="BI4" t="n">
-        <v>1.04</v>
+        <v>2.04</v>
       </c>
       <c r="BJ4" t="n">
         <v>1000</v>
@@ -1588,7 +1588,7 @@
       </c>
       <c r="CB4" t="inlineStr">
         <is>
-          <t>2026-06-11 09:18:50</t>
+          <t>2026-06-11 11:32:36</t>
         </is>
       </c>
     </row>
@@ -1619,13 +1619,13 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>2.18</v>
+        <v>2.16</v>
       </c>
       <c r="G5" t="n">
-        <v>2.42</v>
+        <v>2.4</v>
       </c>
       <c r="H5" t="n">
-        <v>3.7</v>
+        <v>3.9</v>
       </c>
       <c r="I5" t="n">
         <v>4.5</v>
@@ -1634,10 +1634,10 @@
         <v>2.96</v>
       </c>
       <c r="K5" t="n">
-        <v>3.3</v>
+        <v>3.25</v>
       </c>
       <c r="L5" t="n">
-        <v>1.01</v>
+        <v>1.49</v>
       </c>
       <c r="M5" t="n">
         <v>1.13</v>
@@ -1667,10 +1667,10 @@
         <v>1.71</v>
       </c>
       <c r="V5" t="n">
-        <v>1.29</v>
+        <v>1.28</v>
       </c>
       <c r="W5" t="n">
-        <v>1.71</v>
+        <v>1.72</v>
       </c>
       <c r="X5" t="n">
         <v>9.4</v>
@@ -1685,16 +1685,16 @@
         <v>130</v>
       </c>
       <c r="AB5" t="n">
-        <v>7</v>
+        <v>7.2</v>
       </c>
       <c r="AC5" t="n">
-        <v>7.6</v>
+        <v>7.4</v>
       </c>
       <c r="AD5" t="n">
         <v>22</v>
       </c>
       <c r="AE5" t="n">
-        <v>90</v>
+        <v>95</v>
       </c>
       <c r="AF5" t="n">
         <v>14.5</v>
@@ -1709,19 +1709,19 @@
         <v>120</v>
       </c>
       <c r="AJ5" t="n">
-        <v>34</v>
+        <v>40</v>
       </c>
       <c r="AK5" t="n">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="AL5" t="n">
-        <v>80</v>
+        <v>85</v>
       </c>
       <c r="AM5" t="n">
         <v>250</v>
       </c>
       <c r="AN5" t="n">
-        <v>36</v>
+        <v>44</v>
       </c>
       <c r="AO5" t="n">
         <v>140</v>
@@ -1730,7 +1730,7 @@
         <v>3.9</v>
       </c>
       <c r="AQ5" t="n">
-        <v>4.3</v>
+        <v>4.4</v>
       </c>
       <c r="AR5" t="n">
         <v>5.5</v>
@@ -1739,10 +1739,10 @@
         <v>6.4</v>
       </c>
       <c r="AT5" t="n">
-        <v>3.45</v>
+        <v>5.5</v>
       </c>
       <c r="AU5" t="n">
-        <v>3.55</v>
+        <v>3.5</v>
       </c>
       <c r="AV5" t="n">
         <v>5.1</v>
@@ -1757,25 +1757,25 @@
         <v>4.5</v>
       </c>
       <c r="AZ5" t="n">
-        <v>5.4</v>
+        <v>5.5</v>
       </c>
       <c r="BA5" t="n">
-        <v>6.2</v>
+        <v>6.4</v>
       </c>
       <c r="BB5" t="n">
         <v>5.6</v>
       </c>
       <c r="BC5" t="n">
-        <v>5.6</v>
+        <v>5.7</v>
       </c>
       <c r="BD5" t="n">
-        <v>6.2</v>
+        <v>6</v>
       </c>
       <c r="BE5" t="n">
-        <v>6.4</v>
+        <v>6.6</v>
       </c>
       <c r="BF5" t="n">
-        <v>5.6</v>
+        <v>5.7</v>
       </c>
       <c r="BG5" t="n">
         <v>6.4</v>
@@ -1784,7 +1784,7 @@
         <v>1000</v>
       </c>
       <c r="BI5" t="n">
-        <v>2.12</v>
+        <v>1.04</v>
       </c>
       <c r="BJ5" t="n">
         <v>1000</v>
@@ -1842,7 +1842,7 @@
       </c>
       <c r="CB5" t="inlineStr">
         <is>
-          <t>2026-06-11 09:18:50</t>
+          <t>2026-06-11 11:32:36</t>
         </is>
       </c>
     </row>
@@ -1873,166 +1873,166 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>2.96</v>
+        <v>3.35</v>
       </c>
       <c r="G6" t="n">
-        <v>4.1</v>
+        <v>3.75</v>
       </c>
       <c r="H6" t="n">
-        <v>2</v>
+        <v>2.18</v>
       </c>
       <c r="I6" t="n">
-        <v>2.44</v>
+        <v>2.36</v>
       </c>
       <c r="J6" t="n">
-        <v>3.25</v>
+        <v>3.45</v>
       </c>
       <c r="K6" t="n">
-        <v>6.2</v>
+        <v>3.75</v>
       </c>
       <c r="L6" t="n">
         <v>1.3</v>
       </c>
       <c r="M6" t="n">
-        <v>1.01</v>
+        <v>1.06</v>
       </c>
       <c r="N6" t="n">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="O6" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="P6" t="n">
-        <v>1.91</v>
+        <v>1.96</v>
       </c>
       <c r="Q6" t="n">
-        <v>1.84</v>
+        <v>1.89</v>
       </c>
       <c r="R6" t="n">
-        <v>1.32</v>
+        <v>1.37</v>
       </c>
       <c r="S6" t="n">
-        <v>2.74</v>
+        <v>3.25</v>
       </c>
       <c r="T6" t="n">
-        <v>1.11</v>
+        <v>1.73</v>
       </c>
       <c r="U6" t="n">
-        <v>1.11</v>
+        <v>2.16</v>
       </c>
       <c r="V6" t="n">
-        <v>1.7</v>
+        <v>1.74</v>
       </c>
       <c r="W6" t="n">
-        <v>1.32</v>
+        <v>1.36</v>
       </c>
       <c r="X6" t="n">
-        <v>1000</v>
+        <v>18.5</v>
       </c>
       <c r="Y6" t="n">
-        <v>1000</v>
+        <v>12.5</v>
       </c>
       <c r="Z6" t="n">
-        <v>1000</v>
+        <v>15</v>
       </c>
       <c r="AA6" t="n">
-        <v>1000</v>
+        <v>30</v>
       </c>
       <c r="AB6" t="n">
-        <v>1000</v>
+        <v>17</v>
       </c>
       <c r="AC6" t="n">
-        <v>1000</v>
+        <v>10</v>
       </c>
       <c r="AD6" t="n">
-        <v>1000</v>
+        <v>13.5</v>
       </c>
       <c r="AE6" t="n">
-        <v>1000</v>
+        <v>29</v>
       </c>
       <c r="AF6" t="n">
-        <v>1000</v>
+        <v>32</v>
       </c>
       <c r="AG6" t="n">
-        <v>1000</v>
+        <v>15</v>
       </c>
       <c r="AH6" t="n">
-        <v>1000</v>
+        <v>17.5</v>
       </c>
       <c r="AI6" t="n">
-        <v>1000</v>
+        <v>44</v>
       </c>
       <c r="AJ6" t="n">
-        <v>1000</v>
+        <v>80</v>
       </c>
       <c r="AK6" t="n">
-        <v>1000</v>
+        <v>50</v>
       </c>
       <c r="AL6" t="n">
-        <v>1000</v>
+        <v>60</v>
       </c>
       <c r="AM6" t="n">
-        <v>1000</v>
+        <v>110</v>
       </c>
       <c r="AN6" t="n">
-        <v>1000</v>
+        <v>40</v>
       </c>
       <c r="AO6" t="n">
-        <v>1000</v>
+        <v>17.5</v>
       </c>
       <c r="AP6" t="n">
-        <v>1.01</v>
+        <v>11</v>
       </c>
       <c r="AQ6" t="n">
-        <v>1.01</v>
+        <v>9</v>
       </c>
       <c r="AR6" t="n">
-        <v>1.01</v>
+        <v>13</v>
       </c>
       <c r="AS6" t="n">
-        <v>1.01</v>
+        <v>21</v>
       </c>
       <c r="AT6" t="n">
-        <v>1.01</v>
+        <v>10</v>
       </c>
       <c r="AU6" t="n">
-        <v>1.01</v>
+        <v>6.2</v>
       </c>
       <c r="AV6" t="n">
-        <v>1.01</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AW6" t="n">
-        <v>1.01</v>
+        <v>17</v>
       </c>
       <c r="AX6" t="n">
-        <v>1.01</v>
+        <v>18</v>
       </c>
       <c r="AY6" t="n">
-        <v>1.01</v>
+        <v>13</v>
       </c>
       <c r="AZ6" t="n">
-        <v>1.01</v>
+        <v>12.5</v>
       </c>
       <c r="BA6" t="n">
-        <v>1.01</v>
+        <v>4.9</v>
       </c>
       <c r="BB6" t="n">
-        <v>1.01</v>
+        <v>5.1</v>
       </c>
       <c r="BC6" t="n">
-        <v>1.01</v>
+        <v>4.9</v>
       </c>
       <c r="BD6" t="n">
-        <v>1.01</v>
+        <v>32</v>
       </c>
       <c r="BE6" t="n">
-        <v>1.01</v>
+        <v>5.2</v>
       </c>
       <c r="BF6" t="n">
-        <v>1.01</v>
+        <v>4.8</v>
       </c>
       <c r="BG6" t="n">
-        <v>1.01</v>
+        <v>12.5</v>
       </c>
       <c r="BH6" t="n">
         <v>1000</v>
@@ -2096,7 +2096,7 @@
       </c>
       <c r="CB6" t="inlineStr">
         <is>
-          <t>2026-06-11 09:18:50</t>
+          <t>2026-06-11 11:32:36</t>
         </is>
       </c>
     </row>
@@ -2127,19 +2127,19 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>1.06</v>
+        <v>1.08</v>
       </c>
       <c r="G7" t="n">
         <v>1000</v>
       </c>
       <c r="H7" t="n">
-        <v>1.06</v>
+        <v>1.09</v>
       </c>
       <c r="I7" t="n">
         <v>1000</v>
       </c>
       <c r="J7" t="n">
-        <v>1.04</v>
+        <v>1.08</v>
       </c>
       <c r="K7" t="n">
         <v>1000</v>
@@ -2151,7 +2151,7 @@
         <v>1.01</v>
       </c>
       <c r="N7" t="n">
-        <v>1.43</v>
+        <v>1.44</v>
       </c>
       <c r="O7" t="n">
         <v>1.22</v>
@@ -2166,7 +2166,7 @@
         <v>1.18</v>
       </c>
       <c r="S7" t="n">
-        <v>1.22</v>
+        <v>1.21</v>
       </c>
       <c r="T7" t="n">
         <v>1.01</v>
@@ -2350,7 +2350,7 @@
       </c>
       <c r="CB7" t="inlineStr">
         <is>
-          <t>2026-06-11 09:18:50</t>
+          <t>2026-06-11 11:32:36</t>
         </is>
       </c>
     </row>
@@ -2381,46 +2381,46 @@
         </is>
       </c>
       <c r="F8" t="n">
-        <v>1.09</v>
+        <v>1.59</v>
       </c>
       <c r="G8" t="n">
-        <v>1000</v>
+        <v>1.77</v>
       </c>
       <c r="H8" t="n">
-        <v>1.09</v>
+        <v>2.9</v>
       </c>
       <c r="I8" t="n">
-        <v>1000</v>
+        <v>11.5</v>
       </c>
       <c r="J8" t="n">
-        <v>1.46</v>
+        <v>3.75</v>
       </c>
       <c r="K8" t="n">
         <v>950</v>
       </c>
       <c r="L8" t="n">
-        <v>1.01</v>
+        <v>1.31</v>
       </c>
       <c r="M8" t="n">
         <v>1.01</v>
       </c>
       <c r="N8" t="n">
-        <v>1.25</v>
+        <v>3.2</v>
       </c>
       <c r="O8" t="n">
         <v>1.28</v>
       </c>
       <c r="P8" t="n">
-        <v>1.24</v>
+        <v>1.89</v>
       </c>
       <c r="Q8" t="n">
-        <v>1.28</v>
+        <v>1.87</v>
       </c>
       <c r="R8" t="n">
-        <v>1.18</v>
+        <v>1.29</v>
       </c>
       <c r="S8" t="n">
-        <v>1.28</v>
+        <v>2.9</v>
       </c>
       <c r="T8" t="n">
         <v>1.11</v>
@@ -2429,10 +2429,10 @@
         <v>1.11</v>
       </c>
       <c r="V8" t="n">
-        <v>1.02</v>
+        <v>1.11</v>
       </c>
       <c r="W8" t="n">
-        <v>1.05</v>
+        <v>2.28</v>
       </c>
       <c r="X8" t="n">
         <v>1000</v>
@@ -2604,7 +2604,7 @@
       </c>
       <c r="CB8" t="inlineStr">
         <is>
-          <t>2026-06-11 09:18:50</t>
+          <t>2026-06-11 11:32:36</t>
         </is>
       </c>
     </row>
@@ -2635,112 +2635,112 @@
         </is>
       </c>
       <c r="F9" t="n">
-        <v>1.06</v>
+        <v>4</v>
       </c>
       <c r="G9" t="n">
-        <v>1000</v>
+        <v>5.4</v>
       </c>
       <c r="H9" t="n">
-        <v>1.06</v>
+        <v>1.68</v>
       </c>
       <c r="I9" t="n">
-        <v>1000</v>
+        <v>1.85</v>
       </c>
       <c r="J9" t="n">
-        <v>1.04</v>
+        <v>3.95</v>
       </c>
       <c r="K9" t="n">
-        <v>1000</v>
+        <v>5</v>
       </c>
       <c r="L9" t="n">
-        <v>1.01</v>
+        <v>1.24</v>
       </c>
       <c r="M9" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="N9" t="n">
-        <v>1.25</v>
+        <v>1.01</v>
       </c>
       <c r="O9" t="n">
-        <v>1.01</v>
+        <v>1.18</v>
       </c>
       <c r="P9" t="n">
-        <v>1.25</v>
+        <v>2.44</v>
       </c>
       <c r="Q9" t="n">
-        <v>1.01</v>
+        <v>1.53</v>
       </c>
       <c r="R9" t="n">
-        <v>1.24</v>
+        <v>1.6</v>
       </c>
       <c r="S9" t="n">
-        <v>1.01</v>
+        <v>2.2</v>
       </c>
       <c r="T9" t="n">
-        <v>1.01</v>
+        <v>1.58</v>
       </c>
       <c r="U9" t="n">
-        <v>1.01</v>
+        <v>2.38</v>
       </c>
       <c r="V9" t="n">
-        <v>1.02</v>
+        <v>2.16</v>
       </c>
       <c r="W9" t="n">
-        <v>1.02</v>
+        <v>1.23</v>
       </c>
       <c r="X9" t="n">
-        <v>1000</v>
+        <v>30</v>
       </c>
       <c r="Y9" t="n">
-        <v>1000</v>
+        <v>970</v>
       </c>
       <c r="Z9" t="n">
-        <v>1000</v>
+        <v>970</v>
       </c>
       <c r="AA9" t="n">
-        <v>1000</v>
+        <v>22</v>
       </c>
       <c r="AB9" t="n">
-        <v>1000</v>
+        <v>28</v>
       </c>
       <c r="AC9" t="n">
-        <v>1000</v>
+        <v>970</v>
       </c>
       <c r="AD9" t="n">
-        <v>1000</v>
+        <v>970</v>
       </c>
       <c r="AE9" t="n">
-        <v>1000</v>
+        <v>970</v>
       </c>
       <c r="AF9" t="n">
-        <v>1000</v>
+        <v>48</v>
       </c>
       <c r="AG9" t="n">
-        <v>1000</v>
+        <v>23</v>
       </c>
       <c r="AH9" t="n">
-        <v>1000</v>
+        <v>970</v>
       </c>
       <c r="AI9" t="n">
-        <v>1000</v>
+        <v>32</v>
       </c>
       <c r="AJ9" t="n">
-        <v>1000</v>
+        <v>110</v>
       </c>
       <c r="AK9" t="n">
-        <v>1000</v>
+        <v>60</v>
       </c>
       <c r="AL9" t="n">
-        <v>1000</v>
+        <v>55</v>
       </c>
       <c r="AM9" t="n">
-        <v>1000</v>
+        <v>80</v>
       </c>
       <c r="AN9" t="n">
-        <v>1000</v>
+        <v>46</v>
       </c>
       <c r="AO9" t="n">
-        <v>1000</v>
+        <v>8.4</v>
       </c>
       <c r="AP9" t="n">
         <v>1.01</v>
@@ -2797,55 +2797,55 @@
         <v>1.01</v>
       </c>
       <c r="BH9" t="n">
-        <v>1000</v>
+        <v>5.1</v>
       </c>
       <c r="BI9" t="n">
         <v>1.01</v>
       </c>
       <c r="BJ9" t="n">
-        <v>1000</v>
+        <v>10.5</v>
       </c>
       <c r="BK9" t="n">
         <v>1.01</v>
       </c>
       <c r="BL9" t="n">
-        <v>1000</v>
+        <v>95</v>
       </c>
       <c r="BM9" t="n">
         <v>1.01</v>
       </c>
       <c r="BN9" t="n">
-        <v>1000</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BO9" t="n">
         <v>1.01</v>
       </c>
       <c r="BP9" t="n">
-        <v>1000</v>
+        <v>38</v>
       </c>
       <c r="BQ9" t="n">
         <v>1.01</v>
       </c>
       <c r="BR9" t="n">
-        <v>1000</v>
+        <v>42</v>
       </c>
       <c r="BS9" t="n">
         <v>1.01</v>
       </c>
       <c r="BT9" t="n">
-        <v>1000</v>
+        <v>5.5</v>
       </c>
       <c r="BU9" t="n">
         <v>1.01</v>
       </c>
       <c r="BV9" t="n">
-        <v>1000</v>
+        <v>12.5</v>
       </c>
       <c r="BW9" t="n">
         <v>1.01</v>
       </c>
       <c r="BX9" t="n">
-        <v>1000</v>
+        <v>24</v>
       </c>
       <c r="BY9" t="n">
         <v>1.01</v>
@@ -2858,7 +2858,7 @@
       </c>
       <c r="CB9" t="inlineStr">
         <is>
-          <t>2026-06-11 09:18:50</t>
+          <t>2026-06-11 11:32:36</t>
         </is>
       </c>
     </row>
@@ -2889,166 +2889,166 @@
         </is>
       </c>
       <c r="F10" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="G10" t="n">
+        <v>5</v>
+      </c>
+      <c r="H10" t="n">
+        <v>1.87</v>
+      </c>
+      <c r="I10" t="n">
+        <v>2.04</v>
+      </c>
+      <c r="J10" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="K10" t="n">
+        <v>3.95</v>
+      </c>
+      <c r="L10" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="M10" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="N10" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="O10" t="n">
+        <v>1.34</v>
+      </c>
+      <c r="P10" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="Q10" t="n">
         <v>2</v>
       </c>
-      <c r="G10" t="n">
-        <v>1000</v>
-      </c>
-      <c r="H10" t="n">
-        <v>1.23</v>
-      </c>
-      <c r="I10" t="n">
-        <v>1000</v>
-      </c>
-      <c r="J10" t="n">
-        <v>1.52</v>
-      </c>
-      <c r="K10" t="n">
-        <v>100</v>
-      </c>
-      <c r="L10" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="M10" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="N10" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="O10" t="n">
-        <v>1.32</v>
-      </c>
-      <c r="P10" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="Q10" t="n">
-        <v>1.32</v>
-      </c>
       <c r="R10" t="n">
-        <v>1.18</v>
+        <v>1.31</v>
       </c>
       <c r="S10" t="n">
-        <v>1.06</v>
+        <v>3.2</v>
       </c>
       <c r="T10" t="n">
-        <v>1.11</v>
+        <v>1.85</v>
       </c>
       <c r="U10" t="n">
-        <v>1.11</v>
+        <v>1.96</v>
       </c>
       <c r="V10" t="n">
-        <v>1.02</v>
+        <v>1.96</v>
       </c>
       <c r="W10" t="n">
-        <v>1.02</v>
+        <v>1.25</v>
       </c>
       <c r="X10" t="n">
-        <v>1000</v>
+        <v>16</v>
       </c>
       <c r="Y10" t="n">
-        <v>1000</v>
+        <v>10.5</v>
       </c>
       <c r="Z10" t="n">
-        <v>1000</v>
+        <v>14.5</v>
       </c>
       <c r="AA10" t="n">
-        <v>1000</v>
+        <v>28</v>
       </c>
       <c r="AB10" t="n">
-        <v>1000</v>
+        <v>18.5</v>
       </c>
       <c r="AC10" t="n">
-        <v>1000</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AD10" t="n">
-        <v>1000</v>
+        <v>12.5</v>
       </c>
       <c r="AE10" t="n">
-        <v>1000</v>
+        <v>27</v>
       </c>
       <c r="AF10" t="n">
-        <v>1000</v>
+        <v>42</v>
       </c>
       <c r="AG10" t="n">
-        <v>1000</v>
+        <v>23</v>
       </c>
       <c r="AH10" t="n">
-        <v>1000</v>
+        <v>24</v>
       </c>
       <c r="AI10" t="n">
-        <v>1000</v>
+        <v>48</v>
       </c>
       <c r="AJ10" t="n">
-        <v>1000</v>
+        <v>130</v>
       </c>
       <c r="AK10" t="n">
-        <v>1000</v>
+        <v>80</v>
       </c>
       <c r="AL10" t="n">
-        <v>1000</v>
+        <v>85</v>
       </c>
       <c r="AM10" t="n">
-        <v>1000</v>
+        <v>150</v>
       </c>
       <c r="AN10" t="n">
-        <v>1000</v>
+        <v>95</v>
       </c>
       <c r="AO10" t="n">
-        <v>1000</v>
+        <v>18.5</v>
       </c>
       <c r="AP10" t="n">
-        <v>1.01</v>
+        <v>3.4</v>
       </c>
       <c r="AQ10" t="n">
-        <v>1.01</v>
+        <v>3.1</v>
       </c>
       <c r="AR10" t="n">
-        <v>1.01</v>
+        <v>3.35</v>
       </c>
       <c r="AS10" t="n">
-        <v>1.01</v>
+        <v>3.75</v>
       </c>
       <c r="AT10" t="n">
-        <v>1.01</v>
+        <v>3.5</v>
       </c>
       <c r="AU10" t="n">
-        <v>1.01</v>
+        <v>3.05</v>
       </c>
       <c r="AV10" t="n">
-        <v>1.01</v>
+        <v>3.2</v>
       </c>
       <c r="AW10" t="n">
-        <v>1.01</v>
+        <v>3.75</v>
       </c>
       <c r="AX10" t="n">
-        <v>1.01</v>
+        <v>3.9</v>
       </c>
       <c r="AY10" t="n">
-        <v>1.01</v>
+        <v>3.65</v>
       </c>
       <c r="AZ10" t="n">
-        <v>1.01</v>
+        <v>3.65</v>
       </c>
       <c r="BA10" t="n">
-        <v>1.01</v>
+        <v>3.95</v>
       </c>
       <c r="BB10" t="n">
-        <v>1.01</v>
+        <v>4.2</v>
       </c>
       <c r="BC10" t="n">
-        <v>1.01</v>
+        <v>4.1</v>
       </c>
       <c r="BD10" t="n">
-        <v>1.01</v>
+        <v>4.1</v>
       </c>
       <c r="BE10" t="n">
-        <v>1.01</v>
+        <v>4.2</v>
       </c>
       <c r="BF10" t="n">
-        <v>1.01</v>
+        <v>4.1</v>
       </c>
       <c r="BG10" t="n">
-        <v>1.01</v>
+        <v>3.5</v>
       </c>
       <c r="BH10" t="n">
         <v>1000</v>
@@ -3112,7 +3112,7 @@
       </c>
       <c r="CB10" t="inlineStr">
         <is>
-          <t>2026-06-11 09:18:50</t>
+          <t>2026-06-11 11:32:36</t>
         </is>
       </c>
     </row>
@@ -3143,58 +3143,58 @@
         </is>
       </c>
       <c r="F11" t="n">
-        <v>1.12</v>
+        <v>1.14</v>
       </c>
       <c r="G11" t="n">
-        <v>1.16</v>
+        <v>1.18</v>
       </c>
       <c r="H11" t="n">
-        <v>1.09</v>
+        <v>21</v>
       </c>
       <c r="I11" t="n">
-        <v>55</v>
+        <v>32</v>
       </c>
       <c r="J11" t="n">
-        <v>10.5</v>
+        <v>9.4</v>
       </c>
       <c r="K11" t="n">
-        <v>32</v>
+        <v>11.5</v>
       </c>
       <c r="L11" t="n">
         <v>1.19</v>
       </c>
       <c r="M11" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="N11" t="n">
-        <v>3.45</v>
+        <v>7</v>
       </c>
       <c r="O11" t="n">
         <v>1.12</v>
       </c>
       <c r="P11" t="n">
-        <v>2.92</v>
+        <v>3.1</v>
       </c>
       <c r="Q11" t="n">
         <v>1.37</v>
       </c>
       <c r="R11" t="n">
-        <v>1.88</v>
+        <v>1.85</v>
       </c>
       <c r="S11" t="n">
         <v>1.94</v>
       </c>
       <c r="T11" t="n">
-        <v>2.4</v>
+        <v>2.3</v>
       </c>
       <c r="U11" t="n">
-        <v>1.57</v>
+        <v>1.6</v>
       </c>
       <c r="V11" t="n">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="W11" t="n">
-        <v>7.2</v>
+        <v>6.6</v>
       </c>
       <c r="X11" t="n">
         <v>950</v>
@@ -3215,16 +3215,16 @@
         <v>950</v>
       </c>
       <c r="AD11" t="n">
-        <v>1000</v>
+        <v>950</v>
       </c>
       <c r="AE11" t="n">
         <v>1000</v>
       </c>
       <c r="AF11" t="n">
-        <v>970</v>
+        <v>10</v>
       </c>
       <c r="AG11" t="n">
-        <v>970</v>
+        <v>17</v>
       </c>
       <c r="AH11" t="n">
         <v>950</v>
@@ -3233,140 +3233,140 @@
         <v>1000</v>
       </c>
       <c r="AJ11" t="n">
-        <v>970</v>
+        <v>9.6</v>
       </c>
       <c r="AK11" t="n">
-        <v>970</v>
+        <v>17.5</v>
       </c>
       <c r="AL11" t="n">
-        <v>65</v>
+        <v>60</v>
       </c>
       <c r="AM11" t="n">
         <v>1000</v>
       </c>
       <c r="AN11" t="n">
-        <v>2.88</v>
+        <v>3.2</v>
       </c>
       <c r="AO11" t="n">
         <v>1000</v>
       </c>
       <c r="AP11" t="n">
+        <v>5</v>
+      </c>
+      <c r="AQ11" t="n">
+        <v>5.3</v>
+      </c>
+      <c r="AR11" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="AS11" t="n">
+        <v>5.6</v>
+      </c>
+      <c r="AT11" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="AU11" t="n">
+        <v>18</v>
+      </c>
+      <c r="AV11" t="n">
+        <v>5.3</v>
+      </c>
+      <c r="AW11" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="AX11" t="n">
+        <v>7</v>
+      </c>
+      <c r="AY11" t="n">
+        <v>11</v>
+      </c>
+      <c r="AZ11" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="BA11" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="BB11" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="BC11" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="BD11" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="BE11" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="BF11" t="n">
+        <v>2.48</v>
+      </c>
+      <c r="BG11" t="n">
+        <v>5.6</v>
+      </c>
+      <c r="BH11" t="n">
+        <v>5.7</v>
+      </c>
+      <c r="BI11" t="n">
         <v>4.4</v>
       </c>
-      <c r="AQ11" t="n">
-        <v>1.79</v>
-      </c>
-      <c r="AR11" t="n">
-        <v>1.81</v>
-      </c>
-      <c r="AS11" t="n">
-        <v>1.82</v>
-      </c>
-      <c r="AT11" t="n">
-        <v>4.9</v>
-      </c>
-      <c r="AU11" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="AV11" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="AW11" t="n">
-        <v>1.82</v>
-      </c>
-      <c r="AX11" t="n">
-        <v>4</v>
-      </c>
-      <c r="AY11" t="n">
-        <v>4.8</v>
-      </c>
-      <c r="AZ11" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="BA11" t="n">
-        <v>1.82</v>
-      </c>
-      <c r="BB11" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="BC11" t="n">
-        <v>3.85</v>
-      </c>
-      <c r="BD11" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="BE11" t="n">
-        <v>1.81</v>
-      </c>
-      <c r="BF11" t="n">
-        <v>2.36</v>
-      </c>
-      <c r="BG11" t="n">
-        <v>1.82</v>
-      </c>
-      <c r="BH11" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BI11" t="n">
-        <v>3.65</v>
-      </c>
       <c r="BJ11" t="n">
         <v>1000</v>
       </c>
       <c r="BK11" t="n">
-        <v>1.7</v>
+        <v>6.6</v>
       </c>
       <c r="BL11" t="n">
         <v>1000</v>
       </c>
       <c r="BM11" t="n">
-        <v>1.31</v>
+        <v>10</v>
       </c>
       <c r="BN11" t="n">
         <v>3.9</v>
       </c>
       <c r="BO11" t="n">
-        <v>2.8</v>
+        <v>3.1</v>
       </c>
       <c r="BP11" t="n">
-        <v>1000</v>
+        <v>5.9</v>
       </c>
       <c r="BQ11" t="n">
-        <v>3.65</v>
+        <v>4.5</v>
       </c>
       <c r="BR11" t="n">
         <v>1000</v>
       </c>
       <c r="BS11" t="n">
-        <v>1.25</v>
+        <v>7.4</v>
       </c>
       <c r="BT11" t="n">
         <v>1000</v>
       </c>
       <c r="BU11" t="n">
-        <v>1.26</v>
+        <v>7.4</v>
       </c>
       <c r="BV11" t="n">
         <v>1000</v>
       </c>
       <c r="BW11" t="n">
-        <v>1.31</v>
+        <v>10</v>
       </c>
       <c r="BX11" t="n">
         <v>1000</v>
       </c>
       <c r="BY11" t="n">
-        <v>1.31</v>
+        <v>10</v>
       </c>
       <c r="BZ11" t="n">
-        <v>1000</v>
+        <v>6.8</v>
       </c>
       <c r="CA11" t="n">
-        <v>4</v>
+        <v>5.3</v>
       </c>
       <c r="CB11" t="inlineStr">
         <is>
-          <t>2026-06-11 09:18:50</t>
+          <t>2026-06-11 11:32:36</t>
         </is>
       </c>
     </row>
@@ -3400,16 +3400,16 @@
         <v>2.38</v>
       </c>
       <c r="G12" t="n">
-        <v>2.7</v>
+        <v>2.72</v>
       </c>
       <c r="H12" t="n">
-        <v>3.2</v>
+        <v>3.15</v>
       </c>
       <c r="I12" t="n">
         <v>4</v>
       </c>
       <c r="J12" t="n">
-        <v>2.8</v>
+        <v>2.84</v>
       </c>
       <c r="K12" t="n">
         <v>3.25</v>
@@ -3418,31 +3418,31 @@
         <v>1.51</v>
       </c>
       <c r="M12" t="n">
-        <v>1.13</v>
+        <v>1.11</v>
       </c>
       <c r="N12" t="n">
-        <v>2.38</v>
+        <v>2.28</v>
       </c>
       <c r="O12" t="n">
-        <v>1.57</v>
+        <v>1.58</v>
       </c>
       <c r="P12" t="n">
         <v>1.46</v>
       </c>
       <c r="Q12" t="n">
-        <v>2.66</v>
+        <v>2.72</v>
       </c>
       <c r="R12" t="n">
         <v>1.18</v>
       </c>
       <c r="S12" t="n">
-        <v>4.5</v>
+        <v>4.9</v>
       </c>
       <c r="T12" t="n">
         <v>2.16</v>
       </c>
       <c r="U12" t="n">
-        <v>1.72</v>
+        <v>1.7</v>
       </c>
       <c r="V12" t="n">
         <v>1.33</v>
@@ -3493,7 +3493,7 @@
         <v>48</v>
       </c>
       <c r="AL12" t="n">
-        <v>85</v>
+        <v>90</v>
       </c>
       <c r="AM12" t="n">
         <v>260</v>
@@ -3505,64 +3505,64 @@
         <v>120</v>
       </c>
       <c r="AP12" t="n">
-        <v>1.01</v>
+        <v>3</v>
       </c>
       <c r="AQ12" t="n">
-        <v>1.01</v>
+        <v>3.2</v>
       </c>
       <c r="AR12" t="n">
-        <v>1.01</v>
+        <v>3.85</v>
       </c>
       <c r="AS12" t="n">
-        <v>1.03</v>
+        <v>4.2</v>
       </c>
       <c r="AT12" t="n">
-        <v>1.01</v>
+        <v>2.96</v>
       </c>
       <c r="AU12" t="n">
-        <v>1.01</v>
+        <v>2.9</v>
       </c>
       <c r="AV12" t="n">
-        <v>1.01</v>
+        <v>3.65</v>
       </c>
       <c r="AW12" t="n">
-        <v>1.03</v>
+        <v>4.2</v>
       </c>
       <c r="AX12" t="n">
-        <v>1.01</v>
+        <v>3.55</v>
       </c>
       <c r="AY12" t="n">
-        <v>1.01</v>
+        <v>3.45</v>
       </c>
       <c r="AZ12" t="n">
-        <v>1.01</v>
+        <v>3.85</v>
       </c>
       <c r="BA12" t="n">
-        <v>1.03</v>
+        <v>4.3</v>
       </c>
       <c r="BB12" t="n">
-        <v>1.01</v>
+        <v>4.1</v>
       </c>
       <c r="BC12" t="n">
-        <v>1.01</v>
+        <v>4</v>
       </c>
       <c r="BD12" t="n">
-        <v>1.03</v>
+        <v>4.2</v>
       </c>
       <c r="BE12" t="n">
-        <v>1.03</v>
+        <v>4.3</v>
       </c>
       <c r="BF12" t="n">
-        <v>1.01</v>
+        <v>4.1</v>
       </c>
       <c r="BG12" t="n">
-        <v>1.01</v>
+        <v>4.3</v>
       </c>
       <c r="BH12" t="n">
         <v>2.68</v>
       </c>
       <c r="BI12" t="n">
-        <v>2.18</v>
+        <v>2.34</v>
       </c>
       <c r="BJ12" t="n">
         <v>12</v>
@@ -3580,7 +3580,7 @@
         <v>5.3</v>
       </c>
       <c r="BO12" t="n">
-        <v>4</v>
+        <v>3.65</v>
       </c>
       <c r="BP12" t="n">
         <v>24</v>
@@ -3620,7 +3620,7 @@
       </c>
       <c r="CB12" t="inlineStr">
         <is>
-          <t>2026-06-11 09:18:50</t>
+          <t>2026-06-11 11:32:36</t>
         </is>
       </c>
     </row>
@@ -3651,166 +3651,166 @@
         </is>
       </c>
       <c r="F13" t="n">
-        <v>2.3</v>
+        <v>2.34</v>
       </c>
       <c r="G13" t="n">
-        <v>2.74</v>
+        <v>2.6</v>
       </c>
       <c r="H13" t="n">
-        <v>3.6</v>
+        <v>3.65</v>
       </c>
       <c r="I13" t="n">
-        <v>4.9</v>
+        <v>4.7</v>
       </c>
       <c r="J13" t="n">
-        <v>2.52</v>
+        <v>2.86</v>
       </c>
       <c r="K13" t="n">
-        <v>2.88</v>
+        <v>2.9</v>
       </c>
       <c r="L13" t="n">
-        <v>1.46</v>
+        <v>1.5</v>
       </c>
       <c r="M13" t="n">
-        <v>1.01</v>
+        <v>1.14</v>
       </c>
       <c r="N13" t="n">
-        <v>2.4</v>
+        <v>2.44</v>
       </c>
       <c r="O13" t="n">
-        <v>1.52</v>
+        <v>1.58</v>
       </c>
       <c r="P13" t="n">
-        <v>1.36</v>
+        <v>1.48</v>
       </c>
       <c r="Q13" t="n">
-        <v>2.68</v>
+        <v>2.72</v>
       </c>
       <c r="R13" t="n">
         <v>1.18</v>
       </c>
       <c r="S13" t="n">
-        <v>5.3</v>
+        <v>5.7</v>
       </c>
       <c r="T13" t="n">
-        <v>1.11</v>
+        <v>2.16</v>
       </c>
       <c r="U13" t="n">
-        <v>1.11</v>
+        <v>1.72</v>
       </c>
       <c r="V13" t="n">
-        <v>1.26</v>
+        <v>1.29</v>
       </c>
       <c r="W13" t="n">
-        <v>1.57</v>
+        <v>1.62</v>
       </c>
       <c r="X13" t="n">
-        <v>1000</v>
+        <v>9.6</v>
       </c>
       <c r="Y13" t="n">
-        <v>1000</v>
+        <v>10</v>
       </c>
       <c r="Z13" t="n">
-        <v>1000</v>
+        <v>26</v>
       </c>
       <c r="AA13" t="n">
-        <v>1000</v>
+        <v>110</v>
       </c>
       <c r="AB13" t="n">
-        <v>1000</v>
+        <v>7.4</v>
       </c>
       <c r="AC13" t="n">
-        <v>1000</v>
+        <v>7.2</v>
       </c>
       <c r="AD13" t="n">
-        <v>1000</v>
+        <v>17.5</v>
       </c>
       <c r="AE13" t="n">
-        <v>1000</v>
+        <v>80</v>
       </c>
       <c r="AF13" t="n">
-        <v>1000</v>
+        <v>14.5</v>
       </c>
       <c r="AG13" t="n">
-        <v>1000</v>
+        <v>15.5</v>
       </c>
       <c r="AH13" t="n">
-        <v>1000</v>
+        <v>30</v>
       </c>
       <c r="AI13" t="n">
-        <v>1000</v>
+        <v>120</v>
       </c>
       <c r="AJ13" t="n">
-        <v>1000</v>
+        <v>40</v>
       </c>
       <c r="AK13" t="n">
-        <v>1000</v>
+        <v>46</v>
       </c>
       <c r="AL13" t="n">
-        <v>1000</v>
+        <v>85</v>
       </c>
       <c r="AM13" t="n">
-        <v>1000</v>
+        <v>260</v>
       </c>
       <c r="AN13" t="n">
-        <v>1000</v>
+        <v>50</v>
       </c>
       <c r="AO13" t="n">
-        <v>1000</v>
+        <v>120</v>
       </c>
       <c r="AP13" t="n">
-        <v>1.01</v>
+        <v>4.1</v>
       </c>
       <c r="AQ13" t="n">
-        <v>1.01</v>
+        <v>4.1</v>
       </c>
       <c r="AR13" t="n">
-        <v>1.01</v>
+        <v>5.6</v>
       </c>
       <c r="AS13" t="n">
-        <v>1.01</v>
+        <v>6.6</v>
       </c>
       <c r="AT13" t="n">
-        <v>1.01</v>
+        <v>3.65</v>
       </c>
       <c r="AU13" t="n">
-        <v>1.01</v>
+        <v>3.6</v>
       </c>
       <c r="AV13" t="n">
-        <v>1.01</v>
+        <v>5.1</v>
       </c>
       <c r="AW13" t="n">
-        <v>1.01</v>
+        <v>6.6</v>
       </c>
       <c r="AX13" t="n">
-        <v>1.01</v>
+        <v>4.8</v>
       </c>
       <c r="AY13" t="n">
-        <v>1.01</v>
+        <v>4.9</v>
       </c>
       <c r="AZ13" t="n">
-        <v>1.01</v>
+        <v>5.8</v>
       </c>
       <c r="BA13" t="n">
-        <v>1.01</v>
+        <v>6.6</v>
       </c>
       <c r="BB13" t="n">
-        <v>1.01</v>
+        <v>6</v>
       </c>
       <c r="BC13" t="n">
-        <v>1.01</v>
+        <v>6.2</v>
       </c>
       <c r="BD13" t="n">
-        <v>1.01</v>
+        <v>6.6</v>
       </c>
       <c r="BE13" t="n">
-        <v>1.01</v>
+        <v>7</v>
       </c>
       <c r="BF13" t="n">
-        <v>1.01</v>
+        <v>6.2</v>
       </c>
       <c r="BG13" t="n">
-        <v>1.01</v>
+        <v>6.6</v>
       </c>
       <c r="BH13" t="n">
         <v>1000</v>
@@ -3874,7 +3874,7 @@
       </c>
       <c r="CB13" t="inlineStr">
         <is>
-          <t>2026-06-11 09:18:50</t>
+          <t>2026-06-11 11:32:36</t>
         </is>
       </c>
     </row>
@@ -3905,230 +3905,230 @@
         </is>
       </c>
       <c r="F14" t="n">
-        <v>1.09</v>
+        <v>1.46</v>
       </c>
       <c r="G14" t="n">
-        <v>1000</v>
+        <v>1.66</v>
       </c>
       <c r="H14" t="n">
-        <v>1.04</v>
+        <v>5</v>
       </c>
       <c r="I14" t="n">
-        <v>1000</v>
+        <v>7.4</v>
       </c>
       <c r="J14" t="n">
-        <v>1.09</v>
+        <v>3.8</v>
       </c>
       <c r="K14" t="n">
+        <v>5.8</v>
+      </c>
+      <c r="L14" t="n">
+        <v>1.23</v>
+      </c>
+      <c r="M14" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="N14" t="n">
+        <v>3.45</v>
+      </c>
+      <c r="O14" t="n">
+        <v>1.16</v>
+      </c>
+      <c r="P14" t="n">
+        <v>2.32</v>
+      </c>
+      <c r="Q14" t="n">
+        <v>1.47</v>
+      </c>
+      <c r="R14" t="n">
+        <v>1.58</v>
+      </c>
+      <c r="S14" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="T14" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="U14" t="n">
+        <v>2.14</v>
+      </c>
+      <c r="V14" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="W14" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="X14" t="n">
+        <v>34</v>
+      </c>
+      <c r="Y14" t="n">
         <v>950</v>
       </c>
-      <c r="L14" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="M14" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="N14" t="n">
-        <v>1.32</v>
-      </c>
-      <c r="O14" t="n">
-        <v>1.15</v>
-      </c>
-      <c r="P14" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="Q14" t="n">
-        <v>1.15</v>
-      </c>
-      <c r="R14" t="n">
-        <v>1.24</v>
-      </c>
-      <c r="S14" t="n">
-        <v>1.14</v>
-      </c>
-      <c r="T14" t="n">
-        <v>1.11</v>
-      </c>
-      <c r="U14" t="n">
-        <v>1.11</v>
-      </c>
-      <c r="V14" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="W14" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="X14" t="n">
-        <v>1000</v>
-      </c>
-      <c r="Y14" t="n">
-        <v>1000</v>
-      </c>
       <c r="Z14" t="n">
-        <v>1000</v>
+        <v>70</v>
       </c>
       <c r="AA14" t="n">
-        <v>1000</v>
+        <v>190</v>
       </c>
       <c r="AB14" t="n">
-        <v>1000</v>
+        <v>970</v>
       </c>
       <c r="AC14" t="n">
-        <v>1000</v>
+        <v>14</v>
       </c>
       <c r="AD14" t="n">
-        <v>1000</v>
+        <v>30</v>
       </c>
       <c r="AE14" t="n">
-        <v>1000</v>
+        <v>90</v>
       </c>
       <c r="AF14" t="n">
-        <v>1000</v>
+        <v>970</v>
       </c>
       <c r="AG14" t="n">
-        <v>1000</v>
+        <v>13</v>
       </c>
       <c r="AH14" t="n">
-        <v>1000</v>
+        <v>950</v>
       </c>
       <c r="AI14" t="n">
-        <v>1000</v>
+        <v>75</v>
       </c>
       <c r="AJ14" t="n">
-        <v>1000</v>
+        <v>970</v>
       </c>
       <c r="AK14" t="n">
-        <v>1000</v>
+        <v>18</v>
       </c>
       <c r="AL14" t="n">
-        <v>1000</v>
+        <v>34</v>
       </c>
       <c r="AM14" t="n">
-        <v>1000</v>
+        <v>95</v>
       </c>
       <c r="AN14" t="n">
-        <v>1000</v>
+        <v>7</v>
       </c>
       <c r="AO14" t="n">
-        <v>1000</v>
+        <v>80</v>
       </c>
       <c r="AP14" t="n">
-        <v>1.01</v>
+        <v>3.8</v>
       </c>
       <c r="AQ14" t="n">
-        <v>1.01</v>
+        <v>3.8</v>
       </c>
       <c r="AR14" t="n">
-        <v>1.01</v>
+        <v>4</v>
       </c>
       <c r="AS14" t="n">
-        <v>1.01</v>
+        <v>4.2</v>
       </c>
       <c r="AT14" t="n">
-        <v>1.01</v>
+        <v>3.3</v>
       </c>
       <c r="AU14" t="n">
-        <v>1.01</v>
+        <v>3.25</v>
       </c>
       <c r="AV14" t="n">
-        <v>1.01</v>
+        <v>3.75</v>
       </c>
       <c r="AW14" t="n">
-        <v>1.01</v>
+        <v>4.1</v>
       </c>
       <c r="AX14" t="n">
-        <v>1.01</v>
+        <v>3.25</v>
       </c>
       <c r="AY14" t="n">
-        <v>1.01</v>
+        <v>3.2</v>
       </c>
       <c r="AZ14" t="n">
-        <v>1.01</v>
+        <v>3.6</v>
       </c>
       <c r="BA14" t="n">
-        <v>1.01</v>
+        <v>4</v>
       </c>
       <c r="BB14" t="n">
-        <v>1.01</v>
+        <v>3.45</v>
       </c>
       <c r="BC14" t="n">
-        <v>1.01</v>
+        <v>3.45</v>
       </c>
       <c r="BD14" t="n">
-        <v>1.01</v>
+        <v>3.8</v>
       </c>
       <c r="BE14" t="n">
-        <v>1.01</v>
+        <v>4.1</v>
       </c>
       <c r="BF14" t="n">
-        <v>1.01</v>
+        <v>2.66</v>
       </c>
       <c r="BG14" t="n">
-        <v>1.01</v>
+        <v>4</v>
       </c>
       <c r="BH14" t="n">
-        <v>1000</v>
+        <v>5</v>
       </c>
       <c r="BI14" t="n">
-        <v>1.04</v>
+        <v>2.86</v>
       </c>
       <c r="BJ14" t="n">
         <v>1000</v>
       </c>
       <c r="BK14" t="n">
-        <v>1.04</v>
+        <v>4.1</v>
       </c>
       <c r="BL14" t="n">
         <v>1000</v>
       </c>
       <c r="BM14" t="n">
-        <v>1.04</v>
+        <v>6.2</v>
       </c>
       <c r="BN14" t="n">
-        <v>1000</v>
+        <v>4.9</v>
       </c>
       <c r="BO14" t="n">
-        <v>1.04</v>
+        <v>2.82</v>
       </c>
       <c r="BP14" t="n">
         <v>1000</v>
       </c>
       <c r="BQ14" t="n">
-        <v>1.04</v>
+        <v>4</v>
       </c>
       <c r="BR14" t="n">
         <v>1000</v>
       </c>
       <c r="BS14" t="n">
-        <v>1.04</v>
+        <v>5.1</v>
       </c>
       <c r="BT14" t="n">
         <v>1000</v>
       </c>
       <c r="BU14" t="n">
-        <v>1.04</v>
+        <v>4.1</v>
       </c>
       <c r="BV14" t="n">
         <v>1000</v>
       </c>
       <c r="BW14" t="n">
-        <v>1.04</v>
+        <v>5.9</v>
       </c>
       <c r="BX14" t="n">
         <v>1000</v>
       </c>
       <c r="BY14" t="n">
-        <v>1.04</v>
+        <v>5.9</v>
       </c>
       <c r="BZ14" t="n">
         <v>1000</v>
       </c>
       <c r="CA14" t="n">
-        <v>1.04</v>
+        <v>4.4</v>
       </c>
       <c r="CB14" t="inlineStr">
         <is>
-          <t>2026-06-11 09:18:50</t>
+          <t>2026-06-11 11:32:36</t>
         </is>
       </c>
     </row>
@@ -4159,230 +4159,230 @@
         </is>
       </c>
       <c r="F15" t="n">
-        <v>1.34</v>
+        <v>2.38</v>
       </c>
       <c r="G15" t="n">
-        <v>95</v>
+        <v>2.94</v>
       </c>
       <c r="H15" t="n">
-        <v>1.47</v>
+        <v>2.6</v>
       </c>
       <c r="I15" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="J15" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="K15" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="L15" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="M15" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="N15" t="n">
+        <v>3.35</v>
+      </c>
+      <c r="O15" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="P15" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="Q15" t="n">
+        <v>1.79</v>
+      </c>
+      <c r="R15" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="S15" t="n">
+        <v>3</v>
+      </c>
+      <c r="T15" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="U15" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="V15" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="W15" t="n">
+        <v>1.51</v>
+      </c>
+      <c r="X15" t="n">
+        <v>19</v>
+      </c>
+      <c r="Y15" t="n">
+        <v>14</v>
+      </c>
+      <c r="Z15" t="n">
+        <v>23</v>
+      </c>
+      <c r="AA15" t="n">
+        <v>60</v>
+      </c>
+      <c r="AB15" t="n">
+        <v>13</v>
+      </c>
+      <c r="AC15" t="n">
+        <v>9</v>
+      </c>
+      <c r="AD15" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="AE15" t="n">
+        <v>36</v>
+      </c>
+      <c r="AF15" t="n">
+        <v>20</v>
+      </c>
+      <c r="AG15" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="AH15" t="n">
+        <v>18.5</v>
+      </c>
+      <c r="AI15" t="n">
         <v>55</v>
       </c>
-      <c r="J15" t="n">
-        <v>1.76</v>
-      </c>
-      <c r="K15" t="n">
+      <c r="AJ15" t="n">
+        <v>50</v>
+      </c>
+      <c r="AK15" t="n">
         <v>32</v>
       </c>
-      <c r="L15" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="M15" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="N15" t="n">
-        <v>3.9</v>
-      </c>
-      <c r="O15" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="P15" t="n">
-        <v>1.39</v>
-      </c>
-      <c r="Q15" t="n">
-        <v>1.27</v>
-      </c>
-      <c r="R15" t="n">
-        <v>1.24</v>
-      </c>
-      <c r="S15" t="n">
-        <v>1.27</v>
-      </c>
-      <c r="T15" t="n">
-        <v>1.11</v>
-      </c>
-      <c r="U15" t="n">
-        <v>1.11</v>
-      </c>
-      <c r="V15" t="n">
-        <v>1.19</v>
-      </c>
-      <c r="W15" t="n">
-        <v>1.17</v>
-      </c>
-      <c r="X15" t="n">
-        <v>1000</v>
-      </c>
-      <c r="Y15" t="n">
-        <v>1000</v>
-      </c>
-      <c r="Z15" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AA15" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AB15" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AC15" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AD15" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AE15" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AF15" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AG15" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AH15" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AI15" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AJ15" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AK15" t="n">
-        <v>1000</v>
-      </c>
       <c r="AL15" t="n">
-        <v>1000</v>
+        <v>44</v>
       </c>
       <c r="AM15" t="n">
-        <v>1000</v>
+        <v>100</v>
       </c>
       <c r="AN15" t="n">
-        <v>1000</v>
+        <v>25</v>
       </c>
       <c r="AO15" t="n">
-        <v>1000</v>
+        <v>29</v>
       </c>
       <c r="AP15" t="n">
-        <v>1.01</v>
+        <v>4.5</v>
       </c>
       <c r="AQ15" t="n">
-        <v>1.01</v>
+        <v>4.3</v>
       </c>
       <c r="AR15" t="n">
-        <v>1.01</v>
+        <v>4.7</v>
       </c>
       <c r="AS15" t="n">
-        <v>1.01</v>
+        <v>5.4</v>
       </c>
       <c r="AT15" t="n">
-        <v>1.01</v>
+        <v>4.4</v>
       </c>
       <c r="AU15" t="n">
-        <v>1.01</v>
+        <v>6.2</v>
       </c>
       <c r="AV15" t="n">
-        <v>1.01</v>
+        <v>4.3</v>
       </c>
       <c r="AW15" t="n">
-        <v>1.01</v>
+        <v>5.2</v>
       </c>
       <c r="AX15" t="n">
-        <v>1.01</v>
+        <v>4.6</v>
       </c>
       <c r="AY15" t="n">
-        <v>1.01</v>
+        <v>4.2</v>
       </c>
       <c r="AZ15" t="n">
-        <v>1.01</v>
+        <v>4.5</v>
       </c>
       <c r="BA15" t="n">
-        <v>1.01</v>
+        <v>5.4</v>
       </c>
       <c r="BB15" t="n">
-        <v>1.01</v>
+        <v>5.3</v>
       </c>
       <c r="BC15" t="n">
-        <v>1.01</v>
+        <v>5</v>
       </c>
       <c r="BD15" t="n">
-        <v>1.01</v>
+        <v>5.4</v>
       </c>
       <c r="BE15" t="n">
-        <v>1.01</v>
+        <v>5.7</v>
       </c>
       <c r="BF15" t="n">
-        <v>1.01</v>
+        <v>4.8</v>
       </c>
       <c r="BG15" t="n">
-        <v>1.01</v>
+        <v>4.9</v>
       </c>
       <c r="BH15" t="n">
-        <v>1000</v>
+        <v>3.8</v>
       </c>
       <c r="BI15" t="n">
-        <v>1.04</v>
+        <v>2.82</v>
       </c>
       <c r="BJ15" t="n">
-        <v>1000</v>
+        <v>10</v>
       </c>
       <c r="BK15" t="n">
-        <v>1.04</v>
+        <v>4.2</v>
       </c>
       <c r="BL15" t="n">
         <v>1000</v>
       </c>
       <c r="BM15" t="n">
-        <v>1.04</v>
+        <v>7</v>
       </c>
       <c r="BN15" t="n">
-        <v>1000</v>
+        <v>6.2</v>
       </c>
       <c r="BO15" t="n">
-        <v>1.04</v>
+        <v>3.35</v>
       </c>
       <c r="BP15" t="n">
-        <v>1000</v>
+        <v>22</v>
       </c>
       <c r="BQ15" t="n">
-        <v>1.04</v>
+        <v>5.5</v>
       </c>
       <c r="BR15" t="n">
-        <v>1000</v>
+        <v>34</v>
       </c>
       <c r="BS15" t="n">
-        <v>1.04</v>
+        <v>6</v>
       </c>
       <c r="BT15" t="n">
-        <v>1000</v>
+        <v>6.6</v>
       </c>
       <c r="BU15" t="n">
-        <v>1.04</v>
+        <v>3.45</v>
       </c>
       <c r="BV15" t="n">
-        <v>1000</v>
+        <v>24</v>
       </c>
       <c r="BW15" t="n">
-        <v>1.04</v>
+        <v>5.6</v>
       </c>
       <c r="BX15" t="n">
         <v>1000</v>
       </c>
       <c r="BY15" t="n">
-        <v>1.04</v>
+        <v>6</v>
       </c>
       <c r="BZ15" t="n">
-        <v>1000</v>
+        <v>27</v>
       </c>
       <c r="CA15" t="n">
-        <v>1.04</v>
+        <v>5.8</v>
       </c>
       <c r="CB15" t="inlineStr">
         <is>
-          <t>2026-06-11 09:18:50</t>
+          <t>2026-06-11 11:32:36</t>
         </is>
       </c>
     </row>
@@ -4419,13 +4419,13 @@
         <v>1000</v>
       </c>
       <c r="H16" t="n">
-        <v>1.49</v>
+        <v>1.73</v>
       </c>
       <c r="I16" t="n">
         <v>1000</v>
       </c>
       <c r="J16" t="n">
-        <v>1.24</v>
+        <v>1.29</v>
       </c>
       <c r="K16" t="n">
         <v>3.25</v>
@@ -4452,7 +4452,7 @@
         <v>1.12</v>
       </c>
       <c r="S16" t="n">
-        <v>1.05</v>
+        <v>1.51</v>
       </c>
       <c r="T16" t="n">
         <v>1.11</v>
@@ -4636,7 +4636,7 @@
       </c>
       <c r="CB16" t="inlineStr">
         <is>
-          <t>2026-06-11 09:18:50</t>
+          <t>2026-06-11 11:32:36</t>
         </is>
       </c>
     </row>
@@ -4667,22 +4667,22 @@
         </is>
       </c>
       <c r="F17" t="n">
-        <v>3.5</v>
+        <v>3.6</v>
       </c>
       <c r="G17" t="n">
         <v>5.4</v>
       </c>
       <c r="H17" t="n">
-        <v>1.85</v>
+        <v>1.89</v>
       </c>
       <c r="I17" t="n">
-        <v>2.14</v>
+        <v>2.34</v>
       </c>
       <c r="J17" t="n">
-        <v>3.3</v>
+        <v>3.25</v>
       </c>
       <c r="K17" t="n">
-        <v>5.8</v>
+        <v>5.2</v>
       </c>
       <c r="L17" t="n">
         <v>1.01</v>
@@ -4691,22 +4691,22 @@
         <v>1.02</v>
       </c>
       <c r="N17" t="n">
-        <v>3.7</v>
+        <v>4.1</v>
       </c>
       <c r="O17" t="n">
         <v>1.23</v>
       </c>
       <c r="P17" t="n">
-        <v>1.94</v>
+        <v>1.95</v>
       </c>
       <c r="Q17" t="n">
-        <v>1.62</v>
+        <v>1.64</v>
       </c>
       <c r="R17" t="n">
         <v>1.32</v>
       </c>
       <c r="S17" t="n">
-        <v>2.3</v>
+        <v>2.32</v>
       </c>
       <c r="T17" t="n">
         <v>1.37</v>
@@ -4715,7 +4715,7 @@
         <v>1.73</v>
       </c>
       <c r="V17" t="n">
-        <v>1.87</v>
+        <v>1.75</v>
       </c>
       <c r="W17" t="n">
         <v>1.22</v>
@@ -4890,7 +4890,7 @@
       </c>
       <c r="CB17" t="inlineStr">
         <is>
-          <t>2026-06-11 09:18:50</t>
+          <t>2026-06-11 11:32:36</t>
         </is>
       </c>
     </row>
@@ -4921,7 +4921,7 @@
         </is>
       </c>
       <c r="F18" t="n">
-        <v>2.28</v>
+        <v>2.3</v>
       </c>
       <c r="G18" t="n">
         <v>2.5</v>
@@ -4951,7 +4951,7 @@
         <v>1.41</v>
       </c>
       <c r="P18" t="n">
-        <v>1.7</v>
+        <v>1.71</v>
       </c>
       <c r="Q18" t="n">
         <v>2.2</v>
@@ -4960,7 +4960,7 @@
         <v>1.26</v>
       </c>
       <c r="S18" t="n">
-        <v>4.2</v>
+        <v>4.1</v>
       </c>
       <c r="T18" t="n">
         <v>1.89</v>
@@ -4969,10 +4969,10 @@
         <v>1.96</v>
       </c>
       <c r="V18" t="n">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="W18" t="n">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="X18" t="n">
         <v>13.5</v>
@@ -4999,7 +4999,7 @@
         <v>60</v>
       </c>
       <c r="AF18" t="n">
-        <v>17.5</v>
+        <v>18</v>
       </c>
       <c r="AG18" t="n">
         <v>14</v>
@@ -5032,7 +5032,7 @@
         <v>8.199999999999999</v>
       </c>
       <c r="AQ18" t="n">
-        <v>8.6</v>
+        <v>8.4</v>
       </c>
       <c r="AR18" t="n">
         <v>17.5</v>
@@ -5041,7 +5041,7 @@
         <v>4.1</v>
       </c>
       <c r="AT18" t="n">
-        <v>7.2</v>
+        <v>6.6</v>
       </c>
       <c r="AU18" t="n">
         <v>5.6</v>
@@ -5065,7 +5065,7 @@
         <v>4.1</v>
       </c>
       <c r="BB18" t="n">
-        <v>3.95</v>
+        <v>3.9</v>
       </c>
       <c r="BC18" t="n">
         <v>21</v>
@@ -5077,10 +5077,10 @@
         <v>4.2</v>
       </c>
       <c r="BF18" t="n">
-        <v>18.5</v>
+        <v>19</v>
       </c>
       <c r="BG18" t="n">
-        <v>4.1</v>
+        <v>4</v>
       </c>
       <c r="BH18" t="n">
         <v>3.1</v>
@@ -5144,7 +5144,7 @@
       </c>
       <c r="CB18" t="inlineStr">
         <is>
-          <t>2026-06-11 09:18:50</t>
+          <t>2026-06-11 11:32:36</t>
         </is>
       </c>
     </row>
@@ -5181,7 +5181,7 @@
         <v>4.6</v>
       </c>
       <c r="H19" t="n">
-        <v>1.88</v>
+        <v>1.87</v>
       </c>
       <c r="I19" t="n">
         <v>2.04</v>
@@ -5190,7 +5190,7 @@
         <v>3.65</v>
       </c>
       <c r="K19" t="n">
-        <v>4.2</v>
+        <v>4.3</v>
       </c>
       <c r="L19" t="n">
         <v>1.01</v>
@@ -5208,13 +5208,13 @@
         <v>2.18</v>
       </c>
       <c r="Q19" t="n">
-        <v>1.72</v>
+        <v>1.71</v>
       </c>
       <c r="R19" t="n">
         <v>1.52</v>
       </c>
       <c r="S19" t="n">
-        <v>2.56</v>
+        <v>2.54</v>
       </c>
       <c r="T19" t="n">
         <v>1.64</v>
@@ -5226,10 +5226,10 @@
         <v>1.96</v>
       </c>
       <c r="W19" t="n">
-        <v>1.28</v>
+        <v>1.27</v>
       </c>
       <c r="X19" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="Y19" t="n">
         <v>12</v>
@@ -5238,7 +5238,7 @@
         <v>14.5</v>
       </c>
       <c r="AA19" t="n">
-        <v>32</v>
+        <v>27</v>
       </c>
       <c r="AB19" t="n">
         <v>19</v>
@@ -5247,13 +5247,13 @@
         <v>9.800000000000001</v>
       </c>
       <c r="AD19" t="n">
-        <v>14.5</v>
+        <v>12.5</v>
       </c>
       <c r="AE19" t="n">
         <v>18.5</v>
       </c>
       <c r="AF19" t="n">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="AG19" t="n">
         <v>23</v>
@@ -5265,10 +5265,10 @@
         <v>30</v>
       </c>
       <c r="AJ19" t="n">
-        <v>120</v>
+        <v>110</v>
       </c>
       <c r="AK19" t="n">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="AL19" t="n">
         <v>48</v>
@@ -5283,55 +5283,55 @@
         <v>10.5</v>
       </c>
       <c r="AP19" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="AQ19" t="n">
-        <v>8.199999999999999</v>
+        <v>9.4</v>
       </c>
       <c r="AR19" t="n">
-        <v>10</v>
+        <v>11.5</v>
       </c>
       <c r="AS19" t="n">
         <v>18.5</v>
       </c>
       <c r="AT19" t="n">
-        <v>13</v>
+        <v>15.5</v>
       </c>
       <c r="AU19" t="n">
         <v>7</v>
       </c>
       <c r="AV19" t="n">
-        <v>8.6</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AW19" t="n">
-        <v>12.5</v>
+        <v>14.5</v>
       </c>
       <c r="AX19" t="n">
-        <v>6</v>
+        <v>23</v>
       </c>
       <c r="AY19" t="n">
+        <v>16</v>
+      </c>
+      <c r="AZ19" t="n">
         <v>13.5</v>
       </c>
-      <c r="AZ19" t="n">
-        <v>11.5</v>
-      </c>
       <c r="BA19" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="BB19" t="n">
-        <v>6.8</v>
+        <v>7.4</v>
       </c>
       <c r="BC19" t="n">
-        <v>6.2</v>
+        <v>32</v>
       </c>
       <c r="BD19" t="n">
-        <v>6.2</v>
+        <v>30</v>
       </c>
       <c r="BE19" t="n">
-        <v>6.6</v>
+        <v>7.2</v>
       </c>
       <c r="BF19" t="n">
-        <v>6</v>
+        <v>27</v>
       </c>
       <c r="BG19" t="n">
         <v>7.2</v>
@@ -5346,19 +5346,19 @@
         <v>1000</v>
       </c>
       <c r="BK19" t="n">
-        <v>1.04</v>
+        <v>1.54</v>
       </c>
       <c r="BL19" t="n">
         <v>1000</v>
       </c>
       <c r="BM19" t="n">
-        <v>1.04</v>
+        <v>1.73</v>
       </c>
       <c r="BN19" t="n">
         <v>1000</v>
       </c>
       <c r="BO19" t="n">
-        <v>1.04</v>
+        <v>1.51</v>
       </c>
       <c r="BP19" t="n">
         <v>1000</v>
@@ -5376,29 +5376,29 @@
         <v>1000</v>
       </c>
       <c r="BU19" t="n">
-        <v>1.04</v>
+        <v>1.4</v>
       </c>
       <c r="BV19" t="n">
         <v>1000</v>
       </c>
       <c r="BW19" t="n">
-        <v>1.04</v>
+        <v>1.59</v>
       </c>
       <c r="BX19" t="n">
         <v>1000</v>
       </c>
       <c r="BY19" t="n">
-        <v>1.04</v>
+        <v>1.66</v>
       </c>
       <c r="BZ19" t="n">
         <v>1000</v>
       </c>
       <c r="CA19" t="n">
-        <v>1.04</v>
+        <v>1.62</v>
       </c>
       <c r="CB19" t="inlineStr">
         <is>
-          <t>2026-06-11 09:18:50</t>
+          <t>2026-06-11 11:32:36</t>
         </is>
       </c>
     </row>
@@ -5444,10 +5444,10 @@
         <v>3.5</v>
       </c>
       <c r="K20" t="n">
-        <v>3.95</v>
+        <v>3.9</v>
       </c>
       <c r="L20" t="n">
-        <v>1.01</v>
+        <v>1.31</v>
       </c>
       <c r="M20" t="n">
         <v>1.06</v>
@@ -5459,7 +5459,7 @@
         <v>1.3</v>
       </c>
       <c r="P20" t="n">
-        <v>1.9</v>
+        <v>1.94</v>
       </c>
       <c r="Q20" t="n">
         <v>1.89</v>
@@ -5525,13 +5525,13 @@
         <v>65</v>
       </c>
       <c r="AL20" t="n">
-        <v>70</v>
+        <v>75</v>
       </c>
       <c r="AM20" t="n">
         <v>120</v>
       </c>
       <c r="AN20" t="n">
-        <v>90</v>
+        <v>85</v>
       </c>
       <c r="AO20" t="n">
         <v>14</v>
@@ -5540,43 +5540,43 @@
         <v>11</v>
       </c>
       <c r="AQ20" t="n">
-        <v>7</v>
+        <v>7.6</v>
       </c>
       <c r="AR20" t="n">
-        <v>9.199999999999999</v>
+        <v>10</v>
       </c>
       <c r="AS20" t="n">
-        <v>16.5</v>
+        <v>18</v>
       </c>
       <c r="AT20" t="n">
-        <v>12</v>
+        <v>13.5</v>
       </c>
       <c r="AU20" t="n">
-        <v>6.6</v>
+        <v>7.2</v>
       </c>
       <c r="AV20" t="n">
-        <v>8</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AW20" t="n">
-        <v>15.5</v>
+        <v>17</v>
       </c>
       <c r="AX20" t="n">
-        <v>7.2</v>
+        <v>23</v>
       </c>
       <c r="AY20" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AZ20" t="n">
-        <v>14.5</v>
+        <v>16</v>
       </c>
       <c r="BA20" t="n">
-        <v>7.2</v>
+        <v>24</v>
       </c>
       <c r="BB20" t="n">
         <v>8.4</v>
       </c>
       <c r="BC20" t="n">
-        <v>38</v>
+        <v>7.8</v>
       </c>
       <c r="BD20" t="n">
         <v>8</v>
@@ -5588,7 +5588,7 @@
         <v>42</v>
       </c>
       <c r="BG20" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="BH20" t="n">
         <v>1000</v>
@@ -5652,7 +5652,7 @@
       </c>
       <c r="CB20" t="inlineStr">
         <is>
-          <t>2026-06-11 09:18:50</t>
+          <t>2026-06-11 11:32:36</t>
         </is>
       </c>
     </row>
@@ -5686,7 +5686,7 @@
         <v>3.1</v>
       </c>
       <c r="G21" t="n">
-        <v>3.45</v>
+        <v>3.55</v>
       </c>
       <c r="H21" t="n">
         <v>2.42</v>
@@ -5716,7 +5716,7 @@
         <v>1.71</v>
       </c>
       <c r="Q21" t="n">
-        <v>2.2</v>
+        <v>2.16</v>
       </c>
       <c r="R21" t="n">
         <v>1.26</v>
@@ -5731,13 +5731,13 @@
         <v>1.96</v>
       </c>
       <c r="V21" t="n">
-        <v>1.6</v>
+        <v>1.61</v>
       </c>
       <c r="W21" t="n">
-        <v>1.4</v>
+        <v>1.39</v>
       </c>
       <c r="X21" t="n">
-        <v>12</v>
+        <v>13.5</v>
       </c>
       <c r="Y21" t="n">
         <v>9.6</v>
@@ -5746,7 +5746,7 @@
         <v>16.5</v>
       </c>
       <c r="AA21" t="n">
-        <v>50</v>
+        <v>44</v>
       </c>
       <c r="AB21" t="n">
         <v>11.5</v>
@@ -5758,7 +5758,7 @@
         <v>12.5</v>
       </c>
       <c r="AE21" t="n">
-        <v>42</v>
+        <v>34</v>
       </c>
       <c r="AF21" t="n">
         <v>23</v>
@@ -5770,7 +5770,7 @@
         <v>21</v>
       </c>
       <c r="AI21" t="n">
-        <v>70</v>
+        <v>60</v>
       </c>
       <c r="AJ21" t="n">
         <v>80</v>
@@ -5791,7 +5791,7 @@
         <v>38</v>
       </c>
       <c r="AP21" t="n">
-        <v>9.800000000000001</v>
+        <v>9.6</v>
       </c>
       <c r="AQ21" t="n">
         <v>7.8</v>
@@ -5800,7 +5800,7 @@
         <v>13</v>
       </c>
       <c r="AS21" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="AT21" t="n">
         <v>9.199999999999999</v>
@@ -5812,22 +5812,22 @@
         <v>10</v>
       </c>
       <c r="AW21" t="n">
-        <v>7</v>
+        <v>23</v>
       </c>
       <c r="AX21" t="n">
-        <v>18.5</v>
+        <v>18</v>
       </c>
       <c r="AY21" t="n">
-        <v>12</v>
+        <v>11.5</v>
       </c>
       <c r="AZ21" t="n">
-        <v>16.5</v>
+        <v>16</v>
       </c>
       <c r="BA21" t="n">
         <v>32</v>
       </c>
       <c r="BB21" t="n">
-        <v>8</v>
+        <v>7.2</v>
       </c>
       <c r="BC21" t="n">
         <v>28</v>
@@ -5836,10 +5836,10 @@
         <v>36</v>
       </c>
       <c r="BE21" t="n">
-        <v>8.6</v>
+        <v>7.6</v>
       </c>
       <c r="BF21" t="n">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="BG21" t="n">
         <v>22</v>
@@ -5854,7 +5854,7 @@
         <v>10.5</v>
       </c>
       <c r="BK21" t="n">
-        <v>8</v>
+        <v>7.8</v>
       </c>
       <c r="BL21" t="n">
         <v>1000</v>
@@ -5906,7 +5906,7 @@
       </c>
       <c r="CB21" t="inlineStr">
         <is>
-          <t>2026-06-11 09:18:50</t>
+          <t>2026-06-11 11:32:36</t>
         </is>
       </c>
     </row>
@@ -5940,7 +5940,7 @@
         <v>2.2</v>
       </c>
       <c r="G22" t="n">
-        <v>2.36</v>
+        <v>2.34</v>
       </c>
       <c r="H22" t="n">
         <v>3.2</v>
@@ -5955,7 +5955,7 @@
         <v>3.85</v>
       </c>
       <c r="L22" t="n">
-        <v>1.12</v>
+        <v>1.29</v>
       </c>
       <c r="M22" t="n">
         <v>1.06</v>
@@ -5979,28 +5979,28 @@
         <v>3.1</v>
       </c>
       <c r="T22" t="n">
-        <v>1.69</v>
+        <v>1.67</v>
       </c>
       <c r="U22" t="n">
-        <v>2.22</v>
+        <v>2.18</v>
       </c>
       <c r="V22" t="n">
         <v>1.39</v>
       </c>
       <c r="W22" t="n">
-        <v>1.73</v>
+        <v>1.74</v>
       </c>
       <c r="X22" t="n">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="Y22" t="n">
-        <v>17</v>
+        <v>17.5</v>
       </c>
       <c r="Z22" t="n">
         <v>36</v>
       </c>
       <c r="AA22" t="n">
-        <v>70</v>
+        <v>75</v>
       </c>
       <c r="AB22" t="n">
         <v>11.5</v>
@@ -6039,7 +6039,7 @@
         <v>100</v>
       </c>
       <c r="AN22" t="n">
-        <v>19.5</v>
+        <v>17</v>
       </c>
       <c r="AO22" t="n">
         <v>48</v>
@@ -6048,7 +6048,7 @@
         <v>13.5</v>
       </c>
       <c r="AQ22" t="n">
-        <v>12</v>
+        <v>10.5</v>
       </c>
       <c r="AR22" t="n">
         <v>21</v>
@@ -6078,25 +6078,25 @@
         <v>14</v>
       </c>
       <c r="BA22" t="n">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="BB22" t="n">
-        <v>6.2</v>
+        <v>22</v>
       </c>
       <c r="BC22" t="n">
         <v>19.5</v>
       </c>
       <c r="BD22" t="n">
-        <v>6.4</v>
+        <v>25</v>
       </c>
       <c r="BE22" t="n">
-        <v>7.2</v>
+        <v>7</v>
       </c>
       <c r="BF22" t="n">
         <v>11.5</v>
       </c>
       <c r="BG22" t="n">
-        <v>6.4</v>
+        <v>6.2</v>
       </c>
       <c r="BH22" t="n">
         <v>1000</v>
@@ -6160,7 +6160,7 @@
       </c>
       <c r="CB22" t="inlineStr">
         <is>
-          <t>2026-06-11 09:18:50</t>
+          <t>2026-06-11 11:32:36</t>
         </is>
       </c>
     </row>
@@ -6191,16 +6191,16 @@
         </is>
       </c>
       <c r="F23" t="n">
-        <v>1.36</v>
+        <v>1.37</v>
       </c>
       <c r="G23" t="n">
-        <v>1.4</v>
+        <v>1.41</v>
       </c>
       <c r="H23" t="n">
         <v>10.5</v>
       </c>
       <c r="I23" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="J23" t="n">
         <v>4.9</v>
@@ -6215,7 +6215,7 @@
         <v>1.06</v>
       </c>
       <c r="N23" t="n">
-        <v>3.95</v>
+        <v>4</v>
       </c>
       <c r="O23" t="n">
         <v>1.28</v>
@@ -6224,7 +6224,7 @@
         <v>2.06</v>
       </c>
       <c r="Q23" t="n">
-        <v>1.83</v>
+        <v>1.84</v>
       </c>
       <c r="R23" t="n">
         <v>1.39</v>
@@ -6233,13 +6233,13 @@
         <v>3.1</v>
       </c>
       <c r="T23" t="n">
-        <v>2.18</v>
+        <v>2.24</v>
       </c>
       <c r="U23" t="n">
-        <v>1.73</v>
+        <v>1.74</v>
       </c>
       <c r="V23" t="n">
-        <v>1.08</v>
+        <v>1.09</v>
       </c>
       <c r="W23" t="n">
         <v>3.4</v>
@@ -6254,7 +6254,7 @@
         <v>130</v>
       </c>
       <c r="AA23" t="n">
-        <v>610</v>
+        <v>600</v>
       </c>
       <c r="AB23" t="n">
         <v>7.8</v>
@@ -6263,10 +6263,10 @@
         <v>14.5</v>
       </c>
       <c r="AD23" t="n">
-        <v>55</v>
+        <v>50</v>
       </c>
       <c r="AE23" t="n">
-        <v>270</v>
+        <v>260</v>
       </c>
       <c r="AF23" t="n">
         <v>9.199999999999999</v>
@@ -6296,19 +6296,19 @@
         <v>8</v>
       </c>
       <c r="AO23" t="n">
-        <v>440</v>
+        <v>430</v>
       </c>
       <c r="AP23" t="n">
         <v>14.5</v>
       </c>
       <c r="AQ23" t="n">
-        <v>4.2</v>
+        <v>4.3</v>
       </c>
       <c r="AR23" t="n">
         <v>4.6</v>
       </c>
       <c r="AS23" t="n">
-        <v>4.7</v>
+        <v>4.8</v>
       </c>
       <c r="AT23" t="n">
         <v>6.4</v>
@@ -6329,7 +6329,7 @@
         <v>9</v>
       </c>
       <c r="AZ23" t="n">
-        <v>4.2</v>
+        <v>4.3</v>
       </c>
       <c r="BA23" t="n">
         <v>4.7</v>
@@ -6347,10 +6347,10 @@
         <v>4.7</v>
       </c>
       <c r="BF23" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="BG23" t="n">
-        <v>4.7</v>
+        <v>4.8</v>
       </c>
       <c r="BH23" t="n">
         <v>1000</v>
@@ -6414,7 +6414,7 @@
       </c>
       <c r="CB23" t="inlineStr">
         <is>
-          <t>2026-06-11 09:18:50</t>
+          <t>2026-06-11 11:32:36</t>
         </is>
       </c>
     </row>
@@ -6469,7 +6469,7 @@
         <v>1.04</v>
       </c>
       <c r="N24" t="n">
-        <v>5</v>
+        <v>4.8</v>
       </c>
       <c r="O24" t="n">
         <v>1.2</v>
@@ -6478,16 +6478,16 @@
         <v>2.36</v>
       </c>
       <c r="Q24" t="n">
-        <v>1.64</v>
+        <v>1.4</v>
       </c>
       <c r="R24" t="n">
-        <v>1.38</v>
+        <v>1.53</v>
       </c>
       <c r="S24" t="n">
-        <v>2.32</v>
+        <v>2.16</v>
       </c>
       <c r="T24" t="n">
-        <v>1.58</v>
+        <v>1.6</v>
       </c>
       <c r="U24" t="n">
         <v>2.44</v>
@@ -6668,7 +6668,7 @@
       </c>
       <c r="CB24" t="inlineStr">
         <is>
-          <t>2026-06-11 09:18:50</t>
+          <t>2026-06-11 11:32:36</t>
         </is>
       </c>
     </row>
@@ -6708,10 +6708,10 @@
         <v>4.8</v>
       </c>
       <c r="I25" t="n">
-        <v>14</v>
+        <v>95</v>
       </c>
       <c r="J25" t="n">
-        <v>4.7</v>
+        <v>4.9</v>
       </c>
       <c r="K25" t="n">
         <v>1000</v>
@@ -6922,7 +6922,7 @@
       </c>
       <c r="CB25" t="inlineStr">
         <is>
-          <t>2026-06-11 09:18:50</t>
+          <t>2026-06-11 11:32:36</t>
         </is>
       </c>
     </row>
@@ -6953,19 +6953,19 @@
         </is>
       </c>
       <c r="F26" t="n">
-        <v>2.78</v>
+        <v>2.82</v>
       </c>
       <c r="G26" t="n">
-        <v>3.05</v>
+        <v>3</v>
       </c>
       <c r="H26" t="n">
-        <v>2.68</v>
+        <v>2.72</v>
       </c>
       <c r="I26" t="n">
-        <v>2.94</v>
+        <v>2.9</v>
       </c>
       <c r="J26" t="n">
-        <v>3.2</v>
+        <v>3.35</v>
       </c>
       <c r="K26" t="n">
         <v>3.45</v>
@@ -6974,145 +6974,145 @@
         <v>1.01</v>
       </c>
       <c r="M26" t="n">
-        <v>1.08</v>
+        <v>1.09</v>
       </c>
       <c r="N26" t="n">
-        <v>3.1</v>
+        <v>3.2</v>
       </c>
       <c r="O26" t="n">
-        <v>1.36</v>
+        <v>1.4</v>
       </c>
       <c r="P26" t="n">
-        <v>1.75</v>
+        <v>1.76</v>
       </c>
       <c r="Q26" t="n">
         <v>2.16</v>
       </c>
       <c r="R26" t="n">
-        <v>1.25</v>
+        <v>1.28</v>
       </c>
       <c r="S26" t="n">
-        <v>3.5</v>
+        <v>4</v>
       </c>
       <c r="T26" t="n">
+        <v>1.86</v>
+      </c>
+      <c r="U26" t="n">
+        <v>2.04</v>
+      </c>
+      <c r="V26" t="n">
         <v>1.53</v>
       </c>
-      <c r="U26" t="n">
-        <v>1.55</v>
-      </c>
-      <c r="V26" t="n">
-        <v>1.52</v>
-      </c>
       <c r="W26" t="n">
-        <v>1.49</v>
+        <v>1.5</v>
       </c>
       <c r="X26" t="n">
-        <v>1000</v>
+        <v>14.5</v>
       </c>
       <c r="Y26" t="n">
-        <v>1000</v>
+        <v>12.5</v>
       </c>
       <c r="Z26" t="n">
-        <v>1000</v>
+        <v>22</v>
       </c>
       <c r="AA26" t="n">
-        <v>1000</v>
+        <v>55</v>
       </c>
       <c r="AB26" t="n">
-        <v>1000</v>
+        <v>12.5</v>
       </c>
       <c r="AC26" t="n">
-        <v>1000</v>
+        <v>7.6</v>
       </c>
       <c r="AD26" t="n">
-        <v>1000</v>
+        <v>15.5</v>
       </c>
       <c r="AE26" t="n">
-        <v>1000</v>
+        <v>42</v>
       </c>
       <c r="AF26" t="n">
-        <v>1000</v>
+        <v>23</v>
       </c>
       <c r="AG26" t="n">
-        <v>1000</v>
+        <v>13</v>
       </c>
       <c r="AH26" t="n">
-        <v>1000</v>
+        <v>23</v>
       </c>
       <c r="AI26" t="n">
-        <v>1000</v>
+        <v>60</v>
       </c>
       <c r="AJ26" t="n">
-        <v>1000</v>
+        <v>60</v>
       </c>
       <c r="AK26" t="n">
-        <v>1000</v>
+        <v>44</v>
       </c>
       <c r="AL26" t="n">
-        <v>1000</v>
+        <v>65</v>
       </c>
       <c r="AM26" t="n">
-        <v>1000</v>
+        <v>140</v>
       </c>
       <c r="AN26" t="n">
-        <v>1000</v>
+        <v>44</v>
       </c>
       <c r="AO26" t="n">
-        <v>1000</v>
+        <v>42</v>
       </c>
       <c r="AP26" t="n">
-        <v>1.01</v>
+        <v>10</v>
       </c>
       <c r="AQ26" t="n">
-        <v>1.01</v>
+        <v>9</v>
       </c>
       <c r="AR26" t="n">
-        <v>1.01</v>
+        <v>13</v>
       </c>
       <c r="AS26" t="n">
-        <v>1.01</v>
+        <v>36</v>
       </c>
       <c r="AT26" t="n">
-        <v>1.01</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AU26" t="n">
-        <v>1.01</v>
+        <v>6.6</v>
       </c>
       <c r="AV26" t="n">
-        <v>1.01</v>
+        <v>11</v>
       </c>
       <c r="AW26" t="n">
-        <v>1.01</v>
+        <v>4.6</v>
       </c>
       <c r="AX26" t="n">
-        <v>1.01</v>
+        <v>13.5</v>
       </c>
       <c r="AY26" t="n">
-        <v>1.01</v>
+        <v>11.5</v>
       </c>
       <c r="AZ26" t="n">
-        <v>1.01</v>
+        <v>16</v>
       </c>
       <c r="BA26" t="n">
-        <v>1.01</v>
+        <v>4.7</v>
       </c>
       <c r="BB26" t="n">
-        <v>1.01</v>
+        <v>4.7</v>
       </c>
       <c r="BC26" t="n">
-        <v>1.01</v>
+        <v>4.6</v>
       </c>
       <c r="BD26" t="n">
-        <v>1.01</v>
+        <v>4.8</v>
       </c>
       <c r="BE26" t="n">
-        <v>1.01</v>
+        <v>4.9</v>
       </c>
       <c r="BF26" t="n">
-        <v>1.01</v>
+        <v>4.6</v>
       </c>
       <c r="BG26" t="n">
-        <v>1.01</v>
+        <v>4.4</v>
       </c>
       <c r="BH26" t="n">
         <v>1000</v>
@@ -7124,25 +7124,25 @@
         <v>1000</v>
       </c>
       <c r="BK26" t="n">
-        <v>1.48</v>
+        <v>1.04</v>
       </c>
       <c r="BL26" t="n">
         <v>1000</v>
       </c>
       <c r="BM26" t="n">
-        <v>1.65</v>
+        <v>1.04</v>
       </c>
       <c r="BN26" t="n">
         <v>1000</v>
       </c>
       <c r="BO26" t="n">
-        <v>1.39</v>
+        <v>1.04</v>
       </c>
       <c r="BP26" t="n">
         <v>1000</v>
       </c>
       <c r="BQ26" t="n">
-        <v>1.58</v>
+        <v>1.04</v>
       </c>
       <c r="BR26" t="n">
         <v>1000</v>
@@ -7154,13 +7154,13 @@
         <v>1000</v>
       </c>
       <c r="BU26" t="n">
-        <v>1.39</v>
+        <v>1.04</v>
       </c>
       <c r="BV26" t="n">
         <v>1000</v>
       </c>
       <c r="BW26" t="n">
-        <v>1.57</v>
+        <v>1.04</v>
       </c>
       <c r="BX26" t="n">
         <v>1000</v>
@@ -7176,7 +7176,7 @@
       </c>
       <c r="CB26" t="inlineStr">
         <is>
-          <t>2026-06-11 09:18:50</t>
+          <t>2026-06-11 11:32:36</t>
         </is>
       </c>
     </row>
@@ -7207,43 +7207,43 @@
         </is>
       </c>
       <c r="F27" t="n">
-        <v>1.69</v>
+        <v>1.72</v>
       </c>
       <c r="G27" t="n">
-        <v>1.84</v>
+        <v>1.88</v>
       </c>
       <c r="H27" t="n">
-        <v>4</v>
+        <v>3.9</v>
       </c>
       <c r="I27" t="n">
-        <v>4.8</v>
+        <v>4.6</v>
       </c>
       <c r="J27" t="n">
-        <v>4</v>
+        <v>4.4</v>
       </c>
       <c r="K27" t="n">
         <v>5.3</v>
       </c>
       <c r="L27" t="n">
-        <v>1.21</v>
+        <v>1.18</v>
       </c>
       <c r="M27" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="N27" t="n">
-        <v>3.45</v>
+        <v>7.4</v>
       </c>
       <c r="O27" t="n">
         <v>1.12</v>
       </c>
       <c r="P27" t="n">
-        <v>3</v>
+        <v>3.15</v>
       </c>
       <c r="Q27" t="n">
         <v>1.37</v>
       </c>
       <c r="R27" t="n">
-        <v>1.88</v>
+        <v>1.87</v>
       </c>
       <c r="S27" t="n">
         <v>1.92</v>
@@ -7255,22 +7255,22 @@
         <v>2.78</v>
       </c>
       <c r="V27" t="n">
-        <v>1.26</v>
+        <v>1.27</v>
       </c>
       <c r="W27" t="n">
-        <v>2.18</v>
+        <v>2.14</v>
       </c>
       <c r="X27" t="n">
         <v>48</v>
       </c>
       <c r="Y27" t="n">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="Z27" t="n">
-        <v>55</v>
+        <v>50</v>
       </c>
       <c r="AA27" t="n">
-        <v>110</v>
+        <v>95</v>
       </c>
       <c r="AB27" t="n">
         <v>22</v>
@@ -7279,25 +7279,25 @@
         <v>15.5</v>
       </c>
       <c r="AD27" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AE27" t="n">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="AF27" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AG27" t="n">
         <v>14</v>
       </c>
       <c r="AH27" t="n">
-        <v>16.5</v>
+        <v>16</v>
       </c>
       <c r="AI27" t="n">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="AJ27" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="AK27" t="n">
         <v>19.5</v>
@@ -7309,70 +7309,70 @@
         <v>60</v>
       </c>
       <c r="AN27" t="n">
-        <v>5.9</v>
+        <v>7</v>
       </c>
       <c r="AO27" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="AP27" t="n">
-        <v>4.5</v>
+        <v>4.2</v>
       </c>
       <c r="AQ27" t="n">
-        <v>4.4</v>
+        <v>21</v>
       </c>
       <c r="AR27" t="n">
-        <v>4.6</v>
+        <v>32</v>
       </c>
       <c r="AS27" t="n">
-        <v>4.8</v>
+        <v>4.3</v>
       </c>
       <c r="AT27" t="n">
+        <v>13</v>
+      </c>
+      <c r="AU27" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AV27" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="AW27" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="AX27" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="AY27" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="AZ27" t="n">
+        <v>11</v>
+      </c>
+      <c r="BA27" t="n">
         <v>4.1</v>
       </c>
-      <c r="AU27" t="n">
-        <v>3.8</v>
-      </c>
-      <c r="AV27" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="AW27" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="AX27" t="n">
-        <v>4</v>
-      </c>
-      <c r="AY27" t="n">
-        <v>3.7</v>
-      </c>
-      <c r="AZ27" t="n">
-        <v>3.85</v>
-      </c>
-      <c r="BA27" t="n">
-        <v>4.5</v>
-      </c>
       <c r="BB27" t="n">
+        <v>18</v>
+      </c>
+      <c r="BC27" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="BD27" t="n">
+        <v>18</v>
+      </c>
+      <c r="BE27" t="n">
         <v>4.2</v>
       </c>
-      <c r="BC27" t="n">
-        <v>4</v>
-      </c>
-      <c r="BD27" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="BE27" t="n">
-        <v>4.6</v>
-      </c>
       <c r="BF27" t="n">
-        <v>2.72</v>
+        <v>5.1</v>
       </c>
       <c r="BG27" t="n">
-        <v>4.3</v>
+        <v>19</v>
       </c>
       <c r="BH27" t="n">
         <v>5.6</v>
       </c>
       <c r="BI27" t="n">
-        <v>3.65</v>
+        <v>4.1</v>
       </c>
       <c r="BJ27" t="n">
         <v>8.800000000000001</v>
@@ -7384,19 +7384,19 @@
         <v>1000</v>
       </c>
       <c r="BM27" t="n">
-        <v>9.199999999999999</v>
+        <v>9</v>
       </c>
       <c r="BN27" t="n">
         <v>5.5</v>
       </c>
       <c r="BO27" t="n">
-        <v>3.65</v>
+        <v>4.6</v>
       </c>
       <c r="BP27" t="n">
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="BQ27" t="n">
-        <v>5.4</v>
+        <v>5.5</v>
       </c>
       <c r="BR27" t="n">
         <v>18</v>
@@ -7405,10 +7405,10 @@
         <v>6.6</v>
       </c>
       <c r="BT27" t="n">
-        <v>9</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BU27" t="n">
-        <v>4.9</v>
+        <v>4.8</v>
       </c>
       <c r="BV27" t="n">
         <v>1000</v>
@@ -7430,7 +7430,7 @@
       </c>
       <c r="CB27" t="inlineStr">
         <is>
-          <t>2026-06-11 09:18:50</t>
+          <t>2026-06-11 11:32:36</t>
         </is>
       </c>
     </row>
@@ -7461,10 +7461,10 @@
         </is>
       </c>
       <c r="F28" t="n">
-        <v>2.2</v>
+        <v>2.22</v>
       </c>
       <c r="G28" t="n">
-        <v>2.38</v>
+        <v>2.36</v>
       </c>
       <c r="H28" t="n">
         <v>3.6</v>
@@ -7485,7 +7485,7 @@
         <v>1.1</v>
       </c>
       <c r="N28" t="n">
-        <v>2.98</v>
+        <v>3</v>
       </c>
       <c r="O28" t="n">
         <v>1.44</v>
@@ -7494,7 +7494,7 @@
         <v>1.66</v>
       </c>
       <c r="Q28" t="n">
-        <v>2.3</v>
+        <v>2.28</v>
       </c>
       <c r="R28" t="n">
         <v>1.24</v>
@@ -7503,7 +7503,7 @@
         <v>4.5</v>
       </c>
       <c r="T28" t="n">
-        <v>1.97</v>
+        <v>1.96</v>
       </c>
       <c r="U28" t="n">
         <v>1.89</v>
@@ -7512,7 +7512,7 @@
         <v>1.33</v>
       </c>
       <c r="W28" t="n">
-        <v>1.72</v>
+        <v>1.73</v>
       </c>
       <c r="X28" t="n">
         <v>12.5</v>
@@ -7530,7 +7530,7 @@
         <v>970</v>
       </c>
       <c r="AC28" t="n">
-        <v>8</v>
+        <v>7.6</v>
       </c>
       <c r="AD28" t="n">
         <v>970</v>
@@ -7551,13 +7551,13 @@
         <v>80</v>
       </c>
       <c r="AJ28" t="n">
-        <v>38</v>
+        <v>32</v>
       </c>
       <c r="AK28" t="n">
         <v>30</v>
       </c>
       <c r="AL28" t="n">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="AM28" t="n">
         <v>170</v>
@@ -7569,16 +7569,16 @@
         <v>80</v>
       </c>
       <c r="AP28" t="n">
-        <v>4.8</v>
+        <v>5</v>
       </c>
       <c r="AQ28" t="n">
         <v>9.800000000000001</v>
       </c>
       <c r="AR28" t="n">
-        <v>6</v>
+        <v>6.4</v>
       </c>
       <c r="AS28" t="n">
-        <v>7.2</v>
+        <v>7.8</v>
       </c>
       <c r="AT28" t="n">
         <v>6.8</v>
@@ -7587,40 +7587,40 @@
         <v>6.4</v>
       </c>
       <c r="AV28" t="n">
+        <v>5.6</v>
+      </c>
+      <c r="AW28" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="AX28" t="n">
         <v>5.3</v>
       </c>
-      <c r="AW28" t="n">
-        <v>6.8</v>
-      </c>
-      <c r="AX28" t="n">
-        <v>5</v>
-      </c>
       <c r="AY28" t="n">
-        <v>4.7</v>
+        <v>4.9</v>
       </c>
       <c r="AZ28" t="n">
-        <v>5.8</v>
+        <v>6</v>
       </c>
       <c r="BA28" t="n">
-        <v>7</v>
+        <v>7.6</v>
       </c>
       <c r="BB28" t="n">
-        <v>6.4</v>
+        <v>6.6</v>
       </c>
       <c r="BC28" t="n">
-        <v>6.2</v>
+        <v>6.6</v>
       </c>
       <c r="BD28" t="n">
-        <v>6.8</v>
+        <v>7.4</v>
       </c>
       <c r="BE28" t="n">
-        <v>7.4</v>
+        <v>4.1</v>
       </c>
       <c r="BF28" t="n">
-        <v>6</v>
+        <v>19.5</v>
       </c>
       <c r="BG28" t="n">
-        <v>7</v>
+        <v>7.6</v>
       </c>
       <c r="BH28" t="n">
         <v>1000</v>
@@ -7684,7 +7684,7 @@
       </c>
       <c r="CB28" t="inlineStr">
         <is>
-          <t>2026-06-11 09:18:50</t>
+          <t>2026-06-11 11:32:36</t>
         </is>
       </c>
     </row>
@@ -7721,16 +7721,16 @@
         <v>1.49</v>
       </c>
       <c r="H29" t="n">
-        <v>3.65</v>
+        <v>3.6</v>
       </c>
       <c r="I29" t="n">
-        <v>100</v>
+        <v>1000</v>
       </c>
       <c r="J29" t="n">
         <v>4.4</v>
       </c>
       <c r="K29" t="n">
-        <v>9.800000000000001</v>
+        <v>9.6</v>
       </c>
       <c r="L29" t="n">
         <v>1.01</v>
@@ -7739,7 +7739,7 @@
         <v>1.01</v>
       </c>
       <c r="N29" t="n">
-        <v>1.26</v>
+        <v>1.25</v>
       </c>
       <c r="O29" t="n">
         <v>1.09</v>
@@ -7938,7 +7938,7 @@
       </c>
       <c r="CB29" t="inlineStr">
         <is>
-          <t>2026-06-11 09:18:50</t>
+          <t>2026-06-11 11:32:36</t>
         </is>
       </c>
     </row>
@@ -7969,22 +7969,22 @@
         </is>
       </c>
       <c r="F30" t="n">
-        <v>1.97</v>
+        <v>2</v>
       </c>
       <c r="G30" t="n">
-        <v>2.08</v>
+        <v>2.06</v>
       </c>
       <c r="H30" t="n">
         <v>3.8</v>
       </c>
       <c r="I30" t="n">
-        <v>4.2</v>
+        <v>4.1</v>
       </c>
       <c r="J30" t="n">
         <v>3.8</v>
       </c>
       <c r="K30" t="n">
-        <v>4.2</v>
+        <v>4.1</v>
       </c>
       <c r="L30" t="n">
         <v>1.29</v>
@@ -7993,13 +7993,13 @@
         <v>1.05</v>
       </c>
       <c r="N30" t="n">
-        <v>4.2</v>
+        <v>4.4</v>
       </c>
       <c r="O30" t="n">
         <v>1.26</v>
       </c>
       <c r="P30" t="n">
-        <v>2.12</v>
+        <v>2.14</v>
       </c>
       <c r="Q30" t="n">
         <v>1.77</v>
@@ -8011,22 +8011,22 @@
         <v>2.96</v>
       </c>
       <c r="T30" t="n">
-        <v>1.7</v>
+        <v>1.71</v>
       </c>
       <c r="U30" t="n">
-        <v>2.24</v>
+        <v>2.3</v>
       </c>
       <c r="V30" t="n">
-        <v>1.31</v>
+        <v>1.32</v>
       </c>
       <c r="W30" t="n">
-        <v>1.93</v>
+        <v>1.94</v>
       </c>
       <c r="X30" t="n">
         <v>22</v>
       </c>
       <c r="Y30" t="n">
-        <v>19.5</v>
+        <v>20</v>
       </c>
       <c r="Z30" t="n">
         <v>36</v>
@@ -8035,10 +8035,10 @@
         <v>90</v>
       </c>
       <c r="AB30" t="n">
-        <v>12.5</v>
+        <v>13.5</v>
       </c>
       <c r="AC30" t="n">
-        <v>11</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AD30" t="n">
         <v>19.5</v>
@@ -8047,10 +8047,10 @@
         <v>55</v>
       </c>
       <c r="AF30" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AG30" t="n">
-        <v>12.5</v>
+        <v>13</v>
       </c>
       <c r="AH30" t="n">
         <v>21</v>
@@ -8062,7 +8062,7 @@
         <v>30</v>
       </c>
       <c r="AK30" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="AL30" t="n">
         <v>40</v>
@@ -8071,7 +8071,7 @@
         <v>100</v>
       </c>
       <c r="AN30" t="n">
-        <v>15</v>
+        <v>15.5</v>
       </c>
       <c r="AO30" t="n">
         <v>48</v>
@@ -8083,22 +8083,22 @@
         <v>14.5</v>
       </c>
       <c r="AR30" t="n">
-        <v>4.1</v>
+        <v>25</v>
       </c>
       <c r="AS30" t="n">
-        <v>4.4</v>
+        <v>34</v>
       </c>
       <c r="AT30" t="n">
         <v>9.6</v>
       </c>
       <c r="AU30" t="n">
-        <v>7.8</v>
+        <v>8</v>
       </c>
       <c r="AV30" t="n">
         <v>14</v>
       </c>
       <c r="AW30" t="n">
-        <v>4.3</v>
+        <v>38</v>
       </c>
       <c r="AX30" t="n">
         <v>12</v>
@@ -8119,22 +8119,22 @@
         <v>17.5</v>
       </c>
       <c r="BD30" t="n">
-        <v>4.1</v>
+        <v>21</v>
       </c>
       <c r="BE30" t="n">
-        <v>4.5</v>
+        <v>34</v>
       </c>
       <c r="BF30" t="n">
-        <v>9.4</v>
+        <v>11</v>
       </c>
       <c r="BG30" t="n">
-        <v>4.2</v>
+        <v>34</v>
       </c>
       <c r="BH30" t="n">
         <v>3.75</v>
       </c>
       <c r="BI30" t="n">
-        <v>3.4</v>
+        <v>3.35</v>
       </c>
       <c r="BJ30" t="n">
         <v>9.199999999999999</v>
@@ -8192,7 +8192,7 @@
       </c>
       <c r="CB30" t="inlineStr">
         <is>
-          <t>2026-06-11 09:18:50</t>
+          <t>2026-06-11 11:32:36</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-06-12.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-06-12.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:CB30"/>
+  <dimension ref="A1:CB29"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -860,19 +860,19 @@
         <v>1.5</v>
       </c>
       <c r="G2" t="n">
-        <v>1.66</v>
+        <v>1.63</v>
       </c>
       <c r="H2" t="n">
-        <v>5.7</v>
+        <v>7</v>
       </c>
       <c r="I2" t="n">
         <v>9.4</v>
       </c>
       <c r="J2" t="n">
-        <v>3.6</v>
+        <v>3.95</v>
       </c>
       <c r="K2" t="n">
-        <v>32</v>
+        <v>4.9</v>
       </c>
       <c r="L2" t="n">
         <v>1.01</v>
@@ -908,7 +908,7 @@
         <v>1.13</v>
       </c>
       <c r="W2" t="n">
-        <v>2.5</v>
+        <v>2.58</v>
       </c>
       <c r="X2" t="n">
         <v>970</v>
@@ -989,7 +989,7 @@
         <v>4.5</v>
       </c>
       <c r="AX2" t="n">
-        <v>3.25</v>
+        <v>3.35</v>
       </c>
       <c r="AY2" t="n">
         <v>3.35</v>
@@ -1080,7 +1080,7 @@
       </c>
       <c r="CB2" t="inlineStr">
         <is>
-          <t>2026-06-11 11:32:36</t>
+          <t>2026-06-11 13:45:41</t>
         </is>
       </c>
     </row>
@@ -1111,22 +1111,22 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>1.09</v>
+        <v>2.26</v>
       </c>
       <c r="G3" t="n">
-        <v>1000</v>
+        <v>2.9</v>
       </c>
       <c r="H3" t="n">
-        <v>1.09</v>
+        <v>2.48</v>
       </c>
       <c r="I3" t="n">
-        <v>1000</v>
+        <v>2.94</v>
       </c>
       <c r="J3" t="n">
-        <v>1.1</v>
+        <v>3.45</v>
       </c>
       <c r="K3" t="n">
-        <v>1000</v>
+        <v>6.6</v>
       </c>
       <c r="L3" t="n">
         <v>1.01</v>
@@ -1135,34 +1135,34 @@
         <v>1.01</v>
       </c>
       <c r="N3" t="n">
-        <v>1.1</v>
+        <v>1.11</v>
       </c>
       <c r="O3" t="n">
-        <v>1.22</v>
+        <v>1.23</v>
       </c>
       <c r="P3" t="n">
-        <v>1.32</v>
+        <v>2.08</v>
       </c>
       <c r="Q3" t="n">
-        <v>1.22</v>
+        <v>1.65</v>
       </c>
       <c r="R3" t="n">
-        <v>1.18</v>
+        <v>1.42</v>
       </c>
       <c r="S3" t="n">
-        <v>1.22</v>
+        <v>2.6</v>
       </c>
       <c r="T3" t="n">
-        <v>1.11</v>
+        <v>1.12</v>
       </c>
       <c r="U3" t="n">
         <v>1.11</v>
       </c>
       <c r="V3" t="n">
-        <v>1.02</v>
+        <v>1.51</v>
       </c>
       <c r="W3" t="n">
-        <v>1.02</v>
+        <v>1.53</v>
       </c>
       <c r="X3" t="n">
         <v>1000</v>
@@ -1334,7 +1334,7 @@
       </c>
       <c r="CB3" t="inlineStr">
         <is>
-          <t>2026-06-11 11:32:36</t>
+          <t>2026-06-11 13:45:41</t>
         </is>
       </c>
     </row>
@@ -1365,22 +1365,22 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>2.26</v>
+        <v>2.72</v>
       </c>
       <c r="G4" t="n">
-        <v>3.45</v>
+        <v>3.1</v>
       </c>
       <c r="H4" t="n">
-        <v>2.66</v>
+        <v>2.8</v>
       </c>
       <c r="I4" t="n">
-        <v>3.65</v>
+        <v>3.6</v>
       </c>
       <c r="J4" t="n">
-        <v>2.54</v>
+        <v>2.62</v>
       </c>
       <c r="K4" t="n">
-        <v>3.55</v>
+        <v>3.4</v>
       </c>
       <c r="L4" t="n">
         <v>1.01</v>
@@ -1389,34 +1389,34 @@
         <v>1.01</v>
       </c>
       <c r="N4" t="n">
-        <v>2.42</v>
+        <v>2.36</v>
       </c>
       <c r="O4" t="n">
-        <v>1.58</v>
+        <v>1.6</v>
       </c>
       <c r="P4" t="n">
-        <v>1.5</v>
+        <v>1.46</v>
       </c>
       <c r="Q4" t="n">
-        <v>2.52</v>
+        <v>2.78</v>
       </c>
       <c r="R4" t="n">
         <v>1.18</v>
       </c>
       <c r="S4" t="n">
-        <v>2.5</v>
+        <v>5.1</v>
       </c>
       <c r="T4" t="n">
-        <v>1.7</v>
+        <v>1.84</v>
       </c>
       <c r="U4" t="n">
-        <v>1.41</v>
+        <v>1.51</v>
       </c>
       <c r="V4" t="n">
-        <v>1.41</v>
+        <v>1.42</v>
       </c>
       <c r="W4" t="n">
-        <v>1.45</v>
+        <v>1.47</v>
       </c>
       <c r="X4" t="n">
         <v>970</v>
@@ -1431,10 +1431,10 @@
         <v>75</v>
       </c>
       <c r="AB4" t="n">
-        <v>970</v>
+        <v>9</v>
       </c>
       <c r="AC4" t="n">
-        <v>970</v>
+        <v>7.8</v>
       </c>
       <c r="AD4" t="n">
         <v>970</v>
@@ -1458,7 +1458,7 @@
         <v>65</v>
       </c>
       <c r="AK4" t="n">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="AL4" t="n">
         <v>1000</v>
@@ -1473,58 +1473,58 @@
         <v>1000</v>
       </c>
       <c r="AP4" t="n">
-        <v>3.65</v>
+        <v>6</v>
       </c>
       <c r="AQ4" t="n">
-        <v>3.65</v>
+        <v>6.4</v>
       </c>
       <c r="AR4" t="n">
-        <v>2.3</v>
+        <v>4.3</v>
       </c>
       <c r="AS4" t="n">
-        <v>2.44</v>
+        <v>5</v>
       </c>
       <c r="AT4" t="n">
-        <v>3.65</v>
+        <v>3.35</v>
       </c>
       <c r="AU4" t="n">
-        <v>3.4</v>
+        <v>5.6</v>
       </c>
       <c r="AV4" t="n">
-        <v>2.24</v>
+        <v>4.1</v>
       </c>
       <c r="AW4" t="n">
-        <v>2.42</v>
+        <v>4.9</v>
       </c>
       <c r="AX4" t="n">
-        <v>2.28</v>
+        <v>4.3</v>
       </c>
       <c r="AY4" t="n">
-        <v>2.2</v>
+        <v>4</v>
       </c>
       <c r="AZ4" t="n">
-        <v>2.36</v>
+        <v>4.5</v>
       </c>
       <c r="BA4" t="n">
-        <v>2.46</v>
+        <v>5.1</v>
       </c>
       <c r="BB4" t="n">
-        <v>2.42</v>
+        <v>5</v>
       </c>
       <c r="BC4" t="n">
-        <v>3.4</v>
+        <v>4.9</v>
       </c>
       <c r="BD4" t="n">
-        <v>2.46</v>
+        <v>5.1</v>
       </c>
       <c r="BE4" t="n">
-        <v>2.5</v>
+        <v>5.3</v>
       </c>
       <c r="BF4" t="n">
-        <v>2.44</v>
+        <v>5</v>
       </c>
       <c r="BG4" t="n">
-        <v>2.46</v>
+        <v>5</v>
       </c>
       <c r="BH4" t="n">
         <v>2.94</v>
@@ -1588,7 +1588,7 @@
       </c>
       <c r="CB4" t="inlineStr">
         <is>
-          <t>2026-06-11 11:32:36</t>
+          <t>2026-06-11 13:45:41</t>
         </is>
       </c>
     </row>
@@ -1619,22 +1619,22 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>2.16</v>
+        <v>2.18</v>
       </c>
       <c r="G5" t="n">
-        <v>2.4</v>
+        <v>2.36</v>
       </c>
       <c r="H5" t="n">
-        <v>3.9</v>
+        <v>3.95</v>
       </c>
       <c r="I5" t="n">
         <v>4.5</v>
       </c>
       <c r="J5" t="n">
-        <v>2.96</v>
+        <v>2.94</v>
       </c>
       <c r="K5" t="n">
-        <v>3.25</v>
+        <v>3.2</v>
       </c>
       <c r="L5" t="n">
         <v>1.49</v>
@@ -1643,34 +1643,34 @@
         <v>1.13</v>
       </c>
       <c r="N5" t="n">
-        <v>2.46</v>
+        <v>2.5</v>
       </c>
       <c r="O5" t="n">
-        <v>1.56</v>
+        <v>1.57</v>
       </c>
       <c r="P5" t="n">
-        <v>1.49</v>
+        <v>1.5</v>
       </c>
       <c r="Q5" t="n">
-        <v>2.68</v>
+        <v>2.72</v>
       </c>
       <c r="R5" t="n">
         <v>1.18</v>
       </c>
       <c r="S5" t="n">
-        <v>5.5</v>
+        <v>5.8</v>
       </c>
       <c r="T5" t="n">
-        <v>2.16</v>
+        <v>2.18</v>
       </c>
       <c r="U5" t="n">
-        <v>1.71</v>
+        <v>1.72</v>
       </c>
       <c r="V5" t="n">
-        <v>1.28</v>
+        <v>1.29</v>
       </c>
       <c r="W5" t="n">
-        <v>1.72</v>
+        <v>1.73</v>
       </c>
       <c r="X5" t="n">
         <v>9.4</v>
@@ -1685,7 +1685,7 @@
         <v>130</v>
       </c>
       <c r="AB5" t="n">
-        <v>7.2</v>
+        <v>7</v>
       </c>
       <c r="AC5" t="n">
         <v>7.4</v>
@@ -1694,7 +1694,7 @@
         <v>22</v>
       </c>
       <c r="AE5" t="n">
-        <v>95</v>
+        <v>90</v>
       </c>
       <c r="AF5" t="n">
         <v>14.5</v>
@@ -1712,7 +1712,7 @@
         <v>40</v>
       </c>
       <c r="AK5" t="n">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="AL5" t="n">
         <v>85</v>
@@ -1721,61 +1721,61 @@
         <v>250</v>
       </c>
       <c r="AN5" t="n">
-        <v>44</v>
+        <v>40</v>
       </c>
       <c r="AO5" t="n">
         <v>140</v>
       </c>
       <c r="AP5" t="n">
-        <v>3.9</v>
+        <v>6.4</v>
       </c>
       <c r="AQ5" t="n">
-        <v>4.4</v>
+        <v>9.4</v>
       </c>
       <c r="AR5" t="n">
-        <v>5.5</v>
+        <v>21</v>
       </c>
       <c r="AS5" t="n">
-        <v>6.4</v>
+        <v>6.2</v>
       </c>
       <c r="AT5" t="n">
-        <v>5.5</v>
+        <v>6</v>
       </c>
       <c r="AU5" t="n">
-        <v>3.5</v>
+        <v>5.7</v>
       </c>
       <c r="AV5" t="n">
-        <v>5.1</v>
+        <v>16</v>
       </c>
       <c r="AW5" t="n">
         <v>6.2</v>
       </c>
       <c r="AX5" t="n">
-        <v>4.6</v>
+        <v>11</v>
       </c>
       <c r="AY5" t="n">
-        <v>4.5</v>
+        <v>10.5</v>
       </c>
       <c r="AZ5" t="n">
-        <v>5.5</v>
+        <v>21</v>
       </c>
       <c r="BA5" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="BB5" t="n">
         <v>6.4</v>
       </c>
-      <c r="BB5" t="n">
-        <v>5.6</v>
-      </c>
       <c r="BC5" t="n">
-        <v>5.7</v>
+        <v>5.9</v>
       </c>
       <c r="BD5" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="BE5" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="BF5" t="n">
         <v>6</v>
-      </c>
-      <c r="BE5" t="n">
-        <v>6.6</v>
-      </c>
-      <c r="BF5" t="n">
-        <v>5.7</v>
       </c>
       <c r="BG5" t="n">
         <v>6.4</v>
@@ -1842,7 +1842,7 @@
       </c>
       <c r="CB5" t="inlineStr">
         <is>
-          <t>2026-06-11 11:32:36</t>
+          <t>2026-06-11 13:45:41</t>
         </is>
       </c>
     </row>
@@ -1888,7 +1888,7 @@
         <v>3.45</v>
       </c>
       <c r="K6" t="n">
-        <v>3.75</v>
+        <v>3.85</v>
       </c>
       <c r="L6" t="n">
         <v>1.3</v>
@@ -1897,16 +1897,16 @@
         <v>1.06</v>
       </c>
       <c r="N6" t="n">
-        <v>3.75</v>
+        <v>3.85</v>
       </c>
       <c r="O6" t="n">
         <v>1.3</v>
       </c>
       <c r="P6" t="n">
-        <v>1.96</v>
+        <v>1.95</v>
       </c>
       <c r="Q6" t="n">
-        <v>1.89</v>
+        <v>1.9</v>
       </c>
       <c r="R6" t="n">
         <v>1.37</v>
@@ -1942,7 +1942,7 @@
         <v>17</v>
       </c>
       <c r="AC6" t="n">
-        <v>10</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AD6" t="n">
         <v>13.5</v>
@@ -1960,7 +1960,7 @@
         <v>17.5</v>
       </c>
       <c r="AI6" t="n">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="AJ6" t="n">
         <v>80</v>
@@ -1981,7 +1981,7 @@
         <v>17.5</v>
       </c>
       <c r="AP6" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="AQ6" t="n">
         <v>9</v>
@@ -1996,43 +1996,43 @@
         <v>10</v>
       </c>
       <c r="AU6" t="n">
-        <v>6.2</v>
+        <v>7.2</v>
       </c>
       <c r="AV6" t="n">
-        <v>8.199999999999999</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AW6" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="AX6" t="n">
-        <v>18</v>
+        <v>18.5</v>
       </c>
       <c r="AY6" t="n">
         <v>13</v>
       </c>
       <c r="AZ6" t="n">
-        <v>12.5</v>
+        <v>15</v>
       </c>
       <c r="BA6" t="n">
-        <v>4.9</v>
+        <v>5.3</v>
       </c>
       <c r="BB6" t="n">
-        <v>5.1</v>
+        <v>5.7</v>
       </c>
       <c r="BC6" t="n">
-        <v>4.9</v>
+        <v>5.2</v>
       </c>
       <c r="BD6" t="n">
         <v>32</v>
       </c>
       <c r="BE6" t="n">
-        <v>5.2</v>
+        <v>5.3</v>
       </c>
       <c r="BF6" t="n">
-        <v>4.8</v>
+        <v>5.1</v>
       </c>
       <c r="BG6" t="n">
-        <v>12.5</v>
+        <v>15</v>
       </c>
       <c r="BH6" t="n">
         <v>1000</v>
@@ -2096,7 +2096,7 @@
       </c>
       <c r="CB6" t="inlineStr">
         <is>
-          <t>2026-06-11 11:32:36</t>
+          <t>2026-06-11 13:45:41</t>
         </is>
       </c>
     </row>
@@ -2127,7 +2127,7 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>1.08</v>
+        <v>1.09</v>
       </c>
       <c r="G7" t="n">
         <v>1000</v>
@@ -2139,7 +2139,7 @@
         <v>1000</v>
       </c>
       <c r="J7" t="n">
-        <v>1.08</v>
+        <v>1.1</v>
       </c>
       <c r="K7" t="n">
         <v>1000</v>
@@ -2350,7 +2350,7 @@
       </c>
       <c r="CB7" t="inlineStr">
         <is>
-          <t>2026-06-11 11:32:36</t>
+          <t>2026-06-11 13:45:41</t>
         </is>
       </c>
     </row>
@@ -2387,16 +2387,16 @@
         <v>1.77</v>
       </c>
       <c r="H8" t="n">
-        <v>2.9</v>
+        <v>5.5</v>
       </c>
       <c r="I8" t="n">
-        <v>11.5</v>
+        <v>10</v>
       </c>
       <c r="J8" t="n">
-        <v>3.75</v>
+        <v>3.7</v>
       </c>
       <c r="K8" t="n">
-        <v>950</v>
+        <v>5.3</v>
       </c>
       <c r="L8" t="n">
         <v>1.31</v>
@@ -2604,7 +2604,7 @@
       </c>
       <c r="CB8" t="inlineStr">
         <is>
-          <t>2026-06-11 11:32:36</t>
+          <t>2026-06-11 13:45:41</t>
         </is>
       </c>
     </row>
@@ -2635,13 +2635,13 @@
         </is>
       </c>
       <c r="F9" t="n">
-        <v>4</v>
+        <v>4.2</v>
       </c>
       <c r="G9" t="n">
-        <v>5.4</v>
+        <v>5.2</v>
       </c>
       <c r="H9" t="n">
-        <v>1.68</v>
+        <v>1.69</v>
       </c>
       <c r="I9" t="n">
         <v>1.85</v>
@@ -2650,7 +2650,7 @@
         <v>3.95</v>
       </c>
       <c r="K9" t="n">
-        <v>5</v>
+        <v>4.7</v>
       </c>
       <c r="L9" t="n">
         <v>1.24</v>
@@ -2659,7 +2659,7 @@
         <v>1.02</v>
       </c>
       <c r="N9" t="n">
-        <v>1.01</v>
+        <v>4.6</v>
       </c>
       <c r="O9" t="n">
         <v>1.18</v>
@@ -2674,7 +2674,7 @@
         <v>1.6</v>
       </c>
       <c r="S9" t="n">
-        <v>2.2</v>
+        <v>2.24</v>
       </c>
       <c r="T9" t="n">
         <v>1.58</v>
@@ -2692,10 +2692,10 @@
         <v>30</v>
       </c>
       <c r="Y9" t="n">
-        <v>970</v>
+        <v>15</v>
       </c>
       <c r="Z9" t="n">
-        <v>970</v>
+        <v>15.5</v>
       </c>
       <c r="AA9" t="n">
         <v>22</v>
@@ -2704,10 +2704,10 @@
         <v>28</v>
       </c>
       <c r="AC9" t="n">
-        <v>970</v>
+        <v>12.5</v>
       </c>
       <c r="AD9" t="n">
-        <v>970</v>
+        <v>12.5</v>
       </c>
       <c r="AE9" t="n">
         <v>970</v>
@@ -2734,7 +2734,7 @@
         <v>55</v>
       </c>
       <c r="AM9" t="n">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="AN9" t="n">
         <v>46</v>
@@ -2858,14 +2858,14 @@
       </c>
       <c r="CB9" t="inlineStr">
         <is>
-          <t>2026-06-11 11:32:36</t>
+          <t>2026-06-11 13:45:41</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Georgian Umaglesi Liga</t>
+          <t>Swedish Division 1</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -2880,246 +2880,246 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>Dinamo Batumi</t>
+          <t>Umea FC</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Dila Gori</t>
+          <t>Pitea</t>
         </is>
       </c>
       <c r="F10" t="n">
-        <v>3.9</v>
+        <v>1.46</v>
       </c>
       <c r="G10" t="n">
+        <v>1.66</v>
+      </c>
+      <c r="H10" t="n">
         <v>5</v>
       </c>
-      <c r="H10" t="n">
-        <v>1.87</v>
-      </c>
       <c r="I10" t="n">
-        <v>2.04</v>
+        <v>7.4</v>
       </c>
       <c r="J10" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="K10" t="n">
+        <v>5.8</v>
+      </c>
+      <c r="L10" t="n">
+        <v>1.23</v>
+      </c>
+      <c r="M10" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="N10" t="n">
+        <v>3.45</v>
+      </c>
+      <c r="O10" t="n">
+        <v>1.16</v>
+      </c>
+      <c r="P10" t="n">
+        <v>2.32</v>
+      </c>
+      <c r="Q10" t="n">
+        <v>1.47</v>
+      </c>
+      <c r="R10" t="n">
+        <v>1.58</v>
+      </c>
+      <c r="S10" t="n">
+        <v>2.08</v>
+      </c>
+      <c r="T10" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="U10" t="n">
+        <v>2.14</v>
+      </c>
+      <c r="V10" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="W10" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="X10" t="n">
+        <v>34</v>
+      </c>
+      <c r="Y10" t="n">
+        <v>950</v>
+      </c>
+      <c r="Z10" t="n">
+        <v>70</v>
+      </c>
+      <c r="AA10" t="n">
+        <v>190</v>
+      </c>
+      <c r="AB10" t="n">
+        <v>970</v>
+      </c>
+      <c r="AC10" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="AD10" t="n">
+        <v>30</v>
+      </c>
+      <c r="AE10" t="n">
+        <v>90</v>
+      </c>
+      <c r="AF10" t="n">
+        <v>970</v>
+      </c>
+      <c r="AG10" t="n">
+        <v>13</v>
+      </c>
+      <c r="AH10" t="n">
+        <v>950</v>
+      </c>
+      <c r="AI10" t="n">
+        <v>75</v>
+      </c>
+      <c r="AJ10" t="n">
+        <v>970</v>
+      </c>
+      <c r="AK10" t="n">
+        <v>18</v>
+      </c>
+      <c r="AL10" t="n">
+        <v>34</v>
+      </c>
+      <c r="AM10" t="n">
+        <v>95</v>
+      </c>
+      <c r="AN10" t="n">
+        <v>7</v>
+      </c>
+      <c r="AO10" t="n">
+        <v>80</v>
+      </c>
+      <c r="AP10" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="AQ10" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="AR10" t="n">
+        <v>4</v>
+      </c>
+      <c r="AS10" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="AT10" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="AU10" t="n">
         <v>3.25</v>
       </c>
-      <c r="K10" t="n">
-        <v>3.95</v>
-      </c>
-      <c r="L10" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="M10" t="n">
-        <v>1.07</v>
-      </c>
-      <c r="N10" t="n">
+      <c r="AV10" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="AW10" t="n">
+        <v>4</v>
+      </c>
+      <c r="AX10" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="AY10" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="AZ10" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="BA10" t="n">
+        <v>4</v>
+      </c>
+      <c r="BB10" t="n">
+        <v>3.45</v>
+      </c>
+      <c r="BC10" t="n">
         <v>3.4</v>
       </c>
-      <c r="O10" t="n">
-        <v>1.34</v>
-      </c>
-      <c r="P10" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="Q10" t="n">
-        <v>2</v>
-      </c>
-      <c r="R10" t="n">
-        <v>1.31</v>
-      </c>
-      <c r="S10" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="T10" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="U10" t="n">
-        <v>1.96</v>
-      </c>
-      <c r="V10" t="n">
-        <v>1.96</v>
-      </c>
-      <c r="W10" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="X10" t="n">
-        <v>16</v>
-      </c>
-      <c r="Y10" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="Z10" t="n">
-        <v>14.5</v>
-      </c>
-      <c r="AA10" t="n">
-        <v>28</v>
-      </c>
-      <c r="AB10" t="n">
-        <v>18.5</v>
-      </c>
-      <c r="AC10" t="n">
-        <v>9.800000000000001</v>
-      </c>
-      <c r="AD10" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="AE10" t="n">
-        <v>27</v>
-      </c>
-      <c r="AF10" t="n">
-        <v>42</v>
-      </c>
-      <c r="AG10" t="n">
-        <v>23</v>
-      </c>
-      <c r="AH10" t="n">
-        <v>24</v>
-      </c>
-      <c r="AI10" t="n">
-        <v>48</v>
-      </c>
-      <c r="AJ10" t="n">
-        <v>130</v>
-      </c>
-      <c r="AK10" t="n">
-        <v>80</v>
-      </c>
-      <c r="AL10" t="n">
-        <v>85</v>
-      </c>
-      <c r="AM10" t="n">
-        <v>150</v>
-      </c>
-      <c r="AN10" t="n">
-        <v>95</v>
-      </c>
-      <c r="AO10" t="n">
-        <v>18.5</v>
-      </c>
-      <c r="AP10" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="AQ10" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="AR10" t="n">
-        <v>3.35</v>
-      </c>
-      <c r="AS10" t="n">
+      <c r="BD10" t="n">
         <v>3.75</v>
       </c>
-      <c r="AT10" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="AU10" t="n">
-        <v>3.05</v>
-      </c>
-      <c r="AV10" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="AW10" t="n">
-        <v>3.75</v>
-      </c>
-      <c r="AX10" t="n">
-        <v>3.9</v>
-      </c>
-      <c r="AY10" t="n">
-        <v>3.65</v>
-      </c>
-      <c r="AZ10" t="n">
-        <v>3.65</v>
-      </c>
-      <c r="BA10" t="n">
-        <v>3.95</v>
-      </c>
-      <c r="BB10" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="BC10" t="n">
+      <c r="BE10" t="n">
+        <v>4</v>
+      </c>
+      <c r="BF10" t="n">
+        <v>2.64</v>
+      </c>
+      <c r="BG10" t="n">
+        <v>4</v>
+      </c>
+      <c r="BH10" t="n">
+        <v>5</v>
+      </c>
+      <c r="BI10" t="n">
+        <v>2.86</v>
+      </c>
+      <c r="BJ10" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BK10" t="n">
         <v>4.1</v>
       </c>
-      <c r="BD10" t="n">
+      <c r="BL10" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BM10" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="BN10" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="BO10" t="n">
+        <v>2.82</v>
+      </c>
+      <c r="BP10" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BQ10" t="n">
+        <v>4</v>
+      </c>
+      <c r="BR10" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BS10" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="BT10" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BU10" t="n">
         <v>4.1</v>
       </c>
-      <c r="BE10" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="BF10" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="BG10" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="BH10" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BI10" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="BJ10" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BK10" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="BL10" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BM10" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="BN10" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BO10" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="BP10" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BQ10" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="BR10" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BS10" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="BT10" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BU10" t="n">
-        <v>1.04</v>
-      </c>
       <c r="BV10" t="n">
         <v>1000</v>
       </c>
       <c r="BW10" t="n">
-        <v>1.04</v>
+        <v>5.9</v>
       </c>
       <c r="BX10" t="n">
         <v>1000</v>
       </c>
       <c r="BY10" t="n">
-        <v>1.04</v>
+        <v>5.9</v>
       </c>
       <c r="BZ10" t="n">
         <v>1000</v>
       </c>
       <c r="CA10" t="n">
-        <v>1.04</v>
+        <v>4.4</v>
       </c>
       <c r="CB10" t="inlineStr">
         <is>
-          <t>2026-06-11 11:32:36</t>
+          <t>2026-06-11 13:45:41</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Lithuanian A Lyga</t>
+          <t>Moroccan Botola Pro 1</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -3134,246 +3134,246 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>VMFD Zalgiris</t>
+          <t>DHJ El Jadida</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Riteriai</t>
+          <t>Olympique Dcheira</t>
         </is>
       </c>
       <c r="F11" t="n">
+        <v>2.36</v>
+      </c>
+      <c r="G11" t="n">
+        <v>2.58</v>
+      </c>
+      <c r="H11" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="I11" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="J11" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="K11" t="n">
+        <v>3.15</v>
+      </c>
+      <c r="L11" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="M11" t="n">
         <v>1.14</v>
       </c>
-      <c r="G11" t="n">
+      <c r="N11" t="n">
+        <v>2.44</v>
+      </c>
+      <c r="O11" t="n">
+        <v>1.59</v>
+      </c>
+      <c r="P11" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="Q11" t="n">
+        <v>2.76</v>
+      </c>
+      <c r="R11" t="n">
         <v>1.18</v>
       </c>
-      <c r="H11" t="n">
+      <c r="S11" t="n">
+        <v>5.9</v>
+      </c>
+      <c r="T11" t="n">
+        <v>2.18</v>
+      </c>
+      <c r="U11" t="n">
+        <v>1.72</v>
+      </c>
+      <c r="V11" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="W11" t="n">
+        <v>1.63</v>
+      </c>
+      <c r="X11" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="Y11" t="n">
+        <v>10</v>
+      </c>
+      <c r="Z11" t="n">
+        <v>26</v>
+      </c>
+      <c r="AA11" t="n">
+        <v>110</v>
+      </c>
+      <c r="AB11" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="AC11" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="AD11" t="n">
+        <v>17.5</v>
+      </c>
+      <c r="AE11" t="n">
+        <v>80</v>
+      </c>
+      <c r="AF11" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="AG11" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="AH11" t="n">
+        <v>30</v>
+      </c>
+      <c r="AI11" t="n">
+        <v>120</v>
+      </c>
+      <c r="AJ11" t="n">
+        <v>40</v>
+      </c>
+      <c r="AK11" t="n">
+        <v>38</v>
+      </c>
+      <c r="AL11" t="n">
+        <v>85</v>
+      </c>
+      <c r="AM11" t="n">
+        <v>260</v>
+      </c>
+      <c r="AN11" t="n">
+        <v>50</v>
+      </c>
+      <c r="AO11" t="n">
+        <v>120</v>
+      </c>
+      <c r="AP11" t="n">
+        <v>6</v>
+      </c>
+      <c r="AQ11" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="AR11" t="n">
         <v>21</v>
       </c>
-      <c r="I11" t="n">
-        <v>32</v>
-      </c>
-      <c r="J11" t="n">
-        <v>9.4</v>
-      </c>
-      <c r="K11" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="L11" t="n">
-        <v>1.19</v>
-      </c>
-      <c r="M11" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="N11" t="n">
-        <v>7</v>
-      </c>
-      <c r="O11" t="n">
-        <v>1.12</v>
-      </c>
-      <c r="P11" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="Q11" t="n">
-        <v>1.37</v>
-      </c>
-      <c r="R11" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="S11" t="n">
-        <v>1.94</v>
-      </c>
-      <c r="T11" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="U11" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="V11" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="W11" t="n">
-        <v>6.6</v>
-      </c>
-      <c r="X11" t="n">
-        <v>950</v>
-      </c>
-      <c r="Y11" t="n">
-        <v>950</v>
-      </c>
-      <c r="Z11" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AA11" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AB11" t="n">
-        <v>970</v>
-      </c>
-      <c r="AC11" t="n">
-        <v>950</v>
-      </c>
-      <c r="AD11" t="n">
-        <v>950</v>
-      </c>
-      <c r="AE11" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AF11" t="n">
-        <v>10</v>
-      </c>
-      <c r="AG11" t="n">
-        <v>17</v>
-      </c>
-      <c r="AH11" t="n">
-        <v>950</v>
-      </c>
-      <c r="AI11" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AJ11" t="n">
-        <v>9.6</v>
-      </c>
-      <c r="AK11" t="n">
-        <v>17.5</v>
-      </c>
-      <c r="AL11" t="n">
-        <v>60</v>
-      </c>
-      <c r="AM11" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AN11" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="AO11" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AP11" t="n">
-        <v>5</v>
-      </c>
-      <c r="AQ11" t="n">
-        <v>5.3</v>
-      </c>
-      <c r="AR11" t="n">
-        <v>5.5</v>
-      </c>
       <c r="AS11" t="n">
-        <v>5.6</v>
+        <v>6.8</v>
       </c>
       <c r="AT11" t="n">
-        <v>4.1</v>
+        <v>6.2</v>
       </c>
       <c r="AU11" t="n">
-        <v>18</v>
+        <v>6.2</v>
       </c>
       <c r="AV11" t="n">
-        <v>5.3</v>
+        <v>12.5</v>
       </c>
       <c r="AW11" t="n">
-        <v>5.5</v>
+        <v>6.8</v>
       </c>
       <c r="AX11" t="n">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="AY11" t="n">
         <v>11</v>
       </c>
       <c r="AZ11" t="n">
-        <v>5.1</v>
+        <v>17.5</v>
       </c>
       <c r="BA11" t="n">
-        <v>5.5</v>
+        <v>7</v>
       </c>
       <c r="BB11" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="BC11" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="BD11" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="BE11" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="BF11" t="n">
         <v>6.4</v>
       </c>
-      <c r="BC11" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="BD11" t="n">
-        <v>5.1</v>
-      </c>
-      <c r="BE11" t="n">
-        <v>5.5</v>
-      </c>
-      <c r="BF11" t="n">
-        <v>2.48</v>
-      </c>
       <c r="BG11" t="n">
-        <v>5.6</v>
+        <v>7</v>
       </c>
       <c r="BH11" t="n">
-        <v>5.7</v>
+        <v>1000</v>
       </c>
       <c r="BI11" t="n">
-        <v>4.4</v>
+        <v>1.04</v>
       </c>
       <c r="BJ11" t="n">
         <v>1000</v>
       </c>
       <c r="BK11" t="n">
-        <v>6.6</v>
+        <v>1.04</v>
       </c>
       <c r="BL11" t="n">
         <v>1000</v>
       </c>
       <c r="BM11" t="n">
-        <v>10</v>
+        <v>1.04</v>
       </c>
       <c r="BN11" t="n">
-        <v>3.9</v>
+        <v>1000</v>
       </c>
       <c r="BO11" t="n">
-        <v>3.1</v>
+        <v>1.04</v>
       </c>
       <c r="BP11" t="n">
-        <v>5.9</v>
+        <v>1000</v>
       </c>
       <c r="BQ11" t="n">
-        <v>4.5</v>
+        <v>1.04</v>
       </c>
       <c r="BR11" t="n">
         <v>1000</v>
       </c>
       <c r="BS11" t="n">
-        <v>7.4</v>
+        <v>1.04</v>
       </c>
       <c r="BT11" t="n">
         <v>1000</v>
       </c>
       <c r="BU11" t="n">
-        <v>7.4</v>
+        <v>1.04</v>
       </c>
       <c r="BV11" t="n">
         <v>1000</v>
       </c>
       <c r="BW11" t="n">
-        <v>10</v>
+        <v>1.04</v>
       </c>
       <c r="BX11" t="n">
         <v>1000</v>
       </c>
       <c r="BY11" t="n">
-        <v>10</v>
+        <v>1.04</v>
       </c>
       <c r="BZ11" t="n">
-        <v>6.8</v>
+        <v>1000</v>
       </c>
       <c r="CA11" t="n">
-        <v>5.3</v>
+        <v>1.04</v>
       </c>
       <c r="CB11" t="inlineStr">
         <is>
-          <t>2026-06-11 11:32:36</t>
+          <t>2026-06-11 13:45:41</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Moroccan Botola Pro 1</t>
+          <t>Swedish Division 1</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -3388,246 +3388,246 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>CODM Meknes</t>
+          <t>Lunds BK</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Club R Zemamra</t>
+          <t>Ariana FC</t>
         </is>
       </c>
       <c r="F12" t="n">
         <v>2.38</v>
       </c>
       <c r="G12" t="n">
-        <v>2.72</v>
+        <v>2.94</v>
       </c>
       <c r="H12" t="n">
-        <v>3.15</v>
+        <v>2.6</v>
       </c>
       <c r="I12" t="n">
-        <v>4</v>
+        <v>3.25</v>
       </c>
       <c r="J12" t="n">
         <v>2.84</v>
       </c>
       <c r="K12" t="n">
-        <v>3.25</v>
+        <v>4.1</v>
       </c>
       <c r="L12" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="M12" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="N12" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="O12" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="P12" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="Q12" t="n">
+        <v>1.79</v>
+      </c>
+      <c r="R12" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="S12" t="n">
+        <v>2.86</v>
+      </c>
+      <c r="T12" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="U12" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="V12" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="W12" t="n">
         <v>1.51</v>
       </c>
-      <c r="M12" t="n">
-        <v>1.11</v>
-      </c>
-      <c r="N12" t="n">
-        <v>2.28</v>
-      </c>
-      <c r="O12" t="n">
-        <v>1.58</v>
-      </c>
-      <c r="P12" t="n">
-        <v>1.46</v>
-      </c>
-      <c r="Q12" t="n">
-        <v>2.72</v>
-      </c>
-      <c r="R12" t="n">
-        <v>1.18</v>
-      </c>
-      <c r="S12" t="n">
-        <v>4.9</v>
-      </c>
-      <c r="T12" t="n">
-        <v>2.16</v>
-      </c>
-      <c r="U12" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="V12" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="W12" t="n">
-        <v>1.58</v>
-      </c>
       <c r="X12" t="n">
-        <v>9.4</v>
+        <v>19</v>
       </c>
       <c r="Y12" t="n">
-        <v>11.5</v>
+        <v>14</v>
       </c>
       <c r="Z12" t="n">
-        <v>29</v>
+        <v>23</v>
       </c>
       <c r="AA12" t="n">
-        <v>100</v>
+        <v>60</v>
       </c>
       <c r="AB12" t="n">
-        <v>8.800000000000001</v>
+        <v>13</v>
       </c>
       <c r="AC12" t="n">
-        <v>8.4</v>
+        <v>9</v>
       </c>
       <c r="AD12" t="n">
-        <v>21</v>
+        <v>14.5</v>
       </c>
       <c r="AE12" t="n">
-        <v>80</v>
+        <v>36</v>
       </c>
       <c r="AF12" t="n">
-        <v>17.5</v>
+        <v>20</v>
       </c>
       <c r="AG12" t="n">
-        <v>15.5</v>
+        <v>13.5</v>
       </c>
       <c r="AH12" t="n">
-        <v>30</v>
+        <v>18.5</v>
       </c>
       <c r="AI12" t="n">
-        <v>120</v>
+        <v>55</v>
       </c>
       <c r="AJ12" t="n">
         <v>50</v>
       </c>
       <c r="AK12" t="n">
-        <v>48</v>
+        <v>32</v>
       </c>
       <c r="AL12" t="n">
-        <v>90</v>
+        <v>44</v>
       </c>
       <c r="AM12" t="n">
-        <v>260</v>
+        <v>100</v>
       </c>
       <c r="AN12" t="n">
-        <v>55</v>
+        <v>25</v>
       </c>
       <c r="AO12" t="n">
-        <v>120</v>
+        <v>29</v>
       </c>
       <c r="AP12" t="n">
-        <v>3</v>
+        <v>4.5</v>
       </c>
       <c r="AQ12" t="n">
-        <v>3.2</v>
+        <v>4.3</v>
       </c>
       <c r="AR12" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="AS12" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="AT12" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="AU12" t="n">
         <v>3.85</v>
       </c>
-      <c r="AS12" t="n">
+      <c r="AV12" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="AW12" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="AX12" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="AY12" t="n">
         <v>4.2</v>
       </c>
-      <c r="AT12" t="n">
-        <v>2.96</v>
-      </c>
-      <c r="AU12" t="n">
-        <v>2.9</v>
-      </c>
-      <c r="AV12" t="n">
-        <v>3.65</v>
-      </c>
-      <c r="AW12" t="n">
+      <c r="AZ12" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="BA12" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="BB12" t="n">
+        <v>5.3</v>
+      </c>
+      <c r="BC12" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="BD12" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="BE12" t="n">
+        <v>5.6</v>
+      </c>
+      <c r="BF12" t="n">
+        <v>5</v>
+      </c>
+      <c r="BG12" t="n">
+        <v>5</v>
+      </c>
+      <c r="BH12" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="BI12" t="n">
+        <v>2.82</v>
+      </c>
+      <c r="BJ12" t="n">
+        <v>10</v>
+      </c>
+      <c r="BK12" t="n">
         <v>4.2</v>
       </c>
-      <c r="AX12" t="n">
-        <v>3.55</v>
-      </c>
-      <c r="AY12" t="n">
+      <c r="BL12" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BM12" t="n">
+        <v>7</v>
+      </c>
+      <c r="BN12" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="BO12" t="n">
+        <v>3.35</v>
+      </c>
+      <c r="BP12" t="n">
+        <v>22</v>
+      </c>
+      <c r="BQ12" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="BR12" t="n">
+        <v>34</v>
+      </c>
+      <c r="BS12" t="n">
+        <v>6</v>
+      </c>
+      <c r="BT12" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="BU12" t="n">
         <v>3.45</v>
       </c>
-      <c r="AZ12" t="n">
-        <v>3.85</v>
-      </c>
-      <c r="BA12" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="BB12" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="BC12" t="n">
-        <v>4</v>
-      </c>
-      <c r="BD12" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="BE12" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="BF12" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="BG12" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="BH12" t="n">
-        <v>2.68</v>
-      </c>
-      <c r="BI12" t="n">
-        <v>2.34</v>
-      </c>
-      <c r="BJ12" t="n">
-        <v>12</v>
-      </c>
-      <c r="BK12" t="n">
-        <v>5.9</v>
-      </c>
-      <c r="BL12" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BM12" t="n">
-        <v>2.16</v>
-      </c>
-      <c r="BN12" t="n">
-        <v>5.3</v>
-      </c>
-      <c r="BO12" t="n">
-        <v>3.65</v>
-      </c>
-      <c r="BP12" t="n">
+      <c r="BV12" t="n">
         <v>24</v>
       </c>
-      <c r="BQ12" t="n">
-        <v>2</v>
-      </c>
-      <c r="BR12" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BS12" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="BT12" t="n">
-        <v>6.8</v>
-      </c>
-      <c r="BU12" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="BV12" t="n">
-        <v>1000</v>
-      </c>
       <c r="BW12" t="n">
-        <v>2.06</v>
+        <v>5.6</v>
       </c>
       <c r="BX12" t="n">
         <v>1000</v>
       </c>
       <c r="BY12" t="n">
-        <v>2.12</v>
+        <v>6</v>
       </c>
       <c r="BZ12" t="n">
-        <v>1000</v>
+        <v>27</v>
       </c>
       <c r="CA12" t="n">
-        <v>2.1</v>
+        <v>5.8</v>
       </c>
       <c r="CB12" t="inlineStr">
         <is>
-          <t>2026-06-11 11:32:36</t>
+          <t>2026-06-11 13:45:41</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Moroccan Botola Pro 1</t>
+          <t>Lithuanian A Lyga</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -3642,246 +3642,246 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>DHJ El Jadida</t>
+          <t>VMFD Zalgiris</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Olympique Dcheira</t>
+          <t>Riteriai</t>
         </is>
       </c>
       <c r="F13" t="n">
-        <v>2.34</v>
+        <v>1.14</v>
       </c>
       <c r="G13" t="n">
-        <v>2.6</v>
+        <v>1.18</v>
       </c>
       <c r="H13" t="n">
-        <v>3.65</v>
+        <v>21</v>
       </c>
       <c r="I13" t="n">
-        <v>4.7</v>
+        <v>32</v>
       </c>
       <c r="J13" t="n">
-        <v>2.86</v>
+        <v>9.4</v>
       </c>
       <c r="K13" t="n">
-        <v>2.9</v>
+        <v>11.5</v>
       </c>
       <c r="L13" t="n">
-        <v>1.5</v>
+        <v>1.19</v>
       </c>
       <c r="M13" t="n">
-        <v>1.14</v>
+        <v>1.02</v>
       </c>
       <c r="N13" t="n">
-        <v>2.44</v>
+        <v>7.2</v>
       </c>
       <c r="O13" t="n">
-        <v>1.58</v>
+        <v>1.12</v>
       </c>
       <c r="P13" t="n">
-        <v>1.48</v>
+        <v>3.1</v>
       </c>
       <c r="Q13" t="n">
-        <v>2.72</v>
+        <v>1.37</v>
       </c>
       <c r="R13" t="n">
-        <v>1.18</v>
+        <v>1.85</v>
       </c>
       <c r="S13" t="n">
+        <v>1.94</v>
+      </c>
+      <c r="T13" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="U13" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="V13" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="W13" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="X13" t="n">
+        <v>950</v>
+      </c>
+      <c r="Y13" t="n">
+        <v>950</v>
+      </c>
+      <c r="Z13" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AA13" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AB13" t="n">
+        <v>970</v>
+      </c>
+      <c r="AC13" t="n">
+        <v>950</v>
+      </c>
+      <c r="AD13" t="n">
+        <v>950</v>
+      </c>
+      <c r="AE13" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AF13" t="n">
+        <v>10</v>
+      </c>
+      <c r="AG13" t="n">
+        <v>17</v>
+      </c>
+      <c r="AH13" t="n">
+        <v>950</v>
+      </c>
+      <c r="AI13" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AJ13" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="AK13" t="n">
+        <v>17.5</v>
+      </c>
+      <c r="AL13" t="n">
+        <v>60</v>
+      </c>
+      <c r="AM13" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AN13" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="AO13" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AP13" t="n">
+        <v>5</v>
+      </c>
+      <c r="AQ13" t="n">
+        <v>5.3</v>
+      </c>
+      <c r="AR13" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="AS13" t="n">
+        <v>5.6</v>
+      </c>
+      <c r="AT13" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="AU13" t="n">
+        <v>18</v>
+      </c>
+      <c r="AV13" t="n">
+        <v>5.3</v>
+      </c>
+      <c r="AW13" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="AX13" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="AY13" t="n">
+        <v>11</v>
+      </c>
+      <c r="AZ13" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="BA13" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="BB13" t="n">
+        <v>7</v>
+      </c>
+      <c r="BC13" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="BD13" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="BE13" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="BF13" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="BG13" t="n">
+        <v>5.6</v>
+      </c>
+      <c r="BH13" t="n">
         <v>5.7</v>
       </c>
-      <c r="T13" t="n">
-        <v>2.16</v>
-      </c>
-      <c r="U13" t="n">
-        <v>1.72</v>
-      </c>
-      <c r="V13" t="n">
-        <v>1.29</v>
-      </c>
-      <c r="W13" t="n">
-        <v>1.62</v>
-      </c>
-      <c r="X13" t="n">
-        <v>9.6</v>
-      </c>
-      <c r="Y13" t="n">
+      <c r="BI13" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="BJ13" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BK13" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="BL13" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BM13" t="n">
         <v>10</v>
       </c>
-      <c r="Z13" t="n">
-        <v>26</v>
-      </c>
-      <c r="AA13" t="n">
-        <v>110</v>
-      </c>
-      <c r="AB13" t="n">
+      <c r="BN13" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="BO13" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="BP13" t="n">
+        <v>5.9</v>
+      </c>
+      <c r="BQ13" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="BR13" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BS13" t="n">
         <v>7.4</v>
       </c>
-      <c r="AC13" t="n">
-        <v>7.2</v>
-      </c>
-      <c r="AD13" t="n">
-        <v>17.5</v>
-      </c>
-      <c r="AE13" t="n">
-        <v>80</v>
-      </c>
-      <c r="AF13" t="n">
-        <v>14.5</v>
-      </c>
-      <c r="AG13" t="n">
-        <v>15.5</v>
-      </c>
-      <c r="AH13" t="n">
-        <v>30</v>
-      </c>
-      <c r="AI13" t="n">
-        <v>120</v>
-      </c>
-      <c r="AJ13" t="n">
-        <v>40</v>
-      </c>
-      <c r="AK13" t="n">
-        <v>46</v>
-      </c>
-      <c r="AL13" t="n">
-        <v>85</v>
-      </c>
-      <c r="AM13" t="n">
-        <v>260</v>
-      </c>
-      <c r="AN13" t="n">
-        <v>50</v>
-      </c>
-      <c r="AO13" t="n">
-        <v>120</v>
-      </c>
-      <c r="AP13" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="AQ13" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="AR13" t="n">
-        <v>5.6</v>
-      </c>
-      <c r="AS13" t="n">
-        <v>6.6</v>
-      </c>
-      <c r="AT13" t="n">
-        <v>3.65</v>
-      </c>
-      <c r="AU13" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="AV13" t="n">
-        <v>5.1</v>
-      </c>
-      <c r="AW13" t="n">
-        <v>6.6</v>
-      </c>
-      <c r="AX13" t="n">
-        <v>4.8</v>
-      </c>
-      <c r="AY13" t="n">
-        <v>4.9</v>
-      </c>
-      <c r="AZ13" t="n">
-        <v>5.8</v>
-      </c>
-      <c r="BA13" t="n">
-        <v>6.6</v>
-      </c>
-      <c r="BB13" t="n">
-        <v>6</v>
-      </c>
-      <c r="BC13" t="n">
-        <v>6.2</v>
-      </c>
-      <c r="BD13" t="n">
-        <v>6.6</v>
-      </c>
-      <c r="BE13" t="n">
-        <v>7</v>
-      </c>
-      <c r="BF13" t="n">
-        <v>6.2</v>
-      </c>
-      <c r="BG13" t="n">
-        <v>6.6</v>
-      </c>
-      <c r="BH13" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BI13" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="BJ13" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BK13" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="BL13" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BM13" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="BN13" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BO13" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="BP13" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BQ13" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="BR13" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BS13" t="n">
-        <v>1.04</v>
-      </c>
       <c r="BT13" t="n">
         <v>1000</v>
       </c>
       <c r="BU13" t="n">
-        <v>1.04</v>
+        <v>7.4</v>
       </c>
       <c r="BV13" t="n">
         <v>1000</v>
       </c>
       <c r="BW13" t="n">
-        <v>1.04</v>
+        <v>10</v>
       </c>
       <c r="BX13" t="n">
         <v>1000</v>
       </c>
       <c r="BY13" t="n">
-        <v>1.04</v>
+        <v>10</v>
       </c>
       <c r="BZ13" t="n">
-        <v>1000</v>
+        <v>6.8</v>
       </c>
       <c r="CA13" t="n">
-        <v>1.04</v>
+        <v>5.2</v>
       </c>
       <c r="CB13" t="inlineStr">
         <is>
-          <t>2026-06-11 11:32:36</t>
+          <t>2026-06-11 13:45:41</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Swedish Division 1</t>
+          <t>Georgian Umaglesi Liga</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -3896,246 +3896,246 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>Umea FC</t>
+          <t>Dinamo Batumi</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Pitea</t>
+          <t>Dila Gori</t>
         </is>
       </c>
       <c r="F14" t="n">
-        <v>1.46</v>
+        <v>3.95</v>
       </c>
       <c r="G14" t="n">
-        <v>1.66</v>
+        <v>5</v>
       </c>
       <c r="H14" t="n">
-        <v>5</v>
+        <v>1.87</v>
       </c>
       <c r="I14" t="n">
-        <v>7.4</v>
+        <v>2.06</v>
       </c>
       <c r="J14" t="n">
-        <v>3.8</v>
+        <v>3.4</v>
       </c>
       <c r="K14" t="n">
-        <v>5.8</v>
+        <v>3.9</v>
       </c>
       <c r="L14" t="n">
-        <v>1.23</v>
+        <v>1.01</v>
       </c>
       <c r="M14" t="n">
-        <v>1.01</v>
+        <v>1.06</v>
       </c>
       <c r="N14" t="n">
-        <v>3.45</v>
+        <v>3.4</v>
       </c>
       <c r="O14" t="n">
-        <v>1.16</v>
+        <v>1.32</v>
       </c>
       <c r="P14" t="n">
-        <v>2.32</v>
+        <v>1.31</v>
       </c>
       <c r="Q14" t="n">
-        <v>1.47</v>
+        <v>1.92</v>
       </c>
       <c r="R14" t="n">
-        <v>1.58</v>
+        <v>1.31</v>
       </c>
       <c r="S14" t="n">
-        <v>2.1</v>
+        <v>1.07</v>
       </c>
       <c r="T14" t="n">
-        <v>1.62</v>
+        <v>1.11</v>
       </c>
       <c r="U14" t="n">
-        <v>2.14</v>
+        <v>1.11</v>
       </c>
       <c r="V14" t="n">
-        <v>1.15</v>
+        <v>1.94</v>
       </c>
       <c r="W14" t="n">
-        <v>2.5</v>
+        <v>1.26</v>
       </c>
       <c r="X14" t="n">
-        <v>34</v>
+        <v>16</v>
       </c>
       <c r="Y14" t="n">
-        <v>950</v>
+        <v>10.5</v>
       </c>
       <c r="Z14" t="n">
-        <v>70</v>
+        <v>14.5</v>
       </c>
       <c r="AA14" t="n">
-        <v>190</v>
+        <v>28</v>
       </c>
       <c r="AB14" t="n">
-        <v>970</v>
+        <v>18.5</v>
       </c>
       <c r="AC14" t="n">
-        <v>14</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AD14" t="n">
-        <v>30</v>
+        <v>12.5</v>
       </c>
       <c r="AE14" t="n">
-        <v>90</v>
+        <v>27</v>
       </c>
       <c r="AF14" t="n">
-        <v>970</v>
+        <v>42</v>
       </c>
       <c r="AG14" t="n">
-        <v>13</v>
+        <v>23</v>
       </c>
       <c r="AH14" t="n">
-        <v>950</v>
+        <v>24</v>
       </c>
       <c r="AI14" t="n">
-        <v>75</v>
+        <v>48</v>
       </c>
       <c r="AJ14" t="n">
-        <v>970</v>
+        <v>130</v>
       </c>
       <c r="AK14" t="n">
-        <v>18</v>
+        <v>80</v>
       </c>
       <c r="AL14" t="n">
-        <v>34</v>
+        <v>85</v>
       </c>
       <c r="AM14" t="n">
+        <v>150</v>
+      </c>
+      <c r="AN14" t="n">
         <v>95</v>
       </c>
-      <c r="AN14" t="n">
-        <v>7</v>
-      </c>
       <c r="AO14" t="n">
-        <v>80</v>
+        <v>18.5</v>
       </c>
       <c r="AP14" t="n">
-        <v>3.8</v>
+        <v>3.4</v>
       </c>
       <c r="AQ14" t="n">
-        <v>3.8</v>
+        <v>3.1</v>
       </c>
       <c r="AR14" t="n">
-        <v>4</v>
+        <v>3.35</v>
       </c>
       <c r="AS14" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="AT14" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="AU14" t="n">
+        <v>3.05</v>
+      </c>
+      <c r="AV14" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="AW14" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="AX14" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="AY14" t="n">
+        <v>3.65</v>
+      </c>
+      <c r="AZ14" t="n">
+        <v>3.65</v>
+      </c>
+      <c r="BA14" t="n">
+        <v>3.95</v>
+      </c>
+      <c r="BB14" t="n">
         <v>4.2</v>
       </c>
-      <c r="AT14" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="AU14" t="n">
-        <v>3.25</v>
-      </c>
-      <c r="AV14" t="n">
-        <v>3.75</v>
-      </c>
-      <c r="AW14" t="n">
+      <c r="BC14" t="n">
         <v>4.1</v>
       </c>
-      <c r="AX14" t="n">
-        <v>3.25</v>
-      </c>
-      <c r="AY14" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="AZ14" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="BA14" t="n">
-        <v>4</v>
-      </c>
-      <c r="BB14" t="n">
-        <v>3.45</v>
-      </c>
-      <c r="BC14" t="n">
-        <v>3.45</v>
-      </c>
       <c r="BD14" t="n">
-        <v>3.8</v>
+        <v>4.1</v>
       </c>
       <c r="BE14" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="BF14" t="n">
         <v>4.1</v>
       </c>
-      <c r="BF14" t="n">
-        <v>2.66</v>
-      </c>
       <c r="BG14" t="n">
-        <v>4</v>
+        <v>3.5</v>
       </c>
       <c r="BH14" t="n">
-        <v>5</v>
+        <v>1000</v>
       </c>
       <c r="BI14" t="n">
-        <v>2.86</v>
+        <v>1.04</v>
       </c>
       <c r="BJ14" t="n">
         <v>1000</v>
       </c>
       <c r="BK14" t="n">
-        <v>4.1</v>
+        <v>1.04</v>
       </c>
       <c r="BL14" t="n">
         <v>1000</v>
       </c>
       <c r="BM14" t="n">
-        <v>6.2</v>
+        <v>1.04</v>
       </c>
       <c r="BN14" t="n">
-        <v>4.9</v>
+        <v>1000</v>
       </c>
       <c r="BO14" t="n">
-        <v>2.82</v>
+        <v>1.04</v>
       </c>
       <c r="BP14" t="n">
         <v>1000</v>
       </c>
       <c r="BQ14" t="n">
-        <v>4</v>
+        <v>1.04</v>
       </c>
       <c r="BR14" t="n">
         <v>1000</v>
       </c>
       <c r="BS14" t="n">
-        <v>5.1</v>
+        <v>1.04</v>
       </c>
       <c r="BT14" t="n">
         <v>1000</v>
       </c>
       <c r="BU14" t="n">
-        <v>4.1</v>
+        <v>1.04</v>
       </c>
       <c r="BV14" t="n">
         <v>1000</v>
       </c>
       <c r="BW14" t="n">
-        <v>5.9</v>
+        <v>1.04</v>
       </c>
       <c r="BX14" t="n">
         <v>1000</v>
       </c>
       <c r="BY14" t="n">
-        <v>5.9</v>
+        <v>1.04</v>
       </c>
       <c r="BZ14" t="n">
         <v>1000</v>
       </c>
       <c r="CA14" t="n">
-        <v>4.4</v>
+        <v>1.04</v>
       </c>
       <c r="CB14" t="inlineStr">
         <is>
-          <t>2026-06-11 11:32:36</t>
+          <t>2026-06-11 13:45:41</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Swedish Division 1</t>
+          <t>Moroccan Botola Pro 1</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -4150,246 +4150,246 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>Lunds BK</t>
+          <t>CODM Meknes</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Ariana FC</t>
+          <t>Club R Zemamra</t>
         </is>
       </c>
       <c r="F15" t="n">
-        <v>2.38</v>
+        <v>2.48</v>
       </c>
       <c r="G15" t="n">
-        <v>2.94</v>
+        <v>2.78</v>
       </c>
       <c r="H15" t="n">
-        <v>2.6</v>
+        <v>3.3</v>
       </c>
       <c r="I15" t="n">
-        <v>3.25</v>
+        <v>3.9</v>
       </c>
       <c r="J15" t="n">
+        <v>2.78</v>
+      </c>
+      <c r="K15" t="n">
         <v>3.2</v>
       </c>
-      <c r="K15" t="n">
+      <c r="L15" t="n">
+        <v>1.52</v>
+      </c>
+      <c r="M15" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="N15" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="O15" t="n">
+        <v>1.59</v>
+      </c>
+      <c r="P15" t="n">
+        <v>1.46</v>
+      </c>
+      <c r="Q15" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="R15" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="S15" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="T15" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="U15" t="n">
+        <v>1.68</v>
+      </c>
+      <c r="V15" t="n">
+        <v>1.34</v>
+      </c>
+      <c r="W15" t="n">
+        <v>1.56</v>
+      </c>
+      <c r="X15" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="Y15" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="Z15" t="n">
+        <v>28</v>
+      </c>
+      <c r="AA15" t="n">
+        <v>100</v>
+      </c>
+      <c r="AB15" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="AC15" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="AD15" t="n">
+        <v>20</v>
+      </c>
+      <c r="AE15" t="n">
+        <v>80</v>
+      </c>
+      <c r="AF15" t="n">
+        <v>18</v>
+      </c>
+      <c r="AG15" t="n">
+        <v>16</v>
+      </c>
+      <c r="AH15" t="n">
+        <v>32</v>
+      </c>
+      <c r="AI15" t="n">
+        <v>120</v>
+      </c>
+      <c r="AJ15" t="n">
+        <v>55</v>
+      </c>
+      <c r="AK15" t="n">
+        <v>50</v>
+      </c>
+      <c r="AL15" t="n">
+        <v>90</v>
+      </c>
+      <c r="AM15" t="n">
+        <v>270</v>
+      </c>
+      <c r="AN15" t="n">
+        <v>60</v>
+      </c>
+      <c r="AO15" t="n">
+        <v>120</v>
+      </c>
+      <c r="AP15" t="n">
+        <v>5.7</v>
+      </c>
+      <c r="AQ15" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="AR15" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="AS15" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="AT15" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="AU15" t="n">
+        <v>5.9</v>
+      </c>
+      <c r="AV15" t="n">
+        <v>12</v>
+      </c>
+      <c r="AW15" t="n">
         <v>4.1</v>
       </c>
-      <c r="L15" t="n">
-        <v>1.35</v>
-      </c>
-      <c r="M15" t="n">
-        <v>1.06</v>
-      </c>
-      <c r="N15" t="n">
-        <v>3.35</v>
-      </c>
-      <c r="O15" t="n">
-        <v>1.27</v>
-      </c>
-      <c r="P15" t="n">
-        <v>1.9</v>
-      </c>
-      <c r="Q15" t="n">
-        <v>1.79</v>
-      </c>
-      <c r="R15" t="n">
-        <v>1.35</v>
-      </c>
-      <c r="S15" t="n">
-        <v>3</v>
-      </c>
-      <c r="T15" t="n">
-        <v>1.65</v>
-      </c>
-      <c r="U15" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="V15" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="W15" t="n">
-        <v>1.51</v>
-      </c>
-      <c r="X15" t="n">
-        <v>19</v>
-      </c>
-      <c r="Y15" t="n">
-        <v>14</v>
-      </c>
-      <c r="Z15" t="n">
-        <v>23</v>
-      </c>
-      <c r="AA15" t="n">
-        <v>60</v>
-      </c>
-      <c r="AB15" t="n">
-        <v>13</v>
-      </c>
-      <c r="AC15" t="n">
-        <v>9</v>
-      </c>
-      <c r="AD15" t="n">
-        <v>14.5</v>
-      </c>
-      <c r="AE15" t="n">
-        <v>36</v>
-      </c>
-      <c r="AF15" t="n">
-        <v>20</v>
-      </c>
-      <c r="AG15" t="n">
-        <v>13.5</v>
-      </c>
-      <c r="AH15" t="n">
-        <v>18.5</v>
-      </c>
-      <c r="AI15" t="n">
-        <v>55</v>
-      </c>
-      <c r="AJ15" t="n">
-        <v>50</v>
-      </c>
-      <c r="AK15" t="n">
-        <v>32</v>
-      </c>
-      <c r="AL15" t="n">
-        <v>44</v>
-      </c>
-      <c r="AM15" t="n">
-        <v>100</v>
-      </c>
-      <c r="AN15" t="n">
+      <c r="AX15" t="n">
+        <v>11</v>
+      </c>
+      <c r="AY15" t="n">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="AZ15" t="n">
+        <v>18</v>
+      </c>
+      <c r="BA15" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="BB15" t="n">
+        <v>30</v>
+      </c>
+      <c r="BC15" t="n">
+        <v>4</v>
+      </c>
+      <c r="BD15" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="BE15" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="BF15" t="n">
+        <v>34</v>
+      </c>
+      <c r="BG15" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="BH15" t="n">
+        <v>2.64</v>
+      </c>
+      <c r="BI15" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="BJ15" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="BK15" t="n">
+        <v>5.8</v>
+      </c>
+      <c r="BL15" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BM15" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="BN15" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="BO15" t="n">
+        <v>4</v>
+      </c>
+      <c r="BP15" t="n">
         <v>25</v>
       </c>
-      <c r="AO15" t="n">
-        <v>29</v>
-      </c>
-      <c r="AP15" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="AQ15" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="AR15" t="n">
-        <v>4.7</v>
-      </c>
-      <c r="AS15" t="n">
-        <v>5.4</v>
-      </c>
-      <c r="AT15" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="AU15" t="n">
-        <v>6.2</v>
-      </c>
-      <c r="AV15" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="AW15" t="n">
-        <v>5.2</v>
-      </c>
-      <c r="AX15" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="AY15" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="AZ15" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="BA15" t="n">
-        <v>5.4</v>
-      </c>
-      <c r="BB15" t="n">
-        <v>5.3</v>
-      </c>
-      <c r="BC15" t="n">
-        <v>5</v>
-      </c>
-      <c r="BD15" t="n">
-        <v>5.4</v>
-      </c>
-      <c r="BE15" t="n">
-        <v>5.7</v>
-      </c>
-      <c r="BF15" t="n">
-        <v>4.8</v>
-      </c>
-      <c r="BG15" t="n">
+      <c r="BQ15" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="BR15" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BS15" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="BT15" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="BU15" t="n">
         <v>4.9</v>
       </c>
-      <c r="BH15" t="n">
-        <v>3.8</v>
-      </c>
-      <c r="BI15" t="n">
-        <v>2.82</v>
-      </c>
-      <c r="BJ15" t="n">
-        <v>10</v>
-      </c>
-      <c r="BK15" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="BL15" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BM15" t="n">
-        <v>7</v>
-      </c>
-      <c r="BN15" t="n">
-        <v>6.2</v>
-      </c>
-      <c r="BO15" t="n">
-        <v>3.35</v>
-      </c>
-      <c r="BP15" t="n">
-        <v>22</v>
-      </c>
-      <c r="BQ15" t="n">
-        <v>5.5</v>
-      </c>
-      <c r="BR15" t="n">
-        <v>34</v>
-      </c>
-      <c r="BS15" t="n">
-        <v>6</v>
-      </c>
-      <c r="BT15" t="n">
-        <v>6.6</v>
-      </c>
-      <c r="BU15" t="n">
-        <v>3.45</v>
-      </c>
       <c r="BV15" t="n">
-        <v>24</v>
+        <v>1000</v>
       </c>
       <c r="BW15" t="n">
-        <v>5.6</v>
+        <v>8.6</v>
       </c>
       <c r="BX15" t="n">
         <v>1000</v>
       </c>
       <c r="BY15" t="n">
-        <v>6</v>
+        <v>9.4</v>
       </c>
       <c r="BZ15" t="n">
-        <v>27</v>
+        <v>1000</v>
       </c>
       <c r="CA15" t="n">
-        <v>5.8</v>
+        <v>9.4</v>
       </c>
       <c r="CB15" t="inlineStr">
         <is>
-          <t>2026-06-11 11:32:36</t>
+          <t>2026-06-11 13:45:41</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Argentinian Primera C</t>
+          <t>Irish Premier Division</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -4399,72 +4399,72 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>15:30:00</t>
+          <t>15:45:00</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>CD Cambaceres</t>
+          <t>Galway Utd</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>AD Berazategui</t>
+          <t>Dundalk</t>
         </is>
       </c>
       <c r="F16" t="n">
-        <v>1.09</v>
+        <v>2.82</v>
       </c>
       <c r="G16" t="n">
-        <v>1000</v>
+        <v>3.15</v>
       </c>
       <c r="H16" t="n">
-        <v>1.73</v>
+        <v>2.4</v>
       </c>
       <c r="I16" t="n">
-        <v>1000</v>
+        <v>2.56</v>
       </c>
       <c r="J16" t="n">
-        <v>1.29</v>
+        <v>3.65</v>
       </c>
       <c r="K16" t="n">
-        <v>3.25</v>
+        <v>4.1</v>
       </c>
       <c r="L16" t="n">
         <v>1.01</v>
       </c>
       <c r="M16" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="N16" t="n">
-        <v>1.24</v>
+        <v>4.8</v>
       </c>
       <c r="O16" t="n">
-        <v>1.01</v>
+        <v>1.22</v>
       </c>
       <c r="P16" t="n">
-        <v>1.24</v>
+        <v>2.36</v>
       </c>
       <c r="Q16" t="n">
-        <v>1.01</v>
+        <v>1.47</v>
       </c>
       <c r="R16" t="n">
-        <v>1.12</v>
+        <v>1.39</v>
       </c>
       <c r="S16" t="n">
-        <v>1.51</v>
+        <v>2.16</v>
       </c>
       <c r="T16" t="n">
-        <v>1.11</v>
+        <v>1.6</v>
       </c>
       <c r="U16" t="n">
-        <v>1.11</v>
+        <v>2.44</v>
       </c>
       <c r="V16" t="n">
-        <v>1.02</v>
+        <v>1.64</v>
       </c>
       <c r="W16" t="n">
-        <v>1.02</v>
+        <v>1.47</v>
       </c>
       <c r="X16" t="n">
         <v>1000</v>
@@ -4629,21 +4629,21 @@
         <v>1.04</v>
       </c>
       <c r="BZ16" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="CA16" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="CB16" t="inlineStr">
         <is>
-          <t>2026-06-11 11:32:36</t>
+          <t>2026-06-11 13:45:41</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Irish Division 1</t>
+          <t>Irish Premier Division</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -4658,175 +4658,175 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>Finn Harps</t>
+          <t>St Patricks</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>UCD</t>
+          <t>Drogheda</t>
         </is>
       </c>
       <c r="F17" t="n">
-        <v>3.6</v>
+        <v>1.37</v>
       </c>
       <c r="G17" t="n">
-        <v>5.4</v>
+        <v>1.41</v>
       </c>
       <c r="H17" t="n">
-        <v>1.89</v>
+        <v>10.5</v>
       </c>
       <c r="I17" t="n">
-        <v>2.34</v>
+        <v>12</v>
       </c>
       <c r="J17" t="n">
-        <v>3.25</v>
+        <v>5</v>
       </c>
       <c r="K17" t="n">
-        <v>5.2</v>
+        <v>5.5</v>
       </c>
       <c r="L17" t="n">
         <v>1.01</v>
       </c>
       <c r="M17" t="n">
-        <v>1.02</v>
+        <v>1.06</v>
       </c>
       <c r="N17" t="n">
+        <v>4</v>
+      </c>
+      <c r="O17" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="P17" t="n">
+        <v>2.06</v>
+      </c>
+      <c r="Q17" t="n">
+        <v>1.84</v>
+      </c>
+      <c r="R17" t="n">
+        <v>1.39</v>
+      </c>
+      <c r="S17" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="T17" t="n">
+        <v>2.24</v>
+      </c>
+      <c r="U17" t="n">
+        <v>1.74</v>
+      </c>
+      <c r="V17" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="W17" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="X17" t="n">
+        <v>22</v>
+      </c>
+      <c r="Y17" t="n">
+        <v>38</v>
+      </c>
+      <c r="Z17" t="n">
+        <v>130</v>
+      </c>
+      <c r="AA17" t="n">
+        <v>610</v>
+      </c>
+      <c r="AB17" t="n">
+        <v>9</v>
+      </c>
+      <c r="AC17" t="n">
+        <v>15</v>
+      </c>
+      <c r="AD17" t="n">
+        <v>50</v>
+      </c>
+      <c r="AE17" t="n">
+        <v>270</v>
+      </c>
+      <c r="AF17" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="AG17" t="n">
+        <v>13</v>
+      </c>
+      <c r="AH17" t="n">
+        <v>40</v>
+      </c>
+      <c r="AI17" t="n">
+        <v>210</v>
+      </c>
+      <c r="AJ17" t="n">
+        <v>13</v>
+      </c>
+      <c r="AK17" t="n">
+        <v>19.5</v>
+      </c>
+      <c r="AL17" t="n">
+        <v>55</v>
+      </c>
+      <c r="AM17" t="n">
+        <v>270</v>
+      </c>
+      <c r="AN17" t="n">
+        <v>8</v>
+      </c>
+      <c r="AO17" t="n">
+        <v>440</v>
+      </c>
+      <c r="AP17" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="AQ17" t="n">
+        <v>3.95</v>
+      </c>
+      <c r="AR17" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="AS17" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="AT17" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="AU17" t="n">
+        <v>9</v>
+      </c>
+      <c r="AV17" t="n">
+        <v>4</v>
+      </c>
+      <c r="AW17" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="AX17" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="AY17" t="n">
+        <v>9</v>
+      </c>
+      <c r="AZ17" t="n">
+        <v>4</v>
+      </c>
+      <c r="BA17" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="BB17" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="BC17" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="BD17" t="n">
         <v>4.1</v>
       </c>
-      <c r="O17" t="n">
-        <v>1.23</v>
-      </c>
-      <c r="P17" t="n">
-        <v>1.95</v>
-      </c>
-      <c r="Q17" t="n">
-        <v>1.64</v>
-      </c>
-      <c r="R17" t="n">
-        <v>1.32</v>
-      </c>
-      <c r="S17" t="n">
-        <v>2.32</v>
-      </c>
-      <c r="T17" t="n">
-        <v>1.37</v>
-      </c>
-      <c r="U17" t="n">
-        <v>1.73</v>
-      </c>
-      <c r="V17" t="n">
-        <v>1.75</v>
-      </c>
-      <c r="W17" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="X17" t="n">
-        <v>1000</v>
-      </c>
-      <c r="Y17" t="n">
-        <v>1000</v>
-      </c>
-      <c r="Z17" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AA17" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AB17" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AC17" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AD17" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AE17" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AF17" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AG17" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AH17" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AI17" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AJ17" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AK17" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AL17" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AM17" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AN17" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AO17" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AP17" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="AQ17" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="AR17" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="AS17" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="AT17" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="AU17" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="AV17" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="AW17" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="AX17" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="AY17" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="AZ17" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BA17" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BB17" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BC17" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BD17" t="n">
-        <v>1.01</v>
-      </c>
       <c r="BE17" t="n">
-        <v>1.01</v>
+        <v>4.3</v>
       </c>
       <c r="BF17" t="n">
-        <v>1.01</v>
+        <v>5</v>
       </c>
       <c r="BG17" t="n">
-        <v>1.01</v>
+        <v>4.4</v>
       </c>
       <c r="BH17" t="n">
         <v>1000</v>
@@ -4838,66 +4838,66 @@
         <v>1000</v>
       </c>
       <c r="BK17" t="n">
-        <v>1.04</v>
+        <v>1.58</v>
       </c>
       <c r="BL17" t="n">
         <v>1000</v>
       </c>
       <c r="BM17" t="n">
-        <v>1.04</v>
+        <v>1.72</v>
       </c>
       <c r="BN17" t="n">
         <v>1000</v>
       </c>
       <c r="BO17" t="n">
-        <v>1.04</v>
+        <v>1.3</v>
       </c>
       <c r="BP17" t="n">
         <v>1000</v>
       </c>
       <c r="BQ17" t="n">
-        <v>1.04</v>
+        <v>1.5</v>
       </c>
       <c r="BR17" t="n">
         <v>1000</v>
       </c>
       <c r="BS17" t="n">
-        <v>1.04</v>
+        <v>1.65</v>
       </c>
       <c r="BT17" t="n">
         <v>1000</v>
       </c>
       <c r="BU17" t="n">
-        <v>1.04</v>
+        <v>1.59</v>
       </c>
       <c r="BV17" t="n">
         <v>1000</v>
       </c>
       <c r="BW17" t="n">
-        <v>1.04</v>
+        <v>1.72</v>
       </c>
       <c r="BX17" t="n">
         <v>1000</v>
       </c>
       <c r="BY17" t="n">
-        <v>1.04</v>
+        <v>1.72</v>
       </c>
       <c r="BZ17" t="n">
         <v>1000</v>
       </c>
       <c r="CA17" t="n">
-        <v>1.04</v>
+        <v>1.6</v>
       </c>
       <c r="CB17" t="inlineStr">
         <is>
-          <t>2026-06-11 11:32:36</t>
+          <t>2026-06-11 13:45:41</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Irish Division 1</t>
+          <t>Irish Premier Division</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -4912,34 +4912,34 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>Kerry FC</t>
+          <t>Derry City</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Athlone Town</t>
+          <t>Bohemians</t>
         </is>
       </c>
       <c r="F18" t="n">
-        <v>2.3</v>
+        <v>3.15</v>
       </c>
       <c r="G18" t="n">
-        <v>2.5</v>
+        <v>3.45</v>
       </c>
       <c r="H18" t="n">
-        <v>3.35</v>
+        <v>2.46</v>
       </c>
       <c r="I18" t="n">
-        <v>3.75</v>
+        <v>2.62</v>
       </c>
       <c r="J18" t="n">
-        <v>3.15</v>
+        <v>3.25</v>
       </c>
       <c r="K18" t="n">
         <v>3.45</v>
       </c>
       <c r="L18" t="n">
-        <v>1.4</v>
+        <v>1.46</v>
       </c>
       <c r="M18" t="n">
         <v>1.09</v>
@@ -4948,142 +4948,142 @@
         <v>3.05</v>
       </c>
       <c r="O18" t="n">
-        <v>1.41</v>
+        <v>1.4</v>
       </c>
       <c r="P18" t="n">
-        <v>1.71</v>
+        <v>1.7</v>
       </c>
       <c r="Q18" t="n">
         <v>2.2</v>
       </c>
       <c r="R18" t="n">
-        <v>1.26</v>
+        <v>1.25</v>
       </c>
       <c r="S18" t="n">
         <v>4.1</v>
       </c>
       <c r="T18" t="n">
-        <v>1.89</v>
+        <v>1.9</v>
       </c>
       <c r="U18" t="n">
         <v>1.96</v>
       </c>
       <c r="V18" t="n">
-        <v>1.37</v>
+        <v>1.61</v>
       </c>
       <c r="W18" t="n">
-        <v>1.66</v>
+        <v>1.41</v>
       </c>
       <c r="X18" t="n">
-        <v>13.5</v>
+        <v>12</v>
       </c>
       <c r="Y18" t="n">
-        <v>14</v>
+        <v>9.6</v>
       </c>
       <c r="Z18" t="n">
-        <v>30</v>
+        <v>16.5</v>
       </c>
       <c r="AA18" t="n">
+        <v>50</v>
+      </c>
+      <c r="AB18" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="AC18" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="AD18" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="AE18" t="n">
+        <v>46</v>
+      </c>
+      <c r="AF18" t="n">
+        <v>23</v>
+      </c>
+      <c r="AG18" t="n">
+        <v>15</v>
+      </c>
+      <c r="AH18" t="n">
+        <v>21</v>
+      </c>
+      <c r="AI18" t="n">
+        <v>70</v>
+      </c>
+      <c r="AJ18" t="n">
         <v>85</v>
       </c>
-      <c r="AB18" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="AC18" t="n">
-        <v>9</v>
-      </c>
-      <c r="AD18" t="n">
-        <v>18.5</v>
-      </c>
-      <c r="AE18" t="n">
-        <v>60</v>
-      </c>
-      <c r="AF18" t="n">
-        <v>18</v>
-      </c>
-      <c r="AG18" t="n">
-        <v>14</v>
-      </c>
-      <c r="AH18" t="n">
-        <v>24</v>
-      </c>
-      <c r="AI18" t="n">
-        <v>75</v>
-      </c>
-      <c r="AJ18" t="n">
-        <v>42</v>
-      </c>
       <c r="AK18" t="n">
-        <v>36</v>
+        <v>65</v>
       </c>
       <c r="AL18" t="n">
-        <v>60</v>
+        <v>85</v>
       </c>
       <c r="AM18" t="n">
         <v>150</v>
       </c>
       <c r="AN18" t="n">
+        <v>70</v>
+      </c>
+      <c r="AO18" t="n">
         <v>32</v>
       </c>
-      <c r="AO18" t="n">
-        <v>70</v>
-      </c>
       <c r="AP18" t="n">
-        <v>8.199999999999999</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AQ18" t="n">
-        <v>8.4</v>
+        <v>7.8</v>
       </c>
       <c r="AR18" t="n">
-        <v>17.5</v>
+        <v>13</v>
       </c>
       <c r="AS18" t="n">
-        <v>4.1</v>
+        <v>25</v>
       </c>
       <c r="AT18" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="AU18" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="AV18" t="n">
+        <v>10</v>
+      </c>
+      <c r="AW18" t="n">
+        <v>22</v>
+      </c>
+      <c r="AX18" t="n">
+        <v>18</v>
+      </c>
+      <c r="AY18" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="AZ18" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="BA18" t="n">
+        <v>34</v>
+      </c>
+      <c r="BB18" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="BC18" t="n">
+        <v>30</v>
+      </c>
+      <c r="BD18" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="BE18" t="n">
+        <v>8</v>
+      </c>
+      <c r="BF18" t="n">
+        <v>34</v>
+      </c>
+      <c r="BG18" t="n">
         <v>6.6</v>
       </c>
-      <c r="AU18" t="n">
-        <v>5.6</v>
-      </c>
-      <c r="AV18" t="n">
-        <v>11</v>
-      </c>
-      <c r="AW18" t="n">
-        <v>4</v>
-      </c>
-      <c r="AX18" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="AY18" t="n">
-        <v>8.6</v>
-      </c>
-      <c r="AZ18" t="n">
-        <v>14</v>
-      </c>
-      <c r="BA18" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="BB18" t="n">
-        <v>3.9</v>
-      </c>
-      <c r="BC18" t="n">
-        <v>21</v>
-      </c>
-      <c r="BD18" t="n">
-        <v>4</v>
-      </c>
-      <c r="BE18" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="BF18" t="n">
-        <v>19</v>
-      </c>
-      <c r="BG18" t="n">
-        <v>4</v>
-      </c>
       <c r="BH18" t="n">
-        <v>3.1</v>
+        <v>3.15</v>
       </c>
       <c r="BI18" t="n">
         <v>2.56</v>
@@ -5092,66 +5092,66 @@
         <v>10.5</v>
       </c>
       <c r="BK18" t="n">
-        <v>6</v>
+        <v>5.3</v>
       </c>
       <c r="BL18" t="n">
         <v>1000</v>
       </c>
       <c r="BM18" t="n">
-        <v>13.5</v>
+        <v>10</v>
       </c>
       <c r="BN18" t="n">
-        <v>5.1</v>
+        <v>6.6</v>
       </c>
       <c r="BO18" t="n">
-        <v>3.9</v>
+        <v>5</v>
       </c>
       <c r="BP18" t="n">
         <v>1000</v>
       </c>
       <c r="BQ18" t="n">
-        <v>8.199999999999999</v>
+        <v>7.8</v>
       </c>
       <c r="BR18" t="n">
         <v>1000</v>
       </c>
       <c r="BS18" t="n">
-        <v>10.5</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BT18" t="n">
-        <v>6.6</v>
+        <v>5.5</v>
       </c>
       <c r="BU18" t="n">
-        <v>5</v>
+        <v>4.2</v>
       </c>
       <c r="BV18" t="n">
-        <v>1000</v>
+        <v>21</v>
       </c>
       <c r="BW18" t="n">
-        <v>10</v>
+        <v>7.2</v>
       </c>
       <c r="BX18" t="n">
         <v>1000</v>
       </c>
       <c r="BY18" t="n">
-        <v>11</v>
+        <v>8.4</v>
       </c>
       <c r="BZ18" t="n">
         <v>1000</v>
       </c>
       <c r="CA18" t="n">
-        <v>10.5</v>
+        <v>8.4</v>
       </c>
       <c r="CB18" t="inlineStr">
         <is>
-          <t>2026-06-11 11:32:36</t>
+          <t>2026-06-11 13:45:41</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Irish Division 1</t>
+          <t>Irish Premier Division</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -5166,175 +5166,175 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>Treaty United</t>
+          <t>Waterford</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Bray Wanderers</t>
+          <t>Sligo Rovers</t>
         </is>
       </c>
       <c r="F19" t="n">
-        <v>3.9</v>
+        <v>2.2</v>
       </c>
       <c r="G19" t="n">
-        <v>4.6</v>
+        <v>2.36</v>
       </c>
       <c r="H19" t="n">
-        <v>1.87</v>
+        <v>3.2</v>
       </c>
       <c r="I19" t="n">
-        <v>2.04</v>
+        <v>3.6</v>
       </c>
       <c r="J19" t="n">
-        <v>3.65</v>
+        <v>3.5</v>
       </c>
       <c r="K19" t="n">
-        <v>4.3</v>
+        <v>3.85</v>
       </c>
       <c r="L19" t="n">
-        <v>1.01</v>
+        <v>1.29</v>
       </c>
       <c r="M19" t="n">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="N19" t="n">
-        <v>4.4</v>
+        <v>3.95</v>
       </c>
       <c r="O19" t="n">
-        <v>1.23</v>
+        <v>1.28</v>
       </c>
       <c r="P19" t="n">
-        <v>2.18</v>
+        <v>2.02</v>
       </c>
       <c r="Q19" t="n">
-        <v>1.71</v>
+        <v>1.83</v>
       </c>
       <c r="R19" t="n">
-        <v>1.52</v>
+        <v>1.4</v>
       </c>
       <c r="S19" t="n">
-        <v>2.54</v>
+        <v>3.1</v>
       </c>
       <c r="T19" t="n">
-        <v>1.64</v>
+        <v>1.69</v>
       </c>
       <c r="U19" t="n">
-        <v>2.28</v>
+        <v>2.22</v>
       </c>
       <c r="V19" t="n">
-        <v>1.96</v>
+        <v>1.39</v>
       </c>
       <c r="W19" t="n">
-        <v>1.27</v>
+        <v>1.73</v>
       </c>
       <c r="X19" t="n">
-        <v>21</v>
+        <v>19.5</v>
       </c>
       <c r="Y19" t="n">
+        <v>15</v>
+      </c>
+      <c r="Z19" t="n">
+        <v>36</v>
+      </c>
+      <c r="AA19" t="n">
+        <v>75</v>
+      </c>
+      <c r="AB19" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="AC19" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="AD19" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="AE19" t="n">
+        <v>50</v>
+      </c>
+      <c r="AF19" t="n">
+        <v>16</v>
+      </c>
+      <c r="AG19" t="n">
         <v>12</v>
       </c>
-      <c r="Z19" t="n">
-        <v>14.5</v>
-      </c>
-      <c r="AA19" t="n">
-        <v>27</v>
-      </c>
-      <c r="AB19" t="n">
-        <v>19</v>
-      </c>
-      <c r="AC19" t="n">
-        <v>9.800000000000001</v>
-      </c>
-      <c r="AD19" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="AE19" t="n">
-        <v>18.5</v>
-      </c>
-      <c r="AF19" t="n">
-        <v>36</v>
-      </c>
-      <c r="AG19" t="n">
-        <v>23</v>
-      </c>
       <c r="AH19" t="n">
-        <v>16.5</v>
+        <v>17.5</v>
       </c>
       <c r="AI19" t="n">
-        <v>30</v>
+        <v>60</v>
       </c>
       <c r="AJ19" t="n">
-        <v>110</v>
+        <v>32</v>
       </c>
       <c r="AK19" t="n">
-        <v>46</v>
+        <v>25</v>
       </c>
       <c r="AL19" t="n">
+        <v>50</v>
+      </c>
+      <c r="AM19" t="n">
+        <v>100</v>
+      </c>
+      <c r="AN19" t="n">
+        <v>17.5</v>
+      </c>
+      <c r="AO19" t="n">
         <v>48</v>
       </c>
-      <c r="AM19" t="n">
-        <v>95</v>
-      </c>
-      <c r="AN19" t="n">
-        <v>40</v>
-      </c>
-      <c r="AO19" t="n">
+      <c r="AP19" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="AQ19" t="n">
         <v>10.5</v>
       </c>
-      <c r="AP19" t="n">
-        <v>16</v>
-      </c>
-      <c r="AQ19" t="n">
+      <c r="AR19" t="n">
+        <v>20</v>
+      </c>
+      <c r="AS19" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="AT19" t="n">
         <v>9.4</v>
       </c>
-      <c r="AR19" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="AS19" t="n">
-        <v>18.5</v>
-      </c>
-      <c r="AT19" t="n">
-        <v>15.5</v>
-      </c>
       <c r="AU19" t="n">
-        <v>7</v>
+        <v>7.2</v>
       </c>
       <c r="AV19" t="n">
-        <v>9.800000000000001</v>
+        <v>12</v>
       </c>
       <c r="AW19" t="n">
-        <v>14.5</v>
+        <v>24</v>
       </c>
       <c r="AX19" t="n">
-        <v>23</v>
+        <v>13</v>
       </c>
       <c r="AY19" t="n">
-        <v>16</v>
+        <v>9.6</v>
       </c>
       <c r="AZ19" t="n">
+        <v>14</v>
+      </c>
+      <c r="BA19" t="n">
+        <v>32</v>
+      </c>
+      <c r="BB19" t="n">
+        <v>22</v>
+      </c>
+      <c r="BC19" t="n">
+        <v>20</v>
+      </c>
+      <c r="BD19" t="n">
+        <v>25</v>
+      </c>
+      <c r="BE19" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="BF19" t="n">
         <v>13.5</v>
       </c>
-      <c r="BA19" t="n">
-        <v>21</v>
-      </c>
-      <c r="BB19" t="n">
-        <v>7.4</v>
-      </c>
-      <c r="BC19" t="n">
-        <v>32</v>
-      </c>
-      <c r="BD19" t="n">
-        <v>30</v>
-      </c>
-      <c r="BE19" t="n">
-        <v>7.2</v>
-      </c>
-      <c r="BF19" t="n">
-        <v>27</v>
-      </c>
       <c r="BG19" t="n">
-        <v>7.2</v>
+        <v>24</v>
       </c>
       <c r="BH19" t="n">
         <v>1000</v>
@@ -5346,19 +5346,19 @@
         <v>1000</v>
       </c>
       <c r="BK19" t="n">
-        <v>1.54</v>
+        <v>1.04</v>
       </c>
       <c r="BL19" t="n">
         <v>1000</v>
       </c>
       <c r="BM19" t="n">
-        <v>1.73</v>
+        <v>1.04</v>
       </c>
       <c r="BN19" t="n">
         <v>1000</v>
       </c>
       <c r="BO19" t="n">
-        <v>1.51</v>
+        <v>1.04</v>
       </c>
       <c r="BP19" t="n">
         <v>1000</v>
@@ -5376,29 +5376,29 @@
         <v>1000</v>
       </c>
       <c r="BU19" t="n">
-        <v>1.4</v>
+        <v>1.04</v>
       </c>
       <c r="BV19" t="n">
         <v>1000</v>
       </c>
       <c r="BW19" t="n">
-        <v>1.59</v>
+        <v>1.04</v>
       </c>
       <c r="BX19" t="n">
         <v>1000</v>
       </c>
       <c r="BY19" t="n">
-        <v>1.66</v>
+        <v>1.04</v>
       </c>
       <c r="BZ19" t="n">
         <v>1000</v>
       </c>
       <c r="CA19" t="n">
-        <v>1.62</v>
+        <v>1.04</v>
       </c>
       <c r="CB19" t="inlineStr">
         <is>
-          <t>2026-06-11 11:32:36</t>
+          <t>2026-06-11 13:45:41</t>
         </is>
       </c>
     </row>
@@ -5420,175 +5420,175 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>Wexford F.C</t>
+          <t>Treaty United</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Cork City</t>
+          <t>Bray Wanderers</t>
         </is>
       </c>
       <c r="F20" t="n">
-        <v>4.2</v>
+        <v>3.95</v>
       </c>
       <c r="G20" t="n">
-        <v>5</v>
+        <v>4.6</v>
       </c>
       <c r="H20" t="n">
-        <v>1.85</v>
+        <v>1.87</v>
       </c>
       <c r="I20" t="n">
         <v>2.02</v>
       </c>
       <c r="J20" t="n">
-        <v>3.5</v>
+        <v>3.65</v>
       </c>
       <c r="K20" t="n">
-        <v>3.9</v>
+        <v>4.3</v>
       </c>
       <c r="L20" t="n">
-        <v>1.31</v>
+        <v>1.01</v>
       </c>
       <c r="M20" t="n">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="N20" t="n">
-        <v>3.6</v>
+        <v>4.4</v>
       </c>
       <c r="O20" t="n">
-        <v>1.3</v>
+        <v>1.23</v>
       </c>
       <c r="P20" t="n">
-        <v>1.94</v>
+        <v>2.18</v>
       </c>
       <c r="Q20" t="n">
-        <v>1.89</v>
+        <v>1.71</v>
       </c>
       <c r="R20" t="n">
-        <v>1.35</v>
+        <v>1.52</v>
       </c>
       <c r="S20" t="n">
-        <v>3.3</v>
+        <v>2.54</v>
       </c>
       <c r="T20" t="n">
-        <v>1.79</v>
+        <v>1.64</v>
       </c>
       <c r="U20" t="n">
-        <v>2.02</v>
+        <v>2.28</v>
       </c>
       <c r="V20" t="n">
         <v>1.98</v>
       </c>
       <c r="W20" t="n">
-        <v>1.25</v>
+        <v>1.28</v>
       </c>
       <c r="X20" t="n">
-        <v>15.5</v>
+        <v>21</v>
       </c>
       <c r="Y20" t="n">
-        <v>9.4</v>
+        <v>12</v>
       </c>
       <c r="Z20" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="AA20" t="n">
+        <v>27</v>
+      </c>
+      <c r="AB20" t="n">
+        <v>19</v>
+      </c>
+      <c r="AC20" t="n">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="AD20" t="n">
         <v>12.5</v>
       </c>
-      <c r="AA20" t="n">
-        <v>23</v>
-      </c>
-      <c r="AB20" t="n">
-        <v>17</v>
-      </c>
-      <c r="AC20" t="n">
-        <v>9</v>
-      </c>
-      <c r="AD20" t="n">
-        <v>11</v>
-      </c>
       <c r="AE20" t="n">
-        <v>22</v>
+        <v>18.5</v>
       </c>
       <c r="AF20" t="n">
         <v>36</v>
       </c>
       <c r="AG20" t="n">
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="AH20" t="n">
-        <v>20</v>
+        <v>16.5</v>
       </c>
       <c r="AI20" t="n">
-        <v>38</v>
+        <v>30</v>
       </c>
       <c r="AJ20" t="n">
-        <v>120</v>
+        <v>110</v>
       </c>
       <c r="AK20" t="n">
-        <v>65</v>
+        <v>46</v>
       </c>
       <c r="AL20" t="n">
-        <v>75</v>
+        <v>48</v>
       </c>
       <c r="AM20" t="n">
-        <v>120</v>
+        <v>95</v>
       </c>
       <c r="AN20" t="n">
-        <v>85</v>
+        <v>40</v>
       </c>
       <c r="AO20" t="n">
-        <v>14</v>
+        <v>10.5</v>
       </c>
       <c r="AP20" t="n">
-        <v>11</v>
+        <v>16</v>
       </c>
       <c r="AQ20" t="n">
-        <v>7.6</v>
+        <v>9.4</v>
       </c>
       <c r="AR20" t="n">
-        <v>10</v>
+        <v>11.5</v>
       </c>
       <c r="AS20" t="n">
-        <v>18</v>
+        <v>18.5</v>
       </c>
       <c r="AT20" t="n">
-        <v>13.5</v>
+        <v>15.5</v>
       </c>
       <c r="AU20" t="n">
-        <v>7.2</v>
+        <v>7</v>
       </c>
       <c r="AV20" t="n">
-        <v>8.800000000000001</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AW20" t="n">
-        <v>17</v>
+        <v>14.5</v>
       </c>
       <c r="AX20" t="n">
         <v>23</v>
       </c>
       <c r="AY20" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AZ20" t="n">
-        <v>16</v>
+        <v>13.5</v>
       </c>
       <c r="BA20" t="n">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="BB20" t="n">
-        <v>8.4</v>
+        <v>7.4</v>
       </c>
       <c r="BC20" t="n">
-        <v>7.8</v>
+        <v>32</v>
       </c>
       <c r="BD20" t="n">
-        <v>8</v>
+        <v>30</v>
       </c>
       <c r="BE20" t="n">
-        <v>8.4</v>
+        <v>7.2</v>
       </c>
       <c r="BF20" t="n">
-        <v>42</v>
+        <v>27</v>
       </c>
       <c r="BG20" t="n">
-        <v>11</v>
+        <v>7.2</v>
       </c>
       <c r="BH20" t="n">
         <v>1000</v>
@@ -5600,19 +5600,19 @@
         <v>1000</v>
       </c>
       <c r="BK20" t="n">
-        <v>1.04</v>
+        <v>1.54</v>
       </c>
       <c r="BL20" t="n">
         <v>1000</v>
       </c>
       <c r="BM20" t="n">
-        <v>1.04</v>
+        <v>1.73</v>
       </c>
       <c r="BN20" t="n">
         <v>1000</v>
       </c>
       <c r="BO20" t="n">
-        <v>1.04</v>
+        <v>1.51</v>
       </c>
       <c r="BP20" t="n">
         <v>1000</v>
@@ -5630,36 +5630,36 @@
         <v>1000</v>
       </c>
       <c r="BU20" t="n">
-        <v>1.04</v>
+        <v>1.4</v>
       </c>
       <c r="BV20" t="n">
         <v>1000</v>
       </c>
       <c r="BW20" t="n">
-        <v>1.04</v>
+        <v>1.59</v>
       </c>
       <c r="BX20" t="n">
         <v>1000</v>
       </c>
       <c r="BY20" t="n">
-        <v>1.04</v>
+        <v>1.66</v>
       </c>
       <c r="BZ20" t="n">
         <v>1000</v>
       </c>
       <c r="CA20" t="n">
-        <v>1.04</v>
+        <v>1.62</v>
       </c>
       <c r="CB20" t="inlineStr">
         <is>
-          <t>2026-06-11 11:32:36</t>
+          <t>2026-06-11 13:45:41</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Irish Premier Division</t>
+          <t>Irish Division 1</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -5674,34 +5674,34 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>Derry City</t>
+          <t>Kerry FC</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Bohemians</t>
+          <t>Athlone Town</t>
         </is>
       </c>
       <c r="F21" t="n">
-        <v>3.1</v>
+        <v>2.28</v>
       </c>
       <c r="G21" t="n">
-        <v>3.55</v>
+        <v>2.5</v>
       </c>
       <c r="H21" t="n">
-        <v>2.42</v>
+        <v>3.35</v>
       </c>
       <c r="I21" t="n">
-        <v>2.64</v>
+        <v>3.75</v>
       </c>
       <c r="J21" t="n">
-        <v>3.25</v>
+        <v>3.15</v>
       </c>
       <c r="K21" t="n">
-        <v>3.55</v>
+        <v>3.45</v>
       </c>
       <c r="L21" t="n">
-        <v>1.46</v>
+        <v>1.48</v>
       </c>
       <c r="M21" t="n">
         <v>1.09</v>
@@ -5710,142 +5710,142 @@
         <v>3.1</v>
       </c>
       <c r="O21" t="n">
-        <v>1.4</v>
+        <v>1.41</v>
       </c>
       <c r="P21" t="n">
         <v>1.71</v>
       </c>
       <c r="Q21" t="n">
-        <v>2.16</v>
+        <v>2.2</v>
       </c>
       <c r="R21" t="n">
         <v>1.26</v>
       </c>
       <c r="S21" t="n">
-        <v>4.2</v>
+        <v>3.65</v>
       </c>
       <c r="T21" t="n">
-        <v>1.87</v>
+        <v>1.89</v>
       </c>
       <c r="U21" t="n">
         <v>1.96</v>
       </c>
       <c r="V21" t="n">
-        <v>1.61</v>
+        <v>1.37</v>
       </c>
       <c r="W21" t="n">
-        <v>1.39</v>
+        <v>1.66</v>
       </c>
       <c r="X21" t="n">
         <v>13.5</v>
       </c>
       <c r="Y21" t="n">
-        <v>9.6</v>
+        <v>14</v>
       </c>
       <c r="Z21" t="n">
-        <v>16.5</v>
+        <v>30</v>
       </c>
       <c r="AA21" t="n">
-        <v>44</v>
+        <v>85</v>
       </c>
       <c r="AB21" t="n">
-        <v>11.5</v>
+        <v>10.5</v>
       </c>
       <c r="AC21" t="n">
-        <v>7.8</v>
+        <v>9</v>
       </c>
       <c r="AD21" t="n">
-        <v>12.5</v>
+        <v>18.5</v>
       </c>
       <c r="AE21" t="n">
-        <v>34</v>
+        <v>60</v>
       </c>
       <c r="AF21" t="n">
-        <v>23</v>
+        <v>17.5</v>
       </c>
       <c r="AG21" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="AH21" t="n">
+        <v>24</v>
+      </c>
+      <c r="AI21" t="n">
+        <v>75</v>
+      </c>
+      <c r="AJ21" t="n">
+        <v>42</v>
+      </c>
+      <c r="AK21" t="n">
+        <v>36</v>
+      </c>
+      <c r="AL21" t="n">
+        <v>60</v>
+      </c>
+      <c r="AM21" t="n">
+        <v>150</v>
+      </c>
+      <c r="AN21" t="n">
+        <v>32</v>
+      </c>
+      <c r="AO21" t="n">
+        <v>70</v>
+      </c>
+      <c r="AP21" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="AQ21" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="AR21" t="n">
+        <v>17.5</v>
+      </c>
+      <c r="AS21" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="AT21" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="AU21" t="n">
+        <v>5.6</v>
+      </c>
+      <c r="AV21" t="n">
+        <v>11</v>
+      </c>
+      <c r="AW21" t="n">
+        <v>4</v>
+      </c>
+      <c r="AX21" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AY21" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="AZ21" t="n">
+        <v>14</v>
+      </c>
+      <c r="BA21" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="BB21" t="n">
+        <v>3.95</v>
+      </c>
+      <c r="BC21" t="n">
         <v>21</v>
       </c>
-      <c r="AI21" t="n">
-        <v>60</v>
-      </c>
-      <c r="AJ21" t="n">
-        <v>80</v>
-      </c>
-      <c r="AK21" t="n">
-        <v>55</v>
-      </c>
-      <c r="AL21" t="n">
-        <v>80</v>
-      </c>
-      <c r="AM21" t="n">
-        <v>140</v>
-      </c>
-      <c r="AN21" t="n">
-        <v>60</v>
-      </c>
-      <c r="AO21" t="n">
-        <v>38</v>
-      </c>
-      <c r="AP21" t="n">
-        <v>9.6</v>
-      </c>
-      <c r="AQ21" t="n">
-        <v>7.8</v>
-      </c>
-      <c r="AR21" t="n">
-        <v>13</v>
-      </c>
-      <c r="AS21" t="n">
-        <v>29</v>
-      </c>
-      <c r="AT21" t="n">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="AU21" t="n">
-        <v>6.4</v>
-      </c>
-      <c r="AV21" t="n">
-        <v>10</v>
-      </c>
-      <c r="AW21" t="n">
-        <v>23</v>
-      </c>
-      <c r="AX21" t="n">
-        <v>18</v>
-      </c>
-      <c r="AY21" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="AZ21" t="n">
-        <v>16</v>
-      </c>
-      <c r="BA21" t="n">
-        <v>32</v>
-      </c>
-      <c r="BB21" t="n">
-        <v>7.2</v>
-      </c>
-      <c r="BC21" t="n">
-        <v>28</v>
-      </c>
       <c r="BD21" t="n">
-        <v>36</v>
+        <v>4</v>
       </c>
       <c r="BE21" t="n">
-        <v>7.6</v>
+        <v>4.2</v>
       </c>
       <c r="BF21" t="n">
-        <v>36</v>
+        <v>18.5</v>
       </c>
       <c r="BG21" t="n">
-        <v>22</v>
+        <v>4.1</v>
       </c>
       <c r="BH21" t="n">
-        <v>3.15</v>
+        <v>3.1</v>
       </c>
       <c r="BI21" t="n">
         <v>2.56</v>
@@ -5854,66 +5854,66 @@
         <v>10.5</v>
       </c>
       <c r="BK21" t="n">
-        <v>7.8</v>
+        <v>6</v>
       </c>
       <c r="BL21" t="n">
         <v>1000</v>
       </c>
       <c r="BM21" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="BN21" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="BO21" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="BP21" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BQ21" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="BR21" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BS21" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="BT21" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="BU21" t="n">
+        <v>5</v>
+      </c>
+      <c r="BV21" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BW21" t="n">
         <v>10</v>
       </c>
-      <c r="BN21" t="n">
-        <v>6.6</v>
-      </c>
-      <c r="BO21" t="n">
-        <v>5.4</v>
-      </c>
-      <c r="BP21" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BQ21" t="n">
-        <v>7.8</v>
-      </c>
-      <c r="BR21" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BS21" t="n">
-        <v>8.800000000000001</v>
-      </c>
-      <c r="BT21" t="n">
-        <v>5.5</v>
-      </c>
-      <c r="BU21" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="BV21" t="n">
-        <v>21</v>
-      </c>
-      <c r="BW21" t="n">
-        <v>7.2</v>
-      </c>
       <c r="BX21" t="n">
         <v>1000</v>
       </c>
       <c r="BY21" t="n">
-        <v>8.4</v>
+        <v>11</v>
       </c>
       <c r="BZ21" t="n">
         <v>1000</v>
       </c>
       <c r="CA21" t="n">
-        <v>8.4</v>
+        <v>10.5</v>
       </c>
       <c r="CB21" t="inlineStr">
         <is>
-          <t>2026-06-11 11:32:36</t>
+          <t>2026-06-11 13:45:41</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Irish Premier Division</t>
+          <t>Irish Division 1</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -5928,175 +5928,175 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>Waterford</t>
+          <t>Finn Harps</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Sligo Rovers</t>
+          <t>UCD</t>
         </is>
       </c>
       <c r="F22" t="n">
-        <v>2.2</v>
+        <v>3.6</v>
       </c>
       <c r="G22" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="H22" t="n">
+        <v>1.89</v>
+      </c>
+      <c r="I22" t="n">
         <v>2.34</v>
       </c>
-      <c r="H22" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="I22" t="n">
-        <v>3.6</v>
-      </c>
       <c r="J22" t="n">
-        <v>3.5</v>
+        <v>3.25</v>
       </c>
       <c r="K22" t="n">
-        <v>3.85</v>
+        <v>5.2</v>
       </c>
       <c r="L22" t="n">
-        <v>1.29</v>
+        <v>1.01</v>
       </c>
       <c r="M22" t="n">
-        <v>1.06</v>
+        <v>1.02</v>
       </c>
       <c r="N22" t="n">
-        <v>3.95</v>
+        <v>4.1</v>
       </c>
       <c r="O22" t="n">
-        <v>1.28</v>
+        <v>1.23</v>
       </c>
       <c r="P22" t="n">
-        <v>2.02</v>
+        <v>1.96</v>
       </c>
       <c r="Q22" t="n">
-        <v>1.81</v>
+        <v>1.64</v>
       </c>
       <c r="R22" t="n">
-        <v>1.39</v>
+        <v>1.32</v>
       </c>
       <c r="S22" t="n">
-        <v>3.1</v>
+        <v>2.32</v>
       </c>
       <c r="T22" t="n">
-        <v>1.67</v>
+        <v>1.37</v>
       </c>
       <c r="U22" t="n">
-        <v>2.18</v>
+        <v>1.73</v>
       </c>
       <c r="V22" t="n">
-        <v>1.39</v>
+        <v>1.75</v>
       </c>
       <c r="W22" t="n">
-        <v>1.74</v>
+        <v>1.22</v>
       </c>
       <c r="X22" t="n">
-        <v>20</v>
+        <v>1000</v>
       </c>
       <c r="Y22" t="n">
-        <v>17.5</v>
+        <v>1000</v>
       </c>
       <c r="Z22" t="n">
-        <v>36</v>
+        <v>1000</v>
       </c>
       <c r="AA22" t="n">
-        <v>75</v>
+        <v>1000</v>
       </c>
       <c r="AB22" t="n">
-        <v>11.5</v>
+        <v>1000</v>
       </c>
       <c r="AC22" t="n">
-        <v>8.800000000000001</v>
+        <v>1000</v>
       </c>
       <c r="AD22" t="n">
-        <v>15.5</v>
+        <v>1000</v>
       </c>
       <c r="AE22" t="n">
-        <v>50</v>
+        <v>1000</v>
       </c>
       <c r="AF22" t="n">
-        <v>16</v>
+        <v>1000</v>
       </c>
       <c r="AG22" t="n">
-        <v>12</v>
+        <v>1000</v>
       </c>
       <c r="AH22" t="n">
-        <v>17.5</v>
+        <v>1000</v>
       </c>
       <c r="AI22" t="n">
-        <v>60</v>
+        <v>1000</v>
       </c>
       <c r="AJ22" t="n">
-        <v>32</v>
+        <v>1000</v>
       </c>
       <c r="AK22" t="n">
-        <v>25</v>
+        <v>1000</v>
       </c>
       <c r="AL22" t="n">
-        <v>50</v>
+        <v>1000</v>
       </c>
       <c r="AM22" t="n">
-        <v>100</v>
+        <v>1000</v>
       </c>
       <c r="AN22" t="n">
-        <v>17</v>
+        <v>1000</v>
       </c>
       <c r="AO22" t="n">
-        <v>48</v>
+        <v>1000</v>
       </c>
       <c r="AP22" t="n">
-        <v>13.5</v>
+        <v>1.01</v>
       </c>
       <c r="AQ22" t="n">
-        <v>10.5</v>
+        <v>1.01</v>
       </c>
       <c r="AR22" t="n">
-        <v>21</v>
+        <v>1.01</v>
       </c>
       <c r="AS22" t="n">
-        <v>6.8</v>
+        <v>1.01</v>
       </c>
       <c r="AT22" t="n">
-        <v>9.4</v>
+        <v>1.01</v>
       </c>
       <c r="AU22" t="n">
-        <v>7.2</v>
+        <v>1.01</v>
       </c>
       <c r="AV22" t="n">
-        <v>12</v>
+        <v>1.01</v>
       </c>
       <c r="AW22" t="n">
-        <v>24</v>
+        <v>1.01</v>
       </c>
       <c r="AX22" t="n">
-        <v>13</v>
+        <v>1.01</v>
       </c>
       <c r="AY22" t="n">
-        <v>9.6</v>
+        <v>1.01</v>
       </c>
       <c r="AZ22" t="n">
-        <v>14</v>
+        <v>1.01</v>
       </c>
       <c r="BA22" t="n">
-        <v>32</v>
+        <v>1.01</v>
       </c>
       <c r="BB22" t="n">
-        <v>22</v>
+        <v>1.01</v>
       </c>
       <c r="BC22" t="n">
-        <v>19.5</v>
+        <v>1.01</v>
       </c>
       <c r="BD22" t="n">
-        <v>25</v>
+        <v>1.01</v>
       </c>
       <c r="BE22" t="n">
-        <v>7</v>
+        <v>1.01</v>
       </c>
       <c r="BF22" t="n">
-        <v>11.5</v>
+        <v>1.01</v>
       </c>
       <c r="BG22" t="n">
-        <v>6.2</v>
+        <v>1.01</v>
       </c>
       <c r="BH22" t="n">
         <v>1000</v>
@@ -6160,14 +6160,14 @@
       </c>
       <c r="CB22" t="inlineStr">
         <is>
-          <t>2026-06-11 11:32:36</t>
+          <t>2026-06-11 13:45:41</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Irish Premier Division</t>
+          <t>Irish Division 1</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -6182,175 +6182,175 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>St Patricks</t>
+          <t>Wexford F.C</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Drogheda</t>
+          <t>Cork City</t>
         </is>
       </c>
       <c r="F23" t="n">
-        <v>1.37</v>
+        <v>4.3</v>
       </c>
       <c r="G23" t="n">
-        <v>1.41</v>
+        <v>5.1</v>
       </c>
       <c r="H23" t="n">
-        <v>10.5</v>
+        <v>1.83</v>
       </c>
       <c r="I23" t="n">
-        <v>12</v>
+        <v>2</v>
       </c>
       <c r="J23" t="n">
-        <v>4.9</v>
+        <v>3.55</v>
       </c>
       <c r="K23" t="n">
-        <v>5.5</v>
+        <v>4.2</v>
       </c>
       <c r="L23" t="n">
-        <v>1.01</v>
+        <v>1.31</v>
       </c>
       <c r="M23" t="n">
         <v>1.06</v>
       </c>
       <c r="N23" t="n">
-        <v>4</v>
+        <v>3.7</v>
       </c>
       <c r="O23" t="n">
-        <v>1.28</v>
+        <v>1.3</v>
       </c>
       <c r="P23" t="n">
-        <v>2.06</v>
+        <v>1.91</v>
       </c>
       <c r="Q23" t="n">
-        <v>1.84</v>
+        <v>1.89</v>
       </c>
       <c r="R23" t="n">
-        <v>1.39</v>
+        <v>1.35</v>
       </c>
       <c r="S23" t="n">
-        <v>3.1</v>
+        <v>3.25</v>
       </c>
       <c r="T23" t="n">
-        <v>2.24</v>
+        <v>1.79</v>
       </c>
       <c r="U23" t="n">
-        <v>1.74</v>
+        <v>2.02</v>
       </c>
       <c r="V23" t="n">
-        <v>1.09</v>
+        <v>2</v>
       </c>
       <c r="W23" t="n">
-        <v>3.4</v>
+        <v>1.25</v>
       </c>
       <c r="X23" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="Y23" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="Z23" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="AA23" t="n">
+        <v>23</v>
+      </c>
+      <c r="AB23" t="n">
+        <v>17.5</v>
+      </c>
+      <c r="AC23" t="n">
+        <v>9</v>
+      </c>
+      <c r="AD23" t="n">
+        <v>11</v>
+      </c>
+      <c r="AE23" t="n">
         <v>21</v>
       </c>
-      <c r="Y23" t="n">
+      <c r="AF23" t="n">
         <v>38</v>
       </c>
-      <c r="Z23" t="n">
+      <c r="AG23" t="n">
+        <v>19.5</v>
+      </c>
+      <c r="AH23" t="n">
+        <v>20</v>
+      </c>
+      <c r="AI23" t="n">
+        <v>38</v>
+      </c>
+      <c r="AJ23" t="n">
         <v>130</v>
       </c>
-      <c r="AA23" t="n">
-        <v>600</v>
-      </c>
-      <c r="AB23" t="n">
+      <c r="AK23" t="n">
+        <v>65</v>
+      </c>
+      <c r="AL23" t="n">
+        <v>70</v>
+      </c>
+      <c r="AM23" t="n">
+        <v>120</v>
+      </c>
+      <c r="AN23" t="n">
+        <v>85</v>
+      </c>
+      <c r="AO23" t="n">
+        <v>14</v>
+      </c>
+      <c r="AP23" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="AQ23" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="AR23" t="n">
+        <v>10</v>
+      </c>
+      <c r="AS23" t="n">
+        <v>18</v>
+      </c>
+      <c r="AT23" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="AU23" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="AV23" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="AW23" t="n">
+        <v>17</v>
+      </c>
+      <c r="AX23" t="n">
+        <v>23</v>
+      </c>
+      <c r="AY23" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="AZ23" t="n">
+        <v>16</v>
+      </c>
+      <c r="BA23" t="n">
+        <v>24</v>
+      </c>
+      <c r="BB23" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="BC23" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="BD23" t="n">
         <v>7.8</v>
       </c>
-      <c r="AC23" t="n">
-        <v>14.5</v>
-      </c>
-      <c r="AD23" t="n">
-        <v>50</v>
-      </c>
-      <c r="AE23" t="n">
-        <v>260</v>
-      </c>
-      <c r="AF23" t="n">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="AG23" t="n">
-        <v>13</v>
-      </c>
-      <c r="AH23" t="n">
-        <v>40</v>
-      </c>
-      <c r="AI23" t="n">
-        <v>210</v>
-      </c>
-      <c r="AJ23" t="n">
-        <v>13.5</v>
-      </c>
-      <c r="AK23" t="n">
-        <v>19.5</v>
-      </c>
-      <c r="AL23" t="n">
-        <v>55</v>
-      </c>
-      <c r="AM23" t="n">
-        <v>260</v>
-      </c>
-      <c r="AN23" t="n">
-        <v>8</v>
-      </c>
-      <c r="AO23" t="n">
-        <v>430</v>
-      </c>
-      <c r="AP23" t="n">
-        <v>14.5</v>
-      </c>
-      <c r="AQ23" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="AR23" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="AS23" t="n">
-        <v>4.8</v>
-      </c>
-      <c r="AT23" t="n">
-        <v>6.4</v>
-      </c>
-      <c r="AU23" t="n">
-        <v>10</v>
-      </c>
-      <c r="AV23" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="AW23" t="n">
-        <v>4.7</v>
-      </c>
-      <c r="AX23" t="n">
-        <v>6.6</v>
-      </c>
-      <c r="AY23" t="n">
-        <v>9</v>
-      </c>
-      <c r="AZ23" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="BA23" t="n">
-        <v>4.7</v>
-      </c>
-      <c r="BB23" t="n">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="BC23" t="n">
-        <v>13.5</v>
-      </c>
-      <c r="BD23" t="n">
-        <v>4.4</v>
-      </c>
       <c r="BE23" t="n">
-        <v>4.7</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BF23" t="n">
-        <v>5.2</v>
+        <v>7.8</v>
       </c>
       <c r="BG23" t="n">
-        <v>4.8</v>
+        <v>11</v>
       </c>
       <c r="BH23" t="n">
         <v>1000</v>
@@ -6414,14 +6414,14 @@
       </c>
       <c r="CB23" t="inlineStr">
         <is>
-          <t>2026-06-11 11:32:36</t>
+          <t>2026-06-11 13:45:41</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Irish Premier Division</t>
+          <t>Bolivian Liga de Futbol Profesional</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -6431,72 +6431,72 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>15:45:00</t>
+          <t>16:00:00</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>Galway Utd</t>
+          <t>San Antonio Bulo Bulo</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Dundalk</t>
+          <t>Academia de Balompie Boli</t>
         </is>
       </c>
       <c r="F24" t="n">
-        <v>2.78</v>
+        <v>1.42</v>
       </c>
       <c r="G24" t="n">
-        <v>3.05</v>
+        <v>1.63</v>
       </c>
       <c r="H24" t="n">
-        <v>2.38</v>
+        <v>4.8</v>
       </c>
       <c r="I24" t="n">
-        <v>2.6</v>
+        <v>95</v>
       </c>
       <c r="J24" t="n">
-        <v>3.65</v>
+        <v>4.7</v>
       </c>
       <c r="K24" t="n">
-        <v>4.1</v>
+        <v>1000</v>
       </c>
       <c r="L24" t="n">
         <v>1.01</v>
       </c>
       <c r="M24" t="n">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="N24" t="n">
-        <v>4.8</v>
+        <v>1.99</v>
       </c>
       <c r="O24" t="n">
-        <v>1.2</v>
+        <v>1.09</v>
       </c>
       <c r="P24" t="n">
-        <v>2.36</v>
+        <v>1.98</v>
       </c>
       <c r="Q24" t="n">
-        <v>1.4</v>
+        <v>1.09</v>
       </c>
       <c r="R24" t="n">
-        <v>1.53</v>
+        <v>1.18</v>
       </c>
       <c r="S24" t="n">
-        <v>2.16</v>
+        <v>1.09</v>
       </c>
       <c r="T24" t="n">
-        <v>1.6</v>
+        <v>1.11</v>
       </c>
       <c r="U24" t="n">
-        <v>2.44</v>
+        <v>1.11</v>
       </c>
       <c r="V24" t="n">
-        <v>1.62</v>
+        <v>1.09</v>
       </c>
       <c r="W24" t="n">
-        <v>1.48</v>
+        <v>2.58</v>
       </c>
       <c r="X24" t="n">
         <v>1000</v>
@@ -6668,14 +6668,14 @@
       </c>
       <c r="CB24" t="inlineStr">
         <is>
-          <t>2026-06-11 11:32:36</t>
+          <t>2026-06-11 13:45:41</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Bolivian Liga de Futbol Profesional</t>
+          <t>Irish Premier Division</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -6690,175 +6690,175 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>San Antonio Bulo Bulo</t>
+          <t>Shelbourne</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Academia de Balompie Boli</t>
+          <t>Shamrock Rovers</t>
         </is>
       </c>
       <c r="F25" t="n">
-        <v>1.42</v>
+        <v>2.82</v>
       </c>
       <c r="G25" t="n">
-        <v>1.63</v>
+        <v>3</v>
       </c>
       <c r="H25" t="n">
+        <v>2.72</v>
+      </c>
+      <c r="I25" t="n">
+        <v>2.86</v>
+      </c>
+      <c r="J25" t="n">
+        <v>3.35</v>
+      </c>
+      <c r="K25" t="n">
+        <v>3.45</v>
+      </c>
+      <c r="L25" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="M25" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="N25" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="O25" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="P25" t="n">
+        <v>1.76</v>
+      </c>
+      <c r="Q25" t="n">
+        <v>2.16</v>
+      </c>
+      <c r="R25" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="S25" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="T25" t="n">
+        <v>1.86</v>
+      </c>
+      <c r="U25" t="n">
+        <v>2.04</v>
+      </c>
+      <c r="V25" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="W25" t="n">
+        <v>1.51</v>
+      </c>
+      <c r="X25" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="Y25" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="Z25" t="n">
+        <v>22</v>
+      </c>
+      <c r="AA25" t="n">
+        <v>55</v>
+      </c>
+      <c r="AB25" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="AC25" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="AD25" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="AE25" t="n">
+        <v>42</v>
+      </c>
+      <c r="AF25" t="n">
+        <v>23</v>
+      </c>
+      <c r="AG25" t="n">
+        <v>13</v>
+      </c>
+      <c r="AH25" t="n">
+        <v>23</v>
+      </c>
+      <c r="AI25" t="n">
+        <v>60</v>
+      </c>
+      <c r="AJ25" t="n">
+        <v>60</v>
+      </c>
+      <c r="AK25" t="n">
+        <v>44</v>
+      </c>
+      <c r="AL25" t="n">
+        <v>65</v>
+      </c>
+      <c r="AM25" t="n">
+        <v>140</v>
+      </c>
+      <c r="AN25" t="n">
+        <v>44</v>
+      </c>
+      <c r="AO25" t="n">
+        <v>42</v>
+      </c>
+      <c r="AP25" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="AQ25" t="n">
+        <v>9</v>
+      </c>
+      <c r="AR25" t="n">
+        <v>13</v>
+      </c>
+      <c r="AS25" t="n">
+        <v>36</v>
+      </c>
+      <c r="AT25" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="AU25" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="AV25" t="n">
+        <v>11</v>
+      </c>
+      <c r="AW25" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="AX25" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="AY25" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="AZ25" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="BA25" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="BB25" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="BC25" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="BD25" t="n">
         <v>4.8</v>
       </c>
-      <c r="I25" t="n">
-        <v>95</v>
-      </c>
-      <c r="J25" t="n">
+      <c r="BE25" t="n">
         <v>4.9</v>
       </c>
-      <c r="K25" t="n">
-        <v>1000</v>
-      </c>
-      <c r="L25" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="M25" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="N25" t="n">
-        <v>1.99</v>
-      </c>
-      <c r="O25" t="n">
-        <v>1.09</v>
-      </c>
-      <c r="P25" t="n">
-        <v>1.98</v>
-      </c>
-      <c r="Q25" t="n">
-        <v>1.09</v>
-      </c>
-      <c r="R25" t="n">
-        <v>1.18</v>
-      </c>
-      <c r="S25" t="n">
-        <v>1.09</v>
-      </c>
-      <c r="T25" t="n">
-        <v>1.11</v>
-      </c>
-      <c r="U25" t="n">
-        <v>1.11</v>
-      </c>
-      <c r="V25" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="W25" t="n">
-        <v>2.58</v>
-      </c>
-      <c r="X25" t="n">
-        <v>1000</v>
-      </c>
-      <c r="Y25" t="n">
-        <v>1000</v>
-      </c>
-      <c r="Z25" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AA25" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AB25" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AC25" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AD25" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AE25" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AF25" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AG25" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AH25" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AI25" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AJ25" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AK25" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AL25" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AM25" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AN25" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AO25" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AP25" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="AQ25" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="AR25" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="AS25" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="AT25" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="AU25" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="AV25" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="AW25" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="AX25" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="AY25" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="AZ25" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BA25" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BB25" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BC25" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BD25" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BE25" t="n">
-        <v>1.01</v>
-      </c>
       <c r="BF25" t="n">
-        <v>1.01</v>
+        <v>4.6</v>
       </c>
       <c r="BG25" t="n">
-        <v>1.01</v>
+        <v>4.4</v>
       </c>
       <c r="BH25" t="n">
         <v>1000</v>
@@ -6870,25 +6870,25 @@
         <v>1000</v>
       </c>
       <c r="BK25" t="n">
-        <v>1.04</v>
+        <v>1.48</v>
       </c>
       <c r="BL25" t="n">
         <v>1000</v>
       </c>
       <c r="BM25" t="n">
-        <v>1.04</v>
+        <v>1.65</v>
       </c>
       <c r="BN25" t="n">
         <v>1000</v>
       </c>
       <c r="BO25" t="n">
-        <v>1.04</v>
+        <v>1.39</v>
       </c>
       <c r="BP25" t="n">
         <v>1000</v>
       </c>
       <c r="BQ25" t="n">
-        <v>1.04</v>
+        <v>1.58</v>
       </c>
       <c r="BR25" t="n">
         <v>1000</v>
@@ -6900,13 +6900,13 @@
         <v>1000</v>
       </c>
       <c r="BU25" t="n">
-        <v>1.04</v>
+        <v>1.39</v>
       </c>
       <c r="BV25" t="n">
         <v>1000</v>
       </c>
       <c r="BW25" t="n">
-        <v>1.04</v>
+        <v>1.61</v>
       </c>
       <c r="BX25" t="n">
         <v>1000</v>
@@ -6922,14 +6922,14 @@
       </c>
       <c r="CB25" t="inlineStr">
         <is>
-          <t>2026-06-11 11:32:36</t>
+          <t>2026-06-11 13:45:41</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Irish Premier Division</t>
+          <t>Icelandic 1 Deild</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -6939,251 +6939,251 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>16:00:00</t>
+          <t>16:15:00</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>Shelbourne</t>
+          <t>Throttur</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Shamrock Rovers</t>
+          <t>HK Kopavogur</t>
         </is>
       </c>
       <c r="F26" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="G26" t="n">
+        <v>1.88</v>
+      </c>
+      <c r="H26" t="n">
+        <v>3.85</v>
+      </c>
+      <c r="I26" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="J26" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="K26" t="n">
+        <v>5.3</v>
+      </c>
+      <c r="L26" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="M26" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="N26" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="O26" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="P26" t="n">
+        <v>3.15</v>
+      </c>
+      <c r="Q26" t="n">
+        <v>1.37</v>
+      </c>
+      <c r="R26" t="n">
+        <v>1.87</v>
+      </c>
+      <c r="S26" t="n">
+        <v>1.92</v>
+      </c>
+      <c r="T26" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="U26" t="n">
         <v>2.82</v>
       </c>
-      <c r="G26" t="n">
-        <v>3</v>
-      </c>
-      <c r="H26" t="n">
-        <v>2.72</v>
-      </c>
-      <c r="I26" t="n">
-        <v>2.9</v>
-      </c>
-      <c r="J26" t="n">
-        <v>3.35</v>
-      </c>
-      <c r="K26" t="n">
-        <v>3.45</v>
-      </c>
-      <c r="L26" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="M26" t="n">
-        <v>1.09</v>
-      </c>
-      <c r="N26" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="O26" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="P26" t="n">
-        <v>1.76</v>
-      </c>
-      <c r="Q26" t="n">
-        <v>2.16</v>
-      </c>
-      <c r="R26" t="n">
+      <c r="V26" t="n">
         <v>1.28</v>
       </c>
-      <c r="S26" t="n">
-        <v>4</v>
-      </c>
-      <c r="T26" t="n">
-        <v>1.86</v>
-      </c>
-      <c r="U26" t="n">
-        <v>2.04</v>
-      </c>
-      <c r="V26" t="n">
-        <v>1.53</v>
-      </c>
       <c r="W26" t="n">
-        <v>1.5</v>
+        <v>2.12</v>
       </c>
       <c r="X26" t="n">
-        <v>14.5</v>
+        <v>48</v>
       </c>
       <c r="Y26" t="n">
+        <v>36</v>
+      </c>
+      <c r="Z26" t="n">
+        <v>50</v>
+      </c>
+      <c r="AA26" t="n">
+        <v>95</v>
+      </c>
+      <c r="AB26" t="n">
+        <v>22</v>
+      </c>
+      <c r="AC26" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="AD26" t="n">
+        <v>23</v>
+      </c>
+      <c r="AE26" t="n">
+        <v>48</v>
+      </c>
+      <c r="AF26" t="n">
+        <v>21</v>
+      </c>
+      <c r="AG26" t="n">
+        <v>14</v>
+      </c>
+      <c r="AH26" t="n">
+        <v>16</v>
+      </c>
+      <c r="AI26" t="n">
+        <v>44</v>
+      </c>
+      <c r="AJ26" t="n">
+        <v>27</v>
+      </c>
+      <c r="AK26" t="n">
+        <v>20</v>
+      </c>
+      <c r="AL26" t="n">
+        <v>27</v>
+      </c>
+      <c r="AM26" t="n">
+        <v>60</v>
+      </c>
+      <c r="AN26" t="n">
+        <v>7</v>
+      </c>
+      <c r="AO26" t="n">
+        <v>27</v>
+      </c>
+      <c r="AP26" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="AQ26" t="n">
+        <v>21</v>
+      </c>
+      <c r="AR26" t="n">
+        <v>32</v>
+      </c>
+      <c r="AS26" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="AT26" t="n">
+        <v>13</v>
+      </c>
+      <c r="AU26" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AV26" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="AW26" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="AX26" t="n">
         <v>12.5</v>
       </c>
-      <c r="Z26" t="n">
-        <v>22</v>
-      </c>
-      <c r="AA26" t="n">
-        <v>55</v>
-      </c>
-      <c r="AB26" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="AC26" t="n">
-        <v>7.6</v>
-      </c>
-      <c r="AD26" t="n">
-        <v>15.5</v>
-      </c>
-      <c r="AE26" t="n">
-        <v>42</v>
-      </c>
-      <c r="AF26" t="n">
-        <v>23</v>
-      </c>
-      <c r="AG26" t="n">
-        <v>13</v>
-      </c>
-      <c r="AH26" t="n">
-        <v>23</v>
-      </c>
-      <c r="AI26" t="n">
-        <v>60</v>
-      </c>
-      <c r="AJ26" t="n">
-        <v>60</v>
-      </c>
-      <c r="AK26" t="n">
-        <v>44</v>
-      </c>
-      <c r="AL26" t="n">
-        <v>65</v>
-      </c>
-      <c r="AM26" t="n">
-        <v>140</v>
-      </c>
-      <c r="AN26" t="n">
-        <v>44</v>
-      </c>
-      <c r="AO26" t="n">
-        <v>42</v>
-      </c>
-      <c r="AP26" t="n">
-        <v>10</v>
-      </c>
-      <c r="AQ26" t="n">
-        <v>9</v>
-      </c>
-      <c r="AR26" t="n">
-        <v>13</v>
-      </c>
-      <c r="AS26" t="n">
-        <v>36</v>
-      </c>
-      <c r="AT26" t="n">
+      <c r="AY26" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="AZ26" t="n">
+        <v>11</v>
+      </c>
+      <c r="BA26" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="BB26" t="n">
+        <v>18.5</v>
+      </c>
+      <c r="BC26" t="n">
+        <v>12</v>
+      </c>
+      <c r="BD26" t="n">
+        <v>16</v>
+      </c>
+      <c r="BE26" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="BF26" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="BG26" t="n">
+        <v>18.5</v>
+      </c>
+      <c r="BH26" t="n">
+        <v>5.6</v>
+      </c>
+      <c r="BI26" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="BJ26" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="BK26" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="BL26" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BM26" t="n">
         <v>9.199999999999999</v>
       </c>
-      <c r="AU26" t="n">
-        <v>6.6</v>
-      </c>
-      <c r="AV26" t="n">
+      <c r="BN26" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="BO26" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="BP26" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="BQ26" t="n">
+        <v>5.6</v>
+      </c>
+      <c r="BR26" t="n">
+        <v>18</v>
+      </c>
+      <c r="BS26" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="BT26" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="BU26" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="BV26" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BW26" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="BX26" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BY26" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="BZ26" t="n">
         <v>11</v>
       </c>
-      <c r="AW26" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="AX26" t="n">
-        <v>13.5</v>
-      </c>
-      <c r="AY26" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="AZ26" t="n">
-        <v>16</v>
-      </c>
-      <c r="BA26" t="n">
-        <v>4.7</v>
-      </c>
-      <c r="BB26" t="n">
-        <v>4.7</v>
-      </c>
-      <c r="BC26" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="BD26" t="n">
-        <v>4.8</v>
-      </c>
-      <c r="BE26" t="n">
-        <v>4.9</v>
-      </c>
-      <c r="BF26" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="BG26" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="BH26" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BI26" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="BJ26" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BK26" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="BL26" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BM26" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="BN26" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BO26" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="BP26" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BQ26" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="BR26" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BS26" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="BT26" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BU26" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="BV26" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BW26" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="BX26" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BY26" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="BZ26" t="n">
-        <v>1000</v>
-      </c>
       <c r="CA26" t="n">
-        <v>1.04</v>
+        <v>5.5</v>
       </c>
       <c r="CB26" t="inlineStr">
         <is>
-          <t>2026-06-11 11:32:36</t>
+          <t>2026-06-11 13:45:41</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Icelandic 1 Deild</t>
+          <t>Argentinian Primera C</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -7193,244 +7193,244 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>16:15:00</t>
+          <t>18:30:00</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>Throttur</t>
+          <t>CD Cambaceres</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>HK Kopavogur</t>
+          <t>AD Berazategui</t>
         </is>
       </c>
       <c r="F27" t="n">
-        <v>1.72</v>
+        <v>1.09</v>
       </c>
       <c r="G27" t="n">
-        <v>1.88</v>
+        <v>1000</v>
       </c>
       <c r="H27" t="n">
-        <v>3.9</v>
+        <v>1.76</v>
       </c>
       <c r="I27" t="n">
-        <v>4.6</v>
+        <v>1000</v>
       </c>
       <c r="J27" t="n">
-        <v>4.4</v>
+        <v>1.35</v>
       </c>
       <c r="K27" t="n">
-        <v>5.3</v>
+        <v>3.25</v>
       </c>
       <c r="L27" t="n">
-        <v>1.18</v>
+        <v>1.01</v>
       </c>
       <c r="M27" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="N27" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="O27" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="P27" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="Q27" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="R27" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="S27" t="n">
+        <v>1.51</v>
+      </c>
+      <c r="T27" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="U27" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="V27" t="n">
         <v>1.02</v>
       </c>
-      <c r="N27" t="n">
-        <v>7.4</v>
-      </c>
-      <c r="O27" t="n">
-        <v>1.12</v>
-      </c>
-      <c r="P27" t="n">
-        <v>3.15</v>
-      </c>
-      <c r="Q27" t="n">
-        <v>1.37</v>
-      </c>
-      <c r="R27" t="n">
-        <v>1.87</v>
-      </c>
-      <c r="S27" t="n">
-        <v>1.92</v>
-      </c>
-      <c r="T27" t="n">
-        <v>1.45</v>
-      </c>
-      <c r="U27" t="n">
-        <v>2.78</v>
-      </c>
-      <c r="V27" t="n">
-        <v>1.27</v>
-      </c>
       <c r="W27" t="n">
-        <v>2.14</v>
+        <v>1.02</v>
       </c>
       <c r="X27" t="n">
-        <v>48</v>
+        <v>1000</v>
       </c>
       <c r="Y27" t="n">
-        <v>36</v>
+        <v>1000</v>
       </c>
       <c r="Z27" t="n">
-        <v>50</v>
+        <v>1000</v>
       </c>
       <c r="AA27" t="n">
-        <v>95</v>
+        <v>1000</v>
       </c>
       <c r="AB27" t="n">
-        <v>22</v>
+        <v>1000</v>
       </c>
       <c r="AC27" t="n">
-        <v>15.5</v>
+        <v>1000</v>
       </c>
       <c r="AD27" t="n">
-        <v>23</v>
+        <v>1000</v>
       </c>
       <c r="AE27" t="n">
-        <v>48</v>
+        <v>1000</v>
       </c>
       <c r="AF27" t="n">
-        <v>21</v>
+        <v>1000</v>
       </c>
       <c r="AG27" t="n">
-        <v>14</v>
+        <v>1000</v>
       </c>
       <c r="AH27" t="n">
-        <v>16</v>
+        <v>1000</v>
       </c>
       <c r="AI27" t="n">
-        <v>44</v>
+        <v>1000</v>
       </c>
       <c r="AJ27" t="n">
-        <v>26</v>
+        <v>1000</v>
       </c>
       <c r="AK27" t="n">
-        <v>19.5</v>
+        <v>1000</v>
       </c>
       <c r="AL27" t="n">
-        <v>27</v>
+        <v>1000</v>
       </c>
       <c r="AM27" t="n">
-        <v>60</v>
+        <v>1000</v>
       </c>
       <c r="AN27" t="n">
-        <v>7</v>
+        <v>1000</v>
       </c>
       <c r="AO27" t="n">
-        <v>28</v>
+        <v>1000</v>
       </c>
       <c r="AP27" t="n">
-        <v>4.2</v>
+        <v>1.01</v>
       </c>
       <c r="AQ27" t="n">
-        <v>21</v>
+        <v>1.01</v>
       </c>
       <c r="AR27" t="n">
-        <v>32</v>
+        <v>1.01</v>
       </c>
       <c r="AS27" t="n">
-        <v>4.3</v>
+        <v>1.01</v>
       </c>
       <c r="AT27" t="n">
-        <v>13</v>
+        <v>1.01</v>
       </c>
       <c r="AU27" t="n">
-        <v>10.5</v>
+        <v>1.01</v>
       </c>
       <c r="AV27" t="n">
-        <v>13.5</v>
+        <v>1.01</v>
       </c>
       <c r="AW27" t="n">
-        <v>4.2</v>
+        <v>1.01</v>
       </c>
       <c r="AX27" t="n">
-        <v>12.5</v>
+        <v>1.01</v>
       </c>
       <c r="AY27" t="n">
-        <v>8.6</v>
+        <v>1.01</v>
       </c>
       <c r="AZ27" t="n">
-        <v>11</v>
+        <v>1.01</v>
       </c>
       <c r="BA27" t="n">
-        <v>4.1</v>
+        <v>1.01</v>
       </c>
       <c r="BB27" t="n">
-        <v>18</v>
+        <v>1.01</v>
       </c>
       <c r="BC27" t="n">
-        <v>11.5</v>
+        <v>1.01</v>
       </c>
       <c r="BD27" t="n">
-        <v>18</v>
+        <v>1.01</v>
       </c>
       <c r="BE27" t="n">
-        <v>4.2</v>
+        <v>1.01</v>
       </c>
       <c r="BF27" t="n">
-        <v>5.1</v>
+        <v>1.01</v>
       </c>
       <c r="BG27" t="n">
-        <v>19</v>
+        <v>1.01</v>
       </c>
       <c r="BH27" t="n">
-        <v>5.6</v>
+        <v>1000</v>
       </c>
       <c r="BI27" t="n">
-        <v>4.1</v>
+        <v>1.04</v>
       </c>
       <c r="BJ27" t="n">
-        <v>8.800000000000001</v>
+        <v>1000</v>
       </c>
       <c r="BK27" t="n">
-        <v>4.8</v>
+        <v>1.04</v>
       </c>
       <c r="BL27" t="n">
         <v>1000</v>
       </c>
       <c r="BM27" t="n">
-        <v>9</v>
+        <v>1.04</v>
       </c>
       <c r="BN27" t="n">
-        <v>5.5</v>
+        <v>1000</v>
       </c>
       <c r="BO27" t="n">
-        <v>4.6</v>
+        <v>1.04</v>
       </c>
       <c r="BP27" t="n">
-        <v>11.5</v>
+        <v>1000</v>
       </c>
       <c r="BQ27" t="n">
-        <v>5.5</v>
+        <v>1.04</v>
       </c>
       <c r="BR27" t="n">
-        <v>18</v>
+        <v>1000</v>
       </c>
       <c r="BS27" t="n">
-        <v>6.6</v>
+        <v>1.04</v>
       </c>
       <c r="BT27" t="n">
-        <v>8.800000000000001</v>
+        <v>1000</v>
       </c>
       <c r="BU27" t="n">
-        <v>4.8</v>
+        <v>1.04</v>
       </c>
       <c r="BV27" t="n">
         <v>1000</v>
       </c>
       <c r="BW27" t="n">
-        <v>7.8</v>
+        <v>1.04</v>
       </c>
       <c r="BX27" t="n">
         <v>1000</v>
       </c>
       <c r="BY27" t="n">
-        <v>7.8</v>
+        <v>1.04</v>
       </c>
       <c r="BZ27" t="n">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="CA27" t="n">
-        <v>5.4</v>
+        <v>0</v>
       </c>
       <c r="CB27" t="inlineStr">
         <is>
-          <t>2026-06-11 11:32:36</t>
+          <t>2026-06-11 13:45:41</t>
         </is>
       </c>
     </row>
@@ -7470,10 +7470,10 @@
         <v>3.6</v>
       </c>
       <c r="I28" t="n">
-        <v>4.1</v>
+        <v>3.95</v>
       </c>
       <c r="J28" t="n">
-        <v>3.2</v>
+        <v>3.35</v>
       </c>
       <c r="K28" t="n">
         <v>3.4</v>
@@ -7482,28 +7482,28 @@
         <v>1.01</v>
       </c>
       <c r="M28" t="n">
-        <v>1.1</v>
+        <v>1.09</v>
       </c>
       <c r="N28" t="n">
-        <v>3</v>
+        <v>2.5</v>
       </c>
       <c r="O28" t="n">
-        <v>1.44</v>
+        <v>1.43</v>
       </c>
       <c r="P28" t="n">
-        <v>1.66</v>
+        <v>1.57</v>
       </c>
       <c r="Q28" t="n">
-        <v>2.28</v>
+        <v>2.12</v>
       </c>
       <c r="R28" t="n">
-        <v>1.24</v>
+        <v>1.21</v>
       </c>
       <c r="S28" t="n">
-        <v>4.5</v>
+        <v>4</v>
       </c>
       <c r="T28" t="n">
-        <v>1.96</v>
+        <v>1.97</v>
       </c>
       <c r="U28" t="n">
         <v>1.89</v>
@@ -7518,22 +7518,22 @@
         <v>12.5</v>
       </c>
       <c r="Y28" t="n">
-        <v>970</v>
+        <v>13.5</v>
       </c>
       <c r="Z28" t="n">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="AA28" t="n">
         <v>95</v>
       </c>
       <c r="AB28" t="n">
-        <v>970</v>
+        <v>8.6</v>
       </c>
       <c r="AC28" t="n">
         <v>7.6</v>
       </c>
       <c r="AD28" t="n">
-        <v>970</v>
+        <v>18.5</v>
       </c>
       <c r="AE28" t="n">
         <v>60</v>
@@ -7542,7 +7542,7 @@
         <v>970</v>
       </c>
       <c r="AG28" t="n">
-        <v>970</v>
+        <v>13.5</v>
       </c>
       <c r="AH28" t="n">
         <v>950</v>
@@ -7551,10 +7551,10 @@
         <v>80</v>
       </c>
       <c r="AJ28" t="n">
-        <v>32</v>
+        <v>38</v>
       </c>
       <c r="AK28" t="n">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="AL28" t="n">
         <v>55</v>
@@ -7563,64 +7563,64 @@
         <v>170</v>
       </c>
       <c r="AN28" t="n">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="AO28" t="n">
         <v>80</v>
       </c>
       <c r="AP28" t="n">
-        <v>5</v>
+        <v>4.2</v>
       </c>
       <c r="AQ28" t="n">
         <v>9.800000000000001</v>
       </c>
       <c r="AR28" t="n">
-        <v>6.4</v>
+        <v>5.2</v>
       </c>
       <c r="AS28" t="n">
-        <v>7.8</v>
+        <v>5.9</v>
       </c>
       <c r="AT28" t="n">
-        <v>6.8</v>
+        <v>7</v>
       </c>
       <c r="AU28" t="n">
-        <v>6.4</v>
+        <v>5.9</v>
       </c>
       <c r="AV28" t="n">
-        <v>5.6</v>
+        <v>12</v>
       </c>
       <c r="AW28" t="n">
-        <v>7.4</v>
+        <v>5.7</v>
       </c>
       <c r="AX28" t="n">
-        <v>5.3</v>
+        <v>10.5</v>
       </c>
       <c r="AY28" t="n">
-        <v>4.9</v>
+        <v>9.6</v>
       </c>
       <c r="AZ28" t="n">
+        <v>5</v>
+      </c>
+      <c r="BA28" t="n">
+        <v>5.9</v>
+      </c>
+      <c r="BB28" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="BC28" t="n">
+        <v>21</v>
+      </c>
+      <c r="BD28" t="n">
+        <v>5.7</v>
+      </c>
+      <c r="BE28" t="n">
         <v>6</v>
       </c>
-      <c r="BA28" t="n">
-        <v>7.6</v>
-      </c>
-      <c r="BB28" t="n">
-        <v>6.6</v>
-      </c>
-      <c r="BC28" t="n">
-        <v>6.6</v>
-      </c>
-      <c r="BD28" t="n">
-        <v>7.4</v>
-      </c>
-      <c r="BE28" t="n">
-        <v>4.1</v>
-      </c>
       <c r="BF28" t="n">
-        <v>19.5</v>
+        <v>5.2</v>
       </c>
       <c r="BG28" t="n">
-        <v>7.6</v>
+        <v>5.9</v>
       </c>
       <c r="BH28" t="n">
         <v>1000</v>
@@ -7684,14 +7684,14 @@
       </c>
       <c r="CB28" t="inlineStr">
         <is>
-          <t>2026-06-11 11:32:36</t>
+          <t>2026-06-11 13:45:41</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Bolivian Liga de Futbol Profesional</t>
+          <t>Chilean Primera Division</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -7701,498 +7701,244 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>20:00:00</t>
+          <t>21:00:00</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>Nacional Potosi</t>
+          <t>Audax Italiano</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>CDT Real Oruro</t>
+          <t>La Serena</t>
         </is>
       </c>
       <c r="F29" t="n">
-        <v>1.37</v>
+        <v>2</v>
       </c>
       <c r="G29" t="n">
-        <v>1.49</v>
+        <v>2.06</v>
       </c>
       <c r="H29" t="n">
-        <v>3.6</v>
+        <v>3.8</v>
       </c>
       <c r="I29" t="n">
-        <v>1000</v>
+        <v>4.1</v>
       </c>
       <c r="J29" t="n">
-        <v>4.4</v>
+        <v>3.8</v>
       </c>
       <c r="K29" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="L29" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="M29" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="N29" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="O29" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="P29" t="n">
+        <v>2.12</v>
+      </c>
+      <c r="Q29" t="n">
+        <v>1.78</v>
+      </c>
+      <c r="R29" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="S29" t="n">
+        <v>2.94</v>
+      </c>
+      <c r="T29" t="n">
+        <v>1.71</v>
+      </c>
+      <c r="U29" t="n">
+        <v>2.26</v>
+      </c>
+      <c r="V29" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="W29" t="n">
+        <v>1.94</v>
+      </c>
+      <c r="X29" t="n">
+        <v>18.5</v>
+      </c>
+      <c r="Y29" t="n">
+        <v>17</v>
+      </c>
+      <c r="Z29" t="n">
+        <v>30</v>
+      </c>
+      <c r="AA29" t="n">
+        <v>95</v>
+      </c>
+      <c r="AB29" t="n">
+        <v>11</v>
+      </c>
+      <c r="AC29" t="n">
+        <v>9</v>
+      </c>
+      <c r="AD29" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="AE29" t="n">
+        <v>46</v>
+      </c>
+      <c r="AF29" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="AG29" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AH29" t="n">
+        <v>17.5</v>
+      </c>
+      <c r="AI29" t="n">
+        <v>50</v>
+      </c>
+      <c r="AJ29" t="n">
+        <v>24</v>
+      </c>
+      <c r="AK29" t="n">
+        <v>20</v>
+      </c>
+      <c r="AL29" t="n">
+        <v>32</v>
+      </c>
+      <c r="AM29" t="n">
+        <v>100</v>
+      </c>
+      <c r="AN29" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="AO29" t="n">
+        <v>42</v>
+      </c>
+      <c r="AP29" t="n">
+        <v>16</v>
+      </c>
+      <c r="AQ29" t="n">
+        <v>15</v>
+      </c>
+      <c r="AR29" t="n">
+        <v>18.5</v>
+      </c>
+      <c r="AS29" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="AT29" t="n">
         <v>9.6</v>
       </c>
-      <c r="L29" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="M29" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="N29" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="O29" t="n">
-        <v>1.09</v>
-      </c>
-      <c r="P29" t="n">
-        <v>1.24</v>
-      </c>
-      <c r="Q29" t="n">
-        <v>1.09</v>
-      </c>
-      <c r="R29" t="n">
-        <v>1.18</v>
-      </c>
-      <c r="S29" t="n">
-        <v>1.09</v>
-      </c>
-      <c r="T29" t="n">
-        <v>1.11</v>
-      </c>
-      <c r="U29" t="n">
-        <v>1.11</v>
-      </c>
-      <c r="V29" t="n">
-        <v>1.09</v>
-      </c>
-      <c r="W29" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="X29" t="n">
-        <v>1000</v>
-      </c>
-      <c r="Y29" t="n">
-        <v>1000</v>
-      </c>
-      <c r="Z29" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AA29" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AB29" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AC29" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AD29" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AE29" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AF29" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AG29" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AH29" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AI29" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AJ29" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AK29" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AL29" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AM29" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AN29" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AO29" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AP29" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="AQ29" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="AR29" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="AS29" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="AT29" t="n">
-        <v>1.01</v>
-      </c>
       <c r="AU29" t="n">
-        <v>1.01</v>
+        <v>8</v>
       </c>
       <c r="AV29" t="n">
-        <v>1.01</v>
+        <v>14.5</v>
       </c>
       <c r="AW29" t="n">
-        <v>1.01</v>
+        <v>25</v>
       </c>
       <c r="AX29" t="n">
-        <v>1.01</v>
+        <v>11.5</v>
       </c>
       <c r="AY29" t="n">
-        <v>1.01</v>
+        <v>9.4</v>
       </c>
       <c r="AZ29" t="n">
-        <v>1.01</v>
+        <v>15</v>
       </c>
       <c r="BA29" t="n">
-        <v>1.01</v>
+        <v>27</v>
       </c>
       <c r="BB29" t="n">
-        <v>1.01</v>
+        <v>20</v>
       </c>
       <c r="BC29" t="n">
-        <v>1.01</v>
+        <v>17.5</v>
       </c>
       <c r="BD29" t="n">
-        <v>1.01</v>
+        <v>21</v>
       </c>
       <c r="BE29" t="n">
-        <v>1.01</v>
+        <v>11.5</v>
       </c>
       <c r="BF29" t="n">
-        <v>1.01</v>
+        <v>11</v>
       </c>
       <c r="BG29" t="n">
-        <v>1.01</v>
+        <v>24</v>
       </c>
       <c r="BH29" t="n">
-        <v>1000</v>
+        <v>3.75</v>
       </c>
       <c r="BI29" t="n">
-        <v>1.04</v>
+        <v>3.35</v>
       </c>
       <c r="BJ29" t="n">
-        <v>1000</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BK29" t="n">
-        <v>1.04</v>
+        <v>5.8</v>
       </c>
       <c r="BL29" t="n">
         <v>1000</v>
       </c>
       <c r="BM29" t="n">
-        <v>1.04</v>
+        <v>13.5</v>
       </c>
       <c r="BN29" t="n">
-        <v>1000</v>
+        <v>5</v>
       </c>
       <c r="BO29" t="n">
-        <v>1.04</v>
+        <v>3.8</v>
       </c>
       <c r="BP29" t="n">
-        <v>1000</v>
+        <v>14</v>
       </c>
       <c r="BQ29" t="n">
-        <v>1.04</v>
+        <v>7.4</v>
       </c>
       <c r="BR29" t="n">
-        <v>1000</v>
+        <v>26</v>
       </c>
       <c r="BS29" t="n">
-        <v>1.04</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BT29" t="n">
-        <v>1000</v>
+        <v>7.4</v>
       </c>
       <c r="BU29" t="n">
-        <v>1.04</v>
+        <v>5.5</v>
       </c>
       <c r="BV29" t="n">
-        <v>1000</v>
+        <v>30</v>
       </c>
       <c r="BW29" t="n">
-        <v>1.04</v>
+        <v>10</v>
       </c>
       <c r="BX29" t="n">
-        <v>1000</v>
+        <v>38</v>
       </c>
       <c r="BY29" t="n">
-        <v>1.04</v>
+        <v>11</v>
       </c>
       <c r="BZ29" t="n">
-        <v>1000</v>
+        <v>21</v>
       </c>
       <c r="CA29" t="n">
-        <v>1.04</v>
+        <v>9</v>
       </c>
       <c r="CB29" t="inlineStr">
         <is>
-          <t>2026-06-11 11:32:36</t>
-        </is>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" t="inlineStr">
-        <is>
-          <t>Chilean Primera Division</t>
-        </is>
-      </c>
-      <c r="B30" t="inlineStr">
-        <is>
-          <t>2026-06-12</t>
-        </is>
-      </c>
-      <c r="C30" t="inlineStr">
-        <is>
-          <t>21:00:00</t>
-        </is>
-      </c>
-      <c r="D30" t="inlineStr">
-        <is>
-          <t>Audax Italiano</t>
-        </is>
-      </c>
-      <c r="E30" t="inlineStr">
-        <is>
-          <t>La Serena</t>
-        </is>
-      </c>
-      <c r="F30" t="n">
-        <v>2</v>
-      </c>
-      <c r="G30" t="n">
-        <v>2.06</v>
-      </c>
-      <c r="H30" t="n">
-        <v>3.8</v>
-      </c>
-      <c r="I30" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="J30" t="n">
-        <v>3.8</v>
-      </c>
-      <c r="K30" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="L30" t="n">
-        <v>1.29</v>
-      </c>
-      <c r="M30" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="N30" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="O30" t="n">
-        <v>1.26</v>
-      </c>
-      <c r="P30" t="n">
-        <v>2.14</v>
-      </c>
-      <c r="Q30" t="n">
-        <v>1.77</v>
-      </c>
-      <c r="R30" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="S30" t="n">
-        <v>2.96</v>
-      </c>
-      <c r="T30" t="n">
-        <v>1.71</v>
-      </c>
-      <c r="U30" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="V30" t="n">
-        <v>1.32</v>
-      </c>
-      <c r="W30" t="n">
-        <v>1.94</v>
-      </c>
-      <c r="X30" t="n">
-        <v>22</v>
-      </c>
-      <c r="Y30" t="n">
-        <v>20</v>
-      </c>
-      <c r="Z30" t="n">
-        <v>36</v>
-      </c>
-      <c r="AA30" t="n">
-        <v>90</v>
-      </c>
-      <c r="AB30" t="n">
-        <v>13.5</v>
-      </c>
-      <c r="AC30" t="n">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="AD30" t="n">
-        <v>19.5</v>
-      </c>
-      <c r="AE30" t="n">
-        <v>55</v>
-      </c>
-      <c r="AF30" t="n">
-        <v>17</v>
-      </c>
-      <c r="AG30" t="n">
-        <v>13</v>
-      </c>
-      <c r="AH30" t="n">
-        <v>21</v>
-      </c>
-      <c r="AI30" t="n">
-        <v>60</v>
-      </c>
-      <c r="AJ30" t="n">
-        <v>30</v>
-      </c>
-      <c r="AK30" t="n">
-        <v>25</v>
-      </c>
-      <c r="AL30" t="n">
-        <v>40</v>
-      </c>
-      <c r="AM30" t="n">
-        <v>100</v>
-      </c>
-      <c r="AN30" t="n">
-        <v>15.5</v>
-      </c>
-      <c r="AO30" t="n">
-        <v>48</v>
-      </c>
-      <c r="AP30" t="n">
-        <v>15.5</v>
-      </c>
-      <c r="AQ30" t="n">
-        <v>14.5</v>
-      </c>
-      <c r="AR30" t="n">
-        <v>25</v>
-      </c>
-      <c r="AS30" t="n">
-        <v>34</v>
-      </c>
-      <c r="AT30" t="n">
-        <v>9.6</v>
-      </c>
-      <c r="AU30" t="n">
-        <v>8</v>
-      </c>
-      <c r="AV30" t="n">
-        <v>14</v>
-      </c>
-      <c r="AW30" t="n">
-        <v>38</v>
-      </c>
-      <c r="AX30" t="n">
-        <v>12</v>
-      </c>
-      <c r="AY30" t="n">
-        <v>9.4</v>
-      </c>
-      <c r="AZ30" t="n">
-        <v>15</v>
-      </c>
-      <c r="BA30" t="n">
-        <v>40</v>
-      </c>
-      <c r="BB30" t="n">
-        <v>21</v>
-      </c>
-      <c r="BC30" t="n">
-        <v>17.5</v>
-      </c>
-      <c r="BD30" t="n">
-        <v>21</v>
-      </c>
-      <c r="BE30" t="n">
-        <v>34</v>
-      </c>
-      <c r="BF30" t="n">
-        <v>11</v>
-      </c>
-      <c r="BG30" t="n">
-        <v>34</v>
-      </c>
-      <c r="BH30" t="n">
-        <v>3.75</v>
-      </c>
-      <c r="BI30" t="n">
-        <v>3.35</v>
-      </c>
-      <c r="BJ30" t="n">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="BK30" t="n">
-        <v>5.8</v>
-      </c>
-      <c r="BL30" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BM30" t="n">
-        <v>13.5</v>
-      </c>
-      <c r="BN30" t="n">
-        <v>5</v>
-      </c>
-      <c r="BO30" t="n">
-        <v>3.8</v>
-      </c>
-      <c r="BP30" t="n">
-        <v>14</v>
-      </c>
-      <c r="BQ30" t="n">
-        <v>7.4</v>
-      </c>
-      <c r="BR30" t="n">
-        <v>26</v>
-      </c>
-      <c r="BS30" t="n">
-        <v>9.800000000000001</v>
-      </c>
-      <c r="BT30" t="n">
-        <v>7.4</v>
-      </c>
-      <c r="BU30" t="n">
-        <v>5.5</v>
-      </c>
-      <c r="BV30" t="n">
-        <v>30</v>
-      </c>
-      <c r="BW30" t="n">
-        <v>10</v>
-      </c>
-      <c r="BX30" t="n">
-        <v>38</v>
-      </c>
-      <c r="BY30" t="n">
-        <v>11</v>
-      </c>
-      <c r="BZ30" t="n">
-        <v>21</v>
-      </c>
-      <c r="CA30" t="n">
-        <v>9</v>
-      </c>
-      <c r="CB30" t="inlineStr">
-        <is>
-          <t>2026-06-11 11:32:36</t>
+          <t>2026-06-11 13:45:41</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-06-12.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-06-12.xlsx
@@ -860,28 +860,28 @@
         <v>1.5</v>
       </c>
       <c r="G2" t="n">
-        <v>1.63</v>
+        <v>1.64</v>
       </c>
       <c r="H2" t="n">
-        <v>7</v>
+        <v>6.8</v>
       </c>
       <c r="I2" t="n">
         <v>9.4</v>
       </c>
       <c r="J2" t="n">
-        <v>3.95</v>
+        <v>3.6</v>
       </c>
       <c r="K2" t="n">
-        <v>4.9</v>
+        <v>5.4</v>
       </c>
       <c r="L2" t="n">
-        <v>1.01</v>
+        <v>1.32</v>
       </c>
       <c r="M2" t="n">
         <v>1.06</v>
       </c>
       <c r="N2" t="n">
-        <v>3.55</v>
+        <v>3.2</v>
       </c>
       <c r="O2" t="n">
         <v>1.3</v>
@@ -896,7 +896,7 @@
         <v>1.34</v>
       </c>
       <c r="S2" t="n">
-        <v>2.96</v>
+        <v>3</v>
       </c>
       <c r="T2" t="n">
         <v>1.94</v>
@@ -908,7 +908,7 @@
         <v>1.13</v>
       </c>
       <c r="W2" t="n">
-        <v>2.58</v>
+        <v>2.56</v>
       </c>
       <c r="X2" t="n">
         <v>970</v>
@@ -1019,16 +1019,16 @@
         <v>4.5</v>
       </c>
       <c r="BH2" t="n">
-        <v>1000</v>
+        <v>8.4</v>
       </c>
       <c r="BI2" t="n">
-        <v>1.04</v>
+        <v>2.8</v>
       </c>
       <c r="BJ2" t="n">
         <v>1000</v>
       </c>
       <c r="BK2" t="n">
-        <v>1.04</v>
+        <v>1.39</v>
       </c>
       <c r="BL2" t="n">
         <v>1000</v>
@@ -1040,25 +1040,25 @@
         <v>1000</v>
       </c>
       <c r="BO2" t="n">
-        <v>1.04</v>
+        <v>2.82</v>
       </c>
       <c r="BP2" t="n">
         <v>1000</v>
       </c>
       <c r="BQ2" t="n">
-        <v>1.04</v>
+        <v>1.37</v>
       </c>
       <c r="BR2" t="n">
         <v>1000</v>
       </c>
       <c r="BS2" t="n">
-        <v>1.04</v>
+        <v>1.22</v>
       </c>
       <c r="BT2" t="n">
         <v>1000</v>
       </c>
       <c r="BU2" t="n">
-        <v>1.04</v>
+        <v>1.38</v>
       </c>
       <c r="BV2" t="n">
         <v>1000</v>
@@ -1070,17 +1070,17 @@
         <v>1000</v>
       </c>
       <c r="BY2" t="n">
-        <v>1.04</v>
+        <v>1.22</v>
       </c>
       <c r="BZ2" t="n">
         <v>1000</v>
       </c>
       <c r="CA2" t="n">
-        <v>1.04</v>
+        <v>1.24</v>
       </c>
       <c r="CB2" t="inlineStr">
         <is>
-          <t>2026-06-11 13:45:41</t>
+          <t>2026-06-11 15:58:00</t>
         </is>
       </c>
     </row>
@@ -1111,166 +1111,166 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>2.26</v>
+        <v>2.56</v>
       </c>
       <c r="G3" t="n">
-        <v>2.9</v>
+        <v>2.8</v>
       </c>
       <c r="H3" t="n">
-        <v>2.48</v>
+        <v>2.64</v>
       </c>
       <c r="I3" t="n">
-        <v>2.94</v>
+        <v>2.88</v>
       </c>
       <c r="J3" t="n">
-        <v>3.45</v>
+        <v>3.6</v>
       </c>
       <c r="K3" t="n">
-        <v>6.6</v>
+        <v>4</v>
       </c>
       <c r="L3" t="n">
         <v>1.01</v>
       </c>
       <c r="M3" t="n">
-        <v>1.01</v>
+        <v>1.05</v>
       </c>
       <c r="N3" t="n">
-        <v>1.11</v>
+        <v>4.4</v>
       </c>
       <c r="O3" t="n">
-        <v>1.23</v>
+        <v>1.25</v>
       </c>
       <c r="P3" t="n">
-        <v>2.08</v>
+        <v>2.16</v>
       </c>
       <c r="Q3" t="n">
-        <v>1.65</v>
+        <v>1.73</v>
       </c>
       <c r="R3" t="n">
-        <v>1.42</v>
+        <v>1.45</v>
       </c>
       <c r="S3" t="n">
-        <v>2.6</v>
+        <v>2.86</v>
       </c>
       <c r="T3" t="n">
-        <v>1.12</v>
+        <v>1.63</v>
       </c>
       <c r="U3" t="n">
-        <v>1.11</v>
+        <v>2.36</v>
       </c>
       <c r="V3" t="n">
-        <v>1.51</v>
+        <v>1.53</v>
       </c>
       <c r="W3" t="n">
-        <v>1.53</v>
+        <v>1.56</v>
       </c>
       <c r="X3" t="n">
-        <v>1000</v>
+        <v>23</v>
       </c>
       <c r="Y3" t="n">
-        <v>1000</v>
+        <v>14</v>
       </c>
       <c r="Z3" t="n">
-        <v>1000</v>
+        <v>25</v>
       </c>
       <c r="AA3" t="n">
-        <v>1000</v>
+        <v>50</v>
       </c>
       <c r="AB3" t="n">
-        <v>1000</v>
+        <v>13.5</v>
       </c>
       <c r="AC3" t="n">
-        <v>1000</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AD3" t="n">
-        <v>1000</v>
+        <v>15.5</v>
       </c>
       <c r="AE3" t="n">
-        <v>1000</v>
+        <v>29</v>
       </c>
       <c r="AF3" t="n">
-        <v>1000</v>
+        <v>24</v>
       </c>
       <c r="AG3" t="n">
-        <v>1000</v>
+        <v>15</v>
       </c>
       <c r="AH3" t="n">
-        <v>1000</v>
+        <v>16</v>
       </c>
       <c r="AI3" t="n">
-        <v>1000</v>
+        <v>44</v>
       </c>
       <c r="AJ3" t="n">
-        <v>1000</v>
+        <v>48</v>
       </c>
       <c r="AK3" t="n">
-        <v>1000</v>
+        <v>28</v>
       </c>
       <c r="AL3" t="n">
-        <v>1000</v>
+        <v>44</v>
       </c>
       <c r="AM3" t="n">
-        <v>1000</v>
+        <v>85</v>
       </c>
       <c r="AN3" t="n">
-        <v>1000</v>
+        <v>23</v>
       </c>
       <c r="AO3" t="n">
-        <v>1000</v>
+        <v>25</v>
       </c>
       <c r="AP3" t="n">
-        <v>1.01</v>
+        <v>13.5</v>
       </c>
       <c r="AQ3" t="n">
-        <v>1.01</v>
+        <v>10</v>
       </c>
       <c r="AR3" t="n">
-        <v>1.01</v>
+        <v>14.5</v>
       </c>
       <c r="AS3" t="n">
-        <v>1.01</v>
+        <v>5.5</v>
       </c>
       <c r="AT3" t="n">
-        <v>1.01</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AU3" t="n">
-        <v>1.01</v>
+        <v>6.4</v>
       </c>
       <c r="AV3" t="n">
-        <v>1.01</v>
+        <v>9.4</v>
       </c>
       <c r="AW3" t="n">
-        <v>1.01</v>
+        <v>20</v>
       </c>
       <c r="AX3" t="n">
-        <v>1.01</v>
+        <v>14</v>
       </c>
       <c r="AY3" t="n">
-        <v>1.01</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AZ3" t="n">
-        <v>1.01</v>
+        <v>11.5</v>
       </c>
       <c r="BA3" t="n">
-        <v>1.01</v>
+        <v>5.5</v>
       </c>
       <c r="BB3" t="n">
-        <v>1.01</v>
+        <v>5.5</v>
       </c>
       <c r="BC3" t="n">
-        <v>1.01</v>
+        <v>18.5</v>
       </c>
       <c r="BD3" t="n">
-        <v>1.01</v>
+        <v>5.6</v>
       </c>
       <c r="BE3" t="n">
-        <v>1.01</v>
+        <v>5.5</v>
       </c>
       <c r="BF3" t="n">
-        <v>1.01</v>
+        <v>14</v>
       </c>
       <c r="BG3" t="n">
-        <v>1.01</v>
+        <v>14.5</v>
       </c>
       <c r="BH3" t="n">
         <v>1000</v>
@@ -1334,7 +1334,7 @@
       </c>
       <c r="CB3" t="inlineStr">
         <is>
-          <t>2026-06-11 13:45:41</t>
+          <t>2026-06-11 15:58:00</t>
         </is>
       </c>
     </row>
@@ -1365,52 +1365,52 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>2.72</v>
+        <v>2.78</v>
       </c>
       <c r="G4" t="n">
-        <v>3.1</v>
+        <v>3.2</v>
       </c>
       <c r="H4" t="n">
-        <v>2.8</v>
+        <v>2.92</v>
       </c>
       <c r="I4" t="n">
-        <v>3.6</v>
+        <v>3.4</v>
       </c>
       <c r="J4" t="n">
-        <v>2.62</v>
+        <v>2.6</v>
       </c>
       <c r="K4" t="n">
-        <v>3.4</v>
+        <v>3.3</v>
       </c>
       <c r="L4" t="n">
         <v>1.01</v>
       </c>
       <c r="M4" t="n">
-        <v>1.01</v>
+        <v>1.15</v>
       </c>
       <c r="N4" t="n">
-        <v>2.36</v>
+        <v>2.34</v>
       </c>
       <c r="O4" t="n">
         <v>1.6</v>
       </c>
       <c r="P4" t="n">
-        <v>1.46</v>
+        <v>1.45</v>
       </c>
       <c r="Q4" t="n">
-        <v>2.78</v>
+        <v>2.84</v>
       </c>
       <c r="R4" t="n">
         <v>1.18</v>
       </c>
       <c r="S4" t="n">
-        <v>5.1</v>
+        <v>6</v>
       </c>
       <c r="T4" t="n">
-        <v>1.84</v>
+        <v>2.16</v>
       </c>
       <c r="U4" t="n">
-        <v>1.51</v>
+        <v>1.71</v>
       </c>
       <c r="V4" t="n">
         <v>1.42</v>
@@ -1431,10 +1431,10 @@
         <v>75</v>
       </c>
       <c r="AB4" t="n">
-        <v>9</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AC4" t="n">
-        <v>7.8</v>
+        <v>970</v>
       </c>
       <c r="AD4" t="n">
         <v>970</v>
@@ -1449,7 +1449,7 @@
         <v>970</v>
       </c>
       <c r="AH4" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="AI4" t="n">
         <v>1000</v>
@@ -1479,52 +1479,52 @@
         <v>6.4</v>
       </c>
       <c r="AR4" t="n">
-        <v>4.3</v>
+        <v>3.7</v>
       </c>
       <c r="AS4" t="n">
-        <v>5</v>
+        <v>2.7</v>
       </c>
       <c r="AT4" t="n">
-        <v>3.35</v>
+        <v>3.85</v>
       </c>
       <c r="AU4" t="n">
         <v>5.6</v>
       </c>
       <c r="AV4" t="n">
-        <v>4.1</v>
+        <v>4.8</v>
       </c>
       <c r="AW4" t="n">
-        <v>4.9</v>
+        <v>2.66</v>
       </c>
       <c r="AX4" t="n">
-        <v>4.3</v>
+        <v>4.8</v>
       </c>
       <c r="AY4" t="n">
-        <v>4</v>
+        <v>4.6</v>
       </c>
       <c r="AZ4" t="n">
-        <v>4.5</v>
+        <v>5.4</v>
       </c>
       <c r="BA4" t="n">
-        <v>5.1</v>
+        <v>2.72</v>
       </c>
       <c r="BB4" t="n">
-        <v>5</v>
+        <v>2.68</v>
       </c>
       <c r="BC4" t="n">
-        <v>4.9</v>
+        <v>5.5</v>
       </c>
       <c r="BD4" t="n">
-        <v>5.1</v>
+        <v>2.72</v>
       </c>
       <c r="BE4" t="n">
-        <v>5.3</v>
+        <v>2.76</v>
       </c>
       <c r="BF4" t="n">
-        <v>5</v>
+        <v>2.7</v>
       </c>
       <c r="BG4" t="n">
-        <v>5</v>
+        <v>2.7</v>
       </c>
       <c r="BH4" t="n">
         <v>2.94</v>
@@ -1588,7 +1588,7 @@
       </c>
       <c r="CB4" t="inlineStr">
         <is>
-          <t>2026-06-11 13:45:41</t>
+          <t>2026-06-11 15:58:00</t>
         </is>
       </c>
     </row>
@@ -1727,7 +1727,7 @@
         <v>140</v>
       </c>
       <c r="AP5" t="n">
-        <v>6.4</v>
+        <v>7.2</v>
       </c>
       <c r="AQ5" t="n">
         <v>9.4</v>
@@ -1742,7 +1742,7 @@
         <v>6</v>
       </c>
       <c r="AU5" t="n">
-        <v>5.7</v>
+        <v>6.4</v>
       </c>
       <c r="AV5" t="n">
         <v>16</v>
@@ -1763,19 +1763,19 @@
         <v>6.2</v>
       </c>
       <c r="BB5" t="n">
-        <v>6.4</v>
+        <v>5.8</v>
       </c>
       <c r="BC5" t="n">
-        <v>5.9</v>
+        <v>5.8</v>
       </c>
       <c r="BD5" t="n">
-        <v>6.4</v>
+        <v>6.2</v>
       </c>
       <c r="BE5" t="n">
         <v>6.4</v>
       </c>
       <c r="BF5" t="n">
-        <v>6</v>
+        <v>5.8</v>
       </c>
       <c r="BG5" t="n">
         <v>6.4</v>
@@ -1842,7 +1842,7 @@
       </c>
       <c r="CB5" t="inlineStr">
         <is>
-          <t>2026-06-11 13:45:41</t>
+          <t>2026-06-11 15:58:00</t>
         </is>
       </c>
     </row>
@@ -1882,13 +1882,13 @@
         <v>2.18</v>
       </c>
       <c r="I6" t="n">
-        <v>2.36</v>
+        <v>2.32</v>
       </c>
       <c r="J6" t="n">
         <v>3.45</v>
       </c>
       <c r="K6" t="n">
-        <v>3.85</v>
+        <v>3.75</v>
       </c>
       <c r="L6" t="n">
         <v>1.3</v>
@@ -1897,7 +1897,7 @@
         <v>1.06</v>
       </c>
       <c r="N6" t="n">
-        <v>3.85</v>
+        <v>3.75</v>
       </c>
       <c r="O6" t="n">
         <v>1.3</v>
@@ -1921,7 +1921,7 @@
         <v>2.16</v>
       </c>
       <c r="V6" t="n">
-        <v>1.74</v>
+        <v>1.75</v>
       </c>
       <c r="W6" t="n">
         <v>1.36</v>
@@ -1960,7 +1960,7 @@
         <v>17.5</v>
       </c>
       <c r="AI6" t="n">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="AJ6" t="n">
         <v>80</v>
@@ -1981,7 +1981,7 @@
         <v>17.5</v>
       </c>
       <c r="AP6" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="AQ6" t="n">
         <v>9</v>
@@ -1993,7 +1993,7 @@
         <v>21</v>
       </c>
       <c r="AT6" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="AU6" t="n">
         <v>7.2</v>
@@ -2002,10 +2002,10 @@
         <v>9.800000000000001</v>
       </c>
       <c r="AW6" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="AX6" t="n">
-        <v>18.5</v>
+        <v>5.2</v>
       </c>
       <c r="AY6" t="n">
         <v>13</v>
@@ -2032,7 +2032,7 @@
         <v>5.1</v>
       </c>
       <c r="BG6" t="n">
-        <v>15</v>
+        <v>12.5</v>
       </c>
       <c r="BH6" t="n">
         <v>1000</v>
@@ -2096,7 +2096,7 @@
       </c>
       <c r="CB6" t="inlineStr">
         <is>
-          <t>2026-06-11 13:45:41</t>
+          <t>2026-06-11 15:58:00</t>
         </is>
       </c>
     </row>
@@ -2127,166 +2127,166 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>1.09</v>
+        <v>1.68</v>
       </c>
       <c r="G7" t="n">
-        <v>1000</v>
+        <v>1.89</v>
       </c>
       <c r="H7" t="n">
-        <v>1.09</v>
+        <v>4.1</v>
       </c>
       <c r="I7" t="n">
-        <v>1000</v>
+        <v>5.8</v>
       </c>
       <c r="J7" t="n">
-        <v>1.1</v>
+        <v>3.7</v>
       </c>
       <c r="K7" t="n">
-        <v>1000</v>
+        <v>4.6</v>
       </c>
       <c r="L7" t="n">
         <v>1.01</v>
       </c>
       <c r="M7" t="n">
-        <v>1.01</v>
+        <v>1.05</v>
       </c>
       <c r="N7" t="n">
-        <v>1.44</v>
+        <v>3.9</v>
       </c>
       <c r="O7" t="n">
-        <v>1.22</v>
+        <v>1.25</v>
       </c>
       <c r="P7" t="n">
-        <v>1.25</v>
+        <v>1.9</v>
       </c>
       <c r="Q7" t="n">
-        <v>1.22</v>
+        <v>1.65</v>
       </c>
       <c r="R7" t="n">
-        <v>1.18</v>
+        <v>1.4</v>
       </c>
       <c r="S7" t="n">
-        <v>1.21</v>
+        <v>2.66</v>
       </c>
       <c r="T7" t="n">
-        <v>1.01</v>
+        <v>1.73</v>
       </c>
       <c r="U7" t="n">
-        <v>1.01</v>
+        <v>2.04</v>
       </c>
       <c r="V7" t="n">
-        <v>1.02</v>
+        <v>1.2</v>
       </c>
       <c r="W7" t="n">
-        <v>1.02</v>
+        <v>2.12</v>
       </c>
       <c r="X7" t="n">
-        <v>1000</v>
+        <v>22</v>
       </c>
       <c r="Y7" t="n">
-        <v>1000</v>
+        <v>24</v>
       </c>
       <c r="Z7" t="n">
-        <v>1000</v>
+        <v>50</v>
       </c>
       <c r="AA7" t="n">
-        <v>1000</v>
+        <v>150</v>
       </c>
       <c r="AB7" t="n">
-        <v>1000</v>
+        <v>11.5</v>
       </c>
       <c r="AC7" t="n">
-        <v>1000</v>
+        <v>11.5</v>
       </c>
       <c r="AD7" t="n">
-        <v>1000</v>
+        <v>25</v>
       </c>
       <c r="AE7" t="n">
-        <v>1000</v>
+        <v>80</v>
       </c>
       <c r="AF7" t="n">
-        <v>1000</v>
+        <v>14</v>
       </c>
       <c r="AG7" t="n">
-        <v>1000</v>
+        <v>12.5</v>
       </c>
       <c r="AH7" t="n">
-        <v>1000</v>
+        <v>23</v>
       </c>
       <c r="AI7" t="n">
-        <v>1000</v>
+        <v>80</v>
       </c>
       <c r="AJ7" t="n">
-        <v>1000</v>
+        <v>23</v>
       </c>
       <c r="AK7" t="n">
-        <v>1000</v>
+        <v>22</v>
       </c>
       <c r="AL7" t="n">
-        <v>1000</v>
+        <v>40</v>
       </c>
       <c r="AM7" t="n">
-        <v>1000</v>
+        <v>120</v>
       </c>
       <c r="AN7" t="n">
-        <v>1000</v>
+        <v>12.5</v>
       </c>
       <c r="AO7" t="n">
-        <v>1000</v>
+        <v>85</v>
       </c>
       <c r="AP7" t="n">
-        <v>1.01</v>
+        <v>3.55</v>
       </c>
       <c r="AQ7" t="n">
-        <v>1.01</v>
+        <v>3.55</v>
       </c>
       <c r="AR7" t="n">
-        <v>1.01</v>
+        <v>3.85</v>
       </c>
       <c r="AS7" t="n">
-        <v>1.01</v>
+        <v>4.1</v>
       </c>
       <c r="AT7" t="n">
-        <v>1.01</v>
+        <v>3.1</v>
       </c>
       <c r="AU7" t="n">
-        <v>1.01</v>
+        <v>3.1</v>
       </c>
       <c r="AV7" t="n">
-        <v>1.01</v>
+        <v>3.6</v>
       </c>
       <c r="AW7" t="n">
-        <v>1.01</v>
+        <v>4</v>
       </c>
       <c r="AX7" t="n">
-        <v>1.01</v>
+        <v>3.25</v>
       </c>
       <c r="AY7" t="n">
-        <v>1.01</v>
+        <v>3.15</v>
       </c>
       <c r="AZ7" t="n">
-        <v>1.01</v>
+        <v>3.55</v>
       </c>
       <c r="BA7" t="n">
-        <v>1.01</v>
+        <v>4</v>
       </c>
       <c r="BB7" t="n">
-        <v>1.01</v>
+        <v>3.55</v>
       </c>
       <c r="BC7" t="n">
-        <v>1.01</v>
+        <v>3.55</v>
       </c>
       <c r="BD7" t="n">
-        <v>1.01</v>
+        <v>3.8</v>
       </c>
       <c r="BE7" t="n">
-        <v>1.01</v>
+        <v>4</v>
       </c>
       <c r="BF7" t="n">
-        <v>1.01</v>
+        <v>3.15</v>
       </c>
       <c r="BG7" t="n">
-        <v>1.01</v>
+        <v>4</v>
       </c>
       <c r="BH7" t="n">
         <v>1000</v>
@@ -2350,7 +2350,7 @@
       </c>
       <c r="CB7" t="inlineStr">
         <is>
-          <t>2026-06-11 13:45:41</t>
+          <t>2026-06-11 15:58:00</t>
         </is>
       </c>
     </row>
@@ -2381,166 +2381,166 @@
         </is>
       </c>
       <c r="F8" t="n">
-        <v>1.59</v>
+        <v>1.61</v>
       </c>
       <c r="G8" t="n">
-        <v>1.77</v>
+        <v>1.75</v>
       </c>
       <c r="H8" t="n">
-        <v>5.5</v>
+        <v>5.7</v>
       </c>
       <c r="I8" t="n">
-        <v>10</v>
+        <v>6.8</v>
       </c>
       <c r="J8" t="n">
-        <v>3.7</v>
+        <v>3.8</v>
       </c>
       <c r="K8" t="n">
-        <v>5.3</v>
+        <v>4.5</v>
       </c>
       <c r="L8" t="n">
         <v>1.31</v>
       </c>
       <c r="M8" t="n">
-        <v>1.01</v>
+        <v>1.06</v>
       </c>
       <c r="N8" t="n">
-        <v>3.2</v>
+        <v>3.55</v>
       </c>
       <c r="O8" t="n">
-        <v>1.28</v>
+        <v>1.31</v>
       </c>
       <c r="P8" t="n">
-        <v>1.89</v>
+        <v>1.92</v>
       </c>
       <c r="Q8" t="n">
-        <v>1.87</v>
+        <v>1.91</v>
       </c>
       <c r="R8" t="n">
-        <v>1.29</v>
+        <v>1.35</v>
       </c>
       <c r="S8" t="n">
-        <v>2.9</v>
+        <v>3.35</v>
       </c>
       <c r="T8" t="n">
-        <v>1.11</v>
+        <v>1.9</v>
       </c>
       <c r="U8" t="n">
-        <v>1.11</v>
+        <v>1.92</v>
       </c>
       <c r="V8" t="n">
-        <v>1.11</v>
+        <v>1.17</v>
       </c>
       <c r="W8" t="n">
-        <v>2.28</v>
+        <v>2.32</v>
       </c>
       <c r="X8" t="n">
-        <v>1000</v>
+        <v>18</v>
       </c>
       <c r="Y8" t="n">
-        <v>1000</v>
+        <v>21</v>
       </c>
       <c r="Z8" t="n">
-        <v>1000</v>
+        <v>60</v>
       </c>
       <c r="AA8" t="n">
-        <v>1000</v>
+        <v>210</v>
       </c>
       <c r="AB8" t="n">
-        <v>1000</v>
+        <v>8.6</v>
       </c>
       <c r="AC8" t="n">
-        <v>1000</v>
+        <v>11</v>
       </c>
       <c r="AD8" t="n">
-        <v>1000</v>
+        <v>29</v>
       </c>
       <c r="AE8" t="n">
-        <v>1000</v>
+        <v>110</v>
       </c>
       <c r="AF8" t="n">
-        <v>1000</v>
+        <v>10.5</v>
       </c>
       <c r="AG8" t="n">
-        <v>1000</v>
+        <v>12</v>
       </c>
       <c r="AH8" t="n">
-        <v>1000</v>
+        <v>27</v>
       </c>
       <c r="AI8" t="n">
-        <v>1000</v>
+        <v>110</v>
       </c>
       <c r="AJ8" t="n">
-        <v>1000</v>
+        <v>17.5</v>
       </c>
       <c r="AK8" t="n">
-        <v>1000</v>
+        <v>22</v>
       </c>
       <c r="AL8" t="n">
-        <v>1000</v>
+        <v>40</v>
       </c>
       <c r="AM8" t="n">
-        <v>1000</v>
+        <v>160</v>
       </c>
       <c r="AN8" t="n">
-        <v>1000</v>
+        <v>11</v>
       </c>
       <c r="AO8" t="n">
-        <v>1000</v>
+        <v>140</v>
       </c>
       <c r="AP8" t="n">
-        <v>1.01</v>
+        <v>11</v>
       </c>
       <c r="AQ8" t="n">
-        <v>1.01</v>
+        <v>14.5</v>
       </c>
       <c r="AR8" t="n">
-        <v>1.01</v>
+        <v>5.4</v>
       </c>
       <c r="AS8" t="n">
-        <v>1.01</v>
+        <v>5.7</v>
       </c>
       <c r="AT8" t="n">
-        <v>1.01</v>
+        <v>7</v>
       </c>
       <c r="AU8" t="n">
-        <v>1.01</v>
+        <v>6.8</v>
       </c>
       <c r="AV8" t="n">
-        <v>1.01</v>
+        <v>17</v>
       </c>
       <c r="AW8" t="n">
-        <v>1.01</v>
+        <v>5.6</v>
       </c>
       <c r="AX8" t="n">
-        <v>1.01</v>
+        <v>7.4</v>
       </c>
       <c r="AY8" t="n">
-        <v>1.01</v>
+        <v>7.4</v>
       </c>
       <c r="AZ8" t="n">
-        <v>1.01</v>
+        <v>15.5</v>
       </c>
       <c r="BA8" t="n">
-        <v>1.01</v>
+        <v>5.6</v>
       </c>
       <c r="BB8" t="n">
-        <v>1.01</v>
+        <v>12</v>
       </c>
       <c r="BC8" t="n">
-        <v>1.01</v>
+        <v>13</v>
       </c>
       <c r="BD8" t="n">
-        <v>1.01</v>
+        <v>5.3</v>
       </c>
       <c r="BE8" t="n">
-        <v>1.01</v>
+        <v>5.7</v>
       </c>
       <c r="BF8" t="n">
-        <v>1.01</v>
+        <v>9</v>
       </c>
       <c r="BG8" t="n">
-        <v>1.01</v>
+        <v>5.7</v>
       </c>
       <c r="BH8" t="n">
         <v>1000</v>
@@ -2604,7 +2604,7 @@
       </c>
       <c r="CB8" t="inlineStr">
         <is>
-          <t>2026-06-11 13:45:41</t>
+          <t>2026-06-11 15:58:00</t>
         </is>
       </c>
     </row>
@@ -2635,7 +2635,7 @@
         </is>
       </c>
       <c r="F9" t="n">
-        <v>4.2</v>
+        <v>4.4</v>
       </c>
       <c r="G9" t="n">
         <v>5.2</v>
@@ -2647,10 +2647,10 @@
         <v>1.85</v>
       </c>
       <c r="J9" t="n">
-        <v>3.95</v>
+        <v>4.1</v>
       </c>
       <c r="K9" t="n">
-        <v>4.7</v>
+        <v>4.8</v>
       </c>
       <c r="L9" t="n">
         <v>1.24</v>
@@ -2659,13 +2659,13 @@
         <v>1.02</v>
       </c>
       <c r="N9" t="n">
-        <v>4.6</v>
+        <v>5.6</v>
       </c>
       <c r="O9" t="n">
         <v>1.18</v>
       </c>
       <c r="P9" t="n">
-        <v>2.44</v>
+        <v>2.5</v>
       </c>
       <c r="Q9" t="n">
         <v>1.53</v>
@@ -2674,13 +2674,13 @@
         <v>1.6</v>
       </c>
       <c r="S9" t="n">
+        <v>2.34</v>
+      </c>
+      <c r="T9" t="n">
+        <v>1.52</v>
+      </c>
+      <c r="U9" t="n">
         <v>2.24</v>
-      </c>
-      <c r="T9" t="n">
-        <v>1.58</v>
-      </c>
-      <c r="U9" t="n">
-        <v>2.38</v>
       </c>
       <c r="V9" t="n">
         <v>2.16</v>
@@ -2719,7 +2719,7 @@
         <v>23</v>
       </c>
       <c r="AH9" t="n">
-        <v>970</v>
+        <v>19.5</v>
       </c>
       <c r="AI9" t="n">
         <v>32</v>
@@ -2746,34 +2746,34 @@
         <v>1.01</v>
       </c>
       <c r="AQ9" t="n">
-        <v>1.01</v>
+        <v>10</v>
       </c>
       <c r="AR9" t="n">
-        <v>1.01</v>
+        <v>10</v>
       </c>
       <c r="AS9" t="n">
-        <v>1.01</v>
+        <v>14.5</v>
       </c>
       <c r="AT9" t="n">
-        <v>1.01</v>
+        <v>18</v>
       </c>
       <c r="AU9" t="n">
-        <v>1.01</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AV9" t="n">
-        <v>1.01</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AW9" t="n">
-        <v>1.01</v>
+        <v>12.5</v>
       </c>
       <c r="AX9" t="n">
         <v>1.01</v>
       </c>
       <c r="AY9" t="n">
-        <v>1.01</v>
+        <v>14.5</v>
       </c>
       <c r="AZ9" t="n">
-        <v>1.01</v>
+        <v>12.5</v>
       </c>
       <c r="BA9" t="n">
         <v>1.01</v>
@@ -2794,7 +2794,7 @@
         <v>1.01</v>
       </c>
       <c r="BG9" t="n">
-        <v>1.01</v>
+        <v>5.7</v>
       </c>
       <c r="BH9" t="n">
         <v>5.1</v>
@@ -2858,7 +2858,7 @@
       </c>
       <c r="CB9" t="inlineStr">
         <is>
-          <t>2026-06-11 13:45:41</t>
+          <t>2026-06-11 15:58:00</t>
         </is>
       </c>
     </row>
@@ -2889,22 +2889,22 @@
         </is>
       </c>
       <c r="F10" t="n">
-        <v>1.46</v>
+        <v>1.54</v>
       </c>
       <c r="G10" t="n">
-        <v>1.66</v>
+        <v>1.68</v>
       </c>
       <c r="H10" t="n">
-        <v>5</v>
+        <v>5.3</v>
       </c>
       <c r="I10" t="n">
-        <v>7.4</v>
+        <v>6.6</v>
       </c>
       <c r="J10" t="n">
-        <v>4.3</v>
+        <v>4.4</v>
       </c>
       <c r="K10" t="n">
-        <v>5.8</v>
+        <v>5.3</v>
       </c>
       <c r="L10" t="n">
         <v>1.23</v>
@@ -2913,206 +2913,206 @@
         <v>1.01</v>
       </c>
       <c r="N10" t="n">
-        <v>3.45</v>
+        <v>5.4</v>
       </c>
       <c r="O10" t="n">
-        <v>1.16</v>
+        <v>1.18</v>
       </c>
       <c r="P10" t="n">
-        <v>2.32</v>
+        <v>2.5</v>
       </c>
       <c r="Q10" t="n">
-        <v>1.47</v>
+        <v>1.54</v>
       </c>
       <c r="R10" t="n">
-        <v>1.58</v>
+        <v>1.6</v>
       </c>
       <c r="S10" t="n">
-        <v>2.08</v>
+        <v>2.34</v>
       </c>
       <c r="T10" t="n">
-        <v>1.62</v>
+        <v>1.64</v>
       </c>
       <c r="U10" t="n">
-        <v>2.14</v>
+        <v>2.26</v>
       </c>
       <c r="V10" t="n">
-        <v>1.15</v>
+        <v>1.17</v>
       </c>
       <c r="W10" t="n">
-        <v>2.5</v>
+        <v>2.48</v>
       </c>
       <c r="X10" t="n">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="Y10" t="n">
         <v>950</v>
       </c>
       <c r="Z10" t="n">
+        <v>55</v>
+      </c>
+      <c r="AA10" t="n">
+        <v>160</v>
+      </c>
+      <c r="AB10" t="n">
+        <v>13</v>
+      </c>
+      <c r="AC10" t="n">
+        <v>12</v>
+      </c>
+      <c r="AD10" t="n">
+        <v>950</v>
+      </c>
+      <c r="AE10" t="n">
         <v>70</v>
       </c>
-      <c r="AA10" t="n">
-        <v>190</v>
-      </c>
-      <c r="AB10" t="n">
+      <c r="AF10" t="n">
+        <v>13</v>
+      </c>
+      <c r="AG10" t="n">
+        <v>11</v>
+      </c>
+      <c r="AH10" t="n">
         <v>970</v>
       </c>
-      <c r="AC10" t="n">
-        <v>14.5</v>
-      </c>
-      <c r="AD10" t="n">
-        <v>30</v>
-      </c>
-      <c r="AE10" t="n">
-        <v>90</v>
-      </c>
-      <c r="AF10" t="n">
-        <v>970</v>
-      </c>
-      <c r="AG10" t="n">
-        <v>13</v>
-      </c>
-      <c r="AH10" t="n">
-        <v>950</v>
-      </c>
       <c r="AI10" t="n">
-        <v>75</v>
+        <v>60</v>
       </c>
       <c r="AJ10" t="n">
         <v>970</v>
       </c>
       <c r="AK10" t="n">
-        <v>18</v>
+        <v>16.5</v>
       </c>
       <c r="AL10" t="n">
-        <v>34</v>
+        <v>29</v>
       </c>
       <c r="AM10" t="n">
-        <v>95</v>
+        <v>80</v>
       </c>
       <c r="AN10" t="n">
         <v>7</v>
       </c>
       <c r="AO10" t="n">
-        <v>80</v>
+        <v>60</v>
       </c>
       <c r="AP10" t="n">
-        <v>3.75</v>
+        <v>21</v>
       </c>
       <c r="AQ10" t="n">
-        <v>3.8</v>
+        <v>6.8</v>
       </c>
       <c r="AR10" t="n">
-        <v>4</v>
+        <v>6.8</v>
       </c>
       <c r="AS10" t="n">
-        <v>4.1</v>
+        <v>7.4</v>
       </c>
       <c r="AT10" t="n">
-        <v>3.3</v>
+        <v>10</v>
       </c>
       <c r="AU10" t="n">
-        <v>3.25</v>
+        <v>9.4</v>
       </c>
       <c r="AV10" t="n">
-        <v>3.7</v>
+        <v>18</v>
       </c>
       <c r="AW10" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="AX10" t="n">
-        <v>3.25</v>
+        <v>10</v>
       </c>
       <c r="AY10" t="n">
-        <v>3.2</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AZ10" t="n">
-        <v>3.6</v>
+        <v>15</v>
       </c>
       <c r="BA10" t="n">
-        <v>4</v>
+        <v>6.8</v>
       </c>
       <c r="BB10" t="n">
-        <v>3.45</v>
+        <v>14</v>
       </c>
       <c r="BC10" t="n">
-        <v>3.4</v>
+        <v>13</v>
       </c>
       <c r="BD10" t="n">
-        <v>3.75</v>
+        <v>6.8</v>
       </c>
       <c r="BE10" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="BF10" t="n">
-        <v>2.64</v>
+        <v>5.4</v>
       </c>
       <c r="BG10" t="n">
-        <v>4</v>
+        <v>6.8</v>
       </c>
       <c r="BH10" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="BI10" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="BJ10" t="n">
+        <v>10</v>
+      </c>
+      <c r="BK10" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="BL10" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BM10" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="BN10" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="BO10" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="BP10" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="BQ10" t="n">
         <v>5</v>
       </c>
-      <c r="BI10" t="n">
-        <v>2.86</v>
-      </c>
-      <c r="BJ10" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BK10" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="BL10" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BM10" t="n">
-        <v>6.2</v>
-      </c>
-      <c r="BN10" t="n">
+      <c r="BR10" t="n">
+        <v>21</v>
+      </c>
+      <c r="BS10" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="BT10" t="n">
+        <v>10</v>
+      </c>
+      <c r="BU10" t="n">
         <v>4.9</v>
       </c>
-      <c r="BO10" t="n">
-        <v>2.82</v>
-      </c>
-      <c r="BP10" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BQ10" t="n">
-        <v>4</v>
-      </c>
-      <c r="BR10" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BS10" t="n">
-        <v>5.1</v>
-      </c>
-      <c r="BT10" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BU10" t="n">
-        <v>4.1</v>
-      </c>
       <c r="BV10" t="n">
         <v>1000</v>
       </c>
       <c r="BW10" t="n">
-        <v>5.9</v>
+        <v>8</v>
       </c>
       <c r="BX10" t="n">
         <v>1000</v>
       </c>
       <c r="BY10" t="n">
-        <v>5.9</v>
+        <v>8</v>
       </c>
       <c r="BZ10" t="n">
-        <v>1000</v>
+        <v>13.5</v>
       </c>
       <c r="CA10" t="n">
-        <v>4.4</v>
+        <v>5.6</v>
       </c>
       <c r="CB10" t="inlineStr">
         <is>
-          <t>2026-06-11 13:45:41</t>
+          <t>2026-06-11 15:58:00</t>
         </is>
       </c>
     </row>
@@ -3143,169 +3143,169 @@
         </is>
       </c>
       <c r="F11" t="n">
-        <v>2.36</v>
+        <v>2.16</v>
       </c>
       <c r="G11" t="n">
-        <v>2.58</v>
+        <v>2.34</v>
       </c>
       <c r="H11" t="n">
-        <v>3.6</v>
+        <v>4.1</v>
       </c>
       <c r="I11" t="n">
-        <v>4.1</v>
+        <v>4.6</v>
       </c>
       <c r="J11" t="n">
-        <v>2.9</v>
+        <v>2.96</v>
       </c>
       <c r="K11" t="n">
-        <v>3.15</v>
+        <v>3.2</v>
       </c>
       <c r="L11" t="n">
-        <v>1.5</v>
+        <v>1.6</v>
       </c>
       <c r="M11" t="n">
-        <v>1.14</v>
+        <v>1.13</v>
       </c>
       <c r="N11" t="n">
-        <v>2.44</v>
+        <v>2.54</v>
       </c>
       <c r="O11" t="n">
-        <v>1.59</v>
+        <v>1.57</v>
       </c>
       <c r="P11" t="n">
-        <v>1.48</v>
+        <v>1.51</v>
       </c>
       <c r="Q11" t="n">
-        <v>2.76</v>
+        <v>2.72</v>
       </c>
       <c r="R11" t="n">
         <v>1.18</v>
       </c>
       <c r="S11" t="n">
-        <v>5.9</v>
+        <v>5.8</v>
       </c>
       <c r="T11" t="n">
         <v>2.18</v>
       </c>
       <c r="U11" t="n">
-        <v>1.72</v>
+        <v>1.74</v>
       </c>
       <c r="V11" t="n">
-        <v>1.33</v>
+        <v>1.28</v>
       </c>
       <c r="W11" t="n">
-        <v>1.63</v>
+        <v>1.74</v>
       </c>
       <c r="X11" t="n">
-        <v>9.6</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="Y11" t="n">
-        <v>10</v>
+        <v>13.5</v>
       </c>
       <c r="Z11" t="n">
-        <v>26</v>
+        <v>36</v>
       </c>
       <c r="AA11" t="n">
-        <v>110</v>
+        <v>130</v>
       </c>
       <c r="AB11" t="n">
-        <v>7.4</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AC11" t="n">
-        <v>7.2</v>
+        <v>8.6</v>
       </c>
       <c r="AD11" t="n">
-        <v>17.5</v>
+        <v>23</v>
       </c>
       <c r="AE11" t="n">
-        <v>80</v>
+        <v>95</v>
       </c>
       <c r="AF11" t="n">
+        <v>15</v>
+      </c>
+      <c r="AG11" t="n">
         <v>14.5</v>
-      </c>
-      <c r="AG11" t="n">
-        <v>15.5</v>
       </c>
       <c r="AH11" t="n">
         <v>30</v>
       </c>
       <c r="AI11" t="n">
-        <v>120</v>
+        <v>130</v>
       </c>
       <c r="AJ11" t="n">
-        <v>40</v>
+        <v>36</v>
       </c>
       <c r="AK11" t="n">
         <v>38</v>
       </c>
       <c r="AL11" t="n">
-        <v>85</v>
+        <v>80</v>
       </c>
       <c r="AM11" t="n">
         <v>260</v>
       </c>
       <c r="AN11" t="n">
-        <v>50</v>
+        <v>38</v>
       </c>
       <c r="AO11" t="n">
-        <v>120</v>
+        <v>150</v>
       </c>
       <c r="AP11" t="n">
         <v>6</v>
       </c>
       <c r="AQ11" t="n">
-        <v>8.6</v>
+        <v>9.6</v>
       </c>
       <c r="AR11" t="n">
-        <v>21</v>
+        <v>4.1</v>
       </c>
       <c r="AS11" t="n">
-        <v>6.8</v>
+        <v>4.4</v>
       </c>
       <c r="AT11" t="n">
-        <v>6.2</v>
+        <v>6</v>
       </c>
       <c r="AU11" t="n">
-        <v>6.2</v>
+        <v>5.4</v>
       </c>
       <c r="AV11" t="n">
-        <v>12.5</v>
+        <v>3.85</v>
       </c>
       <c r="AW11" t="n">
-        <v>6.8</v>
+        <v>4.4</v>
       </c>
       <c r="AX11" t="n">
-        <v>12</v>
+        <v>3.55</v>
       </c>
       <c r="AY11" t="n">
-        <v>11</v>
+        <v>3.5</v>
       </c>
       <c r="AZ11" t="n">
-        <v>17.5</v>
+        <v>18</v>
       </c>
       <c r="BA11" t="n">
-        <v>7</v>
+        <v>4.4</v>
       </c>
       <c r="BB11" t="n">
-        <v>6.2</v>
+        <v>4.1</v>
       </c>
       <c r="BC11" t="n">
-        <v>6.2</v>
+        <v>4.1</v>
       </c>
       <c r="BD11" t="n">
-        <v>6.8</v>
+        <v>4.3</v>
       </c>
       <c r="BE11" t="n">
-        <v>7.2</v>
+        <v>4.5</v>
       </c>
       <c r="BF11" t="n">
-        <v>6.4</v>
+        <v>4.1</v>
       </c>
       <c r="BG11" t="n">
-        <v>7</v>
+        <v>4.4</v>
       </c>
       <c r="BH11" t="n">
-        <v>1000</v>
+        <v>3.05</v>
       </c>
       <c r="BI11" t="n">
         <v>1.04</v>
@@ -3314,59 +3314,59 @@
         <v>1000</v>
       </c>
       <c r="BK11" t="n">
-        <v>1.04</v>
+        <v>1.5</v>
       </c>
       <c r="BL11" t="n">
         <v>1000</v>
       </c>
       <c r="BM11" t="n">
-        <v>1.04</v>
+        <v>1.5</v>
       </c>
       <c r="BN11" t="n">
         <v>1000</v>
       </c>
       <c r="BO11" t="n">
-        <v>1.04</v>
+        <v>1.5</v>
       </c>
       <c r="BP11" t="n">
         <v>1000</v>
       </c>
       <c r="BQ11" t="n">
-        <v>1.04</v>
+        <v>1.5</v>
       </c>
       <c r="BR11" t="n">
         <v>1000</v>
       </c>
       <c r="BS11" t="n">
-        <v>1.04</v>
+        <v>1.5</v>
       </c>
       <c r="BT11" t="n">
         <v>1000</v>
       </c>
       <c r="BU11" t="n">
-        <v>1.04</v>
+        <v>1.5</v>
       </c>
       <c r="BV11" t="n">
         <v>1000</v>
       </c>
       <c r="BW11" t="n">
-        <v>1.04</v>
+        <v>1.5</v>
       </c>
       <c r="BX11" t="n">
         <v>1000</v>
       </c>
       <c r="BY11" t="n">
-        <v>1.04</v>
+        <v>1.5</v>
       </c>
       <c r="BZ11" t="n">
         <v>1000</v>
       </c>
       <c r="CA11" t="n">
-        <v>1.04</v>
+        <v>1.5</v>
       </c>
       <c r="CB11" t="inlineStr">
         <is>
-          <t>2026-06-11 13:45:41</t>
+          <t>2026-06-11 15:58:00</t>
         </is>
       </c>
     </row>
@@ -3397,100 +3397,100 @@
         </is>
       </c>
       <c r="F12" t="n">
-        <v>2.38</v>
+        <v>2.1</v>
       </c>
       <c r="G12" t="n">
-        <v>2.94</v>
+        <v>2.36</v>
       </c>
       <c r="H12" t="n">
-        <v>2.6</v>
+        <v>3.15</v>
       </c>
       <c r="I12" t="n">
-        <v>3.25</v>
+        <v>3.75</v>
       </c>
       <c r="J12" t="n">
-        <v>2.84</v>
+        <v>3.5</v>
       </c>
       <c r="K12" t="n">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="L12" t="n">
-        <v>1.35</v>
+        <v>1.33</v>
       </c>
       <c r="M12" t="n">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="N12" t="n">
-        <v>3.75</v>
+        <v>4.2</v>
       </c>
       <c r="O12" t="n">
-        <v>1.27</v>
+        <v>1.25</v>
       </c>
       <c r="P12" t="n">
-        <v>1.9</v>
+        <v>2.12</v>
       </c>
       <c r="Q12" t="n">
-        <v>1.79</v>
+        <v>1.72</v>
       </c>
       <c r="R12" t="n">
-        <v>1.35</v>
+        <v>1.44</v>
       </c>
       <c r="S12" t="n">
-        <v>2.86</v>
+        <v>2.8</v>
       </c>
       <c r="T12" t="n">
-        <v>1.65</v>
+        <v>1.62</v>
       </c>
       <c r="U12" t="n">
-        <v>2.1</v>
+        <v>2.26</v>
       </c>
       <c r="V12" t="n">
-        <v>1.44</v>
+        <v>1.37</v>
       </c>
       <c r="W12" t="n">
-        <v>1.51</v>
+        <v>1.73</v>
       </c>
       <c r="X12" t="n">
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="Y12" t="n">
-        <v>14</v>
+        <v>16.5</v>
       </c>
       <c r="Z12" t="n">
-        <v>23</v>
+        <v>40</v>
       </c>
       <c r="AA12" t="n">
-        <v>60</v>
+        <v>90</v>
       </c>
       <c r="AB12" t="n">
-        <v>13</v>
+        <v>12.5</v>
       </c>
       <c r="AC12" t="n">
-        <v>9</v>
+        <v>9.4</v>
       </c>
       <c r="AD12" t="n">
-        <v>14.5</v>
+        <v>15.5</v>
       </c>
       <c r="AE12" t="n">
-        <v>36</v>
+        <v>55</v>
       </c>
       <c r="AF12" t="n">
-        <v>20</v>
+        <v>16.5</v>
       </c>
       <c r="AG12" t="n">
-        <v>13.5</v>
+        <v>12</v>
       </c>
       <c r="AH12" t="n">
-        <v>18.5</v>
+        <v>17</v>
       </c>
       <c r="AI12" t="n">
-        <v>55</v>
+        <v>65</v>
       </c>
       <c r="AJ12" t="n">
-        <v>50</v>
+        <v>38</v>
       </c>
       <c r="AK12" t="n">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="AL12" t="n">
         <v>44</v>
@@ -3499,128 +3499,128 @@
         <v>100</v>
       </c>
       <c r="AN12" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="AO12" t="n">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="AP12" t="n">
-        <v>4.5</v>
+        <v>15.5</v>
       </c>
       <c r="AQ12" t="n">
-        <v>4.3</v>
+        <v>12</v>
       </c>
       <c r="AR12" t="n">
-        <v>4.9</v>
+        <v>19.5</v>
       </c>
       <c r="AS12" t="n">
-        <v>5.4</v>
+        <v>7.2</v>
       </c>
       <c r="AT12" t="n">
-        <v>4.2</v>
+        <v>8.4</v>
       </c>
       <c r="AU12" t="n">
-        <v>3.85</v>
+        <v>6.6</v>
       </c>
       <c r="AV12" t="n">
-        <v>4.3</v>
+        <v>11.5</v>
       </c>
       <c r="AW12" t="n">
-        <v>5.2</v>
+        <v>6.8</v>
       </c>
       <c r="AX12" t="n">
+        <v>11</v>
+      </c>
+      <c r="AY12" t="n">
+        <v>8</v>
+      </c>
+      <c r="AZ12" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="BA12" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="BB12" t="n">
+        <v>19.5</v>
+      </c>
+      <c r="BC12" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="BD12" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="BE12" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="BF12" t="n">
+        <v>10</v>
+      </c>
+      <c r="BG12" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="BH12" t="n">
+        <v>4</v>
+      </c>
+      <c r="BI12" t="n">
+        <v>3</v>
+      </c>
+      <c r="BJ12" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="BK12" t="n">
+        <v>5.6</v>
+      </c>
+      <c r="BL12" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BM12" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="BN12" t="n">
+        <v>5.6</v>
+      </c>
+      <c r="BO12" t="n">
         <v>4.6</v>
       </c>
-      <c r="AY12" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="AZ12" t="n">
-        <v>4.7</v>
-      </c>
-      <c r="BA12" t="n">
-        <v>5.4</v>
-      </c>
-      <c r="BB12" t="n">
-        <v>5.3</v>
-      </c>
-      <c r="BC12" t="n">
-        <v>5.1</v>
-      </c>
-      <c r="BD12" t="n">
-        <v>5.4</v>
-      </c>
-      <c r="BE12" t="n">
-        <v>5.6</v>
-      </c>
-      <c r="BF12" t="n">
-        <v>5</v>
-      </c>
-      <c r="BG12" t="n">
-        <v>5</v>
-      </c>
-      <c r="BH12" t="n">
-        <v>3.8</v>
-      </c>
-      <c r="BI12" t="n">
-        <v>2.82</v>
-      </c>
-      <c r="BJ12" t="n">
-        <v>10</v>
-      </c>
-      <c r="BK12" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="BL12" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BM12" t="n">
+      <c r="BP12" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="BQ12" t="n">
+        <v>6</v>
+      </c>
+      <c r="BR12" t="n">
+        <v>38</v>
+      </c>
+      <c r="BS12" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="BT12" t="n">
         <v>7</v>
       </c>
-      <c r="BN12" t="n">
-        <v>6.2</v>
-      </c>
-      <c r="BO12" t="n">
-        <v>3.35</v>
-      </c>
-      <c r="BP12" t="n">
+      <c r="BU12" t="n">
+        <v>5.7</v>
+      </c>
+      <c r="BV12" t="n">
+        <v>26</v>
+      </c>
+      <c r="BW12" t="n">
+        <v>7</v>
+      </c>
+      <c r="BX12" t="n">
+        <v>48</v>
+      </c>
+      <c r="BY12" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="BZ12" t="n">
         <v>22</v>
       </c>
-      <c r="BQ12" t="n">
-        <v>5.5</v>
-      </c>
-      <c r="BR12" t="n">
-        <v>34</v>
-      </c>
-      <c r="BS12" t="n">
-        <v>6</v>
-      </c>
-      <c r="BT12" t="n">
-        <v>6.6</v>
-      </c>
-      <c r="BU12" t="n">
-        <v>3.45</v>
-      </c>
-      <c r="BV12" t="n">
-        <v>24</v>
-      </c>
-      <c r="BW12" t="n">
-        <v>5.6</v>
-      </c>
-      <c r="BX12" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BY12" t="n">
-        <v>6</v>
-      </c>
-      <c r="BZ12" t="n">
-        <v>27</v>
-      </c>
       <c r="CA12" t="n">
-        <v>5.8</v>
+        <v>6.8</v>
       </c>
       <c r="CB12" t="inlineStr">
         <is>
-          <t>2026-06-11 13:45:41</t>
+          <t>2026-06-11 15:58:00</t>
         </is>
       </c>
     </row>
@@ -3675,7 +3675,7 @@
         <v>1.02</v>
       </c>
       <c r="N13" t="n">
-        <v>7.2</v>
+        <v>7</v>
       </c>
       <c r="O13" t="n">
         <v>1.12</v>
@@ -3783,7 +3783,7 @@
         <v>5.5</v>
       </c>
       <c r="AX13" t="n">
-        <v>6.8</v>
+        <v>7.4</v>
       </c>
       <c r="AY13" t="n">
         <v>11</v>
@@ -3798,7 +3798,7 @@
         <v>7</v>
       </c>
       <c r="BC13" t="n">
-        <v>4.3</v>
+        <v>11.5</v>
       </c>
       <c r="BD13" t="n">
         <v>5.1</v>
@@ -3822,7 +3822,7 @@
         <v>1000</v>
       </c>
       <c r="BK13" t="n">
-        <v>6.6</v>
+        <v>11.5</v>
       </c>
       <c r="BL13" t="n">
         <v>1000</v>
@@ -3834,13 +3834,13 @@
         <v>3.9</v>
       </c>
       <c r="BO13" t="n">
-        <v>3.1</v>
+        <v>3.15</v>
       </c>
       <c r="BP13" t="n">
         <v>5.9</v>
       </c>
       <c r="BQ13" t="n">
-        <v>4.5</v>
+        <v>4.6</v>
       </c>
       <c r="BR13" t="n">
         <v>1000</v>
@@ -3870,11 +3870,11 @@
         <v>6.8</v>
       </c>
       <c r="CA13" t="n">
-        <v>5.2</v>
+        <v>5.3</v>
       </c>
       <c r="CB13" t="inlineStr">
         <is>
-          <t>2026-06-11 13:45:41</t>
+          <t>2026-06-11 15:58:00</t>
         </is>
       </c>
     </row>
@@ -3905,13 +3905,13 @@
         </is>
       </c>
       <c r="F14" t="n">
-        <v>3.95</v>
+        <v>4</v>
       </c>
       <c r="G14" t="n">
         <v>5</v>
       </c>
       <c r="H14" t="n">
-        <v>1.87</v>
+        <v>1.89</v>
       </c>
       <c r="I14" t="n">
         <v>2.06</v>
@@ -3920,37 +3920,37 @@
         <v>3.4</v>
       </c>
       <c r="K14" t="n">
-        <v>3.9</v>
+        <v>3.95</v>
       </c>
       <c r="L14" t="n">
         <v>1.01</v>
       </c>
       <c r="M14" t="n">
-        <v>1.06</v>
+        <v>1.07</v>
       </c>
       <c r="N14" t="n">
         <v>3.4</v>
       </c>
       <c r="O14" t="n">
-        <v>1.32</v>
+        <v>1.34</v>
       </c>
       <c r="P14" t="n">
-        <v>1.31</v>
+        <v>1.8</v>
       </c>
       <c r="Q14" t="n">
-        <v>1.92</v>
+        <v>2</v>
       </c>
       <c r="R14" t="n">
         <v>1.31</v>
       </c>
       <c r="S14" t="n">
-        <v>1.07</v>
+        <v>2.9</v>
       </c>
       <c r="T14" t="n">
-        <v>1.11</v>
+        <v>1.85</v>
       </c>
       <c r="U14" t="n">
-        <v>1.11</v>
+        <v>1.96</v>
       </c>
       <c r="V14" t="n">
         <v>1.94</v>
@@ -4031,7 +4031,7 @@
         <v>3.05</v>
       </c>
       <c r="AV14" t="n">
-        <v>3.2</v>
+        <v>3.25</v>
       </c>
       <c r="AW14" t="n">
         <v>3.75</v>
@@ -4128,7 +4128,7 @@
       </c>
       <c r="CB14" t="inlineStr">
         <is>
-          <t>2026-06-11 13:45:41</t>
+          <t>2026-06-11 15:58:00</t>
         </is>
       </c>
     </row>
@@ -4171,7 +4171,7 @@
         <v>3.9</v>
       </c>
       <c r="J15" t="n">
-        <v>2.78</v>
+        <v>2.76</v>
       </c>
       <c r="K15" t="n">
         <v>3.2</v>
@@ -4204,7 +4204,7 @@
         <v>2.2</v>
       </c>
       <c r="U15" t="n">
-        <v>1.68</v>
+        <v>1.7</v>
       </c>
       <c r="V15" t="n">
         <v>1.34</v>
@@ -4267,55 +4267,55 @@
         <v>120</v>
       </c>
       <c r="AP15" t="n">
-        <v>5.7</v>
+        <v>6.4</v>
       </c>
       <c r="AQ15" t="n">
-        <v>6.8</v>
+        <v>7.8</v>
       </c>
       <c r="AR15" t="n">
-        <v>16.5</v>
+        <v>19.5</v>
       </c>
       <c r="AS15" t="n">
         <v>4.2</v>
       </c>
       <c r="AT15" t="n">
-        <v>5.5</v>
+        <v>6.2</v>
       </c>
       <c r="AU15" t="n">
-        <v>5.9</v>
+        <v>6</v>
       </c>
       <c r="AV15" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="AW15" t="n">
         <v>4.1</v>
       </c>
       <c r="AX15" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="AY15" t="n">
         <v>11</v>
       </c>
-      <c r="AY15" t="n">
-        <v>9.800000000000001</v>
-      </c>
       <c r="AZ15" t="n">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="BA15" t="n">
         <v>4.2</v>
       </c>
       <c r="BB15" t="n">
-        <v>30</v>
+        <v>4.1</v>
       </c>
       <c r="BC15" t="n">
-        <v>4</v>
+        <v>4.1</v>
       </c>
       <c r="BD15" t="n">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="BE15" t="n">
         <v>4.3</v>
       </c>
       <c r="BF15" t="n">
-        <v>34</v>
+        <v>4.1</v>
       </c>
       <c r="BG15" t="n">
         <v>4.2</v>
@@ -4342,7 +4342,7 @@
         <v>5.4</v>
       </c>
       <c r="BO15" t="n">
-        <v>4</v>
+        <v>4.5</v>
       </c>
       <c r="BP15" t="n">
         <v>25</v>
@@ -4360,7 +4360,7 @@
         <v>6.8</v>
       </c>
       <c r="BU15" t="n">
-        <v>4.9</v>
+        <v>5.5</v>
       </c>
       <c r="BV15" t="n">
         <v>1000</v>
@@ -4382,7 +4382,7 @@
       </c>
       <c r="CB15" t="inlineStr">
         <is>
-          <t>2026-06-11 13:45:41</t>
+          <t>2026-06-11 15:58:00</t>
         </is>
       </c>
     </row>
@@ -4413,22 +4413,22 @@
         </is>
       </c>
       <c r="F16" t="n">
-        <v>2.82</v>
+        <v>2.86</v>
       </c>
       <c r="G16" t="n">
-        <v>3.15</v>
+        <v>2.94</v>
       </c>
       <c r="H16" t="n">
-        <v>2.4</v>
+        <v>2.46</v>
       </c>
       <c r="I16" t="n">
-        <v>2.56</v>
+        <v>2.6</v>
       </c>
       <c r="J16" t="n">
-        <v>3.65</v>
+        <v>3.7</v>
       </c>
       <c r="K16" t="n">
-        <v>4.1</v>
+        <v>3.95</v>
       </c>
       <c r="L16" t="n">
         <v>1.01</v>
@@ -4440,139 +4440,139 @@
         <v>4.8</v>
       </c>
       <c r="O16" t="n">
-        <v>1.22</v>
+        <v>1.23</v>
       </c>
       <c r="P16" t="n">
         <v>2.36</v>
       </c>
       <c r="Q16" t="n">
-        <v>1.47</v>
+        <v>1.68</v>
       </c>
       <c r="R16" t="n">
-        <v>1.39</v>
+        <v>1.52</v>
       </c>
       <c r="S16" t="n">
-        <v>2.16</v>
+        <v>2.68</v>
       </c>
       <c r="T16" t="n">
-        <v>1.6</v>
+        <v>1.59</v>
       </c>
       <c r="U16" t="n">
         <v>2.44</v>
       </c>
       <c r="V16" t="n">
-        <v>1.64</v>
+        <v>1.63</v>
       </c>
       <c r="W16" t="n">
-        <v>1.47</v>
+        <v>1.52</v>
       </c>
       <c r="X16" t="n">
-        <v>1000</v>
+        <v>25</v>
       </c>
       <c r="Y16" t="n">
-        <v>1000</v>
+        <v>14.5</v>
       </c>
       <c r="Z16" t="n">
-        <v>1000</v>
+        <v>19.5</v>
       </c>
       <c r="AA16" t="n">
-        <v>1000</v>
+        <v>36</v>
       </c>
       <c r="AB16" t="n">
-        <v>1000</v>
+        <v>18.5</v>
       </c>
       <c r="AC16" t="n">
-        <v>1000</v>
+        <v>11</v>
       </c>
       <c r="AD16" t="n">
-        <v>1000</v>
+        <v>14.5</v>
       </c>
       <c r="AE16" t="n">
-        <v>1000</v>
+        <v>26</v>
       </c>
       <c r="AF16" t="n">
-        <v>1000</v>
+        <v>24</v>
       </c>
       <c r="AG16" t="n">
-        <v>1000</v>
+        <v>16.5</v>
       </c>
       <c r="AH16" t="n">
-        <v>1000</v>
+        <v>16</v>
       </c>
       <c r="AI16" t="n">
-        <v>1000</v>
+        <v>40</v>
       </c>
       <c r="AJ16" t="n">
-        <v>1000</v>
+        <v>48</v>
       </c>
       <c r="AK16" t="n">
-        <v>1000</v>
+        <v>32</v>
       </c>
       <c r="AL16" t="n">
-        <v>1000</v>
+        <v>38</v>
       </c>
       <c r="AM16" t="n">
-        <v>1000</v>
+        <v>70</v>
       </c>
       <c r="AN16" t="n">
-        <v>1000</v>
+        <v>25</v>
       </c>
       <c r="AO16" t="n">
-        <v>1000</v>
+        <v>18.5</v>
       </c>
       <c r="AP16" t="n">
-        <v>1.01</v>
+        <v>17</v>
       </c>
       <c r="AQ16" t="n">
-        <v>1.01</v>
+        <v>11.5</v>
       </c>
       <c r="AR16" t="n">
-        <v>1.01</v>
+        <v>15.5</v>
       </c>
       <c r="AS16" t="n">
-        <v>1.01</v>
+        <v>5.1</v>
       </c>
       <c r="AT16" t="n">
-        <v>1.01</v>
+        <v>12.5</v>
       </c>
       <c r="AU16" t="n">
-        <v>1.01</v>
+        <v>7.6</v>
       </c>
       <c r="AV16" t="n">
-        <v>1.01</v>
+        <v>10</v>
       </c>
       <c r="AW16" t="n">
-        <v>1.01</v>
+        <v>20</v>
       </c>
       <c r="AX16" t="n">
-        <v>1.01</v>
+        <v>19</v>
       </c>
       <c r="AY16" t="n">
-        <v>1.01</v>
+        <v>11</v>
       </c>
       <c r="AZ16" t="n">
-        <v>1.01</v>
+        <v>13</v>
       </c>
       <c r="BA16" t="n">
-        <v>1.01</v>
+        <v>5.1</v>
       </c>
       <c r="BB16" t="n">
-        <v>1.01</v>
+        <v>5.2</v>
       </c>
       <c r="BC16" t="n">
-        <v>1.01</v>
+        <v>5</v>
       </c>
       <c r="BD16" t="n">
-        <v>1.01</v>
+        <v>5.1</v>
       </c>
       <c r="BE16" t="n">
-        <v>1.01</v>
+        <v>5.4</v>
       </c>
       <c r="BF16" t="n">
-        <v>1.01</v>
+        <v>17.5</v>
       </c>
       <c r="BG16" t="n">
-        <v>1.01</v>
+        <v>13</v>
       </c>
       <c r="BH16" t="n">
         <v>1000</v>
@@ -4636,7 +4636,7 @@
       </c>
       <c r="CB16" t="inlineStr">
         <is>
-          <t>2026-06-11 13:45:41</t>
+          <t>2026-06-11 15:58:00</t>
         </is>
       </c>
     </row>
@@ -4709,7 +4709,7 @@
         <v>3.1</v>
       </c>
       <c r="T17" t="n">
-        <v>2.24</v>
+        <v>2.22</v>
       </c>
       <c r="U17" t="n">
         <v>1.74</v>
@@ -4730,19 +4730,19 @@
         <v>130</v>
       </c>
       <c r="AA17" t="n">
-        <v>610</v>
+        <v>580</v>
       </c>
       <c r="AB17" t="n">
         <v>9</v>
       </c>
       <c r="AC17" t="n">
-        <v>15</v>
+        <v>14.5</v>
       </c>
       <c r="AD17" t="n">
         <v>50</v>
       </c>
       <c r="AE17" t="n">
-        <v>270</v>
+        <v>250</v>
       </c>
       <c r="AF17" t="n">
         <v>9.199999999999999</v>
@@ -4754,7 +4754,7 @@
         <v>40</v>
       </c>
       <c r="AI17" t="n">
-        <v>210</v>
+        <v>200</v>
       </c>
       <c r="AJ17" t="n">
         <v>13</v>
@@ -4766,19 +4766,19 @@
         <v>55</v>
       </c>
       <c r="AM17" t="n">
-        <v>270</v>
+        <v>260</v>
       </c>
       <c r="AN17" t="n">
         <v>8</v>
       </c>
       <c r="AO17" t="n">
-        <v>440</v>
+        <v>410</v>
       </c>
       <c r="AP17" t="n">
         <v>14.5</v>
       </c>
       <c r="AQ17" t="n">
-        <v>3.95</v>
+        <v>4</v>
       </c>
       <c r="AR17" t="n">
         <v>4.3</v>
@@ -4793,10 +4793,10 @@
         <v>9</v>
       </c>
       <c r="AV17" t="n">
-        <v>4</v>
+        <v>4.1</v>
       </c>
       <c r="AW17" t="n">
-        <v>4.3</v>
+        <v>4.4</v>
       </c>
       <c r="AX17" t="n">
         <v>6.4</v>
@@ -4808,7 +4808,7 @@
         <v>4</v>
       </c>
       <c r="BA17" t="n">
-        <v>4.3</v>
+        <v>4.4</v>
       </c>
       <c r="BB17" t="n">
         <v>9.199999999999999</v>
@@ -4820,10 +4820,10 @@
         <v>4.1</v>
       </c>
       <c r="BE17" t="n">
-        <v>4.3</v>
+        <v>4.4</v>
       </c>
       <c r="BF17" t="n">
-        <v>5</v>
+        <v>5.1</v>
       </c>
       <c r="BG17" t="n">
         <v>4.4</v>
@@ -4838,37 +4838,37 @@
         <v>1000</v>
       </c>
       <c r="BK17" t="n">
-        <v>1.58</v>
+        <v>1.04</v>
       </c>
       <c r="BL17" t="n">
         <v>1000</v>
       </c>
       <c r="BM17" t="n">
-        <v>1.72</v>
+        <v>1.04</v>
       </c>
       <c r="BN17" t="n">
         <v>1000</v>
       </c>
       <c r="BO17" t="n">
-        <v>1.3</v>
+        <v>1.04</v>
       </c>
       <c r="BP17" t="n">
         <v>1000</v>
       </c>
       <c r="BQ17" t="n">
-        <v>1.5</v>
+        <v>1.04</v>
       </c>
       <c r="BR17" t="n">
         <v>1000</v>
       </c>
       <c r="BS17" t="n">
-        <v>1.65</v>
+        <v>1.04</v>
       </c>
       <c r="BT17" t="n">
         <v>1000</v>
       </c>
       <c r="BU17" t="n">
-        <v>1.59</v>
+        <v>1.04</v>
       </c>
       <c r="BV17" t="n">
         <v>1000</v>
@@ -4890,7 +4890,7 @@
       </c>
       <c r="CB17" t="inlineStr">
         <is>
-          <t>2026-06-11 13:45:41</t>
+          <t>2026-06-11 15:58:00</t>
         </is>
       </c>
     </row>
@@ -4939,7 +4939,7 @@
         <v>3.45</v>
       </c>
       <c r="L18" t="n">
-        <v>1.46</v>
+        <v>1.41</v>
       </c>
       <c r="M18" t="n">
         <v>1.09</v>
@@ -4951,25 +4951,25 @@
         <v>1.4</v>
       </c>
       <c r="P18" t="n">
-        <v>1.7</v>
+        <v>1.74</v>
       </c>
       <c r="Q18" t="n">
         <v>2.2</v>
       </c>
       <c r="R18" t="n">
-        <v>1.25</v>
+        <v>1.26</v>
       </c>
       <c r="S18" t="n">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="T18" t="n">
-        <v>1.9</v>
+        <v>1.89</v>
       </c>
       <c r="U18" t="n">
-        <v>1.96</v>
+        <v>1.93</v>
       </c>
       <c r="V18" t="n">
-        <v>1.61</v>
+        <v>1.62</v>
       </c>
       <c r="W18" t="n">
         <v>1.41</v>
@@ -5002,7 +5002,7 @@
         <v>23</v>
       </c>
       <c r="AG18" t="n">
-        <v>15</v>
+        <v>14.5</v>
       </c>
       <c r="AH18" t="n">
         <v>21</v>
@@ -5029,7 +5029,7 @@
         <v>32</v>
       </c>
       <c r="AP18" t="n">
-        <v>8.800000000000001</v>
+        <v>9.6</v>
       </c>
       <c r="AQ18" t="n">
         <v>7.8</v>
@@ -5065,25 +5065,25 @@
         <v>34</v>
       </c>
       <c r="BB18" t="n">
-        <v>7.4</v>
+        <v>7.8</v>
       </c>
       <c r="BC18" t="n">
         <v>30</v>
       </c>
       <c r="BD18" t="n">
-        <v>7.4</v>
+        <v>7.8</v>
       </c>
       <c r="BE18" t="n">
-        <v>8</v>
+        <v>8.4</v>
       </c>
       <c r="BF18" t="n">
         <v>34</v>
       </c>
       <c r="BG18" t="n">
-        <v>6.6</v>
+        <v>7</v>
       </c>
       <c r="BH18" t="n">
-        <v>3.15</v>
+        <v>3.2</v>
       </c>
       <c r="BI18" t="n">
         <v>2.56</v>
@@ -5092,59 +5092,59 @@
         <v>10.5</v>
       </c>
       <c r="BK18" t="n">
-        <v>5.3</v>
+        <v>7.8</v>
       </c>
       <c r="BL18" t="n">
         <v>1000</v>
       </c>
       <c r="BM18" t="n">
-        <v>10</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BN18" t="n">
         <v>6.6</v>
       </c>
       <c r="BO18" t="n">
-        <v>5</v>
+        <v>5.4</v>
       </c>
       <c r="BP18" t="n">
         <v>1000</v>
       </c>
       <c r="BQ18" t="n">
-        <v>7.8</v>
+        <v>7.6</v>
       </c>
       <c r="BR18" t="n">
         <v>1000</v>
       </c>
       <c r="BS18" t="n">
-        <v>8.800000000000001</v>
+        <v>8.6</v>
       </c>
       <c r="BT18" t="n">
         <v>5.5</v>
       </c>
       <c r="BU18" t="n">
-        <v>4.2</v>
+        <v>4.5</v>
       </c>
       <c r="BV18" t="n">
         <v>21</v>
       </c>
       <c r="BW18" t="n">
-        <v>7.2</v>
+        <v>7</v>
       </c>
       <c r="BX18" t="n">
         <v>1000</v>
       </c>
       <c r="BY18" t="n">
-        <v>8.4</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BZ18" t="n">
         <v>1000</v>
       </c>
       <c r="CA18" t="n">
-        <v>8.4</v>
+        <v>8</v>
       </c>
       <c r="CB18" t="inlineStr">
         <is>
-          <t>2026-06-11 13:45:41</t>
+          <t>2026-06-11 15:58:00</t>
         </is>
       </c>
     </row>
@@ -5175,25 +5175,25 @@
         </is>
       </c>
       <c r="F19" t="n">
-        <v>2.2</v>
+        <v>2.22</v>
       </c>
       <c r="G19" t="n">
-        <v>2.36</v>
+        <v>2.34</v>
       </c>
       <c r="H19" t="n">
-        <v>3.2</v>
+        <v>3.35</v>
       </c>
       <c r="I19" t="n">
         <v>3.6</v>
       </c>
       <c r="J19" t="n">
-        <v>3.5</v>
+        <v>3.55</v>
       </c>
       <c r="K19" t="n">
-        <v>3.85</v>
+        <v>3.95</v>
       </c>
       <c r="L19" t="n">
-        <v>1.29</v>
+        <v>1.36</v>
       </c>
       <c r="M19" t="n">
         <v>1.06</v>
@@ -5202,31 +5202,31 @@
         <v>3.95</v>
       </c>
       <c r="O19" t="n">
-        <v>1.28</v>
+        <v>1.29</v>
       </c>
       <c r="P19" t="n">
-        <v>2.02</v>
+        <v>1.99</v>
       </c>
       <c r="Q19" t="n">
-        <v>1.83</v>
+        <v>1.84</v>
       </c>
       <c r="R19" t="n">
-        <v>1.4</v>
+        <v>1.39</v>
       </c>
       <c r="S19" t="n">
-        <v>3.1</v>
+        <v>3.2</v>
       </c>
       <c r="T19" t="n">
-        <v>1.69</v>
+        <v>1.73</v>
       </c>
       <c r="U19" t="n">
-        <v>2.22</v>
+        <v>2.2</v>
       </c>
       <c r="V19" t="n">
         <v>1.39</v>
       </c>
       <c r="W19" t="n">
-        <v>1.73</v>
+        <v>1.74</v>
       </c>
       <c r="X19" t="n">
         <v>19.5</v>
@@ -5247,13 +5247,13 @@
         <v>8.800000000000001</v>
       </c>
       <c r="AD19" t="n">
-        <v>15.5</v>
+        <v>15</v>
       </c>
       <c r="AE19" t="n">
         <v>50</v>
       </c>
       <c r="AF19" t="n">
-        <v>16</v>
+        <v>15.5</v>
       </c>
       <c r="AG19" t="n">
         <v>12</v>
@@ -5265,7 +5265,7 @@
         <v>60</v>
       </c>
       <c r="AJ19" t="n">
-        <v>32</v>
+        <v>42</v>
       </c>
       <c r="AK19" t="n">
         <v>25</v>
@@ -5277,13 +5277,13 @@
         <v>100</v>
       </c>
       <c r="AN19" t="n">
-        <v>17.5</v>
+        <v>17</v>
       </c>
       <c r="AO19" t="n">
         <v>48</v>
       </c>
       <c r="AP19" t="n">
-        <v>11.5</v>
+        <v>13.5</v>
       </c>
       <c r="AQ19" t="n">
         <v>10.5</v>
@@ -5292,7 +5292,7 @@
         <v>20</v>
       </c>
       <c r="AS19" t="n">
-        <v>7.2</v>
+        <v>7.8</v>
       </c>
       <c r="AT19" t="n">
         <v>9.4</v>
@@ -5316,7 +5316,7 @@
         <v>14</v>
       </c>
       <c r="BA19" t="n">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="BB19" t="n">
         <v>22</v>
@@ -5328,7 +5328,7 @@
         <v>25</v>
       </c>
       <c r="BE19" t="n">
-        <v>7.4</v>
+        <v>8</v>
       </c>
       <c r="BF19" t="n">
         <v>13.5</v>
@@ -5337,68 +5337,68 @@
         <v>24</v>
       </c>
       <c r="BH19" t="n">
-        <v>1000</v>
+        <v>3.75</v>
       </c>
       <c r="BI19" t="n">
-        <v>1.04</v>
+        <v>2.9</v>
       </c>
       <c r="BJ19" t="n">
-        <v>1000</v>
+        <v>9.6</v>
       </c>
       <c r="BK19" t="n">
-        <v>1.04</v>
+        <v>5.8</v>
       </c>
       <c r="BL19" t="n">
         <v>1000</v>
       </c>
       <c r="BM19" t="n">
-        <v>1.04</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BN19" t="n">
-        <v>1000</v>
+        <v>5.4</v>
       </c>
       <c r="BO19" t="n">
-        <v>1.04</v>
+        <v>4.5</v>
       </c>
       <c r="BP19" t="n">
-        <v>1000</v>
+        <v>16.5</v>
       </c>
       <c r="BQ19" t="n">
-        <v>1.04</v>
+        <v>9.6</v>
       </c>
       <c r="BR19" t="n">
-        <v>1000</v>
+        <v>40</v>
       </c>
       <c r="BS19" t="n">
-        <v>1.04</v>
+        <v>7.8</v>
       </c>
       <c r="BT19" t="n">
-        <v>1000</v>
+        <v>7</v>
       </c>
       <c r="BU19" t="n">
-        <v>1.04</v>
+        <v>5.8</v>
       </c>
       <c r="BV19" t="n">
         <v>1000</v>
       </c>
       <c r="BW19" t="n">
-        <v>1.04</v>
+        <v>7.6</v>
       </c>
       <c r="BX19" t="n">
         <v>1000</v>
       </c>
       <c r="BY19" t="n">
-        <v>1.04</v>
+        <v>8.4</v>
       </c>
       <c r="BZ19" t="n">
-        <v>1000</v>
+        <v>24</v>
       </c>
       <c r="CA19" t="n">
-        <v>1.04</v>
+        <v>7.4</v>
       </c>
       <c r="CB19" t="inlineStr">
         <is>
-          <t>2026-06-11 13:45:41</t>
+          <t>2026-06-11 15:58:00</t>
         </is>
       </c>
     </row>
@@ -5438,13 +5438,13 @@
         <v>1.87</v>
       </c>
       <c r="I20" t="n">
-        <v>2.02</v>
+        <v>2.06</v>
       </c>
       <c r="J20" t="n">
-        <v>3.65</v>
+        <v>3.7</v>
       </c>
       <c r="K20" t="n">
-        <v>4.3</v>
+        <v>4.2</v>
       </c>
       <c r="L20" t="n">
         <v>1.01</v>
@@ -5468,16 +5468,16 @@
         <v>1.52</v>
       </c>
       <c r="S20" t="n">
-        <v>2.54</v>
+        <v>2.56</v>
       </c>
       <c r="T20" t="n">
         <v>1.64</v>
       </c>
       <c r="U20" t="n">
-        <v>2.28</v>
+        <v>2.3</v>
       </c>
       <c r="V20" t="n">
-        <v>1.98</v>
+        <v>1.94</v>
       </c>
       <c r="W20" t="n">
         <v>1.28</v>
@@ -5652,7 +5652,7 @@
       </c>
       <c r="CB20" t="inlineStr">
         <is>
-          <t>2026-06-11 13:45:41</t>
+          <t>2026-06-11 15:58:00</t>
         </is>
       </c>
     </row>
@@ -5683,7 +5683,7 @@
         </is>
       </c>
       <c r="F21" t="n">
-        <v>2.28</v>
+        <v>2.3</v>
       </c>
       <c r="G21" t="n">
         <v>2.5</v>
@@ -5716,25 +5716,25 @@
         <v>1.71</v>
       </c>
       <c r="Q21" t="n">
-        <v>2.2</v>
+        <v>2.22</v>
       </c>
       <c r="R21" t="n">
         <v>1.26</v>
       </c>
       <c r="S21" t="n">
-        <v>3.65</v>
+        <v>4.2</v>
       </c>
       <c r="T21" t="n">
-        <v>1.89</v>
+        <v>1.9</v>
       </c>
       <c r="U21" t="n">
-        <v>1.96</v>
+        <v>1.97</v>
       </c>
       <c r="V21" t="n">
         <v>1.37</v>
       </c>
       <c r="W21" t="n">
-        <v>1.66</v>
+        <v>1.67</v>
       </c>
       <c r="X21" t="n">
         <v>13.5</v>
@@ -5803,7 +5803,7 @@
         <v>4.1</v>
       </c>
       <c r="AT21" t="n">
-        <v>6.6</v>
+        <v>6.4</v>
       </c>
       <c r="AU21" t="n">
         <v>5.6</v>
@@ -5839,13 +5839,13 @@
         <v>4.2</v>
       </c>
       <c r="BF21" t="n">
-        <v>18.5</v>
+        <v>19</v>
       </c>
       <c r="BG21" t="n">
         <v>4.1</v>
       </c>
       <c r="BH21" t="n">
-        <v>3.1</v>
+        <v>3.05</v>
       </c>
       <c r="BI21" t="n">
         <v>2.56</v>
@@ -5854,13 +5854,13 @@
         <v>10.5</v>
       </c>
       <c r="BK21" t="n">
-        <v>6</v>
+        <v>6.2</v>
       </c>
       <c r="BL21" t="n">
         <v>1000</v>
       </c>
       <c r="BM21" t="n">
-        <v>13.5</v>
+        <v>14.5</v>
       </c>
       <c r="BN21" t="n">
         <v>5.1</v>
@@ -5872,13 +5872,13 @@
         <v>1000</v>
       </c>
       <c r="BQ21" t="n">
-        <v>8.199999999999999</v>
+        <v>8.6</v>
       </c>
       <c r="BR21" t="n">
         <v>1000</v>
       </c>
       <c r="BS21" t="n">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="BT21" t="n">
         <v>6.6</v>
@@ -5890,23 +5890,23 @@
         <v>1000</v>
       </c>
       <c r="BW21" t="n">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="BX21" t="n">
         <v>1000</v>
       </c>
       <c r="BY21" t="n">
+        <v>12</v>
+      </c>
+      <c r="BZ21" t="n">
+        <v>1000</v>
+      </c>
+      <c r="CA21" t="n">
         <v>11</v>
       </c>
-      <c r="BZ21" t="n">
-        <v>1000</v>
-      </c>
-      <c r="CA21" t="n">
-        <v>10.5</v>
-      </c>
       <c r="CB21" t="inlineStr">
         <is>
-          <t>2026-06-11 13:45:41</t>
+          <t>2026-06-11 15:58:00</t>
         </is>
       </c>
     </row>
@@ -5937,43 +5937,43 @@
         </is>
       </c>
       <c r="F22" t="n">
-        <v>3.6</v>
+        <v>3.75</v>
       </c>
       <c r="G22" t="n">
-        <v>5.4</v>
+        <v>4.4</v>
       </c>
       <c r="H22" t="n">
-        <v>1.89</v>
+        <v>1.92</v>
       </c>
       <c r="I22" t="n">
-        <v>2.34</v>
+        <v>2.08</v>
       </c>
       <c r="J22" t="n">
-        <v>3.25</v>
+        <v>3.7</v>
       </c>
       <c r="K22" t="n">
-        <v>5.2</v>
+        <v>4.2</v>
       </c>
       <c r="L22" t="n">
         <v>1.01</v>
       </c>
       <c r="M22" t="n">
-        <v>1.02</v>
+        <v>1.05</v>
       </c>
       <c r="N22" t="n">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="O22" t="n">
-        <v>1.23</v>
+        <v>1.25</v>
       </c>
       <c r="P22" t="n">
-        <v>1.96</v>
+        <v>2.08</v>
       </c>
       <c r="Q22" t="n">
-        <v>1.64</v>
+        <v>1.74</v>
       </c>
       <c r="R22" t="n">
-        <v>1.32</v>
+        <v>1.34</v>
       </c>
       <c r="S22" t="n">
         <v>2.32</v>
@@ -5985,118 +5985,118 @@
         <v>1.73</v>
       </c>
       <c r="V22" t="n">
-        <v>1.75</v>
+        <v>1.92</v>
       </c>
       <c r="W22" t="n">
-        <v>1.22</v>
+        <v>1.29</v>
       </c>
       <c r="X22" t="n">
-        <v>1000</v>
+        <v>21</v>
       </c>
       <c r="Y22" t="n">
-        <v>1000</v>
+        <v>12.5</v>
       </c>
       <c r="Z22" t="n">
-        <v>1000</v>
+        <v>14.5</v>
       </c>
       <c r="AA22" t="n">
-        <v>1000</v>
+        <v>25</v>
       </c>
       <c r="AB22" t="n">
-        <v>1000</v>
+        <v>19.5</v>
       </c>
       <c r="AC22" t="n">
-        <v>1000</v>
+        <v>10.5</v>
       </c>
       <c r="AD22" t="n">
-        <v>1000</v>
+        <v>12.5</v>
       </c>
       <c r="AE22" t="n">
-        <v>1000</v>
+        <v>23</v>
       </c>
       <c r="AF22" t="n">
-        <v>1000</v>
+        <v>36</v>
       </c>
       <c r="AG22" t="n">
-        <v>1000</v>
+        <v>18.5</v>
       </c>
       <c r="AH22" t="n">
-        <v>1000</v>
+        <v>19</v>
       </c>
       <c r="AI22" t="n">
-        <v>1000</v>
+        <v>38</v>
       </c>
       <c r="AJ22" t="n">
-        <v>1000</v>
+        <v>90</v>
       </c>
       <c r="AK22" t="n">
-        <v>1000</v>
+        <v>55</v>
       </c>
       <c r="AL22" t="n">
-        <v>1000</v>
+        <v>55</v>
       </c>
       <c r="AM22" t="n">
-        <v>1000</v>
+        <v>95</v>
       </c>
       <c r="AN22" t="n">
-        <v>1000</v>
+        <v>44</v>
       </c>
       <c r="AO22" t="n">
-        <v>1000</v>
+        <v>14</v>
       </c>
       <c r="AP22" t="n">
-        <v>1.01</v>
+        <v>13.5</v>
       </c>
       <c r="AQ22" t="n">
-        <v>1.01</v>
+        <v>8.4</v>
       </c>
       <c r="AR22" t="n">
-        <v>1.01</v>
+        <v>10</v>
       </c>
       <c r="AS22" t="n">
-        <v>1.01</v>
+        <v>17.5</v>
       </c>
       <c r="AT22" t="n">
-        <v>1.01</v>
+        <v>13</v>
       </c>
       <c r="AU22" t="n">
-        <v>1.01</v>
+        <v>6.8</v>
       </c>
       <c r="AV22" t="n">
-        <v>1.01</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AW22" t="n">
-        <v>1.01</v>
+        <v>15</v>
       </c>
       <c r="AX22" t="n">
-        <v>1.01</v>
+        <v>4.8</v>
       </c>
       <c r="AY22" t="n">
-        <v>1.01</v>
+        <v>12.5</v>
       </c>
       <c r="AZ22" t="n">
-        <v>1.01</v>
+        <v>13</v>
       </c>
       <c r="BA22" t="n">
-        <v>1.01</v>
+        <v>4.8</v>
       </c>
       <c r="BB22" t="n">
-        <v>1.01</v>
+        <v>5.2</v>
       </c>
       <c r="BC22" t="n">
-        <v>1.01</v>
+        <v>5</v>
       </c>
       <c r="BD22" t="n">
-        <v>1.01</v>
+        <v>5</v>
       </c>
       <c r="BE22" t="n">
-        <v>1.01</v>
+        <v>5.2</v>
       </c>
       <c r="BF22" t="n">
-        <v>1.01</v>
+        <v>4.9</v>
       </c>
       <c r="BG22" t="n">
-        <v>1.01</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BH22" t="n">
         <v>1000</v>
@@ -6160,7 +6160,7 @@
       </c>
       <c r="CB22" t="inlineStr">
         <is>
-          <t>2026-06-11 13:45:41</t>
+          <t>2026-06-11 15:58:00</t>
         </is>
       </c>
     </row>
@@ -6194,22 +6194,22 @@
         <v>4.3</v>
       </c>
       <c r="G23" t="n">
-        <v>5.1</v>
+        <v>5</v>
       </c>
       <c r="H23" t="n">
-        <v>1.83</v>
+        <v>1.84</v>
       </c>
       <c r="I23" t="n">
-        <v>2</v>
+        <v>1.98</v>
       </c>
       <c r="J23" t="n">
         <v>3.55</v>
       </c>
       <c r="K23" t="n">
-        <v>4.2</v>
+        <v>3.9</v>
       </c>
       <c r="L23" t="n">
-        <v>1.31</v>
+        <v>1.39</v>
       </c>
       <c r="M23" t="n">
         <v>1.06</v>
@@ -6221,25 +6221,25 @@
         <v>1.3</v>
       </c>
       <c r="P23" t="n">
-        <v>1.91</v>
+        <v>1.9</v>
       </c>
       <c r="Q23" t="n">
-        <v>1.89</v>
+        <v>1.9</v>
       </c>
       <c r="R23" t="n">
         <v>1.35</v>
       </c>
       <c r="S23" t="n">
-        <v>3.25</v>
+        <v>3.3</v>
       </c>
       <c r="T23" t="n">
-        <v>1.79</v>
+        <v>1.8</v>
       </c>
       <c r="U23" t="n">
+        <v>2.04</v>
+      </c>
+      <c r="V23" t="n">
         <v>2.02</v>
-      </c>
-      <c r="V23" t="n">
-        <v>2</v>
       </c>
       <c r="W23" t="n">
         <v>1.25</v>
@@ -6248,7 +6248,7 @@
         <v>15.5</v>
       </c>
       <c r="Y23" t="n">
-        <v>9.4</v>
+        <v>9.6</v>
       </c>
       <c r="Z23" t="n">
         <v>12.5</v>
@@ -6257,7 +6257,7 @@
         <v>23</v>
       </c>
       <c r="AB23" t="n">
-        <v>17.5</v>
+        <v>17</v>
       </c>
       <c r="AC23" t="n">
         <v>9</v>
@@ -6266,13 +6266,13 @@
         <v>11</v>
       </c>
       <c r="AE23" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AF23" t="n">
         <v>38</v>
       </c>
       <c r="AG23" t="n">
-        <v>19.5</v>
+        <v>19</v>
       </c>
       <c r="AH23" t="n">
         <v>20</v>
@@ -6281,7 +6281,7 @@
         <v>38</v>
       </c>
       <c r="AJ23" t="n">
-        <v>130</v>
+        <v>120</v>
       </c>
       <c r="AK23" t="n">
         <v>65</v>
@@ -6299,10 +6299,10 @@
         <v>14</v>
       </c>
       <c r="AP23" t="n">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="AQ23" t="n">
-        <v>7.6</v>
+        <v>7.8</v>
       </c>
       <c r="AR23" t="n">
         <v>10</v>
@@ -6314,7 +6314,7 @@
         <v>13.5</v>
       </c>
       <c r="AU23" t="n">
-        <v>7.4</v>
+        <v>7.2</v>
       </c>
       <c r="AV23" t="n">
         <v>8.800000000000001</v>
@@ -6329,92 +6329,92 @@
         <v>15.5</v>
       </c>
       <c r="AZ23" t="n">
-        <v>16</v>
+        <v>14.5</v>
       </c>
       <c r="BA23" t="n">
         <v>24</v>
       </c>
       <c r="BB23" t="n">
-        <v>8.199999999999999</v>
+        <v>8</v>
       </c>
       <c r="BC23" t="n">
         <v>7.6</v>
       </c>
       <c r="BD23" t="n">
-        <v>7.8</v>
+        <v>7.6</v>
       </c>
       <c r="BE23" t="n">
-        <v>8.199999999999999</v>
+        <v>8</v>
       </c>
       <c r="BF23" t="n">
-        <v>7.8</v>
+        <v>7.6</v>
       </c>
       <c r="BG23" t="n">
         <v>11</v>
       </c>
       <c r="BH23" t="n">
-        <v>1000</v>
+        <v>3.6</v>
       </c>
       <c r="BI23" t="n">
-        <v>1.04</v>
+        <v>2.86</v>
       </c>
       <c r="BJ23" t="n">
-        <v>1000</v>
+        <v>10.5</v>
       </c>
       <c r="BK23" t="n">
-        <v>1.04</v>
+        <v>5.2</v>
       </c>
       <c r="BL23" t="n">
         <v>1000</v>
       </c>
       <c r="BM23" t="n">
-        <v>1.04</v>
+        <v>9.4</v>
       </c>
       <c r="BN23" t="n">
-        <v>1000</v>
+        <v>8.4</v>
       </c>
       <c r="BO23" t="n">
-        <v>1.04</v>
+        <v>4.6</v>
       </c>
       <c r="BP23" t="n">
-        <v>1000</v>
+        <v>40</v>
       </c>
       <c r="BQ23" t="n">
-        <v>1.04</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BR23" t="n">
-        <v>1000</v>
+        <v>50</v>
       </c>
       <c r="BS23" t="n">
-        <v>1.04</v>
+        <v>8.4</v>
       </c>
       <c r="BT23" t="n">
-        <v>1000</v>
+        <v>4.7</v>
       </c>
       <c r="BU23" t="n">
-        <v>1.04</v>
+        <v>3.65</v>
       </c>
       <c r="BV23" t="n">
-        <v>1000</v>
+        <v>14</v>
       </c>
       <c r="BW23" t="n">
-        <v>1.04</v>
+        <v>5.9</v>
       </c>
       <c r="BX23" t="n">
-        <v>1000</v>
+        <v>29</v>
       </c>
       <c r="BY23" t="n">
-        <v>1.04</v>
+        <v>7.6</v>
       </c>
       <c r="BZ23" t="n">
-        <v>1000</v>
+        <v>25</v>
       </c>
       <c r="CA23" t="n">
-        <v>1.04</v>
+        <v>7.2</v>
       </c>
       <c r="CB23" t="inlineStr">
         <is>
-          <t>2026-06-11 13:45:41</t>
+          <t>2026-06-11 15:58:00</t>
         </is>
       </c>
     </row>
@@ -6457,7 +6457,7 @@
         <v>95</v>
       </c>
       <c r="J24" t="n">
-        <v>4.7</v>
+        <v>4.6</v>
       </c>
       <c r="K24" t="n">
         <v>1000</v>
@@ -6668,7 +6668,7 @@
       </c>
       <c r="CB24" t="inlineStr">
         <is>
-          <t>2026-06-11 13:45:41</t>
+          <t>2026-06-11 15:58:00</t>
         </is>
       </c>
     </row>
@@ -6702,16 +6702,16 @@
         <v>2.82</v>
       </c>
       <c r="G25" t="n">
-        <v>3</v>
+        <v>2.98</v>
       </c>
       <c r="H25" t="n">
-        <v>2.72</v>
+        <v>2.74</v>
       </c>
       <c r="I25" t="n">
-        <v>2.86</v>
+        <v>2.92</v>
       </c>
       <c r="J25" t="n">
-        <v>3.35</v>
+        <v>3.2</v>
       </c>
       <c r="K25" t="n">
         <v>3.45</v>
@@ -6729,13 +6729,13 @@
         <v>1.4</v>
       </c>
       <c r="P25" t="n">
-        <v>1.76</v>
+        <v>1.8</v>
       </c>
       <c r="Q25" t="n">
         <v>2.16</v>
       </c>
       <c r="R25" t="n">
-        <v>1.28</v>
+        <v>1.29</v>
       </c>
       <c r="S25" t="n">
         <v>4.1</v>
@@ -6747,10 +6747,10 @@
         <v>2.04</v>
       </c>
       <c r="V25" t="n">
-        <v>1.53</v>
+        <v>1.52</v>
       </c>
       <c r="W25" t="n">
-        <v>1.51</v>
+        <v>1.5</v>
       </c>
       <c r="X25" t="n">
         <v>14.5</v>
@@ -6759,7 +6759,7 @@
         <v>12.5</v>
       </c>
       <c r="Z25" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="AA25" t="n">
         <v>55</v>
@@ -6795,19 +6795,19 @@
         <v>44</v>
       </c>
       <c r="AL25" t="n">
-        <v>65</v>
+        <v>60</v>
       </c>
       <c r="AM25" t="n">
         <v>140</v>
       </c>
       <c r="AN25" t="n">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="AO25" t="n">
         <v>42</v>
       </c>
       <c r="AP25" t="n">
-        <v>8.6</v>
+        <v>10.5</v>
       </c>
       <c r="AQ25" t="n">
         <v>9</v>
@@ -6816,10 +6816,10 @@
         <v>13</v>
       </c>
       <c r="AS25" t="n">
-        <v>36</v>
+        <v>4.7</v>
       </c>
       <c r="AT25" t="n">
-        <v>9.199999999999999</v>
+        <v>9</v>
       </c>
       <c r="AU25" t="n">
         <v>6.6</v>
@@ -6837,7 +6837,7 @@
         <v>11.5</v>
       </c>
       <c r="AZ25" t="n">
-        <v>13.5</v>
+        <v>4.2</v>
       </c>
       <c r="BA25" t="n">
         <v>4.7</v>
@@ -6849,16 +6849,16 @@
         <v>4.6</v>
       </c>
       <c r="BD25" t="n">
-        <v>4.8</v>
+        <v>4.7</v>
       </c>
       <c r="BE25" t="n">
-        <v>4.9</v>
+        <v>5</v>
       </c>
       <c r="BF25" t="n">
         <v>4.6</v>
       </c>
       <c r="BG25" t="n">
-        <v>4.4</v>
+        <v>4.5</v>
       </c>
       <c r="BH25" t="n">
         <v>1000</v>
@@ -6870,25 +6870,25 @@
         <v>1000</v>
       </c>
       <c r="BK25" t="n">
-        <v>1.48</v>
+        <v>1.54</v>
       </c>
       <c r="BL25" t="n">
         <v>1000</v>
       </c>
       <c r="BM25" t="n">
-        <v>1.65</v>
+        <v>1.67</v>
       </c>
       <c r="BN25" t="n">
         <v>1000</v>
       </c>
       <c r="BO25" t="n">
-        <v>1.39</v>
+        <v>1.44</v>
       </c>
       <c r="BP25" t="n">
         <v>1000</v>
       </c>
       <c r="BQ25" t="n">
-        <v>1.58</v>
+        <v>1.6</v>
       </c>
       <c r="BR25" t="n">
         <v>1000</v>
@@ -6906,7 +6906,7 @@
         <v>1000</v>
       </c>
       <c r="BW25" t="n">
-        <v>1.61</v>
+        <v>1.65</v>
       </c>
       <c r="BX25" t="n">
         <v>1000</v>
@@ -6922,7 +6922,7 @@
       </c>
       <c r="CB25" t="inlineStr">
         <is>
-          <t>2026-06-11 13:45:41</t>
+          <t>2026-06-11 15:58:00</t>
         </is>
       </c>
     </row>
@@ -6998,7 +6998,7 @@
         <v>1.44</v>
       </c>
       <c r="U26" t="n">
-        <v>2.82</v>
+        <v>2.8</v>
       </c>
       <c r="V26" t="n">
         <v>1.28</v>
@@ -7112,7 +7112,7 @@
         <v>5.1</v>
       </c>
       <c r="BG26" t="n">
-        <v>18.5</v>
+        <v>16</v>
       </c>
       <c r="BH26" t="n">
         <v>5.6</v>
@@ -7176,7 +7176,7 @@
       </c>
       <c r="CB26" t="inlineStr">
         <is>
-          <t>2026-06-11 13:45:41</t>
+          <t>2026-06-11 15:58:00</t>
         </is>
       </c>
     </row>
@@ -7207,19 +7207,19 @@
         </is>
       </c>
       <c r="F27" t="n">
-        <v>1.09</v>
+        <v>1.01</v>
       </c>
       <c r="G27" t="n">
         <v>1000</v>
       </c>
       <c r="H27" t="n">
-        <v>1.76</v>
+        <v>1.49</v>
       </c>
       <c r="I27" t="n">
         <v>1000</v>
       </c>
       <c r="J27" t="n">
-        <v>1.35</v>
+        <v>1.43</v>
       </c>
       <c r="K27" t="n">
         <v>3.25</v>
@@ -7430,7 +7430,7 @@
       </c>
       <c r="CB27" t="inlineStr">
         <is>
-          <t>2026-06-11 13:45:41</t>
+          <t>2026-06-11 15:58:00</t>
         </is>
       </c>
     </row>
@@ -7482,34 +7482,34 @@
         <v>1.01</v>
       </c>
       <c r="M28" t="n">
-        <v>1.09</v>
+        <v>1.1</v>
       </c>
       <c r="N28" t="n">
-        <v>2.5</v>
+        <v>3.05</v>
       </c>
       <c r="O28" t="n">
-        <v>1.43</v>
+        <v>1.44</v>
       </c>
       <c r="P28" t="n">
-        <v>1.57</v>
+        <v>1.66</v>
       </c>
       <c r="Q28" t="n">
-        <v>2.12</v>
+        <v>2.26</v>
       </c>
       <c r="R28" t="n">
-        <v>1.21</v>
+        <v>1.25</v>
       </c>
       <c r="S28" t="n">
-        <v>4</v>
+        <v>4.6</v>
       </c>
       <c r="T28" t="n">
-        <v>1.97</v>
+        <v>1.94</v>
       </c>
       <c r="U28" t="n">
         <v>1.89</v>
       </c>
       <c r="V28" t="n">
-        <v>1.33</v>
+        <v>1.34</v>
       </c>
       <c r="W28" t="n">
         <v>1.73</v>
@@ -7518,22 +7518,22 @@
         <v>12.5</v>
       </c>
       <c r="Y28" t="n">
-        <v>13.5</v>
+        <v>970</v>
       </c>
       <c r="Z28" t="n">
-        <v>30</v>
+        <v>27</v>
       </c>
       <c r="AA28" t="n">
-        <v>95</v>
+        <v>85</v>
       </c>
       <c r="AB28" t="n">
         <v>8.6</v>
       </c>
       <c r="AC28" t="n">
-        <v>7.6</v>
+        <v>7.4</v>
       </c>
       <c r="AD28" t="n">
-        <v>18.5</v>
+        <v>970</v>
       </c>
       <c r="AE28" t="n">
         <v>60</v>
@@ -7542,55 +7542,55 @@
         <v>970</v>
       </c>
       <c r="AG28" t="n">
-        <v>13.5</v>
+        <v>970</v>
       </c>
       <c r="AH28" t="n">
         <v>950</v>
       </c>
       <c r="AI28" t="n">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="AJ28" t="n">
-        <v>38</v>
+        <v>34</v>
       </c>
       <c r="AK28" t="n">
-        <v>34</v>
+        <v>30</v>
       </c>
       <c r="AL28" t="n">
         <v>55</v>
       </c>
       <c r="AM28" t="n">
-        <v>170</v>
+        <v>160</v>
       </c>
       <c r="AN28" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="AO28" t="n">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="AP28" t="n">
-        <v>4.2</v>
+        <v>5.1</v>
       </c>
       <c r="AQ28" t="n">
-        <v>9.800000000000001</v>
+        <v>5.1</v>
       </c>
       <c r="AR28" t="n">
-        <v>5.2</v>
+        <v>6.6</v>
       </c>
       <c r="AS28" t="n">
-        <v>5.9</v>
+        <v>8</v>
       </c>
       <c r="AT28" t="n">
         <v>7</v>
       </c>
       <c r="AU28" t="n">
-        <v>5.9</v>
+        <v>6.4</v>
       </c>
       <c r="AV28" t="n">
-        <v>12</v>
+        <v>5.8</v>
       </c>
       <c r="AW28" t="n">
-        <v>5.7</v>
+        <v>7.6</v>
       </c>
       <c r="AX28" t="n">
         <v>10.5</v>
@@ -7599,28 +7599,28 @@
         <v>9.6</v>
       </c>
       <c r="AZ28" t="n">
-        <v>5</v>
+        <v>6.2</v>
       </c>
       <c r="BA28" t="n">
-        <v>5.9</v>
+        <v>7.8</v>
       </c>
       <c r="BB28" t="n">
-        <v>5.4</v>
+        <v>7</v>
       </c>
       <c r="BC28" t="n">
         <v>21</v>
       </c>
       <c r="BD28" t="n">
-        <v>5.7</v>
+        <v>7.6</v>
       </c>
       <c r="BE28" t="n">
-        <v>6</v>
+        <v>8.4</v>
       </c>
       <c r="BF28" t="n">
-        <v>5.2</v>
+        <v>6.6</v>
       </c>
       <c r="BG28" t="n">
-        <v>5.9</v>
+        <v>7.8</v>
       </c>
       <c r="BH28" t="n">
         <v>1000</v>
@@ -7684,7 +7684,7 @@
       </c>
       <c r="CB28" t="inlineStr">
         <is>
-          <t>2026-06-11 13:45:41</t>
+          <t>2026-06-11 15:58:00</t>
         </is>
       </c>
     </row>
@@ -7721,16 +7721,16 @@
         <v>2.06</v>
       </c>
       <c r="H29" t="n">
-        <v>3.8</v>
+        <v>3.85</v>
       </c>
       <c r="I29" t="n">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="J29" t="n">
         <v>3.8</v>
       </c>
       <c r="K29" t="n">
-        <v>4.2</v>
+        <v>4.1</v>
       </c>
       <c r="L29" t="n">
         <v>1.29</v>
@@ -7754,7 +7754,7 @@
         <v>1.44</v>
       </c>
       <c r="S29" t="n">
-        <v>2.94</v>
+        <v>2.96</v>
       </c>
       <c r="T29" t="n">
         <v>1.71</v>
@@ -7781,7 +7781,7 @@
         <v>95</v>
       </c>
       <c r="AB29" t="n">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="AC29" t="n">
         <v>9</v>
@@ -7832,10 +7832,10 @@
         <v>18.5</v>
       </c>
       <c r="AS29" t="n">
-        <v>11.5</v>
+        <v>12</v>
       </c>
       <c r="AT29" t="n">
-        <v>9.6</v>
+        <v>9.4</v>
       </c>
       <c r="AU29" t="n">
         <v>8</v>
@@ -7844,7 +7844,7 @@
         <v>14.5</v>
       </c>
       <c r="AW29" t="n">
-        <v>25</v>
+        <v>38</v>
       </c>
       <c r="AX29" t="n">
         <v>11.5</v>
@@ -7865,22 +7865,22 @@
         <v>17.5</v>
       </c>
       <c r="BD29" t="n">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="BE29" t="n">
-        <v>11.5</v>
+        <v>12</v>
       </c>
       <c r="BF29" t="n">
         <v>11</v>
       </c>
       <c r="BG29" t="n">
-        <v>24</v>
+        <v>34</v>
       </c>
       <c r="BH29" t="n">
         <v>3.75</v>
       </c>
       <c r="BI29" t="n">
-        <v>3.35</v>
+        <v>3.05</v>
       </c>
       <c r="BJ29" t="n">
         <v>9.199999999999999</v>
@@ -7938,7 +7938,7 @@
       </c>
       <c r="CB29" t="inlineStr">
         <is>
-          <t>2026-06-11 13:45:41</t>
+          <t>2026-06-11 15:58:00</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-06-12.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-06-12.xlsx
@@ -863,13 +863,13 @@
         <v>1.64</v>
       </c>
       <c r="H2" t="n">
-        <v>6.8</v>
+        <v>7</v>
       </c>
       <c r="I2" t="n">
-        <v>9.4</v>
+        <v>9.6</v>
       </c>
       <c r="J2" t="n">
-        <v>3.6</v>
+        <v>3.55</v>
       </c>
       <c r="K2" t="n">
         <v>5.4</v>
@@ -965,58 +965,58 @@
         <v>1000</v>
       </c>
       <c r="AP2" t="n">
-        <v>3.7</v>
+        <v>3.55</v>
       </c>
       <c r="AQ2" t="n">
-        <v>3.95</v>
+        <v>3.75</v>
       </c>
       <c r="AR2" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="AS2" t="n">
         <v>4.3</v>
-      </c>
-      <c r="AS2" t="n">
-        <v>4.5</v>
       </c>
       <c r="AT2" t="n">
         <v>2.98</v>
       </c>
       <c r="AU2" t="n">
-        <v>3.35</v>
+        <v>3.2</v>
       </c>
       <c r="AV2" t="n">
+        <v>3.85</v>
+      </c>
+      <c r="AW2" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="AX2" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="AY2" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="AZ2" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="BA2" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="BB2" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="BC2" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="BD2" t="n">
         <v>4</v>
       </c>
-      <c r="AW2" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="AX2" t="n">
-        <v>3.35</v>
-      </c>
-      <c r="AY2" t="n">
-        <v>3.35</v>
-      </c>
-      <c r="AZ2" t="n">
-        <v>4</v>
-      </c>
-      <c r="BA2" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="BB2" t="n">
-        <v>3.65</v>
-      </c>
-      <c r="BC2" t="n">
-        <v>3.8</v>
-      </c>
-      <c r="BD2" t="n">
+      <c r="BE2" t="n">
         <v>4.2</v>
       </c>
-      <c r="BE2" t="n">
-        <v>4.5</v>
-      </c>
       <c r="BF2" t="n">
-        <v>3.3</v>
+        <v>3.15</v>
       </c>
       <c r="BG2" t="n">
-        <v>4.5</v>
+        <v>4.3</v>
       </c>
       <c r="BH2" t="n">
         <v>8.4</v>
@@ -1080,7 +1080,7 @@
       </c>
       <c r="CB2" t="inlineStr">
         <is>
-          <t>2026-06-11 15:58:00</t>
+          <t>2026-06-11 18:11:04</t>
         </is>
       </c>
     </row>
@@ -1114,16 +1114,16 @@
         <v>2.56</v>
       </c>
       <c r="G3" t="n">
-        <v>2.8</v>
+        <v>2.78</v>
       </c>
       <c r="H3" t="n">
-        <v>2.64</v>
+        <v>2.66</v>
       </c>
       <c r="I3" t="n">
-        <v>2.88</v>
+        <v>2.9</v>
       </c>
       <c r="J3" t="n">
-        <v>3.6</v>
+        <v>3.7</v>
       </c>
       <c r="K3" t="n">
         <v>4</v>
@@ -1135,22 +1135,22 @@
         <v>1.05</v>
       </c>
       <c r="N3" t="n">
-        <v>4.4</v>
+        <v>4.3</v>
       </c>
       <c r="O3" t="n">
         <v>1.25</v>
       </c>
       <c r="P3" t="n">
-        <v>2.16</v>
+        <v>2.14</v>
       </c>
       <c r="Q3" t="n">
-        <v>1.73</v>
+        <v>1.74</v>
       </c>
       <c r="R3" t="n">
         <v>1.45</v>
       </c>
       <c r="S3" t="n">
-        <v>2.86</v>
+        <v>2.84</v>
       </c>
       <c r="T3" t="n">
         <v>1.63</v>
@@ -1165,7 +1165,7 @@
         <v>1.56</v>
       </c>
       <c r="X3" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="Y3" t="n">
         <v>14</v>
@@ -1201,16 +1201,16 @@
         <v>44</v>
       </c>
       <c r="AJ3" t="n">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="AK3" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="AL3" t="n">
         <v>44</v>
       </c>
       <c r="AM3" t="n">
-        <v>85</v>
+        <v>90</v>
       </c>
       <c r="AN3" t="n">
         <v>23</v>
@@ -1228,7 +1228,7 @@
         <v>14.5</v>
       </c>
       <c r="AS3" t="n">
-        <v>5.5</v>
+        <v>5.7</v>
       </c>
       <c r="AT3" t="n">
         <v>9.800000000000001</v>
@@ -1246,31 +1246,31 @@
         <v>14</v>
       </c>
       <c r="AY3" t="n">
-        <v>9.199999999999999</v>
+        <v>9</v>
       </c>
       <c r="AZ3" t="n">
         <v>11.5</v>
       </c>
       <c r="BA3" t="n">
-        <v>5.5</v>
+        <v>5.7</v>
       </c>
       <c r="BB3" t="n">
-        <v>5.5</v>
+        <v>5.7</v>
       </c>
       <c r="BC3" t="n">
-        <v>18.5</v>
+        <v>19.5</v>
       </c>
       <c r="BD3" t="n">
+        <v>5.8</v>
+      </c>
+      <c r="BE3" t="n">
         <v>5.6</v>
       </c>
-      <c r="BE3" t="n">
-        <v>5.5</v>
-      </c>
       <c r="BF3" t="n">
-        <v>14</v>
+        <v>13.5</v>
       </c>
       <c r="BG3" t="n">
-        <v>14.5</v>
+        <v>15</v>
       </c>
       <c r="BH3" t="n">
         <v>1000</v>
@@ -1334,7 +1334,7 @@
       </c>
       <c r="CB3" t="inlineStr">
         <is>
-          <t>2026-06-11 15:58:00</t>
+          <t>2026-06-11 18:11:04</t>
         </is>
       </c>
     </row>
@@ -1365,22 +1365,22 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>2.78</v>
+        <v>2.86</v>
       </c>
       <c r="G4" t="n">
-        <v>3.2</v>
+        <v>3.35</v>
       </c>
       <c r="H4" t="n">
-        <v>2.92</v>
+        <v>3</v>
       </c>
       <c r="I4" t="n">
         <v>3.4</v>
       </c>
       <c r="J4" t="n">
-        <v>2.6</v>
+        <v>2.52</v>
       </c>
       <c r="K4" t="n">
-        <v>3.3</v>
+        <v>3</v>
       </c>
       <c r="L4" t="n">
         <v>1.01</v>
@@ -1389,16 +1389,16 @@
         <v>1.15</v>
       </c>
       <c r="N4" t="n">
-        <v>2.34</v>
+        <v>2.18</v>
       </c>
       <c r="O4" t="n">
-        <v>1.6</v>
+        <v>1.61</v>
       </c>
       <c r="P4" t="n">
-        <v>1.45</v>
+        <v>1.41</v>
       </c>
       <c r="Q4" t="n">
-        <v>2.84</v>
+        <v>2.88</v>
       </c>
       <c r="R4" t="n">
         <v>1.18</v>
@@ -1410,16 +1410,16 @@
         <v>2.16</v>
       </c>
       <c r="U4" t="n">
-        <v>1.71</v>
+        <v>1.66</v>
       </c>
       <c r="V4" t="n">
         <v>1.42</v>
       </c>
       <c r="W4" t="n">
-        <v>1.47</v>
+        <v>1.42</v>
       </c>
       <c r="X4" t="n">
-        <v>970</v>
+        <v>90</v>
       </c>
       <c r="Y4" t="n">
         <v>970</v>
@@ -1431,7 +1431,7 @@
         <v>75</v>
       </c>
       <c r="AB4" t="n">
-        <v>9.199999999999999</v>
+        <v>970</v>
       </c>
       <c r="AC4" t="n">
         <v>970</v>
@@ -1479,52 +1479,52 @@
         <v>6.4</v>
       </c>
       <c r="AR4" t="n">
-        <v>3.7</v>
+        <v>2.26</v>
       </c>
       <c r="AS4" t="n">
-        <v>2.7</v>
+        <v>1.9</v>
       </c>
       <c r="AT4" t="n">
-        <v>3.85</v>
+        <v>3.95</v>
       </c>
       <c r="AU4" t="n">
-        <v>5.6</v>
+        <v>5.5</v>
       </c>
       <c r="AV4" t="n">
-        <v>4.8</v>
+        <v>5.2</v>
       </c>
       <c r="AW4" t="n">
-        <v>2.66</v>
+        <v>1.89</v>
       </c>
       <c r="AX4" t="n">
-        <v>4.8</v>
+        <v>3.3</v>
       </c>
       <c r="AY4" t="n">
-        <v>4.6</v>
+        <v>3.2</v>
       </c>
       <c r="AZ4" t="n">
-        <v>5.4</v>
+        <v>5.9</v>
       </c>
       <c r="BA4" t="n">
-        <v>2.72</v>
+        <v>1.91</v>
       </c>
       <c r="BB4" t="n">
-        <v>2.68</v>
+        <v>1.89</v>
       </c>
       <c r="BC4" t="n">
-        <v>5.5</v>
+        <v>2.42</v>
       </c>
       <c r="BD4" t="n">
-        <v>2.72</v>
+        <v>1.91</v>
       </c>
       <c r="BE4" t="n">
-        <v>2.76</v>
+        <v>1.93</v>
       </c>
       <c r="BF4" t="n">
-        <v>2.7</v>
+        <v>1.9</v>
       </c>
       <c r="BG4" t="n">
-        <v>2.7</v>
+        <v>1.91</v>
       </c>
       <c r="BH4" t="n">
         <v>2.94</v>
@@ -1588,7 +1588,7 @@
       </c>
       <c r="CB4" t="inlineStr">
         <is>
-          <t>2026-06-11 15:58:00</t>
+          <t>2026-06-11 18:11:04</t>
         </is>
       </c>
     </row>
@@ -1622,37 +1622,37 @@
         <v>2.18</v>
       </c>
       <c r="G5" t="n">
-        <v>2.36</v>
+        <v>2.4</v>
       </c>
       <c r="H5" t="n">
-        <v>3.95</v>
+        <v>3.9</v>
       </c>
       <c r="I5" t="n">
-        <v>4.5</v>
+        <v>4.4</v>
       </c>
       <c r="J5" t="n">
-        <v>2.94</v>
+        <v>2.92</v>
       </c>
       <c r="K5" t="n">
         <v>3.2</v>
       </c>
       <c r="L5" t="n">
-        <v>1.49</v>
+        <v>1.48</v>
       </c>
       <c r="M5" t="n">
         <v>1.13</v>
       </c>
       <c r="N5" t="n">
-        <v>2.5</v>
+        <v>2.46</v>
       </c>
       <c r="O5" t="n">
         <v>1.57</v>
       </c>
       <c r="P5" t="n">
-        <v>1.5</v>
+        <v>1.49</v>
       </c>
       <c r="Q5" t="n">
-        <v>2.72</v>
+        <v>2.68</v>
       </c>
       <c r="R5" t="n">
         <v>1.18</v>
@@ -1667,10 +1667,10 @@
         <v>1.72</v>
       </c>
       <c r="V5" t="n">
-        <v>1.29</v>
+        <v>1.3</v>
       </c>
       <c r="W5" t="n">
-        <v>1.73</v>
+        <v>1.72</v>
       </c>
       <c r="X5" t="n">
         <v>9.4</v>
@@ -1679,16 +1679,16 @@
         <v>12.5</v>
       </c>
       <c r="Z5" t="n">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="AA5" t="n">
         <v>130</v>
       </c>
       <c r="AB5" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AC5" t="n">
-        <v>7.4</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AD5" t="n">
         <v>22</v>
@@ -1709,13 +1709,13 @@
         <v>120</v>
       </c>
       <c r="AJ5" t="n">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="AK5" t="n">
         <v>40</v>
       </c>
       <c r="AL5" t="n">
-        <v>85</v>
+        <v>80</v>
       </c>
       <c r="AM5" t="n">
         <v>250</v>
@@ -1727,58 +1727,58 @@
         <v>140</v>
       </c>
       <c r="AP5" t="n">
-        <v>7.2</v>
+        <v>3.35</v>
       </c>
       <c r="AQ5" t="n">
-        <v>9.4</v>
+        <v>3.7</v>
       </c>
       <c r="AR5" t="n">
-        <v>21</v>
+        <v>4.5</v>
       </c>
       <c r="AS5" t="n">
-        <v>6.2</v>
+        <v>5</v>
       </c>
       <c r="AT5" t="n">
-        <v>6</v>
+        <v>3.2</v>
       </c>
       <c r="AU5" t="n">
-        <v>6.4</v>
+        <v>3.2</v>
       </c>
       <c r="AV5" t="n">
-        <v>16</v>
+        <v>4.2</v>
       </c>
       <c r="AW5" t="n">
-        <v>6.2</v>
+        <v>4.9</v>
       </c>
       <c r="AX5" t="n">
-        <v>11</v>
+        <v>3.85</v>
       </c>
       <c r="AY5" t="n">
-        <v>10.5</v>
+        <v>3.8</v>
       </c>
       <c r="AZ5" t="n">
-        <v>21</v>
+        <v>4.4</v>
       </c>
       <c r="BA5" t="n">
-        <v>6.2</v>
+        <v>5</v>
       </c>
       <c r="BB5" t="n">
-        <v>5.8</v>
+        <v>4.6</v>
       </c>
       <c r="BC5" t="n">
-        <v>5.8</v>
+        <v>4.6</v>
       </c>
       <c r="BD5" t="n">
-        <v>6.2</v>
+        <v>4.9</v>
       </c>
       <c r="BE5" t="n">
-        <v>6.4</v>
+        <v>5.1</v>
       </c>
       <c r="BF5" t="n">
-        <v>5.8</v>
+        <v>4.6</v>
       </c>
       <c r="BG5" t="n">
-        <v>6.4</v>
+        <v>5</v>
       </c>
       <c r="BH5" t="n">
         <v>1000</v>
@@ -1842,7 +1842,7 @@
       </c>
       <c r="CB5" t="inlineStr">
         <is>
-          <t>2026-06-11 15:58:00</t>
+          <t>2026-06-11 18:11:04</t>
         </is>
       </c>
     </row>
@@ -1879,19 +1879,19 @@
         <v>3.75</v>
       </c>
       <c r="H6" t="n">
-        <v>2.18</v>
+        <v>2.16</v>
       </c>
       <c r="I6" t="n">
-        <v>2.32</v>
+        <v>2.34</v>
       </c>
       <c r="J6" t="n">
         <v>3.45</v>
       </c>
       <c r="K6" t="n">
-        <v>3.75</v>
+        <v>3.85</v>
       </c>
       <c r="L6" t="n">
-        <v>1.3</v>
+        <v>1.31</v>
       </c>
       <c r="M6" t="n">
         <v>1.06</v>
@@ -1903,7 +1903,7 @@
         <v>1.3</v>
       </c>
       <c r="P6" t="n">
-        <v>1.95</v>
+        <v>1.96</v>
       </c>
       <c r="Q6" t="n">
         <v>1.9</v>
@@ -1915,13 +1915,13 @@
         <v>3.25</v>
       </c>
       <c r="T6" t="n">
-        <v>1.73</v>
+        <v>1.74</v>
       </c>
       <c r="U6" t="n">
         <v>2.16</v>
       </c>
       <c r="V6" t="n">
-        <v>1.75</v>
+        <v>1.74</v>
       </c>
       <c r="W6" t="n">
         <v>1.36</v>
@@ -1939,10 +1939,10 @@
         <v>30</v>
       </c>
       <c r="AB6" t="n">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="AC6" t="n">
-        <v>9.800000000000001</v>
+        <v>8.4</v>
       </c>
       <c r="AD6" t="n">
         <v>13.5</v>
@@ -1951,7 +1951,7 @@
         <v>29</v>
       </c>
       <c r="AF6" t="n">
-        <v>32</v>
+        <v>26</v>
       </c>
       <c r="AG6" t="n">
         <v>15</v>
@@ -1963,7 +1963,7 @@
         <v>44</v>
       </c>
       <c r="AJ6" t="n">
-        <v>80</v>
+        <v>85</v>
       </c>
       <c r="AK6" t="n">
         <v>50</v>
@@ -1975,7 +1975,7 @@
         <v>110</v>
       </c>
       <c r="AN6" t="n">
-        <v>40</v>
+        <v>48</v>
       </c>
       <c r="AO6" t="n">
         <v>17.5</v>
@@ -1984,52 +1984,52 @@
         <v>11</v>
       </c>
       <c r="AQ6" t="n">
-        <v>9</v>
+        <v>7.6</v>
       </c>
       <c r="AR6" t="n">
-        <v>13</v>
+        <v>10.5</v>
       </c>
       <c r="AS6" t="n">
         <v>21</v>
       </c>
       <c r="AT6" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="AU6" t="n">
-        <v>7.2</v>
+        <v>6.2</v>
       </c>
       <c r="AV6" t="n">
-        <v>9.800000000000001</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AW6" t="n">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="AX6" t="n">
-        <v>5.2</v>
+        <v>18.5</v>
       </c>
       <c r="AY6" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="AZ6" t="n">
-        <v>15</v>
+        <v>12.5</v>
       </c>
       <c r="BA6" t="n">
-        <v>5.3</v>
+        <v>6.2</v>
       </c>
       <c r="BB6" t="n">
-        <v>5.7</v>
+        <v>6.4</v>
       </c>
       <c r="BC6" t="n">
-        <v>5.2</v>
+        <v>6.2</v>
       </c>
       <c r="BD6" t="n">
-        <v>32</v>
+        <v>6.2</v>
       </c>
       <c r="BE6" t="n">
-        <v>5.3</v>
+        <v>6.4</v>
       </c>
       <c r="BF6" t="n">
-        <v>5.1</v>
+        <v>6.2</v>
       </c>
       <c r="BG6" t="n">
         <v>12.5</v>
@@ -2096,7 +2096,7 @@
       </c>
       <c r="CB6" t="inlineStr">
         <is>
-          <t>2026-06-11 15:58:00</t>
+          <t>2026-06-11 18:11:04</t>
         </is>
       </c>
     </row>
@@ -2127,22 +2127,22 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>1.68</v>
+        <v>1.61</v>
       </c>
       <c r="G7" t="n">
-        <v>1.89</v>
+        <v>1.8</v>
       </c>
       <c r="H7" t="n">
-        <v>4.1</v>
+        <v>4.6</v>
       </c>
       <c r="I7" t="n">
-        <v>5.8</v>
+        <v>6.4</v>
       </c>
       <c r="J7" t="n">
-        <v>3.7</v>
+        <v>3.45</v>
       </c>
       <c r="K7" t="n">
-        <v>4.6</v>
+        <v>4.7</v>
       </c>
       <c r="L7" t="n">
         <v>1.01</v>
@@ -2157,7 +2157,7 @@
         <v>1.25</v>
       </c>
       <c r="P7" t="n">
-        <v>1.9</v>
+        <v>2.02</v>
       </c>
       <c r="Q7" t="n">
         <v>1.65</v>
@@ -2169,124 +2169,124 @@
         <v>2.66</v>
       </c>
       <c r="T7" t="n">
-        <v>1.73</v>
+        <v>1.76</v>
       </c>
       <c r="U7" t="n">
-        <v>2.04</v>
+        <v>2</v>
       </c>
       <c r="V7" t="n">
-        <v>1.2</v>
+        <v>1.18</v>
       </c>
       <c r="W7" t="n">
-        <v>2.12</v>
+        <v>2.24</v>
       </c>
       <c r="X7" t="n">
+        <v>19</v>
+      </c>
+      <c r="Y7" t="n">
         <v>22</v>
-      </c>
-      <c r="Y7" t="n">
-        <v>24</v>
       </c>
       <c r="Z7" t="n">
         <v>50</v>
       </c>
       <c r="AA7" t="n">
-        <v>150</v>
+        <v>180</v>
       </c>
       <c r="AB7" t="n">
-        <v>11.5</v>
+        <v>10</v>
       </c>
       <c r="AC7" t="n">
-        <v>11.5</v>
+        <v>10.5</v>
       </c>
       <c r="AD7" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="AE7" t="n">
         <v>80</v>
       </c>
       <c r="AF7" t="n">
-        <v>14</v>
+        <v>11.5</v>
       </c>
       <c r="AG7" t="n">
-        <v>12.5</v>
+        <v>11</v>
       </c>
       <c r="AH7" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AI7" t="n">
         <v>80</v>
       </c>
       <c r="AJ7" t="n">
-        <v>23</v>
+        <v>18.5</v>
       </c>
       <c r="AK7" t="n">
-        <v>22</v>
+        <v>18.5</v>
       </c>
       <c r="AL7" t="n">
-        <v>40</v>
+        <v>36</v>
       </c>
       <c r="AM7" t="n">
-        <v>120</v>
+        <v>130</v>
       </c>
       <c r="AN7" t="n">
-        <v>12.5</v>
+        <v>10</v>
       </c>
       <c r="AO7" t="n">
-        <v>85</v>
+        <v>100</v>
       </c>
       <c r="AP7" t="n">
-        <v>3.55</v>
+        <v>5.2</v>
       </c>
       <c r="AQ7" t="n">
-        <v>3.55</v>
+        <v>5.4</v>
       </c>
       <c r="AR7" t="n">
-        <v>3.85</v>
+        <v>6.2</v>
       </c>
       <c r="AS7" t="n">
-        <v>4.1</v>
+        <v>6.8</v>
       </c>
       <c r="AT7" t="n">
-        <v>3.1</v>
+        <v>4.2</v>
       </c>
       <c r="AU7" t="n">
-        <v>3.1</v>
+        <v>4.2</v>
       </c>
       <c r="AV7" t="n">
-        <v>3.6</v>
+        <v>5.5</v>
       </c>
       <c r="AW7" t="n">
-        <v>4</v>
+        <v>6.6</v>
       </c>
       <c r="AX7" t="n">
-        <v>3.25</v>
+        <v>4.4</v>
       </c>
       <c r="AY7" t="n">
-        <v>3.15</v>
+        <v>4.3</v>
       </c>
       <c r="AZ7" t="n">
-        <v>3.55</v>
+        <v>5.4</v>
       </c>
       <c r="BA7" t="n">
-        <v>4</v>
+        <v>6.6</v>
       </c>
       <c r="BB7" t="n">
-        <v>3.55</v>
+        <v>5.2</v>
       </c>
       <c r="BC7" t="n">
-        <v>3.55</v>
+        <v>5.2</v>
       </c>
       <c r="BD7" t="n">
-        <v>3.8</v>
+        <v>6</v>
       </c>
       <c r="BE7" t="n">
-        <v>4</v>
+        <v>6.8</v>
       </c>
       <c r="BF7" t="n">
-        <v>3.15</v>
+        <v>4.2</v>
       </c>
       <c r="BG7" t="n">
-        <v>4</v>
+        <v>6.6</v>
       </c>
       <c r="BH7" t="n">
         <v>1000</v>
@@ -2350,7 +2350,7 @@
       </c>
       <c r="CB7" t="inlineStr">
         <is>
-          <t>2026-06-11 15:58:00</t>
+          <t>2026-06-11 18:11:04</t>
         </is>
       </c>
     </row>
@@ -2396,7 +2396,7 @@
         <v>3.8</v>
       </c>
       <c r="K8" t="n">
-        <v>4.5</v>
+        <v>4.4</v>
       </c>
       <c r="L8" t="n">
         <v>1.31</v>
@@ -2423,7 +2423,7 @@
         <v>3.35</v>
       </c>
       <c r="T8" t="n">
-        <v>1.9</v>
+        <v>1.91</v>
       </c>
       <c r="U8" t="n">
         <v>1.92</v>
@@ -2492,10 +2492,10 @@
         <v>11</v>
       </c>
       <c r="AQ8" t="n">
-        <v>14.5</v>
+        <v>16.5</v>
       </c>
       <c r="AR8" t="n">
-        <v>5.4</v>
+        <v>5.5</v>
       </c>
       <c r="AS8" t="n">
         <v>5.7</v>
@@ -2604,7 +2604,7 @@
       </c>
       <c r="CB8" t="inlineStr">
         <is>
-          <t>2026-06-11 15:58:00</t>
+          <t>2026-06-11 18:11:04</t>
         </is>
       </c>
     </row>
@@ -2677,10 +2677,10 @@
         <v>2.34</v>
       </c>
       <c r="T9" t="n">
-        <v>1.52</v>
+        <v>1.58</v>
       </c>
       <c r="U9" t="n">
-        <v>2.24</v>
+        <v>2.42</v>
       </c>
       <c r="V9" t="n">
         <v>2.16</v>
@@ -2858,7 +2858,7 @@
       </c>
       <c r="CB9" t="inlineStr">
         <is>
-          <t>2026-06-11 15:58:00</t>
+          <t>2026-06-11 18:11:04</t>
         </is>
       </c>
     </row>
@@ -2889,19 +2889,19 @@
         </is>
       </c>
       <c r="F10" t="n">
-        <v>1.54</v>
+        <v>1.55</v>
       </c>
       <c r="G10" t="n">
-        <v>1.68</v>
+        <v>1.69</v>
       </c>
       <c r="H10" t="n">
-        <v>5.3</v>
+        <v>5.2</v>
       </c>
       <c r="I10" t="n">
-        <v>6.6</v>
+        <v>6.4</v>
       </c>
       <c r="J10" t="n">
-        <v>4.4</v>
+        <v>4.3</v>
       </c>
       <c r="K10" t="n">
         <v>5.3</v>
@@ -2913,13 +2913,13 @@
         <v>1.01</v>
       </c>
       <c r="N10" t="n">
-        <v>5.4</v>
+        <v>5.3</v>
       </c>
       <c r="O10" t="n">
         <v>1.18</v>
       </c>
       <c r="P10" t="n">
-        <v>2.5</v>
+        <v>2.46</v>
       </c>
       <c r="Q10" t="n">
         <v>1.54</v>
@@ -2937,10 +2937,10 @@
         <v>2.26</v>
       </c>
       <c r="V10" t="n">
-        <v>1.17</v>
+        <v>1.18</v>
       </c>
       <c r="W10" t="n">
-        <v>2.48</v>
+        <v>2.46</v>
       </c>
       <c r="X10" t="n">
         <v>32</v>
@@ -2991,7 +2991,7 @@
         <v>80</v>
       </c>
       <c r="AN10" t="n">
-        <v>7</v>
+        <v>6.8</v>
       </c>
       <c r="AO10" t="n">
         <v>60</v>
@@ -3000,13 +3000,13 @@
         <v>21</v>
       </c>
       <c r="AQ10" t="n">
-        <v>6.8</v>
+        <v>21</v>
       </c>
       <c r="AR10" t="n">
-        <v>6.8</v>
+        <v>7</v>
       </c>
       <c r="AS10" t="n">
-        <v>7.4</v>
+        <v>7.6</v>
       </c>
       <c r="AT10" t="n">
         <v>10</v>
@@ -3015,10 +3015,10 @@
         <v>9.4</v>
       </c>
       <c r="AV10" t="n">
-        <v>18</v>
+        <v>6.6</v>
       </c>
       <c r="AW10" t="n">
-        <v>7</v>
+        <v>7.2</v>
       </c>
       <c r="AX10" t="n">
         <v>10</v>
@@ -3030,7 +3030,7 @@
         <v>15</v>
       </c>
       <c r="BA10" t="n">
-        <v>6.8</v>
+        <v>7</v>
       </c>
       <c r="BB10" t="n">
         <v>14</v>
@@ -3039,16 +3039,16 @@
         <v>13</v>
       </c>
       <c r="BD10" t="n">
-        <v>6.8</v>
+        <v>7</v>
       </c>
       <c r="BE10" t="n">
-        <v>7</v>
+        <v>7.2</v>
       </c>
       <c r="BF10" t="n">
         <v>5.4</v>
       </c>
       <c r="BG10" t="n">
-        <v>6.8</v>
+        <v>7</v>
       </c>
       <c r="BH10" t="n">
         <v>4.7</v>
@@ -3112,7 +3112,7 @@
       </c>
       <c r="CB10" t="inlineStr">
         <is>
-          <t>2026-06-11 15:58:00</t>
+          <t>2026-06-11 18:11:04</t>
         </is>
       </c>
     </row>
@@ -3146,34 +3146,34 @@
         <v>2.16</v>
       </c>
       <c r="G11" t="n">
-        <v>2.34</v>
+        <v>2.32</v>
       </c>
       <c r="H11" t="n">
         <v>4.1</v>
       </c>
       <c r="I11" t="n">
-        <v>4.6</v>
+        <v>4.7</v>
       </c>
       <c r="J11" t="n">
-        <v>2.96</v>
+        <v>2.94</v>
       </c>
       <c r="K11" t="n">
-        <v>3.2</v>
+        <v>3.3</v>
       </c>
       <c r="L11" t="n">
-        <v>1.6</v>
+        <v>1.59</v>
       </c>
       <c r="M11" t="n">
-        <v>1.13</v>
+        <v>1.14</v>
       </c>
       <c r="N11" t="n">
-        <v>2.54</v>
+        <v>2.5</v>
       </c>
       <c r="O11" t="n">
-        <v>1.57</v>
+        <v>1.56</v>
       </c>
       <c r="P11" t="n">
-        <v>1.51</v>
+        <v>1.5</v>
       </c>
       <c r="Q11" t="n">
         <v>2.72</v>
@@ -3182,22 +3182,22 @@
         <v>1.18</v>
       </c>
       <c r="S11" t="n">
-        <v>5.8</v>
+        <v>5.7</v>
       </c>
       <c r="T11" t="n">
-        <v>2.18</v>
+        <v>2.16</v>
       </c>
       <c r="U11" t="n">
-        <v>1.74</v>
+        <v>1.72</v>
       </c>
       <c r="V11" t="n">
         <v>1.28</v>
       </c>
       <c r="W11" t="n">
-        <v>1.74</v>
+        <v>1.75</v>
       </c>
       <c r="X11" t="n">
-        <v>9.800000000000001</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="Y11" t="n">
         <v>13.5</v>
@@ -3209,10 +3209,10 @@
         <v>130</v>
       </c>
       <c r="AB11" t="n">
-        <v>8.199999999999999</v>
+        <v>8</v>
       </c>
       <c r="AC11" t="n">
-        <v>8.6</v>
+        <v>8.4</v>
       </c>
       <c r="AD11" t="n">
         <v>23</v>
@@ -3224,10 +3224,10 @@
         <v>15</v>
       </c>
       <c r="AG11" t="n">
-        <v>14.5</v>
+        <v>14</v>
       </c>
       <c r="AH11" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="AI11" t="n">
         <v>130</v>
@@ -3242,7 +3242,7 @@
         <v>80</v>
       </c>
       <c r="AM11" t="n">
-        <v>260</v>
+        <v>250</v>
       </c>
       <c r="AN11" t="n">
         <v>38</v>
@@ -3251,58 +3251,58 @@
         <v>150</v>
       </c>
       <c r="AP11" t="n">
-        <v>6</v>
+        <v>3.25</v>
       </c>
       <c r="AQ11" t="n">
         <v>9.6</v>
       </c>
       <c r="AR11" t="n">
-        <v>4.1</v>
+        <v>4.6</v>
       </c>
       <c r="AS11" t="n">
-        <v>4.4</v>
+        <v>5.1</v>
       </c>
       <c r="AT11" t="n">
         <v>6</v>
       </c>
       <c r="AU11" t="n">
-        <v>5.4</v>
+        <v>6.2</v>
       </c>
       <c r="AV11" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="AW11" t="n">
+        <v>5</v>
+      </c>
+      <c r="AX11" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="AY11" t="n">
         <v>3.85</v>
       </c>
-      <c r="AW11" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="AX11" t="n">
-        <v>3.55</v>
-      </c>
-      <c r="AY11" t="n">
-        <v>3.5</v>
-      </c>
       <c r="AZ11" t="n">
-        <v>18</v>
+        <v>4.5</v>
       </c>
       <c r="BA11" t="n">
-        <v>4.4</v>
+        <v>5.1</v>
       </c>
       <c r="BB11" t="n">
-        <v>4.1</v>
+        <v>4.6</v>
       </c>
       <c r="BC11" t="n">
-        <v>4.1</v>
+        <v>4.6</v>
       </c>
       <c r="BD11" t="n">
-        <v>4.3</v>
+        <v>5</v>
       </c>
       <c r="BE11" t="n">
-        <v>4.5</v>
+        <v>5.2</v>
       </c>
       <c r="BF11" t="n">
-        <v>4.1</v>
+        <v>4.6</v>
       </c>
       <c r="BG11" t="n">
-        <v>4.4</v>
+        <v>5.1</v>
       </c>
       <c r="BH11" t="n">
         <v>3.05</v>
@@ -3366,7 +3366,7 @@
       </c>
       <c r="CB11" t="inlineStr">
         <is>
-          <t>2026-06-11 15:58:00</t>
+          <t>2026-06-11 18:11:04</t>
         </is>
       </c>
     </row>
@@ -3397,16 +3397,16 @@
         </is>
       </c>
       <c r="F12" t="n">
-        <v>2.1</v>
+        <v>2.14</v>
       </c>
       <c r="G12" t="n">
-        <v>2.36</v>
+        <v>2.4</v>
       </c>
       <c r="H12" t="n">
-        <v>3.15</v>
+        <v>3.05</v>
       </c>
       <c r="I12" t="n">
-        <v>3.75</v>
+        <v>3.65</v>
       </c>
       <c r="J12" t="n">
         <v>3.5</v>
@@ -3424,13 +3424,13 @@
         <v>4.2</v>
       </c>
       <c r="O12" t="n">
-        <v>1.25</v>
+        <v>1.24</v>
       </c>
       <c r="P12" t="n">
         <v>2.12</v>
       </c>
       <c r="Q12" t="n">
-        <v>1.72</v>
+        <v>1.71</v>
       </c>
       <c r="R12" t="n">
         <v>1.44</v>
@@ -3442,13 +3442,13 @@
         <v>1.62</v>
       </c>
       <c r="U12" t="n">
-        <v>2.26</v>
+        <v>2.28</v>
       </c>
       <c r="V12" t="n">
-        <v>1.37</v>
+        <v>1.38</v>
       </c>
       <c r="W12" t="n">
-        <v>1.73</v>
+        <v>1.71</v>
       </c>
       <c r="X12" t="n">
         <v>23</v>
@@ -3466,7 +3466,7 @@
         <v>12.5</v>
       </c>
       <c r="AC12" t="n">
-        <v>9.4</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AD12" t="n">
         <v>15.5</v>
@@ -3502,7 +3502,7 @@
         <v>15</v>
       </c>
       <c r="AO12" t="n">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="AP12" t="n">
         <v>15.5</v>
@@ -3514,7 +3514,7 @@
         <v>19.5</v>
       </c>
       <c r="AS12" t="n">
-        <v>7.2</v>
+        <v>7.4</v>
       </c>
       <c r="AT12" t="n">
         <v>8.4</v>
@@ -3526,7 +3526,7 @@
         <v>11.5</v>
       </c>
       <c r="AW12" t="n">
-        <v>6.8</v>
+        <v>7</v>
       </c>
       <c r="AX12" t="n">
         <v>11</v>
@@ -3538,7 +3538,7 @@
         <v>11.5</v>
       </c>
       <c r="BA12" t="n">
-        <v>6.8</v>
+        <v>7</v>
       </c>
       <c r="BB12" t="n">
         <v>19.5</v>
@@ -3547,16 +3547,16 @@
         <v>15.5</v>
       </c>
       <c r="BD12" t="n">
-        <v>7.4</v>
+        <v>7.2</v>
       </c>
       <c r="BE12" t="n">
-        <v>7.2</v>
+        <v>7.6</v>
       </c>
       <c r="BF12" t="n">
         <v>10</v>
       </c>
       <c r="BG12" t="n">
-        <v>7.2</v>
+        <v>7</v>
       </c>
       <c r="BH12" t="n">
         <v>4</v>
@@ -3568,7 +3568,7 @@
         <v>9.4</v>
       </c>
       <c r="BK12" t="n">
-        <v>5.6</v>
+        <v>6.8</v>
       </c>
       <c r="BL12" t="n">
         <v>1000</v>
@@ -3583,13 +3583,13 @@
         <v>4.6</v>
       </c>
       <c r="BP12" t="n">
-        <v>16.5</v>
+        <v>17</v>
       </c>
       <c r="BQ12" t="n">
-        <v>6</v>
+        <v>6.2</v>
       </c>
       <c r="BR12" t="n">
-        <v>38</v>
+        <v>28</v>
       </c>
       <c r="BS12" t="n">
         <v>7.2</v>
@@ -3601,7 +3601,7 @@
         <v>5.7</v>
       </c>
       <c r="BV12" t="n">
-        <v>26</v>
+        <v>1000</v>
       </c>
       <c r="BW12" t="n">
         <v>7</v>
@@ -3610,17 +3610,17 @@
         <v>48</v>
       </c>
       <c r="BY12" t="n">
-        <v>7.6</v>
+        <v>7.4</v>
       </c>
       <c r="BZ12" t="n">
         <v>22</v>
       </c>
       <c r="CA12" t="n">
-        <v>6.8</v>
+        <v>6.6</v>
       </c>
       <c r="CB12" t="inlineStr">
         <is>
-          <t>2026-06-11 15:58:00</t>
+          <t>2026-06-11 18:11:04</t>
         </is>
       </c>
     </row>
@@ -3663,7 +3663,7 @@
         <v>32</v>
       </c>
       <c r="J13" t="n">
-        <v>9.4</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="K13" t="n">
         <v>11.5</v>
@@ -3675,7 +3675,7 @@
         <v>1.02</v>
       </c>
       <c r="N13" t="n">
-        <v>7</v>
+        <v>7.2</v>
       </c>
       <c r="O13" t="n">
         <v>1.12</v>
@@ -3687,13 +3687,13 @@
         <v>1.37</v>
       </c>
       <c r="R13" t="n">
-        <v>1.85</v>
+        <v>1.87</v>
       </c>
       <c r="S13" t="n">
         <v>1.94</v>
       </c>
       <c r="T13" t="n">
-        <v>2.3</v>
+        <v>2.32</v>
       </c>
       <c r="U13" t="n">
         <v>1.6</v>
@@ -3729,7 +3729,7 @@
         <v>1000</v>
       </c>
       <c r="AF13" t="n">
-        <v>10</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AG13" t="n">
         <v>17</v>
@@ -3741,7 +3741,7 @@
         <v>1000</v>
       </c>
       <c r="AJ13" t="n">
-        <v>9.6</v>
+        <v>9.4</v>
       </c>
       <c r="AK13" t="n">
         <v>17.5</v>
@@ -3753,22 +3753,22 @@
         <v>1000</v>
       </c>
       <c r="AN13" t="n">
-        <v>3.2</v>
+        <v>3.1</v>
       </c>
       <c r="AO13" t="n">
         <v>1000</v>
       </c>
       <c r="AP13" t="n">
-        <v>5</v>
+        <v>5.7</v>
       </c>
       <c r="AQ13" t="n">
-        <v>5.3</v>
+        <v>6</v>
       </c>
       <c r="AR13" t="n">
-        <v>5.5</v>
+        <v>6.2</v>
       </c>
       <c r="AS13" t="n">
-        <v>5.6</v>
+        <v>6.4</v>
       </c>
       <c r="AT13" t="n">
         <v>9.6</v>
@@ -3777,10 +3777,10 @@
         <v>18</v>
       </c>
       <c r="AV13" t="n">
-        <v>5.3</v>
+        <v>6</v>
       </c>
       <c r="AW13" t="n">
-        <v>5.5</v>
+        <v>6.4</v>
       </c>
       <c r="AX13" t="n">
         <v>7.4</v>
@@ -3789,10 +3789,10 @@
         <v>11</v>
       </c>
       <c r="AZ13" t="n">
-        <v>5.1</v>
+        <v>5.8</v>
       </c>
       <c r="BA13" t="n">
-        <v>5.5</v>
+        <v>6.2</v>
       </c>
       <c r="BB13" t="n">
         <v>7</v>
@@ -3801,22 +3801,22 @@
         <v>11.5</v>
       </c>
       <c r="BD13" t="n">
-        <v>5.1</v>
+        <v>5.8</v>
       </c>
       <c r="BE13" t="n">
-        <v>5.5</v>
+        <v>6.2</v>
       </c>
       <c r="BF13" t="n">
-        <v>2.4</v>
+        <v>2.56</v>
       </c>
       <c r="BG13" t="n">
-        <v>5.6</v>
+        <v>6.4</v>
       </c>
       <c r="BH13" t="n">
         <v>5.7</v>
       </c>
       <c r="BI13" t="n">
-        <v>4.4</v>
+        <v>4.7</v>
       </c>
       <c r="BJ13" t="n">
         <v>1000</v>
@@ -3840,19 +3840,19 @@
         <v>5.9</v>
       </c>
       <c r="BQ13" t="n">
-        <v>4.6</v>
+        <v>4.9</v>
       </c>
       <c r="BR13" t="n">
         <v>1000</v>
       </c>
       <c r="BS13" t="n">
-        <v>7.4</v>
+        <v>7.2</v>
       </c>
       <c r="BT13" t="n">
         <v>1000</v>
       </c>
       <c r="BU13" t="n">
-        <v>7.4</v>
+        <v>7.2</v>
       </c>
       <c r="BV13" t="n">
         <v>1000</v>
@@ -3864,17 +3864,17 @@
         <v>1000</v>
       </c>
       <c r="BY13" t="n">
-        <v>10</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BZ13" t="n">
-        <v>6.8</v>
+        <v>7</v>
       </c>
       <c r="CA13" t="n">
-        <v>5.3</v>
+        <v>5.2</v>
       </c>
       <c r="CB13" t="inlineStr">
         <is>
-          <t>2026-06-11 15:58:00</t>
+          <t>2026-06-11 18:11:04</t>
         </is>
       </c>
     </row>
@@ -3905,22 +3905,22 @@
         </is>
       </c>
       <c r="F14" t="n">
-        <v>4</v>
+        <v>3.85</v>
       </c>
       <c r="G14" t="n">
-        <v>5</v>
+        <v>4.4</v>
       </c>
       <c r="H14" t="n">
-        <v>1.89</v>
+        <v>2.06</v>
       </c>
       <c r="I14" t="n">
-        <v>2.06</v>
+        <v>2.2</v>
       </c>
       <c r="J14" t="n">
-        <v>3.4</v>
+        <v>3.35</v>
       </c>
       <c r="K14" t="n">
-        <v>3.95</v>
+        <v>3.8</v>
       </c>
       <c r="L14" t="n">
         <v>1.01</v>
@@ -3929,13 +3929,13 @@
         <v>1.07</v>
       </c>
       <c r="N14" t="n">
-        <v>3.4</v>
+        <v>3.2</v>
       </c>
       <c r="O14" t="n">
         <v>1.34</v>
       </c>
       <c r="P14" t="n">
-        <v>1.8</v>
+        <v>1.81</v>
       </c>
       <c r="Q14" t="n">
         <v>2</v>
@@ -3944,19 +3944,19 @@
         <v>1.31</v>
       </c>
       <c r="S14" t="n">
-        <v>2.9</v>
+        <v>2.92</v>
       </c>
       <c r="T14" t="n">
         <v>1.85</v>
       </c>
       <c r="U14" t="n">
-        <v>1.96</v>
+        <v>1.97</v>
       </c>
       <c r="V14" t="n">
-        <v>1.94</v>
+        <v>1.85</v>
       </c>
       <c r="W14" t="n">
-        <v>1.26</v>
+        <v>1.31</v>
       </c>
       <c r="X14" t="n">
         <v>16</v>
@@ -3971,7 +3971,7 @@
         <v>28</v>
       </c>
       <c r="AB14" t="n">
-        <v>18.5</v>
+        <v>17.5</v>
       </c>
       <c r="AC14" t="n">
         <v>9.800000000000001</v>
@@ -3983,10 +3983,10 @@
         <v>27</v>
       </c>
       <c r="AF14" t="n">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="AG14" t="n">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="AH14" t="n">
         <v>24</v>
@@ -3998,74 +3998,74 @@
         <v>130</v>
       </c>
       <c r="AK14" t="n">
+        <v>75</v>
+      </c>
+      <c r="AL14" t="n">
         <v>80</v>
       </c>
-      <c r="AL14" t="n">
-        <v>85</v>
-      </c>
       <c r="AM14" t="n">
-        <v>150</v>
+        <v>140</v>
       </c>
       <c r="AN14" t="n">
-        <v>95</v>
+        <v>90</v>
       </c>
       <c r="AO14" t="n">
         <v>18.5</v>
       </c>
       <c r="AP14" t="n">
-        <v>3.4</v>
+        <v>3.55</v>
       </c>
       <c r="AQ14" t="n">
-        <v>3.1</v>
+        <v>3.2</v>
       </c>
       <c r="AR14" t="n">
+        <v>3.45</v>
+      </c>
+      <c r="AS14" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="AT14" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="AU14" t="n">
+        <v>3.15</v>
+      </c>
+      <c r="AV14" t="n">
         <v>3.35</v>
       </c>
-      <c r="AS14" t="n">
+      <c r="AW14" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="AX14" t="n">
+        <v>4</v>
+      </c>
+      <c r="AY14" t="n">
         <v>3.75</v>
       </c>
-      <c r="AT14" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="AU14" t="n">
-        <v>3.05</v>
-      </c>
-      <c r="AV14" t="n">
-        <v>3.25</v>
-      </c>
-      <c r="AW14" t="n">
-        <v>3.75</v>
-      </c>
-      <c r="AX14" t="n">
-        <v>3.9</v>
-      </c>
-      <c r="AY14" t="n">
+      <c r="AZ14" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="BA14" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="BB14" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="BC14" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="BD14" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="BE14" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="BF14" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="BG14" t="n">
         <v>3.65</v>
       </c>
-      <c r="AZ14" t="n">
-        <v>3.65</v>
-      </c>
-      <c r="BA14" t="n">
-        <v>3.95</v>
-      </c>
-      <c r="BB14" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="BC14" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="BD14" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="BE14" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="BF14" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="BG14" t="n">
-        <v>3.5</v>
-      </c>
       <c r="BH14" t="n">
         <v>1000</v>
       </c>
@@ -4128,7 +4128,7 @@
       </c>
       <c r="CB14" t="inlineStr">
         <is>
-          <t>2026-06-11 15:58:00</t>
+          <t>2026-06-11 18:11:04</t>
         </is>
       </c>
     </row>
@@ -4159,22 +4159,22 @@
         </is>
       </c>
       <c r="F15" t="n">
-        <v>2.48</v>
+        <v>2.42</v>
       </c>
       <c r="G15" t="n">
-        <v>2.78</v>
+        <v>2.76</v>
       </c>
       <c r="H15" t="n">
-        <v>3.3</v>
+        <v>3.35</v>
       </c>
       <c r="I15" t="n">
         <v>3.9</v>
       </c>
       <c r="J15" t="n">
-        <v>2.76</v>
+        <v>2.78</v>
       </c>
       <c r="K15" t="n">
-        <v>3.2</v>
+        <v>3.15</v>
       </c>
       <c r="L15" t="n">
         <v>1.52</v>
@@ -4198,7 +4198,7 @@
         <v>1.18</v>
       </c>
       <c r="S15" t="n">
-        <v>6.2</v>
+        <v>6</v>
       </c>
       <c r="T15" t="n">
         <v>2.2</v>
@@ -4213,7 +4213,7 @@
         <v>1.56</v>
       </c>
       <c r="X15" t="n">
-        <v>9.199999999999999</v>
+        <v>8</v>
       </c>
       <c r="Y15" t="n">
         <v>11.5</v>
@@ -4237,22 +4237,22 @@
         <v>80</v>
       </c>
       <c r="AF15" t="n">
-        <v>18</v>
+        <v>17.5</v>
       </c>
       <c r="AG15" t="n">
         <v>16</v>
       </c>
       <c r="AH15" t="n">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="AI15" t="n">
         <v>120</v>
       </c>
       <c r="AJ15" t="n">
-        <v>55</v>
+        <v>50</v>
       </c>
       <c r="AK15" t="n">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="AL15" t="n">
         <v>90</v>
@@ -4261,64 +4261,64 @@
         <v>270</v>
       </c>
       <c r="AN15" t="n">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="AO15" t="n">
         <v>120</v>
       </c>
       <c r="AP15" t="n">
-        <v>6.4</v>
+        <v>3.05</v>
       </c>
       <c r="AQ15" t="n">
-        <v>7.8</v>
+        <v>3.45</v>
       </c>
       <c r="AR15" t="n">
-        <v>19.5</v>
+        <v>4.1</v>
       </c>
       <c r="AS15" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="AT15" t="n">
+        <v>3.15</v>
+      </c>
+      <c r="AU15" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="AV15" t="n">
+        <v>3.95</v>
+      </c>
+      <c r="AW15" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="AX15" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="AY15" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="AZ15" t="n">
         <v>4.2</v>
       </c>
-      <c r="AT15" t="n">
-        <v>6.2</v>
-      </c>
-      <c r="AU15" t="n">
-        <v>6</v>
-      </c>
-      <c r="AV15" t="n">
-        <v>14</v>
-      </c>
-      <c r="AW15" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="AX15" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="AY15" t="n">
-        <v>11</v>
-      </c>
-      <c r="AZ15" t="n">
-        <v>21</v>
-      </c>
       <c r="BA15" t="n">
-        <v>4.2</v>
+        <v>4.7</v>
       </c>
       <c r="BB15" t="n">
-        <v>4.1</v>
+        <v>4.4</v>
       </c>
       <c r="BC15" t="n">
-        <v>4.1</v>
+        <v>4.4</v>
       </c>
       <c r="BD15" t="n">
-        <v>4.2</v>
+        <v>4.6</v>
       </c>
       <c r="BE15" t="n">
-        <v>4.3</v>
+        <v>4.8</v>
       </c>
       <c r="BF15" t="n">
-        <v>4.1</v>
+        <v>4.5</v>
       </c>
       <c r="BG15" t="n">
-        <v>4.2</v>
+        <v>4.7</v>
       </c>
       <c r="BH15" t="n">
         <v>2.64</v>
@@ -4330,13 +4330,13 @@
         <v>12.5</v>
       </c>
       <c r="BK15" t="n">
-        <v>5.8</v>
+        <v>5.9</v>
       </c>
       <c r="BL15" t="n">
         <v>1000</v>
       </c>
       <c r="BM15" t="n">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="BN15" t="n">
         <v>5.4</v>
@@ -4345,7 +4345,7 @@
         <v>4.5</v>
       </c>
       <c r="BP15" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="BQ15" t="n">
         <v>7.6</v>
@@ -4354,7 +4354,7 @@
         <v>1000</v>
       </c>
       <c r="BS15" t="n">
-        <v>9.199999999999999</v>
+        <v>9.4</v>
       </c>
       <c r="BT15" t="n">
         <v>6.8</v>
@@ -4366,23 +4366,23 @@
         <v>1000</v>
       </c>
       <c r="BW15" t="n">
-        <v>8.6</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BX15" t="n">
         <v>1000</v>
       </c>
       <c r="BY15" t="n">
-        <v>9.4</v>
+        <v>9.6</v>
       </c>
       <c r="BZ15" t="n">
         <v>1000</v>
       </c>
       <c r="CA15" t="n">
-        <v>9.4</v>
+        <v>9.6</v>
       </c>
       <c r="CB15" t="inlineStr">
         <is>
-          <t>2026-06-11 15:58:00</t>
+          <t>2026-06-11 18:11:04</t>
         </is>
       </c>
     </row>
@@ -4413,22 +4413,22 @@
         </is>
       </c>
       <c r="F16" t="n">
-        <v>2.86</v>
+        <v>2.88</v>
       </c>
       <c r="G16" t="n">
-        <v>2.94</v>
+        <v>3.1</v>
       </c>
       <c r="H16" t="n">
-        <v>2.46</v>
+        <v>2.4</v>
       </c>
       <c r="I16" t="n">
-        <v>2.6</v>
+        <v>2.56</v>
       </c>
       <c r="J16" t="n">
-        <v>3.7</v>
+        <v>3.65</v>
       </c>
       <c r="K16" t="n">
-        <v>3.95</v>
+        <v>4</v>
       </c>
       <c r="L16" t="n">
         <v>1.01</v>
@@ -4449,7 +4449,7 @@
         <v>1.68</v>
       </c>
       <c r="R16" t="n">
-        <v>1.52</v>
+        <v>1.5</v>
       </c>
       <c r="S16" t="n">
         <v>2.68</v>
@@ -4461,10 +4461,10 @@
         <v>2.44</v>
       </c>
       <c r="V16" t="n">
-        <v>1.63</v>
+        <v>1.64</v>
       </c>
       <c r="W16" t="n">
-        <v>1.52</v>
+        <v>1.48</v>
       </c>
       <c r="X16" t="n">
         <v>25</v>
@@ -4473,7 +4473,7 @@
         <v>14.5</v>
       </c>
       <c r="Z16" t="n">
-        <v>19.5</v>
+        <v>19</v>
       </c>
       <c r="AA16" t="n">
         <v>36</v>
@@ -4488,7 +4488,7 @@
         <v>14.5</v>
       </c>
       <c r="AE16" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="AF16" t="n">
         <v>24</v>
@@ -4500,7 +4500,7 @@
         <v>16</v>
       </c>
       <c r="AI16" t="n">
-        <v>40</v>
+        <v>34</v>
       </c>
       <c r="AJ16" t="n">
         <v>48</v>
@@ -4530,7 +4530,7 @@
         <v>15.5</v>
       </c>
       <c r="AS16" t="n">
-        <v>5.1</v>
+        <v>5.3</v>
       </c>
       <c r="AT16" t="n">
         <v>12.5</v>
@@ -4554,19 +4554,19 @@
         <v>13</v>
       </c>
       <c r="BA16" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="BB16" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="BC16" t="n">
         <v>5.2</v>
       </c>
-      <c r="BC16" t="n">
-        <v>5</v>
-      </c>
       <c r="BD16" t="n">
-        <v>5.1</v>
+        <v>5.3</v>
       </c>
       <c r="BE16" t="n">
-        <v>5.4</v>
+        <v>5.7</v>
       </c>
       <c r="BF16" t="n">
         <v>17.5</v>
@@ -4636,7 +4636,7 @@
       </c>
       <c r="CB16" t="inlineStr">
         <is>
-          <t>2026-06-11 15:58:00</t>
+          <t>2026-06-11 18:11:04</t>
         </is>
       </c>
     </row>
@@ -4667,22 +4667,22 @@
         </is>
       </c>
       <c r="F17" t="n">
-        <v>1.37</v>
+        <v>1.36</v>
       </c>
       <c r="G17" t="n">
-        <v>1.41</v>
+        <v>1.4</v>
       </c>
       <c r="H17" t="n">
         <v>10.5</v>
       </c>
       <c r="I17" t="n">
-        <v>12</v>
+        <v>12.5</v>
       </c>
       <c r="J17" t="n">
         <v>5</v>
       </c>
       <c r="K17" t="n">
-        <v>5.5</v>
+        <v>5.6</v>
       </c>
       <c r="L17" t="n">
         <v>1.01</v>
@@ -4715,16 +4715,16 @@
         <v>1.74</v>
       </c>
       <c r="V17" t="n">
-        <v>1.09</v>
+        <v>1.08</v>
       </c>
       <c r="W17" t="n">
-        <v>3.4</v>
+        <v>3.45</v>
       </c>
       <c r="X17" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="Y17" t="n">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="Z17" t="n">
         <v>130</v>
@@ -4733,7 +4733,7 @@
         <v>580</v>
       </c>
       <c r="AB17" t="n">
-        <v>9</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AC17" t="n">
         <v>14.5</v>
@@ -4745,10 +4745,10 @@
         <v>250</v>
       </c>
       <c r="AF17" t="n">
-        <v>9.199999999999999</v>
+        <v>9</v>
       </c>
       <c r="AG17" t="n">
-        <v>13</v>
+        <v>12.5</v>
       </c>
       <c r="AH17" t="n">
         <v>40</v>
@@ -4778,13 +4778,13 @@
         <v>14.5</v>
       </c>
       <c r="AQ17" t="n">
-        <v>4</v>
+        <v>22</v>
       </c>
       <c r="AR17" t="n">
-        <v>4.3</v>
+        <v>4.5</v>
       </c>
       <c r="AS17" t="n">
-        <v>4.4</v>
+        <v>4.7</v>
       </c>
       <c r="AT17" t="n">
         <v>6.4</v>
@@ -4793,10 +4793,10 @@
         <v>9</v>
       </c>
       <c r="AV17" t="n">
-        <v>4.1</v>
+        <v>4.3</v>
       </c>
       <c r="AW17" t="n">
-        <v>4.4</v>
+        <v>4.6</v>
       </c>
       <c r="AX17" t="n">
         <v>6.4</v>
@@ -4805,10 +4805,10 @@
         <v>9</v>
       </c>
       <c r="AZ17" t="n">
-        <v>4</v>
+        <v>4.2</v>
       </c>
       <c r="BA17" t="n">
-        <v>4.4</v>
+        <v>4.6</v>
       </c>
       <c r="BB17" t="n">
         <v>9.199999999999999</v>
@@ -4817,16 +4817,16 @@
         <v>13.5</v>
       </c>
       <c r="BD17" t="n">
-        <v>4.1</v>
+        <v>4.3</v>
       </c>
       <c r="BE17" t="n">
-        <v>4.4</v>
+        <v>4.6</v>
       </c>
       <c r="BF17" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="BG17" t="n">
-        <v>4.4</v>
+        <v>4.7</v>
       </c>
       <c r="BH17" t="n">
         <v>1000</v>
@@ -4838,37 +4838,37 @@
         <v>1000</v>
       </c>
       <c r="BK17" t="n">
-        <v>1.04</v>
+        <v>1.6</v>
       </c>
       <c r="BL17" t="n">
         <v>1000</v>
       </c>
       <c r="BM17" t="n">
-        <v>1.04</v>
+        <v>1.72</v>
       </c>
       <c r="BN17" t="n">
         <v>1000</v>
       </c>
       <c r="BO17" t="n">
-        <v>1.04</v>
+        <v>1.32</v>
       </c>
       <c r="BP17" t="n">
         <v>1000</v>
       </c>
       <c r="BQ17" t="n">
-        <v>1.04</v>
+        <v>1.52</v>
       </c>
       <c r="BR17" t="n">
         <v>1000</v>
       </c>
       <c r="BS17" t="n">
-        <v>1.04</v>
+        <v>1.67</v>
       </c>
       <c r="BT17" t="n">
         <v>1000</v>
       </c>
       <c r="BU17" t="n">
-        <v>1.04</v>
+        <v>1.61</v>
       </c>
       <c r="BV17" t="n">
         <v>1000</v>
@@ -4890,7 +4890,7 @@
       </c>
       <c r="CB17" t="inlineStr">
         <is>
-          <t>2026-06-11 15:58:00</t>
+          <t>2026-06-11 18:11:04</t>
         </is>
       </c>
     </row>
@@ -4924,19 +4924,19 @@
         <v>3.15</v>
       </c>
       <c r="G18" t="n">
-        <v>3.45</v>
+        <v>3.4</v>
       </c>
       <c r="H18" t="n">
         <v>2.46</v>
       </c>
       <c r="I18" t="n">
-        <v>2.62</v>
+        <v>2.58</v>
       </c>
       <c r="J18" t="n">
-        <v>3.25</v>
+        <v>3.3</v>
       </c>
       <c r="K18" t="n">
-        <v>3.45</v>
+        <v>3.55</v>
       </c>
       <c r="L18" t="n">
         <v>1.41</v>
@@ -4945,31 +4945,31 @@
         <v>1.09</v>
       </c>
       <c r="N18" t="n">
-        <v>3.05</v>
+        <v>3.1</v>
       </c>
       <c r="O18" t="n">
-        <v>1.4</v>
+        <v>1.41</v>
       </c>
       <c r="P18" t="n">
-        <v>1.74</v>
+        <v>1.71</v>
       </c>
       <c r="Q18" t="n">
-        <v>2.2</v>
+        <v>2.26</v>
       </c>
       <c r="R18" t="n">
-        <v>1.26</v>
+        <v>1.25</v>
       </c>
       <c r="S18" t="n">
-        <v>4.2</v>
+        <v>4.4</v>
       </c>
       <c r="T18" t="n">
-        <v>1.89</v>
+        <v>1.91</v>
       </c>
       <c r="U18" t="n">
         <v>1.93</v>
       </c>
       <c r="V18" t="n">
-        <v>1.62</v>
+        <v>1.63</v>
       </c>
       <c r="W18" t="n">
         <v>1.41</v>
@@ -4978,10 +4978,10 @@
         <v>12</v>
       </c>
       <c r="Y18" t="n">
-        <v>9.6</v>
+        <v>9.4</v>
       </c>
       <c r="Z18" t="n">
-        <v>16.5</v>
+        <v>16</v>
       </c>
       <c r="AA18" t="n">
         <v>50</v>
@@ -5065,25 +5065,25 @@
         <v>34</v>
       </c>
       <c r="BB18" t="n">
-        <v>7.8</v>
+        <v>8</v>
       </c>
       <c r="BC18" t="n">
         <v>30</v>
       </c>
       <c r="BD18" t="n">
-        <v>7.8</v>
+        <v>8</v>
       </c>
       <c r="BE18" t="n">
-        <v>8.4</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BF18" t="n">
         <v>34</v>
       </c>
       <c r="BG18" t="n">
-        <v>7</v>
+        <v>7.2</v>
       </c>
       <c r="BH18" t="n">
-        <v>3.2</v>
+        <v>3.15</v>
       </c>
       <c r="BI18" t="n">
         <v>2.56</v>
@@ -5098,7 +5098,7 @@
         <v>1000</v>
       </c>
       <c r="BM18" t="n">
-        <v>9.800000000000001</v>
+        <v>10</v>
       </c>
       <c r="BN18" t="n">
         <v>6.6</v>
@@ -5110,13 +5110,13 @@
         <v>1000</v>
       </c>
       <c r="BQ18" t="n">
-        <v>7.6</v>
+        <v>7.8</v>
       </c>
       <c r="BR18" t="n">
         <v>1000</v>
       </c>
       <c r="BS18" t="n">
-        <v>8.6</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BT18" t="n">
         <v>5.5</v>
@@ -5128,23 +5128,23 @@
         <v>21</v>
       </c>
       <c r="BW18" t="n">
-        <v>7</v>
+        <v>7.2</v>
       </c>
       <c r="BX18" t="n">
         <v>1000</v>
       </c>
       <c r="BY18" t="n">
-        <v>8.199999999999999</v>
+        <v>8.4</v>
       </c>
       <c r="BZ18" t="n">
         <v>1000</v>
       </c>
       <c r="CA18" t="n">
-        <v>8</v>
+        <v>8.4</v>
       </c>
       <c r="CB18" t="inlineStr">
         <is>
-          <t>2026-06-11 15:58:00</t>
+          <t>2026-06-11 18:11:04</t>
         </is>
       </c>
     </row>
@@ -5178,19 +5178,19 @@
         <v>2.22</v>
       </c>
       <c r="G19" t="n">
-        <v>2.34</v>
+        <v>2.32</v>
       </c>
       <c r="H19" t="n">
         <v>3.35</v>
       </c>
       <c r="I19" t="n">
-        <v>3.6</v>
+        <v>3.55</v>
       </c>
       <c r="J19" t="n">
-        <v>3.55</v>
+        <v>3.65</v>
       </c>
       <c r="K19" t="n">
-        <v>3.95</v>
+        <v>3.9</v>
       </c>
       <c r="L19" t="n">
         <v>1.36</v>
@@ -5199,49 +5199,49 @@
         <v>1.06</v>
       </c>
       <c r="N19" t="n">
-        <v>3.95</v>
+        <v>3.85</v>
       </c>
       <c r="O19" t="n">
         <v>1.29</v>
       </c>
       <c r="P19" t="n">
-        <v>1.99</v>
+        <v>1.98</v>
       </c>
       <c r="Q19" t="n">
-        <v>1.84</v>
+        <v>1.86</v>
       </c>
       <c r="R19" t="n">
-        <v>1.39</v>
+        <v>1.37</v>
       </c>
       <c r="S19" t="n">
-        <v>3.2</v>
+        <v>3.3</v>
       </c>
       <c r="T19" t="n">
-        <v>1.73</v>
+        <v>1.74</v>
       </c>
       <c r="U19" t="n">
-        <v>2.2</v>
+        <v>2.16</v>
       </c>
       <c r="V19" t="n">
         <v>1.39</v>
       </c>
       <c r="W19" t="n">
-        <v>1.74</v>
+        <v>1.75</v>
       </c>
       <c r="X19" t="n">
         <v>19.5</v>
       </c>
       <c r="Y19" t="n">
-        <v>15</v>
+        <v>14.5</v>
       </c>
       <c r="Z19" t="n">
-        <v>36</v>
+        <v>25</v>
       </c>
       <c r="AA19" t="n">
         <v>75</v>
       </c>
       <c r="AB19" t="n">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="AC19" t="n">
         <v>8.800000000000001</v>
@@ -5256,10 +5256,10 @@
         <v>15.5</v>
       </c>
       <c r="AG19" t="n">
-        <v>12</v>
+        <v>11.5</v>
       </c>
       <c r="AH19" t="n">
-        <v>17.5</v>
+        <v>19</v>
       </c>
       <c r="AI19" t="n">
         <v>60</v>
@@ -5292,7 +5292,7 @@
         <v>20</v>
       </c>
       <c r="AS19" t="n">
-        <v>7.8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AT19" t="n">
         <v>9.4</v>
@@ -5313,7 +5313,7 @@
         <v>9.6</v>
       </c>
       <c r="AZ19" t="n">
-        <v>14</v>
+        <v>14.5</v>
       </c>
       <c r="BA19" t="n">
         <v>34</v>
@@ -5328,7 +5328,7 @@
         <v>25</v>
       </c>
       <c r="BE19" t="n">
-        <v>8</v>
+        <v>8.6</v>
       </c>
       <c r="BF19" t="n">
         <v>13.5</v>
@@ -5340,10 +5340,10 @@
         <v>3.75</v>
       </c>
       <c r="BI19" t="n">
-        <v>2.9</v>
+        <v>2.92</v>
       </c>
       <c r="BJ19" t="n">
-        <v>9.6</v>
+        <v>9.4</v>
       </c>
       <c r="BK19" t="n">
         <v>5.8</v>
@@ -5352,7 +5352,7 @@
         <v>1000</v>
       </c>
       <c r="BM19" t="n">
-        <v>9.800000000000001</v>
+        <v>10.5</v>
       </c>
       <c r="BN19" t="n">
         <v>5.4</v>
@@ -5361,16 +5361,16 @@
         <v>4.5</v>
       </c>
       <c r="BP19" t="n">
-        <v>16.5</v>
+        <v>16</v>
       </c>
       <c r="BQ19" t="n">
         <v>9.6</v>
       </c>
       <c r="BR19" t="n">
-        <v>40</v>
+        <v>1000</v>
       </c>
       <c r="BS19" t="n">
-        <v>7.8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BT19" t="n">
         <v>7</v>
@@ -5382,23 +5382,23 @@
         <v>1000</v>
       </c>
       <c r="BW19" t="n">
-        <v>7.6</v>
+        <v>8</v>
       </c>
       <c r="BX19" t="n">
         <v>1000</v>
       </c>
       <c r="BY19" t="n">
-        <v>8.4</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BZ19" t="n">
         <v>24</v>
       </c>
       <c r="CA19" t="n">
-        <v>7.4</v>
+        <v>7.8</v>
       </c>
       <c r="CB19" t="inlineStr">
         <is>
-          <t>2026-06-11 15:58:00</t>
+          <t>2026-06-11 18:11:04</t>
         </is>
       </c>
     </row>
@@ -5432,19 +5432,19 @@
         <v>3.95</v>
       </c>
       <c r="G20" t="n">
-        <v>4.6</v>
+        <v>4.5</v>
       </c>
       <c r="H20" t="n">
-        <v>1.87</v>
+        <v>1.89</v>
       </c>
       <c r="I20" t="n">
-        <v>2.06</v>
+        <v>2.04</v>
       </c>
       <c r="J20" t="n">
         <v>3.7</v>
       </c>
       <c r="K20" t="n">
-        <v>4.2</v>
+        <v>4.3</v>
       </c>
       <c r="L20" t="n">
         <v>1.01</v>
@@ -5465,7 +5465,7 @@
         <v>1.71</v>
       </c>
       <c r="R20" t="n">
-        <v>1.52</v>
+        <v>1.53</v>
       </c>
       <c r="S20" t="n">
         <v>2.56</v>
@@ -5477,13 +5477,13 @@
         <v>2.3</v>
       </c>
       <c r="V20" t="n">
-        <v>1.94</v>
+        <v>1.96</v>
       </c>
       <c r="W20" t="n">
-        <v>1.28</v>
+        <v>1.3</v>
       </c>
       <c r="X20" t="n">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="Y20" t="n">
         <v>12</v>
@@ -5492,19 +5492,19 @@
         <v>14.5</v>
       </c>
       <c r="AA20" t="n">
-        <v>27</v>
+        <v>32</v>
       </c>
       <c r="AB20" t="n">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="AC20" t="n">
-        <v>9.800000000000001</v>
+        <v>11.5</v>
       </c>
       <c r="AD20" t="n">
         <v>12.5</v>
       </c>
       <c r="AE20" t="n">
-        <v>18.5</v>
+        <v>22</v>
       </c>
       <c r="AF20" t="n">
         <v>36</v>
@@ -5513,37 +5513,37 @@
         <v>23</v>
       </c>
       <c r="AH20" t="n">
-        <v>16.5</v>
+        <v>19</v>
       </c>
       <c r="AI20" t="n">
-        <v>30</v>
+        <v>36</v>
       </c>
       <c r="AJ20" t="n">
-        <v>110</v>
+        <v>120</v>
       </c>
       <c r="AK20" t="n">
-        <v>46</v>
+        <v>55</v>
       </c>
       <c r="AL20" t="n">
         <v>48</v>
       </c>
       <c r="AM20" t="n">
-        <v>95</v>
+        <v>80</v>
       </c>
       <c r="AN20" t="n">
         <v>40</v>
       </c>
       <c r="AO20" t="n">
-        <v>10.5</v>
+        <v>12</v>
       </c>
       <c r="AP20" t="n">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="AQ20" t="n">
-        <v>9.4</v>
+        <v>9.6</v>
       </c>
       <c r="AR20" t="n">
-        <v>11.5</v>
+        <v>10</v>
       </c>
       <c r="AS20" t="n">
         <v>18.5</v>
@@ -5555,40 +5555,40 @@
         <v>7</v>
       </c>
       <c r="AV20" t="n">
-        <v>9.800000000000001</v>
+        <v>10</v>
       </c>
       <c r="AW20" t="n">
-        <v>14.5</v>
+        <v>12.5</v>
       </c>
       <c r="AX20" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="AY20" t="n">
         <v>16</v>
       </c>
       <c r="AZ20" t="n">
-        <v>13.5</v>
+        <v>11.5</v>
       </c>
       <c r="BA20" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="BB20" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="BC20" t="n">
+        <v>30</v>
+      </c>
+      <c r="BD20" t="n">
+        <v>32</v>
+      </c>
+      <c r="BE20" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="BF20" t="n">
+        <v>28</v>
+      </c>
+      <c r="BG20" t="n">
         <v>7.4</v>
-      </c>
-      <c r="BC20" t="n">
-        <v>32</v>
-      </c>
-      <c r="BD20" t="n">
-        <v>30</v>
-      </c>
-      <c r="BE20" t="n">
-        <v>7.2</v>
-      </c>
-      <c r="BF20" t="n">
-        <v>27</v>
-      </c>
-      <c r="BG20" t="n">
-        <v>7.2</v>
       </c>
       <c r="BH20" t="n">
         <v>1000</v>
@@ -5652,7 +5652,7 @@
       </c>
       <c r="CB20" t="inlineStr">
         <is>
-          <t>2026-06-11 15:58:00</t>
+          <t>2026-06-11 18:11:04</t>
         </is>
       </c>
     </row>
@@ -5701,7 +5701,7 @@
         <v>3.45</v>
       </c>
       <c r="L21" t="n">
-        <v>1.48</v>
+        <v>1.4</v>
       </c>
       <c r="M21" t="n">
         <v>1.09</v>
@@ -5710,7 +5710,7 @@
         <v>3.1</v>
       </c>
       <c r="O21" t="n">
-        <v>1.41</v>
+        <v>1.42</v>
       </c>
       <c r="P21" t="n">
         <v>1.71</v>
@@ -5719,7 +5719,7 @@
         <v>2.22</v>
       </c>
       <c r="R21" t="n">
-        <v>1.26</v>
+        <v>1.27</v>
       </c>
       <c r="S21" t="n">
         <v>4.2</v>
@@ -5788,7 +5788,7 @@
         <v>32</v>
       </c>
       <c r="AO21" t="n">
-        <v>70</v>
+        <v>65</v>
       </c>
       <c r="AP21" t="n">
         <v>8.199999999999999</v>
@@ -5812,7 +5812,7 @@
         <v>11</v>
       </c>
       <c r="AW21" t="n">
-        <v>4</v>
+        <v>4.1</v>
       </c>
       <c r="AX21" t="n">
         <v>10.5</v>
@@ -5833,7 +5833,7 @@
         <v>21</v>
       </c>
       <c r="BD21" t="n">
-        <v>4</v>
+        <v>4.1</v>
       </c>
       <c r="BE21" t="n">
         <v>4.2</v>
@@ -5896,7 +5896,7 @@
         <v>1000</v>
       </c>
       <c r="BY21" t="n">
-        <v>12</v>
+        <v>11.5</v>
       </c>
       <c r="BZ21" t="n">
         <v>1000</v>
@@ -5906,7 +5906,7 @@
       </c>
       <c r="CB21" t="inlineStr">
         <is>
-          <t>2026-06-11 15:58:00</t>
+          <t>2026-06-11 18:11:04</t>
         </is>
       </c>
     </row>
@@ -5943,10 +5943,10 @@
         <v>4.4</v>
       </c>
       <c r="H22" t="n">
-        <v>1.92</v>
+        <v>1.93</v>
       </c>
       <c r="I22" t="n">
-        <v>2.08</v>
+        <v>2.1</v>
       </c>
       <c r="J22" t="n">
         <v>3.7</v>
@@ -5967,34 +5967,34 @@
         <v>1.25</v>
       </c>
       <c r="P22" t="n">
-        <v>2.08</v>
+        <v>2.12</v>
       </c>
       <c r="Q22" t="n">
         <v>1.74</v>
       </c>
       <c r="R22" t="n">
-        <v>1.34</v>
+        <v>1.33</v>
       </c>
       <c r="S22" t="n">
-        <v>2.32</v>
+        <v>2.34</v>
       </c>
       <c r="T22" t="n">
-        <v>1.37</v>
+        <v>1.66</v>
       </c>
       <c r="U22" t="n">
-        <v>1.73</v>
+        <v>2.14</v>
       </c>
       <c r="V22" t="n">
-        <v>1.92</v>
+        <v>1.9</v>
       </c>
       <c r="W22" t="n">
-        <v>1.29</v>
+        <v>1.3</v>
       </c>
       <c r="X22" t="n">
         <v>21</v>
       </c>
       <c r="Y22" t="n">
-        <v>12.5</v>
+        <v>11.5</v>
       </c>
       <c r="Z22" t="n">
         <v>14.5</v>
@@ -6003,100 +6003,100 @@
         <v>25</v>
       </c>
       <c r="AB22" t="n">
-        <v>19.5</v>
+        <v>18</v>
       </c>
       <c r="AC22" t="n">
-        <v>10.5</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AD22" t="n">
-        <v>12.5</v>
+        <v>11.5</v>
       </c>
       <c r="AE22" t="n">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="AF22" t="n">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="AG22" t="n">
-        <v>18.5</v>
+        <v>17.5</v>
       </c>
       <c r="AH22" t="n">
-        <v>19</v>
+        <v>17.5</v>
       </c>
       <c r="AI22" t="n">
-        <v>38</v>
+        <v>34</v>
       </c>
       <c r="AJ22" t="n">
-        <v>90</v>
+        <v>85</v>
       </c>
       <c r="AK22" t="n">
-        <v>55</v>
+        <v>48</v>
       </c>
       <c r="AL22" t="n">
         <v>55</v>
       </c>
       <c r="AM22" t="n">
-        <v>95</v>
+        <v>85</v>
       </c>
       <c r="AN22" t="n">
-        <v>44</v>
+        <v>50</v>
       </c>
       <c r="AO22" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="AP22" t="n">
         <v>13.5</v>
       </c>
       <c r="AQ22" t="n">
-        <v>8.4</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AR22" t="n">
-        <v>10</v>
+        <v>11.5</v>
       </c>
       <c r="AS22" t="n">
-        <v>17.5</v>
+        <v>19.5</v>
       </c>
       <c r="AT22" t="n">
         <v>13</v>
       </c>
       <c r="AU22" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="AV22" t="n">
+        <v>9</v>
+      </c>
+      <c r="AW22" t="n">
+        <v>17</v>
+      </c>
+      <c r="AX22" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="AY22" t="n">
+        <v>14</v>
+      </c>
+      <c r="AZ22" t="n">
+        <v>14</v>
+      </c>
+      <c r="BA22" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="BB22" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="BC22" t="n">
         <v>6.8</v>
       </c>
-      <c r="AV22" t="n">
-        <v>8.199999999999999</v>
-      </c>
-      <c r="AW22" t="n">
-        <v>15</v>
-      </c>
-      <c r="AX22" t="n">
-        <v>4.8</v>
-      </c>
-      <c r="AY22" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="AZ22" t="n">
-        <v>13</v>
-      </c>
-      <c r="BA22" t="n">
-        <v>4.8</v>
-      </c>
-      <c r="BB22" t="n">
-        <v>5.2</v>
-      </c>
-      <c r="BC22" t="n">
-        <v>5</v>
-      </c>
       <c r="BD22" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="BE22" t="n">
-        <v>5.2</v>
+        <v>7.2</v>
       </c>
       <c r="BF22" t="n">
-        <v>4.9</v>
+        <v>32</v>
       </c>
       <c r="BG22" t="n">
-        <v>9.199999999999999</v>
+        <v>10</v>
       </c>
       <c r="BH22" t="n">
         <v>1000</v>
@@ -6160,7 +6160,7 @@
       </c>
       <c r="CB22" t="inlineStr">
         <is>
-          <t>2026-06-11 15:58:00</t>
+          <t>2026-06-11 18:11:04</t>
         </is>
       </c>
     </row>
@@ -6197,10 +6197,10 @@
         <v>5</v>
       </c>
       <c r="H23" t="n">
-        <v>1.84</v>
+        <v>1.85</v>
       </c>
       <c r="I23" t="n">
-        <v>1.98</v>
+        <v>1.99</v>
       </c>
       <c r="J23" t="n">
         <v>3.55</v>
@@ -6209,7 +6209,7 @@
         <v>3.9</v>
       </c>
       <c r="L23" t="n">
-        <v>1.39</v>
+        <v>1.35</v>
       </c>
       <c r="M23" t="n">
         <v>1.06</v>
@@ -6233,13 +6233,13 @@
         <v>3.3</v>
       </c>
       <c r="T23" t="n">
-        <v>1.8</v>
+        <v>1.79</v>
       </c>
       <c r="U23" t="n">
         <v>2.04</v>
       </c>
       <c r="V23" t="n">
-        <v>2.02</v>
+        <v>2</v>
       </c>
       <c r="W23" t="n">
         <v>1.25</v>
@@ -6257,7 +6257,7 @@
         <v>23</v>
       </c>
       <c r="AB23" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="AC23" t="n">
         <v>9</v>
@@ -6293,7 +6293,7 @@
         <v>120</v>
       </c>
       <c r="AN23" t="n">
-        <v>85</v>
+        <v>80</v>
       </c>
       <c r="AO23" t="n">
         <v>14</v>
@@ -6329,25 +6329,25 @@
         <v>15.5</v>
       </c>
       <c r="AZ23" t="n">
-        <v>14.5</v>
+        <v>16</v>
       </c>
       <c r="BA23" t="n">
         <v>24</v>
       </c>
       <c r="BB23" t="n">
-        <v>8</v>
+        <v>7.6</v>
       </c>
       <c r="BC23" t="n">
+        <v>38</v>
+      </c>
+      <c r="BD23" t="n">
+        <v>42</v>
+      </c>
+      <c r="BE23" t="n">
         <v>7.6</v>
       </c>
-      <c r="BD23" t="n">
-        <v>7.6</v>
-      </c>
-      <c r="BE23" t="n">
-        <v>8</v>
-      </c>
       <c r="BF23" t="n">
-        <v>7.6</v>
+        <v>7.4</v>
       </c>
       <c r="BG23" t="n">
         <v>11</v>
@@ -6356,7 +6356,7 @@
         <v>3.6</v>
       </c>
       <c r="BI23" t="n">
-        <v>2.86</v>
+        <v>3.05</v>
       </c>
       <c r="BJ23" t="n">
         <v>10.5</v>
@@ -6414,7 +6414,7 @@
       </c>
       <c r="CB23" t="inlineStr">
         <is>
-          <t>2026-06-11 15:58:00</t>
+          <t>2026-06-11 18:11:04</t>
         </is>
       </c>
     </row>
@@ -6445,19 +6445,19 @@
         </is>
       </c>
       <c r="F24" t="n">
-        <v>1.42</v>
+        <v>1.33</v>
       </c>
       <c r="G24" t="n">
         <v>1.63</v>
       </c>
       <c r="H24" t="n">
-        <v>4.8</v>
+        <v>1.04</v>
       </c>
       <c r="I24" t="n">
-        <v>95</v>
+        <v>1000</v>
       </c>
       <c r="J24" t="n">
-        <v>4.6</v>
+        <v>1.03</v>
       </c>
       <c r="K24" t="n">
         <v>1000</v>
@@ -6469,22 +6469,22 @@
         <v>1.01</v>
       </c>
       <c r="N24" t="n">
-        <v>1.99</v>
+        <v>1.1</v>
       </c>
       <c r="O24" t="n">
-        <v>1.09</v>
+        <v>1.01</v>
       </c>
       <c r="P24" t="n">
-        <v>1.98</v>
+        <v>1.25</v>
       </c>
       <c r="Q24" t="n">
-        <v>1.09</v>
+        <v>1.01</v>
       </c>
       <c r="R24" t="n">
         <v>1.18</v>
       </c>
       <c r="S24" t="n">
-        <v>1.09</v>
+        <v>1.05</v>
       </c>
       <c r="T24" t="n">
         <v>1.11</v>
@@ -6493,10 +6493,10 @@
         <v>1.11</v>
       </c>
       <c r="V24" t="n">
-        <v>1.09</v>
+        <v>1.01</v>
       </c>
       <c r="W24" t="n">
-        <v>2.58</v>
+        <v>1.01</v>
       </c>
       <c r="X24" t="n">
         <v>1000</v>
@@ -6668,7 +6668,7 @@
       </c>
       <c r="CB24" t="inlineStr">
         <is>
-          <t>2026-06-11 15:58:00</t>
+          <t>2026-06-11 18:11:04</t>
         </is>
       </c>
     </row>
@@ -6699,22 +6699,22 @@
         </is>
       </c>
       <c r="F25" t="n">
-        <v>2.82</v>
+        <v>2.84</v>
       </c>
       <c r="G25" t="n">
-        <v>2.98</v>
+        <v>2.96</v>
       </c>
       <c r="H25" t="n">
         <v>2.74</v>
       </c>
       <c r="I25" t="n">
-        <v>2.92</v>
+        <v>2.9</v>
       </c>
       <c r="J25" t="n">
-        <v>3.2</v>
+        <v>3.25</v>
       </c>
       <c r="K25" t="n">
-        <v>3.45</v>
+        <v>3.5</v>
       </c>
       <c r="L25" t="n">
         <v>1.01</v>
@@ -6723,10 +6723,10 @@
         <v>1.09</v>
       </c>
       <c r="N25" t="n">
-        <v>3.2</v>
+        <v>3.25</v>
       </c>
       <c r="O25" t="n">
-        <v>1.4</v>
+        <v>1.39</v>
       </c>
       <c r="P25" t="n">
         <v>1.8</v>
@@ -6750,7 +6750,7 @@
         <v>1.52</v>
       </c>
       <c r="W25" t="n">
-        <v>1.5</v>
+        <v>1.51</v>
       </c>
       <c r="X25" t="n">
         <v>14.5</v>
@@ -6759,7 +6759,7 @@
         <v>12.5</v>
       </c>
       <c r="Z25" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AA25" t="n">
         <v>55</v>
@@ -6768,7 +6768,7 @@
         <v>12.5</v>
       </c>
       <c r="AC25" t="n">
-        <v>7.6</v>
+        <v>9</v>
       </c>
       <c r="AD25" t="n">
         <v>15.5</v>
@@ -6780,7 +6780,7 @@
         <v>23</v>
       </c>
       <c r="AG25" t="n">
-        <v>13</v>
+        <v>15.5</v>
       </c>
       <c r="AH25" t="n">
         <v>23</v>
@@ -6804,7 +6804,7 @@
         <v>42</v>
       </c>
       <c r="AO25" t="n">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="AP25" t="n">
         <v>10.5</v>
@@ -6813,13 +6813,13 @@
         <v>9</v>
       </c>
       <c r="AR25" t="n">
-        <v>13</v>
+        <v>3.65</v>
       </c>
       <c r="AS25" t="n">
-        <v>4.7</v>
+        <v>4</v>
       </c>
       <c r="AT25" t="n">
-        <v>9</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AU25" t="n">
         <v>6.6</v>
@@ -6828,37 +6828,37 @@
         <v>11</v>
       </c>
       <c r="AW25" t="n">
-        <v>4.6</v>
+        <v>3.95</v>
       </c>
       <c r="AX25" t="n">
-        <v>13.5</v>
+        <v>3.65</v>
       </c>
       <c r="AY25" t="n">
-        <v>11.5</v>
+        <v>3.4</v>
       </c>
       <c r="AZ25" t="n">
+        <v>16</v>
+      </c>
+      <c r="BA25" t="n">
+        <v>4</v>
+      </c>
+      <c r="BB25" t="n">
+        <v>4</v>
+      </c>
+      <c r="BC25" t="n">
+        <v>3.95</v>
+      </c>
+      <c r="BD25" t="n">
+        <v>4</v>
+      </c>
+      <c r="BE25" t="n">
         <v>4.2</v>
       </c>
-      <c r="BA25" t="n">
-        <v>4.7</v>
-      </c>
-      <c r="BB25" t="n">
-        <v>4.7</v>
-      </c>
-      <c r="BC25" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="BD25" t="n">
-        <v>4.7</v>
-      </c>
-      <c r="BE25" t="n">
-        <v>5</v>
-      </c>
       <c r="BF25" t="n">
-        <v>4.6</v>
+        <v>3.95</v>
       </c>
       <c r="BG25" t="n">
-        <v>4.5</v>
+        <v>3.95</v>
       </c>
       <c r="BH25" t="n">
         <v>1000</v>
@@ -6870,19 +6870,19 @@
         <v>1000</v>
       </c>
       <c r="BK25" t="n">
-        <v>1.54</v>
+        <v>1.04</v>
       </c>
       <c r="BL25" t="n">
         <v>1000</v>
       </c>
       <c r="BM25" t="n">
-        <v>1.67</v>
+        <v>1.04</v>
       </c>
       <c r="BN25" t="n">
         <v>1000</v>
       </c>
       <c r="BO25" t="n">
-        <v>1.44</v>
+        <v>1.04</v>
       </c>
       <c r="BP25" t="n">
         <v>1000</v>
@@ -6900,13 +6900,13 @@
         <v>1000</v>
       </c>
       <c r="BU25" t="n">
-        <v>1.39</v>
+        <v>1.04</v>
       </c>
       <c r="BV25" t="n">
         <v>1000</v>
       </c>
       <c r="BW25" t="n">
-        <v>1.65</v>
+        <v>1.57</v>
       </c>
       <c r="BX25" t="n">
         <v>1000</v>
@@ -6922,7 +6922,7 @@
       </c>
       <c r="CB25" t="inlineStr">
         <is>
-          <t>2026-06-11 15:58:00</t>
+          <t>2026-06-11 18:11:04</t>
         </is>
       </c>
     </row>
@@ -6956,19 +6956,19 @@
         <v>1.73</v>
       </c>
       <c r="G26" t="n">
-        <v>1.88</v>
+        <v>1.89</v>
       </c>
       <c r="H26" t="n">
         <v>3.85</v>
       </c>
       <c r="I26" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="J26" t="n">
         <v>4.5</v>
       </c>
-      <c r="J26" t="n">
-        <v>4.4</v>
-      </c>
       <c r="K26" t="n">
-        <v>5.3</v>
+        <v>5.2</v>
       </c>
       <c r="L26" t="n">
         <v>1.18</v>
@@ -7031,13 +7031,13 @@
         <v>48</v>
       </c>
       <c r="AF26" t="n">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="AG26" t="n">
         <v>14</v>
       </c>
       <c r="AH26" t="n">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="AI26" t="n">
         <v>44</v>
@@ -7061,13 +7061,13 @@
         <v>27</v>
       </c>
       <c r="AP26" t="n">
-        <v>4.1</v>
+        <v>4.5</v>
       </c>
       <c r="AQ26" t="n">
         <v>21</v>
       </c>
       <c r="AR26" t="n">
-        <v>32</v>
+        <v>4.5</v>
       </c>
       <c r="AS26" t="n">
         <v>4.3</v>
@@ -7076,13 +7076,13 @@
         <v>13</v>
       </c>
       <c r="AU26" t="n">
-        <v>10.5</v>
+        <v>9.4</v>
       </c>
       <c r="AV26" t="n">
         <v>13.5</v>
       </c>
       <c r="AW26" t="n">
-        <v>4.1</v>
+        <v>4.5</v>
       </c>
       <c r="AX26" t="n">
         <v>12.5</v>
@@ -7094,10 +7094,10 @@
         <v>11</v>
       </c>
       <c r="BA26" t="n">
-        <v>4.1</v>
+        <v>4.6</v>
       </c>
       <c r="BB26" t="n">
-        <v>18.5</v>
+        <v>15.5</v>
       </c>
       <c r="BC26" t="n">
         <v>12</v>
@@ -7106,10 +7106,10 @@
         <v>16</v>
       </c>
       <c r="BE26" t="n">
-        <v>4.2</v>
+        <v>4.4</v>
       </c>
       <c r="BF26" t="n">
-        <v>5.1</v>
+        <v>4.5</v>
       </c>
       <c r="BG26" t="n">
         <v>16</v>
@@ -7136,7 +7136,7 @@
         <v>5.5</v>
       </c>
       <c r="BO26" t="n">
-        <v>4.7</v>
+        <v>4.2</v>
       </c>
       <c r="BP26" t="n">
         <v>11.5</v>
@@ -7172,11 +7172,11 @@
         <v>11</v>
       </c>
       <c r="CA26" t="n">
-        <v>5.5</v>
+        <v>6.8</v>
       </c>
       <c r="CB26" t="inlineStr">
         <is>
-          <t>2026-06-11 15:58:00</t>
+          <t>2026-06-11 18:11:04</t>
         </is>
       </c>
     </row>
@@ -7207,19 +7207,19 @@
         </is>
       </c>
       <c r="F27" t="n">
-        <v>1.01</v>
+        <v>1.09</v>
       </c>
       <c r="G27" t="n">
         <v>1000</v>
       </c>
       <c r="H27" t="n">
-        <v>1.49</v>
+        <v>1.88</v>
       </c>
       <c r="I27" t="n">
         <v>1000</v>
       </c>
       <c r="J27" t="n">
-        <v>1.43</v>
+        <v>1.5</v>
       </c>
       <c r="K27" t="n">
         <v>3.25</v>
@@ -7261,7 +7261,7 @@
         <v>1.02</v>
       </c>
       <c r="X27" t="n">
-        <v>1000</v>
+        <v>950</v>
       </c>
       <c r="Y27" t="n">
         <v>1000</v>
@@ -7430,7 +7430,7 @@
       </c>
       <c r="CB27" t="inlineStr">
         <is>
-          <t>2026-06-11 15:58:00</t>
+          <t>2026-06-11 18:11:04</t>
         </is>
       </c>
     </row>
@@ -7461,16 +7461,16 @@
         </is>
       </c>
       <c r="F28" t="n">
-        <v>2.22</v>
+        <v>2.24</v>
       </c>
       <c r="G28" t="n">
-        <v>2.36</v>
+        <v>2.38</v>
       </c>
       <c r="H28" t="n">
         <v>3.6</v>
       </c>
       <c r="I28" t="n">
-        <v>3.95</v>
+        <v>3.9</v>
       </c>
       <c r="J28" t="n">
         <v>3.35</v>
@@ -7488,13 +7488,13 @@
         <v>3.05</v>
       </c>
       <c r="O28" t="n">
-        <v>1.44</v>
+        <v>1.43</v>
       </c>
       <c r="P28" t="n">
         <v>1.66</v>
       </c>
       <c r="Q28" t="n">
-        <v>2.26</v>
+        <v>2.28</v>
       </c>
       <c r="R28" t="n">
         <v>1.25</v>
@@ -7503,7 +7503,7 @@
         <v>4.6</v>
       </c>
       <c r="T28" t="n">
-        <v>1.94</v>
+        <v>1.95</v>
       </c>
       <c r="U28" t="n">
         <v>1.89</v>
@@ -7518,7 +7518,7 @@
         <v>12.5</v>
       </c>
       <c r="Y28" t="n">
-        <v>970</v>
+        <v>12.5</v>
       </c>
       <c r="Z28" t="n">
         <v>27</v>
@@ -7530,7 +7530,7 @@
         <v>8.6</v>
       </c>
       <c r="AC28" t="n">
-        <v>7.4</v>
+        <v>7.8</v>
       </c>
       <c r="AD28" t="n">
         <v>970</v>
@@ -7542,13 +7542,13 @@
         <v>970</v>
       </c>
       <c r="AG28" t="n">
-        <v>970</v>
+        <v>12</v>
       </c>
       <c r="AH28" t="n">
         <v>950</v>
       </c>
       <c r="AI28" t="n">
-        <v>75</v>
+        <v>70</v>
       </c>
       <c r="AJ28" t="n">
         <v>34</v>
@@ -7563,22 +7563,22 @@
         <v>160</v>
       </c>
       <c r="AN28" t="n">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="AO28" t="n">
         <v>75</v>
       </c>
       <c r="AP28" t="n">
-        <v>5.1</v>
+        <v>9.4</v>
       </c>
       <c r="AQ28" t="n">
-        <v>5.1</v>
+        <v>10</v>
       </c>
       <c r="AR28" t="n">
-        <v>6.6</v>
+        <v>6.2</v>
       </c>
       <c r="AS28" t="n">
-        <v>8</v>
+        <v>7.4</v>
       </c>
       <c r="AT28" t="n">
         <v>7</v>
@@ -7587,37 +7587,37 @@
         <v>6.4</v>
       </c>
       <c r="AV28" t="n">
-        <v>5.8</v>
+        <v>13</v>
       </c>
       <c r="AW28" t="n">
-        <v>7.6</v>
+        <v>7.2</v>
       </c>
       <c r="AX28" t="n">
-        <v>10.5</v>
+        <v>5.4</v>
       </c>
       <c r="AY28" t="n">
         <v>9.6</v>
       </c>
       <c r="AZ28" t="n">
+        <v>6</v>
+      </c>
+      <c r="BA28" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="BB28" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="BC28" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="BD28" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="BE28" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="BF28" t="n">
         <v>6.2</v>
-      </c>
-      <c r="BA28" t="n">
-        <v>7.8</v>
-      </c>
-      <c r="BB28" t="n">
-        <v>7</v>
-      </c>
-      <c r="BC28" t="n">
-        <v>21</v>
-      </c>
-      <c r="BD28" t="n">
-        <v>7.6</v>
-      </c>
-      <c r="BE28" t="n">
-        <v>8.4</v>
-      </c>
-      <c r="BF28" t="n">
-        <v>6.6</v>
       </c>
       <c r="BG28" t="n">
         <v>7.8</v>
@@ -7684,7 +7684,7 @@
       </c>
       <c r="CB28" t="inlineStr">
         <is>
-          <t>2026-06-11 15:58:00</t>
+          <t>2026-06-11 18:11:04</t>
         </is>
       </c>
     </row>
@@ -7742,19 +7742,19 @@
         <v>4.3</v>
       </c>
       <c r="O29" t="n">
-        <v>1.26</v>
+        <v>1.27</v>
       </c>
       <c r="P29" t="n">
         <v>2.12</v>
       </c>
       <c r="Q29" t="n">
-        <v>1.78</v>
+        <v>1.79</v>
       </c>
       <c r="R29" t="n">
-        <v>1.44</v>
+        <v>1.43</v>
       </c>
       <c r="S29" t="n">
-        <v>2.96</v>
+        <v>3</v>
       </c>
       <c r="T29" t="n">
         <v>1.71</v>
@@ -7772,13 +7772,13 @@
         <v>18.5</v>
       </c>
       <c r="Y29" t="n">
-        <v>17</v>
+        <v>17.5</v>
       </c>
       <c r="Z29" t="n">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="AA29" t="n">
-        <v>95</v>
+        <v>80</v>
       </c>
       <c r="AB29" t="n">
         <v>10.5</v>
@@ -7787,7 +7787,7 @@
         <v>9</v>
       </c>
       <c r="AD29" t="n">
-        <v>16.5</v>
+        <v>17</v>
       </c>
       <c r="AE29" t="n">
         <v>46</v>
@@ -7820,7 +7820,7 @@
         <v>12.5</v>
       </c>
       <c r="AO29" t="n">
-        <v>42</v>
+        <v>110</v>
       </c>
       <c r="AP29" t="n">
         <v>16</v>
@@ -7832,7 +7832,7 @@
         <v>18.5</v>
       </c>
       <c r="AS29" t="n">
-        <v>12</v>
+        <v>11.5</v>
       </c>
       <c r="AT29" t="n">
         <v>9.4</v>
@@ -7844,7 +7844,7 @@
         <v>14.5</v>
       </c>
       <c r="AW29" t="n">
-        <v>38</v>
+        <v>25</v>
       </c>
       <c r="AX29" t="n">
         <v>11.5</v>
@@ -7853,10 +7853,10 @@
         <v>9.4</v>
       </c>
       <c r="AZ29" t="n">
-        <v>15</v>
+        <v>15.5</v>
       </c>
       <c r="BA29" t="n">
-        <v>27</v>
+        <v>42</v>
       </c>
       <c r="BB29" t="n">
         <v>20</v>
@@ -7865,7 +7865,7 @@
         <v>17.5</v>
       </c>
       <c r="BD29" t="n">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="BE29" t="n">
         <v>12</v>
@@ -7874,13 +7874,13 @@
         <v>11</v>
       </c>
       <c r="BG29" t="n">
-        <v>34</v>
+        <v>24</v>
       </c>
       <c r="BH29" t="n">
         <v>3.75</v>
       </c>
       <c r="BI29" t="n">
-        <v>3.05</v>
+        <v>3</v>
       </c>
       <c r="BJ29" t="n">
         <v>9.199999999999999</v>
@@ -7938,7 +7938,7 @@
       </c>
       <c r="CB29" t="inlineStr">
         <is>
-          <t>2026-06-11 15:58:00</t>
+          <t>2026-06-11 18:11:04</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-06-12.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-06-12.xlsx
@@ -860,7 +860,7 @@
         <v>1.5</v>
       </c>
       <c r="G2" t="n">
-        <v>1.64</v>
+        <v>1.63</v>
       </c>
       <c r="H2" t="n">
         <v>7</v>
@@ -869,13 +869,13 @@
         <v>9.6</v>
       </c>
       <c r="J2" t="n">
-        <v>3.55</v>
+        <v>3.7</v>
       </c>
       <c r="K2" t="n">
-        <v>5.4</v>
+        <v>4.9</v>
       </c>
       <c r="L2" t="n">
-        <v>1.32</v>
+        <v>1.33</v>
       </c>
       <c r="M2" t="n">
         <v>1.06</v>
@@ -884,22 +884,22 @@
         <v>3.2</v>
       </c>
       <c r="O2" t="n">
-        <v>1.3</v>
+        <v>1.31</v>
       </c>
       <c r="P2" t="n">
         <v>1.89</v>
       </c>
       <c r="Q2" t="n">
-        <v>1.86</v>
+        <v>1.87</v>
       </c>
       <c r="R2" t="n">
         <v>1.34</v>
       </c>
       <c r="S2" t="n">
-        <v>3</v>
+        <v>3.2</v>
       </c>
       <c r="T2" t="n">
-        <v>1.94</v>
+        <v>1.95</v>
       </c>
       <c r="U2" t="n">
         <v>1.81</v>
@@ -923,10 +923,10 @@
         <v>1000</v>
       </c>
       <c r="AB2" t="n">
-        <v>970</v>
+        <v>500</v>
       </c>
       <c r="AC2" t="n">
-        <v>970</v>
+        <v>42</v>
       </c>
       <c r="AD2" t="n">
         <v>950</v>
@@ -935,10 +935,10 @@
         <v>1000</v>
       </c>
       <c r="AF2" t="n">
-        <v>970</v>
+        <v>40</v>
       </c>
       <c r="AG2" t="n">
-        <v>970</v>
+        <v>500</v>
       </c>
       <c r="AH2" t="n">
         <v>950</v>
@@ -947,140 +947,140 @@
         <v>1000</v>
       </c>
       <c r="AJ2" t="n">
+        <v>900</v>
+      </c>
+      <c r="AK2" t="n">
         <v>970</v>
       </c>
-      <c r="AK2" t="n">
-        <v>21</v>
-      </c>
       <c r="AL2" t="n">
-        <v>48</v>
+        <v>500</v>
       </c>
       <c r="AM2" t="n">
         <v>1000</v>
       </c>
       <c r="AN2" t="n">
-        <v>970</v>
+        <v>29</v>
       </c>
       <c r="AO2" t="n">
         <v>1000</v>
       </c>
       <c r="AP2" t="n">
-        <v>3.55</v>
+        <v>3.85</v>
       </c>
       <c r="AQ2" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="AR2" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="AS2" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="AT2" t="n">
+        <v>3.45</v>
+      </c>
+      <c r="AU2" t="n">
         <v>3.75</v>
       </c>
-      <c r="AR2" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="AS2" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="AT2" t="n">
-        <v>2.98</v>
-      </c>
-      <c r="AU2" t="n">
-        <v>3.2</v>
-      </c>
       <c r="AV2" t="n">
-        <v>3.85</v>
+        <v>4.2</v>
       </c>
       <c r="AW2" t="n">
         <v>4.2</v>
       </c>
       <c r="AX2" t="n">
-        <v>3.1</v>
+        <v>3.75</v>
       </c>
       <c r="AY2" t="n">
-        <v>3.2</v>
+        <v>3.8</v>
       </c>
       <c r="AZ2" t="n">
-        <v>3.8</v>
+        <v>3.9</v>
       </c>
       <c r="BA2" t="n">
         <v>4.2</v>
       </c>
       <c r="BB2" t="n">
-        <v>3.5</v>
+        <v>4.2</v>
       </c>
       <c r="BC2" t="n">
-        <v>3.6</v>
+        <v>3.9</v>
       </c>
       <c r="BD2" t="n">
-        <v>4</v>
+        <v>4.1</v>
       </c>
       <c r="BE2" t="n">
+        <v>2.84</v>
+      </c>
+      <c r="BF2" t="n">
+        <v>3.85</v>
+      </c>
+      <c r="BG2" t="n">
         <v>4.2</v>
       </c>
-      <c r="BF2" t="n">
-        <v>3.15</v>
-      </c>
-      <c r="BG2" t="n">
-        <v>4.3</v>
-      </c>
       <c r="BH2" t="n">
-        <v>8.4</v>
+        <v>1000</v>
       </c>
       <c r="BI2" t="n">
-        <v>2.8</v>
+        <v>2.88</v>
       </c>
       <c r="BJ2" t="n">
         <v>1000</v>
       </c>
       <c r="BK2" t="n">
-        <v>1.39</v>
+        <v>1.21</v>
       </c>
       <c r="BL2" t="n">
         <v>1000</v>
       </c>
       <c r="BM2" t="n">
-        <v>1.04</v>
+        <v>1.17</v>
       </c>
       <c r="BN2" t="n">
         <v>1000</v>
       </c>
       <c r="BO2" t="n">
-        <v>2.82</v>
+        <v>2.84</v>
       </c>
       <c r="BP2" t="n">
         <v>1000</v>
       </c>
       <c r="BQ2" t="n">
-        <v>1.37</v>
+        <v>1.34</v>
       </c>
       <c r="BR2" t="n">
         <v>1000</v>
       </c>
       <c r="BS2" t="n">
-        <v>1.22</v>
+        <v>1.18</v>
       </c>
       <c r="BT2" t="n">
         <v>1000</v>
       </c>
       <c r="BU2" t="n">
-        <v>1.38</v>
+        <v>1.2</v>
       </c>
       <c r="BV2" t="n">
         <v>1000</v>
       </c>
       <c r="BW2" t="n">
-        <v>1.04</v>
+        <v>1.18</v>
       </c>
       <c r="BX2" t="n">
         <v>1000</v>
       </c>
       <c r="BY2" t="n">
-        <v>1.22</v>
+        <v>1.16</v>
       </c>
       <c r="BZ2" t="n">
         <v>1000</v>
       </c>
       <c r="CA2" t="n">
-        <v>1.24</v>
+        <v>1.13</v>
       </c>
       <c r="CB2" t="inlineStr">
         <is>
-          <t>2026-06-11 18:11:04</t>
+          <t>2026-06-11 20:24:12</t>
         </is>
       </c>
     </row>
@@ -1126,7 +1126,7 @@
         <v>3.7</v>
       </c>
       <c r="K3" t="n">
-        <v>4</v>
+        <v>4.1</v>
       </c>
       <c r="L3" t="n">
         <v>1.01</v>
@@ -1135,28 +1135,28 @@
         <v>1.05</v>
       </c>
       <c r="N3" t="n">
-        <v>4.3</v>
+        <v>4.5</v>
       </c>
       <c r="O3" t="n">
         <v>1.25</v>
       </c>
       <c r="P3" t="n">
-        <v>2.14</v>
+        <v>2.22</v>
       </c>
       <c r="Q3" t="n">
-        <v>1.74</v>
+        <v>1.7</v>
       </c>
       <c r="R3" t="n">
-        <v>1.45</v>
+        <v>1.48</v>
       </c>
       <c r="S3" t="n">
-        <v>2.84</v>
+        <v>2.8</v>
       </c>
       <c r="T3" t="n">
-        <v>1.63</v>
+        <v>1.61</v>
       </c>
       <c r="U3" t="n">
-        <v>2.36</v>
+        <v>2.4</v>
       </c>
       <c r="V3" t="n">
         <v>1.53</v>
@@ -1177,16 +1177,16 @@
         <v>50</v>
       </c>
       <c r="AB3" t="n">
-        <v>13.5</v>
+        <v>14</v>
       </c>
       <c r="AC3" t="n">
-        <v>8.800000000000001</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AD3" t="n">
         <v>15.5</v>
       </c>
       <c r="AE3" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="AF3" t="n">
         <v>24</v>
@@ -1195,7 +1195,7 @@
         <v>15</v>
       </c>
       <c r="AH3" t="n">
-        <v>16</v>
+        <v>15.5</v>
       </c>
       <c r="AI3" t="n">
         <v>44</v>
@@ -1210,13 +1210,13 @@
         <v>44</v>
       </c>
       <c r="AM3" t="n">
-        <v>90</v>
+        <v>500</v>
       </c>
       <c r="AN3" t="n">
         <v>23</v>
       </c>
       <c r="AO3" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="AP3" t="n">
         <v>13.5</v>
@@ -1228,13 +1228,13 @@
         <v>14.5</v>
       </c>
       <c r="AS3" t="n">
-        <v>5.7</v>
+        <v>5.8</v>
       </c>
       <c r="AT3" t="n">
         <v>9.800000000000001</v>
       </c>
       <c r="AU3" t="n">
-        <v>6.4</v>
+        <v>7.8</v>
       </c>
       <c r="AV3" t="n">
         <v>9.4</v>
@@ -1252,16 +1252,16 @@
         <v>11.5</v>
       </c>
       <c r="BA3" t="n">
-        <v>5.7</v>
+        <v>18</v>
       </c>
       <c r="BB3" t="n">
-        <v>5.7</v>
+        <v>18</v>
       </c>
       <c r="BC3" t="n">
         <v>19.5</v>
       </c>
       <c r="BD3" t="n">
-        <v>5.8</v>
+        <v>18</v>
       </c>
       <c r="BE3" t="n">
         <v>5.6</v>
@@ -1334,7 +1334,7 @@
       </c>
       <c r="CB3" t="inlineStr">
         <is>
-          <t>2026-06-11 18:11:04</t>
+          <t>2026-06-11 20:24:12</t>
         </is>
       </c>
     </row>
@@ -1365,22 +1365,22 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>2.86</v>
+        <v>2.9</v>
       </c>
       <c r="G4" t="n">
         <v>3.35</v>
       </c>
       <c r="H4" t="n">
-        <v>3</v>
+        <v>2.92</v>
       </c>
       <c r="I4" t="n">
-        <v>3.4</v>
+        <v>3.45</v>
       </c>
       <c r="J4" t="n">
-        <v>2.52</v>
+        <v>2.56</v>
       </c>
       <c r="K4" t="n">
-        <v>3</v>
+        <v>3.05</v>
       </c>
       <c r="L4" t="n">
         <v>1.01</v>
@@ -1389,7 +1389,7 @@
         <v>1.15</v>
       </c>
       <c r="N4" t="n">
-        <v>2.18</v>
+        <v>2.26</v>
       </c>
       <c r="O4" t="n">
         <v>1.61</v>
@@ -1401,46 +1401,46 @@
         <v>2.88</v>
       </c>
       <c r="R4" t="n">
-        <v>1.18</v>
+        <v>1.17</v>
       </c>
       <c r="S4" t="n">
         <v>6</v>
       </c>
       <c r="T4" t="n">
-        <v>2.16</v>
+        <v>2.14</v>
       </c>
       <c r="U4" t="n">
-        <v>1.66</v>
+        <v>1.68</v>
       </c>
       <c r="V4" t="n">
-        <v>1.42</v>
+        <v>1.4</v>
       </c>
       <c r="W4" t="n">
         <v>1.42</v>
       </c>
       <c r="X4" t="n">
-        <v>90</v>
+        <v>16.5</v>
       </c>
       <c r="Y4" t="n">
         <v>970</v>
       </c>
       <c r="Z4" t="n">
-        <v>23</v>
+        <v>500</v>
       </c>
       <c r="AA4" t="n">
-        <v>75</v>
+        <v>500</v>
       </c>
       <c r="AB4" t="n">
-        <v>970</v>
+        <v>16.5</v>
       </c>
       <c r="AC4" t="n">
-        <v>970</v>
+        <v>15</v>
       </c>
       <c r="AD4" t="n">
         <v>970</v>
       </c>
       <c r="AE4" t="n">
-        <v>60</v>
+        <v>500</v>
       </c>
       <c r="AF4" t="n">
         <v>970</v>
@@ -1449,28 +1449,28 @@
         <v>970</v>
       </c>
       <c r="AH4" t="n">
-        <v>28</v>
+        <v>500</v>
       </c>
       <c r="AI4" t="n">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AJ4" t="n">
-        <v>65</v>
+        <v>500</v>
       </c>
       <c r="AK4" t="n">
-        <v>55</v>
+        <v>500</v>
       </c>
       <c r="AL4" t="n">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AM4" t="n">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AN4" t="n">
-        <v>75</v>
+        <v>500</v>
       </c>
       <c r="AO4" t="n">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AP4" t="n">
         <v>6</v>
@@ -1479,52 +1479,52 @@
         <v>6.4</v>
       </c>
       <c r="AR4" t="n">
-        <v>2.26</v>
+        <v>5.9</v>
       </c>
       <c r="AS4" t="n">
-        <v>1.9</v>
+        <v>2.92</v>
       </c>
       <c r="AT4" t="n">
-        <v>3.95</v>
+        <v>4.3</v>
       </c>
       <c r="AU4" t="n">
         <v>5.5</v>
       </c>
       <c r="AV4" t="n">
-        <v>5.2</v>
+        <v>8.4</v>
       </c>
       <c r="AW4" t="n">
-        <v>1.89</v>
+        <v>4.9</v>
       </c>
       <c r="AX4" t="n">
-        <v>3.3</v>
+        <v>6.4</v>
       </c>
       <c r="AY4" t="n">
-        <v>3.2</v>
+        <v>5.9</v>
       </c>
       <c r="AZ4" t="n">
-        <v>5.9</v>
+        <v>6.4</v>
       </c>
       <c r="BA4" t="n">
-        <v>1.91</v>
+        <v>2.98</v>
       </c>
       <c r="BB4" t="n">
-        <v>1.89</v>
+        <v>2.9</v>
       </c>
       <c r="BC4" t="n">
-        <v>2.42</v>
+        <v>4.8</v>
       </c>
       <c r="BD4" t="n">
-        <v>1.91</v>
+        <v>2.92</v>
       </c>
       <c r="BE4" t="n">
-        <v>1.93</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BF4" t="n">
-        <v>1.9</v>
+        <v>7.6</v>
       </c>
       <c r="BG4" t="n">
-        <v>1.91</v>
+        <v>7.6</v>
       </c>
       <c r="BH4" t="n">
         <v>2.94</v>
@@ -1588,7 +1588,7 @@
       </c>
       <c r="CB4" t="inlineStr">
         <is>
-          <t>2026-06-11 18:11:04</t>
+          <t>2026-06-11 20:24:12</t>
         </is>
       </c>
     </row>
@@ -1619,7 +1619,7 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>2.18</v>
+        <v>2.24</v>
       </c>
       <c r="G5" t="n">
         <v>2.4</v>
@@ -1631,10 +1631,10 @@
         <v>4.4</v>
       </c>
       <c r="J5" t="n">
-        <v>2.92</v>
+        <v>2.96</v>
       </c>
       <c r="K5" t="n">
-        <v>3.2</v>
+        <v>3.15</v>
       </c>
       <c r="L5" t="n">
         <v>1.48</v>
@@ -1673,112 +1673,112 @@
         <v>1.72</v>
       </c>
       <c r="X5" t="n">
-        <v>9.4</v>
+        <v>8.4</v>
       </c>
       <c r="Y5" t="n">
-        <v>12.5</v>
+        <v>11</v>
       </c>
       <c r="Z5" t="n">
         <v>34</v>
       </c>
       <c r="AA5" t="n">
-        <v>130</v>
+        <v>900</v>
       </c>
       <c r="AB5" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AC5" t="n">
-        <v>8.199999999999999</v>
+        <v>7.4</v>
       </c>
       <c r="AD5" t="n">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="AE5" t="n">
-        <v>90</v>
+        <v>500</v>
       </c>
       <c r="AF5" t="n">
-        <v>14.5</v>
+        <v>13</v>
       </c>
       <c r="AG5" t="n">
-        <v>14</v>
+        <v>12.5</v>
       </c>
       <c r="AH5" t="n">
-        <v>29</v>
+        <v>80</v>
       </c>
       <c r="AI5" t="n">
-        <v>120</v>
+        <v>540</v>
       </c>
       <c r="AJ5" t="n">
         <v>38</v>
       </c>
       <c r="AK5" t="n">
-        <v>40</v>
+        <v>110</v>
       </c>
       <c r="AL5" t="n">
-        <v>80</v>
+        <v>170</v>
       </c>
       <c r="AM5" t="n">
-        <v>250</v>
+        <v>500</v>
       </c>
       <c r="AN5" t="n">
         <v>40</v>
       </c>
       <c r="AO5" t="n">
-        <v>140</v>
+        <v>500</v>
       </c>
       <c r="AP5" t="n">
-        <v>3.35</v>
+        <v>4.5</v>
       </c>
       <c r="AQ5" t="n">
-        <v>3.7</v>
+        <v>5.6</v>
       </c>
       <c r="AR5" t="n">
-        <v>4.5</v>
+        <v>7.6</v>
       </c>
       <c r="AS5" t="n">
-        <v>5</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AT5" t="n">
-        <v>3.2</v>
+        <v>4.1</v>
       </c>
       <c r="AU5" t="n">
-        <v>3.2</v>
+        <v>4.2</v>
       </c>
       <c r="AV5" t="n">
-        <v>4.2</v>
+        <v>6.4</v>
       </c>
       <c r="AW5" t="n">
-        <v>4.9</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AX5" t="n">
-        <v>3.85</v>
+        <v>6.2</v>
       </c>
       <c r="AY5" t="n">
-        <v>3.8</v>
+        <v>7</v>
       </c>
       <c r="AZ5" t="n">
-        <v>4.4</v>
+        <v>7.2</v>
       </c>
       <c r="BA5" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="BB5" t="n">
-        <v>4.6</v>
+        <v>7.8</v>
       </c>
       <c r="BC5" t="n">
-        <v>4.6</v>
+        <v>7.6</v>
       </c>
       <c r="BD5" t="n">
-        <v>4.9</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BE5" t="n">
-        <v>5.1</v>
+        <v>9.4</v>
       </c>
       <c r="BF5" t="n">
-        <v>4.6</v>
+        <v>7.8</v>
       </c>
       <c r="BG5" t="n">
-        <v>5</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BH5" t="n">
         <v>1000</v>
@@ -1842,7 +1842,7 @@
       </c>
       <c r="CB5" t="inlineStr">
         <is>
-          <t>2026-06-11 18:11:04</t>
+          <t>2026-06-11 20:24:12</t>
         </is>
       </c>
     </row>
@@ -1873,19 +1873,19 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>3.35</v>
+        <v>3.3</v>
       </c>
       <c r="G6" t="n">
-        <v>3.75</v>
+        <v>3.7</v>
       </c>
       <c r="H6" t="n">
         <v>2.16</v>
       </c>
       <c r="I6" t="n">
-        <v>2.34</v>
+        <v>2.36</v>
       </c>
       <c r="J6" t="n">
-        <v>3.45</v>
+        <v>3.5</v>
       </c>
       <c r="K6" t="n">
         <v>3.85</v>
@@ -1897,19 +1897,19 @@
         <v>1.06</v>
       </c>
       <c r="N6" t="n">
-        <v>3.75</v>
+        <v>3.9</v>
       </c>
       <c r="O6" t="n">
         <v>1.3</v>
       </c>
       <c r="P6" t="n">
-        <v>1.96</v>
+        <v>1.99</v>
       </c>
       <c r="Q6" t="n">
-        <v>1.9</v>
+        <v>1.85</v>
       </c>
       <c r="R6" t="n">
-        <v>1.37</v>
+        <v>1.38</v>
       </c>
       <c r="S6" t="n">
         <v>3.25</v>
@@ -1918,13 +1918,13 @@
         <v>1.74</v>
       </c>
       <c r="U6" t="n">
-        <v>2.16</v>
+        <v>2.2</v>
       </c>
       <c r="V6" t="n">
-        <v>1.74</v>
+        <v>1.73</v>
       </c>
       <c r="W6" t="n">
-        <v>1.36</v>
+        <v>1.37</v>
       </c>
       <c r="X6" t="n">
         <v>18.5</v>
@@ -1936,7 +1936,7 @@
         <v>15</v>
       </c>
       <c r="AA6" t="n">
-        <v>30</v>
+        <v>65</v>
       </c>
       <c r="AB6" t="n">
         <v>14</v>
@@ -1951,22 +1951,22 @@
         <v>29</v>
       </c>
       <c r="AF6" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="AG6" t="n">
         <v>15</v>
       </c>
       <c r="AH6" t="n">
-        <v>17.5</v>
+        <v>17</v>
       </c>
       <c r="AI6" t="n">
         <v>44</v>
       </c>
       <c r="AJ6" t="n">
-        <v>85</v>
+        <v>440</v>
       </c>
       <c r="AK6" t="n">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="AL6" t="n">
         <v>60</v>
@@ -1975,10 +1975,10 @@
         <v>110</v>
       </c>
       <c r="AN6" t="n">
-        <v>48</v>
+        <v>44</v>
       </c>
       <c r="AO6" t="n">
-        <v>17.5</v>
+        <v>17</v>
       </c>
       <c r="AP6" t="n">
         <v>11</v>
@@ -2014,22 +2014,22 @@
         <v>12.5</v>
       </c>
       <c r="BA6" t="n">
-        <v>6.2</v>
+        <v>18</v>
       </c>
       <c r="BB6" t="n">
-        <v>6.4</v>
+        <v>6.8</v>
       </c>
       <c r="BC6" t="n">
-        <v>6.2</v>
+        <v>7</v>
       </c>
       <c r="BD6" t="n">
-        <v>6.2</v>
+        <v>6.8</v>
       </c>
       <c r="BE6" t="n">
-        <v>6.4</v>
+        <v>7</v>
       </c>
       <c r="BF6" t="n">
-        <v>6.2</v>
+        <v>7.4</v>
       </c>
       <c r="BG6" t="n">
         <v>12.5</v>
@@ -2096,7 +2096,7 @@
       </c>
       <c r="CB6" t="inlineStr">
         <is>
-          <t>2026-06-11 18:11:04</t>
+          <t>2026-06-11 20:24:12</t>
         </is>
       </c>
     </row>
@@ -2133,7 +2133,7 @@
         <v>1.8</v>
       </c>
       <c r="H7" t="n">
-        <v>4.6</v>
+        <v>4.7</v>
       </c>
       <c r="I7" t="n">
         <v>6.4</v>
@@ -2187,10 +2187,10 @@
         <v>22</v>
       </c>
       <c r="Z7" t="n">
-        <v>50</v>
+        <v>500</v>
       </c>
       <c r="AA7" t="n">
-        <v>180</v>
+        <v>700</v>
       </c>
       <c r="AB7" t="n">
         <v>10</v>
@@ -2202,7 +2202,7 @@
         <v>24</v>
       </c>
       <c r="AE7" t="n">
-        <v>80</v>
+        <v>700</v>
       </c>
       <c r="AF7" t="n">
         <v>11.5</v>
@@ -2214,7 +2214,7 @@
         <v>22</v>
       </c>
       <c r="AI7" t="n">
-        <v>80</v>
+        <v>700</v>
       </c>
       <c r="AJ7" t="n">
         <v>18.5</v>
@@ -2223,16 +2223,16 @@
         <v>18.5</v>
       </c>
       <c r="AL7" t="n">
-        <v>36</v>
+        <v>80</v>
       </c>
       <c r="AM7" t="n">
-        <v>130</v>
+        <v>580</v>
       </c>
       <c r="AN7" t="n">
         <v>10</v>
       </c>
       <c r="AO7" t="n">
-        <v>100</v>
+        <v>700</v>
       </c>
       <c r="AP7" t="n">
         <v>5.2</v>
@@ -2350,7 +2350,7 @@
       </c>
       <c r="CB7" t="inlineStr">
         <is>
-          <t>2026-06-11 18:11:04</t>
+          <t>2026-06-11 20:24:12</t>
         </is>
       </c>
     </row>
@@ -2381,7 +2381,7 @@
         </is>
       </c>
       <c r="F8" t="n">
-        <v>1.61</v>
+        <v>1.62</v>
       </c>
       <c r="G8" t="n">
         <v>1.75</v>
@@ -2393,7 +2393,7 @@
         <v>6.8</v>
       </c>
       <c r="J8" t="n">
-        <v>3.8</v>
+        <v>3.75</v>
       </c>
       <c r="K8" t="n">
         <v>4.4</v>
@@ -2423,7 +2423,7 @@
         <v>3.35</v>
       </c>
       <c r="T8" t="n">
-        <v>1.91</v>
+        <v>1.9</v>
       </c>
       <c r="U8" t="n">
         <v>1.92</v>
@@ -2438,16 +2438,16 @@
         <v>18</v>
       </c>
       <c r="Y8" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="Z8" t="n">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="AA8" t="n">
-        <v>210</v>
+        <v>700</v>
       </c>
       <c r="AB8" t="n">
-        <v>8.6</v>
+        <v>8.4</v>
       </c>
       <c r="AC8" t="n">
         <v>11</v>
@@ -2480,7 +2480,7 @@
         <v>40</v>
       </c>
       <c r="AM8" t="n">
-        <v>160</v>
+        <v>580</v>
       </c>
       <c r="AN8" t="n">
         <v>11</v>
@@ -2495,10 +2495,10 @@
         <v>16.5</v>
       </c>
       <c r="AR8" t="n">
-        <v>5.5</v>
+        <v>5.6</v>
       </c>
       <c r="AS8" t="n">
-        <v>5.7</v>
+        <v>6</v>
       </c>
       <c r="AT8" t="n">
         <v>7</v>
@@ -2510,7 +2510,7 @@
         <v>17</v>
       </c>
       <c r="AW8" t="n">
-        <v>5.6</v>
+        <v>5.8</v>
       </c>
       <c r="AX8" t="n">
         <v>7.4</v>
@@ -2522,7 +2522,7 @@
         <v>15.5</v>
       </c>
       <c r="BA8" t="n">
-        <v>5.6</v>
+        <v>5.8</v>
       </c>
       <c r="BB8" t="n">
         <v>12</v>
@@ -2531,16 +2531,16 @@
         <v>13</v>
       </c>
       <c r="BD8" t="n">
-        <v>5.3</v>
+        <v>5.5</v>
       </c>
       <c r="BE8" t="n">
-        <v>5.7</v>
+        <v>5.9</v>
       </c>
       <c r="BF8" t="n">
         <v>9</v>
       </c>
       <c r="BG8" t="n">
-        <v>5.7</v>
+        <v>5.9</v>
       </c>
       <c r="BH8" t="n">
         <v>1000</v>
@@ -2604,7 +2604,7 @@
       </c>
       <c r="CB8" t="inlineStr">
         <is>
-          <t>2026-06-11 18:11:04</t>
+          <t>2026-06-11 20:24:12</t>
         </is>
       </c>
     </row>
@@ -2635,16 +2635,16 @@
         </is>
       </c>
       <c r="F9" t="n">
-        <v>4.4</v>
+        <v>4.5</v>
       </c>
       <c r="G9" t="n">
         <v>5.2</v>
       </c>
       <c r="H9" t="n">
-        <v>1.69</v>
+        <v>1.71</v>
       </c>
       <c r="I9" t="n">
-        <v>1.85</v>
+        <v>1.82</v>
       </c>
       <c r="J9" t="n">
         <v>4.1</v>
@@ -2659,7 +2659,7 @@
         <v>1.02</v>
       </c>
       <c r="N9" t="n">
-        <v>5.6</v>
+        <v>5.5</v>
       </c>
       <c r="O9" t="n">
         <v>1.18</v>
@@ -2674,7 +2674,7 @@
         <v>1.6</v>
       </c>
       <c r="S9" t="n">
-        <v>2.34</v>
+        <v>2.32</v>
       </c>
       <c r="T9" t="n">
         <v>1.58</v>
@@ -2683,118 +2683,118 @@
         <v>2.42</v>
       </c>
       <c r="V9" t="n">
-        <v>2.16</v>
+        <v>2.2</v>
       </c>
       <c r="W9" t="n">
         <v>1.23</v>
       </c>
       <c r="X9" t="n">
-        <v>30</v>
+        <v>500</v>
       </c>
       <c r="Y9" t="n">
-        <v>15</v>
+        <v>18.5</v>
       </c>
       <c r="Z9" t="n">
-        <v>15.5</v>
+        <v>24</v>
       </c>
       <c r="AA9" t="n">
-        <v>22</v>
+        <v>34</v>
       </c>
       <c r="AB9" t="n">
-        <v>28</v>
+        <v>50</v>
       </c>
       <c r="AC9" t="n">
-        <v>12.5</v>
+        <v>11.5</v>
       </c>
       <c r="AD9" t="n">
-        <v>12.5</v>
+        <v>11.5</v>
       </c>
       <c r="AE9" t="n">
-        <v>970</v>
+        <v>29</v>
       </c>
       <c r="AF9" t="n">
-        <v>48</v>
+        <v>500</v>
       </c>
       <c r="AG9" t="n">
-        <v>23</v>
+        <v>38</v>
       </c>
       <c r="AH9" t="n">
-        <v>19.5</v>
+        <v>29</v>
       </c>
       <c r="AI9" t="n">
-        <v>32</v>
+        <v>500</v>
       </c>
       <c r="AJ9" t="n">
-        <v>110</v>
+        <v>500</v>
       </c>
       <c r="AK9" t="n">
-        <v>60</v>
+        <v>500</v>
       </c>
       <c r="AL9" t="n">
-        <v>55</v>
+        <v>500</v>
       </c>
       <c r="AM9" t="n">
-        <v>75</v>
+        <v>580</v>
       </c>
       <c r="AN9" t="n">
-        <v>46</v>
+        <v>500</v>
       </c>
       <c r="AO9" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="AP9" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="AQ9" t="n">
+        <v>11</v>
+      </c>
+      <c r="AR9" t="n">
+        <v>11</v>
+      </c>
+      <c r="AS9" t="n">
+        <v>9</v>
+      </c>
+      <c r="AT9" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="AU9" t="n">
+        <v>9</v>
+      </c>
+      <c r="AV9" t="n">
+        <v>9</v>
+      </c>
+      <c r="AW9" t="n">
         <v>8.4</v>
       </c>
-      <c r="AP9" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="AQ9" t="n">
-        <v>10</v>
-      </c>
-      <c r="AR9" t="n">
-        <v>10</v>
-      </c>
-      <c r="AS9" t="n">
-        <v>14.5</v>
-      </c>
-      <c r="AT9" t="n">
-        <v>18</v>
-      </c>
-      <c r="AU9" t="n">
-        <v>8.199999999999999</v>
-      </c>
-      <c r="AV9" t="n">
-        <v>8.199999999999999</v>
-      </c>
-      <c r="AW9" t="n">
-        <v>12.5</v>
-      </c>
       <c r="AX9" t="n">
-        <v>1.01</v>
+        <v>7.2</v>
       </c>
       <c r="AY9" t="n">
-        <v>14.5</v>
+        <v>16</v>
       </c>
       <c r="AZ9" t="n">
-        <v>12.5</v>
+        <v>14</v>
       </c>
       <c r="BA9" t="n">
-        <v>1.01</v>
+        <v>6.6</v>
       </c>
       <c r="BB9" t="n">
-        <v>1.01</v>
+        <v>8</v>
       </c>
       <c r="BC9" t="n">
-        <v>1.01</v>
+        <v>7.6</v>
       </c>
       <c r="BD9" t="n">
-        <v>1.01</v>
+        <v>7.4</v>
       </c>
       <c r="BE9" t="n">
-        <v>1.01</v>
+        <v>7.8</v>
       </c>
       <c r="BF9" t="n">
-        <v>1.01</v>
+        <v>8.4</v>
       </c>
       <c r="BG9" t="n">
-        <v>5.7</v>
+        <v>6.2</v>
       </c>
       <c r="BH9" t="n">
         <v>5.1</v>
@@ -2858,7 +2858,7 @@
       </c>
       <c r="CB9" t="inlineStr">
         <is>
-          <t>2026-06-11 18:11:04</t>
+          <t>2026-06-11 20:24:12</t>
         </is>
       </c>
     </row>
@@ -2895,7 +2895,7 @@
         <v>1.69</v>
       </c>
       <c r="H10" t="n">
-        <v>5.2</v>
+        <v>5.3</v>
       </c>
       <c r="I10" t="n">
         <v>6.4</v>
@@ -2919,7 +2919,7 @@
         <v>1.18</v>
       </c>
       <c r="P10" t="n">
-        <v>2.46</v>
+        <v>2.48</v>
       </c>
       <c r="Q10" t="n">
         <v>1.54</v>
@@ -2943,58 +2943,58 @@
         <v>2.46</v>
       </c>
       <c r="X10" t="n">
-        <v>32</v>
+        <v>70</v>
       </c>
       <c r="Y10" t="n">
-        <v>950</v>
+        <v>500</v>
       </c>
       <c r="Z10" t="n">
-        <v>55</v>
+        <v>500</v>
       </c>
       <c r="AA10" t="n">
-        <v>160</v>
+        <v>700</v>
       </c>
       <c r="AB10" t="n">
-        <v>13</v>
+        <v>12.5</v>
       </c>
       <c r="AC10" t="n">
         <v>12</v>
       </c>
       <c r="AD10" t="n">
-        <v>950</v>
+        <v>38</v>
       </c>
       <c r="AE10" t="n">
-        <v>70</v>
+        <v>700</v>
       </c>
       <c r="AF10" t="n">
-        <v>13</v>
+        <v>12.5</v>
       </c>
       <c r="AG10" t="n">
         <v>11</v>
       </c>
       <c r="AH10" t="n">
-        <v>970</v>
+        <v>24</v>
       </c>
       <c r="AI10" t="n">
-        <v>60</v>
+        <v>700</v>
       </c>
       <c r="AJ10" t="n">
-        <v>970</v>
+        <v>17</v>
       </c>
       <c r="AK10" t="n">
         <v>16.5</v>
       </c>
       <c r="AL10" t="n">
-        <v>29</v>
+        <v>48</v>
       </c>
       <c r="AM10" t="n">
-        <v>80</v>
+        <v>580</v>
       </c>
       <c r="AN10" t="n">
         <v>6.8</v>
       </c>
       <c r="AO10" t="n">
-        <v>60</v>
+        <v>700</v>
       </c>
       <c r="AP10" t="n">
         <v>21</v>
@@ -3003,10 +3003,10 @@
         <v>21</v>
       </c>
       <c r="AR10" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AS10" t="n">
-        <v>7.6</v>
+        <v>8.4</v>
       </c>
       <c r="AT10" t="n">
         <v>10</v>
@@ -3015,10 +3015,10 @@
         <v>9.4</v>
       </c>
       <c r="AV10" t="n">
-        <v>6.6</v>
+        <v>11</v>
       </c>
       <c r="AW10" t="n">
-        <v>7.2</v>
+        <v>7.8</v>
       </c>
       <c r="AX10" t="n">
         <v>10</v>
@@ -3030,7 +3030,7 @@
         <v>15</v>
       </c>
       <c r="BA10" t="n">
-        <v>7</v>
+        <v>7.8</v>
       </c>
       <c r="BB10" t="n">
         <v>14</v>
@@ -3039,16 +3039,16 @@
         <v>13</v>
       </c>
       <c r="BD10" t="n">
-        <v>7</v>
+        <v>13</v>
       </c>
       <c r="BE10" t="n">
-        <v>7.2</v>
+        <v>8</v>
       </c>
       <c r="BF10" t="n">
         <v>5.4</v>
       </c>
       <c r="BG10" t="n">
-        <v>7</v>
+        <v>7.8</v>
       </c>
       <c r="BH10" t="n">
         <v>4.7</v>
@@ -3112,7 +3112,7 @@
       </c>
       <c r="CB10" t="inlineStr">
         <is>
-          <t>2026-06-11 18:11:04</t>
+          <t>2026-06-11 20:24:12</t>
         </is>
       </c>
     </row>
@@ -3155,10 +3155,10 @@
         <v>4.7</v>
       </c>
       <c r="J11" t="n">
-        <v>2.94</v>
+        <v>2.9</v>
       </c>
       <c r="K11" t="n">
-        <v>3.3</v>
+        <v>3.15</v>
       </c>
       <c r="L11" t="n">
         <v>1.59</v>
@@ -3170,7 +3170,7 @@
         <v>2.5</v>
       </c>
       <c r="O11" t="n">
-        <v>1.56</v>
+        <v>1.57</v>
       </c>
       <c r="P11" t="n">
         <v>1.5</v>
@@ -3182,16 +3182,16 @@
         <v>1.18</v>
       </c>
       <c r="S11" t="n">
-        <v>5.7</v>
+        <v>5.8</v>
       </c>
       <c r="T11" t="n">
-        <v>2.16</v>
+        <v>2.18</v>
       </c>
       <c r="U11" t="n">
         <v>1.72</v>
       </c>
       <c r="V11" t="n">
-        <v>1.28</v>
+        <v>1.27</v>
       </c>
       <c r="W11" t="n">
         <v>1.75</v>
@@ -3203,10 +3203,10 @@
         <v>13.5</v>
       </c>
       <c r="Z11" t="n">
-        <v>36</v>
+        <v>32</v>
       </c>
       <c r="AA11" t="n">
-        <v>130</v>
+        <v>900</v>
       </c>
       <c r="AB11" t="n">
         <v>8</v>
@@ -3218,7 +3218,7 @@
         <v>23</v>
       </c>
       <c r="AE11" t="n">
-        <v>95</v>
+        <v>210</v>
       </c>
       <c r="AF11" t="n">
         <v>15</v>
@@ -3230,37 +3230,37 @@
         <v>29</v>
       </c>
       <c r="AI11" t="n">
-        <v>130</v>
+        <v>540</v>
       </c>
       <c r="AJ11" t="n">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="AK11" t="n">
-        <v>38</v>
+        <v>34</v>
       </c>
       <c r="AL11" t="n">
-        <v>80</v>
+        <v>460</v>
       </c>
       <c r="AM11" t="n">
-        <v>250</v>
+        <v>500</v>
       </c>
       <c r="AN11" t="n">
         <v>38</v>
       </c>
       <c r="AO11" t="n">
-        <v>150</v>
+        <v>500</v>
       </c>
       <c r="AP11" t="n">
-        <v>3.25</v>
+        <v>7</v>
       </c>
       <c r="AQ11" t="n">
         <v>9.6</v>
       </c>
       <c r="AR11" t="n">
-        <v>4.6</v>
+        <v>4.9</v>
       </c>
       <c r="AS11" t="n">
-        <v>5.1</v>
+        <v>5.5</v>
       </c>
       <c r="AT11" t="n">
         <v>6</v>
@@ -3269,40 +3269,40 @@
         <v>6.2</v>
       </c>
       <c r="AV11" t="n">
-        <v>4.3</v>
+        <v>4.6</v>
       </c>
       <c r="AW11" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="AX11" t="n">
+        <v>5.6</v>
+      </c>
+      <c r="AY11" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="AZ11" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="BA11" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="BB11" t="n">
         <v>5</v>
       </c>
-      <c r="AX11" t="n">
-        <v>3.9</v>
-      </c>
-      <c r="AY11" t="n">
-        <v>3.85</v>
-      </c>
-      <c r="AZ11" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="BA11" t="n">
-        <v>5.1</v>
-      </c>
-      <c r="BB11" t="n">
-        <v>4.6</v>
-      </c>
       <c r="BC11" t="n">
-        <v>4.6</v>
+        <v>5</v>
       </c>
       <c r="BD11" t="n">
-        <v>5</v>
+        <v>5.3</v>
       </c>
       <c r="BE11" t="n">
-        <v>5.2</v>
+        <v>5.7</v>
       </c>
       <c r="BF11" t="n">
-        <v>4.6</v>
+        <v>6</v>
       </c>
       <c r="BG11" t="n">
-        <v>5.1</v>
+        <v>5.6</v>
       </c>
       <c r="BH11" t="n">
         <v>3.05</v>
@@ -3366,7 +3366,7 @@
       </c>
       <c r="CB11" t="inlineStr">
         <is>
-          <t>2026-06-11 18:11:04</t>
+          <t>2026-06-11 20:24:12</t>
         </is>
       </c>
     </row>
@@ -3397,25 +3397,25 @@
         </is>
       </c>
       <c r="F12" t="n">
-        <v>2.14</v>
+        <v>2.2</v>
       </c>
       <c r="G12" t="n">
         <v>2.4</v>
       </c>
       <c r="H12" t="n">
-        <v>3.05</v>
+        <v>3.15</v>
       </c>
       <c r="I12" t="n">
         <v>3.65</v>
       </c>
       <c r="J12" t="n">
-        <v>3.5</v>
+        <v>3.55</v>
       </c>
       <c r="K12" t="n">
-        <v>4.2</v>
+        <v>3.8</v>
       </c>
       <c r="L12" t="n">
-        <v>1.33</v>
+        <v>1.29</v>
       </c>
       <c r="M12" t="n">
         <v>1.05</v>
@@ -3460,7 +3460,7 @@
         <v>40</v>
       </c>
       <c r="AA12" t="n">
-        <v>90</v>
+        <v>500</v>
       </c>
       <c r="AB12" t="n">
         <v>12.5</v>
@@ -3475,7 +3475,7 @@
         <v>55</v>
       </c>
       <c r="AF12" t="n">
-        <v>16.5</v>
+        <v>17</v>
       </c>
       <c r="AG12" t="n">
         <v>12</v>
@@ -3484,7 +3484,7 @@
         <v>17</v>
       </c>
       <c r="AI12" t="n">
-        <v>65</v>
+        <v>100</v>
       </c>
       <c r="AJ12" t="n">
         <v>38</v>
@@ -3496,7 +3496,7 @@
         <v>44</v>
       </c>
       <c r="AM12" t="n">
-        <v>100</v>
+        <v>580</v>
       </c>
       <c r="AN12" t="n">
         <v>15</v>
@@ -3526,10 +3526,10 @@
         <v>11.5</v>
       </c>
       <c r="AW12" t="n">
-        <v>7</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AX12" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AY12" t="n">
         <v>8</v>
@@ -3538,7 +3538,7 @@
         <v>11.5</v>
       </c>
       <c r="BA12" t="n">
-        <v>7</v>
+        <v>7.2</v>
       </c>
       <c r="BB12" t="n">
         <v>19.5</v>
@@ -3547,7 +3547,7 @@
         <v>15.5</v>
       </c>
       <c r="BD12" t="n">
-        <v>7.2</v>
+        <v>8.6</v>
       </c>
       <c r="BE12" t="n">
         <v>7.6</v>
@@ -3556,7 +3556,7 @@
         <v>10</v>
       </c>
       <c r="BG12" t="n">
-        <v>7</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BH12" t="n">
         <v>4</v>
@@ -3568,7 +3568,7 @@
         <v>9.4</v>
       </c>
       <c r="BK12" t="n">
-        <v>6.8</v>
+        <v>4.7</v>
       </c>
       <c r="BL12" t="n">
         <v>1000</v>
@@ -3580,7 +3580,7 @@
         <v>5.6</v>
       </c>
       <c r="BO12" t="n">
-        <v>4.6</v>
+        <v>4.1</v>
       </c>
       <c r="BP12" t="n">
         <v>17</v>
@@ -3598,7 +3598,7 @@
         <v>7</v>
       </c>
       <c r="BU12" t="n">
-        <v>5.7</v>
+        <v>5</v>
       </c>
       <c r="BV12" t="n">
         <v>1000</v>
@@ -3607,7 +3607,7 @@
         <v>7</v>
       </c>
       <c r="BX12" t="n">
-        <v>48</v>
+        <v>1000</v>
       </c>
       <c r="BY12" t="n">
         <v>7.4</v>
@@ -3620,7 +3620,7 @@
       </c>
       <c r="CB12" t="inlineStr">
         <is>
-          <t>2026-06-11 18:11:04</t>
+          <t>2026-06-11 20:24:12</t>
         </is>
       </c>
     </row>
@@ -3654,7 +3654,7 @@
         <v>1.14</v>
       </c>
       <c r="G13" t="n">
-        <v>1.18</v>
+        <v>1.17</v>
       </c>
       <c r="H13" t="n">
         <v>21</v>
@@ -3663,7 +3663,7 @@
         <v>32</v>
       </c>
       <c r="J13" t="n">
-        <v>8.800000000000001</v>
+        <v>9.4</v>
       </c>
       <c r="K13" t="n">
         <v>11.5</v>
@@ -3678,31 +3678,31 @@
         <v>7.2</v>
       </c>
       <c r="O13" t="n">
-        <v>1.12</v>
+        <v>1.13</v>
       </c>
       <c r="P13" t="n">
-        <v>3.1</v>
+        <v>3.15</v>
       </c>
       <c r="Q13" t="n">
-        <v>1.37</v>
+        <v>1.38</v>
       </c>
       <c r="R13" t="n">
-        <v>1.87</v>
+        <v>1.88</v>
       </c>
       <c r="S13" t="n">
-        <v>1.94</v>
+        <v>1.95</v>
       </c>
       <c r="T13" t="n">
-        <v>2.32</v>
+        <v>2.28</v>
       </c>
       <c r="U13" t="n">
-        <v>1.6</v>
+        <v>1.62</v>
       </c>
       <c r="V13" t="n">
         <v>1.03</v>
       </c>
       <c r="W13" t="n">
-        <v>6.6</v>
+        <v>6.8</v>
       </c>
       <c r="X13" t="n">
         <v>950</v>
@@ -3810,19 +3810,19 @@
         <v>2.56</v>
       </c>
       <c r="BG13" t="n">
-        <v>6.4</v>
+        <v>6.6</v>
       </c>
       <c r="BH13" t="n">
-        <v>5.7</v>
+        <v>5.8</v>
       </c>
       <c r="BI13" t="n">
-        <v>4.7</v>
+        <v>4.5</v>
       </c>
       <c r="BJ13" t="n">
         <v>1000</v>
       </c>
       <c r="BK13" t="n">
-        <v>11.5</v>
+        <v>6.2</v>
       </c>
       <c r="BL13" t="n">
         <v>1000</v>
@@ -3831,16 +3831,16 @@
         <v>10</v>
       </c>
       <c r="BN13" t="n">
-        <v>3.9</v>
+        <v>3.95</v>
       </c>
       <c r="BO13" t="n">
-        <v>3.15</v>
+        <v>3.1</v>
       </c>
       <c r="BP13" t="n">
         <v>5.9</v>
       </c>
       <c r="BQ13" t="n">
-        <v>4.9</v>
+        <v>4.5</v>
       </c>
       <c r="BR13" t="n">
         <v>1000</v>
@@ -3867,14 +3867,14 @@
         <v>9.800000000000001</v>
       </c>
       <c r="BZ13" t="n">
-        <v>7</v>
+        <v>6.8</v>
       </c>
       <c r="CA13" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="CB13" t="inlineStr">
         <is>
-          <t>2026-06-11 18:11:04</t>
+          <t>2026-06-11 20:24:12</t>
         </is>
       </c>
     </row>
@@ -3905,166 +3905,166 @@
         </is>
       </c>
       <c r="F14" t="n">
-        <v>3.85</v>
+        <v>4</v>
       </c>
       <c r="G14" t="n">
-        <v>4.4</v>
+        <v>4.5</v>
       </c>
       <c r="H14" t="n">
-        <v>2.06</v>
+        <v>1.98</v>
       </c>
       <c r="I14" t="n">
-        <v>2.2</v>
+        <v>2.14</v>
       </c>
       <c r="J14" t="n">
         <v>3.35</v>
       </c>
       <c r="K14" t="n">
-        <v>3.8</v>
+        <v>3.9</v>
       </c>
       <c r="L14" t="n">
         <v>1.01</v>
       </c>
       <c r="M14" t="n">
-        <v>1.07</v>
+        <v>1.08</v>
       </c>
       <c r="N14" t="n">
-        <v>3.2</v>
+        <v>3.25</v>
       </c>
       <c r="O14" t="n">
-        <v>1.34</v>
+        <v>1.35</v>
       </c>
       <c r="P14" t="n">
-        <v>1.81</v>
+        <v>1.8</v>
       </c>
       <c r="Q14" t="n">
         <v>2</v>
       </c>
       <c r="R14" t="n">
-        <v>1.31</v>
+        <v>1.3</v>
       </c>
       <c r="S14" t="n">
-        <v>2.92</v>
+        <v>4</v>
       </c>
       <c r="T14" t="n">
-        <v>1.85</v>
+        <v>1.84</v>
       </c>
       <c r="U14" t="n">
         <v>1.97</v>
       </c>
       <c r="V14" t="n">
-        <v>1.85</v>
+        <v>1.87</v>
       </c>
       <c r="W14" t="n">
-        <v>1.31</v>
+        <v>1.29</v>
       </c>
       <c r="X14" t="n">
-        <v>16</v>
+        <v>13.5</v>
       </c>
       <c r="Y14" t="n">
-        <v>10.5</v>
+        <v>9</v>
       </c>
       <c r="Z14" t="n">
-        <v>14.5</v>
+        <v>12.5</v>
       </c>
       <c r="AA14" t="n">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="AB14" t="n">
-        <v>17.5</v>
+        <v>15</v>
       </c>
       <c r="AC14" t="n">
-        <v>9.800000000000001</v>
+        <v>8.4</v>
       </c>
       <c r="AD14" t="n">
-        <v>12.5</v>
+        <v>11.5</v>
       </c>
       <c r="AE14" t="n">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="AF14" t="n">
-        <v>40</v>
+        <v>34</v>
       </c>
       <c r="AG14" t="n">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="AH14" t="n">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="AI14" t="n">
-        <v>48</v>
+        <v>44</v>
       </c>
       <c r="AJ14" t="n">
-        <v>130</v>
+        <v>900</v>
       </c>
       <c r="AK14" t="n">
-        <v>75</v>
+        <v>65</v>
       </c>
       <c r="AL14" t="n">
-        <v>80</v>
+        <v>160</v>
       </c>
       <c r="AM14" t="n">
-        <v>140</v>
+        <v>440</v>
       </c>
       <c r="AN14" t="n">
-        <v>90</v>
+        <v>240</v>
       </c>
       <c r="AO14" t="n">
-        <v>18.5</v>
+        <v>16.5</v>
       </c>
       <c r="AP14" t="n">
-        <v>3.55</v>
+        <v>6.2</v>
       </c>
       <c r="AQ14" t="n">
-        <v>3.2</v>
+        <v>5.1</v>
       </c>
       <c r="AR14" t="n">
-        <v>3.45</v>
+        <v>6.4</v>
       </c>
       <c r="AS14" t="n">
-        <v>3.9</v>
+        <v>6.8</v>
       </c>
       <c r="AT14" t="n">
-        <v>3.6</v>
+        <v>6.2</v>
       </c>
       <c r="AU14" t="n">
-        <v>3.15</v>
+        <v>4.9</v>
       </c>
       <c r="AV14" t="n">
-        <v>3.35</v>
+        <v>7</v>
       </c>
       <c r="AW14" t="n">
-        <v>3.9</v>
+        <v>6.8</v>
       </c>
       <c r="AX14" t="n">
-        <v>4</v>
+        <v>7.4</v>
       </c>
       <c r="AY14" t="n">
-        <v>3.75</v>
+        <v>6.2</v>
       </c>
       <c r="AZ14" t="n">
-        <v>3.8</v>
+        <v>6.4</v>
       </c>
       <c r="BA14" t="n">
-        <v>4.1</v>
+        <v>7.8</v>
       </c>
       <c r="BB14" t="n">
-        <v>4.4</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BC14" t="n">
-        <v>4.2</v>
+        <v>8.4</v>
       </c>
       <c r="BD14" t="n">
-        <v>4.3</v>
+        <v>8.4</v>
       </c>
       <c r="BE14" t="n">
-        <v>4.4</v>
+        <v>9</v>
       </c>
       <c r="BF14" t="n">
-        <v>4.3</v>
+        <v>8.6</v>
       </c>
       <c r="BG14" t="n">
-        <v>3.65</v>
+        <v>6</v>
       </c>
       <c r="BH14" t="n">
         <v>1000</v>
@@ -4128,7 +4128,7 @@
       </c>
       <c r="CB14" t="inlineStr">
         <is>
-          <t>2026-06-11 18:11:04</t>
+          <t>2026-06-11 20:24:12</t>
         </is>
       </c>
     </row>
@@ -4162,10 +4162,10 @@
         <v>2.42</v>
       </c>
       <c r="G15" t="n">
-        <v>2.76</v>
+        <v>2.74</v>
       </c>
       <c r="H15" t="n">
-        <v>3.35</v>
+        <v>3.4</v>
       </c>
       <c r="I15" t="n">
         <v>3.9</v>
@@ -4174,7 +4174,7 @@
         <v>2.78</v>
       </c>
       <c r="K15" t="n">
-        <v>3.15</v>
+        <v>3.1</v>
       </c>
       <c r="L15" t="n">
         <v>1.52</v>
@@ -4195,7 +4195,7 @@
         <v>2.8</v>
       </c>
       <c r="R15" t="n">
-        <v>1.18</v>
+        <v>1.17</v>
       </c>
       <c r="S15" t="n">
         <v>6</v>
@@ -4210,34 +4210,34 @@
         <v>1.34</v>
       </c>
       <c r="W15" t="n">
-        <v>1.56</v>
+        <v>1.57</v>
       </c>
       <c r="X15" t="n">
-        <v>8</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="Y15" t="n">
-        <v>11.5</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="Z15" t="n">
         <v>28</v>
       </c>
       <c r="AA15" t="n">
-        <v>100</v>
+        <v>900</v>
       </c>
       <c r="AB15" t="n">
-        <v>8.800000000000001</v>
+        <v>7.6</v>
       </c>
       <c r="AC15" t="n">
-        <v>8.4</v>
+        <v>7.4</v>
       </c>
       <c r="AD15" t="n">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="AE15" t="n">
-        <v>80</v>
+        <v>440</v>
       </c>
       <c r="AF15" t="n">
-        <v>17.5</v>
+        <v>15.5</v>
       </c>
       <c r="AG15" t="n">
         <v>16</v>
@@ -4246,79 +4246,79 @@
         <v>30</v>
       </c>
       <c r="AI15" t="n">
-        <v>120</v>
+        <v>500</v>
       </c>
       <c r="AJ15" t="n">
-        <v>50</v>
+        <v>220</v>
       </c>
       <c r="AK15" t="n">
-        <v>48</v>
+        <v>95</v>
       </c>
       <c r="AL15" t="n">
-        <v>90</v>
+        <v>460</v>
       </c>
       <c r="AM15" t="n">
-        <v>270</v>
+        <v>500</v>
       </c>
       <c r="AN15" t="n">
-        <v>55</v>
+        <v>110</v>
       </c>
       <c r="AO15" t="n">
-        <v>120</v>
+        <v>500</v>
       </c>
       <c r="AP15" t="n">
-        <v>3.05</v>
+        <v>4.2</v>
       </c>
       <c r="AQ15" t="n">
-        <v>3.45</v>
+        <v>5.1</v>
       </c>
       <c r="AR15" t="n">
-        <v>4.1</v>
+        <v>5.5</v>
       </c>
       <c r="AS15" t="n">
-        <v>4.6</v>
+        <v>6.4</v>
       </c>
       <c r="AT15" t="n">
-        <v>3.15</v>
+        <v>4.2</v>
       </c>
       <c r="AU15" t="n">
-        <v>3.1</v>
+        <v>4.2</v>
       </c>
       <c r="AV15" t="n">
-        <v>3.95</v>
+        <v>5</v>
       </c>
       <c r="AW15" t="n">
-        <v>4.6</v>
+        <v>6.2</v>
       </c>
       <c r="AX15" t="n">
-        <v>3.8</v>
+        <v>7</v>
       </c>
       <c r="AY15" t="n">
-        <v>3.75</v>
+        <v>4.9</v>
       </c>
       <c r="AZ15" t="n">
-        <v>4.2</v>
+        <v>5.6</v>
       </c>
       <c r="BA15" t="n">
-        <v>4.7</v>
+        <v>6.4</v>
       </c>
       <c r="BB15" t="n">
-        <v>4.4</v>
+        <v>5.9</v>
       </c>
       <c r="BC15" t="n">
-        <v>4.4</v>
+        <v>5.9</v>
       </c>
       <c r="BD15" t="n">
-        <v>4.6</v>
+        <v>6.2</v>
       </c>
       <c r="BE15" t="n">
-        <v>4.8</v>
+        <v>6.6</v>
       </c>
       <c r="BF15" t="n">
-        <v>4.5</v>
+        <v>6</v>
       </c>
       <c r="BG15" t="n">
-        <v>4.7</v>
+        <v>6.4</v>
       </c>
       <c r="BH15" t="n">
         <v>2.64</v>
@@ -4351,7 +4351,7 @@
         <v>7.6</v>
       </c>
       <c r="BR15" t="n">
-        <v>1000</v>
+        <v>55</v>
       </c>
       <c r="BS15" t="n">
         <v>9.4</v>
@@ -4382,7 +4382,7 @@
       </c>
       <c r="CB15" t="inlineStr">
         <is>
-          <t>2026-06-11 18:11:04</t>
+          <t>2026-06-11 20:24:12</t>
         </is>
       </c>
     </row>
@@ -4416,19 +4416,19 @@
         <v>2.88</v>
       </c>
       <c r="G16" t="n">
-        <v>3.1</v>
+        <v>3.05</v>
       </c>
       <c r="H16" t="n">
         <v>2.4</v>
       </c>
       <c r="I16" t="n">
-        <v>2.56</v>
+        <v>2.58</v>
       </c>
       <c r="J16" t="n">
         <v>3.65</v>
       </c>
       <c r="K16" t="n">
-        <v>4</v>
+        <v>3.95</v>
       </c>
       <c r="L16" t="n">
         <v>1.01</v>
@@ -4437,16 +4437,16 @@
         <v>1.04</v>
       </c>
       <c r="N16" t="n">
-        <v>4.8</v>
+        <v>5.1</v>
       </c>
       <c r="O16" t="n">
         <v>1.23</v>
       </c>
       <c r="P16" t="n">
-        <v>2.36</v>
+        <v>2.32</v>
       </c>
       <c r="Q16" t="n">
-        <v>1.68</v>
+        <v>1.69</v>
       </c>
       <c r="R16" t="n">
         <v>1.5</v>
@@ -4458,40 +4458,40 @@
         <v>1.59</v>
       </c>
       <c r="U16" t="n">
-        <v>2.44</v>
+        <v>2.52</v>
       </c>
       <c r="V16" t="n">
-        <v>1.64</v>
+        <v>1.63</v>
       </c>
       <c r="W16" t="n">
         <v>1.48</v>
       </c>
       <c r="X16" t="n">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="Y16" t="n">
-        <v>14.5</v>
+        <v>14</v>
       </c>
       <c r="Z16" t="n">
         <v>19</v>
       </c>
       <c r="AA16" t="n">
-        <v>36</v>
+        <v>80</v>
       </c>
       <c r="AB16" t="n">
-        <v>18.5</v>
+        <v>16</v>
       </c>
       <c r="AC16" t="n">
         <v>11</v>
       </c>
       <c r="AD16" t="n">
-        <v>14.5</v>
+        <v>12.5</v>
       </c>
       <c r="AE16" t="n">
         <v>25</v>
       </c>
       <c r="AF16" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AG16" t="n">
         <v>16.5</v>
@@ -4503,7 +4503,7 @@
         <v>34</v>
       </c>
       <c r="AJ16" t="n">
-        <v>48</v>
+        <v>110</v>
       </c>
       <c r="AK16" t="n">
         <v>32</v>
@@ -4512,7 +4512,7 @@
         <v>38</v>
       </c>
       <c r="AM16" t="n">
-        <v>70</v>
+        <v>250</v>
       </c>
       <c r="AN16" t="n">
         <v>25</v>
@@ -4530,7 +4530,7 @@
         <v>15.5</v>
       </c>
       <c r="AS16" t="n">
-        <v>5.3</v>
+        <v>16</v>
       </c>
       <c r="AT16" t="n">
         <v>12.5</v>
@@ -4551,22 +4551,22 @@
         <v>11</v>
       </c>
       <c r="AZ16" t="n">
-        <v>13</v>
+        <v>12.5</v>
       </c>
       <c r="BA16" t="n">
-        <v>5.2</v>
+        <v>14.5</v>
       </c>
       <c r="BB16" t="n">
-        <v>5.5</v>
+        <v>6.6</v>
       </c>
       <c r="BC16" t="n">
-        <v>5.2</v>
+        <v>14.5</v>
       </c>
       <c r="BD16" t="n">
-        <v>5.3</v>
+        <v>16</v>
       </c>
       <c r="BE16" t="n">
-        <v>5.7</v>
+        <v>7</v>
       </c>
       <c r="BF16" t="n">
         <v>17.5</v>
@@ -4636,7 +4636,7 @@
       </c>
       <c r="CB16" t="inlineStr">
         <is>
-          <t>2026-06-11 18:11:04</t>
+          <t>2026-06-11 20:24:12</t>
         </is>
       </c>
     </row>
@@ -4667,22 +4667,22 @@
         </is>
       </c>
       <c r="F17" t="n">
-        <v>1.36</v>
+        <v>1.38</v>
       </c>
       <c r="G17" t="n">
         <v>1.4</v>
       </c>
       <c r="H17" t="n">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="I17" t="n">
-        <v>12.5</v>
+        <v>12</v>
       </c>
       <c r="J17" t="n">
         <v>5</v>
       </c>
       <c r="K17" t="n">
-        <v>5.6</v>
+        <v>5.4</v>
       </c>
       <c r="L17" t="n">
         <v>1.01</v>
@@ -4691,7 +4691,7 @@
         <v>1.06</v>
       </c>
       <c r="N17" t="n">
-        <v>4</v>
+        <v>3.95</v>
       </c>
       <c r="O17" t="n">
         <v>1.29</v>
@@ -4700,13 +4700,13 @@
         <v>2.06</v>
       </c>
       <c r="Q17" t="n">
-        <v>1.84</v>
+        <v>1.86</v>
       </c>
       <c r="R17" t="n">
-        <v>1.39</v>
+        <v>1.41</v>
       </c>
       <c r="S17" t="n">
-        <v>3.1</v>
+        <v>3.2</v>
       </c>
       <c r="T17" t="n">
         <v>2.22</v>
@@ -4715,118 +4715,118 @@
         <v>1.74</v>
       </c>
       <c r="V17" t="n">
-        <v>1.08</v>
+        <v>1.09</v>
       </c>
       <c r="W17" t="n">
-        <v>3.45</v>
+        <v>3.4</v>
       </c>
       <c r="X17" t="n">
-        <v>21</v>
+        <v>17</v>
       </c>
       <c r="Y17" t="n">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="Z17" t="n">
-        <v>130</v>
+        <v>110</v>
       </c>
       <c r="AA17" t="n">
-        <v>580</v>
+        <v>510</v>
       </c>
       <c r="AB17" t="n">
-        <v>8.800000000000001</v>
+        <v>8</v>
       </c>
       <c r="AC17" t="n">
-        <v>14.5</v>
+        <v>11.5</v>
       </c>
       <c r="AD17" t="n">
-        <v>50</v>
+        <v>40</v>
       </c>
       <c r="AE17" t="n">
-        <v>250</v>
+        <v>210</v>
       </c>
       <c r="AF17" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AG17" t="n">
-        <v>12.5</v>
+        <v>11</v>
       </c>
       <c r="AH17" t="n">
-        <v>40</v>
+        <v>32</v>
       </c>
       <c r="AI17" t="n">
-        <v>200</v>
+        <v>180</v>
       </c>
       <c r="AJ17" t="n">
-        <v>13</v>
+        <v>11.5</v>
       </c>
       <c r="AK17" t="n">
+        <v>17.5</v>
+      </c>
+      <c r="AL17" t="n">
+        <v>46</v>
+      </c>
+      <c r="AM17" t="n">
+        <v>220</v>
+      </c>
+      <c r="AN17" t="n">
+        <v>7</v>
+      </c>
+      <c r="AO17" t="n">
+        <v>340</v>
+      </c>
+      <c r="AP17" t="n">
+        <v>14</v>
+      </c>
+      <c r="AQ17" t="n">
+        <v>26</v>
+      </c>
+      <c r="AR17" t="n">
+        <v>28</v>
+      </c>
+      <c r="AS17" t="n">
+        <v>11</v>
+      </c>
+      <c r="AT17" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="AU17" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AV17" t="n">
+        <v>34</v>
+      </c>
+      <c r="AW17" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="AX17" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="AY17" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="AZ17" t="n">
+        <v>27</v>
+      </c>
+      <c r="BA17" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="BB17" t="n">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="BC17" t="n">
+        <v>14</v>
+      </c>
+      <c r="BD17" t="n">
         <v>19.5</v>
       </c>
-      <c r="AL17" t="n">
-        <v>55</v>
-      </c>
-      <c r="AM17" t="n">
-        <v>260</v>
-      </c>
-      <c r="AN17" t="n">
-        <v>8</v>
-      </c>
-      <c r="AO17" t="n">
-        <v>410</v>
-      </c>
-      <c r="AP17" t="n">
-        <v>14.5</v>
-      </c>
-      <c r="AQ17" t="n">
-        <v>22</v>
-      </c>
-      <c r="AR17" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="AS17" t="n">
-        <v>4.7</v>
-      </c>
-      <c r="AT17" t="n">
-        <v>6.4</v>
-      </c>
-      <c r="AU17" t="n">
-        <v>9</v>
-      </c>
-      <c r="AV17" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="AW17" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="AX17" t="n">
-        <v>6.4</v>
-      </c>
-      <c r="AY17" t="n">
-        <v>9</v>
-      </c>
-      <c r="AZ17" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="BA17" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="BB17" t="n">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="BC17" t="n">
-        <v>13.5</v>
-      </c>
-      <c r="BD17" t="n">
-        <v>4.3</v>
-      </c>
       <c r="BE17" t="n">
-        <v>4.6</v>
+        <v>11.5</v>
       </c>
       <c r="BF17" t="n">
-        <v>5.2</v>
+        <v>6</v>
       </c>
       <c r="BG17" t="n">
-        <v>4.7</v>
+        <v>12</v>
       </c>
       <c r="BH17" t="n">
         <v>1000</v>
@@ -4838,59 +4838,59 @@
         <v>1000</v>
       </c>
       <c r="BK17" t="n">
-        <v>1.6</v>
+        <v>1.04</v>
       </c>
       <c r="BL17" t="n">
         <v>1000</v>
       </c>
       <c r="BM17" t="n">
-        <v>1.72</v>
+        <v>1.04</v>
       </c>
       <c r="BN17" t="n">
         <v>1000</v>
       </c>
       <c r="BO17" t="n">
-        <v>1.32</v>
+        <v>1.04</v>
       </c>
       <c r="BP17" t="n">
         <v>1000</v>
       </c>
       <c r="BQ17" t="n">
-        <v>1.52</v>
+        <v>1.04</v>
       </c>
       <c r="BR17" t="n">
         <v>1000</v>
       </c>
       <c r="BS17" t="n">
-        <v>1.67</v>
+        <v>1.04</v>
       </c>
       <c r="BT17" t="n">
         <v>1000</v>
       </c>
       <c r="BU17" t="n">
-        <v>1.61</v>
+        <v>1.04</v>
       </c>
       <c r="BV17" t="n">
         <v>1000</v>
       </c>
       <c r="BW17" t="n">
-        <v>1.72</v>
+        <v>1.04</v>
       </c>
       <c r="BX17" t="n">
         <v>1000</v>
       </c>
       <c r="BY17" t="n">
-        <v>1.72</v>
+        <v>1.04</v>
       </c>
       <c r="BZ17" t="n">
         <v>1000</v>
       </c>
       <c r="CA17" t="n">
-        <v>1.6</v>
+        <v>1.04</v>
       </c>
       <c r="CB17" t="inlineStr">
         <is>
-          <t>2026-06-11 18:11:04</t>
+          <t>2026-06-11 20:24:12</t>
         </is>
       </c>
     </row>
@@ -4924,22 +4924,22 @@
         <v>3.15</v>
       </c>
       <c r="G18" t="n">
-        <v>3.4</v>
+        <v>3.45</v>
       </c>
       <c r="H18" t="n">
         <v>2.46</v>
       </c>
       <c r="I18" t="n">
-        <v>2.58</v>
+        <v>2.6</v>
       </c>
       <c r="J18" t="n">
-        <v>3.3</v>
+        <v>3.25</v>
       </c>
       <c r="K18" t="n">
         <v>3.55</v>
       </c>
       <c r="L18" t="n">
-        <v>1.41</v>
+        <v>1.46</v>
       </c>
       <c r="M18" t="n">
         <v>1.09</v>
@@ -4951,28 +4951,28 @@
         <v>1.41</v>
       </c>
       <c r="P18" t="n">
-        <v>1.71</v>
+        <v>1.72</v>
       </c>
       <c r="Q18" t="n">
-        <v>2.26</v>
+        <v>2.16</v>
       </c>
       <c r="R18" t="n">
-        <v>1.25</v>
+        <v>1.26</v>
       </c>
       <c r="S18" t="n">
-        <v>4.4</v>
+        <v>4.1</v>
       </c>
       <c r="T18" t="n">
-        <v>1.91</v>
+        <v>1.88</v>
       </c>
       <c r="U18" t="n">
-        <v>1.93</v>
+        <v>1.95</v>
       </c>
       <c r="V18" t="n">
-        <v>1.63</v>
+        <v>1.62</v>
       </c>
       <c r="W18" t="n">
-        <v>1.41</v>
+        <v>1.4</v>
       </c>
       <c r="X18" t="n">
         <v>12</v>
@@ -5005,28 +5005,28 @@
         <v>14.5</v>
       </c>
       <c r="AH18" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AI18" t="n">
-        <v>70</v>
+        <v>120</v>
       </c>
       <c r="AJ18" t="n">
-        <v>85</v>
+        <v>150</v>
       </c>
       <c r="AK18" t="n">
-        <v>65</v>
+        <v>100</v>
       </c>
       <c r="AL18" t="n">
-        <v>85</v>
+        <v>290</v>
       </c>
       <c r="AM18" t="n">
-        <v>150</v>
+        <v>580</v>
       </c>
       <c r="AN18" t="n">
-        <v>70</v>
+        <v>90</v>
       </c>
       <c r="AO18" t="n">
-        <v>32</v>
+        <v>40</v>
       </c>
       <c r="AP18" t="n">
         <v>9.6</v>
@@ -5065,34 +5065,34 @@
         <v>34</v>
       </c>
       <c r="BB18" t="n">
-        <v>8</v>
+        <v>23</v>
       </c>
       <c r="BC18" t="n">
         <v>30</v>
       </c>
       <c r="BD18" t="n">
-        <v>8</v>
+        <v>23</v>
       </c>
       <c r="BE18" t="n">
-        <v>8.800000000000001</v>
+        <v>9.4</v>
       </c>
       <c r="BF18" t="n">
         <v>34</v>
       </c>
       <c r="BG18" t="n">
-        <v>7.2</v>
+        <v>7.6</v>
       </c>
       <c r="BH18" t="n">
         <v>3.15</v>
       </c>
       <c r="BI18" t="n">
-        <v>2.56</v>
+        <v>2.54</v>
       </c>
       <c r="BJ18" t="n">
         <v>10.5</v>
       </c>
       <c r="BK18" t="n">
-        <v>7.8</v>
+        <v>5.3</v>
       </c>
       <c r="BL18" t="n">
         <v>1000</v>
@@ -5104,7 +5104,7 @@
         <v>6.6</v>
       </c>
       <c r="BO18" t="n">
-        <v>5.4</v>
+        <v>4.9</v>
       </c>
       <c r="BP18" t="n">
         <v>1000</v>
@@ -5122,7 +5122,7 @@
         <v>5.5</v>
       </c>
       <c r="BU18" t="n">
-        <v>4.5</v>
+        <v>4.2</v>
       </c>
       <c r="BV18" t="n">
         <v>21</v>
@@ -5144,7 +5144,7 @@
       </c>
       <c r="CB18" t="inlineStr">
         <is>
-          <t>2026-06-11 18:11:04</t>
+          <t>2026-06-11 20:24:12</t>
         </is>
       </c>
     </row>
@@ -5175,25 +5175,25 @@
         </is>
       </c>
       <c r="F19" t="n">
-        <v>2.22</v>
+        <v>2.24</v>
       </c>
       <c r="G19" t="n">
-        <v>2.32</v>
+        <v>2.34</v>
       </c>
       <c r="H19" t="n">
-        <v>3.35</v>
+        <v>3.3</v>
       </c>
       <c r="I19" t="n">
-        <v>3.55</v>
+        <v>3.5</v>
       </c>
       <c r="J19" t="n">
-        <v>3.65</v>
+        <v>3.6</v>
       </c>
       <c r="K19" t="n">
         <v>3.9</v>
       </c>
       <c r="L19" t="n">
-        <v>1.36</v>
+        <v>1.37</v>
       </c>
       <c r="M19" t="n">
         <v>1.06</v>
@@ -5208,28 +5208,28 @@
         <v>1.98</v>
       </c>
       <c r="Q19" t="n">
-        <v>1.86</v>
+        <v>1.88</v>
       </c>
       <c r="R19" t="n">
         <v>1.37</v>
       </c>
       <c r="S19" t="n">
-        <v>3.3</v>
+        <v>3.35</v>
       </c>
       <c r="T19" t="n">
+        <v>1.71</v>
+      </c>
+      <c r="U19" t="n">
+        <v>2.18</v>
+      </c>
+      <c r="V19" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="W19" t="n">
         <v>1.74</v>
       </c>
-      <c r="U19" t="n">
-        <v>2.16</v>
-      </c>
-      <c r="V19" t="n">
-        <v>1.39</v>
-      </c>
-      <c r="W19" t="n">
-        <v>1.75</v>
-      </c>
       <c r="X19" t="n">
-        <v>19.5</v>
+        <v>17</v>
       </c>
       <c r="Y19" t="n">
         <v>14.5</v>
@@ -5238,7 +5238,7 @@
         <v>25</v>
       </c>
       <c r="AA19" t="n">
-        <v>75</v>
+        <v>130</v>
       </c>
       <c r="AB19" t="n">
         <v>11</v>
@@ -5247,7 +5247,7 @@
         <v>8.800000000000001</v>
       </c>
       <c r="AD19" t="n">
-        <v>15</v>
+        <v>14.5</v>
       </c>
       <c r="AE19" t="n">
         <v>50</v>
@@ -5274,7 +5274,7 @@
         <v>50</v>
       </c>
       <c r="AM19" t="n">
-        <v>100</v>
+        <v>320</v>
       </c>
       <c r="AN19" t="n">
         <v>17</v>
@@ -5292,7 +5292,7 @@
         <v>20</v>
       </c>
       <c r="AS19" t="n">
-        <v>8.199999999999999</v>
+        <v>23</v>
       </c>
       <c r="AT19" t="n">
         <v>9.4</v>
@@ -5304,7 +5304,7 @@
         <v>12</v>
       </c>
       <c r="AW19" t="n">
-        <v>24</v>
+        <v>32</v>
       </c>
       <c r="AX19" t="n">
         <v>13</v>
@@ -5328,7 +5328,7 @@
         <v>25</v>
       </c>
       <c r="BE19" t="n">
-        <v>8.6</v>
+        <v>9.6</v>
       </c>
       <c r="BF19" t="n">
         <v>13.5</v>
@@ -5337,7 +5337,7 @@
         <v>24</v>
       </c>
       <c r="BH19" t="n">
-        <v>3.75</v>
+        <v>3.7</v>
       </c>
       <c r="BI19" t="n">
         <v>2.92</v>
@@ -5346,13 +5346,13 @@
         <v>9.4</v>
       </c>
       <c r="BK19" t="n">
-        <v>5.8</v>
+        <v>5.3</v>
       </c>
       <c r="BL19" t="n">
         <v>1000</v>
       </c>
       <c r="BM19" t="n">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="BN19" t="n">
         <v>5.4</v>
@@ -5364,13 +5364,13 @@
         <v>16</v>
       </c>
       <c r="BQ19" t="n">
-        <v>9.6</v>
+        <v>6.8</v>
       </c>
       <c r="BR19" t="n">
         <v>1000</v>
       </c>
       <c r="BS19" t="n">
-        <v>8.199999999999999</v>
+        <v>8.4</v>
       </c>
       <c r="BT19" t="n">
         <v>7</v>
@@ -5382,23 +5382,23 @@
         <v>1000</v>
       </c>
       <c r="BW19" t="n">
-        <v>8</v>
+        <v>8.4</v>
       </c>
       <c r="BX19" t="n">
         <v>1000</v>
       </c>
       <c r="BY19" t="n">
-        <v>8.800000000000001</v>
+        <v>9</v>
       </c>
       <c r="BZ19" t="n">
         <v>24</v>
       </c>
       <c r="CA19" t="n">
-        <v>7.8</v>
+        <v>8</v>
       </c>
       <c r="CB19" t="inlineStr">
         <is>
-          <t>2026-06-11 18:11:04</t>
+          <t>2026-06-11 20:24:12</t>
         </is>
       </c>
     </row>
@@ -5435,7 +5435,7 @@
         <v>4.5</v>
       </c>
       <c r="H20" t="n">
-        <v>1.89</v>
+        <v>1.91</v>
       </c>
       <c r="I20" t="n">
         <v>2.04</v>
@@ -5444,7 +5444,7 @@
         <v>3.7</v>
       </c>
       <c r="K20" t="n">
-        <v>4.3</v>
+        <v>4.2</v>
       </c>
       <c r="L20" t="n">
         <v>1.01</v>
@@ -5483,7 +5483,7 @@
         <v>1.3</v>
       </c>
       <c r="X20" t="n">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="Y20" t="n">
         <v>12</v>
@@ -5573,7 +5573,7 @@
         <v>20</v>
       </c>
       <c r="BB20" t="n">
-        <v>4.8</v>
+        <v>5</v>
       </c>
       <c r="BC20" t="n">
         <v>30</v>
@@ -5582,7 +5582,7 @@
         <v>32</v>
       </c>
       <c r="BE20" t="n">
-        <v>4.7</v>
+        <v>4.9</v>
       </c>
       <c r="BF20" t="n">
         <v>28</v>
@@ -5600,19 +5600,19 @@
         <v>1000</v>
       </c>
       <c r="BK20" t="n">
-        <v>1.54</v>
+        <v>1.04</v>
       </c>
       <c r="BL20" t="n">
         <v>1000</v>
       </c>
       <c r="BM20" t="n">
-        <v>1.73</v>
+        <v>1.04</v>
       </c>
       <c r="BN20" t="n">
         <v>1000</v>
       </c>
       <c r="BO20" t="n">
-        <v>1.51</v>
+        <v>1.04</v>
       </c>
       <c r="BP20" t="n">
         <v>1000</v>
@@ -5630,29 +5630,29 @@
         <v>1000</v>
       </c>
       <c r="BU20" t="n">
-        <v>1.4</v>
+        <v>1.04</v>
       </c>
       <c r="BV20" t="n">
         <v>1000</v>
       </c>
       <c r="BW20" t="n">
-        <v>1.59</v>
+        <v>1.04</v>
       </c>
       <c r="BX20" t="n">
         <v>1000</v>
       </c>
       <c r="BY20" t="n">
-        <v>1.66</v>
+        <v>1.04</v>
       </c>
       <c r="BZ20" t="n">
         <v>1000</v>
       </c>
       <c r="CA20" t="n">
-        <v>1.62</v>
+        <v>1.04</v>
       </c>
       <c r="CB20" t="inlineStr">
         <is>
-          <t>2026-06-11 18:11:04</t>
+          <t>2026-06-11 20:24:12</t>
         </is>
       </c>
     </row>
@@ -5686,7 +5686,7 @@
         <v>2.3</v>
       </c>
       <c r="G21" t="n">
-        <v>2.5</v>
+        <v>2.48</v>
       </c>
       <c r="H21" t="n">
         <v>3.35</v>
@@ -5725,7 +5725,7 @@
         <v>4.2</v>
       </c>
       <c r="T21" t="n">
-        <v>1.9</v>
+        <v>1.91</v>
       </c>
       <c r="U21" t="n">
         <v>1.97</v>
@@ -5746,13 +5746,13 @@
         <v>30</v>
       </c>
       <c r="AA21" t="n">
-        <v>85</v>
+        <v>900</v>
       </c>
       <c r="AB21" t="n">
-        <v>10.5</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AC21" t="n">
-        <v>9</v>
+        <v>7.6</v>
       </c>
       <c r="AD21" t="n">
         <v>18.5</v>
@@ -5770,7 +5770,7 @@
         <v>24</v>
       </c>
       <c r="AI21" t="n">
-        <v>75</v>
+        <v>160</v>
       </c>
       <c r="AJ21" t="n">
         <v>42</v>
@@ -5782,13 +5782,13 @@
         <v>60</v>
       </c>
       <c r="AM21" t="n">
-        <v>150</v>
+        <v>580</v>
       </c>
       <c r="AN21" t="n">
         <v>32</v>
       </c>
       <c r="AO21" t="n">
-        <v>65</v>
+        <v>90</v>
       </c>
       <c r="AP21" t="n">
         <v>8.199999999999999</v>
@@ -5800,7 +5800,7 @@
         <v>17.5</v>
       </c>
       <c r="AS21" t="n">
-        <v>4.1</v>
+        <v>4.9</v>
       </c>
       <c r="AT21" t="n">
         <v>6.4</v>
@@ -5812,7 +5812,7 @@
         <v>11</v>
       </c>
       <c r="AW21" t="n">
-        <v>4.1</v>
+        <v>4.9</v>
       </c>
       <c r="AX21" t="n">
         <v>10.5</v>
@@ -5824,25 +5824,25 @@
         <v>14</v>
       </c>
       <c r="BA21" t="n">
-        <v>4.1</v>
+        <v>4.9</v>
       </c>
       <c r="BB21" t="n">
-        <v>3.95</v>
+        <v>14.5</v>
       </c>
       <c r="BC21" t="n">
         <v>21</v>
       </c>
       <c r="BD21" t="n">
-        <v>4.1</v>
+        <v>4.9</v>
       </c>
       <c r="BE21" t="n">
-        <v>4.2</v>
+        <v>5.1</v>
       </c>
       <c r="BF21" t="n">
         <v>19</v>
       </c>
       <c r="BG21" t="n">
-        <v>4.1</v>
+        <v>8.6</v>
       </c>
       <c r="BH21" t="n">
         <v>3.05</v>
@@ -5906,7 +5906,7 @@
       </c>
       <c r="CB21" t="inlineStr">
         <is>
-          <t>2026-06-11 18:11:04</t>
+          <t>2026-06-11 20:24:12</t>
         </is>
       </c>
     </row>
@@ -5937,19 +5937,19 @@
         </is>
       </c>
       <c r="F22" t="n">
-        <v>3.75</v>
+        <v>3.9</v>
       </c>
       <c r="G22" t="n">
-        <v>4.4</v>
+        <v>4.3</v>
       </c>
       <c r="H22" t="n">
-        <v>1.93</v>
+        <v>1.95</v>
       </c>
       <c r="I22" t="n">
-        <v>2.1</v>
+        <v>2.08</v>
       </c>
       <c r="J22" t="n">
-        <v>3.7</v>
+        <v>3.65</v>
       </c>
       <c r="K22" t="n">
         <v>4.2</v>
@@ -5964,58 +5964,58 @@
         <v>4.2</v>
       </c>
       <c r="O22" t="n">
-        <v>1.25</v>
+        <v>1.26</v>
       </c>
       <c r="P22" t="n">
         <v>2.12</v>
       </c>
       <c r="Q22" t="n">
-        <v>1.74</v>
+        <v>1.77</v>
       </c>
       <c r="R22" t="n">
         <v>1.33</v>
       </c>
       <c r="S22" t="n">
-        <v>2.34</v>
+        <v>2.84</v>
       </c>
       <c r="T22" t="n">
-        <v>1.66</v>
+        <v>1.37</v>
       </c>
       <c r="U22" t="n">
-        <v>2.14</v>
+        <v>1.73</v>
       </c>
       <c r="V22" t="n">
-        <v>1.9</v>
+        <v>1.92</v>
       </c>
       <c r="W22" t="n">
         <v>1.3</v>
       </c>
       <c r="X22" t="n">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="Y22" t="n">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="Z22" t="n">
-        <v>14.5</v>
+        <v>14</v>
       </c>
       <c r="AA22" t="n">
         <v>25</v>
       </c>
       <c r="AB22" t="n">
-        <v>18</v>
+        <v>17.5</v>
       </c>
       <c r="AC22" t="n">
-        <v>9.199999999999999</v>
+        <v>9</v>
       </c>
       <c r="AD22" t="n">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="AE22" t="n">
         <v>21</v>
       </c>
       <c r="AF22" t="n">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="AG22" t="n">
         <v>17.5</v>
@@ -6027,22 +6027,22 @@
         <v>34</v>
       </c>
       <c r="AJ22" t="n">
-        <v>85</v>
+        <v>900</v>
       </c>
       <c r="AK22" t="n">
-        <v>48</v>
+        <v>110</v>
       </c>
       <c r="AL22" t="n">
         <v>55</v>
       </c>
       <c r="AM22" t="n">
-        <v>85</v>
+        <v>200</v>
       </c>
       <c r="AN22" t="n">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="AO22" t="n">
-        <v>13</v>
+        <v>12.5</v>
       </c>
       <c r="AP22" t="n">
         <v>13.5</v>
@@ -6069,7 +6069,7 @@
         <v>17</v>
       </c>
       <c r="AX22" t="n">
-        <v>6.4</v>
+        <v>14.5</v>
       </c>
       <c r="AY22" t="n">
         <v>14</v>
@@ -6078,22 +6078,22 @@
         <v>14</v>
       </c>
       <c r="BA22" t="n">
-        <v>6.4</v>
+        <v>16</v>
       </c>
       <c r="BB22" t="n">
-        <v>7.2</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BC22" t="n">
-        <v>6.8</v>
+        <v>8.4</v>
       </c>
       <c r="BD22" t="n">
-        <v>7</v>
+        <v>8.6</v>
       </c>
       <c r="BE22" t="n">
-        <v>7.2</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BF22" t="n">
-        <v>32</v>
+        <v>8.4</v>
       </c>
       <c r="BG22" t="n">
         <v>10</v>
@@ -6160,7 +6160,7 @@
       </c>
       <c r="CB22" t="inlineStr">
         <is>
-          <t>2026-06-11 18:11:04</t>
+          <t>2026-06-11 20:24:12</t>
         </is>
       </c>
     </row>
@@ -6200,13 +6200,13 @@
         <v>1.85</v>
       </c>
       <c r="I23" t="n">
-        <v>1.99</v>
+        <v>2</v>
       </c>
       <c r="J23" t="n">
-        <v>3.55</v>
+        <v>3.6</v>
       </c>
       <c r="K23" t="n">
-        <v>3.9</v>
+        <v>3.95</v>
       </c>
       <c r="L23" t="n">
         <v>1.35</v>
@@ -6221,7 +6221,7 @@
         <v>1.3</v>
       </c>
       <c r="P23" t="n">
-        <v>1.9</v>
+        <v>1.91</v>
       </c>
       <c r="Q23" t="n">
         <v>1.9</v>
@@ -6257,7 +6257,7 @@
         <v>23</v>
       </c>
       <c r="AB23" t="n">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="AC23" t="n">
         <v>9</v>
@@ -6281,7 +6281,7 @@
         <v>38</v>
       </c>
       <c r="AJ23" t="n">
-        <v>120</v>
+        <v>900</v>
       </c>
       <c r="AK23" t="n">
         <v>65</v>
@@ -6290,10 +6290,10 @@
         <v>70</v>
       </c>
       <c r="AM23" t="n">
-        <v>120</v>
+        <v>580</v>
       </c>
       <c r="AN23" t="n">
-        <v>80</v>
+        <v>150</v>
       </c>
       <c r="AO23" t="n">
         <v>14</v>
@@ -6335,7 +6335,7 @@
         <v>24</v>
       </c>
       <c r="BB23" t="n">
-        <v>7.6</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BC23" t="n">
         <v>38</v>
@@ -6344,10 +6344,10 @@
         <v>42</v>
       </c>
       <c r="BE23" t="n">
-        <v>7.6</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BF23" t="n">
-        <v>7.4</v>
+        <v>7.8</v>
       </c>
       <c r="BG23" t="n">
         <v>11</v>
@@ -6362,59 +6362,59 @@
         <v>10.5</v>
       </c>
       <c r="BK23" t="n">
-        <v>5.2</v>
+        <v>5</v>
       </c>
       <c r="BL23" t="n">
         <v>1000</v>
       </c>
       <c r="BM23" t="n">
-        <v>9.4</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BN23" t="n">
         <v>8.4</v>
       </c>
       <c r="BO23" t="n">
-        <v>4.6</v>
+        <v>4.5</v>
       </c>
       <c r="BP23" t="n">
         <v>40</v>
       </c>
       <c r="BQ23" t="n">
-        <v>8.199999999999999</v>
+        <v>7.8</v>
       </c>
       <c r="BR23" t="n">
         <v>50</v>
       </c>
       <c r="BS23" t="n">
-        <v>8.4</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BT23" t="n">
-        <v>4.7</v>
+        <v>4.8</v>
       </c>
       <c r="BU23" t="n">
-        <v>3.65</v>
+        <v>3.7</v>
       </c>
       <c r="BV23" t="n">
         <v>14</v>
       </c>
       <c r="BW23" t="n">
-        <v>5.9</v>
+        <v>5.7</v>
       </c>
       <c r="BX23" t="n">
         <v>29</v>
       </c>
       <c r="BY23" t="n">
-        <v>7.6</v>
+        <v>7.2</v>
       </c>
       <c r="BZ23" t="n">
         <v>25</v>
       </c>
       <c r="CA23" t="n">
-        <v>7.2</v>
+        <v>7</v>
       </c>
       <c r="CB23" t="inlineStr">
         <is>
-          <t>2026-06-11 18:11:04</t>
+          <t>2026-06-11 20:24:12</t>
         </is>
       </c>
     </row>
@@ -6668,7 +6668,7 @@
       </c>
       <c r="CB24" t="inlineStr">
         <is>
-          <t>2026-06-11 18:11:04</t>
+          <t>2026-06-11 20:24:12</t>
         </is>
       </c>
     </row>
@@ -6702,16 +6702,16 @@
         <v>2.84</v>
       </c>
       <c r="G25" t="n">
-        <v>2.96</v>
+        <v>2.94</v>
       </c>
       <c r="H25" t="n">
         <v>2.74</v>
       </c>
       <c r="I25" t="n">
-        <v>2.9</v>
+        <v>2.76</v>
       </c>
       <c r="J25" t="n">
-        <v>3.25</v>
+        <v>3.35</v>
       </c>
       <c r="K25" t="n">
         <v>3.5</v>
@@ -6726,7 +6726,7 @@
         <v>3.25</v>
       </c>
       <c r="O25" t="n">
-        <v>1.39</v>
+        <v>1.4</v>
       </c>
       <c r="P25" t="n">
         <v>1.8</v>
@@ -6744,10 +6744,10 @@
         <v>1.86</v>
       </c>
       <c r="U25" t="n">
-        <v>2.04</v>
+        <v>2.06</v>
       </c>
       <c r="V25" t="n">
-        <v>1.52</v>
+        <v>1.56</v>
       </c>
       <c r="W25" t="n">
         <v>1.51</v>
@@ -6780,7 +6780,7 @@
         <v>23</v>
       </c>
       <c r="AG25" t="n">
-        <v>15.5</v>
+        <v>15</v>
       </c>
       <c r="AH25" t="n">
         <v>23</v>
@@ -6798,7 +6798,7 @@
         <v>60</v>
       </c>
       <c r="AM25" t="n">
-        <v>140</v>
+        <v>580</v>
       </c>
       <c r="AN25" t="n">
         <v>42</v>
@@ -6813,10 +6813,10 @@
         <v>9</v>
       </c>
       <c r="AR25" t="n">
-        <v>3.65</v>
+        <v>9</v>
       </c>
       <c r="AS25" t="n">
-        <v>4</v>
+        <v>4.1</v>
       </c>
       <c r="AT25" t="n">
         <v>9.199999999999999</v>
@@ -6828,37 +6828,37 @@
         <v>11</v>
       </c>
       <c r="AW25" t="n">
-        <v>3.95</v>
+        <v>4</v>
       </c>
       <c r="AX25" t="n">
-        <v>3.65</v>
+        <v>9</v>
       </c>
       <c r="AY25" t="n">
-        <v>3.4</v>
+        <v>11</v>
       </c>
       <c r="AZ25" t="n">
-        <v>16</v>
+        <v>10.5</v>
       </c>
       <c r="BA25" t="n">
-        <v>4</v>
+        <v>4.1</v>
       </c>
       <c r="BB25" t="n">
-        <v>4</v>
+        <v>4.1</v>
       </c>
       <c r="BC25" t="n">
-        <v>3.95</v>
+        <v>14.5</v>
       </c>
       <c r="BD25" t="n">
-        <v>4</v>
+        <v>4.1</v>
       </c>
       <c r="BE25" t="n">
         <v>4.2</v>
       </c>
       <c r="BF25" t="n">
-        <v>3.95</v>
+        <v>6.6</v>
       </c>
       <c r="BG25" t="n">
-        <v>3.95</v>
+        <v>6.2</v>
       </c>
       <c r="BH25" t="n">
         <v>1000</v>
@@ -6888,7 +6888,7 @@
         <v>1000</v>
       </c>
       <c r="BQ25" t="n">
-        <v>1.6</v>
+        <v>1.04</v>
       </c>
       <c r="BR25" t="n">
         <v>1000</v>
@@ -6906,7 +6906,7 @@
         <v>1000</v>
       </c>
       <c r="BW25" t="n">
-        <v>1.57</v>
+        <v>1.04</v>
       </c>
       <c r="BX25" t="n">
         <v>1000</v>
@@ -6922,7 +6922,7 @@
       </c>
       <c r="CB25" t="inlineStr">
         <is>
-          <t>2026-06-11 18:11:04</t>
+          <t>2026-06-11 20:24:12</t>
         </is>
       </c>
     </row>
@@ -6971,7 +6971,7 @@
         <v>5.2</v>
       </c>
       <c r="L26" t="n">
-        <v>1.18</v>
+        <v>1.21</v>
       </c>
       <c r="M26" t="n">
         <v>1.02</v>
@@ -6995,10 +6995,10 @@
         <v>1.92</v>
       </c>
       <c r="T26" t="n">
-        <v>1.44</v>
+        <v>1.45</v>
       </c>
       <c r="U26" t="n">
-        <v>2.8</v>
+        <v>2.82</v>
       </c>
       <c r="V26" t="n">
         <v>1.28</v>
@@ -7007,16 +7007,16 @@
         <v>2.12</v>
       </c>
       <c r="X26" t="n">
-        <v>48</v>
+        <v>80</v>
       </c>
       <c r="Y26" t="n">
-        <v>36</v>
+        <v>32</v>
       </c>
       <c r="Z26" t="n">
         <v>50</v>
       </c>
       <c r="AA26" t="n">
-        <v>95</v>
+        <v>470</v>
       </c>
       <c r="AB26" t="n">
         <v>22</v>
@@ -7028,7 +7028,7 @@
         <v>23</v>
       </c>
       <c r="AE26" t="n">
-        <v>48</v>
+        <v>95</v>
       </c>
       <c r="AF26" t="n">
         <v>18</v>
@@ -7055,22 +7055,22 @@
         <v>60</v>
       </c>
       <c r="AN26" t="n">
-        <v>7</v>
+        <v>6.2</v>
       </c>
       <c r="AO26" t="n">
         <v>27</v>
       </c>
       <c r="AP26" t="n">
-        <v>4.5</v>
+        <v>16</v>
       </c>
       <c r="AQ26" t="n">
         <v>21</v>
       </c>
       <c r="AR26" t="n">
-        <v>4.5</v>
+        <v>5.1</v>
       </c>
       <c r="AS26" t="n">
-        <v>4.3</v>
+        <v>5</v>
       </c>
       <c r="AT26" t="n">
         <v>13</v>
@@ -7082,7 +7082,7 @@
         <v>13.5</v>
       </c>
       <c r="AW26" t="n">
-        <v>4.5</v>
+        <v>18</v>
       </c>
       <c r="AX26" t="n">
         <v>12.5</v>
@@ -7094,7 +7094,7 @@
         <v>11</v>
       </c>
       <c r="BA26" t="n">
-        <v>4.6</v>
+        <v>18</v>
       </c>
       <c r="BB26" t="n">
         <v>15.5</v>
@@ -7106,10 +7106,10 @@
         <v>16</v>
       </c>
       <c r="BE26" t="n">
-        <v>4.4</v>
+        <v>5.2</v>
       </c>
       <c r="BF26" t="n">
-        <v>4.5</v>
+        <v>5.1</v>
       </c>
       <c r="BG26" t="n">
         <v>16</v>
@@ -7118,7 +7118,7 @@
         <v>5.6</v>
       </c>
       <c r="BI26" t="n">
-        <v>4.1</v>
+        <v>4.7</v>
       </c>
       <c r="BJ26" t="n">
         <v>8.800000000000001</v>
@@ -7136,7 +7136,7 @@
         <v>5.5</v>
       </c>
       <c r="BO26" t="n">
-        <v>4.2</v>
+        <v>4.7</v>
       </c>
       <c r="BP26" t="n">
         <v>11.5</v>
@@ -7172,11 +7172,11 @@
         <v>11</v>
       </c>
       <c r="CA26" t="n">
-        <v>6.8</v>
+        <v>5.5</v>
       </c>
       <c r="CB26" t="inlineStr">
         <is>
-          <t>2026-06-11 18:11:04</t>
+          <t>2026-06-11 20:24:12</t>
         </is>
       </c>
     </row>
@@ -7207,19 +7207,19 @@
         </is>
       </c>
       <c r="F27" t="n">
-        <v>1.09</v>
+        <v>2.64</v>
       </c>
       <c r="G27" t="n">
-        <v>1000</v>
+        <v>44</v>
       </c>
       <c r="H27" t="n">
-        <v>1.88</v>
+        <v>1.92</v>
       </c>
       <c r="I27" t="n">
-        <v>1000</v>
+        <v>44</v>
       </c>
       <c r="J27" t="n">
-        <v>1.5</v>
+        <v>2.48</v>
       </c>
       <c r="K27" t="n">
         <v>3.25</v>
@@ -7231,7 +7231,7 @@
         <v>1.09</v>
       </c>
       <c r="N27" t="n">
-        <v>1.24</v>
+        <v>1.1</v>
       </c>
       <c r="O27" t="n">
         <v>1.09</v>
@@ -7243,10 +7243,10 @@
         <v>1.1</v>
       </c>
       <c r="R27" t="n">
-        <v>1.12</v>
+        <v>1.13</v>
       </c>
       <c r="S27" t="n">
-        <v>1.51</v>
+        <v>1.52</v>
       </c>
       <c r="T27" t="n">
         <v>1.11</v>
@@ -7255,118 +7255,118 @@
         <v>1.11</v>
       </c>
       <c r="V27" t="n">
-        <v>1.02</v>
+        <v>1.42</v>
       </c>
       <c r="W27" t="n">
-        <v>1.02</v>
+        <v>1.2</v>
       </c>
       <c r="X27" t="n">
+        <v>970</v>
+      </c>
+      <c r="Y27" t="n">
+        <v>970</v>
+      </c>
+      <c r="Z27" t="n">
+        <v>500</v>
+      </c>
+      <c r="AA27" t="n">
+        <v>900</v>
+      </c>
+      <c r="AB27" t="n">
         <v>950</v>
       </c>
-      <c r="Y27" t="n">
-        <v>1000</v>
-      </c>
-      <c r="Z27" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AA27" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AB27" t="n">
-        <v>1000</v>
-      </c>
       <c r="AC27" t="n">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AD27" t="n">
-        <v>1000</v>
+        <v>950</v>
       </c>
       <c r="AE27" t="n">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AF27" t="n">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AG27" t="n">
-        <v>1000</v>
+        <v>950</v>
       </c>
       <c r="AH27" t="n">
-        <v>1000</v>
+        <v>950</v>
       </c>
       <c r="AI27" t="n">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AJ27" t="n">
-        <v>1000</v>
+        <v>900</v>
       </c>
       <c r="AK27" t="n">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AL27" t="n">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AM27" t="n">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AN27" t="n">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AO27" t="n">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AP27" t="n">
-        <v>1.01</v>
+        <v>4.2</v>
       </c>
       <c r="AQ27" t="n">
-        <v>1.01</v>
+        <v>4.2</v>
       </c>
       <c r="AR27" t="n">
-        <v>1.01</v>
+        <v>6.2</v>
       </c>
       <c r="AS27" t="n">
-        <v>1.01</v>
+        <v>1.32</v>
       </c>
       <c r="AT27" t="n">
-        <v>1.01</v>
+        <v>5.6</v>
       </c>
       <c r="AU27" t="n">
-        <v>1.01</v>
+        <v>4.2</v>
       </c>
       <c r="AV27" t="n">
-        <v>1.01</v>
+        <v>1.27</v>
       </c>
       <c r="AW27" t="n">
-        <v>1.01</v>
+        <v>1.32</v>
       </c>
       <c r="AX27" t="n">
-        <v>1.01</v>
+        <v>1.33</v>
       </c>
       <c r="AY27" t="n">
-        <v>1.01</v>
+        <v>1.33</v>
       </c>
       <c r="AZ27" t="n">
-        <v>1.01</v>
+        <v>1.33</v>
       </c>
       <c r="BA27" t="n">
-        <v>1.01</v>
+        <v>1.33</v>
       </c>
       <c r="BB27" t="n">
-        <v>1.01</v>
+        <v>1.33</v>
       </c>
       <c r="BC27" t="n">
-        <v>1.01</v>
+        <v>1.33</v>
       </c>
       <c r="BD27" t="n">
-        <v>1.01</v>
+        <v>1.33</v>
       </c>
       <c r="BE27" t="n">
-        <v>1.01</v>
+        <v>1.33</v>
       </c>
       <c r="BF27" t="n">
-        <v>1.01</v>
+        <v>1.55</v>
       </c>
       <c r="BG27" t="n">
-        <v>1.01</v>
+        <v>1.55</v>
       </c>
       <c r="BH27" t="n">
         <v>1000</v>
@@ -7430,7 +7430,7 @@
       </c>
       <c r="CB27" t="inlineStr">
         <is>
-          <t>2026-06-11 18:11:04</t>
+          <t>2026-06-11 20:24:12</t>
         </is>
       </c>
     </row>
@@ -7464,34 +7464,34 @@
         <v>2.24</v>
       </c>
       <c r="G28" t="n">
-        <v>2.38</v>
+        <v>2.36</v>
       </c>
       <c r="H28" t="n">
-        <v>3.6</v>
+        <v>3.55</v>
       </c>
       <c r="I28" t="n">
-        <v>3.9</v>
+        <v>3.85</v>
       </c>
       <c r="J28" t="n">
-        <v>3.35</v>
+        <v>3.25</v>
       </c>
       <c r="K28" t="n">
         <v>3.4</v>
       </c>
       <c r="L28" t="n">
-        <v>1.01</v>
+        <v>1.4</v>
       </c>
       <c r="M28" t="n">
         <v>1.1</v>
       </c>
       <c r="N28" t="n">
-        <v>3.05</v>
+        <v>3</v>
       </c>
       <c r="O28" t="n">
         <v>1.43</v>
       </c>
       <c r="P28" t="n">
-        <v>1.66</v>
+        <v>1.69</v>
       </c>
       <c r="Q28" t="n">
         <v>2.28</v>
@@ -7500,73 +7500,73 @@
         <v>1.25</v>
       </c>
       <c r="S28" t="n">
-        <v>4.6</v>
+        <v>4.4</v>
       </c>
       <c r="T28" t="n">
-        <v>1.95</v>
+        <v>1.96</v>
       </c>
       <c r="U28" t="n">
         <v>1.89</v>
       </c>
       <c r="V28" t="n">
-        <v>1.34</v>
+        <v>1.35</v>
       </c>
       <c r="W28" t="n">
         <v>1.73</v>
       </c>
       <c r="X28" t="n">
-        <v>12.5</v>
+        <v>19</v>
       </c>
       <c r="Y28" t="n">
-        <v>12.5</v>
+        <v>20</v>
       </c>
       <c r="Z28" t="n">
-        <v>27</v>
+        <v>500</v>
       </c>
       <c r="AA28" t="n">
-        <v>85</v>
+        <v>900</v>
       </c>
       <c r="AB28" t="n">
         <v>8.6</v>
       </c>
       <c r="AC28" t="n">
-        <v>7.8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AD28" t="n">
         <v>970</v>
       </c>
       <c r="AE28" t="n">
-        <v>60</v>
+        <v>500</v>
       </c>
       <c r="AF28" t="n">
-        <v>970</v>
+        <v>24</v>
       </c>
       <c r="AG28" t="n">
         <v>12</v>
       </c>
       <c r="AH28" t="n">
-        <v>950</v>
+        <v>60</v>
       </c>
       <c r="AI28" t="n">
-        <v>70</v>
+        <v>500</v>
       </c>
       <c r="AJ28" t="n">
-        <v>34</v>
+        <v>900</v>
       </c>
       <c r="AK28" t="n">
-        <v>30</v>
+        <v>85</v>
       </c>
       <c r="AL28" t="n">
+        <v>500</v>
+      </c>
+      <c r="AM28" t="n">
+        <v>580</v>
+      </c>
+      <c r="AN28" t="n">
         <v>55</v>
       </c>
-      <c r="AM28" t="n">
-        <v>160</v>
-      </c>
-      <c r="AN28" t="n">
-        <v>30</v>
-      </c>
       <c r="AO28" t="n">
-        <v>75</v>
+        <v>500</v>
       </c>
       <c r="AP28" t="n">
         <v>9.4</v>
@@ -7575,52 +7575,52 @@
         <v>10</v>
       </c>
       <c r="AR28" t="n">
-        <v>6.2</v>
+        <v>21</v>
       </c>
       <c r="AS28" t="n">
-        <v>7.4</v>
+        <v>8</v>
       </c>
       <c r="AT28" t="n">
         <v>7</v>
       </c>
       <c r="AU28" t="n">
-        <v>6.4</v>
+        <v>6.8</v>
       </c>
       <c r="AV28" t="n">
         <v>13</v>
       </c>
       <c r="AW28" t="n">
-        <v>7.2</v>
+        <v>7.6</v>
       </c>
       <c r="AX28" t="n">
-        <v>5.4</v>
+        <v>6.4</v>
       </c>
       <c r="AY28" t="n">
         <v>9.6</v>
       </c>
       <c r="AZ28" t="n">
-        <v>6</v>
+        <v>6.2</v>
       </c>
       <c r="BA28" t="n">
-        <v>7.4</v>
+        <v>7.8</v>
       </c>
       <c r="BB28" t="n">
-        <v>6.6</v>
+        <v>7.2</v>
       </c>
       <c r="BC28" t="n">
-        <v>6.4</v>
+        <v>13</v>
       </c>
       <c r="BD28" t="n">
-        <v>7.2</v>
+        <v>7.6</v>
       </c>
       <c r="BE28" t="n">
-        <v>7.8</v>
+        <v>8.4</v>
       </c>
       <c r="BF28" t="n">
-        <v>6.2</v>
+        <v>21</v>
       </c>
       <c r="BG28" t="n">
-        <v>7.8</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BH28" t="n">
         <v>1000</v>
@@ -7684,7 +7684,7 @@
       </c>
       <c r="CB28" t="inlineStr">
         <is>
-          <t>2026-06-11 18:11:04</t>
+          <t>2026-06-11 20:24:12</t>
         </is>
       </c>
     </row>
@@ -7721,7 +7721,7 @@
         <v>2.06</v>
       </c>
       <c r="H29" t="n">
-        <v>3.85</v>
+        <v>3.8</v>
       </c>
       <c r="I29" t="n">
         <v>4.2</v>
@@ -7733,7 +7733,7 @@
         <v>4.1</v>
       </c>
       <c r="L29" t="n">
-        <v>1.29</v>
+        <v>1.3</v>
       </c>
       <c r="M29" t="n">
         <v>1.05</v>
@@ -7742,7 +7742,7 @@
         <v>4.3</v>
       </c>
       <c r="O29" t="n">
-        <v>1.27</v>
+        <v>1.26</v>
       </c>
       <c r="P29" t="n">
         <v>2.12</v>
@@ -7769,25 +7769,25 @@
         <v>1.94</v>
       </c>
       <c r="X29" t="n">
-        <v>18.5</v>
+        <v>18</v>
       </c>
       <c r="Y29" t="n">
-        <v>17.5</v>
+        <v>17</v>
       </c>
       <c r="Z29" t="n">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="AA29" t="n">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="AB29" t="n">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="AC29" t="n">
         <v>9</v>
       </c>
       <c r="AD29" t="n">
-        <v>17</v>
+        <v>16.5</v>
       </c>
       <c r="AE29" t="n">
         <v>46</v>
@@ -7820,7 +7820,7 @@
         <v>12.5</v>
       </c>
       <c r="AO29" t="n">
-        <v>110</v>
+        <v>100</v>
       </c>
       <c r="AP29" t="n">
         <v>16</v>
@@ -7865,7 +7865,7 @@
         <v>17.5</v>
       </c>
       <c r="BD29" t="n">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="BE29" t="n">
         <v>12</v>
@@ -7883,10 +7883,10 @@
         <v>3</v>
       </c>
       <c r="BJ29" t="n">
-        <v>9.199999999999999</v>
+        <v>9.4</v>
       </c>
       <c r="BK29" t="n">
-        <v>5.8</v>
+        <v>5.9</v>
       </c>
       <c r="BL29" t="n">
         <v>1000</v>
@@ -7895,7 +7895,7 @@
         <v>13.5</v>
       </c>
       <c r="BN29" t="n">
-        <v>5</v>
+        <v>4.9</v>
       </c>
       <c r="BO29" t="n">
         <v>3.8</v>
@@ -7916,13 +7916,13 @@
         <v>7.4</v>
       </c>
       <c r="BU29" t="n">
-        <v>5.5</v>
+        <v>5.6</v>
       </c>
       <c r="BV29" t="n">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="BW29" t="n">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="BX29" t="n">
         <v>38</v>
@@ -7938,7 +7938,7 @@
       </c>
       <c r="CB29" t="inlineStr">
         <is>
-          <t>2026-06-11 18:11:04</t>
+          <t>2026-06-11 20:24:12</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-06-12.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-06-12.xlsx
@@ -881,10 +881,10 @@
         <v>1.06</v>
       </c>
       <c r="N2" t="n">
-        <v>3.2</v>
+        <v>3.5</v>
       </c>
       <c r="O2" t="n">
-        <v>1.31</v>
+        <v>1.3</v>
       </c>
       <c r="P2" t="n">
         <v>1.89</v>
@@ -896,7 +896,7 @@
         <v>1.34</v>
       </c>
       <c r="S2" t="n">
-        <v>3.2</v>
+        <v>3.65</v>
       </c>
       <c r="T2" t="n">
         <v>1.95</v>
@@ -965,7 +965,7 @@
         <v>1000</v>
       </c>
       <c r="AP2" t="n">
-        <v>3.85</v>
+        <v>3.35</v>
       </c>
       <c r="AQ2" t="n">
         <v>4.2</v>
@@ -995,19 +995,19 @@
         <v>3.8</v>
       </c>
       <c r="AZ2" t="n">
-        <v>3.9</v>
+        <v>3.4</v>
       </c>
       <c r="BA2" t="n">
         <v>4.2</v>
       </c>
       <c r="BB2" t="n">
-        <v>4.2</v>
+        <v>3.65</v>
       </c>
       <c r="BC2" t="n">
         <v>3.9</v>
       </c>
       <c r="BD2" t="n">
-        <v>4.1</v>
+        <v>3.55</v>
       </c>
       <c r="BE2" t="n">
         <v>2.84</v>
@@ -1080,7 +1080,7 @@
       </c>
       <c r="CB2" t="inlineStr">
         <is>
-          <t>2026-06-11 20:24:12</t>
+          <t>2026-06-11 22:37:56</t>
         </is>
       </c>
     </row>
@@ -1228,7 +1228,7 @@
         <v>14.5</v>
       </c>
       <c r="AS3" t="n">
-        <v>5.8</v>
+        <v>5.9</v>
       </c>
       <c r="AT3" t="n">
         <v>9.800000000000001</v>
@@ -1334,7 +1334,7 @@
       </c>
       <c r="CB3" t="inlineStr">
         <is>
-          <t>2026-06-11 20:24:12</t>
+          <t>2026-06-11 22:37:56</t>
         </is>
       </c>
     </row>
@@ -1365,7 +1365,7 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>2.9</v>
+        <v>2.86</v>
       </c>
       <c r="G4" t="n">
         <v>3.35</v>
@@ -1413,7 +1413,7 @@
         <v>1.68</v>
       </c>
       <c r="V4" t="n">
-        <v>1.4</v>
+        <v>1.43</v>
       </c>
       <c r="W4" t="n">
         <v>1.42</v>
@@ -1479,7 +1479,7 @@
         <v>6.4</v>
       </c>
       <c r="AR4" t="n">
-        <v>5.9</v>
+        <v>6.4</v>
       </c>
       <c r="AS4" t="n">
         <v>2.92</v>
@@ -1494,7 +1494,7 @@
         <v>8.4</v>
       </c>
       <c r="AW4" t="n">
-        <v>4.9</v>
+        <v>2.9</v>
       </c>
       <c r="AX4" t="n">
         <v>6.4</v>
@@ -1506,16 +1506,16 @@
         <v>6.4</v>
       </c>
       <c r="BA4" t="n">
-        <v>2.98</v>
+        <v>3</v>
       </c>
       <c r="BB4" t="n">
         <v>2.9</v>
       </c>
       <c r="BC4" t="n">
-        <v>4.8</v>
+        <v>2.94</v>
       </c>
       <c r="BD4" t="n">
-        <v>2.92</v>
+        <v>2.7</v>
       </c>
       <c r="BE4" t="n">
         <v>8.199999999999999</v>
@@ -1588,7 +1588,7 @@
       </c>
       <c r="CB4" t="inlineStr">
         <is>
-          <t>2026-06-11 20:24:12</t>
+          <t>2026-06-11 22:37:56</t>
         </is>
       </c>
     </row>
@@ -1619,19 +1619,19 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>2.24</v>
+        <v>2.26</v>
       </c>
       <c r="G5" t="n">
-        <v>2.4</v>
+        <v>2.38</v>
       </c>
       <c r="H5" t="n">
-        <v>3.9</v>
+        <v>4</v>
       </c>
       <c r="I5" t="n">
         <v>4.4</v>
       </c>
       <c r="J5" t="n">
-        <v>2.96</v>
+        <v>2.94</v>
       </c>
       <c r="K5" t="n">
         <v>3.15</v>
@@ -1772,10 +1772,10 @@
         <v>8.800000000000001</v>
       </c>
       <c r="BE5" t="n">
-        <v>9.4</v>
+        <v>9.6</v>
       </c>
       <c r="BF5" t="n">
-        <v>7.8</v>
+        <v>8</v>
       </c>
       <c r="BG5" t="n">
         <v>9.199999999999999</v>
@@ -1842,7 +1842,7 @@
       </c>
       <c r="CB5" t="inlineStr">
         <is>
-          <t>2026-06-11 20:24:12</t>
+          <t>2026-06-11 22:37:56</t>
         </is>
       </c>
     </row>
@@ -1873,13 +1873,13 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>3.3</v>
+        <v>3.35</v>
       </c>
       <c r="G6" t="n">
         <v>3.7</v>
       </c>
       <c r="H6" t="n">
-        <v>2.16</v>
+        <v>2.22</v>
       </c>
       <c r="I6" t="n">
         <v>2.36</v>
@@ -1888,7 +1888,7 @@
         <v>3.5</v>
       </c>
       <c r="K6" t="n">
-        <v>3.85</v>
+        <v>3.75</v>
       </c>
       <c r="L6" t="n">
         <v>1.31</v>
@@ -1903,7 +1903,7 @@
         <v>1.3</v>
       </c>
       <c r="P6" t="n">
-        <v>1.99</v>
+        <v>2</v>
       </c>
       <c r="Q6" t="n">
         <v>1.85</v>
@@ -1918,7 +1918,7 @@
         <v>1.74</v>
       </c>
       <c r="U6" t="n">
-        <v>2.2</v>
+        <v>2.24</v>
       </c>
       <c r="V6" t="n">
         <v>1.73</v>
@@ -2096,7 +2096,7 @@
       </c>
       <c r="CB6" t="inlineStr">
         <is>
-          <t>2026-06-11 20:24:12</t>
+          <t>2026-06-11 22:37:56</t>
         </is>
       </c>
     </row>
@@ -2235,112 +2235,112 @@
         <v>700</v>
       </c>
       <c r="AP7" t="n">
-        <v>5.2</v>
+        <v>5.7</v>
       </c>
       <c r="AQ7" t="n">
-        <v>5.4</v>
+        <v>5.9</v>
       </c>
       <c r="AR7" t="n">
-        <v>6.2</v>
+        <v>7</v>
       </c>
       <c r="AS7" t="n">
-        <v>6.8</v>
+        <v>7.8</v>
       </c>
       <c r="AT7" t="n">
-        <v>4.2</v>
+        <v>4.5</v>
       </c>
       <c r="AU7" t="n">
-        <v>4.2</v>
+        <v>4.6</v>
       </c>
       <c r="AV7" t="n">
-        <v>5.5</v>
+        <v>6</v>
       </c>
       <c r="AW7" t="n">
-        <v>6.6</v>
+        <v>7.4</v>
       </c>
       <c r="AX7" t="n">
-        <v>4.4</v>
+        <v>4.7</v>
       </c>
       <c r="AY7" t="n">
         <v>4.3</v>
       </c>
       <c r="AZ7" t="n">
-        <v>5.4</v>
+        <v>5.9</v>
       </c>
       <c r="BA7" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="BB7" t="n">
+        <v>5.6</v>
+      </c>
+      <c r="BC7" t="n">
+        <v>5.6</v>
+      </c>
+      <c r="BD7" t="n">
         <v>6.6</v>
       </c>
-      <c r="BB7" t="n">
-        <v>5.2</v>
-      </c>
-      <c r="BC7" t="n">
-        <v>5.2</v>
-      </c>
-      <c r="BD7" t="n">
-        <v>6</v>
-      </c>
       <c r="BE7" t="n">
-        <v>6.8</v>
+        <v>7.6</v>
       </c>
       <c r="BF7" t="n">
-        <v>4.2</v>
+        <v>4.5</v>
       </c>
       <c r="BG7" t="n">
-        <v>6.6</v>
+        <v>7.4</v>
       </c>
       <c r="BH7" t="n">
         <v>1000</v>
       </c>
       <c r="BI7" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BJ7" t="n">
         <v>1000</v>
       </c>
       <c r="BK7" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BL7" t="n">
         <v>1000</v>
       </c>
       <c r="BM7" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BN7" t="n">
         <v>1000</v>
       </c>
       <c r="BO7" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BP7" t="n">
         <v>1000</v>
       </c>
       <c r="BQ7" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BR7" t="n">
         <v>1000</v>
       </c>
       <c r="BS7" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BT7" t="n">
         <v>1000</v>
       </c>
       <c r="BU7" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BV7" t="n">
         <v>1000</v>
       </c>
       <c r="BW7" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BX7" t="n">
         <v>1000</v>
       </c>
       <c r="BY7" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BZ7" t="n">
         <v>0</v>
@@ -2350,7 +2350,7 @@
       </c>
       <c r="CB7" t="inlineStr">
         <is>
-          <t>2026-06-11 20:24:12</t>
+          <t>2026-06-11 22:37:56</t>
         </is>
       </c>
     </row>
@@ -2411,7 +2411,7 @@
         <v>1.31</v>
       </c>
       <c r="P8" t="n">
-        <v>1.92</v>
+        <v>1.89</v>
       </c>
       <c r="Q8" t="n">
         <v>1.91</v>
@@ -2495,7 +2495,7 @@
         <v>16.5</v>
       </c>
       <c r="AR8" t="n">
-        <v>5.6</v>
+        <v>5.5</v>
       </c>
       <c r="AS8" t="n">
         <v>6</v>
@@ -2604,7 +2604,7 @@
       </c>
       <c r="CB8" t="inlineStr">
         <is>
-          <t>2026-06-11 20:24:12</t>
+          <t>2026-06-11 22:37:56</t>
         </is>
       </c>
     </row>
@@ -2647,7 +2647,7 @@
         <v>1.82</v>
       </c>
       <c r="J9" t="n">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="K9" t="n">
         <v>4.8</v>
@@ -2800,55 +2800,55 @@
         <v>5.1</v>
       </c>
       <c r="BI9" t="n">
-        <v>1.01</v>
+        <v>2.64</v>
       </c>
       <c r="BJ9" t="n">
         <v>10.5</v>
       </c>
       <c r="BK9" t="n">
-        <v>1.01</v>
+        <v>3.6</v>
       </c>
       <c r="BL9" t="n">
         <v>95</v>
       </c>
       <c r="BM9" t="n">
-        <v>1.01</v>
+        <v>5.2</v>
       </c>
       <c r="BN9" t="n">
         <v>9.800000000000001</v>
       </c>
       <c r="BO9" t="n">
-        <v>1.01</v>
+        <v>3.5</v>
       </c>
       <c r="BP9" t="n">
         <v>38</v>
       </c>
       <c r="BQ9" t="n">
-        <v>1.01</v>
+        <v>4.8</v>
       </c>
       <c r="BR9" t="n">
         <v>42</v>
       </c>
       <c r="BS9" t="n">
-        <v>1.01</v>
+        <v>4.9</v>
       </c>
       <c r="BT9" t="n">
         <v>5.5</v>
       </c>
       <c r="BU9" t="n">
-        <v>1.01</v>
+        <v>2.76</v>
       </c>
       <c r="BV9" t="n">
         <v>12.5</v>
       </c>
       <c r="BW9" t="n">
-        <v>1.01</v>
+        <v>3.8</v>
       </c>
       <c r="BX9" t="n">
         <v>24</v>
       </c>
       <c r="BY9" t="n">
-        <v>1.01</v>
+        <v>4.5</v>
       </c>
       <c r="BZ9" t="n">
         <v>0</v>
@@ -2858,7 +2858,7 @@
       </c>
       <c r="CB9" t="inlineStr">
         <is>
-          <t>2026-06-11 20:24:12</t>
+          <t>2026-06-11 22:37:56</t>
         </is>
       </c>
     </row>
@@ -3112,7 +3112,7 @@
       </c>
       <c r="CB10" t="inlineStr">
         <is>
-          <t>2026-06-11 20:24:12</t>
+          <t>2026-06-11 22:37:56</t>
         </is>
       </c>
     </row>
@@ -3143,19 +3143,19 @@
         </is>
       </c>
       <c r="F11" t="n">
-        <v>2.16</v>
+        <v>2.18</v>
       </c>
       <c r="G11" t="n">
         <v>2.32</v>
       </c>
       <c r="H11" t="n">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="I11" t="n">
-        <v>4.7</v>
+        <v>4.8</v>
       </c>
       <c r="J11" t="n">
-        <v>2.9</v>
+        <v>2.88</v>
       </c>
       <c r="K11" t="n">
         <v>3.15</v>
@@ -3164,43 +3164,43 @@
         <v>1.59</v>
       </c>
       <c r="M11" t="n">
-        <v>1.14</v>
+        <v>1.13</v>
       </c>
       <c r="N11" t="n">
-        <v>2.5</v>
+        <v>2.52</v>
       </c>
       <c r="O11" t="n">
-        <v>1.57</v>
+        <v>1.55</v>
       </c>
       <c r="P11" t="n">
         <v>1.5</v>
       </c>
       <c r="Q11" t="n">
-        <v>2.72</v>
+        <v>2.68</v>
       </c>
       <c r="R11" t="n">
         <v>1.18</v>
       </c>
       <c r="S11" t="n">
-        <v>5.8</v>
+        <v>5.7</v>
       </c>
       <c r="T11" t="n">
-        <v>2.18</v>
+        <v>2.16</v>
       </c>
       <c r="U11" t="n">
-        <v>1.72</v>
+        <v>1.73</v>
       </c>
       <c r="V11" t="n">
         <v>1.27</v>
       </c>
       <c r="W11" t="n">
-        <v>1.75</v>
+        <v>1.76</v>
       </c>
       <c r="X11" t="n">
         <v>8.199999999999999</v>
       </c>
       <c r="Y11" t="n">
-        <v>13.5</v>
+        <v>12</v>
       </c>
       <c r="Z11" t="n">
         <v>32</v>
@@ -3209,31 +3209,31 @@
         <v>900</v>
       </c>
       <c r="AB11" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AC11" t="n">
-        <v>8.4</v>
+        <v>7.2</v>
       </c>
       <c r="AD11" t="n">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="AE11" t="n">
-        <v>210</v>
+        <v>500</v>
       </c>
       <c r="AF11" t="n">
-        <v>15</v>
+        <v>12.5</v>
       </c>
       <c r="AG11" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="AH11" t="n">
-        <v>29</v>
+        <v>25</v>
       </c>
       <c r="AI11" t="n">
         <v>540</v>
       </c>
       <c r="AJ11" t="n">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="AK11" t="n">
         <v>34</v>
@@ -3245,22 +3245,22 @@
         <v>500</v>
       </c>
       <c r="AN11" t="n">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="AO11" t="n">
         <v>500</v>
       </c>
       <c r="AP11" t="n">
-        <v>7</v>
+        <v>7.2</v>
       </c>
       <c r="AQ11" t="n">
-        <v>9.6</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AR11" t="n">
-        <v>4.9</v>
+        <v>11.5</v>
       </c>
       <c r="AS11" t="n">
-        <v>5.5</v>
+        <v>10.5</v>
       </c>
       <c r="AT11" t="n">
         <v>6</v>
@@ -3269,40 +3269,40 @@
         <v>6.2</v>
       </c>
       <c r="AV11" t="n">
-        <v>4.6</v>
+        <v>16.5</v>
       </c>
       <c r="AW11" t="n">
-        <v>5.4</v>
+        <v>10</v>
       </c>
       <c r="AX11" t="n">
-        <v>5.6</v>
+        <v>10.5</v>
       </c>
       <c r="AY11" t="n">
-        <v>6.4</v>
+        <v>10</v>
       </c>
       <c r="AZ11" t="n">
-        <v>4.8</v>
+        <v>21</v>
       </c>
       <c r="BA11" t="n">
-        <v>5.5</v>
+        <v>10.5</v>
       </c>
       <c r="BB11" t="n">
-        <v>5</v>
+        <v>11.5</v>
       </c>
       <c r="BC11" t="n">
-        <v>5</v>
+        <v>14.5</v>
       </c>
       <c r="BD11" t="n">
-        <v>5.3</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BE11" t="n">
-        <v>5.7</v>
+        <v>11</v>
       </c>
       <c r="BF11" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="BG11" t="n">
-        <v>5.6</v>
+        <v>10.5</v>
       </c>
       <c r="BH11" t="n">
         <v>3.05</v>
@@ -3366,7 +3366,7 @@
       </c>
       <c r="CB11" t="inlineStr">
         <is>
-          <t>2026-06-11 20:24:12</t>
+          <t>2026-06-11 22:37:56</t>
         </is>
       </c>
     </row>
@@ -3400,16 +3400,16 @@
         <v>2.2</v>
       </c>
       <c r="G12" t="n">
-        <v>2.4</v>
+        <v>2.42</v>
       </c>
       <c r="H12" t="n">
-        <v>3.15</v>
+        <v>3.2</v>
       </c>
       <c r="I12" t="n">
         <v>3.65</v>
       </c>
       <c r="J12" t="n">
-        <v>3.55</v>
+        <v>3.5</v>
       </c>
       <c r="K12" t="n">
         <v>3.8</v>
@@ -3448,7 +3448,7 @@
         <v>1.38</v>
       </c>
       <c r="W12" t="n">
-        <v>1.71</v>
+        <v>1.7</v>
       </c>
       <c r="X12" t="n">
         <v>23</v>
@@ -3475,7 +3475,7 @@
         <v>55</v>
       </c>
       <c r="AF12" t="n">
-        <v>17</v>
+        <v>19.5</v>
       </c>
       <c r="AG12" t="n">
         <v>12</v>
@@ -3514,49 +3514,49 @@
         <v>19.5</v>
       </c>
       <c r="AS12" t="n">
-        <v>7.4</v>
+        <v>7</v>
       </c>
       <c r="AT12" t="n">
         <v>8.4</v>
       </c>
       <c r="AU12" t="n">
-        <v>6.6</v>
+        <v>7.4</v>
       </c>
       <c r="AV12" t="n">
         <v>11.5</v>
       </c>
       <c r="AW12" t="n">
-        <v>8.199999999999999</v>
+        <v>27</v>
       </c>
       <c r="AX12" t="n">
-        <v>12</v>
+        <v>13.5</v>
       </c>
       <c r="AY12" t="n">
         <v>8</v>
       </c>
       <c r="AZ12" t="n">
-        <v>11.5</v>
+        <v>13</v>
       </c>
       <c r="BA12" t="n">
-        <v>7.2</v>
+        <v>32</v>
       </c>
       <c r="BB12" t="n">
-        <v>19.5</v>
+        <v>20</v>
       </c>
       <c r="BC12" t="n">
-        <v>15.5</v>
+        <v>19</v>
       </c>
       <c r="BD12" t="n">
-        <v>8.6</v>
+        <v>23</v>
       </c>
       <c r="BE12" t="n">
-        <v>7.6</v>
+        <v>28</v>
       </c>
       <c r="BF12" t="n">
         <v>10</v>
       </c>
       <c r="BG12" t="n">
-        <v>8.199999999999999</v>
+        <v>7</v>
       </c>
       <c r="BH12" t="n">
         <v>4</v>
@@ -3620,7 +3620,7 @@
       </c>
       <c r="CB12" t="inlineStr">
         <is>
-          <t>2026-06-11 20:24:12</t>
+          <t>2026-06-11 22:37:56</t>
         </is>
       </c>
     </row>
@@ -3657,7 +3657,7 @@
         <v>1.17</v>
       </c>
       <c r="H13" t="n">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="I13" t="n">
         <v>32</v>
@@ -3696,7 +3696,7 @@
         <v>2.28</v>
       </c>
       <c r="U13" t="n">
-        <v>1.62</v>
+        <v>1.61</v>
       </c>
       <c r="V13" t="n">
         <v>1.03</v>
@@ -3816,7 +3816,7 @@
         <v>5.8</v>
       </c>
       <c r="BI13" t="n">
-        <v>4.5</v>
+        <v>4.8</v>
       </c>
       <c r="BJ13" t="n">
         <v>1000</v>
@@ -3874,7 +3874,7 @@
       </c>
       <c r="CB13" t="inlineStr">
         <is>
-          <t>2026-06-11 20:24:12</t>
+          <t>2026-06-11 22:37:56</t>
         </is>
       </c>
     </row>
@@ -3905,13 +3905,13 @@
         </is>
       </c>
       <c r="F14" t="n">
-        <v>4</v>
+        <v>3.8</v>
       </c>
       <c r="G14" t="n">
-        <v>4.5</v>
+        <v>4.3</v>
       </c>
       <c r="H14" t="n">
-        <v>1.98</v>
+        <v>2.02</v>
       </c>
       <c r="I14" t="n">
         <v>2.14</v>
@@ -3920,7 +3920,7 @@
         <v>3.35</v>
       </c>
       <c r="K14" t="n">
-        <v>3.9</v>
+        <v>3.8</v>
       </c>
       <c r="L14" t="n">
         <v>1.01</v>
@@ -3929,7 +3929,7 @@
         <v>1.08</v>
       </c>
       <c r="N14" t="n">
-        <v>3.25</v>
+        <v>3.3</v>
       </c>
       <c r="O14" t="n">
         <v>1.35</v>
@@ -3956,7 +3956,7 @@
         <v>1.87</v>
       </c>
       <c r="W14" t="n">
-        <v>1.29</v>
+        <v>1.31</v>
       </c>
       <c r="X14" t="n">
         <v>13.5</v>
@@ -4128,7 +4128,7 @@
       </c>
       <c r="CB14" t="inlineStr">
         <is>
-          <t>2026-06-11 20:24:12</t>
+          <t>2026-06-11 22:37:56</t>
         </is>
       </c>
     </row>
@@ -4171,7 +4171,7 @@
         <v>3.9</v>
       </c>
       <c r="J15" t="n">
-        <v>2.78</v>
+        <v>2.8</v>
       </c>
       <c r="K15" t="n">
         <v>3.1</v>
@@ -4231,7 +4231,7 @@
         <v>7.4</v>
       </c>
       <c r="AD15" t="n">
-        <v>18</v>
+        <v>17.5</v>
       </c>
       <c r="AE15" t="n">
         <v>440</v>
@@ -4294,31 +4294,31 @@
         <v>7</v>
       </c>
       <c r="AY15" t="n">
-        <v>4.9</v>
+        <v>5.1</v>
       </c>
       <c r="AZ15" t="n">
         <v>5.6</v>
       </c>
       <c r="BA15" t="n">
-        <v>6.4</v>
+        <v>6.6</v>
       </c>
       <c r="BB15" t="n">
-        <v>5.9</v>
+        <v>6</v>
       </c>
       <c r="BC15" t="n">
         <v>5.9</v>
       </c>
       <c r="BD15" t="n">
-        <v>6.2</v>
+        <v>6.4</v>
       </c>
       <c r="BE15" t="n">
-        <v>6.6</v>
+        <v>6.8</v>
       </c>
       <c r="BF15" t="n">
         <v>6</v>
       </c>
       <c r="BG15" t="n">
-        <v>6.4</v>
+        <v>6.6</v>
       </c>
       <c r="BH15" t="n">
         <v>2.64</v>
@@ -4382,7 +4382,7 @@
       </c>
       <c r="CB15" t="inlineStr">
         <is>
-          <t>2026-06-11 20:24:12</t>
+          <t>2026-06-11 22:37:56</t>
         </is>
       </c>
     </row>
@@ -4413,22 +4413,22 @@
         </is>
       </c>
       <c r="F16" t="n">
-        <v>2.88</v>
+        <v>3</v>
       </c>
       <c r="G16" t="n">
-        <v>3.05</v>
+        <v>3.1</v>
       </c>
       <c r="H16" t="n">
         <v>2.4</v>
       </c>
       <c r="I16" t="n">
-        <v>2.58</v>
+        <v>2.46</v>
       </c>
       <c r="J16" t="n">
-        <v>3.65</v>
+        <v>3.7</v>
       </c>
       <c r="K16" t="n">
-        <v>3.95</v>
+        <v>3.9</v>
       </c>
       <c r="L16" t="n">
         <v>1.01</v>
@@ -4437,16 +4437,16 @@
         <v>1.04</v>
       </c>
       <c r="N16" t="n">
-        <v>5.1</v>
+        <v>4.8</v>
       </c>
       <c r="O16" t="n">
-        <v>1.23</v>
+        <v>1.22</v>
       </c>
       <c r="P16" t="n">
         <v>2.32</v>
       </c>
       <c r="Q16" t="n">
-        <v>1.69</v>
+        <v>1.68</v>
       </c>
       <c r="R16" t="n">
         <v>1.5</v>
@@ -4461,10 +4461,10 @@
         <v>2.52</v>
       </c>
       <c r="V16" t="n">
-        <v>1.63</v>
+        <v>1.68</v>
       </c>
       <c r="W16" t="n">
-        <v>1.48</v>
+        <v>1.47</v>
       </c>
       <c r="X16" t="n">
         <v>21</v>
@@ -4473,7 +4473,7 @@
         <v>14</v>
       </c>
       <c r="Z16" t="n">
-        <v>19</v>
+        <v>18.5</v>
       </c>
       <c r="AA16" t="n">
         <v>80</v>
@@ -4497,13 +4497,13 @@
         <v>16.5</v>
       </c>
       <c r="AH16" t="n">
-        <v>16</v>
+        <v>15.5</v>
       </c>
       <c r="AI16" t="n">
         <v>34</v>
       </c>
       <c r="AJ16" t="n">
-        <v>110</v>
+        <v>280</v>
       </c>
       <c r="AK16" t="n">
         <v>32</v>
@@ -4515,7 +4515,7 @@
         <v>250</v>
       </c>
       <c r="AN16" t="n">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="AO16" t="n">
         <v>18.5</v>
@@ -4557,7 +4557,7 @@
         <v>14.5</v>
       </c>
       <c r="BB16" t="n">
-        <v>6.6</v>
+        <v>7</v>
       </c>
       <c r="BC16" t="n">
         <v>14.5</v>
@@ -4566,7 +4566,7 @@
         <v>16</v>
       </c>
       <c r="BE16" t="n">
-        <v>7</v>
+        <v>7.4</v>
       </c>
       <c r="BF16" t="n">
         <v>17.5</v>
@@ -4636,7 +4636,7 @@
       </c>
       <c r="CB16" t="inlineStr">
         <is>
-          <t>2026-06-11 20:24:12</t>
+          <t>2026-06-11 22:37:56</t>
         </is>
       </c>
     </row>
@@ -4667,22 +4667,22 @@
         </is>
       </c>
       <c r="F17" t="n">
-        <v>1.38</v>
+        <v>1.37</v>
       </c>
       <c r="G17" t="n">
         <v>1.4</v>
       </c>
       <c r="H17" t="n">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="I17" t="n">
         <v>12</v>
       </c>
       <c r="J17" t="n">
-        <v>5</v>
+        <v>5.1</v>
       </c>
       <c r="K17" t="n">
-        <v>5.4</v>
+        <v>5.5</v>
       </c>
       <c r="L17" t="n">
         <v>1.01</v>
@@ -4700,7 +4700,7 @@
         <v>2.06</v>
       </c>
       <c r="Q17" t="n">
-        <v>1.86</v>
+        <v>1.85</v>
       </c>
       <c r="R17" t="n">
         <v>1.41</v>
@@ -4733,40 +4733,40 @@
         <v>510</v>
       </c>
       <c r="AB17" t="n">
-        <v>8</v>
+        <v>7.8</v>
       </c>
       <c r="AC17" t="n">
-        <v>11.5</v>
+        <v>12</v>
       </c>
       <c r="AD17" t="n">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="AE17" t="n">
         <v>210</v>
       </c>
       <c r="AF17" t="n">
-        <v>8</v>
+        <v>7.8</v>
       </c>
       <c r="AG17" t="n">
         <v>11</v>
       </c>
       <c r="AH17" t="n">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="AI17" t="n">
-        <v>180</v>
+        <v>170</v>
       </c>
       <c r="AJ17" t="n">
         <v>11.5</v>
       </c>
       <c r="AK17" t="n">
-        <v>17.5</v>
+        <v>16.5</v>
       </c>
       <c r="AL17" t="n">
         <v>46</v>
       </c>
       <c r="AM17" t="n">
-        <v>220</v>
+        <v>260</v>
       </c>
       <c r="AN17" t="n">
         <v>7</v>
@@ -4775,7 +4775,7 @@
         <v>340</v>
       </c>
       <c r="AP17" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AQ17" t="n">
         <v>26</v>
@@ -4784,7 +4784,7 @@
         <v>28</v>
       </c>
       <c r="AS17" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AT17" t="n">
         <v>6.6</v>
@@ -4796,19 +4796,19 @@
         <v>34</v>
       </c>
       <c r="AW17" t="n">
-        <v>11.5</v>
+        <v>12</v>
       </c>
       <c r="AX17" t="n">
         <v>6.8</v>
       </c>
       <c r="AY17" t="n">
-        <v>9.6</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AZ17" t="n">
         <v>27</v>
       </c>
       <c r="BA17" t="n">
-        <v>11.5</v>
+        <v>12</v>
       </c>
       <c r="BB17" t="n">
         <v>9.800000000000001</v>
@@ -4820,13 +4820,13 @@
         <v>19.5</v>
       </c>
       <c r="BE17" t="n">
-        <v>11.5</v>
+        <v>14</v>
       </c>
       <c r="BF17" t="n">
         <v>6</v>
       </c>
       <c r="BG17" t="n">
-        <v>12</v>
+        <v>14.5</v>
       </c>
       <c r="BH17" t="n">
         <v>1000</v>
@@ -4838,59 +4838,59 @@
         <v>1000</v>
       </c>
       <c r="BK17" t="n">
-        <v>1.04</v>
+        <v>1.58</v>
       </c>
       <c r="BL17" t="n">
         <v>1000</v>
       </c>
       <c r="BM17" t="n">
-        <v>1.04</v>
+        <v>1.72</v>
       </c>
       <c r="BN17" t="n">
         <v>1000</v>
       </c>
       <c r="BO17" t="n">
-        <v>1.04</v>
+        <v>1.3</v>
       </c>
       <c r="BP17" t="n">
         <v>1000</v>
       </c>
       <c r="BQ17" t="n">
-        <v>1.04</v>
+        <v>1.5</v>
       </c>
       <c r="BR17" t="n">
         <v>1000</v>
       </c>
       <c r="BS17" t="n">
-        <v>1.04</v>
+        <v>1.65</v>
       </c>
       <c r="BT17" t="n">
         <v>1000</v>
       </c>
       <c r="BU17" t="n">
-        <v>1.04</v>
+        <v>1.59</v>
       </c>
       <c r="BV17" t="n">
         <v>1000</v>
       </c>
       <c r="BW17" t="n">
-        <v>1.04</v>
+        <v>1.72</v>
       </c>
       <c r="BX17" t="n">
         <v>1000</v>
       </c>
       <c r="BY17" t="n">
-        <v>1.04</v>
+        <v>1.72</v>
       </c>
       <c r="BZ17" t="n">
         <v>1000</v>
       </c>
       <c r="CA17" t="n">
-        <v>1.04</v>
+        <v>1.6</v>
       </c>
       <c r="CB17" t="inlineStr">
         <is>
-          <t>2026-06-11 20:24:12</t>
+          <t>2026-06-11 22:37:56</t>
         </is>
       </c>
     </row>
@@ -4936,10 +4936,10 @@
         <v>3.25</v>
       </c>
       <c r="K18" t="n">
-        <v>3.55</v>
+        <v>3.4</v>
       </c>
       <c r="L18" t="n">
-        <v>1.46</v>
+        <v>1.42</v>
       </c>
       <c r="M18" t="n">
         <v>1.09</v>
@@ -4951,7 +4951,7 @@
         <v>1.41</v>
       </c>
       <c r="P18" t="n">
-        <v>1.72</v>
+        <v>1.73</v>
       </c>
       <c r="Q18" t="n">
         <v>2.16</v>
@@ -4963,7 +4963,7 @@
         <v>4.1</v>
       </c>
       <c r="T18" t="n">
-        <v>1.88</v>
+        <v>1.89</v>
       </c>
       <c r="U18" t="n">
         <v>1.95</v>
@@ -5144,7 +5144,7 @@
       </c>
       <c r="CB18" t="inlineStr">
         <is>
-          <t>2026-06-11 20:24:12</t>
+          <t>2026-06-11 22:37:56</t>
         </is>
       </c>
     </row>
@@ -5184,13 +5184,13 @@
         <v>3.3</v>
       </c>
       <c r="I19" t="n">
-        <v>3.5</v>
+        <v>3.55</v>
       </c>
       <c r="J19" t="n">
         <v>3.6</v>
       </c>
       <c r="K19" t="n">
-        <v>3.9</v>
+        <v>3.8</v>
       </c>
       <c r="L19" t="n">
         <v>1.37</v>
@@ -5220,7 +5220,7 @@
         <v>1.71</v>
       </c>
       <c r="U19" t="n">
-        <v>2.18</v>
+        <v>2.16</v>
       </c>
       <c r="V19" t="n">
         <v>1.4</v>
@@ -5398,7 +5398,7 @@
       </c>
       <c r="CB19" t="inlineStr">
         <is>
-          <t>2026-06-11 20:24:12</t>
+          <t>2026-06-11 22:37:56</t>
         </is>
       </c>
     </row>
@@ -5438,13 +5438,13 @@
         <v>1.91</v>
       </c>
       <c r="I20" t="n">
-        <v>2.04</v>
+        <v>2.02</v>
       </c>
       <c r="J20" t="n">
         <v>3.7</v>
       </c>
       <c r="K20" t="n">
-        <v>4.2</v>
+        <v>4.1</v>
       </c>
       <c r="L20" t="n">
         <v>1.01</v>
@@ -5477,7 +5477,7 @@
         <v>2.3</v>
       </c>
       <c r="V20" t="n">
-        <v>1.96</v>
+        <v>1.98</v>
       </c>
       <c r="W20" t="n">
         <v>1.3</v>
@@ -5600,19 +5600,19 @@
         <v>1000</v>
       </c>
       <c r="BK20" t="n">
-        <v>1.04</v>
+        <v>1.54</v>
       </c>
       <c r="BL20" t="n">
         <v>1000</v>
       </c>
       <c r="BM20" t="n">
-        <v>1.04</v>
+        <v>1.73</v>
       </c>
       <c r="BN20" t="n">
         <v>1000</v>
       </c>
       <c r="BO20" t="n">
-        <v>1.04</v>
+        <v>1.51</v>
       </c>
       <c r="BP20" t="n">
         <v>1000</v>
@@ -5630,29 +5630,29 @@
         <v>1000</v>
       </c>
       <c r="BU20" t="n">
-        <v>1.04</v>
+        <v>1.4</v>
       </c>
       <c r="BV20" t="n">
         <v>1000</v>
       </c>
       <c r="BW20" t="n">
-        <v>1.04</v>
+        <v>1.59</v>
       </c>
       <c r="BX20" t="n">
         <v>1000</v>
       </c>
       <c r="BY20" t="n">
-        <v>1.04</v>
+        <v>1.66</v>
       </c>
       <c r="BZ20" t="n">
         <v>1000</v>
       </c>
       <c r="CA20" t="n">
-        <v>1.04</v>
+        <v>1.62</v>
       </c>
       <c r="CB20" t="inlineStr">
         <is>
-          <t>2026-06-11 20:24:12</t>
+          <t>2026-06-11 22:37:56</t>
         </is>
       </c>
     </row>
@@ -5701,7 +5701,7 @@
         <v>3.45</v>
       </c>
       <c r="L21" t="n">
-        <v>1.4</v>
+        <v>1.49</v>
       </c>
       <c r="M21" t="n">
         <v>1.09</v>
@@ -5906,7 +5906,7 @@
       </c>
       <c r="CB21" t="inlineStr">
         <is>
-          <t>2026-06-11 20:24:12</t>
+          <t>2026-06-11 22:37:56</t>
         </is>
       </c>
     </row>
@@ -5946,7 +5946,7 @@
         <v>1.95</v>
       </c>
       <c r="I22" t="n">
-        <v>2.08</v>
+        <v>2.1</v>
       </c>
       <c r="J22" t="n">
         <v>3.65</v>
@@ -5967,7 +5967,7 @@
         <v>1.26</v>
       </c>
       <c r="P22" t="n">
-        <v>2.12</v>
+        <v>2.08</v>
       </c>
       <c r="Q22" t="n">
         <v>1.77</v>
@@ -5985,7 +5985,7 @@
         <v>1.73</v>
       </c>
       <c r="V22" t="n">
-        <v>1.92</v>
+        <v>1.91</v>
       </c>
       <c r="W22" t="n">
         <v>1.3</v>
@@ -6160,7 +6160,7 @@
       </c>
       <c r="CB22" t="inlineStr">
         <is>
-          <t>2026-06-11 20:24:12</t>
+          <t>2026-06-11 22:37:56</t>
         </is>
       </c>
     </row>
@@ -6197,10 +6197,10 @@
         <v>5</v>
       </c>
       <c r="H23" t="n">
-        <v>1.85</v>
+        <v>1.84</v>
       </c>
       <c r="I23" t="n">
-        <v>2</v>
+        <v>2.02</v>
       </c>
       <c r="J23" t="n">
         <v>3.6</v>
@@ -6239,7 +6239,7 @@
         <v>2.04</v>
       </c>
       <c r="V23" t="n">
-        <v>2</v>
+        <v>1.99</v>
       </c>
       <c r="W23" t="n">
         <v>1.25</v>
@@ -6254,7 +6254,7 @@
         <v>12.5</v>
       </c>
       <c r="AA23" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AB23" t="n">
         <v>17</v>
@@ -6266,16 +6266,16 @@
         <v>11</v>
       </c>
       <c r="AE23" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AF23" t="n">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="AG23" t="n">
         <v>19</v>
       </c>
       <c r="AH23" t="n">
-        <v>20</v>
+        <v>19.5</v>
       </c>
       <c r="AI23" t="n">
         <v>38</v>
@@ -6287,7 +6287,7 @@
         <v>65</v>
       </c>
       <c r="AL23" t="n">
-        <v>70</v>
+        <v>75</v>
       </c>
       <c r="AM23" t="n">
         <v>580</v>
@@ -6296,7 +6296,7 @@
         <v>150</v>
       </c>
       <c r="AO23" t="n">
-        <v>14</v>
+        <v>13.5</v>
       </c>
       <c r="AP23" t="n">
         <v>11</v>
@@ -6335,7 +6335,7 @@
         <v>24</v>
       </c>
       <c r="BB23" t="n">
-        <v>8.199999999999999</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BC23" t="n">
         <v>38</v>
@@ -6344,10 +6344,10 @@
         <v>42</v>
       </c>
       <c r="BE23" t="n">
-        <v>8.199999999999999</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BF23" t="n">
-        <v>7.8</v>
+        <v>8.4</v>
       </c>
       <c r="BG23" t="n">
         <v>11</v>
@@ -6414,7 +6414,7 @@
       </c>
       <c r="CB23" t="inlineStr">
         <is>
-          <t>2026-06-11 20:24:12</t>
+          <t>2026-06-11 22:37:56</t>
         </is>
       </c>
     </row>
@@ -6668,7 +6668,7 @@
       </c>
       <c r="CB24" t="inlineStr">
         <is>
-          <t>2026-06-11 20:24:12</t>
+          <t>2026-06-11 22:37:56</t>
         </is>
       </c>
     </row>
@@ -6699,7 +6699,7 @@
         </is>
       </c>
       <c r="F25" t="n">
-        <v>2.84</v>
+        <v>2.86</v>
       </c>
       <c r="G25" t="n">
         <v>2.94</v>
@@ -6723,28 +6723,28 @@
         <v>1.09</v>
       </c>
       <c r="N25" t="n">
-        <v>3.25</v>
+        <v>3.3</v>
       </c>
       <c r="O25" t="n">
-        <v>1.4</v>
+        <v>1.39</v>
       </c>
       <c r="P25" t="n">
         <v>1.8</v>
       </c>
       <c r="Q25" t="n">
-        <v>2.16</v>
+        <v>2.12</v>
       </c>
       <c r="R25" t="n">
         <v>1.29</v>
       </c>
       <c r="S25" t="n">
-        <v>4.1</v>
+        <v>4</v>
       </c>
       <c r="T25" t="n">
-        <v>1.86</v>
+        <v>1.83</v>
       </c>
       <c r="U25" t="n">
-        <v>2.06</v>
+        <v>2.08</v>
       </c>
       <c r="V25" t="n">
         <v>1.56</v>
@@ -6807,7 +6807,7 @@
         <v>40</v>
       </c>
       <c r="AP25" t="n">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="AQ25" t="n">
         <v>9</v>
@@ -6870,25 +6870,25 @@
         <v>1000</v>
       </c>
       <c r="BK25" t="n">
-        <v>1.04</v>
+        <v>1.48</v>
       </c>
       <c r="BL25" t="n">
         <v>1000</v>
       </c>
       <c r="BM25" t="n">
-        <v>1.04</v>
+        <v>1.65</v>
       </c>
       <c r="BN25" t="n">
         <v>1000</v>
       </c>
       <c r="BO25" t="n">
-        <v>1.04</v>
+        <v>1.39</v>
       </c>
       <c r="BP25" t="n">
         <v>1000</v>
       </c>
       <c r="BQ25" t="n">
-        <v>1.04</v>
+        <v>1.58</v>
       </c>
       <c r="BR25" t="n">
         <v>1000</v>
@@ -6900,13 +6900,13 @@
         <v>1000</v>
       </c>
       <c r="BU25" t="n">
-        <v>1.04</v>
+        <v>1.39</v>
       </c>
       <c r="BV25" t="n">
         <v>1000</v>
       </c>
       <c r="BW25" t="n">
-        <v>1.04</v>
+        <v>1.57</v>
       </c>
       <c r="BX25" t="n">
         <v>1000</v>
@@ -6922,7 +6922,7 @@
       </c>
       <c r="CB25" t="inlineStr">
         <is>
-          <t>2026-06-11 20:24:12</t>
+          <t>2026-06-11 22:37:56</t>
         </is>
       </c>
     </row>
@@ -7055,7 +7055,7 @@
         <v>60</v>
       </c>
       <c r="AN26" t="n">
-        <v>6.2</v>
+        <v>7</v>
       </c>
       <c r="AO26" t="n">
         <v>27</v>
@@ -7067,10 +7067,10 @@
         <v>21</v>
       </c>
       <c r="AR26" t="n">
-        <v>5.1</v>
+        <v>4.7</v>
       </c>
       <c r="AS26" t="n">
-        <v>5</v>
+        <v>4.6</v>
       </c>
       <c r="AT26" t="n">
         <v>13</v>
@@ -7106,7 +7106,7 @@
         <v>16</v>
       </c>
       <c r="BE26" t="n">
-        <v>5.2</v>
+        <v>4.8</v>
       </c>
       <c r="BF26" t="n">
         <v>5.1</v>
@@ -7176,7 +7176,7 @@
       </c>
       <c r="CB26" t="inlineStr">
         <is>
-          <t>2026-06-11 20:24:12</t>
+          <t>2026-06-11 22:37:56</t>
         </is>
       </c>
     </row>
@@ -7210,7 +7210,7 @@
         <v>2.64</v>
       </c>
       <c r="G27" t="n">
-        <v>44</v>
+        <v>110</v>
       </c>
       <c r="H27" t="n">
         <v>1.92</v>
@@ -7240,13 +7240,13 @@
         <v>1.24</v>
       </c>
       <c r="Q27" t="n">
-        <v>1.1</v>
+        <v>1.09</v>
       </c>
       <c r="R27" t="n">
         <v>1.13</v>
       </c>
       <c r="S27" t="n">
-        <v>1.52</v>
+        <v>1.49</v>
       </c>
       <c r="T27" t="n">
         <v>1.11</v>
@@ -7255,7 +7255,7 @@
         <v>1.11</v>
       </c>
       <c r="V27" t="n">
-        <v>1.42</v>
+        <v>1.46</v>
       </c>
       <c r="W27" t="n">
         <v>1.2</v>
@@ -7430,7 +7430,7 @@
       </c>
       <c r="CB27" t="inlineStr">
         <is>
-          <t>2026-06-11 20:24:12</t>
+          <t>2026-06-11 22:37:56</t>
         </is>
       </c>
     </row>
@@ -7461,19 +7461,19 @@
         </is>
       </c>
       <c r="F28" t="n">
-        <v>2.24</v>
+        <v>2.26</v>
       </c>
       <c r="G28" t="n">
-        <v>2.36</v>
+        <v>2.38</v>
       </c>
       <c r="H28" t="n">
         <v>3.55</v>
       </c>
       <c r="I28" t="n">
-        <v>3.85</v>
+        <v>3.8</v>
       </c>
       <c r="J28" t="n">
-        <v>3.25</v>
+        <v>3.3</v>
       </c>
       <c r="K28" t="n">
         <v>3.4</v>
@@ -7497,7 +7497,7 @@
         <v>2.28</v>
       </c>
       <c r="R28" t="n">
-        <v>1.25</v>
+        <v>1.26</v>
       </c>
       <c r="S28" t="n">
         <v>4.4</v>
@@ -7512,7 +7512,7 @@
         <v>1.35</v>
       </c>
       <c r="W28" t="n">
-        <v>1.73</v>
+        <v>1.72</v>
       </c>
       <c r="X28" t="n">
         <v>19</v>
@@ -7530,10 +7530,10 @@
         <v>8.6</v>
       </c>
       <c r="AC28" t="n">
-        <v>8.199999999999999</v>
+        <v>14</v>
       </c>
       <c r="AD28" t="n">
-        <v>970</v>
+        <v>500</v>
       </c>
       <c r="AE28" t="n">
         <v>500</v>
@@ -7572,13 +7572,13 @@
         <v>9.4</v>
       </c>
       <c r="AQ28" t="n">
-        <v>10</v>
+        <v>6.2</v>
       </c>
       <c r="AR28" t="n">
         <v>21</v>
       </c>
       <c r="AS28" t="n">
-        <v>8</v>
+        <v>8.6</v>
       </c>
       <c r="AT28" t="n">
         <v>7</v>
@@ -7590,31 +7590,31 @@
         <v>13</v>
       </c>
       <c r="AW28" t="n">
-        <v>7.6</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AX28" t="n">
-        <v>6.4</v>
+        <v>11.5</v>
       </c>
       <c r="AY28" t="n">
         <v>9.6</v>
       </c>
       <c r="AZ28" t="n">
-        <v>6.2</v>
+        <v>6.6</v>
       </c>
       <c r="BA28" t="n">
-        <v>7.8</v>
+        <v>8.4</v>
       </c>
       <c r="BB28" t="n">
-        <v>7.2</v>
+        <v>7.4</v>
       </c>
       <c r="BC28" t="n">
         <v>13</v>
       </c>
       <c r="BD28" t="n">
-        <v>7.6</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BE28" t="n">
-        <v>8.4</v>
+        <v>9</v>
       </c>
       <c r="BF28" t="n">
         <v>21</v>
@@ -7684,7 +7684,7 @@
       </c>
       <c r="CB28" t="inlineStr">
         <is>
-          <t>2026-06-11 20:24:12</t>
+          <t>2026-06-11 22:37:56</t>
         </is>
       </c>
     </row>
@@ -7721,7 +7721,7 @@
         <v>2.06</v>
       </c>
       <c r="H29" t="n">
-        <v>3.8</v>
+        <v>3.85</v>
       </c>
       <c r="I29" t="n">
         <v>4.2</v>
@@ -7778,7 +7778,7 @@
         <v>30</v>
       </c>
       <c r="AA29" t="n">
-        <v>75</v>
+        <v>95</v>
       </c>
       <c r="AB29" t="n">
         <v>11</v>
@@ -7823,7 +7823,7 @@
         <v>100</v>
       </c>
       <c r="AP29" t="n">
-        <v>16</v>
+        <v>15.5</v>
       </c>
       <c r="AQ29" t="n">
         <v>15</v>
@@ -7832,7 +7832,7 @@
         <v>18.5</v>
       </c>
       <c r="AS29" t="n">
-        <v>11.5</v>
+        <v>12.5</v>
       </c>
       <c r="AT29" t="n">
         <v>9.4</v>
@@ -7868,7 +7868,7 @@
         <v>24</v>
       </c>
       <c r="BE29" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="BF29" t="n">
         <v>11</v>
@@ -7916,7 +7916,7 @@
         <v>7.4</v>
       </c>
       <c r="BU29" t="n">
-        <v>5.6</v>
+        <v>5.5</v>
       </c>
       <c r="BV29" t="n">
         <v>32</v>
@@ -7938,7 +7938,7 @@
       </c>
       <c r="CB29" t="inlineStr">
         <is>
-          <t>2026-06-11 20:24:12</t>
+          <t>2026-06-11 22:37:56</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-06-12.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-06-12.xlsx
@@ -857,7 +857,7 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>1.5</v>
+        <v>1.57</v>
       </c>
       <c r="G2" t="n">
         <v>1.63</v>
@@ -866,13 +866,13 @@
         <v>7</v>
       </c>
       <c r="I2" t="n">
-        <v>9.6</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="J2" t="n">
-        <v>3.7</v>
+        <v>3.8</v>
       </c>
       <c r="K2" t="n">
-        <v>4.9</v>
+        <v>4.5</v>
       </c>
       <c r="L2" t="n">
         <v>1.33</v>
@@ -881,34 +881,34 @@
         <v>1.06</v>
       </c>
       <c r="N2" t="n">
-        <v>3.5</v>
+        <v>3.65</v>
       </c>
       <c r="O2" t="n">
-        <v>1.3</v>
+        <v>1.31</v>
       </c>
       <c r="P2" t="n">
-        <v>1.89</v>
+        <v>1.92</v>
       </c>
       <c r="Q2" t="n">
+        <v>1.94</v>
+      </c>
+      <c r="R2" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="S2" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="T2" t="n">
+        <v>1.96</v>
+      </c>
+      <c r="U2" t="n">
         <v>1.87</v>
       </c>
-      <c r="R2" t="n">
-        <v>1.34</v>
-      </c>
-      <c r="S2" t="n">
-        <v>3.65</v>
-      </c>
-      <c r="T2" t="n">
-        <v>1.95</v>
-      </c>
-      <c r="U2" t="n">
-        <v>1.81</v>
-      </c>
       <c r="V2" t="n">
-        <v>1.13</v>
+        <v>1.15</v>
       </c>
       <c r="W2" t="n">
-        <v>2.56</v>
+        <v>2.58</v>
       </c>
       <c r="X2" t="n">
         <v>970</v>
@@ -917,13 +917,13 @@
         <v>950</v>
       </c>
       <c r="Z2" t="n">
-        <v>75</v>
+        <v>220</v>
       </c>
       <c r="AA2" t="n">
         <v>1000</v>
       </c>
       <c r="AB2" t="n">
-        <v>500</v>
+        <v>27</v>
       </c>
       <c r="AC2" t="n">
         <v>42</v>
@@ -938,7 +938,7 @@
         <v>40</v>
       </c>
       <c r="AG2" t="n">
-        <v>500</v>
+        <v>970</v>
       </c>
       <c r="AH2" t="n">
         <v>950</v>
@@ -965,7 +965,7 @@
         <v>1000</v>
       </c>
       <c r="AP2" t="n">
-        <v>3.35</v>
+        <v>2.48</v>
       </c>
       <c r="AQ2" t="n">
         <v>4.2</v>
@@ -977,10 +977,10 @@
         <v>4.2</v>
       </c>
       <c r="AT2" t="n">
-        <v>3.45</v>
+        <v>2.9</v>
       </c>
       <c r="AU2" t="n">
-        <v>3.75</v>
+        <v>4.7</v>
       </c>
       <c r="AV2" t="n">
         <v>4.2</v>
@@ -989,98 +989,98 @@
         <v>4.2</v>
       </c>
       <c r="AX2" t="n">
-        <v>3.75</v>
+        <v>3.05</v>
       </c>
       <c r="AY2" t="n">
-        <v>3.8</v>
+        <v>2.62</v>
       </c>
       <c r="AZ2" t="n">
-        <v>3.4</v>
+        <v>2.5</v>
       </c>
       <c r="BA2" t="n">
         <v>4.2</v>
       </c>
       <c r="BB2" t="n">
-        <v>3.65</v>
+        <v>2.64</v>
       </c>
       <c r="BC2" t="n">
-        <v>3.9</v>
+        <v>2.78</v>
       </c>
       <c r="BD2" t="n">
-        <v>3.55</v>
+        <v>2.58</v>
       </c>
       <c r="BE2" t="n">
-        <v>2.84</v>
+        <v>2.68</v>
       </c>
       <c r="BF2" t="n">
-        <v>3.85</v>
+        <v>5.1</v>
       </c>
       <c r="BG2" t="n">
         <v>4.2</v>
       </c>
       <c r="BH2" t="n">
-        <v>1000</v>
+        <v>3.65</v>
       </c>
       <c r="BI2" t="n">
-        <v>2.88</v>
+        <v>3.2</v>
       </c>
       <c r="BJ2" t="n">
         <v>1000</v>
       </c>
       <c r="BK2" t="n">
-        <v>1.21</v>
+        <v>3.8</v>
       </c>
       <c r="BL2" t="n">
         <v>1000</v>
       </c>
       <c r="BM2" t="n">
-        <v>1.17</v>
+        <v>1.62</v>
       </c>
       <c r="BN2" t="n">
-        <v>1000</v>
+        <v>4.1</v>
       </c>
       <c r="BO2" t="n">
-        <v>2.84</v>
+        <v>3.55</v>
       </c>
       <c r="BP2" t="n">
         <v>1000</v>
       </c>
       <c r="BQ2" t="n">
-        <v>1.34</v>
+        <v>5.8</v>
       </c>
       <c r="BR2" t="n">
         <v>1000</v>
       </c>
       <c r="BS2" t="n">
-        <v>1.18</v>
+        <v>1.55</v>
       </c>
       <c r="BT2" t="n">
         <v>1000</v>
       </c>
       <c r="BU2" t="n">
-        <v>1.2</v>
+        <v>8.4</v>
       </c>
       <c r="BV2" t="n">
         <v>1000</v>
       </c>
       <c r="BW2" t="n">
-        <v>1.18</v>
+        <v>2.82</v>
       </c>
       <c r="BX2" t="n">
         <v>1000</v>
       </c>
       <c r="BY2" t="n">
-        <v>1.16</v>
+        <v>2.94</v>
       </c>
       <c r="BZ2" t="n">
         <v>1000</v>
       </c>
       <c r="CA2" t="n">
-        <v>1.13</v>
+        <v>3.05</v>
       </c>
       <c r="CB2" t="inlineStr">
         <is>
-          <t>2026-06-11 22:37:56</t>
+          <t>2026-06-12 00:53:26</t>
         </is>
       </c>
     </row>
@@ -1111,64 +1111,64 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>2.56</v>
+        <v>2.64</v>
       </c>
       <c r="G3" t="n">
-        <v>2.78</v>
+        <v>2.8</v>
       </c>
       <c r="H3" t="n">
-        <v>2.66</v>
+        <v>2.7</v>
       </c>
       <c r="I3" t="n">
-        <v>2.9</v>
+        <v>2.86</v>
       </c>
       <c r="J3" t="n">
+        <v>3.65</v>
+      </c>
+      <c r="K3" t="n">
         <v>3.7</v>
       </c>
-      <c r="K3" t="n">
-        <v>4.1</v>
-      </c>
       <c r="L3" t="n">
-        <v>1.01</v>
+        <v>1.28</v>
       </c>
       <c r="M3" t="n">
         <v>1.05</v>
       </c>
       <c r="N3" t="n">
-        <v>4.5</v>
+        <v>4.6</v>
       </c>
       <c r="O3" t="n">
-        <v>1.25</v>
+        <v>1.23</v>
       </c>
       <c r="P3" t="n">
-        <v>2.22</v>
+        <v>2.28</v>
       </c>
       <c r="Q3" t="n">
-        <v>1.7</v>
+        <v>1.69</v>
       </c>
       <c r="R3" t="n">
-        <v>1.48</v>
+        <v>1.5</v>
       </c>
       <c r="S3" t="n">
-        <v>2.8</v>
+        <v>2.72</v>
       </c>
       <c r="T3" t="n">
-        <v>1.61</v>
+        <v>1.6</v>
       </c>
       <c r="U3" t="n">
-        <v>2.4</v>
+        <v>2.46</v>
       </c>
       <c r="V3" t="n">
-        <v>1.53</v>
+        <v>1.54</v>
       </c>
       <c r="W3" t="n">
         <v>1.56</v>
       </c>
       <c r="X3" t="n">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="Y3" t="n">
-        <v>14</v>
+        <v>14.5</v>
       </c>
       <c r="Z3" t="n">
         <v>25</v>
@@ -1177,7 +1177,7 @@
         <v>50</v>
       </c>
       <c r="AB3" t="n">
-        <v>14</v>
+        <v>14.5</v>
       </c>
       <c r="AC3" t="n">
         <v>9.199999999999999</v>
@@ -1186,10 +1186,10 @@
         <v>15.5</v>
       </c>
       <c r="AE3" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="AF3" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="AG3" t="n">
         <v>15</v>
@@ -1204,37 +1204,37 @@
         <v>46</v>
       </c>
       <c r="AK3" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="AL3" t="n">
         <v>44</v>
       </c>
       <c r="AM3" t="n">
-        <v>500</v>
+        <v>200</v>
       </c>
       <c r="AN3" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AO3" t="n">
-        <v>24</v>
+        <v>19.5</v>
       </c>
       <c r="AP3" t="n">
-        <v>13.5</v>
+        <v>17</v>
       </c>
       <c r="AQ3" t="n">
         <v>10</v>
       </c>
       <c r="AR3" t="n">
-        <v>14.5</v>
+        <v>18</v>
       </c>
       <c r="AS3" t="n">
-        <v>5.9</v>
+        <v>18</v>
       </c>
       <c r="AT3" t="n">
         <v>9.800000000000001</v>
       </c>
       <c r="AU3" t="n">
-        <v>7.8</v>
+        <v>8</v>
       </c>
       <c r="AV3" t="n">
         <v>9.4</v>
@@ -1243,19 +1243,19 @@
         <v>20</v>
       </c>
       <c r="AX3" t="n">
-        <v>14</v>
+        <v>17.5</v>
       </c>
       <c r="AY3" t="n">
-        <v>9</v>
+        <v>10.5</v>
       </c>
       <c r="AZ3" t="n">
-        <v>11.5</v>
+        <v>13</v>
       </c>
       <c r="BA3" t="n">
         <v>18</v>
       </c>
       <c r="BB3" t="n">
-        <v>18</v>
+        <v>6.8</v>
       </c>
       <c r="BC3" t="n">
         <v>19.5</v>
@@ -1264,77 +1264,77 @@
         <v>18</v>
       </c>
       <c r="BE3" t="n">
-        <v>5.6</v>
+        <v>5.9</v>
       </c>
       <c r="BF3" t="n">
-        <v>13.5</v>
+        <v>15.5</v>
       </c>
       <c r="BG3" t="n">
-        <v>15</v>
+        <v>16.5</v>
       </c>
       <c r="BH3" t="n">
-        <v>1000</v>
+        <v>3.9</v>
       </c>
       <c r="BI3" t="n">
-        <v>1.04</v>
+        <v>3.05</v>
       </c>
       <c r="BJ3" t="n">
-        <v>1000</v>
+        <v>9</v>
       </c>
       <c r="BK3" t="n">
-        <v>1.04</v>
+        <v>6.4</v>
       </c>
       <c r="BL3" t="n">
         <v>1000</v>
       </c>
       <c r="BM3" t="n">
-        <v>1.04</v>
+        <v>12</v>
       </c>
       <c r="BN3" t="n">
-        <v>1000</v>
+        <v>6</v>
       </c>
       <c r="BO3" t="n">
-        <v>1.04</v>
+        <v>5.2</v>
       </c>
       <c r="BP3" t="n">
-        <v>1000</v>
+        <v>19</v>
       </c>
       <c r="BQ3" t="n">
-        <v>1.04</v>
+        <v>8</v>
       </c>
       <c r="BR3" t="n">
-        <v>1000</v>
+        <v>28</v>
       </c>
       <c r="BS3" t="n">
-        <v>1.04</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BT3" t="n">
-        <v>1000</v>
+        <v>6.2</v>
       </c>
       <c r="BU3" t="n">
-        <v>1.04</v>
+        <v>4.6</v>
       </c>
       <c r="BV3" t="n">
-        <v>1000</v>
+        <v>19.5</v>
       </c>
       <c r="BW3" t="n">
-        <v>1.04</v>
+        <v>8</v>
       </c>
       <c r="BX3" t="n">
-        <v>1000</v>
+        <v>29</v>
       </c>
       <c r="BY3" t="n">
-        <v>1.04</v>
+        <v>9.4</v>
       </c>
       <c r="BZ3" t="n">
-        <v>1000</v>
+        <v>21</v>
       </c>
       <c r="CA3" t="n">
-        <v>1.04</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="CB3" t="inlineStr">
         <is>
-          <t>2026-06-11 22:37:56</t>
+          <t>2026-06-12 00:53:26</t>
         </is>
       </c>
     </row>
@@ -1365,31 +1365,31 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>2.86</v>
+        <v>2.94</v>
       </c>
       <c r="G4" t="n">
-        <v>3.35</v>
+        <v>3.45</v>
       </c>
       <c r="H4" t="n">
         <v>2.92</v>
       </c>
       <c r="I4" t="n">
-        <v>3.45</v>
+        <v>3.35</v>
       </c>
       <c r="J4" t="n">
         <v>2.56</v>
       </c>
       <c r="K4" t="n">
-        <v>3.05</v>
+        <v>2.98</v>
       </c>
       <c r="L4" t="n">
-        <v>1.01</v>
+        <v>1.57</v>
       </c>
       <c r="M4" t="n">
         <v>1.15</v>
       </c>
       <c r="N4" t="n">
-        <v>2.26</v>
+        <v>2.28</v>
       </c>
       <c r="O4" t="n">
         <v>1.61</v>
@@ -1407,7 +1407,7 @@
         <v>6</v>
       </c>
       <c r="T4" t="n">
-        <v>2.14</v>
+        <v>2.16</v>
       </c>
       <c r="U4" t="n">
         <v>1.68</v>
@@ -1416,22 +1416,22 @@
         <v>1.43</v>
       </c>
       <c r="W4" t="n">
-        <v>1.42</v>
+        <v>1.4</v>
       </c>
       <c r="X4" t="n">
         <v>16.5</v>
       </c>
       <c r="Y4" t="n">
+        <v>500</v>
+      </c>
+      <c r="Z4" t="n">
         <v>970</v>
-      </c>
-      <c r="Z4" t="n">
-        <v>500</v>
       </c>
       <c r="AA4" t="n">
         <v>500</v>
       </c>
       <c r="AB4" t="n">
-        <v>16.5</v>
+        <v>500</v>
       </c>
       <c r="AC4" t="n">
         <v>15</v>
@@ -1443,10 +1443,10 @@
         <v>500</v>
       </c>
       <c r="AF4" t="n">
-        <v>970</v>
+        <v>500</v>
       </c>
       <c r="AG4" t="n">
-        <v>970</v>
+        <v>500</v>
       </c>
       <c r="AH4" t="n">
         <v>500</v>
@@ -1455,7 +1455,7 @@
         <v>500</v>
       </c>
       <c r="AJ4" t="n">
-        <v>500</v>
+        <v>420</v>
       </c>
       <c r="AK4" t="n">
         <v>500</v>
@@ -1467,10 +1467,10 @@
         <v>500</v>
       </c>
       <c r="AN4" t="n">
-        <v>500</v>
+        <v>600</v>
       </c>
       <c r="AO4" t="n">
-        <v>500</v>
+        <v>600</v>
       </c>
       <c r="AP4" t="n">
         <v>6</v>
@@ -1479,13 +1479,13 @@
         <v>6.4</v>
       </c>
       <c r="AR4" t="n">
-        <v>6.4</v>
+        <v>8.4</v>
       </c>
       <c r="AS4" t="n">
-        <v>2.92</v>
+        <v>3.55</v>
       </c>
       <c r="AT4" t="n">
-        <v>4.3</v>
+        <v>4.6</v>
       </c>
       <c r="AU4" t="n">
         <v>5.5</v>
@@ -1494,101 +1494,101 @@
         <v>8.4</v>
       </c>
       <c r="AW4" t="n">
-        <v>2.9</v>
+        <v>4.6</v>
       </c>
       <c r="AX4" t="n">
-        <v>6.4</v>
+        <v>6.8</v>
       </c>
       <c r="AY4" t="n">
-        <v>5.9</v>
+        <v>6.2</v>
       </c>
       <c r="AZ4" t="n">
-        <v>6.4</v>
+        <v>7.2</v>
       </c>
       <c r="BA4" t="n">
-        <v>3</v>
+        <v>3.65</v>
       </c>
       <c r="BB4" t="n">
-        <v>2.9</v>
+        <v>4.6</v>
       </c>
       <c r="BC4" t="n">
-        <v>2.94</v>
+        <v>4.5</v>
       </c>
       <c r="BD4" t="n">
-        <v>2.7</v>
+        <v>3.55</v>
       </c>
       <c r="BE4" t="n">
-        <v>8.199999999999999</v>
+        <v>7.4</v>
       </c>
       <c r="BF4" t="n">
-        <v>7.6</v>
+        <v>8</v>
       </c>
       <c r="BG4" t="n">
-        <v>7.6</v>
+        <v>8</v>
       </c>
       <c r="BH4" t="n">
-        <v>2.94</v>
+        <v>2.6</v>
       </c>
       <c r="BI4" t="n">
-        <v>2.04</v>
+        <v>2.26</v>
       </c>
       <c r="BJ4" t="n">
         <v>1000</v>
       </c>
       <c r="BK4" t="n">
-        <v>1.53</v>
+        <v>5.7</v>
       </c>
       <c r="BL4" t="n">
         <v>1000</v>
       </c>
       <c r="BM4" t="n">
-        <v>1.53</v>
+        <v>1.32</v>
       </c>
       <c r="BN4" t="n">
-        <v>1000</v>
+        <v>12.5</v>
       </c>
       <c r="BO4" t="n">
-        <v>1.53</v>
+        <v>3.8</v>
       </c>
       <c r="BP4" t="n">
         <v>1000</v>
       </c>
       <c r="BQ4" t="n">
-        <v>1.53</v>
+        <v>1.96</v>
       </c>
       <c r="BR4" t="n">
         <v>1000</v>
       </c>
       <c r="BS4" t="n">
-        <v>1.53</v>
+        <v>2.02</v>
       </c>
       <c r="BT4" t="n">
-        <v>1000</v>
+        <v>13</v>
       </c>
       <c r="BU4" t="n">
-        <v>1.53</v>
+        <v>3.9</v>
       </c>
       <c r="BV4" t="n">
         <v>1000</v>
       </c>
       <c r="BW4" t="n">
-        <v>1.53</v>
+        <v>1.96</v>
       </c>
       <c r="BX4" t="n">
         <v>1000</v>
       </c>
       <c r="BY4" t="n">
-        <v>1.53</v>
+        <v>1.9</v>
       </c>
       <c r="BZ4" t="n">
         <v>1000</v>
       </c>
       <c r="CA4" t="n">
-        <v>1.53</v>
+        <v>1.91</v>
       </c>
       <c r="CB4" t="inlineStr">
         <is>
-          <t>2026-06-11 22:37:56</t>
+          <t>2026-06-12 00:53:26</t>
         </is>
       </c>
     </row>
@@ -1619,16 +1619,16 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>2.26</v>
+        <v>2.28</v>
       </c>
       <c r="G5" t="n">
-        <v>2.38</v>
+        <v>2.46</v>
       </c>
       <c r="H5" t="n">
-        <v>4</v>
+        <v>3.9</v>
       </c>
       <c r="I5" t="n">
-        <v>4.4</v>
+        <v>4.2</v>
       </c>
       <c r="J5" t="n">
         <v>2.94</v>
@@ -1637,22 +1637,22 @@
         <v>3.15</v>
       </c>
       <c r="L5" t="n">
-        <v>1.48</v>
+        <v>1.59</v>
       </c>
       <c r="M5" t="n">
         <v>1.13</v>
       </c>
       <c r="N5" t="n">
-        <v>2.46</v>
+        <v>2.48</v>
       </c>
       <c r="O5" t="n">
         <v>1.57</v>
       </c>
       <c r="P5" t="n">
-        <v>1.49</v>
+        <v>1.5</v>
       </c>
       <c r="Q5" t="n">
-        <v>2.68</v>
+        <v>2.72</v>
       </c>
       <c r="R5" t="n">
         <v>1.18</v>
@@ -1661,61 +1661,61 @@
         <v>5.8</v>
       </c>
       <c r="T5" t="n">
-        <v>2.18</v>
+        <v>2.14</v>
       </c>
       <c r="U5" t="n">
-        <v>1.72</v>
+        <v>1.73</v>
       </c>
       <c r="V5" t="n">
-        <v>1.3</v>
+        <v>1.31</v>
       </c>
       <c r="W5" t="n">
-        <v>1.72</v>
+        <v>1.69</v>
       </c>
       <c r="X5" t="n">
-        <v>8.4</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="Y5" t="n">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="Z5" t="n">
-        <v>34</v>
+        <v>100</v>
       </c>
       <c r="AA5" t="n">
         <v>900</v>
       </c>
       <c r="AB5" t="n">
-        <v>7</v>
+        <v>7.4</v>
       </c>
       <c r="AC5" t="n">
         <v>7.4</v>
       </c>
       <c r="AD5" t="n">
-        <v>19</v>
+        <v>32</v>
       </c>
       <c r="AE5" t="n">
         <v>500</v>
       </c>
       <c r="AF5" t="n">
-        <v>13</v>
+        <v>13.5</v>
       </c>
       <c r="AG5" t="n">
         <v>12.5</v>
       </c>
       <c r="AH5" t="n">
-        <v>80</v>
+        <v>950</v>
       </c>
       <c r="AI5" t="n">
         <v>540</v>
       </c>
       <c r="AJ5" t="n">
-        <v>38</v>
+        <v>150</v>
       </c>
       <c r="AK5" t="n">
-        <v>110</v>
+        <v>80</v>
       </c>
       <c r="AL5" t="n">
-        <v>170</v>
+        <v>500</v>
       </c>
       <c r="AM5" t="n">
         <v>500</v>
@@ -1724,125 +1724,125 @@
         <v>40</v>
       </c>
       <c r="AO5" t="n">
-        <v>500</v>
+        <v>600</v>
       </c>
       <c r="AP5" t="n">
-        <v>4.5</v>
+        <v>7</v>
       </c>
       <c r="AQ5" t="n">
-        <v>5.6</v>
+        <v>9</v>
       </c>
       <c r="AR5" t="n">
-        <v>7.6</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AS5" t="n">
-        <v>9.199999999999999</v>
+        <v>10.5</v>
       </c>
       <c r="AT5" t="n">
-        <v>4.1</v>
+        <v>6</v>
       </c>
       <c r="AU5" t="n">
-        <v>4.2</v>
+        <v>6.2</v>
       </c>
       <c r="AV5" t="n">
-        <v>6.4</v>
+        <v>7.2</v>
       </c>
       <c r="AW5" t="n">
-        <v>8.800000000000001</v>
+        <v>10</v>
       </c>
       <c r="AX5" t="n">
         <v>6.2</v>
       </c>
       <c r="AY5" t="n">
-        <v>7</v>
+        <v>10.5</v>
       </c>
       <c r="AZ5" t="n">
+        <v>8</v>
+      </c>
+      <c r="BA5" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="BB5" t="n">
+        <v>9</v>
+      </c>
+      <c r="BC5" t="n">
+        <v>9</v>
+      </c>
+      <c r="BD5" t="n">
+        <v>28</v>
+      </c>
+      <c r="BE5" t="n">
+        <v>11</v>
+      </c>
+      <c r="BF5" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="BG5" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="BH5" t="n">
+        <v>2.68</v>
+      </c>
+      <c r="BI5" t="n">
+        <v>2.24</v>
+      </c>
+      <c r="BJ5" t="n">
+        <v>12</v>
+      </c>
+      <c r="BK5" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="BL5" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BM5" t="n">
+        <v>13</v>
+      </c>
+      <c r="BN5" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="BO5" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="BP5" t="n">
+        <v>21</v>
+      </c>
+      <c r="BQ5" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="BR5" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BS5" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="BT5" t="n">
         <v>7.2</v>
       </c>
-      <c r="BA5" t="n">
-        <v>9</v>
-      </c>
-      <c r="BB5" t="n">
-        <v>7.8</v>
-      </c>
-      <c r="BC5" t="n">
-        <v>7.6</v>
-      </c>
-      <c r="BD5" t="n">
-        <v>8.800000000000001</v>
-      </c>
-      <c r="BE5" t="n">
-        <v>9.6</v>
-      </c>
-      <c r="BF5" t="n">
-        <v>8</v>
-      </c>
-      <c r="BG5" t="n">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="BH5" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BI5" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="BJ5" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BK5" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="BL5" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BM5" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="BN5" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BO5" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="BP5" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BQ5" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="BR5" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BS5" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="BT5" t="n">
-        <v>1000</v>
-      </c>
       <c r="BU5" t="n">
-        <v>1.04</v>
+        <v>5.5</v>
       </c>
       <c r="BV5" t="n">
         <v>1000</v>
       </c>
       <c r="BW5" t="n">
-        <v>1.04</v>
+        <v>10.5</v>
       </c>
       <c r="BX5" t="n">
         <v>1000</v>
       </c>
       <c r="BY5" t="n">
-        <v>1.04</v>
+        <v>11.5</v>
       </c>
       <c r="BZ5" t="n">
         <v>1000</v>
       </c>
       <c r="CA5" t="n">
-        <v>1.04</v>
+        <v>11</v>
       </c>
       <c r="CB5" t="inlineStr">
         <is>
-          <t>2026-06-11 22:37:56</t>
+          <t>2026-06-12 00:53:26</t>
         </is>
       </c>
     </row>
@@ -1873,46 +1873,46 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>3.35</v>
+        <v>3.3</v>
       </c>
       <c r="G6" t="n">
-        <v>3.7</v>
+        <v>3.55</v>
       </c>
       <c r="H6" t="n">
-        <v>2.22</v>
+        <v>2.24</v>
       </c>
       <c r="I6" t="n">
-        <v>2.36</v>
+        <v>2.38</v>
       </c>
       <c r="J6" t="n">
         <v>3.5</v>
       </c>
       <c r="K6" t="n">
-        <v>3.75</v>
+        <v>3.8</v>
       </c>
       <c r="L6" t="n">
-        <v>1.31</v>
+        <v>1.38</v>
       </c>
       <c r="M6" t="n">
         <v>1.06</v>
       </c>
       <c r="N6" t="n">
-        <v>3.9</v>
+        <v>3.95</v>
       </c>
       <c r="O6" t="n">
-        <v>1.3</v>
+        <v>1.29</v>
       </c>
       <c r="P6" t="n">
-        <v>2</v>
+        <v>2.02</v>
       </c>
       <c r="Q6" t="n">
         <v>1.85</v>
       </c>
       <c r="R6" t="n">
-        <v>1.38</v>
+        <v>1.4</v>
       </c>
       <c r="S6" t="n">
-        <v>3.25</v>
+        <v>3.15</v>
       </c>
       <c r="T6" t="n">
         <v>1.74</v>
@@ -1924,7 +1924,7 @@
         <v>1.73</v>
       </c>
       <c r="W6" t="n">
-        <v>1.37</v>
+        <v>1.39</v>
       </c>
       <c r="X6" t="n">
         <v>18.5</v>
@@ -1933,7 +1933,7 @@
         <v>12.5</v>
       </c>
       <c r="Z6" t="n">
-        <v>15</v>
+        <v>15.5</v>
       </c>
       <c r="AA6" t="n">
         <v>65</v>
@@ -1954,7 +1954,7 @@
         <v>25</v>
       </c>
       <c r="AG6" t="n">
-        <v>15</v>
+        <v>14.5</v>
       </c>
       <c r="AH6" t="n">
         <v>17</v>
@@ -1981,10 +1981,10 @@
         <v>17</v>
       </c>
       <c r="AP6" t="n">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="AQ6" t="n">
-        <v>7.6</v>
+        <v>9.6</v>
       </c>
       <c r="AR6" t="n">
         <v>10.5</v>
@@ -1996,10 +1996,10 @@
         <v>10</v>
       </c>
       <c r="AU6" t="n">
-        <v>6.2</v>
+        <v>7.4</v>
       </c>
       <c r="AV6" t="n">
-        <v>8.199999999999999</v>
+        <v>10</v>
       </c>
       <c r="AW6" t="n">
         <v>17</v>
@@ -2020,13 +2020,13 @@
         <v>6.8</v>
       </c>
       <c r="BC6" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="BD6" t="n">
         <v>7</v>
       </c>
-      <c r="BD6" t="n">
-        <v>6.8</v>
-      </c>
       <c r="BE6" t="n">
-        <v>7</v>
+        <v>7.2</v>
       </c>
       <c r="BF6" t="n">
         <v>7.4</v>
@@ -2035,68 +2035,68 @@
         <v>12.5</v>
       </c>
       <c r="BH6" t="n">
-        <v>1000</v>
+        <v>3.6</v>
       </c>
       <c r="BI6" t="n">
-        <v>1.04</v>
+        <v>2.94</v>
       </c>
       <c r="BJ6" t="n">
-        <v>1000</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BK6" t="n">
-        <v>1.04</v>
+        <v>5.8</v>
       </c>
       <c r="BL6" t="n">
         <v>1000</v>
       </c>
       <c r="BM6" t="n">
-        <v>1.04</v>
+        <v>14</v>
       </c>
       <c r="BN6" t="n">
-        <v>1000</v>
+        <v>6.8</v>
       </c>
       <c r="BO6" t="n">
-        <v>1.04</v>
+        <v>5</v>
       </c>
       <c r="BP6" t="n">
-        <v>1000</v>
+        <v>27</v>
       </c>
       <c r="BQ6" t="n">
-        <v>1.04</v>
+        <v>10</v>
       </c>
       <c r="BR6" t="n">
-        <v>1000</v>
+        <v>36</v>
       </c>
       <c r="BS6" t="n">
-        <v>1.04</v>
+        <v>11</v>
       </c>
       <c r="BT6" t="n">
-        <v>1000</v>
+        <v>5.2</v>
       </c>
       <c r="BU6" t="n">
-        <v>1.04</v>
+        <v>4</v>
       </c>
       <c r="BV6" t="n">
-        <v>1000</v>
+        <v>16.5</v>
       </c>
       <c r="BW6" t="n">
-        <v>1.04</v>
+        <v>12.5</v>
       </c>
       <c r="BX6" t="n">
         <v>1000</v>
       </c>
       <c r="BY6" t="n">
-        <v>1.04</v>
+        <v>10</v>
       </c>
       <c r="BZ6" t="n">
-        <v>1000</v>
+        <v>24</v>
       </c>
       <c r="CA6" t="n">
-        <v>1.04</v>
+        <v>9.6</v>
       </c>
       <c r="CB6" t="inlineStr">
         <is>
-          <t>2026-06-11 22:37:56</t>
+          <t>2026-06-12 00:53:26</t>
         </is>
       </c>
     </row>
@@ -2127,10 +2127,10 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>1.61</v>
+        <v>1.63</v>
       </c>
       <c r="G7" t="n">
-        <v>1.8</v>
+        <v>1.77</v>
       </c>
       <c r="H7" t="n">
         <v>4.7</v>
@@ -2139,10 +2139,10 @@
         <v>6.4</v>
       </c>
       <c r="J7" t="n">
-        <v>3.45</v>
+        <v>3.55</v>
       </c>
       <c r="K7" t="n">
-        <v>4.7</v>
+        <v>4.6</v>
       </c>
       <c r="L7" t="n">
         <v>1.01</v>
@@ -2154,34 +2154,34 @@
         <v>3.9</v>
       </c>
       <c r="O7" t="n">
-        <v>1.25</v>
+        <v>1.26</v>
       </c>
       <c r="P7" t="n">
-        <v>2.02</v>
+        <v>1.98</v>
       </c>
       <c r="Q7" t="n">
-        <v>1.65</v>
+        <v>1.74</v>
       </c>
       <c r="R7" t="n">
-        <v>1.4</v>
+        <v>1.41</v>
       </c>
       <c r="S7" t="n">
         <v>2.66</v>
       </c>
       <c r="T7" t="n">
-        <v>1.76</v>
+        <v>1.79</v>
       </c>
       <c r="U7" t="n">
-        <v>2</v>
+        <v>2.02</v>
       </c>
       <c r="V7" t="n">
         <v>1.18</v>
       </c>
       <c r="W7" t="n">
-        <v>2.24</v>
+        <v>2.28</v>
       </c>
       <c r="X7" t="n">
-        <v>19</v>
+        <v>18.5</v>
       </c>
       <c r="Y7" t="n">
         <v>22</v>
@@ -2193,22 +2193,22 @@
         <v>700</v>
       </c>
       <c r="AB7" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="AC7" t="n">
         <v>10</v>
       </c>
-      <c r="AC7" t="n">
-        <v>10.5</v>
-      </c>
       <c r="AD7" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AE7" t="n">
         <v>700</v>
       </c>
       <c r="AF7" t="n">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="AG7" t="n">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="AH7" t="n">
         <v>22</v>
@@ -2217,10 +2217,10 @@
         <v>700</v>
       </c>
       <c r="AJ7" t="n">
-        <v>18.5</v>
+        <v>17.5</v>
       </c>
       <c r="AK7" t="n">
-        <v>18.5</v>
+        <v>18</v>
       </c>
       <c r="AL7" t="n">
         <v>80</v>
@@ -2229,64 +2229,64 @@
         <v>580</v>
       </c>
       <c r="AN7" t="n">
-        <v>10</v>
+        <v>9.6</v>
       </c>
       <c r="AO7" t="n">
         <v>700</v>
       </c>
       <c r="AP7" t="n">
-        <v>5.7</v>
+        <v>6.6</v>
       </c>
       <c r="AQ7" t="n">
-        <v>5.9</v>
+        <v>7</v>
       </c>
       <c r="AR7" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="AS7" t="n">
+        <v>9</v>
+      </c>
+      <c r="AT7" t="n">
+        <v>5</v>
+      </c>
+      <c r="AU7" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="AV7" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="AW7" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="AX7" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="AY7" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="AZ7" t="n">
         <v>7</v>
       </c>
-      <c r="AS7" t="n">
-        <v>7.8</v>
-      </c>
-      <c r="AT7" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="AU7" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="AV7" t="n">
-        <v>6</v>
-      </c>
-      <c r="AW7" t="n">
-        <v>7.4</v>
-      </c>
-      <c r="AX7" t="n">
-        <v>4.7</v>
-      </c>
-      <c r="AY7" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="AZ7" t="n">
-        <v>5.9</v>
-      </c>
       <c r="BA7" t="n">
-        <v>7.4</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BB7" t="n">
-        <v>5.6</v>
+        <v>6.6</v>
       </c>
       <c r="BC7" t="n">
-        <v>5.6</v>
+        <v>6.6</v>
       </c>
       <c r="BD7" t="n">
-        <v>6.6</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BE7" t="n">
-        <v>7.6</v>
+        <v>8.6</v>
       </c>
       <c r="BF7" t="n">
-        <v>4.5</v>
+        <v>5</v>
       </c>
       <c r="BG7" t="n">
-        <v>7.4</v>
+        <v>8.6</v>
       </c>
       <c r="BH7" t="n">
         <v>1000</v>
@@ -2350,7 +2350,7 @@
       </c>
       <c r="CB7" t="inlineStr">
         <is>
-          <t>2026-06-11 22:37:56</t>
+          <t>2026-06-12 00:53:26</t>
         </is>
       </c>
     </row>
@@ -2381,19 +2381,19 @@
         </is>
       </c>
       <c r="F8" t="n">
-        <v>1.62</v>
+        <v>1.63</v>
       </c>
       <c r="G8" t="n">
         <v>1.75</v>
       </c>
       <c r="H8" t="n">
-        <v>5.7</v>
+        <v>5.6</v>
       </c>
       <c r="I8" t="n">
-        <v>6.8</v>
+        <v>6.6</v>
       </c>
       <c r="J8" t="n">
-        <v>3.75</v>
+        <v>3.85</v>
       </c>
       <c r="K8" t="n">
         <v>4.4</v>
@@ -2402,31 +2402,31 @@
         <v>1.31</v>
       </c>
       <c r="M8" t="n">
-        <v>1.06</v>
+        <v>1.07</v>
       </c>
       <c r="N8" t="n">
-        <v>3.55</v>
+        <v>3.6</v>
       </c>
       <c r="O8" t="n">
-        <v>1.31</v>
+        <v>1.3</v>
       </c>
       <c r="P8" t="n">
-        <v>1.89</v>
+        <v>1.94</v>
       </c>
       <c r="Q8" t="n">
-        <v>1.91</v>
+        <v>1.9</v>
       </c>
       <c r="R8" t="n">
-        <v>1.35</v>
+        <v>1.32</v>
       </c>
       <c r="S8" t="n">
-        <v>3.35</v>
+        <v>3.3</v>
       </c>
       <c r="T8" t="n">
-        <v>1.9</v>
+        <v>1.87</v>
       </c>
       <c r="U8" t="n">
-        <v>1.92</v>
+        <v>1.94</v>
       </c>
       <c r="V8" t="n">
         <v>1.17</v>
@@ -2438,16 +2438,16 @@
         <v>18</v>
       </c>
       <c r="Y8" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="Z8" t="n">
-        <v>55</v>
+        <v>130</v>
       </c>
       <c r="AA8" t="n">
         <v>700</v>
       </c>
       <c r="AB8" t="n">
-        <v>8.4</v>
+        <v>8.6</v>
       </c>
       <c r="AC8" t="n">
         <v>11</v>
@@ -2456,7 +2456,7 @@
         <v>29</v>
       </c>
       <c r="AE8" t="n">
-        <v>110</v>
+        <v>240</v>
       </c>
       <c r="AF8" t="n">
         <v>10.5</v>
@@ -2465,40 +2465,40 @@
         <v>12</v>
       </c>
       <c r="AH8" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="AI8" t="n">
         <v>110</v>
       </c>
       <c r="AJ8" t="n">
-        <v>17.5</v>
+        <v>17</v>
       </c>
       <c r="AK8" t="n">
         <v>22</v>
       </c>
       <c r="AL8" t="n">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="AM8" t="n">
         <v>580</v>
       </c>
       <c r="AN8" t="n">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="AO8" t="n">
-        <v>140</v>
+        <v>130</v>
       </c>
       <c r="AP8" t="n">
         <v>11</v>
       </c>
       <c r="AQ8" t="n">
-        <v>16.5</v>
+        <v>17</v>
       </c>
       <c r="AR8" t="n">
-        <v>5.5</v>
+        <v>5.8</v>
       </c>
       <c r="AS8" t="n">
-        <v>6</v>
+        <v>6.2</v>
       </c>
       <c r="AT8" t="n">
         <v>7</v>
@@ -2510,7 +2510,7 @@
         <v>17</v>
       </c>
       <c r="AW8" t="n">
-        <v>5.8</v>
+        <v>6</v>
       </c>
       <c r="AX8" t="n">
         <v>7.4</v>
@@ -2522,7 +2522,7 @@
         <v>15.5</v>
       </c>
       <c r="BA8" t="n">
-        <v>5.8</v>
+        <v>6.2</v>
       </c>
       <c r="BB8" t="n">
         <v>12</v>
@@ -2531,16 +2531,16 @@
         <v>13</v>
       </c>
       <c r="BD8" t="n">
-        <v>5.5</v>
+        <v>5.7</v>
       </c>
       <c r="BE8" t="n">
-        <v>5.9</v>
+        <v>6.2</v>
       </c>
       <c r="BF8" t="n">
         <v>9</v>
       </c>
       <c r="BG8" t="n">
-        <v>5.9</v>
+        <v>6.2</v>
       </c>
       <c r="BH8" t="n">
         <v>1000</v>
@@ -2604,7 +2604,7 @@
       </c>
       <c r="CB8" t="inlineStr">
         <is>
-          <t>2026-06-11 22:37:56</t>
+          <t>2026-06-12 00:53:26</t>
         </is>
       </c>
     </row>
@@ -2668,7 +2668,7 @@
         <v>2.5</v>
       </c>
       <c r="Q9" t="n">
-        <v>1.53</v>
+        <v>1.54</v>
       </c>
       <c r="R9" t="n">
         <v>1.6</v>
@@ -2677,10 +2677,10 @@
         <v>2.32</v>
       </c>
       <c r="T9" t="n">
-        <v>1.58</v>
+        <v>1.59</v>
       </c>
       <c r="U9" t="n">
-        <v>2.42</v>
+        <v>2.38</v>
       </c>
       <c r="V9" t="n">
         <v>2.2</v>
@@ -2704,7 +2704,7 @@
         <v>50</v>
       </c>
       <c r="AC9" t="n">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="AD9" t="n">
         <v>11.5</v>
@@ -2767,7 +2767,7 @@
         <v>8.4</v>
       </c>
       <c r="AX9" t="n">
-        <v>7.2</v>
+        <v>7.4</v>
       </c>
       <c r="AY9" t="n">
         <v>16</v>
@@ -2776,19 +2776,19 @@
         <v>14</v>
       </c>
       <c r="BA9" t="n">
-        <v>6.6</v>
+        <v>6.8</v>
       </c>
       <c r="BB9" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="BC9" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="BD9" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="BE9" t="n">
         <v>8</v>
-      </c>
-      <c r="BC9" t="n">
-        <v>7.6</v>
-      </c>
-      <c r="BD9" t="n">
-        <v>7.4</v>
-      </c>
-      <c r="BE9" t="n">
-        <v>7.8</v>
       </c>
       <c r="BF9" t="n">
         <v>8.4</v>
@@ -2800,31 +2800,31 @@
         <v>5.1</v>
       </c>
       <c r="BI9" t="n">
-        <v>2.64</v>
+        <v>3.6</v>
       </c>
       <c r="BJ9" t="n">
         <v>10.5</v>
       </c>
       <c r="BK9" t="n">
-        <v>3.6</v>
+        <v>3.65</v>
       </c>
       <c r="BL9" t="n">
         <v>95</v>
       </c>
       <c r="BM9" t="n">
-        <v>5.2</v>
+        <v>5.3</v>
       </c>
       <c r="BN9" t="n">
         <v>9.800000000000001</v>
       </c>
       <c r="BO9" t="n">
-        <v>3.5</v>
+        <v>3.55</v>
       </c>
       <c r="BP9" t="n">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="BQ9" t="n">
-        <v>4.8</v>
+        <v>4.9</v>
       </c>
       <c r="BR9" t="n">
         <v>42</v>
@@ -2833,16 +2833,16 @@
         <v>4.9</v>
       </c>
       <c r="BT9" t="n">
-        <v>5.5</v>
+        <v>5.4</v>
       </c>
       <c r="BU9" t="n">
-        <v>2.76</v>
+        <v>2.74</v>
       </c>
       <c r="BV9" t="n">
         <v>12.5</v>
       </c>
       <c r="BW9" t="n">
-        <v>3.8</v>
+        <v>3.85</v>
       </c>
       <c r="BX9" t="n">
         <v>24</v>
@@ -2858,7 +2858,7 @@
       </c>
       <c r="CB9" t="inlineStr">
         <is>
-          <t>2026-06-11 22:37:56</t>
+          <t>2026-06-12 00:53:26</t>
         </is>
       </c>
     </row>
@@ -3112,7 +3112,7 @@
       </c>
       <c r="CB10" t="inlineStr">
         <is>
-          <t>2026-06-11 22:37:56</t>
+          <t>2026-06-12 00:53:26</t>
         </is>
       </c>
     </row>
@@ -3152,7 +3152,7 @@
         <v>4.2</v>
       </c>
       <c r="I11" t="n">
-        <v>4.8</v>
+        <v>4.7</v>
       </c>
       <c r="J11" t="n">
         <v>2.88</v>
@@ -3161,7 +3161,7 @@
         <v>3.15</v>
       </c>
       <c r="L11" t="n">
-        <v>1.59</v>
+        <v>1.6</v>
       </c>
       <c r="M11" t="n">
         <v>1.13</v>
@@ -3170,13 +3170,13 @@
         <v>2.52</v>
       </c>
       <c r="O11" t="n">
-        <v>1.55</v>
+        <v>1.56</v>
       </c>
       <c r="P11" t="n">
         <v>1.5</v>
       </c>
       <c r="Q11" t="n">
-        <v>2.68</v>
+        <v>2.72</v>
       </c>
       <c r="R11" t="n">
         <v>1.18</v>
@@ -3185,10 +3185,10 @@
         <v>5.7</v>
       </c>
       <c r="T11" t="n">
-        <v>2.16</v>
+        <v>2.18</v>
       </c>
       <c r="U11" t="n">
-        <v>1.73</v>
+        <v>1.71</v>
       </c>
       <c r="V11" t="n">
         <v>1.27</v>
@@ -3200,7 +3200,7 @@
         <v>8.199999999999999</v>
       </c>
       <c r="Y11" t="n">
-        <v>12</v>
+        <v>11.5</v>
       </c>
       <c r="Z11" t="n">
         <v>32</v>
@@ -3251,19 +3251,19 @@
         <v>500</v>
       </c>
       <c r="AP11" t="n">
-        <v>7.2</v>
+        <v>7</v>
       </c>
       <c r="AQ11" t="n">
-        <v>9.800000000000001</v>
+        <v>9.6</v>
       </c>
       <c r="AR11" t="n">
         <v>11.5</v>
       </c>
       <c r="AS11" t="n">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="AT11" t="n">
-        <v>6</v>
+        <v>5.9</v>
       </c>
       <c r="AU11" t="n">
         <v>6.2</v>
@@ -3272,7 +3272,7 @@
         <v>16.5</v>
       </c>
       <c r="AW11" t="n">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="AX11" t="n">
         <v>10.5</v>
@@ -3293,16 +3293,16 @@
         <v>14.5</v>
       </c>
       <c r="BD11" t="n">
-        <v>9.800000000000001</v>
+        <v>28</v>
       </c>
       <c r="BE11" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="BF11" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="BG11" t="n">
         <v>11</v>
-      </c>
-      <c r="BF11" t="n">
-        <v>9</v>
-      </c>
-      <c r="BG11" t="n">
-        <v>10.5</v>
       </c>
       <c r="BH11" t="n">
         <v>3.05</v>
@@ -3366,7 +3366,7 @@
       </c>
       <c r="CB11" t="inlineStr">
         <is>
-          <t>2026-06-11 22:37:56</t>
+          <t>2026-06-12 00:53:26</t>
         </is>
       </c>
     </row>
@@ -3397,16 +3397,16 @@
         </is>
       </c>
       <c r="F12" t="n">
-        <v>2.2</v>
+        <v>2.24</v>
       </c>
       <c r="G12" t="n">
-        <v>2.42</v>
+        <v>2.44</v>
       </c>
       <c r="H12" t="n">
-        <v>3.2</v>
+        <v>3.15</v>
       </c>
       <c r="I12" t="n">
-        <v>3.65</v>
+        <v>3.6</v>
       </c>
       <c r="J12" t="n">
         <v>3.5</v>
@@ -3415,40 +3415,40 @@
         <v>3.8</v>
       </c>
       <c r="L12" t="n">
-        <v>1.29</v>
+        <v>1.28</v>
       </c>
       <c r="M12" t="n">
         <v>1.05</v>
       </c>
       <c r="N12" t="n">
-        <v>4.2</v>
+        <v>4.3</v>
       </c>
       <c r="O12" t="n">
         <v>1.24</v>
       </c>
       <c r="P12" t="n">
-        <v>2.12</v>
+        <v>2.14</v>
       </c>
       <c r="Q12" t="n">
         <v>1.71</v>
       </c>
       <c r="R12" t="n">
-        <v>1.44</v>
+        <v>1.45</v>
       </c>
       <c r="S12" t="n">
         <v>2.8</v>
       </c>
       <c r="T12" t="n">
-        <v>1.62</v>
+        <v>1.61</v>
       </c>
       <c r="U12" t="n">
-        <v>2.28</v>
+        <v>2.3</v>
       </c>
       <c r="V12" t="n">
         <v>1.38</v>
       </c>
       <c r="W12" t="n">
-        <v>1.7</v>
+        <v>1.69</v>
       </c>
       <c r="X12" t="n">
         <v>23</v>
@@ -3469,19 +3469,19 @@
         <v>9.199999999999999</v>
       </c>
       <c r="AD12" t="n">
-        <v>15.5</v>
+        <v>15</v>
       </c>
       <c r="AE12" t="n">
         <v>55</v>
       </c>
       <c r="AF12" t="n">
-        <v>19.5</v>
+        <v>20</v>
       </c>
       <c r="AG12" t="n">
         <v>12</v>
       </c>
       <c r="AH12" t="n">
-        <v>17</v>
+        <v>16.5</v>
       </c>
       <c r="AI12" t="n">
         <v>100</v>
@@ -3502,7 +3502,7 @@
         <v>15</v>
       </c>
       <c r="AO12" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="AP12" t="n">
         <v>15.5</v>
@@ -3514,7 +3514,7 @@
         <v>19.5</v>
       </c>
       <c r="AS12" t="n">
-        <v>7</v>
+        <v>7.4</v>
       </c>
       <c r="AT12" t="n">
         <v>8.4</v>
@@ -3556,13 +3556,13 @@
         <v>10</v>
       </c>
       <c r="BG12" t="n">
-        <v>7</v>
+        <v>7.2</v>
       </c>
       <c r="BH12" t="n">
-        <v>4</v>
+        <v>4.1</v>
       </c>
       <c r="BI12" t="n">
-        <v>3</v>
+        <v>3.05</v>
       </c>
       <c r="BJ12" t="n">
         <v>9.4</v>
@@ -3574,25 +3574,25 @@
         <v>1000</v>
       </c>
       <c r="BM12" t="n">
-        <v>8.800000000000001</v>
+        <v>8.4</v>
       </c>
       <c r="BN12" t="n">
-        <v>5.6</v>
+        <v>5.7</v>
       </c>
       <c r="BO12" t="n">
         <v>4.1</v>
       </c>
       <c r="BP12" t="n">
-        <v>17</v>
+        <v>16.5</v>
       </c>
       <c r="BQ12" t="n">
-        <v>6.2</v>
+        <v>5.9</v>
       </c>
       <c r="BR12" t="n">
-        <v>28</v>
+        <v>1000</v>
       </c>
       <c r="BS12" t="n">
-        <v>7.2</v>
+        <v>6.8</v>
       </c>
       <c r="BT12" t="n">
         <v>7</v>
@@ -3604,23 +3604,23 @@
         <v>1000</v>
       </c>
       <c r="BW12" t="n">
-        <v>7</v>
+        <v>6.8</v>
       </c>
       <c r="BX12" t="n">
         <v>1000</v>
       </c>
       <c r="BY12" t="n">
-        <v>7.4</v>
+        <v>7.2</v>
       </c>
       <c r="BZ12" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="CA12" t="n">
-        <v>6.6</v>
+        <v>6.4</v>
       </c>
       <c r="CB12" t="inlineStr">
         <is>
-          <t>2026-06-11 22:37:56</t>
+          <t>2026-06-12 00:53:26</t>
         </is>
       </c>
     </row>
@@ -3669,13 +3669,13 @@
         <v>11.5</v>
       </c>
       <c r="L13" t="n">
-        <v>1.19</v>
+        <v>1.18</v>
       </c>
       <c r="M13" t="n">
         <v>1.02</v>
       </c>
       <c r="N13" t="n">
-        <v>7.2</v>
+        <v>7.4</v>
       </c>
       <c r="O13" t="n">
         <v>1.13</v>
@@ -3684,16 +3684,16 @@
         <v>3.15</v>
       </c>
       <c r="Q13" t="n">
-        <v>1.38</v>
+        <v>1.37</v>
       </c>
       <c r="R13" t="n">
-        <v>1.88</v>
+        <v>1.89</v>
       </c>
       <c r="S13" t="n">
         <v>1.95</v>
       </c>
       <c r="T13" t="n">
-        <v>2.28</v>
+        <v>2.32</v>
       </c>
       <c r="U13" t="n">
         <v>1.61</v>
@@ -3753,31 +3753,31 @@
         <v>1000</v>
       </c>
       <c r="AN13" t="n">
-        <v>3.1</v>
+        <v>2.9</v>
       </c>
       <c r="AO13" t="n">
         <v>1000</v>
       </c>
       <c r="AP13" t="n">
-        <v>5.7</v>
+        <v>6.4</v>
       </c>
       <c r="AQ13" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AR13" t="n">
-        <v>6.2</v>
+        <v>6.4</v>
       </c>
       <c r="AS13" t="n">
-        <v>6.4</v>
+        <v>6.6</v>
       </c>
       <c r="AT13" t="n">
         <v>9.6</v>
       </c>
       <c r="AU13" t="n">
-        <v>18</v>
+        <v>5.9</v>
       </c>
       <c r="AV13" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AW13" t="n">
         <v>6.4</v>
@@ -3789,10 +3789,10 @@
         <v>11</v>
       </c>
       <c r="AZ13" t="n">
-        <v>5.8</v>
+        <v>6.6</v>
       </c>
       <c r="BA13" t="n">
-        <v>6.2</v>
+        <v>6.4</v>
       </c>
       <c r="BB13" t="n">
         <v>7</v>
@@ -3801,28 +3801,28 @@
         <v>11.5</v>
       </c>
       <c r="BD13" t="n">
-        <v>5.8</v>
+        <v>6.6</v>
       </c>
       <c r="BE13" t="n">
-        <v>6.2</v>
+        <v>7.4</v>
       </c>
       <c r="BF13" t="n">
         <v>2.56</v>
       </c>
       <c r="BG13" t="n">
-        <v>6.6</v>
+        <v>7.6</v>
       </c>
       <c r="BH13" t="n">
         <v>5.8</v>
       </c>
       <c r="BI13" t="n">
-        <v>4.8</v>
+        <v>4.4</v>
       </c>
       <c r="BJ13" t="n">
-        <v>1000</v>
+        <v>16</v>
       </c>
       <c r="BK13" t="n">
-        <v>6.2</v>
+        <v>6.4</v>
       </c>
       <c r="BL13" t="n">
         <v>1000</v>
@@ -3852,7 +3852,7 @@
         <v>1000</v>
       </c>
       <c r="BU13" t="n">
-        <v>7.2</v>
+        <v>7.4</v>
       </c>
       <c r="BV13" t="n">
         <v>1000</v>
@@ -3864,7 +3864,7 @@
         <v>1000</v>
       </c>
       <c r="BY13" t="n">
-        <v>9.800000000000001</v>
+        <v>10</v>
       </c>
       <c r="BZ13" t="n">
         <v>6.8</v>
@@ -3874,7 +3874,7 @@
       </c>
       <c r="CB13" t="inlineStr">
         <is>
-          <t>2026-06-11 22:37:56</t>
+          <t>2026-06-12 00:53:26</t>
         </is>
       </c>
     </row>
@@ -3908,19 +3908,19 @@
         <v>3.8</v>
       </c>
       <c r="G14" t="n">
-        <v>4.3</v>
+        <v>4.2</v>
       </c>
       <c r="H14" t="n">
-        <v>2.02</v>
+        <v>2.08</v>
       </c>
       <c r="I14" t="n">
-        <v>2.14</v>
+        <v>2.16</v>
       </c>
       <c r="J14" t="n">
-        <v>3.35</v>
+        <v>3.4</v>
       </c>
       <c r="K14" t="n">
-        <v>3.8</v>
+        <v>3.7</v>
       </c>
       <c r="L14" t="n">
         <v>1.01</v>
@@ -3929,142 +3929,142 @@
         <v>1.08</v>
       </c>
       <c r="N14" t="n">
-        <v>3.3</v>
+        <v>3.35</v>
       </c>
       <c r="O14" t="n">
         <v>1.35</v>
       </c>
       <c r="P14" t="n">
-        <v>1.8</v>
+        <v>1.82</v>
       </c>
       <c r="Q14" t="n">
-        <v>2</v>
+        <v>2.04</v>
       </c>
       <c r="R14" t="n">
-        <v>1.3</v>
+        <v>1.31</v>
       </c>
       <c r="S14" t="n">
         <v>4</v>
       </c>
       <c r="T14" t="n">
-        <v>1.84</v>
+        <v>1.86</v>
       </c>
       <c r="U14" t="n">
-        <v>1.97</v>
+        <v>2.02</v>
       </c>
       <c r="V14" t="n">
         <v>1.87</v>
       </c>
       <c r="W14" t="n">
-        <v>1.31</v>
+        <v>1.32</v>
       </c>
       <c r="X14" t="n">
         <v>13.5</v>
       </c>
       <c r="Y14" t="n">
-        <v>9</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="Z14" t="n">
         <v>12.5</v>
       </c>
       <c r="AA14" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="AB14" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="AC14" t="n">
-        <v>8.4</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AD14" t="n">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="AE14" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AF14" t="n">
         <v>34</v>
       </c>
       <c r="AG14" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="AH14" t="n">
-        <v>20</v>
+        <v>19.5</v>
       </c>
       <c r="AI14" t="n">
-        <v>44</v>
+        <v>100</v>
       </c>
       <c r="AJ14" t="n">
         <v>900</v>
       </c>
       <c r="AK14" t="n">
-        <v>65</v>
+        <v>230</v>
       </c>
       <c r="AL14" t="n">
-        <v>160</v>
+        <v>370</v>
       </c>
       <c r="AM14" t="n">
-        <v>440</v>
+        <v>580</v>
       </c>
       <c r="AN14" t="n">
         <v>240</v>
       </c>
       <c r="AO14" t="n">
-        <v>16.5</v>
+        <v>17</v>
       </c>
       <c r="AP14" t="n">
-        <v>6.2</v>
+        <v>6.8</v>
       </c>
       <c r="AQ14" t="n">
-        <v>5.1</v>
+        <v>5.3</v>
       </c>
       <c r="AR14" t="n">
         <v>6.4</v>
       </c>
       <c r="AS14" t="n">
-        <v>6.8</v>
+        <v>8.6</v>
       </c>
       <c r="AT14" t="n">
-        <v>6.2</v>
+        <v>7</v>
       </c>
       <c r="AU14" t="n">
-        <v>4.9</v>
+        <v>5.1</v>
       </c>
       <c r="AV14" t="n">
         <v>7</v>
       </c>
       <c r="AW14" t="n">
-        <v>6.8</v>
+        <v>8.6</v>
       </c>
       <c r="AX14" t="n">
-        <v>7.4</v>
+        <v>9.6</v>
       </c>
       <c r="AY14" t="n">
-        <v>6.2</v>
+        <v>7.6</v>
       </c>
       <c r="AZ14" t="n">
-        <v>6.4</v>
+        <v>8</v>
       </c>
       <c r="BA14" t="n">
-        <v>7.8</v>
+        <v>10</v>
       </c>
       <c r="BB14" t="n">
-        <v>8.800000000000001</v>
+        <v>12</v>
       </c>
       <c r="BC14" t="n">
-        <v>8.4</v>
+        <v>11</v>
       </c>
       <c r="BD14" t="n">
-        <v>8.4</v>
+        <v>11</v>
       </c>
       <c r="BE14" t="n">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="BF14" t="n">
-        <v>8.6</v>
+        <v>11</v>
       </c>
       <c r="BG14" t="n">
-        <v>6</v>
+        <v>7.6</v>
       </c>
       <c r="BH14" t="n">
         <v>1000</v>
@@ -4128,7 +4128,7 @@
       </c>
       <c r="CB14" t="inlineStr">
         <is>
-          <t>2026-06-11 22:37:56</t>
+          <t>2026-06-12 00:53:26</t>
         </is>
       </c>
     </row>
@@ -4382,7 +4382,7 @@
       </c>
       <c r="CB15" t="inlineStr">
         <is>
-          <t>2026-06-11 22:37:56</t>
+          <t>2026-06-12 00:53:26</t>
         </is>
       </c>
     </row>
@@ -4434,7 +4434,7 @@
         <v>1.01</v>
       </c>
       <c r="M16" t="n">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="N16" t="n">
         <v>4.8</v>
@@ -4446,7 +4446,7 @@
         <v>2.32</v>
       </c>
       <c r="Q16" t="n">
-        <v>1.68</v>
+        <v>1.67</v>
       </c>
       <c r="R16" t="n">
         <v>1.5</v>
@@ -4455,7 +4455,7 @@
         <v>2.68</v>
       </c>
       <c r="T16" t="n">
-        <v>1.59</v>
+        <v>1.58</v>
       </c>
       <c r="U16" t="n">
         <v>2.52</v>
@@ -4518,7 +4518,7 @@
         <v>22</v>
       </c>
       <c r="AO16" t="n">
-        <v>18.5</v>
+        <v>15.5</v>
       </c>
       <c r="AP16" t="n">
         <v>17</v>
@@ -4557,7 +4557,7 @@
         <v>14.5</v>
       </c>
       <c r="BB16" t="n">
-        <v>7</v>
+        <v>7.6</v>
       </c>
       <c r="BC16" t="n">
         <v>14.5</v>
@@ -4566,7 +4566,7 @@
         <v>16</v>
       </c>
       <c r="BE16" t="n">
-        <v>7.4</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BF16" t="n">
         <v>17.5</v>
@@ -4636,7 +4636,7 @@
       </c>
       <c r="CB16" t="inlineStr">
         <is>
-          <t>2026-06-11 22:37:56</t>
+          <t>2026-06-12 00:53:26</t>
         </is>
       </c>
     </row>
@@ -4670,7 +4670,7 @@
         <v>1.37</v>
       </c>
       <c r="G17" t="n">
-        <v>1.4</v>
+        <v>1.41</v>
       </c>
       <c r="H17" t="n">
         <v>10.5</v>
@@ -4679,10 +4679,10 @@
         <v>12</v>
       </c>
       <c r="J17" t="n">
-        <v>5.1</v>
+        <v>5</v>
       </c>
       <c r="K17" t="n">
-        <v>5.5</v>
+        <v>5.4</v>
       </c>
       <c r="L17" t="n">
         <v>1.01</v>
@@ -4706,7 +4706,7 @@
         <v>1.41</v>
       </c>
       <c r="S17" t="n">
-        <v>3.2</v>
+        <v>3.15</v>
       </c>
       <c r="T17" t="n">
         <v>2.22</v>
@@ -4772,31 +4772,31 @@
         <v>7</v>
       </c>
       <c r="AO17" t="n">
-        <v>340</v>
+        <v>310</v>
       </c>
       <c r="AP17" t="n">
         <v>15</v>
       </c>
       <c r="AQ17" t="n">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="AR17" t="n">
         <v>28</v>
       </c>
       <c r="AS17" t="n">
-        <v>12</v>
+        <v>11.5</v>
       </c>
       <c r="AT17" t="n">
-        <v>6.6</v>
+        <v>7</v>
       </c>
       <c r="AU17" t="n">
         <v>10.5</v>
       </c>
       <c r="AV17" t="n">
-        <v>34</v>
+        <v>19.5</v>
       </c>
       <c r="AW17" t="n">
-        <v>12</v>
+        <v>12.5</v>
       </c>
       <c r="AX17" t="n">
         <v>6.8</v>
@@ -4808,7 +4808,7 @@
         <v>27</v>
       </c>
       <c r="BA17" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="BB17" t="n">
         <v>9.800000000000001</v>
@@ -4817,16 +4817,16 @@
         <v>14</v>
       </c>
       <c r="BD17" t="n">
-        <v>19.5</v>
+        <v>36</v>
       </c>
       <c r="BE17" t="n">
-        <v>14</v>
+        <v>13.5</v>
       </c>
       <c r="BF17" t="n">
         <v>6</v>
       </c>
       <c r="BG17" t="n">
-        <v>14.5</v>
+        <v>14</v>
       </c>
       <c r="BH17" t="n">
         <v>1000</v>
@@ -4838,59 +4838,59 @@
         <v>1000</v>
       </c>
       <c r="BK17" t="n">
-        <v>1.58</v>
+        <v>1.04</v>
       </c>
       <c r="BL17" t="n">
         <v>1000</v>
       </c>
       <c r="BM17" t="n">
-        <v>1.72</v>
+        <v>1.04</v>
       </c>
       <c r="BN17" t="n">
         <v>1000</v>
       </c>
       <c r="BO17" t="n">
-        <v>1.3</v>
+        <v>1.04</v>
       </c>
       <c r="BP17" t="n">
         <v>1000</v>
       </c>
       <c r="BQ17" t="n">
-        <v>1.5</v>
+        <v>1.04</v>
       </c>
       <c r="BR17" t="n">
         <v>1000</v>
       </c>
       <c r="BS17" t="n">
-        <v>1.65</v>
+        <v>1.04</v>
       </c>
       <c r="BT17" t="n">
         <v>1000</v>
       </c>
       <c r="BU17" t="n">
-        <v>1.59</v>
+        <v>1.04</v>
       </c>
       <c r="BV17" t="n">
         <v>1000</v>
       </c>
       <c r="BW17" t="n">
-        <v>1.72</v>
+        <v>1.04</v>
       </c>
       <c r="BX17" t="n">
         <v>1000</v>
       </c>
       <c r="BY17" t="n">
-        <v>1.72</v>
+        <v>1.04</v>
       </c>
       <c r="BZ17" t="n">
         <v>1000</v>
       </c>
       <c r="CA17" t="n">
-        <v>1.6</v>
+        <v>1.04</v>
       </c>
       <c r="CB17" t="inlineStr">
         <is>
-          <t>2026-06-11 22:37:56</t>
+          <t>2026-06-12 00:53:26</t>
         </is>
       </c>
     </row>
@@ -4921,16 +4921,16 @@
         </is>
       </c>
       <c r="F18" t="n">
-        <v>3.15</v>
+        <v>3.2</v>
       </c>
       <c r="G18" t="n">
         <v>3.45</v>
       </c>
       <c r="H18" t="n">
-        <v>2.46</v>
+        <v>2.48</v>
       </c>
       <c r="I18" t="n">
-        <v>2.6</v>
+        <v>2.58</v>
       </c>
       <c r="J18" t="n">
         <v>3.25</v>
@@ -4969,10 +4969,10 @@
         <v>1.95</v>
       </c>
       <c r="V18" t="n">
-        <v>1.62</v>
+        <v>1.63</v>
       </c>
       <c r="W18" t="n">
-        <v>1.4</v>
+        <v>1.41</v>
       </c>
       <c r="X18" t="n">
         <v>12</v>
@@ -5144,7 +5144,7 @@
       </c>
       <c r="CB18" t="inlineStr">
         <is>
-          <t>2026-06-11 22:37:56</t>
+          <t>2026-06-12 00:53:26</t>
         </is>
       </c>
     </row>
@@ -5175,16 +5175,16 @@
         </is>
       </c>
       <c r="F19" t="n">
-        <v>2.24</v>
+        <v>2.26</v>
       </c>
       <c r="G19" t="n">
-        <v>2.34</v>
+        <v>2.38</v>
       </c>
       <c r="H19" t="n">
         <v>3.3</v>
       </c>
       <c r="I19" t="n">
-        <v>3.55</v>
+        <v>3.4</v>
       </c>
       <c r="J19" t="n">
         <v>3.6</v>
@@ -5199,7 +5199,7 @@
         <v>1.06</v>
       </c>
       <c r="N19" t="n">
-        <v>3.85</v>
+        <v>3.8</v>
       </c>
       <c r="O19" t="n">
         <v>1.29</v>
@@ -5208,7 +5208,7 @@
         <v>1.98</v>
       </c>
       <c r="Q19" t="n">
-        <v>1.88</v>
+        <v>1.89</v>
       </c>
       <c r="R19" t="n">
         <v>1.37</v>
@@ -5223,19 +5223,19 @@
         <v>2.16</v>
       </c>
       <c r="V19" t="n">
-        <v>1.4</v>
+        <v>1.42</v>
       </c>
       <c r="W19" t="n">
-        <v>1.74</v>
+        <v>1.73</v>
       </c>
       <c r="X19" t="n">
-        <v>17</v>
+        <v>16.5</v>
       </c>
       <c r="Y19" t="n">
-        <v>14.5</v>
+        <v>14</v>
       </c>
       <c r="Z19" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="AA19" t="n">
         <v>130</v>
@@ -5268,7 +5268,7 @@
         <v>42</v>
       </c>
       <c r="AK19" t="n">
-        <v>25</v>
+        <v>32</v>
       </c>
       <c r="AL19" t="n">
         <v>50</v>
@@ -5277,7 +5277,7 @@
         <v>320</v>
       </c>
       <c r="AN19" t="n">
-        <v>17</v>
+        <v>18.5</v>
       </c>
       <c r="AO19" t="n">
         <v>48</v>
@@ -5292,10 +5292,10 @@
         <v>20</v>
       </c>
       <c r="AS19" t="n">
-        <v>23</v>
+        <v>34</v>
       </c>
       <c r="AT19" t="n">
-        <v>9.4</v>
+        <v>9</v>
       </c>
       <c r="AU19" t="n">
         <v>7.2</v>
@@ -5328,7 +5328,7 @@
         <v>25</v>
       </c>
       <c r="BE19" t="n">
-        <v>9.6</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BF19" t="n">
         <v>13.5</v>
@@ -5337,7 +5337,7 @@
         <v>24</v>
       </c>
       <c r="BH19" t="n">
-        <v>3.7</v>
+        <v>3.65</v>
       </c>
       <c r="BI19" t="n">
         <v>2.92</v>
@@ -5361,19 +5361,19 @@
         <v>4.5</v>
       </c>
       <c r="BP19" t="n">
-        <v>16</v>
+        <v>17.5</v>
       </c>
       <c r="BQ19" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="BR19" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BS19" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="BT19" t="n">
         <v>6.8</v>
-      </c>
-      <c r="BR19" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BS19" t="n">
-        <v>8.4</v>
-      </c>
-      <c r="BT19" t="n">
-        <v>7</v>
       </c>
       <c r="BU19" t="n">
         <v>5.8</v>
@@ -5388,17 +5388,17 @@
         <v>1000</v>
       </c>
       <c r="BY19" t="n">
-        <v>9</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BZ19" t="n">
         <v>24</v>
       </c>
       <c r="CA19" t="n">
-        <v>8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="CB19" t="inlineStr">
         <is>
-          <t>2026-06-11 22:37:56</t>
+          <t>2026-06-12 00:53:26</t>
         </is>
       </c>
     </row>
@@ -5444,7 +5444,7 @@
         <v>3.7</v>
       </c>
       <c r="K20" t="n">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="L20" t="n">
         <v>1.01</v>
@@ -5513,7 +5513,7 @@
         <v>23</v>
       </c>
       <c r="AH20" t="n">
-        <v>19</v>
+        <v>18.5</v>
       </c>
       <c r="AI20" t="n">
         <v>36</v>
@@ -5600,19 +5600,19 @@
         <v>1000</v>
       </c>
       <c r="BK20" t="n">
-        <v>1.54</v>
+        <v>1.04</v>
       </c>
       <c r="BL20" t="n">
         <v>1000</v>
       </c>
       <c r="BM20" t="n">
-        <v>1.73</v>
+        <v>1.04</v>
       </c>
       <c r="BN20" t="n">
         <v>1000</v>
       </c>
       <c r="BO20" t="n">
-        <v>1.51</v>
+        <v>1.04</v>
       </c>
       <c r="BP20" t="n">
         <v>1000</v>
@@ -5630,29 +5630,29 @@
         <v>1000</v>
       </c>
       <c r="BU20" t="n">
-        <v>1.4</v>
+        <v>1.04</v>
       </c>
       <c r="BV20" t="n">
         <v>1000</v>
       </c>
       <c r="BW20" t="n">
-        <v>1.59</v>
+        <v>1.04</v>
       </c>
       <c r="BX20" t="n">
         <v>1000</v>
       </c>
       <c r="BY20" t="n">
-        <v>1.66</v>
+        <v>1.04</v>
       </c>
       <c r="BZ20" t="n">
         <v>1000</v>
       </c>
       <c r="CA20" t="n">
-        <v>1.62</v>
+        <v>1.04</v>
       </c>
       <c r="CB20" t="inlineStr">
         <is>
-          <t>2026-06-11 22:37:56</t>
+          <t>2026-06-12 00:53:26</t>
         </is>
       </c>
     </row>
@@ -5689,7 +5689,7 @@
         <v>2.48</v>
       </c>
       <c r="H21" t="n">
-        <v>3.35</v>
+        <v>3.4</v>
       </c>
       <c r="I21" t="n">
         <v>3.75</v>
@@ -5701,7 +5701,7 @@
         <v>3.45</v>
       </c>
       <c r="L21" t="n">
-        <v>1.49</v>
+        <v>1.4</v>
       </c>
       <c r="M21" t="n">
         <v>1.09</v>
@@ -5770,7 +5770,7 @@
         <v>24</v>
       </c>
       <c r="AI21" t="n">
-        <v>160</v>
+        <v>370</v>
       </c>
       <c r="AJ21" t="n">
         <v>42</v>
@@ -5800,7 +5800,7 @@
         <v>17.5</v>
       </c>
       <c r="AS21" t="n">
-        <v>4.9</v>
+        <v>5</v>
       </c>
       <c r="AT21" t="n">
         <v>6.4</v>
@@ -5812,7 +5812,7 @@
         <v>11</v>
       </c>
       <c r="AW21" t="n">
-        <v>4.9</v>
+        <v>5</v>
       </c>
       <c r="AX21" t="n">
         <v>10.5</v>
@@ -5824,7 +5824,7 @@
         <v>14</v>
       </c>
       <c r="BA21" t="n">
-        <v>4.9</v>
+        <v>5</v>
       </c>
       <c r="BB21" t="n">
         <v>14.5</v>
@@ -5833,10 +5833,10 @@
         <v>21</v>
       </c>
       <c r="BD21" t="n">
-        <v>4.9</v>
+        <v>5</v>
       </c>
       <c r="BE21" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="BF21" t="n">
         <v>19</v>
@@ -5906,7 +5906,7 @@
       </c>
       <c r="CB21" t="inlineStr">
         <is>
-          <t>2026-06-11 22:37:56</t>
+          <t>2026-06-12 00:53:26</t>
         </is>
       </c>
     </row>
@@ -5958,7 +5958,7 @@
         <v>1.01</v>
       </c>
       <c r="M22" t="n">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="N22" t="n">
         <v>4.2</v>
@@ -5985,7 +5985,7 @@
         <v>1.73</v>
       </c>
       <c r="V22" t="n">
-        <v>1.91</v>
+        <v>1.92</v>
       </c>
       <c r="W22" t="n">
         <v>1.3</v>
@@ -6160,7 +6160,7 @@
       </c>
       <c r="CB22" t="inlineStr">
         <is>
-          <t>2026-06-11 22:37:56</t>
+          <t>2026-06-12 00:53:26</t>
         </is>
       </c>
     </row>
@@ -6191,22 +6191,22 @@
         </is>
       </c>
       <c r="F23" t="n">
-        <v>4.3</v>
+        <v>4.4</v>
       </c>
       <c r="G23" t="n">
-        <v>5</v>
+        <v>4.9</v>
       </c>
       <c r="H23" t="n">
-        <v>1.84</v>
+        <v>1.91</v>
       </c>
       <c r="I23" t="n">
-        <v>2.02</v>
+        <v>1.99</v>
       </c>
       <c r="J23" t="n">
         <v>3.6</v>
       </c>
       <c r="K23" t="n">
-        <v>3.95</v>
+        <v>3.7</v>
       </c>
       <c r="L23" t="n">
         <v>1.35</v>
@@ -6239,10 +6239,10 @@
         <v>2.04</v>
       </c>
       <c r="V23" t="n">
-        <v>1.99</v>
+        <v>2</v>
       </c>
       <c r="W23" t="n">
-        <v>1.25</v>
+        <v>1.26</v>
       </c>
       <c r="X23" t="n">
         <v>15.5</v>
@@ -6347,7 +6347,7 @@
         <v>8.800000000000001</v>
       </c>
       <c r="BF23" t="n">
-        <v>8.4</v>
+        <v>12.5</v>
       </c>
       <c r="BG23" t="n">
         <v>11</v>
@@ -6414,7 +6414,7 @@
       </c>
       <c r="CB23" t="inlineStr">
         <is>
-          <t>2026-06-11 22:37:56</t>
+          <t>2026-06-12 00:53:26</t>
         </is>
       </c>
     </row>
@@ -6668,7 +6668,7 @@
       </c>
       <c r="CB24" t="inlineStr">
         <is>
-          <t>2026-06-11 22:37:56</t>
+          <t>2026-06-12 00:53:26</t>
         </is>
       </c>
     </row>
@@ -6720,28 +6720,28 @@
         <v>1.01</v>
       </c>
       <c r="M25" t="n">
-        <v>1.09</v>
+        <v>1.08</v>
       </c>
       <c r="N25" t="n">
-        <v>3.3</v>
+        <v>3.35</v>
       </c>
       <c r="O25" t="n">
-        <v>1.39</v>
+        <v>1.38</v>
       </c>
       <c r="P25" t="n">
         <v>1.8</v>
       </c>
       <c r="Q25" t="n">
-        <v>2.12</v>
+        <v>2.1</v>
       </c>
       <c r="R25" t="n">
-        <v>1.29</v>
+        <v>1.3</v>
       </c>
       <c r="S25" t="n">
         <v>4</v>
       </c>
       <c r="T25" t="n">
-        <v>1.83</v>
+        <v>1.81</v>
       </c>
       <c r="U25" t="n">
         <v>2.08</v>
@@ -6804,7 +6804,7 @@
         <v>42</v>
       </c>
       <c r="AO25" t="n">
-        <v>40</v>
+        <v>500</v>
       </c>
       <c r="AP25" t="n">
         <v>11</v>
@@ -6816,7 +6816,7 @@
         <v>9</v>
       </c>
       <c r="AS25" t="n">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="AT25" t="n">
         <v>9.199999999999999</v>
@@ -6828,7 +6828,7 @@
         <v>11</v>
       </c>
       <c r="AW25" t="n">
-        <v>4</v>
+        <v>14.5</v>
       </c>
       <c r="AX25" t="n">
         <v>9</v>
@@ -6840,19 +6840,19 @@
         <v>10.5</v>
       </c>
       <c r="BA25" t="n">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="BB25" t="n">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="BC25" t="n">
         <v>14.5</v>
       </c>
       <c r="BD25" t="n">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="BE25" t="n">
-        <v>4.2</v>
+        <v>4.4</v>
       </c>
       <c r="BF25" t="n">
         <v>6.6</v>
@@ -6870,25 +6870,25 @@
         <v>1000</v>
       </c>
       <c r="BK25" t="n">
-        <v>1.48</v>
+        <v>1.04</v>
       </c>
       <c r="BL25" t="n">
         <v>1000</v>
       </c>
       <c r="BM25" t="n">
-        <v>1.65</v>
+        <v>1.04</v>
       </c>
       <c r="BN25" t="n">
         <v>1000</v>
       </c>
       <c r="BO25" t="n">
-        <v>1.39</v>
+        <v>1.04</v>
       </c>
       <c r="BP25" t="n">
         <v>1000</v>
       </c>
       <c r="BQ25" t="n">
-        <v>1.58</v>
+        <v>1.04</v>
       </c>
       <c r="BR25" t="n">
         <v>1000</v>
@@ -6900,13 +6900,13 @@
         <v>1000</v>
       </c>
       <c r="BU25" t="n">
-        <v>1.39</v>
+        <v>1.04</v>
       </c>
       <c r="BV25" t="n">
         <v>1000</v>
       </c>
       <c r="BW25" t="n">
-        <v>1.57</v>
+        <v>1.04</v>
       </c>
       <c r="BX25" t="n">
         <v>1000</v>
@@ -6922,7 +6922,7 @@
       </c>
       <c r="CB25" t="inlineStr">
         <is>
-          <t>2026-06-11 22:37:56</t>
+          <t>2026-06-12 00:53:26</t>
         </is>
       </c>
     </row>
@@ -6962,10 +6962,10 @@
         <v>3.85</v>
       </c>
       <c r="I26" t="n">
-        <v>4.6</v>
+        <v>4.5</v>
       </c>
       <c r="J26" t="n">
-        <v>4.5</v>
+        <v>4.4</v>
       </c>
       <c r="K26" t="n">
         <v>5.2</v>
@@ -7010,7 +7010,7 @@
         <v>80</v>
       </c>
       <c r="Y26" t="n">
-        <v>32</v>
+        <v>75</v>
       </c>
       <c r="Z26" t="n">
         <v>50</v>
@@ -7028,7 +7028,7 @@
         <v>23</v>
       </c>
       <c r="AE26" t="n">
-        <v>95</v>
+        <v>120</v>
       </c>
       <c r="AF26" t="n">
         <v>18</v>
@@ -7040,7 +7040,7 @@
         <v>19</v>
       </c>
       <c r="AI26" t="n">
-        <v>44</v>
+        <v>95</v>
       </c>
       <c r="AJ26" t="n">
         <v>27</v>
@@ -7067,10 +7067,10 @@
         <v>21</v>
       </c>
       <c r="AR26" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="AS26" t="n">
         <v>4.7</v>
-      </c>
-      <c r="AS26" t="n">
-        <v>4.6</v>
       </c>
       <c r="AT26" t="n">
         <v>13</v>
@@ -7109,7 +7109,7 @@
         <v>4.8</v>
       </c>
       <c r="BF26" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="BG26" t="n">
         <v>16</v>
@@ -7118,7 +7118,7 @@
         <v>5.6</v>
       </c>
       <c r="BI26" t="n">
-        <v>4.7</v>
+        <v>4.1</v>
       </c>
       <c r="BJ26" t="n">
         <v>8.800000000000001</v>
@@ -7130,25 +7130,25 @@
         <v>1000</v>
       </c>
       <c r="BM26" t="n">
-        <v>9.199999999999999</v>
+        <v>9</v>
       </c>
       <c r="BN26" t="n">
-        <v>5.5</v>
+        <v>5.6</v>
       </c>
       <c r="BO26" t="n">
-        <v>4.7</v>
+        <v>4.1</v>
       </c>
       <c r="BP26" t="n">
         <v>11.5</v>
       </c>
       <c r="BQ26" t="n">
-        <v>5.6</v>
+        <v>8</v>
       </c>
       <c r="BR26" t="n">
         <v>18</v>
       </c>
       <c r="BS26" t="n">
-        <v>6.8</v>
+        <v>6.6</v>
       </c>
       <c r="BT26" t="n">
         <v>8.800000000000001</v>
@@ -7160,23 +7160,23 @@
         <v>1000</v>
       </c>
       <c r="BW26" t="n">
-        <v>7.8</v>
+        <v>7.6</v>
       </c>
       <c r="BX26" t="n">
         <v>1000</v>
       </c>
       <c r="BY26" t="n">
-        <v>7.8</v>
+        <v>7.6</v>
       </c>
       <c r="BZ26" t="n">
         <v>11</v>
       </c>
       <c r="CA26" t="n">
-        <v>5.5</v>
+        <v>5.4</v>
       </c>
       <c r="CB26" t="inlineStr">
         <is>
-          <t>2026-06-11 22:37:56</t>
+          <t>2026-06-12 00:53:26</t>
         </is>
       </c>
     </row>
@@ -7210,13 +7210,13 @@
         <v>2.64</v>
       </c>
       <c r="G27" t="n">
-        <v>110</v>
+        <v>44</v>
       </c>
       <c r="H27" t="n">
         <v>1.92</v>
       </c>
       <c r="I27" t="n">
-        <v>44</v>
+        <v>8</v>
       </c>
       <c r="J27" t="n">
         <v>2.48</v>
@@ -7430,7 +7430,7 @@
       </c>
       <c r="CB27" t="inlineStr">
         <is>
-          <t>2026-06-11 22:37:56</t>
+          <t>2026-06-12 00:53:26</t>
         </is>
       </c>
     </row>
@@ -7461,10 +7461,10 @@
         </is>
       </c>
       <c r="F28" t="n">
-        <v>2.26</v>
+        <v>2.24</v>
       </c>
       <c r="G28" t="n">
-        <v>2.38</v>
+        <v>2.36</v>
       </c>
       <c r="H28" t="n">
         <v>3.55</v>
@@ -7476,7 +7476,7 @@
         <v>3.3</v>
       </c>
       <c r="K28" t="n">
-        <v>3.4</v>
+        <v>3.45</v>
       </c>
       <c r="L28" t="n">
         <v>1.4</v>
@@ -7503,7 +7503,7 @@
         <v>4.4</v>
       </c>
       <c r="T28" t="n">
-        <v>1.96</v>
+        <v>1.97</v>
       </c>
       <c r="U28" t="n">
         <v>1.89</v>
@@ -7512,7 +7512,7 @@
         <v>1.35</v>
       </c>
       <c r="W28" t="n">
-        <v>1.72</v>
+        <v>1.73</v>
       </c>
       <c r="X28" t="n">
         <v>19</v>
@@ -7530,16 +7530,16 @@
         <v>8.6</v>
       </c>
       <c r="AC28" t="n">
-        <v>14</v>
+        <v>7.8</v>
       </c>
       <c r="AD28" t="n">
-        <v>500</v>
+        <v>30</v>
       </c>
       <c r="AE28" t="n">
         <v>500</v>
       </c>
       <c r="AF28" t="n">
-        <v>24</v>
+        <v>14.5</v>
       </c>
       <c r="AG28" t="n">
         <v>12</v>
@@ -7557,7 +7557,7 @@
         <v>85</v>
       </c>
       <c r="AL28" t="n">
-        <v>500</v>
+        <v>290</v>
       </c>
       <c r="AM28" t="n">
         <v>580</v>
@@ -7572,16 +7572,16 @@
         <v>9.4</v>
       </c>
       <c r="AQ28" t="n">
-        <v>6.2</v>
+        <v>10</v>
       </c>
       <c r="AR28" t="n">
         <v>21</v>
       </c>
       <c r="AS28" t="n">
-        <v>8.6</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AT28" t="n">
-        <v>7</v>
+        <v>7.2</v>
       </c>
       <c r="AU28" t="n">
         <v>6.8</v>
@@ -7590,7 +7590,7 @@
         <v>13</v>
       </c>
       <c r="AW28" t="n">
-        <v>8.199999999999999</v>
+        <v>8.4</v>
       </c>
       <c r="AX28" t="n">
         <v>11.5</v>
@@ -7599,28 +7599,28 @@
         <v>9.6</v>
       </c>
       <c r="AZ28" t="n">
-        <v>6.6</v>
+        <v>6.8</v>
       </c>
       <c r="BA28" t="n">
-        <v>8.4</v>
+        <v>8.6</v>
       </c>
       <c r="BB28" t="n">
-        <v>7.4</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BC28" t="n">
         <v>13</v>
       </c>
       <c r="BD28" t="n">
-        <v>8.199999999999999</v>
+        <v>8.4</v>
       </c>
       <c r="BE28" t="n">
-        <v>9</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BF28" t="n">
         <v>21</v>
       </c>
       <c r="BG28" t="n">
-        <v>9.800000000000001</v>
+        <v>8.6</v>
       </c>
       <c r="BH28" t="n">
         <v>1000</v>
@@ -7684,7 +7684,7 @@
       </c>
       <c r="CB28" t="inlineStr">
         <is>
-          <t>2026-06-11 22:37:56</t>
+          <t>2026-06-12 00:53:26</t>
         </is>
       </c>
     </row>
@@ -7718,22 +7718,22 @@
         <v>2</v>
       </c>
       <c r="G29" t="n">
-        <v>2.06</v>
+        <v>2.1</v>
       </c>
       <c r="H29" t="n">
-        <v>3.85</v>
+        <v>3.75</v>
       </c>
       <c r="I29" t="n">
-        <v>4.2</v>
+        <v>4.1</v>
       </c>
       <c r="J29" t="n">
-        <v>3.8</v>
+        <v>3.7</v>
       </c>
       <c r="K29" t="n">
         <v>4.1</v>
       </c>
       <c r="L29" t="n">
-        <v>1.3</v>
+        <v>1.29</v>
       </c>
       <c r="M29" t="n">
         <v>1.05</v>
@@ -7766,16 +7766,16 @@
         <v>1.32</v>
       </c>
       <c r="W29" t="n">
-        <v>1.94</v>
+        <v>1.92</v>
       </c>
       <c r="X29" t="n">
         <v>18</v>
       </c>
       <c r="Y29" t="n">
-        <v>17</v>
+        <v>16.5</v>
       </c>
       <c r="Z29" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="AA29" t="n">
         <v>95</v>
@@ -7787,7 +7787,7 @@
         <v>9</v>
       </c>
       <c r="AD29" t="n">
-        <v>16.5</v>
+        <v>16</v>
       </c>
       <c r="AE29" t="n">
         <v>46</v>
@@ -7796,7 +7796,7 @@
         <v>13.5</v>
       </c>
       <c r="AG29" t="n">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="AH29" t="n">
         <v>17.5</v>
@@ -7808,10 +7808,10 @@
         <v>24</v>
       </c>
       <c r="AK29" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AL29" t="n">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="AM29" t="n">
         <v>100</v>
@@ -7826,25 +7826,25 @@
         <v>15.5</v>
       </c>
       <c r="AQ29" t="n">
-        <v>15</v>
+        <v>14.5</v>
       </c>
       <c r="AR29" t="n">
         <v>18.5</v>
       </c>
       <c r="AS29" t="n">
-        <v>12.5</v>
+        <v>11</v>
       </c>
       <c r="AT29" t="n">
-        <v>9.4</v>
+        <v>9.6</v>
       </c>
       <c r="AU29" t="n">
         <v>8</v>
       </c>
       <c r="AV29" t="n">
-        <v>14.5</v>
+        <v>14</v>
       </c>
       <c r="AW29" t="n">
-        <v>25</v>
+        <v>38</v>
       </c>
       <c r="AX29" t="n">
         <v>11.5</v>
@@ -7856,7 +7856,7 @@
         <v>15.5</v>
       </c>
       <c r="BA29" t="n">
-        <v>42</v>
+        <v>27</v>
       </c>
       <c r="BB29" t="n">
         <v>20</v>
@@ -7868,25 +7868,25 @@
         <v>24</v>
       </c>
       <c r="BE29" t="n">
-        <v>13</v>
+        <v>11.5</v>
       </c>
       <c r="BF29" t="n">
         <v>11</v>
       </c>
       <c r="BG29" t="n">
-        <v>24</v>
+        <v>34</v>
       </c>
       <c r="BH29" t="n">
         <v>3.75</v>
       </c>
       <c r="BI29" t="n">
-        <v>3</v>
+        <v>3.05</v>
       </c>
       <c r="BJ29" t="n">
-        <v>9.4</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BK29" t="n">
-        <v>5.9</v>
+        <v>5.8</v>
       </c>
       <c r="BL29" t="n">
         <v>1000</v>
@@ -7895,7 +7895,7 @@
         <v>13.5</v>
       </c>
       <c r="BN29" t="n">
-        <v>4.9</v>
+        <v>5</v>
       </c>
       <c r="BO29" t="n">
         <v>3.8</v>
@@ -7919,10 +7919,10 @@
         <v>5.5</v>
       </c>
       <c r="BV29" t="n">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="BW29" t="n">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="BX29" t="n">
         <v>38</v>
@@ -7938,7 +7938,7 @@
       </c>
       <c r="CB29" t="inlineStr">
         <is>
-          <t>2026-06-11 22:37:56</t>
+          <t>2026-06-12 00:53:26</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-06-12.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-06-12.xlsx
@@ -857,58 +857,58 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>1.57</v>
+        <v>1.55</v>
       </c>
       <c r="G2" t="n">
-        <v>1.63</v>
+        <v>1.6</v>
       </c>
       <c r="H2" t="n">
-        <v>7</v>
+        <v>6.4</v>
       </c>
       <c r="I2" t="n">
-        <v>8.800000000000001</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="J2" t="n">
-        <v>3.8</v>
+        <v>4.1</v>
       </c>
       <c r="K2" t="n">
-        <v>4.5</v>
+        <v>4.7</v>
       </c>
       <c r="L2" t="n">
-        <v>1.33</v>
+        <v>1.39</v>
       </c>
       <c r="M2" t="n">
         <v>1.06</v>
       </c>
       <c r="N2" t="n">
-        <v>3.65</v>
+        <v>4</v>
       </c>
       <c r="O2" t="n">
-        <v>1.31</v>
+        <v>1.3</v>
       </c>
       <c r="P2" t="n">
-        <v>1.92</v>
+        <v>2.02</v>
       </c>
       <c r="Q2" t="n">
+        <v>1.89</v>
+      </c>
+      <c r="R2" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="S2" t="n">
+        <v>3.35</v>
+      </c>
+      <c r="T2" t="n">
         <v>1.94</v>
       </c>
-      <c r="R2" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="S2" t="n">
-        <v>3.7</v>
-      </c>
-      <c r="T2" t="n">
-        <v>1.96</v>
-      </c>
       <c r="U2" t="n">
-        <v>1.87</v>
+        <v>1.89</v>
       </c>
       <c r="V2" t="n">
         <v>1.15</v>
       </c>
       <c r="W2" t="n">
-        <v>2.58</v>
+        <v>2.62</v>
       </c>
       <c r="X2" t="n">
         <v>970</v>
@@ -917,22 +917,22 @@
         <v>950</v>
       </c>
       <c r="Z2" t="n">
-        <v>220</v>
+        <v>500</v>
       </c>
       <c r="AA2" t="n">
-        <v>1000</v>
+        <v>700</v>
       </c>
       <c r="AB2" t="n">
-        <v>27</v>
+        <v>14</v>
       </c>
       <c r="AC2" t="n">
-        <v>42</v>
+        <v>17.5</v>
       </c>
       <c r="AD2" t="n">
         <v>950</v>
       </c>
       <c r="AE2" t="n">
-        <v>1000</v>
+        <v>700</v>
       </c>
       <c r="AF2" t="n">
         <v>40</v>
@@ -944,7 +944,7 @@
         <v>950</v>
       </c>
       <c r="AI2" t="n">
-        <v>1000</v>
+        <v>700</v>
       </c>
       <c r="AJ2" t="n">
         <v>900</v>
@@ -956,28 +956,28 @@
         <v>500</v>
       </c>
       <c r="AM2" t="n">
-        <v>1000</v>
+        <v>700</v>
       </c>
       <c r="AN2" t="n">
         <v>29</v>
       </c>
       <c r="AO2" t="n">
-        <v>1000</v>
+        <v>700</v>
       </c>
       <c r="AP2" t="n">
-        <v>2.48</v>
+        <v>6.4</v>
       </c>
       <c r="AQ2" t="n">
         <v>4.2</v>
       </c>
       <c r="AR2" t="n">
-        <v>4.2</v>
+        <v>5.5</v>
       </c>
       <c r="AS2" t="n">
         <v>4.2</v>
       </c>
       <c r="AT2" t="n">
-        <v>2.9</v>
+        <v>4.5</v>
       </c>
       <c r="AU2" t="n">
         <v>4.7</v>
@@ -986,101 +986,101 @@
         <v>4.2</v>
       </c>
       <c r="AW2" t="n">
-        <v>4.2</v>
+        <v>4.6</v>
       </c>
       <c r="AX2" t="n">
-        <v>3.05</v>
+        <v>5</v>
       </c>
       <c r="AY2" t="n">
-        <v>2.62</v>
+        <v>4.8</v>
       </c>
       <c r="AZ2" t="n">
-        <v>2.5</v>
+        <v>3.95</v>
       </c>
       <c r="BA2" t="n">
-        <v>4.2</v>
+        <v>4.6</v>
       </c>
       <c r="BB2" t="n">
-        <v>2.64</v>
+        <v>6.2</v>
       </c>
       <c r="BC2" t="n">
-        <v>2.78</v>
+        <v>6.6</v>
       </c>
       <c r="BD2" t="n">
-        <v>2.58</v>
+        <v>3.9</v>
       </c>
       <c r="BE2" t="n">
-        <v>2.68</v>
+        <v>3.3</v>
       </c>
       <c r="BF2" t="n">
-        <v>5.1</v>
+        <v>6.6</v>
       </c>
       <c r="BG2" t="n">
         <v>4.2</v>
       </c>
       <c r="BH2" t="n">
-        <v>3.65</v>
+        <v>3.75</v>
       </c>
       <c r="BI2" t="n">
         <v>3.2</v>
       </c>
       <c r="BJ2" t="n">
-        <v>1000</v>
+        <v>15.5</v>
       </c>
       <c r="BK2" t="n">
-        <v>3.8</v>
+        <v>5.3</v>
       </c>
       <c r="BL2" t="n">
         <v>1000</v>
       </c>
       <c r="BM2" t="n">
-        <v>1.62</v>
+        <v>3.75</v>
       </c>
       <c r="BN2" t="n">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="BO2" t="n">
-        <v>3.55</v>
+        <v>3.45</v>
       </c>
       <c r="BP2" t="n">
-        <v>1000</v>
+        <v>13.5</v>
       </c>
       <c r="BQ2" t="n">
-        <v>5.8</v>
+        <v>7.4</v>
       </c>
       <c r="BR2" t="n">
         <v>1000</v>
       </c>
       <c r="BS2" t="n">
-        <v>1.55</v>
+        <v>4.9</v>
       </c>
       <c r="BT2" t="n">
         <v>1000</v>
       </c>
       <c r="BU2" t="n">
-        <v>8.4</v>
+        <v>5.6</v>
       </c>
       <c r="BV2" t="n">
         <v>1000</v>
       </c>
       <c r="BW2" t="n">
-        <v>2.82</v>
+        <v>5.7</v>
       </c>
       <c r="BX2" t="n">
         <v>1000</v>
       </c>
       <c r="BY2" t="n">
-        <v>2.94</v>
+        <v>5.7</v>
       </c>
       <c r="BZ2" t="n">
         <v>1000</v>
       </c>
       <c r="CA2" t="n">
-        <v>3.05</v>
+        <v>7.2</v>
       </c>
       <c r="CB2" t="inlineStr">
         <is>
-          <t>2026-06-12 00:53:26</t>
+          <t>2026-06-12 03:08:58</t>
         </is>
       </c>
     </row>
@@ -1114,13 +1114,13 @@
         <v>2.64</v>
       </c>
       <c r="G3" t="n">
-        <v>2.8</v>
+        <v>2.74</v>
       </c>
       <c r="H3" t="n">
-        <v>2.7</v>
+        <v>2.74</v>
       </c>
       <c r="I3" t="n">
-        <v>2.86</v>
+        <v>2.84</v>
       </c>
       <c r="J3" t="n">
         <v>3.65</v>
@@ -1129,7 +1129,7 @@
         <v>3.7</v>
       </c>
       <c r="L3" t="n">
-        <v>1.28</v>
+        <v>1.35</v>
       </c>
       <c r="M3" t="n">
         <v>1.05</v>
@@ -1138,31 +1138,31 @@
         <v>4.6</v>
       </c>
       <c r="O3" t="n">
-        <v>1.23</v>
+        <v>1.25</v>
       </c>
       <c r="P3" t="n">
-        <v>2.28</v>
+        <v>2.2</v>
       </c>
       <c r="Q3" t="n">
-        <v>1.69</v>
+        <v>1.76</v>
       </c>
       <c r="R3" t="n">
         <v>1.5</v>
       </c>
       <c r="S3" t="n">
-        <v>2.72</v>
+        <v>2.92</v>
       </c>
       <c r="T3" t="n">
-        <v>1.6</v>
+        <v>1.62</v>
       </c>
       <c r="U3" t="n">
-        <v>2.46</v>
+        <v>2.42</v>
       </c>
       <c r="V3" t="n">
         <v>1.54</v>
       </c>
       <c r="W3" t="n">
-        <v>1.56</v>
+        <v>1.57</v>
       </c>
       <c r="X3" t="n">
         <v>24</v>
@@ -1180,7 +1180,7 @@
         <v>14.5</v>
       </c>
       <c r="AC3" t="n">
-        <v>9.199999999999999</v>
+        <v>9</v>
       </c>
       <c r="AD3" t="n">
         <v>15.5</v>
@@ -1195,7 +1195,7 @@
         <v>15</v>
       </c>
       <c r="AH3" t="n">
-        <v>15.5</v>
+        <v>15</v>
       </c>
       <c r="AI3" t="n">
         <v>44</v>
@@ -1216,16 +1216,16 @@
         <v>22</v>
       </c>
       <c r="AO3" t="n">
-        <v>19.5</v>
+        <v>20</v>
       </c>
       <c r="AP3" t="n">
-        <v>17</v>
+        <v>16.5</v>
       </c>
       <c r="AQ3" t="n">
         <v>10</v>
       </c>
       <c r="AR3" t="n">
-        <v>18</v>
+        <v>18.5</v>
       </c>
       <c r="AS3" t="n">
         <v>18</v>
@@ -1255,7 +1255,7 @@
         <v>18</v>
       </c>
       <c r="BB3" t="n">
-        <v>6.8</v>
+        <v>17.5</v>
       </c>
       <c r="BC3" t="n">
         <v>19.5</v>
@@ -1267,13 +1267,13 @@
         <v>5.9</v>
       </c>
       <c r="BF3" t="n">
-        <v>15.5</v>
+        <v>16</v>
       </c>
       <c r="BG3" t="n">
         <v>16.5</v>
       </c>
       <c r="BH3" t="n">
-        <v>3.9</v>
+        <v>3.8</v>
       </c>
       <c r="BI3" t="n">
         <v>3.05</v>
@@ -1288,53 +1288,53 @@
         <v>1000</v>
       </c>
       <c r="BM3" t="n">
-        <v>12</v>
+        <v>13.5</v>
       </c>
       <c r="BN3" t="n">
-        <v>6</v>
+        <v>5.8</v>
       </c>
       <c r="BO3" t="n">
         <v>5.2</v>
       </c>
       <c r="BP3" t="n">
-        <v>19</v>
+        <v>18.5</v>
       </c>
       <c r="BQ3" t="n">
-        <v>8</v>
+        <v>8.4</v>
       </c>
       <c r="BR3" t="n">
-        <v>28</v>
+        <v>1000</v>
       </c>
       <c r="BS3" t="n">
-        <v>9.199999999999999</v>
+        <v>10</v>
       </c>
       <c r="BT3" t="n">
         <v>6.2</v>
       </c>
       <c r="BU3" t="n">
-        <v>4.6</v>
+        <v>5.4</v>
       </c>
       <c r="BV3" t="n">
-        <v>19.5</v>
+        <v>21</v>
       </c>
       <c r="BW3" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="BX3" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="BY3" t="n">
-        <v>9.4</v>
+        <v>10</v>
       </c>
       <c r="BZ3" t="n">
         <v>21</v>
       </c>
       <c r="CA3" t="n">
-        <v>8.199999999999999</v>
+        <v>9</v>
       </c>
       <c r="CB3" t="inlineStr">
         <is>
-          <t>2026-06-12 00:53:26</t>
+          <t>2026-06-12 03:08:58</t>
         </is>
       </c>
     </row>
@@ -1365,46 +1365,46 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>2.94</v>
+        <v>3.05</v>
       </c>
       <c r="G4" t="n">
-        <v>3.45</v>
+        <v>3.3</v>
       </c>
       <c r="H4" t="n">
-        <v>2.92</v>
+        <v>2.96</v>
       </c>
       <c r="I4" t="n">
-        <v>3.35</v>
+        <v>3.1</v>
       </c>
       <c r="J4" t="n">
-        <v>2.56</v>
+        <v>2.7</v>
       </c>
       <c r="K4" t="n">
-        <v>2.98</v>
+        <v>2.88</v>
       </c>
       <c r="L4" t="n">
-        <v>1.57</v>
+        <v>1.68</v>
       </c>
       <c r="M4" t="n">
-        <v>1.15</v>
+        <v>1.17</v>
       </c>
       <c r="N4" t="n">
-        <v>2.28</v>
+        <v>2.4</v>
       </c>
       <c r="O4" t="n">
-        <v>1.61</v>
+        <v>1.64</v>
       </c>
       <c r="P4" t="n">
-        <v>1.41</v>
+        <v>1.42</v>
       </c>
       <c r="Q4" t="n">
-        <v>2.88</v>
+        <v>3.05</v>
       </c>
       <c r="R4" t="n">
-        <v>1.17</v>
+        <v>1.16</v>
       </c>
       <c r="S4" t="n">
-        <v>6</v>
+        <v>6.4</v>
       </c>
       <c r="T4" t="n">
         <v>2.16</v>
@@ -1413,10 +1413,10 @@
         <v>1.68</v>
       </c>
       <c r="V4" t="n">
-        <v>1.43</v>
+        <v>1.47</v>
       </c>
       <c r="W4" t="n">
-        <v>1.4</v>
+        <v>1.44</v>
       </c>
       <c r="X4" t="n">
         <v>16.5</v>
@@ -1425,7 +1425,7 @@
         <v>500</v>
       </c>
       <c r="Z4" t="n">
-        <v>970</v>
+        <v>50</v>
       </c>
       <c r="AA4" t="n">
         <v>500</v>
@@ -1446,7 +1446,7 @@
         <v>500</v>
       </c>
       <c r="AG4" t="n">
-        <v>500</v>
+        <v>970</v>
       </c>
       <c r="AH4" t="n">
         <v>500</v>
@@ -1455,7 +1455,7 @@
         <v>500</v>
       </c>
       <c r="AJ4" t="n">
-        <v>420</v>
+        <v>500</v>
       </c>
       <c r="AK4" t="n">
         <v>500</v>
@@ -1473,64 +1473,64 @@
         <v>600</v>
       </c>
       <c r="AP4" t="n">
-        <v>6</v>
+        <v>4.2</v>
       </c>
       <c r="AQ4" t="n">
-        <v>6.4</v>
+        <v>4.4</v>
       </c>
       <c r="AR4" t="n">
-        <v>8.4</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AS4" t="n">
-        <v>3.55</v>
+        <v>7.8</v>
       </c>
       <c r="AT4" t="n">
-        <v>4.6</v>
+        <v>4.4</v>
       </c>
       <c r="AU4" t="n">
-        <v>5.5</v>
+        <v>4.2</v>
       </c>
       <c r="AV4" t="n">
-        <v>8.4</v>
+        <v>6.8</v>
       </c>
       <c r="AW4" t="n">
-        <v>4.6</v>
+        <v>7.8</v>
       </c>
       <c r="AX4" t="n">
-        <v>6.8</v>
+        <v>7.6</v>
       </c>
       <c r="AY4" t="n">
-        <v>6.2</v>
+        <v>7</v>
       </c>
       <c r="AZ4" t="n">
-        <v>7.2</v>
+        <v>7</v>
       </c>
       <c r="BA4" t="n">
-        <v>3.65</v>
+        <v>3.8</v>
       </c>
       <c r="BB4" t="n">
-        <v>4.6</v>
+        <v>7.8</v>
       </c>
       <c r="BC4" t="n">
-        <v>4.5</v>
+        <v>7.8</v>
       </c>
       <c r="BD4" t="n">
-        <v>3.55</v>
+        <v>3.9</v>
       </c>
       <c r="BE4" t="n">
-        <v>7.4</v>
+        <v>5.2</v>
       </c>
       <c r="BF4" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="BG4" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="BH4" t="n">
         <v>2.6</v>
       </c>
       <c r="BI4" t="n">
-        <v>2.26</v>
+        <v>2.14</v>
       </c>
       <c r="BJ4" t="n">
         <v>1000</v>
@@ -1545,7 +1545,7 @@
         <v>1.32</v>
       </c>
       <c r="BN4" t="n">
-        <v>12.5</v>
+        <v>970</v>
       </c>
       <c r="BO4" t="n">
         <v>3.8</v>
@@ -1563,7 +1563,7 @@
         <v>2.02</v>
       </c>
       <c r="BT4" t="n">
-        <v>13</v>
+        <v>19.5</v>
       </c>
       <c r="BU4" t="n">
         <v>3.9</v>
@@ -1588,7 +1588,7 @@
       </c>
       <c r="CB4" t="inlineStr">
         <is>
-          <t>2026-06-12 00:53:26</t>
+          <t>2026-06-12 03:08:58</t>
         </is>
       </c>
     </row>
@@ -1619,22 +1619,22 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>2.28</v>
+        <v>1.99</v>
       </c>
       <c r="G5" t="n">
-        <v>2.46</v>
+        <v>2.12</v>
       </c>
       <c r="H5" t="n">
-        <v>3.9</v>
+        <v>4.5</v>
       </c>
       <c r="I5" t="n">
-        <v>4.2</v>
+        <v>5</v>
       </c>
       <c r="J5" t="n">
-        <v>2.94</v>
+        <v>3.2</v>
       </c>
       <c r="K5" t="n">
-        <v>3.15</v>
+        <v>3.5</v>
       </c>
       <c r="L5" t="n">
         <v>1.59</v>
@@ -1643,40 +1643,40 @@
         <v>1.13</v>
       </c>
       <c r="N5" t="n">
-        <v>2.48</v>
+        <v>2.62</v>
       </c>
       <c r="O5" t="n">
-        <v>1.57</v>
+        <v>1.55</v>
       </c>
       <c r="P5" t="n">
-        <v>1.5</v>
+        <v>1.53</v>
       </c>
       <c r="Q5" t="n">
-        <v>2.72</v>
+        <v>2.66</v>
       </c>
       <c r="R5" t="n">
         <v>1.18</v>
       </c>
       <c r="S5" t="n">
-        <v>5.8</v>
+        <v>5.7</v>
       </c>
       <c r="T5" t="n">
-        <v>2.14</v>
+        <v>2.18</v>
       </c>
       <c r="U5" t="n">
-        <v>1.73</v>
+        <v>1.71</v>
       </c>
       <c r="V5" t="n">
-        <v>1.31</v>
+        <v>1.25</v>
       </c>
       <c r="W5" t="n">
-        <v>1.69</v>
+        <v>1.87</v>
       </c>
       <c r="X5" t="n">
-        <v>8.199999999999999</v>
+        <v>9</v>
       </c>
       <c r="Y5" t="n">
-        <v>10.5</v>
+        <v>12</v>
       </c>
       <c r="Z5" t="n">
         <v>100</v>
@@ -1685,22 +1685,22 @@
         <v>900</v>
       </c>
       <c r="AB5" t="n">
-        <v>7.4</v>
+        <v>6.8</v>
       </c>
       <c r="AC5" t="n">
-        <v>7.4</v>
+        <v>7.8</v>
       </c>
       <c r="AD5" t="n">
-        <v>32</v>
+        <v>21</v>
       </c>
       <c r="AE5" t="n">
         <v>500</v>
       </c>
       <c r="AF5" t="n">
-        <v>13.5</v>
+        <v>11.5</v>
       </c>
       <c r="AG5" t="n">
-        <v>12.5</v>
+        <v>12</v>
       </c>
       <c r="AH5" t="n">
         <v>950</v>
@@ -1721,70 +1721,70 @@
         <v>500</v>
       </c>
       <c r="AN5" t="n">
-        <v>40</v>
+        <v>32</v>
       </c>
       <c r="AO5" t="n">
         <v>600</v>
       </c>
       <c r="AP5" t="n">
-        <v>7</v>
+        <v>7.6</v>
       </c>
       <c r="AQ5" t="n">
         <v>9</v>
       </c>
       <c r="AR5" t="n">
-        <v>8.199999999999999</v>
+        <v>11.5</v>
       </c>
       <c r="AS5" t="n">
-        <v>10.5</v>
+        <v>9.6</v>
       </c>
       <c r="AT5" t="n">
-        <v>6</v>
+        <v>5.7</v>
       </c>
       <c r="AU5" t="n">
         <v>6.2</v>
       </c>
       <c r="AV5" t="n">
-        <v>7.2</v>
+        <v>16.5</v>
       </c>
       <c r="AW5" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="AX5" t="n">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="AY5" t="n">
         <v>10</v>
       </c>
-      <c r="AX5" t="n">
-        <v>6.2</v>
-      </c>
-      <c r="AY5" t="n">
-        <v>10.5</v>
-      </c>
       <c r="AZ5" t="n">
-        <v>8</v>
+        <v>19</v>
       </c>
       <c r="BA5" t="n">
-        <v>10.5</v>
+        <v>9.6</v>
       </c>
       <c r="BB5" t="n">
+        <v>13</v>
+      </c>
+      <c r="BC5" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="BD5" t="n">
         <v>9</v>
       </c>
-      <c r="BC5" t="n">
-        <v>9</v>
-      </c>
-      <c r="BD5" t="n">
-        <v>28</v>
-      </c>
       <c r="BE5" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="BF5" t="n">
-        <v>9.199999999999999</v>
+        <v>7.8</v>
       </c>
       <c r="BG5" t="n">
-        <v>10.5</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BH5" t="n">
-        <v>2.68</v>
+        <v>2.72</v>
       </c>
       <c r="BI5" t="n">
-        <v>2.24</v>
+        <v>2.28</v>
       </c>
       <c r="BJ5" t="n">
         <v>12</v>
@@ -1799,16 +1799,16 @@
         <v>13</v>
       </c>
       <c r="BN5" t="n">
-        <v>4.9</v>
+        <v>4.6</v>
       </c>
       <c r="BO5" t="n">
-        <v>4.2</v>
+        <v>3.95</v>
       </c>
       <c r="BP5" t="n">
-        <v>21</v>
+        <v>1000</v>
       </c>
       <c r="BQ5" t="n">
-        <v>8.4</v>
+        <v>13.5</v>
       </c>
       <c r="BR5" t="n">
         <v>1000</v>
@@ -1817,7 +1817,7 @@
         <v>10.5</v>
       </c>
       <c r="BT5" t="n">
-        <v>7.2</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BU5" t="n">
         <v>5.5</v>
@@ -1826,7 +1826,7 @@
         <v>1000</v>
       </c>
       <c r="BW5" t="n">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="BX5" t="n">
         <v>1000</v>
@@ -1838,11 +1838,11 @@
         <v>1000</v>
       </c>
       <c r="CA5" t="n">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="CB5" t="inlineStr">
         <is>
-          <t>2026-06-12 00:53:26</t>
+          <t>2026-06-12 03:08:58</t>
         </is>
       </c>
     </row>
@@ -1873,61 +1873,61 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>3.3</v>
+        <v>3.35</v>
       </c>
       <c r="G6" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="H6" t="n">
+        <v>2.22</v>
+      </c>
+      <c r="I6" t="n">
+        <v>2.34</v>
+      </c>
+      <c r="J6" t="n">
         <v>3.55</v>
-      </c>
-      <c r="H6" t="n">
-        <v>2.24</v>
-      </c>
-      <c r="I6" t="n">
-        <v>2.38</v>
-      </c>
-      <c r="J6" t="n">
-        <v>3.5</v>
       </c>
       <c r="K6" t="n">
         <v>3.8</v>
       </c>
       <c r="L6" t="n">
-        <v>1.38</v>
+        <v>1.39</v>
       </c>
       <c r="M6" t="n">
         <v>1.06</v>
       </c>
       <c r="N6" t="n">
-        <v>3.95</v>
+        <v>4.1</v>
       </c>
       <c r="O6" t="n">
         <v>1.29</v>
       </c>
       <c r="P6" t="n">
-        <v>2.02</v>
+        <v>2.06</v>
       </c>
       <c r="Q6" t="n">
-        <v>1.85</v>
+        <v>1.89</v>
       </c>
       <c r="R6" t="n">
-        <v>1.4</v>
+        <v>1.41</v>
       </c>
       <c r="S6" t="n">
-        <v>3.15</v>
+        <v>3.25</v>
       </c>
       <c r="T6" t="n">
         <v>1.74</v>
       </c>
       <c r="U6" t="n">
-        <v>2.24</v>
+        <v>2.26</v>
       </c>
       <c r="V6" t="n">
-        <v>1.73</v>
+        <v>1.75</v>
       </c>
       <c r="W6" t="n">
-        <v>1.39</v>
+        <v>1.38</v>
       </c>
       <c r="X6" t="n">
-        <v>18.5</v>
+        <v>18</v>
       </c>
       <c r="Y6" t="n">
         <v>12.5</v>
@@ -1936,10 +1936,10 @@
         <v>15.5</v>
       </c>
       <c r="AA6" t="n">
-        <v>65</v>
+        <v>30</v>
       </c>
       <c r="AB6" t="n">
-        <v>14</v>
+        <v>14.5</v>
       </c>
       <c r="AC6" t="n">
         <v>8.4</v>
@@ -1957,13 +1957,13 @@
         <v>14.5</v>
       </c>
       <c r="AH6" t="n">
-        <v>17</v>
+        <v>16.5</v>
       </c>
       <c r="AI6" t="n">
         <v>44</v>
       </c>
       <c r="AJ6" t="n">
-        <v>440</v>
+        <v>150</v>
       </c>
       <c r="AK6" t="n">
         <v>48</v>
@@ -1972,13 +1972,13 @@
         <v>60</v>
       </c>
       <c r="AM6" t="n">
-        <v>110</v>
+        <v>580</v>
       </c>
       <c r="AN6" t="n">
         <v>44</v>
       </c>
       <c r="AO6" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="AP6" t="n">
         <v>14</v>
@@ -1987,88 +1987,88 @@
         <v>9.6</v>
       </c>
       <c r="AR6" t="n">
-        <v>10.5</v>
+        <v>13</v>
       </c>
       <c r="AS6" t="n">
-        <v>21</v>
+        <v>11.5</v>
       </c>
       <c r="AT6" t="n">
-        <v>10</v>
+        <v>12.5</v>
       </c>
       <c r="AU6" t="n">
         <v>7.4</v>
       </c>
       <c r="AV6" t="n">
-        <v>10</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AW6" t="n">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="AX6" t="n">
-        <v>18.5</v>
+        <v>21</v>
       </c>
       <c r="AY6" t="n">
-        <v>11</v>
+        <v>12.5</v>
       </c>
       <c r="AZ6" t="n">
-        <v>12.5</v>
+        <v>14.5</v>
       </c>
       <c r="BA6" t="n">
-        <v>18</v>
+        <v>13.5</v>
       </c>
       <c r="BB6" t="n">
-        <v>6.8</v>
+        <v>7.2</v>
       </c>
       <c r="BC6" t="n">
-        <v>7.2</v>
+        <v>14</v>
       </c>
       <c r="BD6" t="n">
-        <v>7</v>
+        <v>7.6</v>
       </c>
       <c r="BE6" t="n">
-        <v>7.2</v>
+        <v>7.4</v>
       </c>
       <c r="BF6" t="n">
         <v>7.4</v>
       </c>
       <c r="BG6" t="n">
-        <v>12.5</v>
+        <v>14</v>
       </c>
       <c r="BH6" t="n">
         <v>3.6</v>
       </c>
       <c r="BI6" t="n">
-        <v>2.94</v>
+        <v>2.98</v>
       </c>
       <c r="BJ6" t="n">
         <v>9.199999999999999</v>
       </c>
       <c r="BK6" t="n">
-        <v>5.8</v>
+        <v>6.8</v>
       </c>
       <c r="BL6" t="n">
         <v>1000</v>
       </c>
       <c r="BM6" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="BN6" t="n">
         <v>6.8</v>
       </c>
       <c r="BO6" t="n">
-        <v>5</v>
+        <v>5.1</v>
       </c>
       <c r="BP6" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="BQ6" t="n">
         <v>10</v>
       </c>
       <c r="BR6" t="n">
-        <v>36</v>
+        <v>48</v>
       </c>
       <c r="BS6" t="n">
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="BT6" t="n">
         <v>5.2</v>
@@ -2077,26 +2077,26 @@
         <v>4</v>
       </c>
       <c r="BV6" t="n">
-        <v>16.5</v>
+        <v>16</v>
       </c>
       <c r="BW6" t="n">
         <v>12.5</v>
       </c>
       <c r="BX6" t="n">
-        <v>1000</v>
+        <v>36</v>
       </c>
       <c r="BY6" t="n">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="BZ6" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="CA6" t="n">
-        <v>9.6</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="CB6" t="inlineStr">
         <is>
-          <t>2026-06-12 00:53:26</t>
+          <t>2026-06-12 03:08:58</t>
         </is>
       </c>
     </row>
@@ -2127,85 +2127,85 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>1.63</v>
+        <v>1.64</v>
       </c>
       <c r="G7" t="n">
-        <v>1.77</v>
+        <v>1.69</v>
       </c>
       <c r="H7" t="n">
-        <v>4.7</v>
+        <v>5.8</v>
       </c>
       <c r="I7" t="n">
-        <v>6.4</v>
+        <v>6.6</v>
       </c>
       <c r="J7" t="n">
-        <v>3.55</v>
+        <v>4.1</v>
       </c>
       <c r="K7" t="n">
         <v>4.6</v>
       </c>
       <c r="L7" t="n">
-        <v>1.01</v>
+        <v>1.37</v>
       </c>
       <c r="M7" t="n">
         <v>1.05</v>
       </c>
       <c r="N7" t="n">
-        <v>3.9</v>
+        <v>4.3</v>
       </c>
       <c r="O7" t="n">
-        <v>1.26</v>
+        <v>1.27</v>
       </c>
       <c r="P7" t="n">
-        <v>1.98</v>
+        <v>2.12</v>
       </c>
       <c r="Q7" t="n">
-        <v>1.74</v>
+        <v>1.83</v>
       </c>
       <c r="R7" t="n">
-        <v>1.41</v>
+        <v>1.43</v>
       </c>
       <c r="S7" t="n">
-        <v>2.66</v>
+        <v>3.1</v>
       </c>
       <c r="T7" t="n">
-        <v>1.79</v>
+        <v>1.83</v>
       </c>
       <c r="U7" t="n">
-        <v>2.02</v>
+        <v>2</v>
       </c>
       <c r="V7" t="n">
-        <v>1.18</v>
+        <v>1.19</v>
       </c>
       <c r="W7" t="n">
-        <v>2.28</v>
+        <v>2.44</v>
       </c>
       <c r="X7" t="n">
-        <v>18.5</v>
+        <v>18</v>
       </c>
       <c r="Y7" t="n">
-        <v>22</v>
+        <v>500</v>
       </c>
       <c r="Z7" t="n">
-        <v>500</v>
+        <v>55</v>
       </c>
       <c r="AA7" t="n">
-        <v>700</v>
+        <v>900</v>
       </c>
       <c r="AB7" t="n">
-        <v>9.6</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AC7" t="n">
         <v>10</v>
       </c>
       <c r="AD7" t="n">
-        <v>23</v>
+        <v>40</v>
       </c>
       <c r="AE7" t="n">
         <v>700</v>
       </c>
       <c r="AF7" t="n">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="AG7" t="n">
         <v>10.5</v>
@@ -2217,130 +2217,130 @@
         <v>700</v>
       </c>
       <c r="AJ7" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="AK7" t="n">
         <v>17.5</v>
       </c>
-      <c r="AK7" t="n">
-        <v>18</v>
-      </c>
       <c r="AL7" t="n">
-        <v>80</v>
+        <v>500</v>
       </c>
       <c r="AM7" t="n">
         <v>580</v>
       </c>
       <c r="AN7" t="n">
-        <v>9.6</v>
+        <v>9</v>
       </c>
       <c r="AO7" t="n">
         <v>700</v>
       </c>
       <c r="AP7" t="n">
+        <v>15</v>
+      </c>
+      <c r="AQ7" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="AR7" t="n">
+        <v>10</v>
+      </c>
+      <c r="AS7" t="n">
+        <v>10</v>
+      </c>
+      <c r="AT7" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="AU7" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="AV7" t="n">
+        <v>8</v>
+      </c>
+      <c r="AW7" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AX7" t="n">
+        <v>5.7</v>
+      </c>
+      <c r="AY7" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="AZ7" t="n">
+        <v>17.5</v>
+      </c>
+      <c r="BA7" t="n">
+        <v>11</v>
+      </c>
+      <c r="BB7" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="BC7" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="BD7" t="n">
+        <v>21</v>
+      </c>
+      <c r="BE7" t="n">
+        <v>11</v>
+      </c>
+      <c r="BF7" t="n">
         <v>6.6</v>
       </c>
-      <c r="AQ7" t="n">
-        <v>7</v>
-      </c>
-      <c r="AR7" t="n">
-        <v>8.6</v>
-      </c>
-      <c r="AS7" t="n">
-        <v>9</v>
-      </c>
-      <c r="AT7" t="n">
-        <v>5</v>
-      </c>
-      <c r="AU7" t="n">
+      <c r="BG7" t="n">
+        <v>11</v>
+      </c>
+      <c r="BH7" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="BI7" t="n">
+        <v>2.96</v>
+      </c>
+      <c r="BJ7" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="BK7" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="BL7" t="n">
+        <v>150</v>
+      </c>
+      <c r="BM7" t="n">
         <v>5.1</v>
       </c>
-      <c r="AV7" t="n">
-        <v>7.2</v>
-      </c>
-      <c r="AW7" t="n">
-        <v>9.4</v>
-      </c>
-      <c r="AX7" t="n">
-        <v>5.4</v>
-      </c>
-      <c r="AY7" t="n">
+      <c r="BN7" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="BO7" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="BP7" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="BQ7" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="BR7" t="n">
+        <v>32</v>
+      </c>
+      <c r="BS7" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="BT7" t="n">
+        <v>12</v>
+      </c>
+      <c r="BU7" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="BV7" t="n">
+        <v>55</v>
+      </c>
+      <c r="BW7" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="BX7" t="n">
+        <v>70</v>
+      </c>
+      <c r="BY7" t="n">
         <v>4.9</v>
-      </c>
-      <c r="AZ7" t="n">
-        <v>7</v>
-      </c>
-      <c r="BA7" t="n">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="BB7" t="n">
-        <v>6.6</v>
-      </c>
-      <c r="BC7" t="n">
-        <v>6.6</v>
-      </c>
-      <c r="BD7" t="n">
-        <v>8.199999999999999</v>
-      </c>
-      <c r="BE7" t="n">
-        <v>8.6</v>
-      </c>
-      <c r="BF7" t="n">
-        <v>5</v>
-      </c>
-      <c r="BG7" t="n">
-        <v>8.6</v>
-      </c>
-      <c r="BH7" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BI7" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="BJ7" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BK7" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="BL7" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BM7" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="BN7" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BO7" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="BP7" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BQ7" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="BR7" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BS7" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="BT7" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BU7" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="BV7" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BW7" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="BX7" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BY7" t="n">
-        <v>1.04</v>
       </c>
       <c r="BZ7" t="n">
         <v>0</v>
@@ -2350,7 +2350,7 @@
       </c>
       <c r="CB7" t="inlineStr">
         <is>
-          <t>2026-06-12 00:53:26</t>
+          <t>2026-06-12 03:08:58</t>
         </is>
       </c>
     </row>
@@ -2381,100 +2381,100 @@
         </is>
       </c>
       <c r="F8" t="n">
-        <v>1.63</v>
+        <v>1.77</v>
       </c>
       <c r="G8" t="n">
-        <v>1.75</v>
+        <v>1.79</v>
       </c>
       <c r="H8" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="I8" t="n">
         <v>5.6</v>
       </c>
-      <c r="I8" t="n">
-        <v>6.6</v>
-      </c>
       <c r="J8" t="n">
-        <v>3.85</v>
+        <v>3.95</v>
       </c>
       <c r="K8" t="n">
-        <v>4.4</v>
+        <v>4.3</v>
       </c>
       <c r="L8" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="M8" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="N8" t="n">
+        <v>3.95</v>
+      </c>
+      <c r="O8" t="n">
         <v>1.31</v>
       </c>
-      <c r="M8" t="n">
-        <v>1.07</v>
-      </c>
-      <c r="N8" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="O8" t="n">
-        <v>1.3</v>
-      </c>
       <c r="P8" t="n">
-        <v>1.94</v>
+        <v>2.02</v>
       </c>
       <c r="Q8" t="n">
-        <v>1.9</v>
+        <v>1.91</v>
       </c>
       <c r="R8" t="n">
-        <v>1.32</v>
+        <v>1.37</v>
       </c>
       <c r="S8" t="n">
-        <v>3.3</v>
+        <v>3.4</v>
       </c>
       <c r="T8" t="n">
-        <v>1.87</v>
+        <v>1.11</v>
       </c>
       <c r="U8" t="n">
-        <v>1.94</v>
+        <v>1.98</v>
       </c>
       <c r="V8" t="n">
-        <v>1.17</v>
+        <v>1.22</v>
       </c>
       <c r="W8" t="n">
-        <v>2.32</v>
+        <v>2.26</v>
       </c>
       <c r="X8" t="n">
-        <v>18</v>
+        <v>970</v>
       </c>
       <c r="Y8" t="n">
-        <v>21</v>
+        <v>17.5</v>
       </c>
       <c r="Z8" t="n">
-        <v>130</v>
+        <v>42</v>
       </c>
       <c r="AA8" t="n">
-        <v>700</v>
+        <v>900</v>
       </c>
       <c r="AB8" t="n">
-        <v>8.6</v>
+        <v>11</v>
       </c>
       <c r="AC8" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="AD8" t="n">
-        <v>29</v>
+        <v>20</v>
       </c>
       <c r="AE8" t="n">
         <v>240</v>
       </c>
       <c r="AF8" t="n">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="AG8" t="n">
         <v>12</v>
       </c>
       <c r="AH8" t="n">
-        <v>26</v>
+        <v>22</v>
       </c>
       <c r="AI8" t="n">
-        <v>110</v>
+        <v>240</v>
       </c>
       <c r="AJ8" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="AK8" t="n">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="AL8" t="n">
         <v>38</v>
@@ -2483,128 +2483,128 @@
         <v>580</v>
       </c>
       <c r="AN8" t="n">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="AO8" t="n">
-        <v>130</v>
+        <v>95</v>
       </c>
       <c r="AP8" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="AQ8" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="AR8" t="n">
+        <v>20</v>
+      </c>
+      <c r="AS8" t="n">
+        <v>7</v>
+      </c>
+      <c r="AT8" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="AU8" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="AV8" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="AW8" t="n">
+        <v>7</v>
+      </c>
+      <c r="AX8" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="AY8" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="AZ8" t="n">
+        <v>5.6</v>
+      </c>
+      <c r="BA8" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="BB8" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="BC8" t="n">
+        <v>15</v>
+      </c>
+      <c r="BD8" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="BE8" t="n">
+        <v>7</v>
+      </c>
+      <c r="BF8" t="n">
+        <v>8</v>
+      </c>
+      <c r="BG8" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="BH8" t="n">
+        <v>3.55</v>
+      </c>
+      <c r="BI8" t="n">
+        <v>2.76</v>
+      </c>
+      <c r="BJ8" t="n">
         <v>11</v>
       </c>
-      <c r="AQ8" t="n">
-        <v>17</v>
-      </c>
-      <c r="AR8" t="n">
-        <v>5.8</v>
-      </c>
-      <c r="AS8" t="n">
-        <v>6.2</v>
-      </c>
-      <c r="AT8" t="n">
-        <v>7</v>
-      </c>
-      <c r="AU8" t="n">
-        <v>6.8</v>
-      </c>
-      <c r="AV8" t="n">
-        <v>17</v>
-      </c>
-      <c r="AW8" t="n">
-        <v>6</v>
-      </c>
-      <c r="AX8" t="n">
+      <c r="BK8" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="BL8" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BM8" t="n">
+        <v>10</v>
+      </c>
+      <c r="BN8" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="BO8" t="n">
+        <v>3.35</v>
+      </c>
+      <c r="BP8" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="BQ8" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="BR8" t="n">
+        <v>28</v>
+      </c>
+      <c r="BS8" t="n">
+        <v>8</v>
+      </c>
+      <c r="BT8" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="BU8" t="n">
+        <v>5</v>
+      </c>
+      <c r="BV8" t="n">
+        <v>50</v>
+      </c>
+      <c r="BW8" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="BX8" t="n">
+        <v>60</v>
+      </c>
+      <c r="BY8" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="BZ8" t="n">
+        <v>23</v>
+      </c>
+      <c r="CA8" t="n">
         <v>7.4</v>
       </c>
-      <c r="AY8" t="n">
-        <v>7.4</v>
-      </c>
-      <c r="AZ8" t="n">
-        <v>15.5</v>
-      </c>
-      <c r="BA8" t="n">
-        <v>6.2</v>
-      </c>
-      <c r="BB8" t="n">
-        <v>12</v>
-      </c>
-      <c r="BC8" t="n">
-        <v>13</v>
-      </c>
-      <c r="BD8" t="n">
-        <v>5.7</v>
-      </c>
-      <c r="BE8" t="n">
-        <v>6.2</v>
-      </c>
-      <c r="BF8" t="n">
-        <v>9</v>
-      </c>
-      <c r="BG8" t="n">
-        <v>6.2</v>
-      </c>
-      <c r="BH8" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BI8" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="BJ8" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BK8" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="BL8" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BM8" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="BN8" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BO8" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="BP8" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BQ8" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="BR8" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BS8" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="BT8" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BU8" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="BV8" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BW8" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="BX8" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BY8" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="BZ8" t="n">
-        <v>1000</v>
-      </c>
-      <c r="CA8" t="n">
-        <v>1.04</v>
-      </c>
       <c r="CB8" t="inlineStr">
         <is>
-          <t>2026-06-12 00:53:26</t>
+          <t>2026-06-12 03:08:58</t>
         </is>
       </c>
     </row>
@@ -2638,13 +2638,13 @@
         <v>4.5</v>
       </c>
       <c r="G9" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="H9" t="n">
         <v>1.71</v>
       </c>
       <c r="I9" t="n">
-        <v>1.82</v>
+        <v>1.81</v>
       </c>
       <c r="J9" t="n">
         <v>4.2</v>
@@ -2653,10 +2653,10 @@
         <v>4.8</v>
       </c>
       <c r="L9" t="n">
-        <v>1.24</v>
+        <v>1.28</v>
       </c>
       <c r="M9" t="n">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="N9" t="n">
         <v>5.5</v>
@@ -2665,19 +2665,19 @@
         <v>1.18</v>
       </c>
       <c r="P9" t="n">
-        <v>2.5</v>
+        <v>2.58</v>
       </c>
       <c r="Q9" t="n">
-        <v>1.54</v>
+        <v>1.55</v>
       </c>
       <c r="R9" t="n">
+        <v>1.63</v>
+      </c>
+      <c r="S9" t="n">
+        <v>2.34</v>
+      </c>
+      <c r="T9" t="n">
         <v>1.6</v>
-      </c>
-      <c r="S9" t="n">
-        <v>2.32</v>
-      </c>
-      <c r="T9" t="n">
-        <v>1.59</v>
       </c>
       <c r="U9" t="n">
         <v>2.38</v>
@@ -2686,22 +2686,22 @@
         <v>2.2</v>
       </c>
       <c r="W9" t="n">
-        <v>1.23</v>
+        <v>1.24</v>
       </c>
       <c r="X9" t="n">
-        <v>500</v>
+        <v>50</v>
       </c>
       <c r="Y9" t="n">
-        <v>18.5</v>
+        <v>13.5</v>
       </c>
       <c r="Z9" t="n">
-        <v>24</v>
+        <v>14</v>
       </c>
       <c r="AA9" t="n">
-        <v>34</v>
+        <v>20</v>
       </c>
       <c r="AB9" t="n">
-        <v>50</v>
+        <v>42</v>
       </c>
       <c r="AC9" t="n">
         <v>11</v>
@@ -2710,25 +2710,25 @@
         <v>11.5</v>
       </c>
       <c r="AE9" t="n">
-        <v>29</v>
+        <v>17.5</v>
       </c>
       <c r="AF9" t="n">
-        <v>500</v>
+        <v>220</v>
       </c>
       <c r="AG9" t="n">
-        <v>38</v>
+        <v>21</v>
       </c>
       <c r="AH9" t="n">
-        <v>29</v>
+        <v>17.5</v>
       </c>
       <c r="AI9" t="n">
-        <v>500</v>
+        <v>60</v>
       </c>
       <c r="AJ9" t="n">
-        <v>500</v>
+        <v>900</v>
       </c>
       <c r="AK9" t="n">
-        <v>500</v>
+        <v>320</v>
       </c>
       <c r="AL9" t="n">
         <v>500</v>
@@ -2737,25 +2737,25 @@
         <v>580</v>
       </c>
       <c r="AN9" t="n">
-        <v>500</v>
+        <v>290</v>
       </c>
       <c r="AO9" t="n">
         <v>7.6</v>
       </c>
       <c r="AP9" t="n">
-        <v>11.5</v>
+        <v>21</v>
       </c>
       <c r="AQ9" t="n">
         <v>11</v>
       </c>
       <c r="AR9" t="n">
-        <v>11</v>
+        <v>6.4</v>
       </c>
       <c r="AS9" t="n">
-        <v>9</v>
+        <v>16</v>
       </c>
       <c r="AT9" t="n">
-        <v>11.5</v>
+        <v>20</v>
       </c>
       <c r="AU9" t="n">
         <v>9</v>
@@ -2764,22 +2764,22 @@
         <v>9</v>
       </c>
       <c r="AW9" t="n">
-        <v>8.4</v>
+        <v>7.6</v>
       </c>
       <c r="AX9" t="n">
         <v>7.4</v>
       </c>
       <c r="AY9" t="n">
-        <v>16</v>
+        <v>6.2</v>
       </c>
       <c r="AZ9" t="n">
         <v>14</v>
       </c>
       <c r="BA9" t="n">
-        <v>6.8</v>
+        <v>14.5</v>
       </c>
       <c r="BB9" t="n">
-        <v>8.4</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BC9" t="n">
         <v>7.8</v>
@@ -2858,7 +2858,7 @@
       </c>
       <c r="CB9" t="inlineStr">
         <is>
-          <t>2026-06-12 00:53:26</t>
+          <t>2026-06-12 03:08:58</t>
         </is>
       </c>
     </row>
@@ -2889,13 +2889,13 @@
         </is>
       </c>
       <c r="F10" t="n">
-        <v>1.55</v>
+        <v>1.56</v>
       </c>
       <c r="G10" t="n">
-        <v>1.69</v>
+        <v>1.66</v>
       </c>
       <c r="H10" t="n">
-        <v>5.3</v>
+        <v>5.4</v>
       </c>
       <c r="I10" t="n">
         <v>6.4</v>
@@ -2904,34 +2904,34 @@
         <v>4.3</v>
       </c>
       <c r="K10" t="n">
-        <v>5.3</v>
+        <v>5.2</v>
       </c>
       <c r="L10" t="n">
-        <v>1.23</v>
+        <v>1.28</v>
       </c>
       <c r="M10" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="N10" t="n">
-        <v>5.3</v>
+        <v>5.5</v>
       </c>
       <c r="O10" t="n">
         <v>1.18</v>
       </c>
       <c r="P10" t="n">
-        <v>2.48</v>
+        <v>2.56</v>
       </c>
       <c r="Q10" t="n">
-        <v>1.54</v>
+        <v>1.55</v>
       </c>
       <c r="R10" t="n">
-        <v>1.6</v>
+        <v>1.63</v>
       </c>
       <c r="S10" t="n">
-        <v>2.34</v>
+        <v>2.38</v>
       </c>
       <c r="T10" t="n">
-        <v>1.64</v>
+        <v>1.65</v>
       </c>
       <c r="U10" t="n">
         <v>2.26</v>
@@ -2940,13 +2940,13 @@
         <v>1.18</v>
       </c>
       <c r="W10" t="n">
-        <v>2.46</v>
+        <v>2.48</v>
       </c>
       <c r="X10" t="n">
-        <v>70</v>
+        <v>75</v>
       </c>
       <c r="Y10" t="n">
-        <v>500</v>
+        <v>32</v>
       </c>
       <c r="Z10" t="n">
         <v>500</v>
@@ -2961,7 +2961,7 @@
         <v>12</v>
       </c>
       <c r="AD10" t="n">
-        <v>38</v>
+        <v>25</v>
       </c>
       <c r="AE10" t="n">
         <v>700</v>
@@ -3003,10 +3003,10 @@
         <v>21</v>
       </c>
       <c r="AR10" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="AS10" t="n">
         <v>8</v>
-      </c>
-      <c r="AS10" t="n">
-        <v>8.4</v>
       </c>
       <c r="AT10" t="n">
         <v>10</v>
@@ -3018,7 +3018,7 @@
         <v>11</v>
       </c>
       <c r="AW10" t="n">
-        <v>7.8</v>
+        <v>7.4</v>
       </c>
       <c r="AX10" t="n">
         <v>10</v>
@@ -3030,10 +3030,10 @@
         <v>15</v>
       </c>
       <c r="BA10" t="n">
-        <v>7.8</v>
+        <v>7.4</v>
       </c>
       <c r="BB10" t="n">
-        <v>14</v>
+        <v>13.5</v>
       </c>
       <c r="BC10" t="n">
         <v>13</v>
@@ -3042,31 +3042,31 @@
         <v>13</v>
       </c>
       <c r="BE10" t="n">
-        <v>8</v>
+        <v>7.6</v>
       </c>
       <c r="BF10" t="n">
-        <v>5.4</v>
+        <v>5.5</v>
       </c>
       <c r="BG10" t="n">
-        <v>7.8</v>
+        <v>7.4</v>
       </c>
       <c r="BH10" t="n">
         <v>4.7</v>
       </c>
       <c r="BI10" t="n">
-        <v>3.5</v>
+        <v>3.45</v>
       </c>
       <c r="BJ10" t="n">
         <v>10</v>
       </c>
       <c r="BK10" t="n">
-        <v>4.9</v>
+        <v>4.8</v>
       </c>
       <c r="BL10" t="n">
         <v>1000</v>
       </c>
       <c r="BM10" t="n">
-        <v>8.800000000000001</v>
+        <v>8.4</v>
       </c>
       <c r="BN10" t="n">
         <v>4.7</v>
@@ -3078,41 +3078,41 @@
         <v>10.5</v>
       </c>
       <c r="BQ10" t="n">
-        <v>5</v>
+        <v>4.9</v>
       </c>
       <c r="BR10" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="BS10" t="n">
-        <v>6.6</v>
+        <v>6.4</v>
       </c>
       <c r="BT10" t="n">
         <v>10</v>
       </c>
       <c r="BU10" t="n">
-        <v>4.9</v>
+        <v>4.8</v>
       </c>
       <c r="BV10" t="n">
         <v>1000</v>
       </c>
       <c r="BW10" t="n">
-        <v>8</v>
+        <v>7.6</v>
       </c>
       <c r="BX10" t="n">
         <v>1000</v>
       </c>
       <c r="BY10" t="n">
-        <v>8</v>
+        <v>7.6</v>
       </c>
       <c r="BZ10" t="n">
-        <v>13.5</v>
+        <v>14</v>
       </c>
       <c r="CA10" t="n">
         <v>5.6</v>
       </c>
       <c r="CB10" t="inlineStr">
         <is>
-          <t>2026-06-12 00:53:26</t>
+          <t>2026-06-12 03:08:58</t>
         </is>
       </c>
     </row>
@@ -3143,31 +3143,31 @@
         </is>
       </c>
       <c r="F11" t="n">
-        <v>2.18</v>
+        <v>2.2</v>
       </c>
       <c r="G11" t="n">
         <v>2.32</v>
       </c>
       <c r="H11" t="n">
-        <v>4.2</v>
+        <v>4.3</v>
       </c>
       <c r="I11" t="n">
         <v>4.7</v>
       </c>
       <c r="J11" t="n">
-        <v>2.88</v>
+        <v>2.9</v>
       </c>
       <c r="K11" t="n">
-        <v>3.15</v>
+        <v>3.05</v>
       </c>
       <c r="L11" t="n">
-        <v>1.6</v>
+        <v>1.61</v>
       </c>
       <c r="M11" t="n">
-        <v>1.13</v>
+        <v>1.14</v>
       </c>
       <c r="N11" t="n">
-        <v>2.52</v>
+        <v>2.6</v>
       </c>
       <c r="O11" t="n">
         <v>1.56</v>
@@ -3176,16 +3176,16 @@
         <v>1.5</v>
       </c>
       <c r="Q11" t="n">
-        <v>2.72</v>
+        <v>2.8</v>
       </c>
       <c r="R11" t="n">
         <v>1.18</v>
       </c>
       <c r="S11" t="n">
-        <v>5.7</v>
+        <v>5.8</v>
       </c>
       <c r="T11" t="n">
-        <v>2.18</v>
+        <v>2.16</v>
       </c>
       <c r="U11" t="n">
         <v>1.71</v>
@@ -3239,7 +3239,7 @@
         <v>34</v>
       </c>
       <c r="AL11" t="n">
-        <v>460</v>
+        <v>65</v>
       </c>
       <c r="AM11" t="n">
         <v>500</v>
@@ -3248,7 +3248,7 @@
         <v>40</v>
       </c>
       <c r="AO11" t="n">
-        <v>500</v>
+        <v>600</v>
       </c>
       <c r="AP11" t="n">
         <v>7</v>
@@ -3263,7 +3263,7 @@
         <v>11</v>
       </c>
       <c r="AT11" t="n">
-        <v>5.9</v>
+        <v>6</v>
       </c>
       <c r="AU11" t="n">
         <v>6.2</v>
@@ -3293,7 +3293,7 @@
         <v>14.5</v>
       </c>
       <c r="BD11" t="n">
-        <v>28</v>
+        <v>10</v>
       </c>
       <c r="BE11" t="n">
         <v>11.5</v>
@@ -3305,68 +3305,68 @@
         <v>11</v>
       </c>
       <c r="BH11" t="n">
-        <v>3.05</v>
+        <v>2.68</v>
       </c>
       <c r="BI11" t="n">
-        <v>1.04</v>
+        <v>2.24</v>
       </c>
       <c r="BJ11" t="n">
-        <v>1000</v>
+        <v>12</v>
       </c>
       <c r="BK11" t="n">
-        <v>1.5</v>
+        <v>6.2</v>
       </c>
       <c r="BL11" t="n">
         <v>1000</v>
       </c>
       <c r="BM11" t="n">
-        <v>1.5</v>
+        <v>12.5</v>
       </c>
       <c r="BN11" t="n">
-        <v>1000</v>
+        <v>4.9</v>
       </c>
       <c r="BO11" t="n">
-        <v>1.5</v>
+        <v>4.2</v>
       </c>
       <c r="BP11" t="n">
-        <v>1000</v>
+        <v>20</v>
       </c>
       <c r="BQ11" t="n">
-        <v>1.5</v>
+        <v>8</v>
       </c>
       <c r="BR11" t="n">
         <v>1000</v>
       </c>
       <c r="BS11" t="n">
-        <v>1.5</v>
+        <v>10.5</v>
       </c>
       <c r="BT11" t="n">
-        <v>1000</v>
+        <v>7.4</v>
       </c>
       <c r="BU11" t="n">
-        <v>1.5</v>
+        <v>5.4</v>
       </c>
       <c r="BV11" t="n">
         <v>1000</v>
       </c>
       <c r="BW11" t="n">
-        <v>1.5</v>
+        <v>10</v>
       </c>
       <c r="BX11" t="n">
         <v>1000</v>
       </c>
       <c r="BY11" t="n">
-        <v>1.5</v>
+        <v>11</v>
       </c>
       <c r="BZ11" t="n">
-        <v>1000</v>
+        <v>55</v>
       </c>
       <c r="CA11" t="n">
-        <v>1.5</v>
+        <v>10.5</v>
       </c>
       <c r="CB11" t="inlineStr">
         <is>
-          <t>2026-06-12 00:53:26</t>
+          <t>2026-06-12 03:08:58</t>
         </is>
       </c>
     </row>
@@ -3397,16 +3397,16 @@
         </is>
       </c>
       <c r="F12" t="n">
-        <v>2.24</v>
+        <v>2.3</v>
       </c>
       <c r="G12" t="n">
-        <v>2.44</v>
+        <v>2.42</v>
       </c>
       <c r="H12" t="n">
         <v>3.15</v>
       </c>
       <c r="I12" t="n">
-        <v>3.6</v>
+        <v>3.45</v>
       </c>
       <c r="J12" t="n">
         <v>3.5</v>
@@ -3415,43 +3415,43 @@
         <v>3.8</v>
       </c>
       <c r="L12" t="n">
-        <v>1.28</v>
+        <v>1.33</v>
       </c>
       <c r="M12" t="n">
         <v>1.05</v>
       </c>
       <c r="N12" t="n">
-        <v>4.3</v>
+        <v>4.6</v>
       </c>
       <c r="O12" t="n">
         <v>1.24</v>
       </c>
       <c r="P12" t="n">
-        <v>2.14</v>
+        <v>2.22</v>
       </c>
       <c r="Q12" t="n">
+        <v>1.72</v>
+      </c>
+      <c r="R12" t="n">
+        <v>1.47</v>
+      </c>
+      <c r="S12" t="n">
+        <v>2.82</v>
+      </c>
+      <c r="T12" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="U12" t="n">
+        <v>2.32</v>
+      </c>
+      <c r="V12" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="W12" t="n">
         <v>1.71</v>
       </c>
-      <c r="R12" t="n">
-        <v>1.45</v>
-      </c>
-      <c r="S12" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="T12" t="n">
-        <v>1.61</v>
-      </c>
-      <c r="U12" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="V12" t="n">
-        <v>1.38</v>
-      </c>
-      <c r="W12" t="n">
-        <v>1.69</v>
-      </c>
       <c r="X12" t="n">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="Y12" t="n">
         <v>16.5</v>
@@ -3463,7 +3463,7 @@
         <v>500</v>
       </c>
       <c r="AB12" t="n">
-        <v>12.5</v>
+        <v>13</v>
       </c>
       <c r="AC12" t="n">
         <v>9.199999999999999</v>
@@ -3502,7 +3502,7 @@
         <v>15</v>
       </c>
       <c r="AO12" t="n">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="AP12" t="n">
         <v>15.5</v>
@@ -3514,10 +3514,10 @@
         <v>19.5</v>
       </c>
       <c r="AS12" t="n">
-        <v>7.4</v>
+        <v>8.6</v>
       </c>
       <c r="AT12" t="n">
-        <v>8.4</v>
+        <v>10.5</v>
       </c>
       <c r="AU12" t="n">
         <v>7.4</v>
@@ -3526,13 +3526,13 @@
         <v>11.5</v>
       </c>
       <c r="AW12" t="n">
-        <v>27</v>
+        <v>13</v>
       </c>
       <c r="AX12" t="n">
-        <v>13.5</v>
+        <v>14</v>
       </c>
       <c r="AY12" t="n">
-        <v>8</v>
+        <v>9.6</v>
       </c>
       <c r="AZ12" t="n">
         <v>13</v>
@@ -3541,22 +3541,22 @@
         <v>32</v>
       </c>
       <c r="BB12" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="BC12" t="n">
         <v>19</v>
       </c>
       <c r="BD12" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="BE12" t="n">
         <v>28</v>
       </c>
       <c r="BF12" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="BG12" t="n">
-        <v>7.2</v>
+        <v>12</v>
       </c>
       <c r="BH12" t="n">
         <v>4.1</v>
@@ -3568,7 +3568,7 @@
         <v>9.4</v>
       </c>
       <c r="BK12" t="n">
-        <v>4.7</v>
+        <v>6.8</v>
       </c>
       <c r="BL12" t="n">
         <v>1000</v>
@@ -3580,7 +3580,7 @@
         <v>5.7</v>
       </c>
       <c r="BO12" t="n">
-        <v>4.1</v>
+        <v>4.6</v>
       </c>
       <c r="BP12" t="n">
         <v>16.5</v>
@@ -3598,10 +3598,10 @@
         <v>7</v>
       </c>
       <c r="BU12" t="n">
-        <v>5</v>
+        <v>5.6</v>
       </c>
       <c r="BV12" t="n">
-        <v>1000</v>
+        <v>25</v>
       </c>
       <c r="BW12" t="n">
         <v>6.8</v>
@@ -3620,7 +3620,7 @@
       </c>
       <c r="CB12" t="inlineStr">
         <is>
-          <t>2026-06-12 00:53:26</t>
+          <t>2026-06-12 03:08:58</t>
         </is>
       </c>
     </row>
@@ -3651,58 +3651,58 @@
         </is>
       </c>
       <c r="F13" t="n">
-        <v>1.14</v>
+        <v>1.15</v>
       </c>
       <c r="G13" t="n">
         <v>1.17</v>
       </c>
       <c r="H13" t="n">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="I13" t="n">
-        <v>32</v>
+        <v>27</v>
       </c>
       <c r="J13" t="n">
-        <v>9.4</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="K13" t="n">
-        <v>11.5</v>
+        <v>10.5</v>
       </c>
       <c r="L13" t="n">
-        <v>1.18</v>
+        <v>1.21</v>
       </c>
       <c r="M13" t="n">
         <v>1.02</v>
       </c>
       <c r="N13" t="n">
-        <v>7.4</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="O13" t="n">
-        <v>1.13</v>
+        <v>1.11</v>
       </c>
       <c r="P13" t="n">
-        <v>3.15</v>
+        <v>3.55</v>
       </c>
       <c r="Q13" t="n">
-        <v>1.37</v>
+        <v>1.35</v>
       </c>
       <c r="R13" t="n">
-        <v>1.89</v>
+        <v>2.04</v>
       </c>
       <c r="S13" t="n">
-        <v>1.95</v>
+        <v>1.87</v>
       </c>
       <c r="T13" t="n">
-        <v>2.32</v>
+        <v>2.02</v>
       </c>
       <c r="U13" t="n">
-        <v>1.61</v>
+        <v>1.81</v>
       </c>
       <c r="V13" t="n">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="W13" t="n">
-        <v>6.8</v>
+        <v>6.6</v>
       </c>
       <c r="X13" t="n">
         <v>950</v>
@@ -3711,170 +3711,170 @@
         <v>950</v>
       </c>
       <c r="Z13" t="n">
-        <v>1000</v>
+        <v>290</v>
       </c>
       <c r="AA13" t="n">
         <v>1000</v>
       </c>
       <c r="AB13" t="n">
-        <v>970</v>
+        <v>17</v>
       </c>
       <c r="AC13" t="n">
-        <v>950</v>
+        <v>24</v>
       </c>
       <c r="AD13" t="n">
         <v>950</v>
       </c>
       <c r="AE13" t="n">
-        <v>1000</v>
+        <v>370</v>
       </c>
       <c r="AF13" t="n">
-        <v>9.199999999999999</v>
+        <v>11</v>
       </c>
       <c r="AG13" t="n">
-        <v>17</v>
+        <v>14.5</v>
       </c>
       <c r="AH13" t="n">
         <v>950</v>
       </c>
       <c r="AI13" t="n">
-        <v>1000</v>
+        <v>240</v>
       </c>
       <c r="AJ13" t="n">
-        <v>9.4</v>
+        <v>11</v>
       </c>
       <c r="AK13" t="n">
-        <v>17.5</v>
+        <v>14.5</v>
       </c>
       <c r="AL13" t="n">
-        <v>60</v>
+        <v>50</v>
       </c>
       <c r="AM13" t="n">
-        <v>1000</v>
+        <v>210</v>
       </c>
       <c r="AN13" t="n">
-        <v>2.9</v>
+        <v>2.78</v>
       </c>
       <c r="AO13" t="n">
         <v>1000</v>
       </c>
       <c r="AP13" t="n">
-        <v>6.4</v>
+        <v>7.4</v>
       </c>
       <c r="AQ13" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="AR13" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="AS13" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="AT13" t="n">
+        <v>5.9</v>
+      </c>
+      <c r="AU13" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="AV13" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="AW13" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="AX13" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="AY13" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AZ13" t="n">
         <v>7</v>
       </c>
-      <c r="AR13" t="n">
-        <v>6.4</v>
-      </c>
-      <c r="AS13" t="n">
+      <c r="BA13" t="n">
+        <v>8</v>
+      </c>
+      <c r="BB13" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="BC13" t="n">
+        <v>11</v>
+      </c>
+      <c r="BD13" t="n">
+        <v>7</v>
+      </c>
+      <c r="BE13" t="n">
+        <v>8</v>
+      </c>
+      <c r="BF13" t="n">
+        <v>2.48</v>
+      </c>
+      <c r="BG13" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="BH13" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="BI13" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="BJ13" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="BK13" t="n">
+        <v>5.8</v>
+      </c>
+      <c r="BL13" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BM13" t="n">
+        <v>9</v>
+      </c>
+      <c r="BN13" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="BO13" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="BP13" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="BQ13" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="BR13" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BS13" t="n">
         <v>6.6</v>
       </c>
-      <c r="AT13" t="n">
-        <v>9.6</v>
-      </c>
-      <c r="AU13" t="n">
-        <v>5.9</v>
-      </c>
-      <c r="AV13" t="n">
-        <v>7</v>
-      </c>
-      <c r="AW13" t="n">
-        <v>6.4</v>
-      </c>
-      <c r="AX13" t="n">
-        <v>7.4</v>
-      </c>
-      <c r="AY13" t="n">
-        <v>11</v>
-      </c>
-      <c r="AZ13" t="n">
+      <c r="BT13" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BU13" t="n">
         <v>6.6</v>
       </c>
-      <c r="BA13" t="n">
-        <v>6.4</v>
-      </c>
-      <c r="BB13" t="n">
-        <v>7</v>
-      </c>
-      <c r="BC13" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="BD13" t="n">
+      <c r="BV13" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BW13" t="n">
+        <v>9</v>
+      </c>
+      <c r="BX13" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BY13" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="BZ13" t="n">
         <v>6.6</v>
       </c>
-      <c r="BE13" t="n">
-        <v>7.4</v>
-      </c>
-      <c r="BF13" t="n">
-        <v>2.56</v>
-      </c>
-      <c r="BG13" t="n">
-        <v>7.6</v>
-      </c>
-      <c r="BH13" t="n">
-        <v>5.8</v>
-      </c>
-      <c r="BI13" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="BJ13" t="n">
-        <v>16</v>
-      </c>
-      <c r="BK13" t="n">
-        <v>6.4</v>
-      </c>
-      <c r="BL13" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BM13" t="n">
-        <v>10</v>
-      </c>
-      <c r="BN13" t="n">
-        <v>3.95</v>
-      </c>
-      <c r="BO13" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="BP13" t="n">
-        <v>5.9</v>
-      </c>
-      <c r="BQ13" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="BR13" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BS13" t="n">
-        <v>7.2</v>
-      </c>
-      <c r="BT13" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BU13" t="n">
-        <v>7.4</v>
-      </c>
-      <c r="BV13" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BW13" t="n">
-        <v>10</v>
-      </c>
-      <c r="BX13" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BY13" t="n">
-        <v>10</v>
-      </c>
-      <c r="BZ13" t="n">
-        <v>6.8</v>
-      </c>
       <c r="CA13" t="n">
-        <v>5.1</v>
+        <v>4.9</v>
       </c>
       <c r="CB13" t="inlineStr">
         <is>
-          <t>2026-06-12 00:53:26</t>
+          <t>2026-06-12 03:08:58</t>
         </is>
       </c>
     </row>
@@ -3905,230 +3905,230 @@
         </is>
       </c>
       <c r="F14" t="n">
-        <v>3.8</v>
+        <v>3.25</v>
       </c>
       <c r="G14" t="n">
-        <v>4.2</v>
+        <v>3.45</v>
       </c>
       <c r="H14" t="n">
-        <v>2.08</v>
+        <v>2.36</v>
       </c>
       <c r="I14" t="n">
-        <v>2.16</v>
+        <v>2.44</v>
       </c>
       <c r="J14" t="n">
         <v>3.4</v>
       </c>
       <c r="K14" t="n">
-        <v>3.7</v>
+        <v>3.6</v>
       </c>
       <c r="L14" t="n">
-        <v>1.01</v>
+        <v>1.45</v>
       </c>
       <c r="M14" t="n">
         <v>1.08</v>
       </c>
       <c r="N14" t="n">
-        <v>3.35</v>
+        <v>3.5</v>
       </c>
       <c r="O14" t="n">
-        <v>1.35</v>
+        <v>1.36</v>
       </c>
       <c r="P14" t="n">
-        <v>1.82</v>
+        <v>1.83</v>
       </c>
       <c r="Q14" t="n">
-        <v>2.04</v>
+        <v>2.1</v>
       </c>
       <c r="R14" t="n">
         <v>1.31</v>
       </c>
       <c r="S14" t="n">
-        <v>4</v>
+        <v>3.9</v>
       </c>
       <c r="T14" t="n">
-        <v>1.86</v>
+        <v>1.79</v>
       </c>
       <c r="U14" t="n">
-        <v>2.02</v>
+        <v>2.06</v>
       </c>
       <c r="V14" t="n">
-        <v>1.87</v>
+        <v>1.7</v>
       </c>
       <c r="W14" t="n">
-        <v>1.32</v>
+        <v>1.41</v>
       </c>
       <c r="X14" t="n">
         <v>13.5</v>
       </c>
       <c r="Y14" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="Z14" t="n">
+        <v>16</v>
+      </c>
+      <c r="AA14" t="n">
+        <v>36</v>
+      </c>
+      <c r="AB14" t="n">
+        <v>12</v>
+      </c>
+      <c r="AC14" t="n">
+        <v>8</v>
+      </c>
+      <c r="AD14" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="AE14" t="n">
+        <v>29</v>
+      </c>
+      <c r="AF14" t="n">
+        <v>23</v>
+      </c>
+      <c r="AG14" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="AH14" t="n">
+        <v>18.5</v>
+      </c>
+      <c r="AI14" t="n">
+        <v>44</v>
+      </c>
+      <c r="AJ14" t="n">
+        <v>150</v>
+      </c>
+      <c r="AK14" t="n">
+        <v>42</v>
+      </c>
+      <c r="AL14" t="n">
+        <v>55</v>
+      </c>
+      <c r="AM14" t="n">
+        <v>110</v>
+      </c>
+      <c r="AN14" t="n">
+        <v>42</v>
+      </c>
+      <c r="AO14" t="n">
+        <v>24</v>
+      </c>
+      <c r="AP14" t="n">
+        <v>11</v>
+      </c>
+      <c r="AQ14" t="n">
         <v>8.800000000000001</v>
       </c>
-      <c r="Z14" t="n">
+      <c r="AR14" t="n">
+        <v>13</v>
+      </c>
+      <c r="AS14" t="n">
+        <v>29</v>
+      </c>
+      <c r="AT14" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AU14" t="n">
+        <v>7</v>
+      </c>
+      <c r="AV14" t="n">
+        <v>10</v>
+      </c>
+      <c r="AW14" t="n">
+        <v>24</v>
+      </c>
+      <c r="AX14" t="n">
+        <v>20</v>
+      </c>
+      <c r="AY14" t="n">
         <v>12.5</v>
       </c>
-      <c r="AA14" t="n">
-        <v>24</v>
-      </c>
-      <c r="AB14" t="n">
-        <v>14</v>
-      </c>
-      <c r="AC14" t="n">
+      <c r="AZ14" t="n">
+        <v>17</v>
+      </c>
+      <c r="BA14" t="n">
+        <v>38</v>
+      </c>
+      <c r="BB14" t="n">
+        <v>23</v>
+      </c>
+      <c r="BC14" t="n">
+        <v>36</v>
+      </c>
+      <c r="BD14" t="n">
+        <v>44</v>
+      </c>
+      <c r="BE14" t="n">
+        <v>16</v>
+      </c>
+      <c r="BF14" t="n">
+        <v>34</v>
+      </c>
+      <c r="BG14" t="n">
+        <v>19.5</v>
+      </c>
+      <c r="BH14" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="BI14" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="BJ14" t="n">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="BK14" t="n">
+        <v>5.9</v>
+      </c>
+      <c r="BL14" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BM14" t="n">
+        <v>13</v>
+      </c>
+      <c r="BN14" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="BO14" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="BP14" t="n">
+        <v>28</v>
+      </c>
+      <c r="BQ14" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="BR14" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BS14" t="n">
+        <v>11</v>
+      </c>
+      <c r="BT14" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="BU14" t="n">
+        <v>4</v>
+      </c>
+      <c r="BV14" t="n">
+        <v>18.5</v>
+      </c>
+      <c r="BW14" t="n">
         <v>8.199999999999999</v>
       </c>
-      <c r="AD14" t="n">
-        <v>11</v>
-      </c>
-      <c r="AE14" t="n">
-        <v>23</v>
-      </c>
-      <c r="AF14" t="n">
+      <c r="BX14" t="n">
         <v>34</v>
       </c>
-      <c r="AG14" t="n">
-        <v>17</v>
-      </c>
-      <c r="AH14" t="n">
-        <v>19.5</v>
-      </c>
-      <c r="AI14" t="n">
-        <v>100</v>
-      </c>
-      <c r="AJ14" t="n">
-        <v>900</v>
-      </c>
-      <c r="AK14" t="n">
-        <v>230</v>
-      </c>
-      <c r="AL14" t="n">
-        <v>370</v>
-      </c>
-      <c r="AM14" t="n">
-        <v>580</v>
-      </c>
-      <c r="AN14" t="n">
-        <v>240</v>
-      </c>
-      <c r="AO14" t="n">
-        <v>17</v>
-      </c>
-      <c r="AP14" t="n">
-        <v>6.8</v>
-      </c>
-      <c r="AQ14" t="n">
-        <v>5.3</v>
-      </c>
-      <c r="AR14" t="n">
-        <v>6.4</v>
-      </c>
-      <c r="AS14" t="n">
-        <v>8.6</v>
-      </c>
-      <c r="AT14" t="n">
-        <v>7</v>
-      </c>
-      <c r="AU14" t="n">
-        <v>5.1</v>
-      </c>
-      <c r="AV14" t="n">
-        <v>7</v>
-      </c>
-      <c r="AW14" t="n">
-        <v>8.6</v>
-      </c>
-      <c r="AX14" t="n">
-        <v>9.6</v>
-      </c>
-      <c r="AY14" t="n">
-        <v>7.6</v>
-      </c>
-      <c r="AZ14" t="n">
-        <v>8</v>
-      </c>
-      <c r="BA14" t="n">
+      <c r="BY14" t="n">
         <v>10</v>
       </c>
-      <c r="BB14" t="n">
-        <v>12</v>
-      </c>
-      <c r="BC14" t="n">
-        <v>11</v>
-      </c>
-      <c r="BD14" t="n">
-        <v>11</v>
-      </c>
-      <c r="BE14" t="n">
-        <v>12</v>
-      </c>
-      <c r="BF14" t="n">
-        <v>11</v>
-      </c>
-      <c r="BG14" t="n">
-        <v>7.6</v>
-      </c>
-      <c r="BH14" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BI14" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="BJ14" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BK14" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="BL14" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BM14" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="BN14" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BO14" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="BP14" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BQ14" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="BR14" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BS14" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="BT14" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BU14" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="BV14" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BW14" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="BX14" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BY14" t="n">
-        <v>1.04</v>
-      </c>
       <c r="BZ14" t="n">
-        <v>1000</v>
+        <v>30</v>
       </c>
       <c r="CA14" t="n">
-        <v>1.04</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="CB14" t="inlineStr">
         <is>
-          <t>2026-06-12 00:53:26</t>
+          <t>2026-06-12 03:08:58</t>
         </is>
       </c>
     </row>
@@ -4162,37 +4162,37 @@
         <v>2.42</v>
       </c>
       <c r="G15" t="n">
-        <v>2.74</v>
+        <v>2.66</v>
       </c>
       <c r="H15" t="n">
-        <v>3.4</v>
+        <v>3.45</v>
       </c>
       <c r="I15" t="n">
-        <v>3.9</v>
+        <v>3.85</v>
       </c>
       <c r="J15" t="n">
-        <v>2.8</v>
+        <v>2.88</v>
       </c>
       <c r="K15" t="n">
-        <v>3.1</v>
+        <v>3.15</v>
       </c>
       <c r="L15" t="n">
-        <v>1.52</v>
+        <v>1.63</v>
       </c>
       <c r="M15" t="n">
         <v>1.14</v>
       </c>
       <c r="N15" t="n">
-        <v>2.4</v>
+        <v>2.46</v>
       </c>
       <c r="O15" t="n">
-        <v>1.59</v>
+        <v>1.6</v>
       </c>
       <c r="P15" t="n">
         <v>1.46</v>
       </c>
       <c r="Q15" t="n">
-        <v>2.8</v>
+        <v>2.92</v>
       </c>
       <c r="R15" t="n">
         <v>1.17</v>
@@ -4201,25 +4201,25 @@
         <v>6</v>
       </c>
       <c r="T15" t="n">
-        <v>2.2</v>
+        <v>2.18</v>
       </c>
       <c r="U15" t="n">
-        <v>1.7</v>
+        <v>1.71</v>
       </c>
       <c r="V15" t="n">
-        <v>1.34</v>
+        <v>1.35</v>
       </c>
       <c r="W15" t="n">
-        <v>1.57</v>
+        <v>1.6</v>
       </c>
       <c r="X15" t="n">
-        <v>9.199999999999999</v>
+        <v>8</v>
       </c>
       <c r="Y15" t="n">
         <v>9.800000000000001</v>
       </c>
       <c r="Z15" t="n">
-        <v>28</v>
+        <v>90</v>
       </c>
       <c r="AA15" t="n">
         <v>900</v>
@@ -4240,19 +4240,19 @@
         <v>15.5</v>
       </c>
       <c r="AG15" t="n">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="AH15" t="n">
-        <v>30</v>
+        <v>65</v>
       </c>
       <c r="AI15" t="n">
-        <v>500</v>
+        <v>540</v>
       </c>
       <c r="AJ15" t="n">
-        <v>220</v>
+        <v>170</v>
       </c>
       <c r="AK15" t="n">
-        <v>95</v>
+        <v>140</v>
       </c>
       <c r="AL15" t="n">
         <v>460</v>
@@ -4261,22 +4261,22 @@
         <v>500</v>
       </c>
       <c r="AN15" t="n">
-        <v>110</v>
+        <v>600</v>
       </c>
       <c r="AO15" t="n">
-        <v>500</v>
+        <v>600</v>
       </c>
       <c r="AP15" t="n">
-        <v>4.2</v>
+        <v>4.3</v>
       </c>
       <c r="AQ15" t="n">
         <v>5.1</v>
       </c>
       <c r="AR15" t="n">
-        <v>5.5</v>
+        <v>6.8</v>
       </c>
       <c r="AS15" t="n">
-        <v>6.4</v>
+        <v>8.4</v>
       </c>
       <c r="AT15" t="n">
         <v>4.2</v>
@@ -4285,40 +4285,40 @@
         <v>4.2</v>
       </c>
       <c r="AV15" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AW15" t="n">
-        <v>6.2</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AX15" t="n">
         <v>7</v>
       </c>
       <c r="AY15" t="n">
-        <v>5.1</v>
+        <v>5.7</v>
       </c>
       <c r="AZ15" t="n">
-        <v>5.6</v>
+        <v>6.8</v>
       </c>
       <c r="BA15" t="n">
-        <v>6.6</v>
+        <v>8.6</v>
       </c>
       <c r="BB15" t="n">
-        <v>6</v>
+        <v>7.6</v>
       </c>
       <c r="BC15" t="n">
-        <v>5.9</v>
+        <v>7.6</v>
       </c>
       <c r="BD15" t="n">
-        <v>6.4</v>
+        <v>8.4</v>
       </c>
       <c r="BE15" t="n">
-        <v>6.8</v>
+        <v>9</v>
       </c>
       <c r="BF15" t="n">
-        <v>6</v>
+        <v>7.8</v>
       </c>
       <c r="BG15" t="n">
-        <v>6.6</v>
+        <v>8.6</v>
       </c>
       <c r="BH15" t="n">
         <v>2.64</v>
@@ -4382,7 +4382,7 @@
       </c>
       <c r="CB15" t="inlineStr">
         <is>
-          <t>2026-06-12 00:53:26</t>
+          <t>2026-06-12 03:08:58</t>
         </is>
       </c>
     </row>
@@ -4413,16 +4413,16 @@
         </is>
       </c>
       <c r="F16" t="n">
-        <v>3</v>
+        <v>2.92</v>
       </c>
       <c r="G16" t="n">
         <v>3.1</v>
       </c>
       <c r="H16" t="n">
-        <v>2.4</v>
+        <v>2.44</v>
       </c>
       <c r="I16" t="n">
-        <v>2.46</v>
+        <v>2.52</v>
       </c>
       <c r="J16" t="n">
         <v>3.7</v>
@@ -4431,40 +4431,40 @@
         <v>3.9</v>
       </c>
       <c r="L16" t="n">
-        <v>1.01</v>
+        <v>1.33</v>
       </c>
       <c r="M16" t="n">
         <v>1.05</v>
       </c>
       <c r="N16" t="n">
-        <v>4.8</v>
+        <v>5</v>
       </c>
       <c r="O16" t="n">
-        <v>1.22</v>
+        <v>1.23</v>
       </c>
       <c r="P16" t="n">
-        <v>2.32</v>
+        <v>2.34</v>
       </c>
       <c r="Q16" t="n">
-        <v>1.67</v>
+        <v>1.71</v>
       </c>
       <c r="R16" t="n">
-        <v>1.5</v>
+        <v>1.52</v>
       </c>
       <c r="S16" t="n">
-        <v>2.68</v>
+        <v>2.8</v>
       </c>
       <c r="T16" t="n">
-        <v>1.58</v>
+        <v>1.6</v>
       </c>
       <c r="U16" t="n">
         <v>2.52</v>
       </c>
       <c r="V16" t="n">
-        <v>1.68</v>
+        <v>1.66</v>
       </c>
       <c r="W16" t="n">
-        <v>1.47</v>
+        <v>1.48</v>
       </c>
       <c r="X16" t="n">
         <v>21</v>
@@ -4482,7 +4482,7 @@
         <v>16</v>
       </c>
       <c r="AC16" t="n">
-        <v>11</v>
+        <v>9.4</v>
       </c>
       <c r="AD16" t="n">
         <v>12.5</v>
@@ -4494,7 +4494,7 @@
         <v>23</v>
       </c>
       <c r="AG16" t="n">
-        <v>16.5</v>
+        <v>14</v>
       </c>
       <c r="AH16" t="n">
         <v>15.5</v>
@@ -4512,7 +4512,7 @@
         <v>38</v>
       </c>
       <c r="AM16" t="n">
-        <v>250</v>
+        <v>75</v>
       </c>
       <c r="AN16" t="n">
         <v>22</v>
@@ -4521,7 +4521,7 @@
         <v>15.5</v>
       </c>
       <c r="AP16" t="n">
-        <v>17</v>
+        <v>17.5</v>
       </c>
       <c r="AQ16" t="n">
         <v>11.5</v>
@@ -4530,10 +4530,10 @@
         <v>15.5</v>
       </c>
       <c r="AS16" t="n">
-        <v>16</v>
+        <v>28</v>
       </c>
       <c r="AT16" t="n">
-        <v>12.5</v>
+        <v>13.5</v>
       </c>
       <c r="AU16" t="n">
         <v>7.6</v>
@@ -4551,92 +4551,92 @@
         <v>11</v>
       </c>
       <c r="AZ16" t="n">
-        <v>12.5</v>
+        <v>13</v>
       </c>
       <c r="BA16" t="n">
-        <v>14.5</v>
+        <v>26</v>
       </c>
       <c r="BB16" t="n">
-        <v>7.6</v>
+        <v>38</v>
       </c>
       <c r="BC16" t="n">
-        <v>14.5</v>
+        <v>25</v>
       </c>
       <c r="BD16" t="n">
-        <v>16</v>
+        <v>29</v>
       </c>
       <c r="BE16" t="n">
-        <v>8.199999999999999</v>
+        <v>48</v>
       </c>
       <c r="BF16" t="n">
-        <v>17.5</v>
+        <v>19</v>
       </c>
       <c r="BG16" t="n">
         <v>13</v>
       </c>
       <c r="BH16" t="n">
-        <v>1000</v>
+        <v>4.2</v>
       </c>
       <c r="BI16" t="n">
-        <v>1.04</v>
+        <v>3.15</v>
       </c>
       <c r="BJ16" t="n">
-        <v>1000</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BK16" t="n">
         <v>1.04</v>
       </c>
       <c r="BL16" t="n">
-        <v>1000</v>
+        <v>90</v>
       </c>
       <c r="BM16" t="n">
         <v>1.04</v>
       </c>
       <c r="BN16" t="n">
-        <v>1000</v>
+        <v>6.6</v>
       </c>
       <c r="BO16" t="n">
-        <v>1.04</v>
+        <v>4.8</v>
       </c>
       <c r="BP16" t="n">
-        <v>1000</v>
+        <v>22</v>
       </c>
       <c r="BQ16" t="n">
         <v>1.04</v>
       </c>
       <c r="BR16" t="n">
-        <v>1000</v>
+        <v>30</v>
       </c>
       <c r="BS16" t="n">
         <v>1.04</v>
       </c>
       <c r="BT16" t="n">
-        <v>1000</v>
+        <v>5.9</v>
       </c>
       <c r="BU16" t="n">
-        <v>1.04</v>
+        <v>4.3</v>
       </c>
       <c r="BV16" t="n">
-        <v>1000</v>
+        <v>17.5</v>
       </c>
       <c r="BW16" t="n">
         <v>1.04</v>
       </c>
       <c r="BX16" t="n">
-        <v>1000</v>
+        <v>27</v>
       </c>
       <c r="BY16" t="n">
         <v>1.04</v>
       </c>
       <c r="BZ16" t="n">
-        <v>1000</v>
+        <v>20</v>
       </c>
       <c r="CA16" t="n">
         <v>1.04</v>
       </c>
       <c r="CB16" t="inlineStr">
         <is>
-          <t>2026-06-12 00:53:26</t>
+          <t>2026-06-12 03:08:58</t>
         </is>
       </c>
     </row>
@@ -4667,31 +4667,31 @@
         </is>
       </c>
       <c r="F17" t="n">
-        <v>1.37</v>
+        <v>1.4</v>
       </c>
       <c r="G17" t="n">
-        <v>1.41</v>
+        <v>1.43</v>
       </c>
       <c r="H17" t="n">
-        <v>10.5</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="I17" t="n">
-        <v>12</v>
+        <v>11.5</v>
       </c>
       <c r="J17" t="n">
-        <v>5</v>
+        <v>4.9</v>
       </c>
       <c r="K17" t="n">
-        <v>5.4</v>
+        <v>5.3</v>
       </c>
       <c r="L17" t="n">
-        <v>1.01</v>
+        <v>1.38</v>
       </c>
       <c r="M17" t="n">
         <v>1.06</v>
       </c>
       <c r="N17" t="n">
-        <v>3.95</v>
+        <v>4.2</v>
       </c>
       <c r="O17" t="n">
         <v>1.29</v>
@@ -4700,34 +4700,34 @@
         <v>2.06</v>
       </c>
       <c r="Q17" t="n">
-        <v>1.85</v>
+        <v>1.88</v>
       </c>
       <c r="R17" t="n">
-        <v>1.41</v>
+        <v>1.4</v>
       </c>
       <c r="S17" t="n">
-        <v>3.15</v>
+        <v>3.3</v>
       </c>
       <c r="T17" t="n">
-        <v>2.22</v>
+        <v>2.18</v>
       </c>
       <c r="U17" t="n">
-        <v>1.74</v>
+        <v>1.75</v>
       </c>
       <c r="V17" t="n">
-        <v>1.09</v>
+        <v>1.1</v>
       </c>
       <c r="W17" t="n">
-        <v>3.4</v>
+        <v>3.3</v>
       </c>
       <c r="X17" t="n">
         <v>17</v>
       </c>
       <c r="Y17" t="n">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="Z17" t="n">
-        <v>110</v>
+        <v>95</v>
       </c>
       <c r="AA17" t="n">
         <v>510</v>
@@ -4739,19 +4739,19 @@
         <v>12</v>
       </c>
       <c r="AD17" t="n">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="AE17" t="n">
-        <v>210</v>
+        <v>200</v>
       </c>
       <c r="AF17" t="n">
-        <v>7.8</v>
+        <v>8</v>
       </c>
       <c r="AG17" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="AH17" t="n">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="AI17" t="n">
         <v>170</v>
@@ -4766,34 +4766,34 @@
         <v>46</v>
       </c>
       <c r="AM17" t="n">
-        <v>260</v>
+        <v>240</v>
       </c>
       <c r="AN17" t="n">
         <v>7</v>
       </c>
       <c r="AO17" t="n">
-        <v>310</v>
+        <v>290</v>
       </c>
       <c r="AP17" t="n">
         <v>15</v>
       </c>
       <c r="AQ17" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="AR17" t="n">
-        <v>28</v>
+        <v>36</v>
       </c>
       <c r="AS17" t="n">
-        <v>11.5</v>
+        <v>13.5</v>
       </c>
       <c r="AT17" t="n">
         <v>7</v>
       </c>
       <c r="AU17" t="n">
-        <v>10.5</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AV17" t="n">
-        <v>19.5</v>
+        <v>18</v>
       </c>
       <c r="AW17" t="n">
         <v>12.5</v>
@@ -4808,10 +4808,10 @@
         <v>27</v>
       </c>
       <c r="BA17" t="n">
-        <v>13</v>
+        <v>12.5</v>
       </c>
       <c r="BB17" t="n">
-        <v>9.800000000000001</v>
+        <v>10</v>
       </c>
       <c r="BC17" t="n">
         <v>14</v>
@@ -4820,77 +4820,77 @@
         <v>36</v>
       </c>
       <c r="BE17" t="n">
-        <v>13.5</v>
+        <v>14</v>
       </c>
       <c r="BF17" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="BG17" t="n">
+        <v>15</v>
+      </c>
+      <c r="BH17" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="BI17" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="BJ17" t="n">
+        <v>13</v>
+      </c>
+      <c r="BK17" t="n">
+        <v>5.9</v>
+      </c>
+      <c r="BL17" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BM17" t="n">
+        <v>10</v>
+      </c>
+      <c r="BN17" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="BO17" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="BP17" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="BQ17" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="BR17" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BS17" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="BT17" t="n">
+        <v>14</v>
+      </c>
+      <c r="BU17" t="n">
         <v>6</v>
       </c>
-      <c r="BG17" t="n">
-        <v>14</v>
-      </c>
-      <c r="BH17" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BI17" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="BJ17" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BK17" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="BL17" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BM17" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="BN17" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BO17" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="BP17" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BQ17" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="BR17" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BS17" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="BT17" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BU17" t="n">
-        <v>1.04</v>
-      </c>
       <c r="BV17" t="n">
         <v>1000</v>
       </c>
       <c r="BW17" t="n">
-        <v>1.04</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BX17" t="n">
         <v>1000</v>
       </c>
       <c r="BY17" t="n">
-        <v>1.04</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BZ17" t="n">
-        <v>1000</v>
+        <v>16.5</v>
       </c>
       <c r="CA17" t="n">
-        <v>1.04</v>
+        <v>6.4</v>
       </c>
       <c r="CB17" t="inlineStr">
         <is>
-          <t>2026-06-12 00:53:26</t>
+          <t>2026-06-12 03:08:58</t>
         </is>
       </c>
     </row>
@@ -4924,10 +4924,10 @@
         <v>3.2</v>
       </c>
       <c r="G18" t="n">
-        <v>3.45</v>
+        <v>3.35</v>
       </c>
       <c r="H18" t="n">
-        <v>2.48</v>
+        <v>2.5</v>
       </c>
       <c r="I18" t="n">
         <v>2.58</v>
@@ -4939,40 +4939,40 @@
         <v>3.4</v>
       </c>
       <c r="L18" t="n">
-        <v>1.42</v>
+        <v>1.48</v>
       </c>
       <c r="M18" t="n">
         <v>1.09</v>
       </c>
       <c r="N18" t="n">
-        <v>3.1</v>
+        <v>3.25</v>
       </c>
       <c r="O18" t="n">
-        <v>1.41</v>
+        <v>1.42</v>
       </c>
       <c r="P18" t="n">
-        <v>1.73</v>
+        <v>1.74</v>
       </c>
       <c r="Q18" t="n">
-        <v>2.16</v>
+        <v>2.28</v>
       </c>
       <c r="R18" t="n">
-        <v>1.26</v>
+        <v>1.27</v>
       </c>
       <c r="S18" t="n">
-        <v>4.1</v>
+        <v>4.4</v>
       </c>
       <c r="T18" t="n">
-        <v>1.89</v>
+        <v>1.87</v>
       </c>
       <c r="U18" t="n">
-        <v>1.95</v>
+        <v>1.96</v>
       </c>
       <c r="V18" t="n">
         <v>1.63</v>
       </c>
       <c r="W18" t="n">
-        <v>1.41</v>
+        <v>1.42</v>
       </c>
       <c r="X18" t="n">
         <v>12</v>
@@ -5005,13 +5005,13 @@
         <v>14.5</v>
       </c>
       <c r="AH18" t="n">
-        <v>20</v>
+        <v>19.5</v>
       </c>
       <c r="AI18" t="n">
         <v>120</v>
       </c>
       <c r="AJ18" t="n">
-        <v>150</v>
+        <v>500</v>
       </c>
       <c r="AK18" t="n">
         <v>100</v>
@@ -5032,91 +5032,91 @@
         <v>9.6</v>
       </c>
       <c r="AQ18" t="n">
-        <v>7.8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AR18" t="n">
         <v>13</v>
       </c>
       <c r="AS18" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="AT18" t="n">
-        <v>9.199999999999999</v>
+        <v>9.6</v>
       </c>
       <c r="AU18" t="n">
-        <v>6.4</v>
+        <v>6.6</v>
       </c>
       <c r="AV18" t="n">
         <v>10</v>
       </c>
       <c r="AW18" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="AX18" t="n">
         <v>18</v>
       </c>
       <c r="AY18" t="n">
-        <v>11.5</v>
+        <v>12</v>
       </c>
       <c r="AZ18" t="n">
-        <v>16.5</v>
+        <v>17</v>
       </c>
       <c r="BA18" t="n">
         <v>34</v>
       </c>
       <c r="BB18" t="n">
-        <v>23</v>
+        <v>42</v>
       </c>
       <c r="BC18" t="n">
         <v>30</v>
       </c>
       <c r="BD18" t="n">
-        <v>23</v>
+        <v>40</v>
       </c>
       <c r="BE18" t="n">
-        <v>9.4</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BF18" t="n">
         <v>34</v>
       </c>
       <c r="BG18" t="n">
-        <v>7.6</v>
+        <v>7.8</v>
       </c>
       <c r="BH18" t="n">
         <v>3.15</v>
       </c>
       <c r="BI18" t="n">
-        <v>2.54</v>
+        <v>2.56</v>
       </c>
       <c r="BJ18" t="n">
         <v>10.5</v>
       </c>
       <c r="BK18" t="n">
-        <v>5.3</v>
+        <v>7.8</v>
       </c>
       <c r="BL18" t="n">
         <v>1000</v>
       </c>
       <c r="BM18" t="n">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="BN18" t="n">
         <v>6.6</v>
       </c>
       <c r="BO18" t="n">
-        <v>4.9</v>
+        <v>5</v>
       </c>
       <c r="BP18" t="n">
         <v>1000</v>
       </c>
       <c r="BQ18" t="n">
-        <v>7.8</v>
+        <v>8</v>
       </c>
       <c r="BR18" t="n">
         <v>1000</v>
       </c>
       <c r="BS18" t="n">
-        <v>8.800000000000001</v>
+        <v>9</v>
       </c>
       <c r="BT18" t="n">
         <v>5.5</v>
@@ -5134,17 +5134,17 @@
         <v>1000</v>
       </c>
       <c r="BY18" t="n">
-        <v>8.4</v>
+        <v>8.6</v>
       </c>
       <c r="BZ18" t="n">
         <v>1000</v>
       </c>
       <c r="CA18" t="n">
-        <v>8.4</v>
+        <v>8.6</v>
       </c>
       <c r="CB18" t="inlineStr">
         <is>
-          <t>2026-06-12 00:53:26</t>
+          <t>2026-06-12 03:08:58</t>
         </is>
       </c>
     </row>
@@ -5175,16 +5175,16 @@
         </is>
       </c>
       <c r="F19" t="n">
-        <v>2.26</v>
+        <v>2.3</v>
       </c>
       <c r="G19" t="n">
-        <v>2.38</v>
+        <v>2.36</v>
       </c>
       <c r="H19" t="n">
         <v>3.3</v>
       </c>
       <c r="I19" t="n">
-        <v>3.4</v>
+        <v>3.45</v>
       </c>
       <c r="J19" t="n">
         <v>3.6</v>
@@ -5193,49 +5193,49 @@
         <v>3.8</v>
       </c>
       <c r="L19" t="n">
-        <v>1.37</v>
+        <v>1.39</v>
       </c>
       <c r="M19" t="n">
         <v>1.06</v>
       </c>
       <c r="N19" t="n">
-        <v>3.8</v>
+        <v>4.1</v>
       </c>
       <c r="O19" t="n">
-        <v>1.29</v>
+        <v>1.3</v>
       </c>
       <c r="P19" t="n">
-        <v>1.98</v>
+        <v>2.02</v>
       </c>
       <c r="Q19" t="n">
-        <v>1.89</v>
+        <v>1.93</v>
       </c>
       <c r="R19" t="n">
-        <v>1.37</v>
+        <v>1.39</v>
       </c>
       <c r="S19" t="n">
-        <v>3.35</v>
+        <v>3.4</v>
       </c>
       <c r="T19" t="n">
-        <v>1.71</v>
+        <v>1.7</v>
       </c>
       <c r="U19" t="n">
-        <v>2.16</v>
+        <v>2.22</v>
       </c>
       <c r="V19" t="n">
-        <v>1.42</v>
+        <v>1.41</v>
       </c>
       <c r="W19" t="n">
         <v>1.73</v>
       </c>
       <c r="X19" t="n">
-        <v>16.5</v>
+        <v>16</v>
       </c>
       <c r="Y19" t="n">
-        <v>14</v>
+        <v>13.5</v>
       </c>
       <c r="Z19" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AA19" t="n">
         <v>130</v>
@@ -5244,10 +5244,10 @@
         <v>11</v>
       </c>
       <c r="AC19" t="n">
-        <v>8.800000000000001</v>
+        <v>8.6</v>
       </c>
       <c r="AD19" t="n">
-        <v>14.5</v>
+        <v>14</v>
       </c>
       <c r="AE19" t="n">
         <v>50</v>
@@ -5289,13 +5289,13 @@
         <v>10.5</v>
       </c>
       <c r="AR19" t="n">
-        <v>20</v>
+        <v>19.5</v>
       </c>
       <c r="AS19" t="n">
         <v>34</v>
       </c>
       <c r="AT19" t="n">
-        <v>9</v>
+        <v>9.4</v>
       </c>
       <c r="AU19" t="n">
         <v>7.2</v>
@@ -5328,13 +5328,13 @@
         <v>25</v>
       </c>
       <c r="BE19" t="n">
-        <v>9.199999999999999</v>
+        <v>10</v>
       </c>
       <c r="BF19" t="n">
-        <v>13.5</v>
+        <v>15</v>
       </c>
       <c r="BG19" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="BH19" t="n">
         <v>3.65</v>
@@ -5370,7 +5370,7 @@
         <v>1000</v>
       </c>
       <c r="BS19" t="n">
-        <v>8.800000000000001</v>
+        <v>8.6</v>
       </c>
       <c r="BT19" t="n">
         <v>6.8</v>
@@ -5382,23 +5382,23 @@
         <v>1000</v>
       </c>
       <c r="BW19" t="n">
-        <v>8.4</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BX19" t="n">
         <v>1000</v>
       </c>
       <c r="BY19" t="n">
-        <v>9.199999999999999</v>
+        <v>9</v>
       </c>
       <c r="BZ19" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="CA19" t="n">
         <v>8.199999999999999</v>
       </c>
       <c r="CB19" t="inlineStr">
         <is>
-          <t>2026-06-12 00:53:26</t>
+          <t>2026-06-12 03:08:58</t>
         </is>
       </c>
     </row>
@@ -5429,46 +5429,46 @@
         </is>
       </c>
       <c r="F20" t="n">
-        <v>3.95</v>
+        <v>4.2</v>
       </c>
       <c r="G20" t="n">
         <v>4.5</v>
       </c>
       <c r="H20" t="n">
-        <v>1.91</v>
+        <v>1.92</v>
       </c>
       <c r="I20" t="n">
-        <v>2.02</v>
+        <v>1.97</v>
       </c>
       <c r="J20" t="n">
-        <v>3.7</v>
+        <v>3.75</v>
       </c>
       <c r="K20" t="n">
-        <v>4.2</v>
+        <v>4.1</v>
       </c>
       <c r="L20" t="n">
-        <v>1.01</v>
+        <v>1.34</v>
       </c>
       <c r="M20" t="n">
         <v>1.05</v>
       </c>
       <c r="N20" t="n">
-        <v>4.4</v>
+        <v>4.8</v>
       </c>
       <c r="O20" t="n">
-        <v>1.23</v>
+        <v>1.24</v>
       </c>
       <c r="P20" t="n">
-        <v>2.18</v>
+        <v>2.28</v>
       </c>
       <c r="Q20" t="n">
-        <v>1.71</v>
+        <v>1.73</v>
       </c>
       <c r="R20" t="n">
         <v>1.53</v>
       </c>
       <c r="S20" t="n">
-        <v>2.56</v>
+        <v>2.84</v>
       </c>
       <c r="T20" t="n">
         <v>1.64</v>
@@ -5477,10 +5477,10 @@
         <v>2.3</v>
       </c>
       <c r="V20" t="n">
-        <v>1.98</v>
+        <v>2.02</v>
       </c>
       <c r="W20" t="n">
-        <v>1.3</v>
+        <v>1.28</v>
       </c>
       <c r="X20" t="n">
         <v>21</v>
@@ -5498,161 +5498,161 @@
         <v>22</v>
       </c>
       <c r="AC20" t="n">
-        <v>11.5</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AD20" t="n">
-        <v>12.5</v>
+        <v>12</v>
       </c>
       <c r="AE20" t="n">
         <v>22</v>
       </c>
       <c r="AF20" t="n">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="AG20" t="n">
-        <v>23</v>
+        <v>19.5</v>
       </c>
       <c r="AH20" t="n">
-        <v>18.5</v>
+        <v>16</v>
       </c>
       <c r="AI20" t="n">
         <v>36</v>
       </c>
       <c r="AJ20" t="n">
-        <v>120</v>
+        <v>900</v>
       </c>
       <c r="AK20" t="n">
         <v>55</v>
       </c>
       <c r="AL20" t="n">
-        <v>48</v>
+        <v>44</v>
       </c>
       <c r="AM20" t="n">
-        <v>80</v>
+        <v>320</v>
       </c>
       <c r="AN20" t="n">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="AO20" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="AP20" t="n">
-        <v>14</v>
+        <v>16.5</v>
       </c>
       <c r="AQ20" t="n">
-        <v>9.6</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AR20" t="n">
-        <v>10</v>
+        <v>11.5</v>
       </c>
       <c r="AS20" t="n">
-        <v>18.5</v>
+        <v>21</v>
       </c>
       <c r="AT20" t="n">
-        <v>15.5</v>
+        <v>15</v>
       </c>
       <c r="AU20" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AV20" t="n">
         <v>10</v>
       </c>
       <c r="AW20" t="n">
-        <v>12.5</v>
+        <v>15</v>
       </c>
       <c r="AX20" t="n">
-        <v>24</v>
+        <v>15</v>
       </c>
       <c r="AY20" t="n">
-        <v>16</v>
+        <v>15.5</v>
       </c>
       <c r="AZ20" t="n">
-        <v>11.5</v>
+        <v>13</v>
       </c>
       <c r="BA20" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="BB20" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="BC20" t="n">
         <v>20</v>
       </c>
-      <c r="BB20" t="n">
-        <v>5</v>
-      </c>
-      <c r="BC20" t="n">
-        <v>30</v>
-      </c>
       <c r="BD20" t="n">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="BE20" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="BF20" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="BG20" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="BH20" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="BI20" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="BJ20" t="n">
+        <v>13</v>
+      </c>
+      <c r="BK20" t="n">
+        <v>2.82</v>
+      </c>
+      <c r="BL20" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BM20" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="BN20" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="BO20" t="n">
         <v>4.9</v>
       </c>
-      <c r="BF20" t="n">
+      <c r="BP20" t="n">
+        <v>46</v>
+      </c>
+      <c r="BQ20" t="n">
+        <v>3.35</v>
+      </c>
+      <c r="BR20" t="n">
+        <v>50</v>
+      </c>
+      <c r="BS20" t="n">
+        <v>3.35</v>
+      </c>
+      <c r="BT20" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="BU20" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="BV20" t="n">
+        <v>19</v>
+      </c>
+      <c r="BW20" t="n">
+        <v>3</v>
+      </c>
+      <c r="BX20" t="n">
+        <v>34</v>
+      </c>
+      <c r="BY20" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="BZ20" t="n">
         <v>28</v>
       </c>
-      <c r="BG20" t="n">
-        <v>7.4</v>
-      </c>
-      <c r="BH20" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BI20" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="BJ20" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BK20" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="BL20" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BM20" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="BN20" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BO20" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="BP20" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BQ20" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="BR20" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BS20" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="BT20" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BU20" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="BV20" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BW20" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="BX20" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BY20" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="BZ20" t="n">
-        <v>1000</v>
-      </c>
       <c r="CA20" t="n">
-        <v>1.04</v>
+        <v>3.2</v>
       </c>
       <c r="CB20" t="inlineStr">
         <is>
-          <t>2026-06-12 00:53:26</t>
+          <t>2026-06-12 03:08:58</t>
         </is>
       </c>
     </row>
@@ -5683,46 +5683,46 @@
         </is>
       </c>
       <c r="F21" t="n">
-        <v>2.3</v>
+        <v>2.38</v>
       </c>
       <c r="G21" t="n">
-        <v>2.48</v>
+        <v>2.46</v>
       </c>
       <c r="H21" t="n">
-        <v>3.4</v>
+        <v>3.35</v>
       </c>
       <c r="I21" t="n">
-        <v>3.75</v>
+        <v>3.6</v>
       </c>
       <c r="J21" t="n">
-        <v>3.15</v>
+        <v>3.3</v>
       </c>
       <c r="K21" t="n">
         <v>3.45</v>
       </c>
       <c r="L21" t="n">
-        <v>1.4</v>
+        <v>1.49</v>
       </c>
       <c r="M21" t="n">
-        <v>1.09</v>
+        <v>1.1</v>
       </c>
       <c r="N21" t="n">
-        <v>3.1</v>
+        <v>3.2</v>
       </c>
       <c r="O21" t="n">
         <v>1.42</v>
       </c>
       <c r="P21" t="n">
-        <v>1.71</v>
+        <v>1.73</v>
       </c>
       <c r="Q21" t="n">
-        <v>2.22</v>
+        <v>2.28</v>
       </c>
       <c r="R21" t="n">
         <v>1.27</v>
       </c>
       <c r="S21" t="n">
-        <v>4.2</v>
+        <v>4.3</v>
       </c>
       <c r="T21" t="n">
         <v>1.91</v>
@@ -5731,16 +5731,16 @@
         <v>1.97</v>
       </c>
       <c r="V21" t="n">
-        <v>1.37</v>
+        <v>1.39</v>
       </c>
       <c r="W21" t="n">
-        <v>1.67</v>
+        <v>1.69</v>
       </c>
       <c r="X21" t="n">
         <v>13.5</v>
       </c>
       <c r="Y21" t="n">
-        <v>14</v>
+        <v>13.5</v>
       </c>
       <c r="Z21" t="n">
         <v>30</v>
@@ -5791,55 +5791,55 @@
         <v>90</v>
       </c>
       <c r="AP21" t="n">
-        <v>8.199999999999999</v>
+        <v>9.6</v>
       </c>
       <c r="AQ21" t="n">
-        <v>8.4</v>
+        <v>10</v>
       </c>
       <c r="AR21" t="n">
-        <v>17.5</v>
+        <v>10.5</v>
       </c>
       <c r="AS21" t="n">
-        <v>5</v>
+        <v>5.1</v>
       </c>
       <c r="AT21" t="n">
-        <v>6.4</v>
+        <v>7.6</v>
       </c>
       <c r="AU21" t="n">
-        <v>5.6</v>
+        <v>6.6</v>
       </c>
       <c r="AV21" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="AW21" t="n">
         <v>5</v>
       </c>
       <c r="AX21" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="AY21" t="n">
+        <v>10</v>
+      </c>
+      <c r="AZ21" t="n">
         <v>10.5</v>
       </c>
-      <c r="AY21" t="n">
-        <v>8.6</v>
-      </c>
-      <c r="AZ21" t="n">
-        <v>14</v>
-      </c>
       <c r="BA21" t="n">
-        <v>5</v>
+        <v>5.1</v>
       </c>
       <c r="BB21" t="n">
-        <v>14.5</v>
+        <v>4.9</v>
       </c>
       <c r="BC21" t="n">
-        <v>21</v>
+        <v>13</v>
       </c>
       <c r="BD21" t="n">
         <v>5</v>
       </c>
       <c r="BE21" t="n">
-        <v>5.2</v>
+        <v>5.3</v>
       </c>
       <c r="BF21" t="n">
-        <v>19</v>
+        <v>5.4</v>
       </c>
       <c r="BG21" t="n">
         <v>8.6</v>
@@ -5866,7 +5866,7 @@
         <v>5.1</v>
       </c>
       <c r="BO21" t="n">
-        <v>3.9</v>
+        <v>3.95</v>
       </c>
       <c r="BP21" t="n">
         <v>1000</v>
@@ -5884,7 +5884,7 @@
         <v>6.6</v>
       </c>
       <c r="BU21" t="n">
-        <v>5</v>
+        <v>4.9</v>
       </c>
       <c r="BV21" t="n">
         <v>1000</v>
@@ -5906,7 +5906,7 @@
       </c>
       <c r="CB21" t="inlineStr">
         <is>
-          <t>2026-06-12 00:53:26</t>
+          <t>2026-06-12 03:08:58</t>
         </is>
       </c>
     </row>
@@ -5937,49 +5937,49 @@
         </is>
       </c>
       <c r="F22" t="n">
-        <v>3.9</v>
+        <v>3.8</v>
       </c>
       <c r="G22" t="n">
-        <v>4.3</v>
+        <v>4.2</v>
       </c>
       <c r="H22" t="n">
-        <v>1.95</v>
+        <v>1.99</v>
       </c>
       <c r="I22" t="n">
-        <v>2.1</v>
+        <v>2.08</v>
       </c>
       <c r="J22" t="n">
-        <v>3.65</v>
+        <v>3.75</v>
       </c>
       <c r="K22" t="n">
-        <v>4.2</v>
+        <v>4</v>
       </c>
       <c r="L22" t="n">
-        <v>1.01</v>
+        <v>1.36</v>
       </c>
       <c r="M22" t="n">
         <v>1.06</v>
       </c>
       <c r="N22" t="n">
-        <v>4.2</v>
+        <v>4.5</v>
       </c>
       <c r="O22" t="n">
         <v>1.26</v>
       </c>
       <c r="P22" t="n">
-        <v>2.08</v>
+        <v>2.18</v>
       </c>
       <c r="Q22" t="n">
-        <v>1.77</v>
+        <v>1.79</v>
       </c>
       <c r="R22" t="n">
-        <v>1.33</v>
+        <v>1.46</v>
       </c>
       <c r="S22" t="n">
-        <v>2.84</v>
+        <v>3.05</v>
       </c>
       <c r="T22" t="n">
-        <v>1.37</v>
+        <v>1.69</v>
       </c>
       <c r="U22" t="n">
         <v>1.73</v>
@@ -5988,19 +5988,19 @@
         <v>1.92</v>
       </c>
       <c r="W22" t="n">
-        <v>1.3</v>
+        <v>1.32</v>
       </c>
       <c r="X22" t="n">
-        <v>18</v>
+        <v>17.5</v>
       </c>
       <c r="Y22" t="n">
         <v>11</v>
       </c>
       <c r="Z22" t="n">
-        <v>14</v>
+        <v>13.5</v>
       </c>
       <c r="AA22" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="AB22" t="n">
         <v>17.5</v>
@@ -6027,16 +6027,16 @@
         <v>34</v>
       </c>
       <c r="AJ22" t="n">
-        <v>900</v>
+        <v>500</v>
       </c>
       <c r="AK22" t="n">
-        <v>110</v>
+        <v>48</v>
       </c>
       <c r="AL22" t="n">
         <v>55</v>
       </c>
       <c r="AM22" t="n">
-        <v>200</v>
+        <v>320</v>
       </c>
       <c r="AN22" t="n">
         <v>46</v>
@@ -6045,25 +6045,25 @@
         <v>12.5</v>
       </c>
       <c r="AP22" t="n">
-        <v>13.5</v>
+        <v>14.5</v>
       </c>
       <c r="AQ22" t="n">
-        <v>9.199999999999999</v>
+        <v>9</v>
       </c>
       <c r="AR22" t="n">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="AS22" t="n">
-        <v>19.5</v>
+        <v>20</v>
       </c>
       <c r="AT22" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AU22" t="n">
         <v>7.4</v>
       </c>
       <c r="AV22" t="n">
-        <v>9</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AW22" t="n">
         <v>17</v>
@@ -6081,19 +6081,19 @@
         <v>16</v>
       </c>
       <c r="BB22" t="n">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="BC22" t="n">
         <v>9.199999999999999</v>
       </c>
-      <c r="BC22" t="n">
-        <v>8.4</v>
-      </c>
       <c r="BD22" t="n">
-        <v>8.6</v>
+        <v>9.4</v>
       </c>
       <c r="BE22" t="n">
-        <v>9.199999999999999</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BF22" t="n">
-        <v>8.4</v>
+        <v>9</v>
       </c>
       <c r="BG22" t="n">
         <v>10</v>
@@ -6102,10 +6102,10 @@
         <v>1000</v>
       </c>
       <c r="BI22" t="n">
-        <v>1.04</v>
+        <v>3.1</v>
       </c>
       <c r="BJ22" t="n">
-        <v>1000</v>
+        <v>9.6</v>
       </c>
       <c r="BK22" t="n">
         <v>1.04</v>
@@ -6117,50 +6117,50 @@
         <v>1.04</v>
       </c>
       <c r="BN22" t="n">
-        <v>1000</v>
+        <v>7.8</v>
       </c>
       <c r="BO22" t="n">
-        <v>1.04</v>
+        <v>5.8</v>
       </c>
       <c r="BP22" t="n">
-        <v>1000</v>
+        <v>32</v>
       </c>
       <c r="BQ22" t="n">
         <v>1.04</v>
       </c>
       <c r="BR22" t="n">
-        <v>1000</v>
+        <v>40</v>
       </c>
       <c r="BS22" t="n">
         <v>1.04</v>
       </c>
       <c r="BT22" t="n">
-        <v>1000</v>
+        <v>5.1</v>
       </c>
       <c r="BU22" t="n">
-        <v>1.04</v>
+        <v>3.95</v>
       </c>
       <c r="BV22" t="n">
-        <v>1000</v>
+        <v>14.5</v>
       </c>
       <c r="BW22" t="n">
         <v>1.04</v>
       </c>
       <c r="BX22" t="n">
-        <v>1000</v>
+        <v>26</v>
       </c>
       <c r="BY22" t="n">
         <v>1.04</v>
       </c>
       <c r="BZ22" t="n">
-        <v>1000</v>
+        <v>21</v>
       </c>
       <c r="CA22" t="n">
         <v>1.04</v>
       </c>
       <c r="CB22" t="inlineStr">
         <is>
-          <t>2026-06-12 00:53:26</t>
+          <t>2026-06-12 03:08:58</t>
         </is>
       </c>
     </row>
@@ -6191,16 +6191,16 @@
         </is>
       </c>
       <c r="F23" t="n">
-        <v>4.4</v>
+        <v>4.5</v>
       </c>
       <c r="G23" t="n">
-        <v>4.9</v>
+        <v>5</v>
       </c>
       <c r="H23" t="n">
-        <v>1.91</v>
+        <v>1.9</v>
       </c>
       <c r="I23" t="n">
-        <v>1.99</v>
+        <v>1.95</v>
       </c>
       <c r="J23" t="n">
         <v>3.6</v>
@@ -6209,37 +6209,37 @@
         <v>3.7</v>
       </c>
       <c r="L23" t="n">
-        <v>1.35</v>
+        <v>1.4</v>
       </c>
       <c r="M23" t="n">
         <v>1.06</v>
       </c>
       <c r="N23" t="n">
-        <v>3.7</v>
+        <v>4</v>
       </c>
       <c r="O23" t="n">
         <v>1.3</v>
       </c>
       <c r="P23" t="n">
-        <v>1.91</v>
+        <v>2</v>
       </c>
       <c r="Q23" t="n">
-        <v>1.9</v>
+        <v>1.94</v>
       </c>
       <c r="R23" t="n">
-        <v>1.35</v>
+        <v>1.38</v>
       </c>
       <c r="S23" t="n">
-        <v>3.3</v>
+        <v>3.4</v>
       </c>
       <c r="T23" t="n">
-        <v>1.79</v>
+        <v>1.78</v>
       </c>
       <c r="U23" t="n">
+        <v>2.06</v>
+      </c>
+      <c r="V23" t="n">
         <v>2.04</v>
-      </c>
-      <c r="V23" t="n">
-        <v>2</v>
       </c>
       <c r="W23" t="n">
         <v>1.26</v>
@@ -6260,7 +6260,7 @@
         <v>17</v>
       </c>
       <c r="AC23" t="n">
-        <v>9</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AD23" t="n">
         <v>11</v>
@@ -6272,7 +6272,7 @@
         <v>36</v>
       </c>
       <c r="AG23" t="n">
-        <v>19</v>
+        <v>18.5</v>
       </c>
       <c r="AH23" t="n">
         <v>19.5</v>
@@ -6284,7 +6284,7 @@
         <v>900</v>
       </c>
       <c r="AK23" t="n">
-        <v>65</v>
+        <v>70</v>
       </c>
       <c r="AL23" t="n">
         <v>75</v>
@@ -6293,7 +6293,7 @@
         <v>580</v>
       </c>
       <c r="AN23" t="n">
-        <v>150</v>
+        <v>65</v>
       </c>
       <c r="AO23" t="n">
         <v>13.5</v>
@@ -6335,7 +6335,7 @@
         <v>24</v>
       </c>
       <c r="BB23" t="n">
-        <v>8.800000000000001</v>
+        <v>9.4</v>
       </c>
       <c r="BC23" t="n">
         <v>38</v>
@@ -6344,7 +6344,7 @@
         <v>42</v>
       </c>
       <c r="BE23" t="n">
-        <v>8.800000000000001</v>
+        <v>9</v>
       </c>
       <c r="BF23" t="n">
         <v>12.5</v>
@@ -6353,40 +6353,40 @@
         <v>11</v>
       </c>
       <c r="BH23" t="n">
-        <v>3.6</v>
+        <v>3.65</v>
       </c>
       <c r="BI23" t="n">
-        <v>3.05</v>
+        <v>3.1</v>
       </c>
       <c r="BJ23" t="n">
         <v>10.5</v>
       </c>
       <c r="BK23" t="n">
-        <v>5</v>
+        <v>5.1</v>
       </c>
       <c r="BL23" t="n">
         <v>1000</v>
       </c>
       <c r="BM23" t="n">
-        <v>9.199999999999999</v>
+        <v>9.4</v>
       </c>
       <c r="BN23" t="n">
-        <v>8.4</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BO23" t="n">
-        <v>4.5</v>
+        <v>6</v>
       </c>
       <c r="BP23" t="n">
         <v>40</v>
       </c>
       <c r="BQ23" t="n">
-        <v>7.8</v>
+        <v>8</v>
       </c>
       <c r="BR23" t="n">
-        <v>50</v>
+        <v>1000</v>
       </c>
       <c r="BS23" t="n">
-        <v>8.199999999999999</v>
+        <v>8.4</v>
       </c>
       <c r="BT23" t="n">
         <v>4.8</v>
@@ -6398,23 +6398,23 @@
         <v>14</v>
       </c>
       <c r="BW23" t="n">
-        <v>5.7</v>
+        <v>5.8</v>
       </c>
       <c r="BX23" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="BY23" t="n">
-        <v>7.2</v>
+        <v>7.4</v>
       </c>
       <c r="BZ23" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="CA23" t="n">
         <v>7</v>
       </c>
       <c r="CB23" t="inlineStr">
         <is>
-          <t>2026-06-12 00:53:26</t>
+          <t>2026-06-12 03:08:58</t>
         </is>
       </c>
     </row>
@@ -6668,7 +6668,7 @@
       </c>
       <c r="CB24" t="inlineStr">
         <is>
-          <t>2026-06-12 00:53:26</t>
+          <t>2026-06-12 03:08:58</t>
         </is>
       </c>
     </row>
@@ -6699,43 +6699,43 @@
         </is>
       </c>
       <c r="F25" t="n">
-        <v>2.86</v>
+        <v>2.84</v>
       </c>
       <c r="G25" t="n">
         <v>2.94</v>
       </c>
       <c r="H25" t="n">
-        <v>2.74</v>
+        <v>2.76</v>
       </c>
       <c r="I25" t="n">
-        <v>2.76</v>
+        <v>2.86</v>
       </c>
       <c r="J25" t="n">
-        <v>3.35</v>
+        <v>3.3</v>
       </c>
       <c r="K25" t="n">
         <v>3.5</v>
       </c>
       <c r="L25" t="n">
-        <v>1.01</v>
+        <v>1.46</v>
       </c>
       <c r="M25" t="n">
         <v>1.08</v>
       </c>
       <c r="N25" t="n">
-        <v>3.35</v>
+        <v>3.5</v>
       </c>
       <c r="O25" t="n">
-        <v>1.38</v>
+        <v>1.37</v>
       </c>
       <c r="P25" t="n">
-        <v>1.8</v>
+        <v>1.83</v>
       </c>
       <c r="Q25" t="n">
-        <v>2.1</v>
+        <v>2.14</v>
       </c>
       <c r="R25" t="n">
-        <v>1.3</v>
+        <v>1.31</v>
       </c>
       <c r="S25" t="n">
         <v>4</v>
@@ -6744,43 +6744,43 @@
         <v>1.81</v>
       </c>
       <c r="U25" t="n">
-        <v>2.08</v>
+        <v>2.12</v>
       </c>
       <c r="V25" t="n">
-        <v>1.56</v>
+        <v>1.54</v>
       </c>
       <c r="W25" t="n">
         <v>1.51</v>
       </c>
       <c r="X25" t="n">
-        <v>14.5</v>
+        <v>14</v>
       </c>
       <c r="Y25" t="n">
-        <v>12.5</v>
+        <v>12</v>
       </c>
       <c r="Z25" t="n">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="AA25" t="n">
         <v>55</v>
       </c>
       <c r="AB25" t="n">
-        <v>12.5</v>
+        <v>12</v>
       </c>
       <c r="AC25" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AD25" t="n">
-        <v>15.5</v>
+        <v>15</v>
       </c>
       <c r="AE25" t="n">
         <v>42</v>
       </c>
       <c r="AF25" t="n">
-        <v>23</v>
+        <v>19</v>
       </c>
       <c r="AG25" t="n">
-        <v>15</v>
+        <v>14.5</v>
       </c>
       <c r="AH25" t="n">
         <v>23</v>
@@ -6801,10 +6801,10 @@
         <v>580</v>
       </c>
       <c r="AN25" t="n">
-        <v>42</v>
+        <v>500</v>
       </c>
       <c r="AO25" t="n">
-        <v>500</v>
+        <v>40</v>
       </c>
       <c r="AP25" t="n">
         <v>11</v>
@@ -6813,13 +6813,13 @@
         <v>9</v>
       </c>
       <c r="AR25" t="n">
-        <v>9</v>
+        <v>16</v>
       </c>
       <c r="AS25" t="n">
-        <v>4.2</v>
+        <v>18.5</v>
       </c>
       <c r="AT25" t="n">
-        <v>9.199999999999999</v>
+        <v>9.6</v>
       </c>
       <c r="AU25" t="n">
         <v>6.6</v>
@@ -6828,101 +6828,101 @@
         <v>11</v>
       </c>
       <c r="AW25" t="n">
-        <v>14.5</v>
+        <v>28</v>
       </c>
       <c r="AX25" t="n">
-        <v>9</v>
+        <v>16.5</v>
       </c>
       <c r="AY25" t="n">
         <v>11</v>
       </c>
       <c r="AZ25" t="n">
-        <v>10.5</v>
+        <v>16</v>
       </c>
       <c r="BA25" t="n">
-        <v>4.2</v>
+        <v>26</v>
       </c>
       <c r="BB25" t="n">
-        <v>4.2</v>
+        <v>18</v>
       </c>
       <c r="BC25" t="n">
         <v>14.5</v>
       </c>
       <c r="BD25" t="n">
-        <v>4.2</v>
+        <v>25</v>
       </c>
       <c r="BE25" t="n">
+        <v>29</v>
+      </c>
+      <c r="BF25" t="n">
+        <v>10</v>
+      </c>
+      <c r="BG25" t="n">
+        <v>12</v>
+      </c>
+      <c r="BH25" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="BI25" t="n">
+        <v>2.92</v>
+      </c>
+      <c r="BJ25" t="n">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="BK25" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="BL25" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BM25" t="n">
+        <v>15</v>
+      </c>
+      <c r="BN25" t="n">
+        <v>5.9</v>
+      </c>
+      <c r="BO25" t="n">
         <v>4.4</v>
       </c>
-      <c r="BF25" t="n">
-        <v>6.6</v>
-      </c>
-      <c r="BG25" t="n">
-        <v>6.2</v>
-      </c>
-      <c r="BH25" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BI25" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="BJ25" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BK25" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="BL25" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BM25" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="BN25" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BO25" t="n">
-        <v>1.04</v>
-      </c>
       <c r="BP25" t="n">
         <v>1000</v>
       </c>
       <c r="BQ25" t="n">
-        <v>1.04</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BR25" t="n">
         <v>1000</v>
       </c>
       <c r="BS25" t="n">
-        <v>1.04</v>
+        <v>11.5</v>
       </c>
       <c r="BT25" t="n">
-        <v>1000</v>
+        <v>5.7</v>
       </c>
       <c r="BU25" t="n">
-        <v>1.04</v>
+        <v>4.3</v>
       </c>
       <c r="BV25" t="n">
         <v>1000</v>
       </c>
       <c r="BW25" t="n">
-        <v>1.04</v>
+        <v>9.6</v>
       </c>
       <c r="BX25" t="n">
         <v>1000</v>
       </c>
       <c r="BY25" t="n">
-        <v>1.04</v>
+        <v>11.5</v>
       </c>
       <c r="BZ25" t="n">
         <v>1000</v>
       </c>
       <c r="CA25" t="n">
-        <v>1.04</v>
+        <v>11</v>
       </c>
       <c r="CB25" t="inlineStr">
         <is>
-          <t>2026-06-12 00:53:26</t>
+          <t>2026-06-12 03:08:58</t>
         </is>
       </c>
     </row>
@@ -6953,22 +6953,22 @@
         </is>
       </c>
       <c r="F26" t="n">
-        <v>1.73</v>
+        <v>1.75</v>
       </c>
       <c r="G26" t="n">
-        <v>1.89</v>
+        <v>1.81</v>
       </c>
       <c r="H26" t="n">
-        <v>3.85</v>
+        <v>4.1</v>
       </c>
       <c r="I26" t="n">
-        <v>4.5</v>
+        <v>4.6</v>
       </c>
       <c r="J26" t="n">
-        <v>4.4</v>
+        <v>4.6</v>
       </c>
       <c r="K26" t="n">
-        <v>5.2</v>
+        <v>5.3</v>
       </c>
       <c r="L26" t="n">
         <v>1.21</v>
@@ -6977,46 +6977,46 @@
         <v>1.02</v>
       </c>
       <c r="N26" t="n">
-        <v>7.4</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="O26" t="n">
-        <v>1.12</v>
+        <v>1.11</v>
       </c>
       <c r="P26" t="n">
-        <v>3.15</v>
+        <v>3.6</v>
       </c>
       <c r="Q26" t="n">
-        <v>1.37</v>
+        <v>1.35</v>
       </c>
       <c r="R26" t="n">
+        <v>2.06</v>
+      </c>
+      <c r="S26" t="n">
         <v>1.87</v>
       </c>
-      <c r="S26" t="n">
-        <v>1.92</v>
-      </c>
       <c r="T26" t="n">
-        <v>1.45</v>
+        <v>1.42</v>
       </c>
       <c r="U26" t="n">
-        <v>2.82</v>
+        <v>2.98</v>
       </c>
       <c r="V26" t="n">
         <v>1.28</v>
       </c>
       <c r="W26" t="n">
-        <v>2.12</v>
+        <v>2.22</v>
       </c>
       <c r="X26" t="n">
-        <v>80</v>
+        <v>95</v>
       </c>
       <c r="Y26" t="n">
-        <v>75</v>
+        <v>950</v>
       </c>
       <c r="Z26" t="n">
         <v>50</v>
       </c>
       <c r="AA26" t="n">
-        <v>470</v>
+        <v>500</v>
       </c>
       <c r="AB26" t="n">
         <v>22</v>
@@ -7031,7 +7031,7 @@
         <v>120</v>
       </c>
       <c r="AF26" t="n">
-        <v>18</v>
+        <v>18.5</v>
       </c>
       <c r="AG26" t="n">
         <v>14</v>
@@ -7043,22 +7043,22 @@
         <v>95</v>
       </c>
       <c r="AJ26" t="n">
-        <v>27</v>
+        <v>23</v>
       </c>
       <c r="AK26" t="n">
         <v>20</v>
       </c>
       <c r="AL26" t="n">
-        <v>27</v>
+        <v>42</v>
       </c>
       <c r="AM26" t="n">
         <v>60</v>
       </c>
       <c r="AN26" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AO26" t="n">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="AP26" t="n">
         <v>16</v>
@@ -7067,16 +7067,16 @@
         <v>21</v>
       </c>
       <c r="AR26" t="n">
-        <v>4.8</v>
+        <v>5.3</v>
       </c>
       <c r="AS26" t="n">
-        <v>4.7</v>
+        <v>5.3</v>
       </c>
       <c r="AT26" t="n">
         <v>13</v>
       </c>
       <c r="AU26" t="n">
-        <v>9.4</v>
+        <v>11</v>
       </c>
       <c r="AV26" t="n">
         <v>13.5</v>
@@ -7106,77 +7106,77 @@
         <v>16</v>
       </c>
       <c r="BE26" t="n">
-        <v>4.8</v>
+        <v>5.4</v>
       </c>
       <c r="BF26" t="n">
-        <v>5.2</v>
+        <v>4.7</v>
       </c>
       <c r="BG26" t="n">
         <v>16</v>
       </c>
       <c r="BH26" t="n">
-        <v>5.6</v>
+        <v>6</v>
       </c>
       <c r="BI26" t="n">
-        <v>4.1</v>
+        <v>4.4</v>
       </c>
       <c r="BJ26" t="n">
-        <v>8.800000000000001</v>
+        <v>8.6</v>
       </c>
       <c r="BK26" t="n">
-        <v>4.8</v>
+        <v>4.9</v>
       </c>
       <c r="BL26" t="n">
         <v>1000</v>
       </c>
       <c r="BM26" t="n">
-        <v>9</v>
+        <v>9.6</v>
       </c>
       <c r="BN26" t="n">
         <v>5.6</v>
       </c>
       <c r="BO26" t="n">
-        <v>4.1</v>
+        <v>4.8</v>
       </c>
       <c r="BP26" t="n">
         <v>11.5</v>
       </c>
       <c r="BQ26" t="n">
+        <v>5.8</v>
+      </c>
+      <c r="BR26" t="n">
+        <v>17</v>
+      </c>
+      <c r="BS26" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="BT26" t="n">
+        <v>9</v>
+      </c>
+      <c r="BU26" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="BV26" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BW26" t="n">
         <v>8</v>
       </c>
-      <c r="BR26" t="n">
-        <v>18</v>
-      </c>
-      <c r="BS26" t="n">
-        <v>6.6</v>
-      </c>
-      <c r="BT26" t="n">
-        <v>8.800000000000001</v>
-      </c>
-      <c r="BU26" t="n">
-        <v>4.8</v>
-      </c>
-      <c r="BV26" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BW26" t="n">
-        <v>7.6</v>
-      </c>
       <c r="BX26" t="n">
         <v>1000</v>
       </c>
       <c r="BY26" t="n">
-        <v>7.6</v>
+        <v>8</v>
       </c>
       <c r="BZ26" t="n">
-        <v>11</v>
+        <v>9.6</v>
       </c>
       <c r="CA26" t="n">
-        <v>5.4</v>
+        <v>7.2</v>
       </c>
       <c r="CB26" t="inlineStr">
         <is>
-          <t>2026-06-12 00:53:26</t>
+          <t>2026-06-12 03:08:58</t>
         </is>
       </c>
     </row>
@@ -7207,7 +7207,7 @@
         </is>
       </c>
       <c r="F27" t="n">
-        <v>2.64</v>
+        <v>2.54</v>
       </c>
       <c r="G27" t="n">
         <v>44</v>
@@ -7231,7 +7231,7 @@
         <v>1.09</v>
       </c>
       <c r="N27" t="n">
-        <v>1.1</v>
+        <v>1.24</v>
       </c>
       <c r="O27" t="n">
         <v>1.09</v>
@@ -7243,7 +7243,7 @@
         <v>1.09</v>
       </c>
       <c r="R27" t="n">
-        <v>1.13</v>
+        <v>1.12</v>
       </c>
       <c r="S27" t="n">
         <v>1.49</v>
@@ -7255,7 +7255,7 @@
         <v>1.11</v>
       </c>
       <c r="V27" t="n">
-        <v>1.46</v>
+        <v>1.41</v>
       </c>
       <c r="W27" t="n">
         <v>1.2</v>
@@ -7430,7 +7430,7 @@
       </c>
       <c r="CB27" t="inlineStr">
         <is>
-          <t>2026-06-12 00:53:26</t>
+          <t>2026-06-12 03:08:58</t>
         </is>
       </c>
     </row>
@@ -7461,61 +7461,61 @@
         </is>
       </c>
       <c r="F28" t="n">
-        <v>2.24</v>
+        <v>2.26</v>
       </c>
       <c r="G28" t="n">
-        <v>2.36</v>
+        <v>2.32</v>
       </c>
       <c r="H28" t="n">
-        <v>3.55</v>
+        <v>3.7</v>
       </c>
       <c r="I28" t="n">
-        <v>3.8</v>
+        <v>3.85</v>
       </c>
       <c r="J28" t="n">
         <v>3.3</v>
       </c>
       <c r="K28" t="n">
-        <v>3.45</v>
+        <v>3.4</v>
       </c>
       <c r="L28" t="n">
-        <v>1.4</v>
+        <v>1.5</v>
       </c>
       <c r="M28" t="n">
         <v>1.1</v>
       </c>
       <c r="N28" t="n">
-        <v>3</v>
+        <v>3.15</v>
       </c>
       <c r="O28" t="n">
         <v>1.43</v>
       </c>
       <c r="P28" t="n">
-        <v>1.69</v>
+        <v>1.7</v>
       </c>
       <c r="Q28" t="n">
-        <v>2.28</v>
+        <v>2.32</v>
       </c>
       <c r="R28" t="n">
         <v>1.26</v>
       </c>
       <c r="S28" t="n">
-        <v>4.4</v>
+        <v>4.5</v>
       </c>
       <c r="T28" t="n">
-        <v>1.97</v>
+        <v>1.96</v>
       </c>
       <c r="U28" t="n">
-        <v>1.89</v>
+        <v>1.9</v>
       </c>
       <c r="V28" t="n">
         <v>1.35</v>
       </c>
       <c r="W28" t="n">
-        <v>1.73</v>
+        <v>1.76</v>
       </c>
       <c r="X28" t="n">
-        <v>19</v>
+        <v>11.5</v>
       </c>
       <c r="Y28" t="n">
         <v>20</v>
@@ -7527,22 +7527,22 @@
         <v>900</v>
       </c>
       <c r="AB28" t="n">
-        <v>8.6</v>
+        <v>8.4</v>
       </c>
       <c r="AC28" t="n">
-        <v>7.8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AD28" t="n">
-        <v>30</v>
+        <v>500</v>
       </c>
       <c r="AE28" t="n">
         <v>500</v>
       </c>
       <c r="AF28" t="n">
-        <v>14.5</v>
+        <v>14</v>
       </c>
       <c r="AG28" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="AH28" t="n">
         <v>60</v>
@@ -7557,13 +7557,13 @@
         <v>85</v>
       </c>
       <c r="AL28" t="n">
-        <v>290</v>
+        <v>500</v>
       </c>
       <c r="AM28" t="n">
         <v>580</v>
       </c>
       <c r="AN28" t="n">
-        <v>55</v>
+        <v>500</v>
       </c>
       <c r="AO28" t="n">
         <v>500</v>
@@ -7575,52 +7575,52 @@
         <v>10</v>
       </c>
       <c r="AR28" t="n">
-        <v>21</v>
+        <v>11.5</v>
       </c>
       <c r="AS28" t="n">
-        <v>8.800000000000001</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AT28" t="n">
-        <v>7.2</v>
+        <v>6.8</v>
       </c>
       <c r="AU28" t="n">
-        <v>6.8</v>
+        <v>6.6</v>
       </c>
       <c r="AV28" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="AW28" t="n">
-        <v>8.4</v>
+        <v>9</v>
       </c>
       <c r="AX28" t="n">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="AY28" t="n">
-        <v>9.6</v>
+        <v>9.4</v>
       </c>
       <c r="AZ28" t="n">
-        <v>6.8</v>
+        <v>7</v>
       </c>
       <c r="BA28" t="n">
-        <v>8.6</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BB28" t="n">
-        <v>8.199999999999999</v>
+        <v>8</v>
       </c>
       <c r="BC28" t="n">
         <v>13</v>
       </c>
       <c r="BD28" t="n">
-        <v>8.4</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BE28" t="n">
-        <v>9.199999999999999</v>
+        <v>9.6</v>
       </c>
       <c r="BF28" t="n">
-        <v>21</v>
+        <v>7.4</v>
       </c>
       <c r="BG28" t="n">
-        <v>8.6</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BH28" t="n">
         <v>1000</v>
@@ -7684,7 +7684,7 @@
       </c>
       <c r="CB28" t="inlineStr">
         <is>
-          <t>2026-06-12 00:53:26</t>
+          <t>2026-06-12 03:08:58</t>
         </is>
       </c>
     </row>
@@ -7715,13 +7715,13 @@
         </is>
       </c>
       <c r="F29" t="n">
-        <v>2</v>
+        <v>2.04</v>
       </c>
       <c r="G29" t="n">
         <v>2.1</v>
       </c>
       <c r="H29" t="n">
-        <v>3.75</v>
+        <v>3.8</v>
       </c>
       <c r="I29" t="n">
         <v>4.1</v>
@@ -7730,31 +7730,31 @@
         <v>3.7</v>
       </c>
       <c r="K29" t="n">
-        <v>4.1</v>
+        <v>3.95</v>
       </c>
       <c r="L29" t="n">
-        <v>1.29</v>
+        <v>1.37</v>
       </c>
       <c r="M29" t="n">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="N29" t="n">
         <v>4.3</v>
       </c>
       <c r="O29" t="n">
-        <v>1.26</v>
+        <v>1.28</v>
       </c>
       <c r="P29" t="n">
         <v>2.12</v>
       </c>
       <c r="Q29" t="n">
-        <v>1.79</v>
+        <v>1.85</v>
       </c>
       <c r="R29" t="n">
-        <v>1.43</v>
+        <v>1.42</v>
       </c>
       <c r="S29" t="n">
-        <v>3</v>
+        <v>3.2</v>
       </c>
       <c r="T29" t="n">
         <v>1.71</v>
@@ -7763,13 +7763,13 @@
         <v>2.26</v>
       </c>
       <c r="V29" t="n">
-        <v>1.32</v>
+        <v>1.33</v>
       </c>
       <c r="W29" t="n">
-        <v>1.92</v>
+        <v>1.9</v>
       </c>
       <c r="X29" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="Y29" t="n">
         <v>16.5</v>
@@ -7784,10 +7784,10 @@
         <v>11</v>
       </c>
       <c r="AC29" t="n">
-        <v>9</v>
+        <v>8.6</v>
       </c>
       <c r="AD29" t="n">
-        <v>16</v>
+        <v>16.5</v>
       </c>
       <c r="AE29" t="n">
         <v>46</v>
@@ -7796,16 +7796,16 @@
         <v>13.5</v>
       </c>
       <c r="AG29" t="n">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="AH29" t="n">
-        <v>17.5</v>
+        <v>17</v>
       </c>
       <c r="AI29" t="n">
         <v>50</v>
       </c>
       <c r="AJ29" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="AK29" t="n">
         <v>21</v>
@@ -7814,16 +7814,16 @@
         <v>34</v>
       </c>
       <c r="AM29" t="n">
-        <v>100</v>
+        <v>85</v>
       </c>
       <c r="AN29" t="n">
-        <v>12.5</v>
+        <v>13.5</v>
       </c>
       <c r="AO29" t="n">
-        <v>100</v>
+        <v>48</v>
       </c>
       <c r="AP29" t="n">
-        <v>15.5</v>
+        <v>15</v>
       </c>
       <c r="AQ29" t="n">
         <v>14.5</v>
@@ -7832,13 +7832,13 @@
         <v>18.5</v>
       </c>
       <c r="AS29" t="n">
-        <v>11</v>
+        <v>32</v>
       </c>
       <c r="AT29" t="n">
         <v>9.6</v>
       </c>
       <c r="AU29" t="n">
-        <v>8</v>
+        <v>7.6</v>
       </c>
       <c r="AV29" t="n">
         <v>14</v>
@@ -7850,7 +7850,7 @@
         <v>11.5</v>
       </c>
       <c r="AY29" t="n">
-        <v>9.4</v>
+        <v>9.6</v>
       </c>
       <c r="AZ29" t="n">
         <v>15.5</v>
@@ -7862,16 +7862,16 @@
         <v>20</v>
       </c>
       <c r="BC29" t="n">
-        <v>17.5</v>
+        <v>18</v>
       </c>
       <c r="BD29" t="n">
         <v>24</v>
       </c>
       <c r="BE29" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="BF29" t="n">
         <v>11.5</v>
-      </c>
-      <c r="BF29" t="n">
-        <v>11</v>
       </c>
       <c r="BG29" t="n">
         <v>34</v>
@@ -7880,10 +7880,10 @@
         <v>3.75</v>
       </c>
       <c r="BI29" t="n">
-        <v>3.05</v>
+        <v>3</v>
       </c>
       <c r="BJ29" t="n">
-        <v>9.199999999999999</v>
+        <v>9.4</v>
       </c>
       <c r="BK29" t="n">
         <v>5.8</v>
@@ -7892,7 +7892,7 @@
         <v>1000</v>
       </c>
       <c r="BM29" t="n">
-        <v>13.5</v>
+        <v>13</v>
       </c>
       <c r="BN29" t="n">
         <v>5</v>
@@ -7904,13 +7904,13 @@
         <v>14</v>
       </c>
       <c r="BQ29" t="n">
-        <v>7.4</v>
+        <v>7.2</v>
       </c>
       <c r="BR29" t="n">
         <v>26</v>
       </c>
       <c r="BS29" t="n">
-        <v>9.800000000000001</v>
+        <v>9.6</v>
       </c>
       <c r="BT29" t="n">
         <v>7.4</v>
@@ -7928,17 +7928,17 @@
         <v>38</v>
       </c>
       <c r="BY29" t="n">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="BZ29" t="n">
         <v>21</v>
       </c>
       <c r="CA29" t="n">
-        <v>9</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="CB29" t="inlineStr">
         <is>
-          <t>2026-06-12 00:53:26</t>
+          <t>2026-06-12 03:08:58</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-06-12.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-06-12.xlsx
@@ -857,7 +857,7 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>1.55</v>
+        <v>1.54</v>
       </c>
       <c r="G2" t="n">
         <v>1.6</v>
@@ -866,7 +866,7 @@
         <v>6.4</v>
       </c>
       <c r="I2" t="n">
-        <v>8.199999999999999</v>
+        <v>8</v>
       </c>
       <c r="J2" t="n">
         <v>4.1</v>
@@ -881,28 +881,28 @@
         <v>1.06</v>
       </c>
       <c r="N2" t="n">
-        <v>4</v>
+        <v>4.1</v>
       </c>
       <c r="O2" t="n">
-        <v>1.3</v>
+        <v>1.29</v>
       </c>
       <c r="P2" t="n">
-        <v>2.02</v>
+        <v>2.04</v>
       </c>
       <c r="Q2" t="n">
-        <v>1.89</v>
+        <v>1.87</v>
       </c>
       <c r="R2" t="n">
-        <v>1.38</v>
+        <v>1.39</v>
       </c>
       <c r="S2" t="n">
-        <v>3.35</v>
+        <v>3.3</v>
       </c>
       <c r="T2" t="n">
-        <v>1.94</v>
+        <v>1.95</v>
       </c>
       <c r="U2" t="n">
-        <v>1.89</v>
+        <v>1.9</v>
       </c>
       <c r="V2" t="n">
         <v>1.15</v>
@@ -911,7 +911,7 @@
         <v>2.62</v>
       </c>
       <c r="X2" t="n">
-        <v>970</v>
+        <v>500</v>
       </c>
       <c r="Y2" t="n">
         <v>950</v>
@@ -923,7 +923,7 @@
         <v>700</v>
       </c>
       <c r="AB2" t="n">
-        <v>14</v>
+        <v>27</v>
       </c>
       <c r="AC2" t="n">
         <v>17.5</v>
@@ -935,7 +935,7 @@
         <v>700</v>
       </c>
       <c r="AF2" t="n">
-        <v>40</v>
+        <v>500</v>
       </c>
       <c r="AG2" t="n">
         <v>970</v>
@@ -962,10 +962,10 @@
         <v>29</v>
       </c>
       <c r="AO2" t="n">
-        <v>700</v>
+        <v>1000</v>
       </c>
       <c r="AP2" t="n">
-        <v>6.4</v>
+        <v>6.8</v>
       </c>
       <c r="AQ2" t="n">
         <v>4.2</v>
@@ -977,40 +977,40 @@
         <v>4.2</v>
       </c>
       <c r="AT2" t="n">
-        <v>4.5</v>
+        <v>3.6</v>
       </c>
       <c r="AU2" t="n">
         <v>4.7</v>
       </c>
       <c r="AV2" t="n">
-        <v>4.2</v>
+        <v>4.5</v>
       </c>
       <c r="AW2" t="n">
-        <v>4.6</v>
+        <v>6</v>
       </c>
       <c r="AX2" t="n">
-        <v>5</v>
+        <v>5.3</v>
       </c>
       <c r="AY2" t="n">
-        <v>4.8</v>
+        <v>5.6</v>
       </c>
       <c r="AZ2" t="n">
-        <v>3.95</v>
+        <v>3.3</v>
       </c>
       <c r="BA2" t="n">
-        <v>4.6</v>
+        <v>4.7</v>
       </c>
       <c r="BB2" t="n">
-        <v>6.2</v>
+        <v>6.6</v>
       </c>
       <c r="BC2" t="n">
-        <v>6.6</v>
+        <v>7</v>
       </c>
       <c r="BD2" t="n">
-        <v>3.9</v>
+        <v>3.25</v>
       </c>
       <c r="BE2" t="n">
-        <v>3.3</v>
+        <v>2.98</v>
       </c>
       <c r="BF2" t="n">
         <v>6.6</v>
@@ -1019,68 +1019,68 @@
         <v>4.2</v>
       </c>
       <c r="BH2" t="n">
-        <v>3.75</v>
+        <v>3.8</v>
       </c>
       <c r="BI2" t="n">
-        <v>3.2</v>
+        <v>3.35</v>
       </c>
       <c r="BJ2" t="n">
-        <v>15.5</v>
+        <v>1000</v>
       </c>
       <c r="BK2" t="n">
-        <v>5.3</v>
+        <v>6</v>
       </c>
       <c r="BL2" t="n">
         <v>1000</v>
       </c>
       <c r="BM2" t="n">
-        <v>3.75</v>
+        <v>2.12</v>
       </c>
       <c r="BN2" t="n">
-        <v>4.2</v>
+        <v>4.1</v>
       </c>
       <c r="BO2" t="n">
-        <v>3.45</v>
+        <v>3.6</v>
       </c>
       <c r="BP2" t="n">
-        <v>13.5</v>
+        <v>1000</v>
       </c>
       <c r="BQ2" t="n">
-        <v>7.4</v>
+        <v>5.7</v>
       </c>
       <c r="BR2" t="n">
         <v>1000</v>
       </c>
       <c r="BS2" t="n">
-        <v>4.9</v>
+        <v>2.12</v>
       </c>
       <c r="BT2" t="n">
         <v>1000</v>
       </c>
       <c r="BU2" t="n">
-        <v>5.6</v>
+        <v>5.8</v>
       </c>
       <c r="BV2" t="n">
         <v>1000</v>
       </c>
       <c r="BW2" t="n">
-        <v>5.7</v>
+        <v>2.04</v>
       </c>
       <c r="BX2" t="n">
         <v>1000</v>
       </c>
       <c r="BY2" t="n">
-        <v>5.7</v>
+        <v>2.12</v>
       </c>
       <c r="BZ2" t="n">
         <v>1000</v>
       </c>
       <c r="CA2" t="n">
-        <v>7.2</v>
+        <v>2.38</v>
       </c>
       <c r="CB2" t="inlineStr">
         <is>
-          <t>2026-06-12 03:08:58</t>
+          <t>2026-06-12 05:25:07</t>
         </is>
       </c>
     </row>
@@ -1111,7 +1111,7 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>2.64</v>
+        <v>2.6</v>
       </c>
       <c r="G3" t="n">
         <v>2.74</v>
@@ -1120,10 +1120,10 @@
         <v>2.74</v>
       </c>
       <c r="I3" t="n">
-        <v>2.84</v>
+        <v>2.94</v>
       </c>
       <c r="J3" t="n">
-        <v>3.65</v>
+        <v>3.6</v>
       </c>
       <c r="K3" t="n">
         <v>3.7</v>
@@ -1141,28 +1141,28 @@
         <v>1.25</v>
       </c>
       <c r="P3" t="n">
-        <v>2.2</v>
+        <v>2.24</v>
       </c>
       <c r="Q3" t="n">
         <v>1.76</v>
       </c>
       <c r="R3" t="n">
-        <v>1.5</v>
+        <v>1.49</v>
       </c>
       <c r="S3" t="n">
-        <v>2.92</v>
+        <v>2.96</v>
       </c>
       <c r="T3" t="n">
-        <v>1.62</v>
+        <v>1.6</v>
       </c>
       <c r="U3" t="n">
-        <v>2.42</v>
+        <v>2.48</v>
       </c>
       <c r="V3" t="n">
-        <v>1.54</v>
+        <v>1.52</v>
       </c>
       <c r="W3" t="n">
-        <v>1.57</v>
+        <v>1.58</v>
       </c>
       <c r="X3" t="n">
         <v>24</v>
@@ -1177,19 +1177,19 @@
         <v>50</v>
       </c>
       <c r="AB3" t="n">
-        <v>14.5</v>
+        <v>14</v>
       </c>
       <c r="AC3" t="n">
-        <v>9</v>
+        <v>8.6</v>
       </c>
       <c r="AD3" t="n">
         <v>15.5</v>
       </c>
       <c r="AE3" t="n">
-        <v>27</v>
+        <v>34</v>
       </c>
       <c r="AF3" t="n">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="AG3" t="n">
         <v>15</v>
@@ -1210,34 +1210,34 @@
         <v>44</v>
       </c>
       <c r="AM3" t="n">
-        <v>200</v>
+        <v>320</v>
       </c>
       <c r="AN3" t="n">
         <v>22</v>
       </c>
       <c r="AO3" t="n">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="AP3" t="n">
         <v>16.5</v>
       </c>
       <c r="AQ3" t="n">
-        <v>10</v>
+        <v>12.5</v>
       </c>
       <c r="AR3" t="n">
         <v>18.5</v>
       </c>
       <c r="AS3" t="n">
-        <v>18</v>
+        <v>18.5</v>
       </c>
       <c r="AT3" t="n">
-        <v>9.800000000000001</v>
+        <v>12.5</v>
       </c>
       <c r="AU3" t="n">
-        <v>8</v>
+        <v>7.6</v>
       </c>
       <c r="AV3" t="n">
-        <v>9.4</v>
+        <v>11</v>
       </c>
       <c r="AW3" t="n">
         <v>20</v>
@@ -1252,34 +1252,34 @@
         <v>13</v>
       </c>
       <c r="BA3" t="n">
+        <v>18.5</v>
+      </c>
+      <c r="BB3" t="n">
         <v>18</v>
       </c>
-      <c r="BB3" t="n">
-        <v>17.5</v>
-      </c>
       <c r="BC3" t="n">
-        <v>19.5</v>
+        <v>20</v>
       </c>
       <c r="BD3" t="n">
-        <v>18</v>
+        <v>18.5</v>
       </c>
       <c r="BE3" t="n">
-        <v>5.9</v>
+        <v>27</v>
       </c>
       <c r="BF3" t="n">
         <v>16</v>
       </c>
       <c r="BG3" t="n">
-        <v>16.5</v>
+        <v>18</v>
       </c>
       <c r="BH3" t="n">
         <v>3.8</v>
       </c>
       <c r="BI3" t="n">
-        <v>3.05</v>
+        <v>3.1</v>
       </c>
       <c r="BJ3" t="n">
-        <v>9</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BK3" t="n">
         <v>6.4</v>
@@ -1288,25 +1288,25 @@
         <v>1000</v>
       </c>
       <c r="BM3" t="n">
-        <v>13.5</v>
+        <v>14.5</v>
       </c>
       <c r="BN3" t="n">
         <v>5.8</v>
       </c>
       <c r="BO3" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="BP3" t="n">
         <v>18.5</v>
       </c>
       <c r="BQ3" t="n">
-        <v>8.4</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BR3" t="n">
         <v>1000</v>
       </c>
       <c r="BS3" t="n">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="BT3" t="n">
         <v>6.2</v>
@@ -1315,26 +1315,26 @@
         <v>5.4</v>
       </c>
       <c r="BV3" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="BW3" t="n">
-        <v>9</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BX3" t="n">
         <v>30</v>
       </c>
       <c r="BY3" t="n">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="BZ3" t="n">
         <v>21</v>
       </c>
       <c r="CA3" t="n">
-        <v>9</v>
+        <v>9.4</v>
       </c>
       <c r="CB3" t="inlineStr">
         <is>
-          <t>2026-06-12 03:08:58</t>
+          <t>2026-06-12 05:25:07</t>
         </is>
       </c>
     </row>
@@ -1365,13 +1365,13 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>3.05</v>
+        <v>3</v>
       </c>
       <c r="G4" t="n">
         <v>3.3</v>
       </c>
       <c r="H4" t="n">
-        <v>2.96</v>
+        <v>3</v>
       </c>
       <c r="I4" t="n">
         <v>3.1</v>
@@ -1380,7 +1380,7 @@
         <v>2.7</v>
       </c>
       <c r="K4" t="n">
-        <v>2.88</v>
+        <v>2.94</v>
       </c>
       <c r="L4" t="n">
         <v>1.68</v>
@@ -1389,25 +1389,25 @@
         <v>1.17</v>
       </c>
       <c r="N4" t="n">
-        <v>2.4</v>
+        <v>2.42</v>
       </c>
       <c r="O4" t="n">
-        <v>1.64</v>
+        <v>1.63</v>
       </c>
       <c r="P4" t="n">
-        <v>1.42</v>
+        <v>1.47</v>
       </c>
       <c r="Q4" t="n">
-        <v>3.05</v>
+        <v>3</v>
       </c>
       <c r="R4" t="n">
-        <v>1.16</v>
+        <v>1.15</v>
       </c>
       <c r="S4" t="n">
         <v>6.4</v>
       </c>
       <c r="T4" t="n">
-        <v>2.16</v>
+        <v>2.18</v>
       </c>
       <c r="U4" t="n">
         <v>1.68</v>
@@ -1425,13 +1425,13 @@
         <v>500</v>
       </c>
       <c r="Z4" t="n">
-        <v>50</v>
+        <v>970</v>
       </c>
       <c r="AA4" t="n">
         <v>500</v>
       </c>
       <c r="AB4" t="n">
-        <v>500</v>
+        <v>970</v>
       </c>
       <c r="AC4" t="n">
         <v>15</v>
@@ -1467,10 +1467,10 @@
         <v>500</v>
       </c>
       <c r="AN4" t="n">
-        <v>600</v>
+        <v>100</v>
       </c>
       <c r="AO4" t="n">
-        <v>600</v>
+        <v>85</v>
       </c>
       <c r="AP4" t="n">
         <v>4.2</v>
@@ -1479,13 +1479,13 @@
         <v>4.4</v>
       </c>
       <c r="AR4" t="n">
-        <v>8.199999999999999</v>
+        <v>8.4</v>
       </c>
       <c r="AS4" t="n">
         <v>7.8</v>
       </c>
       <c r="AT4" t="n">
-        <v>4.4</v>
+        <v>4.7</v>
       </c>
       <c r="AU4" t="n">
         <v>4.2</v>
@@ -1506,7 +1506,7 @@
         <v>7</v>
       </c>
       <c r="BA4" t="n">
-        <v>3.8</v>
+        <v>3.05</v>
       </c>
       <c r="BB4" t="n">
         <v>7.8</v>
@@ -1515,16 +1515,16 @@
         <v>7.8</v>
       </c>
       <c r="BD4" t="n">
-        <v>3.9</v>
+        <v>3.1</v>
       </c>
       <c r="BE4" t="n">
-        <v>5.2</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BF4" t="n">
-        <v>5</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BG4" t="n">
-        <v>5</v>
+        <v>2.44</v>
       </c>
       <c r="BH4" t="n">
         <v>2.6</v>
@@ -1542,10 +1542,10 @@
         <v>1000</v>
       </c>
       <c r="BM4" t="n">
-        <v>1.32</v>
+        <v>1.44</v>
       </c>
       <c r="BN4" t="n">
-        <v>970</v>
+        <v>1000</v>
       </c>
       <c r="BO4" t="n">
         <v>3.8</v>
@@ -1554,16 +1554,16 @@
         <v>1000</v>
       </c>
       <c r="BQ4" t="n">
-        <v>1.96</v>
+        <v>1.91</v>
       </c>
       <c r="BR4" t="n">
         <v>1000</v>
       </c>
       <c r="BS4" t="n">
-        <v>2.02</v>
+        <v>1.27</v>
       </c>
       <c r="BT4" t="n">
-        <v>19.5</v>
+        <v>24</v>
       </c>
       <c r="BU4" t="n">
         <v>3.9</v>
@@ -1572,23 +1572,23 @@
         <v>1000</v>
       </c>
       <c r="BW4" t="n">
-        <v>1.96</v>
+        <v>1.91</v>
       </c>
       <c r="BX4" t="n">
         <v>1000</v>
       </c>
       <c r="BY4" t="n">
-        <v>1.9</v>
+        <v>1.97</v>
       </c>
       <c r="BZ4" t="n">
         <v>1000</v>
       </c>
       <c r="CA4" t="n">
-        <v>1.91</v>
+        <v>1.29</v>
       </c>
       <c r="CB4" t="inlineStr">
         <is>
-          <t>2026-06-12 03:08:58</t>
+          <t>2026-06-12 05:25:07</t>
         </is>
       </c>
     </row>
@@ -1619,79 +1619,79 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>1.99</v>
+        <v>2.06</v>
       </c>
       <c r="G5" t="n">
-        <v>2.12</v>
+        <v>2.16</v>
       </c>
       <c r="H5" t="n">
-        <v>4.5</v>
+        <v>4.2</v>
       </c>
       <c r="I5" t="n">
-        <v>5</v>
+        <v>4.8</v>
       </c>
       <c r="J5" t="n">
         <v>3.2</v>
       </c>
       <c r="K5" t="n">
-        <v>3.5</v>
+        <v>3.35</v>
       </c>
       <c r="L5" t="n">
-        <v>1.59</v>
+        <v>1.6</v>
       </c>
       <c r="M5" t="n">
-        <v>1.13</v>
+        <v>1.14</v>
       </c>
       <c r="N5" t="n">
-        <v>2.62</v>
+        <v>2.6</v>
       </c>
       <c r="O5" t="n">
-        <v>1.55</v>
+        <v>1.58</v>
       </c>
       <c r="P5" t="n">
-        <v>1.53</v>
+        <v>1.52</v>
       </c>
       <c r="Q5" t="n">
-        <v>2.66</v>
+        <v>2.74</v>
       </c>
       <c r="R5" t="n">
-        <v>1.18</v>
+        <v>1.17</v>
       </c>
       <c r="S5" t="n">
-        <v>5.7</v>
+        <v>6.2</v>
       </c>
       <c r="T5" t="n">
-        <v>2.18</v>
+        <v>2.24</v>
       </c>
       <c r="U5" t="n">
-        <v>1.71</v>
+        <v>1.68</v>
       </c>
       <c r="V5" t="n">
-        <v>1.25</v>
+        <v>1.26</v>
       </c>
       <c r="W5" t="n">
-        <v>1.87</v>
+        <v>1.86</v>
       </c>
       <c r="X5" t="n">
-        <v>9</v>
+        <v>8.6</v>
       </c>
       <c r="Y5" t="n">
-        <v>12</v>
+        <v>11.5</v>
       </c>
       <c r="Z5" t="n">
-        <v>100</v>
+        <v>50</v>
       </c>
       <c r="AA5" t="n">
         <v>900</v>
       </c>
       <c r="AB5" t="n">
-        <v>6.8</v>
+        <v>6.6</v>
       </c>
       <c r="AC5" t="n">
-        <v>7.8</v>
+        <v>7.6</v>
       </c>
       <c r="AD5" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AE5" t="n">
         <v>500</v>
@@ -1700,28 +1700,28 @@
         <v>11.5</v>
       </c>
       <c r="AG5" t="n">
-        <v>12</v>
+        <v>11.5</v>
       </c>
       <c r="AH5" t="n">
-        <v>950</v>
+        <v>34</v>
       </c>
       <c r="AI5" t="n">
-        <v>540</v>
+        <v>130</v>
       </c>
       <c r="AJ5" t="n">
-        <v>150</v>
+        <v>29</v>
       </c>
       <c r="AK5" t="n">
-        <v>80</v>
+        <v>36</v>
       </c>
       <c r="AL5" t="n">
-        <v>500</v>
+        <v>75</v>
       </c>
       <c r="AM5" t="n">
         <v>500</v>
       </c>
       <c r="AN5" t="n">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="AO5" t="n">
         <v>600</v>
@@ -1730,94 +1730,94 @@
         <v>7.6</v>
       </c>
       <c r="AQ5" t="n">
-        <v>9</v>
+        <v>10.5</v>
       </c>
       <c r="AR5" t="n">
-        <v>11.5</v>
+        <v>26</v>
       </c>
       <c r="AS5" t="n">
-        <v>9.6</v>
+        <v>14</v>
       </c>
       <c r="AT5" t="n">
-        <v>5.7</v>
+        <v>6</v>
       </c>
       <c r="AU5" t="n">
-        <v>6.2</v>
+        <v>6.6</v>
       </c>
       <c r="AV5" t="n">
         <v>16.5</v>
       </c>
       <c r="AW5" t="n">
-        <v>9.199999999999999</v>
+        <v>32</v>
       </c>
       <c r="AX5" t="n">
-        <v>9.800000000000001</v>
+        <v>10</v>
       </c>
       <c r="AY5" t="n">
         <v>10</v>
       </c>
       <c r="AZ5" t="n">
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="BA5" t="n">
-        <v>9.6</v>
+        <v>29</v>
       </c>
       <c r="BB5" t="n">
-        <v>13</v>
+        <v>22</v>
       </c>
       <c r="BC5" t="n">
-        <v>14.5</v>
+        <v>15</v>
       </c>
       <c r="BD5" t="n">
-        <v>9</v>
+        <v>55</v>
       </c>
       <c r="BE5" t="n">
-        <v>10</v>
+        <v>16.5</v>
       </c>
       <c r="BF5" t="n">
-        <v>7.8</v>
+        <v>24</v>
       </c>
       <c r="BG5" t="n">
-        <v>9.800000000000001</v>
+        <v>14</v>
       </c>
       <c r="BH5" t="n">
-        <v>2.72</v>
+        <v>2.7</v>
       </c>
       <c r="BI5" t="n">
-        <v>2.28</v>
+        <v>2.3</v>
       </c>
       <c r="BJ5" t="n">
         <v>12</v>
       </c>
       <c r="BK5" t="n">
-        <v>6.4</v>
+        <v>6.6</v>
       </c>
       <c r="BL5" t="n">
         <v>1000</v>
       </c>
       <c r="BM5" t="n">
-        <v>13</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BN5" t="n">
-        <v>4.6</v>
+        <v>4.7</v>
       </c>
       <c r="BO5" t="n">
-        <v>3.95</v>
+        <v>4.1</v>
       </c>
       <c r="BP5" t="n">
         <v>1000</v>
       </c>
       <c r="BQ5" t="n">
-        <v>13.5</v>
+        <v>8.4</v>
       </c>
       <c r="BR5" t="n">
         <v>1000</v>
       </c>
       <c r="BS5" t="n">
-        <v>10.5</v>
+        <v>11.5</v>
       </c>
       <c r="BT5" t="n">
-        <v>8.199999999999999</v>
+        <v>7.6</v>
       </c>
       <c r="BU5" t="n">
         <v>5.5</v>
@@ -1826,23 +1826,23 @@
         <v>1000</v>
       </c>
       <c r="BW5" t="n">
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="BX5" t="n">
         <v>1000</v>
       </c>
       <c r="BY5" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="BZ5" t="n">
+        <v>1000</v>
+      </c>
+      <c r="CA5" t="n">
         <v>11.5</v>
       </c>
-      <c r="BZ5" t="n">
-        <v>1000</v>
-      </c>
-      <c r="CA5" t="n">
-        <v>10.5</v>
-      </c>
       <c r="CB5" t="inlineStr">
         <is>
-          <t>2026-06-12 03:08:58</t>
+          <t>2026-06-12 05:25:07</t>
         </is>
       </c>
     </row>
@@ -1873,16 +1873,16 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>3.35</v>
+        <v>3.55</v>
       </c>
       <c r="G6" t="n">
-        <v>3.6</v>
+        <v>3.75</v>
       </c>
       <c r="H6" t="n">
+        <v>2.16</v>
+      </c>
+      <c r="I6" t="n">
         <v>2.22</v>
-      </c>
-      <c r="I6" t="n">
-        <v>2.34</v>
       </c>
       <c r="J6" t="n">
         <v>3.55</v>
@@ -1897,46 +1897,46 @@
         <v>1.06</v>
       </c>
       <c r="N6" t="n">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="O6" t="n">
-        <v>1.29</v>
+        <v>1.28</v>
       </c>
       <c r="P6" t="n">
         <v>2.06</v>
       </c>
       <c r="Q6" t="n">
-        <v>1.89</v>
+        <v>1.86</v>
       </c>
       <c r="R6" t="n">
         <v>1.41</v>
       </c>
       <c r="S6" t="n">
-        <v>3.25</v>
+        <v>3.15</v>
       </c>
       <c r="T6" t="n">
         <v>1.74</v>
       </c>
       <c r="U6" t="n">
-        <v>2.26</v>
+        <v>2.24</v>
       </c>
       <c r="V6" t="n">
-        <v>1.75</v>
+        <v>1.81</v>
       </c>
       <c r="W6" t="n">
-        <v>1.38</v>
+        <v>1.36</v>
       </c>
       <c r="X6" t="n">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="Y6" t="n">
-        <v>12.5</v>
+        <v>11.5</v>
       </c>
       <c r="Z6" t="n">
         <v>15.5</v>
       </c>
       <c r="AA6" t="n">
-        <v>30</v>
+        <v>65</v>
       </c>
       <c r="AB6" t="n">
         <v>14.5</v>
@@ -1945,13 +1945,13 @@
         <v>8.4</v>
       </c>
       <c r="AD6" t="n">
-        <v>13.5</v>
+        <v>14</v>
       </c>
       <c r="AE6" t="n">
-        <v>29</v>
+        <v>24</v>
       </c>
       <c r="AF6" t="n">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="AG6" t="n">
         <v>14.5</v>
@@ -1960,31 +1960,31 @@
         <v>16.5</v>
       </c>
       <c r="AI6" t="n">
-        <v>44</v>
+        <v>38</v>
       </c>
       <c r="AJ6" t="n">
         <v>150</v>
       </c>
       <c r="AK6" t="n">
-        <v>48</v>
+        <v>40</v>
       </c>
       <c r="AL6" t="n">
-        <v>60</v>
+        <v>250</v>
       </c>
       <c r="AM6" t="n">
-        <v>580</v>
+        <v>390</v>
       </c>
       <c r="AN6" t="n">
-        <v>44</v>
+        <v>600</v>
       </c>
       <c r="AO6" t="n">
-        <v>16</v>
+        <v>15.5</v>
       </c>
       <c r="AP6" t="n">
         <v>14</v>
       </c>
       <c r="AQ6" t="n">
-        <v>9.6</v>
+        <v>10</v>
       </c>
       <c r="AR6" t="n">
         <v>13</v>
@@ -1996,107 +1996,107 @@
         <v>12.5</v>
       </c>
       <c r="AU6" t="n">
-        <v>7.4</v>
+        <v>7.2</v>
       </c>
       <c r="AV6" t="n">
-        <v>9.800000000000001</v>
+        <v>10</v>
       </c>
       <c r="AW6" t="n">
         <v>20</v>
       </c>
       <c r="AX6" t="n">
-        <v>21</v>
+        <v>11.5</v>
       </c>
       <c r="AY6" t="n">
-        <v>12.5</v>
+        <v>12</v>
       </c>
       <c r="AZ6" t="n">
-        <v>14.5</v>
+        <v>14</v>
       </c>
       <c r="BA6" t="n">
         <v>13.5</v>
       </c>
       <c r="BB6" t="n">
-        <v>7.2</v>
+        <v>23</v>
       </c>
       <c r="BC6" t="n">
         <v>14</v>
       </c>
       <c r="BD6" t="n">
-        <v>7.6</v>
+        <v>9.6</v>
       </c>
       <c r="BE6" t="n">
-        <v>7.4</v>
+        <v>22</v>
       </c>
       <c r="BF6" t="n">
-        <v>7.4</v>
+        <v>8.4</v>
       </c>
       <c r="BG6" t="n">
-        <v>14</v>
+        <v>13.5</v>
       </c>
       <c r="BH6" t="n">
-        <v>3.6</v>
+        <v>3.65</v>
       </c>
       <c r="BI6" t="n">
-        <v>2.98</v>
+        <v>2.94</v>
       </c>
       <c r="BJ6" t="n">
-        <v>9.199999999999999</v>
+        <v>9.4</v>
       </c>
       <c r="BK6" t="n">
-        <v>6.8</v>
+        <v>5.8</v>
       </c>
       <c r="BL6" t="n">
         <v>1000</v>
       </c>
       <c r="BM6" t="n">
-        <v>15</v>
+        <v>13.5</v>
       </c>
       <c r="BN6" t="n">
-        <v>6.8</v>
+        <v>7.2</v>
       </c>
       <c r="BO6" t="n">
-        <v>5.1</v>
+        <v>5.4</v>
       </c>
       <c r="BP6" t="n">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="BQ6" t="n">
         <v>10</v>
       </c>
       <c r="BR6" t="n">
-        <v>48</v>
+        <v>1000</v>
       </c>
       <c r="BS6" t="n">
-        <v>11.5</v>
+        <v>10.5</v>
       </c>
       <c r="BT6" t="n">
-        <v>5.2</v>
+        <v>5</v>
       </c>
       <c r="BU6" t="n">
-        <v>4</v>
+        <v>3.85</v>
       </c>
       <c r="BV6" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="BW6" t="n">
-        <v>12.5</v>
+        <v>7.6</v>
       </c>
       <c r="BX6" t="n">
-        <v>36</v>
+        <v>27</v>
       </c>
       <c r="BY6" t="n">
-        <v>10.5</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BZ6" t="n">
         <v>23</v>
       </c>
       <c r="CA6" t="n">
-        <v>9.800000000000001</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="CB6" t="inlineStr">
         <is>
-          <t>2026-06-12 03:08:58</t>
+          <t>2026-06-12 05:25:07</t>
         </is>
       </c>
     </row>
@@ -2127,10 +2127,10 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>1.64</v>
+        <v>1.63</v>
       </c>
       <c r="G7" t="n">
-        <v>1.69</v>
+        <v>1.65</v>
       </c>
       <c r="H7" t="n">
         <v>5.8</v>
@@ -2139,7 +2139,7 @@
         <v>6.6</v>
       </c>
       <c r="J7" t="n">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="K7" t="n">
         <v>4.6</v>
@@ -2166,28 +2166,28 @@
         <v>1.43</v>
       </c>
       <c r="S7" t="n">
-        <v>3.1</v>
+        <v>3.05</v>
       </c>
       <c r="T7" t="n">
-        <v>1.83</v>
+        <v>1.82</v>
       </c>
       <c r="U7" t="n">
-        <v>2</v>
+        <v>2.02</v>
       </c>
       <c r="V7" t="n">
         <v>1.19</v>
       </c>
       <c r="W7" t="n">
-        <v>2.44</v>
+        <v>2.52</v>
       </c>
       <c r="X7" t="n">
         <v>18</v>
       </c>
       <c r="Y7" t="n">
-        <v>500</v>
+        <v>50</v>
       </c>
       <c r="Z7" t="n">
-        <v>55</v>
+        <v>120</v>
       </c>
       <c r="AA7" t="n">
         <v>900</v>
@@ -2211,7 +2211,7 @@
         <v>10.5</v>
       </c>
       <c r="AH7" t="n">
-        <v>22</v>
+        <v>44</v>
       </c>
       <c r="AI7" t="n">
         <v>700</v>
@@ -2220,10 +2220,10 @@
         <v>16.5</v>
       </c>
       <c r="AK7" t="n">
-        <v>17.5</v>
+        <v>29</v>
       </c>
       <c r="AL7" t="n">
-        <v>500</v>
+        <v>36</v>
       </c>
       <c r="AM7" t="n">
         <v>580</v>
@@ -2232,19 +2232,19 @@
         <v>9</v>
       </c>
       <c r="AO7" t="n">
-        <v>700</v>
+        <v>600</v>
       </c>
       <c r="AP7" t="n">
         <v>15</v>
       </c>
       <c r="AQ7" t="n">
-        <v>7.8</v>
+        <v>18</v>
       </c>
       <c r="AR7" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AS7" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="AT7" t="n">
         <v>7.6</v>
@@ -2253,13 +2253,13 @@
         <v>8.4</v>
       </c>
       <c r="AV7" t="n">
-        <v>8</v>
+        <v>19.5</v>
       </c>
       <c r="AW7" t="n">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="AX7" t="n">
-        <v>5.7</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AY7" t="n">
         <v>8.6</v>
@@ -2268,7 +2268,7 @@
         <v>17.5</v>
       </c>
       <c r="BA7" t="n">
-        <v>11</v>
+        <v>28</v>
       </c>
       <c r="BB7" t="n">
         <v>11.5</v>
@@ -2280,16 +2280,16 @@
         <v>21</v>
       </c>
       <c r="BE7" t="n">
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="BF7" t="n">
         <v>6.6</v>
       </c>
       <c r="BG7" t="n">
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="BH7" t="n">
-        <v>4.4</v>
+        <v>3.8</v>
       </c>
       <c r="BI7" t="n">
         <v>2.96</v>
@@ -2298,16 +2298,16 @@
         <v>12.5</v>
       </c>
       <c r="BK7" t="n">
-        <v>3.75</v>
+        <v>4.5</v>
       </c>
       <c r="BL7" t="n">
-        <v>150</v>
+        <v>1000</v>
       </c>
       <c r="BM7" t="n">
-        <v>5.1</v>
+        <v>6.6</v>
       </c>
       <c r="BN7" t="n">
-        <v>4.4</v>
+        <v>4.3</v>
       </c>
       <c r="BO7" t="n">
         <v>3.3</v>
@@ -2316,31 +2316,31 @@
         <v>12.5</v>
       </c>
       <c r="BQ7" t="n">
-        <v>3.75</v>
+        <v>7.6</v>
       </c>
       <c r="BR7" t="n">
         <v>32</v>
       </c>
       <c r="BS7" t="n">
-        <v>4.5</v>
+        <v>5.7</v>
       </c>
       <c r="BT7" t="n">
-        <v>12</v>
+        <v>11.5</v>
       </c>
       <c r="BU7" t="n">
-        <v>3.7</v>
+        <v>4.3</v>
       </c>
       <c r="BV7" t="n">
-        <v>55</v>
+        <v>65</v>
       </c>
       <c r="BW7" t="n">
-        <v>4.8</v>
+        <v>6.2</v>
       </c>
       <c r="BX7" t="n">
-        <v>70</v>
+        <v>1000</v>
       </c>
       <c r="BY7" t="n">
-        <v>4.9</v>
+        <v>6.2</v>
       </c>
       <c r="BZ7" t="n">
         <v>0</v>
@@ -2350,7 +2350,7 @@
       </c>
       <c r="CB7" t="inlineStr">
         <is>
-          <t>2026-06-12 03:08:58</t>
+          <t>2026-06-12 05:25:07</t>
         </is>
       </c>
     </row>
@@ -2381,64 +2381,64 @@
         </is>
       </c>
       <c r="F8" t="n">
-        <v>1.77</v>
+        <v>1.72</v>
       </c>
       <c r="G8" t="n">
-        <v>1.79</v>
+        <v>1.78</v>
       </c>
       <c r="H8" t="n">
-        <v>4.9</v>
+        <v>4.8</v>
       </c>
       <c r="I8" t="n">
-        <v>5.6</v>
+        <v>5.4</v>
       </c>
       <c r="J8" t="n">
-        <v>3.95</v>
+        <v>4.2</v>
       </c>
       <c r="K8" t="n">
         <v>4.3</v>
       </c>
       <c r="L8" t="n">
-        <v>1.4</v>
+        <v>1.38</v>
       </c>
       <c r="M8" t="n">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="N8" t="n">
-        <v>3.95</v>
+        <v>4.1</v>
       </c>
       <c r="O8" t="n">
-        <v>1.31</v>
+        <v>1.28</v>
       </c>
       <c r="P8" t="n">
-        <v>2.02</v>
+        <v>2.1</v>
       </c>
       <c r="Q8" t="n">
-        <v>1.91</v>
+        <v>1.82</v>
       </c>
       <c r="R8" t="n">
-        <v>1.37</v>
+        <v>1.42</v>
       </c>
       <c r="S8" t="n">
-        <v>3.4</v>
+        <v>3.15</v>
       </c>
       <c r="T8" t="n">
-        <v>1.11</v>
+        <v>1.83</v>
       </c>
       <c r="U8" t="n">
-        <v>1.98</v>
+        <v>2.04</v>
       </c>
       <c r="V8" t="n">
-        <v>1.22</v>
+        <v>1.23</v>
       </c>
       <c r="W8" t="n">
-        <v>2.26</v>
+        <v>2.28</v>
       </c>
       <c r="X8" t="n">
-        <v>970</v>
+        <v>19</v>
       </c>
       <c r="Y8" t="n">
-        <v>17.5</v>
+        <v>18.5</v>
       </c>
       <c r="Z8" t="n">
         <v>42</v>
@@ -2447,164 +2447,164 @@
         <v>900</v>
       </c>
       <c r="AB8" t="n">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="AC8" t="n">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="AD8" t="n">
-        <v>20</v>
+        <v>19.5</v>
       </c>
       <c r="AE8" t="n">
         <v>240</v>
       </c>
       <c r="AF8" t="n">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="AG8" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="AH8" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AI8" t="n">
-        <v>240</v>
+        <v>140</v>
       </c>
       <c r="AJ8" t="n">
-        <v>18</v>
+        <v>17.5</v>
       </c>
       <c r="AK8" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="AL8" t="n">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="AM8" t="n">
         <v>580</v>
       </c>
       <c r="AN8" t="n">
-        <v>11</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AO8" t="n">
-        <v>95</v>
+        <v>150</v>
       </c>
       <c r="AP8" t="n">
-        <v>13.5</v>
+        <v>16</v>
       </c>
       <c r="AQ8" t="n">
-        <v>14.5</v>
+        <v>15.5</v>
       </c>
       <c r="AR8" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="AS8" t="n">
-        <v>7</v>
+        <v>10.5</v>
       </c>
       <c r="AT8" t="n">
-        <v>7.4</v>
+        <v>8.4</v>
       </c>
       <c r="AU8" t="n">
-        <v>8.4</v>
+        <v>8.6</v>
       </c>
       <c r="AV8" t="n">
-        <v>5.4</v>
+        <v>16.5</v>
       </c>
       <c r="AW8" t="n">
-        <v>7</v>
+        <v>9.6</v>
       </c>
       <c r="AX8" t="n">
         <v>8.800000000000001</v>
       </c>
       <c r="AY8" t="n">
-        <v>8.6</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AZ8" t="n">
-        <v>5.6</v>
+        <v>18</v>
       </c>
       <c r="BA8" t="n">
-        <v>6.8</v>
+        <v>9.6</v>
       </c>
       <c r="BB8" t="n">
         <v>14.5</v>
       </c>
       <c r="BC8" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="BD8" t="n">
-        <v>13.5</v>
+        <v>15.5</v>
       </c>
       <c r="BE8" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="BF8" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="BG8" t="n">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="BH8" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="BI8" t="n">
+        <v>2.92</v>
+      </c>
+      <c r="BJ8" t="n">
+        <v>10</v>
+      </c>
+      <c r="BK8" t="n">
+        <v>5.7</v>
+      </c>
+      <c r="BL8" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BM8" t="n">
+        <v>12</v>
+      </c>
+      <c r="BN8" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="BO8" t="n">
+        <v>3.95</v>
+      </c>
+      <c r="BP8" t="n">
+        <v>12</v>
+      </c>
+      <c r="BQ8" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="BR8" t="n">
+        <v>26</v>
+      </c>
+      <c r="BS8" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="BT8" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="BU8" t="n">
+        <v>5.3</v>
+      </c>
+      <c r="BV8" t="n">
+        <v>44</v>
+      </c>
+      <c r="BW8" t="n">
+        <v>10</v>
+      </c>
+      <c r="BX8" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BY8" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="BZ8" t="n">
+        <v>20</v>
+      </c>
+      <c r="CA8" t="n">
         <v>8</v>
       </c>
-      <c r="BG8" t="n">
-        <v>6.8</v>
-      </c>
-      <c r="BH8" t="n">
-        <v>3.55</v>
-      </c>
-      <c r="BI8" t="n">
-        <v>2.76</v>
-      </c>
-      <c r="BJ8" t="n">
-        <v>11</v>
-      </c>
-      <c r="BK8" t="n">
-        <v>5.5</v>
-      </c>
-      <c r="BL8" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BM8" t="n">
-        <v>10</v>
-      </c>
-      <c r="BN8" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="BO8" t="n">
-        <v>3.35</v>
-      </c>
-      <c r="BP8" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="BQ8" t="n">
-        <v>8.6</v>
-      </c>
-      <c r="BR8" t="n">
-        <v>28</v>
-      </c>
-      <c r="BS8" t="n">
-        <v>8</v>
-      </c>
-      <c r="BT8" t="n">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="BU8" t="n">
-        <v>5</v>
-      </c>
-      <c r="BV8" t="n">
-        <v>50</v>
-      </c>
-      <c r="BW8" t="n">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="BX8" t="n">
-        <v>60</v>
-      </c>
-      <c r="BY8" t="n">
-        <v>9.4</v>
-      </c>
-      <c r="BZ8" t="n">
-        <v>23</v>
-      </c>
-      <c r="CA8" t="n">
-        <v>7.4</v>
-      </c>
       <c r="CB8" t="inlineStr">
         <is>
-          <t>2026-06-12 03:08:58</t>
+          <t>2026-06-12 05:25:07</t>
         </is>
       </c>
     </row>
@@ -2638,7 +2638,7 @@
         <v>4.5</v>
       </c>
       <c r="G9" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="H9" t="n">
         <v>1.71</v>
@@ -2674,7 +2674,7 @@
         <v>1.63</v>
       </c>
       <c r="S9" t="n">
-        <v>2.34</v>
+        <v>2.36</v>
       </c>
       <c r="T9" t="n">
         <v>1.6</v>
@@ -2683,7 +2683,7 @@
         <v>2.38</v>
       </c>
       <c r="V9" t="n">
-        <v>2.2</v>
+        <v>2.22</v>
       </c>
       <c r="W9" t="n">
         <v>1.24</v>
@@ -2701,7 +2701,7 @@
         <v>20</v>
       </c>
       <c r="AB9" t="n">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="AC9" t="n">
         <v>11</v>
@@ -2716,7 +2716,7 @@
         <v>220</v>
       </c>
       <c r="AG9" t="n">
-        <v>21</v>
+        <v>38</v>
       </c>
       <c r="AH9" t="n">
         <v>17.5</v>
@@ -2749,7 +2749,7 @@
         <v>11</v>
       </c>
       <c r="AR9" t="n">
-        <v>6.4</v>
+        <v>11</v>
       </c>
       <c r="AS9" t="n">
         <v>16</v>
@@ -2764,13 +2764,13 @@
         <v>9</v>
       </c>
       <c r="AW9" t="n">
-        <v>7.6</v>
+        <v>13.5</v>
       </c>
       <c r="AX9" t="n">
-        <v>7.4</v>
+        <v>18.5</v>
       </c>
       <c r="AY9" t="n">
-        <v>6.2</v>
+        <v>16.5</v>
       </c>
       <c r="AZ9" t="n">
         <v>14</v>
@@ -2779,16 +2779,16 @@
         <v>14.5</v>
       </c>
       <c r="BB9" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="BC9" t="n">
         <v>8.199999999999999</v>
       </c>
-      <c r="BC9" t="n">
-        <v>7.8</v>
-      </c>
       <c r="BD9" t="n">
-        <v>7.6</v>
+        <v>8</v>
       </c>
       <c r="BE9" t="n">
-        <v>8</v>
+        <v>8.4</v>
       </c>
       <c r="BF9" t="n">
         <v>8.4</v>
@@ -2797,58 +2797,58 @@
         <v>6.2</v>
       </c>
       <c r="BH9" t="n">
-        <v>5.1</v>
+        <v>4.7</v>
       </c>
       <c r="BI9" t="n">
         <v>3.6</v>
       </c>
       <c r="BJ9" t="n">
-        <v>10.5</v>
+        <v>9.4</v>
       </c>
       <c r="BK9" t="n">
-        <v>3.65</v>
+        <v>4.8</v>
       </c>
       <c r="BL9" t="n">
-        <v>95</v>
+        <v>1000</v>
       </c>
       <c r="BM9" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="BN9" t="n">
+        <v>9</v>
+      </c>
+      <c r="BO9" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="BP9" t="n">
+        <v>36</v>
+      </c>
+      <c r="BQ9" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="BR9" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BS9" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="BT9" t="n">
+        <v>5</v>
+      </c>
+      <c r="BU9" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="BV9" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="BW9" t="n">
         <v>5.3</v>
       </c>
-      <c r="BN9" t="n">
-        <v>9.800000000000001</v>
-      </c>
-      <c r="BO9" t="n">
-        <v>3.55</v>
-      </c>
-      <c r="BP9" t="n">
-        <v>40</v>
-      </c>
-      <c r="BQ9" t="n">
-        <v>4.9</v>
-      </c>
-      <c r="BR9" t="n">
-        <v>42</v>
-      </c>
-      <c r="BS9" t="n">
-        <v>4.9</v>
-      </c>
-      <c r="BT9" t="n">
-        <v>5.4</v>
-      </c>
-      <c r="BU9" t="n">
-        <v>2.74</v>
-      </c>
-      <c r="BV9" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="BW9" t="n">
-        <v>3.85</v>
-      </c>
       <c r="BX9" t="n">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="BY9" t="n">
-        <v>4.5</v>
+        <v>6.6</v>
       </c>
       <c r="BZ9" t="n">
         <v>0</v>
@@ -2858,7 +2858,7 @@
       </c>
       <c r="CB9" t="inlineStr">
         <is>
-          <t>2026-06-12 03:08:58</t>
+          <t>2026-06-12 05:25:07</t>
         </is>
       </c>
     </row>
@@ -2892,19 +2892,19 @@
         <v>1.56</v>
       </c>
       <c r="G10" t="n">
-        <v>1.66</v>
+        <v>1.65</v>
       </c>
       <c r="H10" t="n">
         <v>5.4</v>
       </c>
       <c r="I10" t="n">
-        <v>6.4</v>
+        <v>6.8</v>
       </c>
       <c r="J10" t="n">
         <v>4.3</v>
       </c>
       <c r="K10" t="n">
-        <v>5.2</v>
+        <v>5.3</v>
       </c>
       <c r="L10" t="n">
         <v>1.28</v>
@@ -2913,7 +2913,7 @@
         <v>1.03</v>
       </c>
       <c r="N10" t="n">
-        <v>5.5</v>
+        <v>5.6</v>
       </c>
       <c r="O10" t="n">
         <v>1.18</v>
@@ -2922,16 +2922,16 @@
         <v>2.56</v>
       </c>
       <c r="Q10" t="n">
-        <v>1.55</v>
+        <v>1.56</v>
       </c>
       <c r="R10" t="n">
-        <v>1.63</v>
+        <v>1.62</v>
       </c>
       <c r="S10" t="n">
-        <v>2.38</v>
+        <v>2.4</v>
       </c>
       <c r="T10" t="n">
-        <v>1.65</v>
+        <v>1.64</v>
       </c>
       <c r="U10" t="n">
         <v>2.26</v>
@@ -2940,13 +2940,13 @@
         <v>1.18</v>
       </c>
       <c r="W10" t="n">
-        <v>2.48</v>
+        <v>2.52</v>
       </c>
       <c r="X10" t="n">
-        <v>75</v>
+        <v>70</v>
       </c>
       <c r="Y10" t="n">
-        <v>32</v>
+        <v>500</v>
       </c>
       <c r="Z10" t="n">
         <v>500</v>
@@ -2955,13 +2955,13 @@
         <v>700</v>
       </c>
       <c r="AB10" t="n">
-        <v>12.5</v>
+        <v>13</v>
       </c>
       <c r="AC10" t="n">
-        <v>12</v>
+        <v>11.5</v>
       </c>
       <c r="AD10" t="n">
-        <v>25</v>
+        <v>38</v>
       </c>
       <c r="AE10" t="n">
         <v>700</v>
@@ -2982,7 +2982,7 @@
         <v>17</v>
       </c>
       <c r="AK10" t="n">
-        <v>16.5</v>
+        <v>16</v>
       </c>
       <c r="AL10" t="n">
         <v>48</v>
@@ -2991,7 +2991,7 @@
         <v>580</v>
       </c>
       <c r="AN10" t="n">
-        <v>6.8</v>
+        <v>6.6</v>
       </c>
       <c r="AO10" t="n">
         <v>700</v>
@@ -3003,10 +3003,10 @@
         <v>21</v>
       </c>
       <c r="AR10" t="n">
-        <v>7.8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AS10" t="n">
-        <v>8</v>
+        <v>8.6</v>
       </c>
       <c r="AT10" t="n">
         <v>10</v>
@@ -3018,7 +3018,7 @@
         <v>11</v>
       </c>
       <c r="AW10" t="n">
-        <v>7.4</v>
+        <v>7.8</v>
       </c>
       <c r="AX10" t="n">
         <v>10</v>
@@ -3030,7 +3030,7 @@
         <v>15</v>
       </c>
       <c r="BA10" t="n">
-        <v>7.4</v>
+        <v>7.8</v>
       </c>
       <c r="BB10" t="n">
         <v>13.5</v>
@@ -3042,19 +3042,19 @@
         <v>13</v>
       </c>
       <c r="BE10" t="n">
-        <v>7.6</v>
+        <v>7.8</v>
       </c>
       <c r="BF10" t="n">
         <v>5.5</v>
       </c>
       <c r="BG10" t="n">
-        <v>7.4</v>
+        <v>7.6</v>
       </c>
       <c r="BH10" t="n">
         <v>4.7</v>
       </c>
       <c r="BI10" t="n">
-        <v>3.45</v>
+        <v>3.5</v>
       </c>
       <c r="BJ10" t="n">
         <v>10</v>
@@ -3069,10 +3069,10 @@
         <v>8.4</v>
       </c>
       <c r="BN10" t="n">
-        <v>4.7</v>
+        <v>4.8</v>
       </c>
       <c r="BO10" t="n">
-        <v>3.5</v>
+        <v>3.55</v>
       </c>
       <c r="BP10" t="n">
         <v>10.5</v>
@@ -3081,7 +3081,7 @@
         <v>4.9</v>
       </c>
       <c r="BR10" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="BS10" t="n">
         <v>6.4</v>
@@ -3105,14 +3105,14 @@
         <v>7.6</v>
       </c>
       <c r="BZ10" t="n">
-        <v>14</v>
+        <v>13.5</v>
       </c>
       <c r="CA10" t="n">
-        <v>5.6</v>
+        <v>5.5</v>
       </c>
       <c r="CB10" t="inlineStr">
         <is>
-          <t>2026-06-12 03:08:58</t>
+          <t>2026-06-12 05:25:07</t>
         </is>
       </c>
     </row>
@@ -3143,19 +3143,19 @@
         </is>
       </c>
       <c r="F11" t="n">
-        <v>2.2</v>
+        <v>2.22</v>
       </c>
       <c r="G11" t="n">
         <v>2.32</v>
       </c>
       <c r="H11" t="n">
-        <v>4.3</v>
+        <v>4.4</v>
       </c>
       <c r="I11" t="n">
-        <v>4.7</v>
+        <v>4.8</v>
       </c>
       <c r="J11" t="n">
-        <v>2.9</v>
+        <v>2.84</v>
       </c>
       <c r="K11" t="n">
         <v>3.05</v>
@@ -3164,7 +3164,7 @@
         <v>1.61</v>
       </c>
       <c r="M11" t="n">
-        <v>1.14</v>
+        <v>1.15</v>
       </c>
       <c r="N11" t="n">
         <v>2.6</v>
@@ -3185,22 +3185,22 @@
         <v>5.8</v>
       </c>
       <c r="T11" t="n">
-        <v>2.16</v>
+        <v>2.18</v>
       </c>
       <c r="U11" t="n">
-        <v>1.71</v>
+        <v>1.72</v>
       </c>
       <c r="V11" t="n">
         <v>1.27</v>
       </c>
       <c r="W11" t="n">
-        <v>1.76</v>
+        <v>1.75</v>
       </c>
       <c r="X11" t="n">
         <v>8.199999999999999</v>
       </c>
       <c r="Y11" t="n">
-        <v>11.5</v>
+        <v>12</v>
       </c>
       <c r="Z11" t="n">
         <v>32</v>
@@ -3251,16 +3251,16 @@
         <v>600</v>
       </c>
       <c r="AP11" t="n">
-        <v>7</v>
+        <v>6.8</v>
       </c>
       <c r="AQ11" t="n">
-        <v>9.6</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AR11" t="n">
-        <v>11.5</v>
+        <v>14</v>
       </c>
       <c r="AS11" t="n">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="AT11" t="n">
         <v>6</v>
@@ -3287,40 +3287,40 @@
         <v>10.5</v>
       </c>
       <c r="BB11" t="n">
-        <v>11.5</v>
+        <v>14.5</v>
       </c>
       <c r="BC11" t="n">
         <v>14.5</v>
       </c>
       <c r="BD11" t="n">
-        <v>10</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BE11" t="n">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="BF11" t="n">
-        <v>9.199999999999999</v>
+        <v>9.4</v>
       </c>
       <c r="BG11" t="n">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="BH11" t="n">
         <v>2.68</v>
       </c>
       <c r="BI11" t="n">
-        <v>2.24</v>
+        <v>2.26</v>
       </c>
       <c r="BJ11" t="n">
         <v>12</v>
       </c>
       <c r="BK11" t="n">
-        <v>6.2</v>
+        <v>6.4</v>
       </c>
       <c r="BL11" t="n">
         <v>1000</v>
       </c>
       <c r="BM11" t="n">
-        <v>12.5</v>
+        <v>13.5</v>
       </c>
       <c r="BN11" t="n">
         <v>4.9</v>
@@ -3332,41 +3332,41 @@
         <v>20</v>
       </c>
       <c r="BQ11" t="n">
-        <v>8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BR11" t="n">
-        <v>1000</v>
+        <v>46</v>
       </c>
       <c r="BS11" t="n">
         <v>10.5</v>
       </c>
       <c r="BT11" t="n">
-        <v>7.4</v>
+        <v>7.2</v>
       </c>
       <c r="BU11" t="n">
-        <v>5.4</v>
+        <v>5.6</v>
       </c>
       <c r="BV11" t="n">
         <v>1000</v>
       </c>
       <c r="BW11" t="n">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="BX11" t="n">
         <v>1000</v>
       </c>
       <c r="BY11" t="n">
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="BZ11" t="n">
         <v>55</v>
       </c>
       <c r="CA11" t="n">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="CB11" t="inlineStr">
         <is>
-          <t>2026-06-12 03:08:58</t>
+          <t>2026-06-12 05:25:07</t>
         </is>
       </c>
     </row>
@@ -3397,22 +3397,22 @@
         </is>
       </c>
       <c r="F12" t="n">
-        <v>2.3</v>
+        <v>2.22</v>
       </c>
       <c r="G12" t="n">
-        <v>2.42</v>
+        <v>2.36</v>
       </c>
       <c r="H12" t="n">
-        <v>3.15</v>
+        <v>3.2</v>
       </c>
       <c r="I12" t="n">
-        <v>3.45</v>
+        <v>3.55</v>
       </c>
       <c r="J12" t="n">
-        <v>3.5</v>
+        <v>3.55</v>
       </c>
       <c r="K12" t="n">
-        <v>3.8</v>
+        <v>4</v>
       </c>
       <c r="L12" t="n">
         <v>1.33</v>
@@ -3445,37 +3445,37 @@
         <v>2.32</v>
       </c>
       <c r="V12" t="n">
-        <v>1.41</v>
+        <v>1.39</v>
       </c>
       <c r="W12" t="n">
-        <v>1.71</v>
+        <v>1.73</v>
       </c>
       <c r="X12" t="n">
-        <v>20</v>
+        <v>90</v>
       </c>
       <c r="Y12" t="n">
-        <v>16.5</v>
+        <v>970</v>
       </c>
       <c r="Z12" t="n">
-        <v>40</v>
+        <v>100</v>
       </c>
       <c r="AA12" t="n">
-        <v>500</v>
+        <v>900</v>
       </c>
       <c r="AB12" t="n">
         <v>13</v>
       </c>
       <c r="AC12" t="n">
-        <v>9.199999999999999</v>
+        <v>9.4</v>
       </c>
       <c r="AD12" t="n">
         <v>15</v>
       </c>
       <c r="AE12" t="n">
-        <v>55</v>
+        <v>85</v>
       </c>
       <c r="AF12" t="n">
-        <v>20</v>
+        <v>970</v>
       </c>
       <c r="AG12" t="n">
         <v>12</v>
@@ -3487,13 +3487,13 @@
         <v>100</v>
       </c>
       <c r="AJ12" t="n">
-        <v>38</v>
+        <v>65</v>
       </c>
       <c r="AK12" t="n">
-        <v>30</v>
+        <v>24</v>
       </c>
       <c r="AL12" t="n">
-        <v>44</v>
+        <v>210</v>
       </c>
       <c r="AM12" t="n">
         <v>580</v>
@@ -3502,58 +3502,58 @@
         <v>15</v>
       </c>
       <c r="AO12" t="n">
-        <v>27</v>
+        <v>600</v>
       </c>
       <c r="AP12" t="n">
-        <v>15.5</v>
+        <v>16</v>
       </c>
       <c r="AQ12" t="n">
+        <v>13</v>
+      </c>
+      <c r="AR12" t="n">
+        <v>20</v>
+      </c>
+      <c r="AS12" t="n">
+        <v>3.85</v>
+      </c>
+      <c r="AT12" t="n">
+        <v>10</v>
+      </c>
+      <c r="AU12" t="n">
+        <v>4</v>
+      </c>
+      <c r="AV12" t="n">
         <v>12</v>
-      </c>
-      <c r="AR12" t="n">
-        <v>19.5</v>
-      </c>
-      <c r="AS12" t="n">
-        <v>8.6</v>
-      </c>
-      <c r="AT12" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="AU12" t="n">
-        <v>7.4</v>
-      </c>
-      <c r="AV12" t="n">
-        <v>11.5</v>
       </c>
       <c r="AW12" t="n">
         <v>13</v>
       </c>
       <c r="AX12" t="n">
-        <v>14</v>
+        <v>3.3</v>
       </c>
       <c r="AY12" t="n">
         <v>9.6</v>
       </c>
       <c r="AZ12" t="n">
-        <v>13</v>
+        <v>3.2</v>
       </c>
       <c r="BA12" t="n">
-        <v>32</v>
+        <v>17</v>
       </c>
       <c r="BB12" t="n">
         <v>21</v>
       </c>
       <c r="BC12" t="n">
-        <v>19</v>
+        <v>18.5</v>
       </c>
       <c r="BD12" t="n">
         <v>24</v>
       </c>
       <c r="BE12" t="n">
-        <v>28</v>
+        <v>3.85</v>
       </c>
       <c r="BF12" t="n">
-        <v>12</v>
+        <v>2.76</v>
       </c>
       <c r="BG12" t="n">
         <v>12</v>
@@ -3620,7 +3620,7 @@
       </c>
       <c r="CB12" t="inlineStr">
         <is>
-          <t>2026-06-12 03:08:58</t>
+          <t>2026-06-12 05:25:07</t>
         </is>
       </c>
     </row>
@@ -3651,22 +3651,22 @@
         </is>
       </c>
       <c r="F13" t="n">
-        <v>1.15</v>
+        <v>1.19</v>
       </c>
       <c r="G13" t="n">
-        <v>1.17</v>
+        <v>1.22</v>
       </c>
       <c r="H13" t="n">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="I13" t="n">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="J13" t="n">
-        <v>9.199999999999999</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="K13" t="n">
-        <v>10.5</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="L13" t="n">
         <v>1.21</v>
@@ -3675,34 +3675,34 @@
         <v>1.02</v>
       </c>
       <c r="N13" t="n">
-        <v>8.800000000000001</v>
+        <v>8</v>
       </c>
       <c r="O13" t="n">
-        <v>1.11</v>
+        <v>1.12</v>
       </c>
       <c r="P13" t="n">
-        <v>3.55</v>
+        <v>3.35</v>
       </c>
       <c r="Q13" t="n">
-        <v>1.35</v>
+        <v>1.38</v>
       </c>
       <c r="R13" t="n">
-        <v>2.04</v>
+        <v>1.98</v>
       </c>
       <c r="S13" t="n">
-        <v>1.87</v>
+        <v>1.92</v>
       </c>
       <c r="T13" t="n">
-        <v>2.02</v>
+        <v>2.12</v>
       </c>
       <c r="U13" t="n">
-        <v>1.81</v>
+        <v>1.72</v>
       </c>
       <c r="V13" t="n">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="W13" t="n">
-        <v>6.6</v>
+        <v>5.6</v>
       </c>
       <c r="X13" t="n">
         <v>950</v>
@@ -3711,13 +3711,13 @@
         <v>950</v>
       </c>
       <c r="Z13" t="n">
-        <v>290</v>
+        <v>200</v>
       </c>
       <c r="AA13" t="n">
         <v>1000</v>
       </c>
       <c r="AB13" t="n">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="AC13" t="n">
         <v>24</v>
@@ -3726,155 +3726,155 @@
         <v>950</v>
       </c>
       <c r="AE13" t="n">
-        <v>370</v>
+        <v>310</v>
       </c>
       <c r="AF13" t="n">
-        <v>11</v>
+        <v>9.6</v>
       </c>
       <c r="AG13" t="n">
-        <v>14.5</v>
+        <v>16.5</v>
       </c>
       <c r="AH13" t="n">
         <v>950</v>
       </c>
       <c r="AI13" t="n">
-        <v>240</v>
+        <v>220</v>
       </c>
       <c r="AJ13" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="AK13" t="n">
+        <v>17</v>
+      </c>
+      <c r="AL13" t="n">
+        <v>44</v>
+      </c>
+      <c r="AM13" t="n">
+        <v>180</v>
+      </c>
+      <c r="AN13" t="n">
+        <v>3.15</v>
+      </c>
+      <c r="AO13" t="n">
+        <v>310</v>
+      </c>
+      <c r="AP13" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="AQ13" t="n">
+        <v>7</v>
+      </c>
+      <c r="AR13" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="AS13" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="AT13" t="n">
         <v>11</v>
       </c>
-      <c r="AK13" t="n">
-        <v>14.5</v>
-      </c>
-      <c r="AL13" t="n">
-        <v>50</v>
-      </c>
-      <c r="AM13" t="n">
-        <v>210</v>
-      </c>
-      <c r="AN13" t="n">
-        <v>2.78</v>
-      </c>
-      <c r="AO13" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AP13" t="n">
+      <c r="AU13" t="n">
+        <v>6</v>
+      </c>
+      <c r="AV13" t="n">
+        <v>7</v>
+      </c>
+      <c r="AW13" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="AX13" t="n">
+        <v>8</v>
+      </c>
+      <c r="AY13" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="AZ13" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="BA13" t="n">
         <v>7.4</v>
       </c>
-      <c r="AQ13" t="n">
+      <c r="BB13" t="n">
         <v>7.8</v>
       </c>
-      <c r="AR13" t="n">
-        <v>8.199999999999999</v>
-      </c>
-      <c r="AS13" t="n">
-        <v>8.4</v>
-      </c>
-      <c r="AT13" t="n">
-        <v>5.9</v>
-      </c>
-      <c r="AU13" t="n">
+      <c r="BC13" t="n">
         <v>6.6</v>
       </c>
-      <c r="AV13" t="n">
-        <v>7.6</v>
-      </c>
-      <c r="AW13" t="n">
-        <v>8.199999999999999</v>
-      </c>
-      <c r="AX13" t="n">
-        <v>8.6</v>
-      </c>
-      <c r="AY13" t="n">
+      <c r="BD13" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="BE13" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="BF13" t="n">
+        <v>2.72</v>
+      </c>
+      <c r="BG13" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="BH13" t="n">
+        <v>5.8</v>
+      </c>
+      <c r="BI13" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="BJ13" t="n">
+        <v>13</v>
+      </c>
+      <c r="BK13" t="n">
+        <v>6</v>
+      </c>
+      <c r="BL13" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BM13" t="n">
         <v>10.5</v>
-      </c>
-      <c r="AZ13" t="n">
-        <v>7</v>
-      </c>
-      <c r="BA13" t="n">
-        <v>8</v>
-      </c>
-      <c r="BB13" t="n">
-        <v>8.199999999999999</v>
-      </c>
-      <c r="BC13" t="n">
-        <v>11</v>
-      </c>
-      <c r="BD13" t="n">
-        <v>7</v>
-      </c>
-      <c r="BE13" t="n">
-        <v>8</v>
-      </c>
-      <c r="BF13" t="n">
-        <v>2.48</v>
-      </c>
-      <c r="BG13" t="n">
-        <v>8.800000000000001</v>
-      </c>
-      <c r="BH13" t="n">
-        <v>6.2</v>
-      </c>
-      <c r="BI13" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="BJ13" t="n">
-        <v>14.5</v>
-      </c>
-      <c r="BK13" t="n">
-        <v>5.8</v>
-      </c>
-      <c r="BL13" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BM13" t="n">
-        <v>9</v>
       </c>
       <c r="BN13" t="n">
         <v>4.2</v>
       </c>
       <c r="BO13" t="n">
-        <v>3.25</v>
+        <v>3.55</v>
       </c>
       <c r="BP13" t="n">
-        <v>6.2</v>
+        <v>6.6</v>
       </c>
       <c r="BQ13" t="n">
-        <v>4.6</v>
+        <v>5.1</v>
       </c>
       <c r="BR13" t="n">
         <v>1000</v>
       </c>
       <c r="BS13" t="n">
-        <v>6.6</v>
+        <v>7.2</v>
       </c>
       <c r="BT13" t="n">
-        <v>1000</v>
+        <v>18.5</v>
       </c>
       <c r="BU13" t="n">
-        <v>6.6</v>
+        <v>7</v>
       </c>
       <c r="BV13" t="n">
         <v>1000</v>
       </c>
       <c r="BW13" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="BX13" t="n">
         <v>1000</v>
       </c>
       <c r="BY13" t="n">
-        <v>8.800000000000001</v>
+        <v>10</v>
       </c>
       <c r="BZ13" t="n">
-        <v>6.6</v>
+        <v>7.2</v>
       </c>
       <c r="CA13" t="n">
-        <v>4.9</v>
+        <v>5.4</v>
       </c>
       <c r="CB13" t="inlineStr">
         <is>
-          <t>2026-06-12 03:08:58</t>
+          <t>2026-06-12 05:25:07</t>
         </is>
       </c>
     </row>
@@ -3905,7 +3905,7 @@
         </is>
       </c>
       <c r="F14" t="n">
-        <v>3.25</v>
+        <v>3.2</v>
       </c>
       <c r="G14" t="n">
         <v>3.45</v>
@@ -3914,10 +3914,10 @@
         <v>2.36</v>
       </c>
       <c r="I14" t="n">
-        <v>2.44</v>
+        <v>2.5</v>
       </c>
       <c r="J14" t="n">
-        <v>3.4</v>
+        <v>3.35</v>
       </c>
       <c r="K14" t="n">
         <v>3.6</v>
@@ -3938,7 +3938,7 @@
         <v>1.83</v>
       </c>
       <c r="Q14" t="n">
-        <v>2.1</v>
+        <v>2.08</v>
       </c>
       <c r="R14" t="n">
         <v>1.31</v>
@@ -3947,28 +3947,28 @@
         <v>3.9</v>
       </c>
       <c r="T14" t="n">
-        <v>1.79</v>
+        <v>1.81</v>
       </c>
       <c r="U14" t="n">
         <v>2.06</v>
       </c>
       <c r="V14" t="n">
-        <v>1.7</v>
+        <v>1.67</v>
       </c>
       <c r="W14" t="n">
-        <v>1.41</v>
+        <v>1.4</v>
       </c>
       <c r="X14" t="n">
-        <v>13.5</v>
+        <v>13</v>
       </c>
       <c r="Y14" t="n">
-        <v>10.5</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="Z14" t="n">
         <v>16</v>
       </c>
       <c r="AA14" t="n">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="AB14" t="n">
         <v>12</v>
@@ -3977,7 +3977,7 @@
         <v>8</v>
       </c>
       <c r="AD14" t="n">
-        <v>12.5</v>
+        <v>12</v>
       </c>
       <c r="AE14" t="n">
         <v>29</v>
@@ -3995,7 +3995,7 @@
         <v>44</v>
       </c>
       <c r="AJ14" t="n">
-        <v>150</v>
+        <v>65</v>
       </c>
       <c r="AK14" t="n">
         <v>42</v>
@@ -4007,7 +4007,7 @@
         <v>110</v>
       </c>
       <c r="AN14" t="n">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="AO14" t="n">
         <v>24</v>
@@ -4016,13 +4016,13 @@
         <v>11</v>
       </c>
       <c r="AQ14" t="n">
-        <v>8.800000000000001</v>
+        <v>8.6</v>
       </c>
       <c r="AR14" t="n">
         <v>13</v>
       </c>
       <c r="AS14" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="AT14" t="n">
         <v>10.5</v>
@@ -4049,16 +4049,16 @@
         <v>38</v>
       </c>
       <c r="BB14" t="n">
-        <v>23</v>
+        <v>32</v>
       </c>
       <c r="BC14" t="n">
-        <v>36</v>
+        <v>21</v>
       </c>
       <c r="BD14" t="n">
         <v>44</v>
       </c>
       <c r="BE14" t="n">
-        <v>16</v>
+        <v>40</v>
       </c>
       <c r="BF14" t="n">
         <v>34</v>
@@ -4067,7 +4067,7 @@
         <v>19.5</v>
       </c>
       <c r="BH14" t="n">
-        <v>3.3</v>
+        <v>3.25</v>
       </c>
       <c r="BI14" t="n">
         <v>2.7</v>
@@ -4076,59 +4076,59 @@
         <v>9.800000000000001</v>
       </c>
       <c r="BK14" t="n">
-        <v>5.9</v>
+        <v>6</v>
       </c>
       <c r="BL14" t="n">
         <v>1000</v>
       </c>
       <c r="BM14" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="BN14" t="n">
         <v>6.6</v>
       </c>
       <c r="BO14" t="n">
-        <v>5.1</v>
+        <v>4.6</v>
       </c>
       <c r="BP14" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="BQ14" t="n">
-        <v>9.6</v>
+        <v>10</v>
       </c>
       <c r="BR14" t="n">
         <v>1000</v>
       </c>
       <c r="BS14" t="n">
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="BT14" t="n">
         <v>5.2</v>
       </c>
       <c r="BU14" t="n">
-        <v>4</v>
+        <v>4.5</v>
       </c>
       <c r="BV14" t="n">
-        <v>18.5</v>
+        <v>18</v>
       </c>
       <c r="BW14" t="n">
-        <v>8.199999999999999</v>
+        <v>8.4</v>
       </c>
       <c r="BX14" t="n">
         <v>34</v>
       </c>
       <c r="BY14" t="n">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="BZ14" t="n">
         <v>30</v>
       </c>
       <c r="CA14" t="n">
-        <v>9.800000000000001</v>
+        <v>10</v>
       </c>
       <c r="CB14" t="inlineStr">
         <is>
-          <t>2026-06-12 03:08:58</t>
+          <t>2026-06-12 05:25:07</t>
         </is>
       </c>
     </row>
@@ -4162,13 +4162,13 @@
         <v>2.42</v>
       </c>
       <c r="G15" t="n">
-        <v>2.66</v>
+        <v>2.68</v>
       </c>
       <c r="H15" t="n">
         <v>3.45</v>
       </c>
       <c r="I15" t="n">
-        <v>3.85</v>
+        <v>3.9</v>
       </c>
       <c r="J15" t="n">
         <v>2.88</v>
@@ -4177,13 +4177,13 @@
         <v>3.15</v>
       </c>
       <c r="L15" t="n">
-        <v>1.63</v>
+        <v>1.64</v>
       </c>
       <c r="M15" t="n">
         <v>1.14</v>
       </c>
       <c r="N15" t="n">
-        <v>2.46</v>
+        <v>2.48</v>
       </c>
       <c r="O15" t="n">
         <v>1.6</v>
@@ -4192,7 +4192,7 @@
         <v>1.46</v>
       </c>
       <c r="Q15" t="n">
-        <v>2.92</v>
+        <v>2.88</v>
       </c>
       <c r="R15" t="n">
         <v>1.17</v>
@@ -4201,7 +4201,7 @@
         <v>6</v>
       </c>
       <c r="T15" t="n">
-        <v>2.18</v>
+        <v>2.2</v>
       </c>
       <c r="U15" t="n">
         <v>1.71</v>
@@ -4216,10 +4216,10 @@
         <v>8</v>
       </c>
       <c r="Y15" t="n">
-        <v>9.800000000000001</v>
+        <v>10</v>
       </c>
       <c r="Z15" t="n">
-        <v>90</v>
+        <v>26</v>
       </c>
       <c r="AA15" t="n">
         <v>900</v>
@@ -4231,7 +4231,7 @@
         <v>7.4</v>
       </c>
       <c r="AD15" t="n">
-        <v>17.5</v>
+        <v>18</v>
       </c>
       <c r="AE15" t="n">
         <v>440</v>
@@ -4240,7 +4240,7 @@
         <v>15.5</v>
       </c>
       <c r="AG15" t="n">
-        <v>14</v>
+        <v>13.5</v>
       </c>
       <c r="AH15" t="n">
         <v>65</v>
@@ -4255,7 +4255,7 @@
         <v>140</v>
       </c>
       <c r="AL15" t="n">
-        <v>460</v>
+        <v>500</v>
       </c>
       <c r="AM15" t="n">
         <v>500</v>
@@ -4267,58 +4267,58 @@
         <v>600</v>
       </c>
       <c r="AP15" t="n">
-        <v>4.3</v>
+        <v>6.6</v>
       </c>
       <c r="AQ15" t="n">
-        <v>5.1</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AR15" t="n">
-        <v>6.8</v>
+        <v>20</v>
       </c>
       <c r="AS15" t="n">
-        <v>8.4</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AT15" t="n">
-        <v>4.2</v>
+        <v>6.2</v>
       </c>
       <c r="AU15" t="n">
-        <v>4.2</v>
+        <v>6</v>
       </c>
       <c r="AV15" t="n">
-        <v>6</v>
+        <v>14.5</v>
       </c>
       <c r="AW15" t="n">
-        <v>8.199999999999999</v>
+        <v>8</v>
       </c>
       <c r="AX15" t="n">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="AY15" t="n">
-        <v>5.7</v>
+        <v>11</v>
       </c>
       <c r="AZ15" t="n">
         <v>6.8</v>
       </c>
       <c r="BA15" t="n">
-        <v>8.6</v>
+        <v>8.4</v>
       </c>
       <c r="BB15" t="n">
-        <v>7.6</v>
+        <v>16</v>
       </c>
       <c r="BC15" t="n">
-        <v>7.6</v>
+        <v>16</v>
       </c>
       <c r="BD15" t="n">
-        <v>8.4</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BE15" t="n">
-        <v>9</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BF15" t="n">
         <v>7.8</v>
       </c>
       <c r="BG15" t="n">
-        <v>8.6</v>
+        <v>8.4</v>
       </c>
       <c r="BH15" t="n">
         <v>2.64</v>
@@ -4330,7 +4330,7 @@
         <v>12.5</v>
       </c>
       <c r="BK15" t="n">
-        <v>5.9</v>
+        <v>6</v>
       </c>
       <c r="BL15" t="n">
         <v>1000</v>
@@ -4339,7 +4339,7 @@
         <v>11</v>
       </c>
       <c r="BN15" t="n">
-        <v>5.4</v>
+        <v>5.3</v>
       </c>
       <c r="BO15" t="n">
         <v>4.5</v>
@@ -4348,13 +4348,13 @@
         <v>24</v>
       </c>
       <c r="BQ15" t="n">
-        <v>7.6</v>
+        <v>8</v>
       </c>
       <c r="BR15" t="n">
         <v>55</v>
       </c>
       <c r="BS15" t="n">
-        <v>9.4</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BT15" t="n">
         <v>6.8</v>
@@ -4366,23 +4366,23 @@
         <v>1000</v>
       </c>
       <c r="BW15" t="n">
-        <v>8.800000000000001</v>
+        <v>9</v>
       </c>
       <c r="BX15" t="n">
         <v>1000</v>
       </c>
       <c r="BY15" t="n">
-        <v>9.6</v>
+        <v>10</v>
       </c>
       <c r="BZ15" t="n">
         <v>1000</v>
       </c>
       <c r="CA15" t="n">
-        <v>9.6</v>
+        <v>10</v>
       </c>
       <c r="CB15" t="inlineStr">
         <is>
-          <t>2026-06-12 03:08:58</t>
+          <t>2026-06-12 05:25:07</t>
         </is>
       </c>
     </row>
@@ -4416,19 +4416,19 @@
         <v>2.92</v>
       </c>
       <c r="G16" t="n">
-        <v>3.1</v>
+        <v>3.05</v>
       </c>
       <c r="H16" t="n">
-        <v>2.44</v>
+        <v>2.46</v>
       </c>
       <c r="I16" t="n">
-        <v>2.52</v>
+        <v>2.54</v>
       </c>
       <c r="J16" t="n">
-        <v>3.7</v>
+        <v>3.75</v>
       </c>
       <c r="K16" t="n">
-        <v>3.9</v>
+        <v>3.95</v>
       </c>
       <c r="L16" t="n">
         <v>1.33</v>
@@ -4443,10 +4443,10 @@
         <v>1.23</v>
       </c>
       <c r="P16" t="n">
-        <v>2.34</v>
+        <v>2.32</v>
       </c>
       <c r="Q16" t="n">
-        <v>1.71</v>
+        <v>1.7</v>
       </c>
       <c r="R16" t="n">
         <v>1.52</v>
@@ -4455,13 +4455,13 @@
         <v>2.8</v>
       </c>
       <c r="T16" t="n">
-        <v>1.6</v>
+        <v>1.59</v>
       </c>
       <c r="U16" t="n">
-        <v>2.52</v>
+        <v>2.56</v>
       </c>
       <c r="V16" t="n">
-        <v>1.66</v>
+        <v>1.64</v>
       </c>
       <c r="W16" t="n">
         <v>1.48</v>
@@ -4473,7 +4473,7 @@
         <v>14</v>
       </c>
       <c r="Z16" t="n">
-        <v>18.5</v>
+        <v>19.5</v>
       </c>
       <c r="AA16" t="n">
         <v>80</v>
@@ -4482,10 +4482,10 @@
         <v>16</v>
       </c>
       <c r="AC16" t="n">
-        <v>9.4</v>
+        <v>9</v>
       </c>
       <c r="AD16" t="n">
-        <v>12.5</v>
+        <v>12</v>
       </c>
       <c r="AE16" t="n">
         <v>25</v>
@@ -4494,7 +4494,7 @@
         <v>23</v>
       </c>
       <c r="AG16" t="n">
-        <v>14</v>
+        <v>13.5</v>
       </c>
       <c r="AH16" t="n">
         <v>15.5</v>
@@ -4512,7 +4512,7 @@
         <v>38</v>
       </c>
       <c r="AM16" t="n">
-        <v>75</v>
+        <v>200</v>
       </c>
       <c r="AN16" t="n">
         <v>22</v>
@@ -4530,13 +4530,13 @@
         <v>15.5</v>
       </c>
       <c r="AS16" t="n">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="AT16" t="n">
         <v>13.5</v>
       </c>
       <c r="AU16" t="n">
-        <v>7.6</v>
+        <v>8</v>
       </c>
       <c r="AV16" t="n">
         <v>10</v>
@@ -4545,7 +4545,7 @@
         <v>20</v>
       </c>
       <c r="AX16" t="n">
-        <v>19</v>
+        <v>19.5</v>
       </c>
       <c r="AY16" t="n">
         <v>11</v>
@@ -4554,7 +4554,7 @@
         <v>13</v>
       </c>
       <c r="BA16" t="n">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="BB16" t="n">
         <v>38</v>
@@ -4581,16 +4581,16 @@
         <v>3.15</v>
       </c>
       <c r="BJ16" t="n">
-        <v>9.199999999999999</v>
+        <v>9</v>
       </c>
       <c r="BK16" t="n">
-        <v>1.04</v>
+        <v>4.8</v>
       </c>
       <c r="BL16" t="n">
-        <v>90</v>
+        <v>1000</v>
       </c>
       <c r="BM16" t="n">
-        <v>1.04</v>
+        <v>9.4</v>
       </c>
       <c r="BN16" t="n">
         <v>6.6</v>
@@ -4602,13 +4602,13 @@
         <v>22</v>
       </c>
       <c r="BQ16" t="n">
-        <v>1.04</v>
+        <v>7</v>
       </c>
       <c r="BR16" t="n">
         <v>30</v>
       </c>
       <c r="BS16" t="n">
-        <v>1.04</v>
+        <v>7.8</v>
       </c>
       <c r="BT16" t="n">
         <v>5.9</v>
@@ -4620,23 +4620,23 @@
         <v>17.5</v>
       </c>
       <c r="BW16" t="n">
-        <v>1.04</v>
+        <v>6.6</v>
       </c>
       <c r="BX16" t="n">
         <v>27</v>
       </c>
       <c r="BY16" t="n">
-        <v>1.04</v>
+        <v>7.6</v>
       </c>
       <c r="BZ16" t="n">
-        <v>20</v>
+        <v>19.5</v>
       </c>
       <c r="CA16" t="n">
-        <v>1.04</v>
+        <v>6.8</v>
       </c>
       <c r="CB16" t="inlineStr">
         <is>
-          <t>2026-06-12 03:08:58</t>
+          <t>2026-06-12 05:25:07</t>
         </is>
       </c>
     </row>
@@ -4667,22 +4667,22 @@
         </is>
       </c>
       <c r="F17" t="n">
-        <v>1.4</v>
+        <v>1.41</v>
       </c>
       <c r="G17" t="n">
-        <v>1.43</v>
+        <v>1.42</v>
       </c>
       <c r="H17" t="n">
         <v>9.800000000000001</v>
       </c>
       <c r="I17" t="n">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="J17" t="n">
         <v>4.9</v>
       </c>
       <c r="K17" t="n">
-        <v>5.3</v>
+        <v>5.2</v>
       </c>
       <c r="L17" t="n">
         <v>1.38</v>
@@ -4697,40 +4697,40 @@
         <v>1.29</v>
       </c>
       <c r="P17" t="n">
-        <v>2.06</v>
+        <v>2.1</v>
       </c>
       <c r="Q17" t="n">
         <v>1.88</v>
       </c>
       <c r="R17" t="n">
-        <v>1.4</v>
+        <v>1.41</v>
       </c>
       <c r="S17" t="n">
-        <v>3.3</v>
+        <v>3.25</v>
       </c>
       <c r="T17" t="n">
-        <v>2.18</v>
+        <v>2.2</v>
       </c>
       <c r="U17" t="n">
-        <v>1.75</v>
+        <v>1.77</v>
       </c>
       <c r="V17" t="n">
         <v>1.1</v>
       </c>
       <c r="W17" t="n">
-        <v>3.3</v>
+        <v>3.35</v>
       </c>
       <c r="X17" t="n">
-        <v>17</v>
+        <v>17.5</v>
       </c>
       <c r="Y17" t="n">
-        <v>32</v>
+        <v>85</v>
       </c>
       <c r="Z17" t="n">
         <v>95</v>
       </c>
       <c r="AA17" t="n">
-        <v>510</v>
+        <v>450</v>
       </c>
       <c r="AB17" t="n">
         <v>7.8</v>
@@ -4739,13 +4739,13 @@
         <v>12</v>
       </c>
       <c r="AD17" t="n">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="AE17" t="n">
-        <v>200</v>
+        <v>190</v>
       </c>
       <c r="AF17" t="n">
-        <v>8</v>
+        <v>7.8</v>
       </c>
       <c r="AG17" t="n">
         <v>10</v>
@@ -4754,7 +4754,7 @@
         <v>32</v>
       </c>
       <c r="AI17" t="n">
-        <v>170</v>
+        <v>160</v>
       </c>
       <c r="AJ17" t="n">
         <v>11.5</v>
@@ -4766,40 +4766,40 @@
         <v>46</v>
       </c>
       <c r="AM17" t="n">
-        <v>240</v>
+        <v>200</v>
       </c>
       <c r="AN17" t="n">
         <v>7</v>
       </c>
       <c r="AO17" t="n">
-        <v>290</v>
+        <v>260</v>
       </c>
       <c r="AP17" t="n">
-        <v>15</v>
+        <v>16.5</v>
       </c>
       <c r="AQ17" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="AR17" t="n">
         <v>36</v>
       </c>
       <c r="AS17" t="n">
-        <v>13.5</v>
+        <v>14</v>
       </c>
       <c r="AT17" t="n">
         <v>7</v>
       </c>
       <c r="AU17" t="n">
-        <v>9.800000000000001</v>
+        <v>10</v>
       </c>
       <c r="AV17" t="n">
-        <v>18</v>
+        <v>32</v>
       </c>
       <c r="AW17" t="n">
-        <v>12.5</v>
+        <v>13.5</v>
       </c>
       <c r="AX17" t="n">
-        <v>6.8</v>
+        <v>7</v>
       </c>
       <c r="AY17" t="n">
         <v>9.199999999999999</v>
@@ -4808,7 +4808,7 @@
         <v>27</v>
       </c>
       <c r="BA17" t="n">
-        <v>12.5</v>
+        <v>13.5</v>
       </c>
       <c r="BB17" t="n">
         <v>10</v>
@@ -4820,10 +4820,10 @@
         <v>36</v>
       </c>
       <c r="BE17" t="n">
-        <v>14</v>
+        <v>14.5</v>
       </c>
       <c r="BF17" t="n">
-        <v>6.2</v>
+        <v>6.6</v>
       </c>
       <c r="BG17" t="n">
         <v>15</v>
@@ -4832,7 +4832,7 @@
         <v>3.8</v>
       </c>
       <c r="BI17" t="n">
-        <v>2.9</v>
+        <v>2.92</v>
       </c>
       <c r="BJ17" t="n">
         <v>13</v>
@@ -4890,7 +4890,7 @@
       </c>
       <c r="CB17" t="inlineStr">
         <is>
-          <t>2026-06-12 03:08:58</t>
+          <t>2026-06-12 05:25:07</t>
         </is>
       </c>
     </row>
@@ -4921,79 +4921,79 @@
         </is>
       </c>
       <c r="F18" t="n">
-        <v>3.2</v>
+        <v>3.25</v>
       </c>
       <c r="G18" t="n">
-        <v>3.35</v>
+        <v>3.3</v>
       </c>
       <c r="H18" t="n">
-        <v>2.5</v>
+        <v>2.48</v>
       </c>
       <c r="I18" t="n">
-        <v>2.58</v>
+        <v>2.52</v>
       </c>
       <c r="J18" t="n">
-        <v>3.25</v>
+        <v>3.3</v>
       </c>
       <c r="K18" t="n">
         <v>3.4</v>
       </c>
       <c r="L18" t="n">
-        <v>1.48</v>
+        <v>1.5</v>
       </c>
       <c r="M18" t="n">
-        <v>1.09</v>
+        <v>1.1</v>
       </c>
       <c r="N18" t="n">
-        <v>3.25</v>
+        <v>3.15</v>
       </c>
       <c r="O18" t="n">
-        <v>1.42</v>
+        <v>1.44</v>
       </c>
       <c r="P18" t="n">
-        <v>1.74</v>
+        <v>1.7</v>
       </c>
       <c r="Q18" t="n">
-        <v>2.28</v>
+        <v>2.34</v>
       </c>
       <c r="R18" t="n">
-        <v>1.27</v>
+        <v>1.26</v>
       </c>
       <c r="S18" t="n">
-        <v>4.4</v>
+        <v>4.7</v>
       </c>
       <c r="T18" t="n">
-        <v>1.87</v>
+        <v>1.97</v>
       </c>
       <c r="U18" t="n">
         <v>1.96</v>
       </c>
       <c r="V18" t="n">
-        <v>1.63</v>
+        <v>1.65</v>
       </c>
       <c r="W18" t="n">
-        <v>1.42</v>
+        <v>1.43</v>
       </c>
       <c r="X18" t="n">
-        <v>12</v>
+        <v>11.5</v>
       </c>
       <c r="Y18" t="n">
-        <v>9.4</v>
+        <v>9</v>
       </c>
       <c r="Z18" t="n">
-        <v>16</v>
+        <v>15.5</v>
       </c>
       <c r="AA18" t="n">
         <v>50</v>
       </c>
       <c r="AB18" t="n">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="AC18" t="n">
         <v>7.8</v>
       </c>
       <c r="AD18" t="n">
-        <v>12.5</v>
+        <v>12</v>
       </c>
       <c r="AE18" t="n">
         <v>46</v>
@@ -5005,10 +5005,10 @@
         <v>14.5</v>
       </c>
       <c r="AH18" t="n">
-        <v>19.5</v>
+        <v>21</v>
       </c>
       <c r="AI18" t="n">
-        <v>120</v>
+        <v>290</v>
       </c>
       <c r="AJ18" t="n">
         <v>500</v>
@@ -5017,7 +5017,7 @@
         <v>100</v>
       </c>
       <c r="AL18" t="n">
-        <v>290</v>
+        <v>130</v>
       </c>
       <c r="AM18" t="n">
         <v>580</v>
@@ -5032,16 +5032,16 @@
         <v>9.6</v>
       </c>
       <c r="AQ18" t="n">
-        <v>8.199999999999999</v>
+        <v>7.8</v>
       </c>
       <c r="AR18" t="n">
-        <v>13</v>
+        <v>12.5</v>
       </c>
       <c r="AS18" t="n">
         <v>26</v>
       </c>
       <c r="AT18" t="n">
-        <v>9.6</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AU18" t="n">
         <v>6.6</v>
@@ -5071,19 +5071,19 @@
         <v>30</v>
       </c>
       <c r="BD18" t="n">
-        <v>40</v>
+        <v>23</v>
       </c>
       <c r="BE18" t="n">
-        <v>9.800000000000001</v>
+        <v>9</v>
       </c>
       <c r="BF18" t="n">
         <v>34</v>
       </c>
       <c r="BG18" t="n">
-        <v>7.8</v>
+        <v>15</v>
       </c>
       <c r="BH18" t="n">
-        <v>3.15</v>
+        <v>3.1</v>
       </c>
       <c r="BI18" t="n">
         <v>2.56</v>
@@ -5104,13 +5104,13 @@
         <v>6.6</v>
       </c>
       <c r="BO18" t="n">
-        <v>5</v>
+        <v>5.4</v>
       </c>
       <c r="BP18" t="n">
         <v>1000</v>
       </c>
       <c r="BQ18" t="n">
-        <v>8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BR18" t="n">
         <v>1000</v>
@@ -5128,23 +5128,23 @@
         <v>21</v>
       </c>
       <c r="BW18" t="n">
-        <v>7.2</v>
+        <v>7.4</v>
       </c>
       <c r="BX18" t="n">
         <v>1000</v>
       </c>
       <c r="BY18" t="n">
-        <v>8.6</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BZ18" t="n">
-        <v>1000</v>
+        <v>44</v>
       </c>
       <c r="CA18" t="n">
-        <v>8.6</v>
+        <v>9</v>
       </c>
       <c r="CB18" t="inlineStr">
         <is>
-          <t>2026-06-12 03:08:58</t>
+          <t>2026-06-12 05:25:07</t>
         </is>
       </c>
     </row>
@@ -5175,22 +5175,22 @@
         </is>
       </c>
       <c r="F19" t="n">
+        <v>2.24</v>
+      </c>
+      <c r="G19" t="n">
         <v>2.3</v>
       </c>
-      <c r="G19" t="n">
-        <v>2.36</v>
-      </c>
       <c r="H19" t="n">
-        <v>3.3</v>
+        <v>3.45</v>
       </c>
       <c r="I19" t="n">
-        <v>3.45</v>
+        <v>3.55</v>
       </c>
       <c r="J19" t="n">
-        <v>3.6</v>
+        <v>3.55</v>
       </c>
       <c r="K19" t="n">
-        <v>3.8</v>
+        <v>3.75</v>
       </c>
       <c r="L19" t="n">
         <v>1.39</v>
@@ -5208,10 +5208,10 @@
         <v>2.02</v>
       </c>
       <c r="Q19" t="n">
-        <v>1.93</v>
+        <v>1.92</v>
       </c>
       <c r="R19" t="n">
-        <v>1.39</v>
+        <v>1.4</v>
       </c>
       <c r="S19" t="n">
         <v>3.4</v>
@@ -5220,31 +5220,31 @@
         <v>1.7</v>
       </c>
       <c r="U19" t="n">
-        <v>2.22</v>
+        <v>2.26</v>
       </c>
       <c r="V19" t="n">
-        <v>1.41</v>
+        <v>1.39</v>
       </c>
       <c r="W19" t="n">
-        <v>1.73</v>
+        <v>1.76</v>
       </c>
       <c r="X19" t="n">
         <v>16</v>
       </c>
       <c r="Y19" t="n">
-        <v>13.5</v>
+        <v>14.5</v>
       </c>
       <c r="Z19" t="n">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="AA19" t="n">
-        <v>130</v>
+        <v>440</v>
       </c>
       <c r="AB19" t="n">
         <v>11</v>
       </c>
       <c r="AC19" t="n">
-        <v>8.6</v>
+        <v>8.4</v>
       </c>
       <c r="AD19" t="n">
         <v>14</v>
@@ -5253,52 +5253,52 @@
         <v>50</v>
       </c>
       <c r="AF19" t="n">
-        <v>15.5</v>
+        <v>15</v>
       </c>
       <c r="AG19" t="n">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="AH19" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="AI19" t="n">
         <v>60</v>
       </c>
       <c r="AJ19" t="n">
-        <v>42</v>
+        <v>32</v>
       </c>
       <c r="AK19" t="n">
-        <v>32</v>
+        <v>26</v>
       </c>
       <c r="AL19" t="n">
+        <v>38</v>
+      </c>
+      <c r="AM19" t="n">
+        <v>200</v>
+      </c>
+      <c r="AN19" t="n">
+        <v>17.5</v>
+      </c>
+      <c r="AO19" t="n">
         <v>50</v>
-      </c>
-      <c r="AM19" t="n">
-        <v>320</v>
-      </c>
-      <c r="AN19" t="n">
-        <v>18.5</v>
-      </c>
-      <c r="AO19" t="n">
-        <v>48</v>
       </c>
       <c r="AP19" t="n">
         <v>13.5</v>
       </c>
       <c r="AQ19" t="n">
-        <v>10.5</v>
+        <v>12.5</v>
       </c>
       <c r="AR19" t="n">
         <v>19.5</v>
       </c>
       <c r="AS19" t="n">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="AT19" t="n">
         <v>9.4</v>
       </c>
       <c r="AU19" t="n">
-        <v>7.2</v>
+        <v>7</v>
       </c>
       <c r="AV19" t="n">
         <v>12</v>
@@ -5310,16 +5310,16 @@
         <v>13</v>
       </c>
       <c r="AY19" t="n">
-        <v>9.6</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AZ19" t="n">
         <v>14.5</v>
       </c>
       <c r="BA19" t="n">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="BB19" t="n">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="BC19" t="n">
         <v>20</v>
@@ -5328,13 +5328,13 @@
         <v>25</v>
       </c>
       <c r="BE19" t="n">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="BF19" t="n">
         <v>15</v>
       </c>
       <c r="BG19" t="n">
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="BH19" t="n">
         <v>3.65</v>
@@ -5361,16 +5361,16 @@
         <v>4.5</v>
       </c>
       <c r="BP19" t="n">
-        <v>17.5</v>
+        <v>17</v>
       </c>
       <c r="BQ19" t="n">
-        <v>7.2</v>
+        <v>11.5</v>
       </c>
       <c r="BR19" t="n">
         <v>1000</v>
       </c>
       <c r="BS19" t="n">
-        <v>8.6</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BT19" t="n">
         <v>6.8</v>
@@ -5382,13 +5382,13 @@
         <v>1000</v>
       </c>
       <c r="BW19" t="n">
-        <v>8.199999999999999</v>
+        <v>8.4</v>
       </c>
       <c r="BX19" t="n">
         <v>1000</v>
       </c>
       <c r="BY19" t="n">
-        <v>9</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BZ19" t="n">
         <v>25</v>
@@ -5398,7 +5398,7 @@
       </c>
       <c r="CB19" t="inlineStr">
         <is>
-          <t>2026-06-12 03:08:58</t>
+          <t>2026-06-12 05:25:07</t>
         </is>
       </c>
     </row>
@@ -5432,7 +5432,7 @@
         <v>4.2</v>
       </c>
       <c r="G20" t="n">
-        <v>4.5</v>
+        <v>4.6</v>
       </c>
       <c r="H20" t="n">
         <v>1.92</v>
@@ -5453,16 +5453,16 @@
         <v>1.05</v>
       </c>
       <c r="N20" t="n">
-        <v>4.8</v>
+        <v>4.6</v>
       </c>
       <c r="O20" t="n">
-        <v>1.24</v>
+        <v>1.25</v>
       </c>
       <c r="P20" t="n">
-        <v>2.28</v>
+        <v>2.26</v>
       </c>
       <c r="Q20" t="n">
-        <v>1.73</v>
+        <v>1.74</v>
       </c>
       <c r="R20" t="n">
         <v>1.53</v>
@@ -5471,10 +5471,10 @@
         <v>2.84</v>
       </c>
       <c r="T20" t="n">
-        <v>1.64</v>
+        <v>1.68</v>
       </c>
       <c r="U20" t="n">
-        <v>2.3</v>
+        <v>2.32</v>
       </c>
       <c r="V20" t="n">
         <v>2.02</v>
@@ -5483,22 +5483,22 @@
         <v>1.28</v>
       </c>
       <c r="X20" t="n">
-        <v>21</v>
+        <v>19.5</v>
       </c>
       <c r="Y20" t="n">
-        <v>12</v>
+        <v>11.5</v>
       </c>
       <c r="Z20" t="n">
-        <v>14.5</v>
+        <v>14</v>
       </c>
       <c r="AA20" t="n">
         <v>32</v>
       </c>
       <c r="AB20" t="n">
-        <v>22</v>
+        <v>19.5</v>
       </c>
       <c r="AC20" t="n">
-        <v>9.800000000000001</v>
+        <v>9.4</v>
       </c>
       <c r="AD20" t="n">
         <v>12</v>
@@ -5513,7 +5513,7 @@
         <v>19.5</v>
       </c>
       <c r="AH20" t="n">
-        <v>16</v>
+        <v>16.5</v>
       </c>
       <c r="AI20" t="n">
         <v>36</v>
@@ -5525,13 +5525,13 @@
         <v>55</v>
       </c>
       <c r="AL20" t="n">
-        <v>44</v>
+        <v>48</v>
       </c>
       <c r="AM20" t="n">
-        <v>320</v>
+        <v>100</v>
       </c>
       <c r="AN20" t="n">
-        <v>38</v>
+        <v>42</v>
       </c>
       <c r="AO20" t="n">
         <v>10</v>
@@ -5549,10 +5549,10 @@
         <v>21</v>
       </c>
       <c r="AT20" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AU20" t="n">
-        <v>8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AV20" t="n">
         <v>10</v>
@@ -5561,7 +5561,7 @@
         <v>15</v>
       </c>
       <c r="AX20" t="n">
-        <v>15</v>
+        <v>27</v>
       </c>
       <c r="AY20" t="n">
         <v>15.5</v>
@@ -5570,13 +5570,13 @@
         <v>13</v>
       </c>
       <c r="BA20" t="n">
-        <v>16.5</v>
+        <v>23</v>
       </c>
       <c r="BB20" t="n">
-        <v>7.2</v>
+        <v>8.6</v>
       </c>
       <c r="BC20" t="n">
-        <v>20</v>
+        <v>34</v>
       </c>
       <c r="BD20" t="n">
         <v>36</v>
@@ -5585,10 +5585,10 @@
         <v>8.800000000000001</v>
       </c>
       <c r="BF20" t="n">
-        <v>16.5</v>
+        <v>16</v>
       </c>
       <c r="BG20" t="n">
-        <v>8.800000000000001</v>
+        <v>8.6</v>
       </c>
       <c r="BH20" t="n">
         <v>4.1</v>
@@ -5597,62 +5597,62 @@
         <v>3.1</v>
       </c>
       <c r="BJ20" t="n">
-        <v>13</v>
+        <v>9.6</v>
       </c>
       <c r="BK20" t="n">
-        <v>2.82</v>
+        <v>5.8</v>
       </c>
       <c r="BL20" t="n">
         <v>1000</v>
       </c>
       <c r="BM20" t="n">
-        <v>3.6</v>
+        <v>9</v>
       </c>
       <c r="BN20" t="n">
-        <v>10.5</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BO20" t="n">
         <v>4.9</v>
       </c>
       <c r="BP20" t="n">
-        <v>46</v>
+        <v>34</v>
       </c>
       <c r="BQ20" t="n">
-        <v>3.35</v>
+        <v>7.6</v>
       </c>
       <c r="BR20" t="n">
-        <v>50</v>
+        <v>40</v>
       </c>
       <c r="BS20" t="n">
-        <v>3.35</v>
+        <v>8</v>
       </c>
       <c r="BT20" t="n">
-        <v>6.8</v>
+        <v>5</v>
       </c>
       <c r="BU20" t="n">
-        <v>3.3</v>
+        <v>4.2</v>
       </c>
       <c r="BV20" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="BW20" t="n">
+        <v>8</v>
+      </c>
+      <c r="BX20" t="n">
+        <v>25</v>
+      </c>
+      <c r="BY20" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="BZ20" t="n">
         <v>19</v>
       </c>
-      <c r="BW20" t="n">
-        <v>3</v>
-      </c>
-      <c r="BX20" t="n">
-        <v>34</v>
-      </c>
-      <c r="BY20" t="n">
-        <v>3.25</v>
-      </c>
-      <c r="BZ20" t="n">
-        <v>28</v>
-      </c>
       <c r="CA20" t="n">
-        <v>3.2</v>
+        <v>6.6</v>
       </c>
       <c r="CB20" t="inlineStr">
         <is>
-          <t>2026-06-12 03:08:58</t>
+          <t>2026-06-12 05:25:07</t>
         </is>
       </c>
     </row>
@@ -5683,25 +5683,25 @@
         </is>
       </c>
       <c r="F21" t="n">
-        <v>2.38</v>
+        <v>2.4</v>
       </c>
       <c r="G21" t="n">
-        <v>2.46</v>
+        <v>2.52</v>
       </c>
       <c r="H21" t="n">
-        <v>3.35</v>
+        <v>3.3</v>
       </c>
       <c r="I21" t="n">
-        <v>3.6</v>
+        <v>3.5</v>
       </c>
       <c r="J21" t="n">
-        <v>3.3</v>
+        <v>3.25</v>
       </c>
       <c r="K21" t="n">
-        <v>3.45</v>
+        <v>3.4</v>
       </c>
       <c r="L21" t="n">
-        <v>1.49</v>
+        <v>1.5</v>
       </c>
       <c r="M21" t="n">
         <v>1.1</v>
@@ -5710,31 +5710,31 @@
         <v>3.2</v>
       </c>
       <c r="O21" t="n">
-        <v>1.42</v>
+        <v>1.43</v>
       </c>
       <c r="P21" t="n">
-        <v>1.73</v>
+        <v>1.72</v>
       </c>
       <c r="Q21" t="n">
-        <v>2.28</v>
+        <v>2.3</v>
       </c>
       <c r="R21" t="n">
-        <v>1.27</v>
+        <v>1.26</v>
       </c>
       <c r="S21" t="n">
-        <v>4.3</v>
+        <v>4.4</v>
       </c>
       <c r="T21" t="n">
-        <v>1.91</v>
+        <v>1.92</v>
       </c>
       <c r="U21" t="n">
         <v>1.97</v>
       </c>
       <c r="V21" t="n">
-        <v>1.39</v>
+        <v>1.4</v>
       </c>
       <c r="W21" t="n">
-        <v>1.69</v>
+        <v>1.66</v>
       </c>
       <c r="X21" t="n">
         <v>13.5</v>
@@ -5752,7 +5752,7 @@
         <v>8.800000000000001</v>
       </c>
       <c r="AC21" t="n">
-        <v>7.6</v>
+        <v>9</v>
       </c>
       <c r="AD21" t="n">
         <v>18.5</v>
@@ -5788,7 +5788,7 @@
         <v>32</v>
       </c>
       <c r="AO21" t="n">
-        <v>90</v>
+        <v>600</v>
       </c>
       <c r="AP21" t="n">
         <v>9.6</v>
@@ -5800,7 +5800,7 @@
         <v>10.5</v>
       </c>
       <c r="AS21" t="n">
-        <v>5.1</v>
+        <v>4.6</v>
       </c>
       <c r="AT21" t="n">
         <v>7.6</v>
@@ -5812,7 +5812,7 @@
         <v>13</v>
       </c>
       <c r="AW21" t="n">
-        <v>5</v>
+        <v>4.6</v>
       </c>
       <c r="AX21" t="n">
         <v>12.5</v>
@@ -5824,19 +5824,19 @@
         <v>10.5</v>
       </c>
       <c r="BA21" t="n">
-        <v>5.1</v>
+        <v>4.6</v>
       </c>
       <c r="BB21" t="n">
-        <v>4.9</v>
+        <v>4.4</v>
       </c>
       <c r="BC21" t="n">
         <v>13</v>
       </c>
       <c r="BD21" t="n">
-        <v>5</v>
+        <v>4.6</v>
       </c>
       <c r="BE21" t="n">
-        <v>5.3</v>
+        <v>4.8</v>
       </c>
       <c r="BF21" t="n">
         <v>5.4</v>
@@ -5845,43 +5845,43 @@
         <v>8.6</v>
       </c>
       <c r="BH21" t="n">
-        <v>3.05</v>
+        <v>2.98</v>
       </c>
       <c r="BI21" t="n">
-        <v>2.56</v>
+        <v>2.54</v>
       </c>
       <c r="BJ21" t="n">
         <v>10.5</v>
       </c>
       <c r="BK21" t="n">
-        <v>6.2</v>
+        <v>6.4</v>
       </c>
       <c r="BL21" t="n">
         <v>1000</v>
       </c>
       <c r="BM21" t="n">
-        <v>14.5</v>
+        <v>15.5</v>
       </c>
       <c r="BN21" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="BO21" t="n">
-        <v>3.95</v>
+        <v>4</v>
       </c>
       <c r="BP21" t="n">
         <v>1000</v>
       </c>
       <c r="BQ21" t="n">
-        <v>8.6</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BR21" t="n">
         <v>1000</v>
       </c>
       <c r="BS21" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="BT21" t="n">
-        <v>6.6</v>
+        <v>6.4</v>
       </c>
       <c r="BU21" t="n">
         <v>4.9</v>
@@ -5890,23 +5890,23 @@
         <v>1000</v>
       </c>
       <c r="BW21" t="n">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="BX21" t="n">
         <v>1000</v>
       </c>
       <c r="BY21" t="n">
-        <v>11.5</v>
+        <v>12.5</v>
       </c>
       <c r="BZ21" t="n">
         <v>1000</v>
       </c>
       <c r="CA21" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="CB21" t="inlineStr">
         <is>
-          <t>2026-06-12 03:08:58</t>
+          <t>2026-06-12 05:25:07</t>
         </is>
       </c>
     </row>
@@ -5937,28 +5937,28 @@
         </is>
       </c>
       <c r="F22" t="n">
-        <v>3.8</v>
+        <v>3.85</v>
       </c>
       <c r="G22" t="n">
         <v>4.2</v>
       </c>
       <c r="H22" t="n">
-        <v>1.99</v>
+        <v>2</v>
       </c>
       <c r="I22" t="n">
         <v>2.08</v>
       </c>
       <c r="J22" t="n">
-        <v>3.75</v>
+        <v>3.65</v>
       </c>
       <c r="K22" t="n">
-        <v>4</v>
+        <v>3.9</v>
       </c>
       <c r="L22" t="n">
         <v>1.36</v>
       </c>
       <c r="M22" t="n">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="N22" t="n">
         <v>4.5</v>
@@ -5976,28 +5976,28 @@
         <v>1.46</v>
       </c>
       <c r="S22" t="n">
-        <v>3.05</v>
+        <v>3</v>
       </c>
       <c r="T22" t="n">
-        <v>1.69</v>
+        <v>1.71</v>
       </c>
       <c r="U22" t="n">
-        <v>1.73</v>
+        <v>2.26</v>
       </c>
       <c r="V22" t="n">
         <v>1.92</v>
       </c>
       <c r="W22" t="n">
-        <v>1.32</v>
+        <v>1.31</v>
       </c>
       <c r="X22" t="n">
-        <v>17.5</v>
+        <v>18</v>
       </c>
       <c r="Y22" t="n">
         <v>11</v>
       </c>
       <c r="Z22" t="n">
-        <v>13.5</v>
+        <v>14.5</v>
       </c>
       <c r="AA22" t="n">
         <v>24</v>
@@ -6018,7 +6018,7 @@
         <v>32</v>
       </c>
       <c r="AG22" t="n">
-        <v>17.5</v>
+        <v>17</v>
       </c>
       <c r="AH22" t="n">
         <v>17.5</v>
@@ -6030,22 +6030,22 @@
         <v>500</v>
       </c>
       <c r="AK22" t="n">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="AL22" t="n">
-        <v>55</v>
+        <v>50</v>
       </c>
       <c r="AM22" t="n">
         <v>320</v>
       </c>
       <c r="AN22" t="n">
-        <v>46</v>
+        <v>40</v>
       </c>
       <c r="AO22" t="n">
         <v>12.5</v>
       </c>
       <c r="AP22" t="n">
-        <v>14.5</v>
+        <v>15.5</v>
       </c>
       <c r="AQ22" t="n">
         <v>9</v>
@@ -6081,7 +6081,7 @@
         <v>16</v>
       </c>
       <c r="BB22" t="n">
-        <v>9.800000000000001</v>
+        <v>10</v>
       </c>
       <c r="BC22" t="n">
         <v>9.199999999999999</v>
@@ -6090,31 +6090,31 @@
         <v>9.4</v>
       </c>
       <c r="BE22" t="n">
-        <v>9.800000000000001</v>
+        <v>10</v>
       </c>
       <c r="BF22" t="n">
-        <v>9</v>
+        <v>29</v>
       </c>
       <c r="BG22" t="n">
         <v>10</v>
       </c>
       <c r="BH22" t="n">
-        <v>1000</v>
+        <v>3.9</v>
       </c>
       <c r="BI22" t="n">
-        <v>3.1</v>
+        <v>3.05</v>
       </c>
       <c r="BJ22" t="n">
         <v>9.6</v>
       </c>
       <c r="BK22" t="n">
-        <v>1.04</v>
+        <v>4.9</v>
       </c>
       <c r="BL22" t="n">
         <v>1000</v>
       </c>
       <c r="BM22" t="n">
-        <v>1.04</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BN22" t="n">
         <v>7.8</v>
@@ -6126,13 +6126,13 @@
         <v>32</v>
       </c>
       <c r="BQ22" t="n">
-        <v>1.04</v>
+        <v>7.6</v>
       </c>
       <c r="BR22" t="n">
         <v>40</v>
       </c>
       <c r="BS22" t="n">
-        <v>1.04</v>
+        <v>8</v>
       </c>
       <c r="BT22" t="n">
         <v>5.1</v>
@@ -6144,23 +6144,23 @@
         <v>14.5</v>
       </c>
       <c r="BW22" t="n">
-        <v>1.04</v>
+        <v>5.9</v>
       </c>
       <c r="BX22" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="BY22" t="n">
-        <v>1.04</v>
+        <v>7.2</v>
       </c>
       <c r="BZ22" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="CA22" t="n">
-        <v>1.04</v>
+        <v>6.8</v>
       </c>
       <c r="CB22" t="inlineStr">
         <is>
-          <t>2026-06-12 03:08:58</t>
+          <t>2026-06-12 05:25:07</t>
         </is>
       </c>
     </row>
@@ -6191,13 +6191,13 @@
         </is>
       </c>
       <c r="F23" t="n">
-        <v>4.5</v>
+        <v>4.6</v>
       </c>
       <c r="G23" t="n">
-        <v>5</v>
+        <v>4.9</v>
       </c>
       <c r="H23" t="n">
-        <v>1.9</v>
+        <v>1.91</v>
       </c>
       <c r="I23" t="n">
         <v>1.95</v>
@@ -6233,10 +6233,10 @@
         <v>3.4</v>
       </c>
       <c r="T23" t="n">
-        <v>1.78</v>
+        <v>1.8</v>
       </c>
       <c r="U23" t="n">
-        <v>2.06</v>
+        <v>2.08</v>
       </c>
       <c r="V23" t="n">
         <v>2.04</v>
@@ -6248,7 +6248,7 @@
         <v>15.5</v>
       </c>
       <c r="Y23" t="n">
-        <v>9.6</v>
+        <v>9.4</v>
       </c>
       <c r="Z23" t="n">
         <v>12.5</v>
@@ -6269,10 +6269,10 @@
         <v>21</v>
       </c>
       <c r="AF23" t="n">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="AG23" t="n">
-        <v>18.5</v>
+        <v>19</v>
       </c>
       <c r="AH23" t="n">
         <v>19.5</v>
@@ -6284,22 +6284,22 @@
         <v>900</v>
       </c>
       <c r="AK23" t="n">
-        <v>70</v>
+        <v>65</v>
       </c>
       <c r="AL23" t="n">
         <v>75</v>
       </c>
       <c r="AM23" t="n">
-        <v>580</v>
+        <v>380</v>
       </c>
       <c r="AN23" t="n">
-        <v>65</v>
+        <v>70</v>
       </c>
       <c r="AO23" t="n">
         <v>13.5</v>
       </c>
       <c r="AP23" t="n">
-        <v>11</v>
+        <v>12.5</v>
       </c>
       <c r="AQ23" t="n">
         <v>7.8</v>
@@ -6308,7 +6308,7 @@
         <v>10</v>
       </c>
       <c r="AS23" t="n">
-        <v>18</v>
+        <v>17.5</v>
       </c>
       <c r="AT23" t="n">
         <v>13.5</v>
@@ -6329,13 +6329,13 @@
         <v>15.5</v>
       </c>
       <c r="AZ23" t="n">
-        <v>16</v>
+        <v>15.5</v>
       </c>
       <c r="BA23" t="n">
         <v>24</v>
       </c>
       <c r="BB23" t="n">
-        <v>9.4</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BC23" t="n">
         <v>38</v>
@@ -6344,13 +6344,13 @@
         <v>42</v>
       </c>
       <c r="BE23" t="n">
-        <v>9</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BF23" t="n">
-        <v>12.5</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BG23" t="n">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="BH23" t="n">
         <v>3.65</v>
@@ -6362,59 +6362,59 @@
         <v>10.5</v>
       </c>
       <c r="BK23" t="n">
-        <v>5.1</v>
+        <v>7.8</v>
       </c>
       <c r="BL23" t="n">
         <v>1000</v>
       </c>
       <c r="BM23" t="n">
-        <v>9.4</v>
+        <v>9.6</v>
       </c>
       <c r="BN23" t="n">
-        <v>8.199999999999999</v>
+        <v>8.4</v>
       </c>
       <c r="BO23" t="n">
-        <v>6</v>
+        <v>4.6</v>
       </c>
       <c r="BP23" t="n">
         <v>40</v>
       </c>
       <c r="BQ23" t="n">
-        <v>8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BR23" t="n">
-        <v>1000</v>
+        <v>50</v>
       </c>
       <c r="BS23" t="n">
-        <v>8.4</v>
+        <v>8.6</v>
       </c>
       <c r="BT23" t="n">
-        <v>4.8</v>
+        <v>4.7</v>
       </c>
       <c r="BU23" t="n">
-        <v>3.7</v>
+        <v>3.95</v>
       </c>
       <c r="BV23" t="n">
-        <v>14</v>
+        <v>13.5</v>
       </c>
       <c r="BW23" t="n">
-        <v>5.8</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BX23" t="n">
         <v>28</v>
       </c>
       <c r="BY23" t="n">
-        <v>7.4</v>
+        <v>7.6</v>
       </c>
       <c r="BZ23" t="n">
         <v>24</v>
       </c>
       <c r="CA23" t="n">
-        <v>7</v>
+        <v>7.2</v>
       </c>
       <c r="CB23" t="inlineStr">
         <is>
-          <t>2026-06-12 03:08:58</t>
+          <t>2026-06-12 05:25:07</t>
         </is>
       </c>
     </row>
@@ -6445,230 +6445,230 @@
         </is>
       </c>
       <c r="F24" t="n">
-        <v>1.33</v>
+        <v>1.61</v>
       </c>
       <c r="G24" t="n">
-        <v>1.63</v>
+        <v>1.71</v>
       </c>
       <c r="H24" t="n">
-        <v>1.04</v>
+        <v>4.8</v>
       </c>
       <c r="I24" t="n">
-        <v>1000</v>
+        <v>5.4</v>
       </c>
       <c r="J24" t="n">
-        <v>1.03</v>
+        <v>4.7</v>
       </c>
       <c r="K24" t="n">
-        <v>1000</v>
+        <v>5.4</v>
       </c>
       <c r="L24" t="n">
-        <v>1.01</v>
+        <v>1.2</v>
       </c>
       <c r="M24" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="N24" t="n">
-        <v>1.1</v>
+        <v>7.4</v>
       </c>
       <c r="O24" t="n">
-        <v>1.01</v>
+        <v>1.13</v>
       </c>
       <c r="P24" t="n">
-        <v>1.25</v>
+        <v>3.15</v>
       </c>
       <c r="Q24" t="n">
-        <v>1.01</v>
+        <v>1.39</v>
       </c>
       <c r="R24" t="n">
-        <v>1.18</v>
+        <v>1.87</v>
       </c>
       <c r="S24" t="n">
-        <v>1.05</v>
+        <v>1.96</v>
       </c>
       <c r="T24" t="n">
-        <v>1.11</v>
+        <v>1.51</v>
       </c>
       <c r="U24" t="n">
-        <v>1.11</v>
+        <v>2.68</v>
       </c>
       <c r="V24" t="n">
-        <v>1.01</v>
+        <v>1.22</v>
       </c>
       <c r="W24" t="n">
-        <v>1.01</v>
+        <v>2.42</v>
       </c>
       <c r="X24" t="n">
-        <v>1000</v>
+        <v>44</v>
       </c>
       <c r="Y24" t="n">
-        <v>1000</v>
+        <v>34</v>
       </c>
       <c r="Z24" t="n">
-        <v>1000</v>
+        <v>55</v>
       </c>
       <c r="AA24" t="n">
-        <v>1000</v>
+        <v>120</v>
       </c>
       <c r="AB24" t="n">
-        <v>1000</v>
+        <v>19.5</v>
       </c>
       <c r="AC24" t="n">
-        <v>1000</v>
+        <v>15</v>
       </c>
       <c r="AD24" t="n">
-        <v>1000</v>
+        <v>24</v>
       </c>
       <c r="AE24" t="n">
-        <v>1000</v>
+        <v>55</v>
       </c>
       <c r="AF24" t="n">
-        <v>1000</v>
+        <v>16</v>
       </c>
       <c r="AG24" t="n">
-        <v>1000</v>
+        <v>13</v>
       </c>
       <c r="AH24" t="n">
-        <v>1000</v>
+        <v>17.5</v>
       </c>
       <c r="AI24" t="n">
-        <v>1000</v>
+        <v>48</v>
       </c>
       <c r="AJ24" t="n">
-        <v>1000</v>
+        <v>22</v>
       </c>
       <c r="AK24" t="n">
-        <v>1000</v>
+        <v>16</v>
       </c>
       <c r="AL24" t="n">
-        <v>1000</v>
+        <v>27</v>
       </c>
       <c r="AM24" t="n">
-        <v>1000</v>
+        <v>55</v>
       </c>
       <c r="AN24" t="n">
-        <v>1000</v>
+        <v>5.5</v>
       </c>
       <c r="AO24" t="n">
-        <v>1000</v>
+        <v>32</v>
       </c>
       <c r="AP24" t="n">
-        <v>1.01</v>
+        <v>5.8</v>
       </c>
       <c r="AQ24" t="n">
-        <v>1.01</v>
+        <v>5.6</v>
       </c>
       <c r="AR24" t="n">
-        <v>1.01</v>
+        <v>6</v>
       </c>
       <c r="AS24" t="n">
-        <v>1.01</v>
+        <v>6.4</v>
       </c>
       <c r="AT24" t="n">
-        <v>1.01</v>
+        <v>14</v>
       </c>
       <c r="AU24" t="n">
-        <v>1.01</v>
+        <v>11</v>
       </c>
       <c r="AV24" t="n">
-        <v>1.01</v>
+        <v>17.5</v>
       </c>
       <c r="AW24" t="n">
-        <v>1.01</v>
+        <v>6</v>
       </c>
       <c r="AX24" t="n">
-        <v>1.01</v>
+        <v>13</v>
       </c>
       <c r="AY24" t="n">
-        <v>1.01</v>
+        <v>9.6</v>
       </c>
       <c r="AZ24" t="n">
-        <v>1.01</v>
+        <v>14</v>
       </c>
       <c r="BA24" t="n">
-        <v>1.01</v>
+        <v>5.9</v>
       </c>
       <c r="BB24" t="n">
-        <v>1.01</v>
+        <v>16</v>
       </c>
       <c r="BC24" t="n">
-        <v>1.01</v>
+        <v>13</v>
       </c>
       <c r="BD24" t="n">
-        <v>1.01</v>
+        <v>19</v>
       </c>
       <c r="BE24" t="n">
-        <v>1.01</v>
+        <v>6</v>
       </c>
       <c r="BF24" t="n">
-        <v>1.01</v>
+        <v>4.6</v>
       </c>
       <c r="BG24" t="n">
-        <v>1.01</v>
+        <v>5.6</v>
       </c>
       <c r="BH24" t="n">
-        <v>1000</v>
+        <v>5.6</v>
       </c>
       <c r="BI24" t="n">
-        <v>1.04</v>
+        <v>4.3</v>
       </c>
       <c r="BJ24" t="n">
-        <v>1000</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BK24" t="n">
-        <v>1.04</v>
+        <v>4.7</v>
       </c>
       <c r="BL24" t="n">
         <v>1000</v>
       </c>
       <c r="BM24" t="n">
-        <v>1.04</v>
+        <v>8.6</v>
       </c>
       <c r="BN24" t="n">
-        <v>1000</v>
+        <v>5.3</v>
       </c>
       <c r="BO24" t="n">
-        <v>1.04</v>
+        <v>4</v>
       </c>
       <c r="BP24" t="n">
-        <v>1000</v>
+        <v>10.5</v>
       </c>
       <c r="BQ24" t="n">
-        <v>1.04</v>
+        <v>5.1</v>
       </c>
       <c r="BR24" t="n">
-        <v>1000</v>
+        <v>18</v>
       </c>
       <c r="BS24" t="n">
-        <v>1.04</v>
+        <v>6.4</v>
       </c>
       <c r="BT24" t="n">
-        <v>1000</v>
+        <v>9.6</v>
       </c>
       <c r="BU24" t="n">
-        <v>1.04</v>
+        <v>4.9</v>
       </c>
       <c r="BV24" t="n">
-        <v>1000</v>
+        <v>34</v>
       </c>
       <c r="BW24" t="n">
-        <v>1.04</v>
+        <v>7.6</v>
       </c>
       <c r="BX24" t="n">
-        <v>1000</v>
+        <v>34</v>
       </c>
       <c r="BY24" t="n">
-        <v>1.04</v>
+        <v>7.6</v>
       </c>
       <c r="BZ24" t="n">
-        <v>1000</v>
+        <v>10.5</v>
       </c>
       <c r="CA24" t="n">
-        <v>1.04</v>
+        <v>5.1</v>
       </c>
       <c r="CB24" t="inlineStr">
         <is>
-          <t>2026-06-12 03:08:58</t>
+          <t>2026-06-12 05:25:07</t>
         </is>
       </c>
     </row>
@@ -6699,58 +6699,58 @@
         </is>
       </c>
       <c r="F25" t="n">
-        <v>2.84</v>
+        <v>2.8</v>
       </c>
       <c r="G25" t="n">
-        <v>2.94</v>
+        <v>2.88</v>
       </c>
       <c r="H25" t="n">
-        <v>2.76</v>
+        <v>2.88</v>
       </c>
       <c r="I25" t="n">
-        <v>2.86</v>
+        <v>2.92</v>
       </c>
       <c r="J25" t="n">
-        <v>3.3</v>
+        <v>3.25</v>
       </c>
       <c r="K25" t="n">
-        <v>3.5</v>
+        <v>3.4</v>
       </c>
       <c r="L25" t="n">
-        <v>1.46</v>
+        <v>1.45</v>
       </c>
       <c r="M25" t="n">
-        <v>1.08</v>
+        <v>1.09</v>
       </c>
       <c r="N25" t="n">
-        <v>3.5</v>
+        <v>3.4</v>
       </c>
       <c r="O25" t="n">
-        <v>1.37</v>
+        <v>1.4</v>
       </c>
       <c r="P25" t="n">
-        <v>1.83</v>
+        <v>1.8</v>
       </c>
       <c r="Q25" t="n">
-        <v>2.14</v>
+        <v>2.18</v>
       </c>
       <c r="R25" t="n">
-        <v>1.31</v>
+        <v>1.3</v>
       </c>
       <c r="S25" t="n">
-        <v>4</v>
+        <v>4.1</v>
       </c>
       <c r="T25" t="n">
-        <v>1.81</v>
+        <v>1.89</v>
       </c>
       <c r="U25" t="n">
-        <v>2.12</v>
+        <v>2.06</v>
       </c>
       <c r="V25" t="n">
-        <v>1.54</v>
+        <v>1.52</v>
       </c>
       <c r="W25" t="n">
-        <v>1.51</v>
+        <v>1.53</v>
       </c>
       <c r="X25" t="n">
         <v>14</v>
@@ -6765,7 +6765,7 @@
         <v>55</v>
       </c>
       <c r="AB25" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="AC25" t="n">
         <v>8</v>
@@ -6783,7 +6783,7 @@
         <v>14.5</v>
       </c>
       <c r="AH25" t="n">
-        <v>23</v>
+        <v>19</v>
       </c>
       <c r="AI25" t="n">
         <v>60</v>
@@ -6795,22 +6795,22 @@
         <v>44</v>
       </c>
       <c r="AL25" t="n">
-        <v>60</v>
+        <v>130</v>
       </c>
       <c r="AM25" t="n">
         <v>580</v>
       </c>
       <c r="AN25" t="n">
-        <v>500</v>
+        <v>600</v>
       </c>
       <c r="AO25" t="n">
         <v>40</v>
       </c>
       <c r="AP25" t="n">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="AQ25" t="n">
-        <v>9</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AR25" t="n">
         <v>16</v>
@@ -6819,19 +6819,19 @@
         <v>18.5</v>
       </c>
       <c r="AT25" t="n">
-        <v>9.6</v>
+        <v>9</v>
       </c>
       <c r="AU25" t="n">
         <v>6.6</v>
       </c>
       <c r="AV25" t="n">
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="AW25" t="n">
         <v>28</v>
       </c>
       <c r="AX25" t="n">
-        <v>16.5</v>
+        <v>16</v>
       </c>
       <c r="AY25" t="n">
         <v>11</v>
@@ -6846,31 +6846,31 @@
         <v>18</v>
       </c>
       <c r="BC25" t="n">
-        <v>14.5</v>
+        <v>29</v>
       </c>
       <c r="BD25" t="n">
         <v>25</v>
       </c>
       <c r="BE25" t="n">
-        <v>29</v>
+        <v>6.2</v>
       </c>
       <c r="BF25" t="n">
-        <v>10</v>
+        <v>6.6</v>
       </c>
       <c r="BG25" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="BH25" t="n">
-        <v>3.2</v>
+        <v>3.3</v>
       </c>
       <c r="BI25" t="n">
-        <v>2.92</v>
+        <v>2.76</v>
       </c>
       <c r="BJ25" t="n">
-        <v>9.800000000000001</v>
+        <v>9.6</v>
       </c>
       <c r="BK25" t="n">
-        <v>6.2</v>
+        <v>7</v>
       </c>
       <c r="BL25" t="n">
         <v>1000</v>
@@ -6879,10 +6879,10 @@
         <v>15</v>
       </c>
       <c r="BN25" t="n">
-        <v>5.9</v>
+        <v>5.7</v>
       </c>
       <c r="BO25" t="n">
-        <v>4.4</v>
+        <v>5.1</v>
       </c>
       <c r="BP25" t="n">
         <v>1000</v>
@@ -6894,10 +6894,10 @@
         <v>1000</v>
       </c>
       <c r="BS25" t="n">
-        <v>11.5</v>
+        <v>12</v>
       </c>
       <c r="BT25" t="n">
-        <v>5.7</v>
+        <v>5.6</v>
       </c>
       <c r="BU25" t="n">
         <v>4.3</v>
@@ -6922,7 +6922,7 @@
       </c>
       <c r="CB25" t="inlineStr">
         <is>
-          <t>2026-06-12 03:08:58</t>
+          <t>2026-06-12 05:25:07</t>
         </is>
       </c>
     </row>
@@ -6965,19 +6965,19 @@
         <v>4.6</v>
       </c>
       <c r="J26" t="n">
-        <v>4.6</v>
+        <v>4.7</v>
       </c>
       <c r="K26" t="n">
         <v>5.3</v>
       </c>
       <c r="L26" t="n">
-        <v>1.21</v>
+        <v>1.2</v>
       </c>
       <c r="M26" t="n">
         <v>1.02</v>
       </c>
       <c r="N26" t="n">
-        <v>8.199999999999999</v>
+        <v>8.4</v>
       </c>
       <c r="O26" t="n">
         <v>1.11</v>
@@ -7001,10 +7001,10 @@
         <v>2.98</v>
       </c>
       <c r="V26" t="n">
-        <v>1.28</v>
+        <v>1.29</v>
       </c>
       <c r="W26" t="n">
-        <v>2.22</v>
+        <v>2.2</v>
       </c>
       <c r="X26" t="n">
         <v>95</v>
@@ -7031,7 +7031,7 @@
         <v>120</v>
       </c>
       <c r="AF26" t="n">
-        <v>18.5</v>
+        <v>22</v>
       </c>
       <c r="AG26" t="n">
         <v>14</v>
@@ -7040,7 +7040,7 @@
         <v>19</v>
       </c>
       <c r="AI26" t="n">
-        <v>95</v>
+        <v>38</v>
       </c>
       <c r="AJ26" t="n">
         <v>23</v>
@@ -7055,64 +7055,64 @@
         <v>60</v>
       </c>
       <c r="AN26" t="n">
-        <v>6</v>
+        <v>5.5</v>
       </c>
       <c r="AO26" t="n">
         <v>25</v>
       </c>
       <c r="AP26" t="n">
-        <v>16</v>
+        <v>6.6</v>
       </c>
       <c r="AQ26" t="n">
-        <v>21</v>
+        <v>14.5</v>
       </c>
       <c r="AR26" t="n">
-        <v>5.3</v>
+        <v>6.6</v>
       </c>
       <c r="AS26" t="n">
-        <v>5.3</v>
+        <v>7.2</v>
       </c>
       <c r="AT26" t="n">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="AU26" t="n">
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="AV26" t="n">
-        <v>13.5</v>
+        <v>16.5</v>
       </c>
       <c r="AW26" t="n">
-        <v>18</v>
+        <v>18.5</v>
       </c>
       <c r="AX26" t="n">
-        <v>12.5</v>
+        <v>15.5</v>
       </c>
       <c r="AY26" t="n">
-        <v>8.6</v>
+        <v>10</v>
       </c>
       <c r="AZ26" t="n">
         <v>11</v>
       </c>
       <c r="BA26" t="n">
-        <v>18</v>
+        <v>18.5</v>
       </c>
       <c r="BB26" t="n">
-        <v>15.5</v>
+        <v>19</v>
       </c>
       <c r="BC26" t="n">
         <v>12</v>
       </c>
       <c r="BD26" t="n">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="BE26" t="n">
-        <v>5.4</v>
+        <v>34</v>
       </c>
       <c r="BF26" t="n">
-        <v>4.7</v>
+        <v>4.6</v>
       </c>
       <c r="BG26" t="n">
-        <v>16</v>
+        <v>17.5</v>
       </c>
       <c r="BH26" t="n">
         <v>6</v>
@@ -7124,13 +7124,13 @@
         <v>8.6</v>
       </c>
       <c r="BK26" t="n">
-        <v>4.9</v>
+        <v>6.4</v>
       </c>
       <c r="BL26" t="n">
         <v>1000</v>
       </c>
       <c r="BM26" t="n">
-        <v>9.6</v>
+        <v>10</v>
       </c>
       <c r="BN26" t="n">
         <v>5.6</v>
@@ -7139,16 +7139,16 @@
         <v>4.8</v>
       </c>
       <c r="BP26" t="n">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="BQ26" t="n">
-        <v>5.8</v>
+        <v>8</v>
       </c>
       <c r="BR26" t="n">
         <v>17</v>
       </c>
       <c r="BS26" t="n">
-        <v>6.8</v>
+        <v>7</v>
       </c>
       <c r="BT26" t="n">
         <v>9</v>
@@ -7160,23 +7160,23 @@
         <v>1000</v>
       </c>
       <c r="BW26" t="n">
-        <v>8</v>
+        <v>8.4</v>
       </c>
       <c r="BX26" t="n">
         <v>1000</v>
       </c>
       <c r="BY26" t="n">
-        <v>8</v>
+        <v>8.4</v>
       </c>
       <c r="BZ26" t="n">
         <v>9.6</v>
       </c>
       <c r="CA26" t="n">
-        <v>7.2</v>
+        <v>5.3</v>
       </c>
       <c r="CB26" t="inlineStr">
         <is>
-          <t>2026-06-12 03:08:58</t>
+          <t>2026-06-12 05:25:07</t>
         </is>
       </c>
     </row>
@@ -7207,7 +7207,7 @@
         </is>
       </c>
       <c r="F27" t="n">
-        <v>2.54</v>
+        <v>2.64</v>
       </c>
       <c r="G27" t="n">
         <v>44</v>
@@ -7216,7 +7216,7 @@
         <v>1.92</v>
       </c>
       <c r="I27" t="n">
-        <v>8</v>
+        <v>44</v>
       </c>
       <c r="J27" t="n">
         <v>2.48</v>
@@ -7231,13 +7231,13 @@
         <v>1.09</v>
       </c>
       <c r="N27" t="n">
-        <v>1.24</v>
+        <v>1.1</v>
       </c>
       <c r="O27" t="n">
-        <v>1.09</v>
+        <v>1.08</v>
       </c>
       <c r="P27" t="n">
-        <v>1.24</v>
+        <v>1.26</v>
       </c>
       <c r="Q27" t="n">
         <v>1.09</v>
@@ -7255,7 +7255,7 @@
         <v>1.11</v>
       </c>
       <c r="V27" t="n">
-        <v>1.41</v>
+        <v>1.46</v>
       </c>
       <c r="W27" t="n">
         <v>1.2</v>
@@ -7430,7 +7430,7 @@
       </c>
       <c r="CB27" t="inlineStr">
         <is>
-          <t>2026-06-12 03:08:58</t>
+          <t>2026-06-12 05:25:07</t>
         </is>
       </c>
     </row>
@@ -7461,10 +7461,10 @@
         </is>
       </c>
       <c r="F28" t="n">
-        <v>2.26</v>
+        <v>2.24</v>
       </c>
       <c r="G28" t="n">
-        <v>2.32</v>
+        <v>2.3</v>
       </c>
       <c r="H28" t="n">
         <v>3.7</v>
@@ -7473,7 +7473,7 @@
         <v>3.85</v>
       </c>
       <c r="J28" t="n">
-        <v>3.3</v>
+        <v>3.35</v>
       </c>
       <c r="K28" t="n">
         <v>3.4</v>
@@ -7527,10 +7527,10 @@
         <v>900</v>
       </c>
       <c r="AB28" t="n">
-        <v>8.4</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AC28" t="n">
-        <v>8.199999999999999</v>
+        <v>8</v>
       </c>
       <c r="AD28" t="n">
         <v>500</v>
@@ -7542,7 +7542,7 @@
         <v>14</v>
       </c>
       <c r="AG28" t="n">
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="AH28" t="n">
         <v>60</v>
@@ -7575,10 +7575,10 @@
         <v>10</v>
       </c>
       <c r="AR28" t="n">
-        <v>11.5</v>
+        <v>22</v>
       </c>
       <c r="AS28" t="n">
-        <v>9.199999999999999</v>
+        <v>9.4</v>
       </c>
       <c r="AT28" t="n">
         <v>6.8</v>
@@ -7587,104 +7587,104 @@
         <v>6.6</v>
       </c>
       <c r="AV28" t="n">
-        <v>11</v>
+        <v>13.5</v>
       </c>
       <c r="AW28" t="n">
-        <v>9</v>
+        <v>20</v>
       </c>
       <c r="AX28" t="n">
         <v>11</v>
       </c>
       <c r="AY28" t="n">
-        <v>9.4</v>
+        <v>6.4</v>
       </c>
       <c r="AZ28" t="n">
-        <v>7</v>
+        <v>10.5</v>
       </c>
       <c r="BA28" t="n">
         <v>9.199999999999999</v>
       </c>
       <c r="BB28" t="n">
-        <v>8</v>
+        <v>26</v>
       </c>
       <c r="BC28" t="n">
-        <v>13</v>
+        <v>23</v>
       </c>
       <c r="BD28" t="n">
-        <v>8.800000000000001</v>
+        <v>8.6</v>
       </c>
       <c r="BE28" t="n">
-        <v>9.6</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BF28" t="n">
-        <v>7.4</v>
+        <v>21</v>
       </c>
       <c r="BG28" t="n">
         <v>9.800000000000001</v>
       </c>
       <c r="BH28" t="n">
-        <v>1000</v>
+        <v>3.1</v>
       </c>
       <c r="BI28" t="n">
-        <v>1.04</v>
+        <v>2.5</v>
       </c>
       <c r="BJ28" t="n">
-        <v>1000</v>
+        <v>11</v>
       </c>
       <c r="BK28" t="n">
-        <v>1.04</v>
+        <v>5.4</v>
       </c>
       <c r="BL28" t="n">
         <v>1000</v>
       </c>
       <c r="BM28" t="n">
-        <v>1.04</v>
+        <v>10</v>
       </c>
       <c r="BN28" t="n">
-        <v>1000</v>
+        <v>5.1</v>
       </c>
       <c r="BO28" t="n">
-        <v>1.04</v>
+        <v>3.95</v>
       </c>
       <c r="BP28" t="n">
         <v>1000</v>
       </c>
       <c r="BQ28" t="n">
-        <v>1.04</v>
+        <v>6.6</v>
       </c>
       <c r="BR28" t="n">
         <v>1000</v>
       </c>
       <c r="BS28" t="n">
-        <v>1.04</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BT28" t="n">
-        <v>1000</v>
+        <v>7.2</v>
       </c>
       <c r="BU28" t="n">
-        <v>1.04</v>
+        <v>5.4</v>
       </c>
       <c r="BV28" t="n">
         <v>1000</v>
       </c>
       <c r="BW28" t="n">
-        <v>1.04</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BX28" t="n">
         <v>1000</v>
       </c>
       <c r="BY28" t="n">
-        <v>1.04</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BZ28" t="n">
         <v>1000</v>
       </c>
       <c r="CA28" t="n">
-        <v>1.04</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="CB28" t="inlineStr">
         <is>
-          <t>2026-06-12 03:08:58</t>
+          <t>2026-06-12 05:25:07</t>
         </is>
       </c>
     </row>
@@ -7748,10 +7748,10 @@
         <v>2.12</v>
       </c>
       <c r="Q29" t="n">
-        <v>1.85</v>
+        <v>1.84</v>
       </c>
       <c r="R29" t="n">
-        <v>1.42</v>
+        <v>1.44</v>
       </c>
       <c r="S29" t="n">
         <v>3.2</v>
@@ -7766,7 +7766,7 @@
         <v>1.33</v>
       </c>
       <c r="W29" t="n">
-        <v>1.9</v>
+        <v>1.91</v>
       </c>
       <c r="X29" t="n">
         <v>17</v>
@@ -7820,7 +7820,7 @@
         <v>13.5</v>
       </c>
       <c r="AO29" t="n">
-        <v>48</v>
+        <v>110</v>
       </c>
       <c r="AP29" t="n">
         <v>15</v>
@@ -7853,7 +7853,7 @@
         <v>9.6</v>
       </c>
       <c r="AZ29" t="n">
-        <v>15.5</v>
+        <v>15</v>
       </c>
       <c r="BA29" t="n">
         <v>27</v>
@@ -7883,7 +7883,7 @@
         <v>3</v>
       </c>
       <c r="BJ29" t="n">
-        <v>9.4</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BK29" t="n">
         <v>5.8</v>
@@ -7892,7 +7892,7 @@
         <v>1000</v>
       </c>
       <c r="BM29" t="n">
-        <v>13</v>
+        <v>13.5</v>
       </c>
       <c r="BN29" t="n">
         <v>5</v>
@@ -7904,13 +7904,13 @@
         <v>14</v>
       </c>
       <c r="BQ29" t="n">
-        <v>7.2</v>
+        <v>7.4</v>
       </c>
       <c r="BR29" t="n">
         <v>26</v>
       </c>
       <c r="BS29" t="n">
-        <v>9.6</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BT29" t="n">
         <v>7.4</v>
@@ -7928,17 +7928,17 @@
         <v>38</v>
       </c>
       <c r="BY29" t="n">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="BZ29" t="n">
         <v>21</v>
       </c>
       <c r="CA29" t="n">
-        <v>8.800000000000001</v>
+        <v>9</v>
       </c>
       <c r="CB29" t="inlineStr">
         <is>
-          <t>2026-06-12 03:08:58</t>
+          <t>2026-06-12 05:25:07</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-06-12.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-06-12.xlsx
@@ -857,16 +857,16 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>1.54</v>
+        <v>1.57</v>
       </c>
       <c r="G2" t="n">
-        <v>1.6</v>
+        <v>1.63</v>
       </c>
       <c r="H2" t="n">
         <v>6.4</v>
       </c>
       <c r="I2" t="n">
-        <v>8</v>
+        <v>7.6</v>
       </c>
       <c r="J2" t="n">
         <v>4.1</v>
@@ -875,40 +875,40 @@
         <v>4.7</v>
       </c>
       <c r="L2" t="n">
-        <v>1.39</v>
+        <v>1.4</v>
       </c>
       <c r="M2" t="n">
         <v>1.06</v>
       </c>
       <c r="N2" t="n">
-        <v>4.1</v>
+        <v>3.95</v>
       </c>
       <c r="O2" t="n">
-        <v>1.29</v>
+        <v>1.3</v>
       </c>
       <c r="P2" t="n">
-        <v>2.04</v>
+        <v>2</v>
       </c>
       <c r="Q2" t="n">
-        <v>1.87</v>
+        <v>1.91</v>
       </c>
       <c r="R2" t="n">
-        <v>1.39</v>
+        <v>1.38</v>
       </c>
       <c r="S2" t="n">
-        <v>3.3</v>
+        <v>3.35</v>
       </c>
       <c r="T2" t="n">
-        <v>1.95</v>
+        <v>1.97</v>
       </c>
       <c r="U2" t="n">
-        <v>1.9</v>
+        <v>1.88</v>
       </c>
       <c r="V2" t="n">
-        <v>1.15</v>
+        <v>1.16</v>
       </c>
       <c r="W2" t="n">
-        <v>2.62</v>
+        <v>2.56</v>
       </c>
       <c r="X2" t="n">
         <v>500</v>
@@ -935,7 +935,7 @@
         <v>700</v>
       </c>
       <c r="AF2" t="n">
-        <v>500</v>
+        <v>970</v>
       </c>
       <c r="AG2" t="n">
         <v>970</v>
@@ -962,7 +962,7 @@
         <v>29</v>
       </c>
       <c r="AO2" t="n">
-        <v>1000</v>
+        <v>170</v>
       </c>
       <c r="AP2" t="n">
         <v>6.8</v>
@@ -977,7 +977,7 @@
         <v>4.2</v>
       </c>
       <c r="AT2" t="n">
-        <v>3.6</v>
+        <v>3.85</v>
       </c>
       <c r="AU2" t="n">
         <v>4.7</v>
@@ -992,13 +992,13 @@
         <v>5.3</v>
       </c>
       <c r="AY2" t="n">
-        <v>5.6</v>
+        <v>4.8</v>
       </c>
       <c r="AZ2" t="n">
-        <v>3.3</v>
+        <v>2.94</v>
       </c>
       <c r="BA2" t="n">
-        <v>4.7</v>
+        <v>4.6</v>
       </c>
       <c r="BB2" t="n">
         <v>6.6</v>
@@ -1007,10 +1007,10 @@
         <v>7</v>
       </c>
       <c r="BD2" t="n">
-        <v>3.25</v>
+        <v>3.3</v>
       </c>
       <c r="BE2" t="n">
-        <v>2.98</v>
+        <v>3</v>
       </c>
       <c r="BF2" t="n">
         <v>6.6</v>
@@ -1019,68 +1019,68 @@
         <v>4.2</v>
       </c>
       <c r="BH2" t="n">
-        <v>3.8</v>
+        <v>3.65</v>
       </c>
       <c r="BI2" t="n">
-        <v>3.35</v>
+        <v>3.2</v>
       </c>
       <c r="BJ2" t="n">
         <v>1000</v>
       </c>
       <c r="BK2" t="n">
-        <v>6</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BL2" t="n">
         <v>1000</v>
       </c>
       <c r="BM2" t="n">
-        <v>2.12</v>
+        <v>1.88</v>
       </c>
       <c r="BN2" t="n">
-        <v>4.1</v>
+        <v>4.5</v>
       </c>
       <c r="BO2" t="n">
-        <v>3.6</v>
+        <v>4</v>
       </c>
       <c r="BP2" t="n">
         <v>1000</v>
       </c>
       <c r="BQ2" t="n">
-        <v>5.7</v>
+        <v>6.2</v>
       </c>
       <c r="BR2" t="n">
         <v>1000</v>
       </c>
       <c r="BS2" t="n">
-        <v>2.12</v>
+        <v>3</v>
       </c>
       <c r="BT2" t="n">
-        <v>1000</v>
+        <v>8</v>
       </c>
       <c r="BU2" t="n">
-        <v>5.8</v>
+        <v>5.1</v>
       </c>
       <c r="BV2" t="n">
         <v>1000</v>
       </c>
       <c r="BW2" t="n">
-        <v>2.04</v>
+        <v>3.65</v>
       </c>
       <c r="BX2" t="n">
         <v>1000</v>
       </c>
       <c r="BY2" t="n">
-        <v>2.12</v>
+        <v>3.15</v>
       </c>
       <c r="BZ2" t="n">
         <v>1000</v>
       </c>
       <c r="CA2" t="n">
-        <v>2.38</v>
+        <v>4.8</v>
       </c>
       <c r="CB2" t="inlineStr">
         <is>
-          <t>2026-06-12 05:25:07</t>
+          <t>2026-06-12 07:41:10</t>
         </is>
       </c>
     </row>
@@ -1111,19 +1111,19 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>2.6</v>
+        <v>2.62</v>
       </c>
       <c r="G3" t="n">
         <v>2.74</v>
       </c>
       <c r="H3" t="n">
-        <v>2.74</v>
+        <v>2.76</v>
       </c>
       <c r="I3" t="n">
-        <v>2.94</v>
+        <v>2.9</v>
       </c>
       <c r="J3" t="n">
-        <v>3.6</v>
+        <v>3.55</v>
       </c>
       <c r="K3" t="n">
         <v>3.7</v>
@@ -1135,34 +1135,34 @@
         <v>1.05</v>
       </c>
       <c r="N3" t="n">
-        <v>4.6</v>
+        <v>4.5</v>
       </c>
       <c r="O3" t="n">
-        <v>1.25</v>
+        <v>1.26</v>
       </c>
       <c r="P3" t="n">
-        <v>2.24</v>
+        <v>2.22</v>
       </c>
       <c r="Q3" t="n">
         <v>1.76</v>
       </c>
       <c r="R3" t="n">
-        <v>1.49</v>
+        <v>1.47</v>
       </c>
       <c r="S3" t="n">
         <v>2.96</v>
       </c>
       <c r="T3" t="n">
-        <v>1.6</v>
+        <v>1.61</v>
       </c>
       <c r="U3" t="n">
-        <v>2.48</v>
+        <v>2.42</v>
       </c>
       <c r="V3" t="n">
         <v>1.52</v>
       </c>
       <c r="W3" t="n">
-        <v>1.58</v>
+        <v>1.57</v>
       </c>
       <c r="X3" t="n">
         <v>24</v>
@@ -1240,10 +1240,10 @@
         <v>11</v>
       </c>
       <c r="AW3" t="n">
-        <v>20</v>
+        <v>13.5</v>
       </c>
       <c r="AX3" t="n">
-        <v>17.5</v>
+        <v>17</v>
       </c>
       <c r="AY3" t="n">
         <v>10.5</v>
@@ -1264,16 +1264,16 @@
         <v>18.5</v>
       </c>
       <c r="BE3" t="n">
-        <v>27</v>
+        <v>7.8</v>
       </c>
       <c r="BF3" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="BG3" t="n">
-        <v>18</v>
+        <v>18.5</v>
       </c>
       <c r="BH3" t="n">
-        <v>3.8</v>
+        <v>3.85</v>
       </c>
       <c r="BI3" t="n">
         <v>3.1</v>
@@ -1288,25 +1288,25 @@
         <v>1000</v>
       </c>
       <c r="BM3" t="n">
-        <v>14.5</v>
+        <v>13.5</v>
       </c>
       <c r="BN3" t="n">
         <v>5.8</v>
       </c>
       <c r="BO3" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="BP3" t="n">
         <v>18.5</v>
       </c>
       <c r="BQ3" t="n">
-        <v>8.800000000000001</v>
+        <v>8.4</v>
       </c>
       <c r="BR3" t="n">
-        <v>1000</v>
+        <v>29</v>
       </c>
       <c r="BS3" t="n">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="BT3" t="n">
         <v>6.2</v>
@@ -1318,23 +1318,23 @@
         <v>20</v>
       </c>
       <c r="BW3" t="n">
-        <v>9.199999999999999</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BX3" t="n">
         <v>30</v>
       </c>
       <c r="BY3" t="n">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="BZ3" t="n">
         <v>21</v>
       </c>
       <c r="CA3" t="n">
-        <v>9.4</v>
+        <v>9</v>
       </c>
       <c r="CB3" t="inlineStr">
         <is>
-          <t>2026-06-12 05:25:07</t>
+          <t>2026-06-12 07:41:10</t>
         </is>
       </c>
     </row>
@@ -1365,25 +1365,25 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>3</v>
+        <v>3.15</v>
       </c>
       <c r="G4" t="n">
-        <v>3.3</v>
+        <v>3.35</v>
       </c>
       <c r="H4" t="n">
-        <v>3</v>
+        <v>3.05</v>
       </c>
       <c r="I4" t="n">
         <v>3.1</v>
       </c>
       <c r="J4" t="n">
-        <v>2.7</v>
+        <v>2.66</v>
       </c>
       <c r="K4" t="n">
-        <v>2.94</v>
+        <v>2.76</v>
       </c>
       <c r="L4" t="n">
-        <v>1.68</v>
+        <v>1.67</v>
       </c>
       <c r="M4" t="n">
         <v>1.17</v>
@@ -1392,31 +1392,31 @@
         <v>2.42</v>
       </c>
       <c r="O4" t="n">
-        <v>1.63</v>
+        <v>1.64</v>
       </c>
       <c r="P4" t="n">
         <v>1.47</v>
       </c>
       <c r="Q4" t="n">
-        <v>3</v>
+        <v>3.05</v>
       </c>
       <c r="R4" t="n">
         <v>1.15</v>
       </c>
       <c r="S4" t="n">
-        <v>6.4</v>
+        <v>6.6</v>
       </c>
       <c r="T4" t="n">
         <v>2.18</v>
       </c>
       <c r="U4" t="n">
-        <v>1.68</v>
+        <v>1.67</v>
       </c>
       <c r="V4" t="n">
         <v>1.47</v>
       </c>
       <c r="W4" t="n">
-        <v>1.44</v>
+        <v>1.43</v>
       </c>
       <c r="X4" t="n">
         <v>16.5</v>
@@ -1431,7 +1431,7 @@
         <v>500</v>
       </c>
       <c r="AB4" t="n">
-        <v>970</v>
+        <v>500</v>
       </c>
       <c r="AC4" t="n">
         <v>15</v>
@@ -1443,7 +1443,7 @@
         <v>500</v>
       </c>
       <c r="AF4" t="n">
-        <v>500</v>
+        <v>970</v>
       </c>
       <c r="AG4" t="n">
         <v>970</v>
@@ -1476,10 +1476,10 @@
         <v>4.2</v>
       </c>
       <c r="AQ4" t="n">
-        <v>4.4</v>
+        <v>6.8</v>
       </c>
       <c r="AR4" t="n">
-        <v>8.4</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AS4" t="n">
         <v>7.8</v>
@@ -1503,7 +1503,7 @@
         <v>7</v>
       </c>
       <c r="AZ4" t="n">
-        <v>7</v>
+        <v>7.2</v>
       </c>
       <c r="BA4" t="n">
         <v>3.05</v>
@@ -1518,13 +1518,13 @@
         <v>3.1</v>
       </c>
       <c r="BE4" t="n">
-        <v>9.199999999999999</v>
+        <v>8.6</v>
       </c>
       <c r="BF4" t="n">
         <v>9.199999999999999</v>
       </c>
       <c r="BG4" t="n">
-        <v>2.44</v>
+        <v>2.82</v>
       </c>
       <c r="BH4" t="n">
         <v>2.6</v>
@@ -1588,7 +1588,7 @@
       </c>
       <c r="CB4" t="inlineStr">
         <is>
-          <t>2026-06-12 05:25:07</t>
+          <t>2026-06-12 07:41:10</t>
         </is>
       </c>
     </row>
@@ -1619,28 +1619,28 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>2.06</v>
+        <v>2.04</v>
       </c>
       <c r="G5" t="n">
-        <v>2.16</v>
+        <v>2.12</v>
       </c>
       <c r="H5" t="n">
-        <v>4.2</v>
+        <v>4.4</v>
       </c>
       <c r="I5" t="n">
-        <v>4.8</v>
+        <v>4.9</v>
       </c>
       <c r="J5" t="n">
         <v>3.2</v>
       </c>
       <c r="K5" t="n">
-        <v>3.35</v>
+        <v>3.4</v>
       </c>
       <c r="L5" t="n">
         <v>1.6</v>
       </c>
       <c r="M5" t="n">
-        <v>1.14</v>
+        <v>1.13</v>
       </c>
       <c r="N5" t="n">
         <v>2.6</v>
@@ -1649,28 +1649,28 @@
         <v>1.58</v>
       </c>
       <c r="P5" t="n">
-        <v>1.52</v>
+        <v>1.51</v>
       </c>
       <c r="Q5" t="n">
-        <v>2.74</v>
+        <v>2.78</v>
       </c>
       <c r="R5" t="n">
-        <v>1.17</v>
+        <v>1.16</v>
       </c>
       <c r="S5" t="n">
         <v>6.2</v>
       </c>
       <c r="T5" t="n">
-        <v>2.24</v>
+        <v>2.26</v>
       </c>
       <c r="U5" t="n">
-        <v>1.68</v>
+        <v>1.67</v>
       </c>
       <c r="V5" t="n">
         <v>1.26</v>
       </c>
       <c r="W5" t="n">
-        <v>1.86</v>
+        <v>1.89</v>
       </c>
       <c r="X5" t="n">
         <v>8.6</v>
@@ -1679,10 +1679,10 @@
         <v>11.5</v>
       </c>
       <c r="Z5" t="n">
-        <v>50</v>
+        <v>34</v>
       </c>
       <c r="AA5" t="n">
-        <v>900</v>
+        <v>130</v>
       </c>
       <c r="AB5" t="n">
         <v>6.6</v>
@@ -1694,7 +1694,7 @@
         <v>20</v>
       </c>
       <c r="AE5" t="n">
-        <v>500</v>
+        <v>100</v>
       </c>
       <c r="AF5" t="n">
         <v>11.5</v>
@@ -1703,16 +1703,16 @@
         <v>11.5</v>
       </c>
       <c r="AH5" t="n">
-        <v>34</v>
+        <v>29</v>
       </c>
       <c r="AI5" t="n">
-        <v>130</v>
+        <v>500</v>
       </c>
       <c r="AJ5" t="n">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="AK5" t="n">
-        <v>36</v>
+        <v>32</v>
       </c>
       <c r="AL5" t="n">
         <v>75</v>
@@ -1721,22 +1721,22 @@
         <v>500</v>
       </c>
       <c r="AN5" t="n">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="AO5" t="n">
-        <v>600</v>
+        <v>170</v>
       </c>
       <c r="AP5" t="n">
-        <v>7.6</v>
+        <v>7.2</v>
       </c>
       <c r="AQ5" t="n">
         <v>10.5</v>
       </c>
       <c r="AR5" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="AS5" t="n">
-        <v>14</v>
+        <v>28</v>
       </c>
       <c r="AT5" t="n">
         <v>6</v>
@@ -1748,19 +1748,19 @@
         <v>16.5</v>
       </c>
       <c r="AW5" t="n">
-        <v>32</v>
+        <v>14.5</v>
       </c>
       <c r="AX5" t="n">
-        <v>10</v>
+        <v>9.4</v>
       </c>
       <c r="AY5" t="n">
         <v>10</v>
       </c>
       <c r="AZ5" t="n">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="BA5" t="n">
-        <v>29</v>
+        <v>13</v>
       </c>
       <c r="BB5" t="n">
         <v>22</v>
@@ -1769,22 +1769,22 @@
         <v>15</v>
       </c>
       <c r="BD5" t="n">
-        <v>55</v>
+        <v>29</v>
       </c>
       <c r="BE5" t="n">
-        <v>16.5</v>
+        <v>15</v>
       </c>
       <c r="BF5" t="n">
         <v>24</v>
       </c>
       <c r="BG5" t="n">
-        <v>14</v>
+        <v>13.5</v>
       </c>
       <c r="BH5" t="n">
         <v>2.7</v>
       </c>
       <c r="BI5" t="n">
-        <v>2.3</v>
+        <v>2.28</v>
       </c>
       <c r="BJ5" t="n">
         <v>12</v>
@@ -1796,28 +1796,28 @@
         <v>1000</v>
       </c>
       <c r="BM5" t="n">
-        <v>8.800000000000001</v>
+        <v>13.5</v>
       </c>
       <c r="BN5" t="n">
-        <v>4.7</v>
+        <v>4.6</v>
       </c>
       <c r="BO5" t="n">
-        <v>4.1</v>
+        <v>4</v>
       </c>
       <c r="BP5" t="n">
-        <v>1000</v>
+        <v>18</v>
       </c>
       <c r="BQ5" t="n">
-        <v>8.4</v>
+        <v>8</v>
       </c>
       <c r="BR5" t="n">
         <v>1000</v>
       </c>
       <c r="BS5" t="n">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="BT5" t="n">
-        <v>7.6</v>
+        <v>8</v>
       </c>
       <c r="BU5" t="n">
         <v>5.5</v>
@@ -1826,23 +1826,23 @@
         <v>1000</v>
       </c>
       <c r="BW5" t="n">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="BX5" t="n">
         <v>1000</v>
       </c>
       <c r="BY5" t="n">
-        <v>12.5</v>
+        <v>12</v>
       </c>
       <c r="BZ5" t="n">
-        <v>1000</v>
+        <v>65</v>
       </c>
       <c r="CA5" t="n">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="CB5" t="inlineStr">
         <is>
-          <t>2026-06-12 05:25:07</t>
+          <t>2026-06-12 07:41:10</t>
         </is>
       </c>
     </row>
@@ -1873,22 +1873,22 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>3.55</v>
+        <v>3.6</v>
       </c>
       <c r="G6" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="H6" t="n">
+        <v>2.18</v>
+      </c>
+      <c r="I6" t="n">
+        <v>2.26</v>
+      </c>
+      <c r="J6" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="K6" t="n">
         <v>3.75</v>
-      </c>
-      <c r="H6" t="n">
-        <v>2.16</v>
-      </c>
-      <c r="I6" t="n">
-        <v>2.22</v>
-      </c>
-      <c r="J6" t="n">
-        <v>3.55</v>
-      </c>
-      <c r="K6" t="n">
-        <v>3.8</v>
       </c>
       <c r="L6" t="n">
         <v>1.39</v>
@@ -1897,22 +1897,22 @@
         <v>1.06</v>
       </c>
       <c r="N6" t="n">
-        <v>4.2</v>
+        <v>4.1</v>
       </c>
       <c r="O6" t="n">
         <v>1.28</v>
       </c>
       <c r="P6" t="n">
-        <v>2.06</v>
+        <v>2.04</v>
       </c>
       <c r="Q6" t="n">
-        <v>1.86</v>
+        <v>1.87</v>
       </c>
       <c r="R6" t="n">
         <v>1.41</v>
       </c>
       <c r="S6" t="n">
-        <v>3.15</v>
+        <v>3.2</v>
       </c>
       <c r="T6" t="n">
         <v>1.74</v>
@@ -1921,28 +1921,28 @@
         <v>2.24</v>
       </c>
       <c r="V6" t="n">
-        <v>1.81</v>
+        <v>1.8</v>
       </c>
       <c r="W6" t="n">
         <v>1.36</v>
       </c>
       <c r="X6" t="n">
-        <v>16</v>
+        <v>16.5</v>
       </c>
       <c r="Y6" t="n">
         <v>11.5</v>
       </c>
       <c r="Z6" t="n">
-        <v>15.5</v>
+        <v>15</v>
       </c>
       <c r="AA6" t="n">
-        <v>65</v>
+        <v>46</v>
       </c>
       <c r="AB6" t="n">
-        <v>14.5</v>
+        <v>15</v>
       </c>
       <c r="AC6" t="n">
-        <v>8.4</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AD6" t="n">
         <v>14</v>
@@ -1960,25 +1960,25 @@
         <v>16.5</v>
       </c>
       <c r="AI6" t="n">
-        <v>38</v>
+        <v>95</v>
       </c>
       <c r="AJ6" t="n">
-        <v>150</v>
+        <v>250</v>
       </c>
       <c r="AK6" t="n">
-        <v>40</v>
+        <v>110</v>
       </c>
       <c r="AL6" t="n">
-        <v>250</v>
+        <v>130</v>
       </c>
       <c r="AM6" t="n">
-        <v>390</v>
+        <v>200</v>
       </c>
       <c r="AN6" t="n">
-        <v>600</v>
+        <v>70</v>
       </c>
       <c r="AO6" t="n">
-        <v>15.5</v>
+        <v>15</v>
       </c>
       <c r="AP6" t="n">
         <v>14</v>
@@ -1990,7 +1990,7 @@
         <v>13</v>
       </c>
       <c r="AS6" t="n">
-        <v>11.5</v>
+        <v>16.5</v>
       </c>
       <c r="AT6" t="n">
         <v>12.5</v>
@@ -2005,7 +2005,7 @@
         <v>20</v>
       </c>
       <c r="AX6" t="n">
-        <v>11.5</v>
+        <v>12</v>
       </c>
       <c r="AY6" t="n">
         <v>12</v>
@@ -2014,52 +2014,52 @@
         <v>14</v>
       </c>
       <c r="BA6" t="n">
-        <v>13.5</v>
+        <v>18</v>
       </c>
       <c r="BB6" t="n">
+        <v>11</v>
+      </c>
+      <c r="BC6" t="n">
+        <v>18</v>
+      </c>
+      <c r="BD6" t="n">
         <v>23</v>
-      </c>
-      <c r="BC6" t="n">
-        <v>14</v>
-      </c>
-      <c r="BD6" t="n">
-        <v>9.6</v>
       </c>
       <c r="BE6" t="n">
         <v>22</v>
       </c>
       <c r="BF6" t="n">
-        <v>8.4</v>
+        <v>12.5</v>
       </c>
       <c r="BG6" t="n">
-        <v>13.5</v>
+        <v>13</v>
       </c>
       <c r="BH6" t="n">
         <v>3.65</v>
       </c>
       <c r="BI6" t="n">
-        <v>2.94</v>
+        <v>2.96</v>
       </c>
       <c r="BJ6" t="n">
         <v>9.4</v>
       </c>
       <c r="BK6" t="n">
-        <v>5.8</v>
+        <v>5.9</v>
       </c>
       <c r="BL6" t="n">
         <v>1000</v>
       </c>
       <c r="BM6" t="n">
-        <v>13.5</v>
+        <v>14</v>
       </c>
       <c r="BN6" t="n">
         <v>7.2</v>
       </c>
       <c r="BO6" t="n">
-        <v>5.4</v>
+        <v>5.3</v>
       </c>
       <c r="BP6" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="BQ6" t="n">
         <v>10</v>
@@ -2068,13 +2068,13 @@
         <v>1000</v>
       </c>
       <c r="BS6" t="n">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="BT6" t="n">
         <v>5</v>
       </c>
       <c r="BU6" t="n">
-        <v>3.85</v>
+        <v>4.4</v>
       </c>
       <c r="BV6" t="n">
         <v>15</v>
@@ -2086,17 +2086,17 @@
         <v>27</v>
       </c>
       <c r="BY6" t="n">
-        <v>9.800000000000001</v>
+        <v>10</v>
       </c>
       <c r="BZ6" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="CA6" t="n">
         <v>9.199999999999999</v>
       </c>
       <c r="CB6" t="inlineStr">
         <is>
-          <t>2026-06-12 05:25:07</t>
+          <t>2026-06-12 07:41:10</t>
         </is>
       </c>
     </row>
@@ -2127,25 +2127,25 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>1.63</v>
+        <v>1.61</v>
       </c>
       <c r="G7" t="n">
         <v>1.65</v>
       </c>
       <c r="H7" t="n">
-        <v>5.8</v>
+        <v>5.9</v>
       </c>
       <c r="I7" t="n">
-        <v>6.6</v>
+        <v>7</v>
       </c>
       <c r="J7" t="n">
-        <v>4.2</v>
+        <v>4.1</v>
       </c>
       <c r="K7" t="n">
-        <v>4.6</v>
+        <v>4.7</v>
       </c>
       <c r="L7" t="n">
-        <v>1.37</v>
+        <v>1.36</v>
       </c>
       <c r="M7" t="n">
         <v>1.05</v>
@@ -2154,13 +2154,13 @@
         <v>4.3</v>
       </c>
       <c r="O7" t="n">
-        <v>1.27</v>
+        <v>1.26</v>
       </c>
       <c r="P7" t="n">
         <v>2.12</v>
       </c>
       <c r="Q7" t="n">
-        <v>1.83</v>
+        <v>1.81</v>
       </c>
       <c r="R7" t="n">
         <v>1.43</v>
@@ -2172,10 +2172,10 @@
         <v>1.82</v>
       </c>
       <c r="U7" t="n">
-        <v>2.02</v>
+        <v>2</v>
       </c>
       <c r="V7" t="n">
-        <v>1.19</v>
+        <v>1.18</v>
       </c>
       <c r="W7" t="n">
         <v>2.52</v>
@@ -2184,10 +2184,10 @@
         <v>18</v>
       </c>
       <c r="Y7" t="n">
-        <v>50</v>
+        <v>40</v>
       </c>
       <c r="Z7" t="n">
-        <v>120</v>
+        <v>90</v>
       </c>
       <c r="AA7" t="n">
         <v>900</v>
@@ -2199,7 +2199,7 @@
         <v>10</v>
       </c>
       <c r="AD7" t="n">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="AE7" t="n">
         <v>700</v>
@@ -2211,16 +2211,16 @@
         <v>10.5</v>
       </c>
       <c r="AH7" t="n">
-        <v>44</v>
+        <v>34</v>
       </c>
       <c r="AI7" t="n">
         <v>700</v>
       </c>
       <c r="AJ7" t="n">
-        <v>16.5</v>
+        <v>16</v>
       </c>
       <c r="AK7" t="n">
-        <v>29</v>
+        <v>24</v>
       </c>
       <c r="AL7" t="n">
         <v>36</v>
@@ -2241,13 +2241,13 @@
         <v>18</v>
       </c>
       <c r="AR7" t="n">
-        <v>11</v>
+        <v>23</v>
       </c>
       <c r="AS7" t="n">
         <v>12</v>
       </c>
       <c r="AT7" t="n">
-        <v>7.6</v>
+        <v>7.8</v>
       </c>
       <c r="AU7" t="n">
         <v>8.4</v>
@@ -2256,28 +2256,28 @@
         <v>19.5</v>
       </c>
       <c r="AW7" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AX7" t="n">
         <v>8.800000000000001</v>
       </c>
       <c r="AY7" t="n">
-        <v>8.6</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AZ7" t="n">
         <v>17.5</v>
       </c>
       <c r="BA7" t="n">
-        <v>28</v>
+        <v>32</v>
       </c>
       <c r="BB7" t="n">
-        <v>11.5</v>
+        <v>13.5</v>
       </c>
       <c r="BC7" t="n">
-        <v>14.5</v>
+        <v>9.6</v>
       </c>
       <c r="BD7" t="n">
-        <v>21</v>
+        <v>10</v>
       </c>
       <c r="BE7" t="n">
         <v>11.5</v>
@@ -2286,7 +2286,7 @@
         <v>6.6</v>
       </c>
       <c r="BG7" t="n">
-        <v>11.5</v>
+        <v>13.5</v>
       </c>
       <c r="BH7" t="n">
         <v>3.8</v>
@@ -2316,7 +2316,7 @@
         <v>12.5</v>
       </c>
       <c r="BQ7" t="n">
-        <v>7.6</v>
+        <v>4.5</v>
       </c>
       <c r="BR7" t="n">
         <v>32</v>
@@ -2350,7 +2350,7 @@
       </c>
       <c r="CB7" t="inlineStr">
         <is>
-          <t>2026-06-12 05:25:07</t>
+          <t>2026-06-12 07:41:10</t>
         </is>
       </c>
     </row>
@@ -2381,230 +2381,230 @@
         </is>
       </c>
       <c r="F8" t="n">
-        <v>1.72</v>
+        <v>1.82</v>
       </c>
       <c r="G8" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="H8" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="I8" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="J8" t="n">
+        <v>3.95</v>
+      </c>
+      <c r="K8" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="L8" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="M8" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="N8" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="O8" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="P8" t="n">
+        <v>2.16</v>
+      </c>
+      <c r="Q8" t="n">
         <v>1.78</v>
       </c>
-      <c r="H8" t="n">
-        <v>4.8</v>
-      </c>
-      <c r="I8" t="n">
-        <v>5.4</v>
-      </c>
-      <c r="J8" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="K8" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="L8" t="n">
-        <v>1.38</v>
-      </c>
-      <c r="M8" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="N8" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="O8" t="n">
-        <v>1.28</v>
-      </c>
-      <c r="P8" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="Q8" t="n">
-        <v>1.82</v>
-      </c>
       <c r="R8" t="n">
-        <v>1.42</v>
+        <v>1.45</v>
       </c>
       <c r="S8" t="n">
-        <v>3.15</v>
+        <v>3</v>
       </c>
       <c r="T8" t="n">
-        <v>1.83</v>
+        <v>1.74</v>
       </c>
       <c r="U8" t="n">
-        <v>2.04</v>
+        <v>2.14</v>
       </c>
       <c r="V8" t="n">
-        <v>1.23</v>
+        <v>1.27</v>
       </c>
       <c r="W8" t="n">
-        <v>2.28</v>
+        <v>2.08</v>
       </c>
       <c r="X8" t="n">
+        <v>17.5</v>
+      </c>
+      <c r="Y8" t="n">
+        <v>18</v>
+      </c>
+      <c r="Z8" t="n">
+        <v>36</v>
+      </c>
+      <c r="AA8" t="n">
+        <v>110</v>
+      </c>
+      <c r="AB8" t="n">
+        <v>11</v>
+      </c>
+      <c r="AC8" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="AD8" t="n">
+        <v>18</v>
+      </c>
+      <c r="AE8" t="n">
+        <v>55</v>
+      </c>
+      <c r="AF8" t="n">
+        <v>12</v>
+      </c>
+      <c r="AG8" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AH8" t="n">
         <v>19</v>
       </c>
-      <c r="Y8" t="n">
-        <v>18.5</v>
-      </c>
-      <c r="Z8" t="n">
-        <v>42</v>
-      </c>
-      <c r="AA8" t="n">
-        <v>900</v>
-      </c>
-      <c r="AB8" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="AC8" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="AD8" t="n">
-        <v>19.5</v>
-      </c>
-      <c r="AE8" t="n">
-        <v>240</v>
-      </c>
-      <c r="AF8" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="AG8" t="n">
+      <c r="AI8" t="n">
+        <v>60</v>
+      </c>
+      <c r="AJ8" t="n">
+        <v>21</v>
+      </c>
+      <c r="AK8" t="n">
+        <v>19</v>
+      </c>
+      <c r="AL8" t="n">
+        <v>32</v>
+      </c>
+      <c r="AM8" t="n">
+        <v>95</v>
+      </c>
+      <c r="AN8" t="n">
         <v>11</v>
       </c>
-      <c r="AH8" t="n">
-        <v>21</v>
-      </c>
-      <c r="AI8" t="n">
-        <v>140</v>
-      </c>
-      <c r="AJ8" t="n">
-        <v>17.5</v>
-      </c>
-      <c r="AK8" t="n">
-        <v>17</v>
-      </c>
-      <c r="AL8" t="n">
-        <v>36</v>
-      </c>
-      <c r="AM8" t="n">
-        <v>580</v>
-      </c>
-      <c r="AN8" t="n">
-        <v>9.800000000000001</v>
-      </c>
       <c r="AO8" t="n">
-        <v>150</v>
+        <v>55</v>
       </c>
       <c r="AP8" t="n">
         <v>16</v>
       </c>
       <c r="AQ8" t="n">
-        <v>15.5</v>
+        <v>16</v>
       </c>
       <c r="AR8" t="n">
-        <v>15</v>
+        <v>30</v>
       </c>
       <c r="AS8" t="n">
+        <v>30</v>
+      </c>
+      <c r="AT8" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="AU8" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="AV8" t="n">
+        <v>16</v>
+      </c>
+      <c r="AW8" t="n">
+        <v>44</v>
+      </c>
+      <c r="AX8" t="n">
         <v>10.5</v>
-      </c>
-      <c r="AT8" t="n">
-        <v>8.4</v>
-      </c>
-      <c r="AU8" t="n">
-        <v>8.6</v>
-      </c>
-      <c r="AV8" t="n">
-        <v>16.5</v>
-      </c>
-      <c r="AW8" t="n">
-        <v>9.6</v>
-      </c>
-      <c r="AX8" t="n">
-        <v>8.800000000000001</v>
       </c>
       <c r="AY8" t="n">
         <v>9.199999999999999</v>
       </c>
       <c r="AZ8" t="n">
-        <v>18</v>
+        <v>16.5</v>
       </c>
       <c r="BA8" t="n">
+        <v>46</v>
+      </c>
+      <c r="BB8" t="n">
+        <v>17.5</v>
+      </c>
+      <c r="BC8" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="BD8" t="n">
+        <v>28</v>
+      </c>
+      <c r="BE8" t="n">
+        <v>29</v>
+      </c>
+      <c r="BF8" t="n">
         <v>9.6</v>
       </c>
-      <c r="BB8" t="n">
-        <v>14.5</v>
-      </c>
-      <c r="BC8" t="n">
-        <v>14</v>
-      </c>
-      <c r="BD8" t="n">
-        <v>15.5</v>
-      </c>
-      <c r="BE8" t="n">
-        <v>10</v>
-      </c>
-      <c r="BF8" t="n">
+      <c r="BG8" t="n">
+        <v>42</v>
+      </c>
+      <c r="BH8" t="n">
+        <v>3.85</v>
+      </c>
+      <c r="BI8" t="n">
+        <v>2.98</v>
+      </c>
+      <c r="BJ8" t="n">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="BK8" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="BL8" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BM8" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="BN8" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="BO8" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="BP8" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="BQ8" t="n">
+        <v>6</v>
+      </c>
+      <c r="BR8" t="n">
+        <v>25</v>
+      </c>
+      <c r="BS8" t="n">
+        <v>8</v>
+      </c>
+      <c r="BT8" t="n">
         <v>8.4</v>
       </c>
-      <c r="BG8" t="n">
-        <v>9.800000000000001</v>
-      </c>
-      <c r="BH8" t="n">
-        <v>3.75</v>
-      </c>
-      <c r="BI8" t="n">
-        <v>2.92</v>
-      </c>
-      <c r="BJ8" t="n">
-        <v>10</v>
-      </c>
-      <c r="BK8" t="n">
-        <v>5.7</v>
-      </c>
-      <c r="BL8" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BM8" t="n">
-        <v>12</v>
-      </c>
-      <c r="BN8" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="BO8" t="n">
-        <v>3.95</v>
-      </c>
-      <c r="BP8" t="n">
-        <v>12</v>
-      </c>
-      <c r="BQ8" t="n">
-        <v>6.2</v>
-      </c>
-      <c r="BR8" t="n">
-        <v>26</v>
-      </c>
-      <c r="BS8" t="n">
-        <v>8.800000000000001</v>
-      </c>
-      <c r="BT8" t="n">
-        <v>8.800000000000001</v>
-      </c>
       <c r="BU8" t="n">
-        <v>5.3</v>
+        <v>6</v>
       </c>
       <c r="BV8" t="n">
-        <v>44</v>
+        <v>1000</v>
       </c>
       <c r="BW8" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="BX8" t="n">
         <v>1000</v>
       </c>
       <c r="BY8" t="n">
-        <v>10.5</v>
+        <v>9.4</v>
       </c>
       <c r="BZ8" t="n">
         <v>20</v>
       </c>
       <c r="CA8" t="n">
-        <v>8</v>
+        <v>7.4</v>
       </c>
       <c r="CB8" t="inlineStr">
         <is>
-          <t>2026-06-12 05:25:07</t>
+          <t>2026-06-12 07:41:10</t>
         </is>
       </c>
     </row>
@@ -2641,10 +2641,10 @@
         <v>5.2</v>
       </c>
       <c r="H9" t="n">
-        <v>1.71</v>
+        <v>1.7</v>
       </c>
       <c r="I9" t="n">
-        <v>1.81</v>
+        <v>1.8</v>
       </c>
       <c r="J9" t="n">
         <v>4.2</v>
@@ -2659,37 +2659,37 @@
         <v>1.03</v>
       </c>
       <c r="N9" t="n">
-        <v>5.5</v>
+        <v>5.7</v>
       </c>
       <c r="O9" t="n">
         <v>1.18</v>
       </c>
       <c r="P9" t="n">
-        <v>2.58</v>
+        <v>2.6</v>
       </c>
       <c r="Q9" t="n">
-        <v>1.55</v>
+        <v>1.53</v>
       </c>
       <c r="R9" t="n">
-        <v>1.63</v>
+        <v>1.64</v>
       </c>
       <c r="S9" t="n">
         <v>2.36</v>
       </c>
       <c r="T9" t="n">
-        <v>1.6</v>
+        <v>1.55</v>
       </c>
       <c r="U9" t="n">
-        <v>2.38</v>
+        <v>2.44</v>
       </c>
       <c r="V9" t="n">
-        <v>2.22</v>
+        <v>2.24</v>
       </c>
       <c r="W9" t="n">
-        <v>1.24</v>
+        <v>1.23</v>
       </c>
       <c r="X9" t="n">
-        <v>50</v>
+        <v>42</v>
       </c>
       <c r="Y9" t="n">
         <v>13.5</v>
@@ -2698,25 +2698,25 @@
         <v>14</v>
       </c>
       <c r="AA9" t="n">
-        <v>20</v>
+        <v>32</v>
       </c>
       <c r="AB9" t="n">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="AC9" t="n">
         <v>11</v>
       </c>
       <c r="AD9" t="n">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="AE9" t="n">
-        <v>17.5</v>
+        <v>17</v>
       </c>
       <c r="AF9" t="n">
         <v>220</v>
       </c>
       <c r="AG9" t="n">
-        <v>38</v>
+        <v>34</v>
       </c>
       <c r="AH9" t="n">
         <v>17.5</v>
@@ -2728,16 +2728,16 @@
         <v>900</v>
       </c>
       <c r="AK9" t="n">
-        <v>320</v>
+        <v>120</v>
       </c>
       <c r="AL9" t="n">
+        <v>120</v>
+      </c>
+      <c r="AM9" t="n">
         <v>500</v>
       </c>
-      <c r="AM9" t="n">
-        <v>580</v>
-      </c>
       <c r="AN9" t="n">
-        <v>290</v>
+        <v>140</v>
       </c>
       <c r="AO9" t="n">
         <v>7.6</v>
@@ -2761,13 +2761,13 @@
         <v>9</v>
       </c>
       <c r="AV9" t="n">
-        <v>9</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AW9" t="n">
-        <v>13.5</v>
+        <v>14</v>
       </c>
       <c r="AX9" t="n">
-        <v>18.5</v>
+        <v>20</v>
       </c>
       <c r="AY9" t="n">
         <v>16.5</v>
@@ -2776,19 +2776,19 @@
         <v>14</v>
       </c>
       <c r="BA9" t="n">
-        <v>14.5</v>
+        <v>15</v>
       </c>
       <c r="BB9" t="n">
         <v>8.800000000000001</v>
       </c>
       <c r="BC9" t="n">
-        <v>8.199999999999999</v>
+        <v>23</v>
       </c>
       <c r="BD9" t="n">
-        <v>8</v>
+        <v>23</v>
       </c>
       <c r="BE9" t="n">
-        <v>8.4</v>
+        <v>20</v>
       </c>
       <c r="BF9" t="n">
         <v>8.4</v>
@@ -2858,7 +2858,7 @@
       </c>
       <c r="CB9" t="inlineStr">
         <is>
-          <t>2026-06-12 05:25:07</t>
+          <t>2026-06-12 07:41:10</t>
         </is>
       </c>
     </row>
@@ -2889,67 +2889,67 @@
         </is>
       </c>
       <c r="F10" t="n">
-        <v>1.56</v>
+        <v>1.55</v>
       </c>
       <c r="G10" t="n">
-        <v>1.65</v>
+        <v>1.59</v>
       </c>
       <c r="H10" t="n">
-        <v>5.4</v>
+        <v>5.7</v>
       </c>
       <c r="I10" t="n">
-        <v>6.8</v>
+        <v>7</v>
       </c>
       <c r="J10" t="n">
-        <v>4.3</v>
+        <v>4.6</v>
       </c>
       <c r="K10" t="n">
-        <v>5.3</v>
+        <v>5.5</v>
       </c>
       <c r="L10" t="n">
-        <v>1.28</v>
+        <v>1.27</v>
       </c>
       <c r="M10" t="n">
         <v>1.03</v>
       </c>
       <c r="N10" t="n">
-        <v>5.6</v>
+        <v>5.8</v>
       </c>
       <c r="O10" t="n">
-        <v>1.18</v>
+        <v>1.17</v>
       </c>
       <c r="P10" t="n">
-        <v>2.56</v>
+        <v>2.74</v>
       </c>
       <c r="Q10" t="n">
-        <v>1.56</v>
+        <v>1.5</v>
       </c>
       <c r="R10" t="n">
-        <v>1.62</v>
+        <v>1.68</v>
       </c>
       <c r="S10" t="n">
-        <v>2.4</v>
+        <v>2.28</v>
       </c>
       <c r="T10" t="n">
-        <v>1.64</v>
+        <v>1.65</v>
       </c>
       <c r="U10" t="n">
         <v>2.26</v>
       </c>
       <c r="V10" t="n">
-        <v>1.18</v>
+        <v>1.16</v>
       </c>
       <c r="W10" t="n">
-        <v>2.52</v>
+        <v>2.66</v>
       </c>
       <c r="X10" t="n">
+        <v>44</v>
+      </c>
+      <c r="Y10" t="n">
         <v>70</v>
       </c>
-      <c r="Y10" t="n">
-        <v>500</v>
-      </c>
       <c r="Z10" t="n">
-        <v>500</v>
+        <v>220</v>
       </c>
       <c r="AA10" t="n">
         <v>700</v>
@@ -2958,16 +2958,16 @@
         <v>13</v>
       </c>
       <c r="AC10" t="n">
-        <v>11.5</v>
+        <v>12</v>
       </c>
       <c r="AD10" t="n">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="AE10" t="n">
         <v>700</v>
       </c>
       <c r="AF10" t="n">
-        <v>12.5</v>
+        <v>12</v>
       </c>
       <c r="AG10" t="n">
         <v>11</v>
@@ -2976,13 +2976,13 @@
         <v>24</v>
       </c>
       <c r="AI10" t="n">
-        <v>700</v>
+        <v>160</v>
       </c>
       <c r="AJ10" t="n">
-        <v>17</v>
+        <v>15.5</v>
       </c>
       <c r="AK10" t="n">
-        <v>16</v>
+        <v>15.5</v>
       </c>
       <c r="AL10" t="n">
         <v>48</v>
@@ -2991,22 +2991,22 @@
         <v>580</v>
       </c>
       <c r="AN10" t="n">
-        <v>6.6</v>
+        <v>6</v>
       </c>
       <c r="AO10" t="n">
         <v>700</v>
       </c>
       <c r="AP10" t="n">
-        <v>21</v>
+        <v>13.5</v>
       </c>
       <c r="AQ10" t="n">
-        <v>21</v>
+        <v>13</v>
       </c>
       <c r="AR10" t="n">
-        <v>8.199999999999999</v>
+        <v>38</v>
       </c>
       <c r="AS10" t="n">
-        <v>8.6</v>
+        <v>9</v>
       </c>
       <c r="AT10" t="n">
         <v>10</v>
@@ -3015,10 +3015,10 @@
         <v>9.4</v>
       </c>
       <c r="AV10" t="n">
-        <v>11</v>
+        <v>20</v>
       </c>
       <c r="AW10" t="n">
-        <v>7.8</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AX10" t="n">
         <v>10</v>
@@ -3027,37 +3027,37 @@
         <v>8.800000000000001</v>
       </c>
       <c r="AZ10" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="BA10" t="n">
-        <v>7.8</v>
+        <v>26</v>
       </c>
       <c r="BB10" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="BC10" t="n">
+        <v>12</v>
+      </c>
+      <c r="BD10" t="n">
         <v>13.5</v>
       </c>
-      <c r="BC10" t="n">
-        <v>13</v>
-      </c>
-      <c r="BD10" t="n">
-        <v>13</v>
-      </c>
       <c r="BE10" t="n">
-        <v>7.8</v>
+        <v>28</v>
       </c>
       <c r="BF10" t="n">
-        <v>5.5</v>
+        <v>4.8</v>
       </c>
       <c r="BG10" t="n">
-        <v>7.6</v>
+        <v>8.4</v>
       </c>
       <c r="BH10" t="n">
-        <v>4.7</v>
+        <v>4.9</v>
       </c>
       <c r="BI10" t="n">
-        <v>3.5</v>
+        <v>3.6</v>
       </c>
       <c r="BJ10" t="n">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="BK10" t="n">
         <v>4.8</v>
@@ -3066,53 +3066,53 @@
         <v>1000</v>
       </c>
       <c r="BM10" t="n">
-        <v>8.4</v>
+        <v>8</v>
       </c>
       <c r="BN10" t="n">
-        <v>4.8</v>
+        <v>4.7</v>
       </c>
       <c r="BO10" t="n">
-        <v>3.55</v>
+        <v>3.45</v>
       </c>
       <c r="BP10" t="n">
-        <v>10.5</v>
+        <v>9.6</v>
       </c>
       <c r="BQ10" t="n">
-        <v>4.9</v>
+        <v>4.6</v>
       </c>
       <c r="BR10" t="n">
         <v>21</v>
       </c>
       <c r="BS10" t="n">
-        <v>6.4</v>
+        <v>6.2</v>
       </c>
       <c r="BT10" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="BU10" t="n">
-        <v>4.8</v>
+        <v>4.9</v>
       </c>
       <c r="BV10" t="n">
         <v>1000</v>
       </c>
       <c r="BW10" t="n">
-        <v>7.6</v>
+        <v>7.4</v>
       </c>
       <c r="BX10" t="n">
         <v>1000</v>
       </c>
       <c r="BY10" t="n">
-        <v>7.6</v>
+        <v>7.4</v>
       </c>
       <c r="BZ10" t="n">
-        <v>13.5</v>
+        <v>12.5</v>
       </c>
       <c r="CA10" t="n">
-        <v>5.5</v>
+        <v>5.2</v>
       </c>
       <c r="CB10" t="inlineStr">
         <is>
-          <t>2026-06-12 05:25:07</t>
+          <t>2026-06-12 07:41:10</t>
         </is>
       </c>
     </row>
@@ -3143,230 +3143,230 @@
         </is>
       </c>
       <c r="F11" t="n">
-        <v>2.22</v>
+        <v>2.3</v>
       </c>
       <c r="G11" t="n">
-        <v>2.32</v>
+        <v>2.4</v>
       </c>
       <c r="H11" t="n">
-        <v>4.4</v>
+        <v>4.1</v>
       </c>
       <c r="I11" t="n">
-        <v>4.8</v>
+        <v>4.5</v>
       </c>
       <c r="J11" t="n">
-        <v>2.84</v>
+        <v>2.8</v>
       </c>
       <c r="K11" t="n">
         <v>3.05</v>
       </c>
       <c r="L11" t="n">
-        <v>1.61</v>
+        <v>1.62</v>
       </c>
       <c r="M11" t="n">
         <v>1.15</v>
       </c>
       <c r="N11" t="n">
-        <v>2.6</v>
+        <v>2.56</v>
       </c>
       <c r="O11" t="n">
-        <v>1.56</v>
+        <v>1.59</v>
       </c>
       <c r="P11" t="n">
-        <v>1.5</v>
+        <v>1.48</v>
       </c>
       <c r="Q11" t="n">
-        <v>2.8</v>
+        <v>2.86</v>
       </c>
       <c r="R11" t="n">
-        <v>1.18</v>
+        <v>1.17</v>
       </c>
       <c r="S11" t="n">
-        <v>5.8</v>
+        <v>6</v>
       </c>
       <c r="T11" t="n">
-        <v>2.18</v>
+        <v>2.14</v>
       </c>
       <c r="U11" t="n">
-        <v>1.72</v>
+        <v>1.11</v>
       </c>
       <c r="V11" t="n">
-        <v>1.27</v>
+        <v>1.29</v>
       </c>
       <c r="W11" t="n">
-        <v>1.75</v>
+        <v>1.71</v>
       </c>
       <c r="X11" t="n">
-        <v>8.199999999999999</v>
+        <v>970</v>
       </c>
       <c r="Y11" t="n">
-        <v>12</v>
+        <v>970</v>
       </c>
       <c r="Z11" t="n">
-        <v>32</v>
+        <v>100</v>
       </c>
       <c r="AA11" t="n">
         <v>900</v>
       </c>
       <c r="AB11" t="n">
-        <v>7</v>
+        <v>970</v>
       </c>
       <c r="AC11" t="n">
-        <v>7.2</v>
+        <v>42</v>
       </c>
       <c r="AD11" t="n">
-        <v>20</v>
+        <v>970</v>
       </c>
       <c r="AE11" t="n">
         <v>500</v>
       </c>
       <c r="AF11" t="n">
-        <v>12.5</v>
+        <v>970</v>
       </c>
       <c r="AG11" t="n">
-        <v>12</v>
+        <v>970</v>
       </c>
       <c r="AH11" t="n">
-        <v>25</v>
+        <v>950</v>
       </c>
       <c r="AI11" t="n">
         <v>540</v>
       </c>
       <c r="AJ11" t="n">
-        <v>32</v>
+        <v>900</v>
       </c>
       <c r="AK11" t="n">
-        <v>34</v>
+        <v>110</v>
       </c>
       <c r="AL11" t="n">
-        <v>65</v>
+        <v>460</v>
       </c>
       <c r="AM11" t="n">
         <v>500</v>
       </c>
       <c r="AN11" t="n">
-        <v>40</v>
+        <v>600</v>
       </c>
       <c r="AO11" t="n">
-        <v>600</v>
+        <v>1000</v>
       </c>
       <c r="AP11" t="n">
-        <v>6.8</v>
+        <v>4.4</v>
       </c>
       <c r="AQ11" t="n">
-        <v>9.800000000000001</v>
+        <v>10.5</v>
       </c>
       <c r="AR11" t="n">
-        <v>14</v>
+        <v>2.24</v>
       </c>
       <c r="AS11" t="n">
-        <v>10.5</v>
+        <v>1.62</v>
       </c>
       <c r="AT11" t="n">
-        <v>6</v>
+        <v>3.85</v>
       </c>
       <c r="AU11" t="n">
-        <v>6.2</v>
+        <v>4.4</v>
       </c>
       <c r="AV11" t="n">
-        <v>16.5</v>
+        <v>9</v>
       </c>
       <c r="AW11" t="n">
-        <v>10.5</v>
+        <v>1.62</v>
       </c>
       <c r="AX11" t="n">
-        <v>10.5</v>
+        <v>5.7</v>
       </c>
       <c r="AY11" t="n">
-        <v>10</v>
+        <v>6.4</v>
       </c>
       <c r="AZ11" t="n">
-        <v>21</v>
+        <v>2.18</v>
       </c>
       <c r="BA11" t="n">
-        <v>10.5</v>
+        <v>1.62</v>
       </c>
       <c r="BB11" t="n">
-        <v>14.5</v>
+        <v>2.24</v>
       </c>
       <c r="BC11" t="n">
-        <v>14.5</v>
+        <v>2.16</v>
       </c>
       <c r="BD11" t="n">
-        <v>9.800000000000001</v>
+        <v>1.61</v>
       </c>
       <c r="BE11" t="n">
-        <v>11</v>
+        <v>1.63</v>
       </c>
       <c r="BF11" t="n">
-        <v>9.4</v>
+        <v>1.58</v>
       </c>
       <c r="BG11" t="n">
-        <v>10.5</v>
+        <v>1.63</v>
       </c>
       <c r="BH11" t="n">
         <v>2.68</v>
       </c>
       <c r="BI11" t="n">
-        <v>2.26</v>
+        <v>2.22</v>
       </c>
       <c r="BJ11" t="n">
         <v>12</v>
       </c>
       <c r="BK11" t="n">
-        <v>6.4</v>
+        <v>6.2</v>
       </c>
       <c r="BL11" t="n">
         <v>1000</v>
       </c>
       <c r="BM11" t="n">
-        <v>13.5</v>
+        <v>12.5</v>
       </c>
       <c r="BN11" t="n">
-        <v>4.9</v>
+        <v>5</v>
       </c>
       <c r="BO11" t="n">
-        <v>4.2</v>
+        <v>4.3</v>
       </c>
       <c r="BP11" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="BQ11" t="n">
         <v>8.199999999999999</v>
       </c>
       <c r="BR11" t="n">
-        <v>46</v>
+        <v>1000</v>
       </c>
       <c r="BS11" t="n">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="BT11" t="n">
         <v>7.2</v>
       </c>
       <c r="BU11" t="n">
-        <v>5.6</v>
+        <v>5.2</v>
       </c>
       <c r="BV11" t="n">
-        <v>1000</v>
+        <v>42</v>
       </c>
       <c r="BW11" t="n">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="BX11" t="n">
         <v>1000</v>
       </c>
       <c r="BY11" t="n">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="BZ11" t="n">
         <v>55</v>
       </c>
       <c r="CA11" t="n">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="CB11" t="inlineStr">
         <is>
-          <t>2026-06-12 05:25:07</t>
+          <t>2026-06-12 07:41:10</t>
         </is>
       </c>
     </row>
@@ -3397,13 +3397,13 @@
         </is>
       </c>
       <c r="F12" t="n">
-        <v>2.22</v>
+        <v>2.2</v>
       </c>
       <c r="G12" t="n">
-        <v>2.36</v>
+        <v>2.4</v>
       </c>
       <c r="H12" t="n">
-        <v>3.2</v>
+        <v>3.15</v>
       </c>
       <c r="I12" t="n">
         <v>3.55</v>
@@ -3412,7 +3412,7 @@
         <v>3.55</v>
       </c>
       <c r="K12" t="n">
-        <v>4</v>
+        <v>4.1</v>
       </c>
       <c r="L12" t="n">
         <v>1.33</v>
@@ -3421,22 +3421,22 @@
         <v>1.05</v>
       </c>
       <c r="N12" t="n">
-        <v>4.6</v>
+        <v>4.7</v>
       </c>
       <c r="O12" t="n">
         <v>1.24</v>
       </c>
       <c r="P12" t="n">
-        <v>2.22</v>
+        <v>2.32</v>
       </c>
       <c r="Q12" t="n">
-        <v>1.72</v>
+        <v>1.69</v>
       </c>
       <c r="R12" t="n">
-        <v>1.47</v>
+        <v>1.48</v>
       </c>
       <c r="S12" t="n">
-        <v>2.82</v>
+        <v>2.78</v>
       </c>
       <c r="T12" t="n">
         <v>1.6</v>
@@ -3445,22 +3445,22 @@
         <v>2.32</v>
       </c>
       <c r="V12" t="n">
-        <v>1.39</v>
+        <v>1.4</v>
       </c>
       <c r="W12" t="n">
-        <v>1.73</v>
+        <v>1.72</v>
       </c>
       <c r="X12" t="n">
-        <v>90</v>
+        <v>20</v>
       </c>
       <c r="Y12" t="n">
-        <v>970</v>
+        <v>16.5</v>
       </c>
       <c r="Z12" t="n">
-        <v>100</v>
+        <v>29</v>
       </c>
       <c r="AA12" t="n">
-        <v>900</v>
+        <v>85</v>
       </c>
       <c r="AB12" t="n">
         <v>13</v>
@@ -3472,10 +3472,10 @@
         <v>15</v>
       </c>
       <c r="AE12" t="n">
-        <v>85</v>
+        <v>44</v>
       </c>
       <c r="AF12" t="n">
-        <v>970</v>
+        <v>17.5</v>
       </c>
       <c r="AG12" t="n">
         <v>12</v>
@@ -3484,25 +3484,25 @@
         <v>16.5</v>
       </c>
       <c r="AI12" t="n">
-        <v>100</v>
+        <v>50</v>
       </c>
       <c r="AJ12" t="n">
-        <v>65</v>
+        <v>55</v>
       </c>
       <c r="AK12" t="n">
         <v>24</v>
       </c>
       <c r="AL12" t="n">
-        <v>210</v>
+        <v>38</v>
       </c>
       <c r="AM12" t="n">
-        <v>580</v>
+        <v>90</v>
       </c>
       <c r="AN12" t="n">
         <v>15</v>
       </c>
       <c r="AO12" t="n">
-        <v>600</v>
+        <v>28</v>
       </c>
       <c r="AP12" t="n">
         <v>16</v>
@@ -3514,13 +3514,13 @@
         <v>20</v>
       </c>
       <c r="AS12" t="n">
-        <v>3.85</v>
+        <v>8.4</v>
       </c>
       <c r="AT12" t="n">
         <v>10</v>
       </c>
       <c r="AU12" t="n">
-        <v>4</v>
+        <v>7.4</v>
       </c>
       <c r="AV12" t="n">
         <v>12</v>
@@ -3529,31 +3529,31 @@
         <v>13</v>
       </c>
       <c r="AX12" t="n">
-        <v>3.3</v>
+        <v>13.5</v>
       </c>
       <c r="AY12" t="n">
         <v>9.6</v>
       </c>
       <c r="AZ12" t="n">
-        <v>3.2</v>
+        <v>13</v>
       </c>
       <c r="BA12" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="BB12" t="n">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="BC12" t="n">
         <v>18.5</v>
       </c>
       <c r="BD12" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="BE12" t="n">
-        <v>3.85</v>
+        <v>46</v>
       </c>
       <c r="BF12" t="n">
-        <v>2.76</v>
+        <v>12</v>
       </c>
       <c r="BG12" t="n">
         <v>12</v>
@@ -3620,7 +3620,7 @@
       </c>
       <c r="CB12" t="inlineStr">
         <is>
-          <t>2026-06-12 05:25:07</t>
+          <t>2026-06-12 07:41:10</t>
         </is>
       </c>
     </row>
@@ -3651,22 +3651,22 @@
         </is>
       </c>
       <c r="F13" t="n">
-        <v>1.19</v>
+        <v>1.2</v>
       </c>
       <c r="G13" t="n">
-        <v>1.22</v>
+        <v>1.23</v>
       </c>
       <c r="H13" t="n">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="I13" t="n">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="J13" t="n">
         <v>8.199999999999999</v>
       </c>
       <c r="K13" t="n">
-        <v>9.800000000000001</v>
+        <v>10</v>
       </c>
       <c r="L13" t="n">
         <v>1.21</v>
@@ -3675,7 +3675,7 @@
         <v>1.02</v>
       </c>
       <c r="N13" t="n">
-        <v>8</v>
+        <v>7.6</v>
       </c>
       <c r="O13" t="n">
         <v>1.12</v>
@@ -3687,22 +3687,22 @@
         <v>1.38</v>
       </c>
       <c r="R13" t="n">
+        <v>1.96</v>
+      </c>
+      <c r="S13" t="n">
+        <v>1.93</v>
+      </c>
+      <c r="T13" t="n">
         <v>1.98</v>
       </c>
-      <c r="S13" t="n">
-        <v>1.92</v>
-      </c>
-      <c r="T13" t="n">
-        <v>2.12</v>
-      </c>
       <c r="U13" t="n">
-        <v>1.72</v>
+        <v>1.81</v>
       </c>
       <c r="V13" t="n">
         <v>1.05</v>
       </c>
       <c r="W13" t="n">
-        <v>5.6</v>
+        <v>5.3</v>
       </c>
       <c r="X13" t="n">
         <v>950</v>
@@ -3711,7 +3711,7 @@
         <v>950</v>
       </c>
       <c r="Z13" t="n">
-        <v>200</v>
+        <v>180</v>
       </c>
       <c r="AA13" t="n">
         <v>1000</v>
@@ -3726,155 +3726,155 @@
         <v>950</v>
       </c>
       <c r="AE13" t="n">
-        <v>310</v>
+        <v>260</v>
       </c>
       <c r="AF13" t="n">
-        <v>9.6</v>
+        <v>10.5</v>
       </c>
       <c r="AG13" t="n">
-        <v>16.5</v>
+        <v>13.5</v>
       </c>
       <c r="AH13" t="n">
         <v>950</v>
       </c>
       <c r="AI13" t="n">
-        <v>220</v>
+        <v>180</v>
       </c>
       <c r="AJ13" t="n">
-        <v>9.4</v>
+        <v>10.5</v>
       </c>
       <c r="AK13" t="n">
-        <v>17</v>
+        <v>14.5</v>
       </c>
       <c r="AL13" t="n">
-        <v>44</v>
+        <v>50</v>
       </c>
       <c r="AM13" t="n">
-        <v>180</v>
+        <v>170</v>
       </c>
       <c r="AN13" t="n">
         <v>3.15</v>
       </c>
       <c r="AO13" t="n">
-        <v>310</v>
+        <v>240</v>
       </c>
       <c r="AP13" t="n">
-        <v>6.8</v>
+        <v>9</v>
       </c>
       <c r="AQ13" t="n">
-        <v>7</v>
+        <v>8.4</v>
       </c>
       <c r="AR13" t="n">
-        <v>7.4</v>
+        <v>8.6</v>
       </c>
       <c r="AS13" t="n">
-        <v>7.8</v>
+        <v>9</v>
       </c>
       <c r="AT13" t="n">
         <v>11</v>
       </c>
       <c r="AU13" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="AV13" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="AW13" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="AX13" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="AY13" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AZ13" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="BA13" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="BB13" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="BC13" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="BD13" t="n">
+        <v>17.5</v>
+      </c>
+      <c r="BE13" t="n">
+        <v>9</v>
+      </c>
+      <c r="BF13" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="BG13" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="BH13" t="n">
         <v>6</v>
       </c>
-      <c r="AV13" t="n">
-        <v>7</v>
-      </c>
-      <c r="AW13" t="n">
-        <v>7.6</v>
-      </c>
-      <c r="AX13" t="n">
-        <v>8</v>
-      </c>
-      <c r="AY13" t="n">
+      <c r="BI13" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="BJ13" t="n">
         <v>12.5</v>
       </c>
-      <c r="AZ13" t="n">
+      <c r="BK13" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="BL13" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BM13" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="BN13" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="BO13" t="n">
+        <v>3.35</v>
+      </c>
+      <c r="BP13" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="BQ13" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="BR13" t="n">
+        <v>19.5</v>
+      </c>
+      <c r="BS13" t="n">
         <v>6.6</v>
       </c>
-      <c r="BA13" t="n">
-        <v>7.4</v>
-      </c>
-      <c r="BB13" t="n">
-        <v>7.8</v>
-      </c>
-      <c r="BC13" t="n">
-        <v>6.6</v>
-      </c>
-      <c r="BD13" t="n">
-        <v>6.8</v>
-      </c>
-      <c r="BE13" t="n">
-        <v>7.4</v>
-      </c>
-      <c r="BF13" t="n">
-        <v>2.72</v>
-      </c>
-      <c r="BG13" t="n">
-        <v>7.8</v>
-      </c>
-      <c r="BH13" t="n">
-        <v>5.8</v>
-      </c>
-      <c r="BI13" t="n">
-        <v>4.9</v>
-      </c>
-      <c r="BJ13" t="n">
-        <v>13</v>
-      </c>
-      <c r="BK13" t="n">
-        <v>6</v>
-      </c>
-      <c r="BL13" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BM13" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="BN13" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="BO13" t="n">
-        <v>3.55</v>
-      </c>
-      <c r="BP13" t="n">
-        <v>6.6</v>
-      </c>
-      <c r="BQ13" t="n">
-        <v>5.1</v>
-      </c>
-      <c r="BR13" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BS13" t="n">
-        <v>7.2</v>
-      </c>
       <c r="BT13" t="n">
-        <v>18.5</v>
+        <v>18</v>
       </c>
       <c r="BU13" t="n">
-        <v>7</v>
+        <v>6.4</v>
       </c>
       <c r="BV13" t="n">
         <v>1000</v>
       </c>
       <c r="BW13" t="n">
-        <v>10</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BX13" t="n">
         <v>1000</v>
       </c>
       <c r="BY13" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="BZ13" t="n">
         <v>7.2</v>
       </c>
       <c r="CA13" t="n">
-        <v>5.4</v>
+        <v>4.2</v>
       </c>
       <c r="CB13" t="inlineStr">
         <is>
-          <t>2026-06-12 05:25:07</t>
+          <t>2026-06-12 07:41:10</t>
         </is>
       </c>
     </row>
@@ -3905,40 +3905,40 @@
         </is>
       </c>
       <c r="F14" t="n">
-        <v>3.2</v>
+        <v>2.98</v>
       </c>
       <c r="G14" t="n">
-        <v>3.45</v>
+        <v>3.15</v>
       </c>
       <c r="H14" t="n">
-        <v>2.36</v>
+        <v>2.52</v>
       </c>
       <c r="I14" t="n">
-        <v>2.5</v>
+        <v>2.6</v>
       </c>
       <c r="J14" t="n">
-        <v>3.35</v>
+        <v>3.55</v>
       </c>
       <c r="K14" t="n">
         <v>3.6</v>
       </c>
       <c r="L14" t="n">
-        <v>1.45</v>
+        <v>1.44</v>
       </c>
       <c r="M14" t="n">
         <v>1.08</v>
       </c>
       <c r="N14" t="n">
-        <v>3.5</v>
+        <v>3.4</v>
       </c>
       <c r="O14" t="n">
-        <v>1.36</v>
+        <v>1.37</v>
       </c>
       <c r="P14" t="n">
         <v>1.83</v>
       </c>
       <c r="Q14" t="n">
-        <v>2.08</v>
+        <v>2.1</v>
       </c>
       <c r="R14" t="n">
         <v>1.31</v>
@@ -3947,58 +3947,58 @@
         <v>3.9</v>
       </c>
       <c r="T14" t="n">
-        <v>1.81</v>
+        <v>1.8</v>
       </c>
       <c r="U14" t="n">
-        <v>2.06</v>
+        <v>2.08</v>
       </c>
       <c r="V14" t="n">
-        <v>1.67</v>
+        <v>1.62</v>
       </c>
       <c r="W14" t="n">
-        <v>1.4</v>
+        <v>1.47</v>
       </c>
       <c r="X14" t="n">
-        <v>13</v>
+        <v>12.5</v>
       </c>
       <c r="Y14" t="n">
-        <v>9.800000000000001</v>
+        <v>10.5</v>
       </c>
       <c r="Z14" t="n">
-        <v>16</v>
+        <v>17.5</v>
       </c>
       <c r="AA14" t="n">
-        <v>34</v>
+        <v>40</v>
       </c>
       <c r="AB14" t="n">
-        <v>12</v>
+        <v>11.5</v>
       </c>
       <c r="AC14" t="n">
-        <v>8</v>
+        <v>7.6</v>
       </c>
       <c r="AD14" t="n">
-        <v>12</v>
+        <v>12.5</v>
       </c>
       <c r="AE14" t="n">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="AF14" t="n">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="AG14" t="n">
-        <v>14.5</v>
+        <v>13.5</v>
       </c>
       <c r="AH14" t="n">
-        <v>18.5</v>
+        <v>18</v>
       </c>
       <c r="AI14" t="n">
-        <v>44</v>
+        <v>55</v>
       </c>
       <c r="AJ14" t="n">
-        <v>65</v>
+        <v>55</v>
       </c>
       <c r="AK14" t="n">
-        <v>42</v>
+        <v>38</v>
       </c>
       <c r="AL14" t="n">
         <v>55</v>
@@ -4007,19 +4007,19 @@
         <v>110</v>
       </c>
       <c r="AN14" t="n">
-        <v>44</v>
+        <v>38</v>
       </c>
       <c r="AO14" t="n">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="AP14" t="n">
         <v>11</v>
       </c>
       <c r="AQ14" t="n">
-        <v>8.6</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AR14" t="n">
-        <v>13</v>
+        <v>14.5</v>
       </c>
       <c r="AS14" t="n">
         <v>28</v>
@@ -4031,104 +4031,104 @@
         <v>7</v>
       </c>
       <c r="AV14" t="n">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="AW14" t="n">
         <v>24</v>
       </c>
       <c r="AX14" t="n">
-        <v>20</v>
+        <v>18.5</v>
       </c>
       <c r="AY14" t="n">
-        <v>12.5</v>
+        <v>11.5</v>
       </c>
       <c r="AZ14" t="n">
-        <v>17</v>
+        <v>16.5</v>
       </c>
       <c r="BA14" t="n">
         <v>38</v>
       </c>
       <c r="BB14" t="n">
+        <v>46</v>
+      </c>
+      <c r="BC14" t="n">
         <v>32</v>
       </c>
-      <c r="BC14" t="n">
-        <v>21</v>
-      </c>
       <c r="BD14" t="n">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="BE14" t="n">
         <v>40</v>
       </c>
       <c r="BF14" t="n">
-        <v>34</v>
+        <v>30</v>
       </c>
       <c r="BG14" t="n">
-        <v>19.5</v>
+        <v>20</v>
       </c>
       <c r="BH14" t="n">
         <v>3.25</v>
       </c>
       <c r="BI14" t="n">
-        <v>2.7</v>
+        <v>2.66</v>
       </c>
       <c r="BJ14" t="n">
         <v>9.800000000000001</v>
       </c>
       <c r="BK14" t="n">
-        <v>6</v>
+        <v>5.9</v>
       </c>
       <c r="BL14" t="n">
         <v>1000</v>
       </c>
       <c r="BM14" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="BN14" t="n">
-        <v>6.6</v>
+        <v>6.4</v>
       </c>
       <c r="BO14" t="n">
-        <v>4.6</v>
+        <v>5.5</v>
       </c>
       <c r="BP14" t="n">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="BQ14" t="n">
-        <v>10</v>
+        <v>9.4</v>
       </c>
       <c r="BR14" t="n">
         <v>1000</v>
       </c>
       <c r="BS14" t="n">
-        <v>11.5</v>
+        <v>10.5</v>
       </c>
       <c r="BT14" t="n">
-        <v>5.2</v>
+        <v>5.4</v>
       </c>
       <c r="BU14" t="n">
-        <v>4.5</v>
+        <v>4.1</v>
       </c>
       <c r="BV14" t="n">
-        <v>18</v>
+        <v>19.5</v>
       </c>
       <c r="BW14" t="n">
         <v>8.4</v>
       </c>
       <c r="BX14" t="n">
-        <v>34</v>
+        <v>1000</v>
       </c>
       <c r="BY14" t="n">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="BZ14" t="n">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="CA14" t="n">
         <v>10</v>
       </c>
       <c r="CB14" t="inlineStr">
         <is>
-          <t>2026-06-12 05:25:07</t>
+          <t>2026-06-12 07:41:10</t>
         </is>
       </c>
     </row>
@@ -4159,64 +4159,64 @@
         </is>
       </c>
       <c r="F15" t="n">
-        <v>2.42</v>
+        <v>2.44</v>
       </c>
       <c r="G15" t="n">
-        <v>2.68</v>
+        <v>2.64</v>
       </c>
       <c r="H15" t="n">
-        <v>3.45</v>
+        <v>3.5</v>
       </c>
       <c r="I15" t="n">
-        <v>3.9</v>
+        <v>3.85</v>
       </c>
       <c r="J15" t="n">
-        <v>2.88</v>
+        <v>2.86</v>
       </c>
       <c r="K15" t="n">
-        <v>3.15</v>
+        <v>3.1</v>
       </c>
       <c r="L15" t="n">
         <v>1.64</v>
       </c>
       <c r="M15" t="n">
-        <v>1.14</v>
+        <v>1.15</v>
       </c>
       <c r="N15" t="n">
-        <v>2.48</v>
+        <v>2.44</v>
       </c>
       <c r="O15" t="n">
-        <v>1.6</v>
+        <v>1.62</v>
       </c>
       <c r="P15" t="n">
         <v>1.46</v>
       </c>
       <c r="Q15" t="n">
-        <v>2.88</v>
+        <v>2.92</v>
       </c>
       <c r="R15" t="n">
         <v>1.17</v>
       </c>
       <c r="S15" t="n">
-        <v>6</v>
+        <v>6.2</v>
       </c>
       <c r="T15" t="n">
         <v>2.2</v>
       </c>
       <c r="U15" t="n">
-        <v>1.71</v>
+        <v>1.7</v>
       </c>
       <c r="V15" t="n">
         <v>1.35</v>
       </c>
       <c r="W15" t="n">
-        <v>1.6</v>
+        <v>1.61</v>
       </c>
       <c r="X15" t="n">
-        <v>8</v>
+        <v>7.8</v>
       </c>
       <c r="Y15" t="n">
-        <v>10</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="Z15" t="n">
         <v>26</v>
@@ -4225,7 +4225,7 @@
         <v>900</v>
       </c>
       <c r="AB15" t="n">
-        <v>7.6</v>
+        <v>7.4</v>
       </c>
       <c r="AC15" t="n">
         <v>7.4</v>
@@ -4237,7 +4237,7 @@
         <v>440</v>
       </c>
       <c r="AF15" t="n">
-        <v>15.5</v>
+        <v>15</v>
       </c>
       <c r="AG15" t="n">
         <v>13.5</v>
@@ -4276,7 +4276,7 @@
         <v>20</v>
       </c>
       <c r="AS15" t="n">
-        <v>8.199999999999999</v>
+        <v>9</v>
       </c>
       <c r="AT15" t="n">
         <v>6.2</v>
@@ -4288,7 +4288,7 @@
         <v>14.5</v>
       </c>
       <c r="AW15" t="n">
-        <v>8</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AX15" t="n">
         <v>12</v>
@@ -4297,10 +4297,10 @@
         <v>11</v>
       </c>
       <c r="AZ15" t="n">
-        <v>6.8</v>
+        <v>7.4</v>
       </c>
       <c r="BA15" t="n">
-        <v>8.4</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BB15" t="n">
         <v>16</v>
@@ -4309,80 +4309,80 @@
         <v>16</v>
       </c>
       <c r="BD15" t="n">
-        <v>8.199999999999999</v>
+        <v>9</v>
       </c>
       <c r="BE15" t="n">
-        <v>8.800000000000001</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BF15" t="n">
-        <v>7.8</v>
+        <v>8.4</v>
       </c>
       <c r="BG15" t="n">
-        <v>8.4</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BH15" t="n">
         <v>2.64</v>
       </c>
       <c r="BI15" t="n">
-        <v>2.3</v>
+        <v>2.12</v>
       </c>
       <c r="BJ15" t="n">
         <v>12.5</v>
       </c>
       <c r="BK15" t="n">
-        <v>6</v>
+        <v>5.8</v>
       </c>
       <c r="BL15" t="n">
         <v>1000</v>
       </c>
       <c r="BM15" t="n">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="BN15" t="n">
         <v>5.3</v>
       </c>
       <c r="BO15" t="n">
-        <v>4.5</v>
+        <v>3.95</v>
       </c>
       <c r="BP15" t="n">
         <v>24</v>
       </c>
       <c r="BQ15" t="n">
-        <v>8</v>
+        <v>7.6</v>
       </c>
       <c r="BR15" t="n">
-        <v>55</v>
+        <v>1000</v>
       </c>
       <c r="BS15" t="n">
-        <v>9.800000000000001</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BT15" t="n">
-        <v>6.8</v>
+        <v>7</v>
       </c>
       <c r="BU15" t="n">
-        <v>5.5</v>
+        <v>5.7</v>
       </c>
       <c r="BV15" t="n">
         <v>1000</v>
       </c>
       <c r="BW15" t="n">
-        <v>9</v>
+        <v>8.6</v>
       </c>
       <c r="BX15" t="n">
         <v>1000</v>
       </c>
       <c r="BY15" t="n">
-        <v>10</v>
+        <v>9.6</v>
       </c>
       <c r="BZ15" t="n">
         <v>1000</v>
       </c>
       <c r="CA15" t="n">
-        <v>10</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="CB15" t="inlineStr">
         <is>
-          <t>2026-06-12 05:25:07</t>
+          <t>2026-06-12 07:41:10</t>
         </is>
       </c>
     </row>
@@ -4413,22 +4413,22 @@
         </is>
       </c>
       <c r="F16" t="n">
-        <v>2.92</v>
+        <v>2.96</v>
       </c>
       <c r="G16" t="n">
         <v>3.05</v>
       </c>
       <c r="H16" t="n">
-        <v>2.46</v>
+        <v>2.44</v>
       </c>
       <c r="I16" t="n">
-        <v>2.54</v>
+        <v>2.5</v>
       </c>
       <c r="J16" t="n">
-        <v>3.75</v>
+        <v>3.85</v>
       </c>
       <c r="K16" t="n">
-        <v>3.95</v>
+        <v>3.9</v>
       </c>
       <c r="L16" t="n">
         <v>1.33</v>
@@ -4437,37 +4437,37 @@
         <v>1.05</v>
       </c>
       <c r="N16" t="n">
-        <v>5</v>
+        <v>5.1</v>
       </c>
       <c r="O16" t="n">
         <v>1.23</v>
       </c>
       <c r="P16" t="n">
-        <v>2.32</v>
+        <v>2.36</v>
       </c>
       <c r="Q16" t="n">
-        <v>1.7</v>
+        <v>1.69</v>
       </c>
       <c r="R16" t="n">
-        <v>1.52</v>
+        <v>1.53</v>
       </c>
       <c r="S16" t="n">
-        <v>2.8</v>
+        <v>2.76</v>
       </c>
       <c r="T16" t="n">
-        <v>1.59</v>
+        <v>1.61</v>
       </c>
       <c r="U16" t="n">
-        <v>2.56</v>
+        <v>2.52</v>
       </c>
       <c r="V16" t="n">
-        <v>1.64</v>
+        <v>1.67</v>
       </c>
       <c r="W16" t="n">
-        <v>1.48</v>
+        <v>1.49</v>
       </c>
       <c r="X16" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="Y16" t="n">
         <v>14</v>
@@ -4476,19 +4476,19 @@
         <v>19.5</v>
       </c>
       <c r="AA16" t="n">
-        <v>80</v>
+        <v>34</v>
       </c>
       <c r="AB16" t="n">
         <v>16</v>
       </c>
       <c r="AC16" t="n">
-        <v>9</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AD16" t="n">
         <v>12</v>
       </c>
       <c r="AE16" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="AF16" t="n">
         <v>23</v>
@@ -4497,82 +4497,82 @@
         <v>13.5</v>
       </c>
       <c r="AH16" t="n">
-        <v>15.5</v>
+        <v>15</v>
       </c>
       <c r="AI16" t="n">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="AJ16" t="n">
-        <v>280</v>
+        <v>110</v>
       </c>
       <c r="AK16" t="n">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="AL16" t="n">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="AM16" t="n">
-        <v>200</v>
+        <v>65</v>
       </c>
       <c r="AN16" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AO16" t="n">
         <v>15.5</v>
       </c>
       <c r="AP16" t="n">
-        <v>17.5</v>
+        <v>18</v>
       </c>
       <c r="AQ16" t="n">
-        <v>11.5</v>
+        <v>12</v>
       </c>
       <c r="AR16" t="n">
-        <v>15.5</v>
+        <v>16</v>
       </c>
       <c r="AS16" t="n">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="AT16" t="n">
-        <v>13.5</v>
+        <v>14</v>
       </c>
       <c r="AU16" t="n">
         <v>8</v>
       </c>
       <c r="AV16" t="n">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="AW16" t="n">
+        <v>21</v>
+      </c>
+      <c r="AX16" t="n">
         <v>20</v>
       </c>
-      <c r="AX16" t="n">
-        <v>19.5</v>
-      </c>
       <c r="AY16" t="n">
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="AZ16" t="n">
-        <v>13</v>
+        <v>13.5</v>
       </c>
       <c r="BA16" t="n">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="BB16" t="n">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="BC16" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="BD16" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="BE16" t="n">
-        <v>48</v>
+        <v>36</v>
       </c>
       <c r="BF16" t="n">
-        <v>19</v>
+        <v>18.5</v>
       </c>
       <c r="BG16" t="n">
-        <v>13</v>
+        <v>13.5</v>
       </c>
       <c r="BH16" t="n">
         <v>4.2</v>
@@ -4636,7 +4636,7 @@
       </c>
       <c r="CB16" t="inlineStr">
         <is>
-          <t>2026-06-12 05:25:07</t>
+          <t>2026-06-12 07:41:10</t>
         </is>
       </c>
     </row>
@@ -4667,22 +4667,22 @@
         </is>
       </c>
       <c r="F17" t="n">
-        <v>1.41</v>
+        <v>1.42</v>
       </c>
       <c r="G17" t="n">
-        <v>1.42</v>
+        <v>1.44</v>
       </c>
       <c r="H17" t="n">
-        <v>9.800000000000001</v>
+        <v>9.6</v>
       </c>
       <c r="I17" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="J17" t="n">
         <v>4.9</v>
       </c>
       <c r="K17" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="L17" t="n">
         <v>1.38</v>
@@ -4697,61 +4697,61 @@
         <v>1.29</v>
       </c>
       <c r="P17" t="n">
-        <v>2.1</v>
+        <v>2.08</v>
       </c>
       <c r="Q17" t="n">
-        <v>1.88</v>
+        <v>1.89</v>
       </c>
       <c r="R17" t="n">
         <v>1.41</v>
       </c>
       <c r="S17" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="T17" t="n">
+        <v>2.16</v>
+      </c>
+      <c r="U17" t="n">
+        <v>1.78</v>
+      </c>
+      <c r="V17" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="W17" t="n">
         <v>3.25</v>
-      </c>
-      <c r="T17" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="U17" t="n">
-        <v>1.77</v>
-      </c>
-      <c r="V17" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="W17" t="n">
-        <v>3.35</v>
       </c>
       <c r="X17" t="n">
         <v>17.5</v>
       </c>
       <c r="Y17" t="n">
-        <v>85</v>
+        <v>30</v>
       </c>
       <c r="Z17" t="n">
         <v>95</v>
       </c>
       <c r="AA17" t="n">
-        <v>450</v>
+        <v>400</v>
       </c>
       <c r="AB17" t="n">
         <v>7.8</v>
       </c>
       <c r="AC17" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="AD17" t="n">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="AE17" t="n">
-        <v>190</v>
+        <v>170</v>
       </c>
       <c r="AF17" t="n">
         <v>7.8</v>
       </c>
       <c r="AG17" t="n">
-        <v>10</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AH17" t="n">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="AI17" t="n">
         <v>160</v>
@@ -4769,25 +4769,25 @@
         <v>200</v>
       </c>
       <c r="AN17" t="n">
-        <v>7</v>
+        <v>7.2</v>
       </c>
       <c r="AO17" t="n">
-        <v>260</v>
+        <v>250</v>
       </c>
       <c r="AP17" t="n">
         <v>16.5</v>
       </c>
       <c r="AQ17" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="AR17" t="n">
         <v>36</v>
       </c>
       <c r="AS17" t="n">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="AT17" t="n">
-        <v>7</v>
+        <v>7.2</v>
       </c>
       <c r="AU17" t="n">
         <v>10</v>
@@ -4796,7 +4796,7 @@
         <v>32</v>
       </c>
       <c r="AW17" t="n">
-        <v>13.5</v>
+        <v>17</v>
       </c>
       <c r="AX17" t="n">
         <v>7</v>
@@ -4805,10 +4805,10 @@
         <v>9.199999999999999</v>
       </c>
       <c r="AZ17" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="BA17" t="n">
-        <v>13.5</v>
+        <v>36</v>
       </c>
       <c r="BB17" t="n">
         <v>10</v>
@@ -4820,43 +4820,43 @@
         <v>36</v>
       </c>
       <c r="BE17" t="n">
-        <v>14.5</v>
+        <v>42</v>
       </c>
       <c r="BF17" t="n">
         <v>6.6</v>
       </c>
       <c r="BG17" t="n">
-        <v>15</v>
+        <v>38</v>
       </c>
       <c r="BH17" t="n">
-        <v>3.8</v>
+        <v>3.75</v>
       </c>
       <c r="BI17" t="n">
-        <v>2.92</v>
+        <v>2.88</v>
       </c>
       <c r="BJ17" t="n">
         <v>13</v>
       </c>
       <c r="BK17" t="n">
-        <v>5.9</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BL17" t="n">
         <v>1000</v>
       </c>
       <c r="BM17" t="n">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="BN17" t="n">
         <v>3.8</v>
       </c>
       <c r="BO17" t="n">
-        <v>3.25</v>
+        <v>2.92</v>
       </c>
       <c r="BP17" t="n">
         <v>8.800000000000001</v>
       </c>
       <c r="BQ17" t="n">
-        <v>4.8</v>
+        <v>4.9</v>
       </c>
       <c r="BR17" t="n">
         <v>1000</v>
@@ -4868,29 +4868,29 @@
         <v>14</v>
       </c>
       <c r="BU17" t="n">
-        <v>6</v>
+        <v>9.6</v>
       </c>
       <c r="BV17" t="n">
         <v>1000</v>
       </c>
       <c r="BW17" t="n">
-        <v>9.800000000000001</v>
+        <v>10</v>
       </c>
       <c r="BX17" t="n">
         <v>1000</v>
       </c>
       <c r="BY17" t="n">
-        <v>9.800000000000001</v>
+        <v>10</v>
       </c>
       <c r="BZ17" t="n">
-        <v>16.5</v>
+        <v>17</v>
       </c>
       <c r="CA17" t="n">
-        <v>6.4</v>
+        <v>6.6</v>
       </c>
       <c r="CB17" t="inlineStr">
         <is>
-          <t>2026-06-12 05:25:07</t>
+          <t>2026-06-12 07:41:10</t>
         </is>
       </c>
     </row>
@@ -4924,157 +4924,157 @@
         <v>3.25</v>
       </c>
       <c r="G18" t="n">
-        <v>3.3</v>
+        <v>3.35</v>
       </c>
       <c r="H18" t="n">
-        <v>2.48</v>
+        <v>2.56</v>
       </c>
       <c r="I18" t="n">
-        <v>2.52</v>
+        <v>2.58</v>
       </c>
       <c r="J18" t="n">
-        <v>3.3</v>
+        <v>3.25</v>
       </c>
       <c r="K18" t="n">
-        <v>3.4</v>
+        <v>3.35</v>
       </c>
       <c r="L18" t="n">
-        <v>1.5</v>
+        <v>1.49</v>
       </c>
       <c r="M18" t="n">
-        <v>1.1</v>
+        <v>1.09</v>
       </c>
       <c r="N18" t="n">
-        <v>3.15</v>
+        <v>3.2</v>
       </c>
       <c r="O18" t="n">
-        <v>1.44</v>
+        <v>1.43</v>
       </c>
       <c r="P18" t="n">
-        <v>1.7</v>
+        <v>1.72</v>
       </c>
       <c r="Q18" t="n">
-        <v>2.34</v>
+        <v>2.3</v>
       </c>
       <c r="R18" t="n">
         <v>1.26</v>
       </c>
       <c r="S18" t="n">
-        <v>4.7</v>
+        <v>4.5</v>
       </c>
       <c r="T18" t="n">
-        <v>1.97</v>
+        <v>1.95</v>
       </c>
       <c r="U18" t="n">
-        <v>1.96</v>
+        <v>1.95</v>
       </c>
       <c r="V18" t="n">
-        <v>1.65</v>
+        <v>1.63</v>
       </c>
       <c r="W18" t="n">
         <v>1.43</v>
       </c>
       <c r="X18" t="n">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="Y18" t="n">
         <v>9</v>
       </c>
       <c r="Z18" t="n">
-        <v>15.5</v>
+        <v>15</v>
       </c>
       <c r="AA18" t="n">
-        <v>50</v>
+        <v>36</v>
       </c>
       <c r="AB18" t="n">
         <v>11</v>
       </c>
       <c r="AC18" t="n">
-        <v>7.8</v>
+        <v>7.6</v>
       </c>
       <c r="AD18" t="n">
         <v>12</v>
       </c>
       <c r="AE18" t="n">
-        <v>46</v>
+        <v>32</v>
       </c>
       <c r="AF18" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AG18" t="n">
-        <v>14.5</v>
+        <v>14</v>
       </c>
       <c r="AH18" t="n">
-        <v>21</v>
+        <v>19.5</v>
       </c>
       <c r="AI18" t="n">
-        <v>290</v>
+        <v>65</v>
       </c>
       <c r="AJ18" t="n">
-        <v>500</v>
+        <v>60</v>
       </c>
       <c r="AK18" t="n">
-        <v>100</v>
+        <v>44</v>
       </c>
       <c r="AL18" t="n">
-        <v>130</v>
+        <v>80</v>
       </c>
       <c r="AM18" t="n">
-        <v>580</v>
+        <v>160</v>
       </c>
       <c r="AN18" t="n">
-        <v>90</v>
+        <v>60</v>
       </c>
       <c r="AO18" t="n">
-        <v>40</v>
+        <v>34</v>
       </c>
       <c r="AP18" t="n">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="AQ18" t="n">
+        <v>8</v>
+      </c>
+      <c r="AR18" t="n">
+        <v>13</v>
+      </c>
+      <c r="AS18" t="n">
+        <v>30</v>
+      </c>
+      <c r="AT18" t="n">
         <v>9.6</v>
       </c>
-      <c r="AQ18" t="n">
-        <v>7.8</v>
-      </c>
-      <c r="AR18" t="n">
+      <c r="AU18" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="AV18" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AW18" t="n">
+        <v>27</v>
+      </c>
+      <c r="AX18" t="n">
+        <v>19</v>
+      </c>
+      <c r="AY18" t="n">
         <v>12.5</v>
       </c>
-      <c r="AS18" t="n">
-        <v>26</v>
-      </c>
-      <c r="AT18" t="n">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="AU18" t="n">
-        <v>6.6</v>
-      </c>
-      <c r="AV18" t="n">
-        <v>10</v>
-      </c>
-      <c r="AW18" t="n">
-        <v>23</v>
-      </c>
-      <c r="AX18" t="n">
-        <v>18</v>
-      </c>
-      <c r="AY18" t="n">
-        <v>12</v>
-      </c>
       <c r="AZ18" t="n">
-        <v>17</v>
+        <v>17.5</v>
       </c>
       <c r="BA18" t="n">
         <v>34</v>
       </c>
       <c r="BB18" t="n">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="BC18" t="n">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="BD18" t="n">
-        <v>23</v>
+        <v>40</v>
       </c>
       <c r="BE18" t="n">
-        <v>9</v>
+        <v>12.5</v>
       </c>
       <c r="BF18" t="n">
         <v>34</v>
@@ -5083,10 +5083,10 @@
         <v>15</v>
       </c>
       <c r="BH18" t="n">
-        <v>3.1</v>
+        <v>3.05</v>
       </c>
       <c r="BI18" t="n">
-        <v>2.56</v>
+        <v>2.78</v>
       </c>
       <c r="BJ18" t="n">
         <v>10.5</v>
@@ -5098,53 +5098,53 @@
         <v>1000</v>
       </c>
       <c r="BM18" t="n">
-        <v>10.5</v>
+        <v>12.5</v>
       </c>
       <c r="BN18" t="n">
         <v>6.6</v>
       </c>
       <c r="BO18" t="n">
-        <v>5.4</v>
+        <v>5.6</v>
       </c>
       <c r="BP18" t="n">
         <v>1000</v>
       </c>
       <c r="BQ18" t="n">
-        <v>8.199999999999999</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BR18" t="n">
         <v>1000</v>
       </c>
       <c r="BS18" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="BT18" t="n">
-        <v>5.5</v>
+        <v>5.3</v>
       </c>
       <c r="BU18" t="n">
-        <v>4.2</v>
+        <v>4.7</v>
       </c>
       <c r="BV18" t="n">
         <v>21</v>
       </c>
       <c r="BW18" t="n">
-        <v>7.4</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BX18" t="n">
         <v>1000</v>
       </c>
       <c r="BY18" t="n">
-        <v>8.800000000000001</v>
+        <v>10</v>
       </c>
       <c r="BZ18" t="n">
-        <v>44</v>
+        <v>1000</v>
       </c>
       <c r="CA18" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="CB18" t="inlineStr">
         <is>
-          <t>2026-06-12 05:25:07</t>
+          <t>2026-06-12 07:41:10</t>
         </is>
       </c>
     </row>
@@ -5175,25 +5175,25 @@
         </is>
       </c>
       <c r="F19" t="n">
-        <v>2.24</v>
+        <v>2.1</v>
       </c>
       <c r="G19" t="n">
-        <v>2.3</v>
+        <v>2.14</v>
       </c>
       <c r="H19" t="n">
-        <v>3.45</v>
+        <v>3.75</v>
       </c>
       <c r="I19" t="n">
-        <v>3.55</v>
+        <v>3.85</v>
       </c>
       <c r="J19" t="n">
-        <v>3.55</v>
+        <v>3.65</v>
       </c>
       <c r="K19" t="n">
-        <v>3.75</v>
+        <v>3.8</v>
       </c>
       <c r="L19" t="n">
-        <v>1.39</v>
+        <v>1.4</v>
       </c>
       <c r="M19" t="n">
         <v>1.06</v>
@@ -5205,7 +5205,7 @@
         <v>1.3</v>
       </c>
       <c r="P19" t="n">
-        <v>2.02</v>
+        <v>2.04</v>
       </c>
       <c r="Q19" t="n">
         <v>1.92</v>
@@ -5214,191 +5214,191 @@
         <v>1.4</v>
       </c>
       <c r="S19" t="n">
-        <v>3.4</v>
+        <v>3.35</v>
       </c>
       <c r="T19" t="n">
-        <v>1.7</v>
+        <v>1.76</v>
       </c>
       <c r="U19" t="n">
-        <v>2.26</v>
+        <v>2.22</v>
       </c>
       <c r="V19" t="n">
-        <v>1.39</v>
+        <v>1.35</v>
       </c>
       <c r="W19" t="n">
-        <v>1.76</v>
+        <v>1.87</v>
       </c>
       <c r="X19" t="n">
         <v>16</v>
       </c>
       <c r="Y19" t="n">
-        <v>14.5</v>
+        <v>15</v>
       </c>
       <c r="Z19" t="n">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="AA19" t="n">
-        <v>440</v>
+        <v>75</v>
       </c>
       <c r="AB19" t="n">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="AC19" t="n">
-        <v>8.4</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AD19" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="AE19" t="n">
+        <v>46</v>
+      </c>
+      <c r="AF19" t="n">
         <v>14</v>
       </c>
-      <c r="AE19" t="n">
-        <v>50</v>
-      </c>
-      <c r="AF19" t="n">
-        <v>15</v>
-      </c>
       <c r="AG19" t="n">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="AH19" t="n">
-        <v>18</v>
+        <v>18.5</v>
       </c>
       <c r="AI19" t="n">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="AJ19" t="n">
-        <v>32</v>
+        <v>27</v>
       </c>
       <c r="AK19" t="n">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="AL19" t="n">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="AM19" t="n">
-        <v>200</v>
+        <v>95</v>
       </c>
       <c r="AN19" t="n">
-        <v>17.5</v>
+        <v>15.5</v>
       </c>
       <c r="AO19" t="n">
-        <v>50</v>
+        <v>44</v>
       </c>
       <c r="AP19" t="n">
         <v>13.5</v>
       </c>
       <c r="AQ19" t="n">
-        <v>12.5</v>
+        <v>13</v>
       </c>
       <c r="AR19" t="n">
+        <v>24</v>
+      </c>
+      <c r="AS19" t="n">
+        <v>60</v>
+      </c>
+      <c r="AT19" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="AU19" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="AV19" t="n">
+        <v>14</v>
+      </c>
+      <c r="AW19" t="n">
+        <v>38</v>
+      </c>
+      <c r="AX19" t="n">
+        <v>12</v>
+      </c>
+      <c r="AY19" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="AZ19" t="n">
+        <v>16</v>
+      </c>
+      <c r="BA19" t="n">
+        <v>44</v>
+      </c>
+      <c r="BB19" t="n">
+        <v>23</v>
+      </c>
+      <c r="BC19" t="n">
         <v>19.5</v>
       </c>
-      <c r="AS19" t="n">
+      <c r="BD19" t="n">
+        <v>30</v>
+      </c>
+      <c r="BE19" t="n">
+        <v>38</v>
+      </c>
+      <c r="BF19" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="BG19" t="n">
         <v>36</v>
-      </c>
-      <c r="AT19" t="n">
-        <v>9.4</v>
-      </c>
-      <c r="AU19" t="n">
-        <v>7</v>
-      </c>
-      <c r="AV19" t="n">
-        <v>12</v>
-      </c>
-      <c r="AW19" t="n">
-        <v>32</v>
-      </c>
-      <c r="AX19" t="n">
-        <v>13</v>
-      </c>
-      <c r="AY19" t="n">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="AZ19" t="n">
-        <v>14.5</v>
-      </c>
-      <c r="BA19" t="n">
-        <v>36</v>
-      </c>
-      <c r="BB19" t="n">
-        <v>24</v>
-      </c>
-      <c r="BC19" t="n">
-        <v>20</v>
-      </c>
-      <c r="BD19" t="n">
-        <v>25</v>
-      </c>
-      <c r="BE19" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="BF19" t="n">
-        <v>15</v>
-      </c>
-      <c r="BG19" t="n">
-        <v>30</v>
       </c>
       <c r="BH19" t="n">
         <v>3.65</v>
       </c>
       <c r="BI19" t="n">
-        <v>2.92</v>
+        <v>2.8</v>
       </c>
       <c r="BJ19" t="n">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="BK19" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="BL19" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BM19" t="n">
         <v>9.4</v>
       </c>
-      <c r="BK19" t="n">
+      <c r="BN19" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="BO19" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="BP19" t="n">
+        <v>16</v>
+      </c>
+      <c r="BQ19" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="BR19" t="n">
+        <v>29</v>
+      </c>
+      <c r="BS19" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="BT19" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="BU19" t="n">
         <v>5.3</v>
       </c>
-      <c r="BL19" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BM19" t="n">
-        <v>11</v>
-      </c>
-      <c r="BN19" t="n">
-        <v>5.4</v>
-      </c>
-      <c r="BO19" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="BP19" t="n">
-        <v>17</v>
-      </c>
-      <c r="BQ19" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="BR19" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BS19" t="n">
-        <v>8.800000000000001</v>
-      </c>
-      <c r="BT19" t="n">
-        <v>6.8</v>
-      </c>
-      <c r="BU19" t="n">
-        <v>5.8</v>
-      </c>
       <c r="BV19" t="n">
-        <v>1000</v>
+        <v>32</v>
       </c>
       <c r="BW19" t="n">
-        <v>8.4</v>
+        <v>7.8</v>
       </c>
       <c r="BX19" t="n">
-        <v>1000</v>
+        <v>42</v>
       </c>
       <c r="BY19" t="n">
-        <v>9.199999999999999</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BZ19" t="n">
         <v>25</v>
       </c>
       <c r="CA19" t="n">
-        <v>8.199999999999999</v>
+        <v>7.2</v>
       </c>
       <c r="CB19" t="inlineStr">
         <is>
-          <t>2026-06-12 05:25:07</t>
+          <t>2026-06-12 07:41:10</t>
         </is>
       </c>
     </row>
@@ -5432,37 +5432,37 @@
         <v>4.2</v>
       </c>
       <c r="G20" t="n">
-        <v>4.6</v>
+        <v>4.4</v>
       </c>
       <c r="H20" t="n">
-        <v>1.92</v>
+        <v>1.93</v>
       </c>
       <c r="I20" t="n">
         <v>1.97</v>
       </c>
       <c r="J20" t="n">
-        <v>3.75</v>
+        <v>3.85</v>
       </c>
       <c r="K20" t="n">
         <v>4.1</v>
       </c>
       <c r="L20" t="n">
-        <v>1.34</v>
+        <v>1.33</v>
       </c>
       <c r="M20" t="n">
         <v>1.05</v>
       </c>
       <c r="N20" t="n">
-        <v>4.6</v>
+        <v>4.8</v>
       </c>
       <c r="O20" t="n">
-        <v>1.25</v>
+        <v>1.24</v>
       </c>
       <c r="P20" t="n">
-        <v>2.26</v>
+        <v>2.28</v>
       </c>
       <c r="Q20" t="n">
-        <v>1.74</v>
+        <v>1.73</v>
       </c>
       <c r="R20" t="n">
         <v>1.53</v>
@@ -5471,16 +5471,16 @@
         <v>2.84</v>
       </c>
       <c r="T20" t="n">
-        <v>1.68</v>
+        <v>1.66</v>
       </c>
       <c r="U20" t="n">
-        <v>2.32</v>
+        <v>2.38</v>
       </c>
       <c r="V20" t="n">
         <v>2.02</v>
       </c>
       <c r="W20" t="n">
-        <v>1.28</v>
+        <v>1.29</v>
       </c>
       <c r="X20" t="n">
         <v>19.5</v>
@@ -5492,10 +5492,10 @@
         <v>14</v>
       </c>
       <c r="AA20" t="n">
-        <v>32</v>
+        <v>26</v>
       </c>
       <c r="AB20" t="n">
-        <v>19.5</v>
+        <v>19</v>
       </c>
       <c r="AC20" t="n">
         <v>9.4</v>
@@ -5510,7 +5510,7 @@
         <v>34</v>
       </c>
       <c r="AG20" t="n">
-        <v>19.5</v>
+        <v>19</v>
       </c>
       <c r="AH20" t="n">
         <v>16.5</v>
@@ -5522,16 +5522,16 @@
         <v>900</v>
       </c>
       <c r="AK20" t="n">
-        <v>55</v>
+        <v>44</v>
       </c>
       <c r="AL20" t="n">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="AM20" t="n">
         <v>100</v>
       </c>
       <c r="AN20" t="n">
-        <v>42</v>
+        <v>38</v>
       </c>
       <c r="AO20" t="n">
         <v>10</v>
@@ -5558,7 +5558,7 @@
         <v>10</v>
       </c>
       <c r="AW20" t="n">
-        <v>15</v>
+        <v>15.5</v>
       </c>
       <c r="AX20" t="n">
         <v>27</v>
@@ -5573,7 +5573,7 @@
         <v>23</v>
       </c>
       <c r="BB20" t="n">
-        <v>8.6</v>
+        <v>9.6</v>
       </c>
       <c r="BC20" t="n">
         <v>34</v>
@@ -5582,13 +5582,13 @@
         <v>36</v>
       </c>
       <c r="BE20" t="n">
-        <v>8.800000000000001</v>
+        <v>9.4</v>
       </c>
       <c r="BF20" t="n">
         <v>16</v>
       </c>
       <c r="BG20" t="n">
-        <v>8.6</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BH20" t="n">
         <v>4.1</v>
@@ -5606,16 +5606,16 @@
         <v>1000</v>
       </c>
       <c r="BM20" t="n">
-        <v>9</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BN20" t="n">
-        <v>8.199999999999999</v>
+        <v>8</v>
       </c>
       <c r="BO20" t="n">
-        <v>4.9</v>
+        <v>5.8</v>
       </c>
       <c r="BP20" t="n">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="BQ20" t="n">
         <v>7.6</v>
@@ -5627,7 +5627,7 @@
         <v>8</v>
       </c>
       <c r="BT20" t="n">
-        <v>5</v>
+        <v>5.1</v>
       </c>
       <c r="BU20" t="n">
         <v>4.2</v>
@@ -5636,7 +5636,7 @@
         <v>13.5</v>
       </c>
       <c r="BW20" t="n">
-        <v>8</v>
+        <v>9.6</v>
       </c>
       <c r="BX20" t="n">
         <v>25</v>
@@ -5652,7 +5652,7 @@
       </c>
       <c r="CB20" t="inlineStr">
         <is>
-          <t>2026-06-12 05:25:07</t>
+          <t>2026-06-12 07:41:10</t>
         </is>
       </c>
     </row>
@@ -5686,13 +5686,13 @@
         <v>2.4</v>
       </c>
       <c r="G21" t="n">
-        <v>2.52</v>
+        <v>2.5</v>
       </c>
       <c r="H21" t="n">
-        <v>3.3</v>
+        <v>3.35</v>
       </c>
       <c r="I21" t="n">
-        <v>3.5</v>
+        <v>3.55</v>
       </c>
       <c r="J21" t="n">
         <v>3.25</v>
@@ -5764,7 +5764,7 @@
         <v>17.5</v>
       </c>
       <c r="AG21" t="n">
-        <v>14</v>
+        <v>14.5</v>
       </c>
       <c r="AH21" t="n">
         <v>24</v>
@@ -5794,16 +5794,16 @@
         <v>9.6</v>
       </c>
       <c r="AQ21" t="n">
-        <v>10</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AR21" t="n">
-        <v>10.5</v>
+        <v>20</v>
       </c>
       <c r="AS21" t="n">
         <v>4.6</v>
       </c>
       <c r="AT21" t="n">
-        <v>7.6</v>
+        <v>7.8</v>
       </c>
       <c r="AU21" t="n">
         <v>6.6</v>
@@ -5815,7 +5815,7 @@
         <v>4.6</v>
       </c>
       <c r="AX21" t="n">
-        <v>12.5</v>
+        <v>13</v>
       </c>
       <c r="AY21" t="n">
         <v>10</v>
@@ -5827,10 +5827,10 @@
         <v>4.6</v>
       </c>
       <c r="BB21" t="n">
-        <v>4.4</v>
+        <v>14.5</v>
       </c>
       <c r="BC21" t="n">
-        <v>13</v>
+        <v>13.5</v>
       </c>
       <c r="BD21" t="n">
         <v>4.6</v>
@@ -5845,7 +5845,7 @@
         <v>8.6</v>
       </c>
       <c r="BH21" t="n">
-        <v>2.98</v>
+        <v>3.05</v>
       </c>
       <c r="BI21" t="n">
         <v>2.54</v>
@@ -5854,31 +5854,31 @@
         <v>10.5</v>
       </c>
       <c r="BK21" t="n">
-        <v>6.4</v>
+        <v>6.2</v>
       </c>
       <c r="BL21" t="n">
         <v>1000</v>
       </c>
       <c r="BM21" t="n">
-        <v>15.5</v>
+        <v>14</v>
       </c>
       <c r="BN21" t="n">
         <v>5.2</v>
       </c>
       <c r="BO21" t="n">
-        <v>4</v>
+        <v>4.1</v>
       </c>
       <c r="BP21" t="n">
         <v>1000</v>
       </c>
       <c r="BQ21" t="n">
-        <v>9.199999999999999</v>
+        <v>8.6</v>
       </c>
       <c r="BR21" t="n">
         <v>1000</v>
       </c>
       <c r="BS21" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="BT21" t="n">
         <v>6.4</v>
@@ -5890,23 +5890,23 @@
         <v>1000</v>
       </c>
       <c r="BW21" t="n">
+        <v>10</v>
+      </c>
+      <c r="BX21" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BY21" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="BZ21" t="n">
+        <v>1000</v>
+      </c>
+      <c r="CA21" t="n">
         <v>11</v>
       </c>
-      <c r="BX21" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BY21" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="BZ21" t="n">
-        <v>1000</v>
-      </c>
-      <c r="CA21" t="n">
-        <v>12</v>
-      </c>
       <c r="CB21" t="inlineStr">
         <is>
-          <t>2026-06-12 05:25:07</t>
+          <t>2026-06-12 07:41:10</t>
         </is>
       </c>
     </row>
@@ -5940,61 +5940,61 @@
         <v>3.85</v>
       </c>
       <c r="G22" t="n">
-        <v>4.2</v>
+        <v>4.1</v>
       </c>
       <c r="H22" t="n">
         <v>2</v>
       </c>
       <c r="I22" t="n">
-        <v>2.08</v>
+        <v>2.06</v>
       </c>
       <c r="J22" t="n">
-        <v>3.65</v>
+        <v>3.75</v>
       </c>
       <c r="K22" t="n">
-        <v>3.9</v>
+        <v>4</v>
       </c>
       <c r="L22" t="n">
-        <v>1.36</v>
+        <v>1.35</v>
       </c>
       <c r="M22" t="n">
         <v>1.05</v>
       </c>
       <c r="N22" t="n">
-        <v>4.5</v>
+        <v>4.7</v>
       </c>
       <c r="O22" t="n">
-        <v>1.26</v>
+        <v>1.25</v>
       </c>
       <c r="P22" t="n">
-        <v>2.18</v>
+        <v>2.24</v>
       </c>
       <c r="Q22" t="n">
-        <v>1.79</v>
+        <v>1.76</v>
       </c>
       <c r="R22" t="n">
-        <v>1.46</v>
+        <v>1.48</v>
       </c>
       <c r="S22" t="n">
-        <v>3</v>
+        <v>2.92</v>
       </c>
       <c r="T22" t="n">
-        <v>1.71</v>
+        <v>1.64</v>
       </c>
       <c r="U22" t="n">
-        <v>2.26</v>
+        <v>2.28</v>
       </c>
       <c r="V22" t="n">
-        <v>1.92</v>
+        <v>1.94</v>
       </c>
       <c r="W22" t="n">
-        <v>1.31</v>
+        <v>1.32</v>
       </c>
       <c r="X22" t="n">
-        <v>18</v>
+        <v>19.5</v>
       </c>
       <c r="Y22" t="n">
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="Z22" t="n">
         <v>14.5</v>
@@ -6009,7 +6009,7 @@
         <v>9</v>
       </c>
       <c r="AD22" t="n">
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="AE22" t="n">
         <v>21</v>
@@ -6021,13 +6021,13 @@
         <v>17</v>
       </c>
       <c r="AH22" t="n">
-        <v>17.5</v>
+        <v>17</v>
       </c>
       <c r="AI22" t="n">
         <v>34</v>
       </c>
       <c r="AJ22" t="n">
-        <v>500</v>
+        <v>80</v>
       </c>
       <c r="AK22" t="n">
         <v>46</v>
@@ -6048,10 +6048,10 @@
         <v>15.5</v>
       </c>
       <c r="AQ22" t="n">
-        <v>9</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AR22" t="n">
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="AS22" t="n">
         <v>20</v>
@@ -6069,10 +6069,10 @@
         <v>17</v>
       </c>
       <c r="AX22" t="n">
-        <v>14.5</v>
+        <v>25</v>
       </c>
       <c r="AY22" t="n">
-        <v>14</v>
+        <v>13.5</v>
       </c>
       <c r="AZ22" t="n">
         <v>14</v>
@@ -6081,40 +6081,40 @@
         <v>16</v>
       </c>
       <c r="BB22" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="BC22" t="n">
-        <v>9.199999999999999</v>
+        <v>36</v>
       </c>
       <c r="BD22" t="n">
-        <v>9.4</v>
+        <v>8.4</v>
       </c>
       <c r="BE22" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="BF22" t="n">
         <v>29</v>
       </c>
       <c r="BG22" t="n">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="BH22" t="n">
-        <v>3.9</v>
+        <v>4</v>
       </c>
       <c r="BI22" t="n">
-        <v>3.05</v>
+        <v>3.15</v>
       </c>
       <c r="BJ22" t="n">
         <v>9.6</v>
       </c>
       <c r="BK22" t="n">
-        <v>4.9</v>
+        <v>4.8</v>
       </c>
       <c r="BL22" t="n">
         <v>1000</v>
       </c>
       <c r="BM22" t="n">
-        <v>9.199999999999999</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BN22" t="n">
         <v>7.8</v>
@@ -6126,16 +6126,16 @@
         <v>32</v>
       </c>
       <c r="BQ22" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="BR22" t="n">
+        <v>38</v>
+      </c>
+      <c r="BS22" t="n">
         <v>7.6</v>
       </c>
-      <c r="BR22" t="n">
-        <v>40</v>
-      </c>
-      <c r="BS22" t="n">
-        <v>8</v>
-      </c>
       <c r="BT22" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="BU22" t="n">
         <v>3.95</v>
@@ -6144,23 +6144,23 @@
         <v>14.5</v>
       </c>
       <c r="BW22" t="n">
-        <v>5.9</v>
+        <v>10.5</v>
       </c>
       <c r="BX22" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="BY22" t="n">
-        <v>7.2</v>
+        <v>7</v>
       </c>
       <c r="BZ22" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="CA22" t="n">
-        <v>6.8</v>
+        <v>6.6</v>
       </c>
       <c r="CB22" t="inlineStr">
         <is>
-          <t>2026-06-12 05:25:07</t>
+          <t>2026-06-12 07:41:10</t>
         </is>
       </c>
     </row>
@@ -6191,40 +6191,40 @@
         </is>
       </c>
       <c r="F23" t="n">
-        <v>4.6</v>
+        <v>4.7</v>
       </c>
       <c r="G23" t="n">
-        <v>4.9</v>
+        <v>5.1</v>
       </c>
       <c r="H23" t="n">
-        <v>1.91</v>
+        <v>1.86</v>
       </c>
       <c r="I23" t="n">
-        <v>1.95</v>
+        <v>1.93</v>
       </c>
       <c r="J23" t="n">
-        <v>3.6</v>
+        <v>3.65</v>
       </c>
       <c r="K23" t="n">
-        <v>3.7</v>
+        <v>3.9</v>
       </c>
       <c r="L23" t="n">
         <v>1.4</v>
       </c>
       <c r="M23" t="n">
-        <v>1.06</v>
+        <v>1.07</v>
       </c>
       <c r="N23" t="n">
-        <v>4</v>
+        <v>3.95</v>
       </c>
       <c r="O23" t="n">
-        <v>1.3</v>
+        <v>1.31</v>
       </c>
       <c r="P23" t="n">
-        <v>2</v>
+        <v>1.98</v>
       </c>
       <c r="Q23" t="n">
-        <v>1.94</v>
+        <v>1.95</v>
       </c>
       <c r="R23" t="n">
         <v>1.38</v>
@@ -6233,19 +6233,19 @@
         <v>3.4</v>
       </c>
       <c r="T23" t="n">
-        <v>1.8</v>
+        <v>1.81</v>
       </c>
       <c r="U23" t="n">
-        <v>2.08</v>
+        <v>2.06</v>
       </c>
       <c r="V23" t="n">
-        <v>2.04</v>
+        <v>2.06</v>
       </c>
       <c r="W23" t="n">
-        <v>1.26</v>
+        <v>1.25</v>
       </c>
       <c r="X23" t="n">
-        <v>15.5</v>
+        <v>15</v>
       </c>
       <c r="Y23" t="n">
         <v>9.4</v>
@@ -6293,10 +6293,10 @@
         <v>380</v>
       </c>
       <c r="AN23" t="n">
-        <v>70</v>
+        <v>90</v>
       </c>
       <c r="AO23" t="n">
-        <v>13.5</v>
+        <v>13</v>
       </c>
       <c r="AP23" t="n">
         <v>12.5</v>
@@ -6308,7 +6308,7 @@
         <v>10</v>
       </c>
       <c r="AS23" t="n">
-        <v>17.5</v>
+        <v>18</v>
       </c>
       <c r="AT23" t="n">
         <v>13.5</v>
@@ -6335,7 +6335,7 @@
         <v>24</v>
       </c>
       <c r="BB23" t="n">
-        <v>9.199999999999999</v>
+        <v>9.4</v>
       </c>
       <c r="BC23" t="n">
         <v>38</v>
@@ -6344,19 +6344,19 @@
         <v>42</v>
       </c>
       <c r="BE23" t="n">
-        <v>9.199999999999999</v>
+        <v>9.4</v>
       </c>
       <c r="BF23" t="n">
-        <v>8.800000000000001</v>
+        <v>9</v>
       </c>
       <c r="BG23" t="n">
         <v>10.5</v>
       </c>
       <c r="BH23" t="n">
-        <v>3.65</v>
+        <v>3.6</v>
       </c>
       <c r="BI23" t="n">
-        <v>3.1</v>
+        <v>3.05</v>
       </c>
       <c r="BJ23" t="n">
         <v>10.5</v>
@@ -6368,25 +6368,25 @@
         <v>1000</v>
       </c>
       <c r="BM23" t="n">
-        <v>9.6</v>
+        <v>10</v>
       </c>
       <c r="BN23" t="n">
         <v>8.4</v>
       </c>
       <c r="BO23" t="n">
-        <v>4.6</v>
+        <v>4.7</v>
       </c>
       <c r="BP23" t="n">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="BQ23" t="n">
-        <v>8.199999999999999</v>
+        <v>8.6</v>
       </c>
       <c r="BR23" t="n">
         <v>50</v>
       </c>
       <c r="BS23" t="n">
-        <v>8.6</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BT23" t="n">
         <v>4.7</v>
@@ -6404,17 +6404,17 @@
         <v>28</v>
       </c>
       <c r="BY23" t="n">
-        <v>7.6</v>
+        <v>7.8</v>
       </c>
       <c r="BZ23" t="n">
         <v>24</v>
       </c>
       <c r="CA23" t="n">
-        <v>7.2</v>
+        <v>7.4</v>
       </c>
       <c r="CB23" t="inlineStr">
         <is>
-          <t>2026-06-12 05:25:07</t>
+          <t>2026-06-12 07:41:10</t>
         </is>
       </c>
     </row>
@@ -6463,7 +6463,7 @@
         <v>5.4</v>
       </c>
       <c r="L24" t="n">
-        <v>1.2</v>
+        <v>1.22</v>
       </c>
       <c r="M24" t="n">
         <v>1.02</v>
@@ -6502,10 +6502,10 @@
         <v>44</v>
       </c>
       <c r="Y24" t="n">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="Z24" t="n">
-        <v>55</v>
+        <v>60</v>
       </c>
       <c r="AA24" t="n">
         <v>120</v>
@@ -6517,28 +6517,28 @@
         <v>15</v>
       </c>
       <c r="AD24" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="AE24" t="n">
-        <v>55</v>
+        <v>60</v>
       </c>
       <c r="AF24" t="n">
-        <v>16</v>
+        <v>17.5</v>
       </c>
       <c r="AG24" t="n">
         <v>13</v>
       </c>
       <c r="AH24" t="n">
-        <v>17.5</v>
+        <v>19.5</v>
       </c>
       <c r="AI24" t="n">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="AJ24" t="n">
         <v>22</v>
       </c>
       <c r="AK24" t="n">
-        <v>16</v>
+        <v>17.5</v>
       </c>
       <c r="AL24" t="n">
         <v>27</v>
@@ -6547,64 +6547,64 @@
         <v>55</v>
       </c>
       <c r="AN24" t="n">
-        <v>5.5</v>
+        <v>6</v>
       </c>
       <c r="AO24" t="n">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="AP24" t="n">
-        <v>5.8</v>
+        <v>4.6</v>
       </c>
       <c r="AQ24" t="n">
-        <v>5.6</v>
+        <v>4.6</v>
       </c>
       <c r="AR24" t="n">
-        <v>6</v>
+        <v>4.8</v>
       </c>
       <c r="AS24" t="n">
-        <v>6.4</v>
+        <v>5</v>
       </c>
       <c r="AT24" t="n">
-        <v>14</v>
+        <v>12.5</v>
       </c>
       <c r="AU24" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="AV24" t="n">
-        <v>17.5</v>
+        <v>16</v>
       </c>
       <c r="AW24" t="n">
-        <v>6</v>
+        <v>4.8</v>
       </c>
       <c r="AX24" t="n">
-        <v>13</v>
+        <v>11.5</v>
       </c>
       <c r="AY24" t="n">
         <v>9.6</v>
       </c>
       <c r="AZ24" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="BA24" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="BB24" t="n">
         <v>14</v>
       </c>
-      <c r="BA24" t="n">
-        <v>5.9</v>
-      </c>
-      <c r="BB24" t="n">
-        <v>16</v>
-      </c>
       <c r="BC24" t="n">
-        <v>13</v>
+        <v>11.5</v>
       </c>
       <c r="BD24" t="n">
         <v>19</v>
       </c>
       <c r="BE24" t="n">
-        <v>6</v>
+        <v>4.7</v>
       </c>
       <c r="BF24" t="n">
-        <v>4.6</v>
+        <v>4.2</v>
       </c>
       <c r="BG24" t="n">
-        <v>5.6</v>
+        <v>4.5</v>
       </c>
       <c r="BH24" t="n">
         <v>5.6</v>
@@ -6616,16 +6616,16 @@
         <v>9.199999999999999</v>
       </c>
       <c r="BK24" t="n">
-        <v>4.7</v>
+        <v>4.8</v>
       </c>
       <c r="BL24" t="n">
         <v>1000</v>
       </c>
       <c r="BM24" t="n">
-        <v>8.6</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BN24" t="n">
-        <v>5.3</v>
+        <v>5.2</v>
       </c>
       <c r="BO24" t="n">
         <v>4</v>
@@ -6634,7 +6634,7 @@
         <v>10.5</v>
       </c>
       <c r="BQ24" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="BR24" t="n">
         <v>18</v>
@@ -6652,23 +6652,23 @@
         <v>34</v>
       </c>
       <c r="BW24" t="n">
-        <v>7.6</v>
+        <v>7.8</v>
       </c>
       <c r="BX24" t="n">
         <v>34</v>
       </c>
       <c r="BY24" t="n">
-        <v>7.6</v>
+        <v>7.8</v>
       </c>
       <c r="BZ24" t="n">
         <v>10.5</v>
       </c>
       <c r="CA24" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="CB24" t="inlineStr">
         <is>
-          <t>2026-06-12 05:25:07</t>
+          <t>2026-06-12 07:41:10</t>
         </is>
       </c>
     </row>
@@ -6699,22 +6699,22 @@
         </is>
       </c>
       <c r="F25" t="n">
-        <v>2.8</v>
+        <v>2.84</v>
       </c>
       <c r="G25" t="n">
-        <v>2.88</v>
+        <v>2.86</v>
       </c>
       <c r="H25" t="n">
         <v>2.88</v>
       </c>
       <c r="I25" t="n">
-        <v>2.92</v>
+        <v>2.9</v>
       </c>
       <c r="J25" t="n">
         <v>3.25</v>
       </c>
       <c r="K25" t="n">
-        <v>3.4</v>
+        <v>3.35</v>
       </c>
       <c r="L25" t="n">
         <v>1.45</v>
@@ -6723,28 +6723,28 @@
         <v>1.09</v>
       </c>
       <c r="N25" t="n">
-        <v>3.4</v>
+        <v>3.5</v>
       </c>
       <c r="O25" t="n">
-        <v>1.4</v>
+        <v>1.39</v>
       </c>
       <c r="P25" t="n">
-        <v>1.8</v>
+        <v>1.83</v>
       </c>
       <c r="Q25" t="n">
-        <v>2.18</v>
+        <v>2.16</v>
       </c>
       <c r="R25" t="n">
-        <v>1.3</v>
+        <v>1.31</v>
       </c>
       <c r="S25" t="n">
-        <v>4.1</v>
+        <v>4</v>
       </c>
       <c r="T25" t="n">
-        <v>1.89</v>
+        <v>1.85</v>
       </c>
       <c r="U25" t="n">
-        <v>2.06</v>
+        <v>2.1</v>
       </c>
       <c r="V25" t="n">
         <v>1.52</v>
@@ -6753,109 +6753,109 @@
         <v>1.53</v>
       </c>
       <c r="X25" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="Y25" t="n">
-        <v>12</v>
+        <v>11.5</v>
       </c>
       <c r="Z25" t="n">
-        <v>19</v>
+        <v>19.5</v>
       </c>
       <c r="AA25" t="n">
         <v>55</v>
       </c>
       <c r="AB25" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AC25" t="n">
-        <v>8</v>
+        <v>7.8</v>
       </c>
       <c r="AD25" t="n">
-        <v>15</v>
+        <v>14.5</v>
       </c>
       <c r="AE25" t="n">
-        <v>42</v>
+        <v>38</v>
       </c>
       <c r="AF25" t="n">
         <v>19</v>
       </c>
       <c r="AG25" t="n">
-        <v>14.5</v>
+        <v>12.5</v>
       </c>
       <c r="AH25" t="n">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="AI25" t="n">
         <v>60</v>
       </c>
       <c r="AJ25" t="n">
+        <v>50</v>
+      </c>
+      <c r="AK25" t="n">
+        <v>32</v>
+      </c>
+      <c r="AL25" t="n">
         <v>60</v>
       </c>
-      <c r="AK25" t="n">
-        <v>44</v>
-      </c>
-      <c r="AL25" t="n">
-        <v>130</v>
-      </c>
       <c r="AM25" t="n">
-        <v>580</v>
+        <v>450</v>
       </c>
       <c r="AN25" t="n">
-        <v>600</v>
+        <v>36</v>
       </c>
       <c r="AO25" t="n">
-        <v>40</v>
+        <v>36</v>
       </c>
       <c r="AP25" t="n">
         <v>10.5</v>
       </c>
       <c r="AQ25" t="n">
-        <v>9.199999999999999</v>
+        <v>10</v>
       </c>
       <c r="AR25" t="n">
-        <v>16</v>
+        <v>16.5</v>
       </c>
       <c r="AS25" t="n">
-        <v>18.5</v>
+        <v>40</v>
       </c>
       <c r="AT25" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AU25" t="n">
-        <v>6.6</v>
+        <v>6.8</v>
       </c>
       <c r="AV25" t="n">
         <v>11.5</v>
       </c>
       <c r="AW25" t="n">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="AX25" t="n">
-        <v>16</v>
+        <v>9.4</v>
       </c>
       <c r="AY25" t="n">
         <v>11</v>
       </c>
       <c r="AZ25" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="BA25" t="n">
-        <v>26</v>
+        <v>48</v>
       </c>
       <c r="BB25" t="n">
-        <v>18</v>
+        <v>38</v>
       </c>
       <c r="BC25" t="n">
         <v>29</v>
       </c>
       <c r="BD25" t="n">
-        <v>25</v>
+        <v>42</v>
       </c>
       <c r="BE25" t="n">
-        <v>6.2</v>
+        <v>29</v>
       </c>
       <c r="BF25" t="n">
-        <v>6.6</v>
+        <v>18.5</v>
       </c>
       <c r="BG25" t="n">
         <v>13</v>
@@ -6864,7 +6864,7 @@
         <v>3.3</v>
       </c>
       <c r="BI25" t="n">
-        <v>2.76</v>
+        <v>2.74</v>
       </c>
       <c r="BJ25" t="n">
         <v>9.6</v>
@@ -6876,7 +6876,7 @@
         <v>1000</v>
       </c>
       <c r="BM25" t="n">
-        <v>15</v>
+        <v>14.5</v>
       </c>
       <c r="BN25" t="n">
         <v>5.7</v>
@@ -6885,19 +6885,19 @@
         <v>5.1</v>
       </c>
       <c r="BP25" t="n">
-        <v>1000</v>
+        <v>23</v>
       </c>
       <c r="BQ25" t="n">
-        <v>9.800000000000001</v>
+        <v>9.6</v>
       </c>
       <c r="BR25" t="n">
         <v>1000</v>
       </c>
       <c r="BS25" t="n">
-        <v>12</v>
+        <v>11.5</v>
       </c>
       <c r="BT25" t="n">
-        <v>5.6</v>
+        <v>5.7</v>
       </c>
       <c r="BU25" t="n">
         <v>4.3</v>
@@ -6906,23 +6906,23 @@
         <v>1000</v>
       </c>
       <c r="BW25" t="n">
-        <v>9.6</v>
+        <v>9.4</v>
       </c>
       <c r="BX25" t="n">
         <v>1000</v>
       </c>
       <c r="BY25" t="n">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="BZ25" t="n">
         <v>1000</v>
       </c>
       <c r="CA25" t="n">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="CB25" t="inlineStr">
         <is>
-          <t>2026-06-12 05:25:07</t>
+          <t>2026-06-12 07:41:10</t>
         </is>
       </c>
     </row>
@@ -6953,10 +6953,10 @@
         </is>
       </c>
       <c r="F26" t="n">
-        <v>1.75</v>
+        <v>1.76</v>
       </c>
       <c r="G26" t="n">
-        <v>1.81</v>
+        <v>1.82</v>
       </c>
       <c r="H26" t="n">
         <v>4.1</v>
@@ -6965,43 +6965,43 @@
         <v>4.6</v>
       </c>
       <c r="J26" t="n">
-        <v>4.7</v>
+        <v>4.5</v>
       </c>
       <c r="K26" t="n">
-        <v>5.3</v>
+        <v>5.1</v>
       </c>
       <c r="L26" t="n">
-        <v>1.2</v>
+        <v>1.22</v>
       </c>
       <c r="M26" t="n">
         <v>1.02</v>
       </c>
       <c r="N26" t="n">
-        <v>8.4</v>
+        <v>7.6</v>
       </c>
       <c r="O26" t="n">
-        <v>1.11</v>
+        <v>1.13</v>
       </c>
       <c r="P26" t="n">
-        <v>3.6</v>
+        <v>3.25</v>
       </c>
       <c r="Q26" t="n">
-        <v>1.35</v>
+        <v>1.4</v>
       </c>
       <c r="R26" t="n">
-        <v>2.06</v>
+        <v>1.92</v>
       </c>
       <c r="S26" t="n">
-        <v>1.87</v>
+        <v>2</v>
       </c>
       <c r="T26" t="n">
-        <v>1.42</v>
+        <v>1.47</v>
       </c>
       <c r="U26" t="n">
-        <v>2.98</v>
+        <v>2.82</v>
       </c>
       <c r="V26" t="n">
-        <v>1.29</v>
+        <v>1.28</v>
       </c>
       <c r="W26" t="n">
         <v>2.2</v>
@@ -7019,7 +7019,7 @@
         <v>500</v>
       </c>
       <c r="AB26" t="n">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="AC26" t="n">
         <v>15.5</v>
@@ -7031,7 +7031,7 @@
         <v>120</v>
       </c>
       <c r="AF26" t="n">
-        <v>22</v>
+        <v>17</v>
       </c>
       <c r="AG26" t="n">
         <v>14</v>
@@ -7040,10 +7040,10 @@
         <v>19</v>
       </c>
       <c r="AI26" t="n">
-        <v>38</v>
+        <v>100</v>
       </c>
       <c r="AJ26" t="n">
-        <v>23</v>
+        <v>75</v>
       </c>
       <c r="AK26" t="n">
         <v>20</v>
@@ -7055,37 +7055,37 @@
         <v>60</v>
       </c>
       <c r="AN26" t="n">
-        <v>5.5</v>
+        <v>7</v>
       </c>
       <c r="AO26" t="n">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="AP26" t="n">
-        <v>6.6</v>
+        <v>18.5</v>
       </c>
       <c r="AQ26" t="n">
-        <v>14.5</v>
+        <v>15</v>
       </c>
       <c r="AR26" t="n">
-        <v>6.6</v>
+        <v>20</v>
       </c>
       <c r="AS26" t="n">
-        <v>7.2</v>
+        <v>28</v>
       </c>
       <c r="AT26" t="n">
-        <v>17</v>
+        <v>15.5</v>
       </c>
       <c r="AU26" t="n">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="AV26" t="n">
         <v>16.5</v>
       </c>
       <c r="AW26" t="n">
-        <v>18.5</v>
+        <v>32</v>
       </c>
       <c r="AX26" t="n">
-        <v>15.5</v>
+        <v>14.5</v>
       </c>
       <c r="AY26" t="n">
         <v>10</v>
@@ -7097,7 +7097,7 @@
         <v>18.5</v>
       </c>
       <c r="BB26" t="n">
-        <v>19</v>
+        <v>17.5</v>
       </c>
       <c r="BC26" t="n">
         <v>12</v>
@@ -7109,34 +7109,34 @@
         <v>34</v>
       </c>
       <c r="BF26" t="n">
-        <v>4.6</v>
+        <v>5</v>
       </c>
       <c r="BG26" t="n">
-        <v>17.5</v>
+        <v>18.5</v>
       </c>
       <c r="BH26" t="n">
-        <v>6</v>
+        <v>5.6</v>
       </c>
       <c r="BI26" t="n">
-        <v>4.4</v>
+        <v>4.1</v>
       </c>
       <c r="BJ26" t="n">
-        <v>8.6</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BK26" t="n">
         <v>6.4</v>
       </c>
       <c r="BL26" t="n">
-        <v>1000</v>
+        <v>75</v>
       </c>
       <c r="BM26" t="n">
-        <v>10</v>
+        <v>9.6</v>
       </c>
       <c r="BN26" t="n">
-        <v>5.6</v>
+        <v>5.4</v>
       </c>
       <c r="BO26" t="n">
-        <v>4.8</v>
+        <v>4.6</v>
       </c>
       <c r="BP26" t="n">
         <v>11</v>
@@ -7145,38 +7145,38 @@
         <v>8</v>
       </c>
       <c r="BR26" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="BS26" t="n">
         <v>7</v>
       </c>
       <c r="BT26" t="n">
-        <v>9</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BU26" t="n">
         <v>6.6</v>
       </c>
       <c r="BV26" t="n">
-        <v>1000</v>
+        <v>36</v>
       </c>
       <c r="BW26" t="n">
-        <v>8.4</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BX26" t="n">
-        <v>1000</v>
+        <v>34</v>
       </c>
       <c r="BY26" t="n">
-        <v>8.4</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BZ26" t="n">
-        <v>9.6</v>
+        <v>11</v>
       </c>
       <c r="CA26" t="n">
-        <v>5.3</v>
+        <v>7.2</v>
       </c>
       <c r="CB26" t="inlineStr">
         <is>
-          <t>2026-06-12 05:25:07</t>
+          <t>2026-06-12 07:41:10</t>
         </is>
       </c>
     </row>
@@ -7207,79 +7207,79 @@
         </is>
       </c>
       <c r="F27" t="n">
-        <v>2.64</v>
+        <v>3.15</v>
       </c>
       <c r="G27" t="n">
-        <v>44</v>
+        <v>4</v>
       </c>
       <c r="H27" t="n">
-        <v>1.92</v>
+        <v>2.38</v>
       </c>
       <c r="I27" t="n">
-        <v>44</v>
+        <v>2.9</v>
       </c>
       <c r="J27" t="n">
-        <v>2.48</v>
+        <v>2.68</v>
       </c>
       <c r="K27" t="n">
-        <v>3.25</v>
+        <v>3.2</v>
       </c>
       <c r="L27" t="n">
-        <v>1.01</v>
+        <v>1.46</v>
       </c>
       <c r="M27" t="n">
-        <v>1.09</v>
+        <v>1.1</v>
       </c>
       <c r="N27" t="n">
-        <v>1.1</v>
+        <v>2.52</v>
       </c>
       <c r="O27" t="n">
-        <v>1.08</v>
+        <v>1.47</v>
       </c>
       <c r="P27" t="n">
-        <v>1.26</v>
+        <v>1.52</v>
       </c>
       <c r="Q27" t="n">
-        <v>1.09</v>
+        <v>2.4</v>
       </c>
       <c r="R27" t="n">
-        <v>1.12</v>
+        <v>1.19</v>
       </c>
       <c r="S27" t="n">
-        <v>1.49</v>
+        <v>3.55</v>
       </c>
       <c r="T27" t="n">
-        <v>1.11</v>
+        <v>1.94</v>
       </c>
       <c r="U27" t="n">
-        <v>1.11</v>
+        <v>1.78</v>
       </c>
       <c r="V27" t="n">
-        <v>1.46</v>
+        <v>1.52</v>
       </c>
       <c r="W27" t="n">
-        <v>1.2</v>
+        <v>1.33</v>
       </c>
       <c r="X27" t="n">
+        <v>17</v>
+      </c>
+      <c r="Y27" t="n">
+        <v>55</v>
+      </c>
+      <c r="Z27" t="n">
         <v>970</v>
-      </c>
-      <c r="Y27" t="n">
-        <v>970</v>
-      </c>
-      <c r="Z27" t="n">
-        <v>500</v>
       </c>
       <c r="AA27" t="n">
         <v>900</v>
       </c>
       <c r="AB27" t="n">
-        <v>950</v>
+        <v>500</v>
       </c>
       <c r="AC27" t="n">
+        <v>14</v>
+      </c>
+      <c r="AD27" t="n">
         <v>500</v>
-      </c>
-      <c r="AD27" t="n">
-        <v>950</v>
       </c>
       <c r="AE27" t="n">
         <v>500</v>
@@ -7288,7 +7288,7 @@
         <v>500</v>
       </c>
       <c r="AG27" t="n">
-        <v>950</v>
+        <v>970</v>
       </c>
       <c r="AH27" t="n">
         <v>950</v>
@@ -7306,13 +7306,13 @@
         <v>500</v>
       </c>
       <c r="AM27" t="n">
-        <v>500</v>
+        <v>580</v>
       </c>
       <c r="AN27" t="n">
-        <v>500</v>
+        <v>600</v>
       </c>
       <c r="AO27" t="n">
-        <v>500</v>
+        <v>600</v>
       </c>
       <c r="AP27" t="n">
         <v>4.2</v>
@@ -7324,7 +7324,7 @@
         <v>6.2</v>
       </c>
       <c r="AS27" t="n">
-        <v>1.32</v>
+        <v>5.6</v>
       </c>
       <c r="AT27" t="n">
         <v>5.6</v>
@@ -7333,94 +7333,94 @@
         <v>4.2</v>
       </c>
       <c r="AV27" t="n">
-        <v>1.27</v>
+        <v>7</v>
       </c>
       <c r="AW27" t="n">
-        <v>1.32</v>
+        <v>5.5</v>
       </c>
       <c r="AX27" t="n">
-        <v>1.33</v>
+        <v>5.1</v>
       </c>
       <c r="AY27" t="n">
-        <v>1.33</v>
+        <v>4.7</v>
       </c>
       <c r="AZ27" t="n">
-        <v>1.33</v>
+        <v>4.9</v>
       </c>
       <c r="BA27" t="n">
-        <v>1.33</v>
+        <v>5.9</v>
       </c>
       <c r="BB27" t="n">
-        <v>1.33</v>
+        <v>5.9</v>
       </c>
       <c r="BC27" t="n">
-        <v>1.33</v>
+        <v>5.8</v>
       </c>
       <c r="BD27" t="n">
-        <v>1.33</v>
+        <v>6</v>
       </c>
       <c r="BE27" t="n">
-        <v>1.33</v>
+        <v>6.2</v>
       </c>
       <c r="BF27" t="n">
-        <v>1.55</v>
+        <v>6</v>
       </c>
       <c r="BG27" t="n">
-        <v>1.55</v>
+        <v>7.8</v>
       </c>
       <c r="BH27" t="n">
-        <v>1000</v>
+        <v>2.94</v>
       </c>
       <c r="BI27" t="n">
-        <v>1.04</v>
+        <v>2.26</v>
       </c>
       <c r="BJ27" t="n">
         <v>1000</v>
       </c>
       <c r="BK27" t="n">
-        <v>1.04</v>
+        <v>4.8</v>
       </c>
       <c r="BL27" t="n">
         <v>1000</v>
       </c>
       <c r="BM27" t="n">
-        <v>1.04</v>
+        <v>2.14</v>
       </c>
       <c r="BN27" t="n">
-        <v>1000</v>
+        <v>7</v>
       </c>
       <c r="BO27" t="n">
-        <v>1.04</v>
+        <v>3.75</v>
       </c>
       <c r="BP27" t="n">
         <v>1000</v>
       </c>
       <c r="BQ27" t="n">
-        <v>1.04</v>
+        <v>6.6</v>
       </c>
       <c r="BR27" t="n">
         <v>1000</v>
       </c>
       <c r="BS27" t="n">
-        <v>1.04</v>
+        <v>7</v>
       </c>
       <c r="BT27" t="n">
-        <v>1000</v>
+        <v>5.6</v>
       </c>
       <c r="BU27" t="n">
-        <v>1.04</v>
+        <v>3.3</v>
       </c>
       <c r="BV27" t="n">
         <v>1000</v>
       </c>
       <c r="BW27" t="n">
-        <v>1.04</v>
+        <v>6</v>
       </c>
       <c r="BX27" t="n">
         <v>1000</v>
       </c>
       <c r="BY27" t="n">
-        <v>1.04</v>
+        <v>6.8</v>
       </c>
       <c r="BZ27" t="n">
         <v>0</v>
@@ -7430,7 +7430,7 @@
       </c>
       <c r="CB27" t="inlineStr">
         <is>
-          <t>2026-06-12 05:25:07</t>
+          <t>2026-06-12 07:41:10</t>
         </is>
       </c>
     </row>
@@ -7461,22 +7461,22 @@
         </is>
       </c>
       <c r="F28" t="n">
-        <v>2.24</v>
+        <v>2.26</v>
       </c>
       <c r="G28" t="n">
-        <v>2.3</v>
+        <v>2.32</v>
       </c>
       <c r="H28" t="n">
-        <v>3.7</v>
+        <v>3.65</v>
       </c>
       <c r="I28" t="n">
-        <v>3.85</v>
+        <v>3.8</v>
       </c>
       <c r="J28" t="n">
         <v>3.35</v>
       </c>
       <c r="K28" t="n">
-        <v>3.4</v>
+        <v>3.45</v>
       </c>
       <c r="L28" t="n">
         <v>1.5</v>
@@ -7494,7 +7494,7 @@
         <v>1.7</v>
       </c>
       <c r="Q28" t="n">
-        <v>2.32</v>
+        <v>2.34</v>
       </c>
       <c r="R28" t="n">
         <v>1.26</v>
@@ -7503,16 +7503,16 @@
         <v>4.5</v>
       </c>
       <c r="T28" t="n">
-        <v>1.96</v>
+        <v>1.98</v>
       </c>
       <c r="U28" t="n">
-        <v>1.9</v>
+        <v>1.93</v>
       </c>
       <c r="V28" t="n">
         <v>1.35</v>
       </c>
       <c r="W28" t="n">
-        <v>1.76</v>
+        <v>1.75</v>
       </c>
       <c r="X28" t="n">
         <v>11.5</v>
@@ -7533,16 +7533,16 @@
         <v>8</v>
       </c>
       <c r="AD28" t="n">
-        <v>500</v>
+        <v>30</v>
       </c>
       <c r="AE28" t="n">
         <v>500</v>
       </c>
       <c r="AF28" t="n">
-        <v>14</v>
+        <v>12.5</v>
       </c>
       <c r="AG28" t="n">
-        <v>11.5</v>
+        <v>12.5</v>
       </c>
       <c r="AH28" t="n">
         <v>60</v>
@@ -7563,13 +7563,13 @@
         <v>580</v>
       </c>
       <c r="AN28" t="n">
-        <v>500</v>
+        <v>600</v>
       </c>
       <c r="AO28" t="n">
-        <v>500</v>
+        <v>600</v>
       </c>
       <c r="AP28" t="n">
-        <v>9.4</v>
+        <v>9.6</v>
       </c>
       <c r="AQ28" t="n">
         <v>10</v>
@@ -7578,10 +7578,10 @@
         <v>22</v>
       </c>
       <c r="AS28" t="n">
-        <v>9.4</v>
+        <v>10.5</v>
       </c>
       <c r="AT28" t="n">
-        <v>6.8</v>
+        <v>7.2</v>
       </c>
       <c r="AU28" t="n">
         <v>6.6</v>
@@ -7590,19 +7590,19 @@
         <v>13.5</v>
       </c>
       <c r="AW28" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AX28" t="n">
         <v>11</v>
       </c>
       <c r="AY28" t="n">
-        <v>6.4</v>
+        <v>8.4</v>
       </c>
       <c r="AZ28" t="n">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="BA28" t="n">
-        <v>9.199999999999999</v>
+        <v>28</v>
       </c>
       <c r="BB28" t="n">
         <v>26</v>
@@ -7611,16 +7611,16 @@
         <v>23</v>
       </c>
       <c r="BD28" t="n">
-        <v>8.6</v>
+        <v>38</v>
       </c>
       <c r="BE28" t="n">
-        <v>9.800000000000001</v>
+        <v>11</v>
       </c>
       <c r="BF28" t="n">
         <v>21</v>
       </c>
       <c r="BG28" t="n">
-        <v>9.800000000000001</v>
+        <v>10.5</v>
       </c>
       <c r="BH28" t="n">
         <v>3.1</v>
@@ -7632,13 +7632,13 @@
         <v>11</v>
       </c>
       <c r="BK28" t="n">
-        <v>5.4</v>
+        <v>5.3</v>
       </c>
       <c r="BL28" t="n">
         <v>1000</v>
       </c>
       <c r="BM28" t="n">
-        <v>10</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BN28" t="n">
         <v>5.1</v>
@@ -7662,13 +7662,13 @@
         <v>7.2</v>
       </c>
       <c r="BU28" t="n">
-        <v>5.4</v>
+        <v>5.8</v>
       </c>
       <c r="BV28" t="n">
         <v>1000</v>
       </c>
       <c r="BW28" t="n">
-        <v>8.199999999999999</v>
+        <v>8</v>
       </c>
       <c r="BX28" t="n">
         <v>1000</v>
@@ -7684,7 +7684,7 @@
       </c>
       <c r="CB28" t="inlineStr">
         <is>
-          <t>2026-06-12 05:25:07</t>
+          <t>2026-06-12 07:41:10</t>
         </is>
       </c>
     </row>
@@ -7715,19 +7715,19 @@
         </is>
       </c>
       <c r="F29" t="n">
-        <v>2.04</v>
+        <v>2.02</v>
       </c>
       <c r="G29" t="n">
-        <v>2.1</v>
+        <v>2.08</v>
       </c>
       <c r="H29" t="n">
-        <v>3.8</v>
+        <v>3.85</v>
       </c>
       <c r="I29" t="n">
         <v>4.1</v>
       </c>
       <c r="J29" t="n">
-        <v>3.7</v>
+        <v>3.75</v>
       </c>
       <c r="K29" t="n">
         <v>3.95</v>
@@ -7739,43 +7739,43 @@
         <v>1.06</v>
       </c>
       <c r="N29" t="n">
-        <v>4.3</v>
+        <v>4.4</v>
       </c>
       <c r="O29" t="n">
-        <v>1.28</v>
+        <v>1.27</v>
       </c>
       <c r="P29" t="n">
-        <v>2.12</v>
+        <v>2.14</v>
       </c>
       <c r="Q29" t="n">
-        <v>1.84</v>
+        <v>1.82</v>
       </c>
       <c r="R29" t="n">
-        <v>1.44</v>
+        <v>1.45</v>
       </c>
       <c r="S29" t="n">
-        <v>3.2</v>
+        <v>3.1</v>
       </c>
       <c r="T29" t="n">
-        <v>1.71</v>
+        <v>1.7</v>
       </c>
       <c r="U29" t="n">
-        <v>2.26</v>
+        <v>2.28</v>
       </c>
       <c r="V29" t="n">
-        <v>1.33</v>
+        <v>1.32</v>
       </c>
       <c r="W29" t="n">
-        <v>1.91</v>
+        <v>1.93</v>
       </c>
       <c r="X29" t="n">
+        <v>17.5</v>
+      </c>
+      <c r="Y29" t="n">
         <v>17</v>
       </c>
-      <c r="Y29" t="n">
-        <v>16.5</v>
-      </c>
       <c r="Z29" t="n">
-        <v>29</v>
+        <v>48</v>
       </c>
       <c r="AA29" t="n">
         <v>95</v>
@@ -7784,7 +7784,7 @@
         <v>11</v>
       </c>
       <c r="AC29" t="n">
-        <v>8.6</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AD29" t="n">
         <v>16.5</v>
@@ -7805,7 +7805,7 @@
         <v>50</v>
       </c>
       <c r="AJ29" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="AK29" t="n">
         <v>21</v>
@@ -7817,28 +7817,28 @@
         <v>85</v>
       </c>
       <c r="AN29" t="n">
-        <v>13.5</v>
+        <v>13</v>
       </c>
       <c r="AO29" t="n">
-        <v>110</v>
+        <v>100</v>
       </c>
       <c r="AP29" t="n">
-        <v>15</v>
+        <v>15.5</v>
       </c>
       <c r="AQ29" t="n">
         <v>14.5</v>
       </c>
       <c r="AR29" t="n">
-        <v>18.5</v>
+        <v>22</v>
       </c>
       <c r="AS29" t="n">
-        <v>32</v>
+        <v>40</v>
       </c>
       <c r="AT29" t="n">
         <v>9.6</v>
       </c>
       <c r="AU29" t="n">
-        <v>7.6</v>
+        <v>7.8</v>
       </c>
       <c r="AV29" t="n">
         <v>14</v>
@@ -7850,34 +7850,34 @@
         <v>11.5</v>
       </c>
       <c r="AY29" t="n">
-        <v>9.6</v>
+        <v>9.4</v>
       </c>
       <c r="AZ29" t="n">
         <v>15</v>
       </c>
       <c r="BA29" t="n">
-        <v>27</v>
+        <v>32</v>
       </c>
       <c r="BB29" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="BC29" t="n">
         <v>18</v>
       </c>
       <c r="BD29" t="n">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="BE29" t="n">
-        <v>12.5</v>
+        <v>34</v>
       </c>
       <c r="BF29" t="n">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="BG29" t="n">
         <v>34</v>
       </c>
       <c r="BH29" t="n">
-        <v>3.75</v>
+        <v>3.8</v>
       </c>
       <c r="BI29" t="n">
         <v>3</v>
@@ -7886,13 +7886,13 @@
         <v>9.199999999999999</v>
       </c>
       <c r="BK29" t="n">
-        <v>5.8</v>
+        <v>5.7</v>
       </c>
       <c r="BL29" t="n">
         <v>1000</v>
       </c>
       <c r="BM29" t="n">
-        <v>13.5</v>
+        <v>13</v>
       </c>
       <c r="BN29" t="n">
         <v>5</v>
@@ -7904,13 +7904,13 @@
         <v>14</v>
       </c>
       <c r="BQ29" t="n">
-        <v>7.4</v>
+        <v>7.2</v>
       </c>
       <c r="BR29" t="n">
         <v>26</v>
       </c>
       <c r="BS29" t="n">
-        <v>9.800000000000001</v>
+        <v>9.4</v>
       </c>
       <c r="BT29" t="n">
         <v>7.4</v>
@@ -7928,17 +7928,17 @@
         <v>38</v>
       </c>
       <c r="BY29" t="n">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="BZ29" t="n">
         <v>21</v>
       </c>
       <c r="CA29" t="n">
-        <v>9</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="CB29" t="inlineStr">
         <is>
-          <t>2026-06-12 05:25:07</t>
+          <t>2026-06-12 07:41:10</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-06-12.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-06-12.xlsx
@@ -857,88 +857,88 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>1.57</v>
+        <v>1.55</v>
       </c>
       <c r="G2" t="n">
-        <v>1.63</v>
+        <v>1.6</v>
       </c>
       <c r="H2" t="n">
-        <v>6.4</v>
+        <v>6.6</v>
       </c>
       <c r="I2" t="n">
-        <v>7.6</v>
+        <v>7.8</v>
       </c>
       <c r="J2" t="n">
         <v>4.1</v>
       </c>
       <c r="K2" t="n">
-        <v>4.7</v>
+        <v>4.8</v>
       </c>
       <c r="L2" t="n">
-        <v>1.4</v>
+        <v>1.39</v>
       </c>
       <c r="M2" t="n">
         <v>1.06</v>
       </c>
       <c r="N2" t="n">
-        <v>3.95</v>
+        <v>4.1</v>
       </c>
       <c r="O2" t="n">
-        <v>1.3</v>
+        <v>1.29</v>
       </c>
       <c r="P2" t="n">
-        <v>2</v>
+        <v>2.02</v>
       </c>
       <c r="Q2" t="n">
-        <v>1.91</v>
+        <v>1.9</v>
       </c>
       <c r="R2" t="n">
-        <v>1.38</v>
+        <v>1.39</v>
       </c>
       <c r="S2" t="n">
-        <v>3.35</v>
+        <v>3.3</v>
       </c>
       <c r="T2" t="n">
-        <v>1.97</v>
+        <v>1.96</v>
       </c>
       <c r="U2" t="n">
-        <v>1.88</v>
+        <v>1.89</v>
       </c>
       <c r="V2" t="n">
-        <v>1.16</v>
+        <v>1.15</v>
       </c>
       <c r="W2" t="n">
-        <v>2.56</v>
+        <v>2.66</v>
       </c>
       <c r="X2" t="n">
-        <v>500</v>
+        <v>90</v>
       </c>
       <c r="Y2" t="n">
         <v>950</v>
       </c>
       <c r="Z2" t="n">
-        <v>500</v>
+        <v>220</v>
       </c>
       <c r="AA2" t="n">
         <v>700</v>
       </c>
       <c r="AB2" t="n">
-        <v>27</v>
+        <v>14</v>
       </c>
       <c r="AC2" t="n">
-        <v>17.5</v>
+        <v>14</v>
       </c>
       <c r="AD2" t="n">
-        <v>950</v>
+        <v>500</v>
       </c>
       <c r="AE2" t="n">
         <v>700</v>
       </c>
       <c r="AF2" t="n">
-        <v>970</v>
+        <v>40</v>
       </c>
       <c r="AG2" t="n">
-        <v>970</v>
+        <v>36</v>
       </c>
       <c r="AH2" t="n">
         <v>950</v>
@@ -947,7 +947,7 @@
         <v>700</v>
       </c>
       <c r="AJ2" t="n">
-        <v>900</v>
+        <v>500</v>
       </c>
       <c r="AK2" t="n">
         <v>970</v>
@@ -962,85 +962,85 @@
         <v>29</v>
       </c>
       <c r="AO2" t="n">
-        <v>170</v>
+        <v>180</v>
       </c>
       <c r="AP2" t="n">
-        <v>6.8</v>
+        <v>7.8</v>
       </c>
       <c r="AQ2" t="n">
-        <v>4.2</v>
+        <v>5</v>
       </c>
       <c r="AR2" t="n">
         <v>5.5</v>
       </c>
       <c r="AS2" t="n">
-        <v>4.2</v>
+        <v>6.2</v>
       </c>
       <c r="AT2" t="n">
-        <v>3.85</v>
+        <v>6.2</v>
       </c>
       <c r="AU2" t="n">
-        <v>4.7</v>
+        <v>7</v>
       </c>
       <c r="AV2" t="n">
-        <v>4.5</v>
+        <v>8.6</v>
       </c>
       <c r="AW2" t="n">
         <v>6</v>
       </c>
       <c r="AX2" t="n">
-        <v>5.3</v>
+        <v>5.7</v>
       </c>
       <c r="AY2" t="n">
-        <v>4.8</v>
+        <v>6.8</v>
       </c>
       <c r="AZ2" t="n">
-        <v>2.94</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BA2" t="n">
-        <v>4.6</v>
+        <v>6</v>
       </c>
       <c r="BB2" t="n">
-        <v>6.6</v>
+        <v>8</v>
       </c>
       <c r="BC2" t="n">
-        <v>7</v>
+        <v>7.8</v>
       </c>
       <c r="BD2" t="n">
-        <v>3.3</v>
+        <v>12</v>
       </c>
       <c r="BE2" t="n">
-        <v>3</v>
+        <v>4.5</v>
       </c>
       <c r="BF2" t="n">
-        <v>6.6</v>
+        <v>7.4</v>
       </c>
       <c r="BG2" t="n">
         <v>4.2</v>
       </c>
       <c r="BH2" t="n">
-        <v>3.65</v>
+        <v>3.6</v>
       </c>
       <c r="BI2" t="n">
-        <v>3.2</v>
+        <v>3.15</v>
       </c>
       <c r="BJ2" t="n">
         <v>1000</v>
       </c>
       <c r="BK2" t="n">
-        <v>9.199999999999999</v>
+        <v>6.4</v>
       </c>
       <c r="BL2" t="n">
         <v>1000</v>
       </c>
       <c r="BM2" t="n">
-        <v>1.88</v>
+        <v>3.25</v>
       </c>
       <c r="BN2" t="n">
-        <v>4.5</v>
+        <v>4.3</v>
       </c>
       <c r="BO2" t="n">
-        <v>4</v>
+        <v>3.7</v>
       </c>
       <c r="BP2" t="n">
         <v>1000</v>
@@ -1052,35 +1052,35 @@
         <v>1000</v>
       </c>
       <c r="BS2" t="n">
-        <v>3</v>
+        <v>4.9</v>
       </c>
       <c r="BT2" t="n">
-        <v>8</v>
+        <v>24</v>
       </c>
       <c r="BU2" t="n">
-        <v>5.1</v>
+        <v>7.2</v>
       </c>
       <c r="BV2" t="n">
         <v>1000</v>
       </c>
       <c r="BW2" t="n">
-        <v>3.65</v>
+        <v>4.5</v>
       </c>
       <c r="BX2" t="n">
         <v>1000</v>
       </c>
       <c r="BY2" t="n">
-        <v>3.15</v>
+        <v>4.5</v>
       </c>
       <c r="BZ2" t="n">
         <v>1000</v>
       </c>
       <c r="CA2" t="n">
-        <v>4.8</v>
+        <v>7.6</v>
       </c>
       <c r="CB2" t="inlineStr">
         <is>
-          <t>2026-06-12 07:41:10</t>
+          <t>2026-06-12 09:58:55</t>
         </is>
       </c>
     </row>
@@ -1111,16 +1111,16 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>2.62</v>
+        <v>2.64</v>
       </c>
       <c r="G3" t="n">
+        <v>2.76</v>
+      </c>
+      <c r="H3" t="n">
         <v>2.74</v>
       </c>
-      <c r="H3" t="n">
-        <v>2.76</v>
-      </c>
       <c r="I3" t="n">
-        <v>2.9</v>
+        <v>2.88</v>
       </c>
       <c r="J3" t="n">
         <v>3.55</v>
@@ -1135,10 +1135,10 @@
         <v>1.05</v>
       </c>
       <c r="N3" t="n">
-        <v>4.5</v>
+        <v>4.7</v>
       </c>
       <c r="O3" t="n">
-        <v>1.26</v>
+        <v>1.25</v>
       </c>
       <c r="P3" t="n">
         <v>2.22</v>
@@ -1147,28 +1147,28 @@
         <v>1.76</v>
       </c>
       <c r="R3" t="n">
-        <v>1.47</v>
+        <v>1.48</v>
       </c>
       <c r="S3" t="n">
-        <v>2.96</v>
+        <v>2.92</v>
       </c>
       <c r="T3" t="n">
-        <v>1.61</v>
+        <v>1.62</v>
       </c>
       <c r="U3" t="n">
         <v>2.42</v>
       </c>
       <c r="V3" t="n">
-        <v>1.52</v>
+        <v>1.53</v>
       </c>
       <c r="W3" t="n">
-        <v>1.57</v>
+        <v>1.56</v>
       </c>
       <c r="X3" t="n">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="Y3" t="n">
-        <v>14.5</v>
+        <v>14</v>
       </c>
       <c r="Z3" t="n">
         <v>25</v>
@@ -1180,10 +1180,10 @@
         <v>14</v>
       </c>
       <c r="AC3" t="n">
-        <v>8.6</v>
+        <v>8.4</v>
       </c>
       <c r="AD3" t="n">
-        <v>15.5</v>
+        <v>14.5</v>
       </c>
       <c r="AE3" t="n">
         <v>34</v>
@@ -1210,7 +1210,7 @@
         <v>44</v>
       </c>
       <c r="AM3" t="n">
-        <v>320</v>
+        <v>200</v>
       </c>
       <c r="AN3" t="n">
         <v>22</v>
@@ -1219,19 +1219,19 @@
         <v>23</v>
       </c>
       <c r="AP3" t="n">
-        <v>16.5</v>
+        <v>17</v>
       </c>
       <c r="AQ3" t="n">
         <v>12.5</v>
       </c>
       <c r="AR3" t="n">
-        <v>18.5</v>
+        <v>18</v>
       </c>
       <c r="AS3" t="n">
-        <v>18.5</v>
+        <v>18</v>
       </c>
       <c r="AT3" t="n">
-        <v>12.5</v>
+        <v>12</v>
       </c>
       <c r="AU3" t="n">
         <v>7.6</v>
@@ -1249,7 +1249,7 @@
         <v>10.5</v>
       </c>
       <c r="AZ3" t="n">
-        <v>13</v>
+        <v>13.5</v>
       </c>
       <c r="BA3" t="n">
         <v>18.5</v>
@@ -1258,13 +1258,13 @@
         <v>18</v>
       </c>
       <c r="BC3" t="n">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="BD3" t="n">
-        <v>18.5</v>
+        <v>18</v>
       </c>
       <c r="BE3" t="n">
-        <v>7.8</v>
+        <v>10.5</v>
       </c>
       <c r="BF3" t="n">
         <v>17</v>
@@ -1273,7 +1273,7 @@
         <v>18.5</v>
       </c>
       <c r="BH3" t="n">
-        <v>3.85</v>
+        <v>3.8</v>
       </c>
       <c r="BI3" t="n">
         <v>3.1</v>
@@ -1288,25 +1288,25 @@
         <v>1000</v>
       </c>
       <c r="BM3" t="n">
-        <v>13.5</v>
+        <v>14</v>
       </c>
       <c r="BN3" t="n">
         <v>5.8</v>
       </c>
       <c r="BO3" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="BP3" t="n">
-        <v>18.5</v>
+        <v>18</v>
       </c>
       <c r="BQ3" t="n">
-        <v>8.4</v>
+        <v>8.6</v>
       </c>
       <c r="BR3" t="n">
-        <v>29</v>
+        <v>1000</v>
       </c>
       <c r="BS3" t="n">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="BT3" t="n">
         <v>6.2</v>
@@ -1315,26 +1315,26 @@
         <v>5.4</v>
       </c>
       <c r="BV3" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="BW3" t="n">
-        <v>8.800000000000001</v>
+        <v>9.4</v>
       </c>
       <c r="BX3" t="n">
         <v>30</v>
       </c>
       <c r="BY3" t="n">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="BZ3" t="n">
         <v>21</v>
       </c>
       <c r="CA3" t="n">
-        <v>9</v>
+        <v>9.4</v>
       </c>
       <c r="CB3" t="inlineStr">
         <is>
-          <t>2026-06-12 07:41:10</t>
+          <t>2026-06-12 09:58:55</t>
         </is>
       </c>
     </row>
@@ -1365,22 +1365,22 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>3.15</v>
+        <v>2.96</v>
       </c>
       <c r="G4" t="n">
-        <v>3.35</v>
+        <v>3.25</v>
       </c>
       <c r="H4" t="n">
-        <v>3.05</v>
+        <v>3</v>
       </c>
       <c r="I4" t="n">
-        <v>3.1</v>
+        <v>3.25</v>
       </c>
       <c r="J4" t="n">
         <v>2.66</v>
       </c>
       <c r="K4" t="n">
-        <v>2.76</v>
+        <v>2.84</v>
       </c>
       <c r="L4" t="n">
         <v>1.67</v>
@@ -1395,7 +1395,7 @@
         <v>1.64</v>
       </c>
       <c r="P4" t="n">
-        <v>1.47</v>
+        <v>1.43</v>
       </c>
       <c r="Q4" t="n">
         <v>3.05</v>
@@ -1407,34 +1407,34 @@
         <v>6.6</v>
       </c>
       <c r="T4" t="n">
-        <v>2.18</v>
+        <v>1.75</v>
       </c>
       <c r="U4" t="n">
-        <v>1.67</v>
+        <v>1.75</v>
       </c>
       <c r="V4" t="n">
-        <v>1.47</v>
+        <v>1.44</v>
       </c>
       <c r="W4" t="n">
-        <v>1.43</v>
+        <v>1.44</v>
       </c>
       <c r="X4" t="n">
-        <v>16.5</v>
+        <v>970</v>
       </c>
       <c r="Y4" t="n">
+        <v>970</v>
+      </c>
+      <c r="Z4" t="n">
         <v>500</v>
-      </c>
-      <c r="Z4" t="n">
-        <v>970</v>
       </c>
       <c r="AA4" t="n">
         <v>500</v>
       </c>
       <c r="AB4" t="n">
-        <v>500</v>
+        <v>970</v>
       </c>
       <c r="AC4" t="n">
-        <v>15</v>
+        <v>7</v>
       </c>
       <c r="AD4" t="n">
         <v>970</v>
@@ -1467,25 +1467,25 @@
         <v>500</v>
       </c>
       <c r="AN4" t="n">
-        <v>100</v>
+        <v>1000</v>
       </c>
       <c r="AO4" t="n">
-        <v>85</v>
+        <v>1000</v>
       </c>
       <c r="AP4" t="n">
         <v>4.2</v>
       </c>
       <c r="AQ4" t="n">
-        <v>6.8</v>
+        <v>4.4</v>
       </c>
       <c r="AR4" t="n">
         <v>8.199999999999999</v>
       </c>
       <c r="AS4" t="n">
-        <v>7.8</v>
+        <v>3.05</v>
       </c>
       <c r="AT4" t="n">
-        <v>4.7</v>
+        <v>4.2</v>
       </c>
       <c r="AU4" t="n">
         <v>4.2</v>
@@ -1494,7 +1494,7 @@
         <v>6.8</v>
       </c>
       <c r="AW4" t="n">
-        <v>7.8</v>
+        <v>3.05</v>
       </c>
       <c r="AX4" t="n">
         <v>7.6</v>
@@ -1503,92 +1503,92 @@
         <v>7</v>
       </c>
       <c r="AZ4" t="n">
-        <v>7.2</v>
+        <v>3.05</v>
       </c>
       <c r="BA4" t="n">
         <v>3.05</v>
       </c>
       <c r="BB4" t="n">
-        <v>7.8</v>
+        <v>3.05</v>
       </c>
       <c r="BC4" t="n">
-        <v>7.8</v>
+        <v>3</v>
       </c>
       <c r="BD4" t="n">
-        <v>3.1</v>
+        <v>3.05</v>
       </c>
       <c r="BE4" t="n">
-        <v>8.6</v>
+        <v>3.05</v>
       </c>
       <c r="BF4" t="n">
-        <v>9.199999999999999</v>
+        <v>2.98</v>
       </c>
       <c r="BG4" t="n">
-        <v>2.82</v>
+        <v>2.98</v>
       </c>
       <c r="BH4" t="n">
-        <v>2.6</v>
+        <v>1000</v>
       </c>
       <c r="BI4" t="n">
-        <v>2.14</v>
+        <v>1.04</v>
       </c>
       <c r="BJ4" t="n">
         <v>1000</v>
       </c>
       <c r="BK4" t="n">
-        <v>5.7</v>
+        <v>1.04</v>
       </c>
       <c r="BL4" t="n">
         <v>1000</v>
       </c>
       <c r="BM4" t="n">
-        <v>1.44</v>
+        <v>1.04</v>
       </c>
       <c r="BN4" t="n">
         <v>1000</v>
       </c>
       <c r="BO4" t="n">
-        <v>3.8</v>
+        <v>1.04</v>
       </c>
       <c r="BP4" t="n">
         <v>1000</v>
       </c>
       <c r="BQ4" t="n">
-        <v>1.91</v>
+        <v>1.04</v>
       </c>
       <c r="BR4" t="n">
         <v>1000</v>
       </c>
       <c r="BS4" t="n">
-        <v>1.27</v>
+        <v>1.04</v>
       </c>
       <c r="BT4" t="n">
-        <v>24</v>
+        <v>1000</v>
       </c>
       <c r="BU4" t="n">
-        <v>3.9</v>
+        <v>1.04</v>
       </c>
       <c r="BV4" t="n">
         <v>1000</v>
       </c>
       <c r="BW4" t="n">
-        <v>1.91</v>
+        <v>1.04</v>
       </c>
       <c r="BX4" t="n">
         <v>1000</v>
       </c>
       <c r="BY4" t="n">
-        <v>1.97</v>
+        <v>1.04</v>
       </c>
       <c r="BZ4" t="n">
         <v>1000</v>
       </c>
       <c r="CA4" t="n">
-        <v>1.29</v>
+        <v>1.04</v>
       </c>
       <c r="CB4" t="inlineStr">
         <is>
-          <t>2026-06-12 07:41:10</t>
+          <t>2026-06-12 09:58:55</t>
         </is>
       </c>
     </row>
@@ -1619,37 +1619,37 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>2.04</v>
+        <v>2.1</v>
       </c>
       <c r="G5" t="n">
-        <v>2.12</v>
+        <v>2.22</v>
       </c>
       <c r="H5" t="n">
-        <v>4.4</v>
+        <v>4.2</v>
       </c>
       <c r="I5" t="n">
-        <v>4.9</v>
+        <v>4.7</v>
       </c>
       <c r="J5" t="n">
-        <v>3.2</v>
+        <v>3.15</v>
       </c>
       <c r="K5" t="n">
         <v>3.4</v>
       </c>
       <c r="L5" t="n">
-        <v>1.6</v>
+        <v>1.61</v>
       </c>
       <c r="M5" t="n">
         <v>1.13</v>
       </c>
       <c r="N5" t="n">
-        <v>2.6</v>
+        <v>2.56</v>
       </c>
       <c r="O5" t="n">
-        <v>1.58</v>
+        <v>1.59</v>
       </c>
       <c r="P5" t="n">
-        <v>1.51</v>
+        <v>1.5</v>
       </c>
       <c r="Q5" t="n">
         <v>2.78</v>
@@ -1658,61 +1658,61 @@
         <v>1.16</v>
       </c>
       <c r="S5" t="n">
-        <v>6.2</v>
+        <v>6.4</v>
       </c>
       <c r="T5" t="n">
-        <v>2.26</v>
+        <v>2.22</v>
       </c>
       <c r="U5" t="n">
-        <v>1.67</v>
+        <v>1.69</v>
       </c>
       <c r="V5" t="n">
-        <v>1.26</v>
+        <v>1.27</v>
       </c>
       <c r="W5" t="n">
-        <v>1.89</v>
+        <v>1.82</v>
       </c>
       <c r="X5" t="n">
-        <v>8.6</v>
+        <v>8.4</v>
       </c>
       <c r="Y5" t="n">
         <v>11.5</v>
       </c>
       <c r="Z5" t="n">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="AA5" t="n">
-        <v>130</v>
+        <v>900</v>
       </c>
       <c r="AB5" t="n">
-        <v>6.6</v>
+        <v>6.8</v>
       </c>
       <c r="AC5" t="n">
         <v>7.6</v>
       </c>
       <c r="AD5" t="n">
-        <v>20</v>
+        <v>19.5</v>
       </c>
       <c r="AE5" t="n">
-        <v>100</v>
+        <v>110</v>
       </c>
       <c r="AF5" t="n">
-        <v>11.5</v>
+        <v>12</v>
       </c>
       <c r="AG5" t="n">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="AH5" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="AI5" t="n">
         <v>500</v>
       </c>
       <c r="AJ5" t="n">
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="AK5" t="n">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="AL5" t="n">
         <v>75</v>
@@ -1721,37 +1721,37 @@
         <v>500</v>
       </c>
       <c r="AN5" t="n">
-        <v>34</v>
+        <v>600</v>
       </c>
       <c r="AO5" t="n">
-        <v>170</v>
+        <v>160</v>
       </c>
       <c r="AP5" t="n">
         <v>7.2</v>
       </c>
       <c r="AQ5" t="n">
-        <v>10.5</v>
+        <v>9.6</v>
       </c>
       <c r="AR5" t="n">
-        <v>27</v>
+        <v>23</v>
       </c>
       <c r="AS5" t="n">
-        <v>28</v>
+        <v>12</v>
       </c>
       <c r="AT5" t="n">
-        <v>6</v>
+        <v>5.7</v>
       </c>
       <c r="AU5" t="n">
         <v>6.6</v>
       </c>
       <c r="AV5" t="n">
-        <v>16.5</v>
+        <v>17</v>
       </c>
       <c r="AW5" t="n">
-        <v>14.5</v>
+        <v>70</v>
       </c>
       <c r="AX5" t="n">
-        <v>9.4</v>
+        <v>10</v>
       </c>
       <c r="AY5" t="n">
         <v>10</v>
@@ -1760,31 +1760,31 @@
         <v>25</v>
       </c>
       <c r="BA5" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="BB5" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="BC5" t="n">
-        <v>15</v>
+        <v>28</v>
       </c>
       <c r="BD5" t="n">
-        <v>29</v>
+        <v>55</v>
       </c>
       <c r="BE5" t="n">
-        <v>15</v>
+        <v>46</v>
       </c>
       <c r="BF5" t="n">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="BG5" t="n">
-        <v>13.5</v>
+        <v>12.5</v>
       </c>
       <c r="BH5" t="n">
-        <v>2.7</v>
+        <v>2.66</v>
       </c>
       <c r="BI5" t="n">
-        <v>2.28</v>
+        <v>2.24</v>
       </c>
       <c r="BJ5" t="n">
         <v>12</v>
@@ -1799,16 +1799,16 @@
         <v>13.5</v>
       </c>
       <c r="BN5" t="n">
-        <v>4.6</v>
+        <v>4.7</v>
       </c>
       <c r="BO5" t="n">
         <v>4</v>
       </c>
       <c r="BP5" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="BQ5" t="n">
-        <v>8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BR5" t="n">
         <v>1000</v>
@@ -1817,13 +1817,13 @@
         <v>11</v>
       </c>
       <c r="BT5" t="n">
-        <v>8</v>
+        <v>7.8</v>
       </c>
       <c r="BU5" t="n">
-        <v>5.5</v>
+        <v>5.8</v>
       </c>
       <c r="BV5" t="n">
-        <v>1000</v>
+        <v>70</v>
       </c>
       <c r="BW5" t="n">
         <v>11</v>
@@ -1838,11 +1838,11 @@
         <v>65</v>
       </c>
       <c r="CA5" t="n">
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="CB5" t="inlineStr">
         <is>
-          <t>2026-06-12 07:41:10</t>
+          <t>2026-06-12 09:58:55</t>
         </is>
       </c>
     </row>
@@ -1873,25 +1873,25 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>3.6</v>
+        <v>3.5</v>
       </c>
       <c r="G6" t="n">
-        <v>3.8</v>
+        <v>3.7</v>
       </c>
       <c r="H6" t="n">
         <v>2.18</v>
       </c>
       <c r="I6" t="n">
-        <v>2.26</v>
+        <v>2.24</v>
       </c>
       <c r="J6" t="n">
-        <v>3.5</v>
+        <v>3.65</v>
       </c>
       <c r="K6" t="n">
-        <v>3.75</v>
+        <v>3.8</v>
       </c>
       <c r="L6" t="n">
-        <v>1.39</v>
+        <v>1.4</v>
       </c>
       <c r="M6" t="n">
         <v>1.06</v>
@@ -1906,13 +1906,13 @@
         <v>2.04</v>
       </c>
       <c r="Q6" t="n">
-        <v>1.87</v>
+        <v>1.89</v>
       </c>
       <c r="R6" t="n">
         <v>1.41</v>
       </c>
       <c r="S6" t="n">
-        <v>3.2</v>
+        <v>3.25</v>
       </c>
       <c r="T6" t="n">
         <v>1.74</v>
@@ -1924,124 +1924,124 @@
         <v>1.8</v>
       </c>
       <c r="W6" t="n">
-        <v>1.36</v>
+        <v>1.37</v>
       </c>
       <c r="X6" t="n">
-        <v>16.5</v>
+        <v>21</v>
       </c>
       <c r="Y6" t="n">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="Z6" t="n">
         <v>15</v>
       </c>
       <c r="AA6" t="n">
-        <v>46</v>
+        <v>28</v>
       </c>
       <c r="AB6" t="n">
-        <v>15</v>
+        <v>14.5</v>
       </c>
       <c r="AC6" t="n">
-        <v>8.199999999999999</v>
+        <v>8.4</v>
       </c>
       <c r="AD6" t="n">
-        <v>14</v>
+        <v>13.5</v>
       </c>
       <c r="AE6" t="n">
         <v>24</v>
       </c>
       <c r="AF6" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="AG6" t="n">
-        <v>14.5</v>
+        <v>15</v>
       </c>
       <c r="AH6" t="n">
         <v>16.5</v>
       </c>
       <c r="AI6" t="n">
-        <v>95</v>
+        <v>36</v>
       </c>
       <c r="AJ6" t="n">
-        <v>250</v>
+        <v>70</v>
       </c>
       <c r="AK6" t="n">
-        <v>110</v>
+        <v>65</v>
       </c>
       <c r="AL6" t="n">
-        <v>130</v>
+        <v>48</v>
       </c>
       <c r="AM6" t="n">
-        <v>200</v>
+        <v>90</v>
       </c>
       <c r="AN6" t="n">
-        <v>70</v>
+        <v>36</v>
       </c>
       <c r="AO6" t="n">
+        <v>16</v>
+      </c>
+      <c r="AP6" t="n">
         <v>15</v>
       </c>
-      <c r="AP6" t="n">
-        <v>14</v>
-      </c>
       <c r="AQ6" t="n">
-        <v>10</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AR6" t="n">
         <v>13</v>
       </c>
       <c r="AS6" t="n">
-        <v>16.5</v>
+        <v>25</v>
       </c>
       <c r="AT6" t="n">
-        <v>12.5</v>
+        <v>13.5</v>
       </c>
       <c r="AU6" t="n">
-        <v>7.2</v>
+        <v>7.6</v>
       </c>
       <c r="AV6" t="n">
-        <v>10</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AW6" t="n">
         <v>20</v>
       </c>
       <c r="AX6" t="n">
-        <v>12</v>
+        <v>23</v>
       </c>
       <c r="AY6" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AZ6" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="BA6" t="n">
+        <v>30</v>
+      </c>
+      <c r="BB6" t="n">
+        <v>42</v>
+      </c>
+      <c r="BC6" t="n">
+        <v>34</v>
+      </c>
+      <c r="BD6" t="n">
+        <v>38</v>
+      </c>
+      <c r="BE6" t="n">
+        <v>60</v>
+      </c>
+      <c r="BF6" t="n">
+        <v>30</v>
+      </c>
+      <c r="BG6" t="n">
         <v>14</v>
       </c>
-      <c r="BA6" t="n">
-        <v>18</v>
-      </c>
-      <c r="BB6" t="n">
-        <v>11</v>
-      </c>
-      <c r="BC6" t="n">
-        <v>18</v>
-      </c>
-      <c r="BD6" t="n">
-        <v>23</v>
-      </c>
-      <c r="BE6" t="n">
-        <v>22</v>
-      </c>
-      <c r="BF6" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="BG6" t="n">
-        <v>13</v>
-      </c>
       <c r="BH6" t="n">
-        <v>3.65</v>
+        <v>3.6</v>
       </c>
       <c r="BI6" t="n">
         <v>2.96</v>
       </c>
       <c r="BJ6" t="n">
-        <v>9.4</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BK6" t="n">
         <v>5.9</v>
@@ -2050,53 +2050,53 @@
         <v>1000</v>
       </c>
       <c r="BM6" t="n">
-        <v>14</v>
+        <v>14.5</v>
       </c>
       <c r="BN6" t="n">
-        <v>7.2</v>
+        <v>6.8</v>
       </c>
       <c r="BO6" t="n">
-        <v>5.3</v>
+        <v>6</v>
       </c>
       <c r="BP6" t="n">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="BQ6" t="n">
         <v>10</v>
       </c>
       <c r="BR6" t="n">
-        <v>1000</v>
+        <v>36</v>
       </c>
       <c r="BS6" t="n">
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="BT6" t="n">
-        <v>5</v>
+        <v>5.2</v>
       </c>
       <c r="BU6" t="n">
-        <v>4.4</v>
+        <v>4.5</v>
       </c>
       <c r="BV6" t="n">
-        <v>15</v>
+        <v>15.5</v>
       </c>
       <c r="BW6" t="n">
-        <v>7.6</v>
+        <v>8</v>
       </c>
       <c r="BX6" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="BY6" t="n">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="BZ6" t="n">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="CA6" t="n">
-        <v>9.199999999999999</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="CB6" t="inlineStr">
         <is>
-          <t>2026-06-12 07:41:10</t>
+          <t>2026-06-12 09:58:55</t>
         </is>
       </c>
     </row>
@@ -2130,16 +2130,16 @@
         <v>1.61</v>
       </c>
       <c r="G7" t="n">
-        <v>1.65</v>
+        <v>1.64</v>
       </c>
       <c r="H7" t="n">
         <v>5.9</v>
       </c>
       <c r="I7" t="n">
-        <v>7</v>
+        <v>6.8</v>
       </c>
       <c r="J7" t="n">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="K7" t="n">
         <v>4.7</v>
@@ -2160,34 +2160,34 @@
         <v>2.12</v>
       </c>
       <c r="Q7" t="n">
-        <v>1.81</v>
+        <v>1.8</v>
       </c>
       <c r="R7" t="n">
-        <v>1.43</v>
+        <v>1.44</v>
       </c>
       <c r="S7" t="n">
         <v>3.05</v>
       </c>
       <c r="T7" t="n">
-        <v>1.82</v>
+        <v>1.83</v>
       </c>
       <c r="U7" t="n">
         <v>2</v>
       </c>
       <c r="V7" t="n">
-        <v>1.18</v>
+        <v>1.17</v>
       </c>
       <c r="W7" t="n">
         <v>2.52</v>
       </c>
       <c r="X7" t="n">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="Y7" t="n">
         <v>40</v>
       </c>
       <c r="Z7" t="n">
-        <v>90</v>
+        <v>120</v>
       </c>
       <c r="AA7" t="n">
         <v>900</v>
@@ -2199,7 +2199,7 @@
         <v>10</v>
       </c>
       <c r="AD7" t="n">
-        <v>38</v>
+        <v>34</v>
       </c>
       <c r="AE7" t="n">
         <v>700</v>
@@ -2208,7 +2208,7 @@
         <v>10.5</v>
       </c>
       <c r="AG7" t="n">
-        <v>10.5</v>
+        <v>9.4</v>
       </c>
       <c r="AH7" t="n">
         <v>34</v>
@@ -2238,13 +2238,13 @@
         <v>15</v>
       </c>
       <c r="AQ7" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AR7" t="n">
         <v>23</v>
       </c>
       <c r="AS7" t="n">
-        <v>12</v>
+        <v>11.5</v>
       </c>
       <c r="AT7" t="n">
         <v>7.8</v>
@@ -2256,28 +2256,28 @@
         <v>19.5</v>
       </c>
       <c r="AW7" t="n">
-        <v>12</v>
+        <v>11.5</v>
       </c>
       <c r="AX7" t="n">
         <v>8.800000000000001</v>
       </c>
       <c r="AY7" t="n">
-        <v>8.800000000000001</v>
+        <v>8.6</v>
       </c>
       <c r="AZ7" t="n">
-        <v>17.5</v>
+        <v>18</v>
       </c>
       <c r="BA7" t="n">
         <v>32</v>
       </c>
       <c r="BB7" t="n">
-        <v>13.5</v>
+        <v>13</v>
       </c>
       <c r="BC7" t="n">
         <v>9.6</v>
       </c>
       <c r="BD7" t="n">
-        <v>10</v>
+        <v>18</v>
       </c>
       <c r="BE7" t="n">
         <v>11.5</v>
@@ -2289,58 +2289,58 @@
         <v>13.5</v>
       </c>
       <c r="BH7" t="n">
-        <v>3.8</v>
+        <v>3.85</v>
       </c>
       <c r="BI7" t="n">
-        <v>2.96</v>
+        <v>3.35</v>
       </c>
       <c r="BJ7" t="n">
-        <v>12.5</v>
+        <v>11</v>
       </c>
       <c r="BK7" t="n">
-        <v>4.5</v>
+        <v>5.2</v>
       </c>
       <c r="BL7" t="n">
         <v>1000</v>
       </c>
       <c r="BM7" t="n">
-        <v>6.6</v>
+        <v>7.8</v>
       </c>
       <c r="BN7" t="n">
         <v>4.3</v>
       </c>
       <c r="BO7" t="n">
-        <v>3.3</v>
+        <v>3.75</v>
       </c>
       <c r="BP7" t="n">
         <v>12.5</v>
       </c>
       <c r="BQ7" t="n">
-        <v>4.5</v>
+        <v>5.4</v>
       </c>
       <c r="BR7" t="n">
         <v>32</v>
       </c>
       <c r="BS7" t="n">
-        <v>5.7</v>
+        <v>6.4</v>
       </c>
       <c r="BT7" t="n">
-        <v>11.5</v>
+        <v>10.5</v>
       </c>
       <c r="BU7" t="n">
-        <v>4.3</v>
+        <v>5</v>
       </c>
       <c r="BV7" t="n">
         <v>65</v>
       </c>
       <c r="BW7" t="n">
-        <v>6.2</v>
+        <v>7.4</v>
       </c>
       <c r="BX7" t="n">
         <v>1000</v>
       </c>
       <c r="BY7" t="n">
-        <v>6.2</v>
+        <v>7.4</v>
       </c>
       <c r="BZ7" t="n">
         <v>0</v>
@@ -2350,7 +2350,7 @@
       </c>
       <c r="CB7" t="inlineStr">
         <is>
-          <t>2026-06-12 07:41:10</t>
+          <t>2026-06-12 09:58:55</t>
         </is>
       </c>
     </row>
@@ -2381,52 +2381,52 @@
         </is>
       </c>
       <c r="F8" t="n">
-        <v>1.82</v>
+        <v>1.84</v>
       </c>
       <c r="G8" t="n">
-        <v>1.91</v>
+        <v>1.92</v>
       </c>
       <c r="H8" t="n">
         <v>4.2</v>
       </c>
       <c r="I8" t="n">
-        <v>4.8</v>
+        <v>4.7</v>
       </c>
       <c r="J8" t="n">
-        <v>3.95</v>
+        <v>4</v>
       </c>
       <c r="K8" t="n">
-        <v>4.2</v>
+        <v>4.1</v>
       </c>
       <c r="L8" t="n">
         <v>1.36</v>
       </c>
       <c r="M8" t="n">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="N8" t="n">
-        <v>4.4</v>
+        <v>4.3</v>
       </c>
       <c r="O8" t="n">
         <v>1.26</v>
       </c>
       <c r="P8" t="n">
-        <v>2.16</v>
+        <v>2.14</v>
       </c>
       <c r="Q8" t="n">
-        <v>1.78</v>
+        <v>1.8</v>
       </c>
       <c r="R8" t="n">
-        <v>1.45</v>
+        <v>1.44</v>
       </c>
       <c r="S8" t="n">
-        <v>3</v>
+        <v>3.1</v>
       </c>
       <c r="T8" t="n">
-        <v>1.74</v>
+        <v>1.73</v>
       </c>
       <c r="U8" t="n">
-        <v>2.14</v>
+        <v>2.18</v>
       </c>
       <c r="V8" t="n">
         <v>1.27</v>
@@ -2435,13 +2435,13 @@
         <v>2.08</v>
       </c>
       <c r="X8" t="n">
-        <v>17.5</v>
+        <v>19</v>
       </c>
       <c r="Y8" t="n">
-        <v>18</v>
+        <v>18.5</v>
       </c>
       <c r="Z8" t="n">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="AA8" t="n">
         <v>110</v>
@@ -2453,7 +2453,7 @@
         <v>9.4</v>
       </c>
       <c r="AD8" t="n">
-        <v>18</v>
+        <v>17.5</v>
       </c>
       <c r="AE8" t="n">
         <v>55</v>
@@ -2462,7 +2462,7 @@
         <v>12</v>
       </c>
       <c r="AG8" t="n">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="AH8" t="n">
         <v>19</v>
@@ -2477,10 +2477,10 @@
         <v>19</v>
       </c>
       <c r="AL8" t="n">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="AM8" t="n">
-        <v>95</v>
+        <v>90</v>
       </c>
       <c r="AN8" t="n">
         <v>11</v>
@@ -2489,28 +2489,28 @@
         <v>55</v>
       </c>
       <c r="AP8" t="n">
-        <v>16</v>
+        <v>16.5</v>
       </c>
       <c r="AQ8" t="n">
-        <v>16</v>
+        <v>16.5</v>
       </c>
       <c r="AR8" t="n">
         <v>30</v>
       </c>
       <c r="AS8" t="n">
-        <v>30</v>
+        <v>75</v>
       </c>
       <c r="AT8" t="n">
-        <v>9.4</v>
+        <v>9</v>
       </c>
       <c r="AU8" t="n">
-        <v>8.4</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AV8" t="n">
-        <v>16</v>
+        <v>15.5</v>
       </c>
       <c r="AW8" t="n">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="AX8" t="n">
         <v>10.5</v>
@@ -2540,7 +2540,7 @@
         <v>9.6</v>
       </c>
       <c r="BG8" t="n">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="BH8" t="n">
         <v>3.85</v>
@@ -2552,7 +2552,7 @@
         <v>9.800000000000001</v>
       </c>
       <c r="BK8" t="n">
-        <v>5.4</v>
+        <v>5.3</v>
       </c>
       <c r="BL8" t="n">
         <v>1000</v>
@@ -2567,44 +2567,44 @@
         <v>3.6</v>
       </c>
       <c r="BP8" t="n">
-        <v>12.5</v>
+        <v>13</v>
       </c>
       <c r="BQ8" t="n">
-        <v>6</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BR8" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="BS8" t="n">
         <v>8</v>
       </c>
       <c r="BT8" t="n">
-        <v>8.4</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BU8" t="n">
-        <v>6</v>
+        <v>4.8</v>
       </c>
       <c r="BV8" t="n">
-        <v>1000</v>
+        <v>36</v>
       </c>
       <c r="BW8" t="n">
-        <v>9</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BX8" t="n">
-        <v>1000</v>
+        <v>44</v>
       </c>
       <c r="BY8" t="n">
-        <v>9.4</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BZ8" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="CA8" t="n">
         <v>7.4</v>
       </c>
       <c r="CB8" t="inlineStr">
         <is>
-          <t>2026-06-12 07:41:10</t>
+          <t>2026-06-12 09:58:55</t>
         </is>
       </c>
     </row>
@@ -2635,19 +2635,19 @@
         </is>
       </c>
       <c r="F9" t="n">
-        <v>4.5</v>
+        <v>4.9</v>
       </c>
       <c r="G9" t="n">
-        <v>5.2</v>
+        <v>5.8</v>
       </c>
       <c r="H9" t="n">
-        <v>1.7</v>
+        <v>1.66</v>
       </c>
       <c r="I9" t="n">
-        <v>1.8</v>
+        <v>1.74</v>
       </c>
       <c r="J9" t="n">
-        <v>4.2</v>
+        <v>4.3</v>
       </c>
       <c r="K9" t="n">
         <v>4.8</v>
@@ -2659,34 +2659,34 @@
         <v>1.03</v>
       </c>
       <c r="N9" t="n">
-        <v>5.7</v>
+        <v>5.8</v>
       </c>
       <c r="O9" t="n">
-        <v>1.18</v>
+        <v>1.17</v>
       </c>
       <c r="P9" t="n">
-        <v>2.6</v>
+        <v>2.64</v>
       </c>
       <c r="Q9" t="n">
-        <v>1.53</v>
+        <v>1.54</v>
       </c>
       <c r="R9" t="n">
-        <v>1.64</v>
+        <v>1.65</v>
       </c>
       <c r="S9" t="n">
         <v>2.36</v>
       </c>
       <c r="T9" t="n">
-        <v>1.55</v>
+        <v>1.58</v>
       </c>
       <c r="U9" t="n">
-        <v>2.44</v>
+        <v>2.48</v>
       </c>
       <c r="V9" t="n">
-        <v>2.24</v>
+        <v>2.34</v>
       </c>
       <c r="W9" t="n">
-        <v>1.23</v>
+        <v>1.22</v>
       </c>
       <c r="X9" t="n">
         <v>42</v>
@@ -2695,10 +2695,10 @@
         <v>13.5</v>
       </c>
       <c r="Z9" t="n">
-        <v>14</v>
+        <v>13.5</v>
       </c>
       <c r="AA9" t="n">
-        <v>32</v>
+        <v>19</v>
       </c>
       <c r="AB9" t="n">
         <v>38</v>
@@ -2707,16 +2707,16 @@
         <v>11</v>
       </c>
       <c r="AD9" t="n">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="AE9" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="AF9" t="n">
         <v>220</v>
       </c>
       <c r="AG9" t="n">
-        <v>34</v>
+        <v>22</v>
       </c>
       <c r="AH9" t="n">
         <v>17.5</v>
@@ -2734,13 +2734,13 @@
         <v>120</v>
       </c>
       <c r="AM9" t="n">
-        <v>500</v>
+        <v>580</v>
       </c>
       <c r="AN9" t="n">
         <v>140</v>
       </c>
       <c r="AO9" t="n">
-        <v>7.6</v>
+        <v>7</v>
       </c>
       <c r="AP9" t="n">
         <v>21</v>
@@ -2761,16 +2761,16 @@
         <v>9</v>
       </c>
       <c r="AV9" t="n">
-        <v>9.199999999999999</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AW9" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="AX9" t="n">
         <v>20</v>
       </c>
       <c r="AY9" t="n">
-        <v>16.5</v>
+        <v>11</v>
       </c>
       <c r="AZ9" t="n">
         <v>14</v>
@@ -2779,7 +2779,7 @@
         <v>15</v>
       </c>
       <c r="BB9" t="n">
-        <v>8.800000000000001</v>
+        <v>10</v>
       </c>
       <c r="BC9" t="n">
         <v>23</v>
@@ -2788,58 +2788,58 @@
         <v>23</v>
       </c>
       <c r="BE9" t="n">
-        <v>20</v>
+        <v>9.4</v>
       </c>
       <c r="BF9" t="n">
-        <v>8.4</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BG9" t="n">
-        <v>6.2</v>
+        <v>6</v>
       </c>
       <c r="BH9" t="n">
         <v>4.7</v>
       </c>
       <c r="BI9" t="n">
-        <v>3.6</v>
+        <v>3.65</v>
       </c>
       <c r="BJ9" t="n">
-        <v>9.4</v>
+        <v>9.6</v>
       </c>
       <c r="BK9" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="BL9" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BM9" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="BN9" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="BO9" t="n">
         <v>4.8</v>
       </c>
-      <c r="BL9" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BM9" t="n">
-        <v>8.800000000000001</v>
-      </c>
-      <c r="BN9" t="n">
-        <v>9</v>
-      </c>
-      <c r="BO9" t="n">
-        <v>4.7</v>
-      </c>
       <c r="BP9" t="n">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="BQ9" t="n">
-        <v>7.8</v>
+        <v>8</v>
       </c>
       <c r="BR9" t="n">
         <v>1000</v>
       </c>
       <c r="BS9" t="n">
-        <v>7.8</v>
+        <v>8</v>
       </c>
       <c r="BT9" t="n">
-        <v>5</v>
+        <v>4.9</v>
       </c>
       <c r="BU9" t="n">
-        <v>3.3</v>
+        <v>3.8</v>
       </c>
       <c r="BV9" t="n">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="BW9" t="n">
         <v>5.3</v>
@@ -2848,7 +2848,7 @@
         <v>21</v>
       </c>
       <c r="BY9" t="n">
-        <v>6.6</v>
+        <v>6.8</v>
       </c>
       <c r="BZ9" t="n">
         <v>0</v>
@@ -2858,7 +2858,7 @@
       </c>
       <c r="CB9" t="inlineStr">
         <is>
-          <t>2026-06-12 07:41:10</t>
+          <t>2026-06-12 09:58:55</t>
         </is>
       </c>
     </row>
@@ -2889,22 +2889,22 @@
         </is>
       </c>
       <c r="F10" t="n">
-        <v>1.55</v>
+        <v>1.56</v>
       </c>
       <c r="G10" t="n">
-        <v>1.59</v>
+        <v>1.64</v>
       </c>
       <c r="H10" t="n">
-        <v>5.7</v>
+        <v>5.4</v>
       </c>
       <c r="I10" t="n">
-        <v>7</v>
+        <v>6.6</v>
       </c>
       <c r="J10" t="n">
-        <v>4.6</v>
+        <v>4.4</v>
       </c>
       <c r="K10" t="n">
-        <v>5.5</v>
+        <v>5.3</v>
       </c>
       <c r="L10" t="n">
         <v>1.27</v>
@@ -2916,37 +2916,37 @@
         <v>5.8</v>
       </c>
       <c r="O10" t="n">
-        <v>1.17</v>
+        <v>1.18</v>
       </c>
       <c r="P10" t="n">
-        <v>2.74</v>
+        <v>2.66</v>
       </c>
       <c r="Q10" t="n">
-        <v>1.5</v>
+        <v>1.52</v>
       </c>
       <c r="R10" t="n">
-        <v>1.68</v>
+        <v>1.66</v>
       </c>
       <c r="S10" t="n">
-        <v>2.28</v>
+        <v>2.34</v>
       </c>
       <c r="T10" t="n">
-        <v>1.65</v>
+        <v>1.61</v>
       </c>
       <c r="U10" t="n">
-        <v>2.26</v>
+        <v>2.3</v>
       </c>
       <c r="V10" t="n">
-        <v>1.16</v>
+        <v>1.18</v>
       </c>
       <c r="W10" t="n">
-        <v>2.66</v>
+        <v>2.52</v>
       </c>
       <c r="X10" t="n">
+        <v>42</v>
+      </c>
+      <c r="Y10" t="n">
         <v>44</v>
-      </c>
-      <c r="Y10" t="n">
-        <v>70</v>
       </c>
       <c r="Z10" t="n">
         <v>220</v>
@@ -2955,19 +2955,19 @@
         <v>700</v>
       </c>
       <c r="AB10" t="n">
-        <v>13</v>
+        <v>13.5</v>
       </c>
       <c r="AC10" t="n">
         <v>12</v>
       </c>
       <c r="AD10" t="n">
-        <v>36</v>
+        <v>24</v>
       </c>
       <c r="AE10" t="n">
-        <v>700</v>
+        <v>200</v>
       </c>
       <c r="AF10" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AG10" t="n">
         <v>11</v>
@@ -2979,10 +2979,10 @@
         <v>160</v>
       </c>
       <c r="AJ10" t="n">
-        <v>15.5</v>
+        <v>17</v>
       </c>
       <c r="AK10" t="n">
-        <v>15.5</v>
+        <v>16</v>
       </c>
       <c r="AL10" t="n">
         <v>48</v>
@@ -2991,7 +2991,7 @@
         <v>580</v>
       </c>
       <c r="AN10" t="n">
-        <v>6</v>
+        <v>6.4</v>
       </c>
       <c r="AO10" t="n">
         <v>700</v>
@@ -3000,13 +3000,13 @@
         <v>13.5</v>
       </c>
       <c r="AQ10" t="n">
-        <v>13</v>
+        <v>23</v>
       </c>
       <c r="AR10" t="n">
-        <v>38</v>
+        <v>20</v>
       </c>
       <c r="AS10" t="n">
-        <v>9</v>
+        <v>36</v>
       </c>
       <c r="AT10" t="n">
         <v>10</v>
@@ -3015,10 +3015,10 @@
         <v>9.4</v>
       </c>
       <c r="AV10" t="n">
-        <v>20</v>
+        <v>11.5</v>
       </c>
       <c r="AW10" t="n">
-        <v>9.800000000000001</v>
+        <v>23</v>
       </c>
       <c r="AX10" t="n">
         <v>10</v>
@@ -3030,10 +3030,10 @@
         <v>16</v>
       </c>
       <c r="BA10" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="BB10" t="n">
-        <v>12.5</v>
+        <v>13.5</v>
       </c>
       <c r="BC10" t="n">
         <v>12</v>
@@ -3042,43 +3042,43 @@
         <v>13.5</v>
       </c>
       <c r="BE10" t="n">
-        <v>28</v>
+        <v>7.8</v>
       </c>
       <c r="BF10" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="BG10" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="BH10" t="n">
         <v>4.8</v>
       </c>
-      <c r="BG10" t="n">
-        <v>8.4</v>
-      </c>
-      <c r="BH10" t="n">
-        <v>4.9</v>
-      </c>
       <c r="BI10" t="n">
-        <v>3.6</v>
+        <v>3.55</v>
       </c>
       <c r="BJ10" t="n">
+        <v>10</v>
+      </c>
+      <c r="BK10" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="BL10" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BM10" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="BN10" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="BO10" t="n">
+        <v>3.55</v>
+      </c>
+      <c r="BP10" t="n">
         <v>10.5</v>
       </c>
-      <c r="BK10" t="n">
+      <c r="BQ10" t="n">
         <v>4.8</v>
-      </c>
-      <c r="BL10" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BM10" t="n">
-        <v>8</v>
-      </c>
-      <c r="BN10" t="n">
-        <v>4.7</v>
-      </c>
-      <c r="BO10" t="n">
-        <v>3.45</v>
-      </c>
-      <c r="BP10" t="n">
-        <v>9.6</v>
-      </c>
-      <c r="BQ10" t="n">
-        <v>4.6</v>
       </c>
       <c r="BR10" t="n">
         <v>21</v>
@@ -3087,10 +3087,10 @@
         <v>6.2</v>
       </c>
       <c r="BT10" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="BU10" t="n">
-        <v>4.9</v>
+        <v>4.7</v>
       </c>
       <c r="BV10" t="n">
         <v>1000</v>
@@ -3105,14 +3105,14 @@
         <v>7.4</v>
       </c>
       <c r="BZ10" t="n">
-        <v>12.5</v>
+        <v>13.5</v>
       </c>
       <c r="CA10" t="n">
-        <v>5.2</v>
+        <v>5.4</v>
       </c>
       <c r="CB10" t="inlineStr">
         <is>
-          <t>2026-06-12 07:41:10</t>
+          <t>2026-06-12 09:58:55</t>
         </is>
       </c>
     </row>
@@ -3143,19 +3143,19 @@
         </is>
       </c>
       <c r="F11" t="n">
-        <v>2.3</v>
+        <v>2.28</v>
       </c>
       <c r="G11" t="n">
-        <v>2.4</v>
+        <v>2.42</v>
       </c>
       <c r="H11" t="n">
-        <v>4.1</v>
+        <v>4</v>
       </c>
       <c r="I11" t="n">
         <v>4.5</v>
       </c>
       <c r="J11" t="n">
-        <v>2.8</v>
+        <v>2.86</v>
       </c>
       <c r="K11" t="n">
         <v>3.05</v>
@@ -3164,31 +3164,31 @@
         <v>1.62</v>
       </c>
       <c r="M11" t="n">
-        <v>1.15</v>
+        <v>1.13</v>
       </c>
       <c r="N11" t="n">
-        <v>2.56</v>
+        <v>2.54</v>
       </c>
       <c r="O11" t="n">
-        <v>1.59</v>
+        <v>1.6</v>
       </c>
       <c r="P11" t="n">
-        <v>1.48</v>
+        <v>1.46</v>
       </c>
       <c r="Q11" t="n">
-        <v>2.86</v>
+        <v>2.96</v>
       </c>
       <c r="R11" t="n">
-        <v>1.17</v>
+        <v>1.16</v>
       </c>
       <c r="S11" t="n">
-        <v>6</v>
+        <v>6.4</v>
       </c>
       <c r="T11" t="n">
-        <v>2.14</v>
+        <v>2.16</v>
       </c>
       <c r="U11" t="n">
-        <v>1.11</v>
+        <v>1.73</v>
       </c>
       <c r="V11" t="n">
         <v>1.29</v>
@@ -3212,7 +3212,7 @@
         <v>970</v>
       </c>
       <c r="AC11" t="n">
-        <v>42</v>
+        <v>970</v>
       </c>
       <c r="AD11" t="n">
         <v>970</v>
@@ -3254,13 +3254,13 @@
         <v>4.4</v>
       </c>
       <c r="AQ11" t="n">
-        <v>10.5</v>
+        <v>5.6</v>
       </c>
       <c r="AR11" t="n">
-        <v>2.24</v>
+        <v>2.4</v>
       </c>
       <c r="AS11" t="n">
-        <v>1.62</v>
+        <v>1.52</v>
       </c>
       <c r="AT11" t="n">
         <v>3.85</v>
@@ -3272,7 +3272,7 @@
         <v>9</v>
       </c>
       <c r="AW11" t="n">
-        <v>1.62</v>
+        <v>1.51</v>
       </c>
       <c r="AX11" t="n">
         <v>5.7</v>
@@ -3281,46 +3281,46 @@
         <v>6.4</v>
       </c>
       <c r="AZ11" t="n">
-        <v>2.18</v>
+        <v>2.34</v>
       </c>
       <c r="BA11" t="n">
-        <v>1.62</v>
+        <v>1.52</v>
       </c>
       <c r="BB11" t="n">
-        <v>2.24</v>
+        <v>2.4</v>
       </c>
       <c r="BC11" t="n">
-        <v>2.16</v>
+        <v>2.36</v>
       </c>
       <c r="BD11" t="n">
-        <v>1.61</v>
+        <v>1.51</v>
       </c>
       <c r="BE11" t="n">
-        <v>1.63</v>
+        <v>1.72</v>
       </c>
       <c r="BF11" t="n">
-        <v>1.58</v>
+        <v>1.55</v>
       </c>
       <c r="BG11" t="n">
-        <v>1.63</v>
+        <v>1.55</v>
       </c>
       <c r="BH11" t="n">
         <v>2.68</v>
       </c>
       <c r="BI11" t="n">
-        <v>2.22</v>
+        <v>2.26</v>
       </c>
       <c r="BJ11" t="n">
         <v>12</v>
       </c>
       <c r="BK11" t="n">
-        <v>6.2</v>
+        <v>6.4</v>
       </c>
       <c r="BL11" t="n">
         <v>1000</v>
       </c>
       <c r="BM11" t="n">
-        <v>12.5</v>
+        <v>13.5</v>
       </c>
       <c r="BN11" t="n">
         <v>5</v>
@@ -3332,41 +3332,41 @@
         <v>21</v>
       </c>
       <c r="BQ11" t="n">
-        <v>8.199999999999999</v>
+        <v>8.6</v>
       </c>
       <c r="BR11" t="n">
         <v>1000</v>
       </c>
       <c r="BS11" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="BT11" t="n">
-        <v>7.2</v>
+        <v>7</v>
       </c>
       <c r="BU11" t="n">
-        <v>5.2</v>
+        <v>5.3</v>
       </c>
       <c r="BV11" t="n">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="BW11" t="n">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="BX11" t="n">
         <v>1000</v>
       </c>
       <c r="BY11" t="n">
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="BZ11" t="n">
         <v>55</v>
       </c>
       <c r="CA11" t="n">
-        <v>10.5</v>
+        <v>11.5</v>
       </c>
       <c r="CB11" t="inlineStr">
         <is>
-          <t>2026-06-12 07:41:10</t>
+          <t>2026-06-12 09:58:55</t>
         </is>
       </c>
     </row>
@@ -3397,64 +3397,64 @@
         </is>
       </c>
       <c r="F12" t="n">
-        <v>2.2</v>
+        <v>2.18</v>
       </c>
       <c r="G12" t="n">
-        <v>2.4</v>
+        <v>2.34</v>
       </c>
       <c r="H12" t="n">
-        <v>3.15</v>
+        <v>3.2</v>
       </c>
       <c r="I12" t="n">
         <v>3.55</v>
       </c>
       <c r="J12" t="n">
-        <v>3.55</v>
+        <v>3.7</v>
       </c>
       <c r="K12" t="n">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="L12" t="n">
-        <v>1.33</v>
+        <v>1.3</v>
       </c>
       <c r="M12" t="n">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="N12" t="n">
-        <v>4.7</v>
+        <v>5.3</v>
       </c>
       <c r="O12" t="n">
-        <v>1.24</v>
+        <v>1.2</v>
       </c>
       <c r="P12" t="n">
-        <v>2.32</v>
+        <v>2.46</v>
       </c>
       <c r="Q12" t="n">
-        <v>1.69</v>
+        <v>1.61</v>
       </c>
       <c r="R12" t="n">
-        <v>1.48</v>
+        <v>1.58</v>
       </c>
       <c r="S12" t="n">
-        <v>2.78</v>
+        <v>2.54</v>
       </c>
       <c r="T12" t="n">
-        <v>1.6</v>
+        <v>1.53</v>
       </c>
       <c r="U12" t="n">
-        <v>2.32</v>
+        <v>2.5</v>
       </c>
       <c r="V12" t="n">
         <v>1.4</v>
       </c>
       <c r="W12" t="n">
-        <v>1.72</v>
+        <v>1.75</v>
       </c>
       <c r="X12" t="n">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="Y12" t="n">
-        <v>16.5</v>
+        <v>19</v>
       </c>
       <c r="Z12" t="n">
         <v>29</v>
@@ -3463,10 +3463,10 @@
         <v>85</v>
       </c>
       <c r="AB12" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="AC12" t="n">
-        <v>9.4</v>
+        <v>10</v>
       </c>
       <c r="AD12" t="n">
         <v>15</v>
@@ -3475,118 +3475,118 @@
         <v>44</v>
       </c>
       <c r="AF12" t="n">
-        <v>17.5</v>
+        <v>18.5</v>
       </c>
       <c r="AG12" t="n">
         <v>12</v>
       </c>
       <c r="AH12" t="n">
-        <v>16.5</v>
+        <v>16</v>
       </c>
       <c r="AI12" t="n">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="AJ12" t="n">
-        <v>55</v>
+        <v>32</v>
       </c>
       <c r="AK12" t="n">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="AL12" t="n">
         <v>38</v>
       </c>
       <c r="AM12" t="n">
-        <v>90</v>
+        <v>200</v>
       </c>
       <c r="AN12" t="n">
-        <v>15</v>
+        <v>12.5</v>
       </c>
       <c r="AO12" t="n">
-        <v>28</v>
+        <v>22</v>
       </c>
       <c r="AP12" t="n">
         <v>16</v>
       </c>
       <c r="AQ12" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="AR12" t="n">
         <v>20</v>
       </c>
       <c r="AS12" t="n">
-        <v>8.4</v>
+        <v>9.6</v>
       </c>
       <c r="AT12" t="n">
         <v>10</v>
       </c>
       <c r="AU12" t="n">
-        <v>7.4</v>
+        <v>7.8</v>
       </c>
       <c r="AV12" t="n">
         <v>12</v>
       </c>
       <c r="AW12" t="n">
-        <v>13</v>
+        <v>26</v>
       </c>
       <c r="AX12" t="n">
-        <v>13.5</v>
+        <v>14.5</v>
       </c>
       <c r="AY12" t="n">
         <v>9.6</v>
       </c>
       <c r="AZ12" t="n">
-        <v>13</v>
+        <v>12.5</v>
       </c>
       <c r="BA12" t="n">
         <v>18</v>
       </c>
       <c r="BB12" t="n">
-        <v>24</v>
+        <v>13.5</v>
       </c>
       <c r="BC12" t="n">
-        <v>18.5</v>
+        <v>17.5</v>
       </c>
       <c r="BD12" t="n">
-        <v>23</v>
+        <v>15</v>
       </c>
       <c r="BE12" t="n">
-        <v>46</v>
+        <v>27</v>
       </c>
       <c r="BF12" t="n">
-        <v>12</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BG12" t="n">
-        <v>12</v>
+        <v>17.5</v>
       </c>
       <c r="BH12" t="n">
-        <v>4.1</v>
+        <v>4.5</v>
       </c>
       <c r="BI12" t="n">
-        <v>3.05</v>
+        <v>3.4</v>
       </c>
       <c r="BJ12" t="n">
-        <v>9.4</v>
+        <v>9</v>
       </c>
       <c r="BK12" t="n">
-        <v>6.8</v>
+        <v>6.6</v>
       </c>
       <c r="BL12" t="n">
         <v>1000</v>
       </c>
       <c r="BM12" t="n">
-        <v>8.4</v>
+        <v>8.6</v>
       </c>
       <c r="BN12" t="n">
-        <v>5.7</v>
+        <v>5.8</v>
       </c>
       <c r="BO12" t="n">
-        <v>4.6</v>
+        <v>4.3</v>
       </c>
       <c r="BP12" t="n">
-        <v>16.5</v>
+        <v>16</v>
       </c>
       <c r="BQ12" t="n">
-        <v>5.9</v>
+        <v>6</v>
       </c>
       <c r="BR12" t="n">
         <v>1000</v>
@@ -3595,13 +3595,13 @@
         <v>6.8</v>
       </c>
       <c r="BT12" t="n">
-        <v>7</v>
+        <v>7.2</v>
       </c>
       <c r="BU12" t="n">
-        <v>5.6</v>
+        <v>5.8</v>
       </c>
       <c r="BV12" t="n">
-        <v>25</v>
+        <v>1000</v>
       </c>
       <c r="BW12" t="n">
         <v>6.8</v>
@@ -3613,14 +3613,14 @@
         <v>7.2</v>
       </c>
       <c r="BZ12" t="n">
-        <v>21</v>
+        <v>17</v>
       </c>
       <c r="CA12" t="n">
-        <v>6.4</v>
+        <v>6.2</v>
       </c>
       <c r="CB12" t="inlineStr">
         <is>
-          <t>2026-06-12 07:41:10</t>
+          <t>2026-06-12 09:58:55</t>
         </is>
       </c>
     </row>
@@ -3651,58 +3651,58 @@
         </is>
       </c>
       <c r="F13" t="n">
-        <v>1.2</v>
+        <v>1.19</v>
       </c>
       <c r="G13" t="n">
-        <v>1.23</v>
+        <v>1.22</v>
       </c>
       <c r="H13" t="n">
-        <v>15</v>
+        <v>14.5</v>
       </c>
       <c r="I13" t="n">
-        <v>21</v>
+        <v>19.5</v>
       </c>
       <c r="J13" t="n">
-        <v>8.199999999999999</v>
+        <v>8.4</v>
       </c>
       <c r="K13" t="n">
         <v>10</v>
       </c>
       <c r="L13" t="n">
-        <v>1.21</v>
+        <v>1.2</v>
       </c>
       <c r="M13" t="n">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="N13" t="n">
-        <v>7.6</v>
+        <v>8</v>
       </c>
       <c r="O13" t="n">
         <v>1.12</v>
       </c>
       <c r="P13" t="n">
-        <v>3.35</v>
+        <v>3.4</v>
       </c>
       <c r="Q13" t="n">
-        <v>1.38</v>
+        <v>1.37</v>
       </c>
       <c r="R13" t="n">
-        <v>1.96</v>
+        <v>1.98</v>
       </c>
       <c r="S13" t="n">
         <v>1.93</v>
       </c>
       <c r="T13" t="n">
-        <v>1.98</v>
+        <v>2</v>
       </c>
       <c r="U13" t="n">
         <v>1.81</v>
       </c>
       <c r="V13" t="n">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="W13" t="n">
-        <v>5.3</v>
+        <v>5.5</v>
       </c>
       <c r="X13" t="n">
         <v>950</v>
@@ -3720,13 +3720,13 @@
         <v>14</v>
       </c>
       <c r="AC13" t="n">
-        <v>24</v>
+        <v>950</v>
       </c>
       <c r="AD13" t="n">
         <v>950</v>
       </c>
       <c r="AE13" t="n">
-        <v>260</v>
+        <v>250</v>
       </c>
       <c r="AF13" t="n">
         <v>10.5</v>
@@ -3738,52 +3738,52 @@
         <v>950</v>
       </c>
       <c r="AI13" t="n">
-        <v>180</v>
+        <v>170</v>
       </c>
       <c r="AJ13" t="n">
         <v>10.5</v>
       </c>
       <c r="AK13" t="n">
-        <v>14.5</v>
+        <v>17.5</v>
       </c>
       <c r="AL13" t="n">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="AM13" t="n">
-        <v>170</v>
+        <v>160</v>
       </c>
       <c r="AN13" t="n">
-        <v>3.15</v>
+        <v>3.1</v>
       </c>
       <c r="AO13" t="n">
-        <v>240</v>
+        <v>250</v>
       </c>
       <c r="AP13" t="n">
+        <v>10</v>
+      </c>
+      <c r="AQ13" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="AR13" t="n">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="AS13" t="n">
+        <v>10</v>
+      </c>
+      <c r="AT13" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="AU13" t="n">
+        <v>17.5</v>
+      </c>
+      <c r="AV13" t="n">
         <v>9</v>
       </c>
-      <c r="AQ13" t="n">
-        <v>8.4</v>
-      </c>
-      <c r="AR13" t="n">
+      <c r="AW13" t="n">
+        <v>10</v>
+      </c>
+      <c r="AX13" t="n">
         <v>8.6</v>
-      </c>
-      <c r="AS13" t="n">
-        <v>9</v>
-      </c>
-      <c r="AT13" t="n">
-        <v>11</v>
-      </c>
-      <c r="AU13" t="n">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="AV13" t="n">
-        <v>8.800000000000001</v>
-      </c>
-      <c r="AW13" t="n">
-        <v>8.800000000000001</v>
-      </c>
-      <c r="AX13" t="n">
-        <v>7.8</v>
       </c>
       <c r="AY13" t="n">
         <v>10.5</v>
@@ -3792,7 +3792,7 @@
         <v>14.5</v>
       </c>
       <c r="BA13" t="n">
-        <v>8.6</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BB13" t="n">
         <v>8.4</v>
@@ -3804,43 +3804,43 @@
         <v>17.5</v>
       </c>
       <c r="BE13" t="n">
-        <v>9</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BF13" t="n">
         <v>2.8</v>
       </c>
       <c r="BG13" t="n">
-        <v>9.6</v>
+        <v>10</v>
       </c>
       <c r="BH13" t="n">
         <v>6</v>
       </c>
       <c r="BI13" t="n">
-        <v>4.5</v>
+        <v>4.6</v>
       </c>
       <c r="BJ13" t="n">
-        <v>12.5</v>
+        <v>13</v>
       </c>
       <c r="BK13" t="n">
-        <v>9.199999999999999</v>
+        <v>5.7</v>
       </c>
       <c r="BL13" t="n">
         <v>1000</v>
       </c>
       <c r="BM13" t="n">
-        <v>9.199999999999999</v>
+        <v>9.4</v>
       </c>
       <c r="BN13" t="n">
         <v>4.3</v>
       </c>
       <c r="BO13" t="n">
-        <v>3.35</v>
+        <v>3.6</v>
       </c>
       <c r="BP13" t="n">
-        <v>6.8</v>
+        <v>6.6</v>
       </c>
       <c r="BQ13" t="n">
-        <v>5.2</v>
+        <v>5.4</v>
       </c>
       <c r="BR13" t="n">
         <v>19.5</v>
@@ -3870,11 +3870,11 @@
         <v>7.2</v>
       </c>
       <c r="CA13" t="n">
-        <v>4.2</v>
+        <v>5.8</v>
       </c>
       <c r="CB13" t="inlineStr">
         <is>
-          <t>2026-06-12 07:41:10</t>
+          <t>2026-06-12 09:58:55</t>
         </is>
       </c>
     </row>
@@ -3911,7 +3911,7 @@
         <v>3.15</v>
       </c>
       <c r="H14" t="n">
-        <v>2.52</v>
+        <v>2.48</v>
       </c>
       <c r="I14" t="n">
         <v>2.6</v>
@@ -3929,19 +3929,19 @@
         <v>1.08</v>
       </c>
       <c r="N14" t="n">
-        <v>3.4</v>
+        <v>3.45</v>
       </c>
       <c r="O14" t="n">
         <v>1.37</v>
       </c>
       <c r="P14" t="n">
-        <v>1.83</v>
+        <v>1.81</v>
       </c>
       <c r="Q14" t="n">
         <v>2.1</v>
       </c>
       <c r="R14" t="n">
-        <v>1.31</v>
+        <v>1.32</v>
       </c>
       <c r="S14" t="n">
         <v>3.9</v>
@@ -3950,13 +3950,13 @@
         <v>1.8</v>
       </c>
       <c r="U14" t="n">
-        <v>2.08</v>
+        <v>2.12</v>
       </c>
       <c r="V14" t="n">
-        <v>1.62</v>
+        <v>1.63</v>
       </c>
       <c r="W14" t="n">
-        <v>1.47</v>
+        <v>1.46</v>
       </c>
       <c r="X14" t="n">
         <v>12.5</v>
@@ -3965,25 +3965,25 @@
         <v>10.5</v>
       </c>
       <c r="Z14" t="n">
-        <v>17.5</v>
+        <v>17</v>
       </c>
       <c r="AA14" t="n">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="AB14" t="n">
         <v>11.5</v>
       </c>
       <c r="AC14" t="n">
-        <v>7.6</v>
+        <v>7.8</v>
       </c>
       <c r="AD14" t="n">
         <v>12.5</v>
       </c>
       <c r="AE14" t="n">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="AF14" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AG14" t="n">
         <v>13.5</v>
@@ -4007,10 +4007,10 @@
         <v>110</v>
       </c>
       <c r="AN14" t="n">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="AO14" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="AP14" t="n">
         <v>11</v>
@@ -4088,7 +4088,7 @@
         <v>6.4</v>
       </c>
       <c r="BO14" t="n">
-        <v>5.5</v>
+        <v>4.8</v>
       </c>
       <c r="BP14" t="n">
         <v>27</v>
@@ -4128,7 +4128,7 @@
       </c>
       <c r="CB14" t="inlineStr">
         <is>
-          <t>2026-06-12 07:41:10</t>
+          <t>2026-06-12 09:58:55</t>
         </is>
       </c>
     </row>
@@ -4159,230 +4159,230 @@
         </is>
       </c>
       <c r="F15" t="n">
-        <v>2.44</v>
+        <v>1.74</v>
       </c>
       <c r="G15" t="n">
-        <v>2.64</v>
+        <v>1.8</v>
       </c>
       <c r="H15" t="n">
-        <v>3.5</v>
+        <v>5.6</v>
       </c>
       <c r="I15" t="n">
-        <v>3.85</v>
+        <v>6.2</v>
       </c>
       <c r="J15" t="n">
-        <v>2.86</v>
+        <v>3.7</v>
       </c>
       <c r="K15" t="n">
-        <v>3.1</v>
+        <v>3.95</v>
       </c>
       <c r="L15" t="n">
-        <v>1.64</v>
+        <v>1.58</v>
       </c>
       <c r="M15" t="n">
-        <v>1.15</v>
+        <v>1.12</v>
       </c>
       <c r="N15" t="n">
-        <v>2.44</v>
+        <v>2.66</v>
       </c>
       <c r="O15" t="n">
-        <v>1.62</v>
+        <v>1.54</v>
       </c>
       <c r="P15" t="n">
-        <v>1.46</v>
+        <v>1.55</v>
       </c>
       <c r="Q15" t="n">
-        <v>2.92</v>
+        <v>2.62</v>
       </c>
       <c r="R15" t="n">
-        <v>1.17</v>
+        <v>1.19</v>
       </c>
       <c r="S15" t="n">
-        <v>6.2</v>
+        <v>5.5</v>
       </c>
       <c r="T15" t="n">
-        <v>2.2</v>
+        <v>2.34</v>
       </c>
       <c r="U15" t="n">
-        <v>1.7</v>
+        <v>1.6</v>
       </c>
       <c r="V15" t="n">
-        <v>1.35</v>
+        <v>1.2</v>
       </c>
       <c r="W15" t="n">
-        <v>1.61</v>
+        <v>2.24</v>
       </c>
       <c r="X15" t="n">
-        <v>7.8</v>
+        <v>9.6</v>
       </c>
       <c r="Y15" t="n">
-        <v>9.800000000000001</v>
+        <v>14</v>
       </c>
       <c r="Z15" t="n">
-        <v>26</v>
+        <v>46</v>
       </c>
       <c r="AA15" t="n">
         <v>900</v>
       </c>
       <c r="AB15" t="n">
-        <v>7.4</v>
+        <v>6.8</v>
       </c>
       <c r="AC15" t="n">
-        <v>7.4</v>
+        <v>9</v>
       </c>
       <c r="AD15" t="n">
-        <v>18</v>
+        <v>25</v>
       </c>
       <c r="AE15" t="n">
-        <v>440</v>
+        <v>160</v>
       </c>
       <c r="AF15" t="n">
-        <v>15</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AG15" t="n">
-        <v>13.5</v>
+        <v>12</v>
       </c>
       <c r="AH15" t="n">
-        <v>65</v>
+        <v>38</v>
       </c>
       <c r="AI15" t="n">
-        <v>540</v>
+        <v>500</v>
       </c>
       <c r="AJ15" t="n">
-        <v>170</v>
+        <v>19</v>
       </c>
       <c r="AK15" t="n">
-        <v>140</v>
+        <v>25</v>
       </c>
       <c r="AL15" t="n">
-        <v>500</v>
+        <v>70</v>
       </c>
       <c r="AM15" t="n">
         <v>500</v>
       </c>
       <c r="AN15" t="n">
-        <v>600</v>
+        <v>19.5</v>
       </c>
       <c r="AO15" t="n">
-        <v>600</v>
+        <v>360</v>
       </c>
       <c r="AP15" t="n">
-        <v>6.6</v>
+        <v>8</v>
       </c>
       <c r="AQ15" t="n">
-        <v>8.199999999999999</v>
+        <v>11.5</v>
       </c>
       <c r="AR15" t="n">
+        <v>28</v>
+      </c>
+      <c r="AS15" t="n">
+        <v>11</v>
+      </c>
+      <c r="AT15" t="n">
+        <v>5.6</v>
+      </c>
+      <c r="AU15" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="AV15" t="n">
         <v>20</v>
       </c>
-      <c r="AS15" t="n">
-        <v>9</v>
-      </c>
-      <c r="AT15" t="n">
-        <v>6.2</v>
-      </c>
-      <c r="AU15" t="n">
-        <v>6</v>
-      </c>
-      <c r="AV15" t="n">
-        <v>14.5</v>
-      </c>
       <c r="AW15" t="n">
-        <v>8.800000000000001</v>
+        <v>11.5</v>
       </c>
       <c r="AX15" t="n">
-        <v>12</v>
+        <v>7.6</v>
       </c>
       <c r="AY15" t="n">
+        <v>10</v>
+      </c>
+      <c r="AZ15" t="n">
+        <v>28</v>
+      </c>
+      <c r="BA15" t="n">
         <v>11</v>
-      </c>
-      <c r="AZ15" t="n">
-        <v>7.4</v>
-      </c>
-      <c r="BA15" t="n">
-        <v>9.199999999999999</v>
       </c>
       <c r="BB15" t="n">
         <v>16</v>
       </c>
       <c r="BC15" t="n">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="BD15" t="n">
-        <v>9</v>
+        <v>55</v>
       </c>
       <c r="BE15" t="n">
+        <v>12</v>
+      </c>
+      <c r="BF15" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="BG15" t="n">
+        <v>11</v>
+      </c>
+      <c r="BH15" t="n">
+        <v>2.84</v>
+      </c>
+      <c r="BI15" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="BJ15" t="n">
+        <v>13</v>
+      </c>
+      <c r="BK15" t="n">
         <v>9.800000000000001</v>
       </c>
-      <c r="BF15" t="n">
-        <v>8.4</v>
-      </c>
-      <c r="BG15" t="n">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="BH15" t="n">
-        <v>2.64</v>
-      </c>
-      <c r="BI15" t="n">
-        <v>2.12</v>
-      </c>
-      <c r="BJ15" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="BK15" t="n">
-        <v>5.8</v>
-      </c>
       <c r="BL15" t="n">
         <v>1000</v>
       </c>
       <c r="BM15" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="BN15" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="BO15" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="BP15" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="BQ15" t="n">
+        <v>10</v>
+      </c>
+      <c r="BR15" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BS15" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="BT15" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="BU15" t="n">
+        <v>5.3</v>
+      </c>
+      <c r="BV15" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BW15" t="n">
+        <v>10</v>
+      </c>
+      <c r="BX15" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BY15" t="n">
         <v>10.5</v>
       </c>
-      <c r="BN15" t="n">
-        <v>5.3</v>
-      </c>
-      <c r="BO15" t="n">
-        <v>3.95</v>
-      </c>
-      <c r="BP15" t="n">
-        <v>24</v>
-      </c>
-      <c r="BQ15" t="n">
-        <v>7.6</v>
-      </c>
-      <c r="BR15" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BS15" t="n">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="BT15" t="n">
-        <v>7</v>
-      </c>
-      <c r="BU15" t="n">
-        <v>5.7</v>
-      </c>
-      <c r="BV15" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BW15" t="n">
-        <v>8.6</v>
-      </c>
-      <c r="BX15" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BY15" t="n">
-        <v>9.6</v>
-      </c>
       <c r="BZ15" t="n">
         <v>1000</v>
       </c>
       <c r="CA15" t="n">
-        <v>9.199999999999999</v>
+        <v>9.4</v>
       </c>
       <c r="CB15" t="inlineStr">
         <is>
-          <t>2026-06-12 07:41:10</t>
+          <t>2026-06-12 09:58:55</t>
         </is>
       </c>
     </row>
@@ -4413,16 +4413,16 @@
         </is>
       </c>
       <c r="F16" t="n">
-        <v>2.96</v>
+        <v>2.92</v>
       </c>
       <c r="G16" t="n">
-        <v>3.05</v>
+        <v>3</v>
       </c>
       <c r="H16" t="n">
         <v>2.44</v>
       </c>
       <c r="I16" t="n">
-        <v>2.5</v>
+        <v>2.52</v>
       </c>
       <c r="J16" t="n">
         <v>3.85</v>
@@ -4437,34 +4437,34 @@
         <v>1.05</v>
       </c>
       <c r="N16" t="n">
-        <v>5.1</v>
+        <v>4.9</v>
       </c>
       <c r="O16" t="n">
-        <v>1.23</v>
+        <v>1.24</v>
       </c>
       <c r="P16" t="n">
-        <v>2.36</v>
+        <v>2.32</v>
       </c>
       <c r="Q16" t="n">
-        <v>1.69</v>
+        <v>1.73</v>
       </c>
       <c r="R16" t="n">
-        <v>1.53</v>
+        <v>1.52</v>
       </c>
       <c r="S16" t="n">
-        <v>2.76</v>
+        <v>2.82</v>
       </c>
       <c r="T16" t="n">
-        <v>1.61</v>
+        <v>1.62</v>
       </c>
       <c r="U16" t="n">
-        <v>2.52</v>
+        <v>2.46</v>
       </c>
       <c r="V16" t="n">
-        <v>1.67</v>
+        <v>1.66</v>
       </c>
       <c r="W16" t="n">
-        <v>1.49</v>
+        <v>1.5</v>
       </c>
       <c r="X16" t="n">
         <v>20</v>
@@ -4476,7 +4476,7 @@
         <v>19.5</v>
       </c>
       <c r="AA16" t="n">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="AB16" t="n">
         <v>16</v>
@@ -4488,7 +4488,7 @@
         <v>12</v>
       </c>
       <c r="AE16" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="AF16" t="n">
         <v>23</v>
@@ -4497,16 +4497,16 @@
         <v>13.5</v>
       </c>
       <c r="AH16" t="n">
-        <v>15</v>
+        <v>15.5</v>
       </c>
       <c r="AI16" t="n">
         <v>32</v>
       </c>
       <c r="AJ16" t="n">
-        <v>110</v>
+        <v>48</v>
       </c>
       <c r="AK16" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="AL16" t="n">
         <v>36</v>
@@ -4518,10 +4518,10 @@
         <v>21</v>
       </c>
       <c r="AO16" t="n">
-        <v>15.5</v>
+        <v>16</v>
       </c>
       <c r="AP16" t="n">
-        <v>18</v>
+        <v>17.5</v>
       </c>
       <c r="AQ16" t="n">
         <v>12</v>
@@ -4536,7 +4536,7 @@
         <v>14</v>
       </c>
       <c r="AU16" t="n">
-        <v>8</v>
+        <v>7.8</v>
       </c>
       <c r="AV16" t="n">
         <v>10.5</v>
@@ -4545,13 +4545,13 @@
         <v>21</v>
       </c>
       <c r="AX16" t="n">
-        <v>20</v>
+        <v>19.5</v>
       </c>
       <c r="AY16" t="n">
         <v>11.5</v>
       </c>
       <c r="AZ16" t="n">
-        <v>13.5</v>
+        <v>14</v>
       </c>
       <c r="BA16" t="n">
         <v>27</v>
@@ -4566,10 +4566,10 @@
         <v>30</v>
       </c>
       <c r="BE16" t="n">
-        <v>36</v>
+        <v>50</v>
       </c>
       <c r="BF16" t="n">
-        <v>18.5</v>
+        <v>18</v>
       </c>
       <c r="BG16" t="n">
         <v>13.5</v>
@@ -4581,16 +4581,16 @@
         <v>3.15</v>
       </c>
       <c r="BJ16" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="BK16" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="BL16" t="n">
+        <v>90</v>
+      </c>
+      <c r="BM16" t="n">
         <v>9</v>
-      </c>
-      <c r="BK16" t="n">
-        <v>4.8</v>
-      </c>
-      <c r="BL16" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BM16" t="n">
-        <v>9.4</v>
       </c>
       <c r="BN16" t="n">
         <v>6.6</v>
@@ -4602,13 +4602,13 @@
         <v>22</v>
       </c>
       <c r="BQ16" t="n">
-        <v>7</v>
+        <v>6.8</v>
       </c>
       <c r="BR16" t="n">
         <v>30</v>
       </c>
       <c r="BS16" t="n">
-        <v>7.8</v>
+        <v>7.4</v>
       </c>
       <c r="BT16" t="n">
         <v>5.9</v>
@@ -4617,26 +4617,26 @@
         <v>4.3</v>
       </c>
       <c r="BV16" t="n">
-        <v>17.5</v>
+        <v>18</v>
       </c>
       <c r="BW16" t="n">
-        <v>6.6</v>
+        <v>6.4</v>
       </c>
       <c r="BX16" t="n">
         <v>27</v>
       </c>
       <c r="BY16" t="n">
-        <v>7.6</v>
+        <v>7.2</v>
       </c>
       <c r="BZ16" t="n">
-        <v>19.5</v>
+        <v>20</v>
       </c>
       <c r="CA16" t="n">
-        <v>6.8</v>
+        <v>6.6</v>
       </c>
       <c r="CB16" t="inlineStr">
         <is>
-          <t>2026-06-12 07:41:10</t>
+          <t>2026-06-12 09:58:55</t>
         </is>
       </c>
     </row>
@@ -4667,13 +4667,13 @@
         </is>
       </c>
       <c r="F17" t="n">
-        <v>1.42</v>
+        <v>1.43</v>
       </c>
       <c r="G17" t="n">
-        <v>1.44</v>
+        <v>1.45</v>
       </c>
       <c r="H17" t="n">
-        <v>9.6</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="I17" t="n">
         <v>10</v>
@@ -4700,25 +4700,25 @@
         <v>2.08</v>
       </c>
       <c r="Q17" t="n">
-        <v>1.89</v>
+        <v>1.87</v>
       </c>
       <c r="R17" t="n">
         <v>1.41</v>
       </c>
       <c r="S17" t="n">
-        <v>3.3</v>
+        <v>3.25</v>
       </c>
       <c r="T17" t="n">
-        <v>2.16</v>
+        <v>2.12</v>
       </c>
       <c r="U17" t="n">
-        <v>1.78</v>
+        <v>1.8</v>
       </c>
       <c r="V17" t="n">
         <v>1.11</v>
       </c>
       <c r="W17" t="n">
-        <v>3.25</v>
+        <v>3.2</v>
       </c>
       <c r="X17" t="n">
         <v>17.5</v>
@@ -4727,10 +4727,10 @@
         <v>30</v>
       </c>
       <c r="Z17" t="n">
-        <v>95</v>
+        <v>85</v>
       </c>
       <c r="AA17" t="n">
-        <v>400</v>
+        <v>380</v>
       </c>
       <c r="AB17" t="n">
         <v>7.8</v>
@@ -4742,67 +4742,67 @@
         <v>36</v>
       </c>
       <c r="AE17" t="n">
-        <v>170</v>
+        <v>180</v>
       </c>
       <c r="AF17" t="n">
-        <v>7.8</v>
+        <v>8</v>
       </c>
       <c r="AG17" t="n">
-        <v>9.800000000000001</v>
+        <v>10</v>
       </c>
       <c r="AH17" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="AI17" t="n">
-        <v>160</v>
+        <v>150</v>
       </c>
       <c r="AJ17" t="n">
-        <v>11.5</v>
+        <v>12</v>
       </c>
       <c r="AK17" t="n">
         <v>16.5</v>
       </c>
       <c r="AL17" t="n">
-        <v>46</v>
+        <v>42</v>
       </c>
       <c r="AM17" t="n">
         <v>200</v>
       </c>
       <c r="AN17" t="n">
-        <v>7.2</v>
+        <v>7.4</v>
       </c>
       <c r="AO17" t="n">
-        <v>250</v>
+        <v>220</v>
       </c>
       <c r="AP17" t="n">
         <v>16.5</v>
       </c>
       <c r="AQ17" t="n">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="AR17" t="n">
-        <v>36</v>
+        <v>40</v>
       </c>
       <c r="AS17" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="AT17" t="n">
-        <v>7.2</v>
+        <v>7.4</v>
       </c>
       <c r="AU17" t="n">
         <v>10</v>
       </c>
       <c r="AV17" t="n">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="AW17" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="AX17" t="n">
         <v>7</v>
       </c>
       <c r="AY17" t="n">
-        <v>9.199999999999999</v>
+        <v>9.4</v>
       </c>
       <c r="AZ17" t="n">
         <v>26</v>
@@ -4811,10 +4811,10 @@
         <v>36</v>
       </c>
       <c r="BB17" t="n">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="BC17" t="n">
-        <v>14</v>
+        <v>14.5</v>
       </c>
       <c r="BD17" t="n">
         <v>36</v>
@@ -4826,49 +4826,49 @@
         <v>6.6</v>
       </c>
       <c r="BG17" t="n">
-        <v>38</v>
+        <v>15.5</v>
       </c>
       <c r="BH17" t="n">
         <v>3.75</v>
       </c>
       <c r="BI17" t="n">
-        <v>2.88</v>
+        <v>2.9</v>
       </c>
       <c r="BJ17" t="n">
         <v>13</v>
       </c>
       <c r="BK17" t="n">
-        <v>9.199999999999999</v>
+        <v>6</v>
       </c>
       <c r="BL17" t="n">
         <v>1000</v>
       </c>
       <c r="BM17" t="n">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="BN17" t="n">
         <v>3.8</v>
       </c>
       <c r="BO17" t="n">
-        <v>2.92</v>
+        <v>3.25</v>
       </c>
       <c r="BP17" t="n">
         <v>8.800000000000001</v>
       </c>
       <c r="BQ17" t="n">
-        <v>4.9</v>
+        <v>5</v>
       </c>
       <c r="BR17" t="n">
         <v>1000</v>
       </c>
       <c r="BS17" t="n">
-        <v>7.8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BT17" t="n">
-        <v>14</v>
+        <v>13.5</v>
       </c>
       <c r="BU17" t="n">
-        <v>9.6</v>
+        <v>6.2</v>
       </c>
       <c r="BV17" t="n">
         <v>1000</v>
@@ -4886,11 +4886,11 @@
         <v>17</v>
       </c>
       <c r="CA17" t="n">
-        <v>6.6</v>
+        <v>6.8</v>
       </c>
       <c r="CB17" t="inlineStr">
         <is>
-          <t>2026-06-12 07:41:10</t>
+          <t>2026-06-12 09:58:55</t>
         </is>
       </c>
     </row>
@@ -4921,16 +4921,16 @@
         </is>
       </c>
       <c r="F18" t="n">
-        <v>3.25</v>
+        <v>3.15</v>
       </c>
       <c r="G18" t="n">
-        <v>3.35</v>
+        <v>3.2</v>
       </c>
       <c r="H18" t="n">
-        <v>2.56</v>
+        <v>2.6</v>
       </c>
       <c r="I18" t="n">
-        <v>2.58</v>
+        <v>2.64</v>
       </c>
       <c r="J18" t="n">
         <v>3.25</v>
@@ -4954,7 +4954,7 @@
         <v>1.72</v>
       </c>
       <c r="Q18" t="n">
-        <v>2.3</v>
+        <v>2.32</v>
       </c>
       <c r="R18" t="n">
         <v>1.26</v>
@@ -4963,34 +4963,34 @@
         <v>4.5</v>
       </c>
       <c r="T18" t="n">
-        <v>1.95</v>
+        <v>1.93</v>
       </c>
       <c r="U18" t="n">
-        <v>1.95</v>
+        <v>1.98</v>
       </c>
       <c r="V18" t="n">
-        <v>1.63</v>
+        <v>1.6</v>
       </c>
       <c r="W18" t="n">
-        <v>1.43</v>
+        <v>1.45</v>
       </c>
       <c r="X18" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="Y18" t="n">
-        <v>9</v>
+        <v>9.4</v>
       </c>
       <c r="Z18" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AA18" t="n">
-        <v>36</v>
+        <v>85</v>
       </c>
       <c r="AB18" t="n">
         <v>11</v>
       </c>
       <c r="AC18" t="n">
-        <v>7.6</v>
+        <v>7.4</v>
       </c>
       <c r="AD18" t="n">
         <v>12</v>
@@ -5005,88 +5005,88 @@
         <v>14</v>
       </c>
       <c r="AH18" t="n">
-        <v>19.5</v>
+        <v>18</v>
       </c>
       <c r="AI18" t="n">
-        <v>65</v>
+        <v>60</v>
       </c>
       <c r="AJ18" t="n">
-        <v>60</v>
+        <v>85</v>
       </c>
       <c r="AK18" t="n">
-        <v>44</v>
+        <v>40</v>
       </c>
       <c r="AL18" t="n">
-        <v>80</v>
+        <v>70</v>
       </c>
       <c r="AM18" t="n">
         <v>160</v>
       </c>
       <c r="AN18" t="n">
-        <v>60</v>
+        <v>46</v>
       </c>
       <c r="AO18" t="n">
         <v>34</v>
       </c>
       <c r="AP18" t="n">
-        <v>9.800000000000001</v>
+        <v>10.5</v>
       </c>
       <c r="AQ18" t="n">
-        <v>8</v>
+        <v>8.4</v>
       </c>
       <c r="AR18" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AS18" t="n">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="AT18" t="n">
-        <v>9.6</v>
+        <v>9.4</v>
       </c>
       <c r="AU18" t="n">
         <v>6.8</v>
       </c>
       <c r="AV18" t="n">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="AW18" t="n">
         <v>27</v>
       </c>
       <c r="AX18" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="AY18" t="n">
         <v>12.5</v>
       </c>
       <c r="AZ18" t="n">
-        <v>17.5</v>
+        <v>15.5</v>
       </c>
       <c r="BA18" t="n">
         <v>34</v>
       </c>
       <c r="BB18" t="n">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="BC18" t="n">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="BD18" t="n">
-        <v>40</v>
+        <v>50</v>
       </c>
       <c r="BE18" t="n">
-        <v>12.5</v>
+        <v>16</v>
       </c>
       <c r="BF18" t="n">
         <v>34</v>
       </c>
       <c r="BG18" t="n">
-        <v>15</v>
+        <v>27</v>
       </c>
       <c r="BH18" t="n">
         <v>3.05</v>
       </c>
       <c r="BI18" t="n">
-        <v>2.78</v>
+        <v>2.8</v>
       </c>
       <c r="BJ18" t="n">
         <v>10.5</v>
@@ -5098,25 +5098,25 @@
         <v>1000</v>
       </c>
       <c r="BM18" t="n">
-        <v>12.5</v>
+        <v>14.5</v>
       </c>
       <c r="BN18" t="n">
-        <v>6.6</v>
+        <v>6.2</v>
       </c>
       <c r="BO18" t="n">
-        <v>5.6</v>
+        <v>5.4</v>
       </c>
       <c r="BP18" t="n">
         <v>1000</v>
       </c>
       <c r="BQ18" t="n">
-        <v>9.199999999999999</v>
+        <v>10</v>
       </c>
       <c r="BR18" t="n">
         <v>1000</v>
       </c>
       <c r="BS18" t="n">
-        <v>10</v>
+        <v>11.5</v>
       </c>
       <c r="BT18" t="n">
         <v>5.3</v>
@@ -5128,23 +5128,23 @@
         <v>21</v>
       </c>
       <c r="BW18" t="n">
-        <v>8.199999999999999</v>
+        <v>9</v>
       </c>
       <c r="BX18" t="n">
         <v>1000</v>
       </c>
       <c r="BY18" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="BZ18" t="n">
         <v>1000</v>
       </c>
       <c r="CA18" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="CB18" t="inlineStr">
         <is>
-          <t>2026-06-12 07:41:10</t>
+          <t>2026-06-12 09:58:55</t>
         </is>
       </c>
     </row>
@@ -5178,61 +5178,61 @@
         <v>2.1</v>
       </c>
       <c r="G19" t="n">
-        <v>2.14</v>
+        <v>2.12</v>
       </c>
       <c r="H19" t="n">
         <v>3.75</v>
       </c>
       <c r="I19" t="n">
-        <v>3.85</v>
+        <v>3.95</v>
       </c>
       <c r="J19" t="n">
-        <v>3.65</v>
+        <v>3.7</v>
       </c>
       <c r="K19" t="n">
         <v>3.8</v>
       </c>
       <c r="L19" t="n">
-        <v>1.4</v>
+        <v>1.38</v>
       </c>
       <c r="M19" t="n">
         <v>1.06</v>
       </c>
       <c r="N19" t="n">
-        <v>4.1</v>
+        <v>4.3</v>
       </c>
       <c r="O19" t="n">
-        <v>1.3</v>
+        <v>1.28</v>
       </c>
       <c r="P19" t="n">
-        <v>2.04</v>
+        <v>2.14</v>
       </c>
       <c r="Q19" t="n">
-        <v>1.92</v>
+        <v>1.86</v>
       </c>
       <c r="R19" t="n">
-        <v>1.4</v>
+        <v>1.43</v>
       </c>
       <c r="S19" t="n">
-        <v>3.35</v>
+        <v>3.2</v>
       </c>
       <c r="T19" t="n">
-        <v>1.76</v>
+        <v>1.72</v>
       </c>
       <c r="U19" t="n">
-        <v>2.22</v>
+        <v>2.26</v>
       </c>
       <c r="V19" t="n">
         <v>1.35</v>
       </c>
       <c r="W19" t="n">
-        <v>1.87</v>
+        <v>1.89</v>
       </c>
       <c r="X19" t="n">
+        <v>17</v>
+      </c>
+      <c r="Y19" t="n">
         <v>16</v>
-      </c>
-      <c r="Y19" t="n">
-        <v>15</v>
       </c>
       <c r="Z19" t="n">
         <v>29</v>
@@ -5244,7 +5244,7 @@
         <v>10.5</v>
       </c>
       <c r="AC19" t="n">
-        <v>8.199999999999999</v>
+        <v>8.6</v>
       </c>
       <c r="AD19" t="n">
         <v>15.5</v>
@@ -5268,7 +5268,7 @@
         <v>27</v>
       </c>
       <c r="AK19" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AL19" t="n">
         <v>36</v>
@@ -5277,16 +5277,16 @@
         <v>95</v>
       </c>
       <c r="AN19" t="n">
-        <v>15.5</v>
+        <v>14.5</v>
       </c>
       <c r="AO19" t="n">
-        <v>44</v>
+        <v>40</v>
       </c>
       <c r="AP19" t="n">
-        <v>13.5</v>
+        <v>15</v>
       </c>
       <c r="AQ19" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AR19" t="n">
         <v>24</v>
@@ -5295,10 +5295,10 @@
         <v>60</v>
       </c>
       <c r="AT19" t="n">
-        <v>9.199999999999999</v>
+        <v>9.6</v>
       </c>
       <c r="AU19" t="n">
-        <v>7.4</v>
+        <v>7.6</v>
       </c>
       <c r="AV19" t="n">
         <v>14</v>
@@ -5307,13 +5307,13 @@
         <v>38</v>
       </c>
       <c r="AX19" t="n">
-        <v>12</v>
+        <v>12.5</v>
       </c>
       <c r="AY19" t="n">
         <v>9.4</v>
       </c>
       <c r="AZ19" t="n">
-        <v>16</v>
+        <v>15.5</v>
       </c>
       <c r="BA19" t="n">
         <v>44</v>
@@ -5322,7 +5322,7 @@
         <v>23</v>
       </c>
       <c r="BC19" t="n">
-        <v>19.5</v>
+        <v>19</v>
       </c>
       <c r="BD19" t="n">
         <v>30</v>
@@ -5331,19 +5331,19 @@
         <v>38</v>
       </c>
       <c r="BF19" t="n">
-        <v>13.5</v>
+        <v>13</v>
       </c>
       <c r="BG19" t="n">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="BH19" t="n">
-        <v>3.65</v>
+        <v>3.75</v>
       </c>
       <c r="BI19" t="n">
-        <v>2.8</v>
+        <v>2.88</v>
       </c>
       <c r="BJ19" t="n">
-        <v>9.800000000000001</v>
+        <v>9.4</v>
       </c>
       <c r="BK19" t="n">
         <v>7.2</v>
@@ -5352,7 +5352,7 @@
         <v>1000</v>
       </c>
       <c r="BM19" t="n">
-        <v>9.4</v>
+        <v>10</v>
       </c>
       <c r="BN19" t="n">
         <v>5.2</v>
@@ -5361,44 +5361,44 @@
         <v>4.3</v>
       </c>
       <c r="BP19" t="n">
-        <v>16</v>
+        <v>15.5</v>
       </c>
       <c r="BQ19" t="n">
-        <v>6.2</v>
+        <v>6.4</v>
       </c>
       <c r="BR19" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="BS19" t="n">
-        <v>7.6</v>
+        <v>8</v>
       </c>
       <c r="BT19" t="n">
         <v>7.4</v>
       </c>
       <c r="BU19" t="n">
-        <v>5.3</v>
+        <v>6</v>
       </c>
       <c r="BV19" t="n">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="BW19" t="n">
-        <v>7.8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BX19" t="n">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="BY19" t="n">
-        <v>8.199999999999999</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BZ19" t="n">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="CA19" t="n">
-        <v>7.2</v>
+        <v>7.4</v>
       </c>
       <c r="CB19" t="inlineStr">
         <is>
-          <t>2026-06-12 07:41:10</t>
+          <t>2026-06-12 09:58:55</t>
         </is>
       </c>
     </row>
@@ -5429,16 +5429,16 @@
         </is>
       </c>
       <c r="F20" t="n">
-        <v>4.2</v>
+        <v>4</v>
       </c>
       <c r="G20" t="n">
         <v>4.4</v>
       </c>
       <c r="H20" t="n">
-        <v>1.93</v>
+        <v>1.92</v>
       </c>
       <c r="I20" t="n">
-        <v>1.97</v>
+        <v>1.98</v>
       </c>
       <c r="J20" t="n">
         <v>3.85</v>
@@ -5453,28 +5453,28 @@
         <v>1.05</v>
       </c>
       <c r="N20" t="n">
-        <v>4.8</v>
+        <v>4.9</v>
       </c>
       <c r="O20" t="n">
         <v>1.24</v>
       </c>
       <c r="P20" t="n">
-        <v>2.28</v>
+        <v>2.3</v>
       </c>
       <c r="Q20" t="n">
-        <v>1.73</v>
+        <v>1.72</v>
       </c>
       <c r="R20" t="n">
         <v>1.53</v>
       </c>
       <c r="S20" t="n">
-        <v>2.84</v>
+        <v>2.78</v>
       </c>
       <c r="T20" t="n">
         <v>1.66</v>
       </c>
       <c r="U20" t="n">
-        <v>2.38</v>
+        <v>2.32</v>
       </c>
       <c r="V20" t="n">
         <v>2.02</v>
@@ -5528,13 +5528,13 @@
         <v>46</v>
       </c>
       <c r="AM20" t="n">
-        <v>100</v>
+        <v>95</v>
       </c>
       <c r="AN20" t="n">
         <v>38</v>
       </c>
       <c r="AO20" t="n">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="AP20" t="n">
         <v>16.5</v>
@@ -5573,22 +5573,22 @@
         <v>23</v>
       </c>
       <c r="BB20" t="n">
-        <v>9.6</v>
+        <v>9</v>
       </c>
       <c r="BC20" t="n">
-        <v>34</v>
+        <v>20</v>
       </c>
       <c r="BD20" t="n">
         <v>36</v>
       </c>
       <c r="BE20" t="n">
-        <v>9.4</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BF20" t="n">
         <v>16</v>
       </c>
       <c r="BG20" t="n">
-        <v>8.800000000000001</v>
+        <v>9</v>
       </c>
       <c r="BH20" t="n">
         <v>4.1</v>
@@ -5606,7 +5606,7 @@
         <v>1000</v>
       </c>
       <c r="BM20" t="n">
-        <v>9.199999999999999</v>
+        <v>9</v>
       </c>
       <c r="BN20" t="n">
         <v>8</v>
@@ -5636,23 +5636,23 @@
         <v>13.5</v>
       </c>
       <c r="BW20" t="n">
-        <v>9.6</v>
+        <v>9.4</v>
       </c>
       <c r="BX20" t="n">
         <v>25</v>
       </c>
       <c r="BY20" t="n">
-        <v>7.2</v>
+        <v>7</v>
       </c>
       <c r="BZ20" t="n">
-        <v>19</v>
+        <v>19.5</v>
       </c>
       <c r="CA20" t="n">
         <v>6.6</v>
       </c>
       <c r="CB20" t="inlineStr">
         <is>
-          <t>2026-06-12 07:41:10</t>
+          <t>2026-06-12 09:58:55</t>
         </is>
       </c>
     </row>
@@ -5683,64 +5683,64 @@
         </is>
       </c>
       <c r="F21" t="n">
+        <v>2.44</v>
+      </c>
+      <c r="G21" t="n">
+        <v>2.54</v>
+      </c>
+      <c r="H21" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="I21" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="J21" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="K21" t="n">
+        <v>3.35</v>
+      </c>
+      <c r="L21" t="n">
+        <v>1.51</v>
+      </c>
+      <c r="M21" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="N21" t="n">
+        <v>3.05</v>
+      </c>
+      <c r="O21" t="n">
+        <v>1.46</v>
+      </c>
+      <c r="P21" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="Q21" t="n">
         <v>2.4</v>
       </c>
-      <c r="G21" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="H21" t="n">
-        <v>3.35</v>
-      </c>
-      <c r="I21" t="n">
-        <v>3.55</v>
-      </c>
-      <c r="J21" t="n">
-        <v>3.25</v>
-      </c>
-      <c r="K21" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="L21" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="M21" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="N21" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="O21" t="n">
-        <v>1.43</v>
-      </c>
-      <c r="P21" t="n">
-        <v>1.72</v>
-      </c>
-      <c r="Q21" t="n">
-        <v>2.3</v>
-      </c>
       <c r="R21" t="n">
-        <v>1.26</v>
+        <v>1.24</v>
       </c>
       <c r="S21" t="n">
-        <v>4.4</v>
+        <v>4.7</v>
       </c>
       <c r="T21" t="n">
-        <v>1.92</v>
+        <v>1.98</v>
       </c>
       <c r="U21" t="n">
-        <v>1.97</v>
+        <v>1.9</v>
       </c>
       <c r="V21" t="n">
         <v>1.4</v>
       </c>
       <c r="W21" t="n">
-        <v>1.66</v>
+        <v>1.65</v>
       </c>
       <c r="X21" t="n">
         <v>13.5</v>
       </c>
       <c r="Y21" t="n">
-        <v>13.5</v>
+        <v>12.5</v>
       </c>
       <c r="Z21" t="n">
         <v>30</v>
@@ -5764,13 +5764,13 @@
         <v>17.5</v>
       </c>
       <c r="AG21" t="n">
-        <v>14.5</v>
+        <v>15</v>
       </c>
       <c r="AH21" t="n">
         <v>24</v>
       </c>
       <c r="AI21" t="n">
-        <v>370</v>
+        <v>500</v>
       </c>
       <c r="AJ21" t="n">
         <v>42</v>
@@ -5791,25 +5791,25 @@
         <v>600</v>
       </c>
       <c r="AP21" t="n">
-        <v>9.6</v>
+        <v>9</v>
       </c>
       <c r="AQ21" t="n">
-        <v>9.800000000000001</v>
+        <v>9.4</v>
       </c>
       <c r="AR21" t="n">
-        <v>20</v>
+        <v>11</v>
       </c>
       <c r="AS21" t="n">
-        <v>4.6</v>
+        <v>4.7</v>
       </c>
       <c r="AT21" t="n">
-        <v>7.8</v>
+        <v>7.4</v>
       </c>
       <c r="AU21" t="n">
-        <v>6.6</v>
+        <v>6.4</v>
       </c>
       <c r="AV21" t="n">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="AW21" t="n">
         <v>4.6</v>
@@ -5818,19 +5818,19 @@
         <v>13</v>
       </c>
       <c r="AY21" t="n">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="AZ21" t="n">
         <v>10.5</v>
       </c>
       <c r="BA21" t="n">
-        <v>4.6</v>
+        <v>4.7</v>
       </c>
       <c r="BB21" t="n">
         <v>14.5</v>
       </c>
       <c r="BC21" t="n">
-        <v>13.5</v>
+        <v>13</v>
       </c>
       <c r="BD21" t="n">
         <v>4.6</v>
@@ -5845,68 +5845,68 @@
         <v>8.6</v>
       </c>
       <c r="BH21" t="n">
-        <v>3.05</v>
+        <v>2.94</v>
       </c>
       <c r="BI21" t="n">
-        <v>2.54</v>
+        <v>2.5</v>
       </c>
       <c r="BJ21" t="n">
         <v>10.5</v>
       </c>
       <c r="BK21" t="n">
-        <v>6.2</v>
+        <v>6.4</v>
       </c>
       <c r="BL21" t="n">
         <v>1000</v>
       </c>
       <c r="BM21" t="n">
-        <v>14</v>
+        <v>15.5</v>
       </c>
       <c r="BN21" t="n">
         <v>5.2</v>
       </c>
       <c r="BO21" t="n">
-        <v>4.1</v>
+        <v>4</v>
       </c>
       <c r="BP21" t="n">
-        <v>1000</v>
+        <v>21</v>
       </c>
       <c r="BQ21" t="n">
-        <v>8.6</v>
+        <v>9.4</v>
       </c>
       <c r="BR21" t="n">
         <v>1000</v>
       </c>
       <c r="BS21" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="BT21" t="n">
         <v>6.4</v>
       </c>
       <c r="BU21" t="n">
-        <v>4.9</v>
+        <v>4.8</v>
       </c>
       <c r="BV21" t="n">
         <v>1000</v>
       </c>
       <c r="BW21" t="n">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="BX21" t="n">
         <v>1000</v>
       </c>
       <c r="BY21" t="n">
-        <v>11.5</v>
+        <v>12.5</v>
       </c>
       <c r="BZ21" t="n">
         <v>1000</v>
       </c>
       <c r="CA21" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="CB21" t="inlineStr">
         <is>
-          <t>2026-06-12 07:41:10</t>
+          <t>2026-06-12 09:58:55</t>
         </is>
       </c>
     </row>
@@ -5943,46 +5943,46 @@
         <v>4.1</v>
       </c>
       <c r="H22" t="n">
-        <v>2</v>
+        <v>1.99</v>
       </c>
       <c r="I22" t="n">
         <v>2.06</v>
       </c>
       <c r="J22" t="n">
-        <v>3.75</v>
+        <v>3.85</v>
       </c>
       <c r="K22" t="n">
-        <v>4</v>
+        <v>4.1</v>
       </c>
       <c r="L22" t="n">
-        <v>1.35</v>
+        <v>1.34</v>
       </c>
       <c r="M22" t="n">
         <v>1.05</v>
       </c>
       <c r="N22" t="n">
-        <v>4.7</v>
+        <v>4.8</v>
       </c>
       <c r="O22" t="n">
-        <v>1.25</v>
+        <v>1.24</v>
       </c>
       <c r="P22" t="n">
-        <v>2.24</v>
+        <v>2.3</v>
       </c>
       <c r="Q22" t="n">
-        <v>1.76</v>
+        <v>1.73</v>
       </c>
       <c r="R22" t="n">
-        <v>1.48</v>
+        <v>1.51</v>
       </c>
       <c r="S22" t="n">
-        <v>2.92</v>
+        <v>2.86</v>
       </c>
       <c r="T22" t="n">
-        <v>1.64</v>
+        <v>1.65</v>
       </c>
       <c r="U22" t="n">
-        <v>2.28</v>
+        <v>2.36</v>
       </c>
       <c r="V22" t="n">
         <v>1.94</v>
@@ -5991,82 +5991,82 @@
         <v>1.32</v>
       </c>
       <c r="X22" t="n">
-        <v>19.5</v>
+        <v>22</v>
       </c>
       <c r="Y22" t="n">
-        <v>11.5</v>
+        <v>12</v>
       </c>
       <c r="Z22" t="n">
-        <v>14.5</v>
+        <v>15</v>
       </c>
       <c r="AA22" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="AB22" t="n">
-        <v>17.5</v>
+        <v>19</v>
       </c>
       <c r="AC22" t="n">
-        <v>9</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AD22" t="n">
         <v>11.5</v>
       </c>
       <c r="AE22" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AF22" t="n">
         <v>32</v>
       </c>
       <c r="AG22" t="n">
-        <v>17</v>
+        <v>16.5</v>
       </c>
       <c r="AH22" t="n">
         <v>17</v>
       </c>
       <c r="AI22" t="n">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="AJ22" t="n">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="AK22" t="n">
+        <v>44</v>
+      </c>
+      <c r="AL22" t="n">
         <v>46</v>
       </c>
-      <c r="AL22" t="n">
-        <v>50</v>
-      </c>
       <c r="AM22" t="n">
-        <v>320</v>
+        <v>75</v>
       </c>
       <c r="AN22" t="n">
-        <v>40</v>
+        <v>36</v>
       </c>
       <c r="AO22" t="n">
-        <v>12.5</v>
+        <v>11.5</v>
       </c>
       <c r="AP22" t="n">
-        <v>15.5</v>
+        <v>17.5</v>
       </c>
       <c r="AQ22" t="n">
-        <v>9.199999999999999</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AR22" t="n">
-        <v>11.5</v>
+        <v>12</v>
       </c>
       <c r="AS22" t="n">
         <v>20</v>
       </c>
       <c r="AT22" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AU22" t="n">
-        <v>7.4</v>
+        <v>7.8</v>
       </c>
       <c r="AV22" t="n">
         <v>9.199999999999999</v>
       </c>
       <c r="AW22" t="n">
-        <v>17</v>
+        <v>16.5</v>
       </c>
       <c r="AX22" t="n">
         <v>25</v>
@@ -6075,46 +6075,46 @@
         <v>13.5</v>
       </c>
       <c r="AZ22" t="n">
-        <v>14</v>
+        <v>13.5</v>
       </c>
       <c r="BA22" t="n">
-        <v>16</v>
+        <v>23</v>
       </c>
       <c r="BB22" t="n">
         <v>9</v>
       </c>
       <c r="BC22" t="n">
-        <v>36</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BD22" t="n">
         <v>8.4</v>
       </c>
       <c r="BE22" t="n">
-        <v>9</v>
+        <v>28</v>
       </c>
       <c r="BF22" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="BG22" t="n">
-        <v>10.5</v>
+        <v>9.6</v>
       </c>
       <c r="BH22" t="n">
-        <v>4</v>
+        <v>4.1</v>
       </c>
       <c r="BI22" t="n">
-        <v>3.15</v>
+        <v>3.2</v>
       </c>
       <c r="BJ22" t="n">
-        <v>9.6</v>
+        <v>9.4</v>
       </c>
       <c r="BK22" t="n">
-        <v>4.8</v>
+        <v>4.9</v>
       </c>
       <c r="BL22" t="n">
-        <v>1000</v>
+        <v>95</v>
       </c>
       <c r="BM22" t="n">
-        <v>8.800000000000001</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BN22" t="n">
         <v>7.8</v>
@@ -6123,44 +6123,44 @@
         <v>5.8</v>
       </c>
       <c r="BP22" t="n">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="BQ22" t="n">
-        <v>7.4</v>
+        <v>7.6</v>
       </c>
       <c r="BR22" t="n">
         <v>38</v>
       </c>
       <c r="BS22" t="n">
-        <v>7.6</v>
+        <v>8</v>
       </c>
       <c r="BT22" t="n">
         <v>5.2</v>
       </c>
       <c r="BU22" t="n">
-        <v>3.95</v>
+        <v>4</v>
       </c>
       <c r="BV22" t="n">
-        <v>14.5</v>
+        <v>14</v>
       </c>
       <c r="BW22" t="n">
-        <v>10.5</v>
+        <v>5.9</v>
       </c>
       <c r="BX22" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="BY22" t="n">
-        <v>7</v>
+        <v>7.2</v>
       </c>
       <c r="BZ22" t="n">
-        <v>21</v>
+        <v>19.5</v>
       </c>
       <c r="CA22" t="n">
         <v>6.6</v>
       </c>
       <c r="CB22" t="inlineStr">
         <is>
-          <t>2026-06-12 07:41:10</t>
+          <t>2026-06-12 09:58:55</t>
         </is>
       </c>
     </row>
@@ -6194,13 +6194,13 @@
         <v>4.7</v>
       </c>
       <c r="G23" t="n">
-        <v>5.1</v>
+        <v>5</v>
       </c>
       <c r="H23" t="n">
-        <v>1.86</v>
+        <v>1.85</v>
       </c>
       <c r="I23" t="n">
-        <v>1.93</v>
+        <v>1.91</v>
       </c>
       <c r="J23" t="n">
         <v>3.65</v>
@@ -6215,37 +6215,37 @@
         <v>1.07</v>
       </c>
       <c r="N23" t="n">
-        <v>3.95</v>
+        <v>4</v>
       </c>
       <c r="O23" t="n">
-        <v>1.31</v>
+        <v>1.3</v>
       </c>
       <c r="P23" t="n">
-        <v>1.98</v>
+        <v>2.02</v>
       </c>
       <c r="Q23" t="n">
-        <v>1.95</v>
+        <v>1.91</v>
       </c>
       <c r="R23" t="n">
-        <v>1.38</v>
+        <v>1.39</v>
       </c>
       <c r="S23" t="n">
-        <v>3.4</v>
+        <v>3.35</v>
       </c>
       <c r="T23" t="n">
         <v>1.81</v>
       </c>
       <c r="U23" t="n">
-        <v>2.06</v>
+        <v>2.08</v>
       </c>
       <c r="V23" t="n">
-        <v>2.06</v>
+        <v>2.08</v>
       </c>
       <c r="W23" t="n">
         <v>1.25</v>
       </c>
       <c r="X23" t="n">
-        <v>15</v>
+        <v>15.5</v>
       </c>
       <c r="Y23" t="n">
         <v>9.4</v>
@@ -6257,7 +6257,7 @@
         <v>22</v>
       </c>
       <c r="AB23" t="n">
-        <v>17</v>
+        <v>17.5</v>
       </c>
       <c r="AC23" t="n">
         <v>8.800000000000001</v>
@@ -6272,7 +6272,7 @@
         <v>38</v>
       </c>
       <c r="AG23" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="AH23" t="n">
         <v>19.5</v>
@@ -6281,7 +6281,7 @@
         <v>38</v>
       </c>
       <c r="AJ23" t="n">
-        <v>900</v>
+        <v>500</v>
       </c>
       <c r="AK23" t="n">
         <v>65</v>
@@ -6320,7 +6320,7 @@
         <v>8.800000000000001</v>
       </c>
       <c r="AW23" t="n">
-        <v>17</v>
+        <v>16.5</v>
       </c>
       <c r="AX23" t="n">
         <v>23</v>
@@ -6335,7 +6335,7 @@
         <v>24</v>
       </c>
       <c r="BB23" t="n">
-        <v>9.4</v>
+        <v>9</v>
       </c>
       <c r="BC23" t="n">
         <v>38</v>
@@ -6344,19 +6344,19 @@
         <v>42</v>
       </c>
       <c r="BE23" t="n">
-        <v>9.4</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BF23" t="n">
-        <v>9</v>
+        <v>12.5</v>
       </c>
       <c r="BG23" t="n">
         <v>10.5</v>
       </c>
       <c r="BH23" t="n">
-        <v>3.6</v>
+        <v>3.65</v>
       </c>
       <c r="BI23" t="n">
-        <v>3.05</v>
+        <v>3.1</v>
       </c>
       <c r="BJ23" t="n">
         <v>10.5</v>
@@ -6368,25 +6368,25 @@
         <v>1000</v>
       </c>
       <c r="BM23" t="n">
-        <v>10</v>
+        <v>9.6</v>
       </c>
       <c r="BN23" t="n">
         <v>8.4</v>
       </c>
       <c r="BO23" t="n">
-        <v>4.7</v>
+        <v>4.6</v>
       </c>
       <c r="BP23" t="n">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="BQ23" t="n">
-        <v>8.6</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BR23" t="n">
         <v>50</v>
       </c>
       <c r="BS23" t="n">
-        <v>8.800000000000001</v>
+        <v>8.6</v>
       </c>
       <c r="BT23" t="n">
         <v>4.7</v>
@@ -6404,17 +6404,17 @@
         <v>28</v>
       </c>
       <c r="BY23" t="n">
-        <v>7.8</v>
+        <v>7.6</v>
       </c>
       <c r="BZ23" t="n">
         <v>24</v>
       </c>
       <c r="CA23" t="n">
-        <v>7.4</v>
+        <v>7.2</v>
       </c>
       <c r="CB23" t="inlineStr">
         <is>
-          <t>2026-06-12 07:41:10</t>
+          <t>2026-06-12 09:58:55</t>
         </is>
       </c>
     </row>
@@ -6445,230 +6445,230 @@
         </is>
       </c>
       <c r="F24" t="n">
-        <v>1.61</v>
+        <v>1.53</v>
       </c>
       <c r="G24" t="n">
-        <v>1.71</v>
+        <v>1000</v>
       </c>
       <c r="H24" t="n">
-        <v>4.8</v>
+        <v>1.04</v>
       </c>
       <c r="I24" t="n">
-        <v>5.4</v>
+        <v>1000</v>
       </c>
       <c r="J24" t="n">
-        <v>4.7</v>
+        <v>1.09</v>
       </c>
       <c r="K24" t="n">
         <v>5.4</v>
       </c>
       <c r="L24" t="n">
-        <v>1.22</v>
+        <v>1.01</v>
       </c>
       <c r="M24" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="N24" t="n">
         <v>1.02</v>
       </c>
-      <c r="N24" t="n">
-        <v>7.4</v>
-      </c>
       <c r="O24" t="n">
-        <v>1.13</v>
+        <v>1.01</v>
       </c>
       <c r="P24" t="n">
-        <v>3.15</v>
+        <v>1.24</v>
       </c>
       <c r="Q24" t="n">
-        <v>1.39</v>
+        <v>1.01</v>
       </c>
       <c r="R24" t="n">
-        <v>1.87</v>
+        <v>1.18</v>
       </c>
       <c r="S24" t="n">
-        <v>1.96</v>
+        <v>1.01</v>
       </c>
       <c r="T24" t="n">
-        <v>1.51</v>
+        <v>1.11</v>
       </c>
       <c r="U24" t="n">
-        <v>2.68</v>
+        <v>1.11</v>
       </c>
       <c r="V24" t="n">
-        <v>1.22</v>
+        <v>1.01</v>
       </c>
       <c r="W24" t="n">
-        <v>2.42</v>
+        <v>1.01</v>
       </c>
       <c r="X24" t="n">
-        <v>44</v>
+        <v>1000</v>
       </c>
       <c r="Y24" t="n">
-        <v>38</v>
+        <v>1000</v>
       </c>
       <c r="Z24" t="n">
-        <v>60</v>
+        <v>1000</v>
       </c>
       <c r="AA24" t="n">
-        <v>120</v>
+        <v>1000</v>
       </c>
       <c r="AB24" t="n">
-        <v>19.5</v>
+        <v>1000</v>
       </c>
       <c r="AC24" t="n">
-        <v>15</v>
+        <v>1000</v>
       </c>
       <c r="AD24" t="n">
-        <v>25</v>
+        <v>1000</v>
       </c>
       <c r="AE24" t="n">
-        <v>60</v>
+        <v>1000</v>
       </c>
       <c r="AF24" t="n">
-        <v>17.5</v>
+        <v>1000</v>
       </c>
       <c r="AG24" t="n">
-        <v>13</v>
+        <v>1000</v>
       </c>
       <c r="AH24" t="n">
-        <v>19.5</v>
+        <v>1000</v>
       </c>
       <c r="AI24" t="n">
-        <v>50</v>
+        <v>1000</v>
       </c>
       <c r="AJ24" t="n">
-        <v>22</v>
+        <v>1000</v>
       </c>
       <c r="AK24" t="n">
-        <v>17.5</v>
+        <v>1000</v>
       </c>
       <c r="AL24" t="n">
-        <v>27</v>
+        <v>1000</v>
       </c>
       <c r="AM24" t="n">
-        <v>55</v>
+        <v>1000</v>
       </c>
       <c r="AN24" t="n">
-        <v>6</v>
+        <v>1000</v>
       </c>
       <c r="AO24" t="n">
-        <v>36</v>
+        <v>1000</v>
       </c>
       <c r="AP24" t="n">
-        <v>4.6</v>
+        <v>1.01</v>
       </c>
       <c r="AQ24" t="n">
-        <v>4.6</v>
+        <v>1.01</v>
       </c>
       <c r="AR24" t="n">
-        <v>4.8</v>
+        <v>1.01</v>
       </c>
       <c r="AS24" t="n">
-        <v>5</v>
+        <v>1.01</v>
       </c>
       <c r="AT24" t="n">
-        <v>12.5</v>
+        <v>1.01</v>
       </c>
       <c r="AU24" t="n">
-        <v>10</v>
+        <v>1.01</v>
       </c>
       <c r="AV24" t="n">
-        <v>16</v>
+        <v>1.01</v>
       </c>
       <c r="AW24" t="n">
-        <v>4.8</v>
+        <v>1.01</v>
       </c>
       <c r="AX24" t="n">
-        <v>11.5</v>
+        <v>1.01</v>
       </c>
       <c r="AY24" t="n">
-        <v>9.6</v>
+        <v>1.01</v>
       </c>
       <c r="AZ24" t="n">
-        <v>12.5</v>
+        <v>1.01</v>
       </c>
       <c r="BA24" t="n">
-        <v>4.7</v>
+        <v>1.01</v>
       </c>
       <c r="BB24" t="n">
-        <v>14</v>
+        <v>1.01</v>
       </c>
       <c r="BC24" t="n">
-        <v>11.5</v>
+        <v>1.01</v>
       </c>
       <c r="BD24" t="n">
-        <v>19</v>
+        <v>1.01</v>
       </c>
       <c r="BE24" t="n">
-        <v>4.7</v>
+        <v>1.01</v>
       </c>
       <c r="BF24" t="n">
-        <v>4.2</v>
+        <v>1.01</v>
       </c>
       <c r="BG24" t="n">
-        <v>4.5</v>
+        <v>1.01</v>
       </c>
       <c r="BH24" t="n">
-        <v>5.6</v>
+        <v>1000</v>
       </c>
       <c r="BI24" t="n">
-        <v>4.3</v>
+        <v>1.04</v>
       </c>
       <c r="BJ24" t="n">
-        <v>9.199999999999999</v>
+        <v>1000</v>
       </c>
       <c r="BK24" t="n">
-        <v>4.8</v>
+        <v>1.04</v>
       </c>
       <c r="BL24" t="n">
         <v>1000</v>
       </c>
       <c r="BM24" t="n">
-        <v>8.800000000000001</v>
+        <v>1.04</v>
       </c>
       <c r="BN24" t="n">
-        <v>5.2</v>
+        <v>1000</v>
       </c>
       <c r="BO24" t="n">
-        <v>4</v>
+        <v>1.04</v>
       </c>
       <c r="BP24" t="n">
-        <v>10.5</v>
+        <v>1000</v>
       </c>
       <c r="BQ24" t="n">
-        <v>5.2</v>
+        <v>1.04</v>
       </c>
       <c r="BR24" t="n">
-        <v>18</v>
+        <v>1000</v>
       </c>
       <c r="BS24" t="n">
-        <v>6.4</v>
+        <v>1.04</v>
       </c>
       <c r="BT24" t="n">
-        <v>9.6</v>
+        <v>1000</v>
       </c>
       <c r="BU24" t="n">
-        <v>4.9</v>
+        <v>1.04</v>
       </c>
       <c r="BV24" t="n">
-        <v>34</v>
+        <v>1000</v>
       </c>
       <c r="BW24" t="n">
-        <v>7.8</v>
+        <v>1.04</v>
       </c>
       <c r="BX24" t="n">
-        <v>34</v>
+        <v>1000</v>
       </c>
       <c r="BY24" t="n">
-        <v>7.8</v>
+        <v>1.04</v>
       </c>
       <c r="BZ24" t="n">
-        <v>10.5</v>
+        <v>1000</v>
       </c>
       <c r="CA24" t="n">
-        <v>5.2</v>
+        <v>1.04</v>
       </c>
       <c r="CB24" t="inlineStr">
         <is>
-          <t>2026-06-12 07:41:10</t>
+          <t>2026-06-12 09:58:55</t>
         </is>
       </c>
     </row>
@@ -6699,7 +6699,7 @@
         </is>
       </c>
       <c r="F25" t="n">
-        <v>2.84</v>
+        <v>2.78</v>
       </c>
       <c r="G25" t="n">
         <v>2.86</v>
@@ -6708,22 +6708,22 @@
         <v>2.88</v>
       </c>
       <c r="I25" t="n">
-        <v>2.9</v>
+        <v>2.98</v>
       </c>
       <c r="J25" t="n">
-        <v>3.25</v>
+        <v>3.3</v>
       </c>
       <c r="K25" t="n">
-        <v>3.35</v>
+        <v>3.4</v>
       </c>
       <c r="L25" t="n">
-        <v>1.45</v>
+        <v>1.46</v>
       </c>
       <c r="M25" t="n">
         <v>1.09</v>
       </c>
       <c r="N25" t="n">
-        <v>3.5</v>
+        <v>3.4</v>
       </c>
       <c r="O25" t="n">
         <v>1.39</v>
@@ -6732,22 +6732,22 @@
         <v>1.83</v>
       </c>
       <c r="Q25" t="n">
-        <v>2.16</v>
+        <v>2.18</v>
       </c>
       <c r="R25" t="n">
-        <v>1.31</v>
+        <v>1.3</v>
       </c>
       <c r="S25" t="n">
-        <v>4</v>
+        <v>4.1</v>
       </c>
       <c r="T25" t="n">
-        <v>1.85</v>
+        <v>1.87</v>
       </c>
       <c r="U25" t="n">
-        <v>2.1</v>
+        <v>2.08</v>
       </c>
       <c r="V25" t="n">
-        <v>1.52</v>
+        <v>1.51</v>
       </c>
       <c r="W25" t="n">
         <v>1.53</v>
@@ -6762,22 +6762,22 @@
         <v>19.5</v>
       </c>
       <c r="AA25" t="n">
-        <v>55</v>
+        <v>50</v>
       </c>
       <c r="AB25" t="n">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="AC25" t="n">
         <v>7.8</v>
       </c>
       <c r="AD25" t="n">
-        <v>14.5</v>
+        <v>15</v>
       </c>
       <c r="AE25" t="n">
         <v>38</v>
       </c>
       <c r="AF25" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="AG25" t="n">
         <v>12.5</v>
@@ -6789,19 +6789,19 @@
         <v>60</v>
       </c>
       <c r="AJ25" t="n">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="AK25" t="n">
         <v>32</v>
       </c>
       <c r="AL25" t="n">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="AM25" t="n">
-        <v>450</v>
+        <v>120</v>
       </c>
       <c r="AN25" t="n">
-        <v>36</v>
+        <v>32</v>
       </c>
       <c r="AO25" t="n">
         <v>36</v>
@@ -6819,7 +6819,7 @@
         <v>40</v>
       </c>
       <c r="AT25" t="n">
-        <v>10</v>
+        <v>9.4</v>
       </c>
       <c r="AU25" t="n">
         <v>6.8</v>
@@ -6831,7 +6831,7 @@
         <v>30</v>
       </c>
       <c r="AX25" t="n">
-        <v>9.4</v>
+        <v>16</v>
       </c>
       <c r="AY25" t="n">
         <v>11</v>
@@ -6843,28 +6843,28 @@
         <v>48</v>
       </c>
       <c r="BB25" t="n">
-        <v>38</v>
+        <v>21</v>
       </c>
       <c r="BC25" t="n">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="BD25" t="n">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="BE25" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="BF25" t="n">
-        <v>18.5</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BG25" t="n">
         <v>13</v>
       </c>
       <c r="BH25" t="n">
-        <v>3.3</v>
+        <v>3.25</v>
       </c>
       <c r="BI25" t="n">
-        <v>2.74</v>
+        <v>2.76</v>
       </c>
       <c r="BJ25" t="n">
         <v>9.6</v>
@@ -6876,53 +6876,53 @@
         <v>1000</v>
       </c>
       <c r="BM25" t="n">
-        <v>14.5</v>
+        <v>16.5</v>
       </c>
       <c r="BN25" t="n">
-        <v>5.7</v>
+        <v>5.6</v>
       </c>
       <c r="BO25" t="n">
-        <v>5.1</v>
+        <v>5</v>
       </c>
       <c r="BP25" t="n">
-        <v>23</v>
+        <v>1000</v>
       </c>
       <c r="BQ25" t="n">
-        <v>9.6</v>
+        <v>10</v>
       </c>
       <c r="BR25" t="n">
         <v>1000</v>
       </c>
       <c r="BS25" t="n">
-        <v>11.5</v>
+        <v>12.5</v>
       </c>
       <c r="BT25" t="n">
         <v>5.7</v>
       </c>
       <c r="BU25" t="n">
-        <v>4.3</v>
+        <v>5.1</v>
       </c>
       <c r="BV25" t="n">
-        <v>1000</v>
+        <v>23</v>
       </c>
       <c r="BW25" t="n">
-        <v>9.4</v>
+        <v>10</v>
       </c>
       <c r="BX25" t="n">
         <v>1000</v>
       </c>
       <c r="BY25" t="n">
-        <v>11</v>
+        <v>12.5</v>
       </c>
       <c r="BZ25" t="n">
         <v>1000</v>
       </c>
       <c r="CA25" t="n">
-        <v>10.5</v>
+        <v>11.5</v>
       </c>
       <c r="CB25" t="inlineStr">
         <is>
-          <t>2026-06-12 07:41:10</t>
+          <t>2026-06-12 09:58:55</t>
         </is>
       </c>
     </row>
@@ -6953,25 +6953,25 @@
         </is>
       </c>
       <c r="F26" t="n">
-        <v>1.76</v>
+        <v>2.14</v>
       </c>
       <c r="G26" t="n">
-        <v>1.82</v>
+        <v>2.2</v>
       </c>
       <c r="H26" t="n">
-        <v>4.1</v>
+        <v>3.15</v>
       </c>
       <c r="I26" t="n">
-        <v>4.6</v>
+        <v>3.35</v>
       </c>
       <c r="J26" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="K26" t="n">
         <v>4.5</v>
       </c>
-      <c r="K26" t="n">
-        <v>5.1</v>
-      </c>
       <c r="L26" t="n">
-        <v>1.22</v>
+        <v>1.23</v>
       </c>
       <c r="M26" t="n">
         <v>1.02</v>
@@ -6983,148 +6983,148 @@
         <v>1.13</v>
       </c>
       <c r="P26" t="n">
-        <v>3.25</v>
+        <v>3.2</v>
       </c>
       <c r="Q26" t="n">
-        <v>1.4</v>
+        <v>1.41</v>
       </c>
       <c r="R26" t="n">
-        <v>1.92</v>
+        <v>1.89</v>
       </c>
       <c r="S26" t="n">
-        <v>2</v>
+        <v>2.04</v>
       </c>
       <c r="T26" t="n">
-        <v>1.47</v>
+        <v>1.44</v>
       </c>
       <c r="U26" t="n">
-        <v>2.82</v>
+        <v>2.96</v>
       </c>
       <c r="V26" t="n">
-        <v>1.28</v>
+        <v>1.43</v>
       </c>
       <c r="W26" t="n">
-        <v>2.2</v>
+        <v>1.83</v>
       </c>
       <c r="X26" t="n">
-        <v>95</v>
+        <v>36</v>
       </c>
       <c r="Y26" t="n">
-        <v>950</v>
+        <v>27</v>
       </c>
       <c r="Z26" t="n">
-        <v>50</v>
+        <v>220</v>
       </c>
       <c r="AA26" t="n">
-        <v>500</v>
+        <v>470</v>
       </c>
       <c r="AB26" t="n">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="AC26" t="n">
-        <v>15.5</v>
+        <v>11.5</v>
       </c>
       <c r="AD26" t="n">
-        <v>23</v>
+        <v>16</v>
       </c>
       <c r="AE26" t="n">
-        <v>120</v>
+        <v>30</v>
       </c>
       <c r="AF26" t="n">
-        <v>17</v>
+        <v>24</v>
       </c>
       <c r="AG26" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="AH26" t="n">
         <v>19</v>
       </c>
       <c r="AI26" t="n">
-        <v>100</v>
+        <v>30</v>
       </c>
       <c r="AJ26" t="n">
-        <v>75</v>
+        <v>500</v>
       </c>
       <c r="AK26" t="n">
         <v>20</v>
       </c>
       <c r="AL26" t="n">
-        <v>42</v>
+        <v>24</v>
       </c>
       <c r="AM26" t="n">
         <v>60</v>
       </c>
       <c r="AN26" t="n">
-        <v>7</v>
+        <v>8.6</v>
       </c>
       <c r="AO26" t="n">
-        <v>27</v>
+        <v>15.5</v>
       </c>
       <c r="AP26" t="n">
-        <v>18.5</v>
+        <v>29</v>
       </c>
       <c r="AQ26" t="n">
-        <v>15</v>
+        <v>22</v>
       </c>
       <c r="AR26" t="n">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="AS26" t="n">
-        <v>28</v>
+        <v>42</v>
       </c>
       <c r="AT26" t="n">
-        <v>15.5</v>
+        <v>17</v>
       </c>
       <c r="AU26" t="n">
-        <v>11</v>
+        <v>9.6</v>
       </c>
       <c r="AV26" t="n">
-        <v>16.5</v>
+        <v>13.5</v>
       </c>
       <c r="AW26" t="n">
-        <v>32</v>
+        <v>25</v>
       </c>
       <c r="AX26" t="n">
-        <v>14.5</v>
+        <v>17.5</v>
       </c>
       <c r="AY26" t="n">
-        <v>10</v>
+        <v>11.5</v>
       </c>
       <c r="AZ26" t="n">
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="BA26" t="n">
-        <v>18.5</v>
+        <v>24</v>
       </c>
       <c r="BB26" t="n">
-        <v>17.5</v>
+        <v>26</v>
       </c>
       <c r="BC26" t="n">
+        <v>17</v>
+      </c>
+      <c r="BD26" t="n">
         <v>12</v>
-      </c>
-      <c r="BD26" t="n">
-        <v>18</v>
       </c>
       <c r="BE26" t="n">
         <v>34</v>
       </c>
       <c r="BF26" t="n">
-        <v>5</v>
+        <v>7.2</v>
       </c>
       <c r="BG26" t="n">
-        <v>18.5</v>
+        <v>13</v>
       </c>
       <c r="BH26" t="n">
-        <v>5.6</v>
+        <v>5.4</v>
       </c>
       <c r="BI26" t="n">
-        <v>4.1</v>
+        <v>4</v>
       </c>
       <c r="BJ26" t="n">
-        <v>8.800000000000001</v>
+        <v>8.4</v>
       </c>
       <c r="BK26" t="n">
-        <v>6.4</v>
+        <v>6.2</v>
       </c>
       <c r="BL26" t="n">
         <v>75</v>
@@ -7133,50 +7133,50 @@
         <v>9.6</v>
       </c>
       <c r="BN26" t="n">
-        <v>5.4</v>
+        <v>6</v>
       </c>
       <c r="BO26" t="n">
-        <v>4.6</v>
+        <v>5.1</v>
       </c>
       <c r="BP26" t="n">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="BQ26" t="n">
         <v>8</v>
       </c>
       <c r="BR26" t="n">
-        <v>18</v>
+        <v>19.5</v>
       </c>
       <c r="BS26" t="n">
-        <v>7</v>
+        <v>7.2</v>
       </c>
       <c r="BT26" t="n">
-        <v>8.800000000000001</v>
+        <v>7.6</v>
       </c>
       <c r="BU26" t="n">
-        <v>6.6</v>
+        <v>5.7</v>
       </c>
       <c r="BV26" t="n">
-        <v>36</v>
+        <v>21</v>
       </c>
       <c r="BW26" t="n">
-        <v>8.199999999999999</v>
+        <v>7.4</v>
       </c>
       <c r="BX26" t="n">
-        <v>34</v>
+        <v>24</v>
       </c>
       <c r="BY26" t="n">
-        <v>8.199999999999999</v>
+        <v>7.8</v>
       </c>
       <c r="BZ26" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="CA26" t="n">
         <v>7.2</v>
       </c>
       <c r="CB26" t="inlineStr">
         <is>
-          <t>2026-06-12 07:41:10</t>
+          <t>2026-06-12 09:58:55</t>
         </is>
       </c>
     </row>
@@ -7207,58 +7207,58 @@
         </is>
       </c>
       <c r="F27" t="n">
-        <v>3.15</v>
+        <v>3.25</v>
       </c>
       <c r="G27" t="n">
-        <v>4</v>
+        <v>3.85</v>
       </c>
       <c r="H27" t="n">
-        <v>2.38</v>
+        <v>2.4</v>
       </c>
       <c r="I27" t="n">
-        <v>2.9</v>
+        <v>2.7</v>
       </c>
       <c r="J27" t="n">
-        <v>2.68</v>
+        <v>2.8</v>
       </c>
       <c r="K27" t="n">
         <v>3.2</v>
       </c>
       <c r="L27" t="n">
-        <v>1.46</v>
+        <v>1.55</v>
       </c>
       <c r="M27" t="n">
-        <v>1.1</v>
+        <v>1.12</v>
       </c>
       <c r="N27" t="n">
-        <v>2.52</v>
+        <v>2.68</v>
       </c>
       <c r="O27" t="n">
-        <v>1.47</v>
+        <v>1.5</v>
       </c>
       <c r="P27" t="n">
-        <v>1.52</v>
+        <v>1.54</v>
       </c>
       <c r="Q27" t="n">
-        <v>2.4</v>
+        <v>2.56</v>
       </c>
       <c r="R27" t="n">
         <v>1.19</v>
       </c>
       <c r="S27" t="n">
-        <v>3.55</v>
+        <v>4.9</v>
       </c>
       <c r="T27" t="n">
-        <v>1.94</v>
+        <v>1.95</v>
       </c>
       <c r="U27" t="n">
-        <v>1.78</v>
+        <v>1.76</v>
       </c>
       <c r="V27" t="n">
-        <v>1.52</v>
+        <v>1.59</v>
       </c>
       <c r="W27" t="n">
-        <v>1.33</v>
+        <v>1.37</v>
       </c>
       <c r="X27" t="n">
         <v>17</v>
@@ -7276,7 +7276,7 @@
         <v>500</v>
       </c>
       <c r="AC27" t="n">
-        <v>14</v>
+        <v>7.6</v>
       </c>
       <c r="AD27" t="n">
         <v>500</v>
@@ -7315,46 +7315,46 @@
         <v>600</v>
       </c>
       <c r="AP27" t="n">
-        <v>4.2</v>
+        <v>7</v>
       </c>
       <c r="AQ27" t="n">
-        <v>4.2</v>
+        <v>6.6</v>
       </c>
       <c r="AR27" t="n">
         <v>6.2</v>
       </c>
       <c r="AS27" t="n">
-        <v>5.6</v>
+        <v>5.7</v>
       </c>
       <c r="AT27" t="n">
         <v>5.6</v>
       </c>
       <c r="AU27" t="n">
-        <v>4.2</v>
+        <v>5.6</v>
       </c>
       <c r="AV27" t="n">
         <v>7</v>
       </c>
       <c r="AW27" t="n">
-        <v>5.5</v>
+        <v>5.7</v>
       </c>
       <c r="AX27" t="n">
-        <v>5.1</v>
+        <v>10</v>
       </c>
       <c r="AY27" t="n">
-        <v>4.7</v>
+        <v>6.8</v>
       </c>
       <c r="AZ27" t="n">
-        <v>4.9</v>
+        <v>5.4</v>
       </c>
       <c r="BA27" t="n">
+        <v>6</v>
+      </c>
+      <c r="BB27" t="n">
+        <v>6</v>
+      </c>
+      <c r="BC27" t="n">
         <v>5.9</v>
-      </c>
-      <c r="BB27" t="n">
-        <v>5.9</v>
-      </c>
-      <c r="BC27" t="n">
-        <v>5.8</v>
       </c>
       <c r="BD27" t="n">
         <v>6</v>
@@ -7366,13 +7366,13 @@
         <v>6</v>
       </c>
       <c r="BG27" t="n">
-        <v>7.8</v>
+        <v>6.2</v>
       </c>
       <c r="BH27" t="n">
-        <v>2.94</v>
+        <v>2.92</v>
       </c>
       <c r="BI27" t="n">
-        <v>2.26</v>
+        <v>2.24</v>
       </c>
       <c r="BJ27" t="n">
         <v>1000</v>
@@ -7384,13 +7384,13 @@
         <v>1000</v>
       </c>
       <c r="BM27" t="n">
-        <v>2.14</v>
+        <v>7.6</v>
       </c>
       <c r="BN27" t="n">
-        <v>7</v>
+        <v>1000</v>
       </c>
       <c r="BO27" t="n">
-        <v>3.75</v>
+        <v>3.65</v>
       </c>
       <c r="BP27" t="n">
         <v>1000</v>
@@ -7402,10 +7402,10 @@
         <v>1000</v>
       </c>
       <c r="BS27" t="n">
-        <v>7</v>
+        <v>3.45</v>
       </c>
       <c r="BT27" t="n">
-        <v>5.6</v>
+        <v>5.7</v>
       </c>
       <c r="BU27" t="n">
         <v>3.3</v>
@@ -7430,7 +7430,7 @@
       </c>
       <c r="CB27" t="inlineStr">
         <is>
-          <t>2026-06-12 07:41:10</t>
+          <t>2026-06-12 09:58:55</t>
         </is>
       </c>
     </row>
@@ -7461,19 +7461,19 @@
         </is>
       </c>
       <c r="F28" t="n">
-        <v>2.26</v>
+        <v>2.22</v>
       </c>
       <c r="G28" t="n">
-        <v>2.32</v>
+        <v>2.24</v>
       </c>
       <c r="H28" t="n">
-        <v>3.65</v>
+        <v>3.8</v>
       </c>
       <c r="I28" t="n">
-        <v>3.8</v>
+        <v>3.9</v>
       </c>
       <c r="J28" t="n">
-        <v>3.35</v>
+        <v>3.4</v>
       </c>
       <c r="K28" t="n">
         <v>3.45</v>
@@ -7482,130 +7482,130 @@
         <v>1.5</v>
       </c>
       <c r="M28" t="n">
-        <v>1.1</v>
+        <v>1.09</v>
       </c>
       <c r="N28" t="n">
-        <v>3.15</v>
+        <v>3.35</v>
       </c>
       <c r="O28" t="n">
-        <v>1.43</v>
+        <v>1.4</v>
       </c>
       <c r="P28" t="n">
-        <v>1.7</v>
+        <v>1.76</v>
       </c>
       <c r="Q28" t="n">
-        <v>2.34</v>
+        <v>2.24</v>
       </c>
       <c r="R28" t="n">
-        <v>1.26</v>
+        <v>1.28</v>
       </c>
       <c r="S28" t="n">
-        <v>4.5</v>
+        <v>4.3</v>
       </c>
       <c r="T28" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="U28" t="n">
         <v>1.98</v>
       </c>
-      <c r="U28" t="n">
-        <v>1.93</v>
-      </c>
       <c r="V28" t="n">
-        <v>1.35</v>
+        <v>1.34</v>
       </c>
       <c r="W28" t="n">
-        <v>1.75</v>
+        <v>1.8</v>
       </c>
       <c r="X28" t="n">
         <v>11.5</v>
       </c>
       <c r="Y28" t="n">
-        <v>20</v>
+        <v>13.5</v>
       </c>
       <c r="Z28" t="n">
-        <v>500</v>
+        <v>26</v>
       </c>
       <c r="AA28" t="n">
-        <v>900</v>
+        <v>80</v>
       </c>
       <c r="AB28" t="n">
-        <v>8.199999999999999</v>
+        <v>8.6</v>
       </c>
       <c r="AC28" t="n">
-        <v>8</v>
+        <v>7.8</v>
       </c>
       <c r="AD28" t="n">
         <v>30</v>
       </c>
       <c r="AE28" t="n">
-        <v>500</v>
+        <v>55</v>
       </c>
       <c r="AF28" t="n">
         <v>12.5</v>
       </c>
       <c r="AG28" t="n">
-        <v>12.5</v>
+        <v>11</v>
       </c>
       <c r="AH28" t="n">
-        <v>60</v>
+        <v>21</v>
       </c>
       <c r="AI28" t="n">
-        <v>500</v>
+        <v>70</v>
       </c>
       <c r="AJ28" t="n">
-        <v>900</v>
+        <v>32</v>
       </c>
       <c r="AK28" t="n">
-        <v>85</v>
+        <v>27</v>
       </c>
       <c r="AL28" t="n">
-        <v>500</v>
+        <v>120</v>
       </c>
       <c r="AM28" t="n">
-        <v>580</v>
+        <v>150</v>
       </c>
       <c r="AN28" t="n">
-        <v>600</v>
+        <v>23</v>
       </c>
       <c r="AO28" t="n">
-        <v>600</v>
+        <v>65</v>
       </c>
       <c r="AP28" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AQ28" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="AR28" t="n">
+        <v>23</v>
+      </c>
+      <c r="AS28" t="n">
+        <v>28</v>
+      </c>
+      <c r="AT28" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="AU28" t="n">
+        <v>7</v>
+      </c>
+      <c r="AV28" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="AW28" t="n">
+        <v>26</v>
+      </c>
+      <c r="AX28" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="AY28" t="n">
         <v>9.6</v>
       </c>
-      <c r="AQ28" t="n">
-        <v>10</v>
-      </c>
-      <c r="AR28" t="n">
-        <v>22</v>
-      </c>
-      <c r="AS28" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="AT28" t="n">
-        <v>7.2</v>
-      </c>
-      <c r="AU28" t="n">
-        <v>6.6</v>
-      </c>
-      <c r="AV28" t="n">
-        <v>13.5</v>
-      </c>
-      <c r="AW28" t="n">
-        <v>21</v>
-      </c>
-      <c r="AX28" t="n">
-        <v>11</v>
-      </c>
-      <c r="AY28" t="n">
-        <v>8.4</v>
-      </c>
       <c r="AZ28" t="n">
-        <v>11</v>
+        <v>18.5</v>
       </c>
       <c r="BA28" t="n">
         <v>28</v>
       </c>
       <c r="BB28" t="n">
-        <v>26</v>
+        <v>14.5</v>
       </c>
       <c r="BC28" t="n">
         <v>23</v>
@@ -7614,77 +7614,77 @@
         <v>38</v>
       </c>
       <c r="BE28" t="n">
+        <v>100</v>
+      </c>
+      <c r="BF28" t="n">
+        <v>10</v>
+      </c>
+      <c r="BG28" t="n">
+        <v>50</v>
+      </c>
+      <c r="BH28" t="n">
+        <v>2.94</v>
+      </c>
+      <c r="BI28" t="n">
+        <v>2.78</v>
+      </c>
+      <c r="BJ28" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="BK28" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="BL28" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BM28" t="n">
+        <v>130</v>
+      </c>
+      <c r="BN28" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="BO28" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="BP28" t="n">
+        <v>18</v>
+      </c>
+      <c r="BQ28" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="BR28" t="n">
+        <v>36</v>
+      </c>
+      <c r="BS28" t="n">
         <v>11</v>
       </c>
-      <c r="BF28" t="n">
-        <v>21</v>
-      </c>
-      <c r="BG28" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="BH28" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="BI28" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="BJ28" t="n">
+      <c r="BT28" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="BU28" t="n">
+        <v>6</v>
+      </c>
+      <c r="BV28" t="n">
+        <v>36</v>
+      </c>
+      <c r="BW28" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="BX28" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BY28" t="n">
+        <v>13</v>
+      </c>
+      <c r="BZ28" t="n">
+        <v>1000</v>
+      </c>
+      <c r="CA28" t="n">
         <v>11</v>
       </c>
-      <c r="BK28" t="n">
-        <v>5.3</v>
-      </c>
-      <c r="BL28" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BM28" t="n">
-        <v>9.800000000000001</v>
-      </c>
-      <c r="BN28" t="n">
-        <v>5.1</v>
-      </c>
-      <c r="BO28" t="n">
-        <v>3.95</v>
-      </c>
-      <c r="BP28" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BQ28" t="n">
-        <v>6.6</v>
-      </c>
-      <c r="BR28" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BS28" t="n">
-        <v>8.199999999999999</v>
-      </c>
-      <c r="BT28" t="n">
-        <v>7.2</v>
-      </c>
-      <c r="BU28" t="n">
-        <v>5.8</v>
-      </c>
-      <c r="BV28" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BW28" t="n">
-        <v>8</v>
-      </c>
-      <c r="BX28" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BY28" t="n">
-        <v>8.800000000000001</v>
-      </c>
-      <c r="BZ28" t="n">
-        <v>1000</v>
-      </c>
-      <c r="CA28" t="n">
-        <v>8.199999999999999</v>
-      </c>
       <c r="CB28" t="inlineStr">
         <is>
-          <t>2026-06-12 07:41:10</t>
+          <t>2026-06-12 09:58:55</t>
         </is>
       </c>
     </row>
@@ -7715,10 +7715,10 @@
         </is>
       </c>
       <c r="F29" t="n">
-        <v>2.02</v>
+        <v>2.04</v>
       </c>
       <c r="G29" t="n">
-        <v>2.08</v>
+        <v>2.1</v>
       </c>
       <c r="H29" t="n">
         <v>3.85</v>
@@ -7736,7 +7736,7 @@
         <v>1.37</v>
       </c>
       <c r="M29" t="n">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="N29" t="n">
         <v>4.4</v>
@@ -7748,7 +7748,7 @@
         <v>2.14</v>
       </c>
       <c r="Q29" t="n">
-        <v>1.82</v>
+        <v>1.84</v>
       </c>
       <c r="R29" t="n">
         <v>1.45</v>
@@ -7766,19 +7766,19 @@
         <v>1.32</v>
       </c>
       <c r="W29" t="n">
-        <v>1.93</v>
+        <v>1.91</v>
       </c>
       <c r="X29" t="n">
-        <v>17.5</v>
+        <v>18</v>
       </c>
       <c r="Y29" t="n">
-        <v>17</v>
+        <v>16.5</v>
       </c>
       <c r="Z29" t="n">
         <v>48</v>
       </c>
       <c r="AA29" t="n">
-        <v>95</v>
+        <v>75</v>
       </c>
       <c r="AB29" t="n">
         <v>11</v>
@@ -7787,19 +7787,19 @@
         <v>8.800000000000001</v>
       </c>
       <c r="AD29" t="n">
-        <v>16.5</v>
+        <v>16</v>
       </c>
       <c r="AE29" t="n">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="AF29" t="n">
-        <v>13.5</v>
+        <v>14</v>
       </c>
       <c r="AG29" t="n">
         <v>10.5</v>
       </c>
       <c r="AH29" t="n">
-        <v>17</v>
+        <v>16.5</v>
       </c>
       <c r="AI29" t="n">
         <v>50</v>
@@ -7811,16 +7811,16 @@
         <v>21</v>
       </c>
       <c r="AL29" t="n">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="AM29" t="n">
-        <v>85</v>
+        <v>80</v>
       </c>
       <c r="AN29" t="n">
         <v>13</v>
       </c>
       <c r="AO29" t="n">
-        <v>100</v>
+        <v>40</v>
       </c>
       <c r="AP29" t="n">
         <v>15.5</v>
@@ -7829,10 +7829,10 @@
         <v>14.5</v>
       </c>
       <c r="AR29" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="AS29" t="n">
-        <v>40</v>
+        <v>34</v>
       </c>
       <c r="AT29" t="n">
         <v>9.6</v>
@@ -7844,7 +7844,7 @@
         <v>14</v>
       </c>
       <c r="AW29" t="n">
-        <v>38</v>
+        <v>25</v>
       </c>
       <c r="AX29" t="n">
         <v>11.5</v>
@@ -7856,7 +7856,7 @@
         <v>15</v>
       </c>
       <c r="BA29" t="n">
-        <v>32</v>
+        <v>27</v>
       </c>
       <c r="BB29" t="n">
         <v>21</v>
@@ -7868,16 +7868,16 @@
         <v>26</v>
       </c>
       <c r="BE29" t="n">
-        <v>34</v>
+        <v>42</v>
       </c>
       <c r="BF29" t="n">
         <v>11</v>
       </c>
       <c r="BG29" t="n">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="BH29" t="n">
-        <v>3.8</v>
+        <v>3.75</v>
       </c>
       <c r="BI29" t="n">
         <v>3</v>
@@ -7886,31 +7886,31 @@
         <v>9.199999999999999</v>
       </c>
       <c r="BK29" t="n">
-        <v>5.7</v>
+        <v>5.8</v>
       </c>
       <c r="BL29" t="n">
         <v>1000</v>
       </c>
       <c r="BM29" t="n">
-        <v>13</v>
+        <v>13.5</v>
       </c>
       <c r="BN29" t="n">
         <v>5</v>
       </c>
       <c r="BO29" t="n">
-        <v>3.8</v>
+        <v>3.85</v>
       </c>
       <c r="BP29" t="n">
         <v>14</v>
       </c>
       <c r="BQ29" t="n">
-        <v>7.2</v>
+        <v>7.4</v>
       </c>
       <c r="BR29" t="n">
         <v>26</v>
       </c>
       <c r="BS29" t="n">
-        <v>9.4</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BT29" t="n">
         <v>7.4</v>
@@ -7928,17 +7928,17 @@
         <v>38</v>
       </c>
       <c r="BY29" t="n">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="BZ29" t="n">
         <v>21</v>
       </c>
       <c r="CA29" t="n">
-        <v>8.800000000000001</v>
+        <v>9</v>
       </c>
       <c r="CB29" t="inlineStr">
         <is>
-          <t>2026-06-12 07:41:10</t>
+          <t>2026-06-12 09:58:55</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-06-12.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-06-12.xlsx
@@ -857,230 +857,230 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>1.55</v>
+        <v>1.61</v>
       </c>
       <c r="G2" t="n">
-        <v>1.6</v>
+        <v>1.66</v>
       </c>
       <c r="H2" t="n">
-        <v>6.6</v>
+        <v>7.2</v>
       </c>
       <c r="I2" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="J2" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="K2" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="L2" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="M2" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="N2" t="n">
+        <v>3.55</v>
+      </c>
+      <c r="O2" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="P2" t="n">
+        <v>1.86</v>
+      </c>
+      <c r="Q2" t="n">
+        <v>2.06</v>
+      </c>
+      <c r="R2" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="S2" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="T2" t="n">
+        <v>1.98</v>
+      </c>
+      <c r="U2" t="n">
+        <v>1.87</v>
+      </c>
+      <c r="V2" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="W2" t="n">
+        <v>2.42</v>
+      </c>
+      <c r="X2" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="Y2" t="n">
+        <v>22</v>
+      </c>
+      <c r="Z2" t="n">
+        <v>70</v>
+      </c>
+      <c r="AA2" t="n">
+        <v>290</v>
+      </c>
+      <c r="AB2" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="AC2" t="n">
+        <v>9</v>
+      </c>
+      <c r="AD2" t="n">
+        <v>34</v>
+      </c>
+      <c r="AE2" t="n">
+        <v>140</v>
+      </c>
+      <c r="AF2" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="AG2" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="AH2" t="n">
+        <v>26</v>
+      </c>
+      <c r="AI2" t="n">
+        <v>140</v>
+      </c>
+      <c r="AJ2" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="AK2" t="n">
+        <v>19.5</v>
+      </c>
+      <c r="AL2" t="n">
+        <v>55</v>
+      </c>
+      <c r="AM2" t="n">
+        <v>200</v>
+      </c>
+      <c r="AN2" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="AO2" t="n">
+        <v>230</v>
+      </c>
+      <c r="AP2" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="AQ2" t="n">
+        <v>21</v>
+      </c>
+      <c r="AR2" t="n">
+        <v>36</v>
+      </c>
+      <c r="AS2" t="n">
+        <v>11</v>
+      </c>
+      <c r="AT2" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="AU2" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="AV2" t="n">
+        <v>23</v>
+      </c>
+      <c r="AW2" t="n">
+        <v>80</v>
+      </c>
+      <c r="AX2" t="n">
         <v>7.8</v>
       </c>
-      <c r="J2" t="n">
+      <c r="AY2" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="AZ2" t="n">
+        <v>21</v>
+      </c>
+      <c r="BA2" t="n">
+        <v>85</v>
+      </c>
+      <c r="BB2" t="n">
+        <v>13</v>
+      </c>
+      <c r="BC2" t="n">
+        <v>16</v>
+      </c>
+      <c r="BD2" t="n">
+        <v>26</v>
+      </c>
+      <c r="BE2" t="n">
+        <v>110</v>
+      </c>
+      <c r="BF2" t="n">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="BG2" t="n">
+        <v>100</v>
+      </c>
+      <c r="BH2" t="n">
+        <v>3.15</v>
+      </c>
+      <c r="BI2" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="BJ2" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="BK2" t="n">
+        <v>10</v>
+      </c>
+      <c r="BL2" t="n">
+        <v>960</v>
+      </c>
+      <c r="BM2" t="n">
+        <v>23</v>
+      </c>
+      <c r="BN2" t="n">
         <v>4.1</v>
       </c>
-      <c r="K2" t="n">
-        <v>4.8</v>
-      </c>
-      <c r="L2" t="n">
-        <v>1.39</v>
-      </c>
-      <c r="M2" t="n">
-        <v>1.06</v>
-      </c>
-      <c r="N2" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="O2" t="n">
-        <v>1.29</v>
-      </c>
-      <c r="P2" t="n">
-        <v>2.02</v>
-      </c>
-      <c r="Q2" t="n">
-        <v>1.9</v>
-      </c>
-      <c r="R2" t="n">
-        <v>1.39</v>
-      </c>
-      <c r="S2" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="T2" t="n">
-        <v>1.96</v>
-      </c>
-      <c r="U2" t="n">
-        <v>1.89</v>
-      </c>
-      <c r="V2" t="n">
-        <v>1.15</v>
-      </c>
-      <c r="W2" t="n">
-        <v>2.66</v>
-      </c>
-      <c r="X2" t="n">
-        <v>90</v>
-      </c>
-      <c r="Y2" t="n">
+      <c r="BO2" t="n">
+        <v>3.55</v>
+      </c>
+      <c r="BP2" t="n">
+        <v>12</v>
+      </c>
+      <c r="BQ2" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="BR2" t="n">
+        <v>36</v>
+      </c>
+      <c r="BS2" t="n">
+        <v>27</v>
+      </c>
+      <c r="BT2" t="n">
+        <v>10</v>
+      </c>
+      <c r="BU2" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="BV2" t="n">
+        <v>80</v>
+      </c>
+      <c r="BW2" t="n">
+        <v>10</v>
+      </c>
+      <c r="BX2" t="n">
         <v>950</v>
       </c>
-      <c r="Z2" t="n">
-        <v>220</v>
-      </c>
-      <c r="AA2" t="n">
-        <v>700</v>
-      </c>
-      <c r="AB2" t="n">
-        <v>14</v>
-      </c>
-      <c r="AC2" t="n">
-        <v>14</v>
-      </c>
-      <c r="AD2" t="n">
-        <v>500</v>
-      </c>
-      <c r="AE2" t="n">
-        <v>700</v>
-      </c>
-      <c r="AF2" t="n">
-        <v>40</v>
-      </c>
-      <c r="AG2" t="n">
-        <v>36</v>
-      </c>
-      <c r="AH2" t="n">
-        <v>950</v>
-      </c>
-      <c r="AI2" t="n">
-        <v>700</v>
-      </c>
-      <c r="AJ2" t="n">
-        <v>500</v>
-      </c>
-      <c r="AK2" t="n">
-        <v>970</v>
-      </c>
-      <c r="AL2" t="n">
-        <v>500</v>
-      </c>
-      <c r="AM2" t="n">
-        <v>700</v>
-      </c>
-      <c r="AN2" t="n">
-        <v>29</v>
-      </c>
-      <c r="AO2" t="n">
-        <v>180</v>
-      </c>
-      <c r="AP2" t="n">
-        <v>7.8</v>
-      </c>
-      <c r="AQ2" t="n">
-        <v>5</v>
-      </c>
-      <c r="AR2" t="n">
-        <v>5.5</v>
-      </c>
-      <c r="AS2" t="n">
-        <v>6.2</v>
-      </c>
-      <c r="AT2" t="n">
-        <v>6.2</v>
-      </c>
-      <c r="AU2" t="n">
-        <v>7</v>
-      </c>
-      <c r="AV2" t="n">
-        <v>8.6</v>
-      </c>
-      <c r="AW2" t="n">
-        <v>6</v>
-      </c>
-      <c r="AX2" t="n">
-        <v>5.7</v>
-      </c>
-      <c r="AY2" t="n">
-        <v>6.8</v>
-      </c>
-      <c r="AZ2" t="n">
-        <v>9.800000000000001</v>
-      </c>
-      <c r="BA2" t="n">
-        <v>6</v>
-      </c>
-      <c r="BB2" t="n">
-        <v>8</v>
-      </c>
-      <c r="BC2" t="n">
-        <v>7.8</v>
-      </c>
-      <c r="BD2" t="n">
-        <v>12</v>
-      </c>
-      <c r="BE2" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="BF2" t="n">
-        <v>7.4</v>
-      </c>
-      <c r="BG2" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="BH2" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="BI2" t="n">
-        <v>3.15</v>
-      </c>
-      <c r="BJ2" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BK2" t="n">
-        <v>6.4</v>
-      </c>
-      <c r="BL2" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BM2" t="n">
-        <v>3.25</v>
-      </c>
-      <c r="BN2" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="BO2" t="n">
-        <v>3.7</v>
-      </c>
-      <c r="BP2" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BQ2" t="n">
-        <v>6.2</v>
-      </c>
-      <c r="BR2" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BS2" t="n">
-        <v>4.9</v>
-      </c>
-      <c r="BT2" t="n">
-        <v>24</v>
-      </c>
-      <c r="BU2" t="n">
-        <v>7.2</v>
-      </c>
-      <c r="BV2" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BW2" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="BX2" t="n">
-        <v>1000</v>
-      </c>
       <c r="BY2" t="n">
-        <v>4.5</v>
+        <v>10</v>
       </c>
       <c r="BZ2" t="n">
-        <v>1000</v>
+        <v>34</v>
       </c>
       <c r="CA2" t="n">
-        <v>7.6</v>
+        <v>23</v>
       </c>
       <c r="CB2" t="inlineStr">
         <is>
-          <t>2026-06-12 09:58:55</t>
+          <t>2026-06-12 12:17:49</t>
         </is>
       </c>
     </row>
@@ -1111,230 +1111,230 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>2.64</v>
+        <v>2.76</v>
       </c>
       <c r="G3" t="n">
-        <v>2.76</v>
+        <v>2.86</v>
       </c>
       <c r="H3" t="n">
-        <v>2.74</v>
+        <v>2.68</v>
       </c>
       <c r="I3" t="n">
-        <v>2.88</v>
+        <v>2.8</v>
       </c>
       <c r="J3" t="n">
         <v>3.55</v>
       </c>
       <c r="K3" t="n">
-        <v>3.7</v>
+        <v>3.65</v>
       </c>
       <c r="L3" t="n">
-        <v>1.35</v>
+        <v>1.5</v>
       </c>
       <c r="M3" t="n">
-        <v>1.05</v>
+        <v>1.07</v>
       </c>
       <c r="N3" t="n">
-        <v>4.7</v>
+        <v>3.85</v>
       </c>
       <c r="O3" t="n">
-        <v>1.25</v>
+        <v>1.33</v>
       </c>
       <c r="P3" t="n">
-        <v>2.22</v>
+        <v>2</v>
       </c>
       <c r="Q3" t="n">
+        <v>1.94</v>
+      </c>
+      <c r="R3" t="n">
+        <v>1.37</v>
+      </c>
+      <c r="S3" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="T3" t="n">
         <v>1.76</v>
       </c>
-      <c r="R3" t="n">
-        <v>1.48</v>
-      </c>
-      <c r="S3" t="n">
-        <v>2.92</v>
-      </c>
-      <c r="T3" t="n">
-        <v>1.62</v>
-      </c>
       <c r="U3" t="n">
-        <v>2.42</v>
+        <v>2.18</v>
       </c>
       <c r="V3" t="n">
-        <v>1.53</v>
+        <v>1.54</v>
       </c>
       <c r="W3" t="n">
-        <v>1.56</v>
+        <v>1.55</v>
       </c>
       <c r="X3" t="n">
-        <v>21</v>
+        <v>15.5</v>
       </c>
       <c r="Y3" t="n">
-        <v>14</v>
+        <v>12.5</v>
       </c>
       <c r="Z3" t="n">
-        <v>25</v>
+        <v>19.5</v>
       </c>
       <c r="AA3" t="n">
-        <v>50</v>
+        <v>55</v>
       </c>
       <c r="AB3" t="n">
-        <v>14</v>
+        <v>12.5</v>
       </c>
       <c r="AC3" t="n">
-        <v>8.4</v>
+        <v>7.8</v>
       </c>
       <c r="AD3" t="n">
-        <v>14.5</v>
+        <v>13</v>
       </c>
       <c r="AE3" t="n">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="AF3" t="n">
-        <v>20</v>
+        <v>18.5</v>
       </c>
       <c r="AG3" t="n">
-        <v>15</v>
+        <v>12.5</v>
       </c>
       <c r="AH3" t="n">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="AI3" t="n">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="AJ3" t="n">
-        <v>46</v>
+        <v>55</v>
       </c>
       <c r="AK3" t="n">
-        <v>26</v>
+        <v>32</v>
       </c>
       <c r="AL3" t="n">
-        <v>44</v>
+        <v>55</v>
       </c>
       <c r="AM3" t="n">
-        <v>200</v>
+        <v>100</v>
       </c>
       <c r="AN3" t="n">
-        <v>22</v>
+        <v>29</v>
       </c>
       <c r="AO3" t="n">
-        <v>23</v>
+        <v>27</v>
       </c>
       <c r="AP3" t="n">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="AQ3" t="n">
-        <v>12.5</v>
+        <v>11</v>
       </c>
       <c r="AR3" t="n">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="AS3" t="n">
-        <v>18</v>
+        <v>32</v>
       </c>
       <c r="AT3" t="n">
-        <v>12</v>
+        <v>10.5</v>
       </c>
       <c r="AU3" t="n">
-        <v>7.6</v>
+        <v>7</v>
       </c>
       <c r="AV3" t="n">
         <v>11</v>
       </c>
       <c r="AW3" t="n">
-        <v>13.5</v>
+        <v>25</v>
       </c>
       <c r="AX3" t="n">
-        <v>17</v>
+        <v>15.5</v>
       </c>
       <c r="AY3" t="n">
+        <v>11</v>
+      </c>
+      <c r="AZ3" t="n">
+        <v>15</v>
+      </c>
+      <c r="BA3" t="n">
+        <v>34</v>
+      </c>
+      <c r="BB3" t="n">
+        <v>25</v>
+      </c>
+      <c r="BC3" t="n">
+        <v>25</v>
+      </c>
+      <c r="BD3" t="n">
+        <v>30</v>
+      </c>
+      <c r="BE3" t="n">
+        <v>65</v>
+      </c>
+      <c r="BF3" t="n">
+        <v>22</v>
+      </c>
+      <c r="BG3" t="n">
+        <v>22</v>
+      </c>
+      <c r="BH3" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="BI3" t="n">
+        <v>2.94</v>
+      </c>
+      <c r="BJ3" t="n">
         <v>10.5</v>
       </c>
-      <c r="AZ3" t="n">
-        <v>13.5</v>
-      </c>
-      <c r="BA3" t="n">
-        <v>18.5</v>
-      </c>
-      <c r="BB3" t="n">
-        <v>18</v>
-      </c>
-      <c r="BC3" t="n">
+      <c r="BK3" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="BL3" t="n">
+        <v>180</v>
+      </c>
+      <c r="BM3" t="n">
+        <v>100</v>
+      </c>
+      <c r="BN3" t="n">
+        <v>5.6</v>
+      </c>
+      <c r="BO3" t="n">
+        <v>5</v>
+      </c>
+      <c r="BP3" t="n">
         <v>22</v>
       </c>
-      <c r="BD3" t="n">
-        <v>18</v>
-      </c>
-      <c r="BE3" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="BF3" t="n">
-        <v>17</v>
-      </c>
-      <c r="BG3" t="n">
-        <v>18.5</v>
-      </c>
-      <c r="BH3" t="n">
-        <v>3.8</v>
-      </c>
-      <c r="BI3" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="BJ3" t="n">
-        <v>8.800000000000001</v>
-      </c>
-      <c r="BK3" t="n">
-        <v>6.4</v>
-      </c>
-      <c r="BL3" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BM3" t="n">
-        <v>14</v>
-      </c>
-      <c r="BN3" t="n">
-        <v>5.8</v>
-      </c>
-      <c r="BO3" t="n">
-        <v>5.1</v>
-      </c>
-      <c r="BP3" t="n">
-        <v>18</v>
-      </c>
       <c r="BQ3" t="n">
-        <v>8.6</v>
+        <v>20</v>
       </c>
       <c r="BR3" t="n">
-        <v>1000</v>
+        <v>44</v>
       </c>
       <c r="BS3" t="n">
-        <v>10.5</v>
+        <v>34</v>
       </c>
       <c r="BT3" t="n">
-        <v>6.2</v>
+        <v>5.7</v>
       </c>
       <c r="BU3" t="n">
-        <v>5.4</v>
+        <v>5</v>
       </c>
       <c r="BV3" t="n">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="BW3" t="n">
-        <v>9.4</v>
+        <v>20</v>
       </c>
       <c r="BX3" t="n">
+        <v>42</v>
+      </c>
+      <c r="BY3" t="n">
+        <v>34</v>
+      </c>
+      <c r="BZ3" t="n">
+        <v>42</v>
+      </c>
+      <c r="CA3" t="n">
         <v>30</v>
       </c>
-      <c r="BY3" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="BZ3" t="n">
-        <v>21</v>
-      </c>
-      <c r="CA3" t="n">
-        <v>9.4</v>
-      </c>
       <c r="CB3" t="inlineStr">
         <is>
-          <t>2026-06-12 09:58:55</t>
+          <t>2026-06-12 12:17:49</t>
         </is>
       </c>
     </row>
@@ -1365,230 +1365,230 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>2.96</v>
+        <v>3.3</v>
       </c>
       <c r="G4" t="n">
-        <v>3.25</v>
+        <v>3.45</v>
       </c>
       <c r="H4" t="n">
-        <v>3</v>
+        <v>3.05</v>
       </c>
       <c r="I4" t="n">
-        <v>3.25</v>
+        <v>3.2</v>
       </c>
       <c r="J4" t="n">
-        <v>2.66</v>
+        <v>2.56</v>
       </c>
       <c r="K4" t="n">
-        <v>2.84</v>
+        <v>2.64</v>
       </c>
       <c r="L4" t="n">
-        <v>1.67</v>
+        <v>2.08</v>
       </c>
       <c r="M4" t="n">
-        <v>1.17</v>
+        <v>1.25</v>
       </c>
       <c r="N4" t="n">
-        <v>2.42</v>
+        <v>1.98</v>
       </c>
       <c r="O4" t="n">
-        <v>1.64</v>
+        <v>1.97</v>
       </c>
       <c r="P4" t="n">
-        <v>1.43</v>
+        <v>1.28</v>
       </c>
       <c r="Q4" t="n">
-        <v>3.05</v>
+        <v>4.2</v>
       </c>
       <c r="R4" t="n">
-        <v>1.15</v>
+        <v>1.08</v>
       </c>
       <c r="S4" t="n">
-        <v>6.6</v>
+        <v>11</v>
       </c>
       <c r="T4" t="n">
-        <v>1.75</v>
+        <v>2.56</v>
       </c>
       <c r="U4" t="n">
-        <v>1.75</v>
+        <v>1.51</v>
       </c>
       <c r="V4" t="n">
         <v>1.44</v>
       </c>
       <c r="W4" t="n">
-        <v>1.44</v>
+        <v>1.4</v>
       </c>
       <c r="X4" t="n">
-        <v>970</v>
+        <v>5.2</v>
       </c>
       <c r="Y4" t="n">
-        <v>970</v>
+        <v>7</v>
       </c>
       <c r="Z4" t="n">
-        <v>500</v>
+        <v>22</v>
       </c>
       <c r="AA4" t="n">
-        <v>500</v>
+        <v>1000</v>
       </c>
       <c r="AB4" t="n">
-        <v>970</v>
+        <v>7.8</v>
       </c>
       <c r="AC4" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="AD4" t="n">
+        <v>21</v>
+      </c>
+      <c r="AE4" t="n">
+        <v>85</v>
+      </c>
+      <c r="AF4" t="n">
+        <v>23</v>
+      </c>
+      <c r="AG4" t="n">
+        <v>990</v>
+      </c>
+      <c r="AH4" t="n">
+        <v>990</v>
+      </c>
+      <c r="AI4" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AJ4" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AK4" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AL4" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AM4" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AN4" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AO4" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AP4" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="AQ4" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="AR4" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="AS4" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="AT4" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="AU4" t="n">
+        <v>5.8</v>
+      </c>
+      <c r="AV4" t="n">
+        <v>13</v>
+      </c>
+      <c r="AW4" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="AX4" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="AY4" t="n">
+        <v>14</v>
+      </c>
+      <c r="AZ4" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="BA4" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="BB4" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="BC4" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="BD4" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="BE4" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="BF4" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="BG4" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="BH4" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="BI4" t="n">
+        <v>1.89</v>
+      </c>
+      <c r="BJ4" t="n">
+        <v>950</v>
+      </c>
+      <c r="BK4" t="n">
+        <v>13</v>
+      </c>
+      <c r="BL4" t="n">
+        <v>960</v>
+      </c>
+      <c r="BM4" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="BN4" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="BO4" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="BP4" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BQ4" t="n">
+        <v>3.15</v>
+      </c>
+      <c r="BR4" t="n">
+        <v>910</v>
+      </c>
+      <c r="BS4" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="BT4" t="n">
         <v>7</v>
       </c>
-      <c r="AD4" t="n">
-        <v>970</v>
-      </c>
-      <c r="AE4" t="n">
-        <v>500</v>
-      </c>
-      <c r="AF4" t="n">
-        <v>970</v>
-      </c>
-      <c r="AG4" t="n">
-        <v>970</v>
-      </c>
-      <c r="AH4" t="n">
-        <v>500</v>
-      </c>
-      <c r="AI4" t="n">
-        <v>500</v>
-      </c>
-      <c r="AJ4" t="n">
-        <v>500</v>
-      </c>
-      <c r="AK4" t="n">
-        <v>500</v>
-      </c>
-      <c r="AL4" t="n">
-        <v>500</v>
-      </c>
-      <c r="AM4" t="n">
-        <v>500</v>
-      </c>
-      <c r="AN4" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AO4" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AP4" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="AQ4" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="AR4" t="n">
-        <v>8.199999999999999</v>
-      </c>
-      <c r="AS4" t="n">
-        <v>3.05</v>
-      </c>
-      <c r="AT4" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="AU4" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="AV4" t="n">
-        <v>6.8</v>
-      </c>
-      <c r="AW4" t="n">
-        <v>3.05</v>
-      </c>
-      <c r="AX4" t="n">
-        <v>7.6</v>
-      </c>
-      <c r="AY4" t="n">
-        <v>7</v>
-      </c>
-      <c r="AZ4" t="n">
-        <v>3.05</v>
-      </c>
-      <c r="BA4" t="n">
-        <v>3.05</v>
-      </c>
-      <c r="BB4" t="n">
-        <v>3.05</v>
-      </c>
-      <c r="BC4" t="n">
-        <v>3</v>
-      </c>
-      <c r="BD4" t="n">
-        <v>3.05</v>
-      </c>
-      <c r="BE4" t="n">
-        <v>3.05</v>
-      </c>
-      <c r="BF4" t="n">
-        <v>2.98</v>
-      </c>
-      <c r="BG4" t="n">
-        <v>2.98</v>
-      </c>
-      <c r="BH4" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BI4" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="BJ4" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BK4" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="BL4" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BM4" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="BN4" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BO4" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="BP4" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BQ4" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="BR4" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BS4" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="BT4" t="n">
-        <v>1000</v>
-      </c>
       <c r="BU4" t="n">
-        <v>1.04</v>
+        <v>5.2</v>
       </c>
       <c r="BV4" t="n">
         <v>1000</v>
       </c>
       <c r="BW4" t="n">
-        <v>1.04</v>
+        <v>3.1</v>
       </c>
       <c r="BX4" t="n">
-        <v>1000</v>
+        <v>950</v>
       </c>
       <c r="BY4" t="n">
-        <v>1.04</v>
+        <v>3.1</v>
       </c>
       <c r="BZ4" t="n">
-        <v>1000</v>
+        <v>960</v>
       </c>
       <c r="CA4" t="n">
-        <v>1.04</v>
+        <v>3.1</v>
       </c>
       <c r="CB4" t="inlineStr">
         <is>
-          <t>2026-06-12 09:58:55</t>
+          <t>2026-06-12 12:17:49</t>
         </is>
       </c>
     </row>
@@ -1619,124 +1619,124 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>2.1</v>
+        <v>2.08</v>
       </c>
       <c r="G5" t="n">
-        <v>2.22</v>
+        <v>2.14</v>
       </c>
       <c r="H5" t="n">
-        <v>4.2</v>
+        <v>4.9</v>
       </c>
       <c r="I5" t="n">
-        <v>4.7</v>
+        <v>5.2</v>
       </c>
       <c r="J5" t="n">
+        <v>3</v>
+      </c>
+      <c r="K5" t="n">
         <v>3.15</v>
       </c>
-      <c r="K5" t="n">
-        <v>3.4</v>
-      </c>
       <c r="L5" t="n">
-        <v>1.61</v>
+        <v>1.92</v>
       </c>
       <c r="M5" t="n">
-        <v>1.13</v>
+        <v>1.18</v>
       </c>
       <c r="N5" t="n">
-        <v>2.56</v>
+        <v>2.24</v>
       </c>
       <c r="O5" t="n">
-        <v>1.59</v>
+        <v>1.76</v>
       </c>
       <c r="P5" t="n">
-        <v>1.5</v>
+        <v>1.36</v>
       </c>
       <c r="Q5" t="n">
-        <v>2.78</v>
+        <v>3.5</v>
       </c>
       <c r="R5" t="n">
-        <v>1.16</v>
+        <v>1.11</v>
       </c>
       <c r="S5" t="n">
+        <v>9</v>
+      </c>
+      <c r="T5" t="n">
+        <v>2.64</v>
+      </c>
+      <c r="U5" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="V5" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="W5" t="n">
+        <v>1.66</v>
+      </c>
+      <c r="X5" t="n">
         <v>6.4</v>
       </c>
-      <c r="T5" t="n">
-        <v>2.22</v>
-      </c>
-      <c r="U5" t="n">
-        <v>1.69</v>
-      </c>
-      <c r="V5" t="n">
-        <v>1.27</v>
-      </c>
-      <c r="W5" t="n">
-        <v>1.82</v>
-      </c>
-      <c r="X5" t="n">
-        <v>8.4</v>
-      </c>
       <c r="Y5" t="n">
-        <v>11.5</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="Z5" t="n">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="AA5" t="n">
-        <v>900</v>
+        <v>130</v>
       </c>
       <c r="AB5" t="n">
-        <v>6.8</v>
+        <v>6.2</v>
       </c>
       <c r="AC5" t="n">
-        <v>7.6</v>
+        <v>7.4</v>
       </c>
       <c r="AD5" t="n">
-        <v>19.5</v>
+        <v>21</v>
       </c>
       <c r="AE5" t="n">
         <v>110</v>
       </c>
       <c r="AF5" t="n">
-        <v>12</v>
+        <v>13.5</v>
       </c>
       <c r="AG5" t="n">
-        <v>11</v>
+        <v>17.5</v>
       </c>
       <c r="AH5" t="n">
-        <v>30</v>
+        <v>42</v>
       </c>
       <c r="AI5" t="n">
-        <v>500</v>
+        <v>190</v>
       </c>
       <c r="AJ5" t="n">
-        <v>30</v>
+        <v>1000</v>
       </c>
       <c r="AK5" t="n">
-        <v>34</v>
+        <v>55</v>
       </c>
       <c r="AL5" t="n">
-        <v>75</v>
+        <v>130</v>
       </c>
       <c r="AM5" t="n">
-        <v>500</v>
+        <v>480</v>
       </c>
       <c r="AN5" t="n">
-        <v>600</v>
+        <v>1000</v>
       </c>
       <c r="AO5" t="n">
-        <v>160</v>
+        <v>210</v>
       </c>
       <c r="AP5" t="n">
-        <v>7.2</v>
+        <v>5.8</v>
       </c>
       <c r="AQ5" t="n">
-        <v>9.6</v>
+        <v>7.8</v>
       </c>
       <c r="AR5" t="n">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="AS5" t="n">
-        <v>12</v>
+        <v>65</v>
       </c>
       <c r="AT5" t="n">
         <v>5.7</v>
@@ -1748,101 +1748,101 @@
         <v>17</v>
       </c>
       <c r="AW5" t="n">
-        <v>70</v>
+        <v>60</v>
       </c>
       <c r="AX5" t="n">
-        <v>10</v>
+        <v>11.5</v>
       </c>
       <c r="AY5" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="AZ5" t="n">
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="BA5" t="n">
-        <v>12</v>
+        <v>100</v>
       </c>
       <c r="BB5" t="n">
-        <v>23</v>
+        <v>32</v>
       </c>
       <c r="BC5" t="n">
-        <v>28</v>
+        <v>34</v>
       </c>
       <c r="BD5" t="n">
-        <v>55</v>
+        <v>75</v>
       </c>
       <c r="BE5" t="n">
-        <v>46</v>
+        <v>7.8</v>
       </c>
       <c r="BF5" t="n">
+        <v>40</v>
+      </c>
+      <c r="BG5" t="n">
+        <v>100</v>
+      </c>
+      <c r="BH5" t="n">
+        <v>2.14</v>
+      </c>
+      <c r="BI5" t="n">
+        <v>1.98</v>
+      </c>
+      <c r="BJ5" t="n">
+        <v>20</v>
+      </c>
+      <c r="BK5" t="n">
+        <v>15</v>
+      </c>
+      <c r="BL5" t="n">
+        <v>960</v>
+      </c>
+      <c r="BM5" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="BN5" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="BO5" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="BP5" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BQ5" t="n">
         <v>21</v>
       </c>
-      <c r="BG5" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="BH5" t="n">
-        <v>2.66</v>
-      </c>
-      <c r="BI5" t="n">
-        <v>2.24</v>
-      </c>
-      <c r="BJ5" t="n">
-        <v>12</v>
-      </c>
-      <c r="BK5" t="n">
+      <c r="BR5" t="n">
+        <v>910</v>
+      </c>
+      <c r="BS5" t="n">
         <v>6.6</v>
       </c>
-      <c r="BL5" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BM5" t="n">
-        <v>13.5</v>
-      </c>
-      <c r="BN5" t="n">
-        <v>4.7</v>
-      </c>
-      <c r="BO5" t="n">
-        <v>4</v>
-      </c>
-      <c r="BP5" t="n">
-        <v>19</v>
-      </c>
-      <c r="BQ5" t="n">
-        <v>8.199999999999999</v>
-      </c>
-      <c r="BR5" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BS5" t="n">
-        <v>11</v>
-      </c>
       <c r="BT5" t="n">
-        <v>7.8</v>
+        <v>7.6</v>
       </c>
       <c r="BU5" t="n">
-        <v>5.8</v>
+        <v>6</v>
       </c>
       <c r="BV5" t="n">
-        <v>70</v>
+        <v>1000</v>
       </c>
       <c r="BW5" t="n">
-        <v>11</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BX5" t="n">
-        <v>1000</v>
+        <v>950</v>
       </c>
       <c r="BY5" t="n">
-        <v>12</v>
+        <v>6.4</v>
       </c>
       <c r="BZ5" t="n">
-        <v>65</v>
+        <v>960</v>
       </c>
       <c r="CA5" t="n">
-        <v>11.5</v>
+        <v>6.4</v>
       </c>
       <c r="CB5" t="inlineStr">
         <is>
-          <t>2026-06-12 09:58:55</t>
+          <t>2026-06-12 12:17:49</t>
         </is>
       </c>
     </row>
@@ -1873,230 +1873,230 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>3.5</v>
+        <v>4.9</v>
       </c>
       <c r="G6" t="n">
-        <v>3.7</v>
+        <v>5.2</v>
       </c>
       <c r="H6" t="n">
-        <v>2.18</v>
+        <v>1.79</v>
       </c>
       <c r="I6" t="n">
-        <v>2.24</v>
+        <v>1.81</v>
       </c>
       <c r="J6" t="n">
-        <v>3.65</v>
+        <v>4</v>
       </c>
       <c r="K6" t="n">
-        <v>3.8</v>
+        <v>4.1</v>
       </c>
       <c r="L6" t="n">
-        <v>1.4</v>
+        <v>1.39</v>
       </c>
       <c r="M6" t="n">
         <v>1.06</v>
       </c>
       <c r="N6" t="n">
-        <v>4.1</v>
+        <v>4.3</v>
       </c>
       <c r="O6" t="n">
-        <v>1.28</v>
+        <v>1.27</v>
       </c>
       <c r="P6" t="n">
-        <v>2.04</v>
+        <v>2.1</v>
       </c>
       <c r="Q6" t="n">
-        <v>1.89</v>
+        <v>1.87</v>
       </c>
       <c r="R6" t="n">
-        <v>1.41</v>
+        <v>1.43</v>
       </c>
       <c r="S6" t="n">
-        <v>3.25</v>
+        <v>3.2</v>
       </c>
       <c r="T6" t="n">
-        <v>1.74</v>
+        <v>1.8</v>
       </c>
       <c r="U6" t="n">
-        <v>2.24</v>
+        <v>2.12</v>
       </c>
       <c r="V6" t="n">
-        <v>1.8</v>
+        <v>2.22</v>
       </c>
       <c r="W6" t="n">
-        <v>1.37</v>
+        <v>1.24</v>
       </c>
       <c r="X6" t="n">
+        <v>17.5</v>
+      </c>
+      <c r="Y6" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="Z6" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="AA6" t="n">
+        <v>18</v>
+      </c>
+      <c r="AB6" t="n">
         <v>21</v>
       </c>
-      <c r="Y6" t="n">
-        <v>11</v>
-      </c>
-      <c r="Z6" t="n">
-        <v>15</v>
-      </c>
-      <c r="AA6" t="n">
-        <v>28</v>
-      </c>
-      <c r="AB6" t="n">
-        <v>14.5</v>
-      </c>
       <c r="AC6" t="n">
-        <v>8.4</v>
+        <v>9.4</v>
       </c>
       <c r="AD6" t="n">
-        <v>13.5</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AE6" t="n">
-        <v>24</v>
+        <v>17</v>
       </c>
       <c r="AF6" t="n">
-        <v>26</v>
+        <v>40</v>
       </c>
       <c r="AG6" t="n">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="AH6" t="n">
-        <v>16.5</v>
+        <v>19</v>
       </c>
       <c r="AI6" t="n">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="AJ6" t="n">
-        <v>70</v>
+        <v>120</v>
       </c>
       <c r="AK6" t="n">
         <v>65</v>
       </c>
       <c r="AL6" t="n">
-        <v>48</v>
+        <v>70</v>
       </c>
       <c r="AM6" t="n">
-        <v>90</v>
+        <v>100</v>
       </c>
       <c r="AN6" t="n">
-        <v>36</v>
+        <v>70</v>
       </c>
       <c r="AO6" t="n">
+        <v>10</v>
+      </c>
+      <c r="AP6" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="AQ6" t="n">
+        <v>9</v>
+      </c>
+      <c r="AR6" t="n">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="AS6" t="n">
         <v>16</v>
       </c>
-      <c r="AP6" t="n">
-        <v>15</v>
-      </c>
-      <c r="AQ6" t="n">
-        <v>9.800000000000001</v>
-      </c>
-      <c r="AR6" t="n">
-        <v>13</v>
-      </c>
-      <c r="AS6" t="n">
-        <v>25</v>
-      </c>
       <c r="AT6" t="n">
-        <v>13.5</v>
+        <v>18</v>
       </c>
       <c r="AU6" t="n">
-        <v>7.6</v>
+        <v>8.4</v>
       </c>
       <c r="AV6" t="n">
-        <v>9.800000000000001</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AW6" t="n">
-        <v>20</v>
+        <v>15.5</v>
       </c>
       <c r="AX6" t="n">
-        <v>23</v>
+        <v>34</v>
       </c>
       <c r="AY6" t="n">
-        <v>13</v>
+        <v>17.5</v>
       </c>
       <c r="AZ6" t="n">
-        <v>15.5</v>
+        <v>17</v>
       </c>
       <c r="BA6" t="n">
         <v>30</v>
       </c>
       <c r="BB6" t="n">
-        <v>42</v>
+        <v>95</v>
       </c>
       <c r="BC6" t="n">
-        <v>34</v>
+        <v>55</v>
       </c>
       <c r="BD6" t="n">
-        <v>38</v>
+        <v>55</v>
       </c>
       <c r="BE6" t="n">
-        <v>60</v>
+        <v>80</v>
       </c>
       <c r="BF6" t="n">
-        <v>30</v>
+        <v>55</v>
       </c>
       <c r="BG6" t="n">
-        <v>14</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BH6" t="n">
-        <v>3.6</v>
+        <v>3.7</v>
       </c>
       <c r="BI6" t="n">
-        <v>2.96</v>
+        <v>3.4</v>
       </c>
       <c r="BJ6" t="n">
-        <v>9.199999999999999</v>
+        <v>9.6</v>
       </c>
       <c r="BK6" t="n">
-        <v>5.9</v>
+        <v>6.6</v>
       </c>
       <c r="BL6" t="n">
         <v>1000</v>
       </c>
       <c r="BM6" t="n">
-        <v>14.5</v>
+        <v>17</v>
       </c>
       <c r="BN6" t="n">
-        <v>6.8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BO6" t="n">
         <v>6</v>
       </c>
       <c r="BP6" t="n">
-        <v>27</v>
+        <v>40</v>
       </c>
       <c r="BQ6" t="n">
-        <v>10</v>
+        <v>19.5</v>
       </c>
       <c r="BR6" t="n">
-        <v>36</v>
+        <v>48</v>
       </c>
       <c r="BS6" t="n">
+        <v>24</v>
+      </c>
+      <c r="BT6" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="BU6" t="n">
+        <v>4</v>
+      </c>
+      <c r="BV6" t="n">
         <v>11.5</v>
       </c>
-      <c r="BT6" t="n">
-        <v>5.2</v>
-      </c>
-      <c r="BU6" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="BV6" t="n">
-        <v>15.5</v>
-      </c>
       <c r="BW6" t="n">
-        <v>8</v>
+        <v>7.6</v>
       </c>
       <c r="BX6" t="n">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="BY6" t="n">
-        <v>10.5</v>
+        <v>14.5</v>
       </c>
       <c r="BZ6" t="n">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="CA6" t="n">
-        <v>9.800000000000001</v>
+        <v>12.5</v>
       </c>
       <c r="CB6" t="inlineStr">
         <is>
-          <t>2026-06-12 09:58:55</t>
+          <t>2026-06-12 12:17:49</t>
         </is>
       </c>
     </row>
@@ -2127,61 +2127,61 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>1.61</v>
+        <v>1.59</v>
       </c>
       <c r="G7" t="n">
-        <v>1.64</v>
+        <v>1.63</v>
       </c>
       <c r="H7" t="n">
-        <v>5.9</v>
+        <v>6</v>
       </c>
       <c r="I7" t="n">
-        <v>6.8</v>
+        <v>6.6</v>
       </c>
       <c r="J7" t="n">
-        <v>4.2</v>
+        <v>4.3</v>
       </c>
       <c r="K7" t="n">
-        <v>4.7</v>
+        <v>4.8</v>
       </c>
       <c r="L7" t="n">
-        <v>1.36</v>
+        <v>1.35</v>
       </c>
       <c r="M7" t="n">
         <v>1.05</v>
       </c>
       <c r="N7" t="n">
-        <v>4.3</v>
+        <v>4.6</v>
       </c>
       <c r="O7" t="n">
-        <v>1.26</v>
+        <v>1.25</v>
       </c>
       <c r="P7" t="n">
-        <v>2.12</v>
+        <v>2.2</v>
       </c>
       <c r="Q7" t="n">
-        <v>1.8</v>
+        <v>1.79</v>
       </c>
       <c r="R7" t="n">
-        <v>1.44</v>
+        <v>1.46</v>
       </c>
       <c r="S7" t="n">
-        <v>3.05</v>
+        <v>2.98</v>
       </c>
       <c r="T7" t="n">
-        <v>1.83</v>
+        <v>1.81</v>
       </c>
       <c r="U7" t="n">
-        <v>2</v>
+        <v>2.04</v>
       </c>
       <c r="V7" t="n">
         <v>1.17</v>
       </c>
       <c r="W7" t="n">
-        <v>2.52</v>
+        <v>2.58</v>
       </c>
       <c r="X7" t="n">
-        <v>20</v>
+        <v>26</v>
       </c>
       <c r="Y7" t="n">
         <v>40</v>
@@ -2190,7 +2190,7 @@
         <v>120</v>
       </c>
       <c r="AA7" t="n">
-        <v>900</v>
+        <v>700</v>
       </c>
       <c r="AB7" t="n">
         <v>9.199999999999999</v>
@@ -2205,10 +2205,10 @@
         <v>700</v>
       </c>
       <c r="AF7" t="n">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="AG7" t="n">
-        <v>9.4</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AH7" t="n">
         <v>34</v>
@@ -2220,7 +2220,7 @@
         <v>16</v>
       </c>
       <c r="AK7" t="n">
-        <v>24</v>
+        <v>16.5</v>
       </c>
       <c r="AL7" t="n">
         <v>36</v>
@@ -2229,34 +2229,34 @@
         <v>580</v>
       </c>
       <c r="AN7" t="n">
-        <v>9</v>
+        <v>8.4</v>
       </c>
       <c r="AO7" t="n">
-        <v>600</v>
+        <v>700</v>
       </c>
       <c r="AP7" t="n">
-        <v>15</v>
+        <v>17.5</v>
       </c>
       <c r="AQ7" t="n">
-        <v>19</v>
+        <v>12</v>
       </c>
       <c r="AR7" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="AS7" t="n">
-        <v>11.5</v>
+        <v>14.5</v>
       </c>
       <c r="AT7" t="n">
         <v>7.8</v>
       </c>
       <c r="AU7" t="n">
-        <v>8.4</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AV7" t="n">
-        <v>19.5</v>
+        <v>20</v>
       </c>
       <c r="AW7" t="n">
-        <v>11.5</v>
+        <v>14</v>
       </c>
       <c r="AX7" t="n">
         <v>8.800000000000001</v>
@@ -2274,28 +2274,28 @@
         <v>13</v>
       </c>
       <c r="BC7" t="n">
-        <v>9.6</v>
+        <v>14</v>
       </c>
       <c r="BD7" t="n">
         <v>18</v>
       </c>
       <c r="BE7" t="n">
-        <v>11.5</v>
+        <v>28</v>
       </c>
       <c r="BF7" t="n">
-        <v>6.6</v>
+        <v>7.4</v>
       </c>
       <c r="BG7" t="n">
         <v>13.5</v>
       </c>
       <c r="BH7" t="n">
-        <v>3.85</v>
+        <v>3.9</v>
       </c>
       <c r="BI7" t="n">
         <v>3.35</v>
       </c>
       <c r="BJ7" t="n">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="BK7" t="n">
         <v>5.2</v>
@@ -2304,43 +2304,43 @@
         <v>1000</v>
       </c>
       <c r="BM7" t="n">
-        <v>7.8</v>
+        <v>9.6</v>
       </c>
       <c r="BN7" t="n">
-        <v>4.3</v>
+        <v>4.2</v>
       </c>
       <c r="BO7" t="n">
         <v>3.75</v>
       </c>
       <c r="BP7" t="n">
-        <v>12.5</v>
+        <v>10.5</v>
       </c>
       <c r="BQ7" t="n">
-        <v>5.4</v>
+        <v>5.2</v>
       </c>
       <c r="BR7" t="n">
         <v>32</v>
       </c>
       <c r="BS7" t="n">
-        <v>6.4</v>
+        <v>7.8</v>
       </c>
       <c r="BT7" t="n">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="BU7" t="n">
-        <v>5</v>
+        <v>5.1</v>
       </c>
       <c r="BV7" t="n">
-        <v>65</v>
+        <v>1000</v>
       </c>
       <c r="BW7" t="n">
-        <v>7.4</v>
+        <v>8.6</v>
       </c>
       <c r="BX7" t="n">
         <v>1000</v>
       </c>
       <c r="BY7" t="n">
-        <v>7.4</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BZ7" t="n">
         <v>0</v>
@@ -2350,7 +2350,7 @@
       </c>
       <c r="CB7" t="inlineStr">
         <is>
-          <t>2026-06-12 09:58:55</t>
+          <t>2026-06-12 12:17:49</t>
         </is>
       </c>
     </row>
@@ -2381,154 +2381,154 @@
         </is>
       </c>
       <c r="F8" t="n">
-        <v>1.84</v>
+        <v>1.9</v>
       </c>
       <c r="G8" t="n">
-        <v>1.92</v>
+        <v>1.96</v>
       </c>
       <c r="H8" t="n">
+        <v>4</v>
+      </c>
+      <c r="I8" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="J8" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="K8" t="n">
         <v>4.2</v>
       </c>
-      <c r="I8" t="n">
-        <v>4.7</v>
-      </c>
-      <c r="J8" t="n">
-        <v>4</v>
-      </c>
-      <c r="K8" t="n">
-        <v>4.1</v>
-      </c>
       <c r="L8" t="n">
-        <v>1.36</v>
+        <v>1.37</v>
       </c>
       <c r="M8" t="n">
         <v>1.05</v>
       </c>
       <c r="N8" t="n">
-        <v>4.3</v>
+        <v>4.4</v>
       </c>
       <c r="O8" t="n">
         <v>1.26</v>
       </c>
       <c r="P8" t="n">
-        <v>2.14</v>
+        <v>2.16</v>
       </c>
       <c r="Q8" t="n">
-        <v>1.8</v>
+        <v>1.79</v>
       </c>
       <c r="R8" t="n">
         <v>1.44</v>
       </c>
       <c r="S8" t="n">
-        <v>3.1</v>
+        <v>3</v>
       </c>
       <c r="T8" t="n">
-        <v>1.73</v>
+        <v>1.7</v>
       </c>
       <c r="U8" t="n">
-        <v>2.18</v>
+        <v>2.2</v>
       </c>
       <c r="V8" t="n">
-        <v>1.27</v>
+        <v>1.29</v>
       </c>
       <c r="W8" t="n">
-        <v>2.08</v>
+        <v>2.04</v>
       </c>
       <c r="X8" t="n">
         <v>19</v>
       </c>
       <c r="Y8" t="n">
-        <v>18.5</v>
+        <v>18</v>
       </c>
       <c r="Z8" t="n">
         <v>34</v>
       </c>
       <c r="AA8" t="n">
-        <v>110</v>
+        <v>85</v>
       </c>
       <c r="AB8" t="n">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="AC8" t="n">
-        <v>9.4</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AD8" t="n">
-        <v>17.5</v>
+        <v>17</v>
       </c>
       <c r="AE8" t="n">
-        <v>55</v>
+        <v>50</v>
       </c>
       <c r="AF8" t="n">
-        <v>12</v>
+        <v>12.5</v>
       </c>
       <c r="AG8" t="n">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="AH8" t="n">
-        <v>19</v>
+        <v>18.5</v>
       </c>
       <c r="AI8" t="n">
-        <v>60</v>
+        <v>50</v>
       </c>
       <c r="AJ8" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AK8" t="n">
         <v>19</v>
       </c>
       <c r="AL8" t="n">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="AM8" t="n">
-        <v>90</v>
+        <v>85</v>
       </c>
       <c r="AN8" t="n">
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="AO8" t="n">
-        <v>55</v>
+        <v>46</v>
       </c>
       <c r="AP8" t="n">
-        <v>16.5</v>
+        <v>17</v>
       </c>
       <c r="AQ8" t="n">
-        <v>16.5</v>
+        <v>15.5</v>
       </c>
       <c r="AR8" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="AS8" t="n">
-        <v>75</v>
+        <v>70</v>
       </c>
       <c r="AT8" t="n">
-        <v>9</v>
+        <v>9.4</v>
       </c>
       <c r="AU8" t="n">
         <v>8.199999999999999</v>
       </c>
       <c r="AV8" t="n">
-        <v>15.5</v>
+        <v>15</v>
       </c>
       <c r="AW8" t="n">
         <v>42</v>
       </c>
       <c r="AX8" t="n">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="AY8" t="n">
         <v>9.199999999999999</v>
       </c>
       <c r="AZ8" t="n">
+        <v>16</v>
+      </c>
+      <c r="BA8" t="n">
+        <v>42</v>
+      </c>
+      <c r="BB8" t="n">
+        <v>19.5</v>
+      </c>
+      <c r="BC8" t="n">
         <v>16.5</v>
-      </c>
-      <c r="BA8" t="n">
-        <v>46</v>
-      </c>
-      <c r="BB8" t="n">
-        <v>17.5</v>
-      </c>
-      <c r="BC8" t="n">
-        <v>15.5</v>
       </c>
       <c r="BD8" t="n">
         <v>28</v>
@@ -2537,74 +2537,74 @@
         <v>29</v>
       </c>
       <c r="BF8" t="n">
-        <v>9.6</v>
+        <v>10</v>
       </c>
       <c r="BG8" t="n">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="BH8" t="n">
         <v>3.85</v>
       </c>
       <c r="BI8" t="n">
-        <v>2.98</v>
+        <v>3</v>
       </c>
       <c r="BJ8" t="n">
-        <v>9.800000000000001</v>
+        <v>9.4</v>
       </c>
       <c r="BK8" t="n">
-        <v>5.3</v>
+        <v>5.7</v>
       </c>
       <c r="BL8" t="n">
         <v>1000</v>
       </c>
       <c r="BM8" t="n">
-        <v>10.5</v>
+        <v>12.5</v>
       </c>
       <c r="BN8" t="n">
-        <v>4.8</v>
+        <v>4.9</v>
       </c>
       <c r="BO8" t="n">
-        <v>3.6</v>
+        <v>3.7</v>
       </c>
       <c r="BP8" t="n">
         <v>13</v>
       </c>
       <c r="BQ8" t="n">
-        <v>9.199999999999999</v>
+        <v>6.8</v>
       </c>
       <c r="BR8" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="BS8" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="BT8" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="BU8" t="n">
+        <v>5.8</v>
+      </c>
+      <c r="BV8" t="n">
+        <v>34</v>
+      </c>
+      <c r="BW8" t="n">
+        <v>10</v>
+      </c>
+      <c r="BX8" t="n">
+        <v>40</v>
+      </c>
+      <c r="BY8" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="BZ8" t="n">
+        <v>19.5</v>
+      </c>
+      <c r="CA8" t="n">
         <v>8.199999999999999</v>
       </c>
-      <c r="BU8" t="n">
-        <v>4.8</v>
-      </c>
-      <c r="BV8" t="n">
-        <v>36</v>
-      </c>
-      <c r="BW8" t="n">
-        <v>8.800000000000001</v>
-      </c>
-      <c r="BX8" t="n">
-        <v>44</v>
-      </c>
-      <c r="BY8" t="n">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="BZ8" t="n">
-        <v>21</v>
-      </c>
-      <c r="CA8" t="n">
-        <v>7.4</v>
-      </c>
       <c r="CB8" t="inlineStr">
         <is>
-          <t>2026-06-12 09:58:55</t>
+          <t>2026-06-12 12:17:49</t>
         </is>
       </c>
     </row>
@@ -2635,100 +2635,100 @@
         </is>
       </c>
       <c r="F9" t="n">
-        <v>4.9</v>
+        <v>5.2</v>
       </c>
       <c r="G9" t="n">
-        <v>5.8</v>
+        <v>5.6</v>
       </c>
       <c r="H9" t="n">
-        <v>1.66</v>
+        <v>1.62</v>
       </c>
       <c r="I9" t="n">
-        <v>1.74</v>
+        <v>1.68</v>
       </c>
       <c r="J9" t="n">
-        <v>4.3</v>
+        <v>4.5</v>
       </c>
       <c r="K9" t="n">
-        <v>4.8</v>
+        <v>5</v>
       </c>
       <c r="L9" t="n">
-        <v>1.28</v>
+        <v>1.27</v>
       </c>
       <c r="M9" t="n">
         <v>1.03</v>
       </c>
       <c r="N9" t="n">
-        <v>5.8</v>
+        <v>6.2</v>
       </c>
       <c r="O9" t="n">
-        <v>1.17</v>
+        <v>1.18</v>
       </c>
       <c r="P9" t="n">
-        <v>2.64</v>
+        <v>2.76</v>
       </c>
       <c r="Q9" t="n">
-        <v>1.54</v>
+        <v>1.53</v>
       </c>
       <c r="R9" t="n">
-        <v>1.65</v>
+        <v>1.7</v>
       </c>
       <c r="S9" t="n">
-        <v>2.36</v>
+        <v>2.32</v>
       </c>
       <c r="T9" t="n">
-        <v>1.58</v>
+        <v>1.56</v>
       </c>
       <c r="U9" t="n">
-        <v>2.48</v>
+        <v>2.5</v>
       </c>
       <c r="V9" t="n">
-        <v>2.34</v>
+        <v>2.46</v>
       </c>
       <c r="W9" t="n">
-        <v>1.22</v>
+        <v>1.21</v>
       </c>
       <c r="X9" t="n">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="Y9" t="n">
         <v>13.5</v>
       </c>
       <c r="Z9" t="n">
-        <v>13.5</v>
+        <v>14</v>
       </c>
       <c r="AA9" t="n">
-        <v>19</v>
+        <v>18.5</v>
       </c>
       <c r="AB9" t="n">
-        <v>38</v>
+        <v>50</v>
       </c>
       <c r="AC9" t="n">
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="AD9" t="n">
         <v>10.5</v>
       </c>
       <c r="AE9" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AF9" t="n">
-        <v>220</v>
+        <v>120</v>
       </c>
       <c r="AG9" t="n">
         <v>22</v>
       </c>
       <c r="AH9" t="n">
-        <v>17.5</v>
+        <v>18</v>
       </c>
       <c r="AI9" t="n">
-        <v>60</v>
+        <v>44</v>
       </c>
       <c r="AJ9" t="n">
-        <v>900</v>
+        <v>500</v>
       </c>
       <c r="AK9" t="n">
-        <v>120</v>
+        <v>150</v>
       </c>
       <c r="AL9" t="n">
         <v>120</v>
@@ -2737,13 +2737,13 @@
         <v>580</v>
       </c>
       <c r="AN9" t="n">
-        <v>140</v>
+        <v>600</v>
       </c>
       <c r="AO9" t="n">
-        <v>7</v>
+        <v>6.2</v>
       </c>
       <c r="AP9" t="n">
-        <v>21</v>
+        <v>11.5</v>
       </c>
       <c r="AQ9" t="n">
         <v>11</v>
@@ -2752,85 +2752,85 @@
         <v>11</v>
       </c>
       <c r="AS9" t="n">
-        <v>16</v>
+        <v>15.5</v>
       </c>
       <c r="AT9" t="n">
-        <v>20</v>
+        <v>14.5</v>
       </c>
       <c r="AU9" t="n">
-        <v>9</v>
+        <v>9.6</v>
       </c>
       <c r="AV9" t="n">
         <v>8.800000000000001</v>
       </c>
       <c r="AW9" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="AX9" t="n">
         <v>20</v>
       </c>
       <c r="AY9" t="n">
-        <v>11</v>
+        <v>15.5</v>
       </c>
       <c r="AZ9" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="BA9" t="n">
         <v>15</v>
       </c>
       <c r="BB9" t="n">
+        <v>11</v>
+      </c>
+      <c r="BC9" t="n">
+        <v>29</v>
+      </c>
+      <c r="BD9" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="BE9" t="n">
         <v>10</v>
       </c>
-      <c r="BC9" t="n">
-        <v>23</v>
-      </c>
-      <c r="BD9" t="n">
-        <v>23</v>
-      </c>
-      <c r="BE9" t="n">
-        <v>9.4</v>
-      </c>
       <c r="BF9" t="n">
-        <v>8.800000000000001</v>
+        <v>12.5</v>
       </c>
       <c r="BG9" t="n">
-        <v>6</v>
+        <v>5.5</v>
       </c>
       <c r="BH9" t="n">
-        <v>4.7</v>
+        <v>4.9</v>
       </c>
       <c r="BI9" t="n">
-        <v>3.65</v>
+        <v>3.75</v>
       </c>
       <c r="BJ9" t="n">
         <v>9.6</v>
       </c>
       <c r="BK9" t="n">
-        <v>4.9</v>
+        <v>4.8</v>
       </c>
       <c r="BL9" t="n">
         <v>1000</v>
       </c>
       <c r="BM9" t="n">
-        <v>9.199999999999999</v>
+        <v>8.6</v>
       </c>
       <c r="BN9" t="n">
-        <v>9.199999999999999</v>
+        <v>9.6</v>
       </c>
       <c r="BO9" t="n">
         <v>4.8</v>
       </c>
       <c r="BP9" t="n">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="BQ9" t="n">
-        <v>8</v>
+        <v>7.8</v>
       </c>
       <c r="BR9" t="n">
-        <v>1000</v>
+        <v>40</v>
       </c>
       <c r="BS9" t="n">
-        <v>8</v>
+        <v>7.8</v>
       </c>
       <c r="BT9" t="n">
         <v>4.9</v>
@@ -2839,16 +2839,16 @@
         <v>3.8</v>
       </c>
       <c r="BV9" t="n">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="BW9" t="n">
-        <v>5.3</v>
+        <v>5</v>
       </c>
       <c r="BX9" t="n">
         <v>21</v>
       </c>
       <c r="BY9" t="n">
-        <v>6.8</v>
+        <v>6.6</v>
       </c>
       <c r="BZ9" t="n">
         <v>0</v>
@@ -2858,7 +2858,7 @@
       </c>
       <c r="CB9" t="inlineStr">
         <is>
-          <t>2026-06-12 09:58:55</t>
+          <t>2026-06-12 12:17:49</t>
         </is>
       </c>
     </row>
@@ -2892,61 +2892,61 @@
         <v>1.56</v>
       </c>
       <c r="G10" t="n">
-        <v>1.64</v>
+        <v>1.63</v>
       </c>
       <c r="H10" t="n">
+        <v>5.3</v>
+      </c>
+      <c r="I10" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="J10" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="K10" t="n">
         <v>5.4</v>
       </c>
-      <c r="I10" t="n">
-        <v>6.6</v>
-      </c>
-      <c r="J10" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="K10" t="n">
-        <v>5.3</v>
-      </c>
       <c r="L10" t="n">
-        <v>1.27</v>
+        <v>1.25</v>
       </c>
       <c r="M10" t="n">
         <v>1.03</v>
       </c>
       <c r="N10" t="n">
-        <v>5.8</v>
+        <v>6.8</v>
       </c>
       <c r="O10" t="n">
-        <v>1.18</v>
+        <v>1.14</v>
       </c>
       <c r="P10" t="n">
-        <v>2.66</v>
+        <v>2.88</v>
       </c>
       <c r="Q10" t="n">
-        <v>1.52</v>
+        <v>1.47</v>
       </c>
       <c r="R10" t="n">
-        <v>1.66</v>
+        <v>1.76</v>
       </c>
       <c r="S10" t="n">
-        <v>2.34</v>
+        <v>2.16</v>
       </c>
       <c r="T10" t="n">
-        <v>1.61</v>
+        <v>1.55</v>
       </c>
       <c r="U10" t="n">
-        <v>2.3</v>
+        <v>2.46</v>
       </c>
       <c r="V10" t="n">
-        <v>1.18</v>
+        <v>1.19</v>
       </c>
       <c r="W10" t="n">
-        <v>2.52</v>
+        <v>2.58</v>
       </c>
       <c r="X10" t="n">
-        <v>42</v>
+        <v>70</v>
       </c>
       <c r="Y10" t="n">
-        <v>44</v>
+        <v>500</v>
       </c>
       <c r="Z10" t="n">
         <v>220</v>
@@ -2955,19 +2955,19 @@
         <v>700</v>
       </c>
       <c r="AB10" t="n">
-        <v>13.5</v>
+        <v>16</v>
       </c>
       <c r="AC10" t="n">
-        <v>12</v>
+        <v>12.5</v>
       </c>
       <c r="AD10" t="n">
-        <v>24</v>
+        <v>36</v>
       </c>
       <c r="AE10" t="n">
         <v>200</v>
       </c>
       <c r="AF10" t="n">
-        <v>13</v>
+        <v>13.5</v>
       </c>
       <c r="AG10" t="n">
         <v>11</v>
@@ -2979,10 +2979,10 @@
         <v>160</v>
       </c>
       <c r="AJ10" t="n">
-        <v>17</v>
+        <v>28</v>
       </c>
       <c r="AK10" t="n">
-        <v>16</v>
+        <v>15.5</v>
       </c>
       <c r="AL10" t="n">
         <v>48</v>
@@ -2991,31 +2991,31 @@
         <v>580</v>
       </c>
       <c r="AN10" t="n">
-        <v>6.4</v>
+        <v>5.8</v>
       </c>
       <c r="AO10" t="n">
-        <v>700</v>
+        <v>600</v>
       </c>
       <c r="AP10" t="n">
-        <v>13.5</v>
+        <v>22</v>
       </c>
       <c r="AQ10" t="n">
-        <v>23</v>
+        <v>14</v>
       </c>
       <c r="AR10" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AS10" t="n">
         <v>36</v>
       </c>
       <c r="AT10" t="n">
-        <v>10</v>
+        <v>12.5</v>
       </c>
       <c r="AU10" t="n">
         <v>9.4</v>
       </c>
       <c r="AV10" t="n">
-        <v>11.5</v>
+        <v>18.5</v>
       </c>
       <c r="AW10" t="n">
         <v>23</v>
@@ -3027,10 +3027,10 @@
         <v>8.800000000000001</v>
       </c>
       <c r="AZ10" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="BA10" t="n">
-        <v>27</v>
+        <v>23</v>
       </c>
       <c r="BB10" t="n">
         <v>13.5</v>
@@ -3039,80 +3039,80 @@
         <v>12</v>
       </c>
       <c r="BD10" t="n">
-        <v>13.5</v>
+        <v>20</v>
       </c>
       <c r="BE10" t="n">
-        <v>7.8</v>
+        <v>8.4</v>
       </c>
       <c r="BF10" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="BG10" t="n">
+        <v>8</v>
+      </c>
+      <c r="BH10" t="n">
+        <v>5</v>
+      </c>
+      <c r="BI10" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="BJ10" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="BK10" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="BL10" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BM10" t="n">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="BN10" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="BO10" t="n">
+        <v>3.65</v>
+      </c>
+      <c r="BP10" t="n">
+        <v>10</v>
+      </c>
+      <c r="BQ10" t="n">
         <v>5.2</v>
       </c>
-      <c r="BG10" t="n">
-        <v>7.6</v>
-      </c>
-      <c r="BH10" t="n">
-        <v>4.8</v>
-      </c>
-      <c r="BI10" t="n">
-        <v>3.55</v>
-      </c>
-      <c r="BJ10" t="n">
-        <v>10</v>
-      </c>
-      <c r="BK10" t="n">
-        <v>4.7</v>
-      </c>
-      <c r="BL10" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BM10" t="n">
-        <v>8.199999999999999</v>
-      </c>
-      <c r="BN10" t="n">
-        <v>4.8</v>
-      </c>
-      <c r="BO10" t="n">
-        <v>3.55</v>
-      </c>
-      <c r="BP10" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="BQ10" t="n">
-        <v>4.8</v>
-      </c>
       <c r="BR10" t="n">
-        <v>21</v>
+        <v>19.5</v>
       </c>
       <c r="BS10" t="n">
-        <v>6.2</v>
+        <v>7</v>
       </c>
       <c r="BT10" t="n">
-        <v>10</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BU10" t="n">
-        <v>4.7</v>
+        <v>5.2</v>
       </c>
       <c r="BV10" t="n">
         <v>1000</v>
       </c>
       <c r="BW10" t="n">
-        <v>7.4</v>
+        <v>8.6</v>
       </c>
       <c r="BX10" t="n">
         <v>1000</v>
       </c>
       <c r="BY10" t="n">
-        <v>7.4</v>
+        <v>8.6</v>
       </c>
       <c r="BZ10" t="n">
-        <v>13.5</v>
+        <v>12</v>
       </c>
       <c r="CA10" t="n">
-        <v>5.4</v>
+        <v>5.8</v>
       </c>
       <c r="CB10" t="inlineStr">
         <is>
-          <t>2026-06-12 09:58:55</t>
+          <t>2026-06-12 12:17:49</t>
         </is>
       </c>
     </row>
@@ -3143,40 +3143,40 @@
         </is>
       </c>
       <c r="F11" t="n">
-        <v>2.28</v>
+        <v>2.48</v>
       </c>
       <c r="G11" t="n">
-        <v>2.42</v>
+        <v>2.62</v>
       </c>
       <c r="H11" t="n">
-        <v>4</v>
+        <v>3.7</v>
       </c>
       <c r="I11" t="n">
-        <v>4.5</v>
+        <v>3.85</v>
       </c>
       <c r="J11" t="n">
-        <v>2.86</v>
+        <v>2.84</v>
       </c>
       <c r="K11" t="n">
         <v>3.05</v>
       </c>
       <c r="L11" t="n">
-        <v>1.62</v>
+        <v>1.59</v>
       </c>
       <c r="M11" t="n">
-        <v>1.13</v>
+        <v>1.14</v>
       </c>
       <c r="N11" t="n">
-        <v>2.54</v>
+        <v>2.64</v>
       </c>
       <c r="O11" t="n">
-        <v>1.6</v>
+        <v>1.57</v>
       </c>
       <c r="P11" t="n">
-        <v>1.46</v>
+        <v>1.52</v>
       </c>
       <c r="Q11" t="n">
-        <v>2.96</v>
+        <v>2.74</v>
       </c>
       <c r="R11" t="n">
         <v>1.16</v>
@@ -3185,188 +3185,188 @@
         <v>6.4</v>
       </c>
       <c r="T11" t="n">
-        <v>2.16</v>
+        <v>1.11</v>
       </c>
       <c r="U11" t="n">
-        <v>1.73</v>
+        <v>1.11</v>
       </c>
       <c r="V11" t="n">
-        <v>1.29</v>
+        <v>1.35</v>
       </c>
       <c r="W11" t="n">
-        <v>1.71</v>
+        <v>1.64</v>
       </c>
       <c r="X11" t="n">
-        <v>970</v>
+        <v>9</v>
       </c>
       <c r="Y11" t="n">
-        <v>970</v>
+        <v>10.5</v>
       </c>
       <c r="Z11" t="n">
-        <v>100</v>
+        <v>22</v>
       </c>
       <c r="AA11" t="n">
-        <v>900</v>
+        <v>500</v>
       </c>
       <c r="AB11" t="n">
-        <v>970</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AC11" t="n">
-        <v>970</v>
+        <v>6.8</v>
       </c>
       <c r="AD11" t="n">
-        <v>970</v>
+        <v>15.5</v>
       </c>
       <c r="AE11" t="n">
         <v>500</v>
       </c>
       <c r="AF11" t="n">
-        <v>970</v>
+        <v>14</v>
       </c>
       <c r="AG11" t="n">
-        <v>970</v>
+        <v>12</v>
       </c>
       <c r="AH11" t="n">
-        <v>950</v>
+        <v>28</v>
       </c>
       <c r="AI11" t="n">
         <v>540</v>
       </c>
       <c r="AJ11" t="n">
-        <v>900</v>
+        <v>38</v>
       </c>
       <c r="AK11" t="n">
-        <v>110</v>
+        <v>65</v>
       </c>
       <c r="AL11" t="n">
-        <v>460</v>
+        <v>230</v>
       </c>
       <c r="AM11" t="n">
         <v>500</v>
       </c>
       <c r="AN11" t="n">
-        <v>600</v>
+        <v>55</v>
       </c>
       <c r="AO11" t="n">
-        <v>1000</v>
+        <v>130</v>
       </c>
       <c r="AP11" t="n">
-        <v>4.4</v>
+        <v>7.6</v>
       </c>
       <c r="AQ11" t="n">
-        <v>5.6</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AR11" t="n">
-        <v>2.4</v>
+        <v>18.5</v>
       </c>
       <c r="AS11" t="n">
-        <v>1.52</v>
+        <v>8.6</v>
       </c>
       <c r="AT11" t="n">
-        <v>3.85</v>
+        <v>6.6</v>
       </c>
       <c r="AU11" t="n">
-        <v>4.4</v>
+        <v>5.9</v>
       </c>
       <c r="AV11" t="n">
         <v>9</v>
       </c>
       <c r="AW11" t="n">
-        <v>1.51</v>
+        <v>8</v>
       </c>
       <c r="AX11" t="n">
-        <v>5.7</v>
+        <v>11.5</v>
       </c>
       <c r="AY11" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AZ11" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="BA11" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="BB11" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="BC11" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="BD11" t="n">
+        <v>8</v>
+      </c>
+      <c r="BE11" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="BF11" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="BG11" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="BH11" t="n">
+        <v>2.72</v>
+      </c>
+      <c r="BI11" t="n">
+        <v>2.48</v>
+      </c>
+      <c r="BJ11" t="n">
+        <v>11</v>
+      </c>
+      <c r="BK11" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="BL11" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BM11" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="BN11" t="n">
+        <v>5.3</v>
+      </c>
+      <c r="BO11" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="BP11" t="n">
+        <v>23</v>
+      </c>
+      <c r="BQ11" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="BR11" t="n">
+        <v>65</v>
+      </c>
+      <c r="BS11" t="n">
+        <v>12</v>
+      </c>
+      <c r="BT11" t="n">
         <v>6.4</v>
       </c>
-      <c r="AZ11" t="n">
-        <v>2.34</v>
-      </c>
-      <c r="BA11" t="n">
-        <v>1.52</v>
-      </c>
-      <c r="BB11" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="BC11" t="n">
-        <v>2.36</v>
-      </c>
-      <c r="BD11" t="n">
-        <v>1.51</v>
-      </c>
-      <c r="BE11" t="n">
-        <v>1.72</v>
-      </c>
-      <c r="BF11" t="n">
-        <v>1.55</v>
-      </c>
-      <c r="BG11" t="n">
-        <v>1.55</v>
-      </c>
-      <c r="BH11" t="n">
-        <v>2.68</v>
-      </c>
-      <c r="BI11" t="n">
-        <v>2.26</v>
-      </c>
-      <c r="BJ11" t="n">
-        <v>12</v>
-      </c>
-      <c r="BK11" t="n">
-        <v>6.4</v>
-      </c>
-      <c r="BL11" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BM11" t="n">
-        <v>13.5</v>
-      </c>
-      <c r="BN11" t="n">
-        <v>5</v>
-      </c>
-      <c r="BO11" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="BP11" t="n">
-        <v>21</v>
-      </c>
-      <c r="BQ11" t="n">
-        <v>8.6</v>
-      </c>
-      <c r="BR11" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BS11" t="n">
+      <c r="BU11" t="n">
+        <v>5.6</v>
+      </c>
+      <c r="BV11" t="n">
+        <v>34</v>
+      </c>
+      <c r="BW11" t="n">
         <v>11</v>
       </c>
-      <c r="BT11" t="n">
-        <v>7</v>
-      </c>
-      <c r="BU11" t="n">
-        <v>5.3</v>
-      </c>
-      <c r="BV11" t="n">
-        <v>40</v>
-      </c>
-      <c r="BW11" t="n">
-        <v>10.5</v>
-      </c>
       <c r="BX11" t="n">
         <v>1000</v>
       </c>
       <c r="BY11" t="n">
-        <v>11.5</v>
+        <v>13</v>
       </c>
       <c r="BZ11" t="n">
-        <v>55</v>
+        <v>65</v>
       </c>
       <c r="CA11" t="n">
-        <v>11.5</v>
+        <v>12.5</v>
       </c>
       <c r="CB11" t="inlineStr">
         <is>
-          <t>2026-06-12 09:58:55</t>
+          <t>2026-06-12 12:17:49</t>
         </is>
       </c>
     </row>
@@ -3400,19 +3400,19 @@
         <v>2.18</v>
       </c>
       <c r="G12" t="n">
-        <v>2.34</v>
+        <v>2.32</v>
       </c>
       <c r="H12" t="n">
         <v>3.2</v>
       </c>
       <c r="I12" t="n">
-        <v>3.55</v>
+        <v>3.5</v>
       </c>
       <c r="J12" t="n">
         <v>3.7</v>
       </c>
       <c r="K12" t="n">
-        <v>4.2</v>
+        <v>4.3</v>
       </c>
       <c r="L12" t="n">
         <v>1.3</v>
@@ -3430,19 +3430,19 @@
         <v>2.46</v>
       </c>
       <c r="Q12" t="n">
-        <v>1.61</v>
+        <v>1.6</v>
       </c>
       <c r="R12" t="n">
-        <v>1.58</v>
+        <v>1.6</v>
       </c>
       <c r="S12" t="n">
-        <v>2.54</v>
+        <v>2.52</v>
       </c>
       <c r="T12" t="n">
-        <v>1.53</v>
+        <v>1.54</v>
       </c>
       <c r="U12" t="n">
-        <v>2.5</v>
+        <v>2.56</v>
       </c>
       <c r="V12" t="n">
         <v>1.4</v>
@@ -3457,16 +3457,16 @@
         <v>19</v>
       </c>
       <c r="Z12" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="AA12" t="n">
         <v>85</v>
       </c>
       <c r="AB12" t="n">
-        <v>15</v>
+        <v>15.5</v>
       </c>
       <c r="AC12" t="n">
-        <v>10</v>
+        <v>9.6</v>
       </c>
       <c r="AD12" t="n">
         <v>15</v>
@@ -3475,13 +3475,13 @@
         <v>44</v>
       </c>
       <c r="AF12" t="n">
-        <v>18.5</v>
+        <v>18</v>
       </c>
       <c r="AG12" t="n">
         <v>12</v>
       </c>
       <c r="AH12" t="n">
-        <v>16</v>
+        <v>15.5</v>
       </c>
       <c r="AI12" t="n">
         <v>48</v>
@@ -3499,34 +3499,34 @@
         <v>200</v>
       </c>
       <c r="AN12" t="n">
-        <v>12.5</v>
+        <v>12</v>
       </c>
       <c r="AO12" t="n">
         <v>22</v>
       </c>
       <c r="AP12" t="n">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="AQ12" t="n">
-        <v>15</v>
+        <v>15.5</v>
       </c>
       <c r="AR12" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AS12" t="n">
-        <v>9.6</v>
+        <v>9.4</v>
       </c>
       <c r="AT12" t="n">
-        <v>10</v>
+        <v>12.5</v>
       </c>
       <c r="AU12" t="n">
-        <v>7.8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AV12" t="n">
         <v>12</v>
       </c>
       <c r="AW12" t="n">
-        <v>26</v>
+        <v>15</v>
       </c>
       <c r="AX12" t="n">
         <v>14.5</v>
@@ -3550,13 +3550,13 @@
         <v>15</v>
       </c>
       <c r="BE12" t="n">
-        <v>27</v>
+        <v>9.4</v>
       </c>
       <c r="BF12" t="n">
         <v>9.800000000000001</v>
       </c>
       <c r="BG12" t="n">
-        <v>17.5</v>
+        <v>18</v>
       </c>
       <c r="BH12" t="n">
         <v>4.5</v>
@@ -3574,16 +3574,16 @@
         <v>1000</v>
       </c>
       <c r="BM12" t="n">
-        <v>8.6</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BN12" t="n">
         <v>5.8</v>
       </c>
       <c r="BO12" t="n">
-        <v>4.3</v>
+        <v>4.8</v>
       </c>
       <c r="BP12" t="n">
-        <v>16</v>
+        <v>15.5</v>
       </c>
       <c r="BQ12" t="n">
         <v>6</v>
@@ -3592,7 +3592,7 @@
         <v>1000</v>
       </c>
       <c r="BS12" t="n">
-        <v>6.8</v>
+        <v>7</v>
       </c>
       <c r="BT12" t="n">
         <v>7.2</v>
@@ -3610,7 +3610,7 @@
         <v>1000</v>
       </c>
       <c r="BY12" t="n">
-        <v>7.2</v>
+        <v>7.4</v>
       </c>
       <c r="BZ12" t="n">
         <v>17</v>
@@ -3620,7 +3620,7 @@
       </c>
       <c r="CB12" t="inlineStr">
         <is>
-          <t>2026-06-12 09:58:55</t>
+          <t>2026-06-12 12:17:49</t>
         </is>
       </c>
     </row>
@@ -3651,58 +3651,58 @@
         </is>
       </c>
       <c r="F13" t="n">
-        <v>1.19</v>
+        <v>1.22</v>
       </c>
       <c r="G13" t="n">
-        <v>1.22</v>
+        <v>1.23</v>
       </c>
       <c r="H13" t="n">
-        <v>14.5</v>
+        <v>15.5</v>
       </c>
       <c r="I13" t="n">
-        <v>19.5</v>
+        <v>18</v>
       </c>
       <c r="J13" t="n">
-        <v>8.4</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="K13" t="n">
-        <v>10</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="L13" t="n">
-        <v>1.2</v>
+        <v>1.21</v>
       </c>
       <c r="M13" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="N13" t="n">
-        <v>8</v>
+        <v>7.4</v>
       </c>
       <c r="O13" t="n">
-        <v>1.12</v>
+        <v>1.13</v>
       </c>
       <c r="P13" t="n">
-        <v>3.4</v>
+        <v>3.2</v>
       </c>
       <c r="Q13" t="n">
-        <v>1.37</v>
+        <v>1.41</v>
       </c>
       <c r="R13" t="n">
-        <v>1.98</v>
+        <v>1.89</v>
       </c>
       <c r="S13" t="n">
-        <v>1.93</v>
+        <v>2.04</v>
       </c>
       <c r="T13" t="n">
-        <v>2</v>
+        <v>2.04</v>
       </c>
       <c r="U13" t="n">
-        <v>1.81</v>
+        <v>1.79</v>
       </c>
       <c r="V13" t="n">
         <v>1.06</v>
       </c>
       <c r="W13" t="n">
-        <v>5.5</v>
+        <v>5.3</v>
       </c>
       <c r="X13" t="n">
         <v>950</v>
@@ -3711,40 +3711,40 @@
         <v>950</v>
       </c>
       <c r="Z13" t="n">
-        <v>180</v>
+        <v>170</v>
       </c>
       <c r="AA13" t="n">
         <v>1000</v>
       </c>
       <c r="AB13" t="n">
-        <v>14</v>
+        <v>12.5</v>
       </c>
       <c r="AC13" t="n">
-        <v>950</v>
+        <v>21</v>
       </c>
       <c r="AD13" t="n">
         <v>950</v>
       </c>
       <c r="AE13" t="n">
-        <v>250</v>
+        <v>270</v>
       </c>
       <c r="AF13" t="n">
-        <v>10.5</v>
+        <v>9.6</v>
       </c>
       <c r="AG13" t="n">
-        <v>13.5</v>
+        <v>13</v>
       </c>
       <c r="AH13" t="n">
         <v>950</v>
       </c>
       <c r="AI13" t="n">
-        <v>170</v>
+        <v>180</v>
       </c>
       <c r="AJ13" t="n">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="AK13" t="n">
-        <v>17.5</v>
+        <v>15</v>
       </c>
       <c r="AL13" t="n">
         <v>48</v>
@@ -3753,46 +3753,46 @@
         <v>160</v>
       </c>
       <c r="AN13" t="n">
-        <v>3.1</v>
+        <v>3.3</v>
       </c>
       <c r="AO13" t="n">
-        <v>250</v>
+        <v>260</v>
       </c>
       <c r="AP13" t="n">
+        <v>20</v>
+      </c>
+      <c r="AQ13" t="n">
+        <v>25</v>
+      </c>
+      <c r="AR13" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AS13" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="AT13" t="n">
         <v>10</v>
       </c>
-      <c r="AQ13" t="n">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="AR13" t="n">
-        <v>9.800000000000001</v>
-      </c>
-      <c r="AS13" t="n">
-        <v>10</v>
-      </c>
-      <c r="AT13" t="n">
-        <v>11.5</v>
-      </c>
       <c r="AU13" t="n">
-        <v>17.5</v>
+        <v>16</v>
       </c>
       <c r="AV13" t="n">
-        <v>9</v>
+        <v>10.5</v>
       </c>
       <c r="AW13" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AX13" t="n">
-        <v>8.6</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AY13" t="n">
         <v>10.5</v>
       </c>
       <c r="AZ13" t="n">
-        <v>14.5</v>
+        <v>15</v>
       </c>
       <c r="BA13" t="n">
-        <v>9.800000000000001</v>
+        <v>11</v>
       </c>
       <c r="BB13" t="n">
         <v>8.4</v>
@@ -3804,77 +3804,77 @@
         <v>17.5</v>
       </c>
       <c r="BE13" t="n">
-        <v>9.800000000000001</v>
+        <v>11.5</v>
       </c>
       <c r="BF13" t="n">
-        <v>2.8</v>
+        <v>3</v>
       </c>
       <c r="BG13" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="BH13" t="n">
+        <v>5.7</v>
+      </c>
+      <c r="BI13" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="BJ13" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="BK13" t="n">
         <v>6</v>
       </c>
-      <c r="BI13" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="BJ13" t="n">
-        <v>13</v>
-      </c>
-      <c r="BK13" t="n">
-        <v>5.7</v>
-      </c>
       <c r="BL13" t="n">
         <v>1000</v>
       </c>
       <c r="BM13" t="n">
-        <v>9.4</v>
+        <v>10.5</v>
       </c>
       <c r="BN13" t="n">
-        <v>4.3</v>
+        <v>4.2</v>
       </c>
       <c r="BO13" t="n">
-        <v>3.6</v>
+        <v>3.4</v>
       </c>
       <c r="BP13" t="n">
-        <v>6.6</v>
+        <v>6.8</v>
       </c>
       <c r="BQ13" t="n">
-        <v>5.4</v>
+        <v>5.2</v>
       </c>
       <c r="BR13" t="n">
         <v>19.5</v>
       </c>
       <c r="BS13" t="n">
-        <v>6.6</v>
+        <v>7.2</v>
       </c>
       <c r="BT13" t="n">
-        <v>18</v>
+        <v>17.5</v>
       </c>
       <c r="BU13" t="n">
-        <v>6.4</v>
+        <v>6.8</v>
       </c>
       <c r="BV13" t="n">
         <v>1000</v>
       </c>
       <c r="BW13" t="n">
-        <v>9.199999999999999</v>
+        <v>10.5</v>
       </c>
       <c r="BX13" t="n">
         <v>1000</v>
       </c>
       <c r="BY13" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="BZ13" t="n">
-        <v>7.2</v>
+        <v>7.4</v>
       </c>
       <c r="CA13" t="n">
         <v>5.8</v>
       </c>
       <c r="CB13" t="inlineStr">
         <is>
-          <t>2026-06-12 09:58:55</t>
+          <t>2026-06-12 12:17:49</t>
         </is>
       </c>
     </row>
@@ -3905,16 +3905,16 @@
         </is>
       </c>
       <c r="F14" t="n">
-        <v>2.98</v>
+        <v>2.92</v>
       </c>
       <c r="G14" t="n">
-        <v>3.15</v>
+        <v>3.05</v>
       </c>
       <c r="H14" t="n">
-        <v>2.48</v>
+        <v>2.52</v>
       </c>
       <c r="I14" t="n">
-        <v>2.6</v>
+        <v>2.64</v>
       </c>
       <c r="J14" t="n">
         <v>3.55</v>
@@ -3923,25 +3923,25 @@
         <v>3.6</v>
       </c>
       <c r="L14" t="n">
-        <v>1.44</v>
+        <v>1.45</v>
       </c>
       <c r="M14" t="n">
         <v>1.08</v>
       </c>
       <c r="N14" t="n">
-        <v>3.45</v>
+        <v>3.4</v>
       </c>
       <c r="O14" t="n">
         <v>1.37</v>
       </c>
       <c r="P14" t="n">
-        <v>1.81</v>
+        <v>1.83</v>
       </c>
       <c r="Q14" t="n">
         <v>2.1</v>
       </c>
       <c r="R14" t="n">
-        <v>1.32</v>
+        <v>1.33</v>
       </c>
       <c r="S14" t="n">
         <v>3.9</v>
@@ -3950,16 +3950,16 @@
         <v>1.8</v>
       </c>
       <c r="U14" t="n">
-        <v>2.12</v>
+        <v>2.14</v>
       </c>
       <c r="V14" t="n">
-        <v>1.63</v>
+        <v>1.6</v>
       </c>
       <c r="W14" t="n">
-        <v>1.46</v>
+        <v>1.48</v>
       </c>
       <c r="X14" t="n">
-        <v>12.5</v>
+        <v>13</v>
       </c>
       <c r="Y14" t="n">
         <v>10.5</v>
@@ -3968,7 +3968,7 @@
         <v>17</v>
       </c>
       <c r="AA14" t="n">
-        <v>38</v>
+        <v>55</v>
       </c>
       <c r="AB14" t="n">
         <v>11.5</v>
@@ -3983,7 +3983,7 @@
         <v>30</v>
       </c>
       <c r="AF14" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AG14" t="n">
         <v>13.5</v>
@@ -3998,19 +3998,19 @@
         <v>55</v>
       </c>
       <c r="AK14" t="n">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="AL14" t="n">
-        <v>55</v>
+        <v>50</v>
       </c>
       <c r="AM14" t="n">
         <v>110</v>
       </c>
       <c r="AN14" t="n">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="AO14" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="AP14" t="n">
         <v>11</v>
@@ -4025,7 +4025,7 @@
         <v>28</v>
       </c>
       <c r="AT14" t="n">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="AU14" t="n">
         <v>7</v>
@@ -4037,10 +4037,10 @@
         <v>24</v>
       </c>
       <c r="AX14" t="n">
-        <v>18.5</v>
+        <v>18</v>
       </c>
       <c r="AY14" t="n">
-        <v>11.5</v>
+        <v>12</v>
       </c>
       <c r="AZ14" t="n">
         <v>16.5</v>
@@ -4049,13 +4049,13 @@
         <v>38</v>
       </c>
       <c r="BB14" t="n">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="BC14" t="n">
         <v>32</v>
       </c>
       <c r="BD14" t="n">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="BE14" t="n">
         <v>40</v>
@@ -4082,16 +4082,16 @@
         <v>1000</v>
       </c>
       <c r="BM14" t="n">
-        <v>13</v>
+        <v>13.5</v>
       </c>
       <c r="BN14" t="n">
         <v>6.4</v>
       </c>
       <c r="BO14" t="n">
-        <v>4.8</v>
+        <v>4.7</v>
       </c>
       <c r="BP14" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="BQ14" t="n">
         <v>9.4</v>
@@ -4100,7 +4100,7 @@
         <v>1000</v>
       </c>
       <c r="BS14" t="n">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="BT14" t="n">
         <v>5.4</v>
@@ -4118,7 +4118,7 @@
         <v>1000</v>
       </c>
       <c r="BY14" t="n">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="BZ14" t="n">
         <v>32</v>
@@ -4128,7 +4128,7 @@
       </c>
       <c r="CB14" t="inlineStr">
         <is>
-          <t>2026-06-12 09:58:55</t>
+          <t>2026-06-12 12:17:49</t>
         </is>
       </c>
     </row>
@@ -4159,82 +4159,82 @@
         </is>
       </c>
       <c r="F15" t="n">
-        <v>1.74</v>
+        <v>1.79</v>
       </c>
       <c r="G15" t="n">
-        <v>1.8</v>
+        <v>1.84</v>
       </c>
       <c r="H15" t="n">
-        <v>5.6</v>
+        <v>5.4</v>
       </c>
       <c r="I15" t="n">
-        <v>6.2</v>
+        <v>5.7</v>
       </c>
       <c r="J15" t="n">
-        <v>3.7</v>
+        <v>3.6</v>
       </c>
       <c r="K15" t="n">
-        <v>3.95</v>
+        <v>3.8</v>
       </c>
       <c r="L15" t="n">
-        <v>1.58</v>
+        <v>1.59</v>
       </c>
       <c r="M15" t="n">
         <v>1.12</v>
       </c>
       <c r="N15" t="n">
-        <v>2.66</v>
+        <v>2.6</v>
       </c>
       <c r="O15" t="n">
-        <v>1.54</v>
+        <v>1.57</v>
       </c>
       <c r="P15" t="n">
-        <v>1.55</v>
+        <v>1.52</v>
       </c>
       <c r="Q15" t="n">
-        <v>2.62</v>
+        <v>2.76</v>
       </c>
       <c r="R15" t="n">
-        <v>1.19</v>
+        <v>1.16</v>
       </c>
       <c r="S15" t="n">
-        <v>5.5</v>
+        <v>6.2</v>
       </c>
       <c r="T15" t="n">
-        <v>2.34</v>
+        <v>2.44</v>
       </c>
       <c r="U15" t="n">
-        <v>1.6</v>
+        <v>1.56</v>
       </c>
       <c r="V15" t="n">
-        <v>1.2</v>
+        <v>1.21</v>
       </c>
       <c r="W15" t="n">
-        <v>2.24</v>
+        <v>2.18</v>
       </c>
       <c r="X15" t="n">
-        <v>9.6</v>
+        <v>9.4</v>
       </c>
       <c r="Y15" t="n">
-        <v>14</v>
+        <v>13.5</v>
       </c>
       <c r="Z15" t="n">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="AA15" t="n">
-        <v>900</v>
+        <v>500</v>
       </c>
       <c r="AB15" t="n">
-        <v>6.8</v>
+        <v>6.4</v>
       </c>
       <c r="AC15" t="n">
-        <v>9</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AD15" t="n">
         <v>25</v>
       </c>
       <c r="AE15" t="n">
-        <v>160</v>
+        <v>140</v>
       </c>
       <c r="AF15" t="n">
         <v>8.800000000000001</v>
@@ -4243,28 +4243,28 @@
         <v>12</v>
       </c>
       <c r="AH15" t="n">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="AI15" t="n">
         <v>500</v>
       </c>
       <c r="AJ15" t="n">
-        <v>19</v>
+        <v>19.5</v>
       </c>
       <c r="AK15" t="n">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="AL15" t="n">
-        <v>70</v>
+        <v>90</v>
       </c>
       <c r="AM15" t="n">
         <v>500</v>
       </c>
       <c r="AN15" t="n">
-        <v>19.5</v>
+        <v>24</v>
       </c>
       <c r="AO15" t="n">
-        <v>360</v>
+        <v>280</v>
       </c>
       <c r="AP15" t="n">
         <v>8</v>
@@ -4273,22 +4273,22 @@
         <v>11.5</v>
       </c>
       <c r="AR15" t="n">
-        <v>28</v>
+        <v>36</v>
       </c>
       <c r="AS15" t="n">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="AT15" t="n">
-        <v>5.6</v>
+        <v>5.4</v>
       </c>
       <c r="AU15" t="n">
         <v>7.6</v>
       </c>
       <c r="AV15" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AW15" t="n">
-        <v>11.5</v>
+        <v>23</v>
       </c>
       <c r="AX15" t="n">
         <v>7.6</v>
@@ -4300,89 +4300,89 @@
         <v>28</v>
       </c>
       <c r="BA15" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="BB15" t="n">
-        <v>16</v>
+        <v>17.5</v>
       </c>
       <c r="BC15" t="n">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="BD15" t="n">
         <v>55</v>
       </c>
       <c r="BE15" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="BF15" t="n">
-        <v>16.5</v>
+        <v>20</v>
       </c>
       <c r="BG15" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="BH15" t="n">
-        <v>2.84</v>
+        <v>2.8</v>
       </c>
       <c r="BI15" t="n">
-        <v>2.3</v>
+        <v>2.44</v>
       </c>
       <c r="BJ15" t="n">
-        <v>13</v>
+        <v>13.5</v>
       </c>
       <c r="BK15" t="n">
-        <v>9.800000000000001</v>
+        <v>6</v>
       </c>
       <c r="BL15" t="n">
         <v>1000</v>
       </c>
       <c r="BM15" t="n">
-        <v>11.5</v>
+        <v>10.5</v>
       </c>
       <c r="BN15" t="n">
-        <v>4.2</v>
+        <v>4.3</v>
       </c>
       <c r="BO15" t="n">
-        <v>3.2</v>
+        <v>3.65</v>
       </c>
       <c r="BP15" t="n">
-        <v>14.5</v>
+        <v>15</v>
       </c>
       <c r="BQ15" t="n">
-        <v>10</v>
+        <v>6.2</v>
       </c>
       <c r="BR15" t="n">
         <v>1000</v>
       </c>
       <c r="BS15" t="n">
-        <v>9.4</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BT15" t="n">
         <v>9.6</v>
       </c>
       <c r="BU15" t="n">
-        <v>5.3</v>
+        <v>6.8</v>
       </c>
       <c r="BV15" t="n">
         <v>1000</v>
       </c>
       <c r="BW15" t="n">
-        <v>10</v>
+        <v>9.6</v>
       </c>
       <c r="BX15" t="n">
         <v>1000</v>
       </c>
       <c r="BY15" t="n">
-        <v>10.5</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BZ15" t="n">
         <v>1000</v>
       </c>
       <c r="CA15" t="n">
-        <v>9.4</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="CB15" t="inlineStr">
         <is>
-          <t>2026-06-12 09:58:55</t>
+          <t>2026-06-12 12:17:49</t>
         </is>
       </c>
     </row>
@@ -4413,16 +4413,16 @@
         </is>
       </c>
       <c r="F16" t="n">
-        <v>2.92</v>
+        <v>2.9</v>
       </c>
       <c r="G16" t="n">
-        <v>3</v>
+        <v>2.98</v>
       </c>
       <c r="H16" t="n">
-        <v>2.44</v>
+        <v>2.46</v>
       </c>
       <c r="I16" t="n">
-        <v>2.52</v>
+        <v>2.54</v>
       </c>
       <c r="J16" t="n">
         <v>3.85</v>
@@ -4437,55 +4437,55 @@
         <v>1.05</v>
       </c>
       <c r="N16" t="n">
-        <v>4.9</v>
+        <v>5.1</v>
       </c>
       <c r="O16" t="n">
-        <v>1.24</v>
+        <v>1.23</v>
       </c>
       <c r="P16" t="n">
-        <v>2.32</v>
+        <v>2.38</v>
       </c>
       <c r="Q16" t="n">
-        <v>1.73</v>
+        <v>1.7</v>
       </c>
       <c r="R16" t="n">
-        <v>1.52</v>
+        <v>1.53</v>
       </c>
       <c r="S16" t="n">
-        <v>2.82</v>
+        <v>2.78</v>
       </c>
       <c r="T16" t="n">
         <v>1.62</v>
       </c>
       <c r="U16" t="n">
-        <v>2.46</v>
+        <v>2.52</v>
       </c>
       <c r="V16" t="n">
-        <v>1.66</v>
+        <v>1.65</v>
       </c>
       <c r="W16" t="n">
         <v>1.5</v>
       </c>
       <c r="X16" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="Y16" t="n">
-        <v>14</v>
+        <v>13.5</v>
       </c>
       <c r="Z16" t="n">
-        <v>19.5</v>
+        <v>19</v>
       </c>
       <c r="AA16" t="n">
         <v>36</v>
       </c>
       <c r="AB16" t="n">
-        <v>16</v>
+        <v>15.5</v>
       </c>
       <c r="AC16" t="n">
         <v>8.800000000000001</v>
       </c>
       <c r="AD16" t="n">
-        <v>12</v>
+        <v>11.5</v>
       </c>
       <c r="AE16" t="n">
         <v>25</v>
@@ -4494,7 +4494,7 @@
         <v>23</v>
       </c>
       <c r="AG16" t="n">
-        <v>13.5</v>
+        <v>12.5</v>
       </c>
       <c r="AH16" t="n">
         <v>15.5</v>
@@ -4503,7 +4503,7 @@
         <v>32</v>
       </c>
       <c r="AJ16" t="n">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="AK16" t="n">
         <v>29</v>
@@ -4512,7 +4512,7 @@
         <v>36</v>
       </c>
       <c r="AM16" t="n">
-        <v>65</v>
+        <v>70</v>
       </c>
       <c r="AN16" t="n">
         <v>21</v>
@@ -4521,22 +4521,22 @@
         <v>16</v>
       </c>
       <c r="AP16" t="n">
-        <v>17.5</v>
+        <v>18</v>
       </c>
       <c r="AQ16" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AR16" t="n">
-        <v>16</v>
+        <v>16.5</v>
       </c>
       <c r="AS16" t="n">
         <v>30</v>
       </c>
       <c r="AT16" t="n">
-        <v>14</v>
+        <v>14.5</v>
       </c>
       <c r="AU16" t="n">
-        <v>7.8</v>
+        <v>8</v>
       </c>
       <c r="AV16" t="n">
         <v>10.5</v>
@@ -4545,19 +4545,19 @@
         <v>21</v>
       </c>
       <c r="AX16" t="n">
-        <v>19.5</v>
+        <v>20</v>
       </c>
       <c r="AY16" t="n">
         <v>11.5</v>
       </c>
       <c r="AZ16" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="BA16" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="BB16" t="n">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="BC16" t="n">
         <v>26</v>
@@ -4569,34 +4569,34 @@
         <v>50</v>
       </c>
       <c r="BF16" t="n">
-        <v>18</v>
+        <v>18.5</v>
       </c>
       <c r="BG16" t="n">
-        <v>13.5</v>
+        <v>14</v>
       </c>
       <c r="BH16" t="n">
         <v>4.2</v>
       </c>
       <c r="BI16" t="n">
-        <v>3.15</v>
+        <v>3.5</v>
       </c>
       <c r="BJ16" t="n">
-        <v>9.199999999999999</v>
+        <v>9</v>
       </c>
       <c r="BK16" t="n">
         <v>4.7</v>
       </c>
       <c r="BL16" t="n">
-        <v>90</v>
+        <v>85</v>
       </c>
       <c r="BM16" t="n">
-        <v>9</v>
+        <v>65</v>
       </c>
       <c r="BN16" t="n">
         <v>6.6</v>
       </c>
       <c r="BO16" t="n">
-        <v>4.8</v>
+        <v>5.4</v>
       </c>
       <c r="BP16" t="n">
         <v>22</v>
@@ -4608,13 +4608,13 @@
         <v>30</v>
       </c>
       <c r="BS16" t="n">
-        <v>7.4</v>
+        <v>7.6</v>
       </c>
       <c r="BT16" t="n">
-        <v>5.9</v>
+        <v>6</v>
       </c>
       <c r="BU16" t="n">
-        <v>4.3</v>
+        <v>4.9</v>
       </c>
       <c r="BV16" t="n">
         <v>18</v>
@@ -4629,14 +4629,14 @@
         <v>7.2</v>
       </c>
       <c r="BZ16" t="n">
-        <v>20</v>
+        <v>19.5</v>
       </c>
       <c r="CA16" t="n">
         <v>6.6</v>
       </c>
       <c r="CB16" t="inlineStr">
         <is>
-          <t>2026-06-12 09:58:55</t>
+          <t>2026-06-12 12:17:49</t>
         </is>
       </c>
     </row>
@@ -4667,16 +4667,16 @@
         </is>
       </c>
       <c r="F17" t="n">
-        <v>1.43</v>
+        <v>1.44</v>
       </c>
       <c r="G17" t="n">
-        <v>1.45</v>
+        <v>1.46</v>
       </c>
       <c r="H17" t="n">
-        <v>9.199999999999999</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="I17" t="n">
-        <v>10</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="J17" t="n">
         <v>4.9</v>
@@ -4700,37 +4700,37 @@
         <v>2.08</v>
       </c>
       <c r="Q17" t="n">
-        <v>1.87</v>
+        <v>1.9</v>
       </c>
       <c r="R17" t="n">
         <v>1.41</v>
       </c>
       <c r="S17" t="n">
-        <v>3.25</v>
+        <v>3.3</v>
       </c>
       <c r="T17" t="n">
         <v>2.12</v>
       </c>
       <c r="U17" t="n">
-        <v>1.8</v>
+        <v>1.81</v>
       </c>
       <c r="V17" t="n">
         <v>1.11</v>
       </c>
       <c r="W17" t="n">
-        <v>3.2</v>
+        <v>3.15</v>
       </c>
       <c r="X17" t="n">
         <v>17.5</v>
       </c>
       <c r="Y17" t="n">
-        <v>30</v>
+        <v>65</v>
       </c>
       <c r="Z17" t="n">
         <v>85</v>
       </c>
       <c r="AA17" t="n">
-        <v>380</v>
+        <v>360</v>
       </c>
       <c r="AB17" t="n">
         <v>7.8</v>
@@ -4739,13 +4739,13 @@
         <v>11</v>
       </c>
       <c r="AD17" t="n">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="AE17" t="n">
-        <v>180</v>
+        <v>170</v>
       </c>
       <c r="AF17" t="n">
-        <v>8</v>
+        <v>8.4</v>
       </c>
       <c r="AG17" t="n">
         <v>10</v>
@@ -4754,22 +4754,22 @@
         <v>28</v>
       </c>
       <c r="AI17" t="n">
-        <v>150</v>
+        <v>160</v>
       </c>
       <c r="AJ17" t="n">
-        <v>12</v>
+        <v>12.5</v>
       </c>
       <c r="AK17" t="n">
         <v>16.5</v>
       </c>
       <c r="AL17" t="n">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="AM17" t="n">
-        <v>200</v>
+        <v>180</v>
       </c>
       <c r="AN17" t="n">
-        <v>7.4</v>
+        <v>7.6</v>
       </c>
       <c r="AO17" t="n">
         <v>220</v>
@@ -4778,16 +4778,16 @@
         <v>16.5</v>
       </c>
       <c r="AQ17" t="n">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="AR17" t="n">
-        <v>40</v>
+        <v>65</v>
       </c>
       <c r="AS17" t="n">
-        <v>16</v>
+        <v>75</v>
       </c>
       <c r="AT17" t="n">
-        <v>7.4</v>
+        <v>7.2</v>
       </c>
       <c r="AU17" t="n">
         <v>10</v>
@@ -4796,7 +4796,7 @@
         <v>30</v>
       </c>
       <c r="AW17" t="n">
-        <v>19</v>
+        <v>36</v>
       </c>
       <c r="AX17" t="n">
         <v>7</v>
@@ -4805,10 +4805,10 @@
         <v>9.4</v>
       </c>
       <c r="AZ17" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="BA17" t="n">
-        <v>36</v>
+        <v>42</v>
       </c>
       <c r="BB17" t="n">
         <v>10.5</v>
@@ -4820,19 +4820,19 @@
         <v>36</v>
       </c>
       <c r="BE17" t="n">
-        <v>42</v>
+        <v>120</v>
       </c>
       <c r="BF17" t="n">
         <v>6.6</v>
       </c>
       <c r="BG17" t="n">
-        <v>15.5</v>
+        <v>15</v>
       </c>
       <c r="BH17" t="n">
         <v>3.75</v>
       </c>
       <c r="BI17" t="n">
-        <v>2.9</v>
+        <v>3.25</v>
       </c>
       <c r="BJ17" t="n">
         <v>13</v>
@@ -4844,16 +4844,16 @@
         <v>1000</v>
       </c>
       <c r="BM17" t="n">
-        <v>11</v>
+        <v>140</v>
       </c>
       <c r="BN17" t="n">
-        <v>3.8</v>
+        <v>3.85</v>
       </c>
       <c r="BO17" t="n">
-        <v>3.25</v>
+        <v>3.4</v>
       </c>
       <c r="BP17" t="n">
-        <v>8.800000000000001</v>
+        <v>9</v>
       </c>
       <c r="BQ17" t="n">
         <v>5</v>
@@ -4862,13 +4862,13 @@
         <v>1000</v>
       </c>
       <c r="BS17" t="n">
-        <v>8.199999999999999</v>
+        <v>8</v>
       </c>
       <c r="BT17" t="n">
-        <v>13.5</v>
+        <v>13</v>
       </c>
       <c r="BU17" t="n">
-        <v>6.2</v>
+        <v>6</v>
       </c>
       <c r="BV17" t="n">
         <v>1000</v>
@@ -4890,7 +4890,7 @@
       </c>
       <c r="CB17" t="inlineStr">
         <is>
-          <t>2026-06-12 09:58:55</t>
+          <t>2026-06-12 12:17:49</t>
         </is>
       </c>
     </row>
@@ -4924,7 +4924,7 @@
         <v>3.15</v>
       </c>
       <c r="G18" t="n">
-        <v>3.2</v>
+        <v>3.25</v>
       </c>
       <c r="H18" t="n">
         <v>2.6</v>
@@ -4951,22 +4951,22 @@
         <v>1.43</v>
       </c>
       <c r="P18" t="n">
-        <v>1.72</v>
+        <v>1.74</v>
       </c>
       <c r="Q18" t="n">
-        <v>2.32</v>
+        <v>2.3</v>
       </c>
       <c r="R18" t="n">
-        <v>1.26</v>
+        <v>1.27</v>
       </c>
       <c r="S18" t="n">
         <v>4.5</v>
       </c>
       <c r="T18" t="n">
-        <v>1.93</v>
+        <v>1.92</v>
       </c>
       <c r="U18" t="n">
-        <v>1.98</v>
+        <v>2</v>
       </c>
       <c r="V18" t="n">
         <v>1.6</v>
@@ -4975,7 +4975,7 @@
         <v>1.45</v>
       </c>
       <c r="X18" t="n">
-        <v>12</v>
+        <v>11.5</v>
       </c>
       <c r="Y18" t="n">
         <v>9.4</v>
@@ -5011,7 +5011,7 @@
         <v>60</v>
       </c>
       <c r="AJ18" t="n">
-        <v>85</v>
+        <v>55</v>
       </c>
       <c r="AK18" t="n">
         <v>40</v>
@@ -5026,13 +5026,13 @@
         <v>46</v>
       </c>
       <c r="AO18" t="n">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="AP18" t="n">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="AQ18" t="n">
-        <v>8.4</v>
+        <v>8.6</v>
       </c>
       <c r="AR18" t="n">
         <v>14</v>
@@ -5053,13 +5053,13 @@
         <v>27</v>
       </c>
       <c r="AX18" t="n">
-        <v>18</v>
+        <v>18.5</v>
       </c>
       <c r="AY18" t="n">
         <v>12.5</v>
       </c>
       <c r="AZ18" t="n">
-        <v>15.5</v>
+        <v>16</v>
       </c>
       <c r="BA18" t="n">
         <v>34</v>
@@ -5074,10 +5074,10 @@
         <v>50</v>
       </c>
       <c r="BE18" t="n">
-        <v>16</v>
+        <v>100</v>
       </c>
       <c r="BF18" t="n">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="BG18" t="n">
         <v>27</v>
@@ -5086,7 +5086,7 @@
         <v>3.05</v>
       </c>
       <c r="BI18" t="n">
-        <v>2.8</v>
+        <v>2.78</v>
       </c>
       <c r="BJ18" t="n">
         <v>10.5</v>
@@ -5098,7 +5098,7 @@
         <v>1000</v>
       </c>
       <c r="BM18" t="n">
-        <v>14.5</v>
+        <v>130</v>
       </c>
       <c r="BN18" t="n">
         <v>6.2</v>
@@ -5144,7 +5144,7 @@
       </c>
       <c r="CB18" t="inlineStr">
         <is>
-          <t>2026-06-12 09:58:55</t>
+          <t>2026-06-12 12:17:49</t>
         </is>
       </c>
     </row>
@@ -5187,7 +5187,7 @@
         <v>3.95</v>
       </c>
       <c r="J19" t="n">
-        <v>3.7</v>
+        <v>3.65</v>
       </c>
       <c r="K19" t="n">
         <v>3.8</v>
@@ -5205,10 +5205,10 @@
         <v>1.28</v>
       </c>
       <c r="P19" t="n">
-        <v>2.14</v>
+        <v>2.12</v>
       </c>
       <c r="Q19" t="n">
-        <v>1.86</v>
+        <v>1.87</v>
       </c>
       <c r="R19" t="n">
         <v>1.43</v>
@@ -5220,10 +5220,10 @@
         <v>1.72</v>
       </c>
       <c r="U19" t="n">
-        <v>2.26</v>
+        <v>2.3</v>
       </c>
       <c r="V19" t="n">
-        <v>1.35</v>
+        <v>1.34</v>
       </c>
       <c r="W19" t="n">
         <v>1.89</v>
@@ -5250,7 +5250,7 @@
         <v>15.5</v>
       </c>
       <c r="AE19" t="n">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="AF19" t="n">
         <v>14</v>
@@ -5259,7 +5259,7 @@
         <v>10.5</v>
       </c>
       <c r="AH19" t="n">
-        <v>18.5</v>
+        <v>17.5</v>
       </c>
       <c r="AI19" t="n">
         <v>55</v>
@@ -5268,13 +5268,13 @@
         <v>27</v>
       </c>
       <c r="AK19" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AL19" t="n">
         <v>36</v>
       </c>
       <c r="AM19" t="n">
-        <v>95</v>
+        <v>90</v>
       </c>
       <c r="AN19" t="n">
         <v>14.5</v>
@@ -5283,7 +5283,7 @@
         <v>40</v>
       </c>
       <c r="AP19" t="n">
-        <v>15</v>
+        <v>14.5</v>
       </c>
       <c r="AQ19" t="n">
         <v>14</v>
@@ -5292,7 +5292,7 @@
         <v>24</v>
       </c>
       <c r="AS19" t="n">
-        <v>60</v>
+        <v>65</v>
       </c>
       <c r="AT19" t="n">
         <v>9.6</v>
@@ -5310,13 +5310,13 @@
         <v>12.5</v>
       </c>
       <c r="AY19" t="n">
-        <v>9.4</v>
+        <v>9.6</v>
       </c>
       <c r="AZ19" t="n">
         <v>15.5</v>
       </c>
       <c r="BA19" t="n">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="BB19" t="n">
         <v>23</v>
@@ -5328,49 +5328,49 @@
         <v>30</v>
       </c>
       <c r="BE19" t="n">
-        <v>38</v>
+        <v>50</v>
       </c>
       <c r="BF19" t="n">
         <v>13</v>
       </c>
       <c r="BG19" t="n">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="BH19" t="n">
         <v>3.75</v>
       </c>
       <c r="BI19" t="n">
-        <v>2.88</v>
+        <v>3.2</v>
       </c>
       <c r="BJ19" t="n">
-        <v>9.4</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BK19" t="n">
-        <v>7.2</v>
+        <v>5.1</v>
       </c>
       <c r="BL19" t="n">
         <v>1000</v>
       </c>
       <c r="BM19" t="n">
-        <v>10</v>
+        <v>75</v>
       </c>
       <c r="BN19" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="BO19" t="n">
-        <v>4.3</v>
+        <v>4.5</v>
       </c>
       <c r="BP19" t="n">
         <v>15.5</v>
       </c>
       <c r="BQ19" t="n">
-        <v>6.4</v>
+        <v>6.2</v>
       </c>
       <c r="BR19" t="n">
         <v>28</v>
       </c>
       <c r="BS19" t="n">
-        <v>8</v>
+        <v>7.6</v>
       </c>
       <c r="BT19" t="n">
         <v>7.4</v>
@@ -5379,26 +5379,26 @@
         <v>6</v>
       </c>
       <c r="BV19" t="n">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="BW19" t="n">
-        <v>8.199999999999999</v>
+        <v>8</v>
       </c>
       <c r="BX19" t="n">
         <v>40</v>
       </c>
       <c r="BY19" t="n">
-        <v>8.800000000000001</v>
+        <v>8.4</v>
       </c>
       <c r="BZ19" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="CA19" t="n">
         <v>7.4</v>
       </c>
       <c r="CB19" t="inlineStr">
         <is>
-          <t>2026-06-12 09:58:55</t>
+          <t>2026-06-12 12:17:49</t>
         </is>
       </c>
     </row>
@@ -5435,46 +5435,46 @@
         <v>4.4</v>
       </c>
       <c r="H20" t="n">
-        <v>1.92</v>
+        <v>1.93</v>
       </c>
       <c r="I20" t="n">
         <v>1.98</v>
       </c>
       <c r="J20" t="n">
-        <v>3.85</v>
+        <v>3.8</v>
       </c>
       <c r="K20" t="n">
         <v>4.1</v>
       </c>
       <c r="L20" t="n">
-        <v>1.33</v>
+        <v>1.34</v>
       </c>
       <c r="M20" t="n">
         <v>1.05</v>
       </c>
       <c r="N20" t="n">
-        <v>4.9</v>
+        <v>4.7</v>
       </c>
       <c r="O20" t="n">
-        <v>1.24</v>
+        <v>1.25</v>
       </c>
       <c r="P20" t="n">
-        <v>2.3</v>
+        <v>2.24</v>
       </c>
       <c r="Q20" t="n">
-        <v>1.72</v>
+        <v>1.76</v>
       </c>
       <c r="R20" t="n">
-        <v>1.53</v>
+        <v>1.5</v>
       </c>
       <c r="S20" t="n">
-        <v>2.78</v>
+        <v>2.84</v>
       </c>
       <c r="T20" t="n">
-        <v>1.66</v>
+        <v>1.68</v>
       </c>
       <c r="U20" t="n">
-        <v>2.32</v>
+        <v>2.26</v>
       </c>
       <c r="V20" t="n">
         <v>2.02</v>
@@ -5483,7 +5483,7 @@
         <v>1.29</v>
       </c>
       <c r="X20" t="n">
-        <v>19.5</v>
+        <v>19</v>
       </c>
       <c r="Y20" t="n">
         <v>11.5</v>
@@ -5492,16 +5492,16 @@
         <v>14</v>
       </c>
       <c r="AA20" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="AB20" t="n">
-        <v>19</v>
+        <v>18.5</v>
       </c>
       <c r="AC20" t="n">
-        <v>9.4</v>
+        <v>9</v>
       </c>
       <c r="AD20" t="n">
-        <v>12</v>
+        <v>11.5</v>
       </c>
       <c r="AE20" t="n">
         <v>22</v>
@@ -5513,34 +5513,34 @@
         <v>19</v>
       </c>
       <c r="AH20" t="n">
-        <v>16.5</v>
+        <v>16</v>
       </c>
       <c r="AI20" t="n">
-        <v>36</v>
+        <v>30</v>
       </c>
       <c r="AJ20" t="n">
-        <v>900</v>
+        <v>100</v>
       </c>
       <c r="AK20" t="n">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="AL20" t="n">
-        <v>46</v>
+        <v>50</v>
       </c>
       <c r="AM20" t="n">
         <v>95</v>
       </c>
       <c r="AN20" t="n">
-        <v>38</v>
+        <v>44</v>
       </c>
       <c r="AO20" t="n">
-        <v>10.5</v>
+        <v>11.5</v>
       </c>
       <c r="AP20" t="n">
-        <v>16.5</v>
+        <v>15.5</v>
       </c>
       <c r="AQ20" t="n">
-        <v>9.800000000000001</v>
+        <v>9.4</v>
       </c>
       <c r="AR20" t="n">
         <v>11.5</v>
@@ -5549,16 +5549,16 @@
         <v>21</v>
       </c>
       <c r="AT20" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AU20" t="n">
-        <v>8.199999999999999</v>
+        <v>7.8</v>
       </c>
       <c r="AV20" t="n">
         <v>10</v>
       </c>
       <c r="AW20" t="n">
-        <v>15.5</v>
+        <v>16</v>
       </c>
       <c r="AX20" t="n">
         <v>27</v>
@@ -5567,34 +5567,34 @@
         <v>15.5</v>
       </c>
       <c r="AZ20" t="n">
-        <v>13</v>
+        <v>13.5</v>
       </c>
       <c r="BA20" t="n">
         <v>23</v>
       </c>
       <c r="BB20" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="BC20" t="n">
-        <v>20</v>
+        <v>34</v>
       </c>
       <c r="BD20" t="n">
         <v>36</v>
       </c>
       <c r="BE20" t="n">
-        <v>9.199999999999999</v>
+        <v>10</v>
       </c>
       <c r="BF20" t="n">
         <v>16</v>
       </c>
       <c r="BG20" t="n">
-        <v>9</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BH20" t="n">
-        <v>4.1</v>
+        <v>3.95</v>
       </c>
       <c r="BI20" t="n">
-        <v>3.1</v>
+        <v>3</v>
       </c>
       <c r="BJ20" t="n">
         <v>9.6</v>
@@ -5606,7 +5606,7 @@
         <v>1000</v>
       </c>
       <c r="BM20" t="n">
-        <v>9</v>
+        <v>9.6</v>
       </c>
       <c r="BN20" t="n">
         <v>8</v>
@@ -5615,19 +5615,19 @@
         <v>5.8</v>
       </c>
       <c r="BP20" t="n">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="BQ20" t="n">
-        <v>7.6</v>
+        <v>8</v>
       </c>
       <c r="BR20" t="n">
         <v>40</v>
       </c>
       <c r="BS20" t="n">
-        <v>8</v>
+        <v>8.4</v>
       </c>
       <c r="BT20" t="n">
-        <v>5.1</v>
+        <v>5</v>
       </c>
       <c r="BU20" t="n">
         <v>4.2</v>
@@ -5636,23 +5636,23 @@
         <v>13.5</v>
       </c>
       <c r="BW20" t="n">
-        <v>9.4</v>
+        <v>9.6</v>
       </c>
       <c r="BX20" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="BY20" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="BZ20" t="n">
+        <v>21</v>
+      </c>
+      <c r="CA20" t="n">
         <v>7</v>
       </c>
-      <c r="BZ20" t="n">
-        <v>19.5</v>
-      </c>
-      <c r="CA20" t="n">
-        <v>6.6</v>
-      </c>
       <c r="CB20" t="inlineStr">
         <is>
-          <t>2026-06-12 09:58:55</t>
+          <t>2026-06-12 12:17:49</t>
         </is>
       </c>
     </row>
@@ -5683,58 +5683,58 @@
         </is>
       </c>
       <c r="F21" t="n">
-        <v>2.44</v>
+        <v>2.48</v>
       </c>
       <c r="G21" t="n">
-        <v>2.54</v>
+        <v>2.6</v>
       </c>
       <c r="H21" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="I21" t="n">
+        <v>3.45</v>
+      </c>
+      <c r="J21" t="n">
+        <v>3.15</v>
+      </c>
+      <c r="K21" t="n">
         <v>3.3</v>
       </c>
-      <c r="I21" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="J21" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="K21" t="n">
-        <v>3.35</v>
-      </c>
       <c r="L21" t="n">
-        <v>1.51</v>
+        <v>1.53</v>
       </c>
       <c r="M21" t="n">
         <v>1.11</v>
       </c>
       <c r="N21" t="n">
-        <v>3.05</v>
+        <v>3</v>
       </c>
       <c r="O21" t="n">
-        <v>1.46</v>
+        <v>1.49</v>
       </c>
       <c r="P21" t="n">
-        <v>1.67</v>
+        <v>1.65</v>
       </c>
       <c r="Q21" t="n">
-        <v>2.4</v>
+        <v>2.46</v>
       </c>
       <c r="R21" t="n">
-        <v>1.24</v>
+        <v>1.23</v>
       </c>
       <c r="S21" t="n">
-        <v>4.7</v>
+        <v>4.9</v>
       </c>
       <c r="T21" t="n">
-        <v>1.98</v>
+        <v>2.02</v>
       </c>
       <c r="U21" t="n">
-        <v>1.9</v>
+        <v>1.89</v>
       </c>
       <c r="V21" t="n">
         <v>1.4</v>
       </c>
       <c r="W21" t="n">
-        <v>1.65</v>
+        <v>1.63</v>
       </c>
       <c r="X21" t="n">
         <v>13.5</v>
@@ -5749,7 +5749,7 @@
         <v>900</v>
       </c>
       <c r="AB21" t="n">
-        <v>8.800000000000001</v>
+        <v>10.5</v>
       </c>
       <c r="AC21" t="n">
         <v>9</v>
@@ -5785,22 +5785,22 @@
         <v>580</v>
       </c>
       <c r="AN21" t="n">
-        <v>32</v>
+        <v>55</v>
       </c>
       <c r="AO21" t="n">
-        <v>600</v>
+        <v>500</v>
       </c>
       <c r="AP21" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="AQ21" t="n">
         <v>9</v>
       </c>
-      <c r="AQ21" t="n">
-        <v>9.4</v>
-      </c>
       <c r="AR21" t="n">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="AS21" t="n">
-        <v>4.7</v>
+        <v>23</v>
       </c>
       <c r="AT21" t="n">
         <v>7.4</v>
@@ -5809,22 +5809,22 @@
         <v>6.4</v>
       </c>
       <c r="AV21" t="n">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="AW21" t="n">
-        <v>4.6</v>
+        <v>20</v>
       </c>
       <c r="AX21" t="n">
-        <v>13</v>
+        <v>13.5</v>
       </c>
       <c r="AY21" t="n">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="AZ21" t="n">
         <v>10.5</v>
       </c>
       <c r="BA21" t="n">
-        <v>4.7</v>
+        <v>4.8</v>
       </c>
       <c r="BB21" t="n">
         <v>14.5</v>
@@ -5833,22 +5833,22 @@
         <v>13</v>
       </c>
       <c r="BD21" t="n">
-        <v>4.6</v>
+        <v>4.7</v>
       </c>
       <c r="BE21" t="n">
         <v>4.8</v>
       </c>
       <c r="BF21" t="n">
-        <v>5.4</v>
+        <v>10.5</v>
       </c>
       <c r="BG21" t="n">
         <v>8.6</v>
       </c>
       <c r="BH21" t="n">
-        <v>2.94</v>
+        <v>2.88</v>
       </c>
       <c r="BI21" t="n">
-        <v>2.5</v>
+        <v>2.44</v>
       </c>
       <c r="BJ21" t="n">
         <v>10.5</v>
@@ -5860,16 +5860,16 @@
         <v>1000</v>
       </c>
       <c r="BM21" t="n">
-        <v>15.5</v>
+        <v>15</v>
       </c>
       <c r="BN21" t="n">
-        <v>5.2</v>
+        <v>5.3</v>
       </c>
       <c r="BO21" t="n">
         <v>4</v>
       </c>
       <c r="BP21" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="BQ21" t="n">
         <v>9.4</v>
@@ -5884,7 +5884,7 @@
         <v>6.4</v>
       </c>
       <c r="BU21" t="n">
-        <v>4.8</v>
+        <v>4.7</v>
       </c>
       <c r="BV21" t="n">
         <v>1000</v>
@@ -5896,7 +5896,7 @@
         <v>1000</v>
       </c>
       <c r="BY21" t="n">
-        <v>12.5</v>
+        <v>12</v>
       </c>
       <c r="BZ21" t="n">
         <v>1000</v>
@@ -5906,7 +5906,7 @@
       </c>
       <c r="CB21" t="inlineStr">
         <is>
-          <t>2026-06-12 09:58:55</t>
+          <t>2026-06-12 12:17:49</t>
         </is>
       </c>
     </row>
@@ -5943,224 +5943,224 @@
         <v>4.1</v>
       </c>
       <c r="H22" t="n">
-        <v>1.99</v>
+        <v>2.02</v>
       </c>
       <c r="I22" t="n">
-        <v>2.06</v>
+        <v>2.08</v>
       </c>
       <c r="J22" t="n">
-        <v>3.85</v>
+        <v>3.7</v>
       </c>
       <c r="K22" t="n">
-        <v>4.1</v>
+        <v>3.95</v>
       </c>
       <c r="L22" t="n">
-        <v>1.34</v>
+        <v>1.37</v>
       </c>
       <c r="M22" t="n">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="N22" t="n">
-        <v>4.8</v>
+        <v>4.4</v>
       </c>
       <c r="O22" t="n">
-        <v>1.24</v>
+        <v>1.27</v>
       </c>
       <c r="P22" t="n">
-        <v>2.3</v>
+        <v>2.14</v>
       </c>
       <c r="Q22" t="n">
-        <v>1.73</v>
+        <v>1.84</v>
       </c>
       <c r="R22" t="n">
-        <v>1.51</v>
+        <v>1.43</v>
       </c>
       <c r="S22" t="n">
-        <v>2.86</v>
+        <v>3.15</v>
       </c>
       <c r="T22" t="n">
-        <v>1.65</v>
+        <v>1.69</v>
       </c>
       <c r="U22" t="n">
-        <v>2.36</v>
+        <v>2.22</v>
       </c>
       <c r="V22" t="n">
-        <v>1.94</v>
+        <v>1.92</v>
       </c>
       <c r="W22" t="n">
         <v>1.32</v>
       </c>
       <c r="X22" t="n">
-        <v>22</v>
+        <v>18.5</v>
       </c>
       <c r="Y22" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="Z22" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="AA22" t="n">
         <v>25</v>
       </c>
       <c r="AB22" t="n">
-        <v>19</v>
+        <v>16.5</v>
       </c>
       <c r="AC22" t="n">
-        <v>9.199999999999999</v>
+        <v>8.6</v>
       </c>
       <c r="AD22" t="n">
         <v>11.5</v>
       </c>
       <c r="AE22" t="n">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="AF22" t="n">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="AG22" t="n">
-        <v>16.5</v>
+        <v>17</v>
       </c>
       <c r="AH22" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="AI22" t="n">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="AJ22" t="n">
-        <v>75</v>
+        <v>140</v>
       </c>
       <c r="AK22" t="n">
+        <v>48</v>
+      </c>
+      <c r="AL22" t="n">
+        <v>55</v>
+      </c>
+      <c r="AM22" t="n">
+        <v>200</v>
+      </c>
+      <c r="AN22" t="n">
         <v>44</v>
       </c>
-      <c r="AL22" t="n">
-        <v>46</v>
-      </c>
-      <c r="AM22" t="n">
-        <v>75</v>
-      </c>
-      <c r="AN22" t="n">
-        <v>36</v>
-      </c>
       <c r="AO22" t="n">
-        <v>11.5</v>
+        <v>13.5</v>
       </c>
       <c r="AP22" t="n">
-        <v>17.5</v>
+        <v>15</v>
       </c>
       <c r="AQ22" t="n">
-        <v>9.800000000000001</v>
+        <v>9</v>
       </c>
       <c r="AR22" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="AS22" t="n">
         <v>20</v>
       </c>
       <c r="AT22" t="n">
-        <v>15</v>
+        <v>13.5</v>
       </c>
       <c r="AU22" t="n">
-        <v>7.8</v>
+        <v>7.4</v>
       </c>
       <c r="AV22" t="n">
-        <v>9.199999999999999</v>
+        <v>9.6</v>
       </c>
       <c r="AW22" t="n">
-        <v>16.5</v>
+        <v>18</v>
       </c>
       <c r="AX22" t="n">
         <v>25</v>
       </c>
       <c r="AY22" t="n">
-        <v>13.5</v>
+        <v>14</v>
       </c>
       <c r="AZ22" t="n">
-        <v>13.5</v>
+        <v>15.5</v>
       </c>
       <c r="BA22" t="n">
-        <v>23</v>
+        <v>16.5</v>
       </c>
       <c r="BB22" t="n">
-        <v>9</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BC22" t="n">
-        <v>8.199999999999999</v>
+        <v>20</v>
       </c>
       <c r="BD22" t="n">
+        <v>22</v>
+      </c>
+      <c r="BE22" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="BF22" t="n">
+        <v>32</v>
+      </c>
+      <c r="BG22" t="n">
+        <v>11</v>
+      </c>
+      <c r="BH22" t="n">
+        <v>3.85</v>
+      </c>
+      <c r="BI22" t="n">
+        <v>3.05</v>
+      </c>
+      <c r="BJ22" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="BK22" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="BL22" t="n">
+        <v>110</v>
+      </c>
+      <c r="BM22" t="n">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="BN22" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="BO22" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="BP22" t="n">
+        <v>32</v>
+      </c>
+      <c r="BQ22" t="n">
+        <v>8</v>
+      </c>
+      <c r="BR22" t="n">
+        <v>40</v>
+      </c>
+      <c r="BS22" t="n">
         <v>8.4</v>
       </c>
-      <c r="BE22" t="n">
-        <v>28</v>
-      </c>
-      <c r="BF22" t="n">
-        <v>30</v>
-      </c>
-      <c r="BG22" t="n">
-        <v>9.6</v>
-      </c>
-      <c r="BH22" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="BI22" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="BJ22" t="n">
-        <v>9.4</v>
-      </c>
-      <c r="BK22" t="n">
-        <v>4.9</v>
-      </c>
-      <c r="BL22" t="n">
-        <v>95</v>
-      </c>
-      <c r="BM22" t="n">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="BN22" t="n">
-        <v>7.8</v>
-      </c>
-      <c r="BO22" t="n">
-        <v>5.8</v>
-      </c>
-      <c r="BP22" t="n">
-        <v>30</v>
-      </c>
-      <c r="BQ22" t="n">
+      <c r="BT22" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="BU22" t="n">
+        <v>3.95</v>
+      </c>
+      <c r="BV22" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="BW22" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="BX22" t="n">
+        <v>27</v>
+      </c>
+      <c r="BY22" t="n">
         <v>7.6</v>
       </c>
-      <c r="BR22" t="n">
-        <v>38</v>
-      </c>
-      <c r="BS22" t="n">
-        <v>8</v>
-      </c>
-      <c r="BT22" t="n">
-        <v>5.2</v>
-      </c>
-      <c r="BU22" t="n">
-        <v>4</v>
-      </c>
-      <c r="BV22" t="n">
-        <v>14</v>
-      </c>
-      <c r="BW22" t="n">
-        <v>5.9</v>
-      </c>
-      <c r="BX22" t="n">
-        <v>25</v>
-      </c>
-      <c r="BY22" t="n">
+      <c r="BZ22" t="n">
+        <v>22</v>
+      </c>
+      <c r="CA22" t="n">
         <v>7.2</v>
       </c>
-      <c r="BZ22" t="n">
-        <v>19.5</v>
-      </c>
-      <c r="CA22" t="n">
-        <v>6.6</v>
-      </c>
       <c r="CB22" t="inlineStr">
         <is>
-          <t>2026-06-12 09:58:55</t>
+          <t>2026-06-12 12:17:49</t>
         </is>
       </c>
     </row>
@@ -6197,7 +6197,7 @@
         <v>5</v>
       </c>
       <c r="H23" t="n">
-        <v>1.85</v>
+        <v>1.86</v>
       </c>
       <c r="I23" t="n">
         <v>1.91</v>
@@ -6209,34 +6209,34 @@
         <v>3.9</v>
       </c>
       <c r="L23" t="n">
-        <v>1.4</v>
+        <v>1.41</v>
       </c>
       <c r="M23" t="n">
         <v>1.07</v>
       </c>
       <c r="N23" t="n">
-        <v>4</v>
+        <v>3.95</v>
       </c>
       <c r="O23" t="n">
-        <v>1.3</v>
+        <v>1.31</v>
       </c>
       <c r="P23" t="n">
-        <v>2.02</v>
+        <v>2</v>
       </c>
       <c r="Q23" t="n">
-        <v>1.91</v>
+        <v>1.94</v>
       </c>
       <c r="R23" t="n">
-        <v>1.39</v>
+        <v>1.38</v>
       </c>
       <c r="S23" t="n">
-        <v>3.35</v>
+        <v>3.45</v>
       </c>
       <c r="T23" t="n">
         <v>1.81</v>
       </c>
       <c r="U23" t="n">
-        <v>2.08</v>
+        <v>2.06</v>
       </c>
       <c r="V23" t="n">
         <v>2.08</v>
@@ -6260,7 +6260,7 @@
         <v>17.5</v>
       </c>
       <c r="AC23" t="n">
-        <v>8.800000000000001</v>
+        <v>8.6</v>
       </c>
       <c r="AD23" t="n">
         <v>11</v>
@@ -6272,16 +6272,16 @@
         <v>38</v>
       </c>
       <c r="AG23" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="AH23" t="n">
-        <v>19.5</v>
+        <v>19</v>
       </c>
       <c r="AI23" t="n">
         <v>38</v>
       </c>
       <c r="AJ23" t="n">
-        <v>500</v>
+        <v>330</v>
       </c>
       <c r="AK23" t="n">
         <v>65</v>
@@ -6290,7 +6290,7 @@
         <v>75</v>
       </c>
       <c r="AM23" t="n">
-        <v>380</v>
+        <v>200</v>
       </c>
       <c r="AN23" t="n">
         <v>90</v>
@@ -6302,40 +6302,40 @@
         <v>12.5</v>
       </c>
       <c r="AQ23" t="n">
-        <v>7.8</v>
+        <v>8</v>
       </c>
       <c r="AR23" t="n">
         <v>10</v>
       </c>
       <c r="AS23" t="n">
-        <v>18</v>
+        <v>18.5</v>
       </c>
       <c r="AT23" t="n">
-        <v>13.5</v>
+        <v>14.5</v>
       </c>
       <c r="AU23" t="n">
-        <v>7.2</v>
+        <v>7.4</v>
       </c>
       <c r="AV23" t="n">
-        <v>8.800000000000001</v>
+        <v>9</v>
       </c>
       <c r="AW23" t="n">
-        <v>16.5</v>
+        <v>17</v>
       </c>
       <c r="AX23" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="AY23" t="n">
-        <v>15.5</v>
+        <v>13</v>
       </c>
       <c r="AZ23" t="n">
-        <v>15.5</v>
+        <v>13</v>
       </c>
       <c r="BA23" t="n">
         <v>24</v>
       </c>
       <c r="BB23" t="n">
-        <v>9</v>
+        <v>9.6</v>
       </c>
       <c r="BC23" t="n">
         <v>38</v>
@@ -6344,19 +6344,19 @@
         <v>42</v>
       </c>
       <c r="BE23" t="n">
-        <v>8.800000000000001</v>
+        <v>9.6</v>
       </c>
       <c r="BF23" t="n">
-        <v>12.5</v>
+        <v>23</v>
       </c>
       <c r="BG23" t="n">
         <v>10.5</v>
       </c>
       <c r="BH23" t="n">
-        <v>3.65</v>
+        <v>3.55</v>
       </c>
       <c r="BI23" t="n">
-        <v>3.1</v>
+        <v>3.05</v>
       </c>
       <c r="BJ23" t="n">
         <v>10.5</v>
@@ -6365,28 +6365,28 @@
         <v>7.8</v>
       </c>
       <c r="BL23" t="n">
-        <v>1000</v>
+        <v>140</v>
       </c>
       <c r="BM23" t="n">
-        <v>9.6</v>
+        <v>10</v>
       </c>
       <c r="BN23" t="n">
         <v>8.4</v>
       </c>
       <c r="BO23" t="n">
-        <v>4.6</v>
+        <v>4.7</v>
       </c>
       <c r="BP23" t="n">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="BQ23" t="n">
-        <v>8.199999999999999</v>
+        <v>8.4</v>
       </c>
       <c r="BR23" t="n">
         <v>50</v>
       </c>
       <c r="BS23" t="n">
-        <v>8.6</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BT23" t="n">
         <v>4.7</v>
@@ -6395,26 +6395,26 @@
         